--- a/Work/policy/runs_results.xlsx
+++ b/Work/policy/runs_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,306 @@
         <v>10</v>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>[2.1898653507232666, 2.115781784057617, 1.3163961172103882, 0.9352938532829285, 2.3865208625793457, 2.1071066856384277, 3.0306177139282227, 1.7363721132278442, 1.7339071035385132, 1.2700375318527222]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACL_MetaDrive__ppo__1__resample-1.0__1773336805</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:35:45</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.096482752779269</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.537081108414607</v>
+      </c>
+      <c r="N4" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>40</v>
+      </c>
+      <c r="P4" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>[0.8374036766248485, 1.078334549426888, 0.995441163566569, 0.5744326807688841, 1.6702731132557975, 1.218901811106923, 0.6073583674391688, 0.661782163484083, 1.4241363123165995, 0.4654379469020727, 0.6952628610995237, 0.6359194567035686, 0.7839298229903975, 1.798758722551923, 2.1521376670629966, 0.9529229008177345, 1.7376615739889585, 1.4638080548253536, 1.778523251456749, 1.8785324795826421, 2.009454476082758, 0.5561290681181337, 0.769483395165944, 1.0826301750314689, 0.8506247162511977, 0.4833931764439908, 0.908630550624271, 0.6837362745292764, 0.8239713172340413, 0.6465285777814483, 1.044123696098036, 1.4140389343873245, 1.0108865031769307, 1.6587572746867092, 1.1373398259453424, 0.0494178522138108, 2.526089737582094, 1.4307339077119943, 0.7567087043439138, 0.6056733717903844]</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1.703704625368118</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7069272060192943</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>[1.9720274209976196, 1.2107954025268555, 2.1133313179016113, 0.8317867517471313, 0.6888299584388733, 1.9322724342346191, 1.7434097528457642, 2.809575080871582, 2.7023940086364746, 1.0326241254806519]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACL_MetaDrive__ppo__1__resample0.25__1773336950</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:38:08</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.058075243535574</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.482355046185963</v>
+      </c>
+      <c r="N5" t="n">
+        <v>96.97619047619048</v>
+      </c>
+      <c r="O5" t="n">
+        <v>42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>[0.8374036766248485, 0.8444592635174868, 1.1292439187573096, 0.816200043106008, 1.770234380186855, 1.3278803532780654, 0.7210871989871477, 1.7284064534661245, 0.710278227387187, 0.2753880391694992, 0.8174954341303233, 0.5999949249392114, 1.6693055467130422, 1.8028417065041173, 1.2669477689632833, 2.0190577207466616, 1.070580181307963, 1.6230305276380863, 0.7614886252684292, 1.665934123554001, 1.6270769216141765, 0.6230102671758053, 0.28485145736239514, 1.2894007771281186, 0.9944573651669629, 1.0295516234674704, 1.345435165151819, 0.574067895339546, 0.7055395030418565, 0.7668994626248564, 0.9366785082983813, 0.979483252930763, 0.9429412960476253, 0.9824575612248967, 0.4860305037504436, 0.2877642191909504, 1.026021282684967, 1.4063220454007381, 1.527906251013189, 2.0778149515672784, 0.8838027961460526, 0.20438900792015702]</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1.671058648824692</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7459984947994835</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>[0.7313354015350342, 1.0346438884735107, 1.456236481666565, 1.7169642448425293, 1.1301178932189941, 0.7952442765235901, 2.0815365314483643, 2.0296669006347656, 2.936178684234619, 2.7986621856689453]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACL_MetaDrive__ppo__1__resample0.5__1773337093</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:40:27</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.112288982305891</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5205586309014635</v>
+      </c>
+      <c r="N6" t="n">
+        <v>98.90243902439025</v>
+      </c>
+      <c r="O6" t="n">
+        <v>41</v>
+      </c>
+      <c r="P6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>[0.8374036766248485, 0.8444592635174868, 1.1292439187573096, 0.816200043106008, 1.770234380186855, 1.3278803532780654, 0.7210871989871477, 1.7284064534661245, 0.710278227387187, 0.7543114497479844, 0.4798174542263331, 0.6244023703933279, 1.822599818000139, 1.7525545078414295, 1.2454425451317637, 2.069121115071968, 1.171301568075612, 1.4636128591107296, 0.8067567858270636, 1.4938471329773333, 1.7602454998134176, 0.6140844857167282, 0.7351533005042188, 1.0190377824427705, 1.1469417491513672, 0.7743038743106174, 1.2007360413169306, 0.6957560941756779, 0.7117372945382958, 0.7391103353488605, 1.480975072944182, 0.8783158622820483, 1.451095287306893, 1.3978801926252205, 0.5414735956826825, 0.5774869836075066, 0.13327488263390358, 2.8041466350374047, 0.8672387253321158, 1.6927126977225082, 0.813180760333446]</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1.598568607866764</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8610455805274631</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>[2.0162370204925537, 0.47628486156463623, 0.23251892626285553, 2.1235005855560303, 1.1892809867858887, 0.8190546035766602, 2.08308482170105, 2.1778481006622314, 3.174619674682617, 1.6932564973831177]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACL_MetaDrive__ppo__1__resample0.75__1773337233</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:43:12</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.228193088175318</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4670063751857588</v>
+      </c>
+      <c r="N7" t="n">
+        <v>108.7567567567568</v>
+      </c>
+      <c r="O7" t="n">
+        <v>37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>[0.8374036766248485, 0.8444592635174868, 1.030513773735713, 0.6904122525552221, 1.2761878837581542, 1.9175400567305143, 0.6077984312334079, 0.9590404999920767, 1.2130032023693995, 0.6274118403616521, 0.8886562710320917, 0.673184344796833, 1.7819745578034965, 1.520368992383798, 1.1835474265150367, 1.5197428078630657, 1.934724546748438, 1.700294917779736, 0.9822849556869981, 1.6700534415306874, 2.270980890123048, 0.6602338134449943, 0.9383360163971074, 0.7557019104691041, 0.9357937215768165, 1.048145856814884, 0.6970152412782714, 1.0839912034030486, 1.1239804915349638, 1.7302259045373474, 1.4239423390513999, 2.021070625679232, 0.6722510951724401, 1.3679577460056298, 1.8132363232265905, 1.9421348929999123, 1.0995430477533052]</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1.882189911603928</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.583760990456122</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>[2.1898653507232666, 2.115781784057617, 1.3163961172103882, 0.9352938532829285, 2.3865208625793457, 2.1071066856384277, 3.0306177139282227, 1.7363721132278442, 1.7339071035385132, 1.2700375318527222]</t>
         </is>

--- a/Work/policy/runs_results.xlsx
+++ b/Work/policy/runs_results.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="2">
@@ -976,79 +976,146 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>p0.75srandom1231</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2026-03-19 16:04:42</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>0.0003</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>ppo</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>90.75461978470474</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>67.21087769566853</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>105.5231256599789</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>4735</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>[1.299442970534115, 0.9242650286220793, 1.12362822991094, 1.2748945868627855, 1.6202752034895118, 0.9170680932342907, 1.0201072426456201, 0.9642534362941488, 0.8072701805092369, 0.5609159351701812, 0.9678233917217578, 1.7334811947102606, 1.7676914621177064, 1.5720809593725253, 2.134607444298924, 1.69896858518717, 0.9549259757172103, 1.8970720085815072, 1.9045028621729911, 0.4223298392725542, 0.6144116388587104, 1.0755350444746086, 0.9434942669838087, 1.1478932057731281, 0.9917901305072447, 1.123726065857584, 0.8140326300759346, 1.6320755370337063, 0.7660029372253463, 1.4433193240537294, 1.42839304440737, 0.9435879973792397, 1.77273157364622, 1.0051758305041816, 1.9083960850451598, 0.7220606113508456, 1.5425301933112219, 1.264892445100116, 1.8599551395552445, 1.0690845877499988, 0.8838361280809942, 1.5322989383329726, 2.3200865002574558, 2.21199972926878, 2.1619543848183223, 1.9255052323668398, 2.9957726094552592, 1.598082524105154, 1.531941284357969, 1.5772595742604427, 2.7958132548435324, 1.7559270581393847, 2.0592679998986205, 2.169556987827566, 2.090051180412207, 2.5241927789621146, 2.41842523364496, 1.005990330547241, 2.587864946632372, 1.9916446084656094, 2.1420745221759336, 1.4717412872456626, 1.6788364816562233, 1.1163329112347178, 1.1991142142659823, 4.658984112602143, 2.8320328298721615, 1.8121696663329956, 1.0364848432841212, 2.1173328570753402, 1.6984131850005864, 3.192883580168828, 2.4373144774873494, 3.346645755333631, 2.7578949886061106, 2.0360609287274687, 1.8461853670753356, 3.052856451725161, 2.7993931213793637, 3.494914841008577, 2.759113098094694, 2.3017548959749754, 3.1171977091111085, 3.6810231150233492, 4.619928460747222, 3.5667772994135456, 3.9545364691012934, 4.076298953570684, 5.841213960836444, 3.0444496137186903, 2.74147665897301, 3.0887726791562065, 2.2995803215059802, 5.464667632164034, 2.9447450333020577, 2.848511933984197, 5.056221302023285, 2.1238336451619695, 2.961598592197947, 0.9410721917448974, 0.5861321405971411, 7.216585311510752, 4.550057394956193, 4.907005966508597, 3.9405928103713936, 4.468400186171093, 2.6911874337811947, 3.450271412860009, 10.278888293875436, 9.075979647623097, 10.138880394732407, 5.546919421690232, 6.2065600282047555, 3.21034984397617, 7.936157899447315, 7.491123073633773, 8.069769877808746, 7.232841282181162, 3.5887482282255627, 2.888365246648476, 10.786743935673542, 3.7619511935791605, 6.435663233816966, 2.8038027150367086, 2.8233766701463527, 8.371337503110404, 8.701802097648663, 6.1726510450125085, 4.096300127186816, 7.19595953070761, 6.181246667870635, 5.472704415874364, 5.40178329094836, 3.032963238591095, 5.733318519141863, 4.576923367053697, 3.242636096462202, 8.706060923532844, 4.628981324332906, 7.031795148903673, 5.880129710900626, 3.97398881104584, 4.806673616474275, 10.921002369947736, 11.681624793520074, 4.508476838581816, 3.5100627742450294, 5.51379635213494, 10.090697291325018, 12.058056212197506, 9.9908314629725, 11.237479098522604, 8.962754266622097, 5.220309289360509, 14.209785604010504, 13.112461710155273, 6.76548065867348, 10.172635606712115, 7.815447099577768, 10.567107283426541, 15.63120211948765, 7.288813994909898, 5.575236331354684, 7.151710807596903, 6.65880989052829, 7.159867008893823, 10.879692997776294, 10.86719739202091, 7.975367387473729, 11.895352777282424, 7.933462529678846, 9.712249874479976, 7.904015627242476, 8.754074343880367, 6.949429681135454, 17.906784996757278, 6.0004344438768085, 10.026678336623723, 11.778933040611353, 13.770251310248666, 11.80029407991272, 13.564801400455304, 11.359277104283803, 12.646557317027899, 21.832605588955204, 9.188918841871097, 14.801429478670476, 18.932181805175905, 10.731251602902164, 19.120734070468984, 17.968050909311884, 10.990621308299907, 21.307883371001836, 30.254815046247003, 13.144978882544214, 25.777699291413793, 22.653511617729148, 18.197408042207623, 25.238022268231674, 8.298627541631499, 11.661296820810257, 26.6192973746, 24.505684874658822, 16.343344628855057, 20.10972840384654, 11.498147796911756, 18.072441255806886, 17.609465571766403, 12.372107581496659, 5.849862558450214, 11.73460183313949, 16.067143787049694, 8.668139849995256, 16.325873433643906, 16.35767472596624, 15.644794461250413, 15.101797935069577, 17.303358025384977, 18.172283616935843, 12.907207651730774, 35.91410593211549, 34.099439979870354, 29.842391626015694, 27.39082855089487, 29.463036353103792, 30.342339414053683, 26.845745708298562, 30.825850002284003, 28.05168650288439, 10.041115534816372, 8.345935687349156, 35.66833891338598, 25.8309429329926, 21.40922381941743, 23.416587848916006, 19.72189977165321, 23.40460349409636, 19.992329230622104, 26.52940664586418, 35.048114882107186, 47.0587348504069, 12.08337474249311, 25.37563365747458, 15.560278380720254, 40.02340183230565, 15.957853910254531, 29.17840148808246, 15.064928491970697, 31.451800587661353, 14.334807526072645, 30.298159560260515, 23.79706781147562, 25.76000523558445, 24.57316271093351, 18.92885261319706, 32.577870277608355, 21.635417044369337, 55.760413073379084, 23.771610709843657, 56.135853069672876, 35.65713470102574, 41.19696921536475, 25.30401200753934, 24.27951311270446, 31.59182881422566, 41.215380068830285, 12.767232257793212, 38.47716104826322, 22.600710061763255, 28.516745749263862, 33.76497055255826, 28.446609057990052, 30.302115650917553, 20.111653673397452, 29.18497263683876, 38.396777999888066, 32.27378589388955, 34.1072567156578, 35.56105274406334, 43.21418394401639, 32.08118194018602, 35.677360708508814, 23.242435412936224, 18.803844115013597, 36.7081594654593, 47.861137111275845, 28.460216032366905, 23.245762727262456, 42.051589522575725, 33.536033651099146, 25.571953417028993, 35.28728973427017, 22.55760760582797, 12.61597535710013, 27.02940872914391, 21.142810075340893, 29.790871200381734, 42.42167692397592, 55.21033710153082, 15.005011721548874, 35.121056430249126, 12.00418733591321, 58.302904387434, 23.72907225941933, 25.462709265496155, 42.288669218723136, 37.801723134110354, 53.60879691874695, 40.74016150829339, 42.41352686964786, 25.979472242515005, 17.188698632380717, 26.967179770105076, 37.2927932719069, 37.962202810812414, 23.331371210546635, 33.202423733419096, 55.07157351668646, 33.34108036982655, 5.008622015050751, 4.781686705103314, 58.043948020606926, 32.54299680031296, 42.05576226150764, 21.630100695689357, 18.73174532074214, 44.370302745518096, 42.74449245568722, 26.913950793982508, 35.18956559164732, 52.79447466291084, 47.47302513703453, 42.64379930877753, 29.751311635286296, 25.444891622842704, 33.33100694771483, 24.39217784218832, 61.86070076869198, 19.73516946601583, 35.28982336929973, 34.47921236396627, 26.31612383074453, 43.08878644278531, 35.71311694857227, 28.085410134719247, 48.97843893419593, 17.764291945052, 28.018964556801727, 24.669251298521473, 24.882162949106316, 34.83112629767116, 20.099637744738438, 33.94063273933182, 37.53840134791584, 32.18902669059011, 33.04983223252823, 30.229604756872863, 54.23303133855073, 39.978895117583306, 58.390799781992136, 31.90827950502552, 27.70847005033227, 33.85649988481415, 59.85759187097741, 89.35282402329273, 36.49181857178372, 41.98771725152491, 39.05014678826906, 35.35678774925792, 35.33742770361992, 42.77880787199321, 40.40883582757039, 53.91140515627098, 35.80859845866236, 89.55826828487696, 81.01738979900892, 33.521531570272195, 44.68521111019893, 24.774762287078257, 18.607059137507253, 69.30792084784308, 30.447171737098177, 67.49404891521057, 68.11535912764712, 20.25884933981441, 50.5291185375236, 37.22663816181516, 30.140351173539084, 28.515699657377596, 36.63102628334285, 71.25457189425873, 33.51754611334671, 27.776267071453805, 27.909700294582755, 69.82621546020337, 32.60005619556792, 69.28532177194532, 75.4436640097749, 61.08661662204542, 73.81349441185161, 58.88649103076485, 30.78051680352343, 49.30931960941643, 31.111289834639635, 48.848150387487195, 72.8736276706957, 65.29718183181825, 29.965092230019973, 58.476544037222, 39.51843640906734, 56.391887192160354, 42.59871147975467, 51.25994764810019, 54.35930322945424, 75.61256635740808, 38.65966568440267, 53.0219012765528, 50.0925196038127, 24.310010914001865, 36.38825304315579, 32.57506197203899, 39.04948106333704, 39.24199559537596, 21.71751030913504, 37.758210440112926, 42.3625918558355, 35.860083192287966, 54.98544979018975, 36.1707360329646, 51.985885063531924, 48.9671987051987, 37.62487960936804, 67.89752043216663, 6.447781184602794, 8.581503219596332, 26.448416136966536, 35.95767820637758, 66.04162130071542, 55.98064990174492, 54.22845406048537, 59.96102199723095, 45.14775305242426, 38.08278812241456, 26.4475595176922, 47.09048101394354, 54.33682950456132, 60.266876608477126, 17.925745621778283, 27.612025597506335, 66.01208476754456, 36.35070830429158, 28.64271991347884, 41.906042623674686, 6.92577209468097, 4.756416253548863, 71.1424279320423, 24.90029251979333, 37.789179175198605, 41.76278378030956, 47.48131534864946, 40.765022589464095, 51.01164393154166, 2.5243786951569143, 3.663312728829526, 50.666222057377915, 66.70357709727263, 35.9007802025535, 65.34197171185149, 35.308477626117714, 33.970029190498096, 65.00544712770774, 30.40018420059492, 18.25811707908801, 18.006637603231482, 115.6250597450168, 57.56871958045248, 40.52400872882455, 55.12481889344275, 70.51399759360464, 42.71600104395106, 45.18176454543708, 29.61101797168633, 29.18406793625104, 40.66527592868476, 51.02198863200574, 86.47686475783692, 32.29971952663433, 44.624028582781335, 46.762204070534395, 76.28724378331003, 78.17691697536075, 43.37977221891368, 62.457457639519816, 64.79159052329786, 73.69420443571954, 31.86754442616419, 39.25291563616291, 43.65608173099885, 60.56635765807719, 60.32786445965821, 29.984054348533313, 69.38843400541124, 76.15990293014306, 21.571823846913386, 51.969816196243976, 33.22699261311309, 29.952210099778206, 77.377758605364, 45.292870634345036, 45.974176761307, 37.87825179559877, 49.044204954093644, 45.90365732750972, 58.46294194092078, 33.500880148028926, 8.844662025291411, 43.046619407395845, 67.05908529326784, 34.255899554502925, 76.69571648502267, 3.7534261922848633, 3.24285219428403, 37.51912308011637, 37.44122879503404, 44.668764793259555, 102.90162425573551, 93.09121961037422, 35.17052883197121, 86.42804097454582, 108.85023984453572, 61.199406421769304, 105.24962614716658, 62.73617537017257, 33.78441808952682, 42.74728019319071, 75.15320131569496, 4.189319072249255, 3.927835161237101, 32.37498045473967, 78.42650544200487, 54.76905944115858, 64.98468737221339, 50.88557741632449, 78.88931548131244, 50.475278854201534, 59.33626835513921, 27.503686269533176, 93.22956196148988, 41.48721402349351, 59.1637742554141, 28.7195775896985, 32.2467451925574, 38.58120682402671, 45.712486201278466, 37.44810614148499, 38.701059304034125, 40.14373622363226, 92.61803304130346, 44.90978768892616, 40.38447064912167, 67.64751181243984, 106.40254878170333, 56.70843549749665, 31.113003794585566, 48.83910760876901, 35.56485333831165, 129.79800071438575, 51.3249796300099, 54.01921724513272, 59.84926770968971, 49.94180298930189, 52.08143285130201, 75.91543345049625, 69.39297363043558, 42.71976418752293, 30.4817807002806, 53.881264654128934, 93.02102117213097, 39.755210935301754, 34.54220892565841, 57.13699865912708, 29.6964864108742, 63.27620601194618, 86.9846980905591, 18.34935087924229, 21.134384003853476, 58.010209752662874, 51.72190741388189, 42.5661183684958, 34.60876916111906, 66.42020680654767, 77.8493632661528, 52.92275985081488, 41.66399993278567, 121.70546975166685, 66.44484397369015, 30.001407024696242, 59.031529231492726, 101.4505102370822, 55.950762458825906, 57.39757840979072, 108.53785856549526, 61.71528861262238, 70.64177569229884, 72.8942702607838, 47.51363108644274, 51.58482696194417, 60.25357389759485, 53.92607826629941, 54.32796438118002, 78.51543069952892, 41.24285525379992, 118.25313765635757, 34.89453758977332, 64.49108473826476, 46.43748934395381, 40.149589834909875, 46.797420827599154, 56.51326657402405, 58.386313755791974, 45.14706169678635, 153.64887382683335, 48.42264299229815, 40.24886054700705, 82.76267955415362, 50.534230739302444, 44.994268987489875, 97.45154228527319, 42.71201673671736, 109.32156941215018, 60.484603148897335, 59.678011963506364, 92.17779543318872, 57.05876892991515, 121.8600842604611, 52.14405640312545, 53.834174854463726, 70.39550522057641, 36.659554838558364, 96.10474873961299, 66.59734615448679, 39.45068520805263, 62.70572319316123, 6.329177176437802, 6.476946945219192, 145.03220732522192, 74.85299378951368, 72.50452947575047, 47.20844396511566, 139.30513454260063, 67.98563161722811, 104.10976825907225, 50.45245931550968, 120.13292963316985, 62.744961168271765, 62.721454999187955, 101.95128339798225, 29.93034672542026, 78.03728472323878, 89.78412051368964, 64.0516885524462, 49.11432388575731, 51.27957160682036, 75.12676772994412, 65.56102298260991, 58.12887700914947, 49.32096492097976, 76.4382923163921, 47.33131512246857, 79.33853093880316, 42.643632771916174, 107.27359953120546, 55.67539645366452, 130.36352537080606, 69.81163482119311, 31.662545415268937, 108.70291730280212, 81.97262108168516, 80.12994072330768, 73.93150857073913, 54.935144676777725, 95.7086864285411, 78.14230158700035, 43.968743739718796, 63.09535274515713, 44.7760617160659, 70.02572975088067, 100.1643547250202, 38.408410465670734, 45.770907736859535, 52.7038329092008, 43.70216848285423, 66.35264083060724, 50.796157071578776, 40.790392259198, 36.96434908309831, 53.07948966479391, 67.00871207607017, 63.22164536191822, 71.97166645352469, 52.56434855551513, 67.59837362826448, 49.692929149059246, 53.02914372848243, 65.64409661704158, 284.84119588593626, 125.91752440519834, 101.4480592131335, 59.08051195304963, 50.89547478318874, 96.9485394212511, 102.25335212082545, 53.04875410435589, 58.89415545849081, 141.7754565092347, 54.04593810751565, 35.423927238302994, 36.31909383760186, 45.463548817235235, 123.52139688045445, 50.323156146629074, 49.41100945831436, 69.32227653704038, 40.63536481766714, 72.01398857981718, 105.51528034082335, 87.1087401274985, 46.079322046972884, 48.5413564253729, 69.07452972903556, 35.90608897790386, 60.779126747717456, 47.06782918056789, 36.21118471550566, 67.09700912475923, 129.8821293170912, 145.23263999279746, 85.6292478427136, 50.75489790897894, 47.23307155856286, 60.171363862298975, 58.97809453764742, 65.1826956611431, 72.59826112109856, 43.16630634774609, 57.98389512683075, 136.15701453036058, 104.12230112640367, 104.99528993046046, 53.53927135658367, 60.33768979292422, 56.334228115131225, 53.53923964719637, 46.572829380881515, 53.507734950486004, 64.38886542138849, 43.526388920792975, 63.28348313137006, 42.062263305447765, 67.64698730513695, 68.71457917186238, 44.319364193116684, 45.47267989457632, 47.99168238093485, 56.04017869349102, 41.00943298870175, 59.64251608379936, 57.493347939535795, 42.29583694526488, 65.75428770226904, 68.03409228756809, 57.51813165034881, 64.72746898115064, 53.10059898486605, 48.01402274288117, 48.19372294571946, 184.36584870490552, 37.14168513307585, 73.27948493892488, 41.874745534190325, 59.97239712566886, 37.0293449581523, 56.66357658193287, 136.8007247136354, 57.04410775008718, 68.43183606744206, 45.434965842792494, 50.09299985679515, 104.88939143750581, 45.8376012144737, 71.01641666099692, 51.741089484087325, 101.91714992484741, 40.78386573337541, 44.44517418802956, 44.55654534787316, 89.65453318072707, 39.72278498325569, 48.254860312571545, 37.272267355782816, 54.68565097146769, 36.65130972641563, 53.285351298831394, 60.03789398996651, 140.2308059227309, 38.19780298550498, 56.00524210182344, 47.4112286727532, 42.74135269121902, 62.15874597983325, 148.55484259751907, 40.8148875492246, 51.61884686156763, 79.97413581004902, 74.32789327603649, 55.94771294355216, 46.06115054728338, 60.13565262596347, 118.38680538539656, 100.88289623223942, 94.1809597104529, 49.724119493905526, 69.2957418040304, 88.1032301446121, 54.21208624905548, 181.89293097693718, 85.85603995123044, 78.68254317465805, 98.22425367031816, 75.52399428844765, 53.909756599553575, 81.05288412022658, 143.49591251313905, 55.78904868839752, 54.195044901484245, 60.52217698615456, 42.26769149817363, 41.25455838933076, 43.362173881475954, 103.92629242905349, 66.15813518499286, 47.50307012293049, 50.325544857009845, 46.092648872235415, 8.843269689085448, 8.96091611835778, 62.54183918214836, 86.2605434319045, 64.9618983856261, 93.12056865562968, 51.36575477299555, 129.49610813706056, 36.74391200778379, 65.29742654381387, 105.99574395992835, 57.5278570980066, 212.18765003676168, 57.64505426665399, 208.57095953529506, 49.66430680071346, 46.01123773866402, 81.72600836799045, 102.80517859759631, 35.810175882827345, 113.88550178893959, 65.13638140151372, 59.33593212658502, 54.02609068766894, 57.02455112410554, 56.59325110242183, 46.95910878209312, 87.20655196797317, 60.41825984570725, 46.24002078889759, 42.389600165316345, 79.65663119032253, 60.35149187730051, 292.910703090919, 41.758870707526455, 80.78007096928916, 165.62006012558348, 70.03261284975679, 138.40834766372154, 55.37800289313476, 73.851735833722, 50.97949371269575, 69.3101204152661, 50.82455358220701, 47.258681873430724, 94.93211364916698, 90.41534279966818, 56.04467817367912, 65.53266824667287, 57.08555398296548, 127.43380519458997, 93.61459687040887, 49.81502477415562, 55.248597682445116, 43.877045774026584, 253.2317427467283, 88.79067494985298, 42.53672576509481, 45.85445054457153, 54.00486110083755, 75.76052833320537, 52.65787539511238, 65.25280465239175, 63.5592917426385, 131.49585630745386, 165.52730192228358, 51.36871609684751, 69.99521072531142, 48.95099529649517, 71.53618515627193, 91.13570369770848, 61.490272276364585, 47.33119186006423, 55.82724708691008, 119.17589204271982, 61.33737905925632, 43.26010863041371, 55.81346084713185, 81.84236171148834, 57.67734198821673, 63.86590970790893, 54.72807431762795, 64.58977654131637, 149.16671288786253, 45.52192486422122, 74.80862818338882, 122.00028747037803, 37.880689241232545, 48.826759131698466, 71.81648991465057, 74.69780862067229, 64.7850157988409, 57.230184318461504, 131.23691921264512, 197.6966691330045, 71.7731039852503, 120.19249016641938, 55.2986503724896, 116.30291296106813, 54.700475165915954, 37.239997185455806, 65.75808984879741, 87.94350706501237, 63.69235923967002, 55.82635655868136, 52.83758697445464, 75.93834375452435, 182.19711571775773, 45.79851737851689, 79.71172700856121, 47.408835099622124, 54.62861210720974, 140.51025685059642, 58.46771087789508, 69.92542752661433, 94.97822514683142, 53.50559777301914, 50.68699615011494, 149.5686543624237, 55.176303702904214, 66.63044931672468, 89.91579425158959, 58.80849675592955, 79.91607352758442, 125.56406271789173, 47.07415876637026, 121.29123346815021, 69.06699397264786, 77.0898250540969, 62.4421859138575, 73.38529100434472, 42.072921633801016, 66.54511057602848, 169.304767403708, 100.34614015901735, 83.40066041121202, 228.82278541645934, 96.90260235588711, 64.65707674421823, 68.22323655513463, 64.00480342220699, 53.189940188482794, 44.539142543656986, 71.2756747106764, 47.50502535414573, 48.56995218904007, 54.35311822299845, 132.77801934417482, 58.41396092447509, 54.74926165197718, 52.75552178055863, 74.71978302432903, 108.38674206525329, 67.23716039667138, 71.83536469795811, 67.84526299012757, 69.05232087227945, 84.12063993736649, 65.56649486896822, 55.7758422869668, 285.31323062030623, 69.8214977167811, 163.04705429728813, 85.29820327234363, 46.38899536598117, 102.39015778291433, 125.49624407071983, 40.58732965473127, 47.02816137371356, 6.516662555567857, 7.148574959809653, 127.75287305582829, 58.12851848187766, 84.92768522762377, 55.22275187509618, 46.561075998304915, 38.77146559686882, 49.681769016194075, 73.05458334736727, 41.86524989799117, 50.805527557921636, 87.94979967518478, 67.63887435345454, 39.75276622785734, 40.52077154794485, 47.32174534156859, 130.40904614493462, 61.77016758273812, 60.720348611064175, 120.54925154426282, 77.65395524979296, 43.752788654714344, 53.577643214742224, 42.910715079311984, 179.28026073554796, 107.87103026426446, 116.77834519657743, 79.13237892170574, 102.0655292061958, 131.59156214125633, 185.07317968097368, 77.6610048682614, 76.9446771997737, 77.26583306760419, 40.47761905029661, 44.68858615075849, 53.879830482435196, 75.34965842938956, 143.50682530535659, 107.1611832962629, 98.48113247127827, 43.307600148713796, 223.72084161217475, 42.653068498291645, 97.15790126008542, 56.819124297001096, 120.70345306489904, 65.9070374171247, 59.37063351473535, 69.5106826121268, 41.557283740494945, 72.69950617739235, 34.188828145374785, 70.17641948556644, 76.04430973746403, 186.27506598388206, 108.76644987237715, 44.780023571991, 73.23161719890857, 66.87735811605695, 58.232700179563416, 72.18689907665056, 61.22704201265133, 40.966635391979345, 200.13503876291352, 26.04714658860759, 29.00730733124971, 48.52770571662195, 112.32026537254998, 80.46060998888747, 33.430205978086725, 56.70036976235504, 82.69728775693694, 168.1965439126936, 43.502441738724, 243.9543232494278, 103.86616684905947, 65.02032747330064, 49.74677992515105, 54.22172513414795, 58.79134690965491, 77.16229500698734, 53.01648125374796, 175.4960806297555, 56.33902033626501, 80.45459097651468, 60.11172133280108, 43.99677485009735, 66.6268196382155, 128.55232311203298, 38.10862910680059, 79.64531067247611, 226.18893109097795, 86.10352387917712, 58.81604691338149, 75.36943970445704, 53.37658037103435, 38.093367093919895, 85.52546161923476, 94.47555158529916, 91.54838399518157, 137.4148725209827, 128.2973471559382, 56.28120869817617, 107.11149849320122, 49.56702212223169, 114.57083136344916, 185.48589845713653, 106.76889279491837, 95.53392387035805, 52.4929645984606, 48.39367698668852, 82.26281837462196, 91.75235362441737, 58.10660915744971, 64.69507369129356, 63.63677672670407, 143.576445097999, 95.94356809980559, 96.44258392624137, 68.30206101457054, 47.4153429134311, 70.48251815271693, 35.87171481983189, 116.0926468636558, 39.38859873361373, 34.02505815242955, 38.65829816094157, 49.517472321707025, 42.155302384642475, 39.470788503992814, 41.47973385219429, 86.68163143115095, 68.05327469267067, 44.98876689580759, 58.409189934243834, 88.12743288271355, 11.531414872555963, 12.188768188488433, 59.13249259660658, 141.56734201942925, 98.97425179087172, 74.53389621983801, 89.17247176727874, 67.1582951101976, 71.05652134367503, 77.35379088471788, 6.623362858601155, 7.08377914290068, 252.55267866824582, 44.46398785228974, 133.45106961449875, 76.88366207875788, 76.07706458770846, 64.69654583519568, 63.99050440144294, 67.90432773884113, 67.1589830673004, 62.15835138996307, 72.4680602470305, 49.70585967920155, 58.23172252939515, 155.23727942808966, 183.70176949485196, 122.47392052036822, 102.93891934025498, 70.52919355026354, 79.07903412001782, 73.32654536775175, 52.84089053163371, 57.81765661981244, 39.38462185553036, 109.4584650568114, 104.6856004541253, 66.74102153743604, 110.03075082728998, 87.05003666666693, 162.51291337275273, 51.492382008624816, 63.55690479622041, 104.75130979686304, 94.31223627291783, 99.78283829019352, 154.3177990126135, 75.27153258211928, 74.02872631896517, 142.3444613090249, 75.40899274174495, 48.49868817444872, 93.47320626504566, 128.14435853128302, 41.19771191245928, 113.46788201569085, 75.22082579574845, 124.76442266092101, 45.32511724669849, 70.67490860444303, 281.18017323512663, 34.51377632188317, 54.66950251438508, 32.97150778983038, 49.4132479797052, 58.416793152363205, 167.97194964807844, 43.39631520775187, 45.042145622964334, 54.75272938791145, 57.27114427850632, 69.7933082185274, 108.45873153674005, 61.9914320515722, 55.618456720066675, 66.55554545274053, 97.28030150462286, 41.43958467749632, 5.457391684480388, 6.162854803833162, 54.87163623971265, 109.37446576925186, 38.80805718420382, 37.72975246948179, 48.32133203809874, 35.79222459680228, 75.07988065488054, 54.109139613032866, 115.88857862661102, 94.25730118145557, 62.08896579558868, 67.97220401434714, 54.595579340028195, 85.32579817495856, 67.04546771743826, 53.96842758163403, 56.35745839676873, 63.88264544328276, 116.24363529084496, 55.83838205631463, 94.59926454232333, 65.34838777227552, 170.0455980484731, 71.27532275825327, 96.74996701075112, 62.53150312749567, 217.25062072242864, 51.34772985632089, 101.2300772306903, 46.64067812835043, 85.87260379838028, 95.3690806877946, 48.68012685575883, 93.4941975285556, 30.57518562886195, 46.426412216318404, 86.18424099398216, 61.469557438584424, 243.7224035396157, 68.27828822935714, 91.84056637873373, 15.223438241238526, 12.666001957991726, 35.85006453019039, 76.63486244407066, 76.86974368049565, 60.406424841204235, 45.52798072399692, 87.67450970702814, 71.01283872021932, 47.04440914647914, 91.06604453481116, 75.50994392718368, 127.63903823968987, 94.69111267902397, 246.57760170556088, 59.00368955494988, 90.06996765528002, 49.651826756323175, 59.67328645444585, 109.29382130116096, 143.18791330008082, 115.33868316010465, 58.15485749929042, 56.50896216960032, 122.62253809297708, 102.37498847143239, 70.78528091652191, 134.35015717785558, 139.92362927684587, 173.24435531647555, 56.39676099764107, 85.98662456548465, 105.758465718937, 55.09811403783638, 103.11275553172857, 49.18315946913488, 65.58341978779353, 71.31221756152004, 60.874160827612386, 46.95083882277269, 92.7267524509579, 69.67878993878082, 47.8327163956097, 49.174131956995694, 69.28984881925155, 81.58698930904315, 40.96643744618771, 116.37912346524043, 112.26934774640111, 142.75619263203555, 61.26570780385023, 78.31157841636168, 64.67437872635693, 44.895994918728434, 98.5898803031006, 128.99209033141062, 44.53733895005189, 82.48358460264886, 90.82103679469756, 39.3768974909712, 84.94935108210393, 63.0084856309972, 100.06136483497514, 86.8068904579816, 198.7869029027234, 48.93948761759872, 98.33392434721266, 47.396401632926384, 75.56256092315374, 43.797922883248, 73.91157298403218, 77.30578265809694, 80.23505224676566, 79.65372862153295, 105.72751951922952, 34.22331179067877, 88.42689613360946, 41.44576922143109, 66.32121509616844, 50.703600695751646, 69.31715058959975, 60.96654195635117, 85.80748437507862, 53.41456918173279, 104.2386753516907, 100.50334267365959, 101.44378026785267, 79.81093588296804, 88.46946230700576, 215.08908520158369, 80.53182117142413, 109.86294287154203, 152.66326362147146, 48.49740712417788, 70.3072479943913, 49.06582886267901, 78.93878168266176, 118.79471030274007, 43.48435262821008, 70.17409235642984, 77.92400547712468, 67.42074935196173, 120.44931404604327, 139.6451902936253, 77.8505136085281, 92.62948731388175, 75.9028852023425, 70.0194260055903, 142.5867585843633, 42.695988314519674, 62.623771753663746, 46.77366151448337, 65.89839144370123, 153.18362855775203, 56.78327576601021, 87.82033184708642, 67.21710867599045, 135.23777946549873, 102.70263814066651, 74.24674172826232, 116.37888065343648, 77.62722443789853, 119.57168152461128, 54.3731677562662, 81.19827858658005, 96.32073801689343, 232.0260644657611, 53.24630947551673, 200.3326409607819, 9.822570041466745, 167.05880316115798, 59.28048353115517, 130.13239872268534, 90.86094358756785, 46.426738869753486, 57.181418571999366, 204.97007996678914, 77.31928405563544, 43.46566076246486, 126.96760973404538, 101.9443584877875, 65.92105877430227, 57.14744712849187, 71.75081275775295, 80.51919105740161, 142.1068229072155, 55.04731551094081, 85.80310313394419, 101.35948886811568, 70.3990492442267, 74.48938683989319, 261.3826695234104, 99.10145004581996, 114.47774228498544, 192.78888697974176, 104.31119045013403, 86.40235988667047, 82.77092817592748, 134.21062107204645, 119.38837011365354, 44.800051146673525, 171.20956509580438, 149.69856559895834, 90.98379866667482, 81.58084284474026, 94.17283785448075, 510.6402459689766, 99.59621570134101, 88.8982843499641, 71.94080971025471, 131.72957675523057, 85.30110567088747, 62.20292015314045, 75.30368878114825, 110.37485212235312, 107.4185079563217, 76.44050979348143, 37.528930493993755, 89.28553407470345, 82.18882695624296, 120.08596510830883, 61.81503414956561, 71.43154992590195, 78.49027825495472, 96.75609862801285, 67.45385233437568, 103.44416389229701, 81.67705412108982, 98.13886269754128, 108.71372389102777, 67.10420557644026, 50.85199933638067, 54.02373427612682, 82.41568895793502, 45.230058363809704, 75.98450113541669, 94.74709408988252, 60.46659984316816, 76.99287469159827, 69.02406805711526, 39.82710440895492, 104.7513335218378, 72.52695403915094, 56.202991558542834, 66.86925189238136, 121.33056600128654, 65.87821118601407, 277.8281206907003, 66.38821332233157, 83.56214254521393, 51.12646895538518, 262.30289592326847, 74.51249602789609, 98.02537970006047, 66.32404473851312, 38.28043226169786, 78.53200016192645, 80.87834516119015, 123.03606004924883, 58.53726901164892, 43.4188078573685, 85.8919082239216, 167.10860639221386, 42.68244840153561, 39.04460898548951, 145.40092965374268, 94.1295257889872, 34.09996835716792, 169.2332433959068, 77.6074169158557, 41.386553462573545, 116.1931095584755, 123.19827739658244, 73.72082807669351, 72.23730191180252, 285.88662892415283, 84.07156656887176, 120.46056209172707, 47.38618099277747, 60.637777157917746, 192.576646420112, 80.71002084505162, 146.22317734856085, 66.69072770167895, 59.89006496139769, 132.10599299190886, 46.12381460568322, 65.22281714292582, 129.5389517496332, 151.5664910401468, 92.49623235683458, 92.44357062031564, 55.749826949973155, 69.63942037030394, 84.42193917158504, 53.349362579149016, 54.51175120338381, 71.18382769528976, 66.96345186222179, 78.66524925640466, 193.02128865407425, 258.0385167407758, 88.95674108719074, 40.68135577397964, 84.8001953217157, 63.18324256790416, 49.5491806870792, 129.26608237049714, 69.74290667551638, 45.487672107087434, 59.21690189607198, 97.7933623858174, 135.00123723558482, 46.56611887266744, 41.520874995184634, 51.78333352209553, 87.12770243795853, 28.427123117539406, 160.1036608434883, 111.16784601364044, 124.78824587277755, 44.29400631687818, 149.73743441787101, 69.96010076300217, 151.62213715163372, 93.47265097783219, 41.019484088549326, 57.999705395065156, 41.23958353951462, 139.81589909049308, 39.60460659143582, 144.67411149345256, 68.92832514905125, 73.15176818397325, 88.78161790061311, 116.7949358469485, 81.63330174223589, 54.49602075937425, 150.1347118324538, 108.37445934366603, 81.78521911713129, 48.17034743109992, 171.71879651337943, 75.05927111210647, 116.71376285852753, 189.53195705383078, 55.631778112951984, 92.6163732735184, 79.60537528352059, 50.27213042573391, 73.83818671692487, 98.60403376168888, 50.64782917804883, 157.00701711684258, 143.1170939846712, 73.62889965920539, 43.847015079256664, 113.69314435598379, 50.37572495706002, 114.46411483513812, 45.10640216575663, 70.9967640755029, 183.92041355074738, 103.75383191472929, 73.2107507330122, 88.19856207753453, 94.69980848120251, 130.0275726519299, 91.4870320851146, 208.2605092155607, 61.607319358519355, 252.08170641691996, 63.64263373617923, 192.79544999819834, 81.29694283184106, 123.98131209164586, 45.099351009728096, 55.43455563386443, 45.70551496896499, 97.82902345337699, 59.19488221614585, 126.9033271620922, 84.57940035090645, 87.3123647456313, 138.37699885043497, 73.95962845281582, 43.44424936816832, 105.87308030242633, 7.851702475355082, 8.932386189588163, 60.85416313650693, 58.35966023754927, 178.83836952947763, 67.82005661414068, 54.622925440452796, 286.0306396159791, 122.51872089313444, 190.03070903046358, 78.46306431924035, 98.45453105052931, 13.1136635864336, 13.501563696124023, 65.3507172016375, 88.48485307525291, 121.50133005805085, 145.4183780926679, 178.74899076579112, 98.15396675466565, 93.8727578781647, 53.4230997843519, 47.52892247194773, 73.28392762867225, 40.37609278621196, 147.16988375984343, 106.04833893931696, 84.14678359542698, 71.31860270410922, 108.26014670942683, 187.60445358923113, 75.3044385779144, 65.49180883351166, 51.06347234465788, 45.460709081764875, 77.55522291943478, 51.27253828944625, 86.04732090394285, 45.85549234435291, 45.46721510516743, 55.39407996851434, 77.79010008422111, 90.34625623994987, 140.695790825201, 104.92194055773422, 198.12861469757314, 33.90082211577253, 51.518211073407315, 95.20399718252423, 106.7279471084375, 73.30830010758842, 254.21849148672493, 97.26528839589331, 145.7082170699157, 95.20738341436615, 22.384867148611953, 23.269770104500694, 102.81659984826709, 46.69084073359076, 71.82014632925801, 82.01752656318986, 32.62650554790432, 163.01326615022256, 36.305398747314186, 10.245543972428187, 9.693697211658565, 128.87189890667742, 37.271775765152476, 76.82576973551201, 56.44204420769854, 110.33938966890261, 96.87162963316794, 195.93342843667259, 68.22216503192247, 112.55504751320815, 94.39232937668568, 75.00163885678371, 225.81802929834316, 49.63175840125541, 62.572766158957364, 109.16615019050198, 132.654791</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="3" t="n">
         <v>123.3914333343506</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="3" t="n">
         <v>57.51475047808284</v>
       </c>
-      <c r="T9" t="n">
-        <v>10</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="T9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>[120.61085510253906, 147.2869110107422, 50.89359664916992, 196.46749877929688, 65.52867126464844, 219.75584411621094, 39.56925964355469, 126.93525695800781, 165.2930908203125, 101.57334899902344]</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>p-1.0shalton2118</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-24 21:21:11</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.183065603014852</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5211024971331032</v>
+      </c>
+      <c r="N10" t="n">
+        <v>106.2631578947368</v>
+      </c>
+      <c r="O10" t="n">
+        <v>38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>[1.0279017306107405, 1.1069428575895663, 1.102887579488172, 0.5255031190730329, 1.8556245880033027, 1.3473975718733877, 0.5094010216220801, 1.7022731783341198, 0.6029745261802829, 0.4281843647253538, 0.7760156169209359, 0.6110677948885319, 1.878591349846404, 2.331854910164841, 1.2721659274641721, 1.6665073055734767, 1.19079453691316, 1.464521078238047, 1.3793445426293414, 1.9345053887238055, 0.926109334437943, 0.3705093887164873, 1.4854944139683282, 1.416748887243379, 1.053260340917286, 0.37237557739556115, 0.5768926841260956, 0.9320532799114819, 0.7844862921441665, 1.539989444796599, 0.921544514320304, 1.4478690084925143, 1.4947647210894344, 1.0060356579060168, 2.3828062964098375, 1.0885134098357379, 1.7405196222649206, 0.7020610517255315]</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="1048557" ht="12.75" customHeight="1" s="2"/>
     <row r="1048558" ht="12.75" customHeight="1" s="2"/>

--- a/Work/policy/runs_results.xlsx
+++ b/Work/policy/runs_results.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="2">
@@ -1051,71 +1051,971 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>p-1.0shalton2118</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>2026-03-24 21:21:11</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>4096</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>0.0003</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>ppo</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>100</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>1.183065603014852</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>0.5211024971331032</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>106.2631578947368</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>[1.0279017306107405, 1.1069428575895663, 1.102887579488172, 0.5255031190730329, 1.8556245880033027, 1.3473975718733877, 0.5094010216220801, 1.7022731783341198, 0.6029745261802829, 0.4281843647253538, 0.7760156169209359, 0.6110677948885319, 1.878591349846404, 2.331854910164841, 1.2721659274641721, 1.6665073055734767, 1.19079453691316, 1.464521078238047, 1.3793445426293414, 1.9345053887238055, 0.926109334437943, 0.3705093887164873, 1.4854944139683282, 1.416748887243379, 1.053260340917286, 0.37237557739556115, 0.5768926841260956, 0.9320532799114819, 0.7844862921441665, 1.539989444796599, 0.921544514320304, 1.4478690084925143, 1.4947647210894344, 1.0060356579060168, 2.3828062964098375, 1.0885134098357379, 1.7405196222649206, 0.7020610517255315]</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandom0824</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:14:28</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>92.08489446510939</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>76.83153280779486</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>99.96039207841568</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>4999</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.8011264649045112, 1.0397675265229656, 0.6921087159347381, 1.1879087140858136, 1.370542536850724, 1.1467446345530485, 0.3101272008032878, 1.677466696456907, 0.10968628275483673, 0.9739010137751829, 0.09134106012846353, 0.8738299798298741, 0.5791869550466108, 1.6631660359728209, 1.687047905785643, 1.4143520046857145, 2.453902457950901, 1.162286198703704, 1.8301598262763996, 2.2871241272206766, 2.383629646350758, 0.38326341737085773, 0.8065916720012456, 1.1502051566957152, 0.3902932823212479, 0.8181783921990464, 1.0168992680820794, 0.6126925980238034, 0.866796133315289, 1.1671784421346127, 1.429448898424296, 1.0371042599417104, 0.7706399286448635, 1.4353685291368015, 1.0092744268480849, 2.383923134277688, 1.3960381406156668, 1.7707493650856978, 0.5135670005957425, 1.6537541102970204, 0.9125980016425912, 1.7378585747918138, 1.464022927906812, 0.2099145581936257, 0.8695553407243071, 2.0565863202183836, 2.1365567814921724, 2.9589193009266412, 1.8634880492918302, 1.5986372577754466, 1.3128611770742944, 2.42098492613957, 1.83677922059439, 1.877694580786745, 2.1511000908966778, 2.25423919449781, 0.8741750549342305, 1.372107059660986, 1.217919491868586, 2.2538366250645656, 0.39159556515185023, 1.6986038691124017, 2.048175746913967, 1.3632789837605974, 1.967574340514835, 1.550380874145835, 1.0544014076429726, 1.8799628312601697, 1.2665415604100014, 1.2599089908296845, 1.2500666934185438, 1.6938076668783904, 3.359980234885317, 3.692934934316, 1.1235018347186292, 0.31808944477619605, 0.8127957309707153, 0.605883319276753, 1.2459912058299738, 3.054819700227895, 1.8061144232045865, 2.7881600242508138, 2.047698435305375, 2.5238624166732673, 2.211664315301465, 3.5288665822178027, 1.73515225324838, 3.4888596343795206, 4.65594977505233, 4.8123229038231425, 2.3690215715360954, 1.549978042958345, 2.930826111194118, 3.0967379163558535, 4.810440824965912, 2.830100973045164, 3.479537919056316, 3.6450962217068286, 3.763129222365414, 5.695815855980006, 2.7280921188014147, 2.7984642941890647, 2.4269542235353456, 0.8256642458504101, 5.537983315768468, 1.334061577714891, 4.657827477712033, 3.6566625733462033, 3.0610863551612453, 3.5097543195661243, 2.1065552581329667, 6.6630334131601, 2.749770613565707, 2.4009215495027108, 5.802499686294344, 4.059364769114884, 3.3879983590053584, 1.528887282855438, 1.6769161861560198, 5.921924797203543, 4.1577160785796865, 7.93428835336614, 12.177738873538074, 4.411838478990764, 8.312319289864735, 3.8655446288893858, 4.7466309917143334, 5.984463668362692, 5.858091206834883, 7.661577286463199, 3.475073446647793, 6.843572292105119, 3.302487169748469, 3.917649300994667, 10.291290553071445, 3.8683336574882143, 0.3509695286400801, 6.419029520367692, 2.019142357667037, 2.9493289736094694, 4.703764117245227, 5.106722362206075, 0.7265195019576574, 9.198251234137336, 6.359987410148027, 3.6103591435009776, 3.654229083211146, 7.720883954209196, 3.650535970669442, 2.9452438161061036, 4.86182541098061, 3.5431652152397817, 7.567439290023942, 4.829087876051966, 6.249143345632968, 7.984426811562893, 1.5081693122197226, 6.354768979154244, 7.60956591468226, 3.462621787551585, 3.5078211862836244, 5.823369432023357, 16.870329959948535, 6.333426306500684, 4.055581993143147, 8.439500364883568, 7.804246707354614, 14.308237930269609, 9.5142632831055, 11.24094590797773, 7.44787774888716, 6.775832580604362, 11.857798457618257, 11.436954767934552, 8.29789903876788, 10.09334184041613, 7.488731454364448, 10.671985698909323, 22.01752240064178, 9.246433952356817, 8.86914595108223, 12.09377236668477, 10.50898307932752, 6.618731189367893, 7.366689949238405, 10.462844100541211, 7.50510428600624, 7.5784637661279985, 9.57033106537716, 7.819205942984615, 7.1300148425217005, 3.7289791871918476, 2.138904406083811, 7.7250733203917035, 6.35979488999298, 9.700706809101858, 11.669418466298369, 9.846697458855694, 17.41987995398308, 17.782745880472497, 16.656283270379593, 10.127222183156361, 20.991112699560805, 10.740280274326436, 10.891869810069764, 22.67347034630413, 8.3507556957312, 24.170953581519857, 8.513968713496693, 13.53344424892108, 21.926167610571007, 38.367111846821885, 9.090709964245539, 6.350237526763104, 15.556739186972585, 28.462632003208384, 7.456770761591448, 15.157142079238364, 14.358957682235694, 10.908874822535324, 13.463099514660062, 23.520448919811418, 14.783678079516445, 27.17042893058838, 20.965126687283888, 11.461611632088232, 29.245313804744633, 9.701609972517758, 16.152472298374924, 8.471105901493477, 16.596708380328977, 13.42038236990996, 14.58475600608884, 17.267380401275577, 10.865742289732193, 10.538837874902773, 24.487315067064863, 23.319616955856084, 10.231543680350434, 22.495931008162124, 21.128844906322875, 19.660188224581873, 34.17513619530154, 14.639868801036881, 31.665736554017712, 17.32934631436291, 21.917276944261115, 14.936843995486768, 54.316835668586094, 11.07388028697524, 6.847972993279075, 35.01905951645273, 8.259598525208252, 15.021523189535992, 32.92557402867176, 23.484975102708724, 22.077675895763186, 19.388770497600355, 14.325029130040047, 24.468466543503784, 40.964156505022366, 28.472756590208, 11.420685639548717, 22.76833616251522, 9.467592957657741, 41.09335153889767, 22.357620600180617, 13.180381481746675, 26.21071988010667, 38.44124077556986, 23.903469914964507, 30.785845620521, 13.132143052318645, 26.712600013905263, 27.39799094205671, 38.499037449224076, 16.01401892779652, 44.977596733083814, 21.72697900302343, 28.305918707417366, 41.87827063438929, 13.824603131836856, 21.821213700855242, 36.1121331779784, 48.408520919746444, 40.76417708964839, 32.6188786367459, 16.09979693244824, 36.64643361183056, 24.49518057164397, 31.787687588114842, 35.15250706679117, 21.932550557338626, 21.188938401905315, 28.451831962561723, 13.964327417288873, 20.956888646179877, 21.520501705686193, 5.33121052866688, 43.37811701436515, 24.427006601603985, 17.480890343227202, 1.9719409396087006, 2.5919304926860676, 33.03521427109687, 20.45390125380923, 3.0548729460246933, 17.207442510340755, 24.576604246189962, 27.680888226262514, 19.974111157775177, 27.79908918509632, 3.3636555958882894, 28.938602441961024, 26.295860254999724, 36.232400065283834, 35.60513466379766, 42.30763858090685, 28.976815257877156, 27.725502205716985, 7.0703164232409215, 23.0715885865725, 51.45491056148781, 45.65341754336696, 22.700239172235236, 37.10893422780629, 56.20759529907237, 37.26405838150994, 42.945056677511396, 32.30761307869497, 46.2908778300959, 25.91587523278549, 19.69874035957433, 29.537774432443523, 32.703558051723185, 34.79843583597234, 28.664254639793835, 23.92568767838975, 40.699849416602135, 49.330130036223764, 19.50106196641234, 23.94246007592643, 47.497986474346106, 3.608313419602759, 42.21891519753306, 66.6695958871585, 81.73837785089435, 20.63120986586413, 25.242692135559, 48.06926199949894, 25.154344873916177, 41.013260834186, 39.33147755291991, 19.84625696692216, 42.27725748191894, 39.85217533693265, 45.90381423725243, 22.20838002333125, 28.169097960643015, 30.255449260231256, 34.850006825155674, 19.487197438493336, 82.50811057894042, 25.767871747095562, 52.516708926752976, 34.953148354794614, 33.100309104753805, 2.893408651527709, 32.54513562849806, 24.643366436831258, 69.97878559951549, 55.96178890248223, 21.767043043424618, 32.671291012682595, 21.23789167751597, 27.410386459090272, 22.849458526198035, 19.370008231090406, 45.52933062031017, 3.795638238623929, 22.127480183241744, 43.674223575962166, 6.731943317086607, 2.984831842832778, 30.739401109637036, 48.019650840493796, 41.96080074446599, 25.569785020519813, 50.505224826185376, 32.58971236222794, 47.989229166125256, 60.78139536056017, 3.113626214187236, 59.02632552291185, 39.53546812100988, 30.39127629014303, 44.492185546222544, 44.37413736360308, 29.189446712858324, 61.29157456558497, 55.55860423456832, 30.86281598086997, 27.96223613108752, 67.64844707883611, 40.0174048129129, 26.283179356332703, 53.71575414395987, 41.86933846020718, 38.63458527929697, 43.23866756937698, 55.28621938157879, 52.19404062907878, 64.16577221949927, 50.91449015870225, 43.12819700456516, 53.6060412038098, 48.333650294980316, 37.65431343696327, 4.15998290672483, 67.06703768256503, 31.9101185200765, 31.056272216870948, 50.07057162832313, 46.198070549722345, 26.04408943139468, 37.93484534266103, 63.67665254688458, 41.217570697848394, 29.727445560000287, 3.7096499867338224, 41.40120205039323, 55.17251554133222, 37.04662511500779, 28.97363205615769, 51.32574802665509, 38.03826180944362, 32.21942411886641, 26.50059161103113, 39.390685194571624, 109.37843306290361, 45.36473910286049, 53.70250452497062, 91.13657979093631, 87.29669383328988, 78.91696088037276, 49.36141271032931, 100.63883586536714, 40.61688253354596, 42.66361000381627, 29.26080649372812, 44.84413412727685, 76.15203314789257, 55.60583186132969, 67.14800393435145, 43.18396841279219, 50.65811065999997, 34.58665374561191, 42.80868016400701, 48.65445954456463, 98.88842229060315, 142.26381947877704, 43.748205751512664, 51.38303393541804, 79.49247096614454, 42.38773597614196, 34.75274540793794, 66.63492824111496, 54.01741128851816, 73.6506050974012, 38.69713194267466, 48.487889807090596, 41.77672003089274, 86.1316538336786, 35.01100027791489, 23.126617209186506, 39.575784957513456, 64.07791806627232, 59.56530868484861, 39.24821895458968, 58.21496258775633, 38.41210071396688, 45.02800144571929, 186.40589568709248, 44.53730343796967, 45.688468016663194, 37.2334187275697, 92.64714116424854, 32.82688085217307, 83.70299335944497, 42.323328077811965, 18.308034950689233, 10.863137910986143, 140.84718810690558, 54.176755161146524, 8.407892961175559, 114.42983789161504, 49.34111252216823, 99.26616541775284, 156.2076227806133, 54.19073926264694, 59.686006837145825, 55.513945161298494, 86.90855364792051, 53.77350429814379, 65.33677269867256, 58.82818397686094, 72.25544859568168, 13.183558602259346, 40.18159942711241, 44.09063900876398, 69.13825901116496, 160.454509246905, 41.63002924507388, 43.645432922235216, 43.089043550922604, 87.92647091746775, 112.20150023555055, 59.3157478390296, 131.66797030852055, 43.12552555227226, 35.37067747871906, 9.500289625248758, 69.0519989605539, 63.25214109032936, 81.43486689606843, 34.11633431519746, 47.43464349594866, 53.626072401571044, 58.79435165808085, 42.40669785491069, 52.329017903065534, 46.836716008906784, 39.04185581302174, 41.89298869482393, 5.985715390013099, 50.78995510779995, 47.343223767933694, 40.50952749876031, 42.578261229702626, 56.57201607309936, 40.86157028996928, 37.224097703375506, 56.56699462225333, 61.06099396782746, 53.90095333845145, 75.41182934937598, 79.70160995804235, 59.00426399988555, 77.63201717980114, 53.245483265651444, 55.05599687972515, 60.6679904831944, 53.086319081747654, 72.59676382628638, 44.17963453358481, 57.16114629866749, 83.06481033025779, 73.71440173796849, 102.92702387360261, 36.399197115255646, 51.36128023453773, 49.557004115306036, 102.93855642023017, 43.47733486969869, 128.98223760905344, 59.35342302346749, 66.15905847768893, 57.856521643795936, 44.54700440228056, 123.1678176773121, 40.063269127821606, 40.15291889108757, 69.45250512817613, 42.81429473732168, 32.73488819819725, 127.84445142481792, 57.515852679477284, 40.74228641880444, 50.41385988447506, 39.83438615068788, 75.71422371114201, 72.70637863160357, 52.89129665718995, 172.13758533334888, 76.90652438726424, 45.93056338442833, 43.11011925827417, 90.07544673010449, 39.58038594809496, 62.84143525785427, 42.490088435091174, 46.019468897716266, 61.67968912333054, 43.77930972484078, 82.19825481064386, 84.66473366468675, 101.88385388936757, 47.4610524547347, 74.52623793577796, 69.84173112002358, 39.163593925043784, 48.49139664466626, 160.8770195690912, 66.97046702144026, 33.67671720906509, 45.00842626650983, 60.15684765547003, 91.49958808421127, 36.52562039169868, 114.80535343832011, 41.83069667340839, 34.98947951558936, 89.03790769424981, 56.198947823665335, 62.91943639117498, 54.232896344777316, 44.64098657671057, 164.46258427148723, 39.289427168873814, 65.1004534527166, 125.04807607009437, 46.49644950394637, 98.11660462580903, 7.642982083641278, 151.70071754167853, 40.07346057693944, 45.97855969118058, 103.14212577052109, 62.67563323629367, 36.46059950599875, 70.06521860080292, 78.3230130451655, 101.87758260718341, 100.52330833221899, 47.758082046902125, 53.62549447240257, 53.876247217412946, 60.9394401012716, 46.788898502773876, 57.3714053607895, 52.24884399046905, 43.65088082506518, 54.00728957263903, 59.23418677796266, 60.74718028066209, 139.6565647216496, 48.102669233421494, 36.944151791444085, 92.0807733920474, 178.80864876175474, 96.2784808023839, 46.820227378485725, 49.76570840614826, 51.52671975325561, 53.90820239878037, 11.156906807217634, 82.3472498000722, 78.16404534785067, 68.81646375041589, 48.37007341826208, 45.09977756951177, 73.63825797745105, 58.04766758170389, 5.379028589452991, 7.283202255278005, 56.621002567246975, 45.910330076622685, 80.94026639343733, 46.839565868320754, 73.26150646456719, 10.988224992663419, 55.22830752304737, 86.9966113677106, 75.9570878208631, 82.19803793716224, 107.86777850831234, 5.709824305339544, 90.65694018046568, 135.33767322595992, 40.437825558295785, 62.919418773893824, 83.02242377827814, 74.40255559632088, 44.87189658822982, 85.93690995195219, 107.88091925320687, 143.1127961013695, 39.65996316884692, 51.44130453110045, 31.29007472709278, 5.210935695908706, 115.36061258877356, 49.85719635254735, 76.37824592352966, 46.932958792513546, 44.20661348271965, 90.49631198323009, 127.28921513693555, 75.5961219471727, 58.619237636764, 42.947906384878046, 4.497376263678527, 116.24779448418302, 94.50173802005449, 80.19834466064525, 65.17396208350543, 113.51458925563387, 37.9381259710599, 47.736073117382034, 46.133695999331636, 40.75186958417568, 132.58392461037658, 109.87589892339238, 68.43335348288606, 101.15434834750225, 59.74161807536133, 41.37352752816048, 50.1598786703727, 5.2956755581642, 77.58098528363027, 67.5626695787534, 35.566531245406736, 76.51784838032094, 37.27636734946912, 51.13586939967696, 128.84692331248607, 99.5753056788879, 88.59677160716454, 60.13967740298746, 37.77936424116223, 46.8745474956856, 43.095425552758996, 45.208729609890504, 71.43320254677606, 172.99850900133305, 48.21521593073485, 163.75689626371454, 51.409206002129615, 61.19632300935425, 122.93998812866377, 42.52486719884167, 84.02118056751874, 10.524183944503218, 46.13707862507433, 7.163924599530511, 142.35599170827845, 55.8712124883518, 124.21617711284205, 75.01523944262931, 56.67454150968598, 46.83130259263562, 53.729442170347525, 42.2708948731368, 25.68858545832742, 96.14246862958028, 15.945549877623616, 5.610969461421016, 91.61159635961731, 87.53178796517399, 81.55857749470354, 40.54268329833342, 8.842347882846262, 74.88343913533501, 85.25800874098877, 53.33246210673838, 79.81703184010091, 53.23036936997829, 44.045634364705755, 93.31739304639338, 82.02638315300764, 53.594931100523084, 51.79213741671038, 7.637707344214119, 106.39531766452181, 83.08017887796764, 90.18084510915678, 83.66616511343355, 54.9752410655857, 86.45151491375555, 29.180984959255163, 70.85664878185801, 78.66978957057886, 38.84488882433372, 56.834220947296444, 57.94014100962795, 55.293325780019586, 66.46029005954355, 41.903933089371925, 94.923768940299, 40.861689468843636, 74.41947565140221, 62.13113610019039, 52.338622116620726, 5.77669667223901, 68.2671039598232, 115.16736697996528, 69.8111513734204, 57.91008012507676, 36.795623352790116, 41.74684368681789, 56.61242466291824, 38.780661851681046, 157.85035602258642, 71.33057165487283, 66.4738458510341, 58.70985665009524, 50.02605107362102, 60.29560442247322, 108.57517710507659, 58.920903371524744, 50.80664286631937, 55.519902450207944, 57.85876105599907, 62.74457861585665, 8.58059466873151, 73.8105609448998, 127.07212191273065, 72.40362931930734, 40.18706314542031, 81.89198777182379, 116.2333196811168, 39.74037133986967, 54.87331500388426, 4.780190527803096, 84.399875295747, 54.92818692247079, 90.65972791133368, 61.87886982811603, 6.356367973646948, 59.82945218420982, 72.24434067560462, 120.0086688284414, 74.45142206238357, 63.60776857870814, 70.92989540761988, 58.378121540007804, 62.57549724029445, 30.375710494772342, 93.0261502004551, 63.23722931281163, 35.41518006519432, 53.355084664973845, 99.64114705341304, 55.74101598304318, 59.094492072694095, 134.7781672821871, 9.120144533249178, 48.781732574951185, 42.04204856261687, 56.297315506410655, 123.53252024997283, 156.88871508988439, 36.292446814396634, 56.04115697376192, 96.15111446203323, 43.13218819411316, 46.03897889105598, 56.94391763329214, 87.07808878671513, 110.83550931089849, 47.744408428003865, 62.55935163839778, 47.21424244985207, 56.41004826422436, 71.05767442365375, 12.843344766721907, 62.978380741278905, 55.55450902848551, 65.06155726631052, 38.837041243767594, 104.50999650648197, 44.508941285106914, 49.394314931491174, 68.2023512259306, 105.88226298820462, 149.89205161313288, 137.4849303615919, 45.43434724742513, 45.78615724733231, 50.08102856128959, 57.69045135072751, 47.32465185231635, 51.37045526540513, 120.05788349698624, 61.31349966023943, 171.50445919701562, 102.04127848362194, 76.72959052514264, 39.07865927841827, 81.58578043888956, 55.86967004742873, 162.0508304653645, 131.3422412273584, 32.264805844150786, 134.92715106860928, 77.20561946596837, 66.40597457495359, 96.69704093704922, 79.5204351140398, 20.859850316076404, 141.73276255533298, 5.3723689716432785, 56.00201289068263, 37.67525346436289, 51.220313064396734, 96.750875514895, 34.738556327115994, 8.198169688898748, 86.91348218336645, 117.44333319078474, 33.607159275887824, 50.85525470731511, 55.46212958971809, 87.58572269856778, 57.813182584515545, 133.8495446250735, 5.091728584171059, 53.86411616100379, 54.11508771140416, 5.362942020780202, 104.83915881585072, 131.23480227775215, 58.98037717448358, 7.917194683751921, 47.27373759030897, 53.410598903410914, 87.27894892237853, 84.42898312307376, 125.56951567150804, 57.444383731326795, 99.91459725795468, 50.85305025274363, 48.39561725472313, 52.5414739308318, 45.299706229648145, 130.74528637790152, 155.05755871369067, 40.45161668001414, 41.408880736612176, 47.23538869502791, 61.26556262793193, 72.98188930964542, 63.45829002330004, 49.20771250317581, 46.43372869648367, 36.4898665686463, 141.67044918488466, 56.53216520015366, 71.24644247460316, 62.49864729877505, 62.08781054589274, 46.859786015396516, 55.68749861922608, 92.4173897111926, 59.14533240897162, 94.71751880028394, 9.221946471304719, 59.65888655312942, 101.82727551263527, 33.90080938338588, 57.47568203569976, 85.7545717036435, 60.90297389500441, 66.69608275526546, 197.08232667731005, 70.21497762212371, 63.33054719743827, 96.24669595231956, 114.41322274778125, 41.38241203188272, 54.05359201005, 111.09653767124185, 53.82940010797016, 78.70356780612353, 39.40806516039195, 46.87989313110441, 65.49482618842634, 81.92890659251579, 117.65860952032628, 133.84151087894554, 147.6100774668454, 65.66985753592904, 71.0648529331936, 42.557787628051386, 57.32866255009316, 59.21755410860304, 42.39339671148626, 84.94200389060963, 40.80075518189583, 84.30326332366933, 48.114282825258826, 78.73814835939133, 7.394953909328541, 52.499956743608955, 80.26792129641413, 105.13781088820124, 42.79551040238589, 52.9819228153046, 6.258377985871508, 84.41472381029601, 121.19793498113528, 94.29005693972816, 78.65111766435382, 42.858302708150866, 59.34342917751509, 97.0585107069197, 93.23064286065915, 75.81105732639391, 63.266879499142156, 57.20199010293682, 71.6903836600043, 136.5705497303385, 73.894926515367, 47.58732225287974, 65.59253100465926, 62.471746651377785, 67.67006168892212, 96.9048295647721, 43.74250267997372, 37.74582055852386, 58.098047370886476, 53.204929916766474, 68.4475853841013, 149.31801516327664, 66.2010573191045, 51.8359372189804, 45.54289479352051, 81.24287078471998, 46.126536333524015, 107.02211722935452, 60.20039288004478, 68.57954715194266, 61.11483397844484, 105.77671084203642, 37.40270407088095, 92.21707386668463, 113.36800236831803, 39.475824710485, 48.246173487651205, 97.09047780757496, 69.09885929625914, 120.65653247464529, 106.05825932641264, 80.26885521687322, 97.20341363023526, 75.76565313314514, 149.09163516818333, 40.031327203513726, 45.62548149950444, 51.08404461888565, 91.74577011022816, 188.40139063952168, 38.68024405463486, 49.8941777480854, 143.57266049638443, 6.83396367037487, 70.4399700826213, 22.74290912846725, 46.229649399739614, 70.29771769918634, 66.2145158759811, 57.029897357247215, 166.45696036203012, 22.471154536568875, 104.31746232677118, 80.97731245480477, 84.99264015475224, 45.8612022814798, 47.63483790489315, 44.63290486949591, 124.12219294707837, 182.74319679099978, 118.15574958226505, 95.04805714453114, 64.90597572443443, 43.60249643980792, 67.2562006825645, 65.20690587749536, 40.883575120593456, 60.54020420370739, 80.20843920035354, 71.45395831805565, 39.14052305600289, 39.89791229729795, 49.81709556658632, 66.31467150614014, 87.08909035700685, 14.235494233086362, 67.66432846440556, 64.24889487663148, 38.21339439080216, 68.08535754386394, 44.29752291362839, 55.07253358975607, 45.02908997016806, 200.77356277704666, 68.64778192032769, 81.6568904887624, 95.34953712669953, 95.89498636624796, 70.71229873520566, 39.78936070315285, 141.44421112321064, 65.84164573813122, 38.63545402722502, 58.9775098170622, 76.6413314924964, 44.003054888579356, 46.1823171322474, 56.58829269939544, 81.34916234985081, 90.16349908880042, 145.4386412121098, 67.12711639719384, 74.74616636966762, 48.32971891429004, 107.374267717469, 51.38234934240345, 224.0143053924552, 69.89776574413247, 72.8074853540622, 153.05677535359618, 96.07391903658684, 46.24992886878018, 73.39191229513911, 32.76427011147123, 87.73640811609911, 84.97602022261864, 88.69197193505455, 210.5958438157215, 49.907199326318505, 125.22891402964748, 74.16862538491148, 118.95627246972352, 84.0629989878589, 47.06639148102354, 166.4068260823372, 78.54831868007311, 82.92462487952976, 185.56681894852818, 90.44691255615462, 45.58138930574956, 55.47028236547342, 99.03454241605647, 148.61172104940977, 40.895720954691356, 64.94313164327912, 271.4447808393013, 107.97974764731663, 56.33089212793698, 67.78746311364063, 59.9471517401646, 160.40122587775534, 67.42523412042539, 59.79419649979569, 72.86485791070616, 88.6602839045331, 122.72997922901907, 47.13910968956069, 40.08394422303202, 74.52343338080837, 72.6552317674469, 219.47323846167723, 79.78917350306173, 79.27021227035996, 77.41119112266571, 38.163750661681085, 84.02620730093606, 13.560066351571127, 48.27547068069415, 118.34467521509696, 58.21472248852931, 58.27414045759634, 89.2183904328654, 75.16476488901372, 58.65610891466643, 82.40162799442591, 53.21505215162737, 82.75260787573457, 205.9773397538921, 66.13135261352507, 67.48786384255243, 97.87252982240548, 64.62992639781726, 101.08388546763551, 40.25264221423513, 10.758716181453467, 135.21708242849363, 8.76957524867095, 38.269892941188836, 56.21350888409274, 136.00011068478992, 59.054713894974725, 99.75072945044208, 193.5190908369115, 94.8482814454643, 111.51839955490001, 128.98308771274426, 63.288087294505246, 108.77836269780369, 45.961025784848886, 82.138799164535, 98.72137548093848, 47.621252615923076, 41.04720746310401, 70.77814992503895, 75.6565776054507, 55.62549250517877, 47.79591923791427, 64.41769326401163, 260.67551672407944, 179.5857394438159, 7.150706500845015, 138.66789603278283, 246.06779142489663, 65.57519724517887, 64.27021340459656, 65.14777469006616, 45.641211246193045, 123.60456659389983, 70.932335571507, 68.01534742180651, 94.8863811819328, 84.26155850284488, 52.74846483355397, 77.87630630409487, 49.12472263855332, 60.12770327311248, 56.44967995407284, 73.76199371622144, 63.35998523925721, 50.02420434792379, 62.931588000207476, 178.26395586644696, 75.72827191765333, 91.43846626011309, 172.57731290291022, 82.38906297032189, 173.18701817897548, 69.3758961609557, 57.99112028291577, 11.77069754264272, 50.99358106397914, 48.51995899187752, 59.29104601890866, 268.06361290716876, 55.68865762481603, 134.67675261275645, 64.63612766157314, 81.29416281275243, 93.1734526284168, 103.91046509818783, 107.01672021217226, 7.076599068881663, 99.19583222410866, 45.71296605059363, 169.9707309534595, 52.78473519538106, 98.8509329319984, 82.74407777466587, 69.36060890405908, 87.93798407070192, 77.32807096357077, 163.59538471580674, 42.941999615364324, 49.49161916518265, 54.61916817687127, 55.61158174143247, 170.38476080826467, 59.69423262762952, 96.30080108739548, 18.49015581870584, 51.545496918275084, 18.885526518335407, 77.086146619811, 8.33449295800861, 66.88938036134742, 58.952790847501596, 117.9515071028101, 78.92184172083948, 62.18265926067276, 55.08885367048237, 53.723860798303576, 90.05501629822948, 128.99302486890133, 52.84131112548076, 78.31258084423746, 87.89118457743129, 74.85380674594832, 45.851040719478625, 47.468884461249786, 119.62900686065173, 107.20480903164938, 48.105162430718245, 118.35553354746196, 77.39209436869255, 76.50998122262601, 65.45131586251011, 57.617374916148286, 70.48368290256282, 102.55830513915264, 12.837913933253141, 57.99506692673399, 120.32833838859618, 68.497384165871, 60.37522625869065, 143.2271406055666, 122.59841453091269, 86.96173338131545, 266.53209773468546, 73.73687009479511, 8.212528163992133, 9.206774440173959, 195.9405204095618, 21.131778217990703, 83.10432478559322, 131.1066188732911, 67.50526172863114, 83.51416379444564, 66.39439589267295, 135.50353600032673, 93.56576456333674, 59.33056250961301, 76.13766832891812, 15.864627695262001, 88.65394513226161, 75.00672680924622, 89.97749300526641, 66.97739053910567, 139.2934015892345, 61.2865320888394, 219.86201658309432, 42.89570132001614, 48.25439231705021, 83.38731627006241, 40.84420096015966, 59.45878183420771, 91.83718796581596, 84.58847184732664, 44.29431010598783, 150.46491840525456, 88.025330913024, 88.62399651003172, 82.22070036081908, 96.89435567358434, 57.49554430202047, 87.31812044171473, 61.88110887581332, 48.46515661795415, 105.72766849170661, 106.30089416624628, 55.45006822412377, 42.408001556587394, 56.605323057956475, 58.72560290345706, 9.441114489768307, 152.64539307036634, 7.737132099013379, 20.14659617976237, 175.39942920440967, 55.81307702389008, 63.40767924387426, 74.48021666693988, 81.21328959777999, 82.07597100186952, 12.057080633916234, 169.8475916143839, 81.3429789095939, 53.38702013308222, 235.06831200790745, 74.62961640174746, 65.65121165434064, 9.130213203062269, 52.198662467485185, 47.537183819512244, 186.90359957528793, 110.79649522124174, 61.06246215156533, 54.29730297945727, 76.95603982196286, 50.90522835821969, 101.86362839026783, 127.76182426669303, 97.54759147811279, 66.65985211143179, 14.21075842042783, 55.73882956979306, 58.66371880238056, 51.375630110389025, 108.2780671317362, 89.9496270305238, 69.71627340789843, 18.17687617091834, 113.58721888928577, 72.75754181503545, 115.21984513640606, 69.44260121195282, 10.88209285612173, 64.08136052880111, 10.240338653993279, 127.5483859831348, 87.21787428521147, 52.03808518179578, 83.00603762724575, 50.53449636500257, 82.569906899692, 63.73204919557044, 53.72501459220624, 69.63527816714549, 34.915252778801616, 63.5705574147226, 55.51646750896433, 60.25040508491689, 39.88545683529349, 8.176204104787399, 64.33920283338962, 43.97942573877519, 49.35390604865415, 51.34561208842463, 61.32639884182064, 54.735727772718846, 116.02275135935565, 157.94635782597734, 10.969944520915057, 96.83852819712325, 11.655839779601378, 166.26178644468325, 228.38794345033568, 191.85827361151294, 51.1843958360235, 299.7071432681201, 87.843214419776, 143.29814252950717, 43.886542770599966, 119.55464633208352, 111.2294664076869, 82.42463821115996, 122.11357140700203, 63.380683782264086, 52.15942844222911, 68.79856076326116, 76.96770140247693, 80.12254128673021, 94.89817959009467, 106.06028886572875, 41.36611112270429, 54.961101236836775, 127.83702986710831, 92.2023422336688, 69.72033669771376, 128.62029998589577, 140.43562798165334, 145.603294116932, 10.893725291625106, 73.1977374654968, 60.77239958013562, 239.11105899811534, 126.21411931407152, 47.084111575795596, 155.99303432330572, 71.82830213857872, 77.2405348722129, 69.97824914729371, 53.257201245633766, 8.419132701233892, 247.32328794139468, 81.69409244103255, 134.54253544539569, 88.41132357521386, 72.92419718814895, 94.56377065878513, 282.9763188879357, 58.96825043767087, 110.37057139230495, 115.24820326554207, 158.60402874029413, 165.5794885898939, 64.44030853271876, 64.34986562738321, 89.05027757701909, 257.7141981800816, 89.8015833437852, 96.95782072495851, 55.3356596501573, 258.3960155041845, 68.06356650100165, 53.13881352682488, 153.0478727666543, 59.31367810002138, 34.19319276506988, 89.70214303136426, 53.29815311751227, 133.0319669890126, 70.57815135867561, 9.256355897304449, 66.12026853112273, 82.24616136572358, 175.11777328976447, 136.21849805237198, 10.95461853708641, 57.789479905810744, 58.61956788063746, 99.9777287361195, 108.76926065380705, 20.94777071791046, 38.019930527461014, 6.042752737898616, 134.6476304266135, 78.04807160279337, 57.862568276448144, 34.9108041497996, 81.82654976094035, 74.35685950111908, 44.039698095625944, 55.34990161082187, 138.02256706673305, 158.889729349368, 84.02777711130715, 82.090035043156, 238.0383815110762, 32.979844598503924, 114.09948490676096, 141.58355573728593, 230.74716667358126, 44.83865568120578, 44.398257766330815, 70.76533361922952, 87.60578851781192, 96.78014098573507, 106.90910406911212, 87.73040248527042, 68.24720259431952, 45.6861601300642, 107.54673496388703, 113.8826278679084, 168.24831830864608, 82.75387382681097, 86.86733053709004, 47.56525405122757, 113.64568206538465, 150.31821778712228, 59.63265630125302, 159.7081572380414, 121.60442796799427, 22.297271962492317, 344.80565496566646, 74.91789041515013, 51.59682724720124, 61.88778817131719, 53.7183917623735, 63.64217696335336, 45.11834901091583, 88.29123948584514, 60.238312473334155, 55.437458010919386, 103.41650026173727, 47.13004885689332, 106.02249066099088, 62.24365624487176, 67.87795806060893, 146.4118443915293, 68.7271156612499, 129.9027132610728, 119.10460758445748, 62.22572399793678, 54.13573380368444, 105.26274402271281, 89.29753688314497, 63.71091902477687, 132.7660293330208, 104.66199656018378, 48.95169171537682, 220.66634347386596, 89.53911041518589, 69.65849976685831, 37.97897664287434, 111.24470393020923, 84.06552171371793, 279.7457394922424, 55.847783195612045, 84.06019803542587, 184.48218159264232, 75.9141653160831, 137.2504189672839, 44.484866777791304, 52.44121276874545, 204.00460648806308, 133.60247041716178, 235.59482968563864, 250.5249426221009, 49.71725683671387, 46.75998872527983, 106.38048562802511, 116.06813793947894, 79.32731933531555, 83.49165580772483, 148.65149264962452, 39.80370237948734, 77.33574737546469, 85.73084829801367, 58.81684554874907, 65.18966763334252, 49.226895749168165, 115.53656472885079, 39.64540194701561, 8.1017568928936, 216.42968476260683, 96.4386961803385, 124.08087978193208, 206.26157868112767, 146.69010717305662, 88.75750250494679, 92.83428969928497, 109.26392148434849, 51.168639782121346, 82.18380053842122, 7.040627565849244, 76.49961986712545, 93.29272879110447, 51.48494517223675, 55.16573892364931, 56.023369335584775, 82.7563219074962, 30.736559287884653, 80.03040905720748, 154.63824249150414, 111.23953809685058, 51.51523165888466, 87.02497489018177, 88.96952760641852, 74.96091515267331, 89.9060804812184, 159.6384081293692, 82.67219900043123, 222.86721507829915, 61.53591260177493, 89.26664277673794, 123.55328603237986, 88.24651561911669, 83.31247485909626, 154.0321944917687, 106.50209814826977, 291.8233925054524, 37.89434571734186, 8.304638541773324, 33.4387433242469, 84.7082914870607, 115.71285391556242, 45.99112383053575, 64.80448524486464, 120.13562105048469, 35.67170295066112, 98.66073329845725, 149.04621566110572, 75.15630021926984, 46.18956935657616, 16.97042305799619, 52.60935880152461, 53.62618944416967, 90.07272726307886, 43.82869733183217, 78.10980779427778, 182.64004667767492, 93.53079819783731, 73.15788057147728, 77.6832795212729, 110.26869830431387, 134.91916670314137, 156.23584459864276, 85.86170763121179, 84.16494424008218, 263.0310147201822, 62.174519050639994, 185.8097539064144, 303.5004987289061, 45.027644984636346, 76.30238280690578, 41.40140976976335, 85.63947342086333, 83.2798851024647, 140.00207410818794, 14.186933035734745, 130.53824342611918, 55.44765757420375, 78.61328838773781, 78.17779761688206, 168.30532207564056, 42.927560176225, 54.48864218663334, 88.83569778714342, 91.14145741897316, 96.08690848701164, 60.22536726617521, 105.35507024728318, 90.4785864423483, 87.65254775164179, 85.97088630746104, 86.42273713440711, 71.22547234893013, 6.4240194052134125, 64.65685103145628, 1</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>113.8439700126648</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>85.93263814105489</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>[131.1273193359375, 159.8739013671875, 53.8621940612793, 235.9087677001953, 64.7526626586914, 251.1658172607422, 34.32735824584961, 117.17913055419922, 196.92556762695312, 87.9483413696289, 66.1889419555664, 58.8765983581543, 92.92533874511719, 85.4333724975586, 203.15487670898438, 128.6514434814453, 305.6389465332031, 15.303524017333984, 42.07221603393555, 128.96324157714844, 68.47811126708984, 57.973331451416016, 60.72064208984375, 66.20027923583984, 42.52860641479492, 92.3326416015625, 269.312255859375, 65.00688171386719, 150.49070739746094, 76.4128189086914, 161.64503479003906, 52.43532943725586, 217.71734619140625, 140.57579040527344, 90.18891143798828, 70.75931549072266, 73.18345642089844, 61.698062896728516, 98.36180877685547, 268.28814697265625, 40.58183288574219, 45.912357330322266, 56.809242248535156, 91.04740905761719, 53.956573486328125, 227.75167846679688, 85.51327514648438, 149.87347412109375, 57.82942199707031, 67.59243774414062, 64.07459259033203, 132.88648986816406, 11.014800071716309, 150.6859130859375, 57.50522994995117, 135.78538513183594, 81.98585510253906, 10.816911697387695, 170.21725463867188, 133.05874633789062, 361.9944763183594, 243.71127319335938, 143.30062866210938, 11.030903816223145, 107.97257995605469, 60.81235885620117, 69.55463409423828, 115.27265930175781, 72.24052429199219, 236.35528564453125, 194.07070922851562, 58.281158447265625, 165.8627166748047, 58.16909408569336, 39.30946350097656, 42.78050231933594, 215.6039276123047, 123.48377990722656, 63.22472381591797, 111.35980987548828, 116.09622192382812, 91.84227752685547, 59.94511032104492, 57.224910736083984, 71.99778747558594, 65.28129577636719, 112.41278076171875, 617.7435913085938, 154.9647216796875, 168.9499969482422, 94.31657409667969, 58.899497985839844, 77.41222381591797, 59.789222717285156, 51.258235931396484, 188.31649780273438, 108.47403717041016, 32.06501007080078, 56.33781433105469, 177.1900634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandom0827</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:15:49</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>90.09189533744842</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>69.37530399729232</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>103.2483984294276</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>4839</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.7255805133167887, 1.2590380581255172, 1.4292546412873066, 1.241618146071886, 2.282943626026312, 0.9768752613824513, 0.38309490460645185, 1.5853552159118565, 0.9180291537048838, 0.7369000508819065, 1.0767731688400461, 0.6788183497080192, 0.8284281168854323, 1.3409171515683538, 1.3323504228347727, 1.2176858075086456, 1.1755294216457342, 0.5281283614655377, 0.7485529059529655, 2.302073456164561, 0.9359968031943504, 1.2070213934790361, 0.8202396966405546, 0.3265085563270601, 1.327581392646706, 0.7923591853482477, 1.8149352548258293, 1.471516498670176, 0.4531338943447032, 1.9274001719880165, 2.0549212846942657, 3.160164735706146, 1.0215299511040163, 1.542986431022076, 1.657724713140219, 1.7248489181517275, 1.2668915958409936, 1.510718084777298, 1.8941259950099036, 1.7018497847327259, 1.448092395791944, 1.7552272261188557, 1.6406605008052262, 2.3721099387147873, 2.631507739983265, 2.114597069255938, 0.8658848015262414, 1.1580663712004429, 2.1560426595039353, 1.0471214967438516, 2.038608191987517, 1.7129572528633816, 1.3679954217537995, 1.3875779295100092, 1.573236656327967, 4.6755787254021675, 1.555266245369124, 1.5514421495791149, 0.9424804400904663, 1.224481263823864, 2.19646082559131, 2.5079514301567776, 2.897345584814668, 1.6589840667858986, 2.054382447887885, 1.6749767046158972, 1.6603153592971076, 2.851470876923824, 1.8808938543639677, 2.80390178315907, 3.658648289560559, 3.5064510888288924, 1.8761084505592485, 1.762034389195663, 2.085467619399406, 4.003251424990843, 3.837301500798081, 3.1378090916068966, 3.68865249847171, 3.3989458921261964, 4.028883689002866, 4.365939924261157, 2.3853282577808774, 2.875246623151911, 2.771545496319353, 2.241283317905404, 4.762823463950421, 2.8031724145383508, 4.0460436214845155, 3.077896371107705, 2.8323145103704346, 1.7569225459436482, 6.261607254843066, 3.4205156074744174, 2.6412430727696123, 4.827173128902528, 2.1811081924300475, 3.1904665636847214, 2.5181098925800938, 1.5136775601609116, 6.74978256875657, 5.974868151960558, 6.391325562622516, 8.096485143505275, 4.023058894888527, 7.738009639022708, 1.6078567355091002, 4.007934245361453, 5.357182492844805, 6.4413207214791175, 6.666483208336883, 6.226234696310157, 3.8487917697375424, 1.7223227063196103, 9.334496817812022, 5.1197229188265405, 3.3760467937064167, 2.246815020655971, 3.33741878734456, 5.870125387779296, 8.44660021099463, 4.879180194513892, 2.712234981922863, 2.7857806330110177, 5.41763171629456, 5.345999935053442, 4.192576697968329, 6.001556041494813, 2.7225027259089054, 5.6929157855949, 3.5060544312555137, 2.9473198359862924, 5.7008447832723235, 5.267774351061098, 5.5150703595741914, 3.47028121782047, 2.4172546322342714, 3.7152846323937507, 7.974885309992898, 16.695730815392483, 6.181369331141029, 4.614171707439839, 6.690087131278021, 7.190224072538277, 11.761722608481943, 8.750520585441324, 5.546297290027569, 8.28265686624133, 11.522176890066723, 5.631161167260205, 7.494232046811736, 7.840153715487794, 8.824779776477977, 8.775209940957062, 6.096546285145402, 9.150694215001288, 6.80061713941654, 6.056300834320574, 12.36120348573899, 7.141657580615346, 8.82610760343462, 6.35623265468596, 5.5022562078638275, 13.54328004642269, 6.911674789254804, 6.288517544122898, 11.349065547570383, 6.04421747401701, 5.059742514007207, 21.70796277267627, 1.5548036955095774, 6.294266160532513, 9.27877422618591, 8.088302998243874, 16.87559250382712, 9.4115995576812, 14.095414389831639, 12.409742014968275, 15.179025969821005, 11.275426378174737, 6.820227756859025, 15.816696439207949, 15.416177542245753, 21.934193131230153, 13.921841726026763, 22.756002799318473, 20.404801585877347, 25.99216911636777, 5.695642081832151, 7.934632765861404, 12.003425637099433, 20.714751325359348, 11.272933256962538, 3.1546974909408063, 16.254931492676455, 15.019261532107445, 7.0307992184739625, 12.352683184243757, 22.230968462093273, 16.11937845829247, 22.018723998396307, 21.398538654569165, 9.900977249594423, 18.85681086676439, 18.773703381400317, 7.387081960939981, 13.346673035433291, 11.935548607801381, 16.587633608122207, 17.376253468466334, 18.81039456909548, 19.535609552231367, 16.388455288297596, 22.490309172580346, 25.545596716283285, 25.8090693291466, 20.860168263229596, 9.67308548107181, 19.902710520823632, 22.16352573587312, 16.069329199223912, 10.626813342527749, 36.983036467667056, 37.14252329974178, 5.607063304681591, 6.335255555942467, 7.220435094025757, 29.804881822357196, 17.764424639041867, 15.296873626419721, 19.044260028344855, 19.45573911882043, 10.827499011417197, 15.623257544188478, 16.39603301973879, 28.831264747646724, 22.905460560450173, 37.19197934812861, 13.121813586927875, 17.571975170792005, 13.578427935625887, 17.145444541760988, 12.780797346016291, 15.190554797268202, 17.82392724147572, 38.43287511702622, 22.180227909633214, 47.026705610684786, 14.310823298596413, 18.653845553139014, 38.22368475983, 40.27510872333266, 14.508059896222813, 21.364745342794805, 39.83537504304935, 3.5076988809830807, 36.50840926756018, 48.91463730105592, 24.63537683714615, 32.68492177645011, 27.647161657534788, 34.05424102003317, 19.66312530919988, 44.74022704242103, 36.48170755642426, 39.85637477142763, 53.73914399337529, 26.066027535159574, 27.944727363113426, 29.863711813230342, 57.93923601068818, 18.20145987384468, 27.405286032393327, 19.157109860483114, 7.34161707804061, 37.27577557919875, 17.490313853272536, 42.003797443376, 32.65159157497087, 22.62612749630192, 14.754399461199803, 32.79390768167918, 39.71590053157728, 20.009052876708374, 30.642505638282145, 23.464512173972665, 18.66968989043803, 57.386954630176774, 54.99585684406067, 28.161798485649314, 39.22535628957386, 27.516008257276756, 58.25542375654552, 26.697806203014316, 34.6483018720174, 32.43910001761124, 22.895461008879337, 51.533137937476425, 24.696876858428308, 6.557205774513479, 26.726753353024517, 27.67480554424199, 60.561869477321586, 17.942428404097647, 32.89063837375406, 36.05118993827803, 27.85739951203509, 29.74434252657725, 29.547697833062465, 24.83665726001421, 28.133928283182893, 30.130486448013585, 4.383819008522849, 22.43694549251836, 23.0156566711621, 52.568520511355, 2.378745855248065, 47.99716259095247, 35.993517764932044, 56.75248465620676, 30.747943596378928, 35.760430782102425, 24.324382918542796, 25.340434759026333, 2.893619002127803, 44.183770920104294, 29.641453999818292, 28.3619624899862, 95.08523805031992, 26.532688629206767, 46.810904950712455, 45.51358658848724, 36.3320610768428, 34.729752463428824, 53.56020859486991, 59.35889957816995, 80.18089718710772, 53.411334756726895, 3.9516495040244046, 50.41537059035409, 26.036938952807223, 40.798400594661416, 46.852857413263344, 52.60622648377055, 24.862403741486357, 11.981392528409794, 69.14315038878608, 65.83382151349241, 61.92953806682994, 21.374284533637645, 36.428296455807136, 38.83289988079866, 33.90017285039594, 52.49355218398827, 29.665405482749662, 62.72260271844532, 5.379162529668469, 60.70367533985439, 39.65070109766367, 25.64531955939038, 32.456281797299255, 75.90586135480565, 59.575933550147504, 4.081610564356053, 64.20033503983413, 38.28926776143499, 70.19355277585817, 49.380466606475906, 51.82418105909613, 28.43344033563177, 41.030439715529425, 44.761722514407694, 25.220881643741716, 20.16543189434832, 57.41704029347053, 55.98153425747364, 96.11198940888352, 6.279256314127458, 40.74547083845675, 36.18842238569384, 30.759073281034418, 34.848159594035245, 34.55115790384194, 75.05786662159053, 87.35090431149456, 37.49463871025167, 39.17118946141931, 28.201310583965164, 27.62421555375372, 55.73193968823127, 31.679330755654217, 29.508378964796684, 63.08122249683376, 26.334082070097878, 61.813164258598526, 56.87285247248003, 29.521717345257784, 48.083082827073405, 51.870590423883215, 54.299724302149784, 5.728726660567589, 29.51233293813768, 50.56818501295769, 81.49594107065407, 35.69194181474191, 35.86194376704638, 34.52449111252443, 45.14851684736375, 67.11435510784275, 56.04470049088741, 80.38040182966921, 38.05656667092366, 12.613675154843452, 83.87410483925527, 119.97647428312692, 35.86841979399454, 33.28444910657365, 57.48618845477128, 28.35752508732432, 64.63656803459466, 14.530346877229277, 102.41538044585856, 37.50002029557685, 43.656387386974174, 46.301249188101615, 27.884937588311825, 38.53489395453407, 53.47160777229763, 22.682423988278543, 30.536331377507597, 30.044270019455656, 67.30416961848225, 6.6623687164677134, 42.99869394510835, 37.392802790203255, 60.96457939820055, 68.415968002848, 43.202753813114946, 43.13772862527255, 52.96921803168977, 26.60798646733457, 34.27856616130268, 55.93236569523266, 46.50205097606428, 27.20893029342629, 59.62523005611635, 40.63092188128135, 63.166911377013164, 82.81994571797823, 36.71756035359123, 5.070282563651048, 44.45086281954333, 68.17708977558873, 58.76198291255666, 24.62323514377698, 41.13921539490769, 48.315777525762634, 89.57457078550188, 104.66337124331899, 38.626234129839226, 81.18548086877567, 62.94272941740371, 49.8833561378183, 33.436471665938015, 47.933004721131674, 60.38176756920275, 52.48353146525273, 72.3479764984387, 66.15227421376837, 38.55849862476679, 35.56504586323282, 65.90874476434894, 31.659561319918755, 58.40746892128986, 327.04832978973786, 55.32652434147272, 39.35292981909188, 49.49146894991573, 51.03690596407558, 71.06048734292301, 66.37440743355405, 49.02585766670293, 47.86887736830922, 28.63167822901265, 70.13468952224859, 44.48413414341507, 105.17144306129673, 72.67807395890632, 40.439953578907854, 40.77182887276886, 107.34662786693032, 197.4984475212825, 72.66005486826715, 64.14544686192097, 36.05097272853655, 36.601060084944585, 43.74553408512067, 66.9815063789342, 66.01320497857168, 58.77047387741324, 58.453708933419165, 64.28400405440343, 84.10288176798461, 29.191254844730565, 51.936264325562576, 51.867124181031144, 51.31925768920415, 62.77275313857254, 82.32420595738476, 78.76573527770978, 69.34247162917302, 66.0205062615385, 42.128028228184824, 91.33821521851327, 86.9218964037265, 78.42746327686432, 88.35259980635793, 75.5010815105044, 77.06340216624287, 71.47782855217973, 109.5533979797726, 53.05621610918535, 63.92818359670955, 65.80465961341099, 45.849302133378174, 43.75857475512737, 56.90432850722218, 67.11769486895027, 151.18368397299287, 75.1383530055595, 117.12617040581375, 80.10634708805526, 56.25146609197524, 140.26697249850608, 50.2782636973693, 66.8747711810642, 52.376444219718785, 47.4428430755786, 50.52929083776232, 50.59179916457461, 56.7910588359095, 51.38937058318473, 67.10922872650583, 53.162768539874754, 40.56410578728501, 41.07474150768222, 82.85901380013948, 55.967532916820595, 104.84862161455203, 37.11500483587426, 61.655975232788286, 139.11110414864405, 51.352363139883636, 132.75327440320333, 7.100342757530634, 44.93408384692811, 65.77861795806821, 41.171548371733365, 106.81857552493624, 5.632666036425224, 33.11211682446517, 76.64245660422988, 48.935715543916125, 52.97660740018614, 33.408179258854446, 95.75450576597119, 36.38620687029924, 133.01192492654246, 29.0574986175943, 58.503727204172314, 68.49434582381062, 51.09565817615327, 44.48058379690268, 54.04643629414609, 86.25723216259028, 34.70434171255078, 31.230446017585134, 59.27825915190709, 57.163625919860635, 80.10115938799657, 49.202260201278634, 32.30878144825544, 31.471142138123497, 59.86298993181904, 60.611410269248545, 60.733645486486765, 57.75037029656957, 38.73487784314846, 57.245741550738266, 50.382390729382436, 55.79976876894733, 88.35840248752113, 50.53929055785553, 57.61159137126489, 83.69910070629503, 85.63658252251832, 91.37822442332723, 53.140792496306794, 34.85762818954098, 59.86428542385048, 102.30779942860137, 45.33188089883181, 153.02116123422755, 77.88439836235594, 108.2845097399146, 56.530395514649044, 45.105387299152966, 50.489371790527784, 13.951622255002963, 145.6527732521619, 50.134875623828826, 68.92113758865594, 71.33458137657917, 41.32393662155814, 41.83044383727796, 61.046138780296396, 76.41252925769511, 87.13062640316564, 41.18500035078641, 119.32485074822971, 118.41668384899243, 188.4091091555677, 54.63751357163627, 52.54309306490932, 75.04257952594702, 85.30326133345253, 40.09910989931991, 57.720571457487644, 52.27372491790809, 74.01743104728624, 37.26050112014778, 70.48326474644821, 74.88764033730205, 16.94283851115186, 44.397289107803616, 59.853268724100005, 48.0196725103047, 42.787763539138076, 5.683694673115619, 123.9633123317422, 91.01576140375703, 57.86755043253594, 82.65332792382634, 106.46386022854263, 58.410083914923305, 50.758723551622374, 77.71510013844673, 73.74724026030813, 38.302164855923074, 72.20178776736208, 58.46873978407492, 87.42381981819636, 40.1019939912046, 65.24825948530659, 5.305744327603529, 107.24363959374249, 126.45573618308306, 40.33612727548807, 54.3672483918042, 32.65011878315842, 168.33119497284, 51.59885121718905, 71.3871440184105, 100.94502917172524, 21.217643750006335, 80.4365940982622, 59.35492277684905, 51.143589163194065, 56.27690260373927, 54.251622508202935, 39.11813032929592, 81.94692473887605, 44.337171065372274, 44.406648806716504, 59.705760806756764, 54.63147384285872, 62.75843686291252, 49.76146970301895, 49.274253934329266, 27.905414214510824, 77.37058514595334, 17.664479176656208, 42.59371198636203, 39.87423669257539, 47.5208044158519, 62.31370698134097, 333.15427419088275, 57.98167572374172, 61.852937076818286, 71.97611386924068, 89.52696380482922, 39.60301344162784, 45.64996520981594, 45.75859188289999, 96.8525873794072, 74.46464560521189, 93.33754052435143, 66.27846307105358, 52.678481985333356, 46.429867252925156, 48.30605781178277, 61.45062442423752, 87.77871655981585, 3.5008063857165053, 58.644963589118134, 159.16518251055146, 63.043573699526554, 115.61393701475815, 54.208938437778635, 76.22615563692875, 52.93280987752687, 136.24500870970178, 89.9120043834918, 37.817246597082345, 43.456890864428935, 81.72649048139503, 58.543192230632215, 74.69481381188828, 44.180185889375664, 45.636861234642225, 69.76347796153175, 52.70961840600265, 3.189000768428225, 159.41334479559222, 53.34863093129431, 54.49962020177864, 49.861293738209454, 81.16145476359844, 53.442720966732914, 61.60936891975536, 59.57835615906505, 62.565233942842454, 73.72958116106895, 130.45027776460154, 69.29506582723737, 33.2200794298358, 81.97286331189379, 57.01683792262844, 181.21857297178474, 56.297537190577444, 61.61141436548635, 131.065228355013, 100.64534176977641, 64.45370530480945, 65.82317921145757, 99.14114359946174, 61.08621741267936, 79.91340545562414, 28.58138038241914, 74.15625862661165, 116.70859920447447, 47.4480867442121, 91.91948876339715, 62.562912799487094, 49.10950026167064, 63.56894134673691, 71.37262369936957, 16.06528592247907, 44.122087472716714, 83.91452042852916, 71.38294621830556, 83.6086553468481, 130.73548544328193, 79.78832285766282, 90.79067232428588, 91.65185424338839, 44.708174040540996, 54.98836591249056, 52.243809118356076, 209.0096419116003, 87.46163337115067, 56.62161911006866, 10.836972384594695, 52.414219803085665, 73.78769898747888, 59.641578016657405, 70.48244281301564, 83.69285384575142, 86.64616745886198, 62.14006662588255, 52.067688778268945, 50.61889200568582, 70.71404351836401, 197.16495987177473, 101.18169325802462, 80.37472742118908, 78.455321659309, 19.60150755682218, 61.69531259368815, 32.21352229239049, 67.52975688186655, 64.6949535429972, 204.34702542294596, 40.429474399807475, 68.05875156093467, 95.96900086844326, 65.15427712870436, 104.57558663283031, 64.23813540099023, 104.04094700516735, 106.25888538805646, 53.02728796581369, 86.74178069767736, 31.90097835384109, 71.91291764765427, 119.15064374801226, 43.721633110347156, 223.48154642133687, 10.13904159506046, 47.446974506274934, 44.07819218730637, 49.833666142151685, 93.56676625945292, 55.834938469955816, 46.786682323908025, 58.46219521092859, 298.64603656301097, 88.64897921830415, 14.43475170970057, 48.81009855823996, 75.23522925179446, 74.95893762490694, 56.58067152803787, 55.3768952761116, 380.8297306052197, 72.15993157852404, 58.90781355377471, 75.50961083030371, 48.075524526956116, 58.93645711057844, 74.85341382133485, 46.543219442214564, 80.85485477492233, 61.264712591555856, 31.2863785577228, 75.431761770385, 9.230198556706512, 81.36925665088748, 11.923581975107124, 59.946055861407764, 57.11997576401286, 69.7816827505999, 79.5346974554262, 48.310412227269886, 92.38715253307303, 51.682892417574855, 56.66115046440491, 53.73273771485532, 68.93511064515062, 36.84148955878118, 49.84102132956521, 73.90498520257766, 78.73175396056273, 59.9651336052316, 44.44151242904041, 79.94625872043096, 106.83910583444595, 57.53734351492569, 64.01954154813534, 54.20910518665539, 65.03596871411654, 83.71323636757856, 4.872606498817284, 164.9979228875215, 176.38763727942415, 69.0578950429439, 89.27705141137163, 70.06942349064916, 69.73647936872881, 57.04331955262507, 110.84090157030388, 41.117291705418985, 70.62150688240112, 41.923521919460384, 8.835577815812854, 39.171899546558066, 90.75807618941316, 11.304957574288338, 64.87370636348392, 115.45615017309204, 50.97070418252266, 82.33531790925475, 89.56592721557982, 78.96362421564149, 96.2882379561977, 82.05279040895358, 37.420310051244016, 6.450754486243643, 75.54176272022842, 130.43924805228374, 198.3492715371315, 42.87725403961014, 66.48408378794389, 12.55603612491553, 59.992731584215576, 81.7743761301769, 74.68362935133409, 136.90841385191968, 58.27294484935425, 111.8363367245123, 48.81122428682167, 47.84082054417954, 56.23708004988619, 39.9418896357142, 46.70506065646215, 51.16242815246026, 92.30912093388133, 54.53975882484706, 13.728242318083284, 5.574970490168219, 76.4372202046473, 68.51452019085026, 83.00984183593422, 72.33826442299534, 46.31585892421779, 43.67003510122469, 34.24272560578688, 168.70684059472765, 62.67543627791875, 91.20772625115289, 47.4825512822044, 62.80393795712878, 112.9845696530024, 51.5892244246597, 70.3502319621582, 128.3421869900101, 62.0293336134559, 84.23578306807133, 50.10829452483283, 37.16705213773214, 142.81726872779493, 51.526955882923104, 97.50919754736572, 53.07188616172372, 5.668944555367417, 73.96326158777097, 60.834307869589466, 124.1632879070847, 70.25687492629741, 74.70937000447823, 76.34374870670143, 57.437986016076344, 57.13321723741214, 171.63610095919753, 47.371834622944675, 122.98364756554598, 77.52495426778485, 71.91750256573194, 105.56909629312716, 35.168516349607266, 15.517881246051115, 104.4896584507702, 140.9639930945414, 70.15279489233035, 39.39003582707539, 62.89406015088232, 48.574313660979094, 159.22412313437076, 52.38504243536853, 60.171422034286756, 120.03139038576883, 88.15421078132836, 71.03793363099413, 36.85780256815049, 51.27870940265299, 100.36150956582223, 72.66489184494216, 95.59598348877805, 265.7303310725659, 101.46423678781188, 43.35990664869016, 50.88060301233547, 57.58668900766771, 68.67729092401757, 171.57113043908197, 60.64010712350096, 96.27912426028269, 67.70927106871801, 49.72792660318972, 93.80446349411262, 244.0285251675366, 157.86310590725876, 48.6041854682121, 47.634585706672965, 51.67898209395043, 167.77871257572312, 84.18689490583618, 59.33034800989363, 63.76124733561255, 59.29320494298902, 52.06163382420434, 56.62377076191226, 42.48405074461334, 91.56320880826502, 62.50220496168795, 81.3014931398831, 139.59962729984886, 48.20401216726417, 44.430706557621626, 91.34171158198536, 65.88091574152635, 42.703471476933, 80.11758366498584, 142.16900089047797, 86.68456324733704, 86.92847715804531, 92.4853668795653, 46.50636423444114, 71.20939569170221, 81.41676949984411, 108.84590229603113, 52.56116546969525, 56.04298905245811, 87.36608773123291, 231.02203874636538, 45.71321971696306, 43.50834170036384, 187.14819201135978, 70.71129586236978, 8.132779428360832, 20.273429679644824, 39.65446084981022, 71.69718415019989, 64.86091223244344, 104.12297808560744, 53.19006311764565, 128.11125535098452, 52.32847241412027, 95.69181807181157, 69.06143770663525, 40.426163560715466, 91.68371407696974, 154.404616269598, 149.01136827907902, 97.83214407278327, 52.08031878336516, 61.88536749630226, 46.289918512585935, 61.168996291967254, 55.72155016402742, 37.519722964018655, 64.68275787066057, 71.7144606582855, 51.08230968230884, 51.006525627529825, 30.171890704643076, 50.93707752067127, 50.994711329801795, 79.85533713741573, 63.92261323840925, 100.28956769187573, 5.089657824101604, 61.61479720848387, 43.690446075259416, 46.77272222770762, 43.65250750773151, 142.57261605780343, 76.45512369005603, 145.0265392275386, 58.05444379539045, 119.80147639794231, 102.45973485343448, 210.67982578522248, 84.09813562917236, 46.75940525027143, 56.36161867766304, 47.33074676741758, 43.438739346203256, 56.57765249640162, 84.37375306030535, 15.87508442305874, 76.08998797846407, 100.56487042967801, 74.08173101025304, 43.04232068960903, 64.86284803770766, 55.11112240691497, 50.55891566360594, 167.46402489653178, 80.18775151264117, 75.16612271515638, 50.28939984267177, 38.970787339861076, 77.70653619768765, 51.63120022420866, 44.716826141999434, 34.590340793795406, 100.70225311750258, 103.4570400533601, 81.41649686475537, 115.96255390535765, 54.295625638190145, 222.13708089584316, 49.213574322901735, 81.21004587057296, 92.02390704620923, 63.08528853193724, 88.37255769187303, 97.33098034518038, 54.719447224200195, 109.89797444580852, 94.45362800286111, 54.34411827649013, 63.90470416184242, 73.5150127800891, 63.075054169660206, 68.36995628774905, 111.03915620868347, 120.42755498953733, 71.46579188227183, 44.651321724611996, 75.83748799432045, 16.514507394366817, 50.37885034975371, 50.85395964008498, 54.129647509424956, 192.19966991190228, 83.11733803327749, 166.25447286133326, 49.10689244728084, 74.27768192277495, 108.20769500168323, 45.450336603062944, 66.07628299493621, 122.10889231173206, 87.91142129543215, 128.69877915651907, 41.50675708747373, 50.456672608030345, 59.40455431472738, 205.66106039938262, 95.47061251611515, 106.36945065408239, 4.952944181307944, 95.26870073779405, 61.515900352814455, 66.08167267067796, 162.02409008819026, 118.11713614445422, 104.61507856266378, 148.82796651736135, 47.388256138250156, 146.78132427274394, 41.91626740092495, 126.54521805689936, 66.69321598346492, 72.0653481874108, 254.6913289954497, 95.52113226087775, 58.04483703254087, 67.15400573608063, 88.32091133828254, 81.09797595491038, 111.41777994103488, 50.232941873805835, 107.19851031826225, 48.38344193553263, 76.90795326626653, 81.12636544746533, 44.57740192959095, 38.45200982640999, 64.41386606393158, 73.71710092690363, 52.91734996150719, 68.66263528699795, 56.76851988682506, 189.2497870388266, 104.52190007127412, 38.671155025874434, 94.52234887515814, 69.20544609899135, 15.398010434835578, 120.07266289791795, 63.96248444175241, 73.548146544346, 60.14303596871222, 65.35587879148794, 63.380624808450015, 15.60012693454148, 5.364465431203752, 173.11995952514343, 78.2326375191564, 48.740402716097954, 70.31491905032048, 44.28791361775742, 55.556849739486054, 65.98386061531168, 188.98599229780586, 52.666413511610564, 57.72459597447232, 110.90088945583629, 262.85400828219366, 7.843627382806471, 111.39029220663821, 50.4395840649204, 101.62477827514167, 53.020862084377264, 56.30760163228214, 60.22401216206319, 52.62975272312837, 36.48922217597338, 301.98063070222054, 70.93583450100628, 107.86725085461944, 72.89019619953183, 163.5546727476775, 53.636208903333895, 81.94178427677696, 54.605639368804795, 84.51634403762172, 102.20035589013122, 50.58861894840884, 6.820051236416038, 77.24555021413374, 71.13777276012766, 62.064453130118984, 71.37194588946417, 87.3503532499357, 211.11351559481693, 96.17097330090716, 46.418609702526595, 84.10111449372393, 61.090272194697704, 182.5244901640532, 44.6440227274383, 57.65785881524448, 115.27376565359538, 54.5380262710914, 51.638103914165036, 78.49783122532202, 51.67791761044371, 54.915119968516485, 111.0093570527209, 116.13685621968114, 59.721453916940305, 233.3262229403457, 56.35075501746575, 49.390209410533906, 57.50164494223599, 161.66844504458203, 53.73187348712941, 57.823220281037166, 40.871265388577456, 66.68519589896049, 68.21372331250295, 80.47867920442872, 64.0151418428629, 12.318625023540992, 34.93069998827406, 67.90382730560401, 136.84897166830189, 84.99627115210038, 63.85895870163243, 65.74728460247665, 91.03593678019435, 51.74378823447111, 53.97508629053886, 130.11706963118218, 96.82538569034725, 61.16166343049414, 67.28423333787944, 128.5710991015617, 72.08231567405424, 6.892475909226164, 191.06236525254587, 61.90405432062453, 128.20984572843034, 113.74486912445313, 67.49518946173878, 76.6038337091405, 63.89354558672629, 109.1600184548899, 121.8391027131869, 69.71338417276307, 58.58514356617562, 52.16958388880296, 87.5448900458863, 47.53869597038976, 142.92298934039684, 49.32727777290999, 84.47914726932682, 131.31145143171776, 10.579789668590777, 54.85539028093285, 113.9535771756313, 39.22765787204703, 72.69843969233007, 197.6267437263521, 176.14692453818049, 54.40492190815704, 76.56215744818445, 89.66763796995065, 57.5071616216978, 110.00699046549855, 119.07527027209792, 61.03857350843516, 93.4962731923468, 100.39112047769007, 75.79927381460914, 89.49596661810916, 69.72156639376956, 101.53261448388243, 53.411643680022394, 77.19849620383388, 56.16214614224285, 220.45599264145287, 67.1509760937566, 77.68321350154953, 194.45395463129077, 80.29204504611906, 125.37781474496246, 61.12998543766256, 130.81063799601995, 89.27899851656994, 52.828880932421974, 76.23625468476962, 61.91724125501686, 59.22911210735195, 77.08714156666935, 56.4907451739919, 46.48990170521939, 152.27841335784112, 93.87450495010418, 54.046333540322436, 66.51344140044316, 66.65624365082203, 43.78558078749764, 104.84026135128792, 112.84585493720562, 93.13534344537783, 64.81735950455953, 91.57456972908678, 98.70899304383352, 109.74211705878055, 197.67706861585071, 48.6281352512265, 129.25006516054904, 78.14888050319301, 233.1199432571884, 116.02420351195084, 82.62741615556499, 67.2741992075144, 59.276648984197394, 63.62893646028087, 68.45129006428071, 75.4476939628371, 62.82440000607834, 85.2512329305581, 85.02173272039296, 193.33786634318136, 73.24375048983786, 42.342706873028796, 83.72503235894364, 42.94661754205233, 55.333772359772816, 164.40157357977432, 19.179329242492713, 146.19593332744108, 124.60731549722583, 155.79015206596756, 183.76149088984687, 113.63105814088705, 198.74030238830738, 77.72681170230064, 104.06427963721477, 185.43637470047577, 87.07783216880952, 59.68207697953373, 106.70778510482644, 142.843787308684, 87.31398944896519, 101.89934550508744, 91.4192023837722, 83.41873043685493, 105.09847897325773, 81.66043737607043, 52.87423639794423, 52.213561632673155, 55.47600300696258, 102.03259672338926, 50.999178484225915, 59.95663792246751, 61.832746594108514, 160.04825700075338, 45.91017871706085, 103.20176612319736, 74.17492550107818, 5.864302541670385, 63.23058554624233, 79.6857699170903, 85.44836452695904, 93.90577108270627, 159.4407169589478, 61.190704300324605, 105.39648152119179, 45.621501055737205, 60.15423962012891, 66.71635671409013, 61.326600331904416, 126.34526716051268, 170.0671966427362, 61.693120843776235, 261.1005605238712, 84.63794475895371, 48.207589881089994, 72.53843682244754, 99.86658311617197, 44.10450353429566, 72.1689003236689, 88.35286156160518, 75.14232581296335, 95.30037862325541, 74.50190639413489, 53.37116873265898, 68.24722790739517, 101.1778032453288, 56.32428144862019, 81.94351365394294, 131.98016642707006, 95.95503267777569, 63.678952915085006, 91.35358810640591, 45.49094141257638, 46.633683129360094, 64.27917151614524, 108.82219818615627, 131.69817432144586, 79.50571832557091, 100.67982934568572, 84.36846104771837, 99.81538081126355, 46.33271345903705, 7.250212031238293, 68.72668895936205, 208.30329193881505, 210.12635074931515, 65.41349819310061, 11.938055752633813, 54.423874824416956, 114.68385400536746, 42.73475911114934, 77.11762749719965, 42.87105792655828, 60.34994817443458, 115.75483013658321, 96.8360583587363, 48.390223386397544, 57.69134107187312, 128.26205057519837, 61.8156539829643, 90.76731467911355, 75.1329495855701, 90.34626495748505, 83.08054872839996, 57.56256793326008, 55.43762994225285, 46.66030572386287, 97.71105602718032, 49.06163267280696, 79.03222222127356, 147.2348738844751, 96.67843370984916, 67.54369244625323, 78.38785605089137, 82.08815193024567, 72.94243211852576, 57.09936953042698, 95.20210837594979, 63.1870555423549, 72.79865131213259, 53.228558510555786, 59.32058380392731, 46.183914807036, 181.60611432764344, 71.48462548415455, 71.39386147221032, 213.1755258395054, 69.66495620275761, 96.43406454708676, 43.20893568448979, 71.11007398554933, 41.41994438159942, 101.02943588261915, 44.183365305866474, 100.67049083623688, 136.80381952377803, 59.06102040399605, 49.81011107288327, 72.61066453694667, 244.1192606332711, 215.45924352699512, 65.34213139178931, 54.81531869997668, 39.048886007589964, 108.37560882548203, 72.31211533408649, 36.53656132063651, 54.25922986547244, 39.22764269598306, 5.125967219406378, 78.3248640059488, 146.1864640687592, 106.27159545544028, 174.63128763318338, 155.14343645747067, 72.12692264513959, 78.80916562949352, 98.83032053741735, 51.871948401611526, 244.04343700723803, 5.639337009089945, 166.55824083616318, 78.3272938555659, 8.73269423575014, 102.64101037874669, 9.510117617623692, 45.30995687841168, 68.20643777024006, 124.25628440624462, 6.626708850695426, 82.6532519796506, 74.5651333650323, 76.7909095031256, 47.23892280882608, 74.58943776660468, 163.37292225263107, 65.50838023540068, 121.66860399847273, 45.959283297422694, 72.11305501655094, 155.75237495126183, 77.97472090528724, 11.349944577437531, 50.97189731766978, 78.25483666714992, 41.43067689017542, 93.85948064659314, 170.56944174104507, 95.04539266023522, 130.49591234542643, 123.76152297404018, 119.40511220770921, 131.04448910833403, 65.07377375571329, 45.14541437426819, 61.04490902301639, 77.40026764674532, 89.623989992324, 45.23452103009873, 67.4582598554838, 48.77916631042887, 73.47766575904639, 99.28678347494977, 72.89872860663274, 66.8838256207753, 90.19188787899917, 6.605568997005443, 89.38254101433542, 146.19205459766727, 77.13804569001705, 127.09850864776134, 112.92227913627934, 70.33433480685778, 76.65228703526756, 8.814637963402115, 53.292776238622025, 6.660960654467799, 73.64161037514322, 57.19235104167082, 56.07804435367104, 69.40671292725364, 111.39210252602844, 72.4644675780393, 86.21829466049219, 92.51574132573388, 49.13041052266175, 35.87054713599954, 88.66028192914895, 52.23659462979144, 51.46039913457121, 56.49256768068369, 95.73586758482165, 30.965957061502298, 260.2776880916281, 105.02071163955858, 58.22051609185916, 51.65378153298066, 63.630639364781054, 59.935145717174755, 46.98296981763855, 65.58590089690274, 158.02018032597596, 66.60586380767293, 46.547488727035706, 66.42584484116969, 85.24432379353047, 112.52660047845535, 94.55392149919143, 116.85443302061076, 54.88276900276713, 161.34138778227, 57.197904561840744, 201.61046636794248, 152.44472633764667, 72.2353691299146, 53.4986596858576, 53.84405692053587, 74.89216536459115, 286.2851532022293, 69.01273491144238, 220.72321513460386, 11.172922680492338, 59.16513422178442, 60.70482708088633, 119.25830098294755, 41.933203427288916, 45.68167238602971, 19.089502144384035, 201.25665067183076, 119.64241828894271, 45.43665229718047, 123.77958148773874, 6.813859841770779, 83.94132149372362, 237.6662708778863, 91.253053373984, 66.16395201575503, 85.87530165905285, 178.7727512555569, 47.27272764243939, 105.0141701557695, 90.77337289554146, 86.15516392974332, 91.32403565628896, 55.21064558811047, 53.97685193586107, 102.52767004989589, 105.40201652892577, 60.13498263564553, 74.43867295765925, 102.39592230820325, 91.04408711896087, 57.76941867914811, 79.00771299105017, 87.93369378892017, 61.27682763240095, 84.92988027068819, 96.59042199579598, 76.12600260412222, 94.73514130307046, 49.44134208700104, 63.69676194285527, 77.4155232550876, 76.66111557119419, 124.68140314100413, 243.32043497744291, 7.427608489292359, 48.481917920523934, 68.48545233791752, 174.32309773942606, 55.520156461440706, 81.26833657329398, 107.49762829916101, 82.91580963744443, 110.8294430458052, 103.9702355897926, 79.19827954118269, 128.44496131324613, 40.033739954009064, 179.64837234832473, 29.555301907427634, 118.22450219323042, 52.05802563097939, 68.7178590262793, 44.679697401186694, 64.90426833002812, 56.38409679179332, 164.9401171616718, 98.09991255884366, 140.2934039362571, 112.80349120390606, 73.64011687475228, 76.05493643</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>119.6728881549835</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>89.1181917350918</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>[98.9356689453125, 158.510498046875, 47.49755096435547, 91.16032409667969, 111.26494598388672, 198.18739318847656, 60.41200637817383, 33.43115234375, 511.23272705078125, 158.48114013671875, 51.626277923583984, 42.90726089477539, 290.29534912109375, 160.8652801513672, 211.46067810058594, 126.84342956542969, 71.72742462158203, 50.49162673950195, 67.76258850097656, 63.333740234375, 54.94013595581055, 53.58266067504883, 106.75363159179688, 53.16450119018555, 152.9922332763672, 103.58588409423828, 105.53788757324219, 503.51153564453125, 186.6125030517578, 151.74859619140625, 153.77078247070312, 123.84358978271484, 81.54293823242188, 61.79313659667969, 77.29109954833984, 141.9077911376953, 48.3979606628418, 52.58103561401367, 37.98579025268555, 49.1172981262207, 72.09815216064453, 145.19972229003906, 80.95294189453125, 118.87158203125, 102.20574951171875, 107.73086547851562, 75.15437316894531, 171.93133544921875, 167.88099670410156, 170.1016082763672, 45.366920471191406, 114.83393096923828, 32.66904067993164, 117.18048858642578, 130.3501739501953, 151.2689971923828, 107.76675415039062, 298.733154296875, 78.19341278076172, 125.46786499023438, 44.67214584350586, 217.32278442382812, 88.65349578857422, 79.83841705322266, 68.30319213867188, 107.1588363647461, 142.2257537841797, 187.5979461669922, 387.2581787109375, 36.692752838134766, 40.369895935058594, 445.363037109375, 181.10043334960938, 49.24034881591797, 132.9916229248047, 85.80288696289062, 56.911922454833984, 52.57532501220703, 65.4236068725586, 73.6100082397461, 98.25428771972656, 191.03663635253906, 102.45861053466797, 174.2705841064453, 192.2865447998047, 73.50181579589844, 155.0643768310547, 135.71324157714844, 73.01736450195312, 97.70698547363281, 8.428105354309082, 45.89398193359375, 63.49058151245117, 53.52174758911133, 63.96279525756836, 77.90684509277344, 134.9002227783203, 104.8642807006836, 112.23931121826172, 144.61178588867188]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>p0.75srandom0828</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:18:04</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>87.72627474727888</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>63.93458778310691</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>105.9285562857749</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>4717</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.9028492323944117, 1.256241178339136, 1.2444520319788563, 0.8934502702258394, 1.8623174472833115, 2.292857017511017, 0.29241265834897784, 1.2382396012729233, 0.7878306557917878, 0.6514772133258966, 1.188677865640958, 0.7147765805796615, 1.0224637143682607, 0.8908788908249153, 1.630030794804901, 0.7652477185345058, 1.2479020215180439, 1.1037795283832708, 0.5963234647452959, 1.254228841338709, 1.6588011764522033, 1.1428861602453695, 1.683145606866618, 0.8009332356922165, 1.5484459718667631, 0.8509949932134616, 2.0812837629807337, 1.3382343202178808, 0.9788793477657318, 2.205119383556384, 0.45436971452619823, 0.9721333636728781, 1.3066721180620602, 1.5516217870740394, 1.2296227761638394, 1.5558479499110893, 1.3064860785010257, 2.3761327899838256, 1.1139418112531023, 2.0726656442216878, 1.796208833724012, 1.8189169001492964, 1.4855580380330775, 0.3218473279404253, 1.4628518002140698, 1.2931157365079162, 0.30332209027999407, 2.8834747307503226, 2.7556566388237935, 2.0273761559140038, 1.1150424119399402, 1.6420156849816532, 1.7053231240378777, 1.356636511478085, 0.29388355928664217, 2.3892512863473936, 1.0610305732309853, 1.1913747594247706, 1.6044291035026892, 1.3361234874879304, 4.776741345469462, 2.221887717475317, 1.6541124419694604, 1.225883121406247, 2.824845238681266, 1.7623983421355347, 3.174136553580772, 3.0360392421560736, 2.9304822604140552, 2.807710371140981, 3.388788273380084, 1.631063211419728, 1.094255719234834, 1.393307946284685, 1.4995997704408515, 5.107551197391156, 1.4465385116395377, 2.4981103658194503, 0.9148562271248754, 2.3139449404020693, 1.2382478168020055, 3.6259066174871926, 3.9803264144647312, 3.4929574100795167, 3.2594270167650294, 4.283430263214599, 3.3550069986671343, 4.639048387034951, 2.272076725901049, 1.9431043914458224, 2.1179528953905105, 2.359418372188211, 1.7973101350142568, 5.122540843914801, 4.144804686092694, 4.418976495739011, 4.130129014614206, 3.4032431518531054, 3.268754126876775, 5.676548277706251, 3.9021433038317985, 1.910465589682462, 3.2943344529331133, 3.177291671290434, 4.161302784907276, 2.787908215120332, 3.6736585251488827, 8.085778235820243, 6.324289756733733, 7.783398438241525, 3.535176671856562, 4.059142814172964, 7.448439363891914, 3.683973855710284, 4.630250939294253, 6.974772122409726, 5.245136535100985, 7.521462286112496, 6.3043730104696, 3.04301689170191, 2.5780586805184997, 5.753076739579638, 4.733237742302065, 5.078007322491269, 3.3489337288831194, 2.5270871481728987, 3.6394525902556127, 5.143980112579411, 6.539000493264869, 5.613500493211108, 2.782854125528603, 2.917030121853674, 3.270707786576132, 3.4970382014546737, 5.870372068092886, 8.115310641633213, 3.850280332672722, 6.441710966219764, 3.9754703379553273, 3.182944581350165, 3.7527631436986204, 6.176069207005732, 3.039067150787524, 6.021801141891894, 5.812499436650697, 3.608776819601643, 2.3159758882270665, 5.736863557965187, 10.085643233594894, 8.049736137218765, 2.6233699781201465, 4.7337749783714616, 7.486983395173638, 5.238414418358538, 10.32976977687695, 9.818969693496673, 8.905225144904614, 4.4113623489371365, 6.468613809413191, 9.062099576955527, 11.527919939512232, 3.762177155701434, 7.92646249980277, 10.517777472785752, 16.841835772452626, 13.295510395893878, 10.475676256038664, 8.172833533391932, 9.987651076573115, 12.293804720802743, 9.615525518326077, 9.538761445366712, 7.063341980713485, 14.463991706967812, 6.058376248180367, 5.873347904021298, 9.478917752612718, 7.10379803716599, 7.518205395108071, 24.54066461912536, 8.271345654045943, 7.754210542761312, 11.346733123709821, 7.925027613917111, 13.30277221437732, 16.33928148171889, 13.093129749380461, 21.88007153316326, 16.84163812088398, 7.995470190728668, 14.90943997813501, 11.749604287990957, 7.731721208336829, 15.788953913063786, 11.648531837963574, 18.26140874628694, 12.1000813460391, 16.65860065131061, 19.31978335268874, 7.0067119107625055, 8.852408023777564, 31.416698124972307, 20.994077392421023, 12.572827701167556, 3.9355020612600704, 7.65423933389111, 7.351166456403039, 8.37382371284377, 26.52011841136218, 23.78965583558464, 21.87469476703916, 9.506592866792161, 16.873822593122494, 24.104776378525557, 13.555043543603695, 4.980830137324132, 11.30428506855911, 17.04207749673816, 8.589302770469292, 13.102074996303516, 15.712215095219571, 20.038855782203974, 18.638887646211337, 30.738151654795892, 19.26681033062816, 20.22607061417776, 36.659049901117605, 26.685562859070952, 16.679236039518766, 24.87182812630442, 33.188357017212134, 33.97944079844766, 33.563305788441625, 35.65208011518668, 12.886003887367169, 23.80371558224932, 24.13444251236202, 33.37355841224194, 35.216475948039594, 16.64328066465448, 14.238416785622533, 14.789677861833145, 15.229780102345066, 25.30595636539416, 34.98929412442951, 25.214073775340953, 16.269950728515894, 24.031269224508147, 9.933930418549945, 28.38441200671129, 17.794046399104978, 32.22121855848927, 27.041229271615272, 41.60753611062396, 26.19558876885629, 32.64666349016496, 16.528338707347608, 24.42766874723641, 34.78142359125267, 35.43555280544274, 14.693507091293657, 16.15166303477867, 53.5221738162951, 35.471567045210726, 36.15493075675728, 38.43430102134184, 30.65454830505763, 40.47753099019697, 42.14589814940464, 17.520071313325914, 44.256391153431615, 25.793751258855313, 29.66762528525653, 24.412530669438183, 36.678779862182964, 50.312253570087464, 23.391450525114777, 63.03656998643818, 43.500851691228874, 31.45577661994243, 25.12744562602194, 15.93857866186138, 36.74101018875161, 32.49344860312725, 50.007367360427565, 24.722691735945677, 33.96777064852009, 20.849208605625602, 26.930341533625736, 25.532884912473868, 19.68735014372081, 38.08125690494861, 33.10316749268974, 28.722738693856474, 42.77319258170141, 40.907035870958964, 22.129245030986514, 34.4056254307326, 24.93665849499851, 30.51803081788474, 20.333051234280333, 45.37987765681209, 25.27573437265947, 40.8165542144206, 41.70611529621471, 38.10985189979042, 44.36219837397137, 26.44088675070117, 26.005178041095363, 31.844901062881966, 46.59996878713101, 42.16407153929842, 37.568914391622485, 26.8176463621379, 32.765258443143786, 28.35702251431496, 43.018592549573505, 16.68792625047332, 24.896437782399715, 31.131121480873603, 41.807654601455624, 27.574279502187927, 22.599308804840163, 46.634834362049084, 45.64509602979463, 57.66788957359969, 60.78547674307187, 23.486320542886116, 29.861056717230994, 32.63353834276951, 29.064607271813358, 21.722938573600477, 27.182939693004798, 28.7399622726264, 48.56082656988313, 49.430311584363245, 22.632898304768364, 27.631892295649603, 30.034523857835687, 43.012867495717195, 31.4260280865605, 21.642407483967023, 37.74816715840796, 22.36670966932006, 43.20545444851272, 27.325396794791608, 10.31485456063951, 42.33949782301102, 47.66036264847558, 33.34040641419746, 25.07912131560731, 53.4931542356774, 12.298484404271548, 75.80020409160916, 25.364326965936602, 15.14414970816124, 40.930115733577395, 43.11298841420582, 41.94341955455777, 28.815584751958728, 29.79844214578346, 10.519521534406856, 25.085589580137487, 44.06610512878037, 73.36646006000002, 69.72059186783174, 58.7122024443246, 39.63973184931049, 37.49706789638038, 34.59068402249107, 49.85600297252408, 71.9847440857615, 55.20612539844189, 64.3153398349343, 77.78359149392884, 44.30500659161951, 46.976760169505546, 47.47067014394123, 31.820472014814726, 26.365250246015712, 26.290795588037522, 46.69782516264421, 15.335711232156862, 48.07294545468081, 32.374615325373895, 38.960848095329986, 13.09294224310172, 50.11262730871753, 42.920258675588585, 44.05220085907456, 70.29393973876427, 13.6782093248409, 50.11865000373562, 3.2362026392930883, 33.82880333429004, 86.38213507183373, 29.46250181071741, 35.282303788819334, 5.609626699881395, 53.28475841166312, 60.41339968357268, 38.255880909870115, 41.84280454396721, 33.63571543475816, 31.879732470102468, 26.886610907911273, 78.11533473860308, 32.91537719840655, 38.83572989531595, 32.55216629629603, 66.2196403012434, 64.42092688906547, 27.330133173318707, 32.41473132303054, 68.135605294817, 62.785239681455494, 77.55329825235994, 106.09476234881912, 34.17729161496968, 42.29511196829297, 59.12712083486392, 68.2333860214339, 54.49400118600562, 49.05079415249822, 29.37233835227827, 42.59299970062866, 49.14149619908177, 42.791101955071774, 80.72857769525166, 29.667923959681485, 57.01066878242323, 61.25362116849395, 45.10141548183759, 34.63900048716848, 26.48263273354165, 52.8571874607588, 1.47744736041583, 72.45043653715581, 44.524207304941264, 33.48843403098494, 55.72650718682863, 25.74307423651314, 87.56348025465047, 2.9808280673247243, 72.46863948273983, 44.72198221609055, 34.0411155014133, 50.91800700460669, 31.101856646959085, 54.596123544807895, 4.690773277743432, 58.57231772272306, 49.25805149606006, 40.58270533524058, 27.706369775535787, 68.86861829602539, 41.84542848574974, 42.3956755978687, 4.465149627094089, 54.42102320408062, 52.1411392324445, 60.198903158181125, 50.039335769807565, 67.86183438033873, 72.55145131376702, 40.71381984419523, 53.52345606011064, 54.50209560586898, 38.9470047048891, 58.272311996309284, 52.07051073229829, 35.29839427102154, 39.39725395036662, 81.90236152953798, 115.55570394243003, 36.32630188779019, 67.78494936342709, 68.17562939814201, 70.01928548153745, 136.7337206906688, 78.96587988015796, 42.21145937853064, 34.977444918652985, 116.3520702443058, 35.29987309350483, 42.039011162701236, 41.396044440718704, 43.42354711652638, 35.34882971752276, 36.656985869789835, 97.40593022623526, 46.58559745952699, 66.21762116463954, 86.54996859242254, 44.33206127968205, 45.06060085338379, 81.45059465357555, 63.37016929074174, 3.676291354978317, 27.989809733024696, 87.38729854813879, 79.25595370869114, 71.55094865960763, 10.307017106419861, 53.18607122759577, 25.662638772137264, 181.11064566591563, 36.4304217543787, 66.50185035641728, 11.999807488111584, 31.983256009875284, 43.96567318709449, 99.30055574558207, 74.52311273979058, 4.454665341935477, 9.875503196407157, 38.1380397921687, 38.3694429200119, 52.28617454790708, 54.1293978314166, 47.627252848643984, 109.151543535421, 37.4824492722637, 60.93605845148029, 47.56236574977566, 63.54755147716572, 101.40599727506341, 90.19428354863058, 9.99199250104467, 68.96230706451938, 119.19493289634343, 12.839258670838163, 73.15417501302113, 45.9882308246312, 46.48238510174645, 49.72374343172575, 66.32552912994453, 46.343198882826385, 71.63634847245704, 69.94788690503239, 55.09364543945425, 125.62335983849329, 15.019742600402319, 79.48095332825083, 37.611151101272924, 82.97236013995648, 66.35291456134507, 49.932302328491744, 39.76638138907761, 50.82534839515427, 52.44608327615202, 40.61731926792354, 95.8872743621788, 45.85405473599131, 42.983115926955904, 53.93631466464156, 46.70444270435228, 44.438883017062366, 39.760978819879064, 38.73788889028581, 83.41118821031922, 57.913395613601736, 93.8363402741223, 106.81062873281883, 40.38718283195218, 63.93570210943621, 49.36992301985807, 96.1884975553337, 33.47938328673046, 49.31692949798535, 48.02056270939457, 31.213645760616785, 79.20457535199061, 72.3243895344746, 49.94010190000597, 88.84401697519337, 43.34772895780698, 43.45120009770291, 95.45185293238363, 74.68090243830599, 40.927612554343185, 36.698576897601086, 92.60629124427048, 79.94460541136996, 35.87019864870818, 32.7578791648677, 73.1748630209708, 52.401463232773075, 37.9604291656495, 54.52747662133507, 46.231432411210754, 33.88257078503952, 144.62722702003504, 64.07796203811425, 45.61197714303512, 48.83831491373978, 37.80047405281118, 62.69752853827822, 82.8057379965893, 51.61279166158001, 53.97482826083551, 46.07952570368924, 44.09664257174339, 70.76984185223674, 81.06009670492092, 49.142246589029696, 38.738179563195324, 72.06448825515292, 53.94109410472625, 72.71763526237704, 75.18208089159815, 13.708268967030985, 113.12567359799934, 74.14298907898139, 8.707960727275841, 60.73814005938123, 50.0767484505121, 48.05052303335536, 48.167341961984526, 37.87924133772554, 42.50510973740292, 89.40519590136893, 35.46991204342995, 68.74610084315935, 62.742024458339415, 12.670181783378936, 53.0759382323782, 65.42280080325698, 71.60471638778145, 39.17851106132901, 117.73820403957947, 79.66562399669564, 47.203713585519566, 87.29959627720895, 44.075456664860845, 6.843199688579949, 44.06838913261642, 75.87058345456981, 57.78854121995741, 43.264392591708656, 65.53736702229916, 107.08844029997722, 41.703097874177885, 79.60206094629675, 58.57491149708891, 56.7204419820224, 53.709443770405066, 95.12827899131815, 63.270959616490465, 96.06425952768765, 51.885909217775925, 10.879439310286294, 50.32399227444583, 224.83933078604502, 125.79334037634118, 42.01478212482121, 67.0070677674274, 55.05157125403813, 8.067617843840353, 38.48958630239559, 50.52907282169256, 90.80605654630126, 110.95379074780791, 52.45467490793335, 116.88940291261972, 40.34720780445571, 77.09256436865128, 43.55135786414922, 92.9609958428801, 32.52148274295598, 114.85268238124526, 64.296022054773, 51.48612641379083, 76.79246996317762, 49.4092335549933, 71.40479148058185, 82.50252807431112, 40.868795536199784, 58.26395641161419, 80.42850255577623, 54.42095691071699, 117.74017469557552, 60.753492001535406, 117.05018956626662, 61.07952679974951, 137.5012083064273, 67.10483730415244, 31.174895779364842, 118.60070611945915, 130.92066450039067, 149.41940530716795, 60.740470472904896, 68.65408021647185, 46.4502087067478, 82.19535716550901, 50.39577354279572, 55.73434619094086, 40.02057716121865, 75.07517728330379, 83.72430980491653, 37.36103396582534, 85.10245507713323, 135.82406215647765, 134.2022944530588, 61.04186485350213, 47.8386214421913, 80.71390620564087, 49.23141147333024, 42.60878392180507, 89.21401214586878, 49.31459131369234, 67.62176230782913, 108.17946351816622, 61.05237772426801, 80.65866142245112, 67.56029218132818, 137.57482703366202, 54.74091004132934, 116.99787310094628, 40.643380277353096, 59.653002271856764, 49.7124914712753, 66.71927694285915, 66.48143752471826, 81.05476996331814, 66.40764017368409, 169.53281178728554, 68.49662006778397, 34.29315750280212, 57.041602984225904, 115.8491609398636, 130.2640717006611, 55.55211081043748, 59.710917776471796, 196.70971307326684, 67.71815537283851, 75.69128341997904, 98.40725796757407, 55.802742846933704, 110.5529492918416, 114.12161343992956, 50.581668649992615, 60.85966241431649, 79.09356747290512, 51.93867183319931, 80.60749876943038, 107.81836180933037, 90.46286567618034, 54.52396312678389, 50.452641814591466, 51.935850505123135, 46.99668784904268, 114.02781579920365, 138.58769670987652, 52.46795343710926, 63.50436611315082, 73.44282440423783, 123.87455315618944, 74.29464866881516, 65.27675219692709, 73.58733371870919, 103.98242144286391, 72.99713145986303, 67.22574061049248, 53.80748175468671, 35.92644798685733, 136.06689245173214, 49.11148715799876, 130.00159065735832, 74.41802146060506, 73.9502569478373, 116.07388149039657, 89.78066759064447, 52.32373563815172, 79.72080039500571, 63.164162321185906, 55.87901628954753, 56.58215174171361, 190.10436619997557, 51.96117629967461, 74.38116422806895, 121.47629256734979, 49.83139380184027, 8.461414303618776, 77.35902134439222, 59.046398049309055, 6.9627760132220615, 84.41221994279074, 55.02877411353881, 65.75168145888412, 28.09420619982478, 62.670892306214405, 144.34605526791785, 70.34848240215405, 7.578294792148549, 144.46340741324258, 61.260408129452266, 77.91539888702192, 85.79185159143383, 82.15566616891387, 58.16938173206072, 50.309849440699296, 61.86312440972562, 55.98430357098683, 117.97250450065411, 66.9071350316441, 58.53591373547439, 47.14289275370677, 39.76407970751325, 92.34052908897856, 80.12282871667139, 41.561892125333884, 50.96316361377104, 199.69852715662677, 88.37418304666667, 43.72400565734808, 44.991199319316614, 219.18225595609647, 60.3398794803671, 36.38852771326046, 48.89187617595672, 87.0662141452887, 47.21677787954024, 69.6702420426933, 58.12435257915088, 180.67720476481045, 159.9136433771576, 72.31952415905556, 102.81082050149493, 49.471164427917124, 61.606012759930955, 70.68565615460152, 46.15363120273287, 181.30071903157673, 37.93849184943827, 87.28536354541707, 53.706722645101486, 102.33224191441217, 57.28943327571004, 64.1328567317809, 95.51581213679628, 78.37265478517553, 123.13965858314195, 56.60802998763426, 54.24818333380821, 51.238544529071156, 68.32809611982418, 38.59992763161584, 47.56646604829191, 51.88189070786682, 99.803840060187, 116.1877532862813, 55.97767780066536, 205.60922689662095, 77.74416255741913, 115.28196066991279, 54.378001160328765, 74.32866859885733, 63.18390680028331, 74.9729605953557, 56.02419613306514, 113.80007868577495, 95.96633228519832, 74.13871127591683, 77.45264523136731, 115.50110578406505, 65.3658617163092, 67.68419412877682, 46.661723384603704, 78.81055413432732, 51.291774946964274, 36.42083487247561, 108.93191802986591, 8.655366891028923, 46.96527914818315, 199.81938572101726, 52.74588614584574, 53.83621741445701, 51.9552224694726, 111.54658613600795, 156.75060091625832, 78.42628125843198, 37.70476221674376, 68.19551996691058, 91.98547317684995, 68.56913336378767, 128.21029379932745, 67.24598565659433, 99.74483355735472, 76.08126739202473, 88.37104115804487, 73.92019045013441, 162.22808971764104, 57.38271443177171, 98.1334177739375, 49.111500416213275, 47.17317697038144, 58.05542960865709, 40.58238971786082, 139.85347876504542, 4.34881190648125, 104.50998914378422, 55.48316762589754, 47.92276854243596, 61.98011207906695, 160.57586774834454, 93.94933500561527, 38.436268134002205, 61.13865756094242, 41.79825931576573, 186.94643901966595, 58.148805129537216, 104.56904905075389, 45.990045442416005, 62.20984019536335, 122.79694812876349, 57.26228162650306, 64.10997472436546, 61.50829856239626, 133.62910384190553, 80.01459344975817, 46.55969656818574, 45.26089683925172, 98.01755648849547, 84.27871822010117, 78.09465773620704, 54.23693986308729, 66.68767659957267, 54.23106421028238, 146.47824169156397, 82.14453977153246, 55.06341980636054, 48.319775692587974, 80.24879434656049, 99.2002641507146, 87.83652415024045, 70.18784432303973, 48.18933260059563, 114.1430332309888, 88.877438940133, 85.58894689149997, 93.5448469114908, 39.255575838855606, 57.366922932417715, 57.318225074634185, 90.06508613035278, 49.95319059786918, 76.17293790975779, 139.27007953333566, 162.66621420802423, 58.870883625753876, 63.291970778413244, 55.25303950997811, 95.78203608571724, 120.73599460536262, 53.684997446429094, 53.81335302731926, 71.49908873599436, 51.40594689737535, 80.65342561161889, 60.56096061552048, 164.19044177534587, 79.38965870279976, 47.76330720908652, 52.1081303590819, 112.03309652605547, 76.86079344136992, 98.13866217910767, 50.9054743550643, 72.03260570147908, 79.43706770457399, 79.45450047722402, 52.819439166620334, 93.64945980610749, 90.1565471761642, 142.64770853593237, 72.40645885868224, 45.46739488480511, 48.39373708748931, 65.65317698375885, 109.36105909641836, 50.79329712943, 103.36716250547565, 67.16714359525822, 56.393403814224136, 47.35150337476907, 65.70926994724368, 47.478082133252705, 58.23942228994163, 61.267566026759994, 73.44197266221276, 134.21467610998963, 80.92857122452125, 37.893791472861516, 90.5852931565922, 128.43360905626278, 48.159611388815314, 110.02755176334367, 119.22088181823432, 47.7847738783087, 42.911877373161566, 77.115680501622, 97.46401631495989, 94.91522621715082, 84.02705989031338, 88.5315455403679, 47.21304261789149, 52.84242238661467, 59.406739008850515, 194.00285762824427, 53.25706404694689, 43.56253020408116, 62.679319675904274, 99.9441127415952, 57.9443966766001, 62.21319303099177, 63.81924557447568, 79.04963579498799, 85.09998357672892, 68.34193780053349, 139.8779080271036, 82.64465211628202, 43.82993616634754, 119.59873160314429, 95.2864560921202, 42.38263010850367, 89.51056297137443, 64.5800459365072, 55.4288900180668, 95.44213406757927, 96.44775617858103, 65.42898131370012, 56.25078703939058, 216.88680938614274, 56.00613590109168, 63.655628942176605, 86.02290522991882, 77.61674604703393, 38.87972171949905, 38.03915176794799, 48.31420992382403, 88.66641562813014, 62.84243431798669, 70.86232982507214, 138.70710346863794, 57.891047693654905, 42.540862095279365, 71.13365067337111, 47.63786651899498, 140.8531449031369, 47.08626095617068, 209.5482738101509, 103.63114753785324, 55.70853289792903, 60.76796644642728, 39.00831858557538, 148.76489451501743, 84.24189917362798, 109.65024567633378, 71.47164729877811, 45.95545618986599, 43.08225234956495, 62.104629190401276, 81.55799376635846, 97.53766930956913, 121.83590192623922, 57.75163432058476, 75.88929076587866, 91.26890604889053, 50.87893103264128, 41.3513980724859, 60.18930007274185, 113.764883476862, 133.52155196214807, 118.93723026595407, 72.60600200571392, 38.9709619174178, 45.780958919549285, 55.96584275334634, 52.51752657361984, 63.440838264846676, 79.37531152318438, 64.74077479590949, 80.9164404194695, 96.72991313736536, 49.06718904855599, 117.23953649631154, 58.33163849258695, 90.15809049109046, 59.8804061987938, 78.97058735481406, 182.39457857759064, 96.88512377454362, 70.20222523483542, 51.97382172022571, 61.303145971894075, 34.52009718129945, 47.996206871264924, 54.938465706355466, 117.99923475366262, 77.86859782040182, 70.2139607707097, 85.98508923041379, 82.01268495305081, 102.32171741567316, 48.20967942840984, 66.39279285408298, 202.9438784438261, 66.71146364086992, 71.0175357381615, 95.68323743702675, 63.88267688497038, 139.45084577178605, 44.87156584161776, 59.096432790967214, 69.90854264596045, 56.72889419496443, 62.746236780937345, 64.5256856940993, 173.10072711677182, 62.45047665412949, 62.868533706559944, 100.13605611782155, 64.39986763972051, 93.48892727889279, 74.67080408150429, 102.34298623588488, 80.57732045735331, 69.30356263783837, 83.85170880535563, 52.23906056104047, 145.0820800855153, 87.13599980708618, 82.99060398606245, 341.71703746389244, 93.63223554390989, 63.898685432179946, 70.37769606201046, 76.57822444620462, 63.08286623604721, 120.07571876768611, 157.5018370692471, 143.53490881749528, 69.19989040558916, 157.67397821624553, 120.19336250195275, 152.44024934261904, 78.01017530272978, 57.491311924709485, 52.126990559649734, 70.00516939995535, 123.30821817199212, 43.31501048298435, 46.88794355026023, 128.7414660528325, 71.03593443141854, 69.69230078357401, 59.32752848743168, 117.42627935465377, 117.73047829646995, 55.605160381722406, 58.97955275702411, 75.71836378903691, 67.4123215488446, 154.74657917126865, 56.71330905533947, 68.38826961492258, 43.27395693090454, 73.115231945022, 78.9772362076358, 119.88974932837449, 64.09144391420355, 63.6012568695382, 56.89049085251276, 63.873652298883755, 66.79128721552694, 47.37427303884897, 56.420490773914274, 66.06336100311533, 72.68149972054407, 44.690329646402695, 69.12375975206888, 90.34119756265902, 309.20225978104503, 73.88014033355577, 116.63131126531519, 127.3774394470426, 33.081571605610065, 60.71996600309057, 80.54024830416269, 68.98019796530157, 79.50870134385113, 79.41930810237854, 97.23809211423799, 84.48895536330399, 96.32608807772715, 196.70535554566632, 58.16347825593659, 60.3340340287577, 59.942742027967974, 82.35003686318618, 201.43236374334523, 104.04898818625696, 105.02720423926355, 58.88606386704592, 120.09931511277478, 98.09034742874633, 104.63690746203714, 142.03238093560515, 46.03562356933111, 126.84571516883307, 72.35303581361316, 103.05559284570195, 44.26752178471369, 63.971847806072674, 94.50275290632422, 53.34598943766438, 40.065613027554186, 77.94699220243744, 54.615411048048635, 64.3412114356599, 70.0626724185735, 52.39329048493695, 51.92496782240826, 64.1593261052439, 49.14750085117134, 97.01127988952194, 80.06181282086617, 78.58872262889902, 201.18986685616602, 50.68914079438061, 51.64486266395055, 55.0920627981595, 151.80177406638705, 53.46203502531672, 83.72371633704547, 54.30947928685318, 52.25518394468923, 159.5644471912371, 72.8074736170798, 49.71381531074732, 66.42621200990087, 112.80063401872938, 46.17525344380515, 102.8060703370831, 64.0203708007868, 75.92297181594411, 62.726914388956985, 65.47585788588184, 162.2872061081304, 117.715481984633, 64.0793895353289, 89.6181522395059, 145.75425446859933, 48.78535178345326, 84.50496458255718, 59.35914636460403, 50.94155854156914, 100.49720789835472, 49.30344406668621, 92.44845192080281, 84.67202888818133, 66.12092065945008, 62.77067961073425, 30.576945189615223, 183.7550667123126, 70.82822134343758, 61.517723359369555, 85.98931069084894, 56.48402096578679, 229.57408070765578, 41.762083332587004, 7.9965214905793545, 17.938233852645315, 63.57585408364495, 18.05353658442623, 73.63642938677012, 3.3553927471860816, 74.2176813373721, 159.83888258633144, 3.2095651480336533, 98.12159550872708, 62.56550071582689, 84.90951457885672, 46.79177545468157, 50.808854993880495, 97.763620938803, 45.1193211340329, 75.42227098813132, 40.979610803145235, 43.67002757021038, 96.38563674516864, 72.4597289890495, 80.67290396615967, 69.39346408959925, 51.6907413691864, 45.36494231909703, 124.25478131680427, 63.856490336032984, 74.8471596492149, 57.06835408619502, 69.55722184675363, 117.29043175009681, 117.32422778168419, 55.37629879333614, 67.14500520761419, 112.7985868648496, 54.55397792248452, 53.10355738856304, 52.565621453512314, 104.57055816393364, 62.270422795863894, 49.268395957650014, 42.52513899065508, 136.82896228325478, 68.98379162383, 64.92641122574048, 111.37941514230575, 59.51144703172234, 45.118514547003784, 113.65126747462149, 85.28952787555058, 164.67884792663017, 159.55005211614903, 170.89219454480804, 58.166078049473434, 142.95022010121156, 52.57922500443778, 67.26875518892462, 159.37358058915706, 142.47873515571212, 64.30509219996515, 68.3866937071185, 126.43119578830962, 153.1748368569216, 49.45994387213692, 77.15347450775302, 54.64517392172323, 70.85309381249968, 106.54634624828103, 84.21619366955353, 117.64465387873373, 71.25052312493352, 49.4600632811297, 36.6955223888067, 98.27828854136422, 38.66398609723759, 58.998870835512484, 87.6344133582333, 52.25461533097596, 153.53119405751906, 87.8667251130474, 81.70782607233947, 74.71286643538384, 111.08326929812719, 129.28639989015613, 3.0981369727566497, 65.35279003494519, 65.31355210632029, 63.772025847878254, 73.42799688332258, 107.56734388664555, 48.62942383379754, 106.6601749081839, 46.31526412175432, 70.56907888997215, 146.61472781646006, 69.22697121141974, 76.31780377111534, 83.73068434666392, 134.02416265945158, 111.6442103018068, 66.39766333808053, 67.99374974108392, 99.68631193249917, 69.18084301022432, 95.3133437473751, 49.90898535990631, 60.824114914033316, 63.77395288554818, 85.82382890242835, 75.23276892001434, 127.45701641713174, 99.23789997767878, 64.55383562888133, 369.306105645819, 76.66865969522513, 129.84631711583282, 93.35621113063935, 48.20268817403835, 56.80037621251574, 178.8117333529659, 107.87371870187324, 78.31905189208841, 223.44313046644848, 164.83775745387473, 211.10716212252245, 96.38323134350398, 52.8164165321659, 84.81884341815417, 97.18516853167709, 62.67648551568771, 75.96943719220745, 100.32920558234021, 155.8281151985075, 268.6376997752024, 8.601953525935615, 65.15469651443604, 226.79457342883995, 103.57129099928959, 310.92734899734626, 104.23432701881521, 81.00029800372376, 41.92811309820163, 41.0733042106531, 77.42854459720564, 150.41450367244585, 138.5714637028725, 54.31267773101006, 8.92630642452423, 123.83009495470311, 81.23329465025863, 45.82044389528204, 203.97900919556838, 131.33401677718476, 75.47904210265801, 106.93298679331991, 78.87721550141171, 153.5402696833614, 106.21298446767061, 168.459017839973, 40.663514223052694, 66.13318087647914, 116.7160282889954, 127.90066662966977, 52.97945055815981, 52.03829850962778, 108.04483321518195, 73.15283728114065, 56.92982457685128, 54.421485405048145, 59.44794527290112, 70.96483042711074, 116.13804993687387, 56.6973587497847, 71.91452273382, 126.20233570126855, 47.75866820085126, 231.41601880339942, 131.03343170241956, 44.58810516880274, 61.57217513427272, 62.779733844553874, 64.07310914230672, 45.65301754424994, 55.28652072482322, 51.07939168773219, 76.77585804727279, 60.961046848232684, 58.95341088058434, 78.43125455928791, 38.91823651932922, 47.2488278279963, 96.52827983276731, 106.07480315153514, 69.34965149363528, 151.69211450970928, 274.8480864376845, 93.12694345674596, 110.30100654542102, 47.22767590295078, 148.5036372322738, 235.81801682021313, 115.61597067448963, 86.07367040309245, 50.63301740187066, 49.23181011754741, 112.83880321857184, 86.62081033635346, 86.22073634682474, 98.52711979810772, 61.85954735695946, 40.35952800024297, 84.25133366633794, 89.59890318734986, 43.09553720361272, 175.84617319166324, 79.0231574875362, 103.34546129180436, 63.44149478076755, 94.59185629492131, 111.68949337526735, 130.62432442089255, 245.4937491697246, 126.57857027811092, 62.064930495735105, 139.15437383128298, 78.13621049897007, 108.82594664209122, 112.31503593941474, 101.74063093277306, 15.67685911436692, 41.8373264676571, 17.605556766652587, 48.87015755452721, 79.4021479924002, 97.20541943008459, 116.08031835055509, 84.16409686003269, 44.06993066680828, 57.37894642482959, 87.1176806128598, 57.162672942941285, 81.1743702010743, 100.95375062752188, 65.54318154183296, 70.8053976659339, 72.85639537129858, 89.31062987760515, 59.76497425749142, 79.37983276206107, 56.78800439302847, 158.03693633676016, 73.59696732935963, 69.62382489838717, 227.40911451653685, 76.30467610401969, 238.65815637446335, 58.17311430449037, 163.30857015252536, 38.77075261626429, 76.67264500159587, 173.9960995632613, 62.33632517203448, 51.065603904689375, 83.54013997655488, 77.53560220022304, 63.68895786889423, 90.29544260362574, 53.807840083077984, 97.24924480648129, 52.58104227381752, 60.01510618855324, 54.6240708291037, 139.77747537134184, 71.91248455906415, 113.39054688185823, 44.179210344859094, 98.13954926018886, 52.02940362056429, 46.664770932793054, 106.91202720041915, 191.50615050915377, 98.56599198452527, 71.51663093791738, 53.14213427674682, 72.04693640575368, 121.40295175553695, 57.84892460837823, 29.854202916047626, 189.4061490498644, 69.16132933409843, 49.46650641275081, 50.882948010901046, 40.5813660639085, 27.519793194257968, 101.77535008184326, 12.340216823850819, 75.71521455722737, 88.62418128274518, 83.52690648787458, 99.54200255213952, 49.79784268492864, 36.069912662559716, 56.689014217424564, 77.59011470986988, 53.25326331427224, 11.469716298192624, 57.326151603830525, 37.34623458263935, 153.7811307004605, 97.70948529268904, 49.7280061106093, 126.99366490608313, 110.10444773615852, 177.33467333219457, 50.37420062111983, 90.35958399127546, 60.706350351909, 74.15854700369302, 68.46903714219599, 43.21557368239223, 84.49099562360263, 39.85186909477553, 62.22647319370164, 93.2958305929197, 86.32051001588964, 54.47136464586688, 164.96502252275081, 76.02335417027598, 64.25273454737186, 129.25522856094636, 42.121011581751404, 55.27862890427466, 79.87341961803762, 74.91252881057342, 116.70431024177707, 52.01775999569365, 174.7115951192133, 104.3982803315848, 217.19067046987206, 85.30804303660837, 71.01252958212325, 59.03532755554258, 132.13100584604746, 103.46694453803734, 99.63655659123904, 64.63212500198202, 57.001168923104565, 115.74225009688432, 95.4088865161018, 65.22459475255373, 72.36129630504621, 51.21664658787224, 61.53552463500049, 58.58840283869058, 97.64941226795182, 77.05673023269355, 5.3661027845080085, 75.85932919461082, 136.048819622395, 96.17857819911742, 120.11671931306884, 52.624890270627304, 69.70384853456105, 70.5303804904187, 76.58050829639556, 47.070797174461966, 78.37422131986492, 279.65478364483107, 399.07734842835447, 127.41279541826025, 71.95515977135082, 73.54111440721543, 105.15403584887123, 71.4626437969597, 240.09088625870547, 134.79220379253024, 95.21181579160724, 5.901672880105959, 52.78103350590294, 35.4008528546257, 129.89932135679197, 80.50186860580533, 69.30755635214213, 30.19943768520745, 136.3249009742816, 43.15960005682498, 61.35814955188754, 56.1417234483141, 73.27792664506676, 74.62221778183536, 66.6052360827607, 83.1280481571303, 59.85727033518388, 67.49552751065391, 70.00562216328234, 123.37068202217455, 65.31448896421732, 81.97965443435663, 62.03755699853173, 71.25359330803929, 70.35606773474412, 276.33783698497007, 86.59361299596495, 62.812875250224415, 15.826119360924228, 91.29637689737744, 133.46789567468343, 35.48595073986555, 86.4441290695425, 103.81448003138225, 69.09802760117992, 59.993438373882846, 115.20295197435985, 83.654717628</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>124.3526091194153</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>85.98523860094066</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>[186.54254150390625, 112.83699798583984, 49.157981872558594, 172.89317321777344, 67.00299835205078, 232.68405151367188, 39.64781188964844, 93.53485107421875, 156.6045379638672, 114.82766723632812, 48.40279769897461, 48.338409423828125, 88.9443130493164, 107.2418212890625, 74.18020629882812, 96.24806213378906, 221.39279174804688, 79.15724182128906, 55.6410026550293, 51.989479064941406, 80.95623779296875, 59.278385162353516, 47.92695999145508, 63.631317138671875, 47.13606643676758, 431.8485412597656, 16.043081283569336, 45.07783508300781, 293.5909729003906, 147.01861572265625, 49.75657272338867, 378.46673583984375, 355.34332275390625, 92.39151763916016, 49.177734375, 118.3093032836914, 71.50887298583984, 48.73383712768555, 153.42410278320312, 66.58624267578125, 77.7724609375, 149.13902282714844, 188.12249755859375, 186.3377685546875, 131.6587677001953, 60.06648635864258, 35.260292053222656, 298.2196044921875, 105.64337158203125, 144.59613037109375, 75.08891296386719, 63.226829528808594, 114.37191772460938, 64.33262634277344, 139.11715698242188, 422.5877990722656, 156.2446746826172, 74.42463684082031, 80.83448028564453, 75.19371032714844, 121.22832489013672, 60.053009033203125, 186.2601318359375, 153.4071044921875, 82.40025329589844, 109.60369873046875, 74.18858337402344, 40.04911804199219, 43.226444244384766, 172.53878784179688, 135.344482421875, 77.74302673339844, 47.085418701171875, 144.2643280029297, 91.12940216064453, 72.4911880493164, 83.88932800292969, 154.58331298828125, 59.8418083190918, 319.9363098144531, 329.38043212890625, 246.65843200683594, 143.01951599121094, 71.48017120361328, 177.39065551757812, 179.6132049560547, 79.86885070800781, 125.23357391357422, 233.73707580566406, 84.78630065917969, 80.53805541992188, 173.88265991210938, 73.98485565185547, 78.92781829833984, 57.46463394165039, 175.62063598632812, 95.3134765625, 87.5716781616211, 233.06939697265625, 122.74128723144531]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>p0.25srandom0826</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:20:40</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>91.92057926362534</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>71.78511871940323</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>102.4523272503588</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>4877</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.8573178763975757, 0.7129361593841252, 2.1022056305933696, 1.2342918200185407, 0.6787053390790106, 1.6981013364941546, 0.7996719245466541, 0.7012660368373773, 0.6813028995155447, 1.490680881177236, 1.6804768619653787, 1.4683457722777595, 2.4597696586971587, 1.3412832082199255, 1.506992478711743, 1.5167577792562155, 2.108158687975253, 0.9366939652583386, 1.066086528366466, 1.031294724505506, 0.851184035139559, 1.3586403384689942, 0.8700189125070323, 0.99611775668417, 0.9622477323758405, 1.49020664031226, 1.188907663322625, 1.5064098159500763, 0.9106424915421457, 1.395263621646713, 1.7085005411025154, 1.2624530929210542, 1.7792969595270436, 0.977574289716415, 1.6127992299918643, 1.6976808563035903, 1.68302765754256, 0.8480866267964314, 1.616400658683369, 2.6918456482917645, 3.3640409896388825, 1.4954021751864026, 1.9639102402334156, 2.7700982435564554, 1.346775422292876, 2.369132964640345, 1.7047221220836475, 2.429713323116509, 1.711775141976648, 1.9466345748238614, 1.5869486102564074, 2.8351050368758175, 2.5889939757706415, 1.0674797842312476, 1.925854582972994, 0.3840383989460226, 1.781893559148619, 1.973521295147137, 0.9417869655772896, 2.021513862582362, 1.2978234038985415, 0.6775106012242604, 1.0409845680541931, 1.2572965271246124, 1.300167121844765, 5.9903409895992, 1.9480595451842266, 0.5560557965410825, 1.1315290642631497, 0.7797043481298308, 2.8987306765899143, 2.3544074516840108, 3.0287029546512727, 2.3357848481496695, 2.5799765615111965, 2.624271147816705, 2.5123344836614883, 2.3160280656278482, 2.1072126622721927, 2.25654605327901, 4.192189864357269, 4.696305565418728, 2.0186353961450734, 1.8625203197432942, 3.1755966698379616, 4.676262258363323, 4.669571453360281, 2.5948565123990153, 2.3931170433396245, 3.815393784106276, 3.0798129597395345, 5.362241112601205, 2.9258838267123917, 2.4926023976807783, 0.7290461532333848, 2.4782707521991227, 2.080825207682969, 5.591093651077041, 2.449718565418051, 3.687403647935377, 3.168264447241353, 0.40682183640555486, 1.9179738624820428, 2.9142316211678714, 2.5469452159867116, 6.657323825751184, 4.064123783579056, 2.4518917315209583, 3.1777955131926734, 5.195936354721951, 3.9873581082638916, 1.24470133717167, 8.283417911493578, 4.64576246693295, 5.416713727816818, 11.475754453184683, 2.8949320508563057, 6.611400420947421, 4.767171032250924, 2.396348265370509, 4.705214813616738, 3.6852528105414004, 6.693077853160261, 5.053220576976159, 5.8744585246173475, 4.308653750080835, 2.5914174320886048, 9.939889750559296, 3.173269438347513, 5.726228869472005, 2.6807087948865576, 2.980034662240055, 2.6025565524044385, 7.249482089097536, 7.862444552424617, 5.60134559547231, 3.4431055791082956, 2.9797112322055774, 6.208051014432956, 6.453060898592214, 7.589595955485791, 4.132959462840392, 5.624935983920124, 3.863587804906307, 5.8535144500204055, 4.611022810794884, 6.077228413797024, 3.8365269971856937, 6.4626635899981935, 7.588913295049196, 3.4032618686768146, 3.2231341532823907, 9.585334779627798, 15.074907353024374, 4.429009135774775, 5.884442825157961, 3.120076505516077, 8.58263930236438, 12.974670453362478, 2.407629088079772, 9.498550174077387, 5.580127487741869, 8.266727641876185, 4.268652424133305, 12.584087028318136, 14.423415382009217, 8.76847141591471, 8.98470926536161, 10.358759617445243, 6.34229663696921, 13.743349426034921, 6.492092135869117, 7.8995599848985965, 11.216801622074492, 9.56871426900056, 1.3992649661565542, 9.374639985304103, 10.582482893379792, 6.0999820672999965, 9.60169118614502, 7.405591938505076, 7.277063325128818, 12.015808547989765, 9.664430693358208, 13.629316351036241, 8.73026708262902, 12.896394576445115, 1.3095275997338813, 2.869126396135629, 8.22803518598471, 7.730174780433789, 13.799590916253667, 17.69541709422311, 18.59913018298199, 30.4202121819928, 10.968721258450245, 1.6866293106068593, 10.136711103303918, 14.266166560059972, 13.892692886549021, 15.351010870670823, 13.096045431416789, 17.35321726593304, 18.28887918238309, 20.088108520437494, 14.275612374894978, 12.04857220755149, 8.715207315257533, 25.111670107644148, 27.30569124360604, 21.096711345985607, 19.46273759805802, 10.378091819148699, 14.319809481611813, 20.74077588012561, 14.26322166451448, 19.99404680081161, 20.795828891113054, 11.66661283379386, 16.56604634593483, 17.40216501278511, 24.768807401652108, 2.1697971630561104, 10.796261378673496, 22.028600495233952, 10.517206710007503, 17.137161801444382, 10.871101090559547, 17.35643753480809, 2.5553973648860224, 27.243346934711244, 15.644241380058727, 18.666512876342075, 22.104295672482227, 20.85314646343017, 2.1340875059001037, 17.762404170425313, 21.482551278011087, 21.063912987979162, 22.87305840133671, 30.43305952397066, 29.621234577590265, 33.00699402136713, 40.62881591118415, 13.176932608418607, 40.84420566053283, 5.322320624366838, 14.991283635500265, 28.678907903948257, 35.585173529388264, 24.991327523526873, 17.95824967304021, 14.27584582272221, 28.557014215019876, 40.16336257458741, 48.63939806576527, 36.76646048570939, 14.42236831513525, 26.309211882785522, 16.887574441266874, 17.635918743096006, 18.82023307006202, 2.8400163094809256, 19.676289395164083, 17.74246257543296, 16.363983522996875, 27.76071486361064, 15.10963533286995, 5.259628213856588, 20.809110018501272, 23.108170153754983, 44.00921015604139, 1.2759109332600072, 19.065714966342515, 32.32401442119254, 30.959653748823207, 36.898620550882534, 57.760938637401146, 30.41011069788321, 19.27923522475328, 31.05268783786367, 30.392008800556045, 18.52479629255268, 47.728214361401406, 27.844021815937566, 49.307111923034114, 28.74126292395091, 22.4340579899712, 24.31115098118712, 30.329832514749185, 26.641827829404022, 48.35208889114445, 20.26481375451591, 31.303080244565997, 19.99754073933893, 36.83639698089688, 31.088106451142366, 51.71007596994376, 43.93039363283818, 25.71443791463373, 44.61582476778253, 26.61212758885963, 2.4277533997725644, 33.00753939352384, 16.994043086890795, 33.23835487042804, 28.916489232005073, 26.614320729522138, 24.368702623751208, 29.28695559910793, 18.493471765814967, 25.129916102360582, 31.442324321429968, 33.03567450192859, 25.575071951367065, 28.214500732339445, 6.434294277397658, 44.30674060721219, 48.41239477222992, 46.47091285970862, 43.460218567272264, 38.04191539127383, 37.96329608310946, 70.69672246873314, 43.286850724920114, 36.4876847475176, 60.9535555135633, 35.09357285806061, 22.052307901253894, 68.82017698824501, 21.131523444909103, 33.282534592768535, 39.8544248547834, 29.379354667335942, 24.41196760845136, 38.034149499635646, 31.329599864965985, 76.97515428024722, 4.281611484201376, 65.80891067098956, 20.397028101423683, 2.0146633986437323, 20.739626321501845, 58.17958506552452, 32.65552314745544, 39.30220361125068, 24.249079773969555, 30.801789855046344, 33.107726094175355, 78.46990016912564, 31.91893741931315, 23.271797814095514, 27.273184721737668, 43.63568981045433, 33.05560318214427, 58.09089183295021, 77.0545466882268, 30.643252688863303, 26.436263233892987, 32.875650563596665, 55.60342364482805, 37.19517232812663, 84.03110241162143, 54.327684336878946, 71.68446895569197, 40.720489158837225, 32.40365155426188, 39.02837463236046, 41.74729182613663, 42.24599773564778, 25.297610904866342, 26.554359761592433, 45.50382200118767, 29.439729659584213, 3.6391623281070156, 77.30866750638693, 82.57663160737812, 93.81999585034244, 39.00845244036105, 29.271565968474476, 32.58800624167542, 60.75534393048021, 64.10396008324271, 63.672175833520996, 71.1911236468446, 71.3510041745685, 75.53280633079841, 65.95209917421515, 47.631382086995885, 43.18350371115527, 19.654971287387745, 49.40928480234325, 101.97601807573305, 130.28004234260672, 33.392284945660656, 50.96663599915657, 47.13077041621697, 64.81572449702718, 44.28857700671258, 8.33067856435255, 65.4848811061126, 72.77810996547282, 36.771194351107916, 59.65774199930746, 28.255101886369925, 60.3383217079521, 66.06938806720412, 64.95282101587262, 8.444557371735574, 26.356281444369767, 56.64237620403925, 24.81628047934923, 48.25090822289722, 66.50249265041795, 48.956519586560155, 30.550528583786758, 84.43286343762237, 48.369478450091755, 96.94812690572321, 61.719854861174255, 27.1437836308609, 79.38044763870134, 66.90442171162101, 37.511044011901994, 37.65409168323136, 29.003730363813272, 84.21701872772967, 54.66094217605226, 3.1078191749715938, 30.106300954951212, 38.596277676316596, 23.760203249670223, 65.21265934995691, 68.5701850894791, 61.69953011604591, 56.155488082755326, 97.26192311813459, 45.809875734046585, 35.626940019037335, 60.01765256922783, 30.938442706209138, 46.62707074649473, 70.71534050728577, 67.86223057663632, 21.473116954762105, 38.08218249025341, 40.73307683763592, 32.247334085661265, 40.76942399874753, 42.11797015125279, 41.70140468194842, 55.6375044969688, 66.790569092374, 48.236219241341516, 35.02631091146427, 33.98720990520719, 29.34866651913066, 25.293883066283822, 43.003936765046944, 68.09604275545641, 50.97948821538824, 46.694001005265605, 38.17897165877205, 52.88737652021675, 32.307559158096126, 33.658912252135345, 54.479707627814676, 54.854934396464564, 43.38101586344159, 37.205221513491956, 10.271581447482035, 97.33011632513123, 48.484707143412436, 39.1539838260369, 39.355206480518426, 48.682047106983354, 46.954871849835754, 53.38398674907238, 80.47227713717893, 34.22271012351793, 41.623402268389555, 51.45570541505424, 79.67927449506847, 59.632540991276464, 4.781883286519899, 40.170240069738675, 29.968345337304005, 58.36349556297919, 40.39860518916111, 56.237386700401, 49.0713637849601, 52.77525419102893, 61.99231114312682, 73.915192840615, 48.764913489928155, 55.389351936367774, 37.389423724547655, 49.06151754745123, 2.773154685358241, 32.72696134878384, 37.29929237978292, 35.78899639411744, 31.159065561880436, 44.6482376757706, 68.1161292592966, 31.955657095696345, 36.130698218484156, 39.61173879081034, 50.919838991736306, 39.52156239254898, 45.1002610421359, 10.605165349902304, 53.73928588582787, 149.41733714249497, 29.8170277660091, 26.384989854124335, 54.480521365576955, 51.56127628468659, 53.73317657499269, 6.631948963620028, 44.24809636216729, 42.44765980301987, 10.090863785657916, 39.156335518574565, 53.88453816050229, 43.9620568281713, 45.27087492539392, 86.37485124558049, 57.36351557829659, 64.45278688095746, 51.13070860179167, 42.91206835353823, 38.941980303528446, 71.01105015527912, 162.78137412843893, 47.76112345076695, 122.88478844803981, 52.72007890215187, 52.33089738514032, 70.04896867222236, 44.49252802082043, 84.255732488687, 119.97148351892841, 48.977378794369564, 58.24633032077226, 86.47480058762778, 33.6537560225281, 68.89573491329917, 35.78915471248015, 80.65293496497553, 35.5738107669878, 39.96074696535182, 80.42055321471791, 41.641918197909106, 73.46770504829409, 37.97474693618538, 4.483493685938308, 76.60488014933408, 61.96855908846509, 40.886919609606736, 78.85555680066777, 50.02755374036206, 60.47696993273276, 157.54129790186465, 56.521315301772376, 34.54265591174882, 35.071144212185544, 76.7021275315063, 52.46662301246315, 127.40413433836197, 41.902464200002534, 45.01573941585288, 94.46093131305052, 14.920141086708231, 35.231420831824174, 52.17961896321704, 86.96119250907029, 60.564613737779936, 57.51739097391694, 45.25589977411073, 73.03852854479604, 64.92853874949252, 68.9166871428954, 96.58841493316797, 33.10679538720164, 52.14323627597393, 31.354050621399267, 56.25929924559806, 40.84666824681172, 36.281160446999884, 61.25332270122063, 56.73227056834975, 102.51061275914813, 56.0966217261422, 58.636652475185834, 38.90332699970277, 66.06915357000774, 102.12201195781284, 97.29215003636618, 47.87084205966816, 84.31525358916872, 47.72963320301958, 58.80301387447075, 47.12531984850578, 73.39986474752057, 74.07804403249665, 69.22027529687946, 174.75857880922464, 45.29977761284554, 21.92443542317326, 83.76404785856309, 86.35271954805562, 102.53989664792822, 90.0256650298115, 13.936505666369417, 46.09009206065874, 30.451452957518537, 55.57763783479701, 49.69115230315871, 39.83580832267709, 43.66324140748776, 53.304116869904384, 54.606327682062066, 59.27118230835325, 66.19771012293286, 98.18644296497054, 54.03051474049194, 41.101934148024036, 8.78288750844944, 56.703740598487826, 53.70838445704282, 54.84130412035778, 39.13625891720696, 65.67221254207631, 101.44642597313077, 119.03874231293524, 104.41826970995734, 39.13424828593946, 38.47149514173447, 8.162081481117164, 94.50709990121463, 193.9784177474403, 37.8177731055734, 51.23075942594359, 57.10479020852157, 48.36427875443904, 54.828402478462735, 47.56121835427949, 41.75329822161527, 53.65678404680082, 45.594101608492, 85.6737332129177, 56.91085045607554, 73.7255358081537, 110.72319123117936, 53.08346731144005, 47.11802458714604, 206.1797775475424, 9.60066430693687, 137.0305365666858, 51.04321779545871, 47.08239628117832, 111.37505457787756, 57.1704103359167, 72.52794237798894, 51.73760393058497, 76.59331743209066, 104.07895831921002, 41.39840718268845, 83.70404269869184, 13.555617429777111, 58.776403909725786, 80.63746237098331, 44.122283167546115, 115.1128721072998, 40.45811051808616, 45.556144675353536, 10.997636944274015, 65.66409176674055, 118.4397125368925, 38.462341156601234, 78.57923940312557, 82.3547534526342, 60.56826862913343, 52.60735756728813, 9.154340486161098, 46.205562006488826, 55.43126516286038, 61.44098532491555, 12.489866706171108, 114.46084857793649, 160.60772891661605, 49.825806587636166, 111.08001528780574, 32.689229543472706, 56.34258091158758, 113.52205501381862, 73.5855278983117, 42.712820328062044, 65.35867129060243, 31.961823163542242, 83.33481394066999, 72.8127624616693, 38.64230519355622, 53.53183183569621, 71.73058441923551, 50.872042236965676, 117.42631596997835, 56.1942784621965, 31.782115055317036, 50.59924504451426, 86.94440464355615, 6.467940192099755, 73.16862367877566, 144.4753882646328, 34.68764905749424, 12.552419418129958, 12.085855156418823, 158.677065114984, 94.11733487790019, 8.286345710884067, 82.25341472371908, 51.75742058670604, 6.235386759960344, 68.31836162018769, 68.22680287196806, 71.99541451024646, 22.025278590876074, 46.12663608682061, 103.05842910112051, 91.04587967817396, 89.3063341658487, 80.25021755494484, 91.6211890680951, 71.18936213353187, 76.09369552450678, 55.489181246268, 73.40843967006076, 62.21377421927555, 59.78527911699622, 63.57970728356822, 59.847206080528814, 15.169296563429718, 73.4873334894939, 40.12343535110953, 56.87458110844968, 58.17717894953048, 55.38755739925604, 102.92931426959981, 84.08412923009043, 56.69333046399154, 92.8598048003749, 79.45156966230753, 58.78686563530893, 58.51126608219364, 58.97220850932459, 104.83861369285844, 215.84101140362895, 171.77281393479817, 78.20200539086179, 39.328828193205915, 88.32224006971488, 38.973908552608314, 50.04579327208468, 47.54260692508673, 48.94592634193191, 77.64024219875208, 64.24750508630086, 92.92806707252923, 89.49819382706009, 26.96053888956491, 45.274036755064486, 48.33149924082944, 499.78420222814776, 75.59332980404409, 49.08391449438584, 49.40196838457443, 56.809605153000085, 7.385811774237524, 122.29776412592389, 56.77319010682678, 85.22414154941713, 36.82813174491006, 118.17893864699023, 47.517997632827, 45.60650775722171, 69.08216777841781, 47.51053525859139, 51.68575139067966, 52.37944331188244, 50.85038964810813, 5.9326833006249275, 189.785371621605, 108.7612675194825, 52.92984097295374, 100.19358524424231, 56.121429960450044, 60.42978300700514, 87.41154780697215, 89.96083650956483, 69.05848574252589, 85.93422141747052, 91.99522780486083, 88.29077110233142, 54.24434605419539, 75.0354135059205, 60.616910296375394, 75.27125646871032, 107.88553487957726, 251.78087808109433, 117.39538990277615, 33.459825184116, 4.230482015534351, 68.76390806065041, 58.45500767974187, 83.31878077805861, 53.8937134055323, 122.13291322995451, 68.78065764707102, 58.723002857862866, 52.102369782854524, 159.88230651799725, 69.9454315529098, 60.44269585687823, 60.606742230766194, 71.60207320327333, 50.35104459714238, 87.29596701468176, 68.50949056051121, 48.53759241142582, 47.9356686192305, 115.31440846671357, 77.6491391111866, 44.00666449245852, 69.45159458581055, 6.469696539269448, 61.08164612319918, 33.9830033894741, 56.371547385656775, 36.86998861509439, 41.584790343844766, 12.814303847464505, 84.60295186349904, 54.40849924110304, 57.73804758089192, 56.44611345660885, 47.06260747167652, 4.539539983054761, 50.81909374181896, 40.45543689124091, 62.03162011293081, 51.650642105680745, 74.22533108421437, 66.34353989489233, 78.51058222589174, 67.47767964758303, 6.372935522668816, 81.48905674106712, 55.321470903470825, 52.22329491896634, 96.37810172622778, 59.199416847327726, 106.66725858377168, 102.54945677038718, 59.35998001087034, 52.772058092728464, 12.411977247098628, 58.1209003170538, 51.096779103833455, 59.37130957448372, 54.9469696009988, 66.99946396248296, 51.003007590643406, 74.3162853963987, 79.92898244519294, 74.80739685772885, 103.62432489144285, 80.32145738903331, 77.04222104086165, 74.87580247749354, 132.38735976626612, 97.16718580985084, 49.51837222816513, 171.0396766955585, 51.43422685986372, 58.6397674635367, 63.93545389762823, 101.416195057742, 78.49526993700121, 55.50716147084301, 72.43722349155375, 35.65964466599989, 88.65779827389208, 22.63576144893564, 130.58384797016214, 93.37298172477183, 159.3658458426459, 67.09935015521792, 82.05434961979445, 41.448790170001715, 51.49844573416029, 4.7078603794542015, 61.76729059233924, 66.26429647853355, 51.02443900631531, 49.615546180424936, 142.4355451634189, 86.38817082460716, 85.01284222048467, 74.35145336766367, 6.8037650927432445, 110.69203745557932, 80.2433693225636, 102.69762986592947, 93.28347851714837, 142.36322681515912, 66.99481696134944, 104.99231533613269, 76.0702873648896, 71.45286963695364, 57.729571547591455, 117.85419914738192, 85.9811368476083, 134.22004154007743, 47.06991630832023, 69.09718415810825, 68.9264345967412, 51.960615957107855, 49.09689260965033, 37.93715979518477, 54.627367237162865, 103.61620056865617, 464.2318036590558, 72.05354625726808, 52.314567030698896, 64.0211537193155, 136.59614118960806, 45.503425549302264, 49.52275665388042, 32.70832757010127, 102.14403007457919, 64.84794836695112, 79.58259920892411, 42.904855060219184, 44.684120035501934, 57.307665292557, 219.60036055336653, 64.95849024929922, 68.40612375247757, 56.237482457973684, 62.65890588796645, 56.282333049083526, 94.44453315129651, 47.12058214608279, 80.52870674640785, 65.93369144951392, 77.54479514924189, 158.57214336144648, 63.48657138189224, 14.481203664388403, 84.52665319474409, 132.84589043446815, 6.432630024032709, 85.59508971893908, 47.94225925803573, 75.51630097200687, 194.62458101724047, 72.20577130769267, 99.4840355790713, 35.32464414446979, 102.61982520433399, 116.2819250829704, 87.43253616253993, 196.58323326448118, 67.27445000086654, 252.7428645405039, 87.03087107969044, 85.97110014429539, 62.58053715594091, 56.18336384872114, 69.03899916442354, 11.075503419361938, 49.096904043040546, 9.564261574588848, 143.39313835809983, 141.9219440381988, 62.86229492600996, 103.94434180834736, 54.07935287172418, 50.42558604639132, 207.99118323043564, 50.39863016735654, 49.22941307170815, 80.79862711686353, 96.87963535343516, 88.61244655948647, 120.27936692662996, 60.4366940857707, 46.26741234004632, 68.55948571330947, 133.2548017857199, 7.701913503029473, 53.56079348757852, 102.2503403974916, 59.1075892037362, 52.59186522048395, 117.14792236293476, 71.25573868591468, 119.4564292618755, 70.6906545266684, 6.360821921335587, 66.19825226233061, 106.47534910803657, 52.916484741749684, 67.99226289252326, 46.512068080741564, 109.80037814401845, 87.31761904399734, 121.63567405124041, 106.4842286786259, 36.15046257201236, 36.80333899754279, 55.08417845901871, 51.99510749464579, 51.07443385297705, 76.17469673281477, 83.29562256140392, 51.257472876143744, 75.80823521593373, 88.57127358143005, 36.971821021628834, 46.507582035644944, 369.41708878521086, 54.76087521470024, 45.6620674859274, 7.8634339603846986, 49.56204604454347, 72.6410961081564, 108.6747726760437, 82.92517439545344, 94.15462413603333, 46.46654522070508, 53.584729114518666, 58.505700722332726, 394.300668084533, 43.746184525723756, 67.58052145985, 104.74590535996671, 62.03673782675083, 63.934567458701416, 63.58202745091406, 62.25581900239642, 148.04222494153234, 129.86804888512026, 58.758384966620405, 160.06481241412547, 63.989705127826674, 104.13710587491381, 48.36467886462508, 47.117031624680074, 12.163360157706489, 41.223501978896984, 65.78080754305968, 77.77643424271143, 66.51702336349922, 123.81380213842317, 68.11098920469252, 55.22824255365441, 45.041871622045626, 156.44076849909234, 42.313595308032404, 63.03908538920629, 97.62670445555368, 74.91810514489293, 44.401709352972404, 29.556012817713942, 41.56454374365035, 109.99420744878938, 92.44700767260343, 54.46072353384505, 110.63282849720069, 113.9595265504932, 39.24797670060495, 43.87988348089255, 42.78433676676355, 149.36482317701623, 116.20486572248605, 7.848635142776702, 83.00710842836239, 68.24580989205035, 71.49477837079152, 75.95058657505417, 36.48069353439953, 72.49794270528142, 105.47442026283372, 41.35776688672822, 73.83841810262675, 82.35232377923377, 39.84085858831461, 45.47200597783472, 56.22117485110604, 67.67816582195331, 65.09623786681021, 51.65844528102261, 59.50033727695447, 90.05085998587083, 59.29458204633848, 263.262289163948, 60.950057465040636, 82.49065939148781, 72.01061818113519, 120.42376839189691, 168.3069377690622, 85.53614439950192, 43.198902979997065, 77.54779253889376, 33.99938540837995, 79.13321592269112, 85.74673843473853, 11.37320575472963, 95.98289128066895, 10.768823050780108, 143.2608135810091, 132.77942505289073, 99.9775087944394, 87.09508962648502, 56.08536117825719, 81.94979681554739, 339.5524741179289, 90.3675718944905, 45.05971762190937, 114.2553368543078, 88.31009632124795, 35.709780357169656, 10.189642353650461, 55.655063385087885, 99.65577478968815, 84.13694313476857, 51.346339550416296, 149.08873994794567, 97.89493215430767, 94.78843478982317, 40.67004368725928, 60.58167399857025, 124.57266878089114, 62.964504371188184, 151.03348796232294, 73.30208762595846, 81.3211560629675, 162.4107116886175, 75.12430900724014, 73.53554735638889, 101.30902174395095, 69.91642765225414, 113.40059670184719, 107.17073411662486, 70.1211622396605, 71.59259353897747, 52.96149147120339, 103.19748782144913, 19.631101792878766, 46.22114850543072, 137.48522474194533, 68.68171151543682, 67.04643854110302, 70.72202225430574, 69.97546771753511, 12.449579387028962, 106.99752448541189, 76.3758818950323, 72.2749138235824, 78.28299788384943, 92.93586504261641, 60.181886680432896, 130.9404973862693, 67.25470834928122, 116.59926964803847, 41.29549608059268, 83.0812679129002, 68.77389132235854, 73.31589743847097, 64.58877456326742, 12.640149848294067, 50.2738519921322, 58.87676217261775, 51.02609252419028, 126.027357717487, 74.22773236288899, 182.89613387307756, 93.949143268668, 61.18464404219546, 86.08696440718558, 104.99739537781238, 12.357291729357321, 52.02588962368535, 55.29021800852194, 51.97690988619348, 44.99937665054857, 112.16621089073017, 69.22603039900363, 96.39186579145806, 54.14426996218689, 58.438218455448926, 490.74239944745614, 75.62936227057266, 96.16304399496924, 97.3514962921443, 84.58703816719276, 53.94027733723814, 67.02595071605776, 38.47836166983834, 76.79156319619045, 61.98882659837224, 135.68929428231587, 67.45752304933646, 66.42968307449355, 57.821999993644305, 68.44021934453166, 68.1039252687171, 49.452027829878745, 59.36939008317604, 66.16744429298865, 56.63980193662884, 46.84841914783051, 74.20202966192839, 119.1970440233752, 72.21475557181247, 7.167400709285051, 56.68148839875019, 77.15468631551306, 57.53413366473201, 85.46221240933384, 7.304234089584076, 19.401973445610828, 61.88311757497951, 139.25908790887203, 48.38602892991668, 106.52889481176024, 58.15355764941224, 160.3727856633446, 98.4714383061859, 53.977656186684754, 81.23789433513952, 80.4286972256122, 58.03361438384179, 65.48962348537484, 106.35153948206033, 99.43433178745775, 183.39288474674623, 44.27718480500712, 83.66170195028118, 53.256963921711005, 155.540197691471, 61.805160017570806, 164.9718530851923, 66.43167265914768, 86.10982360148762, 78.4762841545994, 60.22333218898878, 40.47054782681504, 54.091838579636004, 103.57532900930103, 214.61122784594136, 55.22300176832783, 81.4153221162925, 42.07064145492734, 56.685219376167225, 36.43817462356131, 47.86751714695484, 68.92090958802038, 92.5299353195344, 96.34754860284619, 44.998239092334494, 119.47778244426298, 53.41265299756505, 54.00301918036321, 57.27584791816838, 111.14532897156947, 55.684339968138445, 55.24930389291318, 86.22530814187627, 38.96907824728439, 42.56660269802904, 47.02391487346393, 88.3691500630769, 66.64248535736128, 35.24271944206161, 6.373859249955466, 71.83007545305969, 94.74520681283134, 47.727178933588746, 96.27736609866616, 109.2454480231267, 110.23804732701655, 51.36240219769515, 156.4179108058969, 53.721902683315484, 43.76206478863901, 48.42757415316595, 47.68785383707382, 80.8238642125969, 71.60376225595496, 57.3807390912386, 68.03849966738886, 63.30079123250241, 84.42472475432925, 49.07471257489371, 58.937740414509356, 126.18978992817333, 52.9110553817892, 75.37416969568247, 136.19878737816984, 88.86825709012652, 92.13142594571812, 38.430897119164015, 115.92238539838473, 53.54288602940792, 44.63735414344553, 98.56905874917612, 57.82323097906157, 153.45857077582878, 46.60038938647294, 124.32768802929819, 138.66210231459416, 54.96462497332388, 56.394866609469815, 73.57812175024507, 374.9931636557129, 112.91133219659667, 107.40619968501574, 54.111698324330376, 63.67203111833818, 110.94741790666868, 62.002319999679486, 173.47850284284016, 95.40686393734231, 80.31370726979316, 67.70765993745987, 132.57791617260483, 70.50418152339122, 71.60618267826656, 99.04219856528758, 116.47065583984914, 51.6370322528316, 93.93376263597762, 52.717783910995244, 162.87129122895615, 58.21760236632942, 193.97177805004836, 114.43829487837868, 87.79326040633752, 33.91163417250802, 198.74359408747685, 167.24547268107003, 91.49862393514526, 53.87041625401535, 260.10002006055157, 58.469673130779945, 82.8443000946841, 62.666007042159926, 49.47344706442839, 93.95875514977394, 85.84953148829813, 48.424661698687245, 60.7092235156894, 53.05655744798505, 75.0933311062384, 52.897414307238094, 65.06601494291482, 49.37173527131268, 67.37529676873626, 101.38333260887197, 7.074595922049311, 159.82228050686808, 51.161500154563875, 68.09625899250698, 93.35887026341504, 92.87725254856537, 66.9573765991647, 85.26058129115161, 59.213173222726404, 77.38559810014343, 106.09923975144613, 71.45643333320476, 97.9808192371144, 100.86838081210723, 75.11255712272333, 145.90218966550168, 128.314482468399, 95.3604787857741, 56.68693145185548, 120.40016384553124, 98.70970456283047, 100.32894026692742, 59.244665909142086, 45.454945557046415, 35.132092404804844, 108.00456986809621, 37.7176023109407, 67.42325518360859, 95.63175738162975, 53.48262961758047, 111.10268481467007, 47.01130621664575, 47.341165284539706, 5.710006460416504, 220.30906635806073, 118.72548467347437, 85.80407160244687, 49.15463785242518, 82.56194571687116, 71.76252098417122, 5.038240313701083, 105.16737305308615, 120.44314386957039, 71.95662403728011, 55.27560727406767, 76.51712331186381, 119.83025262662252, 129.19563524468904, 66.62689932835616, 85.99067583350933, 71.92944781739268, 86.46525898873509, 62.91213132109439, 101.33086105594703, 88.49054651860948, 70.92563620689788, 50.35478591146133, 65.56937718202589, 8.318242455676273, 75.46690895855035, 53.62930711445181, 12.435657778980229, 45.053124413985124, 89.51747398176494, 115.80973189767118, 46.98871326239741, 117.6109151688634, 85.45530438000411, 54.57722330273266, 58.21240751156958, 109.18993718317161, 72.19413564574631, 467.44885873225206, 55.84099755595166, 106.46306322113519, 44.53259353465104, 6.891375364696117, 98.11091527893821, 8.617622531906147, 53.91253042536536, 219.06898024313963, 59.48445466259518, 131.90079814250024, 123.32350502307139, 101.71161386891605, 50.65632390198455, 7.162602752270385, 55.67329869286069, 218.14533480231265, 47.09836963747011, 67.68427506615488, 80.33483486452087, 66.6117161764124, 117.30251876930275, 194.43754967901577, 79.81332216321519, 85.58302339561848, 127.92386015739582, 99.05901999522888, 88.01588811167066, 83.08030897578114, 99.41246048549507, 66.71867411585099, 72.63650953777429, 72.9449352684966, 294.86310468664556, 161.29809796502306, 370.21010386064245, 78.5385762420266, 110.73061030058363, 66.8050319939111, 153.55793973995844, 116.86834500650271, 94.38398977079545, 97.58892737912937, 72.08471507580684, 173.44190880957117, 108.15166844958551, 246.29541627350486, 49.460695092150786, 97.98326975619044, 62.40366165706203, 146.2222584934693, 60.55882515149996, 57.10050357797233, 87.88026195365462, 81.97627787369042, 113.1619032153958, 87.1726635313076, 105.08587999262605, 74.11648716024469, 76.79994372644813, 61.02529945017101, 55.56485473397529, 113.75010976255228, 84.20840190879281, 326.125643910034, 102.3829750935357, 53.77328879186475, 78.49292773722725, 77.60082935574503, 52.86242797559598, 73.35599810523549, 59.39969022986119, 16.239446797011365, 111.19849150596775, 68.2924453295409, 106.38240852070082, 39.71487552682162, 66.76864793664836, 8.208152130694298, 92.64857543939017, 68.28057273148147, 104.9712172120902, 93.00532701938181, 137.16071964855544, 63.02764417113583, 71.06727530750149, 133.29723129792777, 43.33107173182322, 105.75805534943841, 47.61584282289802, 65.06826346514534, 197.0964832862655, 110.0435088106544, 49.631474625592205, 53.21150326601172, 78.22110119436118, 167.82928841165983, 85.82541873580477, 84.96867673660007, 59.6455999208681, 76.80305010104337, 105.63595544510447, 91.56913195124815, 37.38160067810002, 74.35471134240271, 41.87048849037525, 74.61493164613312, 70.78833414472591, 16.561563157299446, 16.145363150483476, 185.08163048521072, 121.00350634581373, 5.7843549215120795, 223.0786212186724, 16.507643278748823, 60.81408329019368, 151.63285929473426, 79.3755179102433, 106.51854843438869, 82.36497893708341, 146.42403702783113, 33.95595584947397, 49.24640832722769, 183.38774001803733, 45.901979822969025, 78.59839162205373, 188.93584781089376, 84.32989965586523, 222.05187034774335, 62.72113166278543, 47.375394591143824, 54.02792959744609, 98.55679759911548, 47.11960076434263, 95.5680013537092, 75.65930805038091, 47.23669158131789, 102.96425387022384, 89.54240834847123, 125.2105501201602, 58.92107454234601, 75.86239626754262, 58.111301660698125, 108.05843356832403, 41.14835829402434, 423.5495966725156, 68.16571395471686, 100.42601753455519, 104.15279224366253, 46.338566625045765, 68.82536100837282, 111.05742487941097, 32.78831018256502, 101.96487858625737, 257.4186913652167, 58.18530823796837, 45.0171205692439, 78.41637707540758, 95.36872494050857, 203.4213870607956, 50.27387562759693, 98.57150240101167, 44.74333568590654, 6.652890541913406, 93.12251439104456, 52.19511129312857, 81.21152117065375, 354.2234536044103, 62.223257322806774, 110.16427109119266, 63.175224328502416, 55.80253992391922, 137.22912606182737, 73.33688687837204, 121.5570288474387, 54.002032342789505, 90.37988752229604, 87.86493810197327, 8.144939867490955, 174.4564194101849, 43.388823168318304, 40.10514894784154, 123.43533068200075, 20.526898406921667, 59.06947888586819, 66.65952924078637, 63.739506113820255, 40.8982767248507, 29.32026932078712, 113.32487247695019, 73.62531815056522, 90.66172697326729, 51.72357398452479, 60.034930833805895, 62.3153705769367, 71.16437203648508, 36.575503282949036, 81.66473848362827, 109.66847129293299, 149.9626256005687, 66.63852625303001, 131.79402780299012, 48.02621944301626, 87.57005586486811, 75.45263561633305, 94.61743007444562, 370.75729329608015, 66.02279299465964, 16.657984157352434, 121.62557704501472, 40.959003326605085, 98.07981021606342, 72.21840004366021, 52.95658150105751, 43.62682514062877, 40.17557827569198, 67.08494084346518, 81.39367044244845, 79.71001001956492, 63.02496170387346, 162.7193617732625, 103.99064836418825, 71.09410401811698, 42.318562913733125, 71.7383929172995, 43.60671244843202, 50.28090231195971, 78.57830454058184, 87.26119625563105, 163.54650008266535, 49.190751636406624, 166.26472195501233, 134.64776597181503, 227.13956000732688, 81.37605132457807, 80.95993220355163, 113.32070589668088, 80.36643042087054, 141.82008117156892, 122.77924860662567, 67.42162967976323, 83.82437759212011, 109.12507016009776, 70.97600807438259, 55.28003648667307, 95.22331685566093, 45.44103066676934, 86.72272410609476, 60.04672108541062, 85.38565765677411, 114.92179783406559, 67.3754944021815, 239.09525295760477, 66.28278069401965, 87.7</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>121.7855602169037</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>104.5013879652519</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>[214.9851531982422, 125.64620971679688, 49.854190826416016, 21.764440536499023, 12.753067970275879, 153.9107666015625, 153.01010131835938, 107.27509307861328, 106.27147674560547, 288.2225646972656, 151.61749267578125, 91.37881469726562, 71.86844635009766, 215.323974609375, 83.49060821533203, 103.75284576416016, 229.65797424316406, 134.54237365722656, 58.42601776123047, 57.080322265625, 78.70662689208984, 64.84070587158203, 63.79326629638672, 12.803939819335938, 61.93999099731445, 49.84661102294922, 407.0923767089844, 88.57682800292969, 116.17475891113281, 118.85279083251953, 163.85707092285156, 51.80604934692383, 10.732376098632812, 201.8744659423828, 253.14932250976562, 82.08084106445312, 99.94010925292969, 58.40296936035156, 68.04603576660156, 145.9533233642578, 47.84347152709961, 40.70295715332031, 47.1295166015625, 51.13360595703125, 139.15960693359375, 323.3901672363281, 55.47226333618164, 216.57485961914062, 51.135982513427734, 235.58250427246094, 36.56724166870117, 23.097393035888672, 166.861572265625, 60.540855407714844, 20.595455169677734, 159.3545684814453, 71.33511352539062, 16.915395736694336, 283.09930419921875, 70.80377960205078, 190.13877868652344, 426.3892822265625, 168.82582092285156, 43.942962646484375, 145.3155517578125, 85.20169067382812, 142.34686279296875, 69.44017028808594, 197.32228088378906, 146.25689697265625, 66.50871276855469, 48.044158935546875, 135.9477081298828, 55.028846740722656, 44.41989517211914, 57.93391036987305, 19.690561294555664, 82.76795959472656, 369.28790283203125, 63.03044509887695, 174.1285858154297, 92.34661865234375, 77.65593719482422, 93.9992446899414, 252.47567749023438, 39.274330139160156, 613.0933227539062, 93.19087982177734, 452.8214111328125, 77.67024993896484, 76.16633605957031, 54.740753173828125, 54.13482666015625, 223.37496948242188, 35.536041259765625, 49.93939971923828, 57.49876022338867, 218.91400146484375, 98.13279724121094, 39.02347183227539]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandom1215</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:59:58</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>92.08489446510939</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>76.83153280779486</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>99.96039207841568</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>4999</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.8011264649045112, 1.0397675265229656, 0.6921087159347381, 1.1879087140858136, 1.370542536850724, 1.1467446345530485, 0.3101272008032878, 1.677466696456907, 0.10968628275483673, 0.9739010137751829, 0.09134106012846353, 0.8738299798298741, 0.5791869550466108, 1.6631660359728209, 1.687047905785643, 1.4143520046857145, 2.453902457950901, 1.162286198703704, 1.8301598262763996, 2.2871241272206766, 2.383629646350758, 0.38326341737085773, 0.8065916720012456, 1.1502051566957152, 0.3902932823212479, 0.8181783921990464, 1.0168992680820794, 0.6126925980238034, 0.866796133315289, 1.1671784421346127, 1.429448898424296, 1.0371042599417104, 0.7706399286448635, 1.4353685291368015, 1.0092744268480849, 2.383923134277688, 1.3960381406156668, 1.7707493650856978, 0.5135670005957425, 1.6537541102970204, 0.9125980016425912, 1.7378585747918138, 1.464022927906812, 0.2099145581936257, 0.8695553407243071, 2.0565863202183836, 2.1365567814921724, 2.9589193009266412, 1.8634880492918302, 1.5986372577754466, 1.3128611770742944, 2.42098492613957, 1.83677922059439, 1.877694580786745, 2.1511000908966778, 2.25423919449781, 0.8741750549342305, 1.372107059660986, 1.217919491868586, 2.2538366250645656, 0.39159556515185023, 1.6986038691124017, 2.048175746913967, 1.3632789837605974, 1.967574340514835, 1.550380874145835, 1.0544014076429726, 1.8799628312601697, 1.2665415604100014, 1.2599089908296845, 1.2500666934185438, 1.6938076668783904, 3.359980234885317, 3.692934934316, 1.1235018347186292, 0.31808944477619605, 0.8127957309707153, 0.605883319276753, 1.2459912058299738, 3.054819700227895, 1.8061144232045865, 2.7881600242508138, 2.047698435305375, 2.5238624166732673, 2.211664315301465, 3.5288665822178027, 1.73515225324838, 3.4888596343795206, 4.65594977505233, 4.8123229038231425, 2.3690215715360954, 1.549978042958345, 2.930826111194118, 3.0967379163558535, 4.810440824965912, 2.830100973045164, 3.479537919056316, 3.6450962217068286, 3.763129222365414, 5.695815855980006, 2.7280921188014147, 2.7984642941890647, 2.4269542235353456, 0.8256642458504101, 5.537983315768468, 1.334061577714891, 4.657827477712033, 3.6566625733462033, 3.0610863551612453, 3.5097543195661243, 2.1065552581329667, 6.6630334131601, 2.749770613565707, 2.4009215495027108, 5.802499686294344, 4.059364769114884, 3.3879983590053584, 1.528887282855438, 1.6769161861560198, 5.921924797203543, 4.1577160785796865, 7.93428835336614, 12.177738873538074, 4.411838478990764, 8.312319289864735, 3.8655446288893858, 4.7466309917143334, 5.984463668362692, 5.858091206834883, 7.661577286463199, 3.475073446647793, 6.843572292105119, 3.302487169748469, 3.917649300994667, 10.291290553071445, 3.8683336574882143, 0.3509695286400801, 6.419029520367692, 2.019142357667037, 2.9493289736094694, 4.703764117245227, 5.106722362206075, 0.7265195019576574, 9.198251234137336, 6.359987410148027, 3.6103591435009776, 3.654229083211146, 7.720883954209196, 3.650535970669442, 2.9452438161061036, 4.86182541098061, 3.5431652152397817, 7.567439290023942, 4.829087876051966, 6.249143345632968, 7.984426811562893, 1.5081693122197226, 6.354768979154244, 7.60956591468226, 3.462621787551585, 3.5078211862836244, 5.823369432023357, 16.870329959948535, 6.333426306500684, 4.055581993143147, 8.439500364883568, 7.804246707354614, 14.308237930269609, 9.5142632831055, 11.24094590797773, 7.44787774888716, 6.775832580604362, 11.857798457618257, 11.436954767934552, 8.29789903876788, 10.09334184041613, 7.488731454364448, 10.671985698909323, 22.01752240064178, 9.246433952356817, 8.86914595108223, 12.09377236668477, 10.50898307932752, 6.618731189367893, 7.366689949238405, 10.462844100541211, 7.50510428600624, 7.5784637661279985, 9.57033106537716, 7.819205942984615, 7.1300148425217005, 3.7289791871918476, 2.138904406083811, 7.7250733203917035, 6.35979488999298, 9.700706809101858, 11.669418466298369, 9.846697458855694, 17.41987995398308, 17.782745880472497, 16.656283270379593, 10.127222183156361, 20.991112699560805, 10.740280274326436, 10.891869810069764, 22.67347034630413, 8.3507556957312, 24.170953581519857, 8.513968713496693, 13.53344424892108, 21.926167610571007, 38.367111846821885, 9.090709964245539, 6.350237526763104, 15.556739186972585, 28.462632003208384, 7.456770761591448, 15.157142079238364, 14.358957682235694, 10.908874822535324, 13.463099514660062, 23.520448919811418, 14.783678079516445, 27.17042893058838, 20.965126687283888, 11.461611632088232, 29.245313804744633, 9.701609972517758, 16.152472298374924, 8.471105901493477, 16.596708380328977, 13.42038236990996, 14.58475600608884, 17.267380401275577, 10.865742289732193, 10.538837874902773, 24.487315067064863, 23.319616955856084, 10.231543680350434, 22.495931008162124, 21.128844906322875, 19.660188224581873, 34.17513619530154, 14.639868801036881, 31.665736554017712, 17.32934631436291, 21.917276944261115, 14.936843995486768, 54.316835668586094, 11.07388028697524, 6.847972993279075, 35.01905951645273, 8.259598525208252, 15.021523189535992, 32.92557402867176, 23.484975102708724, 22.077675895763186, 19.388770497600355, 14.325029130040047, 24.468466543503784, 40.964156505022366, 28.472756590208, 11.420685639548717, 22.76833616251522, 9.467592957657741, 41.09335153889767, 22.357620600180617, 13.180381481746675, 26.21071988010667, 38.44124077556986, 23.903469914964507, 30.785845620521, 13.132143052318645, 26.712600013905263, 27.39799094205671, 38.499037449224076, 16.01401892779652, 44.977596733083814, 21.72697900302343, 28.305918707417366, 41.87827063438929, 13.824603131836856, 21.821213700855242, 36.1121331779784, 48.408520919746444, 40.76417708964839, 32.6188786367459, 16.09979693244824, 36.64643361183056, 24.49518057164397, 31.787687588114842, 35.15250706679117, 21.932550557338626, 21.188938401905315, 28.451831962561723, 13.964327417288873, 20.956888646179877, 21.520501705686193, 5.33121052866688, 43.37811701436515, 24.427006601603985, 17.480890343227202, 1.9719409396087006, 2.5919304926860676, 33.03521427109687, 20.45390125380923, 3.0548729460246933, 17.207442510340755, 24.576604246189962, 27.680888226262514, 19.974111157775177, 27.79908918509632, 3.3636555958882894, 28.938602441961024, 26.295860254999724, 36.232400065283834, 35.60513466379766, 42.30763858090685, 28.976815257877156, 27.725502205716985, 7.0703164232409215, 23.0715885865725, 51.45491056148781, 45.65341754336696, 22.700239172235236, 37.10893422780629, 56.20759529907237, 37.26405838150994, 42.945056677511396, 32.30761307869497, 46.2908778300959, 25.91587523278549, 19.69874035957433, 29.537774432443523, 32.703558051723185, 34.79843583597234, 28.664254639793835, 23.92568767838975, 40.699849416602135, 49.330130036223764, 19.50106196641234, 23.94246007592643, 47.497986474346106, 3.608313419602759, 42.21891519753306, 66.6695958871585, 81.73837785089435, 20.63120986586413, 25.242692135559, 48.06926199949894, 25.154344873916177, 41.013260834186, 39.33147755291991, 19.84625696692216, 42.27725748191894, 39.85217533693265, 45.90381423725243, 22.20838002333125, 28.169097960643015, 30.255449260231256, 34.850006825155674, 19.487197438493336, 82.50811057894042, 25.767871747095562, 52.516708926752976, 34.953148354794614, 33.100309104753805, 2.893408651527709, 32.54513562849806, 24.643366436831258, 69.97878559951549, 55.96178890248223, 21.767043043424618, 32.671291012682595, 21.23789167751597, 27.410386459090272, 22.849458526198035, 19.370008231090406, 45.52933062031017, 3.795638238623929, 22.127480183241744, 43.674223575962166, 6.731943317086607, 2.984831842832778, 30.739401109637036, 48.019650840493796, 41.96080074446599, 25.569785020519813, 50.505224826185376, 32.58971236222794, 47.989229166125256, 60.78139536056017, 3.113626214187236, 59.02632552291185, 39.53546812100988, 30.39127629014303, 44.492185546222544, 44.37413736360308, 29.189446712858324, 61.29157456558497, 55.55860423456832, 30.86281598086997, 27.96223613108752, 67.64844707883611, 40.0174048129129, 26.283179356332703, 53.71575414395987, 41.86933846020718, 38.63458527929697, 43.23866756937698, 55.28621938157879, 52.19404062907878, 64.16577221949927, 50.91449015870225, 43.12819700456516, 53.6060412038098, 48.333650294980316, 37.65431343696327, 4.15998290672483, 67.06703768256503, 31.9101185200765, 31.056272216870948, 50.07057162832313, 46.198070549722345, 26.04408943139468, 37.93484534266103, 63.67665254688458, 41.217570697848394, 29.727445560000287, 3.7096499867338224, 41.40120205039323, 55.17251554133222, 37.04662511500779, 28.97363205615769, 51.32574802665509, 38.03826180944362, 32.21942411886641, 26.50059161103113, 39.390685194571624, 109.37843306290361, 45.36473910286049, 53.70250452497062, 91.13657979093631, 87.29669383328988, 78.91696088037276, 49.36141271032931, 100.63883586536714, 40.61688253354596, 42.66361000381627, 29.26080649372812, 44.84413412727685, 76.15203314789257, 55.60583186132969, 67.14800393435145, 43.18396841279219, 50.65811065999997, 34.58665374561191, 42.80868016400701, 48.65445954456463, 98.88842229060315, 142.26381947877704, 43.748205751512664, 51.38303393541804, 79.49247096614454, 42.38773597614196, 34.75274540793794, 66.63492824111496, 54.01741128851816, 73.6506050974012, 38.69713194267466, 48.487889807090596, 41.77672003089274, 86.1316538336786, 35.01100027791489, 23.126617209186506, 39.575784957513456, 64.07791806627232, 59.56530868484861, 39.24821895458968, 58.21496258775633, 38.41210071396688, 45.02800144571929, 186.40589568709248, 44.53730343796967, 45.688468016663194, 37.2334187275697, 92.64714116424854, 32.82688085217307, 83.70299335944497, 42.323328077811965, 18.308034950689233, 10.863137910986143, 140.84718810690558, 54.176755161146524, 8.407892961175559, 114.42983789161504, 49.34111252216823, 99.26616541775284, 156.2076227806133, 54.19073926264694, 59.686006837145825, 55.513945161298494, 86.90855364792051, 53.77350429814379, 65.33677269867256, 58.82818397686094, 72.25544859568168, 13.183558602259346, 40.18159942711241, 44.09063900876398, 69.13825901116496, 160.454509246905, 41.63002924507388, 43.645432922235216, 43.089043550922604, 87.92647091746775, 112.20150023555055, 59.3157478390296, 131.66797030852055, 43.12552555227226, 35.37067747871906, 9.500289625248758, 69.0519989605539, 63.25214109032936, 81.43486689606843, 34.11633431519746, 47.43464349594866, 53.626072401571044, 58.79435165808085, 42.40669785491069, 52.329017903065534, 46.836716008906784, 39.04185581302174, 41.89298869482393, 5.985715390013099, 50.78995510779995, 47.343223767933694, 40.50952749876031, 42.578261229702626, 56.57201607309936, 40.86157028996928, 37.224097703375506, 56.56699462225333, 61.06099396782746, 53.90095333845145, 75.41182934937598, 79.70160995804235, 59.00426399988555, 77.63201717980114, 53.245483265651444, 55.05599687972515, 60.6679904831944, 53.086319081747654, 72.59676382628638, 44.17963453358481, 57.16114629866749, 83.06481033025779, 73.71440173796849, 102.92702387360261, 36.399197115255646, 51.36128023453773, 49.557004115306036, 102.93855642023017, 43.47733486969869, 128.98223760905344, 59.35342302346749, 66.15905847768893, 57.856521643795936, 44.54700440228056, 123.1678176773121, 40.063269127821606, 40.15291889108757, 69.45250512817613, 42.81429473732168, 32.73488819819725, 127.84445142481792, 57.515852679477284, 40.74228641880444, 50.41385988447506, 39.83438615068788, 75.71422371114201, 72.70637863160357, 52.89129665718995, 172.13758533334888, 76.90652438726424, 45.93056338442833, 43.11011925827417, 90.07544673010449, 39.58038594809496, 62.84143525785427, 42.490088435091174, 46.019468897716266, 61.67968912333054, 43.77930972484078, 82.19825481064386, 84.66473366468675, 101.88385388936757, 47.4610524547347, 74.52623793577796, 69.84173112002358, 39.163593925043784, 48.49139664466626, 160.8770195690912, 66.97046702144026, 33.67671720906509, 45.00842626650983, 60.15684765547003, 91.49958808421127, 36.52562039169868, 114.80535343832011, 41.83069667340839, 34.98947951558936, 89.03790769424981, 56.198947823665335, 62.91943639117498, 54.232896344777316, 44.64098657671057, 164.46258427148723, 39.289427168873814, 65.1004534527166, 125.04807607009437, 46.49644950394637, 98.11660462580903, 7.642982083641278, 151.70071754167853, 40.07346057693944, 45.97855969118058, 103.14212577052109, 62.67563323629367, 36.46059950599875, 70.06521860080292, 78.3230130451655, 101.87758260718341, 100.52330833221899, 47.758082046902125, 53.62549447240257, 53.876247217412946, 60.9394401012716, 46.788898502773876, 57.3714053607895, 52.24884399046905, 43.65088082506518, 54.00728957263903, 59.23418677796266, 60.74718028066209, 139.6565647216496, 48.102669233421494, 36.944151791444085, 92.0807733920474, 178.80864876175474, 96.2784808023839, 46.820227378485725, 49.76570840614826, 51.52671975325561, 53.90820239878037, 11.156906807217634, 82.3472498000722, 78.16404534785067, 68.81646375041589, 48.37007341826208, 45.09977756951177, 73.63825797745105, 58.04766758170389, 5.379028589452991, 7.283202255278005, 56.621002567246975, 45.910330076622685, 80.94026639343733, 46.839565868320754, 73.26150646456719, 10.988224992663419, 55.22830752304737, 86.9966113677106, 75.9570878208631, 82.19803793716224, 107.86777850831234, 5.709824305339544, 90.65694018046568, 135.33767322595992, 40.437825558295785, 62.919418773893824, 83.02242377827814, 74.40255559632088, 44.87189658822982, 85.93690995195219, 107.88091925320687, 143.1127961013695, 39.65996316884692, 51.44130453110045, 31.29007472709278, 5.210935695908706, 115.36061258877356, 49.85719635254735, 76.37824592352966, 46.932958792513546, 44.20661348271965, 90.49631198323009, 127.28921513693555, 75.5961219471727, 58.619237636764, 42.947906384878046, 4.497376263678527, 116.24779448418302, 94.50173802005449, 80.19834466064525, 65.17396208350543, 113.51458925563387, 37.9381259710599, 47.736073117382034, 46.133695999331636, 40.75186958417568, 132.58392461037658, 109.87589892339238, 68.43335348288606, 101.15434834750225, 59.74161807536133, 41.37352752816048, 50.1598786703727, 5.2956755581642, 77.58098528363027, 67.5626695787534, 35.566531245406736, 76.51784838032094, 37.27636734946912, 51.13586939967696, 128.84692331248607, 99.5753056788879, 88.59677160716454, 60.13967740298746, 37.77936424116223, 46.8745474956856, 43.095425552758996, 45.208729609890504, 71.43320254677606, 172.99850900133305, 48.21521593073485, 163.75689626371454, 51.409206002129615, 61.19632300935425, 122.93998812866377, 42.52486719884167, 84.02118056751874, 10.524183944503218, 46.13707862507433, 7.163924599530511, 142.35599170827845, 55.8712124883518, 124.21617711284205, 75.01523944262931, 56.67454150968598, 46.83130259263562, 53.729442170347525, 42.2708948731368, 25.68858545832742, 96.14246862958028, 15.945549877623616, 5.610969461421016, 91.61159635961731, 87.53178796517399, 81.55857749470354, 40.54268329833342, 8.842347882846262, 74.88343913533501, 85.25800874098877, 53.33246210673838, 79.81703184010091, 53.23036936997829, 44.045634364705755, 93.31739304639338, 82.02638315300764, 53.594931100523084, 51.79213741671038, 7.637707344214119, 106.39531766452181, 83.08017887796764, 90.18084510915678, 83.66616511343355, 54.9752410655857, 86.45151491375555, 29.180984959255163, 70.85664878185801, 78.66978957057886, 38.84488882433372, 56.834220947296444, 57.94014100962795, 55.293325780019586, 66.46029005954355, 41.903933089371925, 94.923768940299, 40.861689468843636, 74.41947565140221, 62.13113610019039, 52.338622116620726, 5.77669667223901, 68.2671039598232, 115.16736697996528, 69.8111513734204, 57.91008012507676, 36.795623352790116, 41.74684368681789, 56.61242466291824, 38.780661851681046, 157.85035602258642, 71.33057165487283, 66.4738458510341, 58.70985665009524, 50.02605107362102, 60.29560442247322, 108.57517710507659, 58.920903371524744, 50.80664286631937, 55.519902450207944, 57.85876105599907, 62.74457861585665, 8.58059466873151, 73.8105609448998, 127.07212191273065, 72.40362931930734, 40.18706314542031, 81.89198777182379, 116.2333196811168, 39.74037133986967, 54.87331500388426, 4.780190527803096, 84.399875295747, 54.92818692247079, 90.65972791133368, 61.87886982811603, 6.356367973646948, 59.82945218420982, 72.24434067560462, 120.0086688284414, 74.45142206238357, 63.60776857870814, 70.92989540761988, 58.378121540007804, 62.57549724029445, 30.375710494772342, 93.0261502004551, 63.23722931281163, 35.41518006519432, 53.355084664973845, 99.64114705341304, 55.74101598304318, 59.094492072694095, 134.7781672821871, 9.120144533249178, 48.781732574951185, 42.04204856261687, 56.297315506410655, 123.53252024997283, 156.88871508988439, 36.292446814396634, 56.04115697376192, 96.15111446203323, 43.13218819411316, 46.03897889105598, 56.94391763329214, 87.07808878671513, 110.83550931089849, 47.744408428003865, 62.55935163839778, 47.21424244985207, 56.41004826422436, 71.05767442365375, 12.843344766721907, 62.978380741278905, 55.55450902848551, 65.06155726631052, 38.837041243767594, 104.50999650648197, 44.508941285106914, 49.394314931491174, 68.2023512259306, 105.88226298820462, 149.89205161313288, 137.4849303615919, 45.43434724742513, 45.78615724733231, 50.08102856128959, 57.69045135072751, 47.32465185231635, 51.37045526540513, 120.05788349698624, 61.31349966023943, 171.50445919701562, 102.04127848362194, 76.72959052514264, 39.07865927841827, 81.58578043888956, 55.86967004742873, 162.0508304653645, 131.3422412273584, 32.264805844150786, 134.92715106860928, 77.20561946596837, 66.40597457495359, 96.69704093704922, 79.5204351140398, 20.859850316076404, 141.73276255533298, 5.3723689716432785, 56.00201289068263, 37.67525346436289, 51.220313064396734, 96.750875514895, 34.738556327115994, 8.198169688898748, 86.91348218336645, 117.44333319078474, 33.607159275887824, 50.85525470731511, 55.46212958971809, 87.58572269856778, 57.813182584515545, 133.8495446250735, 5.091728584171059, 53.86411616100379, 54.11508771140416, 5.362942020780202, 104.83915881585072, 131.23480227775215, 58.98037717448358, 7.917194683751921, 47.27373759030897, 53.410598903410914, 87.27894892237853, 84.42898312307376, 125.56951567150804, 57.444383731326795, 99.91459725795468, 50.85305025274363, 48.39561725472313, 52.5414739308318, 45.299706229648145, 130.74528637790152, 155.05755871369067, 40.45161668001414, 41.408880736612176, 47.23538869502791, 61.26556262793193, 72.98188930964542, 63.45829002330004, 49.20771250317581, 46.43372869648367, 36.4898665686463, 141.67044918488466, 56.53216520015366, 71.24644247460316, 62.49864729877505, 62.08781054589274, 46.859786015396516, 55.68749861922608, 92.4173897111926, 59.14533240897162, 94.71751880028394, 9.221946471304719, 59.65888655312942, 101.82727551263527, 33.90080938338588, 57.47568203569976, 85.7545717036435, 60.90297389500441, 66.69608275526546, 197.08232667731005, 70.21497762212371, 63.33054719743827, 96.24669595231956, 114.41322274778125, 41.38241203188272, 54.05359201005, 111.09653767124185, 53.82940010797016, 78.70356780612353, 39.40806516039195, 46.87989313110441, 65.49482618842634, 81.92890659251579, 117.65860952032628, 133.84151087894554, 147.6100774668454, 65.66985753592904, 71.0648529331936, 42.557787628051386, 57.32866255009316, 59.21755410860304, 42.39339671148626, 84.94200389060963, 40.80075518189583, 84.30326332366933, 48.114282825258826, 78.73814835939133, 7.394953909328541, 52.499956743608955, 80.26792129641413, 105.13781088820124, 42.79551040238589, 52.9819228153046, 6.258377985871508, 84.41472381029601, 121.19793498113528, 94.29005693972816, 78.65111766435382, 42.858302708150866, 59.34342917751509, 97.0585107069197, 93.23064286065915, 75.81105732639391, 63.266879499142156, 57.20199010293682, 71.6903836600043, 136.5705497303385, 73.894926515367, 47.58732225287974, 65.59253100465926, 62.471746651377785, 67.67006168892212, 96.9048295647721, 43.74250267997372, 37.74582055852386, 58.098047370886476, 53.204929916766474, 68.4475853841013, 149.31801516327664, 66.2010573191045, 51.8359372189804, 45.54289479352051, 81.24287078471998, 46.126536333524015, 107.02211722935452, 60.20039288004478, 68.57954715194266, 61.11483397844484, 105.77671084203642, 37.40270407088095, 92.21707386668463, 113.36800236831803, 39.475824710485, 48.246173487651205, 97.09047780757496, 69.09885929625914, 120.65653247464529, 106.05825932641264, 80.26885521687322, 97.20341363023526, 75.76565313314514, 149.09163516818333, 40.031327203513726, 45.62548149950444, 51.08404461888565, 91.74577011022816, 188.40139063952168, 38.68024405463486, 49.8941777480854, 143.57266049638443, 6.83396367037487, 70.4399700826213, 22.74290912846725, 46.229649399739614, 70.29771769918634, 66.2145158759811, 57.029897357247215, 166.45696036203012, 22.471154536568875, 104.31746232677118, 80.97731245480477, 84.99264015475224, 45.8612022814798, 47.63483790489315, 44.63290486949591, 124.12219294707837, 182.74319679099978, 118.15574958226505, 95.04805714453114, 64.90597572443443, 43.60249643980792, 67.2562006825645, 65.20690587749536, 40.883575120593456, 60.54020420370739, 80.20843920035354, 71.45395831805565, 39.14052305600289, 39.89791229729795, 49.81709556658632, 66.31467150614014, 87.08909035700685, 14.235494233086362, 67.66432846440556, 64.24889487663148, 38.21339439080216, 68.08535754386394, 44.29752291362839, 55.07253358975607, 45.02908997016806, 200.77356277704666, 68.64778192032769, 81.6568904887624, 95.34953712669953, 95.89498636624796, 70.71229873520566, 39.78936070315285, 141.44421112321064, 65.84164573813122, 38.63545402722502, 58.9775098170622, 76.6413314924964, 44.003054888579356, 46.1823171322474, 56.58829269939544, 81.34916234985081, 90.16349908880042, 145.4386412121098, 67.12711639719384, 74.74616636966762, 48.32971891429004, 107.374267717469, 51.38234934240345, 224.0143053924552, 69.89776574413247, 72.8074853540622, 153.05677535359618, 96.07391903658684, 46.24992886878018, 73.39191229513911, 32.76427011147123, 87.73640811609911, 84.97602022261864, 88.69197193505455, 210.5958438157215, 49.907199326318505, 125.22891402964748, 74.16862538491148, 118.95627246972352, 84.0629989878589, 47.06639148102354, 166.4068260823372, 78.54831868007311, 82.92462487952976, 185.56681894852818, 90.44691255615462, 45.58138930574956, 55.47028236547342, 99.03454241605647, 148.61172104940977, 40.895720954691356, 64.94313164327912, 271.4447808393013, 107.97974764731663, 56.33089212793698, 67.78746311364063, 59.9471517401646, 160.40122587775534, 67.42523412042539, 59.79419649979569, 72.86485791070616, 88.6602839045331, 122.72997922901907, 47.13910968956069, 40.08394422303202, 74.52343338080837, 72.6552317674469, 219.47323846167723, 79.78917350306173, 79.27021227035996, 77.41119112266571, 38.163750661681085, 84.02620730093606, 13.560066351571127, 48.27547068069415, 118.34467521509696, 58.21472248852931, 58.27414045759634, 89.2183904328654, 75.16476488901372, 58.65610891466643, 82.40162799442591, 53.21505215162737, 82.75260787573457, 205.9773397538921, 66.13135261352507, 67.48786384255243, 97.87252982240548, 64.62992639781726, 101.08388546763551, 40.25264221423513, 10.758716181453467, 135.21708242849363, 8.76957524867095, 38.269892941188836, 56.21350888409274, 136.00011068478992, 59.054713894974725, 99.75072945044208, 193.5190908369115, 94.8482814454643, 111.51839955490001, 128.98308771274426, 63.288087294505246, 108.77836269780369, 45.961025784848886, 82.138799164535, 98.72137548093848, 47.621252615923076, 41.04720746310401, 70.77814992503895, 75.6565776054507, 55.62549250517877, 47.79591923791427, 64.41769326401163, 260.67551672407944, 179.5857394438159, 7.150706500845015, 138.66789603278283, 246.06779142489663, 65.57519724517887, 64.27021340459656, 65.14777469006616, 45.641211246193045, 123.60456659389983, 70.932335571507, 68.01534742180651, 94.8863811819328, 84.26155850284488, 52.74846483355397, 77.87630630409487, 49.12472263855332, 60.12770327311248, 56.44967995407284, 73.76199371622144, 63.35998523925721, 50.02420434792379, 62.931588000207476, 178.26395586644696, 75.72827191765333, 91.43846626011309, 172.57731290291022, 82.38906297032189, 173.18701817897548, 69.3758961609557, 57.99112028291577, 11.77069754264272, 50.99358106397914, 48.51995899187752, 59.29104601890866, 268.06361290716876, 55.68865762481603, 134.67675261275645, 64.63612766157314, 81.29416281275243, 93.1734526284168, 103.91046509818783, 107.01672021217226, 7.076599068881663, 99.19583222410866, 45.71296605059363, 169.9707309534595, 52.78473519538106, 98.8509329319984, 82.74407777466587, 69.36060890405908, 87.93798407070192, 77.32807096357077, 163.59538471580674, 42.941999615364324, 49.49161916518265, 54.61916817687127, 55.61158174143247, 170.38476080826467, 59.69423262762952, 96.30080108739548, 18.49015581870584, 51.545496918275084, 18.885526518335407, 77.086146619811, 8.33449295800861, 66.88938036134742, 58.952790847501596, 117.9515071028101, 78.92184172083948, 62.18265926067276, 55.08885367048237, 53.723860798303576, 90.05501629822948, 128.99302486890133, 52.84131112548076, 78.31258084423746, 87.89118457743129, 74.85380674594832, 45.851040719478625, 47.468884461249786, 119.62900686065173, 107.20480903164938, 48.105162430718245, 118.35553354746196, 77.39209436869255, 76.50998122262601, 65.45131586251011, 57.617374916148286, 70.48368290256282, 102.55830513915264, 12.837913933253141, 57.99506692673399, 120.32833838859618, 68.497384165871, 60.37522625869065, 143.2271406055666, 122.59841453091269, 86.96173338131545, 266.53209773468546, 73.73687009479511, 8.212528163992133, 9.206774440173959, 195.9405204095618, 21.131778217990703, 83.10432478559322, 131.1066188732911, 67.50526172863114, 83.51416379444564, 66.39439589267295, 135.50353600032673, 93.56576456333674, 59.33056250961301, 76.13766832891812, 15.864627695262001, 88.65394513226161, 75.00672680924622, 89.97749300526641, 66.97739053910567, 139.2934015892345, 61.2865320888394, 219.86201658309432, 42.89570132001614, 48.25439231705021, 83.38731627006241, 40.84420096015966, 59.45878183420771, 91.83718796581596, 84.58847184732664, 44.29431010598783, 150.46491840525456, 88.025330913024, 88.62399651003172, 82.22070036081908, 96.89435567358434, 57.49554430202047, 87.31812044171473, 61.88110887581332, 48.46515661795415, 105.72766849170661, 106.30089416624628, 55.45006822412377, 42.408001556587394, 56.605323057956475, 58.72560290345706, 9.441114489768307, 152.64539307036634, 7.737132099013379, 20.14659617976237, 175.39942920440967, 55.81307702389008, 63.40767924387426, 74.48021666693988, 81.21328959777999, 82.07597100186952, 12.057080633916234, 169.8475916143839, 81.3429789095939, 53.38702013308222, 235.06831200790745, 74.62961640174746, 65.65121165434064, 9.130213203062269, 52.198662467485185, 47.537183819512244, 186.90359957528793, 110.79649522124174, 61.06246215156533, 54.29730297945727, 76.95603982196286, 50.90522835821969, 101.86362839026783, 127.76182426669303, 97.54759147811279, 66.65985211143179, 14.21075842042783, 55.73882956979306, 58.66371880238056, 51.375630110389025, 108.2780671317362, 89.9496270305238, 69.71627340789843, 18.17687617091834, 113.58721888928577, 72.75754181503545, 115.21984513640606, 69.44260121195282, 10.88209285612173, 64.08136052880111, 10.240338653993279, 127.5483859831348, 87.21787428521147, 52.03808518179578, 83.00603762724575, 50.53449636500257, 82.569906899692, 63.73204919557044, 53.72501459220624, 69.63527816714549, 34.915252778801616, 63.5705574147226, 55.51646750896433, 60.25040508491689, 39.88545683529349, 8.176204104787399, 64.33920283338962, 43.97942573877519, 49.35390604865415, 51.34561208842463, 61.32639884182064, 54.735727772718846, 116.02275135935565, 157.94635782597734, 10.969944520915057, 96.83852819712325, 11.655839779601378, 166.26178644468325, 228.38794345033568, 191.85827361151294, 51.1843958360235, 299.7071432681201, 87.843214419776, 143.29814252950717, 43.886542770599966, 119.55464633208352, 111.2294664076869, 82.42463821115996, 122.11357140700203, 63.380683782264086, 52.15942844222911, 68.79856076326116, 76.96770140247693, 80.12254128673021, 94.89817959009467, 106.06028886572875, 41.36611112270429, 54.961101236836775, 127.83702986710831, 92.2023422336688, 69.72033669771376, 128.62029998589577, 140.43562798165334, 145.603294116932, 10.893725291625106, 73.1977374654968, 60.77239958013562, 239.11105899811534, 126.21411931407152, 47.084111575795596, 155.99303432330572, 71.82830213857872, 77.2405348722129, 69.97824914729371, 53.257201245633766, 8.419132701233892, 247.32328794139468, 81.69409244103255, 134.54253544539569, 88.41132357521386, 72.92419718814895, 94.56377065878513, 282.9763188879357, 58.96825043767087, 110.37057139230495, 115.24820326554207, 158.60402874029413, 165.5794885898939, 64.44030853271876, 64.34986562738321, 89.05027757701909, 257.7141981800816, 89.8015833437852, 96.95782072495851, 55.3356596501573, 258.3960155041845, 68.06356650100165, 53.13881352682488, 153.0478727666543, 59.31367810002138, 34.19319276506988, 89.70214303136426, 53.29815311751227, 133.0319669890126, 70.57815135867561, 9.256355897304449, 66.12026853112273, 82.24616136572358, 175.11777328976447, 136.21849805237198, 10.95461853708641, 57.789479905810744, 58.61956788063746, 99.9777287361195, 108.76926065380705, 20.94777071791046, 38.019930527461014, 6.042752737898616, 134.6476304266135, 78.04807160279337, 57.862568276448144, 34.9108041497996, 81.82654976094035, 74.35685950111908, 44.039698095625944, 55.34990161082187, 138.02256706673305, 158.889729349368, 84.02777711130715, 82.090035043156, 238.0383815110762, 32.979844598503924, 114.09948490676096, 141.58355573728593, 230.74716667358126, 44.83865568120578, 44.398257766330815, 70.76533361922952, 87.60578851781192, 96.78014098573507, 106.90910406911212, 87.73040248527042, 68.24720259431952, 45.6861601300642, 107.54673496388703, 113.8826278679084, 168.24831830864608, 82.75387382681097, 86.86733053709004, 47.56525405122757, 113.64568206538465, 150.31821778712228, 59.63265630125302, 159.7081572380414, 121.60442796799427, 22.297271962492317, 344.80565496566646, 74.91789041515013, 51.59682724720124, 61.88778817131719, 53.7183917623735, 63.64217696335336, 45.11834901091583, 88.29123948584514, 60.238312473334155, 55.437458010919386, 103.41650026173727, 47.13004885689332, 106.02249066099088, 62.24365624487176, 67.87795806060893, 146.4118443915293, 68.7271156612499, 129.9027132610728, 119.10460758445748, 62.22572399793678, 54.13573380368444, 105.26274402271281, 89.29753688314497, 63.71091902477687, 132.7660293330208, 104.66199656018378, 48.95169171537682, 220.66634347386596, 89.53911041518589, 69.65849976685831, 37.97897664287434, 111.24470393020923, 84.06552171371793, 279.7457394922424, 55.847783195612045, 84.06019803542587, 184.48218159264232, 75.9141653160831, 137.2504189672839, 44.484866777791304, 52.44121276874545, 204.00460648806308, 133.60247041716178, 235.59482968563864, 250.5249426221009, 49.71725683671387, 46.75998872527983, 106.38048562802511, 116.06813793947894, 79.32731933531555, 83.49165580772483, 148.65149264962452, 39.80370237948734, 77.33574737546469, 85.73084829801367, 58.81684554874907, 65.18966763334252, 49.226895749168165, 115.53656472885079, 39.64540194701561, 8.1017568928936, 216.42968476260683, 96.4386961803385, 124.08087978193208, 206.26157868112767, 146.69010717305662, 88.75750250494679, 92.83428969928497, 109.26392148434849, 51.168639782121346, 82.18380053842122, 7.040627565849244, 76.49961986712545, 93.29272879110447, 51.48494517223675, 55.16573892364931, 56.023369335584775, 82.7563219074962, 30.736559287884653, 80.03040905720748, 154.63824249150414, 111.23953809685058, 51.51523165888466, 87.02497489018177, 88.96952760641852, 74.96091515267331, 89.9060804812184, 159.6384081293692, 82.67219900043123, 222.86721507829915, 61.53591260177493, 89.26664277673794, 123.55328603237986, 88.24651561911669, 83.31247485909626, 154.0321944917687, 106.50209814826977, 291.8233925054524, 37.89434571734186, 8.304638541773324, 33.4387433242469, 84.7082914870607, 115.71285391556242, 45.99112383053575, 64.80448524486464, 120.13562105048469, 35.67170295066112, 98.66073329845725, 149.04621566110572, 75.15630021926984, 46.18956935657616, 16.97042305799619, 52.60935880152461, 53.62618944416967, 90.07272726307886, 43.82869733183217, 78.10980779427778, 182.64004667767492, 93.53079819783731, 73.15788057147728, 77.6832795212729, 110.26869830431387, 134.91916670314137, 156.23584459864276, 85.86170763121179, 84.16494424008218, 263.0310147201822, 62.174519050639994, 185.8097539064144, 303.5004987289061, 45.027644984636346, 76.30238280690578, 41.40140976976335, 85.63947342086333, 83.2798851024647, 140.00207410818794, 14.186933035734745, 130.53824342611918, 55.44765757420375, 78.61328838773781, 78.17779761688206, 168.30532207564056, 42.927560176225, 54.48864218663334, 88.83569778714342, 91.14145741897316, 96.08690848701164, 60.22536726617521, 105.35507024728318, 90.4785864423483, 87.65254775164179, 85.97088630746104, 86.42273713440711, 71.22547234893013, 6.4240194052134125, 64.65685103145628, 1</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>113.8439700126648</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>85.93263814105489</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>[131.1273193359375, 159.8739013671875, 53.8621940612793, 235.9087677001953, 64.7526626586914, 251.1658172607422, 34.32735824584961, 117.17913055419922, 196.92556762695312, 87.9483413696289, 66.1889419555664, 58.8765983581543, 92.92533874511719, 85.4333724975586, 203.15487670898438, 128.6514434814453, 305.6389465332031, 15.303524017333984, 42.07221603393555, 128.96324157714844, 68.47811126708984, 57.973331451416016, 60.72064208984375, 66.20027923583984, 42.52860641479492, 92.3326416015625, 269.312255859375, 65.00688171386719, 150.49070739746094, 76.4128189086914, 161.64503479003906, 52.43532943725586, 217.71734619140625, 140.57579040527344, 90.18891143798828, 70.75931549072266, 73.18345642089844, 61.698062896728516, 98.36180877685547, 268.28814697265625, 40.58183288574219, 45.912357330322266, 56.809242248535156, 91.04740905761719, 53.956573486328125, 227.75167846679688, 85.51327514648438, 149.87347412109375, 57.82942199707031, 67.59243774414062, 64.07459259033203, 132.88648986816406, 11.014800071716309, 150.6859130859375, 57.50522994995117, 135.78538513183594, 81.98585510253906, 10.816911697387695, 170.21725463867188, 133.05874633789062, 361.9944763183594, 243.71127319335938, 143.30062866210938, 11.030903816223145, 107.97257995605469, 60.81235885620117, 69.55463409423828, 115.27265930175781, 72.24052429199219, 236.35528564453125, 194.07070922851562, 58.281158447265625, 165.8627166748047, 58.16909408569336, 39.30946350097656, 42.78050231933594, 215.6039276123047, 123.48377990722656, 63.22472381591797, 111.35980987548828, 116.09622192382812, 91.84227752685547, 59.94511032104492, 57.224910736083984, 71.99778747558594, 65.28129577636719, 112.41278076171875, 617.7435913085938, 154.9647216796875, 168.9499969482422, 94.31657409667969, 58.899497985839844, 77.41222381591797, 59.789222717285156, 51.258235931396484, 188.31649780273438, 108.47403717041016, 32.06501007080078, 56.33781433105469, 177.1900634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>p0.75srandom1219</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:00:52</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>92.31500839886435</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>70.60865227750965</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>101.5346474293843</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>4921</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.9028492323944117, 1.256241178339136, 1.2444520319788563, 0.8934502702258394, 1.8623174472833115, 2.292857017511017, 0.29241265834897784, 1.2382396012729233, 0.7878306557917878, 0.6514772133258966, 1.1846737542222805, 0.7125771019080109, 0.7332350446476239, 0.8424852461866987, 1.4888663214835574, 1.0041221406361054, 0.9367796391193094, 1.4868060598600459, 0.7698854275157389, 0.6905043873681661, 1.294843279831881, 1.6012913564644853, 1.8939841964357675, 0.9633743690154158, 0.35759624657137007, 1.6878878351594797, 1.4317603675712176, 1.6896629757927804, 1.0807659471315119, 0.7383679615947868, 1.1339855895416922, 0.8936969351378177, 1.8831412164325103, 0.35696349888663265, 3.054347189021156, 1.788867838333933, 1.7606936628193168, 2.6541400583489794, 0.7592405179928446, 1.990721997193744, 0.9714209877985736, 1.8674321397944897, 2.0225943548453653, 1.3063713593087025, 1.2037795749352178, 1.3638619588256176, 0.9041077665727433, 0.6599529337623169, 3.0042669569384284, 1.3783695239739093, 0.5013700254715328, 1.6380056805109142, 2.108262421163836, 2.115104624144019, 1.0198531748499016, 1.7888765387123327, 1.1484888173093897, 0.9801713954837087, 0.5540708312987758, 1.0665451963860597, 0.46651797528028116, 1.2657043688533576, 1.2929259420487478, 5.947328683984008, 2.3755412988034976, 1.1012993609057837, 1.391248457603671, 3.1883244446942967, 3.1017678873738634, 2.53339044562262, 3.2609602244522877, 3.0812797662926403, 0.5354295668768058, 3.750345116322393, 3.128731495770774, 2.2288360418003057, 3.908487215015702, 4.682802139830349, 2.456067739173513, 3.204325188224698, 3.368770252200358, 4.601874019515768, 2.8351790496671563, 3.838419259628561, 4.634088360342589, 5.034630630557021, 2.505385228359885, 2.0680961873604398, 2.3518948565534057, 1.7221394405633816, 2.006161843629311, 3.8248703655945557, 1.5970466580805487, 3.431668618897418, 3.255787934807872, 4.377453003420798, 2.450590435903922, 2.608466223571474, 6.397376521032196, 2.7707463572353395, 3.593278562129126, 4.413758856430677, 2.2116306505366237, 5.391895303421362, 2.9352545172020115, 1.6923420019094098, 8.16870416599442, 6.679874094979533, 7.468557778688639, 8.206219994584599, 4.23946896199409, 7.9171147049578865, 3.9718357329430556, 3.462534985797334, 6.003671207987001, 7.338422532081797, 6.373032432055126, 6.659223524144315, 4.410650808820593, 2.2296236246173193, 4.792217382270305, 2.4983280466821753, 3.6413918219740213, 4.18477928767566, 2.9187240342855163, 4.64494707575081, 6.390311787857725, 7.634097457448174, 5.177857567733086, 4.398708716706555, 3.535681272271031, 4.151459037681211, 3.9261215874108775, 9.921151147274568, 3.4242409981236244, 4.9414236831672165, 3.7555407314346905, 5.700413475205607, 3.7130173472493606, 5.404485222125718, 3.9532690406163895, 5.331427024321633, 6.743800070425288, 3.8052083217697183, 2.3745997623098, 6.3264527035811335, 13.349528603355918, 5.717909505150812, 2.887665509850175, 5.604412706615612, 9.380569101726278, 8.335514236320627, 9.610582837664502, 9.310461935987336, 7.045433686440299, 5.7912478621297545, 12.314977454368986, 11.06257561786184, 4.8589131089286175, 3.303683012161689, 8.133647082131011, 15.059562641488672, 12.875881688319328, 8.496994992744696, 5.604984427877279, 11.29986625042584, 10.347929081196167, 7.723870250512447, 6.774264686018, 5.788126021375604, 12.212846882202038, 6.837058235217201, 5.2003870819493905, 6.883306767671329, 8.638846685492057, 8.58847644101321, 10.179592135237558, 6.625771832748713, 6.745367968314041, 8.349396985008545, 9.457958591471986, 8.034162089712417, 15.845329725357105, 14.577231636984225, 17.519859179804023, 22.815227678044895, 12.060407945979591, 10.188342606509783, 9.655077355177005, 9.230892198343932, 17.228260317071452, 11.312528972187916, 15.83098682904457, 12.511689711350602, 22.951268420554356, 20.456783218016785, 7.75154403794806, 9.976584650676967, 26.81917857490451, 13.370643054812836, 15.725399200256904, 20.59753097660529, 10.76814668072246, 11.657594014194048, 16.212826846471227, 11.322018813564249, 24.850704324059397, 17.85652336302134, 14.358774748061004, 22.342812260839676, 10.208323221304706, 9.423321160944862, 7.887124070640637, 15.696287968536852, 7.8287856127397095, 13.796482190475267, 17.11395426097545, 17.9622448781154, 25.44002374429536, 13.46187351228945, 21.529921425059243, 20.712806383086765, 14.148453370985388, 15.686366712173005, 15.037662687580697, 15.334087601450406, 23.15385047847105, 19.72173514048916, 13.465965438367547, 17.05719697301413, 16.68931246695861, 30.383097039150254, 17.67058750670193, 9.73140648007955, 24.55583301345241, 26.53177912943235, 32.132952474583945, 23.348013443081527, 18.842087633857293, 19.58080413869048, 17.680790424103552, 21.363090325374742, 26.233718230853718, 19.231389809726537, 29.05204192845288, 8.287565044956066, 27.41197742896263, 8.462929414751306, 33.88133553687838, 17.706110818795025, 14.170225575042165, 16.919822022354552, 24.684478847475436, 25.4109542125887, 33.56161544582909, 19.70707705497276, 27.400386134657662, 19.73042166196434, 16.980356056095676, 29.261678478762676, 18.39047849222219, 39.64645271560834, 21.84115969655122, 31.923176004670275, 40.91799490415187, 30.224806440918645, 26.961463539947427, 33.2706269121551, 16.344988959233003, 19.15823627137618, 27.269909265899873, 19.288761326326863, 28.90456387568292, 52.471195244917006, 20.94177167244242, 27.98269299449107, 25.217981339087245, 22.92493781926483, 43.15748428508799, 25.90132253814775, 44.57859565134972, 24.570800380493164, 26.75601753955959, 32.618975644166106, 32.76555463582735, 25.795639836393654, 25.892709024439217, 28.94454931082666, 20.419157210963363, 49.0111123746138, 33.80519327775202, 43.12838081003725, 51.99411800996938, 34.2999001137205, 30.64227835180797, 27.292731372230023, 14.94027477958908, 13.989121873536426, 35.73709558859473, 25.281077527671385, 57.1415912865072, 35.801733602785355, 32.459282769250315, 50.207277591640114, 3.409121111070422, 17.920339745809173, 49.083024787373624, 39.138303300363745, 57.533183748799125, 31.1366637446541, 32.37160955700468, 19.287514044267006, 13.275015121306648, 45.056069973734395, 48.320355295725655, 30.3993502801433, 31.633766803139874, 29.45837305020379, 24.057400669281144, 23.486513267058108, 55.07567740112114, 29.19401542436147, 56.72357483491591, 46.206341226387195, 21.70194735500902, 32.48944857454031, 43.527057880890965, 18.221236665349686, 22.559161932583116, 37.58799318444702, 29.610452946573147, 35.35204708807955, 48.8379875085241, 7.279325612030878, 50.20230733741337, 26.458446903929485, 27.04347938491605, 27.96528179779577, 23.937931502043604, 66.5476817653499, 32.497563484106294, 46.870342929341895, 19.07517821406619, 32.763351132483486, 78.86841975593751, 28.989421747813218, 11.914848603984174, 29.508362517660185, 57.54358023721436, 51.47604440561737, 20.84273053426981, 21.692870113399863, 7.613356856861935, 34.904995608035605, 35.71814205852733, 44.71568489453815, 7.061399640709228, 25.509497653609028, 8.692260486624981, 35.53030669232932, 34.891090144546794, 42.37354903411497, 99.70938531808974, 34.22488007464023, 29.989937331264, 41.6007773250143, 63.10579151674815, 61.922851614149906, 49.19622207510145, 82.21761627534367, 47.79468434232968, 67.0753411977269, 38.73128854546009, 47.53717805814688, 60.179905019452626, 18.514255820152094, 41.80721179817161, 22.436809313393805, 27.30235930015742, 76.57614305394743, 52.81477671778079, 44.61327736121481, 64.53326433170272, 32.82530586363025, 54.52208462866176, 29.399912231442904, 13.387507623156985, 50.9234536548959, 30.368350042737063, 25.11825696636042, 60.86323109208502, 33.64565259889102, 10.65952480587174, 4.191529980688184, 32.185893485298934, 64.49174008275979, 4.052278003052732, 32.87777721498445, 36.371608765234946, 69.78297818443178, 74.76552320239698, 42.40384274401415, 29.502970449855788, 59.915417148691084, 37.7553371531262, 47.45558205429373, 50.05485302905248, 48.69200885543373, 31.910925367908778, 25.516100694992357, 51.67884054561024, 25.69618116223717, 28.142850514437487, 11.476375859040163, 56.00729943574051, 46.324764728753024, 49.9715778153798, 96.6171300563226, 67.91439878871772, 37.79626576485172, 33.04274101614858, 43.81192001525798, 53.33342904743886, 70.14732902735496, 64.6713689768952, 37.632500318861624, 45.92460368124205, 23.51532209755794, 25.304983323863148, 40.048835262106515, 33.50896828586118, 58.501486733063736, 56.55224708659174, 38.01855061700575, 41.164100463498414, 43.47487156017178, 3.1766886493853472, 40.359700564640235, 38.79804517766128, 66.44556046663385, 38.57400474664504, 47.70141069890513, 2.6314974208135564, 30.485689974527673, 71.27441529105161, 34.25701264057846, 70.37671960342112, 58.17068601864898, 50.46049076410899, 121.61893485492162, 4.965312686486929, 34.49023057456963, 74.50450796339753, 41.07034749697401, 30.529149278507152, 51.18688887561584, 34.673609772917324, 4.3980753353865785, 24.44026818597081, 49.68500620229467, 52.998968643405604, 34.742101905289175, 70.2435207260357, 84.09065172393665, 34.39920774495968, 77.38350545130069, 63.623681558526556, 49.62127119876565, 53.2456856296637, 73.97758933759886, 26.549023227823486, 40.24687072796723, 67.93688235593922, 47.53545720404385, 76.9561414038443, 107.34203715381837, 41.87771874640464, 64.79486490436193, 38.6959362470274, 81.9868528971006, 37.43996689024075, 74.96849558353271, 48.40667594233271, 47.98322884735439, 60.088652431163815, 60.777525688389254, 43.47017207082391, 81.26936648376581, 30.714744668689946, 48.08297321508998, 50.296461574406116, 86.50049172512308, 50.89143375620866, 60.364627196949165, 61.835844151966974, 42.157096936187315, 77.84594527466986, 3.8736185365974722, 32.301488302047375, 90.60383965701426, 53.314807591577406, 79.3250635588885, 70.413752476711, 67.18048713573992, 238.95374612250683, 53.418443818190454, 53.54325954190182, 61.979511015788766, 56.13463172551562, 10.109266121637662, 45.11420631454485, 41.92517026662854, 54.57273851933096, 10.436328645040337, 34.336316282594986, 55.616892464119374, 52.4921637767083, 48.901655275887805, 104.37698245045327, 67.3182656440882, 56.71030885865799, 19.226232357567188, 55.43801389638843, 106.11590845632782, 81.78531271216812, 81.5345203979708, 48.28943902371479, 53.72139381912283, 13.95048398637649, 15.65787981751593, 4.602135417694726, 43.82052951265767, 50.725735069479555, 8.765470726235963, 73.18376258514148, 42.223846634872814, 68.2131402297219, 52.10267004898072, 143.79483004645414, 49.82786375612206, 135.61735672000842, 61.55355288934928, 67.2936396438097, 78.6084311198261, 41.966899061310805, 63.35613289948722, 36.05697893354897, 60.56037910590397, 58.03018766029731, 64.44079112129927, 42.17196684661057, 61.6008030222975, 83.06194321100367, 35.603613282873596, 123.81061793789647, 96.63933409484798, 40.96659002681561, 43.9784422928427, 142.0856531065733, 74.17528089291412, 181.6216638187866, 37.77460964185574, 44.897962105211505, 63.094303340683005, 39.161334913877624, 57.36282763156553, 61.34987559835542, 65.44050049595897, 30.76558633684599, 126.74205138139486, 100.84983801665926, 34.88238298064267, 73.32241981470513, 47.25664500826744, 71.68575739612042, 51.822338550396005, 75.59246176566482, 60.6641533419384, 56.97323107678524, 48.04371443487644, 86.97895013106587, 42.19655441402102, 38.61208755676101, 60.95383811123314, 35.26239877428065, 46.96223013479827, 174.80849128901994, 35.327924519008924, 36.18103852904198, 91.67496513770176, 72.35976666700277, 34.39514516142321, 56.51132920367224, 53.34450948744777, 61.287353685031995, 122.68809303348965, 68.17347562640829, 81.68844993126969, 49.414492103442996, 67.26001487671977, 101.20984853225535, 88.83757558384609, 43.92679757690019, 57.11897334533252, 66.21614083554817, 84.69242669952654, 107.6238647974068, 203.93225245365048, 90.72691492821879, 35.87343903458071, 33.838955673227225, 16.313174752769374, 52.11359054082665, 66.12663646403823, 74.41717605436212, 47.96457134469025, 82.76661475049933, 35.938053402557074, 45.519603984030724, 47.233329354787855, 12.05518927629905, 43.09424176365087, 76.70159147710946, 70.24980238620934, 38.150984722388834, 93.79538715557057, 129.10746316669596, 52.983085613310266, 41.56500261497992, 47.6505855567238, 51.13538629223943, 54.52182691681655, 48.69899012800042, 45.957797297287364, 39.12678048696498, 70.71689832285396, 75.2122276677225, 77.94178027420948, 177.0938984994337, 94.3353672894848, 38.3622798990725, 47.68142672604726, 59.716650598657196, 101.68873997463487, 64.02745287092175, 117.92327299304884, 45.71611493538392, 36.39536816491554, 147.80864144655268, 119.37753130580302, 55.3356770480555, 79.67909705174675, 93.44760605651862, 42.421372000575225, 58.01706489691476, 83.33183825123874, 94.11022597105301, 51.4364022135892, 105.55076236295237, 45.63634198401447, 220.3815798708183, 82.15858361509312, 19.34303239269226, 71.10825164790832, 72.3910651163649, 74.62467870610668, 52.27396425099371, 52.32135814426264, 49.86936242678171, 122.46437819615157, 92.9284550379523, 86.63069353676326, 111.36386069481755, 45.980585319470514, 159.85833822058328, 36.94760514745729, 135.09802412314437, 40.935741539998, 46.990757875266034, 41.251929640068504, 55.176383696777904, 32.150793910016205, 54.95975121323646, 105.13277687343017, 39.32484669576666, 88.23262753762765, 53.874013157849, 49.648884205577716, 100.06944031147667, 57.08984623932149, 32.298601796078, 52.23981443322321, 100.57780363965578, 43.898818012451585, 36.97990070764588, 69.04028202070022, 40.83173543865391, 76.22228112178195, 84.20558874113878, 83.28015191034504, 57.351803468596465, 54.15516232188194, 48.26983319696278, 89.5285949242212, 54.444292632563766, 51.195908230025324, 108.39052232957792, 47.2084708739422, 112.78882057136921, 53.21201402833108, 80.25733993082261, 57.18889375474064, 130.45147774058626, 64.55746231327385, 73.55683265880893, 92.05754864246155, 49.2608443885674, 53.98583907426327, 64.67139996902414, 31.902656893536655, 145.98994421972273, 46.66009726539562, 48.448727761624475, 68.77298520667486, 59.578161349084, 102.84306280058527, 36.46297891869107, 53.02504467187941, 60.195878232046205, 70.42690380522357, 93.63499311434316, 45.74752439814634, 50.38602706780688, 52.62929969431671, 67.89437951330079, 63.62253305623915, 90.87492725542377, 244.2452596183954, 18.89935355687788, 126.2440930094526, 123.44704949032987, 50.04147564809763, 62.627332648142875, 76.87948191472424, 88.2958208958004, 309.8203646913025, 216.6428584694804, 35.68487722262314, 42.25614342659366, 41.16133880295944, 37.32919373667754, 66.00740946382686, 84.73065875363766, 49.15704331264419, 52.94967375793065, 78.28048333695347, 54.115914699475674, 89.23738341365481, 38.74769102172133, 80.9904282731123, 49.62015989068851, 46.17372906954472, 66.82981827775247, 68.27845010532856, 47.910886716963034, 137.96599604912907, 54.07225689512168, 104.3530711120664, 44.457965718356434, 143.98566657152634, 77.59457644847586, 81.27695914397806, 71.2734506396664, 193.27156929164022, 78.26907577087577, 62.80077744273028, 114.40556139455639, 80.39897267022158, 250.82873617911474, 118.81540687338092, 56.171306990777374, 78.07612467858145, 53.570955664881694, 8.47856971694611, 66.51295778342384, 70.52681209431627, 7.2830526258364054, 95.13237401826451, 59.981592988468506, 68.20916979455768, 29.181425204989782, 68.25470770182551, 141.02462501369442, 70.98172690483891, 65.7040844975817, 72.75979192682108, 80.65183479452503, 68.43021983673756, 67.49668465280425, 115.06152213928716, 61.742428763013244, 50.99573476593355, 66.15086278316373, 60.328661590360525, 101.8871569545218, 80.35780289551765, 69.29821802603927, 55.68231665044955, 41.31953613880047, 86.04476605429555, 93.96879370381825, 36.71250528177479, 40.25339747437732, 106.8098616619821, 69.12517214338236, 50.64706895937671, 18.062648110206798, 42.066592656118495, 38.50088809349992, 125.77822536475608, 192.1931909399289, 116.52672103848595, 81.09489717482991, 68.03226683504522, 65.1198536518087, 49.297646289620864, 54.56714963357322, 54.88288840907871, 109.66261897313935, 80.60833936937036, 49.685271542119544, 66.86429729506803, 50.209241287920094, 59.43047786628572, 99.53067384013342, 51.64575015295001, 102.9657189945488, 67.34563596169677, 70.18549672512822, 54.52588662292644, 85.29203809256197, 50.73080811623436, 46.167685636130514, 68.94774270457826, 86.70902038686158, 64.05946882521476, 95.40599966615447, 47.44432888526806, 31.809641766591774, 100.24969166258211, 77.49413365202338, 58.09734368158002, 83.09476890870022, 82.50047468705463, 100.68870343660612, 20.29288965825451, 149.5072766273534, 16.549512052225804, 94.19468517179604, 67.57621406414911, 66.74499276912844, 164.1582570219681, 151.11541503510216, 81.39127588012097, 79.04266522138424, 36.11165820694424, 75.50741524043393, 145.9332647176222, 183.88156846174346, 65.37694353132714, 124.87288799622087, 84.90410030004725, 97.62650202547657, 67.09342477351827, 162.0017151086538, 44.26729836378669, 70.36172537335, 34.051696088448836, 248.3520298435359, 86.2596311672708, 39.62037590397986, 100.7619970753587, 61.1267173954724, 68.22128253209367, 133.7770082172275, 123.41937953004786, 71.89424183895684, 77.4733528204972, 120.53497570280759, 225.9234131218715, 57.08543578578867, 84.43354137713418, 81.92885300713021, 104.78759473203215, 93.23491194428283, 112.55636362922338, 40.674017091406995, 72.47058376429494, 103.87617157759423, 12.491084578218109, 68.82058629365976, 57.10135384949549, 40.81984243662111, 155.72222651299418, 118.85131462144744, 60.598137764650524, 67.0583372036631, 70.7354394008184, 136.73375265890758, 72.91136344069528, 70.78586033720786, 93.64631393079864, 58.16688246347489, 55.35068743948969, 64.41404561105156, 180.47714990503957, 38.83951702827055, 49.4086540497717, 66.06906290669905, 132.29715448946297, 54.553290116876745, 81.05438981590818, 58.10761086944509, 108.24171310855594, 66.95018596112408, 95.33832043601106, 75.86232626105466, 77.48037529991464, 66.66715382891121, 80.3518880620835, 137.50130161017705, 81.12534181596884, 140.4672324745034, 116.22438707354848, 79.00192920401689, 62.960397755517725, 48.90279432997079, 82.30943855435635, 187.06744699278343, 86.99509831387316, 93.93424444429657, 42.28471600092519, 81.98040558200643, 84.17499556794009, 72.09579168661922, 62.358430038141854, 111.1703755755742, 35.235972855240405, 56.600975600014884, 548.3605728749191, 83.33556837181376, 48.402327137457114, 79.9697630547652, 8.8009362700275, 168.40680889882142, 82.43593670178248, 91.25771047597541, 67.26205923992345, 70.73764494749983, 177.267605474131, 42.01891434395067, 50.96728939700433, 90.69034702716897, 85.18942691742504, 71.23847073561123, 74.31753714587785, 62.9139102081427, 57.377031281515514, 109.05578211625694, 66.12514513431209, 79.75251507964302, 40.923986545151415, 56.90912668599855, 117.4725006911737, 35.4314614520022, 69.10668563659421, 130.4341547162107, 69.40257613033452, 54.190329208103236, 125.4121068200854, 109.14517144928004, 87.9939216884568, 106.26710664715463, 53.38543041108609, 55.61932674522746, 47.49946684050408, 105.11513593087503, 53.772067163836496, 62.79343171099529, 67.91168111906656, 61.113748706407776, 86.1736643312977, 64.958197477826, 81.04936345775727, 37.7352924547202, 66.12199338993561, 134.44623662165426, 67.37261535886302, 75.49411855930052, 105.61341655212495, 43.90715549093515, 157.16621963489163, 86.1759574185159, 47.45978327413313, 94.17462161311714, 61.88770347482018, 69.19408450302171, 62.89709328117818, 135.98156589100302, 103.89927756858705, 99.05448854113621, 76.18009203443764, 130.06974603462945, 40.53919787189719, 50.43846033713271, 54.95022601884051, 70.04181736585981, 71.60913650278044, 98.93869009586227, 37.47109701155263, 57.946517247556145, 142.9731181314395, 43.972360667660105, 128.29865487160774, 40.69271193361565, 77.26893657843688, 144.15955061444606, 200.84997995761265, 70.46258465171957, 103.99936120116705, 108.95255038735492, 141.2966727549291, 39.483849414142846, 50.742631297184104, 42.629852308465445, 102.703788278681, 101.54977717601345, 13.862726941090543, 171.93704322762835, 73.8879040127375, 65.57682190615567, 99.98699861443549, 68.79738117170788, 42.651619757727566, 60.694902706757496, 129.48557408917654, 75.4091715181038, 42.08032137022251, 30.127644748944252, 45.004464120086304, 73.20142636378003, 68.34910422090677, 8.622047054684188, 63.59286764086775, 70.62677912429818, 42.38166828948666, 82.29309999050223, 41.87876385780617, 60.21491818464147, 41.442283078721566, 139.06012546415693, 42.68002233050763, 58.322732016735, 66.64854079411113, 81.2403479371315, 52.573393419769296, 47.62274106088911, 56.77087066988315, 41.44951283221119, 144.7524957042193, 76.31577848927887, 39.15635596292013, 49.27091058957711, 88.86814931646427, 39.206074052509294, 43.182958778295855, 64.76631463396687, 68.6230658060224, 156.62580163147246, 115.98774892993679, 91.29150097326048, 63.994709423874006, 299.07034306121625, 78.96653888853126, 143.86111107164396, 69.82791442361274, 67.58464402377022, 91.8153609766754, 40.159074547513924, 80.22974426732978, 51.75043143725131, 44.497293401997666, 32.56093514420618, 100.55833737005251, 81.95459482291272, 93.56322152028757, 272.18585686358097, 57.88859109856066, 53.359172418631296, 69.67513344155846, 57.302610258603174, 80.61614516950199, 88.30560222551446, 224.73213822306644, 116.33599490367449, 75.14177347373078, 234.9782706490336, 64.76817703699444, 55.901860264502524, 60.60841776827751, 67.05739520530312, 113.17406258148297, 57.951133278537895, 84.02569482610917, 259.55207524946746, 118.0096511108849, 57.42549827742865, 71.86551184938214, 53.9058198161028, 134.48966928094387, 55.03835013665358, 105.0551998817075, 75.22965880580658, 60.260011776160454, 89.26201812604079, 52.41432721863792, 95.26851772774721, 129.8418113049557, 39.09828554792439, 63.29332975725834, 54.64263858613222, 105.36608509240273, 51.030719970769425, 136.58256366198847, 111.36524373357912, 105.00129258520869, 130.21411813973478, 91.36845625939765, 112.74682166132408, 172.2368835226756, 91.10212658635558, 54.15701747618128, 111.35210881785521, 65.48390513493285, 86.83582968834594, 77.90279038570104, 423.16420937057734, 78.64627962443774, 80.63824730943224, 54.31123406766888, 97.60276279183603, 62.89267581917334, 253.23317901404388, 56.69853802837114, 133.46484814566458, 123.5976507928339, 216.68690018293574, 96.140076877077, 190.45924670292948, 112.26343982432249, 65.98424828378491, 38.64995747980604, 74.77170358349915, 69.15759550881239, 51.96935211515018, 21.235273745610627, 45.46246094794317, 138.45166153008867, 73.84763294263217, 77.71020810169266, 58.3505898526036, 163.69196194496254, 106.2391291323872, 62.511881716792125, 70.0857485344152, 67.29485377875842, 93.0931313595513, 127.90329383695865, 92.15687361439474, 101.72548266834416, 38.77610299582993, 73.89569106513306, 76.37147746397235, 60.40076737293916, 93.56008921674942, 79.3668664459051, 88.82264201769667, 62.26814569869324, 116.03045822397804, 47.70667275508556, 60.71920139991491, 68.16174174426646, 90.94706476004139, 46.79113351622651, 68.76788930140873, 84.99658065762112, 187.1637578019005, 109.66168390659261, 131.4804960485261, 54.22126010788656, 74.85956622052959, 53.30015540488271, 68.75040987254611, 61.90382251850503, 63.41425410924242, 32.62344099109556, 179.81607407042202, 80.18650266572538, 51.342380019867896, 213.05573361299994, 201.01147790083107, 38.982030574255944, 195.33637789092828, 77.77203321069882, 88.29094882434687, 111.21789288939699, 85.37576496140217, 72.79090334532728, 81.67439585447882, 49.85399049996682, 208.27193338194064, 53.99377564902745, 70.37228955545574, 131.60897255375076, 52.81641397036726, 35.13428625514208, 142.25836385943944, 69.4356056806467, 92.33660483933558, 48.01524653328494, 86.83892963432046, 121.89794919143054, 58.11426488313374, 38.49948020458061, 76.18293322136873, 43.18420628769509, 136.43113812718917, 136.10887279462526, 82.25011029424589, 60.879972731952414, 46.23148424651372, 65.01865286309334, 95.02783196860207, 86.52888068170009, 60.73177369535991, 410.4150058299498, 45.195611219668635, 39.36445621187563, 64.65356949693918, 68.58329077220165, 93.5798318483186, 65.43128496982474, 97.34470199604411, 77.4072865579141, 92.81865077142893, 67.90828668894947, 56.086515898922016, 70.21070172796605, 89.58361006749502, 88.89332568496445, 83.56129270646662, 85.49184006635852, 66.8110372400631, 92.97353787702248, 45.960224029783426, 116.30008118692278, 73.71114902365971, 137.6995318961941, 149.28504675799215, 54.06086654558648, 164.6645077455168, 81.58873435743982, 164.01983237140328, 20.844896712017867, 48.023475833326366, 104.08761406028559, 43.43530513736954, 3.3314975023801585, 17.53854689428597, 84.04317450451757, 46.81452607357621, 2.818275245191353, 69.10219265392335, 58.599772796006455, 77.74461642475485, 55.34800805846388, 51.14212317221557, 64.47894521530338, 86.99067296869153, 51.172338117372455, 57.58240612363978, 121.88244412462517, 83.2583703200716, 61.90784697475705, 90.13142313301307, 52.852725238095076, 45.54820651399329, 86.49110931543557, 155.90847135969065, 65.8559325611691, 74.90576469068503, 155.773505176718, 48.444572480285444, 60.25859338416568, 126.93447165494334, 59.261808050851535, 121.36362454447475, 47.52165363982982, 81.22935253720287, 107.0938512125017, 88.71928386176154, 39.99418302961521, 65.48764006089488, 59.17559236299423, 84.32594530714883, 68.30104124273808, 45.15885886297167, 123.4693752707337, 156.49457266575422, 65.33595187938752, 50.06570081779695, 75.12775360416269, 72.36613912222775, 173.0235967921887, 65.68379187866263, 50.30988731616747, 128.6284704490985, 67.60878205854584, 47.279281093907954, 90.75600332409438, 61.33613464396593, 52.115923896962876, 87.3555020629889, 80.32298243416255, 40.217594811964105, 69.00742670676883, 48.242983599243416, 81.5934853886004, 57.45276218751387, 80.48009444485984, 59.000878900222745, 217.886890502582, 52.357251431949074, 82.06517682746247, 45.20790907598747, 77.63617290613097, 224.5866984984194, 80.52874058632568, 55.5109056655756, 115.10619693120937, 82.80472640832815, 87.33760183166284, 93.19058823913565, 101.18571519175865, 226.44852879920674, 79.50338120221738, 47.898297135109935, 94.46544560898009, 44.93797925362115, 157.3744795334113, 86.35904205495818, 79.94589740434259, 105.46376981259016, 75.90908269804538, 57.854239266482494, 40.600408575181504, 89.74741751531984, 42.87276624004905, 66.57885664840008, 83.02746932793369, 44.671462899559124, 68.36083888270635, 93.52569040190241, 108.78044008911863, 165.080240527976, 104.28909775208821, 84.6137930188217, 94.69690432845921, 150.12886625045104, 126.04573690995798, 111.8577669878368, 141.22824535303982, 86.34356790629386, 51.676389595127645, 45.06772485192496, 92.40772778275763, 165.89537555291085, 86.54970300610934, 79.71251651686613, 65.61813631806685, 48.33077814526795, 51.47154219329188, 24.082694124784865, 45.082493270020315, 294.45929788529884, 40.25059416669736, 40.850787524695505, 58.27464560024994, 121.66094490284065, 84.58693062138067, 47.774397249069494, 108.11205905675347, 61.35830796098027, 59.00452861973262, 227.0427741588382, 53.54939471820172, 10.220975597964419, 8.45290999397381, 152.28826396156444, 128.14283886910616, 90.17020438204985, 233.0448701328499, 35.10787026666613, 74.31174323795237, 55.39042832114975, 53.99246999297692, 120.32621159754447, 66.43855938884923, 81.06999321433152, 72.86926426608645, 65.01135927065683, 84.40667874007161, 48.902520821977966, 79.24878574871353, 60.54405068016712, 43.73175707640451, 54.42447800269507, 115.01661382557951, 92.029332591012, 166.28415122517657, 187.90985608934284, 103.92094941834493, 103.81102700229286, 122.77469168403591, 268.0203484467725, 110.19031247283849, 145.83193843642164, 93.22068246837428, 81.28237448517842, 71.2988973204302, 151.83396762805032, 60.00234352370374, 48.257963579293296, 79.23068443527163, 148.70362000757746, 94.55745591125186, 176.94723636671785, 97.77554315526153, 165.89762149045842, 91.59587291929338, 117.5366341637249, 121.5113514285982, 77.3836633537732, 68.65712102417389, 45.43513156517807, 67.10080009329387, 76.1479319326222, 89.14108602517894, 60.08663023365143, 157.48777006289424, 45.81274108393459, 48.23979139873239, 75.26906299651601, 133.32401894895224, 75.50510946047721, 20.936501262860475, 66.71418643268115, 265.38417820826965, 68.56535468656647, 44.7665293841977, 75.08531288392332, 77.3339097547751, 108.41451253001793, 61.08019982828986, 76.00172804603784, 82.01459626511254, 91.99317006237244, 57.63301066267203, 273.04052183328713, 152.77277523393792, 109.90600590458358, 63.691888165674776, 53.28824210284837, 49.86962184348202, 75.55849886618488, 48.917283706797264, 84.2578647827642, 83.32443387244976, 58.538319558546114, 76.64543309622549, 49.74194624577339, 40.91438619536027, 107.58291580028151, 124.20668685331432, 47.83527488874573, 75.61005645639061, 91.40599019584633, 111.23293288410483, 181.86340187357965, 54.245793867088864, 77.21953250433404, 17.710637638461478, 42.43696016378102, 138.23230364691028, 133.83473629613798, 106.31505276593239, 44.824896722271326, 65.59323014039512, 43.93544334076832, 71.63002478129162, 133.84174401542543, 117.99702428702254, 90.02560569401881, 198.30219894475587, 49.443055722163244, 37.33063471948117, 166.5440855624501, 69.55732985220129, 34.45140644593349, 86.67459522779014, 37.374740388244795, 14.285321811596498, 62.055862199064606, 119.45092212222697, 148.02499867085453, 60.17481089544459, 90.92630520809162, 192.9650651776966, 85.46004085574012, 86.23624681558208, 90.41162443463342, 68.0900880589405, 158.6316016817019, 152.92512301723684, 89.3888539999347, 104.88625381789876, 76.9249988904539, 98.80372274132381, 44.96804254846994, 66.82333185462043, 103.081607994005, 135.47098599007816, 104.9804933878343, 103.96391273564475, 47.952771848038815, 78.66421572850145, 123.50852029923024, 54.2692611974194, 66.35590680165033, 155.85304793451266, 60.458656199351466, 66.50796035338497, 154.8507055913178, 79.51208172903402, 50.66766957452201, 97.58451379145164, 44.55604615661825, 106.22363012889706, 48.40785533660604, 90.6479655311483, 151.3075500533164, 134.68798877679745, 95.77800640789089, 99.72324272004703, 40.37704567403614, 63.751301019438365, 241.97403928658667, 14.603759375853615, 73.94601325320292, 86.96073510173916, 103.77212366622621, 52.818724247386605, 227.64854604648065, 86.89885805186319, 56.6100675875769, 219.36979849592194, 128.23776754439237, 55.563497956328035, 76.39162817140647, 64.88498630878112, 95.80067009069325, 140.02280363762227, 80.61486189099476, 73.36465473072789, 238.0254010941309, 51.320353779553166, 136.11000545313422, 165.2888620162385, 104.39402046363425, 56.89562078987896, 18.172698286309846, 52.117907126892085, 284.6019111666246, 91.62730393776307, 51.642144048574494, 30.717688701178112, 12.702368333019674, 65.81683720803665, 86.0957252585488, 62.700947967755354, 63.11979055470906, 91.37510192122883, 30.2545141993046, 305.7493923103604, 114.78389641683161, 51.53186570926917, 65.96270449406798, 58.98034699790214, 87.48137145532881, 37.48159621018347, 83.27837253572872, 326.26769110150434, 87.71994574664076, 28.50497531870504, 98.89797684988787, 51.29644111399289, 114.37126775803002, 77.64678208874376, 128.99228114269553, 62.30381542720116, 96.69769445704745, 61.105742262861696, 99.57950154056458, 144.0813997535956, 148.3054134277731, 119.69256410773271, 126.80560712050655, 38.415603487094366, 6.220080444338877, 47.452376427829876, 7.34801711717029, 101.66668454956589, 128.34022748286245, 226.7422459550905, 80.90913211789388, 53.98888416742064, 37.80908197735296, 93.31137219503402, 37.920748921765565, 59.10111182058506, 205.4784903627391, 55.426419475981156, 122.34783902821829, 44.71685063394758, 108.33146877572379, 67.34307063789673, 79.22364688869689, 109.63447997239176, 48.83743286034249, 234.39132621435598, 73.28889739684682, 217.67197411932474, 57.724751189168984, 59.883453998615686, 53.540341009479704, 77.45171429510582, 63.760118073145144, 92.82035217790471, 67.54974137036143, 85.24735475335363, 102.215623103406, 66.6250850724937, 45.00201891505519, 52.99425627371403, 115.36428766321399, 75.07787637831078, 82.5518675317017, 89.39184597905688, 92.36871329241507, 76.5518043588025, 58.818149897264824, 55.27074423447606, 46.752574276126154, 93.28434286039679, 284.0462025526678, 48.295838051521855, 16.777592891700213, 105.49337407377809, 126.02415049536664, 104.45332687502705, 130.5162843249726, 92.52572573684944, 63.380642579291504</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>113.8826338768005</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>68.62566683492051</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>[120.96910858154297, 161.51248168945312, 54.949493408203125, 225.33921813964844, 66.46082305908203, 241.66830444335938, 39.80750274658203, 128.67935180664062, 177.6754608154297, 105.93475341796875, 58.356590270996094, 53.2330207824707, 96.05014038085938, 82.7920913696289, 230.88124084472656, 106.91734313964844, 449.00372314453125, 47.36863708496094, 82.26827239990234, 67.25086212158203, 57.51864242553711, 57.298728942871094, 81.43876647949219, 46.87489700317383, 204.8370361328125, 89.07156372070312, 108.80776977539062, 169.97955322265625, 63.07613754272461, 246.71432495117188, 289.2467956542969, 153.75914001464844, 84.86138916015625, 71.95138549804688, 69.22465515136719, 64.41472625732422, 254.86056518554688, 94.90160369873047, 36.89086151123047, 51.91044235229492, 54.961082458496094, 153.3472442626953, 110.69775390625, 98.65987396240234, 90.76470947265625, 130.22276306152344, 52.0273551940918, 60.56564712524414, 71.69319915771484, 141.01319885253906, 98.85438537597656, 155.16470336914062, 134.0498046875, 77.10527038574219, 49.19114685058594, 132.8599090576172, 104.08433532714844, 150.29464721679688, 249.97637939453125, 84.65513610839844, 133.88375854492188, 45.148719787597656, 156.5490264892578, 78.7134017944336, 113.98652648925781, 78.26325988769531, 250.62510681152344, 197.74000549316406, 51.872806549072266, 152.61566162109375, 56.55564880371094, 41.75651931762695, 42.236507415771484, 237.56570434570312, 128.54641723632812, 88.5694351196289, 52.22129821777344, 152.87289428710938, 91.6121597290039, 68.9032211303711, 65.65884399414062, 116.06089782714844, 94.02924346923828, 31.78407859802246, 141.34445190429688, 125.86182403564453, 223.46275329589844, 182.16049194335938, 88.86763000488281, 61.2100944519043, 78.89681243896484, 64.99457550048828, 48.37896728515625, 174.61317443847656, 118.48283386230469, 95.49102020263672, 103.38932037353516, 52.05623245239258, 108.39539337158203, 97.94071960449219]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandom1216</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:02:26</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>90.91248101685777</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>72.7067348926073</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>102.2404338039697</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>4887</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.7255805133167887, 1.2590380581255172, 1.4292546412873066, 1.241618146071886, 2.282943626026312, 0.9768752613824513, 0.38309490460645185, 1.5853552159118565, 0.9180291537048838, 0.7369000508819065, 1.0767731688400461, 0.6788183497080192, 0.8284281168854323, 1.3409171515683538, 1.3323504228347727, 1.2176858075086456, 1.1755294216457342, 0.5281283614655377, 0.7485529059529655, 2.302073456164561, 0.9359968031943504, 1.2070213934790361, 0.8202396966405546, 0.3265085563270601, 1.327581392646706, 0.7923591853482477, 1.8149352548258293, 1.1880833623055909, 0.8154377181302586, 1.2492141042069274, 2.0017223214351496, 1.5201892544170084, 1.4698011529386739, 2.1164504731237423, 1.6395365188637114, 1.6019691193152223, 1.2156306929570724, 1.975184328704708, 1.5960377653385875, 1.738484752070153, 1.4884161464093841, 1.4764292734390414, 1.6118714642926155, 1.6118490904123473, 2.2787986708909593, 1.997673636432237, 1.5288196123022195, 0.8523194346402005, 1.9114214223156967, 1.835190067132173, 0.643610320978356, 2.088562909777497, 1.3660541955465229, 1.277652387064438, 1.9538107289103102, 1.2433544734050295, 5.814280832371341, 1.274801607620082, 1.3665788799417622, 1.0240511831679586, 1.1867482938720364, 2.6461237166452323, 2.2667654770557424, 2.0912445463107243, 1.6430875726236922, 2.074853829719356, 2.3579852563969146, 2.00844550655796, 3.5203678741387336, 1.183943576107192, 3.247974130446157, 2.603869287273189, 4.34185026725789, 2.2952873323267817, 2.795832418806219, 2.0682538612245263, 4.166308903329296, 4.108700969199681, 3.55302457842758, 3.12809251445492, 4.336020492871513, 3.7930934920243033, 4.663911757926579, 2.9436057527888444, 3.064302054172256, 1.8123457927818363, 2.5031649075647526, 5.497198203926484, 3.4413528210712734, 4.18793280285417, 4.311806105746972, 1.9981234413363564, 2.6540677852247687, 4.829941581672334, 2.29091885495992, 3.6089882213389246, 4.482105857380585, 2.3956851339980054, 5.6191297881344395, 3.0789244622277456, 3.546372565016253, 7.186821217429305, 4.967169867682717, 6.536706107380563, 7.063688920523514, 4.085754142953639, 7.79518419239187, 3.76437707574741, 2.843169408474341, 6.52893766362321, 7.755425152811117, 6.692847899329482, 7.018137060157498, 4.463302105287651, 3.4383380349121255, 10.658366896280741, 3.1855214635554345, 7.579719412154549, 2.2522987334724167, 2.037748384874693, 5.148636192889327, 6.132465523445036, 10.1974886054885, 3.369128389707572, 3.1210680426660224, 5.2437067017239665, 4.256660374572787, 3.4293012240279253, 9.284453630446308, 3.2755959985292336, 6.49647005345254, 2.2431010416418866, 4.879543008837509, 4.277456306703828, 6.4857984357384195, 3.1748753136856465, 5.382375994206452, 5.710440829058135, 4.055120162500276, 4.02643343110743, 10.170448231164869, 15.604305221179219, 6.639029663498468, 4.556314224474471, 8.805848324653738, 9.003213682946107, 14.945491051887965, 13.001385835431062, 5.572004510286582, 8.324963978613694, 5.773638265257179, 13.17428101028239, 11.745552733924608, 4.048560295610283, 8.198222796245288, 12.005781149732016, 13.80039849164831, 8.684999472491583, 10.33996501380882, 6.3108814637257575, 10.995262259702924, 9.250272185732534, 6.3048711393555905, 10.423281423671238, 5.64743297524077, 10.361508456943865, 12.782138434564311, 4.275569288936858, 6.56087373120523, 11.847024274023825, 9.975511018894128, 16.052784529833698, 9.794055828182938, 12.496480212820723, 13.820993821902674, 6.3125905594338825, 18.05938948063751, 11.91420863552181, 17.22309280427457, 16.28668934938626, 18.049721916379, 11.229928941295451, 9.276542619472762, 19.55401843316926, 16.212898702416858, 22.298847816165985, 15.317323804084612, 20.360317740886284, 5.997569882764959, 24.195505305978372, 34.93509386099433, 9.873948478275532, 18.972023853178165, 20.752844209202138, 17.853226866207407, 17.786245086553112, 25.989919653077273, 3.350984185117196, 14.956552885111774, 10.74225712121422, 16.698383873772382, 20.116129748625557, 27.59538404252054, 15.47054479772217, 18.855353916075515, 25.04357106090682, 22.222332580936342, 3.219003302389434, 12.014507468930807, 18.566120600009103, 13.777962825698625, 29.181962775053265, 8.394785078710438, 20.857983385581967, 24.772888726798712, 27.080901386168737, 16.488677293018082, 25.306178993508812, 30.291802322650142, 33.95148508411217, 23.561506103743717, 15.72142533395147, 26.77523158395426, 13.23640988948668, 33.02608449582514, 35.06552237871042, 25.618690016068207, 13.93222889513648, 20.567744264969058, 27.47522355623853, 15.276444524877968, 25.80187718249314, 24.02225124668621, 31.954445646342165, 7.772885545806847, 19.72902879862869, 36.964978790228315, 14.638179034837787, 15.01329677058258, 42.7418462736355, 15.346880028165161, 17.373795027688157, 13.914913192847417, 32.95611637806026, 15.21815059013917, 13.958567499069877, 17.346102444016548, 52.113030390757515, 20.47248587400905, 30.620324501627696, 23.9644982863359, 26.894800784095736, 30.837924742563413, 29.252586384018915, 36.79814985471768, 3.898536487593935, 56.78540812798954, 28.52825787222087, 20.361643144529097, 47.96263920314068, 29.058720123686626, 39.655913558120574, 43.57597574422352, 17.250970077825237, 41.97848778300936, 39.69794972834842, 35.64472741714298, 31.55613829917351, 25.275563348754165, 44.59670564868703, 22.003101997446084, 54.735815722514936, 38.207577013612855, 20.943754307132085, 23.775494359164068, 23.107916120705497, 5.048737109098298, 26.064235166949814, 16.99375371091007, 24.425579569937536, 25.398840647572065, 43.12314745328817, 35.18425566488853, 20.50468841093268, 25.771780953913336, 28.617243672045152, 25.95322521781365, 19.92932304737255, 29.30214100448642, 27.051776934035598, 23.130478619766578, 25.806493439989268, 25.57628624601574, 57.711622160210865, 25.322221652680046, 20.069198381331383, 31.52972007487363, 40.80063129985566, 19.611092677111678, 8.913887729124932, 20.599592352702324, 55.81080958321619, 7.700535909897609, 43.34532412441964, 22.65107696376456, 67.4130293919655, 36.86448307934303, 32.73716100247621, 79.53359867927277, 16.3893504596948, 32.38763975774532, 34.89282222938348, 24.42047314742317, 46.27747259519483, 23.30503755341859, 37.21914055168175, 2.522353028402027, 25.03547649548313, 21.38689303720315, 31.60708078097885, 25.35797824072052, 29.644067117238272, 50.91571557767546, 50.52526273241956, 75.1573254917934, 31.195632335393462, 21.54135398543111, 51.35768245826728, 41.63883602167096, 2.5517401588811133, 22.108310948140176, 45.38171580455112, 35.25513373489371, 24.364749809346442, 64.63573642401632, 27.261706476494165, 59.00077773581852, 63.16026438989796, 3.9329023724697767, 31.911893552962233, 48.4867987316402, 4.335743567878159, 54.30662088307963, 38.548256816857254, 39.79240548032875, 41.75037017966463, 59.78560636836299, 65.4366292644589, 32.80455398827734, 34.22198420426487, 41.84855801540573, 31.20483589203693, 59.9610086748908, 37.50437977991276, 31.126266592076796, 40.38193853021001, 3.3417761360565414, 26.18530113664532, 5.292492543578944, 23.057731889704005, 47.0237176912067, 87.11552931787995, 85.71642826752462, 78.13103333192655, 38.68179415319054, 24.086995991870648, 40.77155005416282, 31.625477767521655, 27.414874422281045, 31.254595274646142, 38.88531037838067, 21.81073758938662, 28.031888994715967, 42.33020435124248, 39.74471880003687, 24.169468989498995, 23.549709159231984, 34.770054037847196, 30.986006473276003, 41.54037957806281, 25.614594181018997, 89.65234427641286, 24.654073053559618, 29.643767420977806, 68.96591906169505, 29.76159753600582, 53.519933540412445, 60.2084318139164, 29.38108803962091, 29.909927733365265, 28.170866071164035, 34.06746716034952, 19.14694448751402, 28.095349945254473, 70.16756488057182, 24.163275816474883, 31.588102713658014, 60.62749580247378, 25.86612926035297, 36.31766761465575, 35.63513412217372, 35.99910556765723, 47.986530692098974, 34.091358701191865, 56.328382094963054, 50.726895184957016, 33.144026362410315, 33.944492328326696, 57.59520714520912, 80.25817605152116, 65.21866057074445, 58.43175096590744, 12.057865821292724, 39.365489966470776, 26.624606023674037, 35.91454818599985, 140.51403676057012, 81.47955900919602, 36.207161741864425, 67.09160703522137, 33.92362748090098, 28.432892462307052, 51.08745897916731, 29.029063807274895, 28.013910199654404, 49.48282981508565, 53.74213689315926, 46.37780001586315, 64.59854221069865, 51.27277872857764, 69.32168844598009, 38.045517913823915, 5.091113689935699, 57.462322532890106, 27.291260452358177, 45.198241722016284, 36.57207602106258, 34.71904399292224, 32.05541961761302, 65.60514884372684, 58.667897695921226, 12.849237780778624, 43.600559085946884, 45.576283134177594, 45.8546108087837, 26.943391080015285, 30.224227650063277, 41.80519813123815, 33.69691009285811, 73.2438306547277, 108.67293181031579, 30.900483719380727, 27.531714284548062, 4.751694904443727, 61.905537396973145, 61.29989354403857, 34.59021278179096, 38.73890547332704, 42.33196106881732, 32.36015171104129, 38.48491186923649, 54.338449748922145, 48.399515118609095, 63.66475131560482, 57.27744775012013, 87.02066156831057, 52.183219803770626, 46.164514579062974, 40.40787206985545, 41.345112053307155, 33.53363481542998, 33.66475309205017, 75.13388735706796, 92.23398958848665, 44.76298576605386, 46.43907828239156, 53.91371950156364, 33.6944877638986, 49.99724495645354, 43.10122014384389, 111.46754580944109, 32.91898112758362, 21.473128717770493, 31.457896316063096, 66.0525864290327, 132.7181306230125, 55.4823432115781, 63.97219504073966, 71.09111103061069, 37.801905294556626, 44.34731508485246, 59.22763770018278, 14.440182118065236, 109.06811117870862, 31.75329691045177, 55.14538785801002, 95.72755869585768, 68.16308806964543, 33.68425442958885, 35.839705515402514, 65.23040015301557, 79.98465851730008, 47.33194232160062, 32.945225972145245, 35.585422722376094, 75.82307045017596, 52.400947786925585, 34.67901210042096, 47.68134356850057, 59.99045208720191, 52.72016566336989, 58.75703677568319, 61.60274384363364, 95.87718335329117, 54.57682548508715, 159.76014854071926, 110.39093670207666, 50.09009405519299, 80.70883737920838, 66.83713840375306, 45.041270858024575, 59.781820218097316, 88.7226825400138, 82.87691128060811, 87.71117346989531, 43.15362657910367, 113.3857345090082, 54.569925368744805, 115.23416050609951, 64.94487538862163, 36.54616778187498, 42.38894093808565, 66.80687531431255, 100.87341703824437, 36.567979278740296, 36.466240858714364, 41.16450982566992, 63.782813217702135, 29.66146169272069, 93.83922968055835, 35.581811570815226, 69.00272043029474, 34.905700741718825, 36.57086542239231, 68.90838087522569, 56.23705389186891, 39.768104025739206, 96.66875736222741, 90.04323325775184, 78.87273575014719, 44.27573902078518, 34.528721079875204, 53.73604317456735, 39.10516681059527, 5.560691056102742, 48.84375941653742, 39.24494473898932, 48.190378967184564, 124.68284963104654, 47.738211676683434, 58.82016722754993, 79.49724484182732, 33.66734512095888, 50.760744773181706, 44.844231376205315, 79.22063187024226, 42.77797482519295, 66.1581538097552, 40.59966949809947, 53.501127800362156, 55.1312561728061, 41.25407671250968, 41.351168320555885, 51.50755311748886, 48.36070970984119, 33.55999056601751, 6.71961869527892, 40.716280738757746, 56.62116078246306, 121.42471038472397, 52.496306459670585, 39.4694324219888, 40.60889332471765, 44.35989891444751, 64.06365924383877, 42.3574249724323, 97.70958883337072, 66.07926486614801, 43.302947705440616, 50.50652338564199, 76.4301188770189, 121.95893643794477, 40.54470771297697, 89.01003104610338, 65.31550126748272, 50.569241829014345, 61.49352447293114, 108.78890227546343, 45.70934407485589, 56.45621664273532, 68.35877082136525, 79.52817565838951, 51.45304138217796, 47.15887556797549, 84.43625387934367, 54.45851890245405, 41.29879495507914, 48.5594932756713, 10.904173707217751, 42.30562204286508, 85.74950491969227, 146.60950759459703, 84.25054286259453, 40.64259691316158, 46.91179132919312, 56.00778960182459, 81.81554328567712, 41.37887080897134, 43.07291199933536, 62.09933759147853, 59.74811902712577, 62.51077496002048, 101.86977513509709, 42.686260660054685, 40.582452714075465, 98.50974490503368, 63.139554881824324, 83.50067457084887, 86.0635537083848, 13.074582859790128, 44.475402308350155, 46.60173077725931, 56.081284009551474, 49.15145398793656, 55.80763730297564, 51.491445597277604, 66.7524232588847, 50.305413198628855, 4.115770803705359, 59.58061204806938, 36.27649247814952, 101.78077836277107, 43.09648100969313, 94.45538569725112, 68.41107944153806, 80.29602615984236, 117.97179261176787, 55.58524183139319, 136.8494998283706, 297.2584166299406, 70.88187651457466, 71.45276756069408, 46.78987786239563, 115.8684642233069, 57.15535919355495, 112.74499226317599, 38.83785785935464, 174.4378334224253, 52.301923345087154, 98.82612908355007, 200.18550375949147, 64.56910656838504, 52.022034551534716, 60.252597176423535, 15.870108613895141, 50.57280113121062, 59.798245425210624, 83.90768898999377, 59.438215038273675, 46.3807855217528, 57.03278525216684, 94.01765769935666, 44.903334543168995, 119.45436532972886, 34.10349379815341, 55.255772652564744, 112.53623983090544, 119.02302113654547, 33.06272248506923, 54.067062554160856, 60.94666361230031, 102.82402223921679, 44.17117794516728, 74.0987237000215, 63.52680890159872, 49.88844338470125, 59.96470598892631, 51.264397623203024, 17.034136707003793, 34.78338095309932, 70.57062625403765, 48.957220606425594, 4.591765047567297, 38.32873762003294, 47.208254060723625, 68.32712854408722, 63.86968383369031, 63.214842232477935, 31.42384550925226, 52.954337650546314, 109.59435223852628, 94.4137673229538, 68.09419742610652, 2.9039669186698145, 63.09873247421342, 106.77487570079013, 47.88077981065399, 104.38320305674293, 55.2341989101292, 55.88186973008005, 64.94173232159808, 60.55832370564218, 54.0850886941052, 100.08915385226294, 58.913017641682714, 52.7479280816405, 44.158968415106, 46.02294273841379, 40.73181666643615, 58.56753637480489, 43.906572753063585, 50.750270424682384, 149.93114017472672, 2.65246496615307, 67.88405168721822, 73.29257976954946, 107.5902809845778, 46.85542845158447, 39.02334485147674, 67.78223130115349, 56.7472693156567, 108.59141652446372, 53.34060127875851, 108.54459289796951, 53.53926316343852, 56.257220975286636, 82.14306977193976, 61.026178490193416, 34.92302200142632, 58.344319640303375, 53.52444079696905, 136.92638172107002, 96.03788620355769, 63.484835831217254, 100.28465237686102, 56.169017892839136, 62.135569664887576, 83.0750300609339, 100.45134634110902, 58.72406211248122, 69.22619213064088, 30.393762971820912, 67.07168952676163, 119.62298432071967, 67.77891387996321, 6.37145726176352, 175.98446751544205, 17.02655008206707, 69.35739803439355, 63.392396723185115, 79.56432438437717, 80.30574250890476, 54.977132636995044, 64.1682847095785, 49.19666652061618, 49.42092444297909, 68.94258295729438, 87.67903111031623, 80.11890853481069, 70.01968599542877, 68.27518652100056, 39.27763374587249, 8.090696630217128, 139.8519032065984, 76.01531009938465, 37.349003683674766, 54.400871222681864, 68.6222270034721, 39.2508728472466, 80.89714788119926, 141.40416042681574, 66.16954659322968, 38.52231216760138, 46.87638910018304, 90.73841948457451, 9.814468687176443, 68.28184766004134, 61.386500372025395, 40.15826118604618, 127.06269953294245, 91.07173683474079, 30.44227257282174, 69.90171820762055, 74.35083253096944, 13.530168659757445, 42.937308174373634, 45.71204647423926, 66.59956286328662, 48.97159107654643, 16.89110919818572, 56.394626350900815, 129.89227668068162, 60.31181741350852, 57.86940246602297, 52.839281455269074, 60.82802660159301, 97.39335971017452, 66.79952906818244, 61.06252013503866, 42.675809210802015, 48.468618330243125, 49.30077170580472, 98.8614144902057, 52.19932660734641, 50.64767000951192, 67.31219499241104, 38.78713388172107, 37.55506079467847, 12.951931980131107, 40.15238961090029, 77.75457159217258, 68.36068729762445, 48.95078022046378, 33.82851385105981, 71.12724340335052, 109.58408642219767, 73.95240787293226, 68.32391031451046, 10.076578900559213, 53.17827432790448, 95.46009765095599, 139.8135303792642, 111.13646490377025, 55.791641244133906, 57.31921445360847, 62.35587803471132, 7.084994079438339, 55.238462370697604, 56.146597138821804, 37.69199842655984, 84.15607895640188, 100.04948042499393, 102.043077340514, 48.74885354309218, 161.9959523089058, 73.09801811779697, 52.27180738261641, 60.97174076556163, 47.767810919979674, 47.182482009550085, 16.228469679386134, 41.36544599065806, 98.99702639739982, 60.13386770726668, 64.90102265801576, 58.906475021430495, 70.04890133901725, 120.2253161848934, 92.00407096183422, 72.96847463119428, 12.732930565216567, 54.64069458189642, 4.561611725851334, 73.38421107042892, 94.73492189657144, 40.32995693424245, 140.71976076119205, 93.03481441623734, 130.71866655377212, 96.18135828199458, 63.07499341041733, 109.18081268341757, 36.13872841451222, 52.77785771320491, 56.76155112159917, 40.60061832665527, 76.15785838814666, 9.90111179393605, 49.04867784045247, 74.8940371049648, 51.94096522015194, 53.0725970168714, 88.88156535043137, 80.85067954350197, 154.29070470951822, 78.60327478792031, 70.71130580895833, 5.794404565339759, 9.356016259947452, 173.3157451531335, 152.61887930707712, 43.6343826354008, 61.9630117834919, 12.571933654843287, 58.22920645771359, 47.33567972293127, 64.85049688268403, 128.66578123581158, 50.061587615567134, 80.93999428675521, 89.16369104656528, 44.511456540312956, 52.348678024283075, 42.69605781093394, 96.36333438671983, 114.77546637690203, 57.86721937379971, 52.850680684786724, 12.521855770075971, 3.7095365524420356, 44.80201673804069, 133.58054485634796, 63.157347125811754, 62.10573122962285, 46.61214376048447, 35.96203690968669, 151.22241793743893, 109.81209767768068, 39.515586272706756, 42.34648242993687, 51.26336749480968, 53.8219260939392, 64.56805569369709, 92.54989436610245, 56.42002346805237, 116.20101967172012, 73.98311608399074, 52.46504891871532, 37.71414094552307, 74.03867723018195, 47.89697611889419, 5.378634444307324, 73.25533537784807, 99.87326558192134, 95.91072870755677, 94.8518100156205, 64.52497400136264, 160.51887494843243, 42.89246106158474, 63.36019538639637, 149.49555097083913, 67.37329525189229, 48.191894735669806, 47.79390425298317, 79.1823860044659, 69.40798002876535, 107.4801873132126, 61.773434916827256, 15.336547774935678, 41.55602530977613, 62.83956125292336, 145.93009618344402, 52.65159251329461, 49.86239407485358, 48.058950619959724, 84.86157422129725, 9.343058804096248, 99.93586458589854, 49.4891327674067, 175.9589515170631, 99.26564402323531, 59.81837891157952, 165.50983521394235, 48.21591950098902, 89.84193639960992, 54.68897661682421, 65.98674093481831, 121.96098047046213, 61.746434254945854, 59.49637464534296, 41.76066671296942, 43.27502653143998, 72.83517977636052, 52.38478231994698, 66.07164584594786, 81.32801632186805, 60.566812630503485, 81.61038115320635, 45.854659282580144, 44.111444086903504, 176.54557763121335, 68.06566598647333, 215.16168151432726, 58.91010257110639, 51.78878041016968, 43.78881068124497, 115.99053381996845, 46.95378646984038, 106.39608531305268, 94.52259109281502, 98.94756518780939, 111.13857521629551, 41.958772779383054, 64.60562088656616, 57.10389221619931, 67.60891828367626, 51.69995386343162, 61.239268698048974, 42.507242617691276, 75.23539347157312, 88.3348781624762, 42.2553715009745, 46.48076316476681, 189.69957918578962, 52.521611535008134, 44.87249092762719, 61.10804464415224, 64.6398445786468, 146.20412799759384, 94.26484800085115, 60.95410095044123, 48.22445537920489, 65.79950431815573, 69.17057227169313, 194.98038808527525, 68.43815080216689, 57.46422558170057, 90.02501312554176, 52.903583280205304, 72.72982637158975, 18.390042798445748, 63.19594404283998, 63.3016147187233, 37.1988076467256, 71.48210179480807, 68.16414986849162, 60.99244077533769, 50.42984727727398, 86.76483584291415, 111.67275230112902, 36.776019010115654, 83.14430806539153, 57.916521364819474, 87.5627121797261, 45.49833575591054, 104.22486712504896, 44.946405874562004, 48.80691794211402, 37.253325871352835, 61.58298426692494, 62.301568971944036, 37.28993708631113, 63.07698737746492, 58.4045521662935, 63.04077610416869, 48.587797839148095, 29.70126997505423, 14.08622810664481, 192.1700785302613, 62.15578108159257, 51.29727620896341, 5.522722438118922, 48.02374376018838, 74.34498782660447, 43.97217354895944, 46.432128167165374, 43.59271007341599, 162.60138868397826, 57.66383676346819, 55.70848181826695, 119.43869808786795, 106.08740217299223, 49.499027273901106, 50.92621379042856, 56.85967089973075, 95.79541031381176, 41.32990028905175, 43.512007445117355, 66.66731821191803, 41.59056219498857, 48.032434104104375, 61.400889544171065, 58.39797188090239, 113.51844676800039, 19.20913858225277, 52.31953536530193, 63.83257158437888, 45.85840630076231, 79.7020527664958, 47.64887755254307, 35.90636727794189, 117.16457629101754, 59.324789112491096, 106.27205529969287, 89.23789976693287, 41.51587380705737, 81.69606508539107, 47.994726254120515, 48.224217316566246, 44.136029378327926, 96.96930933389527, 70.48503012735686, 97.75861772323884, 66.08482800678996, 69.7905224976098, 235.96856152216034, 53.525646355497834, 194.3088782777385, 45.516029200706235, 132.4281544987612, 100.5856320559207, 65.99286812589857, 146.17815349295918, 73.13825496611251, 35.396626758878135, 54.392166247551685, 101.75860535333712, 56.62539500802513, 80.98528432980264, 104.61323765453199, 107.72059074714927, 99.60043943361926, 15.163650321565445, 51.93663614732543, 60.0575927957326, 49.093881526436384, 81.94590738378602, 110.30585974212465, 86.10595343574481, 82.44405589219275, 105.43057728059054, 102.95093847434131, 80.19963511710242, 93.13315172804612, 47.93670774072522, 68.34954997177091, 52.84682598592547, 201.1416682728124, 128.04640144239093, 95.52880871011807, 124.77203912390985, 189.6076723450659, 124.74256425898724, 208.71007603403362, 5.31436451876952, 68.88498714751952, 59.27177565651549, 87.115244789076, 61.01345541729514, 171.9541381754355, 122.93487872395676, 80.69242712233456, 75.30502858802885, 114.36984760167775, 53.76830620481326, 83.7291242447938, 65.53291989806516, 74.95425098574661, 118.0855990011624, 70.0316595543416, 16.428855373664017, 53.32781903036576, 86.75792869917808, 54.39647712962446, 119.90856988684699, 131.02584563363294, 37.791473490894745, 147.03708709555468, 46.19147742617303, 83.69431724742913, 66.99949700033467, 43.86383094464207, 36.801090245827844, 62.395402742578185, 84.03044621116352, 54.633536264471196, 49.566994020419195, 69.67988597392214, 70.01250148751515, 112.31542800802454, 106.51657778634828, 153.02674663916244, 63.973292789583525, 150.65549405955352, 18.898139589991402, 50.22111483760384, 63.04072540344373, 45.98945025748352, 160.97734421299543, 7.094387163673252, 92.48533057168093, 102.34321855523582, 75.82285295351899, 49.033929796226296, 71.18769512883689, 43.621355332301164, 56.45251288042515, 58.72847386707773, 79.00372270611729, 74.76712653962566, 143.66595321443253, 257.9047870924495, 6.491206560226397, 69.88850754275524, 94.70385720225359, 111.49145202301916, 80.76237310814838, 65.48826039475362, 61.21478706273318, 39.45989330021619, 44.50755862585645, 57.14849313940175, 77.76621418498068, 312.49254914248, 69.7779319072345, 184.3674797514962, 124.02283889651288, 114.38250934389792, 116.9857133586651, 114.54005244922365, 41.95004046136418, 62.14693272250746, 119.66349998654636, 51.65906837316087, 6.740100277586186, 124.76512624858982, 56.9557868679521, 135.47351213742883, 68.80543640872143, 98.46645985855646, 60.59265153047845, 55.79012017602071, 40.45935270053849, 52.9846543215479, 113.14550647953604, 72.96089383025588, 44.263136475515225, 74.92750878980762, 58.11479622811067, 50.024390132168804, 86.6490423123728, 54.17486318743784, 78.59719475224607, 49.73143962987837, 52.96484470245746, 57.378897993663166, 7.291777728024144, 80.48792438674855, 52.19407769784186, 84.98807656905817, 81.49020990588518, 71.89973567200158, 103.32146934895466, 206.44285632328865, 45.55955776251072, 67.397431295833, 63.84277020828036, 12.17514090889688, 48.333188406464885, 70.52522491412077, 62.26236081002829, 70.38509445103867, 178.17734589401007, 65.85395179443506, 63.172287310061584, 102.26141355055763, 57.829959248196246, 47.73911376083706, 53.04903772804253, 99.03596924065397, 93.70903646986876, 61.29984539855493, 71.97338422831757, 204.8403197614669, 72.69048749127614, 117.2165654780212, 78.33189869763179, 131.17986799705858, 136.07076794434087, 150.16103583128563, 67.10525592052997, 199.61445415999208, 42.14577296831871, 100.86119959753813, 83.13695652485153, 130.85735580801068, 65.65356470280362, 151.71659554069544, 64.70603200375379, 88.45570469995756, 57.53974589854823, 104.70271890606071, 87.58350473976247, 31.607166348288327, 50.081479024570925, 206.56418794401816, 62.14609522165444, 77.82470543235137, 56.61449494756489, 60.11548607249307, 108.21301725055798, 61.965684501703194, 2.910767872048062, 96.12842496193778, 76.03872900953259, 81.2037956150328, 63.53230603823303, 153.8679847671371, 66.40478229064632, 137.42292387393533, 71.53193966827988, 88.02305163947192, 131.63695622179185, 46.34667516603552, 91.53750899486452, 66.40389202435148, 200.9217528210184, 78.45849902706398, 67.7157239647702, 41.69325810579575, 52.892342179145444, 56.928890486846335, 109.79273179157234, 88.8214157077907, 40.58177267700738, 36.70469654407653, 54.77300566808132, 54.99354740125013, 52.58096730586301, 86.9388287618728, 54.017014033403285, 47.79275899863319, 62.210606567204216, 65.5192814430775, 41.98195910880995, 58.0303190275802, 54.13937312174535, 81.84847384334054, 75.52007990044778, 58.3725094859874, 95.94315475413543, 85.70656327418166, 67.00389526996929, 87.71609503243012, 56.270927192101766, 52.9826260012653, 10.772008938498454, 60.29358887191956, 74.73078901884243, 52.9525318636148, 95.357098401115, 144.2174430309326, 69.91024709671379, 64.78739202743579, 133.81472863066196, 420.291579611468, 49.713963002325094, 77.53775652158669, 53.20445986849613, 77.32055826604847, 102.28861038924313, 118.23160694219357, 119.9101285867087, 58.30726320784154, 47.4927403082729, 35.567528303144414, 59.01345942064365, 58.01939256405899, 88.06262906263133, 100.92700453653687, 52.636475767053604, 104.47813761176167, 49.21161364768229, 84.42108440473237, 173.89174765878857, 69.89025396608545, 85.66572788181462, 62.32423899717734, 101.76829429029621, 74.42955779359413, 69.20495847809451, 73.5083603451435, 157.9286011635614, 56.57277586847724, 58.00102488681695, 39.190333229547264, 69.05431013532225, 154.98152680908737, 70.53684838706346, 73.59867178493771, 78.29917570726163, 200.2656324718323, 105.9586474276989, 75.66208366511331, 60.12006556317004, 53.89680354189147, 77.14870719991622, 95.2162297629091, 48.218020270199254, 60.21370659071109, 53.043209366075835, 155.57166516503816, 45.20575146726379, 78.75559535895387, 92.57814371077566, 47.48689962055905, 77.81624170619719, 85.84796445945355, 76.61025994022853, 69.91368109336663, 105.01658251274138, 73.47904323154116, 44.368064397515205, 50.50475522947602, 45.30999261327834, 90.56399337482601, 96.15691534182473, 50.18558789884292, 203.44122198413018, 259.8921502346693, 221.50844519733687, 76.6752800824452, 41.11616218665533, 50.58910574009711, 172.95067495876197, 44.074186890967844, 73.14513672007475, 81.05627521858123, 9.433156272280922, 92.82836419458266, 82.10967066895758, 56.78359590482708, 98.42235311712184, 67.97115245779403, 82.8510667858032, 40.496976915919085, 76.65836309956411, 133.48581636829502, 68.57025121278544, 72.01270170426466, 73.57205636242425, 55.545608873557484, 6.490963259909974, 39.34284877065715, 99.224858486132, 276.5966084961057, 43.3999296781889, 12.750493870075964, 16.081253748541908, 78.87468318146544, 107.80862522833468, 104.18239166801166, 44.5222068245646, 82.71765186025262, 206.224465120122, 173.94555965989858, 70.35972325814731, 79.29310519256173, 68.08402236530554, 117.51706802054159, 86.89098979684249, 63.824148636942795, 56.289286751983475, 97.96826389357315, 80.00793382720141, 70.95584340659308, 7.121201749269727, 62.414187702520636, 190.72943057100818, 80.44433321768057, 47.981779819429725, 143.12674134335165, 68.38782808241035, 117.92109174888263, 156.67269570339005, 48.51815178440069, 165.12274776288578, 104.07127552102267, 204.1824914226006, 64.2681184944653, 72.70317012935112, 79.57985541289185, 62.72122190080543, 49.3297219854085, 70.84370758486499, 51.27836075957537, 68.86411403438679, 62.18718910948226, 60.45700848177342, 82.19244092340847, 39.04400514681344, 47.92870957834251, 14.035688106374785, 116.14861956253453, 62.699309336630186, 82.92569993513636, 148.31918372530157, 237.11643333694346, 89.15029525083617, 124.57750766439605, 45.429298820096605, 139.59696816609738, 56.90284699608387, 79.8757277150639, 142.28256490736715, 76.09130273484662, 40.98268403713259, 67.00088435818134, 132.09383486380625, 6.01703437141542, 71.45289621376645, 93.9890094929473, 255.40052172888886, 72.97293413191606, 140.83597931461463, 72.69678424534861, 33.77675536425864, 182.60856236207152, 83.12032308986485, 127.58283265685141, 77.01991125906522, 70.22199559483293, 104.1584907413981, 8.204237813267628, 209.41199923487238, 11.866014179108497, 59.60204444246344, 177.77432329017498, 5.770957354297879, 6.767166558969512, 77.1431339177993, 83.10392400270577, 95.00259575102136, 88.26592286697823, 54.95442113483939, 61.1466333327458, 69.82425027034954, 63.31560371627886, 157.16015696886828, 95.02333016671994, 114.85478609324116, 93.57721175788167, 96.96926292988891, 46.09823752519345, 61.3182172647925, 107.48774510254464, 57.813586468119176, 80.40648462411545, 129.217532519633, 72.23006143888148, 12.903341134692571, 86.2886535194651, 72.06970159046692, 56.986929126805634, 51.898716779321326, 81.18349099906186, 47.71418993382764, 161.09418309272013, 191.06982155177326, 220.97928026484868, 77.95758788578618, 88.93636564055984, 47.637545558330835, 47.21167433113424, 81.76098660851068, 166.00760015105038, 8.473688194462012, 82.0675814710876, 74.18488039099496, 90.33063773136897, 58.57778700250403, 250.5131458979756, 59.122859729181386, 8.92556357034988, 219.26031282102414, 48.93252235151389, 69.58502867017128, 52.08819234547795, 71.88784570295452, 54.356848855204696, 69.4668427202073, 188.2229212343788, 161.87674465773017, 6.741645531528148, 107.37962643418895, 60.73697054196125, 7.179414622278869, 61.93599077881975, 82.93876222032533, 70.10092666655059, 127.81713634420046, 46.293506127917546, 84.22285687666187, 159.15445452361823, 68.0114644078311, 103.26714996975774, 40.741356044015056, 111.12621346279528, 101.23696424566438, 84.25917157922673, 61.37983175534637, 49.938653631650816, 11.526418820468223, 145.73573937715153, 70.19310591537173, 110.93132311583553, 63.31873049297023, 48.64263468802792, 68.58143660298487, 56.99549216617627, 38.402230722199036, 69.76249130022337, 98.28182940922045, 158.6093552505045, 63.92969308164135, 69.54004945936761, 67.30635654906972, 98.77378573281152, 60.271309257610355, 166.18615648283836, 61.92635023556969, 92.35675362449365, 68.63179816965705, 73.53323875264178, 121.95087092734285, 208.71205448625662, 51.29356726143129, 57.490092244348475, 58.09873006325424, 79.09855266957311, 189.4653519112117, 296.9950099182991, 90.68385037967073, 79.85459490955786, 69.16940300578462, 127.71023134481317, 41.638519787757325, 62.02226120258405, 109.44135510950449, 67.21775997518579, 127.57440689186701, 50.31375212564152, 96.92700874273226, 75.26003014359938, 90.17805767262487, 184.0527580795455, 98.11733129187297, 69.0920007312376, 82.5841914418405, 152.02236914132126, 66.18431503009938, 63.72016617846594, 42.5330809336092, 79.30904490439744, 62.32918508959745, 128.87961861062547, 52.89267263140433, 58.87967088538488, 114.19431574391386, 123.71377653196024, 60.836441004707304, 88.63444165131014, 77.3467376292948, 68.13119587971708, 62.13323838003668, 126.32638067241437, 157.98580123042655, 186.58587651396553, 189.3467410784886, 7.3153103117199825, 150.62660564105963, 59.712840998248964, 48.357917324848415, 62.57440483268178, 66.90616873554832, 73.44789106240033, 48.21040304084486, 117.1101451417445, 85.25665491765278, 38.44298137182521, 64.73812006363633, 109.97783534678976, 139.14443939958718, 130.21847892189336, 90.65601886111685, 96.46059944066495, 102.9711988853254, 129.47158502744034, 46.97549276544768, 112.29022105895586, 55.8560182095297, 89.36765241357553, 135.460344</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>116.7532060527802</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>80.27308581483524</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>[140.60032653808594, 157.72544860839844, 10.72118854522705, 62.86947250366211, 277.2611083984375, 146.67381286621094, 63.31480407714844, 13.029439926147461, 151.5391845703125, 216.7476043701172, 81.69488525390625, 69.5611572265625, 65.74591064453125, 92.8314208984375, 87.15933227539062, 197.20547485351562, 118.52790069580078, 343.1767272949219, 53.5223388671875, 23.24957847595215, 90.52674102783203, 70.99396514892578, 60.76948165893555, 61.30970764160156, 70.76118469238281, 41.85939407348633, 68.60692596435547, 151.49876403808594, 208.2129364013672, 144.4435577392578, 85.86971282958984, 135.1082305908203, 51.40895462036133, 277.0621643066406, 115.50450134277344, 100.394287109375, 74.41860961914062, 78.1587142944336, 61.56439971923828, 79.82330322265625, 164.518310546875, 158.97377014160156, 45.09062576293945, 66.5380630493164, 18.27484130859375, 54.485721588134766, 127.57748413085938, 85.95061492919922, 86.82808685302734, 160.23362731933594, 74.0547103881836, 173.7333526611328, 41.389888763427734, 346.8572692871094, 80.99012756347656, 133.5198211669922, 55.360050201416016, 90.86895751953125, 179.22799682617188, 91.59136962890625, 186.61587524414062, 261.1429443359375, 9.026141166687012, 54.627113342285156, 212.6452178955078, 213.81251525878906, 71.20989227294922, 123.3603286743164, 11.398931503295898, 51.06068801879883, 226.4202117919922, 164.36338806152344, 61.753910064697266, 170.83096313476562, 59.92792510986328, 41.56831359863281, 43.5516471862793, 147.1851348876953, 10.486481666564941, 133.76449584960938, 79.70829010009766, 88.87542724609375, 118.613525390625, 93.5879898071289, 61.17301559448242, 58.158512115478516, 73.43897247314453, 75.98473358154297, 99.94901275634766, 386.4532775878906, 332.3446044921875, 321.935791015625, 220.97402954101562, 72.33314514160156, 124.78690338134766, 137.58692932128906, 48.53984832763672, 63.63276290893555, 124.65239715576172, 200.3219757080078]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>p0.25srandom1221</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:05:04</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>89.6259979276638</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>69.90138488429621</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>103.0627062706271</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>4848</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.8573178763975757, 0.7129361593841252, 2.1022056305933696, 1.2342918200185407, 0.6787053390790106, 1.6981013364941546, 0.7996719245466541, 0.7012660368373773, 0.6813028995155447, 1.490680881177236, 1.6804768619653787, 1.4683457722777595, 2.4597696586971587, 1.3412832082199255, 1.506992478711743, 1.5167577792562155, 2.108158687975253, 0.9366939652583386, 1.066086528366466, 1.031294724505506, 0.851184035139559, 1.3586403384689942, 0.8700189125070323, 0.99611775668417, 0.9622477323758405, 1.49020664031226, 1.188907663322625, 1.5064098159500763, 0.9106424915421457, 1.395263621646713, 1.7085005411025154, 1.2624530929210542, 1.7792969595270436, 0.977574289716415, 1.6127992299918643, 1.6976808563035903, 1.68302765754256, 0.8480866267964314, 1.616400658683369, 2.6918456482917645, 3.3640409896388825, 1.4954021751864026, 1.9639102402334156, 2.7700982435564554, 1.346775422292876, 2.369132964640345, 2.2871184479245743, 2.095515179825222, 2.013421971136294, 1.9215411919065888, 1.5879990451181365, 2.0864487963372333, 3.0972514732276877, 1.6015803834336284, 0.8676238984128601, 0.7399548570160119, 1.7291713591706264, 1.9374045415283112, 0.8134088047728842, 1.8889990961428436, 1.2818317938530235, 1.27978624254919, 1.2338243197790095, 1.0473195556988828, 2.3662678838091655, 5.645046002185236, 2.018146090688072, 0.33266905542021913, 1.050552891867931, 1.169973406778357, 2.0985673940638194, 1.8018905171502069, 2.56534067382593, 2.465212122959353, 2.203857699911883, 2.384043832815306, 2.0763686845751805, 2.9109710896802454, 1.819573112407816, 3.602668899471058, 4.388266733721104, 4.195775941255576, 1.7407977508472416, 1.4731559627039617, 4.655690781088696, 4.585754402034386, 3.505778954540538, 3.225747018680144, 2.120537802298669, 2.9477325860350385, 4.033183516034156, 5.025373308270298, 3.1071340992548198, 2.7191163113833166, 0.3076110962032987, 2.3484254759078054, 3.494703536206428, 2.454421373634572, 2.953693549584926, 4.041063066899756, 3.0570260605746684, 0.7609078810365607, 2.7457727201298456, 2.001604447747618, 6.699075343170687, 4.8214462387271535, 2.965214856074629, 2.990548419191015, 4.01433670247113, 3.5013726594627697, 2.267652361048719, 2.511016322602605, 9.735836934336424, 7.634954707941899, 13.484170276060604, 4.192577434677816, 7.136572405461364, 3.7936876682208522, 2.492183259257352, 7.036154806945439, 3.8213664193429513, 7.734285836562095, 4.041893306105901, 6.725082157609707, 3.263061471342631, 4.110243566971834, 10.637432797802505, 3.547089608840179, 5.561185768216847, 2.5477337267605007, 0.6603132540472936, 5.697358315631873, 6.647687151933929, 8.93820220662404, 5.966301318962013, 3.752345885274893, 5.616612540850082, 5.055221153016096, 4.381401423117533, 9.435876179659068, 1.9878881861478244, 5.826172443094991, 2.4825405802218583, 3.1571596187785027, 4.610297219915682, 6.448123600990913, 3.7824125612181203, 6.823004043086346, 6.974949431629646, 4.935984400514083, 7.663450881462191, 11.392062085640788, 8.634452356948417, 2.3166284660623226, 6.211049713851831, 11.312191156894684, 8.553174858614092, 11.696374642621986, 2.6925596035920734, 1.2802434337003998, 10.588914257226943, 5.991587795047195, 10.271790976004535, 0.8861092943854085, 14.078869187770396, 4.62889862375808, 10.330593001018574, 10.828771470009444, 7.676138603970377, 13.063923921422552, 6.389665527849105, 9.83302487321865, 11.56490264885124, 7.339050068949207, 7.233213207211886, 8.661082220668698, 12.651075566227442, 6.2997821036208626, 5.937900045340225, 6.218152502795985, 6.951267764570656, 10.221239646452323, 8.086086880168365, 17.271789229749935, 7.138909426268802, 5.206074186695446, 11.943751872042053, 2.368704514763445, 9.881332962328925, 14.638575569351973, 11.398550172223153, 9.747112099760828, 20.637635863491315, 20.694422518449368, 12.61197887504246, 17.18382772898685, 9.658029976218334, 13.448037554151124, 18.228668644577656, 1.9910017258740502, 22.491387940666506, 27.248773131814204, 29.76285489112374, 14.806009569485528, 12.425578563411259, 29.83140910406883, 17.542168560145452, 16.882065961884773, 26.937804291271828, 10.719313349400448, 20.434468686717203, 16.88670887628766, 14.365712505763259, 18.351991166829848, 18.860161431749763, 13.233650234988124, 17.971080158959158, 25.31622205326013, 16.33392350043814, 10.741924328766455, 14.980481657338979, 11.028104449789199, 5.242170734800246, 18.88628269275751, 7.259752393945409, 5.379586905695124, 12.875165528437892, 22.752510485412966, 18.83145059244383, 7.5173424730220715, 10.25879742502813, 21.024537526806427, 20.355664759748013, 26.921216291473996, 33.217167300228574, 0.8930744502544095, 43.46471004748671, 3.4275726134903537, 17.508501282440704, 34.07787455626615, 37.90190197623581, 12.343303586145801, 9.809784910660744, 12.670109233014376, 39.22275013513932, 28.736922951045575, 16.48720341534281, 20.180777622624294, 18.6895612591004, 18.595200198317364, 26.374340931959985, 26.16664506963138, 19.952776297266652, 33.39501697684793, 17.216589456583737, 1.9536953054779913, 16.433685250548322, 11.947198879083274, 19.290726656182855, 27.480477522054056, 20.472770215044175, 17.343378294891522, 0.9454821887638908, 32.6711105282087, 15.082112902607811, 36.21043277129115, 14.314601702260628, 41.852876362884736, 3.2521765610005837, 36.214965323909716, 26.07268175039696, 20.671997469738308, 41.86425161729488, 36.660145071690316, 41.093558394136636, 30.763169987068625, 40.180042524353595, 30.94080737225022, 39.19666930966145, 20.327688648176707, 18.724782791577002, 46.07817090846863, 35.057561524246545, 66.81867660705441, 51.842875199166635, 56.60002902896787, 1.9200316684286955, 44.847459056820554, 19.357593077380752, 21.926170893569935, 41.85599335850072, 40.36265280811453, 26.874855664183777, 16.635348620427326, 39.5567705798529, 32.100905995732205, 33.72046273148752, 26.213116356433055, 29.481201719690016, 36.40915169901427, 63.18261883974559, 28.04249884836307, 2.2602025063307063, 46.03581900757963, 23.953462376404303, 30.734321276911196, 25.8736612700323, 36.47220755223451, 20.456976217629524, 18.9968424225795, 19.767002041857154, 56.99129254224961, 57.20455664809869, 24.686436297165987, 30.122784282325615, 14.51008710203404, 7.372204660262424, 2.689221145283911, 29.21276657944705, 40.63837004769304, 36.6038992896278, 45.16602034686791, 42.957693698132594, 43.24413969423824, 47.45036876557316, 21.440634509504054, 18.540574978554858, 28.21331512542674, 51.75028485865771, 46.004872809407644, 24.518619650885174, 26.6618846697331, 51.202845896585195, 24.97281079299948, 5.52232472954841, 57.69075055631051, 56.60319343407072, 102.96931055337822, 36.29648432037912, 26.135049235609895, 76.4909004563517, 2.974988488618318, 21.355063431000435, 51.10612265814221, 29.22738945975955, 28.738400405484953, 54.28034157010995, 44.51378150830817, 27.593129644003927, 46.48729465712459, 48.30375700367907, 22.121102471621025, 45.20931773452788, 38.84442914879386, 45.339974842881816, 30.25507021005289, 6.052914497873937, 23.1178001849605, 46.96413185028457, 38.347319699404686, 36.891634587291904, 29.69028857675068, 39.459163957339335, 78.60026267030692, 19.793960321884153, 41.341714030478514, 48.05775022133035, 40.44003216539523, 46.65116805170831, 2.036454217463394, 43.59041528755571, 67.69218457174232, 30.70591483851565, 52.00104670012236, 49.687140543616145, 58.15743634086586, 50.08972510713598, 65.82212720935654, 49.381117829006506, 36.362465620727264, 27.933159783258578, 46.336676802417166, 90.77805166145399, 58.462663203489825, 84.10941550184907, 31.815237965523597, 89.39174868055328, 42.70961547306555, 55.57829768361582, 27.31942521751033, 36.111331446355734, 54.391552077837055, 39.470930899826485, 97.0494374942014, 36.56636112974147, 47.46684698694161, 50.532765519767416, 97.81601442136417, 59.46687918760643, 87.0417114860039, 72.48045965284528, 43.52626462477415, 31.108531353231616, 39.82988402130915, 52.91587136380203, 56.93291666444461, 43.745626918244994, 5.5720426183193466, 30.87873358676479, 47.642051412227865, 41.83004492810251, 36.19931697431203, 42.21104482147926, 34.53701267104407, 29.09191620931966, 48.61596346065163, 45.34195206663528, 50.65655766215613, 102.52311280770691, 50.68789436877043, 62.20635177354105, 40.82916796181149, 48.29226941393535, 41.28555490773332, 139.44344823200282, 36.40690634950037, 89.26659994759854, 43.66887912470851, 71.42032635322101, 29.218422570994004, 45.00856691612854, 65.3906077629103, 135.10238481079688, 45.477259965448916, 69.96491289276459, 50.707101072748756, 73.29147746006632, 72.4965782284553, 31.079392435751938, 72.7591150715788, 45.950452558071824, 46.4751166098871, 38.49425628549115, 33.07542238847063, 33.81348478340191, 44.27555776642519, 101.14644061413067, 58.42723224380152, 54.88183440814313, 66.67563402466502, 45.15553912775346, 33.81721050709299, 64.5427933421926, 48.36468563365912, 51.662735063889215, 39.978098186183125, 43.5880101257916, 54.45527544932965, 61.1527595931438, 67.61886703445558, 48.56640673649551, 41.56389449853235, 54.42914350923618, 38.962353503714795, 36.02986122221302, 32.99984619026284, 33.57765474595162, 118.16971651129383, 65.1312483153286, 53.75837426698123, 14.486041894192061, 64.66548999007372, 58.56978855580053, 31.02391676467794, 30.504798715017515, 77.29299325778695, 37.59595335975724, 65.12743088549665, 87.2812671485394, 58.96744206217311, 40.15662249821354, 37.476521451578535, 38.12214454310762, 59.23310504696366, 66.89582088575257, 53.86389115943579, 42.05777671630336, 55.069143203920234, 33.50264501237581, 56.71454305366409, 75.58116758385718, 63.104827459133176, 49.121410859754405, 47.47096403020004, 62.9975126515675, 40.006929443941516, 34.63133654302996, 46.62978655997262, 4.577556512868863, 79.14224498722035, 58.236566432699085, 43.217964050801186, 41.12987831742607, 79.6115409487588, 80.41224382727161, 61.37535734545319, 30.697913457885516, 46.25356300436101, 129.42684557332566, 31.667705494125205, 36.92704624789959, 40.68136403826443, 49.39755468642881, 123.0944948172908, 52.31366346064566, 50.08737295646559, 64.90025539581349, 23.16349203092391, 42.49962340379857, 46.352584486458596, 42.47733300460166, 71.46443429173031, 16.1633916531698, 58.05194833496467, 42.63233738634488, 58.66257649349866, 53.90426528582818, 57.9031991333343, 81.3307625934798, 67.3406168378528, 55.38965812585454, 76.94864325683201, 50.55768993255077, 77.00248615544619, 55.148598015700095, 43.06246409543957, 137.41544189762007, 134.5428802853987, 119.20905346349727, 87.5233587472107, 33.107789328306936, 41.228550282711446, 72.80043219270182, 65.74311844051685, 45.486495679858834, 90.62540707738725, 54.71926646383218, 50.57343726266634, 9.772118703693643, 41.90255686591726, 107.89904804112601, 65.05636107495793, 60.20102409873345, 36.932199112235914, 86.97414466593457, 47.190120872854045, 16.53643082663294, 51.441077844228936, 113.76401409001332, 43.70483988781238, 70.87761073422531, 4.5300486443492, 118.54811329192485, 38.29053300119843, 69.92994932375296, 49.186624026184724, 56.72812696972782, 110.17209770764944, 70.48867153627359, 43.72803597101732, 69.11185793476795, 77.20852850336354, 47.62169123752763, 44.686432474963176, 75.09370973641785, 39.77359925420095, 89.86861807267165, 40.34182806891247, 80.16972222634735, 28.899819682233453, 144.19629381893935, 83.9408972041978, 64.68283206694309, 77.35863425332401, 43.564665924151726, 45.08128681225943, 59.216221132385904, 33.39331929232812, 62.6558894684293, 31.293797021811812, 39.69759202197716, 54.67014732985029, 103.4285586890171, 107.12040784318609, 58.21304224472156, 34.49914316542903, 104.93924227790293, 57.40404160032086, 28.531872626743855, 50.14376972065001, 103.86786587167592, 78.12153373291437, 51.27514959827348, 133.13730898041504, 94.58723424766144, 115.74429563713119, 142.4756487760134, 49.3779809326023, 53.40657694023715, 72.33760228755602, 54.158264899272915, 68.07617069502682, 69.11945029406887, 69.42543898670863, 16.475887783244513, 42.02280823370868, 31.790273127115032, 54.57161471856815, 47.137971649278505, 65.84328777410562, 51.53851525634857, 109.35065852860619, 34.211337502571766, 38.42756465498783, 56.25644357434565, 73.73519302436966, 47.27882669108484, 51.093996708823454, 7.9371762052076225, 85.71467655572859, 85.55099899816348, 77.6689555331892, 59.62067508526117, 30.19010756525873, 36.92606674312271, 54.91872016543674, 55.76060028896122, 43.62008059288438, 98.689568487724, 6.165115910667672, 46.574024209438974, 49.44300447777204, 41.575067468186866, 45.5393681504603, 55.88043228544645, 44.59527194425692, 62.07983551336217, 43.73340524419359, 38.259669695270496, 42.96057840798271, 47.86441948236412, 56.18482440077625, 72.60784201318499, 76.31468408581844, 76.89876893575243, 76.53635674238191, 44.80172451843362, 46.87303590303617, 81.72176174846805, 77.44733354320398, 53.452725999000045, 56.58610978468057, 128.51682478357674, 42.04386179901349, 76.47114828071591, 47.03792742949308, 39.7277180498071, 72.92246691089163, 43.588573984318806, 60.09979378400192, 11.941915070656082, 98.6811697130687, 39.864575541527046, 47.781990733158956, 62.23290099280193, 49.28772147077653, 39.01518090380266, 43.83522416015024, 65.84360293484359, 53.614923607587706, 36.27410269183943, 55.46090453157563, 37.233350805381534, 50.94075776612678, 47.37264169903237, 6.3391805885195645, 6.7869673675748246, 59.749411446405276, 37.20863661394041, 56.51456937291893, 45.36938111873055, 39.14301097541558, 28.010947052826044, 61.37105517309093, 78.77979738985839, 38.34023963601632, 74.04176266724934, 126.10162898226599, 59.92266014259727, 119.33335806545462, 116.45771361826999, 8.003977602998606, 35.564658832036784, 30.134990690509802, 49.398721010373826, 58.08917576015867, 95.4305589612673, 41.009001874545795, 71.12985498366274, 51.55529270733009, 7.584736820500153, 40.51649623980877, 37.08357964886272, 50.743157916526904, 50.30146622056033, 50.832227369233266, 13.001419097344904, 44.08501485428094, 75.42670605965718, 292.0762485898581, 46.774519850822635, 116.77788582940792, 71.53784978548055, 4.302332931630238, 87.09046272737359, 60.51218651816407, 76.4914646706202, 65.0790932519848, 165.05128081797906, 58.10646181586675, 49.16275235924384, 104.4069935972959, 68.56206641167937, 7.61217546930266, 10.789891642276604, 34.257560374670064, 45.39487459677192, 60.22997496513659, 59.62928663576987, 43.601852000802324, 40.535629763285584, 15.003480597187622, 12.314529759135791, 129.74527259917784, 78.78547132228427, 56.35064736645385, 44.79770299367109, 92.76434832717588, 52.46022656304839, 56.13188714760015, 40.6698332663861, 32.94487577268645, 38.248464573299245, 53.25000207156107, 135.1863992268128, 99.22049293966786, 147.07451290587667, 29.14662272033891, 46.30504351628976, 38.880440555589324, 41.39524473544002, 69.6060185317321, 107.19210880715173, 35.224345280552676, 32.59515306256905, 94.15599775799784, 135.00357340119962, 74.70004118494288, 62.51738723931627, 42.23056854407448, 5.091186655360264, 31.955933862443427, 63.070077862847604, 42.28580352109778, 150.216439879571, 56.03387392525309, 35.90236072836871, 42.73146709313274, 108.27755482364043, 55.015061440459604, 40.967186365145594, 48.947705357520434, 83.60153524197872, 51.49307891418901, 37.00001663330941, 51.52666054537639, 71.40044738474309, 87.72262392571025, 91.37079415433868, 51.992570843829654, 94.06692239949476, 4.34148335415177, 99.40991567384138, 48.68402918077785, 44.61356399556749, 87.5836069963913, 39.774028430886105, 66.42046335420503, 77.12164292033647, 39.83805388001239, 33.864725095517706, 40.752976918018035, 38.008441485068595, 41.797354313730665, 93.79869843622005, 58.23998429908872, 65.11474554973195, 98.06840100434783, 38.19784897317963, 70.55510929026708, 53.88526822405006, 37.29255026287009, 54.81890056885308, 50.828129294439464, 95.15373693423822, 59.70125198068325, 36.835131026485286, 44.20240932116399, 39.73804709488045, 89.54735103027062, 52.002414151053415, 54.20723792409239, 108.86086538672154, 91.02798083229399, 46.05674513241327, 48.90870735480689, 49.11967011354505, 105.70331550662559, 89.0776679535517, 34.90336922975232, 34.78591090444408, 151.84805499946233, 71.4386431818573, 55.43182247910892, 57.12871341204832, 104.3356147964217, 68.6363844561185, 4.68393558944915, 66.5459097327377, 85.7997008947436, 51.685927816206245, 73.4533269812931, 12.93983452339581, 43.38319492794235, 84.81533331998557, 59.77116222564557, 85.72186057560242, 5.017635399945784, 148.03894403978265, 67.02273653578189, 106.22813216529589, 71.93399294198002, 23.904106872857618, 83.43319329876495, 66.65357836053937, 38.921705392126086, 48.59309966053699, 79.61687839869751, 35.14070927509613, 84.51811251428553, 6.1842362118338885, 164.4299849340821, 61.2011650784941, 60.310446358892136, 70.47047570229086, 70.7176827765939, 54.9427078355238, 55.05556060515662, 69.7089463346607, 62.934716017618584, 49.06796967584317, 85.44833385208193, 103.96832280141382, 185.9944680773365, 72.31298298155926, 95.13437374705813, 58.79369545662402, 59.57385961280548, 48.048775943883925, 70.75256704429424, 44.402219856902015, 37.70264056917689, 58.69660809412867, 40.82859224849397, 44.52189003994182, 127.30996207599075, 52.43061061297311, 68.33004426507117, 74.76080836877479, 97.48898220436975, 58.00912026842309, 50.82299896309225, 45.28323922618857, 62.24306365271623, 37.635671617002544, 59.10768809256178, 48.453182360703586, 89.11520848721284, 53.347625181164375, 69.90763177311064, 73.03690485288811, 33.4559166267085, 43.97491548962282, 116.54461213173909, 85.65790053408509, 83.56098150344563, 123.18009279830612, 94.9866531275528, 65.80348403449271, 4.163663197986259, 6.298344591340338, 66.99693886784962, 50.814353033121634, 5.646391852066667, 53.802176141763056, 53.60843837138786, 70.16119137885514, 94.92600096537139, 54.43306246662103, 48.62047843780298, 34.989789584421786, 71.20259183505894, 33.70840804383393, 62.59653512430223, 48.54718166386329, 56.488215010273, 59.915999691097056, 75.27403337617139, 48.88004154440017, 58.79072676944032, 99.63871348222654, 126.71770760999806, 40.47316013447132, 81.31732297881496, 62.25343404395324, 48.263434087204466, 59.27344061372509, 65.56572991475261, 7.058119755704982, 123.24092412289913, 231.44855365230376, 67.76871636116029, 67.75521065359233, 38.49728532410982, 56.14735133440993, 71.6682541641931, 91.81128920847968, 74.94260991192398, 45.02354497637417, 53.8037883784331, 48.49488966300939, 97.60937860055901, 70.01862250413186, 54.225313524968094, 51.6755816153271, 65.89552694494377, 59.42918905274651, 71.89610700643871, 39.88851225698955, 13.109159043698526, 117.73008390855134, 46.830370373242076, 5.943608415380606, 63.43021786123989, 94.4062764058727, 71.49501729162753, 88.17573620219268, 45.16863795341348, 68.87043630259319, 46.986834894665776, 44.30846683859138, 58.57229399396422, 100.50454164370834, 102.3043185572812, 103.5415252935029, 67.76115449494922, 45.21154332116766, 41.479293014467665, 59.23870219807986, 42.54538438267511, 62.51661688548051, 9.20491894851863, 65.23142134399191, 9.385283177822853, 77.15597138619692, 75.59667588983486, 91.61309077081481, 87.8544509659442, 71.3194113031989, 62.57380976361559, 58.78180594321195, 55.58341536099631, 55.73887890372608, 46.62728937093498, 60.234197460771234, 49.21043040437292, 64.5312881742096, 98.57911578904603, 40.789403222317944, 52.69557853240427, 67.76893319596307, 66.02373960485835, 5.850355735545179, 47.292371670928176, 118.37207043121055, 64.02949998727539, 104.38210649865238, 44.102594285019066, 53.48102542956093, 60.8173154653038, 78.10703211301941, 42.12337226606515, 53.11541828436196, 204.51443669025088, 60.206768699768965, 43.9975592968845, 5.397158942659846, 55.4245729863453, 71.16955154786947, 60.61289111981626, 10.468784506660612, 182.80150772785547, 50.20826640947796, 56.13460383186672, 61.85078777240121, 48.0284962464367, 117.56893557200962, 59.33280598153787, 48.99253401513131, 86.22140850830993, 60.505829571235296, 47.70126543832826, 63.725196092829805, 65.65316149631961, 89.56973162900915, 69.82091027291436, 47.79032177660397, 36.64965758417544, 74.01481847229896, 42.74833854942719, 139.03800005891995, 65.63029106768413, 61.33082726591059, 101.3037593782271, 103.69236557262225, 49.95624458730763, 68.7999228361544, 64.53492736521603, 58.7939059904955, 49.94953618294491, 91.26692991226689, 43.7455408396978, 76.34122071172051, 62.06022809174043, 9.70953841704527, 148.40681641501018, 39.894046451241095, 118.42115991857678, 69.90625212834495, 80.36489154276236, 69.91378146622029, 44.55953832238425, 16.35885125111852, 43.50575891643391, 73.98158788813248, 11.857649341399625, 62.56731473658686, 90.7231018471279, 76.62832806895157, 233.65791061321875, 87.20648193226536, 68.6544901448858, 42.14437338250824, 97.51432128789884, 65.19164946561523, 42.319708280279286, 50.30719817107265, 4.810621805129928, 51.638632315491904, 41.15819117143521, 48.382961022034976, 64.46288350583515, 71.18912654877897, 183.85879154507387, 62.191231951394606, 57.64570069866763, 40.274808435019736, 7.17882024775335, 196.23487577564654, 74.16541387427381, 188.66449039794927, 94.98841089540784, 110.22936630569716, 68.89176344967913, 37.87285047926055, 50.565605108065284, 45.11256372782786, 103.9499679666255, 128.68065121422444, 111.3627249309652, 86.12778891916152, 56.13854344151466, 86.29897057977902, 56.49739123732686, 124.12117458441475, 54.46807082779636, 51.35075052421828, 271.8457632837047, 89.44351755158407, 45.00968324251125, 90.5499085448288, 67.52051003604203, 43.10762003277775, 49.47469044830806, 190.75101570208403, 10.003751078552984, 59.89039450000934, 109.65412108021391, 251.36266117365818, 58.00918500102816, 50.33692658785474, 63.44311425465773, 132.0911297733715, 10.470900296556016, 11.980360117102611, 48.44679071279548, 200.48921245988177, 56.794665334934955, 7.033495284516546, 62.783509823022804, 61.101057098644, 101.57343068468082, 140.9938059371056, 43.53743621275523, 87.11336791612656, 63.53783803521626, 56.89561146760566, 68.663355486599, 66.90599965500911, 117.79992258523464, 40.66891912525487, 104.08756653435694, 50.50313996550655, 182.597745960394, 376.9484761718709, 47.83803010803717, 130.04148391144204, 59.499296639073506, 67.25164953205015, 56.33284316048701, 86.51129288259938, 127.35688875415357, 73.68237694942371, 49.88090852928378, 111.2637713876065, 148.09266018535902, 98.92657747341812, 109.5494608492796, 155.45638024098068, 89.84085756171774, 19.550037362331064, 164.25593925314726, 55.56993134387545, 87.4513162295519, 72.7844313443419, 67.75700478257016, 100.00540876113914, 12.27388940019621, 47.383678328236854, 57.41393378569512, 51.53201574333751, 46.60732897181532, 125.3106433089938, 72.87728008669883, 68.28693575652312, 56.72632825710039, 114.2800025173636, 91.35370469076302, 76.74594094027758, 62.7916955849343, 76.74704805802605, 64.74623372666083, 96.23419393359057, 73.48954568194564, 102.46957070910645, 38.23457922383634, 72.05033221902504, 61.02619308799018, 137.74006608436977, 60.32603256256336, 55.3556648883208, 58.374915537902254, 60.89579370067022, 56.127460733711466, 47.23121504781812, 51.23697762259506, 54.74202326743676, 81.23199173069862, 44.50932353645363, 76.00321742989797, 111.86777996752652, 88.07205769103119, 7.355910652747948, 337.8723641687423, 105.81069657760105, 112.7980075571903, 67.0399028350665, 45.163660228094, 59.08387710736521, 56.90164513299732, 135.48095430125562, 274.941654698278, 83.0115072234003, 203.0650895988533, 87.04628718295587, 95.95869065405553, 88.54250747757624, 109.0658212259316, 139.28910002743362, 40.0127439049886, 78.2516760617429, 77.7743628326638, 87.985526734012, 96.38566438392719, 56.89241296025944, 54.38504428794108, 75.17665450157345, 115.16040104956426, 53.5845826958726, 48.07492641878238, 44.05120153306075, 62.214276096605836, 6.504227504142569, 77.12698346860002, 55.68144511486725, 53.66569378671939, 136.8468044845013, 6.587473135195602, 47.96764967678725, 66.18742804829377, 34.4487506179033, 53.56370631924912, 64.20799122758363, 300.1724506445226, 50.75357866379698, 20.951468773774728, 43.879997162667856, 68.55796386045466, 44.946741612451326, 75.04808347768073, 56.91965692805837, 105.17086605970829, 65.35073099977357, 56.254137159009304, 38.086753445551714, 41.174232394448424, 88.13522075924, 59.372221637473125, 39.14387107460963, 64.31734886124012, 44.88098468365555, 104.93155602852875, 54.42138522635942, 106.9724063549346, 68.75672161328377, 152.9462034419765, 55.56893907475074, 87.38344504272835, 111.89823579933702, 51.7676919401331, 58.51795432893677, 78.8681127803162, 237.6202627733939, 131.5521194011955, 69.43544999164321, 155.48301770359117, 67.29423246556613, 79.91335639322757, 79.70144720076371, 96.17189655187755, 170.47580841895115, 81.74074851409898, 58.52913631952344, 74.95267634502609, 110.88874763452482, 38.353676867575686, 144.9520671569121, 5.871719196773631, 41.64138031552477, 155.64801004320321, 59.85695281657936, 103.94028060890159, 7.957751873758624, 77.1973909679408, 71.29476377580873, 154.13878565871494, 150.37382728191443, 107.50855563309656, 81.1001306424149, 81.70059549867271, 61.58282340917721, 56.661393068932455, 12.022685326553066, 54.86379767147844, 65.76414657226448, 125.09059721748986, 94.35930438805809, 83.40207739644558, 54.744900564418295, 181.76572982773266, 66.43703962473568, 157.13763714690194, 61.28352469385061, 41.85931978989968, 62.37740132363111, 12.633664926035376, 70.20068426197483, 84.97357482836912, 61.980561450839545, 44.539823112813764, 69.18396234536839, 191.26806398299564, 38.77221146861438, 45.727359758734245, 167.49233236642024, 111.9582869858407, 150.79105738466396, 41.94440488563774, 38.68346236847287, 84.92970001390877, 95.93917722541217, 43.386584366370805, 188.35224338981934, 62.2761650568221, 62.913878329283676, 196.53421861173504, 78.92092628684485, 50.21069846987998, 150.88480531963265, 115.84511385047666, 42.35873210168038, 190.5084996444714, 88.46312194597122, 89.20268777383475, 54.15816082307373, 120.64612092731478, 129.19302871211517, 244.92043203316246, 122.62583035439661, 72.13537834475382, 78.94502469300073, 112.24294658554206, 116.52875114210434, 381.0245375423184, 78.01757611249951, 104.0820977778381, 47.25399299611191, 98.88475281170204, 134.93324509114777, 87.25414711388184, 217.0202945958345, 51.21558983372253, 62.91064213937122, 57.17229815690174, 104.28726547932871, 57.9230433625609, 184.87017513952446, 64.10082344733746, 100.62481637760072, 137.5201154633331, 84.2588227597154, 88.00261573281331, 142.4529818589494, 79.53296536897932, 123.84329346599513, 165.48752028061986, 95.83991719273439, 92.67974648177714, 55.23595116101836, 123.90130589750723, 44.53922560332398, 74.35523924481471, 156.33662218690458, 76.20402043464269, 62.82078330188032, 73.99453629736807, 69.11687574818947, 59.568162218520946, 77.22097142790057, 199.34402056052676, 43.484101933844144, 39.84615831468494, 53.03392326373305, 62.420116601190756, 114.20306267523371, 76.69972208914926, 118.75119902539569, 72.89809515232444, 58.49300475347241, 201.32064681274537, 7.910071167510108, 58.668228274744095, 56.03609964780148, 347.8148121785405, 107.59228251711944, 208.6823534654852, 42.59196706677681, 77.65930513438968, 55.28647825354543, 53.13617815173388, 138.08387400891388, 61.546144123875074, 5.873847132750476, 53.87019427656265, 92.01634755204215, 257.87210980177315, 404.5836982906651, 55.14969680914485, 165.32906119311065, 69.29412127588324, 165.18007878077827, 93.1660457857128, 4.970508969268472, 83.50367554014554, 57.376538949874245, 60.95679574889148, 204.0916787797719, 96.3414779883303, 74.91821688323343, 85.21927949557794, 163.96749563531, 75.74555766657377, 72.6236432267693, 105.45626392440552, 111.63864680913396, 102.6632803388131, 194.41574289887248, 76.40261228317982, 58.07450255765604, 61.87253579400626, 149.0121714433384, 131.3257461252861, 75.00404427331311, 58.21541049967466, 145.51116842844337, 180.23318665741775, 42.573485322464634, 72.32725170800006, 99.43239666696334, 118.81832652394517, 8.11673882336975, 74.77679341287168, 51.70272451535741, 50.104685196887104, 79.83956130189395, 92.39917978997121, 79.9757056184456, 79.73923615135561, 6.071501489853239, 108.97004594192347, 68.77067300619241, 111.62602057461214, 152.92233062337544, 49.77581151023345, 116.80344703813111, 75.13654174008903, 59.531640252863156, 120.51945409503772, 44.340058173271245, 99.43643612657448, 180.01857983012036, 93.17169947958097, 55.4817540956254, 72.28151558842097, 72.76121768661257, 49.91650808387204, 71.1150965728898, 57.2017836836712, 70.63203498675608, 47.962461706410316, 60.63712750463792, 89.84796269996038, 38.440550214655445, 58.85275765640314, 141.67595791665354, 67.55360292214843, 87.29309728010142, 161.47837162806204, 93.53257460315388, 63.46950985073802, 58.99924540244008, 95.24042404143881, 59.29068577524439, 69.20125692608515, 69.12995080253327, 66.97304921350354, 73.72265220331347, 52.6483633923306, 79.02904028165204, 60.82303055137259, 77.0944699706698, 133.00483782856958, 55.4891753730446, 355.3935571807097, 59.03611774665929, 56.426364406444506, 87.26788003159528, 175.73139261019926, 211.17373525140874, 126.73435632991554, 112.8188010267207, 125.03362968321476, 77.64615369705052, 71.03827529881318, 112.0000980439463, 83.87748353766203, 14.890774211840064, 117.24969299425582, 49.91174698186218, 89.28596913392211, 97.3423898771348, 86.33022462201126, 8.23783397340703, 151.2371898649503, 39.49355960421886, 48.82509861502795, 68.74031080357976, 60.13936316983016, 74.86420837172811, 117.86341158392068, 211.16075554590114, 49.81981064972383, 67.49226598968343, 68.89264461067934, 202.52616332090295, 61.70167913333298, 132.71858198807385, 88.47932434684307, 48.76221784680392, 90.67134640161859, 177.8319378524899, 59.68975752086223, 51.00051780958184, 81.49574805338547, 46.973623176007884, 162.69386628941976, 240.9174894967504, 130.86168395054446, 160.4394787335261, 81.1751100167432, 65.50869058574683, 73.08258992940868, 75.51260453575037, 15.54623155353136, 37.017743726957974, 94.62975050193732, 5.691001305072274, 174.75247111657623, 64.97285911076428, 55.967569580156294, 71.78534660743074, 143.03000425110577, 80.75365507439406, 109.23480107030278, 49.93113351008886, 57.603600206140825, 50.76713108454435, 76.43606683699697, 54.99028572031637, 141.18974847410226, 75.70487222020523, 104.15466167193728, 49.380769060022644, 79.28267854039767, 6.5219547278617345, 55.62348739939199, 49.122558844858084, 126.21455717769084, 105.01954479127893, 155.48739806481407, 55.027886874482206, 54.82552622793623, 112.8043141340526, 62.57619175708774, 67.42225761898148, 48.0015993677922, 31.133213778329118, 460.9897831177546, 50.447401129751356, 52.68023221540462, 41.191650975125896, 27.978951324807987, 142.4425686617722, 67.92093256110496, 175.06011844867578, 77.88788599969726, 82.143555485136, 46.73390526264721, 33.31051026923171, 92.41469925923937, 89.50898472292337, 51.39937487309955, 61.60512424859151, 72.38185933166628, 184.44464468420279, 106.28833253421521, 50.18279224312397, 174.32997367988662, 96.27235479247419, 198.4690908551264, 44.04583429370882, 155.62283246585127, 43.888840715016116, 251.71584502235757, 45.5290629547793, 58.55180561982313, 41.60813629846873, 81.2260079607885, 69.28580515107207, 114.54107998131094, 76.63773956970381, 89.41211213417304, 112.49126329264696, 72.45260123582582, 43.05593405566352, 76.72997449631977, 46.81261980141698, 23.972982528712848, 140.40272911553822, 88.85408266745385, 136.82896401944393, 48.70152516170116, 131.95338559235603, 269.9265822697715, 84.00682626951023, 83.6241581336346, 7.827171072641271, 60.81303313830396, 100.54803449845632, 77.78627786967212, 132.24313641096091, 121.52919451060959, 109.46344907566834, 227.4364504018883, 99.32384442342418, 62.808978751970294, 88.56199537356609, 49.8648483157781, 63.56819788295295, 63.90773605374676, 76.33185667313543, 103.47571078088026, 72.20220819222064, 83.09657930395602, 91.06448667812096, 63.38890683216032, 60.50376253543869, 53.19769207832604, 45.91142156417756, 88.06752127149312, 135.1273418957384, 51.08267486330673, 50.08073811148653, 48.92070442508467, 66.24109281950592, 79.9966496434715, 127.02109964526738, 551.4578913124818, 82.6438834245555, 201.90983499358842, 55.64207234151323, 86.30566798646453, 160.8517076123984, 351.89297568283075, 67.98995857589203, 76.92269739806449, 188.323127259953, 113.09547671262806, 55.373417033197136, 28.87793931628286, 114.25909248356926, 15.83068483219612, 112.39593264969955, 9.291982298925856, 67.90359758917808, 45.15439656785262, 128.5057809931569, 86.39216738271803, 73.02792881912458, 91.77244568697272, 195.0443523933571, 263.5210245535013, 323.90622092598164, 61.51372982251887, 84.11750068114598, 56.984571532115275, 102.74380349176784, 57.20955816859876, 55.596670607344734, 7.98924118477175, 443.84</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>113.621737279892</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>91.70751202075107</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>[188.7426300048828, 14.492074966430664, 42.60511779785156, 46.67363739013672, 194.1195526123047, 62.683467864990234, 263.3599548339844, 39.16868591308594, 91.68588256835938, 184.99703979492188, 211.4731903076172, 51.489906311035156, 82.73592376708984, 106.58729553222656, 101.66658020019531, 103.13973999023438, 231.4219207763672, 85.69194030761719, 54.036781311035156, 55.39414596557617, 75.129638671875, 59.99843978881836, 55.978797912597656, 63.42280578613281, 46.77250289916992, 517.5328369140625, 47.91580581665039, 120.15680694580078, 87.59761810302734, 22.57648468017578, 136.51223754882812, 385.6273193359375, 245.06600952148438, 66.70626831054688, 79.67749786376953, 48.45403289794922, 21.58257484436035, 68.41600799560547, 52.986328125, 17.08926773071289, 45.914119720458984, 49.81611633300781, 49.65057373046875, 130.852294921875, 314.494140625, 58.53708267211914, 173.74728393554688, 52.79454803466797, 214.3779296875, 44.295501708984375, 185.66360473632812, 63.794429779052734, 10.01522445678711, 147.574951171875, 49.73012161254883, 79.58137512207031, 205.34426879882812, 50.063194274902344, 10.2536039352417, 79.68937683105469, 418.90826416015625, 135.10894775390625, 44.16107940673828, 188.51837158203125, 68.86436462402344, 58.32927703857422, 16.747657775878906, 59.02018356323242, 194.0004119873047, 158.9393310546875, 77.41419982910156, 118.0616226196289, 54.42605209350586, 52.9885368347168, 43.92014694213867, 171.6186065673828, 143.46641540527344, 78.8525161743164, 57.91845703125, 135.5035400390625, 97.128662109375, 73.4919662475586, 87.2523422241211, 169.99192810058594, 11.353031158447266, 35.231529235839844, 182.01931762695312, 15.683120727539062, 308.9900817871094, 299.4203186035156, 122.30390167236328, 72.09854888916016, 202.1248779296875, 174.29856872558594, 78.8182601928711, 128.38250732421875, 229.67396545410156, 88.79756164550781, 84.91422271728516, 175.8765411376953]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandom1601</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:38:37</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>92.08489446510939</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>76.83153280779486</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>99.96039207841568</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>4999</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.8011264649045112, 1.0397675265229656, 0.6921087159347381, 1.1879087140858136, 1.370542536850724, 1.1467446345530485, 0.3101272008032878, 1.677466696456907, 0.10968628275483673, 0.9739010137751829, 0.09134106012846353, 0.8738299798298741, 0.5791869550466108, 1.6631660359728209, 1.687047905785643, 1.4143520046857145, 2.453902457950901, 1.162286198703704, 1.8301598262763996, 2.2871241272206766, 2.383629646350758, 0.38326341737085773, 0.8065916720012456, 1.1502051566957152, 0.3902932823212479, 0.8181783921990464, 1.0168992680820794, 0.6126925980238034, 0.866796133315289, 1.1671784421346127, 1.429448898424296, 1.0371042599417104, 0.7706399286448635, 1.4353685291368015, 1.0092744268480849, 2.383923134277688, 1.3960381406156668, 1.7707493650856978, 0.5135670005957425, 1.6537541102970204, 0.9125980016425912, 1.7378585747918138, 1.464022927906812, 0.2099145581936257, 0.8695553407243071, 2.0565863202183836, 2.1365567814921724, 2.9589193009266412, 1.8634880492918302, 1.5986372577754466, 1.3128611770742944, 2.42098492613957, 1.83677922059439, 1.877694580786745, 2.1511000908966778, 2.25423919449781, 0.8741750549342305, 1.372107059660986, 1.217919491868586, 2.2538366250645656, 0.39159556515185023, 1.6986038691124017, 2.048175746913967, 1.3632789837605974, 1.967574340514835, 1.550380874145835, 1.0544014076429726, 1.8799628312601697, 1.2665415604100014, 1.2599089908296845, 1.2500666934185438, 1.6938076668783904, 3.359980234885317, 3.692934934316, 1.1235018347186292, 0.31808944477619605, 0.8127957309707153, 0.605883319276753, 1.2459912058299738, 3.054819700227895, 1.8061144232045865, 2.7881600242508138, 2.047698435305375, 2.5238624166732673, 2.211664315301465, 3.5288665822178027, 1.73515225324838, 3.4888596343795206, 4.65594977505233, 4.8123229038231425, 2.3690215715360954, 1.549978042958345, 2.930826111194118, 3.0967379163558535, 4.810440824965912, 2.830100973045164, 3.479537919056316, 3.6450962217068286, 3.763129222365414, 5.695815855980006, 2.7280921188014147, 2.7984642941890647, 2.4269542235353456, 0.8256642458504101, 5.537983315768468, 1.334061577714891, 4.657827477712033, 3.6566625733462033, 3.0610863551612453, 3.5097543195661243, 2.1065552581329667, 6.6630334131601, 2.749770613565707, 2.4009215495027108, 5.802499686294344, 4.059364769114884, 3.3879983590053584, 1.528887282855438, 1.6769161861560198, 5.921924797203543, 4.1577160785796865, 7.93428835336614, 12.177738873538074, 4.411838478990764, 8.312319289864735, 3.8655446288893858, 4.7466309917143334, 5.984463668362692, 5.858091206834883, 7.661577286463199, 3.475073446647793, 6.843572292105119, 3.302487169748469, 3.917649300994667, 10.291290553071445, 3.8683336574882143, 0.3509695286400801, 6.419029520367692, 2.019142357667037, 2.9493289736094694, 4.703764117245227, 5.106722362206075, 0.7265195019576574, 9.198251234137336, 6.359987410148027, 3.6103591435009776, 3.654229083211146, 7.720883954209196, 3.650535970669442, 2.9452438161061036, 4.86182541098061, 3.5431652152397817, 7.567439290023942, 4.829087876051966, 6.249143345632968, 7.984426811562893, 1.5081693122197226, 6.354768979154244, 7.60956591468226, 3.462621787551585, 3.5078211862836244, 5.823369432023357, 16.870329959948535, 6.333426306500684, 4.055581993143147, 8.439500364883568, 7.804246707354614, 14.308237930269609, 9.5142632831055, 11.24094590797773, 7.44787774888716, 6.775832580604362, 11.857798457618257, 11.436954767934552, 8.29789903876788, 10.09334184041613, 7.488731454364448, 10.671985698909323, 22.01752240064178, 9.246433952356817, 8.86914595108223, 12.09377236668477, 10.50898307932752, 6.618731189367893, 7.366689949238405, 10.462844100541211, 7.50510428600624, 7.5784637661279985, 9.57033106537716, 7.819205942984615, 7.1300148425217005, 3.7289791871918476, 2.138904406083811, 7.7250733203917035, 6.35979488999298, 9.700706809101858, 11.669418466298369, 9.846697458855694, 17.41987995398308, 17.782745880472497, 16.656283270379593, 10.127222183156361, 20.991112699560805, 10.740280274326436, 10.891869810069764, 22.67347034630413, 8.3507556957312, 24.170953581519857, 8.513968713496693, 13.53344424892108, 21.926167610571007, 38.367111846821885, 9.090709964245539, 6.350237526763104, 15.556739186972585, 28.462632003208384, 7.456770761591448, 15.157142079238364, 14.358957682235694, 10.908874822535324, 13.463099514660062, 23.520448919811418, 14.783678079516445, 27.17042893058838, 20.965126687283888, 11.461611632088232, 29.245313804744633, 9.701609972517758, 16.152472298374924, 8.471105901493477, 16.596708380328977, 13.42038236990996, 14.58475600608884, 17.267380401275577, 10.865742289732193, 10.538837874902773, 24.487315067064863, 23.319616955856084, 10.231543680350434, 22.495931008162124, 21.128844906322875, 19.660188224581873, 34.17513619530154, 14.639868801036881, 31.665736554017712, 17.32934631436291, 21.917276944261115, 14.936843995486768, 54.316835668586094, 11.07388028697524, 6.847972993279075, 35.01905951645273, 8.259598525208252, 15.021523189535992, 32.92557402867176, 23.484975102708724, 22.077675895763186, 19.388770497600355, 14.325029130040047, 24.468466543503784, 40.964156505022366, 28.472756590208, 11.420685639548717, 22.76833616251522, 9.467592957657741, 41.09335153889767, 22.357620600180617, 13.180381481746675, 26.21071988010667, 38.44124077556986, 23.903469914964507, 30.785845620521, 13.132143052318645, 26.712600013905263, 27.39799094205671, 38.499037449224076, 16.01401892779652, 44.977596733083814, 21.72697900302343, 28.305918707417366, 41.87827063438929, 13.824603131836856, 21.821213700855242, 36.1121331779784, 48.408520919746444, 40.76417708964839, 32.6188786367459, 16.09979693244824, 36.64643361183056, 24.49518057164397, 31.787687588114842, 35.15250706679117, 21.932550557338626, 21.188938401905315, 28.451831962561723, 13.964327417288873, 20.956888646179877, 21.520501705686193, 5.33121052866688, 43.37811701436515, 24.427006601603985, 17.480890343227202, 1.9719409396087006, 2.5919304926860676, 33.03521427109687, 20.45390125380923, 3.0548729460246933, 17.207442510340755, 24.576604246189962, 27.680888226262514, 19.974111157775177, 27.79908918509632, 3.3636555958882894, 28.938602441961024, 26.295860254999724, 36.232400065283834, 35.60513466379766, 42.30763858090685, 28.976815257877156, 27.725502205716985, 7.0703164232409215, 23.0715885865725, 51.45491056148781, 45.65341754336696, 22.700239172235236, 37.10893422780629, 56.20759529907237, 37.26405838150994, 42.945056677511396, 32.30761307869497, 46.2908778300959, 25.91587523278549, 19.69874035957433, 29.537774432443523, 32.703558051723185, 34.79843583597234, 28.664254639793835, 23.92568767838975, 40.699849416602135, 49.330130036223764, 19.50106196641234, 23.94246007592643, 47.497986474346106, 3.608313419602759, 42.21891519753306, 66.6695958871585, 81.73837785089435, 20.63120986586413, 25.242692135559, 48.06926199949894, 25.154344873916177, 41.013260834186, 39.33147755291991, 19.84625696692216, 42.27725748191894, 39.85217533693265, 45.90381423725243, 22.20838002333125, 28.169097960643015, 30.255449260231256, 34.850006825155674, 19.487197438493336, 82.50811057894042, 25.767871747095562, 52.516708926752976, 34.953148354794614, 33.100309104753805, 2.893408651527709, 32.54513562849806, 24.643366436831258, 69.97878559951549, 55.96178890248223, 21.767043043424618, 32.671291012682595, 21.23789167751597, 27.410386459090272, 22.849458526198035, 19.370008231090406, 45.52933062031017, 3.795638238623929, 22.127480183241744, 43.674223575962166, 6.731943317086607, 2.984831842832778, 30.739401109637036, 48.019650840493796, 41.96080074446599, 25.569785020519813, 50.505224826185376, 32.58971236222794, 47.989229166125256, 60.78139536056017, 3.113626214187236, 59.02632552291185, 39.53546812100988, 30.39127629014303, 44.492185546222544, 44.37413736360308, 29.189446712858324, 61.29157456558497, 55.55860423456832, 30.86281598086997, 27.96223613108752, 67.64844707883611, 40.0174048129129, 26.283179356332703, 53.71575414395987, 41.86933846020718, 38.63458527929697, 43.23866756937698, 55.28621938157879, 52.19404062907878, 64.16577221949927, 50.91449015870225, 43.12819700456516, 53.6060412038098, 48.333650294980316, 37.65431343696327, 4.15998290672483, 67.06703768256503, 31.9101185200765, 31.056272216870948, 50.07057162832313, 46.198070549722345, 26.04408943139468, 37.93484534266103, 63.67665254688458, 41.217570697848394, 29.727445560000287, 3.7096499867338224, 41.40120205039323, 55.17251554133222, 37.04662511500779, 28.97363205615769, 51.32574802665509, 38.03826180944362, 32.21942411886641, 26.50059161103113, 39.390685194571624, 109.37843306290361, 45.36473910286049, 53.70250452497062, 91.13657979093631, 87.29669383328988, 78.91696088037276, 49.36141271032931, 100.63883586536714, 40.61688253354596, 42.66361000381627, 29.26080649372812, 44.84413412727685, 76.15203314789257, 55.60583186132969, 67.14800393435145, 43.18396841279219, 50.65811065999997, 34.58665374561191, 42.80868016400701, 48.65445954456463, 98.88842229060315, 142.26381947877704, 43.748205751512664, 51.38303393541804, 79.49247096614454, 42.38773597614196, 34.75274540793794, 66.63492824111496, 54.01741128851816, 73.6506050974012, 38.69713194267466, 48.487889807090596, 41.77672003089274, 86.1316538336786, 35.01100027791489, 23.126617209186506, 39.575784957513456, 64.07791806627232, 59.56530868484861, 39.24821895458968, 58.21496258775633, 38.41210071396688, 45.02800144571929, 186.40589568709248, 44.53730343796967, 45.688468016663194, 37.2334187275697, 92.64714116424854, 32.82688085217307, 83.70299335944497, 42.323328077811965, 18.308034950689233, 10.863137910986143, 140.84718810690558, 54.176755161146524, 8.407892961175559, 114.42983789161504, 49.34111252216823, 99.26616541775284, 156.2076227806133, 54.19073926264694, 59.686006837145825, 55.513945161298494, 86.90855364792051, 53.77350429814379, 65.33677269867256, 58.82818397686094, 72.25544859568168, 13.183558602259346, 40.18159942711241, 44.09063900876398, 69.13825901116496, 160.454509246905, 41.63002924507388, 43.645432922235216, 43.089043550922604, 87.92647091746775, 112.20150023555055, 59.3157478390296, 131.66797030852055, 43.12552555227226, 35.37067747871906, 9.500289625248758, 69.0519989605539, 63.25214109032936, 81.43486689606843, 34.11633431519746, 47.43464349594866, 53.626072401571044, 58.79435165808085, 42.40669785491069, 52.329017903065534, 46.836716008906784, 39.04185581302174, 41.89298869482393, 5.985715390013099, 50.78995510779995, 47.343223767933694, 40.50952749876031, 42.578261229702626, 56.57201607309936, 40.86157028996928, 37.224097703375506, 56.56699462225333, 61.06099396782746, 53.90095333845145, 75.41182934937598, 79.70160995804235, 59.00426399988555, 77.63201717980114, 53.245483265651444, 55.05599687972515, 60.6679904831944, 53.086319081747654, 72.59676382628638, 44.17963453358481, 57.16114629866749, 83.06481033025779, 73.71440173796849, 102.92702387360261, 36.399197115255646, 51.36128023453773, 49.557004115306036, 102.93855642023017, 43.47733486969869, 128.98223760905344, 59.35342302346749, 66.15905847768893, 57.856521643795936, 44.54700440228056, 123.1678176773121, 40.063269127821606, 40.15291889108757, 69.45250512817613, 42.81429473732168, 32.73488819819725, 127.84445142481792, 57.515852679477284, 40.74228641880444, 50.41385988447506, 39.83438615068788, 75.71422371114201, 72.70637863160357, 52.89129665718995, 172.13758533334888, 76.90652438726424, 45.93056338442833, 43.11011925827417, 90.07544673010449, 39.58038594809496, 62.84143525785427, 42.490088435091174, 46.019468897716266, 61.67968912333054, 43.77930972484078, 82.19825481064386, 84.66473366468675, 101.88385388936757, 47.4610524547347, 74.52623793577796, 69.84173112002358, 39.163593925043784, 48.49139664466626, 160.8770195690912, 66.97046702144026, 33.67671720906509, 45.00842626650983, 60.15684765547003, 91.49958808421127, 36.52562039169868, 114.80535343832011, 41.83069667340839, 34.98947951558936, 89.03790769424981, 56.198947823665335, 62.91943639117498, 54.232896344777316, 44.64098657671057, 164.46258427148723, 39.289427168873814, 65.1004534527166, 125.04807607009437, 46.49644950394637, 98.11660462580903, 7.642982083641278, 151.70071754167853, 40.07346057693944, 45.97855969118058, 103.14212577052109, 62.67563323629367, 36.46059950599875, 70.06521860080292, 78.3230130451655, 101.87758260718341, 100.52330833221899, 47.758082046902125, 53.62549447240257, 53.876247217412946, 60.9394401012716, 46.788898502773876, 57.3714053607895, 52.24884399046905, 43.65088082506518, 54.00728957263903, 59.23418677796266, 60.74718028066209, 139.6565647216496, 48.102669233421494, 36.944151791444085, 92.0807733920474, 178.80864876175474, 96.2784808023839, 46.820227378485725, 49.76570840614826, 51.52671975325561, 53.90820239878037, 11.156906807217634, 82.3472498000722, 78.16404534785067, 68.81646375041589, 48.37007341826208, 45.09977756951177, 73.63825797745105, 58.04766758170389, 5.379028589452991, 7.283202255278005, 56.621002567246975, 45.910330076622685, 80.94026639343733, 46.839565868320754, 73.26150646456719, 10.988224992663419, 55.22830752304737, 86.9966113677106, 75.9570878208631, 82.19803793716224, 107.86777850831234, 5.709824305339544, 90.65694018046568, 135.33767322595992, 40.437825558295785, 62.919418773893824, 83.02242377827814, 74.40255559632088, 44.87189658822982, 85.93690995195219, 107.88091925320687, 143.1127961013695, 39.65996316884692, 51.44130453110045, 31.29007472709278, 5.210935695908706, 115.36061258877356, 49.85719635254735, 76.37824592352966, 46.932958792513546, 44.20661348271965, 90.49631198323009, 127.28921513693555, 75.5961219471727, 58.619237636764, 42.947906384878046, 4.497376263678527, 116.24779448418302, 94.50173802005449, 80.19834466064525, 65.17396208350543, 113.51458925563387, 37.9381259710599, 47.736073117382034, 46.133695999331636, 40.75186958417568, 132.58392461037658, 109.87589892339238, 68.43335348288606, 101.15434834750225, 59.74161807536133, 41.37352752816048, 50.1598786703727, 5.2956755581642, 77.58098528363027, 67.5626695787534, 35.566531245406736, 76.51784838032094, 37.27636734946912, 51.13586939967696, 128.84692331248607, 99.5753056788879, 88.59677160716454, 60.13967740298746, 37.77936424116223, 46.8745474956856, 43.095425552758996, 45.208729609890504, 71.43320254677606, 172.99850900133305, 48.21521593073485, 163.75689626371454, 51.409206002129615, 61.19632300935425, 122.93998812866377, 42.52486719884167, 84.02118056751874, 10.524183944503218, 46.13707862507433, 7.163924599530511, 142.35599170827845, 55.8712124883518, 124.21617711284205, 75.01523944262931, 56.67454150968598, 46.83130259263562, 53.729442170347525, 42.2708948731368, 25.68858545832742, 96.14246862958028, 15.945549877623616, 5.610969461421016, 91.61159635961731, 87.53178796517399, 81.55857749470354, 40.54268329833342, 8.842347882846262, 74.88343913533501, 85.25800874098877, 53.33246210673838, 79.81703184010091, 53.23036936997829, 44.045634364705755, 93.31739304639338, 82.02638315300764, 53.594931100523084, 51.79213741671038, 7.637707344214119, 106.39531766452181, 83.08017887796764, 90.18084510915678, 83.66616511343355, 54.9752410655857, 86.45151491375555, 29.180984959255163, 70.85664878185801, 78.66978957057886, 38.84488882433372, 56.834220947296444, 57.94014100962795, 55.293325780019586, 66.46029005954355, 41.903933089371925, 94.923768940299, 40.861689468843636, 74.41947565140221, 62.13113610019039, 52.338622116620726, 5.77669667223901, 68.2671039598232, 115.16736697996528, 69.8111513734204, 57.91008012507676, 36.795623352790116, 41.74684368681789, 56.61242466291824, 38.780661851681046, 157.85035602258642, 71.33057165487283, 66.4738458510341, 58.70985665009524, 50.02605107362102, 60.29560442247322, 108.57517710507659, 58.920903371524744, 50.80664286631937, 55.519902450207944, 57.85876105599907, 62.74457861585665, 8.58059466873151, 73.8105609448998, 127.07212191273065, 72.40362931930734, 40.18706314542031, 81.89198777182379, 116.2333196811168, 39.74037133986967, 54.87331500388426, 4.780190527803096, 84.399875295747, 54.92818692247079, 90.65972791133368, 61.87886982811603, 6.356367973646948, 59.82945218420982, 72.24434067560462, 120.0086688284414, 74.45142206238357, 63.60776857870814, 70.92989540761988, 58.378121540007804, 62.57549724029445, 30.375710494772342, 93.0261502004551, 63.23722931281163, 35.41518006519432, 53.355084664973845, 99.64114705341304, 55.74101598304318, 59.094492072694095, 134.7781672821871, 9.120144533249178, 48.781732574951185, 42.04204856261687, 56.297315506410655, 123.53252024997283, 156.88871508988439, 36.292446814396634, 56.04115697376192, 96.15111446203323, 43.13218819411316, 46.03897889105598, 56.94391763329214, 87.07808878671513, 110.83550931089849, 47.744408428003865, 62.55935163839778, 47.21424244985207, 56.41004826422436, 71.05767442365375, 12.843344766721907, 62.978380741278905, 55.55450902848551, 65.06155726631052, 38.837041243767594, 104.50999650648197, 44.508941285106914, 49.394314931491174, 68.2023512259306, 105.88226298820462, 149.89205161313288, 137.4849303615919, 45.43434724742513, 45.78615724733231, 50.08102856128959, 57.69045135072751, 47.32465185231635, 51.37045526540513, 120.05788349698624, 61.31349966023943, 171.50445919701562, 102.04127848362194, 76.72959052514264, 39.07865927841827, 81.58578043888956, 55.86967004742873, 162.0508304653645, 131.3422412273584, 32.264805844150786, 134.92715106860928, 77.20561946596837, 66.40597457495359, 96.69704093704922, 79.5204351140398, 20.859850316076404, 141.73276255533298, 5.3723689716432785, 56.00201289068263, 37.67525346436289, 51.220313064396734, 96.750875514895, 34.738556327115994, 8.198169688898748, 86.91348218336645, 117.44333319078474, 33.607159275887824, 50.85525470731511, 55.46212958971809, 87.58572269856778, 57.813182584515545, 133.8495446250735, 5.091728584171059, 53.86411616100379, 54.11508771140416, 5.362942020780202, 104.83915881585072, 131.23480227775215, 58.98037717448358, 7.917194683751921, 47.27373759030897, 53.410598903410914, 87.27894892237853, 84.42898312307376, 125.56951567150804, 57.444383731326795, 99.91459725795468, 50.85305025274363, 48.39561725472313, 52.5414739308318, 45.299706229648145, 130.74528637790152, 155.05755871369067, 40.45161668001414, 41.408880736612176, 47.23538869502791, 61.26556262793193, 72.98188930964542, 63.45829002330004, 49.20771250317581, 46.43372869648367, 36.4898665686463, 141.67044918488466, 56.53216520015366, 71.24644247460316, 62.49864729877505, 62.08781054589274, 46.859786015396516, 55.68749861922608, 92.4173897111926, 59.14533240897162, 94.71751880028394, 9.221946471304719, 59.65888655312942, 101.82727551263527, 33.90080938338588, 57.47568203569976, 85.7545717036435, 60.90297389500441, 66.69608275526546, 197.08232667731005, 70.21497762212371, 63.33054719743827, 96.24669595231956, 114.41322274778125, 41.38241203188272, 54.05359201005, 111.09653767124185, 53.82940010797016, 78.70356780612353, 39.40806516039195, 46.87989313110441, 65.49482618842634, 81.92890659251579, 117.65860952032628, 133.84151087894554, 147.6100774668454, 65.66985753592904, 71.0648529331936, 42.557787628051386, 57.32866255009316, 59.21755410860304, 42.39339671148626, 84.94200389060963, 40.80075518189583, 84.30326332366933, 48.114282825258826, 78.73814835939133, 7.394953909328541, 52.499956743608955, 80.26792129641413, 105.13781088820124, 42.79551040238589, 52.9819228153046, 6.258377985871508, 84.41472381029601, 121.19793498113528, 94.29005693972816, 78.65111766435382, 42.858302708150866, 59.34342917751509, 97.0585107069197, 93.23064286065915, 75.81105732639391, 63.266879499142156, 57.20199010293682, 71.6903836600043, 136.5705497303385, 73.894926515367, 47.58732225287974, 65.59253100465926, 62.471746651377785, 67.67006168892212, 96.9048295647721, 43.74250267997372, 37.74582055852386, 58.098047370886476, 53.204929916766474, 68.4475853841013, 149.31801516327664, 66.2010573191045, 51.8359372189804, 45.54289479352051, 81.24287078471998, 46.126536333524015, 107.02211722935452, 60.20039288004478, 68.57954715194266, 61.11483397844484, 105.77671084203642, 37.40270407088095, 92.21707386668463, 113.36800236831803, 39.475824710485, 48.246173487651205, 97.09047780757496, 69.09885929625914, 120.65653247464529, 106.05825932641264, 80.26885521687322, 97.20341363023526, 75.76565313314514, 149.09163516818333, 40.031327203513726, 45.62548149950444, 51.08404461888565, 91.74577011022816, 188.40139063952168, 38.68024405463486, 49.8941777480854, 143.57266049638443, 6.83396367037487, 70.4399700826213, 22.74290912846725, 46.229649399739614, 70.29771769918634, 66.2145158759811, 57.029897357247215, 166.45696036203012, 22.471154536568875, 104.31746232677118, 80.97731245480477, 84.99264015475224, 45.8612022814798, 47.63483790489315, 44.63290486949591, 124.12219294707837, 182.74319679099978, 118.15574958226505, 95.04805714453114, 64.90597572443443, 43.60249643980792, 67.2562006825645, 65.20690587749536, 40.883575120593456, 60.54020420370739, 80.20843920035354, 71.45395831805565, 39.14052305600289, 39.89791229729795, 49.81709556658632, 66.31467150614014, 87.08909035700685, 14.235494233086362, 67.66432846440556, 64.24889487663148, 38.21339439080216, 68.08535754386394, 44.29752291362839, 55.07253358975607, 45.02908997016806, 200.77356277704666, 68.64778192032769, 81.6568904887624, 95.34953712669953, 95.89498636624796, 70.71229873520566, 39.78936070315285, 141.44421112321064, 65.84164573813122, 38.63545402722502, 58.9775098170622, 76.6413314924964, 44.003054888579356, 46.1823171322474, 56.58829269939544, 81.34916234985081, 90.16349908880042, 145.4386412121098, 67.12711639719384, 74.74616636966762, 48.32971891429004, 107.374267717469, 51.38234934240345, 224.0143053924552, 69.89776574413247, 72.8074853540622, 153.05677535359618, 96.07391903658684, 46.24992886878018, 73.39191229513911, 32.76427011147123, 87.73640811609911, 84.97602022261864, 88.69197193505455, 210.5958438157215, 49.907199326318505, 125.22891402964748, 74.16862538491148, 118.95627246972352, 84.0629989878589, 47.06639148102354, 166.4068260823372, 78.54831868007311, 82.92462487952976, 185.56681894852818, 90.44691255615462, 45.58138930574956, 55.47028236547342, 99.03454241605647, 148.61172104940977, 40.895720954691356, 64.94313164327912, 271.4447808393013, 107.97974764731663, 56.33089212793698, 67.78746311364063, 59.9471517401646, 160.40122587775534, 67.42523412042539, 59.79419649979569, 72.86485791070616, 88.6602839045331, 122.72997922901907, 47.13910968956069, 40.08394422303202, 74.52343338080837, 72.6552317674469, 219.47323846167723, 79.78917350306173, 79.27021227035996, 77.41119112266571, 38.163750661681085, 84.02620730093606, 13.560066351571127, 48.27547068069415, 118.34467521509696, 58.21472248852931, 58.27414045759634, 89.2183904328654, 75.16476488901372, 58.65610891466643, 82.40162799442591, 53.21505215162737, 82.75260787573457, 205.9773397538921, 66.13135261352507, 67.48786384255243, 97.87252982240548, 64.62992639781726, 101.08388546763551, 40.25264221423513, 10.758716181453467, 135.21708242849363, 8.76957524867095, 38.269892941188836, 56.21350888409274, 136.00011068478992, 59.054713894974725, 99.75072945044208, 193.5190908369115, 94.8482814454643, 111.51839955490001, 128.98308771274426, 63.288087294505246, 108.77836269780369, 45.961025784848886, 82.138799164535, 98.72137548093848, 47.621252615923076, 41.04720746310401, 70.77814992503895, 75.6565776054507, 55.62549250517877, 47.79591923791427, 64.41769326401163, 260.67551672407944, 179.5857394438159, 7.150706500845015, 138.66789603278283, 246.06779142489663, 65.57519724517887, 64.27021340459656, 65.14777469006616, 45.641211246193045, 123.60456659389983, 70.932335571507, 68.01534742180651, 94.8863811819328, 84.26155850284488, 52.74846483355397, 77.87630630409487, 49.12472263855332, 60.12770327311248, 56.44967995407284, 73.76199371622144, 63.35998523925721, 50.02420434792379, 62.931588000207476, 178.26395586644696, 75.72827191765333, 91.43846626011309, 172.57731290291022, 82.38906297032189, 173.18701817897548, 69.3758961609557, 57.99112028291577, 11.77069754264272, 50.99358106397914, 48.51995899187752, 59.29104601890866, 268.06361290716876, 55.68865762481603, 134.67675261275645, 64.63612766157314, 81.29416281275243, 93.1734526284168, 103.91046509818783, 107.01672021217226, 7.076599068881663, 99.19583222410866, 45.71296605059363, 169.9707309534595, 52.78473519538106, 98.8509329319984, 82.74407777466587, 69.36060890405908, 87.93798407070192, 77.32807096357077, 163.59538471580674, 42.941999615364324, 49.49161916518265, 54.61916817687127, 55.61158174143247, 170.38476080826467, 59.69423262762952, 96.30080108739548, 18.49015581870584, 51.545496918275084, 18.885526518335407, 77.086146619811, 8.33449295800861, 66.88938036134742, 58.952790847501596, 117.9515071028101, 78.92184172083948, 62.18265926067276, 55.08885367048237, 53.723860798303576, 90.05501629822948, 128.99302486890133, 52.84131112548076, 78.31258084423746, 87.89118457743129, 74.85380674594832, 45.851040719478625, 47.468884461249786, 119.62900686065173, 107.20480903164938, 48.105162430718245, 118.35553354746196, 77.39209436869255, 76.50998122262601, 65.45131586251011, 57.617374916148286, 70.48368290256282, 102.55830513915264, 12.837913933253141, 57.99506692673399, 120.32833838859618, 68.497384165871, 60.37522625869065, 143.2271406055666, 122.59841453091269, 86.96173338131545, 266.53209773468546, 73.73687009479511, 8.212528163992133, 9.206774440173959, 195.9405204095618, 21.131778217990703, 83.10432478559322, 131.1066188732911, 67.50526172863114, 83.51416379444564, 66.39439589267295, 135.50353600032673, 93.56576456333674, 59.33056250961301, 76.13766832891812, 15.864627695262001, 88.65394513226161, 75.00672680924622, 89.97749300526641, 66.97739053910567, 139.2934015892345, 61.2865320888394, 219.86201658309432, 42.89570132001614, 48.25439231705021, 83.38731627006241, 40.84420096015966, 59.45878183420771, 91.83718796581596, 84.58847184732664, 44.29431010598783, 150.46491840525456, 88.025330913024, 88.62399651003172, 82.22070036081908, 96.89435567358434, 57.49554430202047, 87.31812044171473, 61.88110887581332, 48.46515661795415, 105.72766849170661, 106.30089416624628, 55.45006822412377, 42.408001556587394, 56.605323057956475, 58.72560290345706, 9.441114489768307, 152.64539307036634, 7.737132099013379, 20.14659617976237, 175.39942920440967, 55.81307702389008, 63.40767924387426, 74.48021666693988, 81.21328959777999, 82.07597100186952, 12.057080633916234, 169.8475916143839, 81.3429789095939, 53.38702013308222, 235.06831200790745, 74.62961640174746, 65.65121165434064, 9.130213203062269, 52.198662467485185, 47.537183819512244, 186.90359957528793, 110.79649522124174, 61.06246215156533, 54.29730297945727, 76.95603982196286, 50.90522835821969, 101.86362839026783, 127.76182426669303, 97.54759147811279, 66.65985211143179, 14.21075842042783, 55.73882956979306, 58.66371880238056, 51.375630110389025, 108.2780671317362, 89.9496270305238, 69.71627340789843, 18.17687617091834, 113.58721888928577, 72.75754181503545, 115.21984513640606, 69.44260121195282, 10.88209285612173, 64.08136052880111, 10.240338653993279, 127.5483859831348, 87.21787428521147, 52.03808518179578, 83.00603762724575, 50.53449636500257, 82.569906899692, 63.73204919557044, 53.72501459220624, 69.63527816714549, 34.915252778801616, 63.5705574147226, 55.51646750896433, 60.25040508491689, 39.88545683529349, 8.176204104787399, 64.33920283338962, 43.97942573877519, 49.35390604865415, 51.34561208842463, 61.32639884182064, 54.735727772718846, 116.02275135935565, 157.94635782597734, 10.969944520915057, 96.83852819712325, 11.655839779601378, 166.26178644468325, 228.38794345033568, 191.85827361151294, 51.1843958360235, 299.7071432681201, 87.843214419776, 143.29814252950717, 43.886542770599966, 119.55464633208352, 111.2294664076869, 82.42463821115996, 122.11357140700203, 63.380683782264086, 52.15942844222911, 68.79856076326116, 76.96770140247693, 80.12254128673021, 94.89817959009467, 106.06028886572875, 41.36611112270429, 54.961101236836775, 127.83702986710831, 92.2023422336688, 69.72033669771376, 128.62029998589577, 140.43562798165334, 145.603294116932, 10.893725291625106, 73.1977374654968, 60.77239958013562, 239.11105899811534, 126.21411931407152, 47.084111575795596, 155.99303432330572, 71.82830213857872, 77.2405348722129, 69.97824914729371, 53.257201245633766, 8.419132701233892, 247.32328794139468, 81.69409244103255, 134.54253544539569, 88.41132357521386, 72.92419718814895, 94.56377065878513, 282.9763188879357, 58.96825043767087, 110.37057139230495, 115.24820326554207, 158.60402874029413, 165.5794885898939, 64.44030853271876, 64.34986562738321, 89.05027757701909, 257.7141981800816, 89.8015833437852, 96.95782072495851, 55.3356596501573, 258.3960155041845, 68.06356650100165, 53.13881352682488, 153.0478727666543, 59.31367810002138, 34.19319276506988, 89.70214303136426, 53.29815311751227, 133.0319669890126, 70.57815135867561, 9.256355897304449, 66.12026853112273, 82.24616136572358, 175.11777328976447, 136.21849805237198, 10.95461853708641, 57.789479905810744, 58.61956788063746, 99.9777287361195, 108.76926065380705, 20.94777071791046, 38.019930527461014, 6.042752737898616, 134.6476304266135, 78.04807160279337, 57.862568276448144, 34.9108041497996, 81.82654976094035, 74.35685950111908, 44.039698095625944, 55.34990161082187, 138.02256706673305, 158.889729349368, 84.02777711130715, 82.090035043156, 238.0383815110762, 32.979844598503924, 114.09948490676096, 141.58355573728593, 230.74716667358126, 44.83865568120578, 44.398257766330815, 70.76533361922952, 87.60578851781192, 96.78014098573507, 106.90910406911212, 87.73040248527042, 68.24720259431952, 45.6861601300642, 107.54673496388703, 113.8826278679084, 168.24831830864608, 82.75387382681097, 86.86733053709004, 47.56525405122757, 113.64568206538465, 150.31821778712228, 59.63265630125302, 159.7081572380414, 121.60442796799427, 22.297271962492317, 344.80565496566646, 74.91789041515013, 51.59682724720124, 61.88778817131719, 53.7183917623735, 63.64217696335336, 45.11834901091583, 88.29123948584514, 60.238312473334155, 55.437458010919386, 103.41650026173727, 47.13004885689332, 106.02249066099088, 62.24365624487176, 67.87795806060893, 146.4118443915293, 68.7271156612499, 129.9027132610728, 119.10460758445748, 62.22572399793678, 54.13573380368444, 105.26274402271281, 89.29753688314497, 63.71091902477687, 132.7660293330208, 104.66199656018378, 48.95169171537682, 220.66634347386596, 89.53911041518589, 69.65849976685831, 37.97897664287434, 111.24470393020923, 84.06552171371793, 279.7457394922424, 55.847783195612045, 84.06019803542587, 184.48218159264232, 75.9141653160831, 137.2504189672839, 44.484866777791304, 52.44121276874545, 204.00460648806308, 133.60247041716178, 235.59482968563864, 250.5249426221009, 49.71725683671387, 46.75998872527983, 106.38048562802511, 116.06813793947894, 79.32731933531555, 83.49165580772483, 148.65149264962452, 39.80370237948734, 77.33574737546469, 85.73084829801367, 58.81684554874907, 65.18966763334252, 49.226895749168165, 115.53656472885079, 39.64540194701561, 8.1017568928936, 216.42968476260683, 96.4386961803385, 124.08087978193208, 206.26157868112767, 146.69010717305662, 88.75750250494679, 92.83428969928497, 109.26392148434849, 51.168639782121346, 82.18380053842122, 7.040627565849244, 76.49961986712545, 93.29272879110447, 51.48494517223675, 55.16573892364931, 56.023369335584775, 82.7563219074962, 30.736559287884653, 80.03040905720748, 154.63824249150414, 111.23953809685058, 51.51523165888466, 87.02497489018177, 88.96952760641852, 74.96091515267331, 89.9060804812184, 159.6384081293692, 82.67219900043123, 222.86721507829915, 61.53591260177493, 89.26664277673794, 123.55328603237986, 88.24651561911669, 83.31247485909626, 154.0321944917687, 106.50209814826977, 291.8233925054524, 37.89434571734186, 8.304638541773324, 33.4387433242469, 84.7082914870607, 115.71285391556242, 45.99112383053575, 64.80448524486464, 120.13562105048469, 35.67170295066112, 98.66073329845725, 149.04621566110572, 75.15630021926984, 46.18956935657616, 16.97042305799619, 52.60935880152461, 53.62618944416967, 90.07272726307886, 43.82869733183217, 78.10980779427778, 182.64004667767492, 93.53079819783731, 73.15788057147728, 77.6832795212729, 110.26869830431387, 134.91916670314137, 156.23584459864276, 85.86170763121179, 84.16494424008218, 263.0310147201822, 62.174519050639994, 185.8097539064144, 303.5004987289061, 45.027644984636346, 76.30238280690578, 41.40140976976335, 85.63947342086333, 83.2798851024647, 140.00207410818794, 14.186933035734745, 130.53824342611918, 55.44765757420375, 78.61328838773781, 78.17779761688206, 168.30532207564056, 42.927560176225, 54.48864218663334, 88.83569778714342, 91.14145741897316, 96.08690848701164, 60.22536726617521, 105.35507024728318, 90.4785864423483, 87.65254775164179, 85.97088630746104, 86.42273713440711, 71.22547234893013, 6.4240194052134125, 64.65685103145628, 1</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>113.8439700126648</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>85.93263814105489</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>[131.1273193359375, 159.8739013671875, 53.8621940612793, 235.9087677001953, 64.7526626586914, 251.1658172607422, 34.32735824584961, 117.17913055419922, 196.92556762695312, 87.9483413696289, 66.1889419555664, 58.8765983581543, 92.92533874511719, 85.4333724975586, 203.15487670898438, 128.6514434814453, 305.6389465332031, 15.303524017333984, 42.07221603393555, 128.96324157714844, 68.47811126708984, 57.973331451416016, 60.72064208984375, 66.20027923583984, 42.52860641479492, 92.3326416015625, 269.312255859375, 65.00688171386719, 150.49070739746094, 76.4128189086914, 161.64503479003906, 52.43532943725586, 217.71734619140625, 140.57579040527344, 90.18891143798828, 70.75931549072266, 73.18345642089844, 61.698062896728516, 98.36180877685547, 268.28814697265625, 40.58183288574219, 45.912357330322266, 56.809242248535156, 91.04740905761719, 53.956573486328125, 227.75167846679688, 85.51327514648438, 149.87347412109375, 57.82942199707031, 67.59243774414062, 64.07459259033203, 132.88648986816406, 11.014800071716309, 150.6859130859375, 57.50522994995117, 135.78538513183594, 81.98585510253906, 10.816911697387695, 170.21725463867188, 133.05874633789062, 361.9944763183594, 243.71127319335938, 143.30062866210938, 11.030903816223145, 107.97257995605469, 60.81235885620117, 69.55463409423828, 115.27265930175781, 72.24052429199219, 236.35528564453125, 194.07070922851562, 58.281158447265625, 165.8627166748047, 58.16909408569336, 39.30946350097656, 42.78050231933594, 215.6039276123047, 123.48377990722656, 63.22472381591797, 111.35980987548828, 116.09622192382812, 91.84227752685547, 59.94511032104492, 57.224910736083984, 71.99778747558594, 65.28129577636719, 112.41278076171875, 617.7435913085938, 154.9647216796875, 168.9499969482422, 94.31657409667969, 58.899497985839844, 77.41222381591797, 59.789222717285156, 51.258235931396484, 188.31649780273438, 108.47403717041016, 32.06501007080078, 56.33781433105469, 177.1900634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>p0.75srandom1601</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:42:26</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>92.96919714191866</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>72.26089224070554</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>105.8373226011438</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>4721</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.9028492323944117, 1.256241178339136, 1.2444520319788563, 0.8934502702258394, 1.8623174472833115, 2.292857017511017, 0.29241265834897784, 1.2382396012729233, 0.7878306557917878, 0.6514772133258966, 1.1846737542222805, 0.7125771019080109, 0.7332350446476239, 0.8424852461866987, 1.4888663214835574, 1.0041221406361054, 0.9367796391193094, 1.4868060598600459, 0.7698854275157389, 0.6905043873681661, 1.294843279831881, 1.6012913564644853, 1.8939841964357675, 0.9633743690154158, 0.35759624657137007, 1.6878878351594797, 1.4317603675712176, 2.051615573472867, 0.9524660210762239, 0.5736687285348947, 1.1996217570385301, 0.3977817026527808, 2.023125558393351, 0.4063623679981806, 2.8897237829284084, 1.7025563544219728, 1.6857537077276379, 2.8986604560066103, 0.7646635807646174, 2.2147866961884453, 0.8312075476234438, 1.7332531876942037, 1.9121970472792094, 1.30582537985289, 1.2217099910001061, 1.172271113278295, 0.2524062886172744, 0.6873218010526648, 2.7641164939987544, 2.6324640397386068, 0.464374994472563, 1.5416790280788444, 1.7572909653230937, 1.8211777932857955, 1.0566056097289322, 1.071374611126936, 1.7498206758246635, 1.1149420494229285, 0.3666154342979158, 1.081971360813293, 0.2235572923152514, 0.34178019048182745, 1.1698602007137475, 1.971162356615912, 6.810264468761832, 2.166759998889408, 1.039439972612783, 1.4676774067996978, 2.583306690651597, 0.8386075193726643, 2.759226970252658, 2.6660707526592415, 2.4540047008673405, 3.5422761177031474, 1.395557200251363, 2.8350044796310523, 2.8576059189751435, 2.2576254561828257, 3.3893014354042252, 5.058899635137124, 2.9057980842933544, 2.7157066336309406, 3.8047008194532643, 3.3238669126003364, 3.526460689675806, 3.2477625078917765, 3.4627274471667917, 4.308201457991827, 5.066608430919447, 2.183211927078195, 1.1941419989216662, 3.692587694457984, 2.050640471322157, 0.5165769073828321, 1.7423326053338797, 6.21491005397247, 0.7941878004589699, 1.3571020896997865, 4.994917414714954, 4.6026201225249785, 1.932889481813032, 2.8841506115291424, 2.476800272258692, 6.676940762792265, 3.900630522903253, 2.73119680383307, 5.315742119786568, 3.4202331118875544, 4.270554854119984, 2.9741740255055893, 3.8656669006256923, 9.343139987713935, 7.49154812563598, 10.61307119104265, 2.5697027640417662, 9.194135752519186, 4.730888436108848, 3.1977915347886885, 8.00234968691447, 7.922354584297941, 6.728835187343977, 7.122991078671692, 2.3538777561198545, 4.288639779543759, 2.709102614584736, 5.056898475428457, 3.9697148149119914, 4.838633052056615, 3.0146337755147736, 1.8811557275366995, 5.373766265003135, 6.120560520634595, 9.248179803403094, 4.246091652142854, 2.9860761964892997, 3.3204961669806776, 4.355953711738647, 4.848740329632112, 4.609467403841694, 8.426807281674558, 3.448500274401739, 8.460811074672629, 5.077606226769789, 2.176052131048919, 6.196428789200507, 4.784027134431278, 3.7448896731447197, 1.7433650457868515, 6.29665937246474, 4.024533888362069, 2.439937720703485, 6.420949514721843, 13.283952871245798, 8.627153848237432, 3.3376159996042882, 8.052023910566714, 11.807858350023855, 13.00312550750731, 10.26571952123642, 10.459686749510535, 6.022480835543581, 3.443746755175624, 9.179316906038421, 7.406802747331634, 12.28758301604503, 5.223794305682398, 8.700000074193067, 13.129968628655698, 8.201730470952507, 13.70487974386571, 9.765632830826958, 8.66193958733797, 12.228155783471431, 10.643411790207299, 11.87710035854691, 8.137775669656756, 7.597754959340645, 16.43366580391738, 7.30781632561996, 8.704511468350866, 7.706864464788525, 11.829346617594206, 9.608000873634877, 23.481358514003066, 10.984151970023447, 8.463513944426126, 1.7575671575178624, 8.87289361445344, 6.845810795226133, 14.14733119289216, 17.608223466602112, 16.538737371454065, 13.845766155465869, 17.811708742937753, 15.23704256072296, 12.616615242223002, 18.000350402449786, 11.713325350986148, 10.959010489542347, 17.593534235050246, 10.868893574126314, 16.54271490266961, 38.11440412282682, 18.224843830428497, 9.63806060433763, 12.595826810358878, 35.13161990253821, 20.71734835366529, 21.186095644444432, 21.80563389495936, 10.33429165845586, 14.193747530988869, 19.721568867052802, 15.72037055643229, 31.227933099985677, 24.425880531785324, 10.15365243364201, 25.807198024868605, 24.698527629586415, 15.754205847001131, 6.47710031025315, 12.820652040433782, 22.83406660775616, 9.403155704288425, 33.71237051467202, 5.99076665087741, 25.43939554398019, 21.16249871001542, 32.316172864770394, 7.982517839066878, 36.036543678900586, 38.8030921770691, 36.94352843983795, 24.066847437128054, 33.80864619141216, 29.50201643764282, 30.403281715962237, 52.92957984207038, 13.17761433997835, 9.792218669467534, 29.967295912549304, 31.851798277468077, 16.057456163699637, 30.640904562849816, 31.697895156357436, 17.0231282299037, 19.807707371807155, 10.541149126068118, 29.85089706186582, 44.3073232289686, 29.953768214152863, 22.525420234226203, 19.132858883158423, 8.850715760995062, 25.373918940440497, 16.68537913975418, 17.61559017757642, 19.941232444842885, 59.511111464213926, 13.811206509841176, 26.96033610142666, 28.971978486882556, 34.01266794740924, 34.521388378577555, 45.31639603519515, 22.422508561003735, 24.863083272370634, 40.703940496039245, 24.75924797790902, 51.774248213065924, 33.205857402650565, 27.200336758682248, 40.397398374269386, 63.16679144755405, 35.691335219542204, 45.290327707954475, 28.557187850095552, 28.390741159612986, 50.51183363382358, 29.581160995080822, 18.54948615033824, 25.137611825359592, 25.892021932378604, 47.246831090120764, 26.731539683531103, 33.25619076807535, 27.619119286115392, 34.955907159508804, 28.90315358705, 25.48761369061074, 23.839382645384873, 31.41876226110465, 27.727695457531173, 45.95377485206697, 25.75478944193345, 32.881973228852665, 40.26667899447045, 25.57868304262885, 34.660720369682466, 46.489377387112846, 28.719105359466525, 39.220325805470345, 38.444125174058584, 22.061296497840246, 15.86779381109115, 38.39907304049525, 46.34855139229682, 46.720355752053514, 55.80635831892762, 40.1146477469881, 55.512292584444786, 34.81293488314672, 27.149611419982033, 31.673644569792017, 32.51016566800213, 56.19796283387576, 27.88186237983953, 24.428990232165265, 47.398050565310264, 4.2373914592804836, 54.863816408631415, 36.24729924975349, 21.63015007340359, 53.95111089395856, 71.43721166122985, 31.337818854801817, 23.761229504883815, 55.327047565010304, 42.33212794186166, 60.87460128214375, 60.25267421950541, 24.33924176806716, 24.582390658939687, 51.953688691168374, 34.49498406846146, 49.48249743257492, 39.38945250964936, 46.4583320348144, 48.873537913499725, 23.36812231310406, 28.93405555326808, 33.342665125412836, 38.637846998925845, 38.09615527772285, 22.31645200289495, 40.23348367431421, 8.792425729341476, 46.838990275880036, 35.776325559449006, 27.258337744637377, 32.73923685248083, 10.937756296279053, 14.075758843157868, 50.33354112347024, 68.66830307618176, 48.59150503661227, 39.57098597977185, 24.928960322674552, 39.089732457774915, 58.516869715660114, 49.05975605504422, 49.29240772710226, 23.396099568574737, 46.03368839035394, 12.47417322462685, 71.5564045737485, 51.72241434040175, 49.311195425125106, 95.48342209962935, 31.62091925968927, 39.97333295932077, 49.062877718049386, 39.50507897576867, 32.6039377513544, 55.8321594003352, 44.698251201568304, 64.73222809970272, 46.790484891849246, 41.54296236691554, 34.8785321286939, 30.333560729283718, 63.573244467804756, 47.80663133415921, 46.46424716829698, 56.28155086598869, 50.0247855268732, 12.64284183305524, 47.01532006224611, 40.349562575960555, 39.55747733517895, 35.043023281968814, 74.24875139134889, 38.6594159775941, 6.749638928816641, 12.545501816366853, 39.08623404952954, 59.43307123698258, 57.134660157518596, 96.80827141726614, 48.85199979373385, 47.985022334375245, 4.40701681288056, 42.40333490017555, 102.03010051837579, 44.86469391817094, 94.90809405575386, 36.57631796064178, 38.34165750084224, 41.82705840477176, 48.61648173549086, 46.1492404763009, 105.26938501708584, 60.930155542901126, 83.53355831459382, 73.43081370575335, 27.307379447001797, 38.535812226721134, 47.55680370318152, 58.51849362148499, 38.950066766011076, 98.54989100955993, 50.12155084470419, 43.11283256760253, 35.39491208820156, 71.31440652328563, 105.41006415856515, 72.6456274782138, 53.94204516201501, 143.54863371732887, 64.41979657080105, 165.48196419554117, 23.292834903501436, 31.91171245898454, 64.50204686463493, 29.911956713327474, 110.4601982575533, 1.8365603269969277, 31.7561151914488, 56.16804250725681, 47.319919852634364, 94.3497846527115, 43.31399973459605, 152.18022110309184, 43.436171603491275, 3.1918102497637877, 48.972290634215845, 27.091661787512532, 42.018140775883104, 30.46741475570601, 50.029467353426675, 4.968966248636052, 62.645194321181116, 44.398442271590724, 60.33070182011922, 49.46898581306536, 76.71459669203794, 42.93820967239065, 45.66304583197884, 55.402755146654336, 4.296838266129153, 50.36901879778435, 46.41663989798972, 49.37687112089007, 82.18250485535822, 38.82731110455494, 79.58387309881772, 82.90810020739931, 42.170826119796736, 44.73488530141141, 51.90101162582699, 38.47754439762589, 47.32749080888947, 23.97140866312771, 30.462633072280227, 56.72204129498136, 27.194293639987873, 39.58185886068245, 37.232379968562654, 65.67242124289373, 55.63646819216099, 60.47901140333391, 53.37552449346445, 53.12246500729388, 104.0960988187964, 106.68791037967878, 39.93071051531887, 28.290235048102097, 32.124343835017385, 42.165712635470186, 56.91244328072979, 79.14059573629076, 136.8409229326494, 30.636630223833084, 47.45073439705328, 34.5930210465862, 42.29443176584044, 37.67015907086713, 55.49515728518063, 91.86552773110124, 60.743499566684875, 61.72588136551885, 142.25992172242707, 78.02830271013114, 41.709071735093545, 42.220130578209094, 114.59626419103388, 49.414736607887384, 32.9109651226059, 87.04875531649122, 6.813755467991263, 56.362434076865846, 138.55156838486246, 42.37939102542437, 38.44674654324602, 58.02797995216924, 44.44315719890251, 67.5307415511743, 41.10824784061112, 12.479226125287843, 83.33188641759371, 54.25931585829366, 16.011332267648076, 55.64894314927948, 48.16730554150423, 172.2564157535813, 50.13376372613628, 38.46419843575892, 59.98128557902026, 12.926111076776346, 47.17580393815951, 56.399876386004316, 76.01223302256436, 57.30413184788911, 42.18309741233434, 11.631591216514325, 72.32932878126442, 44.93503114034806, 38.204966543007714, 48.648279202499474, 64.28245354929273, 44.165811918266634, 38.86506494096754, 72.05428291465348, 75.59845129330904, 48.30125415106228, 38.79803417354766, 51.95902923403045, 48.011062347652995, 67.49655928734936, 35.4884427906712, 34.36956401680591, 150.38712881671572, 48.26064967077997, 43.52887622987773, 52.794531933545656, 76.02089103157478, 55.15992524944104, 40.257250510291485, 100.51524693662833, 63.08488323506779, 44.994360663079604, 169.4499792777652, 78.56953380843032, 36.89549417100388, 42.209776624210825, 91.68059387739856, 89.08930339942148, 60.68513784698021, 102.7980125437118, 40.95280022466616, 68.82531837996717, 52.78896162442851, 48.075818341500735, 49.00918828699372, 43.348806626821286, 57.97138939422489, 40.52188887442246, 52.899407314147865, 158.42245195828625, 75.5525526395052, 83.18496975899725, 69.26790246308353, 41.0818417107961, 82.40248016712218, 8.047436789351453, 43.019469031800114, 41.407410901291016, 35.94416494658926, 113.53992066729282, 78.02880810830875, 55.23604549132759, 48.888347794105826, 77.42748827354242, 67.1162812559937, 37.67874989051074, 49.64618785942096, 8.737782116214257, 60.77489406763732, 17.087812976261414, 65.26031992568569, 53.11628729052109, 63.45869011168755, 52.19559700683547, 44.79941521234356, 73.3361597573618, 68.44764991368595, 42.292877666902804, 52.00329976042787, 147.84321735116689, 45.065927868786936, 135.63715844219658, 13.669219835650201, 81.30109969683566, 48.057751008434934, 57.66466473981729, 86.87202482574975, 66.8042972509171, 67.98814399958376, 14.379081635839885, 80.62734615352629, 64.88881879070918, 53.65374721608669, 68.2330695887066, 50.4340875046945, 49.83043813038463, 65.81726633060826, 104.83063467546164, 128.85409333420935, 54.35640429949571, 48.56030893008858, 63.052876407456516, 82.19308901166382, 62.52656930852078, 74.43613038988418, 47.036067525789825, 11.526234824782293, 78.39326296781607, 483.16712313911063, 42.95865922615176, 45.028079936625666, 41.8751260772947, 56.98877763134503, 53.30282089234405, 37.40220085773547, 65.31903337001813, 4.137078499376468, 97.0077445568932, 58.54114688533547, 87.94195529250904, 48.759593910148254, 94.4783160025293, 53.00067539834763, 74.94749229584389, 105.75874376086306, 132.73892902963354, 47.17082976185893, 101.63631770951939, 68.60278143655452, 93.63137223877385, 13.507674908339137, 60.60797603059007, 4.439454354606401, 131.4439286821045, 43.25524924478907, 55.648850223312344, 50.758290293912296, 48.68278517940357, 240.04381656344268, 35.768074201644055, 58.94888701331321, 118.34164795269457, 43.712803991209825, 59.944091228682765, 98.79311788944393, 38.39862489023489, 57.514335041686536, 46.98260884550428, 63.29763239839921, 50.9154785268617, 56.625664062888674, 49.877578760138384, 58.96902808413562, 68.31428813970649, 51.04190804804405, 72.73042072425646, 81.59008863717916, 35.264798003460506, 94.52575035414141, 62.42302669652396, 44.36817476788861, 106.63016824209255, 37.17662923676533, 64.09789106122629, 35.19493870991023, 42.830453294107635, 31.14864509940828, 6.769434039591053, 57.095139106985464, 52.605587480310966, 43.20159239976962, 82.89296183951417, 69.25057875126413, 119.6164688167651, 43.949181992584066, 66.25705912255816, 45.610456418805924, 69.27653547993481, 42.368943669528534, 79.34707736308212, 120.74392039905011, 34.85009883544936, 41.869615778531134, 160.40353005705813, 63.60166115368298, 100.96675527290687, 46.0537269795218, 39.65142483628366, 64.62997649057245, 51.465770944804696, 57.5171823015231, 104.60997388465358, 60.78688165031947, 79.50060091883478, 48.851249083462505, 69.07630614945427, 46.88993466651994, 299.06210306153844, 63.95327700772339, 61.28926288775898, 8.923137772922413, 57.25405656447648, 56.37788414272113, 64.50475208720081, 37.810988317130985, 138.51329571707646, 75.15185133564485, 62.783250597102565, 235.58369108114314, 44.794557114277026, 37.418821511189044, 34.439781599156866, 57.10219844820683, 104.67439288196194, 58.39728727569662, 45.88812143914248, 44.614249945548494, 58.31740013838126, 63.85977132587131, 63.63652856168162, 86.55577727722012, 140.64362371657742, 57.897103812541275, 4.280338507460177, 137.2442302784861, 153.49519253385017, 107.62099066918911, 94.44051478969135, 79.19038645566029, 57.15881266975535, 73.59630682214394, 86.77998625464491, 84.37182182058328, 18.16656749971039, 50.04470927649303, 58.15888567627272, 35.743542675348024, 58.900187684031955, 141.75633438697832, 67.0908609606868, 82.82663401183385, 49.691797186385344, 67.86447569814317, 52.86566734608648, 87.86341421044764, 51.480669733643744, 73.58814605844691, 73.34317664415563, 81.16027198678663, 46.94004912987691, 43.09013022139936, 76.49889466501811, 272.9460407133163, 97.2799730894575, 8.221024213704105, 70.48883576181935, 103.1788727786713, 74.69456714331808, 141.23957022622753, 33.67076454371922, 45.53569617136146, 84.93959867215527, 8.035891429222803, 159.05546648282345, 87.0202228439218, 94.70437657119739, 79.6318472841795, 51.23389684587304, 77.46279999565016, 62.41960097773864, 70.22989740975677, 87.714368171369, 386.2235141576675, 61.11769679079091, 53.556040502578604, 95.1993942850364, 168.2815770263076, 58.97726338587135, 114.02910992034411, 77.18542888108796, 70.94672384182877, 171.44493591383858, 60.598735117774616, 48.91279563198592, 60.09086225167458, 49.47307464708012, 80.51912007845304, 35.607214257089076, 141.67656145823244, 102.26245144068655, 46.06671784898552, 57.81624665437425, 80.749708086215, 47.39400146074099, 53.36611704471288, 79.81688268701245, 67.89020085916684, 68.4794097692698, 44.010472121269835, 45.287135790416194, 104.05521778115846, 71.24213317627405, 179.66956024018813, 51.526983208819686, 65.64472596883131, 68.31811094192398, 58.219384468147425, 99.57015984606889, 125.84140149439727, 47.72211048693426, 45.476684893396325, 91.0825225195523, 68.09296935390817, 16.22210237217691, 47.88842057306363, 58.472281370591894, 95.99474229455213, 45.9844401468765, 53.53148416874201, 76.82513712660935, 30.75847963527348, 76.36354500930139, 60.81211432414798, 78.287314747854, 60.38488971572702, 84.87388551698814, 99.24242344649775, 73.73398203378359, 97.52926072246885, 78.88704357681904, 59.455738648811376, 54.7834645331687, 120.90685145032597, 61.59647529535256, 87.29497376780604, 5.945932395516744, 67.64543507945201, 110.71042078471257, 62.192430055150446, 67.53315984728617, 59.910073266438, 75.95983208118393, 10.168889708704054, 47.263304886474366, 62.55153010147281, 70.28483601473712, 76.28110029204427, 49.47235114498837, 69.79683988335607, 41.13753132131164, 72.04371944208881, 122.44069396526052, 118.48363807220879, 77.73112628941789, 74.0941660311358, 63.46457397196559, 82.71493978354849, 38.6753301510959, 72.51223814916992, 53.12145959407878, 37.56804309250221, 156.5304318438739, 86.36540684803023, 114.42326808253296, 96.36159326217961, 265.61002978796034, 91.09974097393558, 139.79230548092303, 81.01074943026046, 35.91357229047274, 60.15945024562132, 133.51512413670213, 134.81698395182605, 57.58221876886232, 47.519193583304336, 183.1264313674167, 157.42588291864604, 68.1785574196294, 76.87366556737256, 56.195900602067724, 78.00180994198432, 133.76813204373545, 122.67539456846487, 55.83499822948307, 43.83998582333135, 76.23682206283922, 69.40965601110999, 88.38687785243124, 95.58208125416445, 85.38107299029635, 87.36711169037362, 97.45040776442947, 83.49536947220791, 56.6823998667338, 52.58971044629556, 70.03645210259843, 97.69674181421627, 121.20657268433816, 40.80508582940508, 56.89318860071739, 119.60551220314069, 69.23199912285274, 60.60080630513496, 146.20267830482348, 68.24245193167182, 40.187958346106775, 99.10013382926826, 63.58976893112245, 31.59743964322204, 68.27349959301742, 71.07009825014832, 83.53379349619779, 112.71243338899116, 108.09256830397646, 130.07279624784513, 73.89535003244941, 126.8800720377568, 62.1882418425501, 66.27849348009592, 226.25626750556654, 69.66393294615595, 92.91707193569007, 36.923631711261955, 99.45817212781762, 72.76828946279944, 127.13325108229836, 56.37591452931253, 67.94908638967631, 56.089178657585045, 71.29688327190978, 76.30799425143685, 113.42547935510508, 86.46531891663378, 94.03142979481233, 56.52974917253667, 70.54684378643066, 49.871565572775346, 66.42102871018982, 91.78004049384525, 175.99498560231896, 66.12350227239605, 73.84178225285952, 62.665927070229074, 80.5009994364365, 98.33955112572177, 70.44541800031533, 116.54634338179443, 73.9525149226325, 154.87695837282675, 57.54804021118115, 64.71513134740486, 44.993478090411166, 54.38187699060743, 150.91865854696076, 54.54312844747088, 73.47634756539256, 118.42430960873779, 52.37411340470942, 51.72750636601744, 87.13847205094912, 65.03366620375697, 79.51759457767047, 80.45523487101342, 59.7292665528417, 53.240612108370584, 45.987147802754876, 101.24935357112538, 47.86013711014956, 72.5566013828464, 63.03672694248288, 111.1745496281566, 90.64760283221733, 128.46801495590788, 43.770038515114386, 73.00965834102362, 126.08924828855088, 56.865112016122865, 181.48349973158193, 43.10453227774267, 113.26195054611102, 175.43986637259277, 60.91672953438263, 93.97172547743959, 47.30986542655508, 49.54549412430746, 51.38001643821632, 61.12733258531883, 77.03475751464642, 107.11002931644687, 65.86712726944468, 68.19318320465092, 37.31592742074743, 69.59981581451443, 103.11199632194939, 52.699413128263586, 50.485551962888984, 66.77974918043492, 62.20299444698317, 72.98729436374536, 65.39856026225235, 85.93863758263629, 66.50736319615848, 56.86840408797977, 236.5372677586177, 53.03781473239076, 61.719691650740835, 91.55586015740309, 66.1428005174316, 37.1261783119445, 65.6904351646893, 62.22861751829321, 62.25143852237677, 43.159928032389644, 46.54681179773653, 51.39482552082209, 77.4000332098478, 70.3618415838018, 85.3534075383277, 63.65712231346324, 44.553872665998526, 38.38631593628324, 72.70378356691322, 60.58932397388241, 40.55386498946322, 57.55762412645888, 75.05324414408474, 93.42668447712518, 40.82936138976503, 31.170420468233438, 44.98475322139894, 128.36849266976054, 102.28359837488082, 48.257495040970575, 102.86490083895846, 92.23721444479592, 43.347507384068436, 55.96952313070069, 43.42914244802703, 169.84792380416246, 92.43504475635521, 72.31104558258485, 69.23119477079887, 54.84664914276054, 54.34397639465937, 53.6961346388509, 42.348645653173115, 149.70832652347164, 8.20119847921222, 124.18070188937138, 48.208534922181535, 70.67706595750164, 40.21433426823121, 45.484459278867504, 53.25584857835904, 70.46075292162729, 65.9766166926595, 63.784715735593736, 54.58867366381663, 98.04272057140868, 48.340892649459285, 98.59121297644252, 64.80561066765715, 44.30035769335443, 92.75365662853935, 134.10840157362097, 72.775400856407, 346.20044994034674, 37.66082075401165, 124.09292878900192, 42.75871599781987, 83.90618961202591, 89.43262578118213, 125.04788088760974, 140.4508278011877, 41.384088438681076, 90.05559167290805, 53.311561779764254, 97.85868166727587, 9.877131549379413, 72.80434799407506, 46.34686335347425, 356.1396585032235, 99.625366338709, 81.1537145277596, 52.91530934876484, 15.169977296872588, 59.055404777815774, 65.46259754729282, 55.380498689334544, 126.11269313137414, 128.4103667867006, 248.80990107273786, 110.06915957121987, 71.83085493908976, 49.3874186527575, 64.32979938648086, 113.21654619223897, 66.68489990499954, 48.01287197833403, 87.07594364671074, 81.23970626573559, 66.61968898649026, 88.84292874498317, 47.815037662253616, 81.66764108902518, 122.4619706911809, 40.595881949459105, 75.19095459972348, 197.41140958698819, 50.14713658913764, 87.95183435726697, 48.84754975776158, 55.5829056338213, 123.60476652508643, 206.29818340078612, 83.29009810071538, 98.45725623868124, 138.14828291793262, 99.291906822442, 97.65832782401849, 81.21874722038254, 107.64842957561598, 101.32530536639831, 174.24746430502998, 62.1015704070443, 76.28281152365646, 58.72157208036646, 53.90480617274817, 109.86568756620359, 57.1154649959875, 82.01715618180133, 99.28853241047146, 82.20740628541, 138.95385144592223, 91.76027689505949, 68.69848517064104, 66.34274268176725, 50.332882527023706, 71.65120965510602, 39.52578474354745, 144.78175492560962, 80.56977467119677, 68.2941378243289, 24.44892102621312, 51.00302066330263, 51.650894977358135, 45.372970606521015, 110.76837376767513, 65.21333219241014, 78.68697175848996, 63.76684041609137, 131.13402464610243, 105.61400191693414, 90.98244066991242, 262.35011419196087, 74.68450565285687, 173.39507159725076, 58.18245589601736, 89.67550975345154, 38.2848880129336, 73.45775788019489, 75.92480718541219, 143.95001228238092, 64.35339365975746, 57.13991890260279, 57.6454830524641, 72.62213817156857, 63.96728383072081, 51.73204069085395, 51.227667165462, 60.182400605181506, 91.2382221003201, 45.30740484421478, 70.60472046648091, 102.38160609063267, 100.46356729586344, 149.12829767644422, 215.57721795485236, 51.928131184027144, 152.47286499400664, 77.54191596723282, 62.653087158555394, 47.700365746415706, 38.671412607668884, 90.37011759128032, 149.297350354293, 227.25900174454736, 126.35969700582213, 101.6004603835396, 54.4807167386636, 49.99776084277391, 75.42480605723033, 109.02018453646721, 140.25943434846346, 40.36345939951642, 177.87053403906467, 60.63702094840584, 82.65352100101155, 90.01491509022202, 140.69910526412596, 77.79479172506358, 135.09436322309955, 53.964391949782765, 51.66655252193272, 44.32571978620755, 55.95705433949535, 180.42061139154833, 86.61216018122252, 42.08034832566985, 130.54832617477473, 46.3782511136628, 53.59253925268165, 37.64366429972476, 56.52690240360135, 66.53583563595559, 123.92924601025668, 72.57640813901021, 52.9906364032249, 64.22704686045903, 52.545855542776955, 62.13936282199138, 168.8138332328367, 49.51164184849514, 118.24977245498522, 92.72470929944026, 41.869271768827346, 37.23314717918595, 53.94735068009568, 109.56298039702769, 77.26754527886325, 42.2687790194574, 52.37135998478224, 38.77846149349399, 72.91098692091208, 56.88496664240403, 123.18723540369221, 76.63480249565207, 206.61356165438488, 91.30763717442687, 178.6005818883905, 52.79834111439039, 60.40326539998627, 81.39724576120983, 186.0428019337884, 19.08177278596155, 133.68948507467798, 70.5895426115024, 173.255002497125, 3.522683644893317, 156.49449578039682, 157.31693806487624, 214.29708764499122, 45.55795627716883, 92.42642990356022, 45.26480899937908, 74.8108089599158, 86.92935524795924, 3.334663067272412, 18.221834184859734, 133.53614474645772, 32.36633901232793, 50.71111572643628, 77.52517207450045, 64.19378729930047, 207.87540911878412, 77.16132823427947, 89.15422850017254, 112.91683360642226, 53.890534175319864, 50.90789741246834, 115.67202489709241, 84.44359117472479, 100.08961646316716, 65.5182337016833, 48.0784000737148, 164.02003919356218, 65.43138936306819, 99.61087287698278, 83.5408271589785, 264.3639551900109, 85.34186363745644, 48.458667574541074, 50.51169997719901, 88.42887283224344, 120.02028686798654, 119.5081720683047, 95.33058605702313, 52.493439886555805, 232.98675163560108, 52.84266554760175, 131.9387835430659, 161.45448802134487, 93.39021337292567, 2.7555175520656703, 124.216829089376, 65.681683344047, 92.4019986744021, 79.7744753488766, 40.63259666126361, 39.01755837453352, 122.69493116532409, 79.15169546124655, 173.6369685844444, 59.42214029230534, 50.28692732333515, 97.79518716331938, 26.312310018137868, 99.85684049678028, 60.73294603857511, 53.23195411741883, 65.59821196842107, 45.04524238849982, 110.69775161613168, 76.33518005078338, 309.6048306879653, 83.45282952785658, 62.9103506438202, 76.9672307417818, 56.621457077963285, 81.72507541638826, 64.76856641520145, 49.31407967434578, 88.63027603338435, 162.32253608582764, 133.29237181063112, 85.23782351420338, 57.0361270480731, 124.1761515451482, 138.95135856662208, 73.79985441839541, 70.16942750513739, 52.32906018432966, 94.12204854591178, 172.57199141025114, 59.77181747447348, 31.703499395126332, 65.29141066187566, 52.457066110270766, 70.26515660823833, 41.3307124284691, 65.18210731807564, 64.08822039175871, 48.24051671628059, 41.951167736628115, 73.68844775236988, 48.89581468064449, 141.39157598415292, 75.22658499006306, 136.73451856962333, 148.45386005982456, 72.88330696206916, 196.60060426048548, 227.40468615847894, 44.727554958106786, 183.66920218843035, 91.39689585040993, 136.08504066539578, 62.661089364975176, 71.57432241056536, 151.52774457604653, 78.64216227690508, 131.40922023557363, 94.95886114753115, 44.95594468735248, 64.06791187084602, 97.83385545155888, 98.12662033940609, 77.8545577218081, 46.54233262955737, 51.202262232002475, 67.86256946711094, 88.27877452052411, 69.36179024892772, 51.60715467561407, 133.30300839761588, 97.10653122805921, 91.52146658402594, 9.003582694020702, 108.2365933439818, 58.43526646083081, 53.679342475137695, 87.74793554850497, 77.63820239822645, 165.79977999149452, 201.68283635511298, 45.07412167601779, 58.501917143203045, 45.035612274745574, 58.94329877863417, 184.68133397018175, 79.06537260109806, 143.61552602685413, 332.3076385682901, 71.26175773354116, 101.4468504616158, 9.841689838094888, 37.15929016199959, 57.37846049460535, 141.75111711924325, 50.48355727854469, 118.25583954246652, 62.73406609271307, 97.90305318050098, 109.86593381078805, 89.88943562043026, 58.02853145844872, 95.30221273094999, 91.98767189648416, 110.44988160196105, 75.2517496188149, 93.95240714245807, 80.28492021894007, 85.33815412679293, 75.93406160174727, 72.10496254477373, 65.34597461576384, 163.65654969738026, 97.0637623307254, 80.3370543203911, 59.467991615157494, 57.69983752563847, 69.08864983235658, 74.39659632085119, 104.95794396601944, 50.52380085354716, 172.47243015741049, 116.1286865477784, 82.59727880581397, 90.12613118651382, 85.1645450688704, 274.1427513748589, 170.53579998399414, 152.1218781979743, 63.236969794183544, 136.68029372445346, 220.5783697162753, 22.759453981861085, 53.494047371305484, 108.43927773803999, 151.71774348976876, 41.98716586926487, 116.97971368650653, 119.30428504785787, 95.78174245419748, 84.26747724329941, 69.94168865902182, 63.66204952737712, 137.4027889248332, 82.60175179934294, 98.02017552084611, 92.53149036468945, 62.49809623552962, 45.27084533933163, 67.56983130089648, 91.42659266687099, 61.233915620470455, 79.39937666578834, 76.11115539736079, 88.44076136292546, 48.74734386383501, 121.26450193041538, 106.66443759762969, 55.1612325050368, 130.61158457343706, 171.82726693344904, 317.72111752139307, 104.98426153838028, 63.28389920272495, 75.56086167708592, 9.637844041724112, 107.71292394774972, 53.33166954180539, 17.199206681265593, 74.00367958220504, 109.10852729382893, 90.50239373706933, 57.225062263037124, 124.46833718432892, 150.47296300431722, 102.60995436319898, 64.02761059704953, 40.28181468783021, 207.98662659660476, 72.64409704446965, 34.237071470531454, 46.642925847471446, 85.03987800627911, 243.54945583369266, 103.25067535231733, 35.32898228998927, 88.298556824473, 112.00753332602822, 150.5277277312665, 226.4911653614975, 79.46426785345032, 70.76471851760942, 49.678693617826404, 153.3173806406309, 85.04441438435575, 67.9922644199191, 89.44895090638077, 84.21431380073021, 104.77856696161236, 19.450347934081957, 54.370821346229306, 48.65807491731414, 219.47498609460752, 102.46633839044914, 120.72518403401803, 196.34229273768372, 61.8936792502576, 55.53010779309639, 77.49268554617076, 18.620498283722352, 149.23941364238422, 67.4068939550361, 81.71333531462838, 116.56518155054364, 52.99504337447496, 84.83671271702798, 78.3338893697104, 64.65894087139091, 69.3613431139877, 49.466111328900354, 77.96551848413722, 55.728201269845876, 208.7247977407657, 124.33550429265867, 107.1809135469789, 165.08481682565358, 92.8209822751617, 108.44108635402988, 40.89543158863822, 63.922107618176064, 232.082005998999, 116.29345987398297, 101.79428464505128, 108.91725430077258, 12.264292808841319, 77.120090187394, 68.95442249873803, 150.66456121485064, 66.3874839703267, 186.405802317894, 123.14493699253393, 54.74753635488998, 82.12687804042683, 62.20133340488436, 102.3249181699999, 166.7166575509636, 186.75630636237952, 107.67283610809312, 66.81893809900004, 55.36371987649174, 127.67493245309137, 87.97706892695226, 123.67397372597455, 104.85865684912415, 80.00821111505448, 74.91628789420561, 79.7409118343645, 148.42458788586237, 58.53460020108356, 116.82848992842625, 88.87310089956308, 11.393203803286028, 126.37999725987585, 93.23332828636255, 47.80292225407659, 79.03646316907854, 178.46054798490707, 83.50227287865916, 48.56551524208069, 94.20668348475363, 54.19074966058606, 93.81426078754689, 50.49704820929357, 67.89397656778104, 124.96031579225709, 115.23111954179964, 70.09816265730538, 84.39403085988802, 94.40336608055422, 134.0518116073007, 126.15730758965867, 88.12116916562921, 77.54185661856859, 81.38544464543874, 77.9229115155494, 64.20266149159681, 129.65517427866624, 181.6264495690186, 81.40326274293011, 61.1269463931552, 54.16099111691364, 66.35010582039929, 61.61379547677771, 93.191626479622, 86.80536196458117, 6.4505314187297875, 92.92521190797834, 59.872278659517505, 72.235446646485, 65.31488783259886, 41.50374539089185, 57.204931260003995, 39.19900868493143, 53.38936255444473, 120.32004658894947, 64.21927632199994, 115.27257042695507, 44.409997621644436, 121.31916969668981, 65.76315323528347, 66.55838311500003, 138.3231105812022, 47.20767202025265, 230.98445205585605, 6.1101591035315135, 70.24341105716537, 241.480539620073, 43.576867102277376, 64.39690228715604, 38.95462097010664, 64.27374626925, 67.82226990877103, 137.50272516826567, 23.785877534555798, 94.17237260292151, 165.22322842293852, 123.98221992342977, 53.939432015591194, 113.71323319917053, 68.85886016041593, 87.21664018667506, 85.55949476658114, 187.24371626380147, 72.9130557360936, 75.13245923429935, 45.28615030903592, 93.84738538577675, 143.91805580726637, 48.681575252861045, 46.5978720715657, 55.74912075163785, 70.1042371406404, 79.76036618026208, 13.74707512160142, 157.77202934569488, 228.10414162901978, 45.243710116798624, 72.24719853125144, 16.874735905326, 171.60123271475967, 6</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>125.7476991462707</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>86.95457203203192</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>[141.7095489501953, 133.89088439941406, 46.45655059814453, 100.4916000366211, 89.17498016357422, 305.4960632324219, 35.48274612426758, 85.88623046875, 185.39556884765625, 234.0635528564453, 47.90821838378906, 86.13985443115234, 109.81585693359375, 86.02196502685547, 107.69452667236328, 277.5309143066406, 57.736061096191406, 55.15618133544922, 54.2105598449707, 85.2115707397461, 50.392208099365234, 40.972389221191406, 70.45540618896484, 53.85332489013672, 233.84405517578125, 183.482421875, 131.4799346923828, 67.04307556152344, 208.94125366210938, 411.8990173339844, 221.5637664794922, 77.25148010253906, 72.17190551757812, 53.5526008605957, 27.552318572998047, 96.57039642333984, 96.8009033203125, 43.076229095458984, 45.112327575683594, 10.592142105102539, 182.7982177734375, 160.81825256347656, 349.3326721191406, 81.38158416748047, 300.9937438964844, 40.61442184448242, 280.96710205078125, 86.53350830078125, 135.61233520507812, 65.96678924560547, 53.2736701965332, 147.39181518554688, 74.28846740722656, 104.57015991210938, 330.4984130859375, 54.06337356567383, 109.74053955078125, 210.01641845703125, 90.46161651611328, 135.4842987060547, 65.82154846191406, 201.44606018066406, 159.40525817871094, 59.389732360839844, 131.33810424804688, 57.27678680419922, 39.15760803222656, 42.53987503051758, 188.6296844482422, 371.08990478515625, 45.18812942504883, 93.81523895263672, 95.66194152832031, 73.74959564208984, 85.5728530883789, 192.15509033203125, 47.399967193603516, 350.65167236328125, 253.5960693359375, 273.01153564453125, 159.03302001953125, 156.93212890625, 57.84264373779297, 157.20980834960938, 127.23432922363281, 80.2174072265625, 185.7419891357422, 97.51793670654297, 46.18451690673828, 40.69829177856445, 158.6654052734375, 85.03028106689453, 94.52629852294922, 228.65660095214844, 98.2096176147461, 66.45872497558594, 62.3085823059082, 153.8042449951172, 123.9892807006836, 50.724159240722656]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>p0.25srandom1606</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:47:23</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>91.4567861531785</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>70.19047323810628</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>104.8814021830395</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>4764</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.8573178763975757, 0.7129361593841252, 2.1022056305933696, 1.2342918200185407, 0.6787053390790106, 1.6981013364941546, 0.7996719245466541, 0.7012660368373773, 0.6813028995155447, 1.490680881177236, 1.6804768619653787, 1.4683457722777595, 2.4597696586971587, 1.3412832082199255, 1.506992478711743, 1.5167577792562155, 2.108158687975253, 0.9366939652583386, 1.066086528366466, 1.031294724505506, 0.851184035139559, 1.3586403384689942, 0.7904249485237761, 0.9974519582458856, 1.0905154879385024, 1.8206844521236847, 1.1245058668335695, 1.8022839670808934, 0.8771030380581496, 1.3692171171455714, 1.3973867828965647, 2.104836232160666, 0.8838721994933577, 1.8167099505589186, 0.7542451134425409, 2.183396890987597, 1.2975860239532548, 0.8675030899155493, 2.393222740726443, 1.6143406453008458, 3.334689095044736, 1.8860020925728633, 1.9298066379980912, 2.8301747152099765, 1.34151548877145, 2.296837481839192, 1.9718037912626971, 1.968519707007062, 2.07279120263344, 1.9027620830283187, 1.6388653577595507, 2.175538632014518, 2.7494877339772246, 1.3757119604027268, 0.8233158888007008, 0.37089854779164044, 1.9622995822788551, 1.8770848132363507, 0.894110186910693, 1.6886985840666364, 1.772969486406855, 0.8061640995740333, 1.194677575347849, 1.033474037943152, 1.0009047411832013, 5.088984206335256, 2.3630801616157933, 0.6022598172203307, 1.3879941511202816, 0.8243011091549527, 1.2354120172232645, 1.7701501255458574, 2.994831838539365, 2.123042559556843, 2.2228503784268883, 2.217711792989184, 2.2687981363646923, 3.0450019280791634, 1.659323343906069, 3.4675421477959647, 3.7426019280337957, 4.230194128707474, 2.0350275225565144, 1.7146752605540183, 2.100177383150846, 4.216328407856746, 3.710684109301198, 3.0884476807229913, 2.370649371132727, 3.6328027812286106, 2.285364594784951, 6.0066435507658635, 2.0872808909661633, 2.35426044255163, 0.8984276221981288, 1.8709602676650499, 2.3724579004047532, 6.189843818239812, 2.627057064956575, 4.297938707561718, 4.158136239351739, 0.2293994508917651, 1.6910111740534262, 2.950144365740686, 5.090650502099265, 1.929726887195064, 3.884728494082624, 4.6873170348076725, 2.7512194813834165, 4.398051746435608, 3.1212455622880255, 3.1382066341397965, 6.7560627210254784, 5.556647759477464, 5.794705447091662, 7.700155853628671, 3.8845941470091736, 6.3261577890048155, 4.300040416006356, 2.3179169099498305, 5.020910695981644, 3.3419656280966152, 6.202015962242567, 5.160035787155297, 5.565351573327584, 3.4563530799722764, 2.705251648556654, 9.65381810579003, 3.4017162225250304, 5.098250905252848, 2.377652606045551, 2.268552432775115, 2.289397272063556, 7.3496442050379445, 6.233323289724943, 6.201057526114802, 3.507586929200027, 2.8827821136200718, 5.921356441060449, 6.271861252960713, 8.533463381054585, 4.098269355129548, 4.985884239819992, 4.024862330041975, 5.963225807632551, 2.3617283419002018, 5.28594280229952, 4.245154102592726, 5.834131596322802, 7.511974149947893, 2.9661997719089794, 3.5922463394439905, 8.406263496738049, 16.43803522191122, 6.1267013039836415, 5.476879146545406, 5.740411785892121, 7.6043170591668945, 3.453393952967714, 1.5971790374942403, 8.586001865048198, 10.522632754237513, 7.3368248331053545, 6.083541936846542, 10.387291538127212, 9.973001709275096, 7.022760025545263, 8.648756118218005, 9.77006359435812, 12.407266173267281, 6.833177849950306, 7.054590386835042, 10.994746409296331, 13.061544488837923, 6.721503510877495, 7.722965313815906, 7.930698678098743, 13.29036430789863, 6.027089666541784, 5.3867063841561444, 5.217164522620462, 8.209138491288284, 8.742965642628818, 6.956847107301628, 13.126198421535115, 6.583916845706758, 7.861516169978329, 3.870787753696378, 8.619729003552564, 12.993282884759568, 12.713558173743044, 12.675592025294263, 22.255820321551372, 30.662514566356364, 13.863348116352295, 11.791096590313218, 21.192455945120077, 9.557828818278598, 21.639019597705868, 3.1458412166188223, 24.197203922843972, 29.26478143542537, 30.20936314628413, 14.992851299112719, 12.725610467668469, 33.22590607782265, 22.37303220068134, 17.5719152446561, 26.378646728320373, 13.371957086331284, 17.630363105672302, 25.831965131103157, 26.493019604319972, 13.520973070452044, 24.322546849245267, 21.797807098249077, 16.744645557862476, 14.610336952329865, 5.437675390616997, 9.751568658100993, 16.865348603089643, 11.452518617399104, 5.377491968463054, 3.907854123517756, 21.289134695824522, 16.452736284034472, 14.415349030138907, 20.640102391132114, 16.111462899669068, 13.613961844408198, 15.12063203146778, 37.553308343607306, 17.793471681361854, 21.038305223691893, 18.900011558332658, 2.69773631233902, 23.028463338526635, 19.754159550563934, 14.262742534470798, 26.298595309527386, 38.68046450003984, 25.720952176267804, 9.47229133890047, 8.263499241593857, 43.004665343842525, 26.248053707772417, 8.917964724245994, 18.325648999194176, 21.010447363279212, 28.16690170395726, 19.74745690029321, 19.96359061440138, 22.36948193720615, 41.59332139399874, 39.89277341207416, 20.66367806660992, 21.008556520370274, 20.532656936967243, 19.930106315687897, 23.226114211692952, 13.988950635873143, 14.567575516469013, 2.736739909386406, 20.016965274350785, 19.959845878130363, 22.491227597062984, 24.1393927281281, 26.40931090227235, 3.7209449625548565, 42.54422488882342, 17.172817555446212, 21.145194075764106, 22.34682638785957, 60.48893309031318, 24.11413973578286, 30.259217737472195, 32.4063557269244, 26.23176596321758, 28.44237224127997, 24.759214009434547, 28.7449916492767, 28.893698323863614, 21.883371599701746, 43.98520781511114, 12.641059727237247, 47.64295605765127, 54.772198538725114, 26.30237238349708, 21.06288045764138, 40.17205902680046, 22.794364818197366, 25.26161464802313, 2.5585118597063325, 22.64120218216132, 29.522079172487434, 35.26664113144495, 42.96534995391873, 41.23262200416839, 32.96910894776536, 25.77263415477189, 43.424677226447706, 48.83851943720987, 2.622561179462228, 43.870190475935345, 29.07838285821822, 33.10436886460805, 37.18096588060916, 5.491962905288764, 31.593086477855195, 30.46810105572671, 29.92022846024631, 35.7661597566758, 41.36016409037669, 43.57935729418606, 23.03145770003194, 24.03290212208314, 7.823120159908451, 48.98925144695511, 52.400528466030444, 16.56486044798721, 41.15580986787378, 18.38649686807593, 37.10275498549424, 25.92501206731428, 64.32302005179163, 62.81492845477416, 33.62770858428523, 48.53445260012733, 45.05408924280158, 25.652424743055704, 2.2743917334348227, 32.958268009817985, 18.344466541526774, 21.33419309929051, 19.32218851620644, 53.03353944909338, 33.8178749843751, 21.252582183565284, 30.169008512813225, 23.314986473515354, 23.633971013122707, 31.42661570260666, 28.530914348731724, 43.00777356413001, 3.5595443929636734, 28.42685736188261, 52.86488729377093, 34.45098558697909, 36.78488347823645, 25.569822378637216, 19.555101424557282, 67.01256849907105, 42.74250170838902, 41.31213345489618, 29.115290505136525, 43.870505058250835, 40.2068546535223, 34.10141361512677, 38.810555189048216, 40.29274297813463, 59.260663636295355, 35.7812772577483, 38.00387324384796, 79.29607086046136, 38.161233900745884, 66.63806357010458, 27.78995161131178, 61.667347934805335, 50.10857932020092, 5.404323379820543, 26.770401077117338, 38.90102492109721, 27.7371522613801, 47.87518972497608, 39.02955894791248, 32.55007114457472, 35.260026199378764, 35.90038929520194, 32.14365770914077, 61.497199339029955, 58.99450145520927, 45.91516299983727, 89.02943531200673, 38.75153691828263, 28.460816927259774, 93.3800539173627, 101.70618463856093, 42.93195067042638, 90.2191786870689, 38.18249432925764, 44.756228948866855, 36.81773006420286, 30.77759349846204, 35.10256021629062, 27.15865577494701, 35.042779519962245, 73.89668126997391, 93.72776522339089, 50.424950787031364, 7.40432963926034, 64.95477730932475, 25.75909292417547, 61.643345155921, 35.34629376651351, 55.059032070266966, 87.0948738347419, 35.67568997510012, 49.17738191525177, 39.014749691625646, 39.738611355044135, 98.19332823876158, 65.50865962442336, 39.38659183664082, 31.192772337623044, 75.76917660679304, 6.574289513101378, 33.90024236731958, 37.22154358700999, 42.47057300756307, 105.4835241452777, 65.29022913972278, 37.078911294862856, 49.792075929617155, 25.06171564381782, 29.990424733649583, 63.54118782320083, 28.290920077024854, 50.47745950051434, 45.3989343254522, 63.31486212810243, 61.2600255145796, 38.654520189242156, 114.83565952661165, 56.19305643992115, 52.91270538069175, 35.198080633109534, 49.59908703020579, 47.016449142910545, 31.755526603708294, 37.93638214806529, 61.71713432373899, 73.27326639794137, 46.9169341059886, 90.91480464602165, 33.766906922697146, 10.25682551970339, 26.55278681882322, 62.49158597616662, 52.54683734993287, 79.12088898436447, 39.44323619179419, 31.710485829410786, 65.50240409880945, 37.79039467003071, 41.252195466628606, 71.1564493159803, 48.03357245740415, 68.89311989917125, 42.25814886091762, 35.491295803851365, 76.86570094670729, 30.42240578584959, 43.593519866554104, 40.949250358189055, 32.26805681967033, 34.14347309529601, 90.35821489692832, 40.23519054668374, 53.109098036369055, 38.90952868246223, 10.233042428259386, 53.901636409688216, 54.66986577295708, 25.64082263434375, 38.170346809545705, 41.27926927376881, 36.923793497724034, 80.26406500008416, 68.10568686275715, 37.55057767213736, 64.40082556786393, 49.182054191682305, 100.31071934840786, 28.38719596341421, 36.87840638859099, 61.86936641812454, 33.582060468135744, 39.84181582654408, 49.25435748893934, 96.77690867751271, 52.83675250098547, 62.061793619780005, 46.931752865415014, 44.60484307553314, 73.14924817092874, 84.3214582624754, 41.50054099026533, 55.28921789599811, 3.683801794399758, 128.58842614326556, 70.7300419389098, 85.65624023623305, 40.317651055170096, 35.06042954219177, 28.802832628279436, 31.7541742637827, 54.26076327661988, 55.41297662988403, 84.80294841794348, 66.05814959043009, 50.02534201261383, 57.506523388373225, 50.470671092607866, 66.67433123275579, 99.282864938662, 62.77823265210953, 98.72987979259342, 45.39218090464591, 40.8161130728596, 38.649269585840855, 38.68943476486202, 53.717489447961995, 17.004078768688736, 56.545288755304085, 39.894479029280355, 52.46219385221768, 63.900651685977934, 35.03241014543695, 77.57747013252656, 61.78899052339764, 53.193832850825196, 33.72820712532702, 38.71313707819452, 48.75947236113814, 77.59235451297488, 80.61939736018391, 45.599436216131906, 36.54034656414823, 57.44710989190706, 13.242135736476515, 50.38684307345855, 124.28917122970483, 61.845986219576794, 58.74871199179244, 101.90212352090963, 61.45094710956927, 89.36792143327247, 74.05511350115778, 67.1027179752045, 49.60645234450199, 50.439848856775775, 68.20022205998288, 40.62787187540604, 70.34229833363683, 42.31295039389045, 39.02407898142368, 99.38547830694898, 53.65830801199964, 5.388795861988377, 43.84828428650461, 3.958079514386381, 88.77347547645961, 42.34798071831234, 39.39319436534031, 50.96832882050083, 54.328285604778905, 43.951317406394054, 102.33417887879531, 40.98233753603859, 103.51063383253761, 60.18094122606285, 42.032948737612784, 101.8509076419241, 56.50064898314713, 14.03744274662629, 38.08313764061887, 62.1703472066491, 123.76313586401263, 153.77765928421383, 108.59785402480973, 42.99147831132062, 43.410349875548334, 53.33596146038826, 45.45857946858834, 54.76368149194229, 43.86547097422746, 57.608293412755486, 39.964022122677626, 42.84948122854879, 4.513958327626819, 90.75065770752367, 99.24731178369682, 93.16279304338349, 86.77252337673782, 56.45788096912878, 55.014300592598715, 53.87180216024631, 34.980840967275775, 65.82198545391257, 129.28232535290613, 92.9007913556998, 35.20338075120614, 36.224989345376805, 80.72042076517037, 82.62449463005964, 44.371267123592794, 170.45290397727558, 34.4138926749784, 115.41850473254003, 81.62620500181828, 52.00112519805838, 44.196180270774086, 74.44300352897639, 21.833935812182062, 15.56323038503097, 46.86094261144364, 55.0411351486164, 99.61098070836509, 48.367430709070014, 4.5083679028315995, 51.65113872439539, 147.72164526769106, 42.55065190023607, 22.52029361962887, 36.35365637492251, 124.96481973788063, 60.36347192049405, 77.24032678141785, 9.13481189896223, 71.96724367648909, 78.59170319628194, 37.95537470259356, 55.86929704267636, 63.53068664434659, 49.384970813414434, 67.31682400629357, 48.754456492176104, 158.16297246244812, 72.07638690203137, 6.593952346572214, 67.75153586893121, 64.24196795711072, 58.881382808853374, 129.0319622549611, 42.35074036534668, 47.98527156481015, 64.71294926347058, 108.55636918182553, 140.11783719448098, 84.21827510544465, 44.36445218615579, 42.073044374402365, 60.064110859534935, 33.62924733311053, 57.19464435790208, 94.56098067848706, 54.677410017292324, 101.89958154899848, 33.41340802037996, 102.96979887285184, 43.20422846720875, 85.72070688642077, 66.9098433749428, 43.14109726990638, 62.998176679097064, 110.64807092296269, 46.595142799467105, 140.34425225273372, 255.09764533607037, 49.8419265095518, 12.936557169611381, 86.89548151010338, 39.28276413058689, 49.631214072206205, 44.36776610522797, 91.83969788044249, 75.18537991341603, 182.2767889438638, 39.1820282124218, 76.43443517945613, 48.374109495338445, 75.56973009687897, 45.66746367378774, 63.06793336483258, 47.1531986557927, 6.805780116595477, 85.25727115128261, 69.54264034668472, 8.38869553073571, 43.589079953792776, 49.521827612273675, 61.01536006126008, 46.47351404340847, 71.42173945956756, 64.30773497878064, 67.97555806204522, 151.57207904619662, 38.307337404290216, 122.77037658942632, 49.53538698973044, 132.48194353823237, 86.60722347107583, 42.616907334731, 49.51423746388018, 134.9797333146411, 59.28161102314575, 84.87554493595657, 59.008575159369606, 126.57064537626987, 69.84429905394123, 43.77962661060987, 73.28977517777912, 44.967952496407506, 56.44280031126121, 120.24836534574776, 36.09586416267507, 12.91623270668165, 53.865661101394664, 108.72469005239321, 86.615752806458, 101.0960238744859, 51.677204219809745, 42.06904057845257, 5.061172502217012, 85.39342036855687, 166.08023129831548, 50.7684187974635, 94.29708785085903, 99.62587202423019, 9.152759530734809, 72.81985884905298, 43.82257355812173, 103.86118142673331, 95.58929154521469, 57.25320474650208, 141.4608520720548, 49.17133146819303, 43.44524203952482, 46.591111704845105, 121.9022549992566, 67.24152812122333, 40.265017421774374, 12.458410925790574, 159.95133894861104, 79.57191546623372, 39.95635790013824, 44.89559187488074, 46.541819775252456, 164.29276840550241, 55.67313143830905, 59.811160164434796, 85.72300273101618, 16.075083431336825, 88.29719721696485, 46.770801709357684, 71.3463409424752, 112.52786576523326, 127.5403964379692, 55.80339401868502, 76.39604409128441, 41.06161829458645, 85.23555633123345, 68.42204047488305, 91.69358048059273, 424.53457655924456, 136.6458399489891, 51.99445483130419, 51.79872097668207, 81.9120323603473, 68.6670955064869, 134.6851616288237, 45.40469450273821, 76.95128386305325, 93.08343763142979, 145.73042278354706, 85.12396182797255, 77.58391034951171, 8.257914832498248, 76.607144552189, 42.9856584684758, 71.80460525805061, 103.04449140471738, 11.414875633932065, 51.830629189985274, 99.0694477365771, 55.352020108633134, 150.1554038444999, 104.19389949557346, 49.74278943019288, 128.8939500469785, 103.86543461527968, 5.910093398407646, 59.71153797584631, 117.1196817971806, 94.30585956487577, 63.44578354426048, 127.03115911263622, 61.72769513423706, 79.18309809939245, 84.27693290379827, 73.87810290053284, 149.04458360436573, 92.9593830059235, 110.85364895871516, 64.59904465987917, 52.329828884114384, 38.21490810832742, 41.68814473988238, 119.34799765240831, 62.85185221483477, 12.602898394065045, 58.605957293303625, 86.10995060810413, 81.66270516701665, 56.62086071028744, 66.04916707936817, 117.34041051723699, 62.112439643974426, 47.67504855293597, 65.35853782459458, 58.03239155637333, 98.17861452568933, 46.85864491158512, 54.710559557894456, 79.37517040046764, 40.17961467045277, 96.65164098431889, 94.35971621554884, 52.93294531671279, 107.39843462828574, 57.40677439040773, 41.811484429779654, 64.90559350919202, 51.11743218745708, 45.94410634091493, 179.0626955057215, 93.71799144814504, 36.83441366912396, 54.07394523127739, 87.77278152053326, 49.74618430143485, 46.94666541076767, 4.946218950496247, 76.13354527229271, 94.32774760603239, 88.76663909524903, 123.31248995174883, 6.290247869939314, 138.43336546549313, 50.66404663827108, 75.65329300667774, 61.83934810110171, 41.798871631791606, 61.50614729528634, 57.16722135097034, 33.080726963389814, 61.748774989273294, 87.01465207855713, 98.66867537301844, 65.50430034355392, 107.45053156937017, 140.0091127490713, 75.90693185620019, 52.07428949766887, 41.42917269823633, 50.75615542417642, 45.63758409688877, 62.440636764126246, 45.36784632147983, 55.1104561062882, 69.60855012091835, 122.95615091430042, 132.44320995336827, 107.41003001645117, 88.12484255650753, 61.693095077865976, 127.206129078294, 91.1076520721215, 57.62463127437329, 64.37753624182363, 99.12811148840882, 12.649846796288335, 97.03479532969476, 98.71824924879262, 54.30711267400207, 118.0319351592877, 70.73514135871321, 75.90514291297853, 161.09063657625808, 41.222539839887304, 49.62237536921547, 60.72260216103914, 43.45334267699247, 71.51622957282572, 35.726062291242876, 5.15038049874203, 87.67470423218263, 129.43463183394886, 42.48152420265434, 5.716995853284433, 78.43505475488038, 64.79370585687519, 68.96925167778785, 90.40841462170958, 83.40387573254172, 97.42748642251799, 109.43493714156659, 65.47070403484828, 148.80609680950417, 65.04267067590736, 7.195601278015389, 44.76192310237702, 73.1099054439957, 99.52161782695293, 97.47568268574643, 99.66198859350654, 50.40802623613253, 74.33212012112412, 56.16563776901538, 116.93266206749362, 52.11637247900339, 45.31481079519576, 153.05551158016655, 134.8590130971467, 50.709523817503836, 43.43282419940697, 53.752930060904376, 128.90551221707636, 165.91266902223842, 54.420185513616396, 47.56626438001287, 36.403830857322156, 54.023823751461066, 68.19140493894714, 97.98482412280624, 40.08493202184847, 45.01913554880141, 59.272076609552286, 165.62286142012402, 62.23039450227749, 116.61206222401826, 72.19027250401439, 55.47282353727595, 9.308943848142674, 121.02382001093707, 52.19397587581492, 94.75910722554286, 54.790038057717894, 64.40146644945449, 107.7598835851769, 76.12503498306444, 75.93377140768973, 89.59078369570986, 52.89758636377226, 120.5449259750521, 55.22537246249143, 86.9425217697621, 63.11908950315669, 51.737329760069606, 14.150304868260008, 76.78406080057844, 85.42339631269718, 4.522098188793114, 71.49319831894425, 147.24121831396738, 4.675644909525483, 98.55552231560574, 84.51762808540224, 61.3392550548021, 116.26508605514154, 16.16744753701191, 126.73151307514269, 71.74925210598619, 57.77449752866553, 66.33906799953978, 160.2290697722585, 67.14986685826233, 95.51753387362449, 94.93724009328662, 81.05954315393511, 86.74838032669578, 9.591965390107493, 82.9779880712812, 8.45557443287905, 62.52446126903939, 93.94909082643504, 82.25288850112162, 69.66698520786493, 131.56846188255807, 139.61889521432022, 61.98330382575857, 81.09663668836878, 74.23965435034013, 239.6514536474146, 57.795822775564545, 80.12211301023638, 106.77821319422894, 54.14108306249977, 54.5382753070952, 77.41707532461982, 82.73578354455806, 60.407152489636466, 172.91791091735973, 56.28263769392661, 100.81700145947265, 96.23944125732649, 50.62961487284752, 64.50285267996344, 66.48535133757596, 70.06640388027483, 69.68329561279906, 55.946162672974054, 92.54407844616259, 45.19484973659606, 72.7685545512779, 63.32375313204553, 75.6918907954216, 90.00758654189767, 80.36450222413181, 251.7179240416391, 94.8606222959763, 82.47457140719251, 57.666239034401514, 82.24395471279293, 50.64389006483884, 67.3691989445367, 59.84610824593772, 47.1102855900308, 54.519320361516975, 7.343957476946343, 115.54836780215663, 79.12227611056807, 45.69105227813053, 78.00318948692609, 93.12000739397473, 53.95323413867324, 63.21516516235965, 67.5525097630863, 69.17919119712136, 112.6964400308226, 52.26851341906666, 68.34176456104524, 53.73981783604532, 85.2265665173569, 117.05712481302047, 46.80627762928204, 50.5414546747374, 57.823525822505914, 86.33523495278044, 81.28696450383912, 36.46270249068005, 56.63845057061573, 60.68566899468816, 79.2388081219598, 43.53611532513427, 49.91443275013069, 50.52013219161113, 60.075093224358405, 74.13586766776078, 77.27681019405584, 43.5209211318191, 41.01336653289882, 45.4816065429327, 35.02081995023239, 157.44560490132895, 48.71488496397982, 56.88693751247386, 303.73653357820615, 41.80486569301732, 42.43418073904054, 48.267873379025765, 60.217680363401186, 88.9238936940795, 62.786023282537585, 46.80557237172863, 74.35034390747497, 92.97474935318267, 41.99360992811306, 57.31861355062431, 41.500410117048006, 116.47512397000031, 46.334168024058975, 12.16847249761219, 95.79412845299743, 151.7351599691948, 73.96903963908595, 103.51921233345846, 8.342004739151873, 60.304188414753696, 243.81856043786217, 46.97750583463256, 13.382508993870669, 75.7587259210793, 51.50673796574179, 38.59581933683227, 242.71131430604683, 137.9495584965714, 90.28408605405711, 14.566109278455283, 86.14500337236672, 6.499431231880503, 47.00172907866743, 80.22857374937249, 129.97470365677563, 90.72592708216783, 65.00509968060551, 191.19478278883435, 133.7992314211678, 78.05061244266915, 52.64014868356725, 111.20810196325426, 33.62088885983284, 291.0444592042885, 85.55114312625632, 78.74012104005892, 120.04309619036704, 84.18728556314774, 71.41241644819492, 67.74143998946897, 107.85904712508172, 111.00024747011246, 111.7184955551858, 84.20009035542611, 82.75978316393183, 10.220927602546391, 100.85875299172481, 68.25387680789714, 80.3130492817864, 64.88472802262135, 85.68649017502757, 76.41247782363213, 54.26587086876676, 60.35082364527116, 76.52771829509639, 90.87305598354655, 66.01572984639593, 162.7554086913255, 131.83641608417616, 50.3727810971137, 91.98831585364626, 83.9539338936168, 107.44720887019625, 48.14474770602843, 66.04556050775899, 125.18625327894468, 47.5017252904679, 70.92158970691257, 140.75758080139545, 39.665521852212, 84.29093412556469, 235.44509571150317, 90.07505174986194, 63.458420137080225, 67.68710361528962, 67.46092722808802, 38.92103183888951, 89.9918310014389, 100.00229510085374, 86.84101105603264, 122.81087492462619, 21.690279190525587, 185.52551097521734, 112.32416997047584, 58.10321219480617, 84.94662847341331, 55.996460766057886, 206.29853807632475, 11.370279024383434, 85.00364292339229, 92.14760011774128, 46.12212644082402, 73.50553651687041, 61.255828692696795, 54.25271415531671, 89.08684805985412, 298.6226322774703, 81.88209316069357, 99.84984836727361, 165.35744911733403, 125.13080412018712, 76.43075384974637, 67.86732799854485, 71.88208878758023, 37.546604553979854, 18.83168486340448, 65.16011075054453, 144.54878748421876, 46.157679227789195, 53.498279319136195, 71.18922310064734, 92.86213376944191, 83.37160793840226, 50.96582347436598, 70.80936155881533, 181.27865418010728, 86.75134772623561, 56.12642764555292, 82.54005654550615, 61.89490842311808, 324.8852340023164, 56.13966775630205, 102.7705391500265, 54.80473260389148, 96.9104668010596, 78.74502546203618, 66.9229872150631, 60.54278624997151, 91.62586895673388, 59.869424372275844, 92.35100601300242, 44.54410107752051, 52.453935542282245, 62.41209193841167, 66.69719208258186, 44.18261245901717, 85.92796905789706, 83.35420502980476, 243.53899320938996, 75.19857961060998, 157.7413317974862, 197.42371299648167, 32.073792998804066, 57.93496147835135, 95.4269395834624, 67.90493678558558, 72.94374069785829, 91.8392267695663, 86.35418741216832, 114.16338508656031, 74.36691658991725, 159.6825786826402, 45.37891124078483, 6.591255079419769, 55.75085040141319, 217.50631086860855, 6.759743764279474, 100.35063394343504, 11.328270103276006, 216.0258844273195, 90.71547403409605, 58.77188234722338, 198.72677143198152, 54.645265275030255, 126.75215567193467, 67.39050431732154, 53.346206395931056, 43.56882685102755, 51.649513973540834, 82.62953933048638, 94.46511340556663, 4.8600969541222, 43.47923164835331, 64.91751889436992, 114.29465114258794, 60.49711970024107, 89.1991019464879, 16.180377305922704, 64.87329862580036, 70.3423197305128, 79.07892547959662, 48.53158624555143, 58.60251556178092, 113.45402815311901, 67.32785136931018, 144.5418674634848, 45.870936847230524, 50.16591648352927, 144.1444447937502, 58.81856452559138, 63.54501647144268, 44.15058432468639, 55.87925226458843, 62.77694093228472, 80.65002563811238, 95.32676245327067, 68.0774123021725, 66.31528104031642, 104.30386340204191, 62.756879762098684, 52.07916656075478, 65.01820201230936, 196.03030515871066, 45.578463754216756, 79.85080670063293, 98.11265401191758, 104.06064615608734, 57.89110798689908, 7.086262851109963, 64.79286702604384, 50.24829322354588, 115.91342915113769, 228.60908318164425, 79.385936057155, 122.24262342959261, 143.57423070262564, 80.65240372159126, 117.19722190684097, 68.55143044846831, 99.56395916116566, 40.839821450855474, 164.76243357923312, 49.0374675025566, 164.92011461986795, 51.21283717557176, 127.21757152799448, 56.236081432526994, 118.05564394315347, 134.79980658068567, 59.35643809038142, 56.0931166988124, 58.40519593939948, 114.23843026501872, 134.74931770380735, 94.03080630995821, 87.1560044126279, 52.44940935210151, 66.80809740557171, 103.82133356715948, 62.391334368661916, 201.5548700503527, 87.55114909880294, 218.6353469804963, 61.1248290723063, 70.06775124011186, 155.28040296888534, 149.93052726005024, 42.19355223317224, 76.7353487327809, 66.90459655347578, 52.833917468044035, 77.76241836278753, 72.33143275554778, 293.94641688719327, 51.409810091817725, 55.017275956889605, 65.3812433266818, 75.4766890653026, 80.5298919519164, 173.52854247239696, 56.85970881785054, 47.468417065247245, 111.2662599147534, 68.82970470994279, 49.37460818375458, 6.599837660633978, 80.22019531269419, 50.922310563318916, 224.11527007892877, 131.70067712232432, 67.74470652166198, 52.937936508741046, 103.72461041391723, 188.71875960474497, 46.745050967618866, 241.976651240717, 59.81370168053536, 91.40010491486761, 46.62867112183689, 75.24657976152407, 371.29021713566294, 59.875137798004914, 151.9204828772396, 106.5495176677249, 79.60060974233902, 105.2525410159067, 74.62396739564987, 154.6402625128757, 103.09770739481901, 48.67254868871541, 81.49518716328183, 49.2215036840879, 74.2096581639771, 141.2303316052951, 87.92952961001959, 74.76791370126955, 79.2007618192201, 62.06446205186179, 40.29849575275717, 83.88272242208005, 44.835165595009556, 55.30133378940913, 166.07534777233792, 60.35942469399695, 112.49154143454398, 73.06173220238372, 98.41789464107131, 111.85123954688021, 129.33889181962167, 107.75299288035283, 101.50258502198581, 67.58422345421852, 62.92509371541287, 97.94081236499709, 138.69337832439942, 69.82501634445555, 60.718018636871385, 51.48954971161688, 74.43873368253583, 86.15766263221445, 88.99776380008342, 84.19775493863949, 88.99308895666151, 105.94408697608205, 88.58045408503578, 189.01270956481565, 53.66167309603415, 40.50284990384788, 52.19934765232764, 59.196609592439756, 136.6142716787011, 55.35147717377058, 90.67367125148535, 5.201691427525359, 66.14526237683265, 63.15401863759588, 141.91048862488037, 103.14657634942328, 54.47709390873939, 137.78454422701964, 110.71047705005863, 78.500795899272, 157.76417681548975, 60.88705032709979, 73.81281396374361, 64.5059723863306, 52.080140037279826, 74.86685689581907, 85.86686797583918, 73.60731890621678, 151.16423925146816, 76.33106825309294, 69.29848534580378, 106.46624243084496, 122.44910871082722, 61.8603363746603, 115.21477164019998, 113.58347616474667, 200.17478190448662, 126.21876867032691, 90.41369833437483, 77.44168629445657, 317.85855191094186, 81.4622364489432, 75.15590473502347, 131.18629958702851, 76.73677243010731, 74.25344064225591, 71.23353179747002, 148.37396351167797, 89.38417245090398, 6.841721146842809, 76.00985967182675, 171.98760455984973, 82.22900000447032, 111.88283967023104, 168.54018107727157, 140.59741756573342, 44.66000634287901, 5.953138519514466, 61.778494195096606, 178.05465441902882, 174.60265326445725, 42.87630834320714, 64.56319733883757, 201.860632094983, 53.002972120025916, 126.99647373364091, 49.588626828253624, 54.98635356559232, 131.7255176588436, 89.42462886100971, 62.11198257706768, 65.0588226472467, 73.54571170010438, 94.14373536830031, 58.19037007463932, 56.91832176610408, 94.93964748976776, 43.980013951923986, 82.91214325121771, 186.8328255379056, 75.52342742468714, 83.53554610484272, 72.55357006178821, 104.61234396740176, 104.06554985187636, 52.425018748246266, 74.85196682550374, 56.49503311718539, 62.92799826186847, 45.45132955592475, 66.54056860155598, 49.373202930933445, 63.531497520234936, 58.9448622209646, 7.091983255402438, 79.4418530582099, 85.70279958211403, 41.66456615107869, 139.48656926313248, 101.25728799871358, 61.20615638570124, 117.68808912340737, 65.35215036078837, 114.23833822345141, 107.00141226770417, 108.20818316509046, 47.08258501038281, 220.2831890006239, 65.80022153085817, 99.93895992336084, 45.526091485599395, 87.03373589047708, 68.43805371210831, 59.098966869302224, 81.18708494622881, 13.782380238136312, 53.25013654209112, 64.97320634684806, 276.502069492732, 51.53646483365894, 166.85624826736557, 7.530065167932202, 73.09793174874504, 100.98237435532734, 44.21133047672304, 73.38192327200846, 80.97309211312297, 64.19666290778582, 104.24160678930866, 113.50552107006185, 154.84326204853974, 93.975572890808, 85.12078828511017, 71.5317966042322, 73.70128238230792, 123.70599649896687, 206.96966028943478, 47.762926348740336, 63.68922385620678, 205.09254519647604, 46.278238113608666, 101.96976412228787, 94.67555972744816, 113.24449525015426, 108.38424753712374, 92.38765476338484, 44.93527342375993, 62.65399158101213, 100.66048254143358, 49.52201828324156, 171.78382443645978, 62.447973551227776, 16.328382356926102, 107.58773277303713, 108.1735975020921, 94.53456598726244, 196.50021193371822, 54.447466451056165, 131.6961196793069, 217.85957881109863, 104.69796045098116, 79.32364475445584, 74.22264432344514, 107.18902678293429, 59.534824170087866, 80.72977394214955, 125.57694517096849, 156.68118837553465, 283.45063360423393, 146.07619730780974, 67.91885806348418, 73.42448435188767, 184.04339057612012, 51.797295572543334, 86.92898700937225, 46.383619153001874, 130.29419307769945, 49.02598833893821, 235.96958168988434, 116.33627923328257, 82.86847701693002, 84.41031192761541, 69.64351873031657, 57.90132460713371, 286.31448918613245, 128.83760439967088, 73.98597829311272, 87.8833300637245, 75.9042807686678, 126.29246565749463, 109.63294935952703, 51.70610716874689, 24.9448599484723, 57.79001215731022, 56.61433759544098, 58.847067083103234, 70.72428390589435, 90.2454394167889, 35.21219418138173, 271.98731278041004, 77.62851736230787, 7.503975491245509, 112.98960713135773, 56.764201769408885, 106.70154695619036, 87.11551712961183, 104.32380524793524, 53.560821317261265, 93.96185026452989, 65.83300456542763, 94.92081090997459, 62.73171750191514, 128.47326901006872, 184.02697208040874, 237.5401058628551, 123.03731389204017, 6.849730477548659, 4.979509282987341, 93.50936712097983, 68.65709312762301, 82.83659221125909, 99.54576196974973, 43.26691970971994, 64.03149681546446, 59.15137816894026, 81.43713349452247, 22.33770660606829, 115.85004403308358, 82.39089507464465, 83.97597172551403, 126.34567291498864, 103.08571324866406, 63.26503576633223, 62.441356741780304, 89.45638698676181, 61.355036412091856, 206.5616661701803, 110.0619031264842, 501.0071639083904, 159.94049298481414, 59.67109017105088, 62.41360991288548, 69.18156421828374, 65.77709155183442, 86.01873220763594, 87.50113010144537, 76.44623631153387, 142.7143984885924, 56.55121959419921, 6.302385038665646, 74.57437770768117, 238.32914654784582, 43.769960731561916, 56.210055593285766, 40.64860023930325, 134.59942393322424, 107.94521253852419, 170.08501751250853, 86.62510494183768, 42.485796244417415, 75.26475509082032, 200.37394717009266, 71.33436598255402, 46.489993670836824, 91.30212451163861, 201.42908789830594, 43.878516982495896, 173.12092285831665, 194.49198589564136, 122.98783868566072, 307.3440712105594, 56.082635564615636, 71.86555768093083, 148.02133026092955, 64.8499314176806, 70.49691594500497, 133.4098547230101, 63.47074290979841, 149.8316679300762, 129.31348466401184, 55.14409893534805, 119.38701226998164, 47.560231473613754, 109.81834726724198, 72.98341696576118, 114.08287064596038, 14.731111262365035, 110.43798023550842, 8.954839225288652, 92.5064789393427, 68.79290095014402, 70.6372707066871, 94.81114186064232, 82.27559175173926, 67.29671965230392, 104.37894373664315, 72.41</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>112.6355842208862</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>73.15941672270789</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>[144.37789916992188, 11.32820987701416, 81.6587905883789, 47.1556396484375, 206.01339721679688, 74.25999450683594, 212.56134033203125, 32.902679443359375, 96.88993835449219, 196.00393676757812, 125.1919937133789, 49.94477081298828, 48.62160110473633, 104.01342010498047, 93.10458374023438, 82.85257720947266, 111.90489959716797, 327.0174560546875, 51.77920150756836, 60.706947326660156, 53.73728942871094, 88.77464294433594, 49.582603454589844, 39.30732345581055, 71.95425415039062, 54.82795333862305, 236.01190185546875, 193.2176971435547, 138.4569854736328, 71.72187805175781, 211.06932067871094, 188.92532348632812, 140.11807250976562, 273.3631286621094, 167.85865783691406, 19.237619400024414, 55.91483688354492, 67.28598022460938, 53.63860321044922, 165.0924530029297, 30.000959396362305, 69.08069610595703, 111.4623031616211, 107.31437683105469, 94.52547454833984, 109.4842758178711, 117.73888397216797, 158.4254913330078, 64.15277862548828, 143.13145446777344, 129.60923767089844, 72.41873931884766, 139.98114013671875, 68.81127166748047, 52.679161071777344, 148.549072265625, 82.62013244628906, 112.51473999023438, 341.439697265625, 55.998382568359375, 213.16348266601562, 199.4562530517578, 71.7152099609375, 106.8954086303711, 10.356305122375488, 60.45893096923828, 73.78459930419922, 147.5721893310547, 74.73395538330078, 41.98382568359375, 127.37140655517578, 62.53797149658203, 45.383358001708984, 16.60811424255371, 111.03040313720703, 125.00404357910156, 146.97335815429688, 70.94113159179688, 110.66688537597656, 99.53714752197266, 73.88607025146484, 87.70616912841797, 202.6584014892578, 48.10628890991211, 413.7713317871094, 205.76473999023438, 296.4822692871094, 204.741943359375, 135.78553771972656, 61.370784759521484, 116.37174224853516, 46.490962982177734, 60.47822189331055, 78.79439544677734, 118.30986785888672, 61.18773651123047, 79.51907348632812, 82.49214935302734, 148.61593627929688, 116.52674865722656]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>p0.5srandom1603</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:51:50</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>83.88271367607108</v>
+      </c>
+      <c r="M22" t="n">
+        <v>63.74470914996073</v>
+      </c>
+      <c r="N22" t="n">
+        <v>102.8316526034163</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4859</v>
+      </c>
+      <c r="P22" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.7255805133167887, 1.2590380581255172, 1.4292546412873066, 1.241618146071886, 2.282943626026312, 0.9768752613824513, 0.38309490460645185, 1.5853552159118565, 0.9180291537048838, 0.7369000508819065, 1.0767731688400461, 0.6788183497080192, 0.8284281168854323, 1.3409171515683538, 1.3323504228347727, 1.2176858075086456, 1.1755294216457342, 0.5281283614655377, 0.7485529059529655, 1.8745155658880739, 1.10442434813151, 0.3312317015949828, 1.439982706453322, 0.5665682105246186, 1.909647824458278, 0.45727330482563033, 1.6913385842787592, 1.5924358150136717, 0.8115756305968403, 1.5089984430550982, 2.503713164941037, 1.2123388336761873, 2.517874342610418, 1.6924750983472763, 1.6557588525187519, 1.6817406468312255, 1.188792140463649, 1.4658578936553923, 1.7641420110709924, 1.4564667931581934, 2.2339365254725494, 1.461380088578911, 1.1831225388418751, 1.6888359413121687, 1.902044595926248, 3.3432901470990837, 1.3150830928111577, 1.697528267263924, 2.229192119170013, 1.742152720460141, 0.9983572529474544, 2.170162002924203, 0.5226499370492278, 1.5885789702508448, 1.389439853200526, 1.6871010166058222, 3.8533454927562985, 3.4476197359838476, 0.8710867177051876, 1.5192535082057732, 0.9228482032077159, 0.6738060700380119, 2.9551285561281033, 1.6553857046773008, 2.889137170807501, 1.5209543537073071, 2.316086044153534, 2.179372778400217, 2.6208761090186914, 2.6558739128761375, 1.686888501691304, 2.455099644470165, 1.9389601130721041, 4.0967666214649405, 3.8622346631558893, 1.8475085828376425, 1.8458877661416657, 3.5699377383112916, 3.2436993253874937, 5.392477334117146, 3.6401103562706796, 2.7319299598886464, 2.7122115721478126, 4.800962172862329, 3.3671934672683754, 3.081820975166846, 2.1012882706947233, 2.374789829950085, 4.102353788161767, 1.6701086550745299, 3.4094912694779356, 3.3179362716363037, 4.932464514578133, 1.8205873361964497, 2.6942526947224392, 6.6949899058691935, 4.270786809636794, 2.3104726703633456, 4.139626028801318, 4.807938657458377, 3.2725626033767243, 2.1725492778461573, 3.703398149089798, 10.768031506466642, 7.120179853231581, 7.428746774579902, 3.4337351333583865, 6.865335982146324, 4.3317919014881205, 2.3462807210267034, 7.811544883752805, 5.078478200159672, 7.879455295004212, 6.399357131902911, 4.258066783212949, 3.406036702936921, 9.268458798716336, 4.254964755159608, 6.099631111622319, 2.454812897369196, 2.517082341975786, 4.849143750974082, 7.212848092290718, 4.236862189235778, 4.281567528739331, 3.592273577160496, 3.3352415263141157, 8.175031297619984, 3.8097068206792404, 6.462376092976334, 4.557652833313409, 4.964869234840876, 2.082149642747466, 3.8041453979546325, 3.9669821993546197, 7.010624889040711, 2.0633986815901197, 6.730562014701173, 6.254975524739278, 3.726249868305762, 5.266810620462419, 8.573181197354439, 11.493413639103093, 3.783527415737813, 5.837273576161085, 8.74182912545239, 11.229806922912589, 13.024777698553004, 9.49582428673251, 5.779008500322163, 3.894184188225597, 13.295430281473529, 14.33791883102146, 3.0683631527727635, 6.498518304679644, 7.769186743976527, 12.382973841992822, 6.886323899691744, 11.804929713959456, 6.788511362461539, 8.815287258726093, 9.519183920170548, 7.140346719712407, 9.805097297799644, 5.906815928916916, 11.406369141852535, 11.710887682871675, 5.747131061552977, 7.300474224019662, 11.896768891227861, 7.6963438471321055, 12.49210471528493, 8.850174244708642, 6.356479199131453, 9.837578388148726, 10.039571573107501, 12.915349499064527, 12.067535881076033, 16.575893997869752, 15.012907084459382, 18.863509931091254, 12.118534943272271, 7.751212079966364, 11.959103660893799, 21.323203606363524, 18.58349501354173, 12.745408517565124, 18.404596513781666, 5.750370733239165, 33.89976202844353, 30.47118998176494, 8.361805107966184, 9.48121498638616, 30.110039963151873, 18.649259224485913, 14.494807913963948, 23.995377103422904, 12.896050873718183, 15.986617351131814, 20.251914529877, 23.04001367036304, 16.94514029097562, 20.624300316468002, 8.937353104475172, 29.770885991703505, 18.6640329817582, 17.504140648410484, 6.893549621267247, 16.50825153407385, 11.14216745139596, 15.436264883184236, 21.400492535011082, 18.95652130601516, 18.593494286448642, 27.373374676278836, 22.262196963865904, 25.8013330280672, 29.789546982678203, 16.754603259283048, 27.63203428461334, 27.684986134247026, 18.66882673549191, 21.080738766233974, 11.924421516327191, 21.423545847774744, 26.063687305205043, 11.947100752100534, 19.49285919775795, 9.248744667631861, 17.986375714316168, 26.22076851143668, 20.08619066667692, 20.658895768699242, 36.60262595055289, 22.578766122258468, 12.429311949865294, 10.74075749665999, 35.084515418340175, 43.78689524531291, 34.200934773825395, 13.822331432721045, 18.000338443168225, 8.435736420533757, 41.14388489856603, 18.090911633839738, 13.143236638989556, 21.177833554148226, 51.478334547754855, 21.767311517427125, 43.71970391399368, 30.708406484039283, 29.7612933891195, 13.444918934521164, 24.812959048812004, 22.640194076562043, 8.228940133210084, 28.811100324081973, 23.86181113955181, 24.138449435838403, 50.53456361068117, 29.8949829148841, 25.009674746042943, 40.00439770670074, 15.018347985011555, 19.793217211065016, 30.142769387855083, 21.057369692474815, 24.759021061453492, 34.45333646520076, 29.78572785560014, 42.58161284626438, 4.355630202918045, 28.82097571875096, 20.023775420492765, 34.944917999422394, 23.943967232336405, 40.03676878472161, 22.20129477345941, 43.284337537070584, 20.81056930028349, 8.13476996856156, 38.108228530435234, 31.349352585340796, 26.3289119156141, 24.43404997274871, 28.866013097834323, 36.93075784361356, 4.600968196748113, 29.191213106165115, 23.362105433260826, 30.021331674437494, 16.80678210992021, 23.845282346215548, 36.23265523469241, 40.70624924012992, 19.288485352685072, 24.06007327660415, 35.233857632601065, 60.27440973758814, 9.431266810013105, 18.215205189385266, 33.106878746726416, 28.494198854099725, 30.54015643080856, 30.09587410449068, 40.30540512773184, 36.307460095497305, 52.118152348521875, 35.44900534151593, 17.667938706649956, 22.511843513266964, 22.8148212785027, 9.287541385468835, 33.34516273263217, 46.460905306986525, 23.38666788282658, 2.7204586461810463, 6.633582773684648, 43.956520616527065, 32.40658885062601, 2.520094691612072, 24.265535375726227, 23.395527995576387, 53.52720898353806, 49.247650006231986, 25.539567264291257, 51.14230186432069, 19.02867376448494, 24.82140082855724, 81.12447489808262, 28.571411418233613, 39.077220297299064, 36.1453242740432, 23.11765630359107, 57.84372072398672, 59.29875437067163, 44.84919196162148, 39.578628879939295, 5.24060317180577, 27.992546599718967, 49.89634364208571, 68.09597212144541, 28.79021147054738, 36.15605191978831, 39.55119307583011, 33.40236586837063, 45.776319259480765, 13.731422115454096, 37.642567718470275, 63.75138993352665, 25.16715075719642, 3.288822586235904, 21.119868933114674, 28.920254425197793, 26.72587079664852, 28.22184939372021, 4.559310458864519, 38.127978307776175, 23.56338265546626, 45.24784147480285, 23.415639443935934, 41.331266568491486, 57.483093284962415, 62.294706423418695, 30.16719181687896, 35.17964254975877, 29.6921972381754, 27.42989372642123, 4.086680780617179, 49.7777159118346, 64.1497578851316, 40.9801732775763, 115.21630838655544, 68.60540425641962, 66.0061205744677, 22.81195871489726, 63.55369380699861, 33.082207556680196, 29.73544977627362, 39.6548097373243, 20.74649393164839, 23.563758972863354, 51.70467934652371, 44.805395731851966, 54.107577398537714, 73.13973118947385, 59.199482937080724, 19.87213993852872, 3.363110493636782, 33.58230531001054, 44.220588439682544, 70.07682432848547, 80.58740303264213, 39.400803619253736, 34.53009129765651, 32.089702329966975, 25.503068629709897, 41.23091354130749, 72.15054077302798, 73.58990616953126, 42.54057797257046, 73.18601556772641, 25.74520722189096, 34.406100224514404, 64.9574855726883, 54.29721857436314, 62.728933668906066, 36.9986531907474, 42.57112135436556, 52.032527066724974, 37.033090543916956, 9.66078733730994, 10.647225339311984, 31.471670500058412, 36.605844268432236, 32.28107443832828, 75.22560196435964, 51.692195265533826, 101.45592247053621, 72.01523198574593, 49.22081681035032, 44.215637719026155, 104.77968582455493, 24.251092211225572, 47.499146068825944, 25.738871587086678, 30.07656999636619, 74.74434406166667, 49.856642558338024, 112.89072184653755, 29.118790712305966, 15.101023024087873, 8.780127489912408, 43.00941004584761, 72.99042249410076, 58.56657816307762, 25.774090854722328, 43.46648513658884, 32.52806764619429, 33.706535074144185, 61.19795318115446, 48.655650834780715, 66.64396726517998, 60.482465332596504, 53.55335592261415, 49.238362156022234, 72.6690034139931, 27.1973005364806, 10.867586002920808, 56.333996776202184, 54.300076141568454, 26.55489356469748, 85.62387842932358, 75.01735809102402, 33.10361951598599, 39.641007182558106, 42.11788264261004, 31.530666496253836, 35.72975740082657, 49.156256002700005, 33.267994204208854, 37.126666917246176, 30.752212656470196, 45.435964468743926, 48.790679693351166, 34.492769603785895, 47.11446337878384, 50.86180720546212, 64.41517113720457, 61.161230792585066, 49.02885660951614, 82.12843056925796, 28.02139825487321, 29.230385952637857, 32.96100636049132, 39.95583055212447, 74.93745731322946, 60.04193684843548, 9.205492130772567, 46.87958977417886, 95.17760835082552, 36.193393514918746, 54.19275271881398, 63.74465105125551, 79.68891015571059, 52.860894046066406, 42.65633152496481, 36.535756354196714, 34.09653520552718, 58.40316117451063, 104.60637648603849, 42.89316942347648, 45.01412782426444, 99.03659134891261, 38.19256584086891, 45.79457946757092, 67.65689885542892, 68.49188585928158, 104.53251795648198, 63.25809908301019, 165.17081166940903, 91.79780330915949, 71.61289523623829, 139.34030433240463, 58.983235696611864, 53.790015949795794, 40.51381761260738, 79.93354990046254, 103.83642931297001, 48.26695847298578, 36.40556179601989, 68.99618449823491, 35.45186683658109, 55.368964312049556, 45.796462162884225, 42.02559102931264, 73.64148253543694, 32.92603426182049, 39.838444338947475, 57.25151142934602, 47.293490358861504, 49.92348127306016, 45.451632626304274, 74.75990526060257, 113.00194988191804, 37.424881436706166, 121.74562768251033, 39.20150436034803, 72.36095454786783, 60.773959175533754, 86.22342426034723, 51.58556181243721, 37.2827220082, 50.395764521046864, 38.96498843674931, 49.42773055149002, 68.01066797531195, 35.48195665969751, 56.15268418464203, 92.42854175550747, 45.55656198122035, 5.120725711630495, 126.08249682882894, 77.29265041757733, 36.05147481852575, 42.62750618637265, 79.68763605175154, 57.08378885281514, 50.56142315595458, 38.08167844940438, 53.95461042012813, 49.827221737336124, 10.841397882180905, 57.93777245231042, 6.276445024453069, 123.58120600230241, 45.0734163790884, 125.18228119053805, 106.5582182896447, 39.28828997197198, 80.02241141518695, 72.7812831356343, 142.8970297925148, 66.88243851523356, 49.09358027923035, 71.29766739817077, 54.857607677002804, 37.49175751594, 61.193264142394, 44.85656647721225, 53.41223733577929, 37.99639635385087, 63.038263488286795, 68.40392008852429, 85.10057661016127, 34.64830693187976, 85.34903182255162, 40.89944837882791, 56.55061405240605, 45.664838524119205, 82.3696325159046, 43.41726332101766, 5.83150663343873, 63.36846927381801, 77.60271815168912, 58.07301837982258, 33.3422649079389, 45.82807471566937, 46.13238432724701, 27.533012956620315, 62.45347504771889, 64.51806416835929, 53.368201129848195, 36.29562345906039, 61.52886846552628, 103.64391041268073, 48.01011759251766, 73.74451504614169, 42.60113988501378, 92.2137489982497, 17.44582721974525, 40.10702045801638, 90.49330024613792, 81.15199504111811, 94.73160556501527, 59.51190523456865, 84.50886190491643, 34.342602233833084, 11.694784118262358, 74.59433377788551, 58.97865580096246, 39.311103486059345, 11.64324803804929, 76.39222088406108, 76.13622403751663, 77.26954554649762, 63.15809467462067, 41.575494669570276, 63.462360142228974, 55.74294852861604, 52.46730230158737, 43.87887231296799, 94.54050851600127, 45.42000642943922, 49.541057189478614, 48.661548202879864, 91.24417592915172, 46.97599788210576, 62.89729756038777, 48.401991547043274, 76.42053880603085, 93.8741806755767, 119.39986081873275, 61.40210933243081, 48.26097759467203, 55.43407388913968, 69.91201699459606, 87.6906119481201, 4.161418188442323, 62.07658261100854, 49.18500696367323, 65.25332321337915, 46.57904159011836, 84.59600583401146, 36.21846836046893, 65.43314699925865, 41.768303981421774, 158.14254800763325, 48.169525289418615, 124.99405387702156, 69.14723554095818, 65.90152837244938, 72.5171553133078, 53.42786450576715, 99.57528953934039, 48.59140814918502, 81.54520974740485, 114.95298182275201, 64.461346610259, 108.14037282811101, 53.88016808308162, 47.50108916628748, 68.94538717718397, 43.93433344700206, 17.319170085126917, 128.03724932625866, 44.1981396736355, 18.36551309387006, 53.60840746140763, 87.92236065566686, 16.862288906654925, 51.20891488466814, 79.71892029944466, 119.03821551633884, 91.37833443401934, 39.6124016716933, 50.27665102696774, 50.87121005019056, 96.42364368282932, 31.13893698214806, 80.86897302386383, 49.200253466257635, 5.114462130454944, 73.52890237515328, 54.90574630341216, 30.4568545952507, 110.84719656634074, 44.14911253319195, 29.2308886700549, 72.75465360217649, 84.6258206376004, 59.64584416142865, 56.02693082014227, 67.67356275520932, 75.01332591500352, 40.58408839864503, 46.47229692544884, 46.309549678699256, 57.2783014678216, 41.453108072245094, 49.705532409853014, 84.07701328159658, 48.37085619969606, 2.5561177642681177, 43.469590216103754, 73.68391743290152, 2.5923134333763405, 68.03035359877634, 63.701241484948646, 43.85321043648208, 40.347264183578645, 87.67585249953473, 42.2878415973209, 54.878281673327756, 60.93986926240091, 41.07226520874106, 60.905454120208894, 95.35638610026233, 59.82566350685563, 44.75255552424824, 46.581761584390215, 87.99525993876254, 63.869135372537286, 34.85457043483822, 60.23531472171507, 58.98654421473155, 4.882216247583285, 62.8414519876147, 55.89795144706889, 66.09225748938128, 65.36907984806908, 43.087792507616335, 52.92230113865026, 45.29032774426527, 141.04406530934244, 60.248509773255925, 53.837929742584116, 43.43270857067175, 100.39307089841414, 49.2770900312363, 42.77507360157807, 50.97934793127966, 51.23319182414785, 168.81445499915964, 52.521626994552975, 59.395771743767476, 91.67558125611401, 69.2842923819631, 58.6328419626384, 61.94237642300004, 40.47367610889929, 74.8292773514887, 60.054315459913006, 77.93792131443433, 62.812826282850466, 152.32120202977723, 136.2509643264938, 15.574722538583094, 51.583330625700164, 61.14531841876591, 34.536693831531764, 83.77063627576443, 135.19314477843187, 52.53864673192616, 87.83657177944671, 54.85761448298741, 88.89137146471478, 115.61323502404083, 68.72143841737662, 45.50823654239856, 74.97912062900834, 58.0710154122119, 8.204872000176934, 51.02599816397871, 134.34855505773197, 8.699240581738707, 61.98642086925074, 95.05364772279137, 145.08535181331118, 46.19632621684797, 55.37067912877619, 73.41666068873693, 161.41706417234366, 61.516069508986774, 75.72923557549102, 48.503393304844735, 73.29073931784563, 17.151028443046172, 189.40596335963946, 80.5109029258016, 52.45481436773772, 41.82548822187688, 41.88725267294554, 139.05183775412596, 62.23203741357454, 47.7086579960424, 66.38027353842541, 103.37602093593551, 29.157142457513785, 51.956881743517144, 90.78184103371397, 49.06373322352213, 62.749476043736536, 56.23910336564498, 62.273455378383694, 50.79646248674157, 74.69910798201605, 63.60179154308084, 60.89460077343271, 105.96783797471703, 57.48853182454177, 47.91341875946955, 60.41662842081502, 33.28266456902267, 62.34522599342446, 50.876597449848056, 36.10871154126309, 39.9926050836341, 11.952734354414831, 61.06967518904165, 49.76536681366055, 49.0636066345601, 133.74944946150634, 47.150709003250725, 85.99286006438632, 46.262136601689164, 46.68288425268064, 145.73000673516557, 125.61810370324307, 65.20223913372803, 65.62551834936633, 87.90710575973961, 53.0354635735692, 42.60216192255459, 121.65552396892983, 87.41536541296455, 7.146531903171943, 88.15295512388688, 101.46683488539516, 72.31670348915311, 74.44577852568445, 6.804811533604963, 53.61238005698927, 79.22701412827821, 50.621103266236894, 56.35671701335983, 103.6412332154946, 94.84410718798269, 59.88723489312559, 59.1802616872049, 84.88381635737588, 120.5600098680534, 133.25463446307145, 53.20008021480338, 49.7982524139113, 48.32389727534979, 81.9440965770064, 41.58171423330302, 63.360290224507125, 46.89750960128353, 12.393538921314889, 55.836814585320354, 4.218732192638734, 34.343376764482166, 90.18827305338576, 116.44083678040118, 45.63307483046042, 55.8930059443818, 54.100238665799154, 46.05181911658872, 181.35170535951266, 91.73499579627578, 30.994676393250028, 110.86269213159812, 80.66751742683685, 102.32592313708267, 118.21175452714253, 14.100642255426537, 74.71946767453596, 84.52894348560407, 38.72384128199669, 52.05402237147883, 63.25199605724302, 41.84151692228469, 69.23567397815727, 42.72571621784601, 73.09625495232156, 5.13604415642694, 124.76483902182225, 78.27628405886433, 69.96455065948801, 90.37775615378008, 159.7610017757899, 12.921600075993574, 53.17898183321383, 53.82278805213126, 59.192985170862315, 5.146958977830076, 95.31947544620837, 99.08380704532091, 47.54743663878996, 41.02863787950682, 66.84840452484485, 62.81227855625238, 62.35552240868542, 63.947455288398, 99.12596800686907, 55.60280243524941, 15.702282517433881, 50.80122203129989, 48.23070389331526, 56.36836796637306, 50.55980898551402, 45.52074943443328, 93.43318181311543, 88.92549159294097, 57.856815333201844, 71.44763893375054, 67.95043389558963, 70.3025104171384, 59.37825366723006, 70.54167941625202, 77.5646280570723, 51.402350084502395, 54.157609904213125, 53.7093951636465, 51.414953315882734, 59.09886786983226, 56.26398471962171, 70.45799887238888, 68.92936657395522, 90.38865264646522, 89.57410213125758, 55.48044902234506, 5.537867872163554, 52.35899466362144, 71.55808436185757, 75.86086806185831, 51.633357893328906, 68.4457277409156, 57.14984856458676, 54.89633128926657, 57.35382206351211, 54.645267153495965, 63.17696823506595, 69.6524017421351, 15.083963416270064, 43.073843869074544, 96.83651191317003, 132.20821050398516, 54.49327947566729, 169.567543009957, 61.99572859235109, 157.61352981218934, 54.81560512252704, 65.74090680487508, 13.099307304464062, 68.2914834147384, 103.5202691054962, 73.13378459351132, 71.22634292966599, 153.20686274840767, 78.38656243275831, 128.27642207169825, 47.65101930923626, 52.92457138193139, 96.82894307970741, 42.5846169748705, 6.093036722797016, 105.25255446794534, 96.23091204254622, 61.43057352077586, 101.71702049117938, 42.656232517111654, 46.84517268254613, 67.23787087336848, 84.29181159436973, 65.03380266963742, 46.06961431934594, 56.615036436603184, 69.6741082943934, 58.03462696962156, 46.85378909790045, 71.95223500372819, 43.117523708624375, 47.64181254729687, 108.47539187921126, 39.11336173892536, 81.74659278955802, 131.32406385273725, 57.41482006113055, 57.39880510846045, 83.38134927722771, 69.09406012661383, 207.69159834576612, 64.13966825111565, 52.19946932133817, 42.22723539130618, 109.81837396778667, 38.743386954203686, 90.92754813488206, 42.219572954441404, 64.45904294398548, 103.07879390894948, 74.65134052015709, 37.17867032180125, 47.10635604606759, 213.27329768655522, 55.508088435374276, 49.8900915326086, 79.77294378818073, 48.302649463836886, 83.72145321208268, 80.60215669776106, 67.82980145501031, 84.03835308238904, 55.44623407646189, 47.20649858331669, 49.472853684825395, 56.93231331115552, 16.33451847721137, 62.43214086664511, 51.3971145865593, 109.36216142482658, 57.44788806492367, 59.039287595663644, 10.050296695995371, 61.207186580660874, 58.949345760052886, 63.13192090301462, 54.9939730004276, 68.97032604251918, 83.47132685729858, 54.13988706511166, 51.755379257966844, 66.6010794843492, 53.0424568527004, 143.72077693509672, 33.70275509383315, 63.640291893629254, 78.74682996793902, 48.15257681465081, 46.600604297247294, 47.81441798282408, 71.12573292333654, 108.3746436973611, 38.9880933688301, 54.961905371072724, 53.56666439855179, 62.85079570161948, 46.008600488660484, 4.669839744276338, 55.409361735611505, 59.54133637064234, 42.75120671114957, 35.50080055230012, 61.36078953345953, 55.46054181765713, 40.26126704247509, 37.43654031910351, 79.47394366351946, 75.92163428986083, 39.98109550300382, 31.32245743094881, 45.537610465260975, 148.7505861596743, 54.6733309190797, 49.90564956395984, 76.61805343294307, 58.88739009290419, 17.310626111912256, 69.2075231557532, 48.020982476643084, 211.1483070764497, 56.08524530341306, 102.65623814151411, 99.26557859074597, 97.79187555253904, 99.88881478209062, 72.4603354522201, 130.06345405586296, 47.614664829179304, 46.015373340309615, 56.33551619600392, 39.49600430420503, 46.812513567210615, 63.834327533047905, 77.86201440153971, 137.10313473461932, 82.01566599377855, 88.72354610434196, 35.147458665621215, 193.73328371559649, 65.52609947912327, 63.43039267516805, 70.69334457401467, 58.546667493774514, 59.26344090144307, 68.06096054387208, 60.84500901686899, 39.2493442217898, 60.24435377823748, 35.15564161035937, 63.56519149736467, 122.92084595094386, 50.70715093701497, 94.54168893340145, 66.4199646685041, 93.73582774391646, 93.03240625255167, 113.60567830273041, 44.025575066891335, 13.898811827267057, 38.041784222540045, 159.9759090738862, 89.23636018096953, 48.98740343722023, 113.89082627520077, 69.24000774503045, 32.828081161704894, 49.362393943809195, 86.97788638068184, 83.74433616857192, 22.23854709660597, 34.06226389796751, 5.1503023302875865, 104.84437947278508, 70.62452397973857, 98.68112223601761, 45.377971839339445, 57.84287404057296, 62.32142183969405, 64.64213681190932, 66.84735561379365, 97.23764098869229, 68.86809965341916, 62.0137612646193, 88.19626866678455, 45.49649734427099, 71.33886941638006, 109.90724722799982, 14.169589924098158, 56.036046325573764, 100.74494818365915, 104.06153781104943, 90.5725429952936, 49.49435648966738, 72.61078544732763, 58.38844767309733, 80.77818085080361, 74.89760169757832, 97.5514776443813, 153.36527325913534, 52.70163725242176, 52.01253209202187, 216.073871317273, 72.29107115603681, 68.55675560023994, 133.11343457907472, 102.73885583832612, 132.0751911691033, 44.13774546088416, 129.63469434552, 94.12589845951203, 52.20001464569088, 83.15553888654333, 52.86452901855444, 131.535020156559, 96.29759849986073, 63.47753560301202, 74.98288425308992, 45.549079851920496, 79.21307331478506, 81.19782427536497, 68.0731392067872, 40.37306036424359, 51.04749980661956, 118.73191385575751, 41.969009805961136, 6.255100573499363, 58.36539898788757, 104.19848932775659, 54.2153712901187, 46.254674953879835, 58.06692006948734, 104.19462013311178, 60.818540736541806, 99.3597555649323, 72.09783811310751, 90.99374533293968, 66.62594506238719, 85.64474020272816, 6.181968220693581, 53.41247098419378, 43.83990731564278, 58.618798919602696, 58.18915130338422, 62.171834697702174, 54.29146844951018, 67.09994282013102, 65.51299942890907, 55.767324539684736, 55.07507239026142, 61.02989087567798, 43.84572017106356, 52.40064115267765, 77.73431629098356, 57.11667350255337, 61.365243667077614, 83.96648813980353, 157.44494109695958, 91.68322215581412, 120.58542218447364, 67.81659994791183, 95.26725202234056, 45.87874648997902, 126.25636424591337, 45.62466833925568, 5.73274711502059, 40.476598029525135, 62.4026273393779, 159.6009501990415, 90.77353125939857, 48.94683618369491, 78.34133374088786, 70.42543956446276, 46.67922307234691, 43.690072039917496, 120.68979265209516, 86.2111978072361, 46.178583739208385, 55.527748925891565, 150.16257000038115, 51.87086138447365, 55.659183919934655, 70.38450167572643, 120.6299497091825, 56.56345252429925, 71.4485437134202, 76.20946343915075, 41.841766136459256, 51.32270273120103, 49.49201911906682, 70.92221569553156, 84.57130162734562, 55.29082275066604, 56.58007741210063, 10.023765209484338, 46.207439448198, 40.48727648617576, 55.73481744564862, 32.57860273399745, 52.070230208006706, 49.469896809073134, 53.02011612477612, 58.088596720747645, 45.88204017237777, 185.0682560580789, 49.26532909564464, 47.97591452861268, 88.25725534209779, 70.12624306675781, 89.65081151089609, 101.09868413343179, 38.501323987777525, 46.09603657653028, 172.1453021628736, 37.87910078827566, 54.15009501445857, 63.40821500338119, 70.14388386153054, 58.18533159677571, 95.36848485605009, 87.66949660159226, 95.91168982508798, 51.685052381113834, 6.692851759193627, 154.06294490088516, 53.13867897924731, 53.92108948028911, 68.6489772031704, 53.321168267148195, 91.90086759540836, 59.576440238685755, 117.60607174964102, 137.52772627345368, 57.26183860169051, 183.55420646886694, 57.16284944252194, 162.5602144049505, 48.86915990578842, 83.77760016536317, 46.726911910412156, 51.619982029957654, 117.13697330413613, 36.72314986195859, 57.69074479488756, 35.36939678630193, 47.25441349054354, 66.74255136766911, 51.268056461336016, 197.90160301845094, 70.83092508403816, 88.3850028532676, 131.29777108776273, 71.26421618371397, 89.7829706100583, 84.35536345176386, 22.446069659949117, 51.872073259589946, 61.172699426725785, 48.4696192370407, 132.8324416972373, 67.05773562853682, 57.347507074728355, 65.77655963200561, 73.09321510041576, 60.03289198441646, 98.54710778342888, 47.90923011602839, 59.616062566674294, 168.6860419798981, 186.90504716258476, 61.94986907488438, 56.673739088841295, 63.422475425307674, 102.42800229961675, 110.49857752616992, 76.57891702873681, 62.94452049429174, 103.65861579551644, 220.5013354231681, 94.14094608241943, 79.85828128379516, 42.39793924506555, 11.465210518547327, 73.25752475425611, 63.02543170684537, 72.27886429213858, 4.551065095009679, 63.260012482462166, 49.060779053727956, 44.99667461646224, 147.26876190734276, 113.90047861516635, 57.885433801582806, 56.6248402410105, 60.370321256413554, 78.85982752429668, 55.077423934605406, 82.46438926800802, 56.02622053284792, 101.02583665726682, 82.75087767743547, 95.59988295165336, 163.68575391725807, 75.06749223033295, 62.709917280582204, 68.41644597506311, 110.11323655413014, 147.3626575343086, 65.96229123459358, 120.63186175034826, 220.1051161333457, 126.1061790785196, 127.27128742144906, 55.389152020095445, 82.50509858627464, 121.48235190227666, 92.98671534407559, 223.41038452664003, 46.316773596314626, 34.638903609853834, 100.65850297861023, 37.10947333169813, 60.05376626274489, 86.14574661672876, 52.7740925271958, 96.3001944344141, 46.098862604058965, 55.32829791674519, 256.80396587277676, 90.662321066569, 80.35621983164208, 48.47015593579235, 24.74520321324076, 100.39144429804372, 55.26713942387922, 61.66644172669334, 73.29714443847959, 95.23071362393573, 108.92458465386238, 45.26631341673433, 67.41708016624932, 142.91251769754575, 66.35211009891259, 76.39264204382476, 58.185921032353136, 73.24844080163952, 49.195469843855044, 64.10080353440466, 175.1382859685084, 63.72927866189657, 35.57346906163205, 41.29516560202995, 49.88188719024134, 139.48724167407065, 75.94549355311636, 262.70164063331094, 82.21597539061905, 125.98514537352392, 144.79488311586255, 64.66247297775521, 49.52053335785806, 113.26917978407445, 134.95706543577333, 14.562917192904465, 115.22800004471031, 68.49478764255132, 71.0835547890013, 66.5618353064941, 48.824117808068124, 96.09310056223063, 73.87151126487312, 70.78501304997873, 94.96413621854725, 75.84591144864592, 89.53337274634207, 120.12943096547478, 116.13008292170846, 60.15170468970962, 115.61762005162159, 5.943174623394112, 91.65496038826475, 16.04733601351805, 111.09071559410073, 72.57039453289896, 10.278295793042567, 90.1233505446739, 89.88917571445127, 102.03189432978029, 159.51642108933012, 61.90965886113531, 42.91253682888495, 131.41579096338597, 80.86528369834929, 69.29266039061119, 68.26110599983315, 173.901300489019, 51.10260863758729, 91.16001753454292, 75.14907399110957, 84.96894471632451, 55.820926627929374, 63.33228294533847, 56.19534810982903, 50.00915664768241, 112.65075047060144, 101.10977360042983, 85.23587877511055, 112.06888140351128, 193.1041179997515, 48.898479270612526, 85.453535431648, 75.14011283730956, 12.843269866521473, 72.45961023935499, 35.786811923575605, 66.36774973275372, 60.56655648198822, 45.05264456591042, 66.72229341722746, 86.58934703327512, 112.09134185570866, 78.95338615914277, 83.8132802599488, 8.110274087621717, 72.20681726413277, 104.95112973844998, 169.224905206235, 43.93844390766806, 116.4968715209654, 120.03465629266101, 45.90358088008543, 94.11100946187031, 47.521622289971866, 79.11097884818729, 289.5663744948701, 7.350823861290871, 93.24917125319374, 83.02627282677247, 72.50363670568308, 49.91397503285384, 71.46567405793476, 56.66446043410312, 76.00084956291461, 43.45412284297406, 60.51593522113302, 91.82839103296418, 6.66021293330951, 42.285679650928536, 94.6793564410611, 104.32902783554243, 58.98169796831002, 172.19297997724507, 147.73402233841466, 68.15441540143324, 74.16973614876369, 106.90372845042366, 50.966902225539215, 70.68044502187051, 65.4549334003847, 63.43935490860792, 8.57500675311728, 165.55164177842278, 8.78843189539218, 90.89176333617804, 89.68178995132192, 110.3971313279634, 6.409267786696905, 88.12615041647567, 76.98305567904056, 112.30437660709337, 78.12776745517122, 40.61035493857145, 149.537304635548, 71.41372464212714, 33.091382524766495, 71.18569198564317, 36.33562176957706, 81.67666442759386, 128.33407123073198, 253.2868412081136, 85.17759347034728, 180.15831142823603, 96.52169309693386, 71.9910889840556, 98.48637750112017, 45.95424866190718, 6.934517503609007, 75.62059549512095, 145.19005736480676, 89.97853512582242, 33.64424204642451, 50.73443616525907, 127.04225350765218, 60.08166654876116, 159.52409517805262, 95.06418501044139, 104.43722234109441, 93.71009773697013, 95.88217248756429, 44.69594409120601, 53.79616440896037, 65.59892139100975, 77.21324657829796, 7.978159302831104, 65.35023506647288, 109.19439821204801, 49.40115012180179, 76.67446546746129, 134.00959440193282, 70.21644898879924, 53.682125570771646, 90.51604143213166, 49.55104042761292, 223.94590320606486, 78.19100484876962, 116.19838012716048, 174.2582936255353, 87.65731437356261, 7.494661029894933, 54.17844737475916, 40.85141137443402, 74.75128125943922, 76.99744362939917, 43.062223468093904, 83.67424021581455, 102.13295230365406, 101.27142553354506, 51.283642634709224, 10.357862632697561, 77.52046290997497, 88.70310615728484, 29.99622228486723, 113.52969107773386, 67.56001486598274, 113.58662707169948, 46.48491332504641, 98.59370982676138, 72.59512910030821, 87.3354820630001, 130.92268450797366, 77.9396548984418, 67.18607828768562, 11.38942380002127, 145.64929011142561, 62.67939686450689, 111.5342896482136, 130.01457306669298, 70.9184026023235, 47.43729689495857, 177.09815653053798, 25.278971143817145, 115.08822368938519, 60.42402176855104, 54.90582126610887, 55.84748236004461, 94.61022992204764, 65.50415480666092, 44.928275733515854, 74.9836317781259, 132.0586329590945, 34.36567434926975, 78.70006575922186, 225.0480234419256, 218.5916517868651, 108.02898665924906, 7.906984975246746, 83.25552728227844, 99.0713919211378, 219.23613694665144, 164.35875819321697, 47.97310626297119, 84.25519598050715, 87.49243948123943, 131.70188687908555, 133.52375944243713, 123.23551075348657, 122.73234902307078, 120.79349004973488, 57.29364439854882, 185.99733830763074, 224.92029554208906, 39.210072000052406, 62.93633254681876, 60.46244745793681, 92.22525829953526, 62.6162939849401, 114.73801872347673, 80.09263479530262, 81.05472194238124, 124.66327312471621, 72.68550522108187, 44.2563054886675, 71.65030077139244, 46.29158444535554, 47.66073985306069, 66.39645775464575, 117.89053589356836, 207.80953928715064, 207.7044561041148, 122.76353110899763, 139.12529163804805, 48.16420439442528, 65.54089831665958, 61.48936907252984, 56.84081044471952, 126.36851428032828, 108.72929217807884, 86.1748919207379, 67.8564610640654, 82.01154848131144, 429.46656444634345, 72.60822940081673, 73.18152312785742, 54.84965974403139, 120.13251052817587, 86.51327806311627, 80.46093375761129, 77.44458336259503, 83.43297468146021, 48.44510491507894, 62.89134742073523, 58.120530249368436, 79.47879056829521, 41.86477601153319, 51.719343485944584, 67.06324348183469, 71.6718718386472, 68.24363425784196, 38.15271477383369, 64.04904932980082, 118.81226505</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>126.7334906291962</v>
+      </c>
+      <c r="S22" t="n">
+        <v>94.83142804184381</v>
+      </c>
+      <c r="T22" t="n">
+        <v>100</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>[47.39111328125, 253.44850158691406, 49.47150802612305, 375.9620361328125, 284.6610107421875, 33.47676467895508, 78.76140594482422, 216.46347045898438, 212.0768585205078, 49.723628997802734, 79.77813720703125, 102.9930419921875, 98.9692611694336, 93.7397689819336, 224.87966918945312, 99.90669250488281, 52.09374237060547, 54.72404861450195, 72.45823669433594, 59.878665924072266, 55.13337326049805, 62.51871871948242, 45.34178924560547, 554.0001831054688, 37.80451965332031, 110.55432891845703, 86.283203125, 127.95295715332031, 49.40147399902344, 367.1196594238281, 244.6734619140625, 62.736412048339844, 67.48023986816406, 48.4473876953125, 208.5186767578125, 65.86968994140625, 11.22708797454834, 94.2147216796875, 49.0908317565918, 124.61121368408203, 294.46875, 51.59496307373047, 175.61495971679688, 47.59966278076172, 212.5167999267578, 35.484012603759766, 294.880615234375, 110.87374114990234, 145.59091186523438, 74.22002410888672, 60.8696403503418, 107.08590698242188, 72.44198608398438, 147.9236602783203, 399.0144348144531, 145.6873321533203, 39.43885803222656, 148.90916442871094, 74.16263580322266, 121.02523040771484, 62.025596618652344, 180.46072387695312, 149.95199584960938, 104.25252532958984, 104.4835205078125, 73.10602569580078, 39.25535202026367, 41.0587158203125, 168.33514404296875, 136.59359741210938, 75.11053466796875, 61.6622428894043, 128.832763671875, 95.94859313964844, 72.2741470336914, 85.43560791015625, 180.25375366210938, 48.586917877197266, 383.87530517578125, 257.08526611328125, 260.6573791503906, 137.83700561523438, 68.89118957519531, 76.9351806640625, 63.021663665771484, 121.99996948242188, 82.78441619873047, 128.0511016845703, 237.3063507080078, 83.85111999511719, 81.3267593383789, 139.53451538085938, 119.27399444580078, 71.76697540283203, 59.674320220947266, 160.76893615722656, 101.19999694824219, 85.00640106201172, 247.19996643066406, 124.43270874023438]</t>
+        </is>
+      </c>
     </row>
     <row r="1048557" ht="12.75" customHeight="1" s="2"/>
     <row r="1048558" ht="12.75" customHeight="1" s="2"/>

--- a/Work/policy/runs_results.xlsx
+++ b/Work/policy/runs_results.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="2">
@@ -1943,77 +1943,1127 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>p0.5srandom1603</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>2026-03-27 19:51:50</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ppo</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>100</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="E22" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>83.88271367607108</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="3" t="n">
         <v>63.74470914996073</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="3" t="n">
         <v>102.8316526034163</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3" t="n">
         <v>4859</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.7255805133167887, 1.2590380581255172, 1.4292546412873066, 1.241618146071886, 2.282943626026312, 0.9768752613824513, 0.38309490460645185, 1.5853552159118565, 0.9180291537048838, 0.7369000508819065, 1.0767731688400461, 0.6788183497080192, 0.8284281168854323, 1.3409171515683538, 1.3323504228347727, 1.2176858075086456, 1.1755294216457342, 0.5281283614655377, 0.7485529059529655, 1.8745155658880739, 1.10442434813151, 0.3312317015949828, 1.439982706453322, 0.5665682105246186, 1.909647824458278, 0.45727330482563033, 1.6913385842787592, 1.5924358150136717, 0.8115756305968403, 1.5089984430550982, 2.503713164941037, 1.2123388336761873, 2.517874342610418, 1.6924750983472763, 1.6557588525187519, 1.6817406468312255, 1.188792140463649, 1.4658578936553923, 1.7641420110709924, 1.4564667931581934, 2.2339365254725494, 1.461380088578911, 1.1831225388418751, 1.6888359413121687, 1.902044595926248, 3.3432901470990837, 1.3150830928111577, 1.697528267263924, 2.229192119170013, 1.742152720460141, 0.9983572529474544, 2.170162002924203, 0.5226499370492278, 1.5885789702508448, 1.389439853200526, 1.6871010166058222, 3.8533454927562985, 3.4476197359838476, 0.8710867177051876, 1.5192535082057732, 0.9228482032077159, 0.6738060700380119, 2.9551285561281033, 1.6553857046773008, 2.889137170807501, 1.5209543537073071, 2.316086044153534, 2.179372778400217, 2.6208761090186914, 2.6558739128761375, 1.686888501691304, 2.455099644470165, 1.9389601130721041, 4.0967666214649405, 3.8622346631558893, 1.8475085828376425, 1.8458877661416657, 3.5699377383112916, 3.2436993253874937, 5.392477334117146, 3.6401103562706796, 2.7319299598886464, 2.7122115721478126, 4.800962172862329, 3.3671934672683754, 3.081820975166846, 2.1012882706947233, 2.374789829950085, 4.102353788161767, 1.6701086550745299, 3.4094912694779356, 3.3179362716363037, 4.932464514578133, 1.8205873361964497, 2.6942526947224392, 6.6949899058691935, 4.270786809636794, 2.3104726703633456, 4.139626028801318, 4.807938657458377, 3.2725626033767243, 2.1725492778461573, 3.703398149089798, 10.768031506466642, 7.120179853231581, 7.428746774579902, 3.4337351333583865, 6.865335982146324, 4.3317919014881205, 2.3462807210267034, 7.811544883752805, 5.078478200159672, 7.879455295004212, 6.399357131902911, 4.258066783212949, 3.406036702936921, 9.268458798716336, 4.254964755159608, 6.099631111622319, 2.454812897369196, 2.517082341975786, 4.849143750974082, 7.212848092290718, 4.236862189235778, 4.281567528739331, 3.592273577160496, 3.3352415263141157, 8.175031297619984, 3.8097068206792404, 6.462376092976334, 4.557652833313409, 4.964869234840876, 2.082149642747466, 3.8041453979546325, 3.9669821993546197, 7.010624889040711, 2.0633986815901197, 6.730562014701173, 6.254975524739278, 3.726249868305762, 5.266810620462419, 8.573181197354439, 11.493413639103093, 3.783527415737813, 5.837273576161085, 8.74182912545239, 11.229806922912589, 13.024777698553004, 9.49582428673251, 5.779008500322163, 3.894184188225597, 13.295430281473529, 14.33791883102146, 3.0683631527727635, 6.498518304679644, 7.769186743976527, 12.382973841992822, 6.886323899691744, 11.804929713959456, 6.788511362461539, 8.815287258726093, 9.519183920170548, 7.140346719712407, 9.805097297799644, 5.906815928916916, 11.406369141852535, 11.710887682871675, 5.747131061552977, 7.300474224019662, 11.896768891227861, 7.6963438471321055, 12.49210471528493, 8.850174244708642, 6.356479199131453, 9.837578388148726, 10.039571573107501, 12.915349499064527, 12.067535881076033, 16.575893997869752, 15.012907084459382, 18.863509931091254, 12.118534943272271, 7.751212079966364, 11.959103660893799, 21.323203606363524, 18.58349501354173, 12.745408517565124, 18.404596513781666, 5.750370733239165, 33.89976202844353, 30.47118998176494, 8.361805107966184, 9.48121498638616, 30.110039963151873, 18.649259224485913, 14.494807913963948, 23.995377103422904, 12.896050873718183, 15.986617351131814, 20.251914529877, 23.04001367036304, 16.94514029097562, 20.624300316468002, 8.937353104475172, 29.770885991703505, 18.6640329817582, 17.504140648410484, 6.893549621267247, 16.50825153407385, 11.14216745139596, 15.436264883184236, 21.400492535011082, 18.95652130601516, 18.593494286448642, 27.373374676278836, 22.262196963865904, 25.8013330280672, 29.789546982678203, 16.754603259283048, 27.63203428461334, 27.684986134247026, 18.66882673549191, 21.080738766233974, 11.924421516327191, 21.423545847774744, 26.063687305205043, 11.947100752100534, 19.49285919775795, 9.248744667631861, 17.986375714316168, 26.22076851143668, 20.08619066667692, 20.658895768699242, 36.60262595055289, 22.578766122258468, 12.429311949865294, 10.74075749665999, 35.084515418340175, 43.78689524531291, 34.200934773825395, 13.822331432721045, 18.000338443168225, 8.435736420533757, 41.14388489856603, 18.090911633839738, 13.143236638989556, 21.177833554148226, 51.478334547754855, 21.767311517427125, 43.71970391399368, 30.708406484039283, 29.7612933891195, 13.444918934521164, 24.812959048812004, 22.640194076562043, 8.228940133210084, 28.811100324081973, 23.86181113955181, 24.138449435838403, 50.53456361068117, 29.8949829148841, 25.009674746042943, 40.00439770670074, 15.018347985011555, 19.793217211065016, 30.142769387855083, 21.057369692474815, 24.759021061453492, 34.45333646520076, 29.78572785560014, 42.58161284626438, 4.355630202918045, 28.82097571875096, 20.023775420492765, 34.944917999422394, 23.943967232336405, 40.03676878472161, 22.20129477345941, 43.284337537070584, 20.81056930028349, 8.13476996856156, 38.108228530435234, 31.349352585340796, 26.3289119156141, 24.43404997274871, 28.866013097834323, 36.93075784361356, 4.600968196748113, 29.191213106165115, 23.362105433260826, 30.021331674437494, 16.80678210992021, 23.845282346215548, 36.23265523469241, 40.70624924012992, 19.288485352685072, 24.06007327660415, 35.233857632601065, 60.27440973758814, 9.431266810013105, 18.215205189385266, 33.106878746726416, 28.494198854099725, 30.54015643080856, 30.09587410449068, 40.30540512773184, 36.307460095497305, 52.118152348521875, 35.44900534151593, 17.667938706649956, 22.511843513266964, 22.8148212785027, 9.287541385468835, 33.34516273263217, 46.460905306986525, 23.38666788282658, 2.7204586461810463, 6.633582773684648, 43.956520616527065, 32.40658885062601, 2.520094691612072, 24.265535375726227, 23.395527995576387, 53.52720898353806, 49.247650006231986, 25.539567264291257, 51.14230186432069, 19.02867376448494, 24.82140082855724, 81.12447489808262, 28.571411418233613, 39.077220297299064, 36.1453242740432, 23.11765630359107, 57.84372072398672, 59.29875437067163, 44.84919196162148, 39.578628879939295, 5.24060317180577, 27.992546599718967, 49.89634364208571, 68.09597212144541, 28.79021147054738, 36.15605191978831, 39.55119307583011, 33.40236586837063, 45.776319259480765, 13.731422115454096, 37.642567718470275, 63.75138993352665, 25.16715075719642, 3.288822586235904, 21.119868933114674, 28.920254425197793, 26.72587079664852, 28.22184939372021, 4.559310458864519, 38.127978307776175, 23.56338265546626, 45.24784147480285, 23.415639443935934, 41.331266568491486, 57.483093284962415, 62.294706423418695, 30.16719181687896, 35.17964254975877, 29.6921972381754, 27.42989372642123, 4.086680780617179, 49.7777159118346, 64.1497578851316, 40.9801732775763, 115.21630838655544, 68.60540425641962, 66.0061205744677, 22.81195871489726, 63.55369380699861, 33.082207556680196, 29.73544977627362, 39.6548097373243, 20.74649393164839, 23.563758972863354, 51.70467934652371, 44.805395731851966, 54.107577398537714, 73.13973118947385, 59.199482937080724, 19.87213993852872, 3.363110493636782, 33.58230531001054, 44.220588439682544, 70.07682432848547, 80.58740303264213, 39.400803619253736, 34.53009129765651, 32.089702329966975, 25.503068629709897, 41.23091354130749, 72.15054077302798, 73.58990616953126, 42.54057797257046, 73.18601556772641, 25.74520722189096, 34.406100224514404, 64.9574855726883, 54.29721857436314, 62.728933668906066, 36.9986531907474, 42.57112135436556, 52.032527066724974, 37.033090543916956, 9.66078733730994, 10.647225339311984, 31.471670500058412, 36.605844268432236, 32.28107443832828, 75.22560196435964, 51.692195265533826, 101.45592247053621, 72.01523198574593, 49.22081681035032, 44.215637719026155, 104.77968582455493, 24.251092211225572, 47.499146068825944, 25.738871587086678, 30.07656999636619, 74.74434406166667, 49.856642558338024, 112.89072184653755, 29.118790712305966, 15.101023024087873, 8.780127489912408, 43.00941004584761, 72.99042249410076, 58.56657816307762, 25.774090854722328, 43.46648513658884, 32.52806764619429, 33.706535074144185, 61.19795318115446, 48.655650834780715, 66.64396726517998, 60.482465332596504, 53.55335592261415, 49.238362156022234, 72.6690034139931, 27.1973005364806, 10.867586002920808, 56.333996776202184, 54.300076141568454, 26.55489356469748, 85.62387842932358, 75.01735809102402, 33.10361951598599, 39.641007182558106, 42.11788264261004, 31.530666496253836, 35.72975740082657, 49.156256002700005, 33.267994204208854, 37.126666917246176, 30.752212656470196, 45.435964468743926, 48.790679693351166, 34.492769603785895, 47.11446337878384, 50.86180720546212, 64.41517113720457, 61.161230792585066, 49.02885660951614, 82.12843056925796, 28.02139825487321, 29.230385952637857, 32.96100636049132, 39.95583055212447, 74.93745731322946, 60.04193684843548, 9.205492130772567, 46.87958977417886, 95.17760835082552, 36.193393514918746, 54.19275271881398, 63.74465105125551, 79.68891015571059, 52.860894046066406, 42.65633152496481, 36.535756354196714, 34.09653520552718, 58.40316117451063, 104.60637648603849, 42.89316942347648, 45.01412782426444, 99.03659134891261, 38.19256584086891, 45.79457946757092, 67.65689885542892, 68.49188585928158, 104.53251795648198, 63.25809908301019, 165.17081166940903, 91.79780330915949, 71.61289523623829, 139.34030433240463, 58.983235696611864, 53.790015949795794, 40.51381761260738, 79.93354990046254, 103.83642931297001, 48.26695847298578, 36.40556179601989, 68.99618449823491, 35.45186683658109, 55.368964312049556, 45.796462162884225, 42.02559102931264, 73.64148253543694, 32.92603426182049, 39.838444338947475, 57.25151142934602, 47.293490358861504, 49.92348127306016, 45.451632626304274, 74.75990526060257, 113.00194988191804, 37.424881436706166, 121.74562768251033, 39.20150436034803, 72.36095454786783, 60.773959175533754, 86.22342426034723, 51.58556181243721, 37.2827220082, 50.395764521046864, 38.96498843674931, 49.42773055149002, 68.01066797531195, 35.48195665969751, 56.15268418464203, 92.42854175550747, 45.55656198122035, 5.120725711630495, 126.08249682882894, 77.29265041757733, 36.05147481852575, 42.62750618637265, 79.68763605175154, 57.08378885281514, 50.56142315595458, 38.08167844940438, 53.95461042012813, 49.827221737336124, 10.841397882180905, 57.93777245231042, 6.276445024453069, 123.58120600230241, 45.0734163790884, 125.18228119053805, 106.5582182896447, 39.28828997197198, 80.02241141518695, 72.7812831356343, 142.8970297925148, 66.88243851523356, 49.09358027923035, 71.29766739817077, 54.857607677002804, 37.49175751594, 61.193264142394, 44.85656647721225, 53.41223733577929, 37.99639635385087, 63.038263488286795, 68.40392008852429, 85.10057661016127, 34.64830693187976, 85.34903182255162, 40.89944837882791, 56.55061405240605, 45.664838524119205, 82.3696325159046, 43.41726332101766, 5.83150663343873, 63.36846927381801, 77.60271815168912, 58.07301837982258, 33.3422649079389, 45.82807471566937, 46.13238432724701, 27.533012956620315, 62.45347504771889, 64.51806416835929, 53.368201129848195, 36.29562345906039, 61.52886846552628, 103.64391041268073, 48.01011759251766, 73.74451504614169, 42.60113988501378, 92.2137489982497, 17.44582721974525, 40.10702045801638, 90.49330024613792, 81.15199504111811, 94.73160556501527, 59.51190523456865, 84.50886190491643, 34.342602233833084, 11.694784118262358, 74.59433377788551, 58.97865580096246, 39.311103486059345, 11.64324803804929, 76.39222088406108, 76.13622403751663, 77.26954554649762, 63.15809467462067, 41.575494669570276, 63.462360142228974, 55.74294852861604, 52.46730230158737, 43.87887231296799, 94.54050851600127, 45.42000642943922, 49.541057189478614, 48.661548202879864, 91.24417592915172, 46.97599788210576, 62.89729756038777, 48.401991547043274, 76.42053880603085, 93.8741806755767, 119.39986081873275, 61.40210933243081, 48.26097759467203, 55.43407388913968, 69.91201699459606, 87.6906119481201, 4.161418188442323, 62.07658261100854, 49.18500696367323, 65.25332321337915, 46.57904159011836, 84.59600583401146, 36.21846836046893, 65.43314699925865, 41.768303981421774, 158.14254800763325, 48.169525289418615, 124.99405387702156, 69.14723554095818, 65.90152837244938, 72.5171553133078, 53.42786450576715, 99.57528953934039, 48.59140814918502, 81.54520974740485, 114.95298182275201, 64.461346610259, 108.14037282811101, 53.88016808308162, 47.50108916628748, 68.94538717718397, 43.93433344700206, 17.319170085126917, 128.03724932625866, 44.1981396736355, 18.36551309387006, 53.60840746140763, 87.92236065566686, 16.862288906654925, 51.20891488466814, 79.71892029944466, 119.03821551633884, 91.37833443401934, 39.6124016716933, 50.27665102696774, 50.87121005019056, 96.42364368282932, 31.13893698214806, 80.86897302386383, 49.200253466257635, 5.114462130454944, 73.52890237515328, 54.90574630341216, 30.4568545952507, 110.84719656634074, 44.14911253319195, 29.2308886700549, 72.75465360217649, 84.6258206376004, 59.64584416142865, 56.02693082014227, 67.67356275520932, 75.01332591500352, 40.58408839864503, 46.47229692544884, 46.309549678699256, 57.2783014678216, 41.453108072245094, 49.705532409853014, 84.07701328159658, 48.37085619969606, 2.5561177642681177, 43.469590216103754, 73.68391743290152, 2.5923134333763405, 68.03035359877634, 63.701241484948646, 43.85321043648208, 40.347264183578645, 87.67585249953473, 42.2878415973209, 54.878281673327756, 60.93986926240091, 41.07226520874106, 60.905454120208894, 95.35638610026233, 59.82566350685563, 44.75255552424824, 46.581761584390215, 87.99525993876254, 63.869135372537286, 34.85457043483822, 60.23531472171507, 58.98654421473155, 4.882216247583285, 62.8414519876147, 55.89795144706889, 66.09225748938128, 65.36907984806908, 43.087792507616335, 52.92230113865026, 45.29032774426527, 141.04406530934244, 60.248509773255925, 53.837929742584116, 43.43270857067175, 100.39307089841414, 49.2770900312363, 42.77507360157807, 50.97934793127966, 51.23319182414785, 168.81445499915964, 52.521626994552975, 59.395771743767476, 91.67558125611401, 69.2842923819631, 58.6328419626384, 61.94237642300004, 40.47367610889929, 74.8292773514887, 60.054315459913006, 77.93792131443433, 62.812826282850466, 152.32120202977723, 136.2509643264938, 15.574722538583094, 51.583330625700164, 61.14531841876591, 34.536693831531764, 83.77063627576443, 135.19314477843187, 52.53864673192616, 87.83657177944671, 54.85761448298741, 88.89137146471478, 115.61323502404083, 68.72143841737662, 45.50823654239856, 74.97912062900834, 58.0710154122119, 8.204872000176934, 51.02599816397871, 134.34855505773197, 8.699240581738707, 61.98642086925074, 95.05364772279137, 145.08535181331118, 46.19632621684797, 55.37067912877619, 73.41666068873693, 161.41706417234366, 61.516069508986774, 75.72923557549102, 48.503393304844735, 73.29073931784563, 17.151028443046172, 189.40596335963946, 80.5109029258016, 52.45481436773772, 41.82548822187688, 41.88725267294554, 139.05183775412596, 62.23203741357454, 47.7086579960424, 66.38027353842541, 103.37602093593551, 29.157142457513785, 51.956881743517144, 90.78184103371397, 49.06373322352213, 62.749476043736536, 56.23910336564498, 62.273455378383694, 50.79646248674157, 74.69910798201605, 63.60179154308084, 60.89460077343271, 105.96783797471703, 57.48853182454177, 47.91341875946955, 60.41662842081502, 33.28266456902267, 62.34522599342446, 50.876597449848056, 36.10871154126309, 39.9926050836341, 11.952734354414831, 61.06967518904165, 49.76536681366055, 49.0636066345601, 133.74944946150634, 47.150709003250725, 85.99286006438632, 46.262136601689164, 46.68288425268064, 145.73000673516557, 125.61810370324307, 65.20223913372803, 65.62551834936633, 87.90710575973961, 53.0354635735692, 42.60216192255459, 121.65552396892983, 87.41536541296455, 7.146531903171943, 88.15295512388688, 101.46683488539516, 72.31670348915311, 74.44577852568445, 6.804811533604963, 53.61238005698927, 79.22701412827821, 50.621103266236894, 56.35671701335983, 103.6412332154946, 94.84410718798269, 59.88723489312559, 59.1802616872049, 84.88381635737588, 120.5600098680534, 133.25463446307145, 53.20008021480338, 49.7982524139113, 48.32389727534979, 81.9440965770064, 41.58171423330302, 63.360290224507125, 46.89750960128353, 12.393538921314889, 55.836814585320354, 4.218732192638734, 34.343376764482166, 90.18827305338576, 116.44083678040118, 45.63307483046042, 55.8930059443818, 54.100238665799154, 46.05181911658872, 181.35170535951266, 91.73499579627578, 30.994676393250028, 110.86269213159812, 80.66751742683685, 102.32592313708267, 118.21175452714253, 14.100642255426537, 74.71946767453596, 84.52894348560407, 38.72384128199669, 52.05402237147883, 63.25199605724302, 41.84151692228469, 69.23567397815727, 42.72571621784601, 73.09625495232156, 5.13604415642694, 124.76483902182225, 78.27628405886433, 69.96455065948801, 90.37775615378008, 159.7610017757899, 12.921600075993574, 53.17898183321383, 53.82278805213126, 59.192985170862315, 5.146958977830076, 95.31947544620837, 99.08380704532091, 47.54743663878996, 41.02863787950682, 66.84840452484485, 62.81227855625238, 62.35552240868542, 63.947455288398, 99.12596800686907, 55.60280243524941, 15.702282517433881, 50.80122203129989, 48.23070389331526, 56.36836796637306, 50.55980898551402, 45.52074943443328, 93.43318181311543, 88.92549159294097, 57.856815333201844, 71.44763893375054, 67.95043389558963, 70.3025104171384, 59.37825366723006, 70.54167941625202, 77.5646280570723, 51.402350084502395, 54.157609904213125, 53.7093951636465, 51.414953315882734, 59.09886786983226, 56.26398471962171, 70.45799887238888, 68.92936657395522, 90.38865264646522, 89.57410213125758, 55.48044902234506, 5.537867872163554, 52.35899466362144, 71.55808436185757, 75.86086806185831, 51.633357893328906, 68.4457277409156, 57.14984856458676, 54.89633128926657, 57.35382206351211, 54.645267153495965, 63.17696823506595, 69.6524017421351, 15.083963416270064, 43.073843869074544, 96.83651191317003, 132.20821050398516, 54.49327947566729, 169.567543009957, 61.99572859235109, 157.61352981218934, 54.81560512252704, 65.74090680487508, 13.099307304464062, 68.2914834147384, 103.5202691054962, 73.13378459351132, 71.22634292966599, 153.20686274840767, 78.38656243275831, 128.27642207169825, 47.65101930923626, 52.92457138193139, 96.82894307970741, 42.5846169748705, 6.093036722797016, 105.25255446794534, 96.23091204254622, 61.43057352077586, 101.71702049117938, 42.656232517111654, 46.84517268254613, 67.23787087336848, 84.29181159436973, 65.03380266963742, 46.06961431934594, 56.615036436603184, 69.6741082943934, 58.03462696962156, 46.85378909790045, 71.95223500372819, 43.117523708624375, 47.64181254729687, 108.47539187921126, 39.11336173892536, 81.74659278955802, 131.32406385273725, 57.41482006113055, 57.39880510846045, 83.38134927722771, 69.09406012661383, 207.69159834576612, 64.13966825111565, 52.19946932133817, 42.22723539130618, 109.81837396778667, 38.743386954203686, 90.92754813488206, 42.219572954441404, 64.45904294398548, 103.07879390894948, 74.65134052015709, 37.17867032180125, 47.10635604606759, 213.27329768655522, 55.508088435374276, 49.8900915326086, 79.77294378818073, 48.302649463836886, 83.72145321208268, 80.60215669776106, 67.82980145501031, 84.03835308238904, 55.44623407646189, 47.20649858331669, 49.472853684825395, 56.93231331115552, 16.33451847721137, 62.43214086664511, 51.3971145865593, 109.36216142482658, 57.44788806492367, 59.039287595663644, 10.050296695995371, 61.207186580660874, 58.949345760052886, 63.13192090301462, 54.9939730004276, 68.97032604251918, 83.47132685729858, 54.13988706511166, 51.755379257966844, 66.6010794843492, 53.0424568527004, 143.72077693509672, 33.70275509383315, 63.640291893629254, 78.74682996793902, 48.15257681465081, 46.600604297247294, 47.81441798282408, 71.12573292333654, 108.3746436973611, 38.9880933688301, 54.961905371072724, 53.56666439855179, 62.85079570161948, 46.008600488660484, 4.669839744276338, 55.409361735611505, 59.54133637064234, 42.75120671114957, 35.50080055230012, 61.36078953345953, 55.46054181765713, 40.26126704247509, 37.43654031910351, 79.47394366351946, 75.92163428986083, 39.98109550300382, 31.32245743094881, 45.537610465260975, 148.7505861596743, 54.6733309190797, 49.90564956395984, 76.61805343294307, 58.88739009290419, 17.310626111912256, 69.2075231557532, 48.020982476643084, 211.1483070764497, 56.08524530341306, 102.65623814151411, 99.26557859074597, 97.79187555253904, 99.88881478209062, 72.4603354522201, 130.06345405586296, 47.614664829179304, 46.015373340309615, 56.33551619600392, 39.49600430420503, 46.812513567210615, 63.834327533047905, 77.86201440153971, 137.10313473461932, 82.01566599377855, 88.72354610434196, 35.147458665621215, 193.73328371559649, 65.52609947912327, 63.43039267516805, 70.69334457401467, 58.546667493774514, 59.26344090144307, 68.06096054387208, 60.84500901686899, 39.2493442217898, 60.24435377823748, 35.15564161035937, 63.56519149736467, 122.92084595094386, 50.70715093701497, 94.54168893340145, 66.4199646685041, 93.73582774391646, 93.03240625255167, 113.60567830273041, 44.025575066891335, 13.898811827267057, 38.041784222540045, 159.9759090738862, 89.23636018096953, 48.98740343722023, 113.89082627520077, 69.24000774503045, 32.828081161704894, 49.362393943809195, 86.97788638068184, 83.74433616857192, 22.23854709660597, 34.06226389796751, 5.1503023302875865, 104.84437947278508, 70.62452397973857, 98.68112223601761, 45.377971839339445, 57.84287404057296, 62.32142183969405, 64.64213681190932, 66.84735561379365, 97.23764098869229, 68.86809965341916, 62.0137612646193, 88.19626866678455, 45.49649734427099, 71.33886941638006, 109.90724722799982, 14.169589924098158, 56.036046325573764, 100.74494818365915, 104.06153781104943, 90.5725429952936, 49.49435648966738, 72.61078544732763, 58.38844767309733, 80.77818085080361, 74.89760169757832, 97.5514776443813, 153.36527325913534, 52.70163725242176, 52.01253209202187, 216.073871317273, 72.29107115603681, 68.55675560023994, 133.11343457907472, 102.73885583832612, 132.0751911691033, 44.13774546088416, 129.63469434552, 94.12589845951203, 52.20001464569088, 83.15553888654333, 52.86452901855444, 131.535020156559, 96.29759849986073, 63.47753560301202, 74.98288425308992, 45.549079851920496, 79.21307331478506, 81.19782427536497, 68.0731392067872, 40.37306036424359, 51.04749980661956, 118.73191385575751, 41.969009805961136, 6.255100573499363, 58.36539898788757, 104.19848932775659, 54.2153712901187, 46.254674953879835, 58.06692006948734, 104.19462013311178, 60.818540736541806, 99.3597555649323, 72.09783811310751, 90.99374533293968, 66.62594506238719, 85.64474020272816, 6.181968220693581, 53.41247098419378, 43.83990731564278, 58.618798919602696, 58.18915130338422, 62.171834697702174, 54.29146844951018, 67.09994282013102, 65.51299942890907, 55.767324539684736, 55.07507239026142, 61.02989087567798, 43.84572017106356, 52.40064115267765, 77.73431629098356, 57.11667350255337, 61.365243667077614, 83.96648813980353, 157.44494109695958, 91.68322215581412, 120.58542218447364, 67.81659994791183, 95.26725202234056, 45.87874648997902, 126.25636424591337, 45.62466833925568, 5.73274711502059, 40.476598029525135, 62.4026273393779, 159.6009501990415, 90.77353125939857, 48.94683618369491, 78.34133374088786, 70.42543956446276, 46.67922307234691, 43.690072039917496, 120.68979265209516, 86.2111978072361, 46.178583739208385, 55.527748925891565, 150.16257000038115, 51.87086138447365, 55.659183919934655, 70.38450167572643, 120.6299497091825, 56.56345252429925, 71.4485437134202, 76.20946343915075, 41.841766136459256, 51.32270273120103, 49.49201911906682, 70.92221569553156, 84.57130162734562, 55.29082275066604, 56.58007741210063, 10.023765209484338, 46.207439448198, 40.48727648617576, 55.73481744564862, 32.57860273399745, 52.070230208006706, 49.469896809073134, 53.02011612477612, 58.088596720747645, 45.88204017237777, 185.0682560580789, 49.26532909564464, 47.97591452861268, 88.25725534209779, 70.12624306675781, 89.65081151089609, 101.09868413343179, 38.501323987777525, 46.09603657653028, 172.1453021628736, 37.87910078827566, 54.15009501445857, 63.40821500338119, 70.14388386153054, 58.18533159677571, 95.36848485605009, 87.66949660159226, 95.91168982508798, 51.685052381113834, 6.692851759193627, 154.06294490088516, 53.13867897924731, 53.92108948028911, 68.6489772031704, 53.321168267148195, 91.90086759540836, 59.576440238685755, 117.60607174964102, 137.52772627345368, 57.26183860169051, 183.55420646886694, 57.16284944252194, 162.5602144049505, 48.86915990578842, 83.77760016536317, 46.726911910412156, 51.619982029957654, 117.13697330413613, 36.72314986195859, 57.69074479488756, 35.36939678630193, 47.25441349054354, 66.74255136766911, 51.268056461336016, 197.90160301845094, 70.83092508403816, 88.3850028532676, 131.29777108776273, 71.26421618371397, 89.7829706100583, 84.35536345176386, 22.446069659949117, 51.872073259589946, 61.172699426725785, 48.4696192370407, 132.8324416972373, 67.05773562853682, 57.347507074728355, 65.77655963200561, 73.09321510041576, 60.03289198441646, 98.54710778342888, 47.90923011602839, 59.616062566674294, 168.6860419798981, 186.90504716258476, 61.94986907488438, 56.673739088841295, 63.422475425307674, 102.42800229961675, 110.49857752616992, 76.57891702873681, 62.94452049429174, 103.65861579551644, 220.5013354231681, 94.14094608241943, 79.85828128379516, 42.39793924506555, 11.465210518547327, 73.25752475425611, 63.02543170684537, 72.27886429213858, 4.551065095009679, 63.260012482462166, 49.060779053727956, 44.99667461646224, 147.26876190734276, 113.90047861516635, 57.885433801582806, 56.6248402410105, 60.370321256413554, 78.85982752429668, 55.077423934605406, 82.46438926800802, 56.02622053284792, 101.02583665726682, 82.75087767743547, 95.59988295165336, 163.68575391725807, 75.06749223033295, 62.709917280582204, 68.41644597506311, 110.11323655413014, 147.3626575343086, 65.96229123459358, 120.63186175034826, 220.1051161333457, 126.1061790785196, 127.27128742144906, 55.389152020095445, 82.50509858627464, 121.48235190227666, 92.98671534407559, 223.41038452664003, 46.316773596314626, 34.638903609853834, 100.65850297861023, 37.10947333169813, 60.05376626274489, 86.14574661672876, 52.7740925271958, 96.3001944344141, 46.098862604058965, 55.32829791674519, 256.80396587277676, 90.662321066569, 80.35621983164208, 48.47015593579235, 24.74520321324076, 100.39144429804372, 55.26713942387922, 61.66644172669334, 73.29714443847959, 95.23071362393573, 108.92458465386238, 45.26631341673433, 67.41708016624932, 142.91251769754575, 66.35211009891259, 76.39264204382476, 58.185921032353136, 73.24844080163952, 49.195469843855044, 64.10080353440466, 175.1382859685084, 63.72927866189657, 35.57346906163205, 41.29516560202995, 49.88188719024134, 139.48724167407065, 75.94549355311636, 262.70164063331094, 82.21597539061905, 125.98514537352392, 144.79488311586255, 64.66247297775521, 49.52053335785806, 113.26917978407445, 134.95706543577333, 14.562917192904465, 115.22800004471031, 68.49478764255132, 71.0835547890013, 66.5618353064941, 48.824117808068124, 96.09310056223063, 73.87151126487312, 70.78501304997873, 94.96413621854725, 75.84591144864592, 89.53337274634207, 120.12943096547478, 116.13008292170846, 60.15170468970962, 115.61762005162159, 5.943174623394112, 91.65496038826475, 16.04733601351805, 111.09071559410073, 72.57039453289896, 10.278295793042567, 90.1233505446739, 89.88917571445127, 102.03189432978029, 159.51642108933012, 61.90965886113531, 42.91253682888495, 131.41579096338597, 80.86528369834929, 69.29266039061119, 68.26110599983315, 173.901300489019, 51.10260863758729, 91.16001753454292, 75.14907399110957, 84.96894471632451, 55.820926627929374, 63.33228294533847, 56.19534810982903, 50.00915664768241, 112.65075047060144, 101.10977360042983, 85.23587877511055, 112.06888140351128, 193.1041179997515, 48.898479270612526, 85.453535431648, 75.14011283730956, 12.843269866521473, 72.45961023935499, 35.786811923575605, 66.36774973275372, 60.56655648198822, 45.05264456591042, 66.72229341722746, 86.58934703327512, 112.09134185570866, 78.95338615914277, 83.8132802599488, 8.110274087621717, 72.20681726413277, 104.95112973844998, 169.224905206235, 43.93844390766806, 116.4968715209654, 120.03465629266101, 45.90358088008543, 94.11100946187031, 47.521622289971866, 79.11097884818729, 289.5663744948701, 7.350823861290871, 93.24917125319374, 83.02627282677247, 72.50363670568308, 49.91397503285384, 71.46567405793476, 56.66446043410312, 76.00084956291461, 43.45412284297406, 60.51593522113302, 91.82839103296418, 6.66021293330951, 42.285679650928536, 94.6793564410611, 104.32902783554243, 58.98169796831002, 172.19297997724507, 147.73402233841466, 68.15441540143324, 74.16973614876369, 106.90372845042366, 50.966902225539215, 70.68044502187051, 65.4549334003847, 63.43935490860792, 8.57500675311728, 165.55164177842278, 8.78843189539218, 90.89176333617804, 89.68178995132192, 110.3971313279634, 6.409267786696905, 88.12615041647567, 76.98305567904056, 112.30437660709337, 78.12776745517122, 40.61035493857145, 149.537304635548, 71.41372464212714, 33.091382524766495, 71.18569198564317, 36.33562176957706, 81.67666442759386, 128.33407123073198, 253.2868412081136, 85.17759347034728, 180.15831142823603, 96.52169309693386, 71.9910889840556, 98.48637750112017, 45.95424866190718, 6.934517503609007, 75.62059549512095, 145.19005736480676, 89.97853512582242, 33.64424204642451, 50.73443616525907, 127.04225350765218, 60.08166654876116, 159.52409517805262, 95.06418501044139, 104.43722234109441, 93.71009773697013, 95.88217248756429, 44.69594409120601, 53.79616440896037, 65.59892139100975, 77.21324657829796, 7.978159302831104, 65.35023506647288, 109.19439821204801, 49.40115012180179, 76.67446546746129, 134.00959440193282, 70.21644898879924, 53.682125570771646, 90.51604143213166, 49.55104042761292, 223.94590320606486, 78.19100484876962, 116.19838012716048, 174.2582936255353, 87.65731437356261, 7.494661029894933, 54.17844737475916, 40.85141137443402, 74.75128125943922, 76.99744362939917, 43.062223468093904, 83.67424021581455, 102.13295230365406, 101.27142553354506, 51.283642634709224, 10.357862632697561, 77.52046290997497, 88.70310615728484, 29.99622228486723, 113.52969107773386, 67.56001486598274, 113.58662707169948, 46.48491332504641, 98.59370982676138, 72.59512910030821, 87.3354820630001, 130.92268450797366, 77.9396548984418, 67.18607828768562, 11.38942380002127, 145.64929011142561, 62.67939686450689, 111.5342896482136, 130.01457306669298, 70.9184026023235, 47.43729689495857, 177.09815653053798, 25.278971143817145, 115.08822368938519, 60.42402176855104, 54.90582126610887, 55.84748236004461, 94.61022992204764, 65.50415480666092, 44.928275733515854, 74.9836317781259, 132.0586329590945, 34.36567434926975, 78.70006575922186, 225.0480234419256, 218.5916517868651, 108.02898665924906, 7.906984975246746, 83.25552728227844, 99.0713919211378, 219.23613694665144, 164.35875819321697, 47.97310626297119, 84.25519598050715, 87.49243948123943, 131.70188687908555, 133.52375944243713, 123.23551075348657, 122.73234902307078, 120.79349004973488, 57.29364439854882, 185.99733830763074, 224.92029554208906, 39.210072000052406, 62.93633254681876, 60.46244745793681, 92.22525829953526, 62.6162939849401, 114.73801872347673, 80.09263479530262, 81.05472194238124, 124.66327312471621, 72.68550522108187, 44.2563054886675, 71.65030077139244, 46.29158444535554, 47.66073985306069, 66.39645775464575, 117.89053589356836, 207.80953928715064, 207.7044561041148, 122.76353110899763, 139.12529163804805, 48.16420439442528, 65.54089831665958, 61.48936907252984, 56.84081044471952, 126.36851428032828, 108.72929217807884, 86.1748919207379, 67.8564610640654, 82.01154848131144, 429.46656444634345, 72.60822940081673, 73.18152312785742, 54.84965974403139, 120.13251052817587, 86.51327806311627, 80.46093375761129, 77.44458336259503, 83.43297468146021, 48.44510491507894, 62.89134742073523, 58.120530249368436, 79.47879056829521, 41.86477601153319, 51.719343485944584, 67.06324348183469, 71.6718718386472, 68.24363425784196, 38.15271477383369, 64.04904932980082, 118.81226505</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="3" t="n">
         <v>126.7334906291962</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="3" t="n">
         <v>94.83142804184381</v>
       </c>
-      <c r="T22" t="n">
-        <v>100</v>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="T22" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t>[47.39111328125, 253.44850158691406, 49.47150802612305, 375.9620361328125, 284.6610107421875, 33.47676467895508, 78.76140594482422, 216.46347045898438, 212.0768585205078, 49.723628997802734, 79.77813720703125, 102.9930419921875, 98.9692611694336, 93.7397689819336, 224.87966918945312, 99.90669250488281, 52.09374237060547, 54.72404861450195, 72.45823669433594, 59.878665924072266, 55.13337326049805, 62.51871871948242, 45.34178924560547, 554.0001831054688, 37.80451965332031, 110.55432891845703, 86.283203125, 127.95295715332031, 49.40147399902344, 367.1196594238281, 244.6734619140625, 62.736412048339844, 67.48023986816406, 48.4473876953125, 208.5186767578125, 65.86968994140625, 11.22708797454834, 94.2147216796875, 49.0908317565918, 124.61121368408203, 294.46875, 51.59496307373047, 175.61495971679688, 47.59966278076172, 212.5167999267578, 35.484012603759766, 294.880615234375, 110.87374114990234, 145.59091186523438, 74.22002410888672, 60.8696403503418, 107.08590698242188, 72.44198608398438, 147.9236602783203, 399.0144348144531, 145.6873321533203, 39.43885803222656, 148.90916442871094, 74.16263580322266, 121.02523040771484, 62.025596618652344, 180.46072387695312, 149.95199584960938, 104.25252532958984, 104.4835205078125, 73.10602569580078, 39.25535202026367, 41.0587158203125, 168.33514404296875, 136.59359741210938, 75.11053466796875, 61.6622428894043, 128.832763671875, 95.94859313964844, 72.2741470336914, 85.43560791015625, 180.25375366210938, 48.586917877197266, 383.87530517578125, 257.08526611328125, 260.6573791503906, 137.83700561523438, 68.89118957519531, 76.9351806640625, 63.021663665771484, 121.99996948242188, 82.78441619873047, 128.0511016845703, 237.3063507080078, 83.85111999511719, 81.3267593383789, 139.53451538085938, 119.27399444580078, 71.76697540283203, 59.674320220947266, 160.76893615722656, 101.19999694824219, 85.00640106201172, 247.19996643066406, 124.43270874023438]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01210</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:00:21</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>92.08489446510939</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>76.83153280779486</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>99.96039207841568</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>4999</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.8011264649045112, 1.0397675265229656, 0.6921087159347381, 1.1879087140858136, 1.370542536850724, 1.1467446345530485, 0.3101272008032878, 1.677466696456907, 0.10968628275483673, 0.9739010137751829, 0.09134106012846353, 0.8738299798298741, 0.5791869550466108, 1.6631660359728209, 1.687047905785643, 1.4143520046857145, 2.453902457950901, 1.162286198703704, 1.8301598262763996, 2.2871241272206766, 2.383629646350758, 0.38326341737085773, 0.8065916720012456, 1.1502051566957152, 0.3902932823212479, 0.8181783921990464, 1.0168992680820794, 0.6126925980238034, 0.866796133315289, 1.1671784421346127, 1.429448898424296, 1.0371042599417104, 0.7706399286448635, 1.4353685291368015, 1.0092744268480849, 2.383923134277688, 1.3960381406156668, 1.7707493650856978, 0.5135670005957425, 1.6537541102970204, 0.9125980016425912, 1.7378585747918138, 1.464022927906812, 0.2099145581936257, 0.8695553407243071, 2.0565863202183836, 2.1365567814921724, 2.9589193009266412, 1.8634880492918302, 1.5986372577754466, 1.3128611770742944, 2.42098492613957, 1.83677922059439, 1.877694580786745, 2.1511000908966778, 2.25423919449781, 0.8741750549342305, 1.372107059660986, 1.217919491868586, 2.2538366250645656, 0.39159556515185023, 1.6986038691124017, 2.048175746913967, 1.3632789837605974, 1.967574340514835, 1.550380874145835, 1.0544014076429726, 1.8799628312601697, 1.2665415604100014, 1.2599089908296845, 1.2500666934185438, 1.6938076668783904, 3.359980234885317, 3.692934934316, 1.1235018347186292, 0.31808944477619605, 0.8127957309707153, 0.605883319276753, 1.2459912058299738, 3.054819700227895, 1.8061144232045865, 2.7881600242508138, 2.047698435305375, 2.5238624166732673, 2.211664315301465, 3.5288665822178027, 1.73515225324838, 3.4888596343795206, 4.65594977505233, 4.8123229038231425, 2.3690215715360954, 1.549978042958345, 2.930826111194118, 3.0967379163558535, 4.810440824965912, 2.830100973045164, 3.479537919056316, 3.6450962217068286, 3.763129222365414, 5.695815855980006, 2.7280921188014147, 2.7984642941890647, 2.4269542235353456, 0.8256642458504101, 5.537983315768468, 1.334061577714891, 4.657827477712033, 3.6566625733462033, 3.0610863551612453, 3.5097543195661243, 2.1065552581329667, 6.6630334131601, 2.749770613565707, 2.4009215495027108, 5.802499686294344, 4.059364769114884, 3.3879983590053584, 1.528887282855438, 1.6769161861560198, 5.921924797203543, 4.1577160785796865, 7.93428835336614, 12.177738873538074, 4.411838478990764, 8.312319289864735, 3.8655446288893858, 4.7466309917143334, 5.984463668362692, 5.858091206834883, 7.661577286463199, 3.475073446647793, 6.843572292105119, 3.302487169748469, 3.917649300994667, 10.291290553071445, 3.8683336574882143, 0.3509695286400801, 6.419029520367692, 2.019142357667037, 2.9493289736094694, 4.703764117245227, 5.106722362206075, 0.7265195019576574, 9.198251234137336, 6.359987410148027, 3.6103591435009776, 3.654229083211146, 7.720883954209196, 3.650535970669442, 2.9452438161061036, 4.86182541098061, 3.5431652152397817, 7.567439290023942, 4.829087876051966, 6.249143345632968, 7.984426811562893, 1.5081693122197226, 6.354768979154244, 7.60956591468226, 3.462621787551585, 3.5078211862836244, 5.823369432023357, 16.870329959948535, 6.333426306500684, 4.055581993143147, 8.439500364883568, 7.804246707354614, 14.308237930269609, 9.5142632831055, 11.24094590797773, 7.44787774888716, 6.775832580604362, 11.857798457618257, 11.436954767934552, 8.29789903876788, 10.09334184041613, 7.488731454364448, 10.671985698909323, 22.01752240064178, 9.246433952356817, 8.86914595108223, 12.09377236668477, 10.50898307932752, 6.618731189367893, 7.366689949238405, 10.462844100541211, 7.50510428600624, 7.5784637661279985, 9.57033106537716, 7.819205942984615, 7.1300148425217005, 3.7289791871918476, 2.138904406083811, 7.7250733203917035, 6.35979488999298, 9.700706809101858, 11.669418466298369, 9.846697458855694, 17.41987995398308, 17.782745880472497, 16.656283270379593, 10.127222183156361, 20.991112699560805, 10.740280274326436, 10.891869810069764, 22.67347034630413, 8.3507556957312, 24.170953581519857, 8.513968713496693, 13.53344424892108, 21.926167610571007, 38.367111846821885, 9.090709964245539, 6.350237526763104, 15.556739186972585, 28.462632003208384, 7.456770761591448, 15.157142079238364, 14.358957682235694, 10.908874822535324, 13.463099514660062, 23.520448919811418, 14.783678079516445, 27.17042893058838, 20.965126687283888, 11.461611632088232, 29.245313804744633, 9.701609972517758, 16.152472298374924, 8.471105901493477, 16.596708380328977, 13.42038236990996, 14.58475600608884, 17.267380401275577, 10.865742289732193, 10.538837874902773, 24.487315067064863, 23.319616955856084, 10.231543680350434, 22.495931008162124, 21.128844906322875, 19.660188224581873, 34.17513619530154, 14.639868801036881, 31.665736554017712, 17.32934631436291, 21.917276944261115, 14.936843995486768, 54.316835668586094, 11.07388028697524, 6.847972993279075, 35.01905951645273, 8.259598525208252, 15.021523189535992, 32.92557402867176, 23.484975102708724, 22.077675895763186, 19.388770497600355, 14.325029130040047, 24.468466543503784, 40.964156505022366, 28.472756590208, 11.420685639548717, 22.76833616251522, 9.467592957657741, 41.09335153889767, 22.357620600180617, 13.180381481746675, 26.21071988010667, 38.44124077556986, 23.903469914964507, 30.785845620521, 13.132143052318645, 26.712600013905263, 27.39799094205671, 38.499037449224076, 16.01401892779652, 44.977596733083814, 21.72697900302343, 28.305918707417366, 41.87827063438929, 13.824603131836856, 21.821213700855242, 36.1121331779784, 48.408520919746444, 40.76417708964839, 32.6188786367459, 16.09979693244824, 36.64643361183056, 24.49518057164397, 31.787687588114842, 35.15250706679117, 21.932550557338626, 21.188938401905315, 28.451831962561723, 13.964327417288873, 20.956888646179877, 21.520501705686193, 5.33121052866688, 43.37811701436515, 24.427006601603985, 17.480890343227202, 1.9719409396087006, 2.5919304926860676, 33.03521427109687, 20.45390125380923, 3.0548729460246933, 17.207442510340755, 24.576604246189962, 27.680888226262514, 19.974111157775177, 27.79908918509632, 3.3636555958882894, 28.938602441961024, 26.295860254999724, 36.232400065283834, 35.60513466379766, 42.30763858090685, 28.976815257877156, 27.725502205716985, 7.0703164232409215, 23.0715885865725, 51.45491056148781, 45.65341754336696, 22.700239172235236, 37.10893422780629, 56.20759529907237, 37.26405838150994, 42.945056677511396, 32.30761307869497, 46.2908778300959, 25.91587523278549, 19.69874035957433, 29.537774432443523, 32.703558051723185, 34.79843583597234, 28.664254639793835, 23.92568767838975, 40.699849416602135, 49.330130036223764, 19.50106196641234, 23.94246007592643, 47.497986474346106, 3.608313419602759, 42.21891519753306, 66.6695958871585, 81.73837785089435, 20.63120986586413, 25.242692135559, 48.06926199949894, 25.154344873916177, 41.013260834186, 39.33147755291991, 19.84625696692216, 42.27725748191894, 39.85217533693265, 45.90381423725243, 22.20838002333125, 28.169097960643015, 30.255449260231256, 34.850006825155674, 19.487197438493336, 82.50811057894042, 25.767871747095562, 52.516708926752976, 34.953148354794614, 33.100309104753805, 2.893408651527709, 32.54513562849806, 24.643366436831258, 69.97878559951549, 55.96178890248223, 21.767043043424618, 32.671291012682595, 21.23789167751597, 27.410386459090272, 22.849458526198035, 19.370008231090406, 45.52933062031017, 3.795638238623929, 22.127480183241744, 43.674223575962166, 6.731943317086607, 2.984831842832778, 30.739401109637036, 48.019650840493796, 41.96080074446599, 25.569785020519813, 50.505224826185376, 32.58971236222794, 47.989229166125256, 60.78139536056017, 3.113626214187236, 59.02632552291185, 39.53546812100988, 30.39127629014303, 44.492185546222544, 44.37413736360308, 29.189446712858324, 61.29157456558497, 55.55860423456832, 30.86281598086997, 27.96223613108752, 67.64844707883611, 40.0174048129129, 26.283179356332703, 53.71575414395987, 41.86933846020718, 38.63458527929697, 43.23866756937698, 55.28621938157879, 52.19404062907878, 64.16577221949927, 50.91449015870225, 43.12819700456516, 53.6060412038098, 48.333650294980316, 37.65431343696327, 4.15998290672483, 67.06703768256503, 31.9101185200765, 31.056272216870948, 50.07057162832313, 46.198070549722345, 26.04408943139468, 37.93484534266103, 63.67665254688458, 41.217570697848394, 29.727445560000287, 3.7096499867338224, 41.40120205039323, 55.17251554133222, 37.04662511500779, 28.97363205615769, 51.32574802665509, 38.03826180944362, 32.21942411886641, 26.50059161103113, 39.390685194571624, 109.37843306290361, 45.36473910286049, 53.70250452497062, 91.13657979093631, 87.29669383328988, 78.91696088037276, 49.36141271032931, 100.63883586536714, 40.61688253354596, 42.66361000381627, 29.26080649372812, 44.84413412727685, 76.15203314789257, 55.60583186132969, 67.14800393435145, 43.18396841279219, 50.65811065999997, 34.58665374561191, 42.80868016400701, 48.65445954456463, 98.88842229060315, 142.26381947877704, 43.748205751512664, 51.38303393541804, 79.49247096614454, 42.38773597614196, 34.75274540793794, 66.63492824111496, 54.01741128851816, 73.6506050974012, 38.69713194267466, 48.487889807090596, 41.77672003089274, 86.1316538336786, 35.01100027791489, 23.126617209186506, 39.575784957513456, 64.07791806627232, 59.56530868484861, 39.24821895458968, 58.21496258775633, 38.41210071396688, 45.02800144571929, 186.40589568709248, 44.53730343796967, 45.688468016663194, 37.2334187275697, 92.64714116424854, 32.82688085217307, 83.70299335944497, 42.323328077811965, 18.308034950689233, 10.863137910986143, 140.84718810690558, 54.176755161146524, 8.407892961175559, 114.42983789161504, 49.34111252216823, 99.26616541775284, 156.2076227806133, 54.19073926264694, 59.686006837145825, 55.513945161298494, 86.90855364792051, 53.77350429814379, 65.33677269867256, 58.82818397686094, 72.25544859568168, 13.183558602259346, 40.18159942711241, 44.09063900876398, 69.13825901116496, 160.454509246905, 41.63002924507388, 43.645432922235216, 43.089043550922604, 87.92647091746775, 112.20150023555055, 59.3157478390296, 131.66797030852055, 43.12552555227226, 35.37067747871906, 9.500289625248758, 69.0519989605539, 63.25214109032936, 81.43486689606843, 34.11633431519746, 47.43464349594866, 53.626072401571044, 58.79435165808085, 42.40669785491069, 52.329017903065534, 46.836716008906784, 39.04185581302174, 41.89298869482393, 5.985715390013099, 50.78995510779995, 47.343223767933694, 40.50952749876031, 42.578261229702626, 56.57201607309936, 40.86157028996928, 37.224097703375506, 56.56699462225333, 61.06099396782746, 53.90095333845145, 75.41182934937598, 79.70160995804235, 59.00426399988555, 77.63201717980114, 53.245483265651444, 55.05599687972515, 60.6679904831944, 53.086319081747654, 72.59676382628638, 44.17963453358481, 57.16114629866749, 83.06481033025779, 73.71440173796849, 102.92702387360261, 36.399197115255646, 51.36128023453773, 49.557004115306036, 102.93855642023017, 43.47733486969869, 128.98223760905344, 59.35342302346749, 66.15905847768893, 57.856521643795936, 44.54700440228056, 123.1678176773121, 40.063269127821606, 40.15291889108757, 69.45250512817613, 42.81429473732168, 32.73488819819725, 127.84445142481792, 57.515852679477284, 40.74228641880444, 50.41385988447506, 39.83438615068788, 75.71422371114201, 72.70637863160357, 52.89129665718995, 172.13758533334888, 76.90652438726424, 45.93056338442833, 43.11011925827417, 90.07544673010449, 39.58038594809496, 62.84143525785427, 42.490088435091174, 46.019468897716266, 61.67968912333054, 43.77930972484078, 82.19825481064386, 84.66473366468675, 101.88385388936757, 47.4610524547347, 74.52623793577796, 69.84173112002358, 39.163593925043784, 48.49139664466626, 160.8770195690912, 66.97046702144026, 33.67671720906509, 45.00842626650983, 60.15684765547003, 91.49958808421127, 36.52562039169868, 114.80535343832011, 41.83069667340839, 34.98947951558936, 89.03790769424981, 56.198947823665335, 62.91943639117498, 54.232896344777316, 44.64098657671057, 164.46258427148723, 39.289427168873814, 65.1004534527166, 125.04807607009437, 46.49644950394637, 98.11660462580903, 7.642982083641278, 151.70071754167853, 40.07346057693944, 45.97855969118058, 103.14212577052109, 62.67563323629367, 36.46059950599875, 70.06521860080292, 78.3230130451655, 101.87758260718341, 100.52330833221899, 47.758082046902125, 53.62549447240257, 53.876247217412946, 60.9394401012716, 46.788898502773876, 57.3714053607895, 52.24884399046905, 43.65088082506518, 54.00728957263903, 59.23418677796266, 60.74718028066209, 139.6565647216496, 48.102669233421494, 36.944151791444085, 92.0807733920474, 178.80864876175474, 96.2784808023839, 46.820227378485725, 49.76570840614826, 51.52671975325561, 53.90820239878037, 11.156906807217634, 82.3472498000722, 78.16404534785067, 68.81646375041589, 48.37007341826208, 45.09977756951177, 73.63825797745105, 58.04766758170389, 5.379028589452991, 7.283202255278005, 56.621002567246975, 45.910330076622685, 80.94026639343733, 46.839565868320754, 73.26150646456719, 10.988224992663419, 55.22830752304737, 86.9966113677106, 75.9570878208631, 82.19803793716224, 107.86777850831234, 5.709824305339544, 90.65694018046568, 135.33767322595992, 40.437825558295785, 62.919418773893824, 83.02242377827814, 74.40255559632088, 44.87189658822982, 85.93690995195219, 107.88091925320687, 143.1127961013695, 39.65996316884692, 51.44130453110045, 31.29007472709278, 5.210935695908706, 115.36061258877356, 49.85719635254735, 76.37824592352966, 46.932958792513546, 44.20661348271965, 90.49631198323009, 127.28921513693555, 75.5961219471727, 58.619237636764, 42.947906384878046, 4.497376263678527, 116.24779448418302, 94.50173802005449, 80.19834466064525, 65.17396208350543, 113.51458925563387, 37.9381259710599, 47.736073117382034, 46.133695999331636, 40.75186958417568, 132.58392461037658, 109.87589892339238, 68.43335348288606, 101.15434834750225, 59.74161807536133, 41.37352752816048, 50.1598786703727, 5.2956755581642, 77.58098528363027, 67.5626695787534, 35.566531245406736, 76.51784838032094, 37.27636734946912, 51.13586939967696, 128.84692331248607, 99.5753056788879, 88.59677160716454, 60.13967740298746, 37.77936424116223, 46.8745474956856, 43.095425552758996, 45.208729609890504, 71.43320254677606, 172.99850900133305, 48.21521593073485, 163.75689626371454, 51.409206002129615, 61.19632300935425, 122.93998812866377, 42.52486719884167, 84.02118056751874, 10.524183944503218, 46.13707862507433, 7.163924599530511, 142.35599170827845, 55.8712124883518, 124.21617711284205, 75.01523944262931, 56.67454150968598, 46.83130259263562, 53.729442170347525, 42.2708948731368, 25.68858545832742, 96.14246862958028, 15.945549877623616, 5.610969461421016, 91.61159635961731, 87.53178796517399, 81.55857749470354, 40.54268329833342, 8.842347882846262, 74.88343913533501, 85.25800874098877, 53.33246210673838, 79.81703184010091, 53.23036936997829, 44.045634364705755, 93.31739304639338, 82.02638315300764, 53.594931100523084, 51.79213741671038, 7.637707344214119, 106.39531766452181, 83.08017887796764, 90.18084510915678, 83.66616511343355, 54.9752410655857, 86.45151491375555, 29.180984959255163, 70.85664878185801, 78.66978957057886, 38.84488882433372, 56.834220947296444, 57.94014100962795, 55.293325780019586, 66.46029005954355, 41.903933089371925, 94.923768940299, 40.861689468843636, 74.41947565140221, 62.13113610019039, 52.338622116620726, 5.77669667223901, 68.2671039598232, 115.16736697996528, 69.8111513734204, 57.91008012507676, 36.795623352790116, 41.74684368681789, 56.61242466291824, 38.780661851681046, 157.85035602258642, 71.33057165487283, 66.4738458510341, 58.70985665009524, 50.02605107362102, 60.29560442247322, 108.57517710507659, 58.920903371524744, 50.80664286631937, 55.519902450207944, 57.85876105599907, 62.74457861585665, 8.58059466873151, 73.8105609448998, 127.07212191273065, 72.40362931930734, 40.18706314542031, 81.89198777182379, 116.2333196811168, 39.74037133986967, 54.87331500388426, 4.780190527803096, 84.399875295747, 54.92818692247079, 90.65972791133368, 61.87886982811603, 6.356367973646948, 59.82945218420982, 72.24434067560462, 120.0086688284414, 74.45142206238357, 63.60776857870814, 70.92989540761988, 58.378121540007804, 62.57549724029445, 30.375710494772342, 93.0261502004551, 63.23722931281163, 35.41518006519432, 53.355084664973845, 99.64114705341304, 55.74101598304318, 59.094492072694095, 134.7781672821871, 9.120144533249178, 48.781732574951185, 42.04204856261687, 56.297315506410655, 123.53252024997283, 156.88871508988439, 36.292446814396634, 56.04115697376192, 96.15111446203323, 43.13218819411316, 46.03897889105598, 56.94391763329214, 87.07808878671513, 110.83550931089849, 47.744408428003865, 62.55935163839778, 47.21424244985207, 56.41004826422436, 71.05767442365375, 12.843344766721907, 62.978380741278905, 55.55450902848551, 65.06155726631052, 38.837041243767594, 104.50999650648197, 44.508941285106914, 49.394314931491174, 68.2023512259306, 105.88226298820462, 149.89205161313288, 137.4849303615919, 45.43434724742513, 45.78615724733231, 50.08102856128959, 57.69045135072751, 47.32465185231635, 51.37045526540513, 120.05788349698624, 61.31349966023943, 171.50445919701562, 102.04127848362194, 76.72959052514264, 39.07865927841827, 81.58578043888956, 55.86967004742873, 162.0508304653645, 131.3422412273584, 32.264805844150786, 134.92715106860928, 77.20561946596837, 66.40597457495359, 96.69704093704922, 79.5204351140398, 20.859850316076404, 141.73276255533298, 5.3723689716432785, 56.00201289068263, 37.67525346436289, 51.220313064396734, 96.750875514895, 34.738556327115994, 8.198169688898748, 86.91348218336645, 117.44333319078474, 33.607159275887824, 50.85525470731511, 55.46212958971809, 87.58572269856778, 57.813182584515545, 133.8495446250735, 5.091728584171059, 53.86411616100379, 54.11508771140416, 5.362942020780202, 104.83915881585072, 131.23480227775215, 58.98037717448358, 7.917194683751921, 47.27373759030897, 53.410598903410914, 87.27894892237853, 84.42898312307376, 125.56951567150804, 57.444383731326795, 99.91459725795468, 50.85305025274363, 48.39561725472313, 52.5414739308318, 45.299706229648145, 130.74528637790152, 155.05755871369067, 40.45161668001414, 41.408880736612176, 47.23538869502791, 61.26556262793193, 72.98188930964542, 63.45829002330004, 49.20771250317581, 46.43372869648367, 36.4898665686463, 141.67044918488466, 56.53216520015366, 71.24644247460316, 62.49864729877505, 62.08781054589274, 46.859786015396516, 55.68749861922608, 92.4173897111926, 59.14533240897162, 94.71751880028394, 9.221946471304719, 59.65888655312942, 101.82727551263527, 33.90080938338588, 57.47568203569976, 85.7545717036435, 60.90297389500441, 66.69608275526546, 197.08232667731005, 70.21497762212371, 63.33054719743827, 96.24669595231956, 114.41322274778125, 41.38241203188272, 54.05359201005, 111.09653767124185, 53.82940010797016, 78.70356780612353, 39.40806516039195, 46.87989313110441, 65.49482618842634, 81.92890659251579, 117.65860952032628, 133.84151087894554, 147.6100774668454, 65.66985753592904, 71.0648529331936, 42.557787628051386, 57.32866255009316, 59.21755410860304, 42.39339671148626, 84.94200389060963, 40.80075518189583, 84.30326332366933, 48.114282825258826, 78.73814835939133, 7.394953909328541, 52.499956743608955, 80.26792129641413, 105.13781088820124, 42.79551040238589, 52.9819228153046, 6.258377985871508, 84.41472381029601, 121.19793498113528, 94.29005693972816, 78.65111766435382, 42.858302708150866, 59.34342917751509, 97.0585107069197, 93.23064286065915, 75.81105732639391, 63.266879499142156, 57.20199010293682, 71.6903836600043, 136.5705497303385, 73.894926515367, 47.58732225287974, 65.59253100465926, 62.471746651377785, 67.67006168892212, 96.9048295647721, 43.74250267997372, 37.74582055852386, 58.098047370886476, 53.204929916766474, 68.4475853841013, 149.31801516327664, 66.2010573191045, 51.8359372189804, 45.54289479352051, 81.24287078471998, 46.126536333524015, 107.02211722935452, 60.20039288004478, 68.57954715194266, 61.11483397844484, 105.77671084203642, 37.40270407088095, 92.21707386668463, 113.36800236831803, 39.475824710485, 48.246173487651205, 97.09047780757496, 69.09885929625914, 120.65653247464529, 106.05825932641264, 80.26885521687322, 97.20341363023526, 75.76565313314514, 149.09163516818333, 40.031327203513726, 45.62548149950444, 51.08404461888565, 91.74577011022816, 188.40139063952168, 38.68024405463486, 49.8941777480854, 143.57266049638443, 6.83396367037487, 70.4399700826213, 22.74290912846725, 46.229649399739614, 70.29771769918634, 66.2145158759811, 57.029897357247215, 166.45696036203012, 22.471154536568875, 104.31746232677118, 80.97731245480477, 84.99264015475224, 45.8612022814798, 47.63483790489315, 44.63290486949591, 124.12219294707837, 182.74319679099978, 118.15574958226505, 95.04805714453114, 64.90597572443443, 43.60249643980792, 67.2562006825645, 65.20690587749536, 40.883575120593456, 60.54020420370739, 80.20843920035354, 71.45395831805565, 39.14052305600289, 39.89791229729795, 49.81709556658632, 66.31467150614014, 87.08909035700685, 14.235494233086362, 67.66432846440556, 64.24889487663148, 38.21339439080216, 68.08535754386394, 44.29752291362839, 55.07253358975607, 45.02908997016806, 200.77356277704666, 68.64778192032769, 81.6568904887624, 95.34953712669953, 95.89498636624796, 70.71229873520566, 39.78936070315285, 141.44421112321064, 65.84164573813122, 38.63545402722502, 58.9775098170622, 76.6413314924964, 44.003054888579356, 46.1823171322474, 56.58829269939544, 81.34916234985081, 90.16349908880042, 145.4386412121098, 67.12711639719384, 74.74616636966762, 48.32971891429004, 107.374267717469, 51.38234934240345, 224.0143053924552, 69.89776574413247, 72.8074853540622, 153.05677535359618, 96.07391903658684, 46.24992886878018, 73.39191229513911, 32.76427011147123, 87.73640811609911, 84.97602022261864, 88.69197193505455, 210.5958438157215, 49.907199326318505, 125.22891402964748, 74.16862538491148, 118.95627246972352, 84.0629989878589, 47.06639148102354, 166.4068260823372, 78.54831868007311, 82.92462487952976, 185.56681894852818, 90.44691255615462, 45.58138930574956, 55.47028236547342, 99.03454241605647, 148.61172104940977, 40.895720954691356, 64.94313164327912, 271.4447808393013, 107.97974764731663, 56.33089212793698, 67.78746311364063, 59.9471517401646, 160.40122587775534, 67.42523412042539, 59.79419649979569, 72.86485791070616, 88.6602839045331, 122.72997922901907, 47.13910968956069, 40.08394422303202, 74.52343338080837, 72.6552317674469, 219.47323846167723, 79.78917350306173, 79.27021227035996, 77.41119112266571, 38.163750661681085, 84.02620730093606, 13.560066351571127, 48.27547068069415, 118.34467521509696, 58.21472248852931, 58.27414045759634, 89.2183904328654, 75.16476488901372, 58.65610891466643, 82.40162799442591, 53.21505215162737, 82.75260787573457, 205.9773397538921, 66.13135261352507, 67.48786384255243, 97.87252982240548, 64.62992639781726, 101.08388546763551, 40.25264221423513, 10.758716181453467, 135.21708242849363, 8.76957524867095, 38.269892941188836, 56.21350888409274, 136.00011068478992, 59.054713894974725, 99.75072945044208, 193.5190908369115, 94.8482814454643, 111.51839955490001, 128.98308771274426, 63.288087294505246, 108.77836269780369, 45.961025784848886, 82.138799164535, 98.72137548093848, 47.621252615923076, 41.04720746310401, 70.77814992503895, 75.6565776054507, 55.62549250517877, 47.79591923791427, 64.41769326401163, 260.67551672407944, 179.5857394438159, 7.150706500845015, 138.66789603278283, 246.06779142489663, 65.57519724517887, 64.27021340459656, 65.14777469006616, 45.641211246193045, 123.60456659389983, 70.932335571507, 68.01534742180651, 94.8863811819328, 84.26155850284488, 52.74846483355397, 77.87630630409487, 49.12472263855332, 60.12770327311248, 56.44967995407284, 73.76199371622144, 63.35998523925721, 50.02420434792379, 62.931588000207476, 178.26395586644696, 75.72827191765333, 91.43846626011309, 172.57731290291022, 82.38906297032189, 173.18701817897548, 69.3758961609557, 57.99112028291577, 11.77069754264272, 50.99358106397914, 48.51995899187752, 59.29104601890866, 268.06361290716876, 55.68865762481603, 134.67675261275645, 64.63612766157314, 81.29416281275243, 93.1734526284168, 103.91046509818783, 107.01672021217226, 7.076599068881663, 99.19583222410866, 45.71296605059363, 169.9707309534595, 52.78473519538106, 98.8509329319984, 82.74407777466587, 69.36060890405908, 87.93798407070192, 77.32807096357077, 163.59538471580674, 42.941999615364324, 49.49161916518265, 54.61916817687127, 55.61158174143247, 170.38476080826467, 59.69423262762952, 96.30080108739548, 18.49015581870584, 51.545496918275084, 18.885526518335407, 77.086146619811, 8.33449295800861, 66.88938036134742, 58.952790847501596, 117.9515071028101, 78.92184172083948, 62.18265926067276, 55.08885367048237, 53.723860798303576, 90.05501629822948, 128.99302486890133, 52.84131112548076, 78.31258084423746, 87.89118457743129, 74.85380674594832, 45.851040719478625, 47.468884461249786, 119.62900686065173, 107.20480903164938, 48.105162430718245, 118.35553354746196, 77.39209436869255, 76.50998122262601, 65.45131586251011, 57.617374916148286, 70.48368290256282, 102.55830513915264, 12.837913933253141, 57.99506692673399, 120.32833838859618, 68.497384165871, 60.37522625869065, 143.2271406055666, 122.59841453091269, 86.96173338131545, 266.53209773468546, 73.73687009479511, 8.212528163992133, 9.206774440173959, 195.9405204095618, 21.131778217990703, 83.10432478559322, 131.1066188732911, 67.50526172863114, 83.51416379444564, 66.39439589267295, 135.50353600032673, 93.56576456333674, 59.33056250961301, 76.13766832891812, 15.864627695262001, 88.65394513226161, 75.00672680924622, 89.97749300526641, 66.97739053910567, 139.2934015892345, 61.2865320888394, 219.86201658309432, 42.89570132001614, 48.25439231705021, 83.38731627006241, 40.84420096015966, 59.45878183420771, 91.83718796581596, 84.58847184732664, 44.29431010598783, 150.46491840525456, 88.025330913024, 88.62399651003172, 82.22070036081908, 96.89435567358434, 57.49554430202047, 87.31812044171473, 61.88110887581332, 48.46515661795415, 105.72766849170661, 106.30089416624628, 55.45006822412377, 42.408001556587394, 56.605323057956475, 58.72560290345706, 9.441114489768307, 152.64539307036634, 7.737132099013379, 20.14659617976237, 175.39942920440967, 55.81307702389008, 63.40767924387426, 74.48021666693988, 81.21328959777999, 82.07597100186952, 12.057080633916234, 169.8475916143839, 81.3429789095939, 53.38702013308222, 235.06831200790745, 74.62961640174746, 65.65121165434064, 9.130213203062269, 52.198662467485185, 47.537183819512244, 186.90359957528793, 110.79649522124174, 61.06246215156533, 54.29730297945727, 76.95603982196286, 50.90522835821969, 101.86362839026783, 127.76182426669303, 97.54759147811279, 66.65985211143179, 14.21075842042783, 55.73882956979306, 58.66371880238056, 51.375630110389025, 108.2780671317362, 89.9496270305238, 69.71627340789843, 18.17687617091834, 113.58721888928577, 72.75754181503545, 115.21984513640606, 69.44260121195282, 10.88209285612173, 64.08136052880111, 10.240338653993279, 127.5483859831348, 87.21787428521147, 52.03808518179578, 83.00603762724575, 50.53449636500257, 82.569906899692, 63.73204919557044, 53.72501459220624, 69.63527816714549, 34.915252778801616, 63.5705574147226, 55.51646750896433, 60.25040508491689, 39.88545683529349, 8.176204104787399, 64.33920283338962, 43.97942573877519, 49.35390604865415, 51.34561208842463, 61.32639884182064, 54.735727772718846, 116.02275135935565, 157.94635782597734, 10.969944520915057, 96.83852819712325, 11.655839779601378, 166.26178644468325, 228.38794345033568, 191.85827361151294, 51.1843958360235, 299.7071432681201, 87.843214419776, 143.29814252950717, 43.886542770599966, 119.55464633208352, 111.2294664076869, 82.42463821115996, 122.11357140700203, 63.380683782264086, 52.15942844222911, 68.79856076326116, 76.96770140247693, 80.12254128673021, 94.89817959009467, 106.06028886572875, 41.36611112270429, 54.961101236836775, 127.83702986710831, 92.2023422336688, 69.72033669771376, 128.62029998589577, 140.43562798165334, 145.603294116932, 10.893725291625106, 73.1977374654968, 60.77239958013562, 239.11105899811534, 126.21411931407152, 47.084111575795596, 155.99303432330572, 71.82830213857872, 77.2405348722129, 69.97824914729371, 53.257201245633766, 8.419132701233892, 247.32328794139468, 81.69409244103255, 134.54253544539569, 88.41132357521386, 72.92419718814895, 94.56377065878513, 282.9763188879357, 58.96825043767087, 110.37057139230495, 115.24820326554207, 158.60402874029413, 165.5794885898939, 64.44030853271876, 64.34986562738321, 89.05027757701909, 257.7141981800816, 89.8015833437852, 96.95782072495851, 55.3356596501573, 258.3960155041845, 68.06356650100165, 53.13881352682488, 153.0478727666543, 59.31367810002138, 34.19319276506988, 89.70214303136426, 53.29815311751227, 133.0319669890126, 70.57815135867561, 9.256355897304449, 66.12026853112273, 82.24616136572358, 175.11777328976447, 136.21849805237198, 10.95461853708641, 57.789479905810744, 58.61956788063746, 99.9777287361195, 108.76926065380705, 20.94777071791046, 38.019930527461014, 6.042752737898616, 134.6476304266135, 78.04807160279337, 57.862568276448144, 34.9108041497996, 81.82654976094035, 74.35685950111908, 44.039698095625944, 55.34990161082187, 138.02256706673305, 158.889729349368, 84.02777711130715, 82.090035043156, 238.0383815110762, 32.979844598503924, 114.09948490676096, 141.58355573728593, 230.74716667358126, 44.83865568120578, 44.398257766330815, 70.76533361922952, 87.60578851781192, 96.78014098573507, 106.90910406911212, 87.73040248527042, 68.24720259431952, 45.6861601300642, 107.54673496388703, 113.8826278679084, 168.24831830864608, 82.75387382681097, 86.86733053709004, 47.56525405122757, 113.64568206538465, 150.31821778712228, 59.63265630125302, 159.7081572380414, 121.60442796799427, 22.297271962492317, 344.80565496566646, 74.91789041515013, 51.59682724720124, 61.88778817131719, 53.7183917623735, 63.64217696335336, 45.11834901091583, 88.29123948584514, 60.238312473334155, 55.437458010919386, 103.41650026173727, 47.13004885689332, 106.02249066099088, 62.24365624487176, 67.87795806060893, 146.4118443915293, 68.7271156612499, 129.9027132610728, 119.10460758445748, 62.22572399793678, 54.13573380368444, 105.26274402271281, 89.29753688314497, 63.71091902477687, 132.7660293330208, 104.66199656018378, 48.95169171537682, 220.66634347386596, 89.53911041518589, 69.65849976685831, 37.97897664287434, 111.24470393020923, 84.06552171371793, 279.7457394922424, 55.847783195612045, 84.06019803542587, 184.48218159264232, 75.9141653160831, 137.2504189672839, 44.484866777791304, 52.44121276874545, 204.00460648806308, 133.60247041716178, 235.59482968563864, 250.5249426221009, 49.71725683671387, 46.75998872527983, 106.38048562802511, 116.06813793947894, 79.32731933531555, 83.49165580772483, 148.65149264962452, 39.80370237948734, 77.33574737546469, 85.73084829801367, 58.81684554874907, 65.18966763334252, 49.226895749168165, 115.53656472885079, 39.64540194701561, 8.1017568928936, 216.42968476260683, 96.4386961803385, 124.08087978193208, 206.26157868112767, 146.69010717305662, 88.75750250494679, 92.83428969928497, 109.26392148434849, 51.168639782121346, 82.18380053842122, 7.040627565849244, 76.49961986712545, 93.29272879110447, 51.48494517223675, 55.16573892364931, 56.023369335584775, 82.7563219074962, 30.736559287884653, 80.03040905720748, 154.63824249150414, 111.23953809685058, 51.51523165888466, 87.02497489018177, 88.96952760641852, 74.96091515267331, 89.9060804812184, 159.6384081293692, 82.67219900043123, 222.86721507829915, 61.53591260177493, 89.26664277673794, 123.55328603237986, 88.24651561911669, 83.31247485909626, 154.0321944917687, 106.50209814826977, 291.8233925054524, 37.89434571734186, 8.304638541773324, 33.4387433242469, 84.7082914870607, 115.71285391556242, 45.99112383053575, 64.80448524486464, 120.13562105048469, 35.67170295066112, 98.66073329845725, 149.04621566110572, 75.15630021926984, 46.18956935657616, 16.97042305799619, 52.60935880152461, 53.62618944416967, 90.07272726307886, 43.82869733183217, 78.10980779427778, 182.64004667767492, 93.53079819783731, 73.15788057147728, 77.6832795212729, 110.26869830431387, 134.91916670314137, 156.23584459864276, 85.86170763121179, 84.16494424008218, 263.0310147201822, 62.174519050639994, 185.8097539064144, 303.5004987289061, 45.027644984636346, 76.30238280690578, 41.40140976976335, 85.63947342086333, 83.2798851024647, 140.00207410818794, 14.186933035734745, 130.53824342611918, 55.44765757420375, 78.61328838773781, 78.17779761688206, 168.30532207564056, 42.927560176225, 54.48864218663334, 88.83569778714342, 91.14145741897316, 96.08690848701164, 60.22536726617521, 105.35507024728318, 90.4785864423483, 87.65254775164179, 85.97088630746104, 86.42273713440711, 71.22547234893013, 6.4240194052134125, 64.65685103145628, 1</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>113.8439700126648</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>85.93263814105489</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>[131.1273193359375, 159.8739013671875, 53.8621940612793, 235.9087677001953, 64.7526626586914, 251.1658172607422, 34.32735824584961, 117.17913055419922, 196.92556762695312, 87.9483413696289, 66.1889419555664, 58.8765983581543, 92.92533874511719, 85.4333724975586, 203.15487670898438, 128.6514434814453, 305.6389465332031, 15.303524017333984, 42.07221603393555, 128.96324157714844, 68.47811126708984, 57.973331451416016, 60.72064208984375, 66.20027923583984, 42.52860641479492, 92.3326416015625, 269.312255859375, 65.00688171386719, 150.49070739746094, 76.4128189086914, 161.64503479003906, 52.43532943725586, 217.71734619140625, 140.57579040527344, 90.18891143798828, 70.75931549072266, 73.18345642089844, 61.698062896728516, 98.36180877685547, 268.28814697265625, 40.58183288574219, 45.912357330322266, 56.809242248535156, 91.04740905761719, 53.956573486328125, 227.75167846679688, 85.51327514648438, 149.87347412109375, 57.82942199707031, 67.59243774414062, 64.07459259033203, 132.88648986816406, 11.014800071716309, 150.6859130859375, 57.50522994995117, 135.78538513183594, 81.98585510253906, 10.816911697387695, 170.21725463867188, 133.05874633789062, 361.9944763183594, 243.71127319335938, 143.30062866210938, 11.030903816223145, 107.97257995605469, 60.81235885620117, 69.55463409423828, 115.27265930175781, 72.24052429199219, 236.35528564453125, 194.07070922851562, 58.281158447265625, 165.8627166748047, 58.16909408569336, 39.30946350097656, 42.78050231933594, 215.6039276123047, 123.48377990722656, 63.22472381591797, 111.35980987548828, 116.09622192382812, 91.84227752685547, 59.94511032104492, 57.224910736083984, 71.99778747558594, 65.28129577636719, 112.41278076171875, 617.7435913085938, 154.9647216796875, 168.9499969482422, 94.31657409667969, 58.899497985839844, 77.41222381591797, 59.789222717285156, 51.258235931396484, 188.31649780273438, 108.47403717041016, 32.06501007080078, 56.33781433105469, 177.1900634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01209</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:02:04</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>92.08489446510939</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>76.83153280779486</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>99.96039207841568</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>4999</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.8011264649045112, 1.0397675265229656, 0.6921087159347381, 1.1879087140858136, 1.370542536850724, 1.1467446345530485, 0.3101272008032878, 1.677466696456907, 0.10968628275483673, 0.9739010137751829, 0.09134106012846353, 0.8738299798298741, 0.5791869550466108, 1.6631660359728209, 1.687047905785643, 1.4143520046857145, 2.453902457950901, 1.162286198703704, 1.8301598262763996, 2.2871241272206766, 2.383629646350758, 0.38326341737085773, 0.8065916720012456, 1.1502051566957152, 0.3902932823212479, 0.8181783921990464, 1.0168992680820794, 0.6126925980238034, 0.866796133315289, 1.1671784421346127, 1.429448898424296, 1.0371042599417104, 0.7706399286448635, 1.4353685291368015, 1.0092744268480849, 2.383923134277688, 1.3960381406156668, 1.7707493650856978, 0.5135670005957425, 1.6537541102970204, 0.9125980016425912, 1.7378585747918138, 1.464022927906812, 0.2099145581936257, 0.8695553407243071, 2.0565863202183836, 2.1365567814921724, 2.9589193009266412, 1.8634880492918302, 1.5986372577754466, 1.3128611770742944, 2.42098492613957, 1.83677922059439, 1.877694580786745, 2.1511000908966778, 2.25423919449781, 0.8741750549342305, 1.372107059660986, 1.217919491868586, 2.2538366250645656, 0.39159556515185023, 1.6986038691124017, 2.048175746913967, 1.3632789837605974, 1.967574340514835, 1.550380874145835, 1.0544014076429726, 1.8799628312601697, 1.2665415604100014, 1.2599089908296845, 1.2500666934185438, 1.6938076668783904, 3.359980234885317, 3.692934934316, 1.1235018347186292, 0.31808944477619605, 0.8127957309707153, 0.605883319276753, 1.2459912058299738, 3.054819700227895, 1.8061144232045865, 2.7881600242508138, 2.047698435305375, 2.5238624166732673, 2.211664315301465, 3.5288665822178027, 1.73515225324838, 3.4888596343795206, 4.65594977505233, 4.8123229038231425, 2.3690215715360954, 1.549978042958345, 2.930826111194118, 3.0967379163558535, 4.810440824965912, 2.830100973045164, 3.479537919056316, 3.6450962217068286, 3.763129222365414, 5.695815855980006, 2.7280921188014147, 2.7984642941890647, 2.4269542235353456, 0.8256642458504101, 5.537983315768468, 1.334061577714891, 4.657827477712033, 3.6566625733462033, 3.0610863551612453, 3.5097543195661243, 2.1065552581329667, 6.6630334131601, 2.749770613565707, 2.4009215495027108, 5.802499686294344, 4.059364769114884, 3.3879983590053584, 1.528887282855438, 1.6769161861560198, 5.921924797203543, 4.1577160785796865, 7.93428835336614, 12.177738873538074, 4.411838478990764, 8.312319289864735, 3.8655446288893858, 4.7466309917143334, 5.984463668362692, 5.858091206834883, 7.661577286463199, 3.475073446647793, 6.843572292105119, 3.302487169748469, 3.917649300994667, 10.291290553071445, 3.8683336574882143, 0.3509695286400801, 6.419029520367692, 2.019142357667037, 2.9493289736094694, 4.703764117245227, 5.106722362206075, 0.7265195019576574, 9.198251234137336, 6.359987410148027, 3.6103591435009776, 3.654229083211146, 7.720883954209196, 3.650535970669442, 2.9452438161061036, 4.86182541098061, 3.5431652152397817, 7.567439290023942, 4.829087876051966, 6.249143345632968, 7.984426811562893, 1.5081693122197226, 6.354768979154244, 7.60956591468226, 3.462621787551585, 3.5078211862836244, 5.823369432023357, 16.870329959948535, 6.333426306500684, 4.055581993143147, 8.439500364883568, 7.804246707354614, 14.308237930269609, 9.5142632831055, 11.24094590797773, 7.44787774888716, 6.775832580604362, 11.857798457618257, 11.436954767934552, 8.29789903876788, 10.09334184041613, 7.488731454364448, 10.671985698909323, 22.01752240064178, 9.246433952356817, 8.86914595108223, 12.09377236668477, 10.50898307932752, 6.618731189367893, 7.366689949238405, 10.462844100541211, 7.50510428600624, 7.5784637661279985, 9.57033106537716, 7.819205942984615, 7.1300148425217005, 3.7289791871918476, 2.138904406083811, 7.7250733203917035, 6.35979488999298, 9.700706809101858, 11.669418466298369, 9.846697458855694, 17.41987995398308, 17.782745880472497, 16.656283270379593, 10.127222183156361, 20.991112699560805, 10.740280274326436, 10.891869810069764, 22.67347034630413, 8.3507556957312, 24.170953581519857, 8.513968713496693, 13.53344424892108, 21.926167610571007, 38.367111846821885, 9.090709964245539, 6.350237526763104, 15.556739186972585, 28.462632003208384, 7.456770761591448, 15.157142079238364, 14.358957682235694, 10.908874822535324, 13.463099514660062, 23.520448919811418, 14.783678079516445, 27.17042893058838, 20.965126687283888, 11.461611632088232, 29.245313804744633, 9.701609972517758, 16.152472298374924, 8.471105901493477, 16.596708380328977, 13.42038236990996, 14.58475600608884, 17.267380401275577, 10.865742289732193, 10.538837874902773, 24.487315067064863, 23.319616955856084, 10.231543680350434, 22.495931008162124, 21.128844906322875, 19.660188224581873, 34.17513619530154, 14.639868801036881, 31.665736554017712, 17.32934631436291, 21.917276944261115, 14.936843995486768, 54.316835668586094, 11.07388028697524, 6.847972993279075, 35.01905951645273, 8.259598525208252, 15.021523189535992, 32.92557402867176, 23.484975102708724, 22.077675895763186, 19.388770497600355, 14.325029130040047, 24.468466543503784, 40.964156505022366, 28.472756590208, 11.420685639548717, 22.76833616251522, 9.467592957657741, 41.09335153889767, 22.357620600180617, 13.180381481746675, 26.21071988010667, 38.44124077556986, 23.903469914964507, 30.785845620521, 13.132143052318645, 26.712600013905263, 27.39799094205671, 38.499037449224076, 16.01401892779652, 44.977596733083814, 21.72697900302343, 28.305918707417366, 41.87827063438929, 13.824603131836856, 21.821213700855242, 36.1121331779784, 48.408520919746444, 40.76417708964839, 32.6188786367459, 16.09979693244824, 36.64643361183056, 24.49518057164397, 31.787687588114842, 35.15250706679117, 21.932550557338626, 21.188938401905315, 28.451831962561723, 13.964327417288873, 20.956888646179877, 21.520501705686193, 5.33121052866688, 43.37811701436515, 24.427006601603985, 17.480890343227202, 1.9719409396087006, 2.5919304926860676, 33.03521427109687, 20.45390125380923, 3.0548729460246933, 17.207442510340755, 24.576604246189962, 27.680888226262514, 19.974111157775177, 27.79908918509632, 3.3636555958882894, 28.938602441961024, 26.295860254999724, 36.232400065283834, 35.60513466379766, 42.30763858090685, 28.976815257877156, 27.725502205716985, 7.0703164232409215, 23.0715885865725, 51.45491056148781, 45.65341754336696, 22.700239172235236, 37.10893422780629, 56.20759529907237, 37.26405838150994, 42.945056677511396, 32.30761307869497, 46.2908778300959, 25.91587523278549, 19.69874035957433, 29.537774432443523, 32.703558051723185, 34.79843583597234, 28.664254639793835, 23.92568767838975, 40.699849416602135, 49.330130036223764, 19.50106196641234, 23.94246007592643, 47.497986474346106, 3.608313419602759, 42.21891519753306, 66.6695958871585, 81.73837785089435, 20.63120986586413, 25.242692135559, 48.06926199949894, 25.154344873916177, 41.013260834186, 39.33147755291991, 19.84625696692216, 42.27725748191894, 39.85217533693265, 45.90381423725243, 22.20838002333125, 28.169097960643015, 30.255449260231256, 34.850006825155674, 19.487197438493336, 82.50811057894042, 25.767871747095562, 52.516708926752976, 34.953148354794614, 33.100309104753805, 2.893408651527709, 32.54513562849806, 24.643366436831258, 69.97878559951549, 55.96178890248223, 21.767043043424618, 32.671291012682595, 21.23789167751597, 27.410386459090272, 22.849458526198035, 19.370008231090406, 45.52933062031017, 3.795638238623929, 22.127480183241744, 43.674223575962166, 6.731943317086607, 2.984831842832778, 30.739401109637036, 48.019650840493796, 41.96080074446599, 25.569785020519813, 50.505224826185376, 32.58971236222794, 47.989229166125256, 60.78139536056017, 3.113626214187236, 59.02632552291185, 39.53546812100988, 30.39127629014303, 44.492185546222544, 44.37413736360308, 29.189446712858324, 61.29157456558497, 55.55860423456832, 30.86281598086997, 27.96223613108752, 67.64844707883611, 40.0174048129129, 26.283179356332703, 53.71575414395987, 41.86933846020718, 38.63458527929697, 43.23866756937698, 55.28621938157879, 52.19404062907878, 64.16577221949927, 50.91449015870225, 43.12819700456516, 53.6060412038098, 48.333650294980316, 37.65431343696327, 4.15998290672483, 67.06703768256503, 31.9101185200765, 31.056272216870948, 50.07057162832313, 46.198070549722345, 26.04408943139468, 37.93484534266103, 63.67665254688458, 41.217570697848394, 29.727445560000287, 3.7096499867338224, 41.40120205039323, 55.17251554133222, 37.04662511500779, 28.97363205615769, 51.32574802665509, 38.03826180944362, 32.21942411886641, 26.50059161103113, 39.390685194571624, 109.37843306290361, 45.36473910286049, 53.70250452497062, 91.13657979093631, 87.29669383328988, 78.91696088037276, 49.36141271032931, 100.63883586536714, 40.61688253354596, 42.66361000381627, 29.26080649372812, 44.84413412727685, 76.15203314789257, 55.60583186132969, 67.14800393435145, 43.18396841279219, 50.65811065999997, 34.58665374561191, 42.80868016400701, 48.65445954456463, 98.88842229060315, 142.26381947877704, 43.748205751512664, 51.38303393541804, 79.49247096614454, 42.38773597614196, 34.75274540793794, 66.63492824111496, 54.01741128851816, 73.6506050974012, 38.69713194267466, 48.487889807090596, 41.77672003089274, 86.1316538336786, 35.01100027791489, 23.126617209186506, 39.575784957513456, 64.07791806627232, 59.56530868484861, 39.24821895458968, 58.21496258775633, 38.41210071396688, 45.02800144571929, 186.40589568709248, 44.53730343796967, 45.688468016663194, 37.2334187275697, 92.64714116424854, 32.82688085217307, 83.70299335944497, 42.323328077811965, 18.308034950689233, 10.863137910986143, 140.84718810690558, 54.176755161146524, 8.407892961175559, 114.42983789161504, 49.34111252216823, 99.26616541775284, 156.2076227806133, 54.19073926264694, 59.686006837145825, 55.513945161298494, 86.90855364792051, 53.77350429814379, 65.33677269867256, 58.82818397686094, 72.25544859568168, 13.183558602259346, 40.18159942711241, 44.09063900876398, 69.13825901116496, 160.454509246905, 41.63002924507388, 43.645432922235216, 43.089043550922604, 87.92647091746775, 112.20150023555055, 59.3157478390296, 131.66797030852055, 43.12552555227226, 35.37067747871906, 9.500289625248758, 69.0519989605539, 63.25214109032936, 81.43486689606843, 34.11633431519746, 47.43464349594866, 53.626072401571044, 58.79435165808085, 42.40669785491069, 52.329017903065534, 46.836716008906784, 39.04185581302174, 41.89298869482393, 5.985715390013099, 50.78995510779995, 47.343223767933694, 40.50952749876031, 42.578261229702626, 56.57201607309936, 40.86157028996928, 37.224097703375506, 56.56699462225333, 61.06099396782746, 53.90095333845145, 75.41182934937598, 79.70160995804235, 59.00426399988555, 77.63201717980114, 53.245483265651444, 55.05599687972515, 60.6679904831944, 53.086319081747654, 72.59676382628638, 44.17963453358481, 57.16114629866749, 83.06481033025779, 73.71440173796849, 102.92702387360261, 36.399197115255646, 51.36128023453773, 49.557004115306036, 102.93855642023017, 43.47733486969869, 128.98223760905344, 59.35342302346749, 66.15905847768893, 57.856521643795936, 44.54700440228056, 123.1678176773121, 40.063269127821606, 40.15291889108757, 69.45250512817613, 42.81429473732168, 32.73488819819725, 127.84445142481792, 57.515852679477284, 40.74228641880444, 50.41385988447506, 39.83438615068788, 75.71422371114201, 72.70637863160357, 52.89129665718995, 172.13758533334888, 76.90652438726424, 45.93056338442833, 43.11011925827417, 90.07544673010449, 39.58038594809496, 62.84143525785427, 42.490088435091174, 46.019468897716266, 61.67968912333054, 43.77930972484078, 82.19825481064386, 84.66473366468675, 101.88385388936757, 47.4610524547347, 74.52623793577796, 69.84173112002358, 39.163593925043784, 48.49139664466626, 160.8770195690912, 66.97046702144026, 33.67671720906509, 45.00842626650983, 60.15684765547003, 91.49958808421127, 36.52562039169868, 114.80535343832011, 41.83069667340839, 34.98947951558936, 89.03790769424981, 56.198947823665335, 62.91943639117498, 54.232896344777316, 44.64098657671057, 164.46258427148723, 39.289427168873814, 65.1004534527166, 125.04807607009437, 46.49644950394637, 98.11660462580903, 7.642982083641278, 151.70071754167853, 40.07346057693944, 45.97855969118058, 103.14212577052109, 62.67563323629367, 36.46059950599875, 70.06521860080292, 78.3230130451655, 101.87758260718341, 100.52330833221899, 47.758082046902125, 53.62549447240257, 53.876247217412946, 60.9394401012716, 46.788898502773876, 57.3714053607895, 52.24884399046905, 43.65088082506518, 54.00728957263903, 59.23418677796266, 60.74718028066209, 139.6565647216496, 48.102669233421494, 36.944151791444085, 92.0807733920474, 178.80864876175474, 96.2784808023839, 46.820227378485725, 49.76570840614826, 51.52671975325561, 53.90820239878037, 11.156906807217634, 82.3472498000722, 78.16404534785067, 68.81646375041589, 48.37007341826208, 45.09977756951177, 73.63825797745105, 58.04766758170389, 5.379028589452991, 7.283202255278005, 56.621002567246975, 45.910330076622685, 80.94026639343733, 46.839565868320754, 73.26150646456719, 10.988224992663419, 55.22830752304737, 86.9966113677106, 75.9570878208631, 82.19803793716224, 107.86777850831234, 5.709824305339544, 90.65694018046568, 135.33767322595992, 40.437825558295785, 62.919418773893824, 83.02242377827814, 74.40255559632088, 44.87189658822982, 85.93690995195219, 107.88091925320687, 143.1127961013695, 39.65996316884692, 51.44130453110045, 31.29007472709278, 5.210935695908706, 115.36061258877356, 49.85719635254735, 76.37824592352966, 46.932958792513546, 44.20661348271965, 90.49631198323009, 127.28921513693555, 75.5961219471727, 58.619237636764, 42.947906384878046, 4.497376263678527, 116.24779448418302, 94.50173802005449, 80.19834466064525, 65.17396208350543, 113.51458925563387, 37.9381259710599, 47.736073117382034, 46.133695999331636, 40.75186958417568, 132.58392461037658, 109.87589892339238, 68.43335348288606, 101.15434834750225, 59.74161807536133, 41.37352752816048, 50.1598786703727, 5.2956755581642, 77.58098528363027, 67.5626695787534, 35.566531245406736, 76.51784838032094, 37.27636734946912, 51.13586939967696, 128.84692331248607, 99.5753056788879, 88.59677160716454, 60.13967740298746, 37.77936424116223, 46.8745474956856, 43.095425552758996, 45.208729609890504, 71.43320254677606, 172.99850900133305, 48.21521593073485, 163.75689626371454, 51.409206002129615, 61.19632300935425, 122.93998812866377, 42.52486719884167, 84.02118056751874, 10.524183944503218, 46.13707862507433, 7.163924599530511, 142.35599170827845, 55.8712124883518, 124.21617711284205, 75.01523944262931, 56.67454150968598, 46.83130259263562, 53.729442170347525, 42.2708948731368, 25.68858545832742, 96.14246862958028, 15.945549877623616, 5.610969461421016, 91.61159635961731, 87.53178796517399, 81.55857749470354, 40.54268329833342, 8.842347882846262, 74.88343913533501, 85.25800874098877, 53.33246210673838, 79.81703184010091, 53.23036936997829, 44.045634364705755, 93.31739304639338, 82.02638315300764, 53.594931100523084, 51.79213741671038, 7.637707344214119, 106.39531766452181, 83.08017887796764, 90.18084510915678, 83.66616511343355, 54.9752410655857, 86.45151491375555, 29.180984959255163, 70.85664878185801, 78.66978957057886, 38.84488882433372, 56.834220947296444, 57.94014100962795, 55.293325780019586, 66.46029005954355, 41.903933089371925, 94.923768940299, 40.861689468843636, 74.41947565140221, 62.13113610019039, 52.338622116620726, 5.77669667223901, 68.2671039598232, 115.16736697996528, 69.8111513734204, 57.91008012507676, 36.795623352790116, 41.74684368681789, 56.61242466291824, 38.780661851681046, 157.85035602258642, 71.33057165487283, 66.4738458510341, 58.70985665009524, 50.02605107362102, 60.29560442247322, 108.57517710507659, 58.920903371524744, 50.80664286631937, 55.519902450207944, 57.85876105599907, 62.74457861585665, 8.58059466873151, 73.8105609448998, 127.07212191273065, 72.40362931930734, 40.18706314542031, 81.89198777182379, 116.2333196811168, 39.74037133986967, 54.87331500388426, 4.780190527803096, 84.399875295747, 54.92818692247079, 90.65972791133368, 61.87886982811603, 6.356367973646948, 59.82945218420982, 72.24434067560462, 120.0086688284414, 74.45142206238357, 63.60776857870814, 70.92989540761988, 58.378121540007804, 62.57549724029445, 30.375710494772342, 93.0261502004551, 63.23722931281163, 35.41518006519432, 53.355084664973845, 99.64114705341304, 55.74101598304318, 59.094492072694095, 134.7781672821871, 9.120144533249178, 48.781732574951185, 42.04204856261687, 56.297315506410655, 123.53252024997283, 156.88871508988439, 36.292446814396634, 56.04115697376192, 96.15111446203323, 43.13218819411316, 46.03897889105598, 56.94391763329214, 87.07808878671513, 110.83550931089849, 47.744408428003865, 62.55935163839778, 47.21424244985207, 56.41004826422436, 71.05767442365375, 12.843344766721907, 62.978380741278905, 55.55450902848551, 65.06155726631052, 38.837041243767594, 104.50999650648197, 44.508941285106914, 49.394314931491174, 68.2023512259306, 105.88226298820462, 149.89205161313288, 137.4849303615919, 45.43434724742513, 45.78615724733231, 50.08102856128959, 57.69045135072751, 47.32465185231635, 51.37045526540513, 120.05788349698624, 61.31349966023943, 171.50445919701562, 102.04127848362194, 76.72959052514264, 39.07865927841827, 81.58578043888956, 55.86967004742873, 162.0508304653645, 131.3422412273584, 32.264805844150786, 134.92715106860928, 77.20561946596837, 66.40597457495359, 96.69704093704922, 79.5204351140398, 20.859850316076404, 141.73276255533298, 5.3723689716432785, 56.00201289068263, 37.67525346436289, 51.220313064396734, 96.750875514895, 34.738556327115994, 8.198169688898748, 86.91348218336645, 117.44333319078474, 33.607159275887824, 50.85525470731511, 55.46212958971809, 87.58572269856778, 57.813182584515545, 133.8495446250735, 5.091728584171059, 53.86411616100379, 54.11508771140416, 5.362942020780202, 104.83915881585072, 131.23480227775215, 58.98037717448358, 7.917194683751921, 47.27373759030897, 53.410598903410914, 87.27894892237853, 84.42898312307376, 125.56951567150804, 57.444383731326795, 99.91459725795468, 50.85305025274363, 48.39561725472313, 52.5414739308318, 45.299706229648145, 130.74528637790152, 155.05755871369067, 40.45161668001414, 41.408880736612176, 47.23538869502791, 61.26556262793193, 72.98188930964542, 63.45829002330004, 49.20771250317581, 46.43372869648367, 36.4898665686463, 141.67044918488466, 56.53216520015366, 71.24644247460316, 62.49864729877505, 62.08781054589274, 46.859786015396516, 55.68749861922608, 92.4173897111926, 59.14533240897162, 94.71751880028394, 9.221946471304719, 59.65888655312942, 101.82727551263527, 33.90080938338588, 57.47568203569976, 85.7545717036435, 60.90297389500441, 66.69608275526546, 197.08232667731005, 70.21497762212371, 63.33054719743827, 96.24669595231956, 114.41322274778125, 41.38241203188272, 54.05359201005, 111.09653767124185, 53.82940010797016, 78.70356780612353, 39.40806516039195, 46.87989313110441, 65.49482618842634, 81.92890659251579, 117.65860952032628, 133.84151087894554, 147.6100774668454, 65.66985753592904, 71.0648529331936, 42.557787628051386, 57.32866255009316, 59.21755410860304, 42.39339671148626, 84.94200389060963, 40.80075518189583, 84.30326332366933, 48.114282825258826, 78.73814835939133, 7.394953909328541, 52.499956743608955, 80.26792129641413, 105.13781088820124, 42.79551040238589, 52.9819228153046, 6.258377985871508, 84.41472381029601, 121.19793498113528, 94.29005693972816, 78.65111766435382, 42.858302708150866, 59.34342917751509, 97.0585107069197, 93.23064286065915, 75.81105732639391, 63.266879499142156, 57.20199010293682, 71.6903836600043, 136.5705497303385, 73.894926515367, 47.58732225287974, 65.59253100465926, 62.471746651377785, 67.67006168892212, 96.9048295647721, 43.74250267997372, 37.74582055852386, 58.098047370886476, 53.204929916766474, 68.4475853841013, 149.31801516327664, 66.2010573191045, 51.8359372189804, 45.54289479352051, 81.24287078471998, 46.126536333524015, 107.02211722935452, 60.20039288004478, 68.57954715194266, 61.11483397844484, 105.77671084203642, 37.40270407088095, 92.21707386668463, 113.36800236831803, 39.475824710485, 48.246173487651205, 97.09047780757496, 69.09885929625914, 120.65653247464529, 106.05825932641264, 80.26885521687322, 97.20341363023526, 75.76565313314514, 149.09163516818333, 40.031327203513726, 45.62548149950444, 51.08404461888565, 91.74577011022816, 188.40139063952168, 38.68024405463486, 49.8941777480854, 143.57266049638443, 6.83396367037487, 70.4399700826213, 22.74290912846725, 46.229649399739614, 70.29771769918634, 66.2145158759811, 57.029897357247215, 166.45696036203012, 22.471154536568875, 104.31746232677118, 80.97731245480477, 84.99264015475224, 45.8612022814798, 47.63483790489315, 44.63290486949591, 124.12219294707837, 182.74319679099978, 118.15574958226505, 95.04805714453114, 64.90597572443443, 43.60249643980792, 67.2562006825645, 65.20690587749536, 40.883575120593456, 60.54020420370739, 80.20843920035354, 71.45395831805565, 39.14052305600289, 39.89791229729795, 49.81709556658632, 66.31467150614014, 87.08909035700685, 14.235494233086362, 67.66432846440556, 64.24889487663148, 38.21339439080216, 68.08535754386394, 44.29752291362839, 55.07253358975607, 45.02908997016806, 200.77356277704666, 68.64778192032769, 81.6568904887624, 95.34953712669953, 95.89498636624796, 70.71229873520566, 39.78936070315285, 141.44421112321064, 65.84164573813122, 38.63545402722502, 58.9775098170622, 76.6413314924964, 44.003054888579356, 46.1823171322474, 56.58829269939544, 81.34916234985081, 90.16349908880042, 145.4386412121098, 67.12711639719384, 74.74616636966762, 48.32971891429004, 107.374267717469, 51.38234934240345, 224.0143053924552, 69.89776574413247, 72.8074853540622, 153.05677535359618, 96.07391903658684, 46.24992886878018, 73.39191229513911, 32.76427011147123, 87.73640811609911, 84.97602022261864, 88.69197193505455, 210.5958438157215, 49.907199326318505, 125.22891402964748, 74.16862538491148, 118.95627246972352, 84.0629989878589, 47.06639148102354, 166.4068260823372, 78.54831868007311, 82.92462487952976, 185.56681894852818, 90.44691255615462, 45.58138930574956, 55.47028236547342, 99.03454241605647, 148.61172104940977, 40.895720954691356, 64.94313164327912, 271.4447808393013, 107.97974764731663, 56.33089212793698, 67.78746311364063, 59.9471517401646, 160.40122587775534, 67.42523412042539, 59.79419649979569, 72.86485791070616, 88.6602839045331, 122.72997922901907, 47.13910968956069, 40.08394422303202, 74.52343338080837, 72.6552317674469, 219.47323846167723, 79.78917350306173, 79.27021227035996, 77.41119112266571, 38.163750661681085, 84.02620730093606, 13.560066351571127, 48.27547068069415, 118.34467521509696, 58.21472248852931, 58.27414045759634, 89.2183904328654, 75.16476488901372, 58.65610891466643, 82.40162799442591, 53.21505215162737, 82.75260787573457, 205.9773397538921, 66.13135261352507, 67.48786384255243, 97.87252982240548, 64.62992639781726, 101.08388546763551, 40.25264221423513, 10.758716181453467, 135.21708242849363, 8.76957524867095, 38.269892941188836, 56.21350888409274, 136.00011068478992, 59.054713894974725, 99.75072945044208, 193.5190908369115, 94.8482814454643, 111.51839955490001, 128.98308771274426, 63.288087294505246, 108.77836269780369, 45.961025784848886, 82.138799164535, 98.72137548093848, 47.621252615923076, 41.04720746310401, 70.77814992503895, 75.6565776054507, 55.62549250517877, 47.79591923791427, 64.41769326401163, 260.67551672407944, 179.5857394438159, 7.150706500845015, 138.66789603278283, 246.06779142489663, 65.57519724517887, 64.27021340459656, 65.14777469006616, 45.641211246193045, 123.60456659389983, 70.932335571507, 68.01534742180651, 94.8863811819328, 84.26155850284488, 52.74846483355397, 77.87630630409487, 49.12472263855332, 60.12770327311248, 56.44967995407284, 73.76199371622144, 63.35998523925721, 50.02420434792379, 62.931588000207476, 178.26395586644696, 75.72827191765333, 91.43846626011309, 172.57731290291022, 82.38906297032189, 173.18701817897548, 69.3758961609557, 57.99112028291577, 11.77069754264272, 50.99358106397914, 48.51995899187752, 59.29104601890866, 268.06361290716876, 55.68865762481603, 134.67675261275645, 64.63612766157314, 81.29416281275243, 93.1734526284168, 103.91046509818783, 107.01672021217226, 7.076599068881663, 99.19583222410866, 45.71296605059363, 169.9707309534595, 52.78473519538106, 98.8509329319984, 82.74407777466587, 69.36060890405908, 87.93798407070192, 77.32807096357077, 163.59538471580674, 42.941999615364324, 49.49161916518265, 54.61916817687127, 55.61158174143247, 170.38476080826467, 59.69423262762952, 96.30080108739548, 18.49015581870584, 51.545496918275084, 18.885526518335407, 77.086146619811, 8.33449295800861, 66.88938036134742, 58.952790847501596, 117.9515071028101, 78.92184172083948, 62.18265926067276, 55.08885367048237, 53.723860798303576, 90.05501629822948, 128.99302486890133, 52.84131112548076, 78.31258084423746, 87.89118457743129, 74.85380674594832, 45.851040719478625, 47.468884461249786, 119.62900686065173, 107.20480903164938, 48.105162430718245, 118.35553354746196, 77.39209436869255, 76.50998122262601, 65.45131586251011, 57.617374916148286, 70.48368290256282, 102.55830513915264, 12.837913933253141, 57.99506692673399, 120.32833838859618, 68.497384165871, 60.37522625869065, 143.2271406055666, 122.59841453091269, 86.96173338131545, 266.53209773468546, 73.73687009479511, 8.212528163992133, 9.206774440173959, 195.9405204095618, 21.131778217990703, 83.10432478559322, 131.1066188732911, 67.50526172863114, 83.51416379444564, 66.39439589267295, 135.50353600032673, 93.56576456333674, 59.33056250961301, 76.13766832891812, 15.864627695262001, 88.65394513226161, 75.00672680924622, 89.97749300526641, 66.97739053910567, 139.2934015892345, 61.2865320888394, 219.86201658309432, 42.89570132001614, 48.25439231705021, 83.38731627006241, 40.84420096015966, 59.45878183420771, 91.83718796581596, 84.58847184732664, 44.29431010598783, 150.46491840525456, 88.025330913024, 88.62399651003172, 82.22070036081908, 96.89435567358434, 57.49554430202047, 87.31812044171473, 61.88110887581332, 48.46515661795415, 105.72766849170661, 106.30089416624628, 55.45006822412377, 42.408001556587394, 56.605323057956475, 58.72560290345706, 9.441114489768307, 152.64539307036634, 7.737132099013379, 20.14659617976237, 175.39942920440967, 55.81307702389008, 63.40767924387426, 74.48021666693988, 81.21328959777999, 82.07597100186952, 12.057080633916234, 169.8475916143839, 81.3429789095939, 53.38702013308222, 235.06831200790745, 74.62961640174746, 65.65121165434064, 9.130213203062269, 52.198662467485185, 47.537183819512244, 186.90359957528793, 110.79649522124174, 61.06246215156533, 54.29730297945727, 76.95603982196286, 50.90522835821969, 101.86362839026783, 127.76182426669303, 97.54759147811279, 66.65985211143179, 14.21075842042783, 55.73882956979306, 58.66371880238056, 51.375630110389025, 108.2780671317362, 89.9496270305238, 69.71627340789843, 18.17687617091834, 113.58721888928577, 72.75754181503545, 115.21984513640606, 69.44260121195282, 10.88209285612173, 64.08136052880111, 10.240338653993279, 127.5483859831348, 87.21787428521147, 52.03808518179578, 83.00603762724575, 50.53449636500257, 82.569906899692, 63.73204919557044, 53.72501459220624, 69.63527816714549, 34.915252778801616, 63.5705574147226, 55.51646750896433, 60.25040508491689, 39.88545683529349, 8.176204104787399, 64.33920283338962, 43.97942573877519, 49.35390604865415, 51.34561208842463, 61.32639884182064, 54.735727772718846, 116.02275135935565, 157.94635782597734, 10.969944520915057, 96.83852819712325, 11.655839779601378, 166.26178644468325, 228.38794345033568, 191.85827361151294, 51.1843958360235, 299.7071432681201, 87.843214419776, 143.29814252950717, 43.886542770599966, 119.55464633208352, 111.2294664076869, 82.42463821115996, 122.11357140700203, 63.380683782264086, 52.15942844222911, 68.79856076326116, 76.96770140247693, 80.12254128673021, 94.89817959009467, 106.06028886572875, 41.36611112270429, 54.961101236836775, 127.83702986710831, 92.2023422336688, 69.72033669771376, 128.62029998589577, 140.43562798165334, 145.603294116932, 10.893725291625106, 73.1977374654968, 60.77239958013562, 239.11105899811534, 126.21411931407152, 47.084111575795596, 155.99303432330572, 71.82830213857872, 77.2405348722129, 69.97824914729371, 53.257201245633766, 8.419132701233892, 247.32328794139468, 81.69409244103255, 134.54253544539569, 88.41132357521386, 72.92419718814895, 94.56377065878513, 282.9763188879357, 58.96825043767087, 110.37057139230495, 115.24820326554207, 158.60402874029413, 165.5794885898939, 64.44030853271876, 64.34986562738321, 89.05027757701909, 257.7141981800816, 89.8015833437852, 96.95782072495851, 55.3356596501573, 258.3960155041845, 68.06356650100165, 53.13881352682488, 153.0478727666543, 59.31367810002138, 34.19319276506988, 89.70214303136426, 53.29815311751227, 133.0319669890126, 70.57815135867561, 9.256355897304449, 66.12026853112273, 82.24616136572358, 175.11777328976447, 136.21849805237198, 10.95461853708641, 57.789479905810744, 58.61956788063746, 99.9777287361195, 108.76926065380705, 20.94777071791046, 38.019930527461014, 6.042752737898616, 134.6476304266135, 78.04807160279337, 57.862568276448144, 34.9108041497996, 81.82654976094035, 74.35685950111908, 44.039698095625944, 55.34990161082187, 138.02256706673305, 158.889729349368, 84.02777711130715, 82.090035043156, 238.0383815110762, 32.979844598503924, 114.09948490676096, 141.58355573728593, 230.74716667358126, 44.83865568120578, 44.398257766330815, 70.76533361922952, 87.60578851781192, 96.78014098573507, 106.90910406911212, 87.73040248527042, 68.24720259431952, 45.6861601300642, 107.54673496388703, 113.8826278679084, 168.24831830864608, 82.75387382681097, 86.86733053709004, 47.56525405122757, 113.64568206538465, 150.31821778712228, 59.63265630125302, 159.7081572380414, 121.60442796799427, 22.297271962492317, 344.80565496566646, 74.91789041515013, 51.59682724720124, 61.88778817131719, 53.7183917623735, 63.64217696335336, 45.11834901091583, 88.29123948584514, 60.238312473334155, 55.437458010919386, 103.41650026173727, 47.13004885689332, 106.02249066099088, 62.24365624487176, 67.87795806060893, 146.4118443915293, 68.7271156612499, 129.9027132610728, 119.10460758445748, 62.22572399793678, 54.13573380368444, 105.26274402271281, 89.29753688314497, 63.71091902477687, 132.7660293330208, 104.66199656018378, 48.95169171537682, 220.66634347386596, 89.53911041518589, 69.65849976685831, 37.97897664287434, 111.24470393020923, 84.06552171371793, 279.7457394922424, 55.847783195612045, 84.06019803542587, 184.48218159264232, 75.9141653160831, 137.2504189672839, 44.484866777791304, 52.44121276874545, 204.00460648806308, 133.60247041716178, 235.59482968563864, 250.5249426221009, 49.71725683671387, 46.75998872527983, 106.38048562802511, 116.06813793947894, 79.32731933531555, 83.49165580772483, 148.65149264962452, 39.80370237948734, 77.33574737546469, 85.73084829801367, 58.81684554874907, 65.18966763334252, 49.226895749168165, 115.53656472885079, 39.64540194701561, 8.1017568928936, 216.42968476260683, 96.4386961803385, 124.08087978193208, 206.26157868112767, 146.69010717305662, 88.75750250494679, 92.83428969928497, 109.26392148434849, 51.168639782121346, 82.18380053842122, 7.040627565849244, 76.49961986712545, 93.29272879110447, 51.48494517223675, 55.16573892364931, 56.023369335584775, 82.7563219074962, 30.736559287884653, 80.03040905720748, 154.63824249150414, 111.23953809685058, 51.51523165888466, 87.02497489018177, 88.96952760641852, 74.96091515267331, 89.9060804812184, 159.6384081293692, 82.67219900043123, 222.86721507829915, 61.53591260177493, 89.26664277673794, 123.55328603237986, 88.24651561911669, 83.31247485909626, 154.0321944917687, 106.50209814826977, 291.8233925054524, 37.89434571734186, 8.304638541773324, 33.4387433242469, 84.7082914870607, 115.71285391556242, 45.99112383053575, 64.80448524486464, 120.13562105048469, 35.67170295066112, 98.66073329845725, 149.04621566110572, 75.15630021926984, 46.18956935657616, 16.97042305799619, 52.60935880152461, 53.62618944416967, 90.07272726307886, 43.82869733183217, 78.10980779427778, 182.64004667767492, 93.53079819783731, 73.15788057147728, 77.6832795212729, 110.26869830431387, 134.91916670314137, 156.23584459864276, 85.86170763121179, 84.16494424008218, 263.0310147201822, 62.174519050639994, 185.8097539064144, 303.5004987289061, 45.027644984636346, 76.30238280690578, 41.40140976976335, 85.63947342086333, 83.2798851024647, 140.00207410818794, 14.186933035734745, 130.53824342611918, 55.44765757420375, 78.61328838773781, 78.17779761688206, 168.30532207564056, 42.927560176225, 54.48864218663334, 88.83569778714342, 91.14145741897316, 96.08690848701164, 60.22536726617521, 105.35507024728318, 90.4785864423483, 87.65254775164179, 85.97088630746104, 86.42273713440711, 71.22547234893013, 6.4240194052134125, 64.65685103145628, 1</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>113.8439700126648</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>85.93263814105489</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>[131.1273193359375, 159.8739013671875, 53.8621940612793, 235.9087677001953, 64.7526626586914, 251.1658172607422, 34.32735824584961, 117.17913055419922, 196.92556762695312, 87.9483413696289, 66.1889419555664, 58.8765983581543, 92.92533874511719, 85.4333724975586, 203.15487670898438, 128.6514434814453, 305.6389465332031, 15.303524017333984, 42.07221603393555, 128.96324157714844, 68.47811126708984, 57.973331451416016, 60.72064208984375, 66.20027923583984, 42.52860641479492, 92.3326416015625, 269.312255859375, 65.00688171386719, 150.49070739746094, 76.4128189086914, 161.64503479003906, 52.43532943725586, 217.71734619140625, 140.57579040527344, 90.18891143798828, 70.75931549072266, 73.18345642089844, 61.698062896728516, 98.36180877685547, 268.28814697265625, 40.58183288574219, 45.912357330322266, 56.809242248535156, 91.04740905761719, 53.956573486328125, 227.75167846679688, 85.51327514648438, 149.87347412109375, 57.82942199707031, 67.59243774414062, 64.07459259033203, 132.88648986816406, 11.014800071716309, 150.6859130859375, 57.50522994995117, 135.78538513183594, 81.98585510253906, 10.816911697387695, 170.21725463867188, 133.05874633789062, 361.9944763183594, 243.71127319335938, 143.30062866210938, 11.030903816223145, 107.97257995605469, 60.81235885620117, 69.55463409423828, 115.27265930175781, 72.24052429199219, 236.35528564453125, 194.07070922851562, 58.281158447265625, 165.8627166748047, 58.16909408569336, 39.30946350097656, 42.78050231933594, 215.6039276123047, 123.48377990722656, 63.22472381591797, 111.35980987548828, 116.09622192382812, 91.84227752685547, 59.94511032104492, 57.224910736083984, 71.99778747558594, 65.28129577636719, 112.41278076171875, 617.7435913085938, 154.9647216796875, 168.9499969482422, 94.31657409667969, 58.899497985839844, 77.41222381591797, 59.789222717285156, 51.258235931396484, 188.31649780273438, 108.47403717041016, 32.06501007080078, 56.33781433105469, 177.1900634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011214</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:05:49</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>88.88922269517488</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>69.91416583486324</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>106.1051178594181</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>4709</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>[0.7430754746654005, 0.8429539048339204, 0.45011073337225205, 0.7357876661449371, 0.5260147067296467, 0.8559978631617374, 0.5350806028446405, 0.6258678161476883, 1.1237511894258752, 1.1705172055535455, 1.1413959273778327, 0.8572395372887303, 1.162658481259171, 0.5324503424768722, 0.8776140632685685, 1.0800709346527264, 0.867282783653985, 1.1709348097037695, 1.2575208637471607, 1.1180839642785945, 1.3539435489925429, 1.8764741127795987, 1.1647734121636617, 0.9875215847416456, 1.5349774727001098, 0.8238355150737295, 0.7216369888681052, 1.0884113737501322, 0.520342094612604, 0.8728618638401641, 0.9704538365163728, 0.459141824004376, 1.108805676678924, 0.9653628280694393, 1.8408778146899767, 0.4582024834417386, 1.4432841582058706, 1.884951989311475, 1.0363873914317026, 0.8710663321304711, 1.545042277635392, 1.0388026598021451, 3.8930763635151058, 1.2814276303685959, 1.153479239733601, 0.5563930023946171, 2.2949581062969484, 1.640158462085867, 1.3309384418429069, 0.9863458306727367, 1.5414363061669534, 1.7078111903179714, 1.2210908638379774, 1.9221477110694098, 1.3129685407637015, 4.294784287791509, 0.7797313769795949, 1.4764560858059819, 3.2268888436020196, 1.4196105136561947, 2.2545420631503172, 2.132745062211672, 1.25048056440489, 1.3585289905716278, 1.7486405499193438, 0.8433082099237086, 0.33019520185033735, 1.8587194984282833, 1.7094884961086692, 2.326160242276061, 0.9890764288184353, 1.4383212303525137, 1.9603775806684833, 0.22962962833323752, 0.6994423839237986, 1.2354179200808035, 1.6674814537070002, 1.0304296923230678, 1.3210608528067558, 1.8799735132222628, 1.8997570590288881, 3.214913134301599, 4.6707547374310465, 1.8207327149059354, 1.6260461512926625, 1.8177117172518453, 1.7972626764108313, 3.149458844972019, 3.353309987322595, 1.8112920108107753, 2.7012636622237487, 2.840498334091846, 1.0933132948846638, 4.8832567234024005, 2.662882666823331, 2.7227798725380654, 2.941983996364016, 1.938884734770474, 2.063871095502566, 4.664009477236247, 4.892137008147233, 2.955530376445196, 2.8973014595028044, 1.8549166274832718, 3.8037832211667815, 3.234078884423099, 1.4502712644167608, 2.3124142327557813, 1.6448834843485183, 3.4482047033320327, 3.0381764172556665, 1.863051450427636, 1.986227354714138, 2.608341698349837, 2.682858036840817, 3.679095148944809, 2.052330764940179, 2.7728740369589078, 1.633837379061535, 1.4583637732814276, 12.655309237670824, 2.0404930580639, 3.900159904909674, 3.868790092546041, 1.5041235528917989, 6.823787298490057, 3.403723739940117, 5.092630218353478, 4.440225536913377, 4.777716740076702, 3.4374759227342624, 3.412177698232878, 7.975997322717014, 3.711093559741586, 7.31430303500592, 2.567866867055587, 2.418744306095157, 5.3328977045049895, 4.851409735586761, 1.8356723143682743, 3.6219234859788894, 5.3265925573903194, 4.738970636460796, 3.943839114598148, 7.2576202262638185, 3.542980234367442, 5.164686020011408, 7.152618302215456, 1.3660438125983123, 4.9709074268058355, 6.48943096927271, 3.4056072946735423, 3.288268446052045, 4.079108852495393, 8.86092147439823, 2.387939932804473, 5.5465413118318505, 2.8968845942718455, 3.9318777845088024, 6.327391846542455, 7.303561493094162, 3.6090377241007556, 3.1430136277047356, 3.0006770085054395, 7.363451721084978, 12.422219053845273, 5.4188273599311945, 3.1550982595604697, 15.653275507004345, 2.540011101016709, 11.151895351895206, 12.31878130802017, 12.38739321451829, 6.105799442787358, 0.7458036383395189, 7.239490147005932, 17.518443468380056, 11.299982674347143, 5.311654606275599, 4.038604267229816, 5.705656377153056, 10.88483544174533, 8.48047551207796, 4.4474813852625825, 6.391799474667899, 5.884961135505874, 9.501993230536593, 7.235485893820188, 4.780166382677976, 11.438275014773742, 14.332537323188058, 13.556301125615745, 4.293833045570375, 9.318641952923898, 9.559441758952364, 10.140847779228814, 4.56981755770456, 10.481782726755045, 3.8344508002511746, 6.858179560510932, 8.802693067568205, 10.49110200616056, 24.082830529436908, 25.62065761589289, 17.509572835059007, 19.15842000325776, 9.670291235781791, 11.151192565991348, 11.261184085904459, 8.180634904053736, 12.87711400741472, 17.756334718923256, 13.491111291850016, 13.885569525203454, 24.36556572402264, 26.236932930700316, 9.053048565880566, 7.964961154546725, 8.524748835944104, 5.426412156466095, 6.888963979432508, 13.427969814834771, 11.081447335087715, 17.994814775174053, 11.008990530882762, 29.04064991972168, 15.43539164166747, 11.97321850184972, 11.596605752109737, 17.794443960512424, 5.491439924498847, 33.104442396975685, 5.466911944608408, 12.579820651994043, 8.487169506177391, 10.195714808804407, 12.133381664906487, 17.47515434523651, 19.278292707650653, 22.142252706941402, 17.52471121283741, 24.29986801470695, 19.88107606251115, 37.66703537432316, 40.44032970535829, 33.01794288740583, 13.263436076454832, 17.228353594846766, 9.880108209195289, 7.732612777216169, 13.211163460603844, 11.706876557617075, 21.8809749159315, 37.674051717619, 47.33739393815463, 13.70944561077187, 26.0141709959322, 44.82471505282077, 17.485412023877846, 15.98194903843962, 25.871720279539165, 15.646763455245228, 23.476495263405713, 17.90709014625798, 18.693200826077902, 14.785849483513987, 27.126370073483056, 10.58340785692055, 24.18754482698397, 23.427567937207495, 45.211780450060026, 18.15152434643985, 1.8095759015831852, 12.86907977681349, 47.51263743779774, 40.7970563670392, 9.831847437893835, 23.2301586975687, 36.862606814367304, 28.41829290326737, 33.795310466351374, 42.70045942365185, 35.086301426416775, 39.33273118953918, 31.382319604240035, 34.50600836108163, 36.15580992398526, 16.516545010516786, 20.570753151108498, 4.194967769275721, 25.23179781432027, 37.1202062392863, 19.983446427642082, 52.324552180112434, 38.70402360278534, 19.608894160773147, 33.096218582988385, 26.99654616977599, 28.673146155818, 6.197134924200548, 36.425143038398275, 42.08808115605406, 28.615656947335236, 18.692662345623, 30.531827677723154, 42.78399884244822, 2.9422749340357104, 28.56748746811605, 26.15496862953244, 22.11190657048083, 48.19343491490098, 38.57878793310051, 24.907841525418185, 23.514769765137245, 17.60112321123446, 24.92648443243273, 50.07798092305674, 3.077279267178135, 22.524308045677504, 45.660244057064325, 55.08463525762059, 32.55037316854613, 59.100488927829275, 35.91978122132918, 49.507672743456965, 11.14430337880813, 18.293682855265548, 23.18677524171763, 44.82994812683823, 16.40381363969173, 37.744950966785176, 27.12168180167455, 26.963380375101636, 12.916956186621048, 56.088989126069215, 24.56902763506286, 35.156043710034965, 19.782981779543626, 27.474880845147613, 22.429119098047458, 28.95898437975098, 25.81413280126945, 28.673575871358537, 47.47334567994899, 49.896835326292546, 39.57871027269874, 32.20211717974705, 53.26536640081675, 30.823919051839727, 64.61137483417495, 53.121672319391315, 39.804269441592936, 25.407176506322003, 4.168630605306046, 51.116086973151035, 46.40107811821869, 34.339541006011466, 21.384433317480717, 36.60708260426766, 63.31283271161359, 53.79366393788726, 77.2203655442879, 24.95343452016212, 28.724442194692035, 22.026549114665915, 73.26696520423353, 50.59607882507709, 37.69788037425757, 63.29806414852456, 50.059884958931136, 67.29814248131439, 35.27441240035875, 66.02246907548967, 26.933662728646798, 49.50302946282842, 40.06208937479791, 52.84339221595364, 50.472236902095744, 15.837034592203503, 26.639002246209692, 30.18383563263429, 21.317873879156693, 55.331628166792626, 32.33679232184335, 61.1533330110453, 32.229286764518, 40.66498815083046, 71.92223681055684, 52.639509630811204, 66.0735215967178, 27.27565883517865, 41.515612209934055, 56.25070056293198, 55.717715584715265, 63.507570001024085, 36.28263911958298, 42.31839875575888, 38.8159079604229, 45.064576229174364, 45.24526514833036, 23.09664564170223, 34.846156312934085, 32.10007864617194, 14.814858374586182, 72.52552571912071, 33.68800586201436, 87.3219629717716, 93.40656054408262, 30.696100752015894, 31.306860952619516, 65.66337666700775, 67.4990481655246, 48.112099492462065, 67.3469183029162, 63.60064017414925, 110.78046140489842, 65.60791688318362, 87.21567658684994, 66.62326050957425, 32.42951030532209, 71.3204895798258, 47.798929125725124, 54.78753948637205, 98.78837104248234, 37.29688579216764, 3.165896254574986, 95.82162347424209, 49.117689767046706, 33.05363764892325, 52.984241632060225, 88.3533606833292, 47.835731273629754, 42.76560882814091, 43.124997229121455, 102.97798101103807, 73.34269908405466, 35.41773129195242, 41.532611755368386, 31.55028531944651, 91.39248666347198, 39.977293227220514, 55.29667039140305, 38.990658157057474, 50.56498000807084, 28.867919660856476, 96.04953421266133, 129.77374967659551, 104.4586496723903, 38.054423612025, 60.4077100889977, 42.824719534500915, 45.99701497836055, 60.30753433353578, 61.65995508033568, 61.27836948605246, 89.3029769978581, 87.83727340573085, 81.49275853837932, 32.301175150630364, 100.56078728318548, 59.119826566348046, 47.44541983150332, 39.459865522443614, 29.072193625217245, 4.45309575347468, 51.60638489159961, 64.34016665644397, 32.18037023592178, 88.5480248316448, 91.36967494828829, 49.47039169432153, 29.500331893138977, 84.4740257529869, 72.33061207182901, 60.89455336752798, 37.58663613363394, 34.96533165155392, 74.78834163083779, 87.03162289068526, 78.09412083806023, 42.88537331881744, 53.56516976399712, 37.20393086946115, 39.19604077002573, 51.53359042695449, 72.07029976971687, 27.215596226626904, 32.47513411638475, 43.858782708131656, 89.17696754489153, 5.289094558547528, 91.69590471023838, 12.76531458253603, 49.81790105198775, 32.33989350054425, 56.765865091650156, 54.16129064307088, 49.73664436712207, 26.655739384923884, 51.55855091620527, 86.79264129057769, 42.736229270352005, 55.648426401673404, 17.93282080266228, 129.10129149603864, 66.85969380367047, 4.286742601422575, 46.3465010670169, 13.917068459875386, 68.68180040468083, 41.289352788620576, 71.4009802738511, 55.46419032493173, 51.29548826891184, 46.58593681746616, 79.87249425916757, 28.148139973636734, 90.33681586068231, 91.81474699980494, 37.8289700009125, 26.352995644078952, 43.653766983802925, 48.479996792474836, 74.40125043824075, 38.447563094600135, 72.80796079684286, 38.97828427033883, 47.20107694081875, 45.33332713137099, 67.5541357065607, 58.64839719114164, 27.63026241911563, 62.67013234861439, 43.68105618745946, 56.468981120790176, 38.24207072261981, 43.67539476113426, 49.54277061639379, 35.810372420586184, 38.20990883990499, 70.88293105917563, 33.28307025542936, 46.08495172239855, 62.61100621487478, 47.32250683369959, 53.11900581214422, 58.46592158821036, 27.735058735337912, 44.586366214640734, 67.0054343145892, 55.37667941796792, 31.99900823789745, 51.27883105274883, 56.66791231585767, 31.044793773673558, 17.631431887197426, 37.04140199057193, 25.671612894322784, 52.35965539491558, 39.18576245983145, 5.297669278276795, 54.1754683079454, 36.26706893436983, 106.38883348250226, 17.233463490373264, 43.755864334566816, 37.25740624601042, 55.88977932621947, 57.286691265347436, 87.87612987127162, 98.32737021247495, 52.5583238461884, 112.98924835892058, 26.92493008758159, 61.90427029238113, 115.62557322456775, 32.62292482654709, 70.73537104759154, 38.96872307133442, 63.9155007578076, 60.86357669401085, 44.96851916328096, 38.83214082854403, 50.91297121299041, 97.39018357311521, 52.6702063330219, 37.36388409203525, 71.35550348960005, 106.77401904634958, 42.975746603839966, 26.396044446666654, 20.10574762551188, 37.92949869800717, 40.695888867737935, 42.86797495854108, 52.424835730043924, 48.580720963371114, 39.32504808564551, 91.6433245034573, 37.95307463470103, 120.41146880764447, 80.03032341261995, 98.62367967623211, 49.90927808000379, 39.43105511005504, 47.330385365511546, 41.34000799751393, 63.89593563882579, 37.97229054131154, 84.86320470801647, 124.54692798404216, 90.22357722658246, 46.21298546927093, 54.00511311142743, 3.7807642042533205, 15.13974153293239, 38.37241474215964, 135.5173914960846, 51.447812799425584, 94.8790964368657, 42.49589286665431, 111.20619755050245, 40.61383953265893, 80.26077120987898, 96.22870919899262, 47.03878230622097, 41.09878008349803, 54.581623162927, 50.75863440088699, 56.0998668793908, 51.25031377511793, 35.71182239326361, 42.87612103922458, 30.114390109016824, 32.63001165097765, 99.20590513596763, 46.78512939682215, 42.436355514576235, 38.151853984194375, 8.516802581407363, 104.30422085087724, 34.93180237592672, 44.091085022004826, 61.72765218992141, 44.60317297570797, 40.325115242953316, 39.337166368803516, 47.302271197125826, 52.8107219268671, 98.77465112861564, 4.82954800892199, 19.022208073033003, 50.76466296866964, 36.114275853281825, 80.65956598362001, 35.93725667033156, 70.66864161910084, 41.665842225989756, 62.751014678175935, 49.151273139305395, 59.88582833338766, 68.43384116897684, 6.866715934890598, 6.778710574080831, 62.06351656178806, 42.916501299465295, 98.6614499796989, 113.67461899148398, 63.238502687604196, 55.08661693715875, 8.550585305327475, 74.97303796765249, 67.68360246777338, 47.14437833975129, 77.57671003222934, 103.26654495284572, 61.12108796525916, 43.193263307866594, 130.33725027072003, 92.89713490247503, 107.23700783125771, 57.82936189643749, 7.771954255386175, 61.016812173231244, 78.09565251473562, 42.04609349410612, 51.990510782136546, 91.15748668638068, 78.86044834667351, 49.22222182987655, 70.47729206994651, 65.73444597558974, 83.69319386987348, 50.467718831221596, 76.35251157077914, 44.432108631553106, 7.818835645640384, 49.08218223068757, 40.50905910547252, 52.958961671667474, 96.19052986470659, 44.01044451692584, 76.89778937992823, 57.34312881130848, 74.08730940338435, 4.887565183290328, 54.75287756419077, 35.333762501961395, 38.14466837934309, 46.04785557663772, 114.66917684293145, 69.30095281470138, 53.696929388588785, 431.5434925114224, 52.81720142609521, 72.03725293512309, 53.29938491560185, 55.767867935036634, 72.27027574324731, 39.10129263057363, 83.57354227184531, 76.03107087729377, 52.34996456066587, 111.36957571495753, 50.63614291663258, 60.25724538244104, 97.8444836865846, 89.53508163307417, 46.884605008620525, 61.884644776470054, 75.364325768528, 106.02147078354949, 124.29209813631927, 46.68581741482942, 58.46734371033218, 5.1808081935427, 53.72228654180313, 52.85173902573985, 29.303243433631923, 78.88895815254062, 69.64540515865423, 36.99027635036594, 59.47473512131794, 58.56412283116723, 61.42332027720132, 61.1883040287293, 67.35280864942071, 70.56660549406651, 101.10369736373593, 44.71426476000975, 41.441888050971734, 39.39060422408955, 64.54965929801193, 36.47847319441659, 97.50598220546644, 40.51678680874206, 87.47090810843886, 100.91333219054577, 63.142440746511994, 39.26723855517156, 92.59849274478721, 56.70275334053867, 296.6075951753499, 75.03163835775739, 54.46304343326654, 55.44823469382776, 56.98409698069879, 46.412677932114306, 67.8225112512931, 71.61321241075126, 55.947060757633395, 74.78240397928592, 49.885180601342405, 155.04860102341547, 100.3069927443218, 51.60048005696037, 54.8487243843143, 129.0845380819613, 84.73020852782321, 67.91711821515166, 7.745191164614528, 61.28689728233031, 48.358906548286285, 110.0107100508903, 94.1620382188711, 64.00987281572802, 158.3073212868488, 80.98794875948519, 88.8540095174007, 59.2987337937941, 44.03993103213097, 7.22547486964957, 38.48038230486299, 44.199900603576204, 99.85359412574414, 54.32127256187089, 65.95387790645513, 5.589133860055151, 52.32032857126554, 129.0288051344141, 56.76312494474839, 62.745296384963794, 67.26907578437968, 56.383936825564675, 73.81765550118234, 68.32241418596263, 36.081518526966555, 57.60137272428603, 34.500939949789384, 79.28092004412741, 49.26065117510784, 6.389192326250638, 53.84827450552399, 38.914513483694115, 57.99852671921772, 55.005128987053176, 72.56872864852511, 166.5385884299665, 46.576417026743485, 30.364851156525816, 47.359760846830206, 38.60468721182482, 42.185677609402354, 70.06740722721088, 95.10357912333323, 36.63044108649656, 110.23017825466323, 45.57666828515441, 60.96564315681116, 66.93468235434909, 105.14540595432787, 52.35767116698544, 56.13827253298701, 47.75717468261693, 63.65629969525237, 41.32954065258147, 155.73046875925832, 5.0204944782484775, 78.97755023727466, 103.97104945671725, 47.75431790571507, 38.003258532387775, 75.84305526206981, 88.05609239530185, 29.300656317408098, 54.37123828170194, 57.21575755235421, 49.351945795007204, 62.119117133372, 104.31961279308308, 191.44004866548494, 35.38767742754019, 8.062004794072731, 37.611409036252, 52.90557236546859, 57.89119931932634, 36.80154109692211, 42.37096698079917, 69.89460053099187, 77.13603733361015, 47.67875736581758, 53.66225786310966, 45.08638646623529, 44.83091085590141, 135.67511704974333, 54.699392261792376, 55.78761882172496, 58.92108385913716, 52.62039812990146, 49.365076071833016, 79.7019004394685, 82.13669675606788, 33.825425559079555, 71.92459195933941, 72.5255528764224, 106.06881439101281, 55.268970535460554, 79.26716231922312, 59.41430094178201, 63.5458839321557, 24.806890881566947, 66.71763564916529, 82.14000418239681, 6.591246283053749, 89.38941939710426, 46.55164161859746, 90.1329465458551, 58.55507121752506, 95.72855919153008, 175.3285607927861, 130.21779641030395, 217.3503941437906, 114.0733961886302, 80.7865785634012, 82.3870876473997, 62.77231139317923, 65.19032957346013, 8.891332510393282, 53.208364586148825, 61.1831726831839, 19.99027764473769, 56.82548787154109, 59.49608993515736, 84.29469630276932, 103.68918467200277, 39.489997955510795, 128.43554838467995, 73.29050948535269, 44.90655094785271, 88.13419632793267, 71.07274762112111, 39.337985290349245, 89.56821621498771, 97.30244570770849, 111.96039647769574, 65.88152036681566, 141.30025719011016, 86.08458140356288, 59.76057819523194, 80.54559458249243, 68.89208762029634, 68.40358129269782, 83.29775025447759, 57.03720391879179, 50.51340772579341, 90.14629014713623, 62.27485754895555, 68.12233770689039, 101.51197409730794, 47.965768425664464, 63.031169399942534, 70.68059448921646, 131.74659865698197, 50.21566031402452, 104.53599237464749, 161.81956370832165, 126.5406938021607, 47.63619857461775, 47.736027550993974, 60.77072522168878, 56.106133372979784, 185.18744247368295, 87.59583169417563, 4.938276623898963, 95.41167216274106, 72.55981201350085, 105.12353933127325, 69.11103502640758, 53.568630386747515, 53.245874624367865, 147.10835144622393, 161.72729714285586, 71.67494712185777, 51.52156145340942, 98.84379311647193, 56.010293353888024, 129.93028209050837, 149.80826641391852, 79.5541172611235, 131.49796829267663, 68.36862461714237, 124.94049723391926, 55.74633665869, 49.38644045319792, 46.135729401376615, 61.8926613077176, 60.55605095863986, 83.92438591750366, 73.12566448533605, 51.270745782116734, 183.30712804018236, 32.14655343110294, 170.7931837470124, 121.44794947201193, 61.920378400880864, 225.1363654691449, 61.85293646978955, 115.87292054426685, 54.11886001277042, 68.48754178860354, 43.1534596724404, 62.29332056929876, 135.30561796134134, 61.906034166229624, 166.82212843547248, 142.54853850132343, 116.5400704282241, 37.14747642717771, 122.89102047537351, 97.3691133715273, 59.02518730896409, 145.30899194377537, 40.38476945224907, 140.80574906972498, 72.253249132419, 68.7154788358603, 65.60023193887778, 48.515716686627, 71.44723696691236, 69.06775690882155, 84.86316486669494, 61.21175009076964, 53.820847339193286, 104.88663230455757, 38.67235423928122, 197.78449034177362, 120.4668838445851, 90.31928342436534, 89.07708626894411, 42.94153282447426, 63.626431865401415, 46.712952031710984, 74.28683444619153, 73.43501107318802, 89.9216600199689, 80.69101370041905, 66.96590181487281, 109.55841616126484, 55.54443423668623, 52.92413325921502, 39.29388646629756, 42.13883187838179, 88.22711794093634, 116.70018915195115, 42.59355498925561, 168.7804787545721, 72.09295339346878, 91.4157145980948, 67.49022601120852, 81.62391992020116, 67.71805103217248, 41.38080934837378, 37.86775524799612, 206.3941376550672, 72.2411229582766, 58.72540255264802, 12.674020506205405, 100.6179581151004, 84.8867611582316, 60.379616544202406, 61.64665187153851, 58.220404147204135, 58.74319050399235, 95.29084929070616, 33.05623981824818, 101.85714460024933, 52.63607790632762, 57.77930662472241, 106.75141358077272, 97.94672707169502, 61.08408278143486, 69.98909355868174, 90.9518840854064, 38.61951910207932, 75.16661651744424, 82.75334642456167, 46.7301412307762, 81.29690725988894, 63.43703249090877, 73.66913493114424, 111.92142577492523, 54.43663971986751, 45.56630542804506, 60.62734171460955, 62.42642850047074, 69.9347480808001, 55.75395182675902, 137.7709131121599, 51.81295649442585, 91.53902795484395, 100.55954398071056, 88.07438191015135, 146.23260724234737, 113.20787522178819, 303.67401131128287, 83.97371044070061, 110.84180840756511, 65.13484929697681, 59.23633754190264, 202.1895204401034, 102.62455627208419, 84.76515678861595, 68.34014042212924, 73.4876058082751, 56.82072474907734, 83.28993430174617, 63.13550540783861, 52.50981188069542, 14.943882045566852, 57.554911127480565, 44.97054214190233, 87.1671437405573, 105.77903227345912, 9.777123414596495, 203.50992907224617, 44.5405894387019, 120.14979468167682, 106.7981203926857, 64.01282414737447, 100.18291490308975, 74.39290245310671, 53.96845287569511, 51.778411952687094, 93.06653633345903, 57.17782504631972, 100.81891724057613, 50.47738959441157, 38.30167441427177, 44.28908449043761, 122.99516144173468, 74.36689292924544, 53.33824267840744, 66.9018116376793, 71.14906821376553, 63.612813201568216, 31.753268670378482, 138.68642470136413, 130.56949689742257, 88.37534377459471, 62.46210321531774, 81.03269181404659, 51.00680652243415, 67.3552586141678, 74.22490272931415, 67.29460676958216, 170.38431061237014, 47.35949346648406, 169.8576781707451, 67.84196815249837, 105.88777018738969, 59.25847362558025, 86.01428392277575, 62.75324149434321, 73.01401636413543, 9.278954270444222, 135.84149136923156, 81.80740623458924, 89.84562582312473, 52.87042602184087, 62.584963452223406, 49.70301885820642, 157.2525378578954, 79.74820302499299, 81.91257688827962, 77.7354132357573, 76.8563921494783, 40.47902237916319, 68.28412911765832, 76.48539593127687, 91.87574820317644, 105.54558813307865, 49.74270124740702, 166.27505330227058, 163.92388940827993, 67.36525690124631, 59.79139596833688, 166.5620821117276, 86.84591471874892, 61.702440345099795, 19.186319603185495, 80.30843125679503, 79.03573153934775, 102.55289797938603, 88.76739267030081, 147.88507542536263, 52.854120027335185, 54.35031137510892, 51.52388019089968, 100.86609209494766, 49.20303689024624, 109.78737143961114, 101.71576077300575, 86.27397801799228, 73.387917610386, 26.710281679980024, 46.283008917660915, 73.09147505071904, 66.03683733477384, 71.71677627552843, 154.58304131126462, 106.67908858674515, 75.18365876654474, 77.60973952451887, 77.0848653925762, 110.86696590751286, 51.507345559660216, 61.17093754213342, 231.9758702057871, 109.5706693082697, 70.43384383176101, 52.50793040752902, 52.80493525949632, 98.2135968115702, 66.54915697719254, 54.02980988352867, 55.364144842733445, 58.80271625406797, 96.2224578858755, 91.97044522517719, 111.41082937406635, 181.47271991983953, 54.74967954583326, 45.666107753058505, 83.99825346537571, 59.38005235825784, 246.27547395569906, 47.87382050025302, 7.851785240736027, 35.344635143071784, 31.556003969937564, 134.58633516395045, 54.354472675466646, 114.56074827091207, 69.63368865810668, 99.71393144065452, 7.762217157996281, 47.59185124706784, 42.046222521200086, 131.99450705447543, 113.97592293817009, 53.75692326300829, 148.68160281395419, 63.83201498696707, 40.021225679310525, 48.27043744883269, 98.50380384731919, 65.91441230722992, 65.03928646276795, 80.58733076306838, 42.99995684046395, 74.70356816888065, 63.64048012077562, 99.61058026310768, 106.23199295945174, 58.15150327124822, 46.189616174256756, 92.92444236645348, 50.65995036590467, 172.62875396064462, 20.328630775761173, 65.83507142889778, 114.3644000006625, 114.79016068666436, 35.29911634690146, 43.872668763741515, 72.08804900776254, 110.18182739815802, 69.64230248321273, 226.94351688365987, 83.17082527014793, 10.491049218415682, 12.729150256715117, 59.33508757998874, 73.03332273754516, 65.81670132345668, 84.7183989800833, 58.02628926608967, 145.5625803705018, 61.63451189402904, 146.90993497853577, 50.68786027525683, 34.50353237826119, 58.942792700632985, 110.16243185802635, 6.815699967844399, 78.12726685429698, 244.30764395582355, 92.49804289909507, 47.211020282203926, 103.89326140003135, 62.285179666578195, 185.7137833052511, 89.23449605223172, 115.64316683586797, 70.19781281130304, 92.99250146047846, 77.68285153251823, 88.3208014434497, 48.032680104700624, 108.44785776478271, 61.66949201466981, 60.922596271802966, 82.87136821071684, 132.44605824488434, 91.72198003650036, 73.94769280733956, 43.281253747091256, 98.2935350593821, 9.421404836555377, 115.00293327510813, 117.45053541204973, 37.503952424437905, 135.09033843327356, 43.4228080238213, 8.486348423031448, 50.48891303737398, 69.929529965782, 77.2624400987995, 39.89124748545142, 78.31820979180037, 85.11502592444305, 60.670982523325, 44.20249269255483, 66.61725517695508, 139.6753578195998, 81.67458055750977, 62.37927407205922, 98.32300698590542, 40.09054587751911, 46.625866616947775, 51.025332424224686, 112.6997613900126, 61.321178351001706, 69.96977473922284, 116.5694388845572, 68.37938397032298, 104.33873513330691, 68.90250247543989, 60.461365302677095, 74.69632395013433, 145.16013290871308, 67.49020253144974, 104.96779571711431, 118.08988606143497, 141.15399782195342, 92.2679711414976, 170.6527648435169, 99.43249308684499, 65.97496144066106, 164.77908060766515, 51.675853718624225, 8.46250526249754, 93.59087226657003, 112.16214260118483, 101.35528958885203, 51.51416579707541, 94.8665473467864, 106.51410654679124, 56.12096669654257, 44.733773133086146, 102.66206749044201, 155.8098796985664, 51.03121503799713, 43.87103046454777, 177.13541130394447, 144.57816819808983, 7.29675206343726, 100.59185910669314, 124.0047374159944, 42.012551139946886, 75.70798427577354, 129.2683469450325, 44.47136089590681, 146.15361617370374, 170.58669937099688, 79.87652782813683, 38.79088356104971, 88.54612215297323, 159.73834152489778, 89.15334162901286, 54.82353592454453, 158.1003239899552, 28.187808234860324, 76.03979833465652, 168.48363847726728, 134.74185030920066, 125.36249034582228, 80.57499884704143, 58.5974966021359, 66.01732226699022, 33.858080037643475, 80.23554382143276, 129.17070852439156, 63.19397581437278, 68.42015970293997, 55.12179232129496, 62.27784576308597, 88.00778854821615, 59.057102162822666, 48.07267906426588, 50.281678333987784, 40.06556399659841, 67.05537143879157, 85.14849308035959, 102.36320255493276, 92.60168540309168, 109.56589104246956, 105.64994548604626, 65.12539371170404, 101.90943112835102, 41.2569882950961, 119.22871290053442, 61.15381732974488, 208.11110462347756, 143.13983740360845, 64.97992768014612, 49.764170775704066, 75.855878369285, 111.05663893405354, 65.07267080808353, 59.34299419898102, 51.16775058828258, 66.30049907765886, 158.4249980458964, 107.66413082849304, 148.41731233830518, 55.645453993434664, 38.011463611267494, 11.52320955000481, 30.99954921903554, 624.3262380760134, 31.853335347396115, 120.39358828710228, 137.9546562324699, 172.4290491138581, 112.23356797330788, 39.83036892832015, 56.646294001753574, 135.86378944373885, 38.48541153896562, 89.77722686717499, 45.337675118457135, 98.95289515917467, 166.87429599285946, 101.3887751917527, 54.8007645560088, 51.380604804022724, 59.13709241047396, 80.99385970506441, 41.25817140263627, 6.611537515250003, 79.23018251636846, 212.79558779062023, 80.96952777799117, 73.39453305202682, 98.97348093086413, 212.6716890547899, 86.32568577190158, 111.16454967045317, 111.50921196106376, 78.97549492374606, 178.18801999861137, 55.46351075695667, 63.665918316189995, 61.07705668277115, 127.31239059519275, 68.0657573246924, 51.145111670783436, 55.14702315176241, 104.31589546019487, 67.81770011570926, 53.581471739596715, 94.20901155817016, 235.8933345108891, 95.87982806015447, 54.76786658498017, 87.69860751418824, 513.0675148730012, 132.08800691673804, 68.32527471895857, 57.13023494716519, 83.89558085603979, 62.21908030451341, 136.00187463727937, 60.186022946588764, 52.27882597365692, 121.39843499640158, 80.81923675469281, 52.98958040589849, 87.56702401873285, 92.477387686033, 59.04689993870385, 218.42640962056697, 63.93439022569666, 468.56149069412044, 99.20497602828463, 62.961789485517684, 48.89356760775277, 129.07874394251942, 104.76726427748957, 180.43066543039737, 73.90423054153634, 52.79835754549281, 110.61039578690887, 56.17628219636266, 57.81593420394269, 86.30713931989654, 166.09823190768077, 89.59573432669966, 53.39680550605944, 131.00646831800236, 75.63894992977045, 46.54202420719372, 423.23668618065807, 127.22416250332385, 69.21404135769949, 48.60564544121381, 43.145934383843134, 152.468968798827, 69.83297066342179, 112.97567453650551, 122.64276055457265, 56.935018946753736, 59.82783976868263, 57.70922917843048, 59.01169672938535, 137.4151179517375, 47.33632475411276, 58.37855636345309, 80.99732642649919, 154.5711798137404, 119.5233831503898, 77.34356272811404, 178.95979443809767, 47.95470761405898, 60.63568199586664, 128.22664555815612, 7.039570984078563, 103.93856343113926, 61.93671543120618, 108.36380792265558, 85.9809007234173, 78.11891591222266, 106.99763378125303, 43.35554801775701, 47.404798702108195, 50.4960264989509, 109.69372229778033, 118.61888006981658, 141.39023449731314, 179.00919350560739, 102.98270261895341, 108.31145334632585, 61.86577659116485, 156.85852111167569, 47.496882175421085, 55.53294198732126, 45.660351323989374, 43.35712283793236, 255.18038848166725, 54.6655638398691, 79.50319553989412, 107.86138446013824, 146.68340330734125, 106.31532621528216, 76.89359714203997, 87.79450108854265, 97.24047060768741, 96.79192609816357, 59.67647942222416, 93.00277399194222, 63.15116768782022, 106.69974814104798, 78.2556323925597, 62.24788444470516, 73.65097322170567, 49.274452393763305, 100.42937993003909, 160.7031009117356, 48.73420525902535, 75.2915630683141, 73.36245859217135, 55.57910442659696, 166.5347358846123, 6.145525513698858, 59.33009166932294, 123.18182537032337, 49.41762459563309, 76.72633220334959, 103.8938696684478, 92.08216038599939, 54.351405946093934, 95.47871300323798, 54.35298228451214, 13.349030863390684, 66.69288601662655, 154.97667085075798, 57.332168958353904, 62.890447896810926, 47.60005888281139, 93.93370581199632, 182.35963819815197, 130.41120986690402, 140.92890444819804, 60.24676169645877, 93.3845234389851, 120.61686434848329, 79.43126257092374, 93.95577204800941, 140.8037880594286, 63.71026627386837, 43.330379952009565, 67.29396126280464, 105.16712885913856, 50.86852167971458, 35.477455296614686, 127.17115465413539, 107.21180465705154, 48.2966834189839, 66.88616348158357, 77.10902519949583, 81.42716055097124, 133.53588108860308, 100.81038335758872, 148.9863649256062, 5.242761560474308, 37.58354467814856, 53.04122797847155, 130.00605231486625, 81.30958491492353, 99.79145902937636, 33.22751739642196, 84.79707733434398, 12.489454024627099, 96.6356128894135, 45.576620484149586, 138.61557984284863, 63.87620560119324, 42.60876726826047, 8.090334699908842, 146.03509895165118, 74.83943172310794, 107.86748655162373, 96.41719383277945, 89.37006451138662, 72.41600634915257, 327.7067821608814, 5.713533200680677, 39.90407865157462, 66.73110277254074, 66.27329531512336, 100.90419914805823, 59.39093677730596, 52.411364014113026, 92.26184361258446, 115.25179872148381, 73.9048863451948, 102.13250826355339, 77.73153225157228, 83.99061783848478, 136.9796514577386, 68.50600476041772, 124.0823028593924, 113.5686457140425, 70.16203749263462, 144.69130992244143, 38.85184639269121, 99.38132094008874, 72.25146340614378, 63.457581149149064, 74.59880425577988, 100.39581420426731, 168.7492093256681, 73.26064236021382, 54.84950398786521, 60.44108709212421, 65.49411436854129, 146.00522763182974, 78.42914706233506, 128.49638931496347, 50.52444418581285, 58.31553659906684, 145.556007007324, 134.1002558510567, 53.85698467609524, 59.93109002944491, 74.44474004537994, 45.670674892694294, 55.076498927665156, 61.4628602394692, 56.785134369329214, 65.81537063160751, 53.16798661311112, 103.28061167634176, 102.51994159376177, 98.11902224643816, 110.59265681796182, 57.24763943630933, 158.21712547938887, 52.83162466819109, 63.87663602532852, 62.30762454629739, 287.4198591674875, 81.19757826827097, 83.15805040597417, 111.84424625101636, 64.97240519815824, 41.243178295609226, 91.17277254564375, 87.875015267709, 53.72381878737569, 71.3188972962884, 77.38990523493392, 79.59634592768036, 102.73069835052529, 59.93173772081423, 81.18149479004681, 181.8178844018854, 44.622787135730675, 74.35</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>117.398115606308</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>77.57533555107825</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>[132.60726928710938, 177.53530883789062, 62.73810958862305, 192.7012176513672, 347.95751953125, 107.25402069091797, 66.06195831298828, 56.47565841674805, 55.656314849853516, 55.10020446777344, 73.3519287109375, 94.70220184326172, 298.0073547363281, 13.494720458984375, 103.66983795166016, 74.32172393798828, 61.16044616699219, 159.2171630859375, 112.33750915527344, 86.51134490966797, 65.09469604492188, 49.03791427612305, 101.7927474975586, 73.04530334472656, 54.40673828125, 68.6087875366211, 257.7593688964844, 101.51750183105469, 108.8827133178711, 199.8745880126953, 166.2242889404297, 117.15812683105469, 108.49653625488281, 449.47552490234375, 172.49923706054688, 152.84217834472656, 8.644379615783691, 200.34181213378906, 90.66146087646484, 115.58428192138672, 61.113189697265625, 217.3282470703125, 47.79256057739258, 97.88401794433594, 70.79193878173828, 228.25282287597656, 47.0992546081543, 21.304288864135742, 97.5264892578125, 95.22174072265625, 159.72076416015625, 303.47796630859375, 45.11713790893555, 59.632965087890625, 48.42362594604492, 86.3714828491211, 109.54113006591797, 68.06111907958984, 222.38197326660156, 95.7950439453125, 65.33130645751953, 149.57528686523438, 68.30615997314453, 82.70047760009766, 77.13939666748047, 53.86267852783203, 197.7880859375, 101.45763397216797, 286.0135498046875, 75.33302307128906, 48.334251403808594, 138.84210205078125, 63.07204055786133, 68.4803466796875, 57.479644775390625, 100.92115020751953, 83.99578094482422, 99.84783935546875, 113.2650146484375, 46.65465545654297, 131.8516845703125, 308.5207214355469, 212.24693298339844, 73.01914978027344, 160.8163299560547, 90.08904266357422, 88.68103790283203, 175.34132385253906, 108.34219360351562, 77.2236328125, 206.59597778320312, 66.06932830810547, 86.25226593017578, 269.9859313964844, 46.155967712402344, 38.6164436340332, 86.4067153930664, 145.26327514648438, 132.05665588378906, 82.22876739501953]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011214</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:06:30</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>88.88922269517488</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>69.91416583486324</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>106.1051178594181</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>4709</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>[0.7430754746654005, 0.8429539048339204, 0.45011073337225205, 0.7357876661449371, 0.5260147067296467, 0.8559978631617374, 0.5350806028446405, 0.6258678161476883, 1.1237511894258752, 1.1705172055535455, 1.1413959273778327, 0.8572395372887303, 1.162658481259171, 0.5324503424768722, 0.8776140632685685, 1.0800709346527264, 0.867282783653985, 1.1709348097037695, 1.2575208637471607, 1.1180839642785945, 1.3539435489925429, 1.8764741127795987, 1.1647734121636617, 0.9875215847416456, 1.5349774727001098, 0.8238355150737295, 0.7216369888681052, 1.0884113737501322, 0.520342094612604, 0.8728618638401641, 0.9704538365163728, 0.459141824004376, 1.108805676678924, 0.9653628280694393, 1.8408778146899767, 0.4582024834417386, 1.4432841582058706, 1.884951989311475, 1.0363873914317026, 0.8710663321304711, 1.545042277635392, 1.0388026598021451, 3.8930763635151058, 1.2814276303685959, 1.153479239733601, 0.5563930023946171, 2.2949581062969484, 1.640158462085867, 1.3309384418429069, 0.9863458306727367, 1.5414363061669534, 1.7078111903179714, 1.2210908638379774, 1.9221477110694098, 1.3129685407637015, 4.294784287791509, 0.7797313769795949, 1.4764560858059819, 3.2268888436020196, 1.4196105136561947, 2.2545420631503172, 2.132745062211672, 1.25048056440489, 1.3585289905716278, 1.7486405499193438, 0.8433082099237086, 0.33019520185033735, 1.8587194984282833, 1.7094884961086692, 2.326160242276061, 0.9890764288184353, 1.4383212303525137, 1.9603775806684833, 0.22962962833323752, 0.6994423839237986, 1.2354179200808035, 1.6674814537070002, 1.0304296923230678, 1.3210608528067558, 1.8799735132222628, 1.8997570590288881, 3.214913134301599, 4.6707547374310465, 1.8207327149059354, 1.6260461512926625, 1.8177117172518453, 1.7972626764108313, 3.149458844972019, 3.353309987322595, 1.8112920108107753, 2.7012636622237487, 2.840498334091846, 1.0933132948846638, 4.8832567234024005, 2.662882666823331, 2.7227798725380654, 2.941983996364016, 1.938884734770474, 2.063871095502566, 4.664009477236247, 4.892137008147233, 2.955530376445196, 2.8973014595028044, 1.8549166274832718, 3.8037832211667815, 3.234078884423099, 1.4502712644167608, 2.3124142327557813, 1.6448834843485183, 3.4482047033320327, 3.0381764172556665, 1.863051450427636, 1.986227354714138, 2.608341698349837, 2.682858036840817, 3.679095148944809, 2.052330764940179, 2.7728740369589078, 1.633837379061535, 1.4583637732814276, 12.655309237670824, 2.0404930580639, 3.900159904909674, 3.868790092546041, 1.5041235528917989, 6.823787298490057, 3.403723739940117, 5.092630218353478, 4.440225536913377, 4.777716740076702, 3.4374759227342624, 3.412177698232878, 7.975997322717014, 3.711093559741586, 7.31430303500592, 2.567866867055587, 2.418744306095157, 5.3328977045049895, 4.851409735586761, 1.8356723143682743, 3.6219234859788894, 5.3265925573903194, 4.738970636460796, 3.943839114598148, 7.2576202262638185, 3.542980234367442, 5.164686020011408, 7.152618302215456, 1.3660438125983123, 4.9709074268058355, 6.48943096927271, 3.4056072946735423, 3.288268446052045, 4.079108852495393, 8.86092147439823, 2.387939932804473, 5.5465413118318505, 2.8968845942718455, 3.9318777845088024, 6.327391846542455, 7.303561493094162, 3.6090377241007556, 3.1430136277047356, 3.0006770085054395, 7.363451721084978, 12.422219053845273, 5.4188273599311945, 3.1550982595604697, 15.653275507004345, 2.540011101016709, 11.151895351895206, 12.31878130802017, 12.38739321451829, 6.105799442787358, 0.7458036383395189, 7.239490147005932, 17.518443468380056, 11.299982674347143, 5.311654606275599, 4.038604267229816, 5.705656377153056, 10.88483544174533, 8.48047551207796, 4.4474813852625825, 6.391799474667899, 5.884961135505874, 9.501993230536593, 7.235485893820188, 4.780166382677976, 11.438275014773742, 14.332537323188058, 13.556301125615745, 4.293833045570375, 9.318641952923898, 9.559441758952364, 10.140847779228814, 4.56981755770456, 10.481782726755045, 3.8344508002511746, 6.858179560510932, 8.802693067568205, 10.49110200616056, 24.082830529436908, 25.62065761589289, 17.509572835059007, 19.15842000325776, 9.670291235781791, 11.151192565991348, 11.261184085904459, 8.180634904053736, 12.87711400741472, 17.756334718923256, 13.491111291850016, 13.885569525203454, 24.36556572402264, 26.236932930700316, 9.053048565880566, 7.964961154546725, 8.524748835944104, 5.426412156466095, 6.888963979432508, 13.427969814834771, 11.081447335087715, 17.994814775174053, 11.008990530882762, 29.04064991972168, 15.43539164166747, 11.97321850184972, 11.596605752109737, 17.794443960512424, 5.491439924498847, 33.104442396975685, 5.466911944608408, 12.579820651994043, 8.487169506177391, 10.195714808804407, 12.133381664906487, 17.47515434523651, 19.278292707650653, 22.142252706941402, 17.52471121283741, 24.29986801470695, 19.88107606251115, 37.66703537432316, 40.44032970535829, 33.01794288740583, 13.263436076454832, 17.228353594846766, 9.880108209195289, 7.732612777216169, 13.211163460603844, 11.706876557617075, 21.8809749159315, 37.674051717619, 47.33739393815463, 13.70944561077187, 26.0141709959322, 44.82471505282077, 17.485412023877846, 15.98194903843962, 25.871720279539165, 15.646763455245228, 23.476495263405713, 17.90709014625798, 18.693200826077902, 14.785849483513987, 27.126370073483056, 10.58340785692055, 24.18754482698397, 23.427567937207495, 45.211780450060026, 18.15152434643985, 1.8095759015831852, 12.86907977681349, 47.51263743779774, 40.7970563670392, 9.831847437893835, 23.2301586975687, 36.862606814367304, 28.41829290326737, 33.795310466351374, 42.70045942365185, 35.086301426416775, 39.33273118953918, 31.382319604240035, 34.50600836108163, 36.15580992398526, 16.516545010516786, 20.570753151108498, 4.194967769275721, 25.23179781432027, 37.1202062392863, 19.983446427642082, 52.324552180112434, 38.70402360278534, 19.608894160773147, 33.096218582988385, 26.99654616977599, 28.673146155818, 6.197134924200548, 36.425143038398275, 42.08808115605406, 28.615656947335236, 18.692662345623, 30.531827677723154, 42.78399884244822, 2.9422749340357104, 28.56748746811605, 26.15496862953244, 22.11190657048083, 48.19343491490098, 38.57878793310051, 24.907841525418185, 23.514769765137245, 17.60112321123446, 24.92648443243273, 50.07798092305674, 3.077279267178135, 22.524308045677504, 45.660244057064325, 55.08463525762059, 32.55037316854613, 59.100488927829275, 35.91978122132918, 49.507672743456965, 11.14430337880813, 18.293682855265548, 23.18677524171763, 44.82994812683823, 16.40381363969173, 37.744950966785176, 27.12168180167455, 26.963380375101636, 12.916956186621048, 56.088989126069215, 24.56902763506286, 35.156043710034965, 19.782981779543626, 27.474880845147613, 22.429119098047458, 28.95898437975098, 25.81413280126945, 28.673575871358537, 47.47334567994899, 49.896835326292546, 39.57871027269874, 32.20211717974705, 53.26536640081675, 30.823919051839727, 64.61137483417495, 53.121672319391315, 39.804269441592936, 25.407176506322003, 4.168630605306046, 51.116086973151035, 46.40107811821869, 34.339541006011466, 21.384433317480717, 36.60708260426766, 63.31283271161359, 53.79366393788726, 77.2203655442879, 24.95343452016212, 28.724442194692035, 22.026549114665915, 73.26696520423353, 50.59607882507709, 37.69788037425757, 63.29806414852456, 50.059884958931136, 67.29814248131439, 35.27441240035875, 66.02246907548967, 26.933662728646798, 49.50302946282842, 40.06208937479791, 52.84339221595364, 50.472236902095744, 15.837034592203503, 26.639002246209692, 30.18383563263429, 21.317873879156693, 55.331628166792626, 32.33679232184335, 61.1533330110453, 32.229286764518, 40.66498815083046, 71.92223681055684, 52.639509630811204, 66.0735215967178, 27.27565883517865, 41.515612209934055, 56.25070056293198, 55.717715584715265, 63.507570001024085, 36.28263911958298, 42.31839875575888, 38.8159079604229, 45.064576229174364, 45.24526514833036, 23.09664564170223, 34.846156312934085, 32.10007864617194, 14.814858374586182, 72.52552571912071, 33.68800586201436, 87.3219629717716, 93.40656054408262, 30.696100752015894, 31.306860952619516, 65.66337666700775, 67.4990481655246, 48.112099492462065, 67.3469183029162, 63.60064017414925, 110.78046140489842, 65.60791688318362, 87.21567658684994, 66.62326050957425, 32.42951030532209, 71.3204895798258, 47.798929125725124, 54.78753948637205, 98.78837104248234, 37.29688579216764, 3.165896254574986, 95.82162347424209, 49.117689767046706, 33.05363764892325, 52.984241632060225, 88.3533606833292, 47.835731273629754, 42.76560882814091, 43.124997229121455, 102.97798101103807, 73.34269908405466, 35.41773129195242, 41.532611755368386, 31.55028531944651, 91.39248666347198, 39.977293227220514, 55.29667039140305, 38.990658157057474, 50.56498000807084, 28.867919660856476, 96.04953421266133, 129.77374967659551, 104.4586496723903, 38.054423612025, 60.4077100889977, 42.824719534500915, 45.99701497836055, 60.30753433353578, 61.65995508033568, 61.27836948605246, 89.3029769978581, 87.83727340573085, 81.49275853837932, 32.301175150630364, 100.56078728318548, 59.119826566348046, 47.44541983150332, 39.459865522443614, 29.072193625217245, 4.45309575347468, 51.60638489159961, 64.34016665644397, 32.18037023592178, 88.5480248316448, 91.36967494828829, 49.47039169432153, 29.500331893138977, 84.4740257529869, 72.33061207182901, 60.89455336752798, 37.58663613363394, 34.96533165155392, 74.78834163083779, 87.03162289068526, 78.09412083806023, 42.88537331881744, 53.56516976399712, 37.20393086946115, 39.19604077002573, 51.53359042695449, 72.07029976971687, 27.215596226626904, 32.47513411638475, 43.858782708131656, 89.17696754489153, 5.289094558547528, 91.69590471023838, 12.76531458253603, 49.81790105198775, 32.33989350054425, 56.765865091650156, 54.16129064307088, 49.73664436712207, 26.655739384923884, 51.55855091620527, 86.79264129057769, 42.736229270352005, 55.648426401673404, 17.93282080266228, 129.10129149603864, 66.85969380367047, 4.286742601422575, 46.3465010670169, 13.917068459875386, 68.68180040468083, 41.289352788620576, 71.4009802738511, 55.46419032493173, 51.29548826891184, 46.58593681746616, 79.87249425916757, 28.148139973636734, 90.33681586068231, 91.81474699980494, 37.8289700009125, 26.352995644078952, 43.653766983802925, 48.479996792474836, 74.40125043824075, 38.447563094600135, 72.80796079684286, 38.97828427033883, 47.20107694081875, 45.33332713137099, 67.5541357065607, 58.64839719114164, 27.63026241911563, 62.67013234861439, 43.68105618745946, 56.468981120790176, 38.24207072261981, 43.67539476113426, 49.54277061639379, 35.810372420586184, 38.20990883990499, 70.88293105917563, 33.28307025542936, 46.08495172239855, 62.61100621487478, 47.32250683369959, 53.11900581214422, 58.46592158821036, 27.735058735337912, 44.586366214640734, 67.0054343145892, 55.37667941796792, 31.99900823789745, 51.27883105274883, 56.66791231585767, 31.044793773673558, 17.631431887197426, 37.04140199057193, 25.671612894322784, 52.35965539491558, 39.18576245983145, 5.297669278276795, 54.1754683079454, 36.26706893436983, 106.38883348250226, 17.233463490373264, 43.755864334566816, 37.25740624601042, 55.88977932621947, 57.286691265347436, 87.87612987127162, 98.32737021247495, 52.5583238461884, 112.98924835892058, 26.92493008758159, 61.90427029238113, 115.62557322456775, 32.62292482654709, 70.73537104759154, 38.96872307133442, 63.9155007578076, 60.86357669401085, 44.96851916328096, 38.83214082854403, 50.91297121299041, 97.39018357311521, 52.6702063330219, 37.36388409203525, 71.35550348960005, 106.77401904634958, 42.975746603839966, 26.396044446666654, 20.10574762551188, 37.92949869800717, 40.695888867737935, 42.86797495854108, 52.424835730043924, 48.580720963371114, 39.32504808564551, 91.6433245034573, 37.95307463470103, 120.41146880764447, 80.03032341261995, 98.62367967623211, 49.90927808000379, 39.43105511005504, 47.330385365511546, 41.34000799751393, 63.89593563882579, 37.97229054131154, 84.86320470801647, 124.54692798404216, 90.22357722658246, 46.21298546927093, 54.00511311142743, 3.7807642042533205, 15.13974153293239, 38.37241474215964, 135.5173914960846, 51.447812799425584, 94.8790964368657, 42.49589286665431, 111.20619755050245, 40.61383953265893, 80.26077120987898, 96.22870919899262, 47.03878230622097, 41.09878008349803, 54.581623162927, 50.75863440088699, 56.0998668793908, 51.25031377511793, 35.71182239326361, 42.87612103922458, 30.114390109016824, 32.63001165097765, 99.20590513596763, 46.78512939682215, 42.436355514576235, 38.151853984194375, 8.516802581407363, 104.30422085087724, 34.93180237592672, 44.091085022004826, 61.72765218992141, 44.60317297570797, 40.325115242953316, 39.337166368803516, 47.302271197125826, 52.8107219268671, 98.77465112861564, 4.82954800892199, 19.022208073033003, 50.76466296866964, 36.114275853281825, 80.65956598362001, 35.93725667033156, 70.66864161910084, 41.665842225989756, 62.751014678175935, 49.151273139305395, 59.88582833338766, 68.43384116897684, 6.866715934890598, 6.778710574080831, 62.06351656178806, 42.916501299465295, 98.6614499796989, 113.67461899148398, 63.238502687604196, 55.08661693715875, 8.550585305327475, 74.97303796765249, 67.68360246777338, 47.14437833975129, 77.57671003222934, 103.26654495284572, 61.12108796525916, 43.193263307866594, 130.33725027072003, 92.89713490247503, 107.23700783125771, 57.82936189643749, 7.771954255386175, 61.016812173231244, 78.09565251473562, 42.04609349410612, 51.990510782136546, 91.15748668638068, 78.86044834667351, 49.22222182987655, 70.47729206994651, 65.73444597558974, 83.69319386987348, 50.467718831221596, 76.35251157077914, 44.432108631553106, 7.818835645640384, 49.08218223068757, 40.50905910547252, 52.958961671667474, 96.19052986470659, 44.01044451692584, 76.89778937992823, 57.34312881130848, 74.08730940338435, 4.887565183290328, 54.75287756419077, 35.333762501961395, 38.14466837934309, 46.04785557663772, 114.66917684293145, 69.30095281470138, 53.696929388588785, 431.5434925114224, 52.81720142609521, 72.03725293512309, 53.29938491560185, 55.767867935036634, 72.27027574324731, 39.10129263057363, 83.57354227184531, 76.03107087729377, 52.34996456066587, 111.36957571495753, 50.63614291663258, 60.25724538244104, 97.8444836865846, 89.53508163307417, 46.884605008620525, 61.884644776470054, 75.364325768528, 106.02147078354949, 124.29209813631927, 46.68581741482942, 58.46734371033218, 5.1808081935427, 53.72228654180313, 52.85173902573985, 29.303243433631923, 78.88895815254062, 69.64540515865423, 36.99027635036594, 59.47473512131794, 58.56412283116723, 61.42332027720132, 61.1883040287293, 67.35280864942071, 70.56660549406651, 101.10369736373593, 44.71426476000975, 41.441888050971734, 39.39060422408955, 64.54965929801193, 36.47847319441659, 97.50598220546644, 40.51678680874206, 87.47090810843886, 100.91333219054577, 63.142440746511994, 39.26723855517156, 92.59849274478721, 56.70275334053867, 296.6075951753499, 75.03163835775739, 54.46304343326654, 55.44823469382776, 56.98409698069879, 46.412677932114306, 67.8225112512931, 71.61321241075126, 55.947060757633395, 74.78240397928592, 49.885180601342405, 155.04860102341547, 100.3069927443218, 51.60048005696037, 54.8487243843143, 129.0845380819613, 84.73020852782321, 67.91711821515166, 7.745191164614528, 61.28689728233031, 48.358906548286285, 110.0107100508903, 94.1620382188711, 64.00987281572802, 158.3073212868488, 80.98794875948519, 88.8540095174007, 59.2987337937941, 44.03993103213097, 7.22547486964957, 38.48038230486299, 44.199900603576204, 99.85359412574414, 54.32127256187089, 65.95387790645513, 5.589133860055151, 52.32032857126554, 129.0288051344141, 56.76312494474839, 62.745296384963794, 67.26907578437968, 56.383936825564675, 73.81765550118234, 68.32241418596263, 36.081518526966555, 57.60137272428603, 34.500939949789384, 79.28092004412741, 49.26065117510784, 6.389192326250638, 53.84827450552399, 38.914513483694115, 57.99852671921772, 55.005128987053176, 72.56872864852511, 166.5385884299665, 46.576417026743485, 30.364851156525816, 47.359760846830206, 38.60468721182482, 42.185677609402354, 70.06740722721088, 95.10357912333323, 36.63044108649656, 110.23017825466323, 45.57666828515441, 60.96564315681116, 66.93468235434909, 105.14540595432787, 52.35767116698544, 56.13827253298701, 47.75717468261693, 63.65629969525237, 41.32954065258147, 155.73046875925832, 5.0204944782484775, 78.97755023727466, 103.97104945671725, 47.75431790571507, 38.003258532387775, 75.84305526206981, 88.05609239530185, 29.300656317408098, 54.37123828170194, 57.21575755235421, 49.351945795007204, 62.119117133372, 104.31961279308308, 191.44004866548494, 35.38767742754019, 8.062004794072731, 37.611409036252, 52.90557236546859, 57.89119931932634, 36.80154109692211, 42.37096698079917, 69.89460053099187, 77.13603733361015, 47.67875736581758, 53.66225786310966, 45.08638646623529, 44.83091085590141, 135.67511704974333, 54.699392261792376, 55.78761882172496, 58.92108385913716, 52.62039812990146, 49.365076071833016, 79.7019004394685, 82.13669675606788, 33.825425559079555, 71.92459195933941, 72.5255528764224, 106.06881439101281, 55.268970535460554, 79.26716231922312, 59.41430094178201, 63.5458839321557, 24.806890881566947, 66.71763564916529, 82.14000418239681, 6.591246283053749, 89.38941939710426, 46.55164161859746, 90.1329465458551, 58.55507121752506, 95.72855919153008, 175.3285607927861, 130.21779641030395, 217.3503941437906, 114.0733961886302, 80.7865785634012, 82.3870876473997, 62.77231139317923, 65.19032957346013, 8.891332510393282, 53.208364586148825, 61.1831726831839, 19.99027764473769, 56.82548787154109, 59.49608993515736, 84.29469630276932, 103.68918467200277, 39.489997955510795, 128.43554838467995, 73.29050948535269, 44.90655094785271, 88.13419632793267, 71.07274762112111, 39.337985290349245, 89.56821621498771, 97.30244570770849, 111.96039647769574, 65.88152036681566, 141.30025719011016, 86.08458140356288, 59.76057819523194, 80.54559458249243, 68.89208762029634, 68.40358129269782, 83.29775025447759, 57.03720391879179, 50.51340772579341, 90.14629014713623, 62.27485754895555, 68.12233770689039, 101.51197409730794, 47.965768425664464, 63.031169399942534, 70.68059448921646, 131.74659865698197, 50.21566031402452, 104.53599237464749, 161.81956370832165, 126.5406938021607, 47.63619857461775, 47.736027550993974, 60.77072522168878, 56.106133372979784, 185.18744247368295, 87.59583169417563, 4.938276623898963, 95.41167216274106, 72.55981201350085, 105.12353933127325, 69.11103502640758, 53.568630386747515, 53.245874624367865, 147.10835144622393, 161.72729714285586, 71.67494712185777, 51.52156145340942, 98.84379311647193, 56.010293353888024, 129.93028209050837, 149.80826641391852, 79.5541172611235, 131.49796829267663, 68.36862461714237, 124.94049723391926, 55.74633665869, 49.38644045319792, 46.135729401376615, 61.8926613077176, 60.55605095863986, 83.92438591750366, 73.12566448533605, 51.270745782116734, 183.30712804018236, 32.14655343110294, 170.7931837470124, 121.44794947201193, 61.920378400880864, 225.1363654691449, 61.85293646978955, 115.87292054426685, 54.11886001277042, 68.48754178860354, 43.1534596724404, 62.29332056929876, 135.30561796134134, 61.906034166229624, 166.82212843547248, 142.54853850132343, 116.5400704282241, 37.14747642717771, 122.89102047537351, 97.3691133715273, 59.02518730896409, 145.30899194377537, 40.38476945224907, 140.80574906972498, 72.253249132419, 68.7154788358603, 65.60023193887778, 48.515716686627, 71.44723696691236, 69.06775690882155, 84.86316486669494, 61.21175009076964, 53.820847339193286, 104.88663230455757, 38.67235423928122, 197.78449034177362, 120.4668838445851, 90.31928342436534, 89.07708626894411, 42.94153282447426, 63.626431865401415, 46.712952031710984, 74.28683444619153, 73.43501107318802, 89.9216600199689, 80.69101370041905, 66.96590181487281, 109.55841616126484, 55.54443423668623, 52.92413325921502, 39.29388646629756, 42.13883187838179, 88.22711794093634, 116.70018915195115, 42.59355498925561, 168.7804787545721, 72.09295339346878, 91.4157145980948, 67.49022601120852, 81.62391992020116, 67.71805103217248, 41.38080934837378, 37.86775524799612, 206.3941376550672, 72.2411229582766, 58.72540255264802, 12.674020506205405, 100.6179581151004, 84.8867611582316, 60.379616544202406, 61.64665187153851, 58.220404147204135, 58.74319050399235, 95.29084929070616, 33.05623981824818, 101.85714460024933, 52.63607790632762, 57.77930662472241, 106.75141358077272, 97.94672707169502, 61.08408278143486, 69.98909355868174, 90.9518840854064, 38.61951910207932, 75.16661651744424, 82.75334642456167, 46.7301412307762, 81.29690725988894, 63.43703249090877, 73.66913493114424, 111.92142577492523, 54.43663971986751, 45.56630542804506, 60.62734171460955, 62.42642850047074, 69.9347480808001, 55.75395182675902, 137.7709131121599, 51.81295649442585, 91.53902795484395, 100.55954398071056, 88.07438191015135, 146.23260724234737, 113.20787522178819, 303.67401131128287, 83.97371044070061, 110.84180840756511, 65.13484929697681, 59.23633754190264, 202.1895204401034, 102.62455627208419, 84.76515678861595, 68.34014042212924, 73.4876058082751, 56.82072474907734, 83.28993430174617, 63.13550540783861, 52.50981188069542, 14.943882045566852, 57.554911127480565, 44.97054214190233, 87.1671437405573, 105.77903227345912, 9.777123414596495, 203.50992907224617, 44.5405894387019, 120.14979468167682, 106.7981203926857, 64.01282414737447, 100.18291490308975, 74.39290245310671, 53.96845287569511, 51.778411952687094, 93.06653633345903, 57.17782504631972, 100.81891724057613, 50.47738959441157, 38.30167441427177, 44.28908449043761, 122.99516144173468, 74.36689292924544, 53.33824267840744, 66.9018116376793, 71.14906821376553, 63.612813201568216, 31.753268670378482, 138.68642470136413, 130.56949689742257, 88.37534377459471, 62.46210321531774, 81.03269181404659, 51.00680652243415, 67.3552586141678, 74.22490272931415, 67.29460676958216, 170.38431061237014, 47.35949346648406, 169.8576781707451, 67.84196815249837, 105.88777018738969, 59.25847362558025, 86.01428392277575, 62.75324149434321, 73.01401636413543, 9.278954270444222, 135.84149136923156, 81.80740623458924, 89.84562582312473, 52.87042602184087, 62.584963452223406, 49.70301885820642, 157.2525378578954, 79.74820302499299, 81.91257688827962, 77.7354132357573, 76.8563921494783, 40.47902237916319, 68.28412911765832, 76.48539593127687, 91.87574820317644, 105.54558813307865, 49.74270124740702, 166.27505330227058, 163.92388940827993, 67.36525690124631, 59.79139596833688, 166.5620821117276, 86.84591471874892, 61.702440345099795, 19.186319603185495, 80.30843125679503, 79.03573153934775, 102.55289797938603, 88.76739267030081, 147.88507542536263, 52.854120027335185, 54.35031137510892, 51.52388019089968, 100.86609209494766, 49.20303689024624, 109.78737143961114, 101.71576077300575, 86.27397801799228, 73.387917610386, 26.710281679980024, 46.283008917660915, 73.09147505071904, 66.03683733477384, 71.71677627552843, 154.58304131126462, 106.67908858674515, 75.18365876654474, 77.60973952451887, 77.0848653925762, 110.86696590751286, 51.507345559660216, 61.17093754213342, 231.9758702057871, 109.5706693082697, 70.43384383176101, 52.50793040752902, 52.80493525949632, 98.2135968115702, 66.54915697719254, 54.02980988352867, 55.364144842733445, 58.80271625406797, 96.2224578858755, 91.97044522517719, 111.41082937406635, 181.47271991983953, 54.74967954583326, 45.666107753058505, 83.99825346537571, 59.38005235825784, 246.27547395569906, 47.87382050025302, 7.851785240736027, 35.344635143071784, 31.556003969937564, 134.58633516395045, 54.354472675466646, 114.56074827091207, 69.63368865810668, 99.71393144065452, 7.762217157996281, 47.59185124706784, 42.046222521200086, 131.99450705447543, 113.97592293817009, 53.75692326300829, 148.68160281395419, 63.83201498696707, 40.021225679310525, 48.27043744883269, 98.50380384731919, 65.91441230722992, 65.03928646276795, 80.58733076306838, 42.99995684046395, 74.70356816888065, 63.64048012077562, 99.61058026310768, 106.23199295945174, 58.15150327124822, 46.189616174256756, 92.92444236645348, 50.65995036590467, 172.62875396064462, 20.328630775761173, 65.83507142889778, 114.3644000006625, 114.79016068666436, 35.29911634690146, 43.872668763741515, 72.08804900776254, 110.18182739815802, 69.64230248321273, 226.94351688365987, 83.17082527014793, 10.491049218415682, 12.729150256715117, 59.33508757998874, 73.03332273754516, 65.81670132345668, 84.7183989800833, 58.02628926608967, 145.5625803705018, 61.63451189402904, 146.90993497853577, 50.68786027525683, 34.50353237826119, 58.942792700632985, 110.16243185802635, 6.815699967844399, 78.12726685429698, 244.30764395582355, 92.49804289909507, 47.211020282203926, 103.89326140003135, 62.285179666578195, 185.7137833052511, 89.23449605223172, 115.64316683586797, 70.19781281130304, 92.99250146047846, 77.68285153251823, 88.3208014434497, 48.032680104700624, 108.44785776478271, 61.66949201466981, 60.922596271802966, 82.87136821071684, 132.44605824488434, 91.72198003650036, 73.94769280733956, 43.281253747091256, 98.2935350593821, 9.421404836555377, 115.00293327510813, 117.45053541204973, 37.503952424437905, 135.09033843327356, 43.4228080238213, 8.486348423031448, 50.48891303737398, 69.929529965782, 77.2624400987995, 39.89124748545142, 78.31820979180037, 85.11502592444305, 60.670982523325, 44.20249269255483, 66.61725517695508, 139.6753578195998, 81.67458055750977, 62.37927407205922, 98.32300698590542, 40.09054587751911, 46.625866616947775, 51.025332424224686, 112.6997613900126, 61.321178351001706, 69.96977473922284, 116.5694388845572, 68.37938397032298, 104.33873513330691, 68.90250247543989, 60.461365302677095, 74.69632395013433, 145.16013290871308, 67.49020253144974, 104.96779571711431, 118.08988606143497, 141.15399782195342, 92.2679711414976, 170.6527648435169, 99.43249308684499, 65.97496144066106, 164.77908060766515, 51.675853718624225, 8.46250526249754, 93.59087226657003, 112.16214260118483, 101.35528958885203, 51.51416579707541, 94.8665473467864, 106.51410654679124, 56.12096669654257, 44.733773133086146, 102.66206749044201, 155.8098796985664, 51.03121503799713, 43.87103046454777, 177.13541130394447, 144.57816819808983, 7.29675206343726, 100.59185910669314, 124.0047374159944, 42.012551139946886, 75.70798427577354, 129.2683469450325, 44.47136089590681, 146.15361617370374, 170.58669937099688, 79.87652782813683, 38.79088356104971, 88.54612215297323, 159.73834152489778, 89.15334162901286, 54.82353592454453, 158.1003239899552, 28.187808234860324, 76.03979833465652, 168.48363847726728, 134.74185030920066, 125.36249034582228, 80.57499884704143, 58.5974966021359, 66.01732226699022, 33.858080037643475, 80.23554382143276, 129.17070852439156, 63.19397581437278, 68.42015970293997, 55.12179232129496, 62.27784576308597, 88.00778854821615, 59.057102162822666, 48.07267906426588, 50.281678333987784, 40.06556399659841, 67.05537143879157, 85.14849308035959, 102.36320255493276, 92.60168540309168, 109.56589104246956, 105.64994548604626, 65.12539371170404, 101.90943112835102, 41.2569882950961, 119.22871290053442, 61.15381732974488, 208.11110462347756, 143.13983740360845, 64.97992768014612, 49.764170775704066, 75.855878369285, 111.05663893405354, 65.07267080808353, 59.34299419898102, 51.16775058828258, 66.30049907765886, 158.4249980458964, 107.66413082849304, 148.41731233830518, 55.645453993434664, 38.011463611267494, 11.52320955000481, 30.99954921903554, 624.3262380760134, 31.853335347396115, 120.39358828710228, 137.9546562324699, 172.4290491138581, 112.23356797330788, 39.83036892832015, 56.646294001753574, 135.86378944373885, 38.48541153896562, 89.77722686717499, 45.337675118457135, 98.95289515917467, 166.87429599285946, 101.3887751917527, 54.8007645560088, 51.380604804022724, 59.13709241047396, 80.99385970506441, 41.25817140263627, 6.611537515250003, 79.23018251636846, 212.79558779062023, 80.96952777799117, 73.39453305202682, 98.97348093086413, 212.6716890547899, 86.32568577190158, 111.16454967045317, 111.50921196106376, 78.97549492374606, 178.18801999861137, 55.46351075695667, 63.665918316189995, 61.07705668277115, 127.31239059519275, 68.0657573246924, 51.145111670783436, 55.14702315176241, 104.31589546019487, 67.81770011570926, 53.581471739596715, 94.20901155817016, 235.8933345108891, 95.87982806015447, 54.76786658498017, 87.69860751418824, 513.0675148730012, 132.08800691673804, 68.32527471895857, 57.13023494716519, 83.89558085603979, 62.21908030451341, 136.00187463727937, 60.186022946588764, 52.27882597365692, 121.39843499640158, 80.81923675469281, 52.98958040589849, 87.56702401873285, 92.477387686033, 59.04689993870385, 218.42640962056697, 63.93439022569666, 468.56149069412044, 99.20497602828463, 62.961789485517684, 48.89356760775277, 129.07874394251942, 104.76726427748957, 180.43066543039737, 73.90423054153634, 52.79835754549281, 110.61039578690887, 56.17628219636266, 57.81593420394269, 86.30713931989654, 166.09823190768077, 89.59573432669966, 53.39680550605944, 131.00646831800236, 75.63894992977045, 46.54202420719372, 423.23668618065807, 127.22416250332385, 69.21404135769949, 48.60564544121381, 43.145934383843134, 152.468968798827, 69.83297066342179, 112.97567453650551, 122.64276055457265, 56.935018946753736, 59.82783976868263, 57.70922917843048, 59.01169672938535, 137.4151179517375, 47.33632475411276, 58.37855636345309, 80.99732642649919, 154.5711798137404, 119.5233831503898, 77.34356272811404, 178.95979443809767, 47.95470761405898, 60.63568199586664, 128.22664555815612, 7.039570984078563, 103.93856343113926, 61.93671543120618, 108.36380792265558, 85.9809007234173, 78.11891591222266, 106.99763378125303, 43.35554801775701, 47.404798702108195, 50.4960264989509, 109.69372229778033, 118.61888006981658, 141.39023449731314, 179.00919350560739, 102.98270261895341, 108.31145334632585, 61.86577659116485, 156.85852111167569, 47.496882175421085, 55.53294198732126, 45.660351323989374, 43.35712283793236, 255.18038848166725, 54.6655638398691, 79.50319553989412, 107.86138446013824, 146.68340330734125, 106.31532621528216, 76.89359714203997, 87.79450108854265, 97.24047060768741, 96.79192609816357, 59.67647942222416, 93.00277399194222, 63.15116768782022, 106.69974814104798, 78.2556323925597, 62.24788444470516, 73.65097322170567, 49.274452393763305, 100.42937993003909, 160.7031009117356, 48.73420525902535, 75.2915630683141, 73.36245859217135, 55.57910442659696, 166.5347358846123, 6.145525513698858, 59.33009166932294, 123.18182537032337, 49.41762459563309, 76.72633220334959, 103.8938696684478, 92.08216038599939, 54.351405946093934, 95.47871300323798, 54.35298228451214, 13.349030863390684, 66.69288601662655, 154.97667085075798, 57.332168958353904, 62.890447896810926, 47.60005888281139, 93.93370581199632, 182.35963819815197, 130.41120986690402, 140.92890444819804, 60.24676169645877, 93.3845234389851, 120.61686434848329, 79.43126257092374, 93.95577204800941, 140.8037880594286, 63.71026627386837, 43.330379952009565, 67.29396126280464, 105.16712885913856, 50.86852167971458, 35.477455296614686, 127.17115465413539, 107.21180465705154, 48.2966834189839, 66.88616348158357, 77.10902519949583, 81.42716055097124, 133.53588108860308, 100.81038335758872, 148.9863649256062, 5.242761560474308, 37.58354467814856, 53.04122797847155, 130.00605231486625, 81.30958491492353, 99.79145902937636, 33.22751739642196, 84.79707733434398, 12.489454024627099, 96.6356128894135, 45.576620484149586, 138.61557984284863, 63.87620560119324, 42.60876726826047, 8.090334699908842, 146.03509895165118, 74.83943172310794, 107.86748655162373, 96.41719383277945, 89.37006451138662, 72.41600634915257, 327.7067821608814, 5.713533200680677, 39.90407865157462, 66.73110277254074, 66.27329531512336, 100.90419914805823, 59.39093677730596, 52.411364014113026, 92.26184361258446, 115.25179872148381, 73.9048863451948, 102.13250826355339, 77.73153225157228, 83.99061783848478, 136.9796514577386, 68.50600476041772, 124.0823028593924, 113.5686457140425, 70.16203749263462, 144.69130992244143, 38.85184639269121, 99.38132094008874, 72.25146340614378, 63.457581149149064, 74.59880425577988, 100.39581420426731, 168.7492093256681, 73.26064236021382, 54.84950398786521, 60.44108709212421, 65.49411436854129, 146.00522763182974, 78.42914706233506, 128.49638931496347, 50.52444418581285, 58.31553659906684, 145.556007007324, 134.1002558510567, 53.85698467609524, 59.93109002944491, 74.44474004537994, 45.670674892694294, 55.076498927665156, 61.4628602394692, 56.785134369329214, 65.81537063160751, 53.16798661311112, 103.28061167634176, 102.51994159376177, 98.11902224643816, 110.59265681796182, 57.24763943630933, 158.21712547938887, 52.83162466819109, 63.87663602532852, 62.30762454629739, 287.4198591674875, 81.19757826827097, 83.15805040597417, 111.84424625101636, 64.97240519815824, 41.243178295609226, 91.17277254564375, 87.875015267709, 53.72381878737569, 71.3188972962884, 77.38990523493392, 79.59634592768036, 102.73069835052529, 59.93173772081423, 81.18149479004681, 181.8178844018854, 44.622787135730675, 74.35</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>117.398115606308</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>77.57533555107825</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>[132.60726928710938, 177.53530883789062, 62.73810958862305, 192.7012176513672, 347.95751953125, 107.25402069091797, 66.06195831298828, 56.47565841674805, 55.656314849853516, 55.10020446777344, 73.3519287109375, 94.70220184326172, 298.0073547363281, 13.494720458984375, 103.66983795166016, 74.32172393798828, 61.16044616699219, 159.2171630859375, 112.33750915527344, 86.51134490966797, 65.09469604492188, 49.03791427612305, 101.7927474975586, 73.04530334472656, 54.40673828125, 68.6087875366211, 257.7593688964844, 101.51750183105469, 108.8827133178711, 199.8745880126953, 166.2242889404297, 117.15812683105469, 108.49653625488281, 449.47552490234375, 172.49923706054688, 152.84217834472656, 8.644379615783691, 200.34181213378906, 90.66146087646484, 115.58428192138672, 61.113189697265625, 217.3282470703125, 47.79256057739258, 97.88401794433594, 70.79193878173828, 228.25282287597656, 47.0992546081543, 21.304288864135742, 97.5264892578125, 95.22174072265625, 159.72076416015625, 303.47796630859375, 45.11713790893555, 59.632965087890625, 48.42362594604492, 86.3714828491211, 109.54113006591797, 68.06111907958984, 222.38197326660156, 95.7950439453125, 65.33130645751953, 149.57528686523438, 68.30615997314453, 82.70047760009766, 77.13939666748047, 53.86267852783203, 197.7880859375, 101.45763397216797, 286.0135498046875, 75.33302307128906, 48.334251403808594, 138.84210205078125, 63.07204055786133, 68.4803466796875, 57.479644775390625, 100.92115020751953, 83.99578094482422, 99.84783935546875, 113.2650146484375, 46.65465545654297, 131.8516845703125, 308.5207214355469, 212.24693298339844, 73.01914978027344, 160.8163299560547, 90.08904266357422, 88.68103790283203, 175.34132385253906, 108.34219360351562, 77.2236328125, 206.59597778320312, 66.06932830810547, 86.25226593017578, 269.9859313964844, 46.155967712402344, 38.6164436340332, 86.4067153930664, 145.26327514648438, 132.05665588378906, 82.22876739501953]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01603</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:52:15</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>92.87847997134118</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>73.9342401989328</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>102.0968532897425</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>4894</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>[1.791905026366888, 1.3010169958952844, 1.0150659413346061, 0.9433648147114375, 1.0985008911394603, 0.8888757802655948, 0.7971336736282806, 1.2326146338525328, 1.7619542232915808, 1.3099188177238998, 0.48923231660157535, 0.6593706449355985, 2.3124665737249352, 1.0235254395812428, 0.7094685862087237, 1.9369961681559702, 0.818134232836132, 0.1167570854957368, 1.656721279034246, 1.5196171521854092, 0.9056908605171352, 0.74923034897314, 0.7942249491040085, 0.6925880935252906, 1.5417286781056552, 0.9353407922771527, 0.5944822349840808, 0.73868651271964, 1.6423732950161432, 1.4922250217544855, 1.0538238224661471, 0.850817721408198, 1.6274402340087666, 0.7202557569062857, 1.3875038147857741, 1.0572730447842864, 0.34067507537688735, 1.767262153962756, 1.235853315962273, 1.673779509280209, 2.6767923088043624, 1.7308399046183693, 1.2026002660490425, 1.9495777879858374, 1.1230980079905328, 2.194625169345459, 0.8535736373376334, 1.5432049013526439, 1.7891005337109362, 3.037811794785571, 2.5390872715370145, 2.218842908018713, 2.206126732014045, 2.58742435942109, 2.3921828495469666, 1.7066015801477927, 1.0522756417850256, 1.0054658029755654, 1.8053724477942261, 1.804670859892601, 1.8822323044983034, 1.3617662698162565, 2.1981627394970396, 1.9218669424340689, 1.2473607016321473, 1.4659899005827064, 1.1666760590511553, 2.290417200367891, 2.5728678130344504, 1.5378812565310707, 0.8978681731036975, 1.271506547513332, 1.6741948684390862, 0.2782461206956111, 2.3454133418520033, 2.4332134312696283, 1.4138974636454038, 1.9455154420808003, 2.320562165717182, 1.7216287602301479, 1.6063632864564854, 2.7102268391051494, 3.004531701405533, 1.554626426001957, 2.280956458856382, 2.630608308392429, 1.6042341226898427, 2.6290510018491138, 2.9877692580686337, 2.302042723268449, 2.1553092346774925, 1.8860526450558133, 4.9640650370067005, 2.5218363151291316, 2.0894406008217916, 3.181309816938488, 3.1110708086581, 2.468477223544514, 2.656676961230786, 2.5796593951226376, 1.4488383329748231, 1.1550711352096417, 3.5293175809889816, 2.4558861955539673, 3.7213564837643447, 0.3021907694569457, 2.339538912550999, 1.5023188486135537, 0.5758921914485103, 2.7547641770567624, 4.435150079660148, 0.581000519842096, 1.8871377876085493, 2.4843147585787255, 1.957266120743147, 2.8435284891701498, 1.8779515509208886, 2.215873736996479, 2.7989398817547153, 1.86863076480136, 6.2610905515814474, 4.142163828162156, 0.7244821104711041, 0.6484526125693522, 4.5020007490678005, 3.958862536628215, 3.5593529223827813, 3.937697330718128, 3.5085067803999213, 1.672410723413894, 6.1668654218337, 4.921921893950546, 8.17221382131015, 3.01650709147298, 3.66540036344841, 4.802521163215286, 5.023663309577043, 6.040723896458913, 9.90371807068252, 4.180027919994757, 7.324714378166915, 3.4552394218984253, 10.439758546375435, 3.1833389645158854, 4.5428828993897294, 5.261112241160853, 5.912097810987724, 2.8544489047912345, 3.477632931566342, 5.496637255247493, 8.852328505365751, 4.5826004387075665, 2.838013422699156, 3.826772182997652, 5.160063317531868, 4.486460597852789, 3.159002315983087, 7.502686569350438, 6.124787743313522, 6.364393722106999, 10.071911109825972, 1.9086435965970352, 13.777968555428613, 23.172773996923713, 3.303011018752318, 14.20744517779001, 10.781206760082268, 5.870682962553566, 7.198077744654327, 14.072850922950677, 0.6833414944852915, 5.1265444109841205, 7.082840945260149, 1.185230302295049, 8.567300974270985, 10.152418055214259, 8.368846279144922, 5.104072454690381, 12.401216016217212, 1.5077381601413844, 3.9464981259807814, 4.1277204375588035, 9.529073981653172, 4.41517460862186, 4.13727806362454, 13.668362111146557, 5.269558488624456, 5.418796835785533, 10.508397326907446, 1.9731556945924367, 9.35747944479535, 11.551702949326687, 1.3612704503569504, 22.70419746301439, 8.003453273382503, 5.85766437107236, 4.078385625179295, 4.674930120617179, 10.225808822522533, 8.275047895625177, 18.33382765198861, 7.619508342981999, 5.85112408757491, 12.376585063856567, 30.293341030241656, 24.448852754722548, 17.519824584042595, 13.602243024127018, 15.929202183822317, 1.7980239466631363, 20.540012970871498, 8.550549905589307, 5.107723322963023, 16.535865776270928, 16.715685789331953, 27.559934615290317, 5.871632142873665, 1.4872119246436246, 11.643945600828793, 16.64881598593775, 22.4591160235992, 14.397316185055251, 24.402618904091156, 18.913136115602057, 16.58496180641556, 19.655474295980415, 14.51586241048827, 8.967390493935003, 16.864030406255004, 10.419670913769611, 13.473005161558621, 13.798447655360102, 15.268505927163853, 20.78234186736726, 16.37581275929988, 14.058273680755143, 16.418230837835445, 23.88462563703701, 24.8872708740144, 16.818091181940453, 26.925547996835466, 10.827927423729841, 12.448642222042443, 19.62565781544332, 20.29621811133168, 22.134867079436592, 19.66709765210296, 27.589428890447067, 8.948227833362466, 18.49685573816845, 42.99531816334173, 19.848390986960737, 25.708660319803077, 22.449019143723593, 10.496494360996108, 9.853781445618006, 22.754187732617602, 25.517440708176927, 8.229945978844293, 25.112013484554158, 54.645786548213415, 7.319992196656946, 19.513143033443036, 17.69795517509939, 19.986454510206435, 22.467558010549336, 20.842058562073312, 34.65098206010161, 30.49428615265586, 8.566258094495614, 14.577438607236687, 25.223853639112267, 21.19876854024204, 41.959559321464056, 41.53623396749895, 27.257807594809375, 18.13991612325218, 29.732038298302523, 24.6305313347685, 21.269343177847812, 50.51139644865968, 18.013624186269777, 32.91053255543198, 17.45542289054734, 22.407188701171574, 22.601723679670876, 16.645624022181902, 1.8913823712459976, 28.108758375597347, 28.91926335801034, 24.024677419509185, 6.702763017996514, 24.21248710286362, 21.081871251371798, 25.15347833342394, 41.84294026890452, 46.30597161965847, 23.55854389165271, 35.01735525432404, 19.995649232564407, 33.88502200057036, 33.88447228598672, 33.4095566418075, 34.96808980267317, 34.47695049587563, 40.22485924212042, 28.73020730678259, 27.842414575939415, 20.876700443023243, 4.8020500586515205, 45.261126221712644, 57.636450986316554, 41.056133726545845, 33.95071827162646, 29.27378923755751, 34.06433123681448, 55.37173408392715, 41.57620596211573, 53.11485956731456, 37.164917549777485, 4.455663937634546, 18.490472088442715, 36.34767337063336, 41.017010058647784, 28.455510968859407, 30.56069078169406, 27.678338358852088, 28.459808572884814, 48.99271271431106, 25.518037998098528, 20.166191934896194, 18.96438386282776, 29.48636630610711, 72.75033569218672, 54.45175528748937, 38.61551845853181, 4.071960623333411, 10.674533120370228, 32.19667448243843, 24.968999910375157, 13.653419332502063, 31.86541629210018, 46.07843141002158, 25.4686364831154, 37.578538593220124, 8.987114222241622, 35.8512375005983, 44.20255117992451, 29.821866350217693, 38.43047090790472, 66.09019307439704, 32.41678513867279, 32.0490704083456, 36.84776161049775, 27.703525979980277, 65.37568967195419, 50.706000919006435, 72.36822622483702, 10.530563683407868, 6.2940573827367166, 19.51301201698688, 16.744953476450995, 19.64565329937916, 36.7304505473473, 67.92277251844642, 27.83750849354939, 71.05947070576163, 60.57284047740022, 45.19259503582297, 65.25282909958435, 51.20309412619243, 28.258376099562017, 60.46449908560553, 5.123643572409799, 17.51157920215477, 31.54386828629317, 38.941174711081146, 45.72485965672568, 40.029465731858615, 68.35025418210053, 55.45505349274063, 44.31381620346688, 49.42497855523662, 41.55594576532728, 52.63306891623221, 60.04294347795202, 39.070283972187966, 45.35480347926433, 55.19058226753481, 8.149513187263057, 47.487790542600465, 41.651557165969734, 19.979223668553644, 59.38669872756424, 47.62673204251652, 57.48905406216047, 22.900106369443424, 33.99589404179026, 32.95113275083658, 54.972822250887084, 20.810558136072284, 59.153408580309396, 40.484885396024445, 75.07438083745203, 31.522911074414132, 38.365940220263035, 35.943105377795675, 57.13704211263793, 44.9208901021943, 40.266084757314665, 99.66782054549766, 34.8022318339232, 43.49426430057174, 38.339963588266976, 94.29437370089978, 34.06844631243059, 44.092284070641895, 34.444662363282475, 44.33486658850188, 37.46672003765845, 52.486364142214896, 58.76569567153347, 121.33635304385186, 6.369210677841172, 58.143687204651336, 37.64919671092013, 38.55419450496247, 29.344266884814754, 60.56374175945956, 54.62679602168081, 54.847752826930176, 37.701823938622766, 47.3524711015876, 3.6798415998229665, 56.61797937009459, 6.79885590969346, 72.85957211344189, 5.200934080492342, 23.89394442242345, 59.0529168570508, 83.90442220575491, 37.86528948786085, 71.02278752034296, 29.840930355727316, 37.75146249744752, 53.79165063936281, 38.75357021700282, 42.257303952903456, 55.637573475471044, 40.30876450502305, 57.89463159348971, 44.779620557758726, 29.880192603104366, 34.82193986994567, 47.67392266560487, 32.44992727942023, 41.17907740152336, 28.429137429317525, 72.01684225826052, 74.03221868600683, 53.20771632464036, 37.46663802211991, 52.56831040455813, 44.67178094391978, 29.657860395901626, 36.698057434826694, 39.91075222837209, 49.34337977752497, 86.59438391974366, 84.9505048696406, 69.52673610183528, 40.260080547898376, 60.909556487883904, 52.21326595082048, 126.57854837149875, 49.94742726102981, 36.94541388870338, 96.79065285249806, 41.88819719967606, 75.4562989957606, 18.990628793196674, 38.38021004788993, 67.65701763717946, 46.25389518187263, 45.067591574733136, 52.79102027671692, 34.71625765208127, 28.91143833017233, 23.605884767181852, 36.68443964763187, 42.84211657896953, 10.677991399607917, 75.29464306420452, 35.89047540462664, 69.73437260459134, 51.90994571809972, 30.067151213651634, 81.56606110483875, 46.25706633435722, 132.64980890423186, 80.04989556703532, 88.43808234172118, 50.83610875765218, 68.87285943254052, 76.03982253072346, 77.28948383170464, 5.906135277627611, 95.38545439546057, 34.764161938476185, 157.98645873443334, 63.59358071634348, 45.96171851373734, 58.462582254751844, 66.23444568018672, 49.79261771531047, 41.58620942872443, 156.53874896333284, 93.56187654854482, 75.0293290262925, 34.92924498437207, 54.205256273173646, 54.54169714030592, 32.14854404234053, 87.03932739027996, 37.06186147951223, 69.12945924840727, 41.24518132347695, 56.604193288221154, 140.3231727669713, 134.9740096004644, 47.523477355869275, 125.09945611729847, 86.90901997510717, 40.83009724888596, 5.28632344502106, 59.49013819440144, 55.54568087189807, 59.329189887981464, 54.80630257777096, 104.07820934065823, 53.768502887116234, 55.968696843953964, 37.57279368340611, 7.828846785094682, 34.887296314174534, 45.8857500542483, 43.45261779433585, 7.453587105252277, 54.573230139801666, 7.444491713012559, 149.0015910091176, 41.51920466318397, 177.44288025421935, 62.99398759657701, 64.49380481824717, 48.96299794841684, 60.50616407431204, 5.613077280791438, 50.37385636698936, 95.37421712588963, 40.63860595446138, 51.50942048170517, 61.3397636991035, 3.985003129139425, 56.39186562485457, 109.64872708976557, 61.2728807707452, 98.04062234121363, 25.611390157193718, 57.83226385300619, 31.75580884229773, 73.52871255416326, 50.59767607070122, 47.22484909442595, 35.265763543832215, 58.42708476558035, 56.41687013100923, 40.73982503117736, 9.073977066989697, 37.590346008334805, 86.61757662867166, 61.39164340019092, 78.52280563332569, 63.569996561255046, 42.137389610541625, 45.84018977892336, 35.195991967323295, 49.60400622875765, 13.911519596400696, 57.56036579320855, 43.8178569987518, 44.84930540511661, 38.888386918910456, 61.83414492465612, 81.2051615228152, 63.88854036915456, 137.90607467114867, 208.17279336426313, 52.81905392626197, 26.185031202544614, 52.50238199131728, 36.019911677346606, 79.53061066064086, 52.717369202610406, 57.791162499451275, 4.715892687345638, 94.03048039257304, 85.80124888083212, 104.14884159253715, 112.87714714121067, 52.53955626439842, 92.52586713363722, 74.0630740647741, 40.72312244281483, 63.84339007740629, 5.487280648564505, 57.93375306365576, 6.527471015396227, 86.3888896136954, 48.97437733175297, 38.16504643373114, 53.32222085029766, 31.599775975721755, 75.39899391560817, 98.88968540697736, 63.7710198271251, 54.659724691189766, 6.66836207937002, 45.99371996544522, 124.26041149202246, 132.94353452085315, 64.92654400295622, 45.266370215028296, 48.863567845634826, 40.66819881322784, 85.7992729559816, 68.79271167739296, 86.22043836205498, 70.41441087218303, 68.91719727791049, 64.50885839361499, 34.64872214062452, 43.12485062366652, 143.97554567543222, 65.87556176398422, 60.122304399194796, 76.0853424815315, 58.0908122975184, 57.59513288717158, 42.55463907108784, 48.81090730858126, 81.2129044966117, 45.385639901359966, 43.56837921918735, 52.026190978423465, 73.11285241082788, 73.4554029062277, 38.30319800800579, 75.14308725254944, 107.3447607268007, 37.03066408980199, 70.22739743848587, 61.3250333472931, 38.813544687021945, 39.17923402866275, 87.73916751955139, 55.480074578015724, 65.1674963202, 122.96388081448939, 46.961402517149, 47.29349029534995, 49.044099465518656, 53.56430128506149, 88.86979744893446, 39.4062757776664, 49.089238076108366, 113.90135833751985, 90.70282287309244, 152.43258244005693, 102.08979572472192, 60.743591781138946, 49.01518143645927, 129.1948165534763, 70.46801892301535, 128.47066428053765, 34.92780218822479, 42.47157703642657, 56.084154617988276, 70.80891858606677, 33.184271855154286, 46.686121752518474, 42.037233640212925, 74.42239517073916, 32.10023574848282, 40.51284788939236, 64.22890171180903, 130.87277947677927, 74.9085759251806, 64.20608078591212, 66.16494860964976, 58.601447630729425, 64.22742395464925, 53.74381883616847, 45.916493842861264, 33.54940282233128, 60.317026664981434, 108.41404041965932, 71.92774784020247, 52.569567698453966, 10.222675813882933, 65.55724630347987, 63.55909018634872, 58.21627563653601, 84.6908172937526, 66.04810303314078, 55.74077199647441, 58.38231102336333, 157.78736493180799, 98.60318352704145, 36.40553619919302, 58.82768561934975, 68.36782227458666, 25.200901033184735, 52.91925500342019, 71.40387780399953, 149.24652919465595, 118.42971552289589, 50.19486775805727, 112.6886226921969, 57.023590700579966, 48.12423476881213, 155.3598300770898, 38.395256434656034, 50.058066990236526, 87.16875587955039, 44.22578078832557, 34.60473078131036, 66.62574585428611, 43.90347268380367, 113.28435489954083, 149.3057597011795, 91.63602000198462, 53.79234797080391, 8.312345991436127, 35.565284619953886, 136.57561910384976, 140.78699474577726, 86.92925406271145, 47.54169859386598, 71.45946811699719, 60.49079810816098, 85.40794610555147, 44.35885546938249, 45.20310921141466, 36.68366536738548, 35.81451460929159, 37.54089478348286, 44.896934749110294, 118.10483523440382, 60.003691622637845, 83.9657986998848, 55.97961383624707, 83.04791997419188, 41.10673445980004, 39.60139656488636, 45.48838635674089, 80.0735919952449, 95.38250432759273, 55.65961601516094, 68.92493036578841, 7.529262582956462, 62.864693064552796, 44.67950982287612, 45.280265595784186, 53.769486977783835, 84.26139801214369, 46.52785507412941, 57.8827483632673, 107.69750928899265, 60.89088957984095, 40.45821361731332, 52.96384067020143, 115.86474387368256, 52.2133538445067, 122.68066705944932, 35.76892185637398, 187.54121424805805, 88.80671571446362, 43.45654249217392, 97.25351250340601, 39.86858028946747, 55.52741947007124, 117.44642771913463, 67.26269589233023, 68.60084475096528, 60.94376218671525, 43.494986731721625, 58.801612824973276, 71.2199952980688, 97.57474513369057, 37.885307152347586, 46.09832712709615, 46.83182079203476, 78.19650785864413, 40.446619437135965, 99.21338986208593, 46.514634381042015, 82.0940154046289, 55.50954270689544, 14.688628687456898, 65.00576131732979, 75.40802235312736, 95.34758266651295, 64.73922904199348, 40.67908393215272, 68.80712814289359, 50.95996739275931, 42.001110099768, 53.443817157563984, 44.82154728300939, 58.122015592936556, 103.7241026257589, 66.51006940772763, 44.03555092074464, 127.07499301196533, 5.812427827535264, 119.59298045817606, 70.25202485468996, 38.324611867255854, 54.58417633434757, 40.368745219475386, 44.6592520624522, 70.35384839944668, 47.857804880869196, 76.10851625282736, 11.152542903186259, 13.425263276648515, 35.56839642105546, 54.581749343512705, 71.5003590177949, 43.06618034414469, 100.08561630366391, 48.069211870518686, 36.267484271052744, 47.76845968177633, 81.12046852091066, 59.062242930440426, 253.03290923589535, 84.12608779384483, 57.936862372335305, 91.48544040215799, 49.934576631011545, 4.446010748693644, 4.758321876967535, 132.9378660535625, 72.18815176605001, 41.02161789881002, 93.59294446593252, 74.34847848896938, 46.158845817336555, 65.71602972663736, 53.80043635711261, 52.79112376812316, 54.375710268930256, 8.171790117226374, 61.94521595303919, 8.222082203018926, 96.17220880490424, 154.13956777640584, 74.42668156290073, 110.28557795238017, 120.91501360239346, 110.41236784160238, 69.10322041431426, 131.5933439045842, 7.023555011500464, 46.68191357929973, 86.52616776894894, 51.95477643139989, 54.10151705617602, 117.03505028569522, 91.70531976447663, 77.49106251942511, 18.49607026910686, 5.950566523474429, 129.39762356413803, 57.54802970783017, 54.187047657763976, 6.064235537825508, 70.56040080059616, 145.30682438690368, 49.21885032937067, 54.534487772469376, 12.037474560461924, 76.31559607905025, 75.14094830891361, 67.37791504489061, 107.24090590638663, 70.48866787276391, 27.006219365326157, 106.63352246981309, 48.58233903101121, 8.00714026770601, 61.62706142373174, 146.98854060332638, 2.8903619296639085, 83.50328903604589, 80.28075891173079, 61.28866149779996, 40.004108408610904, 55.74361745041923, 80.58660475036528, 85.70534361231798, 47.24878068253633, 7.880663969876809, 82.86953322443544, 92.5967955562406, 190.2851202192012, 58.6005231974809, 69.39839065774576, 37.20945786912637, 109.71854273104138, 138.42102875642007, 61.13692927100841, 59.198098423367696, 68.04365982645443, 135.36943945197783, 90.66385825649999, 141.74423512951185, 51.947491557639786, 99.72623809093344, 17.338933791055453, 74.94589195629136, 64.7667651610405, 69.53156662963804, 135.06564721226934, 141.5540622805224, 13.43840195643446, 84.9031676042008, 68.43833324063606, 45.08661870329172, 104.38467075084706, 59.39479379673186, 254.39086881565663, 55.83841134410927, 91.13185452578823, 86.55295930008438, 81.29157844529053, 102.16517848465844, 44.34848790683972, 96.80378310078035, 96.59508951351867, 5.567634473469761, 48.966581710114006, 105.73591357789688, 101.47505933038435, 58.63459021101165, 94.65045892551177, 157.3653102121077, 150.29231819617974, 68.9892134861079, 102.18163291765485, 80.34687144268825, 54.256867736002846, 95.22610068140553, 100.19645291085452, 65.3027205430036, 43.0286643353928, 184.885173408109, 48.16447982334327, 34.21267650131063, 157.9975424813589, 71.30419534128515, 62.55310537544759, 73.66806635946071, 81.52345913088273, 7.032336931860621, 71.43282467436998, 71.83785099294136, 38.86757371887328, 13.56546822430212, 5.309688317404079, 56.34980127908283, 48.968845251940344, 42.73378380768727, 71.2414521800358, 41.984408897593944, 73.35976790191116, 46.211724401149574, 67.64010070955992, 81.16192543662203, 60.51403078199629, 124.79647712756699, 112.53748637065009, 40.29543536090092, 81.07771370246341, 42.85883621053616, 192.48755073664714, 45.48898212916565, 57.14108115439338, 119.5453379875609, 100.7314937634884, 101.78549131465871, 131.76722364151655, 31.03180797723621, 66.48917430210255, 219.65090715284137, 189.72849827296136, 71.73745047078701, 114.77420120603239, 46.33729156004908, 101.40514073346124, 152.1756825101743, 144.51310862755935, 4.095397689156454, 59.85313879115728, 73.50437149756033, 98.8986408149934, 9.67988469075395, 60.59090623381699, 82.01326530670106, 135.66225957935885, 117.3329504076108, 53.17691439422779, 80.7233388987927, 79.31584925667117, 63.59241727824222, 89.20872289357173, 44.84853281725903, 366.89238305653714, 53.8022979896646, 131.68490716873964, 62.46458211148585, 112.22398246242194, 8.73912773427841, 59.08811737385771, 94.13534577156955, 73.75438650567125, 40.06288319915959, 65.47350531961419, 132.19976709040532, 49.9589461547936, 15.274255250654637, 113.1071498361514, 55.06334964410844, 71.41219969093294, 68.1093641318905, 50.85256711305601, 58.52611683400266, 44.89964813041467, 77.9555104464742, 145.42779729887627, 201.53169451447675, 62.2433703472967, 84.29831742865812, 94.73923114378431, 100.06457457253846, 88.3107821313069, 157.07503101886437, 50.05239395382919, 49.26247605320565, 75.18219341209591, 192.40844211350338, 85.07185549352575, 43.84065086728446, 63.38189012830808, 239.2982257827995, 46.24168163088468, 174.0979466480235, 65.90500573621378, 58.02228864603604, 95.25545278875495, 124.21479927985659, 68.3131917462511, 77.08286356851303, 9.208347911241995, 58.66194344240576, 154.33428601228408, 77.30434610968263, 120.72922296027933, 99.5026935098889, 57.93555361169973, 36.696454136059394, 85.82134767549913, 76.34890392952202, 71.4774765343251, 15.313006185361095, 64.5444451285496, 9.671284579982629, 84.02849607390976, 69.52336288311226, 48.74965613057597, 9.806376900510564, 62.008688192596324, 71.74422638085466, 52.03645565671369, 58.79510064829656, 94.6040616244942, 6.432135934003563, 105.28448733550968, 43.77122786330202, 65.98713510455599, 72.77350696880572, 80.37333738329599, 74.92062849523404, 72.86857667051025, 60.21313350072693, 57.11657512680067, 182.72652254618328, 57.96398889322257, 72.67077869276217, 59.549797332282466, 86.88140512110108, 62.80674784387146, 53.73266889351609, 60.57090059590232, 57.303589319852826, 123.4182045751211, 70.89568268480056, 49.820728800108675, 162.6245166578212, 202.76605691914628, 62.316813531137925, 78.09393237888791, 86.5439293575495, 37.271306936979535, 116.73640419379328, 109.16949631957966, 151.16348755973405, 80.48800218771188, 102.27244374165232, 187.86614116566574, 72.65087824559757, 196.6726246099767, 62.31464308183951, 79.28967482201348, 146.53136965729277, 23.262336794642202, 182.49585503027868, 59.368426127558614, 30.76397266820981, 99.22414697091536, 117.34807135447329, 91.37766921209881, 70.25451008460021, 58.627460166040684, 130.6799350598134, 112.63376751322006, 49.23954712186007, 96.99379499247104, 284.53464076080337, 112.19924009147775, 37.7655156327239, 70.85282460414437, 57.1323871317944, 53.391357348839136, 98.48097026608201, 70.02201048989794, 88.43164859428695, 88.21979008232617, 169.9981564684883, 111.62995826315638, 44.20421621534462, 59.408901877712566, 96.4840237352404, 88.44749568198611, 17.102500483034444, 47.6219768409176, 165.23962843170418, 119.53782228495918, 6.351488472776844, 115.32677867823978, 101.34026075611513, 185.17659901671394, 9.23397080872119, 200.1038434532831, 68.29526105139381, 84.33278496977253, 57.41091004597678, 39.863295272327186, 107.0249739624742, 143.69830219989518, 141.8525015064163, 19.56807053749575, 62.99997257404265, 64.78122078752666, 78.65204853227142, 38.56360370826181, 92.41092224244801, 40.927547624237384, 101.89495847686739, 174.40633425442624, 42.860494805369164, 41.70182009591218, 8.971263301523761, 61.88919963403031, 86.9491184612691, 53.845060766140016, 10.632958102351907, 106.05554035082332, 212.03392812077945, 65.61749093795547, 138.15580077663824, 50.369229946582166, 186.90882449786446, 88.8645948234537, 71.28285498148226, 185.05760543729082, 80.7112744830952, 85.64972091889724, 57.8943339988716, 56.68793592444311, 58.390045241537976, 48.60220673252767, 77.48061249939305, 76.96921280837125, 108.25888588923975, 357.97171402501124, 63.33734613273082, 10.902654566096473, 106.77675083743213, 50.44833450356905, 61.381352872900344, 66.59941824358918, 78.50031640307594, 74.40288988244751, 124.88459632427411, 14.086457729198864, 193.43639703626212, 59.09311733307664, 94.15853147260519, 87.7795748034424, 9.262719709421425, 96.03314366467497, 107.5950846985982, 72.8720517390195, 62.97852027899475, 44.97572712183164, 74.80864408523671, 59.4132088946959, 58.22578652730874, 70.74459712533753, 58.62086776708409, 95.9265467756664, 61.72122958885642, 128.0868377796909, 223.50001051095984, 150.84248500044197, 200.36423034081017, 118.87733970575982, 18.351749858357795, 58.73132008787275, 81.98861494639483, 171.7970917991569, 142.46043229910225, 41.38201453097326, 110.08057568967305, 49.882946033673086, 55.03462734506039, 51.33697452907524, 80.13863742219974, 71.5746776540939, 43.247172684124685, 62.465029510414205, 30.731273130423645, 88.63120997126586, 123.27300017010826, 60.704437267249105, 68.82940995352689, 68.86203709121344, 7.484054857845522, 93.30453755152531, 103.65053304395327, 54.917259626097106, 78.07895332758956, 79.25577897651856, 47.48874026464522, 47.150938924875405, 66.40949291419368, 86.36700951513548, 57.00191641922674, 147.4322886329905, 69.51894774992144, 51.42651446740464, 73.03842041986385, 74.66348674088884, 112.56933849783462, 235.50615890834578, 132.55974620218373, 128.45410958344132, 106.10617424022597, 87.99917577772547, 171.49632982628376, 63.18681091141343, 217.42371416985247, 84.00329606882094, 94.648478306557, 125.30086446189974, 45.210752245527345, 53.91581403471846, 58.80790389877452, 97.6124054213655, 117.279727504876, 67.46251445219534, 57.44888075514844, 72.26790441175866, 52.21452490388049, 47.024065333939475, 59.98638549840384, 46.22225801790414, 172.09188109250437, 58.14060160993145, 54.457044407918126, 130.04335448061533, 82.06978073387756, 31.68071168837447, 138.91978834079697, 77.58898698255184, 67.8568578695711, 88.1785024987815, 104.69760275229473, 42.09456754287861, 67.06433872856698, 45.41674391249855, 43.08629965268446, 11.533224894352868, 51.58281386020288, 133.3575366793077, 112.37794326106123, 57.148109268400816, 84.14334415353298, 129.7295580572975, 67.89397566562322, 66.04358620535191, 169.1489351657481, 195.09310238763132, 64.96382898736206, 47.75770506853003, 105.5102166384344, 56.5826016285002, 77.60091474290671, 66.88873075433764, 58.614174030368936, 148.46849925355505, 131.4523230373653, 147.20374466194696, 40.06653201989345, 97.746776168846, 181.9018889898334, 71.87712910557273, 127.8219731557708, 62.69196868636935, 40.54659406742199, 102.76826054245964, 89.01971170013852, 108.04754038259559, 199.7070680756706, 95.47938373787163, 74.33294164913258, 50.46086338979212, 94.09854386094929, 48.74772658218934, 49.49183965887565, 84.02319089087146, 91.57146905885726, 42.729828704040514, 140.65552276232643, 57.087228158155185, 87.61508592096605, 68.72220160582297, 234.05500145915377, 70.87107889750918, 63.29062637305736, 120.24913552762524, 47.21242095214779, 156.53370643659332, 86.60377870750212, 159.3966483891154, 58.0018093596295, 152.47547975879726, 61.096181323855625, 23.94920529087307, 115.0542924908236, 189.56322781540428, 70.33760805674521, 57.19077122219511, 51.502584848503645, 172.90198273843848, 92.96533537385217, 64.86645194136727, 68.34087548567861, 58.73390235702113, 60.26470351535103, 59.64548849575278, 39.10501132356204, 14.783631007819734, 43.26052480302777, 68.6201903384732, 140.56995929334087, 73.82091559794887, 54.82126115920452, 111.52449552259658, 75.16753363094031, 80.13699870584168, 47.73966743258944, 250.29056572150964, 61.19739977021884, 39.541110914625726, 160.91227170194313, 74.99646075085656, 41.201421153503325, 57.859498641195906, 74.17849122194818, 49.693069721603834, 78.78803364383901, 61.189312290843226, 102.87121081496275, 57.58370545995628, 68.09709982788002, 44.78885795119801, 177.22614593674496, 211.51191506623624, 52.6558716751666, 60.22301143450045, 175.4005671857726, 77.21446283450577, 78.33558074738141, 214.6900414653839, 209.11734781646882, 105.49585905868324, 101.398198743197, 44.76977615477372, 37.55989923253924, 89.81698856105844, 68.37976984335536, 50.17583434582687, 321.92510392054817, 78.25779575439225, 9.050038778879838, 68.51919326427986, 261.5367500711804, 45.72071976744781, 7.360418745452854, 45.70089286291591, 210.905068871074, 67.41763413415921, 56.7902870619477, 52.920326656074245, 60.941532679215925, 64.27183246505746, 144.45628583883794, 39.31996585822135, 11.400012028247959, 13.25863680703837, 102.88126236095839, 91.29115155638361, 213.3280575149798, 55.42850532336168, 97.85810528493008, 32.71320699350291, 92.38822691090095, 57.66787358647021, 105.6930932549859, 71.6706202874189, 117.7495201044596, 68.66772120897826, 89.13353874181344, 139.98945430206996, 15.026514050014908, 194.82211011026638, 74.12517081811069, 120.60408652295348, 75.38091392600447, 45.7062629315687, 35.42662787102553, 88.46432979204106, 10.501341563700073, 352.3283653425748, 204.095812215991, 130.45254795915238, 35.63752878811298, 39.883837934771876, 40.64486015112076, 13.553325438350813, 214.81607866795056, 11.174482414352429, 63.749252950335716, 96.37408229268961, 111.55664950326899, 137.92684020206048, 221.21193810603427, 72.69679778065323, 135.36264266293975, 141.01972449174534, 99.49703120340874, 83.35136095694456, 81.69048316186496, 42.32838893516446, 193.69699661132086, 31.243292340386482, 97.04789881056956, 156.28335739755164, 151.69877790778528, 53.80148395202951, 62.88527866355429, 223.2442260986337, 273.0307734446303, 58.52841433462713, 90.23291447133813, 51.671804787198894, 58.92516628353959, 8.456137813330997, 43.53392681915274, 58.94616756907893, 130.8961468888274, 122.74018896873001, 65.16151351390249, 75.70674997462584, 38.985768822771675, 98.31980095252861, 52.804996374695406, 50.29240747671428, 173.3372131438109, 76.1652361259814, 79.5048514493565, 68.93166535781795, 95.49625691575503, 104.0031246963308, 58.90551627894415, 67.8906355165281, 152.39857564404625, 71.6751984762578, 41.8219991071519, 141.09138642898043, 92.75631397950463, 50.69050131019569, 192.81980505538755, 53.60600513156879, 90.70936788874043, 61.29423728170263, 215.27844677831115, 37.53610513502807, 54.251035550502216, 62.09694379799174, 39.171824675718035, 20.02126890937994, 50.64366028959734, 44.79730028859147, 55.97113359058402, 81.32342986451627, 124.28914784169503, 87.61247930072395, 112.0148091101083, 54.38114673657503, 53.127193976893594, 54.11263151904092, 23.57062301560085, 42.15431627263163, 192.68352530834602, 62.07426902595887, 96.60229233860508, 199.43993968351643, 129.79390977163325, 89.69300796261764, 48.803259267671415, 42.050853481887316, 142.77357894869374, 46.777598608699805, 58.47446204170538, 209.17902192054726, 91.69223086056563, 132.9955900020596, 82.24796199345614, 67.68788889222, 16.8332694863998, 95.49120422096134, 80.2657202444745, 163.85411057758995, 61.520067702338395, 114.8526240246929, 10.326242325941829, 75.6680444858211, 73.52669283836691, 168.69548088148284, 187.89362861063475, 58.83331909912433, 143.43228976345776, 62.73089873890606, 85.28198320699288, 189.0961004275783, 120.85486402292956, 79.78291201985922, 62.38328396137613, 7.451825441182232, 84.51757097251406, 233.40828377873117, 74.76200861476808, 98.17194110081608, 102.56824949740948, 124.58306404997488, 60.08106661161749, 67.84731072712736, 71.72815823569535, 80.93692693964668, 66.45729507159056, 80.14153352349658, 72.6335198114026, 44.9134344339926, 81.69358591806902, 114.01732816528215, 49.1239521731901, 45.19246816656911, 6.8132901315696195, 108.48284638331673, 80.15082737591119, 79.66958251389788, 83.96740579648235, 54.3913680442158, 88.99179025756621, 123.23663898696464, 78.95382886478625, 133.27267759237037, 197.79584074432753, 87.52958802904773, 81.4015765845694, 135.75190654385955, 64.3322030313299, 54.40540933284468, 76.13478964422742, 91.36710679042865, 75.46199754021396, 64.03630777207864, 91.21040765401666, 56.055629237060515, 52.0365158535152, 139.7098257269959, 66.45261481930984, 66.82957100075598, 141.01386475916289, 60.373423114767114, 183.14455590228422, 64.78272614990335, 14.506449131644155, 73.08043290429661, 86.70318083353592, 72.62500161880364, 33.70303597778161, 77.58418414361041, 94.52082719424318, 140.94552833996113, 45.97816677987489, 40.136738266930294, 163.13398330445656, 125.10034272847412, 127.21787128094245, 99.11743928281913, 69.373042708943, 43.94717741275196, 68.41604955674025, 117.28881459611104, 25.27555182147373, 63.70444509656064, 66.9912540003081, 80.46376417595236, 155.98982336960358, 64.49503249148297, 79.8975306933646, 143.09516470717722, 54.82441412424907, 45.5519060626322, 86.13643332537664, 165.58367873772474, 97.1748693030914, 12.03549697449105, 71.60327476598357, 78.47893122895381, 63.39772100581489, 78.34828649592058, 113.1087509261375, 66.35981560021342, 72.63019054919793, 36.596886949600325, 48.66264765362546, 97.68848655466182, 113.21915043147276, 129.03412729313928, 51.357121541488624, 51.901760505765466, 227.98078457141213, 104.42480035398262, 37.34541226448467, 77.52714268869205, 59.57667827351905, 9.337684649278643, 86.16155452344059, 221.53899144837152, 98.01792395210393, 72.12255999309951, 143.71401307120175, 66.47064117</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>112.2095406150818</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>68.13062484665633</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>[124.0470962524414, 62.17881393432617, 182.22433471679688, 108.7799301147461, 146.55189514160156, 82.53931427001953, 79.67486572265625, 54.97074508666992, 59.73379135131836, 21.535446166992188, 17.63085174560547, 94.80231475830078, 106.9712142944336, 95.52789306640625, 66.38414001464844, 56.07547378540039, 147.6909637451172, 96.76985931396484, 80.27373504638672, 127.1262435913086, 225.6326904296875, 69.50129699707031, 54.974021911621094, 120.16658782958984, 46.92890930175781, 63.97251510620117, 69.55636596679688, 42.999515533447266, 151.23892211914062, 72.09327697753906, 278.3799743652344, 143.71145629882812, 139.65452575683594, 102.4893798828125, 53.99258041381836, 159.42381286621094, 11.760284423828125, 52.29745864868164, 172.6008758544922, 203.1627960205078, 96.9002456665039, 106.08184051513672, 140.292724609375, 210.3992919921875, 344.2892761230469, 47.768638610839844, 244.9041748046875, 179.1565399169922, 74.48597717285156, 141.63851928710938, 207.7462158203125, 72.93447875976562, 14.993000030517578, 104.1656265258789, 7.667314529418945, 97.15251159667969, 10.034051895141602, 148.97901916503906, 246.16323852539062, 20.872098922729492, 267.87701416015625, 81.27671813964844, 60.178009033203125, 57.43025588989258, 114.2837142944336, 96.63896179199219, 78.44661712646484, 54.89338302612305, 137.9124298095703, 88.775146484375, 86.16093444824219, 106.36314392089844, 59.19734191894531, 235.592041015625, 54.05049133300781, 86.73017883300781, 246.34886169433594, 59.735260009765625, 61.3568000793457, 138.55210876464844, 94.49560546875, 191.5329132080078, 105.0457534790039, 107.06875610351562, 167.26953125, 57.81262969970703, 162.57070922851562, 246.54515075683594, 97.76509094238281, 51.61533737182617, 58.20122146606445, 136.0362091064453, 46.91468811035156, 57.178672790527344, 155.3135528564453, 248.94119262695312, 156.07862854003906, 115.60499572753906, 43.98484420776367, 186.52821350097656]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01601</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:53:09</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>92.87847997134118</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>73.9342401989328</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>102.0968532897425</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>4894</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>[1.791905026366888, 1.3010169958952844, 1.0150659413346061, 0.9433648147114375, 1.0985008911394603, 0.8888757802655948, 0.7971336736282806, 1.2326146338525328, 1.7619542232915808, 1.3099188177238998, 0.48923231660157535, 0.6593706449355985, 2.3124665737249352, 1.0235254395812428, 0.7094685862087237, 1.9369961681559702, 0.818134232836132, 0.1167570854957368, 1.656721279034246, 1.5196171521854092, 0.9056908605171352, 0.74923034897314, 0.7942249491040085, 0.6925880935252906, 1.5417286781056552, 0.9353407922771527, 0.5944822349840808, 0.73868651271964, 1.6423732950161432, 1.4922250217544855, 1.0538238224661471, 0.850817721408198, 1.6274402340087666, 0.7202557569062857, 1.3875038147857741, 1.0572730447842864, 0.34067507537688735, 1.767262153962756, 1.235853315962273, 1.673779509280209, 2.6767923088043624, 1.7308399046183693, 1.2026002660490425, 1.9495777879858374, 1.1230980079905328, 2.194625169345459, 0.8535736373376334, 1.5432049013526439, 1.7891005337109362, 3.037811794785571, 2.5390872715370145, 2.218842908018713, 2.206126732014045, 2.58742435942109, 2.3921828495469666, 1.7066015801477927, 1.0522756417850256, 1.0054658029755654, 1.8053724477942261, 1.804670859892601, 1.8822323044983034, 1.3617662698162565, 2.1981627394970396, 1.9218669424340689, 1.2473607016321473, 1.4659899005827064, 1.1666760590511553, 2.290417200367891, 2.5728678130344504, 1.5378812565310707, 0.8978681731036975, 1.271506547513332, 1.6741948684390862, 0.2782461206956111, 2.3454133418520033, 2.4332134312696283, 1.4138974636454038, 1.9455154420808003, 2.320562165717182, 1.7216287602301479, 1.6063632864564854, 2.7102268391051494, 3.004531701405533, 1.554626426001957, 2.280956458856382, 2.630608308392429, 1.6042341226898427, 2.6290510018491138, 2.9877692580686337, 2.302042723268449, 2.1553092346774925, 1.8860526450558133, 4.9640650370067005, 2.5218363151291316, 2.0894406008217916, 3.181309816938488, 3.1110708086581, 2.468477223544514, 2.656676961230786, 2.5796593951226376, 1.4488383329748231, 1.1550711352096417, 3.5293175809889816, 2.4558861955539673, 3.7213564837643447, 0.3021907694569457, 2.339538912550999, 1.5023188486135537, 0.5758921914485103, 2.7547641770567624, 4.435150079660148, 0.581000519842096, 1.8871377876085493, 2.4843147585787255, 1.957266120743147, 2.8435284891701498, 1.8779515509208886, 2.215873736996479, 2.7989398817547153, 1.86863076480136, 6.2610905515814474, 4.142163828162156, 0.7244821104711041, 0.6484526125693522, 4.5020007490678005, 3.958862536628215, 3.5593529223827813, 3.937697330718128, 3.5085067803999213, 1.672410723413894, 6.1668654218337, 4.921921893950546, 8.17221382131015, 3.01650709147298, 3.66540036344841, 4.802521163215286, 5.023663309577043, 6.040723896458913, 9.90371807068252, 4.180027919994757, 7.324714378166915, 3.4552394218984253, 10.439758546375435, 3.1833389645158854, 4.5428828993897294, 5.261112241160853, 5.912097810987724, 2.8544489047912345, 3.477632931566342, 5.496637255247493, 8.852328505365751, 4.5826004387075665, 2.838013422699156, 3.826772182997652, 5.160063317531868, 4.486460597852789, 3.159002315983087, 7.502686569350438, 6.124787743313522, 6.364393722106999, 10.071911109825972, 1.9086435965970352, 13.777968555428613, 23.172773996923713, 3.303011018752318, 14.20744517779001, 10.781206760082268, 5.870682962553566, 7.198077744654327, 14.072850922950677, 0.6833414944852915, 5.1265444109841205, 7.082840945260149, 1.185230302295049, 8.567300974270985, 10.152418055214259, 8.368846279144922, 5.104072454690381, 12.401216016217212, 1.5077381601413844, 3.9464981259807814, 4.1277204375588035, 9.529073981653172, 4.41517460862186, 4.13727806362454, 13.668362111146557, 5.269558488624456, 5.418796835785533, 10.508397326907446, 1.9731556945924367, 9.35747944479535, 11.551702949326687, 1.3612704503569504, 22.70419746301439, 8.003453273382503, 5.85766437107236, 4.078385625179295, 4.674930120617179, 10.225808822522533, 8.275047895625177, 18.33382765198861, 7.619508342981999, 5.85112408757491, 12.376585063856567, 30.293341030241656, 24.448852754722548, 17.519824584042595, 13.602243024127018, 15.929202183822317, 1.7980239466631363, 20.540012970871498, 8.550549905589307, 5.107723322963023, 16.535865776270928, 16.715685789331953, 27.559934615290317, 5.871632142873665, 1.4872119246436246, 11.643945600828793, 16.64881598593775, 22.4591160235992, 14.397316185055251, 24.402618904091156, 18.913136115602057, 16.58496180641556, 19.655474295980415, 14.51586241048827, 8.967390493935003, 16.864030406255004, 10.419670913769611, 13.473005161558621, 13.798447655360102, 15.268505927163853, 20.78234186736726, 16.37581275929988, 14.058273680755143, 16.418230837835445, 23.88462563703701, 24.8872708740144, 16.818091181940453, 26.925547996835466, 10.827927423729841, 12.448642222042443, 19.62565781544332, 20.29621811133168, 22.134867079436592, 19.66709765210296, 27.589428890447067, 8.948227833362466, 18.49685573816845, 42.99531816334173, 19.848390986960737, 25.708660319803077, 22.449019143723593, 10.496494360996108, 9.853781445618006, 22.754187732617602, 25.517440708176927, 8.229945978844293, 25.112013484554158, 54.645786548213415, 7.319992196656946, 19.513143033443036, 17.69795517509939, 19.986454510206435, 22.467558010549336, 20.842058562073312, 34.65098206010161, 30.49428615265586, 8.566258094495614, 14.577438607236687, 25.223853639112267, 21.19876854024204, 41.959559321464056, 41.53623396749895, 27.257807594809375, 18.13991612325218, 29.732038298302523, 24.6305313347685, 21.269343177847812, 50.51139644865968, 18.013624186269777, 32.91053255543198, 17.45542289054734, 22.407188701171574, 22.601723679670876, 16.645624022181902, 1.8913823712459976, 28.108758375597347, 28.91926335801034, 24.024677419509185, 6.702763017996514, 24.21248710286362, 21.081871251371798, 25.15347833342394, 41.84294026890452, 46.30597161965847, 23.55854389165271, 35.01735525432404, 19.995649232564407, 33.88502200057036, 33.88447228598672, 33.4095566418075, 34.96808980267317, 34.47695049587563, 40.22485924212042, 28.73020730678259, 27.842414575939415, 20.876700443023243, 4.8020500586515205, 45.261126221712644, 57.636450986316554, 41.056133726545845, 33.95071827162646, 29.27378923755751, 34.06433123681448, 55.37173408392715, 41.57620596211573, 53.11485956731456, 37.164917549777485, 4.455663937634546, 18.490472088442715, 36.34767337063336, 41.017010058647784, 28.455510968859407, 30.56069078169406, 27.678338358852088, 28.459808572884814, 48.99271271431106, 25.518037998098528, 20.166191934896194, 18.96438386282776, 29.48636630610711, 72.75033569218672, 54.45175528748937, 38.61551845853181, 4.071960623333411, 10.674533120370228, 32.19667448243843, 24.968999910375157, 13.653419332502063, 31.86541629210018, 46.07843141002158, 25.4686364831154, 37.578538593220124, 8.987114222241622, 35.8512375005983, 44.20255117992451, 29.821866350217693, 38.43047090790472, 66.09019307439704, 32.41678513867279, 32.0490704083456, 36.84776161049775, 27.703525979980277, 65.37568967195419, 50.706000919006435, 72.36822622483702, 10.530563683407868, 6.2940573827367166, 19.51301201698688, 16.744953476450995, 19.64565329937916, 36.7304505473473, 67.92277251844642, 27.83750849354939, 71.05947070576163, 60.57284047740022, 45.19259503582297, 65.25282909958435, 51.20309412619243, 28.258376099562017, 60.46449908560553, 5.123643572409799, 17.51157920215477, 31.54386828629317, 38.941174711081146, 45.72485965672568, 40.029465731858615, 68.35025418210053, 55.45505349274063, 44.31381620346688, 49.42497855523662, 41.55594576532728, 52.63306891623221, 60.04294347795202, 39.070283972187966, 45.35480347926433, 55.19058226753481, 8.149513187263057, 47.487790542600465, 41.651557165969734, 19.979223668553644, 59.38669872756424, 47.62673204251652, 57.48905406216047, 22.900106369443424, 33.99589404179026, 32.95113275083658, 54.972822250887084, 20.810558136072284, 59.153408580309396, 40.484885396024445, 75.07438083745203, 31.522911074414132, 38.365940220263035, 35.943105377795675, 57.13704211263793, 44.9208901021943, 40.266084757314665, 99.66782054549766, 34.8022318339232, 43.49426430057174, 38.339963588266976, 94.29437370089978, 34.06844631243059, 44.092284070641895, 34.444662363282475, 44.33486658850188, 37.46672003765845, 52.486364142214896, 58.76569567153347, 121.33635304385186, 6.369210677841172, 58.143687204651336, 37.64919671092013, 38.55419450496247, 29.344266884814754, 60.56374175945956, 54.62679602168081, 54.847752826930176, 37.701823938622766, 47.3524711015876, 3.6798415998229665, 56.61797937009459, 6.79885590969346, 72.85957211344189, 5.200934080492342, 23.89394442242345, 59.0529168570508, 83.90442220575491, 37.86528948786085, 71.02278752034296, 29.840930355727316, 37.75146249744752, 53.79165063936281, 38.75357021700282, 42.257303952903456, 55.637573475471044, 40.30876450502305, 57.89463159348971, 44.779620557758726, 29.880192603104366, 34.82193986994567, 47.67392266560487, 32.44992727942023, 41.17907740152336, 28.429137429317525, 72.01684225826052, 74.03221868600683, 53.20771632464036, 37.46663802211991, 52.56831040455813, 44.67178094391978, 29.657860395901626, 36.698057434826694, 39.91075222837209, 49.34337977752497, 86.59438391974366, 84.9505048696406, 69.52673610183528, 40.260080547898376, 60.909556487883904, 52.21326595082048, 126.57854837149875, 49.94742726102981, 36.94541388870338, 96.79065285249806, 41.88819719967606, 75.4562989957606, 18.990628793196674, 38.38021004788993, 67.65701763717946, 46.25389518187263, 45.067591574733136, 52.79102027671692, 34.71625765208127, 28.91143833017233, 23.605884767181852, 36.68443964763187, 42.84211657896953, 10.677991399607917, 75.29464306420452, 35.89047540462664, 69.73437260459134, 51.90994571809972, 30.067151213651634, 81.56606110483875, 46.25706633435722, 132.64980890423186, 80.04989556703532, 88.43808234172118, 50.83610875765218, 68.87285943254052, 76.03982253072346, 77.28948383170464, 5.906135277627611, 95.38545439546057, 34.764161938476185, 157.98645873443334, 63.59358071634348, 45.96171851373734, 58.462582254751844, 66.23444568018672, 49.79261771531047, 41.58620942872443, 156.53874896333284, 93.56187654854482, 75.0293290262925, 34.92924498437207, 54.205256273173646, 54.54169714030592, 32.14854404234053, 87.03932739027996, 37.06186147951223, 69.12945924840727, 41.24518132347695, 56.604193288221154, 140.3231727669713, 134.9740096004644, 47.523477355869275, 125.09945611729847, 86.90901997510717, 40.83009724888596, 5.28632344502106, 59.49013819440144, 55.54568087189807, 59.329189887981464, 54.80630257777096, 104.07820934065823, 53.768502887116234, 55.968696843953964, 37.57279368340611, 7.828846785094682, 34.887296314174534, 45.8857500542483, 43.45261779433585, 7.453587105252277, 54.573230139801666, 7.444491713012559, 149.0015910091176, 41.51920466318397, 177.44288025421935, 62.99398759657701, 64.49380481824717, 48.96299794841684, 60.50616407431204, 5.613077280791438, 50.37385636698936, 95.37421712588963, 40.63860595446138, 51.50942048170517, 61.3397636991035, 3.985003129139425, 56.39186562485457, 109.64872708976557, 61.2728807707452, 98.04062234121363, 25.611390157193718, 57.83226385300619, 31.75580884229773, 73.52871255416326, 50.59767607070122, 47.22484909442595, 35.265763543832215, 58.42708476558035, 56.41687013100923, 40.73982503117736, 9.073977066989697, 37.590346008334805, 86.61757662867166, 61.39164340019092, 78.52280563332569, 63.569996561255046, 42.137389610541625, 45.84018977892336, 35.195991967323295, 49.60400622875765, 13.911519596400696, 57.56036579320855, 43.8178569987518, 44.84930540511661, 38.888386918910456, 61.83414492465612, 81.2051615228152, 63.88854036915456, 137.90607467114867, 208.17279336426313, 52.81905392626197, 26.185031202544614, 52.50238199131728, 36.019911677346606, 79.53061066064086, 52.717369202610406, 57.791162499451275, 4.715892687345638, 94.03048039257304, 85.80124888083212, 104.14884159253715, 112.87714714121067, 52.53955626439842, 92.52586713363722, 74.0630740647741, 40.72312244281483, 63.84339007740629, 5.487280648564505, 57.93375306365576, 6.527471015396227, 86.3888896136954, 48.97437733175297, 38.16504643373114, 53.32222085029766, 31.599775975721755, 75.39899391560817, 98.88968540697736, 63.7710198271251, 54.659724691189766, 6.66836207937002, 45.99371996544522, 124.26041149202246, 132.94353452085315, 64.92654400295622, 45.266370215028296, 48.863567845634826, 40.66819881322784, 85.7992729559816, 68.79271167739296, 86.22043836205498, 70.41441087218303, 68.91719727791049, 64.50885839361499, 34.64872214062452, 43.12485062366652, 143.97554567543222, 65.87556176398422, 60.122304399194796, 76.0853424815315, 58.0908122975184, 57.59513288717158, 42.55463907108784, 48.81090730858126, 81.2129044966117, 45.385639901359966, 43.56837921918735, 52.026190978423465, 73.11285241082788, 73.4554029062277, 38.30319800800579, 75.14308725254944, 107.3447607268007, 37.03066408980199, 70.22739743848587, 61.3250333472931, 38.813544687021945, 39.17923402866275, 87.73916751955139, 55.480074578015724, 65.1674963202, 122.96388081448939, 46.961402517149, 47.29349029534995, 49.044099465518656, 53.56430128506149, 88.86979744893446, 39.4062757776664, 49.089238076108366, 113.90135833751985, 90.70282287309244, 152.43258244005693, 102.08979572472192, 60.743591781138946, 49.01518143645927, 129.1948165534763, 70.46801892301535, 128.47066428053765, 34.92780218822479, 42.47157703642657, 56.084154617988276, 70.80891858606677, 33.184271855154286, 46.686121752518474, 42.037233640212925, 74.42239517073916, 32.10023574848282, 40.51284788939236, 64.22890171180903, 130.87277947677927, 74.9085759251806, 64.20608078591212, 66.16494860964976, 58.601447630729425, 64.22742395464925, 53.74381883616847, 45.916493842861264, 33.54940282233128, 60.317026664981434, 108.41404041965932, 71.92774784020247, 52.569567698453966, 10.222675813882933, 65.55724630347987, 63.55909018634872, 58.21627563653601, 84.6908172937526, 66.04810303314078, 55.74077199647441, 58.38231102336333, 157.78736493180799, 98.60318352704145, 36.40553619919302, 58.82768561934975, 68.36782227458666, 25.200901033184735, 52.91925500342019, 71.40387780399953, 149.24652919465595, 118.42971552289589, 50.19486775805727, 112.6886226921969, 57.023590700579966, 48.12423476881213, 155.3598300770898, 38.395256434656034, 50.058066990236526, 87.16875587955039, 44.22578078832557, 34.60473078131036, 66.62574585428611, 43.90347268380367, 113.28435489954083, 149.3057597011795, 91.63602000198462, 53.79234797080391, 8.312345991436127, 35.565284619953886, 136.57561910384976, 140.78699474577726, 86.92925406271145, 47.54169859386598, 71.45946811699719, 60.49079810816098, 85.40794610555147, 44.35885546938249, 45.20310921141466, 36.68366536738548, 35.81451460929159, 37.54089478348286, 44.896934749110294, 118.10483523440382, 60.003691622637845, 83.9657986998848, 55.97961383624707, 83.04791997419188, 41.10673445980004, 39.60139656488636, 45.48838635674089, 80.0735919952449, 95.38250432759273, 55.65961601516094, 68.92493036578841, 7.529262582956462, 62.864693064552796, 44.67950982287612, 45.280265595784186, 53.769486977783835, 84.26139801214369, 46.52785507412941, 57.8827483632673, 107.69750928899265, 60.89088957984095, 40.45821361731332, 52.96384067020143, 115.86474387368256, 52.2133538445067, 122.68066705944932, 35.76892185637398, 187.54121424805805, 88.80671571446362, 43.45654249217392, 97.25351250340601, 39.86858028946747, 55.52741947007124, 117.44642771913463, 67.26269589233023, 68.60084475096528, 60.94376218671525, 43.494986731721625, 58.801612824973276, 71.2199952980688, 97.57474513369057, 37.885307152347586, 46.09832712709615, 46.83182079203476, 78.19650785864413, 40.446619437135965, 99.21338986208593, 46.514634381042015, 82.0940154046289, 55.50954270689544, 14.688628687456898, 65.00576131732979, 75.40802235312736, 95.34758266651295, 64.73922904199348, 40.67908393215272, 68.80712814289359, 50.95996739275931, 42.001110099768, 53.443817157563984, 44.82154728300939, 58.122015592936556, 103.7241026257589, 66.51006940772763, 44.03555092074464, 127.07499301196533, 5.812427827535264, 119.59298045817606, 70.25202485468996, 38.324611867255854, 54.58417633434757, 40.368745219475386, 44.6592520624522, 70.35384839944668, 47.857804880869196, 76.10851625282736, 11.152542903186259, 13.425263276648515, 35.56839642105546, 54.581749343512705, 71.5003590177949, 43.06618034414469, 100.08561630366391, 48.069211870518686, 36.267484271052744, 47.76845968177633, 81.12046852091066, 59.062242930440426, 253.03290923589535, 84.12608779384483, 57.936862372335305, 91.48544040215799, 49.934576631011545, 4.446010748693644, 4.758321876967535, 132.9378660535625, 72.18815176605001, 41.02161789881002, 93.59294446593252, 74.34847848896938, 46.158845817336555, 65.71602972663736, 53.80043635711261, 52.79112376812316, 54.375710268930256, 8.171790117226374, 61.94521595303919, 8.222082203018926, 96.17220880490424, 154.13956777640584, 74.42668156290073, 110.28557795238017, 120.91501360239346, 110.41236784160238, 69.10322041431426, 131.5933439045842, 7.023555011500464, 46.68191357929973, 86.52616776894894, 51.95477643139989, 54.10151705617602, 117.03505028569522, 91.70531976447663, 77.49106251942511, 18.49607026910686, 5.950566523474429, 129.39762356413803, 57.54802970783017, 54.187047657763976, 6.064235537825508, 70.56040080059616, 145.30682438690368, 49.21885032937067, 54.534487772469376, 12.037474560461924, 76.31559607905025, 75.14094830891361, 67.37791504489061, 107.24090590638663, 70.48866787276391, 27.006219365326157, 106.63352246981309, 48.58233903101121, 8.00714026770601, 61.62706142373174, 146.98854060332638, 2.8903619296639085, 83.50328903604589, 80.28075891173079, 61.28866149779996, 40.004108408610904, 55.74361745041923, 80.58660475036528, 85.70534361231798, 47.24878068253633, 7.880663969876809, 82.86953322443544, 92.5967955562406, 190.2851202192012, 58.6005231974809, 69.39839065774576, 37.20945786912637, 109.71854273104138, 138.42102875642007, 61.13692927100841, 59.198098423367696, 68.04365982645443, 135.36943945197783, 90.66385825649999, 141.74423512951185, 51.947491557639786, 99.72623809093344, 17.338933791055453, 74.94589195629136, 64.7667651610405, 69.53156662963804, 135.06564721226934, 141.5540622805224, 13.43840195643446, 84.9031676042008, 68.43833324063606, 45.08661870329172, 104.38467075084706, 59.39479379673186, 254.39086881565663, 55.83841134410927, 91.13185452578823, 86.55295930008438, 81.29157844529053, 102.16517848465844, 44.34848790683972, 96.80378310078035, 96.59508951351867, 5.567634473469761, 48.966581710114006, 105.73591357789688, 101.47505933038435, 58.63459021101165, 94.65045892551177, 157.3653102121077, 150.29231819617974, 68.9892134861079, 102.18163291765485, 80.34687144268825, 54.256867736002846, 95.22610068140553, 100.19645291085452, 65.3027205430036, 43.0286643353928, 184.885173408109, 48.16447982334327, 34.21267650131063, 157.9975424813589, 71.30419534128515, 62.55310537544759, 73.66806635946071, 81.52345913088273, 7.032336931860621, 71.43282467436998, 71.83785099294136, 38.86757371887328, 13.56546822430212, 5.309688317404079, 56.34980127908283, 48.968845251940344, 42.73378380768727, 71.2414521800358, 41.984408897593944, 73.35976790191116, 46.211724401149574, 67.64010070955992, 81.16192543662203, 60.51403078199629, 124.79647712756699, 112.53748637065009, 40.29543536090092, 81.07771370246341, 42.85883621053616, 192.48755073664714, 45.48898212916565, 57.14108115439338, 119.5453379875609, 100.7314937634884, 101.78549131465871, 131.76722364151655, 31.03180797723621, 66.48917430210255, 219.65090715284137, 189.72849827296136, 71.73745047078701, 114.77420120603239, 46.33729156004908, 101.40514073346124, 152.1756825101743, 144.51310862755935, 4.095397689156454, 59.85313879115728, 73.50437149756033, 98.8986408149934, 9.67988469075395, 60.59090623381699, 82.01326530670106, 135.66225957935885, 117.3329504076108, 53.17691439422779, 80.7233388987927, 79.31584925667117, 63.59241727824222, 89.20872289357173, 44.84853281725903, 366.89238305653714, 53.8022979896646, 131.68490716873964, 62.46458211148585, 112.22398246242194, 8.73912773427841, 59.08811737385771, 94.13534577156955, 73.75438650567125, 40.06288319915959, 65.47350531961419, 132.19976709040532, 49.9589461547936, 15.274255250654637, 113.1071498361514, 55.06334964410844, 71.41219969093294, 68.1093641318905, 50.85256711305601, 58.52611683400266, 44.89964813041467, 77.9555104464742, 145.42779729887627, 201.53169451447675, 62.2433703472967, 84.29831742865812, 94.73923114378431, 100.06457457253846, 88.3107821313069, 157.07503101886437, 50.05239395382919, 49.26247605320565, 75.18219341209591, 192.40844211350338, 85.07185549352575, 43.84065086728446, 63.38189012830808, 239.2982257827995, 46.24168163088468, 174.0979466480235, 65.90500573621378, 58.02228864603604, 95.25545278875495, 124.21479927985659, 68.3131917462511, 77.08286356851303, 9.208347911241995, 58.66194344240576, 154.33428601228408, 77.30434610968263, 120.72922296027933, 99.5026935098889, 57.93555361169973, 36.696454136059394, 85.82134767549913, 76.34890392952202, 71.4774765343251, 15.313006185361095, 64.5444451285496, 9.671284579982629, 84.02849607390976, 69.52336288311226, 48.74965613057597, 9.806376900510564, 62.008688192596324, 71.74422638085466, 52.03645565671369, 58.79510064829656, 94.6040616244942, 6.432135934003563, 105.28448733550968, 43.77122786330202, 65.98713510455599, 72.77350696880572, 80.37333738329599, 74.92062849523404, 72.86857667051025, 60.21313350072693, 57.11657512680067, 182.72652254618328, 57.96398889322257, 72.67077869276217, 59.549797332282466, 86.88140512110108, 62.80674784387146, 53.73266889351609, 60.57090059590232, 57.303589319852826, 123.4182045751211, 70.89568268480056, 49.820728800108675, 162.6245166578212, 202.76605691914628, 62.316813531137925, 78.09393237888791, 86.5439293575495, 37.271306936979535, 116.73640419379328, 109.16949631957966, 151.16348755973405, 80.48800218771188, 102.27244374165232, 187.86614116566574, 72.65087824559757, 196.6726246099767, 62.31464308183951, 79.28967482201348, 146.53136965729277, 23.262336794642202, 182.49585503027868, 59.368426127558614, 30.76397266820981, 99.22414697091536, 117.34807135447329, 91.37766921209881, 70.25451008460021, 58.627460166040684, 130.6799350598134, 112.63376751322006, 49.23954712186007, 96.99379499247104, 284.53464076080337, 112.19924009147775, 37.7655156327239, 70.85282460414437, 57.1323871317944, 53.391357348839136, 98.48097026608201, 70.02201048989794, 88.43164859428695, 88.21979008232617, 169.9981564684883, 111.62995826315638, 44.20421621534462, 59.408901877712566, 96.4840237352404, 88.44749568198611, 17.102500483034444, 47.6219768409176, 165.23962843170418, 119.53782228495918, 6.351488472776844, 115.32677867823978, 101.34026075611513, 185.17659901671394, 9.23397080872119, 200.1038434532831, 68.29526105139381, 84.33278496977253, 57.41091004597678, 39.863295272327186, 107.0249739624742, 143.69830219989518, 141.8525015064163, 19.56807053749575, 62.99997257404265, 64.78122078752666, 78.65204853227142, 38.56360370826181, 92.41092224244801, 40.927547624237384, 101.89495847686739, 174.40633425442624, 42.860494805369164, 41.70182009591218, 8.971263301523761, 61.88919963403031, 86.9491184612691, 53.845060766140016, 10.632958102351907, 106.05554035082332, 212.03392812077945, 65.61749093795547, 138.15580077663824, 50.369229946582166, 186.90882449786446, 88.8645948234537, 71.28285498148226, 185.05760543729082, 80.7112744830952, 85.64972091889724, 57.8943339988716, 56.68793592444311, 58.390045241537976, 48.60220673252767, 77.48061249939305, 76.96921280837125, 108.25888588923975, 357.97171402501124, 63.33734613273082, 10.902654566096473, 106.77675083743213, 50.44833450356905, 61.381352872900344, 66.59941824358918, 78.50031640307594, 74.40288988244751, 124.88459632427411, 14.086457729198864, 193.43639703626212, 59.09311733307664, 94.15853147260519, 87.7795748034424, 9.262719709421425, 96.03314366467497, 107.5950846985982, 72.8720517390195, 62.97852027899475, 44.97572712183164, 74.80864408523671, 59.4132088946959, 58.22578652730874, 70.74459712533753, 58.62086776708409, 95.9265467756664, 61.72122958885642, 128.0868377796909, 223.50001051095984, 150.84248500044197, 200.36423034081017, 118.87733970575982, 18.351749858357795, 58.73132008787275, 81.98861494639483, 171.7970917991569, 142.46043229910225, 41.38201453097326, 110.08057568967305, 49.882946033673086, 55.03462734506039, 51.33697452907524, 80.13863742219974, 71.5746776540939, 43.247172684124685, 62.465029510414205, 30.731273130423645, 88.63120997126586, 123.27300017010826, 60.704437267249105, 68.82940995352689, 68.86203709121344, 7.484054857845522, 93.30453755152531, 103.65053304395327, 54.917259626097106, 78.07895332758956, 79.25577897651856, 47.48874026464522, 47.150938924875405, 66.40949291419368, 86.36700951513548, 57.00191641922674, 147.4322886329905, 69.51894774992144, 51.42651446740464, 73.03842041986385, 74.66348674088884, 112.56933849783462, 235.50615890834578, 132.55974620218373, 128.45410958344132, 106.10617424022597, 87.99917577772547, 171.49632982628376, 63.18681091141343, 217.42371416985247, 84.00329606882094, 94.648478306557, 125.30086446189974, 45.210752245527345, 53.91581403471846, 58.80790389877452, 97.6124054213655, 117.279727504876, 67.46251445219534, 57.44888075514844, 72.26790441175866, 52.21452490388049, 47.024065333939475, 59.98638549840384, 46.22225801790414, 172.09188109250437, 58.14060160993145, 54.457044407918126, 130.04335448061533, 82.06978073387756, 31.68071168837447, 138.91978834079697, 77.58898698255184, 67.8568578695711, 88.1785024987815, 104.69760275229473, 42.09456754287861, 67.06433872856698, 45.41674391249855, 43.08629965268446, 11.533224894352868, 51.58281386020288, 133.3575366793077, 112.37794326106123, 57.148109268400816, 84.14334415353298, 129.7295580572975, 67.89397566562322, 66.04358620535191, 169.1489351657481, 195.09310238763132, 64.96382898736206, 47.75770506853003, 105.5102166384344, 56.5826016285002, 77.60091474290671, 66.88873075433764, 58.614174030368936, 148.46849925355505, 131.4523230373653, 147.20374466194696, 40.06653201989345, 97.746776168846, 181.9018889898334, 71.87712910557273, 127.8219731557708, 62.69196868636935, 40.54659406742199, 102.76826054245964, 89.01971170013852, 108.04754038259559, 199.7070680756706, 95.47938373787163, 74.33294164913258, 50.46086338979212, 94.09854386094929, 48.74772658218934, 49.49183965887565, 84.02319089087146, 91.57146905885726, 42.729828704040514, 140.65552276232643, 57.087228158155185, 87.61508592096605, 68.72220160582297, 234.05500145915377, 70.87107889750918, 63.29062637305736, 120.24913552762524, 47.21242095214779, 156.53370643659332, 86.60377870750212, 159.3966483891154, 58.0018093596295, 152.47547975879726, 61.096181323855625, 23.94920529087307, 115.0542924908236, 189.56322781540428, 70.33760805674521, 57.19077122219511, 51.502584848503645, 172.90198273843848, 92.96533537385217, 64.86645194136727, 68.34087548567861, 58.73390235702113, 60.26470351535103, 59.64548849575278, 39.10501132356204, 14.783631007819734, 43.26052480302777, 68.6201903384732, 140.56995929334087, 73.82091559794887, 54.82126115920452, 111.52449552259658, 75.16753363094031, 80.13699870584168, 47.73966743258944, 250.29056572150964, 61.19739977021884, 39.541110914625726, 160.91227170194313, 74.99646075085656, 41.201421153503325, 57.859498641195906, 74.17849122194818, 49.693069721603834, 78.78803364383901, 61.189312290843226, 102.87121081496275, 57.58370545995628, 68.09709982788002, 44.78885795119801, 177.22614593674496, 211.51191506623624, 52.6558716751666, 60.22301143450045, 175.4005671857726, 77.21446283450577, 78.33558074738141, 214.6900414653839, 209.11734781646882, 105.49585905868324, 101.398198743197, 44.76977615477372, 37.55989923253924, 89.81698856105844, 68.37976984335536, 50.17583434582687, 321.92510392054817, 78.25779575439225, 9.050038778879838, 68.51919326427986, 261.5367500711804, 45.72071976744781, 7.360418745452854, 45.70089286291591, 210.905068871074, 67.41763413415921, 56.7902870619477, 52.920326656074245, 60.941532679215925, 64.27183246505746, 144.45628583883794, 39.31996585822135, 11.400012028247959, 13.25863680703837, 102.88126236095839, 91.29115155638361, 213.3280575149798, 55.42850532336168, 97.85810528493008, 32.71320699350291, 92.38822691090095, 57.66787358647021, 105.6930932549859, 71.6706202874189, 117.7495201044596, 68.66772120897826, 89.13353874181344, 139.98945430206996, 15.026514050014908, 194.82211011026638, 74.12517081811069, 120.60408652295348, 75.38091392600447, 45.7062629315687, 35.42662787102553, 88.46432979204106, 10.501341563700073, 352.3283653425748, 204.095812215991, 130.45254795915238, 35.63752878811298, 39.883837934771876, 40.64486015112076, 13.553325438350813, 214.81607866795056, 11.174482414352429, 63.749252950335716, 96.37408229268961, 111.55664950326899, 137.92684020206048, 221.21193810603427, 72.69679778065323, 135.36264266293975, 141.01972449174534, 99.49703120340874, 83.35136095694456, 81.69048316186496, 42.32838893516446, 193.69699661132086, 31.243292340386482, 97.04789881056956, 156.28335739755164, 151.69877790778528, 53.80148395202951, 62.88527866355429, 223.2442260986337, 273.0307734446303, 58.52841433462713, 90.23291447133813, 51.671804787198894, 58.92516628353959, 8.456137813330997, 43.53392681915274, 58.94616756907893, 130.8961468888274, 122.74018896873001, 65.16151351390249, 75.70674997462584, 38.985768822771675, 98.31980095252861, 52.804996374695406, 50.29240747671428, 173.3372131438109, 76.1652361259814, 79.5048514493565, 68.93166535781795, 95.49625691575503, 104.0031246963308, 58.90551627894415, 67.8906355165281, 152.39857564404625, 71.6751984762578, 41.8219991071519, 141.09138642898043, 92.75631397950463, 50.69050131019569, 192.81980505538755, 53.60600513156879, 90.70936788874043, 61.29423728170263, 215.27844677831115, 37.53610513502807, 54.251035550502216, 62.09694379799174, 39.171824675718035, 20.02126890937994, 50.64366028959734, 44.79730028859147, 55.97113359058402, 81.32342986451627, 124.28914784169503, 87.61247930072395, 112.0148091101083, 54.38114673657503, 53.127193976893594, 54.11263151904092, 23.57062301560085, 42.15431627263163, 192.68352530834602, 62.07426902595887, 96.60229233860508, 199.43993968351643, 129.79390977163325, 89.69300796261764, 48.803259267671415, 42.050853481887316, 142.77357894869374, 46.777598608699805, 58.47446204170538, 209.17902192054726, 91.69223086056563, 132.9955900020596, 82.24796199345614, 67.68788889222, 16.8332694863998, 95.49120422096134, 80.2657202444745, 163.85411057758995, 61.520067702338395, 114.8526240246929, 10.326242325941829, 75.6680444858211, 73.52669283836691, 168.69548088148284, 187.89362861063475, 58.83331909912433, 143.43228976345776, 62.73089873890606, 85.28198320699288, 189.0961004275783, 120.85486402292956, 79.78291201985922, 62.38328396137613, 7.451825441182232, 84.51757097251406, 233.40828377873117, 74.76200861476808, 98.17194110081608, 102.56824949740948, 124.58306404997488, 60.08106661161749, 67.84731072712736, 71.72815823569535, 80.93692693964668, 66.45729507159056, 80.14153352349658, 72.6335198114026, 44.9134344339926, 81.69358591806902, 114.01732816528215, 49.1239521731901, 45.19246816656911, 6.8132901315696195, 108.48284638331673, 80.15082737591119, 79.66958251389788, 83.96740579648235, 54.3913680442158, 88.99179025756621, 123.23663898696464, 78.95382886478625, 133.27267759237037, 197.79584074432753, 87.52958802904773, 81.4015765845694, 135.75190654385955, 64.3322030313299, 54.40540933284468, 76.13478964422742, 91.36710679042865, 75.46199754021396, 64.03630777207864, 91.21040765401666, 56.055629237060515, 52.0365158535152, 139.7098257269959, 66.45261481930984, 66.82957100075598, 141.01386475916289, 60.373423114767114, 183.14455590228422, 64.78272614990335, 14.506449131644155, 73.08043290429661, 86.70318083353592, 72.62500161880364, 33.70303597778161, 77.58418414361041, 94.52082719424318, 140.94552833996113, 45.97816677987489, 40.136738266930294, 163.13398330445656, 125.10034272847412, 127.21787128094245, 99.11743928281913, 69.373042708943, 43.94717741275196, 68.41604955674025, 117.28881459611104, 25.27555182147373, 63.70444509656064, 66.9912540003081, 80.46376417595236, 155.98982336960358, 64.49503249148297, 79.8975306933646, 143.09516470717722, 54.82441412424907, 45.5519060626322, 86.13643332537664, 165.58367873772474, 97.1748693030914, 12.03549697449105, 71.60327476598357, 78.47893122895381, 63.39772100581489, 78.34828649592058, 113.1087509261375, 66.35981560021342, 72.63019054919793, 36.596886949600325, 48.66264765362546, 97.68848655466182, 113.21915043147276, 129.03412729313928, 51.357121541488624, 51.901760505765466, 227.98078457141213, 104.42480035398262, 37.34541226448467, 77.52714268869205, 59.57667827351905, 9.337684649278643, 86.16155452344059, 221.53899144837152, 98.01792395210393, 72.12255999309951, 143.71401307120175, 66.47064117</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>112.2095406150818</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>68.13062484665633</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>[124.0470962524414, 62.17881393432617, 182.22433471679688, 108.7799301147461, 146.55189514160156, 82.53931427001953, 79.67486572265625, 54.97074508666992, 59.73379135131836, 21.535446166992188, 17.63085174560547, 94.80231475830078, 106.9712142944336, 95.52789306640625, 66.38414001464844, 56.07547378540039, 147.6909637451172, 96.76985931396484, 80.27373504638672, 127.1262435913086, 225.6326904296875, 69.50129699707031, 54.974021911621094, 120.16658782958984, 46.92890930175781, 63.97251510620117, 69.55636596679688, 42.999515533447266, 151.23892211914062, 72.09327697753906, 278.3799743652344, 143.71145629882812, 139.65452575683594, 102.4893798828125, 53.99258041381836, 159.42381286621094, 11.760284423828125, 52.29745864868164, 172.6008758544922, 203.1627960205078, 96.9002456665039, 106.08184051513672, 140.292724609375, 210.3992919921875, 344.2892761230469, 47.768638610839844, 244.9041748046875, 179.1565399169922, 74.48597717285156, 141.63851928710938, 207.7462158203125, 72.93447875976562, 14.993000030517578, 104.1656265258789, 7.667314529418945, 97.15251159667969, 10.034051895141602, 148.97901916503906, 246.16323852539062, 20.872098922729492, 267.87701416015625, 81.27671813964844, 60.178009033203125, 57.43025588989258, 114.2837142944336, 96.63896179199219, 78.44661712646484, 54.89338302612305, 137.9124298095703, 88.775146484375, 86.16093444824219, 106.36314392089844, 59.19734191894531, 235.592041015625, 54.05049133300781, 86.73017883300781, 246.34886169433594, 59.735260009765625, 61.3568000793457, 138.55210876464844, 94.49560546875, 191.5329132080078, 105.0457534790039, 107.06875610351562, 167.26953125, 57.81262969970703, 162.57070922851562, 246.54515075683594, 97.76509094238281, 51.61533737182617, 58.20122146606445, 136.0362091064453, 46.91468811035156, 57.178672790527344, 155.3135528564453, 248.94119262695312, 156.07862854003906, 115.60499572753906, 43.98484420776367, 186.52821350097656]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011607</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:00:23</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>84.13482557341565</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>60.64578292850809</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>108.3456201214224</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>4612</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>[0.8887089685177488, 1.712225472645772, 1.9042459995872083, 0.5580048086616287, 1.3030470707213684, 1.0023846375984764, 0.3884482898432192, 0.9866477581663341, 0.4440388557033221, 0.37992265713830287, 1.1334478273243294, 1.424265855721227, 0.8671015725920974, 0.6280641742032147, 0.8844584399508091, 0.5647851117569135, 0.9947568788689259, 0.4535687915144612, 0.6537179135451869, 0.2974611546271942, 0.5104095746621956, 1.2527079470141929, 2.241966398700211, 0.6919658689608159, 1.7732839644020344, 1.2177886065103076, 0.6480204131731068, 1.8999008087420743, 0.8019236454871834, 1.2370839172917278, 0.976062477949543, 0.7790388677379393, 1.7527867703507165, 0.9401750420662629, 1.0212125709120414, 0.5326104257849563, 1.686466419016164, 0.5959832707734757, 0.6063592819819427, 1.0889144473965748, 1.659179408443752, 1.0328375211239469, 1.2243564168492815, 1.5788691700675368, 1.8406294854852097, 2.9761563556351507, 1.5977811101615451, 1.9616978928747988, 2.009924307799277, 4.513250718067399, 1.3183582615606169, 1.7385873738958093, 1.0424822582703273, 1.7655242455000053, 1.2923306556544272, 1.6762808211827263, 3.4705805661686906, 0.9207428474221231, 1.2834475343100509, 1.6511833885201457, 1.7564492547833515, 2.6422873326683187, 1.1399558401465946, 2.8536824778252026, 2.086821584232492, 2.211705735235304, 2.1819748520748954, 1.684602957288307, 2.741883688828091, 2.6447404863542365, 2.2461251491161836, 2.018782798517402, 2.464079196103907, 1.5863166583675314, 1.7543022323938335, 1.1493925099870703, 1.4128292788619987, 2.791818548627871, 1.748568275861171, 3.0621791329624823, 1.984169283562311, 1.7049750054137343, 1.9747567380111386, 4.64609085911598, 2.479141207928678, 2.2396834420702785, 2.6147077918806563, 2.006606940505993, 2.6710700125289897, 1.288051805099176, 2.196091486729384, 2.6221943078922494, 1.9668834518605895, 2.297359609460382, 4.209966352000175, 3.831072962496946, 2.0732035395184716, 3.0125213730030826, 2.761156377553286, 3.8671841415067973, 1.8139330450937265, 1.3241686285375842, 3.1055675147895143, 1.6460172059466087, 1.976345325623754, 3.331710347466923, 2.8782637852911366, 3.2011593550470185, 1.4153121980355927, 2.6764657123468565, 1.6542263624215305, 3.5048874646273482, 2.6762041813669373, 3.4201427046356283, 2.7127374573339442, 3.0385358298017793, 5.098792800522228, 5.769496677850722, 1.8950236065720243, 5.073062572169857, 4.529860219018123, 5.32433313805565, 2.407131803203464, 3.9094224845087053, 2.414361198286116, 3.7667547066266556, 2.495580729024547, 3.406464012699505, 8.07094870618879, 3.8593066483584084, 3.3696249176017843, 5.26314294954754, 1.7974919809088117, 14.648055204521011, 7.115543055483097, 3.233849368335289, 2.1705459166080554, 2.766630003527251, 3.7058084356451295, 5.021236028047337, 2.5154758540630895, 0.7908661398870743, 4.734866593874382, 3.0353056885893634, 3.6805299644135117, 1.757400939703125, 1.92404952198473, 3.3205327285140616, 5.372873532430028, 4.546538733517711, 2.932093739016275, 5.057811830843822, 2.340382245879197, 3.5767926706161637, 4.308625314154804, 1.9528365395770328, 8.392399263082751, 5.865270121926468, 16.67587052677299, 13.533800313564702, 7.249479595675118, 16.99824205391536, 2.6160234477800945, 12.223765047968246, 1.7241060353553639, 9.811273548955063, 12.230758543396085, 4.616929994851838, 4.982029561009453, 3.9800804067193885, 9.149545011122196, 6.697570850624993, 8.489616158298695, 17.876309395303927, 10.926549882057957, 3.6888232953535103, 6.519603514457053, 5.825878182087193, 4.035547199902397, 9.29331342842939, 5.66528833761525, 3.593648109782876, 10.674106410177213, 6.340209856687467, 3.225525251174467, 4.963418339265314, 6.187013593855035, 8.115825708949245, 12.385611561164696, 3.944215837698885, 26.24343093634278, 14.822857620054487, 0.8713025645354406, 7.7566801527352665, 18.788187067965602, 5.509348195787599, 8.09123328372199, 7.791965255245548, 21.345173079149504, 19.57456327797773, 1.4147732751828266, 11.859280730034092, 10.696448205460154, 9.973068135100496, 17.434200326672663, 4.941535625193868, 13.862308161337282, 16.812289233463197, 25.1350682136862, 14.521538381251718, 10.05889362137205, 7.760846309697314, 10.043600692992127, 10.053006247368364, 10.609515662357122, 13.991737601603823, 17.241809561833715, 17.500524745528836, 22.36463148804343, 16.822943124994804, 28.30373807163844, 23.568378164919565, 19.259216054284316, 22.9118291349566, 20.722336738724145, 14.122752555078856, 5.465075520811643, 31.654096144667374, 10.516765528387472, 25.315026549121164, 10.681593227291588, 8.816212737670146, 34.091440587021864, 14.25051346784954, 13.22204221029307, 3.6698724200644413, 13.263561943211561, 20.176248053170795, 17.7902469111846, 25.365094910155523, 22.34142789861294, 12.34155603209597, 10.642691364349535, 8.973843981836154, 25.519582212490963, 10.576123054666072, 3.0430116303239814, 26.081110210714726, 1.972248335001023, 31.53095617660606, 17.971974072840588, 35.168995202341286, 28.671045280410766, 14.08945593690217, 23.19452126999494, 7.014084521115692, 16.828288493477434, 34.14224449784001, 18.866301485769764, 13.315590487195681, 1.7292562840459131, 29.43429267930902, 9.59025556957668, 25.659846630101367, 28.384397775946297, 10.868228774543873, 23.07911859203101, 8.857609907977238, 29.146578024560114, 31.404567465699863, 18.379645630796606, 13.0805666966965, 25.132528348104803, 23.451250444272045, 12.334445868600817, 43.88858545619872, 17.477222564996573, 48.327797876600606, 24.098105691516608, 15.801477009626533, 32.512829420782154, 18.155442475012126, 22.163519142799128, 19.439790668540997, 24.721250534870435, 35.354894252944256, 19.855370396081604, 29.904585060630065, 15.978140706864975, 22.821920076839074, 29.144737312205223, 15.655365191071946, 26.69835131387461, 23.237386451805364, 10.797364433538409, 31.887550164569586, 6.479742281647486, 26.394770603869596, 33.215433162079506, 17.974707642450806, 36.775758264759325, 38.212622167324064, 46.531836932963174, 41.997508928308505, 64.1787422169227, 38.48949683935999, 34.59951421397093, 23.6787940186647, 2.6250911732150706, 40.788067362763705, 26.628819163451826, 84.8746081307158, 26.919933450615037, 67.31001009326492, 18.809104464536503, 29.056431307561553, 22.45896503566018, 20.877182849540617, 18.520811441493297, 24.534228960133923, 29.241809722468847, 24.447648608342657, 25.885948353290875, 36.35596442892324, 44.10299432013161, 3.2560059643531623, 31.99709114497215, 34.826912371294675, 44.14403354226578, 50.97171055755981, 26.40914795509347, 32.406034047450305, 32.84754520117083, 3.77399782946677, 22.362406668186903, 3.831390320553308, 86.79262987291071, 19.761760130917963, 36.49311046651712, 46.21594511192208, 13.27830653015261, 59.34936200099434, 62.80637877300573, 25.247066281887207, 56.16360699252498, 49.94241897784501, 9.678340571801039, 34.60880675506916, 25.451289696031303, 48.18480777884153, 49.30420958084721, 51.40355011804683, 59.34441793363768, 29.96606985592455, 41.52002465872067, 67.40207758129735, 46.69553899414056, 60.880367862631594, 21.98775846292552, 29.38552631108299, 32.05678705029762, 46.20930932236945, 34.466326739032176, 79.45205519084814, 64.08376725214228, 54.99177489137162, 41.431227840518794, 24.253102732826864, 22.3721588340406, 43.7983901986984, 39.027885237975475, 7.144388705232764, 33.896598302269105, 33.55154974474901, 73.85851498908207, 49.06713036397746, 57.87849777751066, 17.84322974369946, 59.4411741702046, 43.197401576051085, 7.25357768538847, 7.252722671387152, 81.99587094494015, 43.57712449781483, 43.66172792920521, 43.831822055008956, 51.70266386918994, 51.72990896363609, 34.31533367994624, 7.990126960955725, 43.35187288944054, 38.66880315772372, 19.826215449730757, 38.221843118474666, 51.96729985253195, 43.12530459363515, 30.552942038673713, 53.836945855225345, 85.1171336446072, 20.270588178212222, 34.06805929310595, 59.52589763527516, 28.746067024094124, 66.61812168324603, 43.34396416851378, 40.47257497122024, 24.793217955608387, 39.55440233948394, 39.73163209719389, 68.52762889451922, 35.732527059532735, 35.709752952757405, 43.99304935879458, 43.24838200314481, 45.244104148743546, 40.869905762137186, 62.42548808372114, 51.908258643508, 44.118335887552675, 43.77051436679684, 62.08146222966476, 47.32104861172965, 37.70854208831732, 53.19307599540974, 30.601011277211164, 45.90669125580153, 39.5091864857827, 83.10415481066187, 100.52677044698375, 26.49555304786025, 50.62554001409608, 40.45885621265647, 33.511602189495406, 46.06775609467562, 72.0827497223349, 104.6406357276736, 65.11511272222324, 4.584141501884143, 53.05271078715996, 45.30202389106285, 54.20488873591991, 38.00654918542655, 38.827658885257044, 68.64073762735593, 45.755447693617924, 102.70168555903209, 7.021552666457668, 48.90486566279585, 77.22841907115017, 46.332513007026094, 44.6237339917996, 52.52238312077793, 39.014795532014496, 33.18266468454177, 51.842133103181446, 30.830098431757335, 51.508436679708176, 58.71940995278818, 45.50497288178434, 48.70690328119047, 76.67991161464923, 37.70924982688256, 43.824655801243324, 38.369615836397415, 43.97159744365416, 34.31852639504848, 32.17813310330609, 48.08222714016049, 82.95112841173002, 43.60177380701165, 41.58124870978047, 112.41067752740251, 22.83352021251616, 33.24384916072669, 40.807474312444974, 59.838656902220364, 69.53467461414982, 50.567873969015, 38.104813381416506, 27.572460609329895, 33.3249603637756, 32.86212310836141, 47.69871456831165, 138.83386995067832, 55.42624846627559, 52.072684254604745, 79.02832731559985, 7.305148871805976, 36.6976059057047, 32.1210599324309, 83.29737993042487, 38.082693124286784, 34.69700406108914, 88.8756123455617, 51.081545257156776, 57.66737511300893, 76.114399117976, 34.9460148815557, 27.83996733172616, 56.46597773090904, 84.31645909827175, 26.7514107106657, 58.330108508725075, 137.00098908612847, 4.760729805521677, 95.26462889899054, 62.01527092989234, 42.27144317760841, 83.70177503320501, 39.27335878413663, 50.72804664387351, 87.59802160424327, 102.58760690413891, 64.8040203219586, 45.638859658869364, 35.68712510553472, 46.1526326413628, 42.7140779305245, 42.656624174929355, 38.719569009883344, 118.34093812283635, 57.98357441981647, 32.304672925905955, 38.74955350161331, 111.78973192676845, 84.38699281542188, 72.43140071353082, 62.57845630239641, 56.29419263821576, 45.86385426016898, 62.069527187855115, 37.90403723066706, 51.55721807646017, 66.6445945515142, 80.98246462361944, 34.99203832791488, 37.72183574584413, 58.98824723833712, 39.90212115600404, 73.34927304520467, 38.70575591904467, 3.548760824217505, 38.813420999667656, 20.858476057434434, 71.03430944525982, 50.4348882246382, 43.64554894452859, 67.39291987673285, 66.45960610252898, 72.49759997309124, 25.943918434239926, 42.58021525752917, 38.3014148100721, 53.79888601113553, 99.51832262440742, 56.52149143305707, 66.19137728687089, 82.1346822658412, 47.50721380717321, 92.25944355932741, 33.85159273755295, 56.686451606103454, 42.196835300566214, 68.41923073482316, 132.94493649923666, 50.702410904972155, 44.062134300239634, 47.37824899741116, 57.42307281194324, 36.821571990756546, 88.45518091840697, 46.46227007777652, 132.7755994065055, 28.621231349858267, 238.34898566930232, 43.92727143310851, 27.997845380754555, 57.459025843998425, 50.92371174608637, 65.99033705614121, 70.44189722910421, 88.63432408556535, 9.616616726460933, 87.93543198317467, 37.76044645666855, 101.44987024478195, 58.29353781196732, 64.59723576645654, 60.28179391955307, 32.99765433692537, 38.047276478135814, 43.52707971530303, 72.45267875443695, 31.6156011981017, 53.34720492444149, 90.18482133477764, 34.23598837513797, 51.19348364688994, 70.02638533384172, 50.585709680437084, 131.79780501390437, 90.24052041241771, 136.91333462516428, 56.721047784014644, 54.2303030705596, 41.74410105424103, 74.23639133615926, 83.65783435400256, 50.165106770999444, 40.123248184181065, 50.90509225513024, 46.3964868425827, 46.569039449481544, 77.15326968296463, 196.7867042236132, 139.46461732201143, 81.13282098052419, 39.06956979240709, 103.36867415574524, 47.50392338882948, 69.84150131035409, 101.05371704440135, 57.888791461046424, 47.20335558783233, 96.64672584861853, 44.976887759056794, 58.057174612215796, 59.9863638898859, 45.13140836621309, 12.622564007942872, 46.34090508733095, 47.92350030266242, 10.558786128720417, 72.97163131874161, 56.676413448998346, 217.28992887521588, 96.23243901539297, 38.582694601444445, 124.84552526159194, 56.207396932944945, 52.69294660460942, 99.95662710219476, 60.336769321953135, 52.53157176364334, 155.298078333903, 90.85006492828505, 36.248917543219235, 50.61933021553778, 47.51198612104027, 48.4720920692254, 53.58252212123689, 48.621029702441305, 45.131387698992455, 45.174224610969205, 77.1900637611584, 79.46377108427771, 58.20720174526986, 50.91569190798426, 169.74039846231219, 51.706052805401846, 52.22271363714883, 45.60870334847906, 47.98717139202123, 14.409423575230251, 59.04951032212936, 50.324107258063364, 67.57296041530604, 69.62781177981084, 82.75352376290782, 112.4461275646527, 55.80498664368203, 51.508589393066565, 66.24637620614037, 56.89231767882717, 53.41824865223853, 176.5712367043482, 57.804071957114296, 78.81055172002513, 144.3324298861058, 47.53009392923205, 36.38396760155702, 46.73943634291367, 63.26813158020861, 109.54154457580425, 87.65870057043986, 70.06230373867318, 74.7200371162448, 70.5597138221116, 120.80613604549868, 68.6226157991827, 39.26658930141194, 81.49199887125957, 66.74988470122157, 125.1239296627308, 107.79457244390291, 39.36686933119677, 43.892032847721865, 99.02730837192178, 54.709120696451045, 65.54539963850299, 45.715776862839554, 80.79309073492126, 66.9531144576852, 56.43134344851399, 108.29804076655668, 51.194358875179866, 109.96415895453192, 13.788940212142865, 64.7634976104482, 44.46079433587535, 45.2371992462639, 52.0702043350904, 90.68862388960179, 39.31555876881965, 141.49460890001214, 93.00733188697336, 52.61237630088471, 52.34082626203474, 61.703368595274554, 117.1538859741898, 119.73631518960947, 167.72041893558153, 39.4849022098719, 65.5534406854431, 83.17901696358636, 61.10278837442334, 104.53233583787066, 70.39195264649366, 45.994418093495035, 97.05544995099409, 48.59227362349289, 13.162225051305796, 82.29821728019661, 60.92920802317213, 88.52460343295883, 97.87295251341482, 60.057592600650594, 62.17054886992021, 96.22657586572929, 40.96645142017313, 80.69541804729167, 55.81378023279333, 20.996133318272992, 60.92776002940662, 39.09215931517099, 56.05541473252577, 48.806580238988275, 51.53395662256053, 82.80630572226555, 71.64694422309297, 46.893142546900656, 10.375914950563311, 43.0976713960905, 60.236048024802514, 67.34468898831297, 72.00596037174179, 43.53383800155532, 53.065361228211394, 171.11199147081751, 45.73809809461049, 46.36543054333735, 59.4351341241743, 97.27436875156337, 57.19354974746135, 55.45822965673569, 67.98066275679098, 153.23937462630292, 62.64784773584174, 74.5812344529155, 67.95679005129729, 61.557574090481666, 39.47192004958602, 178.66434476616965, 68.03041208949703, 43.66227385789698, 69.51183219025661, 42.21775337136035, 101.90221335028467, 48.19443103105172, 48.43230674887109, 46.72588391248215, 11.543257788073417, 46.80635469353427, 32.70347930294541, 49.56048154965827, 40.12351460398011, 14.224163444318316, 59.753779801695146, 58.027849490468604, 56.55772794306697, 37.6965528047249, 58.12231816740636, 99.38738794994063, 78.28911638429953, 127.80614156063254, 80.82035169587873, 86.48069969393359, 23.042984488046006, 120.69888393513253, 82.80955827570907, 35.313456293804094, 49.726238097174885, 52.73348110079853, 66.00690131919691, 9.912285734138024, 48.52406317893619, 40.7610704289889, 116.82661597026535, 109.45529552415228, 38.536615509094, 67.74934790766338, 49.06851413438267, 42.61658347592212, 68.80116966713945, 53.402048544275154, 52.534044381960186, 62.834813392594015, 10.36424878166743, 62.89788872184975, 92.41986889603099, 72.0546886974777, 53.19785888257127, 67.43082932002808, 5.328350060833591, 43.6925415682291, 151.46213230821877, 114.664129312131, 14.072673834586341, 76.2318474711704, 74.08193590262938, 40.300406263052444, 58.8177152911809, 51.20767569634738, 53.400012161610235, 132.85281884015623, 56.023382861443444, 45.11353055848411, 9.984263362000679, 171.70143807833193, 71.50433268987172, 71.35798713204206, 48.63617614366252, 53.49882713636286, 48.13267013956243, 54.72268199017617, 54.314430723791226, 97.26814222684386, 167.3471088616285, 53.94321967125368, 46.67158116213399, 8.299079099626391, 50.45372919603592, 54.68229011164935, 82.03386561324506, 158.13573387799013, 134.36038174374121, 94.93480818009992, 61.5491571481375, 79.34991066503954, 53.357346716554645, 139.00933909397205, 63.51382466203502, 131.35379724015488, 138.26080663001673, 53.86434412429845, 158.76581931216506, 75.99808846542427, 126.81034088227925, 123.22950224363028, 68.76293288143167, 262.0813829758751, 44.569298888436684, 68.8788383462911, 88.47730461274708, 62.20448702003681, 71.22530328779993, 72.77304396373319, 5.510704399228976, 81.42634205957435, 44.30797588972194, 38.66695452163209, 5.649579502143722, 138.83039756608497, 73.98703643548511, 95.17715371420461, 70.31137036805947, 102.18331540216818, 74.43960169452639, 100.26412737157781, 101.0933844974834, 83.91530426062906, 60.62747170125295, 65.89514384593755, 81.25532640806502, 109.16365531124164, 46.072326509901046, 36.62669292335144, 49.72863050914623, 51.150106420203706, 115.87836352150988, 77.15041733203967, 77.45630534434723, 56.61088371358333, 119.63001507384696, 69.02479597217791, 100.53883841125631, 71.0540299540751, 70.33259478013848, 40.87450807914039, 35.588842436052985, 184.1579616234172, 43.36044007641704, 57.963345717839196, 81.60730416228407, 193.62021394191427, 86.89574912690085, 47.39634675586547, 59.222828170874465, 81.9628834258791, 60.33320385207296, 65.63396908675364, 10.633910857774378, 66.95867629238046, 73.36745770183512, 40.7353895721239, 55.34558828174014, 70.52439552975629, 51.38709769725738, 60.57907510920989, 42.830012777067644, 76.32157537402058, 70.81824199750912, 54.83933540556516, 106.13976330275679, 66.23549403664354, 43.01203279462836, 64.38129281557498, 57.22562318158401, 86.76678567288438, 84.2654079518967, 43.941296589668866, 77.79283861473925, 88.00028552048494, 184.6775574020316, 68.10408208304626, 94.61491967856058, 74.31546932540905, 121.72254214040976, 114.47662023017982, 78.07576817823397, 179.49211613125217, 53.80702330434315, 88.24527646296984, 75.53403561011358, 67.25543098362215, 8.943183435716033, 50.727659612094016, 133.37650662326683, 54.904683723648766, 48.63676906497277, 88.02492499118927, 89.30602118248498, 8.392563016387756, 47.69650538399387, 86.37034720888596, 63.449092515184816, 57.925656280866306, 70.45095643625072, 64.15512479856675, 40.559924014610225, 44.983971223917536, 74.59413644558038, 61.5185155997663, 54.47162624169898, 43.89756038877283, 75.04349234653571, 54.01306655015833, 105.32111240349047, 50.10322211148362, 55.2024970541723, 58.46745934838089, 63.43069839993366, 71.48983370849254, 89.19637706812352, 60.93666357178454, 105.92233646057835, 6.953007975892873, 97.804093511876, 47.313098075300516, 42.56397667887682, 53.5121055167081, 131.4745271114379, 65.09212863308369, 11.61121745179167, 58.77297628583139, 62.33013878976661, 43.03829667516636, 36.30334922503967, 63.640182450352995, 71.26828953503606, 64.11345393263223, 80.88082949679357, 51.71259907098031, 83.44040929651152, 52.12102819063755, 147.4380356509542, 52.62679984600366, 152.00629754350496, 164.62740422577582, 53.22941561044456, 59.820901825602405, 108.99784818042917, 36.10411595758472, 71.40104028023781, 66.43352665036211, 132.31863446391125, 140.20851299844736, 52.78729633650634, 7.533573630046856, 62.13982913323741, 73.276640452532, 40.97695748096037, 68.56584615435793, 98.51705222454099, 114.13597942697493, 9.760196216844427, 55.352729947074714, 57.783085200677185, 67.36657238825707, 87.65280868845755, 9.05859469249432, 65.07111290475446, 72.3418251837813, 78.47234403691233, 61.308110711964986, 65.42128064651887, 64.85369874305708, 153.7640940299229, 107.65640685861584, 5.368158544217574, 54.800971824946096, 86.90814083049875, 35.73759951847718, 37.636638835623394, 74.76400555994893, 104.25490878181348, 40.92500894965638, 190.5192844903526, 67.08328345144282, 6.0677920207109, 65.61819948088045, 141.438532452098, 116.58356668568115, 70.81982640942675, 86.89123178503012, 36.26697880131296, 52.264785416500885, 174.4240402059672, 10.483025374169287, 54.59455328066912, 54.785474976323236, 75.40605700795636, 49.11608202028295, 4.4106084030228185, 50.58341289012401, 65.39968536587459, 81.10904679615487, 81.0821002903309, 86.56653802742865, 4.115883296636163, 75.91545209315944, 241.74453972989303, 41.13247293001133, 56.02112728673534, 48.05384495583302, 69.65973707895616, 48.02505508152368, 119.1325305231535, 102.4778155740211, 103.05205365537923, 64.88380029624386, 50.80510461531294, 42.88355021709965, 61.470977020084725, 122.74315788723298, 54.86770199104113, 50.84114455552768, 33.96062064986782, 48.395368245963006, 4.283582547692108, 166.4225718510937, 73.34933878623288, 40.858000969177986, 81.77484636802814, 60.56946558147946, 7.176178398021136, 84.94271970619624, 78.88789162229983, 4.706427186462356, 89.09813093531636, 72.51867556115465, 56.23709085508429, 55.26667886612936, 38.78554344865483, 66.809977114151, 111.62511375350952, 35.799805777453855, 120.48865689560043, 47.549655475035436, 7.494786448902967, 93.00017119835036, 61.27855987891383, 58.1246395689163, 67.69606039678935, 43.329321998054404, 70.19611387704516, 45.69973562492667, 236.3928896795644, 46.08711748766359, 55.4323637126079, 125.70327043915974, 178.96819849353216, 68.6634039968901, 101.60510285270382, 10.695068794323738, 82.74244989654188, 75.32828733364612, 52.52196885359215, 119.8529336891564, 95.10703037276218, 58.56473161268, 49.72343568042289, 84.99392003097826, 122.60844496241755, 55.10205904620841, 392.8598123111764, 49.90721137854303, 8.45631218306583, 49.851956005588015, 49.69136287485437, 108.85248535570922, 77.89607788812673, 53.81688509707613, 93.00619600890205, 73.85142206423176, 62.36990927179324, 41.362241678258336, 76.48290540306189, 53.56318010311284, 37.772221181735084, 58.97029067275863, 74.96174777722527, 115.48103879168455, 42.97068338974291, 134.37494819283916, 78.61156227107604, 95.99754353891441, 38.812867121355815, 72.34266503897067, 86.51147601507634, 51.23921060324104, 76.76800011381032, 49.05932909643334, 101.8627082714484, 56.920008314547566, 73.46180700256683, 104.20677174387764, 98.5138916654795, 49.40964826440717, 73.50914591418024, 200.58597642468072, 89.00306387191394, 76.52050895391046, 57.79115629664022, 55.68572045534194, 239.67652641062242, 46.507498184353025, 110.50218536032153, 96.15059564077929, 49.74498026580406, 62.29283353570816, 54.22346549476095, 55.84473400588336, 47.06986093339287, 123.3583410709414, 91.41084768152936, 4.9905948608100195, 54.01288635223917, 46.825858887229096, 75.52472328300117, 57.213115281894076, 98.69212451666012, 60.681723694399125, 86.62149235319274, 64.6895691788856, 42.223570755873524, 113.96572001387639, 36.818678024887795, 50.66767129937317, 61.784144102650444, 91.64447771956696, 166.08167285494753, 59.95354675385812, 88.8736357547602, 45.63069700411885, 156.68733878009377, 42.09806989960326, 86.43411726888401, 51.60877989268699, 37.72102448242862, 47.39958394827547, 105.93187089169199, 57.485820693021466, 139.38669687211183, 64.36600964348256, 139.85402064840582, 53.73374705794362, 43.979307360399446, 67.9445318793456, 75.81663415048962, 6.477940237090464, 136.61112935246607, 144.4484744943298, 44.11528542797369, 50.76733022833727, 88.69828613346883, 64.57293230346792, 5.294024558169323, 79.0273351975366, 210.00710098655424, 52.0992495921553, 45.83741663817397, 62.54371403061016, 82.01986973469131, 100.22694200948415, 43.88714749758585, 79.09818191633103, 87.94660812782521, 49.56248742742737, 79.41440096810379, 82.61976879790915, 55.02007077968821, 49.21342269082203, 69.7458238629503, 54.21947341126793, 186.9606190287596, 46.235569501169756, 76.3801480075906, 80.597290530286, 82.17225781041162, 66.07758216275562, 37.29655308461, 54.82468852835984, 51.618057513108226, 11.18240702700659, 80.84084981107561, 39.02443229769619, 59.37754916477753, 107.64211519633847, 49.817393787901956, 58.49460954368823, 67.88238714965146, 46.93258947279999, 97.14722886809837, 69.79832839475674, 56.405659534974795, 75.87466768008792, 55.90528449972499, 52.218523807589754, 62.557147812911886, 92.08849425358666, 7.480500680402535, 64.13439853857989, 87.95614080467568, 135.41861192237926, 82.48942273243793, 60.7488418889298, 62.01624716392449, 60.7658820155287, 47.6324202642397, 107.08001165798309, 75.34958733422519, 68.03685168454003, 52.10008299693521, 162.34988665619764, 222.89095731093863, 56.60369389134535, 55.778913660401, 54.023990156109456, 74.90638360302736, 198.30246470643178, 77.09100439569288, 96.81928805813615, 63.135943563870754, 8.899977888795032, 66.98440499741392, 81.0595935132939, 137.50428415512758, 42.388067024804116, 97.3979887571189, 48.872530326034166, 99.05946267817382, 135.6498037862238, 63.02105850074694, 145.83176305047596, 86.4465938782821, 204.4434615837188, 91.51258394758935, 87.4091594432661, 66.69367319236247, 35.02539005157709, 10.91375722968961, 160.13036969391112, 77.7021546659581, 56.22155142860149, 232.21164788652624, 50.16708944171709, 70.62119999632891, 56.76645709155568, 66.49026848628776, 66.8941776788849, 89.62860128457768, 77.91304697554902, 253.76147293359168, 129.9956597864669, 19.071247139437794, 90.80321548372785, 32.33667443357453, 120.69152212647586, 53.4010641505496, 102.69861571250046, 196.81843020725364, 53.17519630973277, 114.26766939191701, 119.40042658165737, 83.55664643279705, 67.85409588077482, 10.340519608030723, 60.41640296812306, 59.238416119880405, 97.9969309348846, 55.70313883126553, 61.67037887938985, 38.50984034958462, 109.55720587655362, 101.09000774316829, 91.63400614026165, 177.84999555614266, 50.57542908267233, 11.831877405819446, 80.79003172687693, 58.60283783020579, 72.95530932401816, 51.76360928060449, 52.334901044362155, 80.43639041581106, 52.098321568007904, 64.42563932497376, 151.76227523262486, 55.43697708248133, 61.20308492260095, 28.087618021154164, 21.727382340657982, 109.29169705890598, 52.42542300764047, 52.42510549397237, 38.678737086369374, 81.95736422668202, 249.31020491837182, 65.95799488083243, 170.76991100730493, 103.61934082185027, 67.70290844803112, 69.85737088537027, 82.9287450831601, 57.056278683966234, 93.75083000459308, 54.441768890910666, 141.916911337182, 68.72101551799122, 49.56439774027633, 64.99907273010507, 55.870912237348776, 98.75665530823025, 58.24834130493659, 12.525481182558284, 54.382794684137025, 90.07727869332344, 67.51165701606789, 104.03724517746168, 53.6451008900408, 63.537652922167545, 57.754180124683764, 103.52613954623338, 103.11569116112061, 57.604022386341775, 68.85077785094597, 118.96241524629053, 80.7264573534448, 83.67963672053385, 114.82011292214096, 110.56489385224423, 129.20293640201845, 14.353895584650068, 59.92859910002737, 127.96509348039585, 61.47891620083969, 114.55591306337558, 70.57868920573108, 104.61382631501748, 56.96932428347318, 54.960457035232416, 75.63306228029089, 217.17554670886412, 46.584471141377406, 81.11189797418572, 46.93544505836479, 183.99598287638239, 93.31697063094839, 69.82438181292362, 110.3394998275943, 130.34472999079387, 89.83638032828232, 55.972557721530016, 54.94624821769081, 181.20926582738392, 57.53865081652353, 45.88766439968928, 12.310142476769434, 64.92307286823774, 26.66424081411822, 58.03237782436778, 59.144336395060385, 140.8354334616216, 48.16387781112998, 76.75304006336793, 75.0032660293663, 111.81558185356124, 66.2296272337867, 141.31435418960092, 97.76991691960461, 68.55297509340915, 65.10095486372535, 111.99517222560065, 132.39063722676522, 59.13045999025403, 56.91289474954233, 51.25684317706616, 51.48579198531454, 204.54173029087488, 68.10715821515385, 80.0553328502837, 63.447703304830355, 173.81402067622133, 57.88854551864448, 63.29411463494907, 92.98938939244138, 16.845091137415316, 95.79410355251095, 44.802460773080114, 72.84010678647958, 79.43898785100838, 57.043863097731766, 63.80508361509534, 66.17968901864067, 47.1426286073357, 41.72772074430934, 187.8039778033721, 57.11639783411555, 28.071450928703246, 9.577961447516321, 190.46653970717313, 59.47659493354791, 115.16059080376651, 48.33812734280414, 58.39381863438972, 8.781149142380295, 247.127287818012, 42.57354370077624, 61.478405000257936, 64.98301418987255, 142.6605772544876, 51.63350700444049, 74.21274938383114, 8.793315937414148, 57.68475834552679, 112.74756838254444, 93.08092914598153, 10.596829754650999, 45.000099232365955, 61.30747814639495, 53.27989179087411, 39.149643371579096, 51.10450349960194, 40.15894831444544, 50.635974054439856, 40.73817145838093, 147.58324328788308, 119.48026818345514, 136.29927675183208, 97.00877586939214, 85.49214830775908, 87.68203874523785, 105.8318654620911, 51.43254262034667, 257.5432999476919, 140.53370317050963, 93.63839998632307, 122.80694470300251, 85.30066619071441, 57.92260664984667, 69.80639742277818, 48.21162149032162, 109.35500218375434, 11.786904945284375, 70.28277356469485, 54.465730538408216, 79.21524679515987, 6.459390096022294, 65.95233518986755, 80.92218645001081, 56.50837124278097, 91.48718922355627, 70.58135639055706, 265.7219075176302, 128.57424138089084, 91.56454992894108, 60.253949811605736, 5.328268912065525, 108.94086763690201, 54.817241870780556, 58.18743170813878, 43.64732557682871, 135.83122319005872, 85.38268183040837, 67.15727415536495, 49.492678379476516, 200.84063048037626, 82.71131089203203, 140.24501128020944, 214.21171662785196, 151.7636486374656, 61.31995395113028, 40.81446681004847, 61.00512750921866, 97.29858099108623, 7.7435392870671915, 62.91309595605582, 56.61380494919728, 95.37035224423832, 44.07966322046615, 39.79559762000984, 51.55595591254373, 115.70179328756736, 26.270463290081466, 70.02254856504378, 48.363176834606456, 83.21729693573424, 79.12184666966827, 58.72102833152302, 59.619608665753624, 91.51560446957406, 58.15010338187861, 123.40307915753307, 80.17289695119942, 84.5496006035815, 68.9496964596954, 58.088622678252854, 174.05225395028026, 128.94692535021923, 47.060913212550076, 69.59690278565274, 50.04033989392471, 81.72744864461197, 63.11188143929784, 67.90504659268169, 132.5266092183081, 46.88826113539379, 64.05842543495845, 82.26180161659859, 73.4546399520216, 67.25411740623741, 37.5665606760813, 91.71395896355422, 69.4837288943816, 52.270052606396845, 65.2507871415101, 77.12477284814305, 67.33658382056892, 187.0240669773952, 64.10917091964961, 71.69183770666562, 65.71563860090627, 94.57008986639087, 35.93112562720872, 199.70675149039158, 5.1232034739261945, 100.679062841855, 88.93529869499893, 75.07666079164488, 135.2677213677407, 240.38787676505754, 221.19791599259995, 86.94969650636232, 66.67158089739694, 113.75397230260758, 88.25635110051653, 101.13005751206711, 67.56633362747331, 71.51328467609756, 82.6751456200513, 134.77179848600485, 71.58475851803739, 117.07546744625257, 36.843374353762314, 94.89416942827351, 82.04900147129904, 73.5885597741083, 55.004443898751354, 131.2479499018124, 100.44405672345455, 79.14124359394876, 116.024630876287, 56.84052723091203, 45.66989464043534, 120.53526017641673, 45.34686416595384, 62.72425474981112, 107.34489625481999, 85.57064456469264, 67.98352190396908, 92.30873800523575, 57.336392952512234, 78.46849242028665, 102.89433906510135, 115.70744327666557, 113.42405245866257, 155.10243041411428, 129.55399946808464, 61.35140592495943, 47.450500305825024, 46.57118053824667, 78.67739845498774, 9.234262578779258, 15.179172850349776, 41.58918791670225, 7.539500606085145, 128.29851330500605, 120.64737899361272, 48.905201414828625, 36.510962141308, 127.29014474653115, 84.8484674212219, 37.82625641075411, 47.26664399374979, 55.708328767463016, 52.70304798796808, 100.36893819879148, 66.94830510262065, 85.70497739523405, 89.85407183303589, 81.342669316438, 49.06000323424421, 95.05936924325471, 7.253721708859535, 60.46278027203516, 70.47442206015192, 61.78528443938956, 196.40006668118872, 71.81308724972587, 96.85499755150349, 73.17491036993239, 56.3895590443987, 73.0332569545063, 135.62913873646517, 106.95663709387361, 132.4536396103402, 50.3733277138087, 54.393220605856925, 121.99101085766033, 108.2579564580014, 104.35994963792129, 79.07888416868131, 82.01292758819119, 77.2373225252642, 67.8324705117757, 62.46029325789678, 226.04447581169, 62.75024130782986, 100.47532636249923, 180.10058936510572, 63.500945923445, 56.42448816625763, 37.185422640929275, 9.462951920674499, 124.35573852750494, 80.87819031579826, 38.22908847341013, 39.054768118889065, 60.45154529735426,</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>116.6561097002029</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>91.42631236766378</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>[143.48963928222656, 326.1622619628906, 69.28093719482422, 92.43937683105469, 143.802001953125, 118.70943450927734, 185.10617065429688, 40.069801330566406, 82.00274658203125, 114.99384307861328, 86.00995635986328, 36.8582649230957, 65.27339935302734, 103.33013916015625, 10.834807395935059, 130.8031463623047, 89.24749755859375, 291.50189208984375, 100.2730712890625, 325.65728759765625, 176.21511840820312, 130.5067596435547, 90.04840087890625, 44.581268310546875, 164.7112579345703, 47.827125549316406, 82.00736999511719, 51.93645477294922, 59.57971954345703, 83.8161849975586, 82.53952026367188, 70.61274719238281, 52.45607376098633, 178.52223205566406, 103.54358673095703, 94.51954650878906, 72.3996810913086, 154.10768127441406, 77.8081283569336, 331.55389404296875, 65.15716552734375, 299.51129150390625, 14.877571105957031, 139.9371337890625, 54.557743072509766, 62.05116653442383, 11.47998046875, 80.88436126708984, 59.23856735229492, 339.4112243652344, 10.88602352142334, 72.44685363769531, 108.35030364990234, 72.33270263671875, 60.58228302001953, 88.6363296508789, 72.11585235595703, 81.46212768554688, 178.194091796875, 89.84587860107422, 86.3440933227539, 94.31182098388672, 119.1676025390625, 68.55699920654297, 90.58576965332031, 64.05364990234375, 281.7703552246094, 125.21050262451172, 62.515907287597656, 6.454470157623291, 195.3822021484375, 79.83858489990234, 83.45240783691406, 76.71018981933594, 389.5791015625, 72.66000366210938, 129.28221130371094, 512.9075317382812, 153.90965270996094, 67.89747619628906, 79.28311920166016, 49.56065368652344, 83.87783813476562, 99.24405670166016, 233.8200225830078, 271.23736572265625, 62.70868682861328, 45.7745361328125, 44.08491516113281, 45.093536376953125, 119.03602600097656, 86.1363754272461, 134.13424682617188, 8.734367370605469, 63.46535110473633, 56.75837707519531, 359.3381652832031, 89.79326629638672, 183.5789337158203, 122.26351928710938]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011607</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:01:51</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>84.13482557341565</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>60.64578292850809</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>108.3456201214224</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>4612</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>[0.8887089685177488, 1.712225472645772, 1.9042459995872083, 0.5580048086616287, 1.3030470707213684, 1.0023846375984764, 0.3884482898432192, 0.9866477581663341, 0.4440388557033221, 0.37992265713830287, 1.1334478273243294, 1.424265855721227, 0.8671015725920974, 0.6280641742032147, 0.8844584399508091, 0.5647851117569135, 0.9947568788689259, 0.4535687915144612, 0.6537179135451869, 0.2974611546271942, 0.5104095746621956, 1.2527079470141929, 2.241966398700211, 0.6919658689608159, 1.7732839644020344, 1.2177886065103076, 0.6480204131731068, 1.8999008087420743, 0.8019236454871834, 1.2370839172917278, 0.976062477949543, 0.7790388677379393, 1.7527867703507165, 0.9401750420662629, 1.0212125709120414, 0.5326104257849563, 1.686466419016164, 0.5959832707734757, 0.6063592819819427, 1.0889144473965748, 1.659179408443752, 1.0328375211239469, 1.2243564168492815, 1.5788691700675368, 1.8406294854852097, 2.9761563556351507, 1.5977811101615451, 1.9616978928747988, 2.009924307799277, 4.513250718067399, 1.3183582615606169, 1.7385873738958093, 1.0424822582703273, 1.7655242455000053, 1.2923306556544272, 1.6762808211827263, 3.4705805661686906, 0.9207428474221231, 1.2834475343100509, 1.6511833885201457, 1.7564492547833515, 2.6422873326683187, 1.1399558401465946, 2.8536824778252026, 2.086821584232492, 2.211705735235304, 2.1819748520748954, 1.684602957288307, 2.741883688828091, 2.6447404863542365, 2.2461251491161836, 2.018782798517402, 2.464079196103907, 1.5863166583675314, 1.7543022323938335, 1.1493925099870703, 1.4128292788619987, 2.791818548627871, 1.748568275861171, 3.0621791329624823, 1.984169283562311, 1.7049750054137343, 1.9747567380111386, 4.64609085911598, 2.479141207928678, 2.2396834420702785, 2.6147077918806563, 2.006606940505993, 2.6710700125289897, 1.288051805099176, 2.196091486729384, 2.6221943078922494, 1.9668834518605895, 2.297359609460382, 4.209966352000175, 3.831072962496946, 2.0732035395184716, 3.0125213730030826, 2.761156377553286, 3.8671841415067973, 1.8139330450937265, 1.3241686285375842, 3.1055675147895143, 1.6460172059466087, 1.976345325623754, 3.331710347466923, 2.8782637852911366, 3.2011593550470185, 1.4153121980355927, 2.6764657123468565, 1.6542263624215305, 3.5048874646273482, 2.6762041813669373, 3.4201427046356283, 2.7127374573339442, 3.0385358298017793, 5.098792800522228, 5.769496677850722, 1.8950236065720243, 5.073062572169857, 4.529860219018123, 5.32433313805565, 2.407131803203464, 3.9094224845087053, 2.414361198286116, 3.7667547066266556, 2.495580729024547, 3.406464012699505, 8.07094870618879, 3.8593066483584084, 3.3696249176017843, 5.26314294954754, 1.7974919809088117, 14.648055204521011, 7.115543055483097, 3.233849368335289, 2.1705459166080554, 2.766630003527251, 3.7058084356451295, 5.021236028047337, 2.5154758540630895, 0.7908661398870743, 4.734866593874382, 3.0353056885893634, 3.6805299644135117, 1.757400939703125, 1.92404952198473, 3.3205327285140616, 5.372873532430028, 4.546538733517711, 2.932093739016275, 5.057811830843822, 2.340382245879197, 3.5767926706161637, 4.308625314154804, 1.9528365395770328, 8.392399263082751, 5.865270121926468, 16.67587052677299, 13.533800313564702, 7.249479595675118, 16.99824205391536, 2.6160234477800945, 12.223765047968246, 1.7241060353553639, 9.811273548955063, 12.230758543396085, 4.616929994851838, 4.982029561009453, 3.9800804067193885, 9.149545011122196, 6.697570850624993, 8.489616158298695, 17.876309395303927, 10.926549882057957, 3.6888232953535103, 6.519603514457053, 5.825878182087193, 4.035547199902397, 9.29331342842939, 5.66528833761525, 3.593648109782876, 10.674106410177213, 6.340209856687467, 3.225525251174467, 4.963418339265314, 6.187013593855035, 8.115825708949245, 12.385611561164696, 3.944215837698885, 26.24343093634278, 14.822857620054487, 0.8713025645354406, 7.7566801527352665, 18.788187067965602, 5.509348195787599, 8.09123328372199, 7.791965255245548, 21.345173079149504, 19.57456327797773, 1.4147732751828266, 11.859280730034092, 10.696448205460154, 9.973068135100496, 17.434200326672663, 4.941535625193868, 13.862308161337282, 16.812289233463197, 25.1350682136862, 14.521538381251718, 10.05889362137205, 7.760846309697314, 10.043600692992127, 10.053006247368364, 10.609515662357122, 13.991737601603823, 17.241809561833715, 17.500524745528836, 22.36463148804343, 16.822943124994804, 28.30373807163844, 23.568378164919565, 19.259216054284316, 22.9118291349566, 20.722336738724145, 14.122752555078856, 5.465075520811643, 31.654096144667374, 10.516765528387472, 25.315026549121164, 10.681593227291588, 8.816212737670146, 34.091440587021864, 14.25051346784954, 13.22204221029307, 3.6698724200644413, 13.263561943211561, 20.176248053170795, 17.7902469111846, 25.365094910155523, 22.34142789861294, 12.34155603209597, 10.642691364349535, 8.973843981836154, 25.519582212490963, 10.576123054666072, 3.0430116303239814, 26.081110210714726, 1.972248335001023, 31.53095617660606, 17.971974072840588, 35.168995202341286, 28.671045280410766, 14.08945593690217, 23.19452126999494, 7.014084521115692, 16.828288493477434, 34.14224449784001, 18.866301485769764, 13.315590487195681, 1.7292562840459131, 29.43429267930902, 9.59025556957668, 25.659846630101367, 28.384397775946297, 10.868228774543873, 23.07911859203101, 8.857609907977238, 29.146578024560114, 31.404567465699863, 18.379645630796606, 13.0805666966965, 25.132528348104803, 23.451250444272045, 12.334445868600817, 43.88858545619872, 17.477222564996573, 48.327797876600606, 24.098105691516608, 15.801477009626533, 32.512829420782154, 18.155442475012126, 22.163519142799128, 19.439790668540997, 24.721250534870435, 35.354894252944256, 19.855370396081604, 29.904585060630065, 15.978140706864975, 22.821920076839074, 29.144737312205223, 15.655365191071946, 26.69835131387461, 23.237386451805364, 10.797364433538409, 31.887550164569586, 6.479742281647486, 26.394770603869596, 33.215433162079506, 17.974707642450806, 36.775758264759325, 38.212622167324064, 46.531836932963174, 41.997508928308505, 64.1787422169227, 38.48949683935999, 34.59951421397093, 23.6787940186647, 2.6250911732150706, 40.788067362763705, 26.628819163451826, 84.8746081307158, 26.919933450615037, 67.31001009326492, 18.809104464536503, 29.056431307561553, 22.45896503566018, 20.877182849540617, 18.520811441493297, 24.534228960133923, 29.241809722468847, 24.447648608342657, 25.885948353290875, 36.35596442892324, 44.10299432013161, 3.2560059643531623, 31.99709114497215, 34.826912371294675, 44.14403354226578, 50.97171055755981, 26.40914795509347, 32.406034047450305, 32.84754520117083, 3.77399782946677, 22.362406668186903, 3.831390320553308, 86.79262987291071, 19.761760130917963, 36.49311046651712, 46.21594511192208, 13.27830653015261, 59.34936200099434, 62.80637877300573, 25.247066281887207, 56.16360699252498, 49.94241897784501, 9.678340571801039, 34.60880675506916, 25.451289696031303, 48.18480777884153, 49.30420958084721, 51.40355011804683, 59.34441793363768, 29.96606985592455, 41.52002465872067, 67.40207758129735, 46.69553899414056, 60.880367862631594, 21.98775846292552, 29.38552631108299, 32.05678705029762, 46.20930932236945, 34.466326739032176, 79.45205519084814, 64.08376725214228, 54.99177489137162, 41.431227840518794, 24.253102732826864, 22.3721588340406, 43.7983901986984, 39.027885237975475, 7.144388705232764, 33.896598302269105, 33.55154974474901, 73.85851498908207, 49.06713036397746, 57.87849777751066, 17.84322974369946, 59.4411741702046, 43.197401576051085, 7.25357768538847, 7.252722671387152, 81.99587094494015, 43.57712449781483, 43.66172792920521, 43.831822055008956, 51.70266386918994, 51.72990896363609, 34.31533367994624, 7.990126960955725, 43.35187288944054, 38.66880315772372, 19.826215449730757, 38.221843118474666, 51.96729985253195, 43.12530459363515, 30.552942038673713, 53.836945855225345, 85.1171336446072, 20.270588178212222, 34.06805929310595, 59.52589763527516, 28.746067024094124, 66.61812168324603, 43.34396416851378, 40.47257497122024, 24.793217955608387, 39.55440233948394, 39.73163209719389, 68.52762889451922, 35.732527059532735, 35.709752952757405, 43.99304935879458, 43.24838200314481, 45.244104148743546, 40.869905762137186, 62.42548808372114, 51.908258643508, 44.118335887552675, 43.77051436679684, 62.08146222966476, 47.32104861172965, 37.70854208831732, 53.19307599540974, 30.601011277211164, 45.90669125580153, 39.5091864857827, 83.10415481066187, 100.52677044698375, 26.49555304786025, 50.62554001409608, 40.45885621265647, 33.511602189495406, 46.06775609467562, 72.0827497223349, 104.6406357276736, 65.11511272222324, 4.584141501884143, 53.05271078715996, 45.30202389106285, 54.20488873591991, 38.00654918542655, 38.827658885257044, 68.64073762735593, 45.755447693617924, 102.70168555903209, 7.021552666457668, 48.90486566279585, 77.22841907115017, 46.332513007026094, 44.6237339917996, 52.52238312077793, 39.014795532014496, 33.18266468454177, 51.842133103181446, 30.830098431757335, 51.508436679708176, 58.71940995278818, 45.50497288178434, 48.70690328119047, 76.67991161464923, 37.70924982688256, 43.824655801243324, 38.369615836397415, 43.97159744365416, 34.31852639504848, 32.17813310330609, 48.08222714016049, 82.95112841173002, 43.60177380701165, 41.58124870978047, 112.41067752740251, 22.83352021251616, 33.24384916072669, 40.807474312444974, 59.838656902220364, 69.53467461414982, 50.567873969015, 38.104813381416506, 27.572460609329895, 33.3249603637756, 32.86212310836141, 47.69871456831165, 138.83386995067832, 55.42624846627559, 52.072684254604745, 79.02832731559985, 7.305148871805976, 36.6976059057047, 32.1210599324309, 83.29737993042487, 38.082693124286784, 34.69700406108914, 88.8756123455617, 51.081545257156776, 57.66737511300893, 76.114399117976, 34.9460148815557, 27.83996733172616, 56.46597773090904, 84.31645909827175, 26.7514107106657, 58.330108508725075, 137.00098908612847, 4.760729805521677, 95.26462889899054, 62.01527092989234, 42.27144317760841, 83.70177503320501, 39.27335878413663, 50.72804664387351, 87.59802160424327, 102.58760690413891, 64.8040203219586, 45.638859658869364, 35.68712510553472, 46.1526326413628, 42.7140779305245, 42.656624174929355, 38.719569009883344, 118.34093812283635, 57.98357441981647, 32.304672925905955, 38.74955350161331, 111.78973192676845, 84.38699281542188, 72.43140071353082, 62.57845630239641, 56.29419263821576, 45.86385426016898, 62.069527187855115, 37.90403723066706, 51.55721807646017, 66.6445945515142, 80.98246462361944, 34.99203832791488, 37.72183574584413, 58.98824723833712, 39.90212115600404, 73.34927304520467, 38.70575591904467, 3.548760824217505, 38.813420999667656, 20.858476057434434, 71.03430944525982, 50.4348882246382, 43.64554894452859, 67.39291987673285, 66.45960610252898, 72.49759997309124, 25.943918434239926, 42.58021525752917, 38.3014148100721, 53.79888601113553, 99.51832262440742, 56.52149143305707, 66.19137728687089, 82.1346822658412, 47.50721380717321, 92.25944355932741, 33.85159273755295, 56.686451606103454, 42.196835300566214, 68.41923073482316, 132.94493649923666, 50.702410904972155, 44.062134300239634, 47.37824899741116, 57.42307281194324, 36.821571990756546, 88.45518091840697, 46.46227007777652, 132.7755994065055, 28.621231349858267, 238.34898566930232, 43.92727143310851, 27.997845380754555, 57.459025843998425, 50.92371174608637, 65.99033705614121, 70.44189722910421, 88.63432408556535, 9.616616726460933, 87.93543198317467, 37.76044645666855, 101.44987024478195, 58.29353781196732, 64.59723576645654, 60.28179391955307, 32.99765433692537, 38.047276478135814, 43.52707971530303, 72.45267875443695, 31.6156011981017, 53.34720492444149, 90.18482133477764, 34.23598837513797, 51.19348364688994, 70.02638533384172, 50.585709680437084, 131.79780501390437, 90.24052041241771, 136.91333462516428, 56.721047784014644, 54.2303030705596, 41.74410105424103, 74.23639133615926, 83.65783435400256, 50.165106770999444, 40.123248184181065, 50.90509225513024, 46.3964868425827, 46.569039449481544, 77.15326968296463, 196.7867042236132, 139.46461732201143, 81.13282098052419, 39.06956979240709, 103.36867415574524, 47.50392338882948, 69.84150131035409, 101.05371704440135, 57.888791461046424, 47.20335558783233, 96.64672584861853, 44.976887759056794, 58.057174612215796, 59.9863638898859, 45.13140836621309, 12.622564007942872, 46.34090508733095, 47.92350030266242, 10.558786128720417, 72.97163131874161, 56.676413448998346, 217.28992887521588, 96.23243901539297, 38.582694601444445, 124.84552526159194, 56.207396932944945, 52.69294660460942, 99.95662710219476, 60.336769321953135, 52.53157176364334, 155.298078333903, 90.85006492828505, 36.248917543219235, 50.61933021553778, 47.51198612104027, 48.4720920692254, 53.58252212123689, 48.621029702441305, 45.131387698992455, 45.174224610969205, 77.1900637611584, 79.46377108427771, 58.20720174526986, 50.91569190798426, 169.74039846231219, 51.706052805401846, 52.22271363714883, 45.60870334847906, 47.98717139202123, 14.409423575230251, 59.04951032212936, 50.324107258063364, 67.57296041530604, 69.62781177981084, 82.75352376290782, 112.4461275646527, 55.80498664368203, 51.508589393066565, 66.24637620614037, 56.89231767882717, 53.41824865223853, 176.5712367043482, 57.804071957114296, 78.81055172002513, 144.3324298861058, 47.53009392923205, 36.38396760155702, 46.73943634291367, 63.26813158020861, 109.54154457580425, 87.65870057043986, 70.06230373867318, 74.7200371162448, 70.5597138221116, 120.80613604549868, 68.6226157991827, 39.26658930141194, 81.49199887125957, 66.74988470122157, 125.1239296627308, 107.79457244390291, 39.36686933119677, 43.892032847721865, 99.02730837192178, 54.709120696451045, 65.54539963850299, 45.715776862839554, 80.79309073492126, 66.9531144576852, 56.43134344851399, 108.29804076655668, 51.194358875179866, 109.96415895453192, 13.788940212142865, 64.7634976104482, 44.46079433587535, 45.2371992462639, 52.0702043350904, 90.68862388960179, 39.31555876881965, 141.49460890001214, 93.00733188697336, 52.61237630088471, 52.34082626203474, 61.703368595274554, 117.1538859741898, 119.73631518960947, 167.72041893558153, 39.4849022098719, 65.5534406854431, 83.17901696358636, 61.10278837442334, 104.53233583787066, 70.39195264649366, 45.994418093495035, 97.05544995099409, 48.59227362349289, 13.162225051305796, 82.29821728019661, 60.92920802317213, 88.52460343295883, 97.87295251341482, 60.057592600650594, 62.17054886992021, 96.22657586572929, 40.96645142017313, 80.69541804729167, 55.81378023279333, 20.996133318272992, 60.92776002940662, 39.09215931517099, 56.05541473252577, 48.806580238988275, 51.53395662256053, 82.80630572226555, 71.64694422309297, 46.893142546900656, 10.375914950563311, 43.0976713960905, 60.236048024802514, 67.34468898831297, 72.00596037174179, 43.53383800155532, 53.065361228211394, 171.11199147081751, 45.73809809461049, 46.36543054333735, 59.4351341241743, 97.27436875156337, 57.19354974746135, 55.45822965673569, 67.98066275679098, 153.23937462630292, 62.64784773584174, 74.5812344529155, 67.95679005129729, 61.557574090481666, 39.47192004958602, 178.66434476616965, 68.03041208949703, 43.66227385789698, 69.51183219025661, 42.21775337136035, 101.90221335028467, 48.19443103105172, 48.43230674887109, 46.72588391248215, 11.543257788073417, 46.80635469353427, 32.70347930294541, 49.56048154965827, 40.12351460398011, 14.224163444318316, 59.753779801695146, 58.027849490468604, 56.55772794306697, 37.6965528047249, 58.12231816740636, 99.38738794994063, 78.28911638429953, 127.80614156063254, 80.82035169587873, 86.48069969393359, 23.042984488046006, 120.69888393513253, 82.80955827570907, 35.313456293804094, 49.726238097174885, 52.73348110079853, 66.00690131919691, 9.912285734138024, 48.52406317893619, 40.7610704289889, 116.82661597026535, 109.45529552415228, 38.536615509094, 67.74934790766338, 49.06851413438267, 42.61658347592212, 68.80116966713945, 53.402048544275154, 52.534044381960186, 62.834813392594015, 10.36424878166743, 62.89788872184975, 92.41986889603099, 72.0546886974777, 53.19785888257127, 67.43082932002808, 5.328350060833591, 43.6925415682291, 151.46213230821877, 114.664129312131, 14.072673834586341, 76.2318474711704, 74.08193590262938, 40.300406263052444, 58.8177152911809, 51.20767569634738, 53.400012161610235, 132.85281884015623, 56.023382861443444, 45.11353055848411, 9.984263362000679, 171.70143807833193, 71.50433268987172, 71.35798713204206, 48.63617614366252, 53.49882713636286, 48.13267013956243, 54.72268199017617, 54.314430723791226, 97.26814222684386, 167.3471088616285, 53.94321967125368, 46.67158116213399, 8.299079099626391, 50.45372919603592, 54.68229011164935, 82.03386561324506, 158.13573387799013, 134.36038174374121, 94.93480818009992, 61.5491571481375, 79.34991066503954, 53.357346716554645, 139.00933909397205, 63.51382466203502, 131.35379724015488, 138.26080663001673, 53.86434412429845, 158.76581931216506, 75.99808846542427, 126.81034088227925, 123.22950224363028, 68.76293288143167, 262.0813829758751, 44.569298888436684, 68.8788383462911, 88.47730461274708, 62.20448702003681, 71.22530328779993, 72.77304396373319, 5.510704399228976, 81.42634205957435, 44.30797588972194, 38.66695452163209, 5.649579502143722, 138.83039756608497, 73.98703643548511, 95.17715371420461, 70.31137036805947, 102.18331540216818, 74.43960169452639, 100.26412737157781, 101.0933844974834, 83.91530426062906, 60.62747170125295, 65.89514384593755, 81.25532640806502, 109.16365531124164, 46.072326509901046, 36.62669292335144, 49.72863050914623, 51.150106420203706, 115.87836352150988, 77.15041733203967, 77.45630534434723, 56.61088371358333, 119.63001507384696, 69.02479597217791, 100.53883841125631, 71.0540299540751, 70.33259478013848, 40.87450807914039, 35.588842436052985, 184.1579616234172, 43.36044007641704, 57.963345717839196, 81.60730416228407, 193.62021394191427, 86.89574912690085, 47.39634675586547, 59.222828170874465, 81.9628834258791, 60.33320385207296, 65.63396908675364, 10.633910857774378, 66.95867629238046, 73.36745770183512, 40.7353895721239, 55.34558828174014, 70.52439552975629, 51.38709769725738, 60.57907510920989, 42.830012777067644, 76.32157537402058, 70.81824199750912, 54.83933540556516, 106.13976330275679, 66.23549403664354, 43.01203279462836, 64.38129281557498, 57.22562318158401, 86.76678567288438, 84.2654079518967, 43.941296589668866, 77.79283861473925, 88.00028552048494, 184.6775574020316, 68.10408208304626, 94.61491967856058, 74.31546932540905, 121.72254214040976, 114.47662023017982, 78.07576817823397, 179.49211613125217, 53.80702330434315, 88.24527646296984, 75.53403561011358, 67.25543098362215, 8.943183435716033, 50.727659612094016, 133.37650662326683, 54.904683723648766, 48.63676906497277, 88.02492499118927, 89.30602118248498, 8.392563016387756, 47.69650538399387, 86.37034720888596, 63.449092515184816, 57.925656280866306, 70.45095643625072, 64.15512479856675, 40.559924014610225, 44.983971223917536, 74.59413644558038, 61.5185155997663, 54.47162624169898, 43.89756038877283, 75.04349234653571, 54.01306655015833, 105.32111240349047, 50.10322211148362, 55.2024970541723, 58.46745934838089, 63.43069839993366, 71.48983370849254, 89.19637706812352, 60.93666357178454, 105.92233646057835, 6.953007975892873, 97.804093511876, 47.313098075300516, 42.56397667887682, 53.5121055167081, 131.4745271114379, 65.09212863308369, 11.61121745179167, 58.77297628583139, 62.33013878976661, 43.03829667516636, 36.30334922503967, 63.640182450352995, 71.26828953503606, 64.11345393263223, 80.88082949679357, 51.71259907098031, 83.44040929651152, 52.12102819063755, 147.4380356509542, 52.62679984600366, 152.00629754350496, 164.62740422577582, 53.22941561044456, 59.820901825602405, 108.99784818042917, 36.10411595758472, 71.40104028023781, 66.43352665036211, 132.31863446391125, 140.20851299844736, 52.78729633650634, 7.533573630046856, 62.13982913323741, 73.276640452532, 40.97695748096037, 68.56584615435793, 98.51705222454099, 114.13597942697493, 9.760196216844427, 55.352729947074714, 57.783085200677185, 67.36657238825707, 87.65280868845755, 9.05859469249432, 65.07111290475446, 72.3418251837813, 78.47234403691233, 61.308110711964986, 65.42128064651887, 64.85369874305708, 153.7640940299229, 107.65640685861584, 5.368158544217574, 54.800971824946096, 86.90814083049875, 35.73759951847718, 37.636638835623394, 74.76400555994893, 104.25490878181348, 40.92500894965638, 190.5192844903526, 67.08328345144282, 6.0677920207109, 65.61819948088045, 141.438532452098, 116.58356668568115, 70.81982640942675, 86.89123178503012, 36.26697880131296, 52.264785416500885, 174.4240402059672, 10.483025374169287, 54.59455328066912, 54.785474976323236, 75.40605700795636, 49.11608202028295, 4.4106084030228185, 50.58341289012401, 65.39968536587459, 81.10904679615487, 81.0821002903309, 86.56653802742865, 4.115883296636163, 75.91545209315944, 241.74453972989303, 41.13247293001133, 56.02112728673534, 48.05384495583302, 69.65973707895616, 48.02505508152368, 119.1325305231535, 102.4778155740211, 103.05205365537923, 64.88380029624386, 50.80510461531294, 42.88355021709965, 61.470977020084725, 122.74315788723298, 54.86770199104113, 50.84114455552768, 33.96062064986782, 48.395368245963006, 4.283582547692108, 166.4225718510937, 73.34933878623288, 40.858000969177986, 81.77484636802814, 60.56946558147946, 7.176178398021136, 84.94271970619624, 78.88789162229983, 4.706427186462356, 89.09813093531636, 72.51867556115465, 56.23709085508429, 55.26667886612936, 38.78554344865483, 66.809977114151, 111.62511375350952, 35.799805777453855, 120.48865689560043, 47.549655475035436, 7.494786448902967, 93.00017119835036, 61.27855987891383, 58.1246395689163, 67.69606039678935, 43.329321998054404, 70.19611387704516, 45.69973562492667, 236.3928896795644, 46.08711748766359, 55.4323637126079, 125.70327043915974, 178.96819849353216, 68.6634039968901, 101.60510285270382, 10.695068794323738, 82.74244989654188, 75.32828733364612, 52.52196885359215, 119.8529336891564, 95.10703037276218, 58.56473161268, 49.72343568042289, 84.99392003097826, 122.60844496241755, 55.10205904620841, 392.8598123111764, 49.90721137854303, 8.45631218306583, 49.851956005588015, 49.69136287485437, 108.85248535570922, 77.89607788812673, 53.81688509707613, 93.00619600890205, 73.85142206423176, 62.36990927179324, 41.362241678258336, 76.48290540306189, 53.56318010311284, 37.772221181735084, 58.97029067275863, 74.96174777722527, 115.48103879168455, 42.97068338974291, 134.37494819283916, 78.61156227107604, 95.99754353891441, 38.812867121355815, 72.34266503897067, 86.51147601507634, 51.23921060324104, 76.76800011381032, 49.05932909643334, 101.8627082714484, 56.920008314547566, 73.46180700256683, 104.20677174387764, 98.5138916654795, 49.40964826440717, 73.50914591418024, 200.58597642468072, 89.00306387191394, 76.52050895391046, 57.79115629664022, 55.68572045534194, 239.67652641062242, 46.507498184353025, 110.50218536032153, 96.15059564077929, 49.74498026580406, 62.29283353570816, 54.22346549476095, 55.84473400588336, 47.06986093339287, 123.3583410709414, 91.41084768152936, 4.9905948608100195, 54.01288635223917, 46.825858887229096, 75.52472328300117, 57.213115281894076, 98.69212451666012, 60.681723694399125, 86.62149235319274, 64.6895691788856, 42.223570755873524, 113.96572001387639, 36.818678024887795, 50.66767129937317, 61.784144102650444, 91.64447771956696, 166.08167285494753, 59.95354675385812, 88.8736357547602, 45.63069700411885, 156.68733878009377, 42.09806989960326, 86.43411726888401, 51.60877989268699, 37.72102448242862, 47.39958394827547, 105.93187089169199, 57.485820693021466, 139.38669687211183, 64.36600964348256, 139.85402064840582, 53.73374705794362, 43.979307360399446, 67.9445318793456, 75.81663415048962, 6.477940237090464, 136.61112935246607, 144.4484744943298, 44.11528542797369, 50.76733022833727, 88.69828613346883, 64.57293230346792, 5.294024558169323, 79.0273351975366, 210.00710098655424, 52.0992495921553, 45.83741663817397, 62.54371403061016, 82.01986973469131, 100.22694200948415, 43.88714749758585, 79.09818191633103, 87.94660812782521, 49.56248742742737, 79.41440096810379, 82.61976879790915, 55.02007077968821, 49.21342269082203, 69.7458238629503, 54.21947341126793, 186.9606190287596, 46.235569501169756, 76.3801480075906, 80.597290530286, 82.17225781041162, 66.07758216275562, 37.29655308461, 54.82468852835984, 51.618057513108226, 11.18240702700659, 80.84084981107561, 39.02443229769619, 59.37754916477753, 107.64211519633847, 49.817393787901956, 58.49460954368823, 67.88238714965146, 46.93258947279999, 97.14722886809837, 69.79832839475674, 56.405659534974795, 75.87466768008792, 55.90528449972499, 52.218523807589754, 62.557147812911886, 92.08849425358666, 7.480500680402535, 64.13439853857989, 87.95614080467568, 135.41861192237926, 82.48942273243793, 60.7488418889298, 62.01624716392449, 60.7658820155287, 47.6324202642397, 107.08001165798309, 75.34958733422519, 68.03685168454003, 52.10008299693521, 162.34988665619764, 222.89095731093863, 56.60369389134535, 55.778913660401, 54.023990156109456, 74.90638360302736, 198.30246470643178, 77.09100439569288, 96.81928805813615, 63.135943563870754, 8.899977888795032, 66.98440499741392, 81.0595935132939, 137.50428415512758, 42.388067024804116, 97.3979887571189, 48.872530326034166, 99.05946267817382, 135.6498037862238, 63.02105850074694, 145.83176305047596, 86.4465938782821, 204.4434615837188, 91.51258394758935, 87.4091594432661, 66.69367319236247, 35.02539005157709, 10.91375722968961, 160.13036969391112, 77.7021546659581, 56.22155142860149, 232.21164788652624, 50.16708944171709, 70.62119999632891, 56.76645709155568, 66.49026848628776, 66.8941776788849, 89.62860128457768, 77.91304697554902, 253.76147293359168, 129.9956597864669, 19.071247139437794, 90.80321548372785, 32.33667443357453, 120.69152212647586, 53.4010641505496, 102.69861571250046, 196.81843020725364, 53.17519630973277, 114.26766939191701, 119.40042658165737, 83.55664643279705, 67.85409588077482, 10.340519608030723, 60.41640296812306, 59.238416119880405, 97.9969309348846, 55.70313883126553, 61.67037887938985, 38.50984034958462, 109.55720587655362, 101.09000774316829, 91.63400614026165, 177.84999555614266, 50.57542908267233, 11.831877405819446, 80.79003172687693, 58.60283783020579, 72.95530932401816, 51.76360928060449, 52.334901044362155, 80.43639041581106, 52.098321568007904, 64.42563932497376, 151.76227523262486, 55.43697708248133, 61.20308492260095, 28.087618021154164, 21.727382340657982, 109.29169705890598, 52.42542300764047, 52.42510549397237, 38.678737086369374, 81.95736422668202, 249.31020491837182, 65.95799488083243, 170.76991100730493, 103.61934082185027, 67.70290844803112, 69.85737088537027, 82.9287450831601, 57.056278683966234, 93.75083000459308, 54.441768890910666, 141.916911337182, 68.72101551799122, 49.56439774027633, 64.99907273010507, 55.870912237348776, 98.75665530823025, 58.24834130493659, 12.525481182558284, 54.382794684137025, 90.07727869332344, 67.51165701606789, 104.03724517746168, 53.6451008900408, 63.537652922167545, 57.754180124683764, 103.52613954623338, 103.11569116112061, 57.604022386341775, 68.85077785094597, 118.96241524629053, 80.7264573534448, 83.67963672053385, 114.82011292214096, 110.56489385224423, 129.20293640201845, 14.353895584650068, 59.92859910002737, 127.96509348039585, 61.47891620083969, 114.55591306337558, 70.57868920573108, 104.61382631501748, 56.96932428347318, 54.960457035232416, 75.63306228029089, 217.17554670886412, 46.584471141377406, 81.11189797418572, 46.93544505836479, 183.99598287638239, 93.31697063094839, 69.82438181292362, 110.3394998275943, 130.34472999079387, 89.83638032828232, 55.972557721530016, 54.94624821769081, 181.20926582738392, 57.53865081652353, 45.88766439968928, 12.310142476769434, 64.92307286823774, 26.66424081411822, 58.03237782436778, 59.144336395060385, 140.8354334616216, 48.16387781112998, 76.75304006336793, 75.0032660293663, 111.81558185356124, 66.2296272337867, 141.31435418960092, 97.76991691960461, 68.55297509340915, 65.10095486372535, 111.99517222560065, 132.39063722676522, 59.13045999025403, 56.91289474954233, 51.25684317706616, 51.48579198531454, 204.54173029087488, 68.10715821515385, 80.0553328502837, 63.447703304830355, 173.81402067622133, 57.88854551864448, 63.29411463494907, 92.98938939244138, 16.845091137415316, 95.79410355251095, 44.802460773080114, 72.84010678647958, 79.43898785100838, 57.043863097731766, 63.80508361509534, 66.17968901864067, 47.1426286073357, 41.72772074430934, 187.8039778033721, 57.11639783411555, 28.071450928703246, 9.577961447516321, 190.46653970717313, 59.47659493354791, 115.16059080376651, 48.33812734280414, 58.39381863438972, 8.781149142380295, 247.127287818012, 42.57354370077624, 61.478405000257936, 64.98301418987255, 142.6605772544876, 51.63350700444049, 74.21274938383114, 8.793315937414148, 57.68475834552679, 112.74756838254444, 93.08092914598153, 10.596829754650999, 45.000099232365955, 61.30747814639495, 53.27989179087411, 39.149643371579096, 51.10450349960194, 40.15894831444544, 50.635974054439856, 40.73817145838093, 147.58324328788308, 119.48026818345514, 136.29927675183208, 97.00877586939214, 85.49214830775908, 87.68203874523785, 105.8318654620911, 51.43254262034667, 257.5432999476919, 140.53370317050963, 93.63839998632307, 122.80694470300251, 85.30066619071441, 57.92260664984667, 69.80639742277818, 48.21162149032162, 109.35500218375434, 11.786904945284375, 70.28277356469485, 54.465730538408216, 79.21524679515987, 6.459390096022294, 65.95233518986755, 80.92218645001081, 56.50837124278097, 91.48718922355627, 70.58135639055706, 265.7219075176302, 128.57424138089084, 91.56454992894108, 60.253949811605736, 5.328268912065525, 108.94086763690201, 54.817241870780556, 58.18743170813878, 43.64732557682871, 135.83122319005872, 85.38268183040837, 67.15727415536495, 49.492678379476516, 200.84063048037626, 82.71131089203203, 140.24501128020944, 214.21171662785196, 151.7636486374656, 61.31995395113028, 40.81446681004847, 61.00512750921866, 97.29858099108623, 7.7435392870671915, 62.91309595605582, 56.61380494919728, 95.37035224423832, 44.07966322046615, 39.79559762000984, 51.55595591254373, 115.70179328756736, 26.270463290081466, 70.02254856504378, 48.363176834606456, 83.21729693573424, 79.12184666966827, 58.72102833152302, 59.619608665753624, 91.51560446957406, 58.15010338187861, 123.40307915753307, 80.17289695119942, 84.5496006035815, 68.9496964596954, 58.088622678252854, 174.05225395028026, 128.94692535021923, 47.060913212550076, 69.59690278565274, 50.04033989392471, 81.72744864461197, 63.11188143929784, 67.90504659268169, 132.5266092183081, 46.88826113539379, 64.05842543495845, 82.26180161659859, 73.4546399520216, 67.25411740623741, 37.5665606760813, 91.71395896355422, 69.4837288943816, 52.270052606396845, 65.2507871415101, 77.12477284814305, 67.33658382056892, 187.0240669773952, 64.10917091964961, 71.69183770666562, 65.71563860090627, 94.57008986639087, 35.93112562720872, 199.70675149039158, 5.1232034739261945, 100.679062841855, 88.93529869499893, 75.07666079164488, 135.2677213677407, 240.38787676505754, 221.19791599259995, 86.94969650636232, 66.67158089739694, 113.75397230260758, 88.25635110051653, 101.13005751206711, 67.56633362747331, 71.51328467609756, 82.6751456200513, 134.77179848600485, 71.58475851803739, 117.07546744625257, 36.843374353762314, 94.89416942827351, 82.04900147129904, 73.5885597741083, 55.004443898751354, 131.2479499018124, 100.44405672345455, 79.14124359394876, 116.024630876287, 56.84052723091203, 45.66989464043534, 120.53526017641673, 45.34686416595384, 62.72425474981112, 107.34489625481999, 85.57064456469264, 67.98352190396908, 92.30873800523575, 57.336392952512234, 78.46849242028665, 102.89433906510135, 115.70744327666557, 113.42405245866257, 155.10243041411428, 129.55399946808464, 61.35140592495943, 47.450500305825024, 46.57118053824667, 78.67739845498774, 9.234262578779258, 15.179172850349776, 41.58918791670225, 7.539500606085145, 128.29851330500605, 120.64737899361272, 48.905201414828625, 36.510962141308, 127.29014474653115, 84.8484674212219, 37.82625641075411, 47.26664399374979, 55.708328767463016, 52.70304798796808, 100.36893819879148, 66.94830510262065, 85.70497739523405, 89.85407183303589, 81.342669316438, 49.06000323424421, 95.05936924325471, 7.253721708859535, 60.46278027203516, 70.47442206015192, 61.78528443938956, 196.40006668118872, 71.81308724972587, 96.85499755150349, 73.17491036993239, 56.3895590443987, 73.0332569545063, 135.62913873646517, 106.95663709387361, 132.4536396103402, 50.3733277138087, 54.393220605856925, 121.99101085766033, 108.2579564580014, 104.35994963792129, 79.07888416868131, 82.01292758819119, 77.2373225252642, 67.8324705117757, 62.46029325789678, 226.04447581169, 62.75024130782986, 100.47532636249923, 180.10058936510572, 63.500945923445, 56.42448816625763, 37.185422640929275, 9.462951920674499, 124.35573852750494, 80.87819031579826, 38.22908847341013, 39.054768118889065, 60.45154529735426,</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>116.6561097002029</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>91.42631236766378</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>[143.48963928222656, 326.1622619628906, 69.28093719482422, 92.43937683105469, 143.802001953125, 118.70943450927734, 185.10617065429688, 40.069801330566406, 82.00274658203125, 114.99384307861328, 86.00995635986328, 36.8582649230957, 65.27339935302734, 103.33013916015625, 10.834807395935059, 130.8031463623047, 89.24749755859375, 291.50189208984375, 100.2730712890625, 325.65728759765625, 176.21511840820312, 130.5067596435547, 90.04840087890625, 44.581268310546875, 164.7112579345703, 47.827125549316406, 82.00736999511719, 51.93645477294922, 59.57971954345703, 83.8161849975586, 82.53952026367188, 70.61274719238281, 52.45607376098633, 178.52223205566406, 103.54358673095703, 94.51954650878906, 72.3996810913086, 154.10768127441406, 77.8081283569336, 331.55389404296875, 65.15716552734375, 299.51129150390625, 14.877571105957031, 139.9371337890625, 54.557743072509766, 62.05116653442383, 11.47998046875, 80.88436126708984, 59.23856735229492, 339.4112243652344, 10.88602352142334, 72.44685363769531, 108.35030364990234, 72.33270263671875, 60.58228302001953, 88.6363296508789, 72.11585235595703, 81.46212768554688, 178.194091796875, 89.84587860107422, 86.3440933227539, 94.31182098388672, 119.1676025390625, 68.55699920654297, 90.58576965332031, 64.05364990234375, 281.7703552246094, 125.21050262451172, 62.515907287597656, 6.454470157623291, 195.3822021484375, 79.83858489990234, 83.45240783691406, 76.71018981933594, 389.5791015625, 72.66000366210938, 129.28221130371094, 512.9075317382812, 153.90965270996094, 67.89747619628906, 79.28311920166016, 49.56065368652344, 83.87783813476562, 99.24405670166016, 233.8200225830078, 271.23736572265625, 62.70868682861328, 45.7745361328125, 44.08491516113281, 45.093536376953125, 119.03602600097656, 86.1363754272461, 134.13424682617188, 8.734367370605469, 63.46535110473633, 56.75837707519531, 359.3381652832031, 89.79326629638672, 183.5789337158203, 122.26351928710938]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01953</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:33:57</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>85.13390095438548</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>65.52634177875433</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>108.4817629179331</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>4606</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>[0.7430754746654005, 0.9516071264234239, 0.47101765608309115, 0.8268527642712138, 0.774658642582967, 0.7091973475797235, 0.6486850622590895, 1.0517904370072042, 1.3881213407761508, 0.9914861481385788, 1.0150029222851085, 0.8159133213273768, 0.4380251397634803, 1.1323555679002562, 0.9876666201128738, 0.8197618406013574, 1.1320753790611495, 0.9275545835340478, 1.0757920421767238, 1.6875814270386005, 0.4012822549530599, 1.942045440990668, 1.7572469822193373, 1.130678642742254, 1.1568536575090367, 0.55682107818823, 1.5192471905759997, 0.7995028815767729, 0.13274337000082717, 0.7189912137933937, 0.920069542002991, 0.5954041878540638, 1.213510767963638, 1.7992984133557715, 1.132722061044552, 0.6978226951381339, 1.761396903580976, 0.8999498538084396, 1.308525763779003, 1.5825888675321764, 1.3209219647727486, 3.359437635992775, 1.973332677254547, 0.6648189971644618, 0.6295640491207432, 0.7282968709112676, 2.035513752495797, 1.5726268700128658, 1.2875687284423016, 0.9015329923997226, 1.2715462992495192, 2.288177788014611, 1.4439567750082924, 1.3478011655958915, 1.1700590454696633, 2.3443685243518306, 1.1804454030965197, 1.5863988231084787, 2.525583694019558, 0.5356183685586686, 1.4642885285990963, 1.073582950474666, 2.393293690257867, 1.6606149370804142, 1.2963902435962738, 1.9226618325049405, 1.8186439820533704, 1.4574387089985503, 1.8525267887052748, 1.8185645505061276, 1.778443568323987, 2.285856235268735, 0.7620794190421781, 1.0133120204741966, 1.0005325117984907, 2.124193744834477, 1.2355787730716394, 1.9603628353886968, 1.0068302205829809, 1.409877608947123, 4.906282073593813, 2.533434521558838, 2.696655557209281, 2.07027695697729, 2.617814297125741, 3.392045298370719, 4.154731151692997, 1.858972319118433, 4.307208513555791, 1.9753449170870685, 4.908254326626589, 5.079194027148657, 0.37721737345305467, 3.554175249085856, 1.6885635714587242, 1.1719757838936102, 0.8669686836082962, 6.541826234981618, 2.471311994835735, 2.739070979485303, 2.56917954667364, 1.3918059116681059, 3.7152478002183607, 2.7836394826254325, 1.9854438691480507, 2.2761848304769443, 2.3366372218294478, 1.9351071837502067, 4.142512895294245, 1.9718516002106308, 2.9995211989872304, 2.718742460512585, 2.1825323856642616, 2.363165221788567, 1.5770065439901948, 2.388515443577054, 0.9561570325618524, 2.3983286751417063, 2.288418514599508, 11.776462642657165, 2.607609844359797, 3.9403009474234634, 3.8469272302289554, 4.275397760793676, 5.106150416812355, 3.889730176415886, 4.986277886827339, 1.8388795303522125, 0.849113674270729, 6.106925181192417, 5.800095842403906, 8.573323744879346, 3.338380893580166, 1.9633322289586352, 7.161297067099867, 2.1326494986384206, 4.311858302211964, 4.18626604508575, 3.2505680012471605, 3.9484830478342317, 5.946337499000536, 7.251619037517923, 5.082167029107762, 7.456005851295896, 5.085228891051909, 3.9882717171545967, 5.370906090424827, 4.976506662414275, 5.640883358068876, 4.202919043352265, 0.9660554776804495, 4.011971950192469, 6.805789246771024, 4.841431457509921, 3.553886221830371, 5.934914232191057, 4.410255316189265, 5.707076478102026, 6.405663910935966, 7.404580536634155, 4.617004272647135, 4.729215470357944, 15.09510029740369, 1.5715071383095798, 4.950416919156829, 11.208878077754285, 17.782260426094965, 23.913729986007123, 5.916262220005946, 11.547655878589511, 7.566208436972218, 0.5140027512495132, 6.603099044145342, 25.114490036157306, 13.126248231181918, 3.32017483610181, 7.301431384626415, 9.62021877443864, 12.912228358350871, 3.7572152727467767, 4.892279059665825, 8.742758917254115, 8.864213408857708, 5.952159016887555, 7.905892884295723, 10.704502025189939, 14.77801920646186, 13.337293824900188, 4.197250824151464, 13.040724683724996, 5.587201686236426, 10.658761561741503, 4.506988551362735, 12.116991357011159, 5.4385078339104265, 11.750137005692412, 9.886094029010417, 2.797890846096096, 13.257255348628203, 15.434632603177889, 31.301649313823084, 21.031348941387478, 19.50241233785641, 18.143360457287876, 9.841678849934233, 18.666625238737787, 11.416964355747144, 34.77726560232245, 17.07719811726002, 4.1273917511378535, 21.60215096536698, 24.36719981123805, 4.3929558231112145, 13.159067004148612, 1.7693479370227112, 7.455134819707652, 16.4803291472972, 8.106148142727829, 13.941957858149426, 7.188088084604996, 15.035160585908837, 12.584750924373493, 15.767887098344453, 10.77044961841191, 15.975463670765658, 13.39159162943851, 10.040449798205596, 18.61799327657394, 7.151557150826483, 26.82500297109701, 8.991873535215847, 15.995684834314972, 14.118181918794743, 12.37071018604221, 11.073554088882434, 21.06297341103957, 13.3212896664807, 27.739892667856754, 17.20758097003332, 4.465374787328531, 22.629864505635673, 31.279585411419628, 17.870678790594543, 51.03281824207483, 30.673100021788645, 18.704751857940412, 25.88008354465698, 10.320723139666722, 23.41626426403821, 23.81812021598304, 20.70189084793962, 20.46819083912074, 43.85231521891965, 5.398734667864117, 24.66806862253457, 34.247089352782346, 31.391940733684333, 20.06291448436824, 14.060611920357621, 32.49161148638269, 17.31653155186244, 22.648069427404184, 25.76662657101343, 13.84530735849341, 12.54501910713889, 24.321347034913824, 36.18059900867895, 25.69139988544801, 36.37735400369422, 19.577242157395226, 20.15431860124181, 4.5294491881998145, 66.12589647354825, 37.05680306477752, 27.88832948713578, 41.86266783093668, 27.666024437740468, 25.01309211933078, 16.486822432747605, 33.95295724309378, 44.07986560190188, 36.280987854750336, 37.167534300636014, 34.827212655296606, 50.48595629140986, 48.58322975802086, 17.525889620794196, 1.3257826437898799, 25.906730481847504, 51.69134576005174, 44.70761398815176, 25.342962781306635, 48.58520853628577, 33.58942367153492, 37.18526033346362, 33.98197674889909, 25.30966729450835, 24.99167169380426, 17.158621724573987, 20.99627562297529, 18.35995060761353, 19.084410974676718, 46.15883368276774, 49.972036532197265, 16.562957008825464, 57.071210301236455, 32.337893647130734, 22.880572942228397, 25.065776940979724, 41.68338021971485, 60.47294698614457, 35.51318315106989, 26.34403676543362, 29.804305403034007, 28.14392627044833, 32.21297465318708, 20.91105562142683, 74.15156575764904, 38.14013936739589, 40.47449216788359, 25.863777341115494, 35.15130491751479, 25.597975338420202, 52.49759802786953, 22.317133413571252, 44.993791449575035, 2.031631280117488, 51.76097119947288, 20.898822985175645, 48.81639595746645, 39.0697140254427, 22.25195053156039, 35.400272362724166, 38.41084515494928, 22.48395547690861, 64.42117245148164, 24.64845906737878, 38.14602075744043, 28.97548571003616, 35.596930526846336, 46.03136237135081, 36.75981405016684, 42.88605442143313, 100.30528192680603, 54.31687388733297, 28.59595982599104, 26.37542498660379, 63.263768474045015, 39.70698661962173, 22.439533772065836, 16.96373093972651, 38.20412636165979, 62.91366019785493, 51.29702436567408, 74.62777606519712, 39.361918247107255, 5.660370789716531, 72.20866800969986, 59.64204602711093, 30.005747785859263, 37.12101121194254, 49.749453768878304, 21.280604299485525, 44.803841969612066, 35.85411382618718, 31.061907422402417, 4.980225790788877, 48.08538323168655, 27.76246878643443, 39.60126112039394, 45.130758795568205, 40.205721918697996, 41.62973425675602, 58.70044120776015, 51.153518252781424, 64.22383565849469, 38.361193051192906, 40.15987312413889, 26.679159367900166, 21.736516322518955, 30.330657336636484, 37.052673551748136, 59.370937741511945, 83.39163590718704, 58.11348179964664, 38.5838605592819, 45.53200794555994, 59.883571221232486, 47.96745915750463, 43.02141310576284, 96.86651395051622, 105.39948775959091, 30.640021917593195, 59.13318903284967, 46.43246221455976, 78.45156021610056, 47.39872595768726, 64.29898928971222, 74.34485047144939, 34.084187308710206, 38.42456747045572, 94.19801784541636, 56.96790594312489, 60.59711430203326, 31.380303670859924, 160.23135613957837, 50.023024926836705, 40.78168320676567, 4.639430656246602, 44.917438601867616, 56.80579098135818, 36.71950726473542, 77.1395440038791, 70.1882880294061, 10.056202532639558, 75.57526102972759, 31.283043760476637, 64.02989531362576, 12.97526885185214, 54.61169889027975, 43.915658020367786, 68.97081479761411, 40.13819392049695, 8.85798396417812, 46.34190873024533, 117.87319082277547, 66.11342011332201, 139.56723885420033, 94.16264570829368, 90.42554913178196, 53.25849149717229, 34.37338050563535, 6.000242561485791, 37.96438247634979, 49.27809139707852, 63.81256102632719, 84.32811089363159, 46.363100536844016, 57.62967509991524, 36.08380900160237, 178.40249304308165, 146.20431979502092, 101.0400173010282, 37.45857956998651, 35.068869429836944, 102.92436629819649, 41.225495727271884, 43.48712766050423, 78.27064685461708, 74.41542935330872, 130.49616419086018, 48.40441549634967, 96.37729506668086, 47.15825911867496, 43.43952385942413, 38.40978832770013, 8.728241638138226, 38.88341643010539, 7.346659478303014, 42.21709489231106, 36.40771537582899, 26.07891585544949, 46.916588883539674, 46.56189864852234, 32.31980926645424, 20.514908365460187, 65.63758763515837, 104.24120036090173, 90.81147314116176, 6.539619901538163, 97.43187839034725, 60.16395767935119, 35.580754249198776, 61.398744629780055, 35.798045534309864, 78.45909111552055, 82.62653501212986, 37.789819986137374, 47.02179620717648, 8.51298212862278, 55.40551329583538, 61.768394624960635, 64.72207043022759, 54.436683747226965, 104.08976746459169, 34.50567682264381, 61.29183650258999, 79.52738562875696, 8.53944387475681, 104.91443587259268, 39.03246485175447, 7.08273651787089, 37.60926736712432, 37.73203105623934, 37.36442954763615, 48.28709520311699, 77.37100633507607, 39.670249243335526, 34.951537901445946, 139.85762065165503, 73.35138389954716, 115.57995344427152, 48.02408558008701, 110.24959535465773, 6.685131656263097, 77.64032928674273, 53.93832305273668, 35.58210842304813, 48.4399488120103, 108.79438835914563, 51.9357655785837, 38.5659332713445, 57.44672621422384, 52.97529625905956, 76.25305277567311, 28.45973523762749, 61.253623240593, 36.13411725289958, 73.10682500186218, 65.14132584516504, 45.57591196337417, 28.5446462010657, 98.78915991651701, 151.31821362026932, 41.654885398828235, 74.19732616329654, 87.21252633066753, 71.2663023943255, 32.47376905905552, 50.638944731156094, 82.33447368728571, 47.439133495693625, 43.187705914347895, 64.45283411032102, 29.183566218615518, 63.44370149123032, 31.33076774711937, 52.76596290701715, 57.2509055555088, 61.997778574995216, 26.080093518935588, 36.60183955870805, 66.42529624387288, 56.41362334220638, 35.49512578438432, 62.492968979845045, 99.51070160876742, 36.47220394404286, 106.17322547946227, 41.922070444091204, 73.0326389016485, 104.84261155006837, 59.88071857592007, 32.54749011883325, 91.041451821892, 44.142463334986694, 33.80605859430692, 53.132120769183125, 50.13853702713732, 32.89047871350658, 65.67734110595835, 35.35273999406683, 97.38709022547985, 194.61469839820447, 46.04507859486678, 86.55114971598596, 48.265065673840624, 77.97897610332696, 40.81512701892442, 50.58186746326103, 54.881910189429604, 41.02490068737602, 44.09991262235779, 81.09103792673116, 52.048284814847804, 41.9181444663499, 9.09786112261639, 53.616287165755665, 81.28813552122112, 158.47989841982002, 81.69104923982627, 94.65299537513033, 40.5656443697015, 61.83932355223557, 50.341247844256785, 6.392951309236307, 145.50622218248816, 34.80537532434381, 63.99672110613553, 86.13466081357625, 68.984715059151, 9.847804298873395, 85.09927874848673, 83.48750802927782, 4.3698114923786635, 102.07152004010925, 50.93255796016027, 78.50792078391709, 7.086147926545102, 55.183418905321034, 40.42453586836624, 77.63435080329599, 59.29679454679922, 112.34472213336208, 65.35048366719259, 46.14602201797251, 76.30049274069356, 56.55215251932044, 50.70467664410138, 39.80945809336516, 71.3538175386989, 67.27693243520363, 82.94703231909432, 38.27088072093486, 83.52665957662909, 82.6656317485853, 128.45575427799758, 39.405325381672675, 33.435236548677764, 47.86650415852333, 4.924568658965381, 54.40897216647606, 71.90165439486339, 37.89329910726344, 70.27659082518964, 44.33151161947488, 51.74178536873088, 35.69982669356389, 92.80061263096113, 41.38016089329654, 58.17975907783789, 68.17877490447853, 42.14639668081742, 87.83135142677928, 65.75250704952074, 136.74141597130102, 67.44427942279698, 52.60384574371393, 91.91520582623173, 134.75567278101127, 7.087908898122953, 56.251637684943645, 54.70301062020871, 33.384118233832446, 5.291154277820578, 51.84744462497908, 47.88734021875598, 68.4045588600017, 45.23867031762343, 47.34444374371623, 99.68684835351353, 41.703443079348745, 6.790113142161861, 42.15256487495367, 134.64411802949377, 58.083851064987854, 50.05134640375782, 40.67611652878609, 43.77946246328429, 61.93119909026521, 69.54518946256096, 61.185333656304, 97.51666955883353, 55.573054759860725, 6.488214141174404, 59.425229499509385, 38.69631329812943, 179.1958278376241, 76.58302669030623, 55.845360928818835, 68.85177085644702, 60.73339176327268, 211.66035782793074, 54.1629213522294, 49.741311940866034, 56.30510219886949, 56.459764020140305, 49.588858623042455, 114.69671836557279, 55.94815495045215, 255.3285677122259, 109.98794548164592, 92.0331188060071, 6.383410422058301, 105.29289931040063, 65.52099801609594, 62.84159992086636, 77.55215714535338, 46.1826032194914, 99.43421580698651, 46.540467605791726, 53.24640199494679, 73.43580929701604, 36.88079713541203, 74.23181188718476, 11.73651070118089, 73.84790243754414, 60.94467580180048, 5.334708343418195, 101.50203214206184, 74.1576860767021, 61.14437064984541, 77.59228743467156, 63.064122284871054, 63.166207168405755, 90.55574878580842, 78.0681914013716, 48.77204666311201, 91.10584502280781, 48.361940309536685, 95.8848739563639, 57.07037104264474, 60.123057182910884, 122.87096335058227, 47.804805147411045, 46.971652107277365, 147.7534848784582, 44.84510749567689, 108.28187569603794, 40.50748896235796, 95.45055547393024, 4.532395941078563, 49.40026086386911, 73.39238789890132, 50.18805535045539, 88.59647693649373, 95.8069915320493, 73.62143469555289, 47.14456785318755, 95.52336643233585, 65.33337752126663, 57.10384348304376, 55.592921324550865, 4.719184752893318, 53.481924042723655, 79.62261892099832, 68.77669793670525, 47.16186580005167, 39.37841367252719, 134.80801619203493, 121.06430724104004, 74.17332378025814, 45.34150603449863, 72.44661126447458, 40.28928338454787, 58.72096535977705, 101.44734463879234, 84.94074845182286, 102.7151992511783, 341.363794456509, 47.32266749677891, 68.24972446018866, 54.44667362683916, 129.06503986543328, 74.32690449613206, 109.36646240875493, 76.6264401089489, 81.68068209224754, 52.4562439271518, 104.77252830083273, 50.038613812505105, 134.22962064650198, 51.725471416914445, 33.99012586543849, 98.71820805021306, 46.87640666110488, 72.5058606287396, 41.99040537072758, 71.22111002590069, 94.84390304282846, 115.22098372665342, 133.80228603164974, 54.99170636063493, 64.08519319517514, 74.9333032760452, 67.43831826092553, 110.13795904048357, 116.37889372809376, 46.94137561471165, 54.852670939913494, 36.44725194969447, 56.16424070733202, 102.3778093783781, 95.17760895095093, 51.10904908900827, 47.22572946393316, 44.35744585498387, 55.62077473729272, 81.59429061679161, 64.89191759147899, 50.53190994631244, 45.70848344819375, 47.242964096318666, 53.25308367486118, 53.493866248733454, 50.82133305092705, 54.52002064830322, 45.44723940943221, 39.78834949797089, 45.64406815780937, 41.245044952471176, 63.665772389559386, 68.11525272358449, 53.69508956951835, 8.390622642305692, 46.00894816993943, 110.65658945140545, 44.97973755763524, 117.19076192344485, 47.970334708387554, 54.38503424226951, 58.05889157783156, 63.404041282167114, 55.54956781110259, 74.74047330065866, 151.22097299941007, 39.70108059905178, 60.83508343224249, 44.19232470231216, 103.22768614008945, 211.6284670883873, 63.91295418321604, 98.71238813085132, 12.244458427956735, 96.61424451420962, 39.38446166525076, 103.04047677145611, 8.234545579353165, 40.64266205411775, 48.208732263231006, 120.01788680323156, 46.65742936349205, 44.91147561574942, 61.750441641011726, 72.80644656895355, 9.761553979679146, 48.761889155910914, 44.626877029111256, 36.159389049135285, 47.848476673379196, 137.16925403347943, 38.50959506957257, 50.5347943777596, 124.45783419032645, 65.16978192138951, 62.54557051488089, 62.86605201937376, 56.39876306378638, 69.02280279211827, 37.72456275171557, 5.180016035792261, 41.60237227978496, 44.07570813794187, 116.44233929714093, 44.89616356162287, 80.13924727174198, 39.04537835115414, 148.63545723326237, 148.27692838444057, 90.26695763359359, 95.42114685078707, 6.244615744547013, 57.03304459487548, 77.94581567644829, 53.8124391114644, 52.920517370182466, 165.30986905061877, 92.41766888578306, 80.42731158181336, 99.98907677905032, 59.74340078711163, 37.500279264057895, 8.169478398845525, 107.64810546012919, 74.92618891308166, 94.09425893687256, 115.41281535701334, 62.47853584595595, 16.1682391496453, 79.88816370122542, 56.56314108913749, 51.02061841873122, 62.26722388918526, 117.97129858983777, 56.096059666233174, 134.94790553564567, 52.183041269432955, 70.70617125065556, 71.72532005036967, 69.04085265736046, 108.79889155291326, 50.70174335337692, 34.957991954569565, 72.23571364225458, 116.90349125706805, 75.58774173842335, 5.641869808603883, 107.14555906105588, 50.081332666580494, 39.735455599452955, 45.874226913812265, 82.14506251185695, 240.3828984481366, 60.14697186509161, 78.3213742063618, 91.06155374935344, 60.38865319987099, 67.8478595645176, 50.10057078292248, 57.81390118875101, 43.469006359257165, 114.04778059673778, 69.00446124050373, 56.768508944592, 76.21564518559465, 49.916720918754734, 40.66162649482016, 61.1896923345016, 53.691787733650315, 64.8244970649751, 98.8762558796364, 78.16308339682116, 68.18719648742436, 69.98605128366538, 55.97498906678412, 43.74256217779109, 51.81912008809622, 53.799855427354004, 93.79569413500629, 96.57398524089288, 100.94922298103718, 42.17074864053927, 104.53074926017187, 292.3174726604967, 89.5419288383722, 36.22826409175142, 45.18365034803517, 60.42910830343739, 44.830164861724406, 46.8893847258983, 63.92759551664025, 98.86339061683758, 85.9317359116303, 124.98601953789834, 42.635962946966316, 67.65547768316027, 52.4631592265655, 144.5667215373639, 51.79083710163587, 112.71823723968527, 82.29632620245056, 43.20252314250781, 7.033790430918764, 150.86456620600788, 10.497688994515851, 129.99313313367003, 44.69394159163977, 50.665210649905106, 61.78384823800027, 63.704622311113496, 70.30979496219189, 6.334181999366464, 74.52955471276441, 54.47274461033372, 40.35533562525497, 67.78486595471776, 170.97631422110385, 45.84899207605473, 45.34242888555908, 80.98941293602981, 49.59772933473961, 50.63609271339685, 52.85091824655129, 38.75629738845395, 41.43084182609584, 51.63187483438901, 66.00082022940913, 58.50195405226803, 48.99988319162312, 59.037549633196235, 57.11094011265616, 65.76705350589266, 52.38727944292171, 56.513273954725186, 47.8758559205858, 43.82078715679211, 131.46598150191994, 48.51427984450133, 10.933032239845211, 153.99544169287716, 66.96335498949405, 89.81515451003104, 56.5613366497317, 81.80203751460031, 62.39975193110215, 47.90185407405338, 99.1206689448293, 130.5027551163164, 72.32930186301174, 63.405898522077266, 56.32563127169843, 39.712752385243256, 94.63946497862791, 107.88117503453894, 4.303809325341904, 40.21452949825527, 116.62799613293332, 65.04899543705653, 152.7469371403321, 101.46473962320968, 82.87206787467855, 41.507392636467095, 45.60925211685653, 89.15681453683914, 69.57574253473999, 114.09676255396049, 88.79560780168245, 39.267565171319085, 46.78611952938101, 127.47018345714825, 39.690138123253334, 42.04793236651825, 56.37039992076067, 50.22607097090121, 65.97965333859838, 60.81488415003473, 7.955248249365607, 68.7238776208113, 42.1134954535158, 91.05573257394155, 68.64865320296128, 67.88910076781576, 88.74229931949786, 52.12900703873796, 41.92991062171162, 61.58513964160367, 40.07225155893067, 101.51995012746647, 52.13521493310728, 41.39217959145813, 45.20693621298297, 60.843500151943545, 108.90033717217288, 80.29811829923695, 41.026453144825744, 82.13238751440198, 168.49505979271134, 38.35371805052404, 33.70604618278676, 44.99313797097163, 113.22119023247586, 138.80908705413677, 86.56076641129117, 40.87958552875943, 8.345567160448763, 37.0986514250683, 57.85767145153713, 42.56773946214999, 47.35831412475848, 90.79589876260492, 70.2714036084462, 47.42623368929489, 65.48255183609852, 8.562261678011323, 42.658109637236564, 38.65019778179774, 109.05605523037114, 81.67810305348587, 40.731146739306986, 136.08974259404684, 16.905961330882512, 78.2326430749701, 108.77442824148959, 40.04254851947619, 129.72786572367983, 141.52688683269125, 54.37063731597738, 104.56524215712093, 75.31835984575808, 56.59192933845098, 92.01138706337892, 78.55657042727846, 60.70493593651376, 47.167237696271656, 71.72656935984627, 120.25332554204704, 13.352791746854717, 49.39347557933587, 67.77421460733703, 60.61008479561856, 56.39526927340809, 8.415968613815437, 183.61549336094234, 54.632926628176484, 29.199031769261232, 74.77335477248499, 59.73660568606594, 43.96038074504864, 78.60653430447135, 99.83799328581472, 46.12687688502657, 111.85048454670613, 87.01915560722736, 83.871413604316, 59.67909207796473, 121.68597259350081, 137.34200422499515, 84.76923752569775, 52.8232002749052, 50.912655468887436, 33.32589315947028, 88.82061044957116, 209.12893047031073, 49.74187281307251, 60.57249077209105, 76.90814954529858, 68.2756800087326, 100.41993928589642, 69.6840060478939, 110.24356416411146, 49.14683012755893, 9.518350118005083, 65.02516213933076, 81.22623239031866, 42.81330836405431, 51.96434381340433, 60.64725722344636, 54.28421015598945, 137.61274189632658, 88.46183536396208, 112.08298334972476, 48.77594429247814, 69.61293977579261, 54.330893250221976, 65.5820638282723, 64.81841242063877, 115.00114260748876, 55.3932388841304, 51.06137507261755, 39.31318872615676, 49.13458338311278, 36.19642138757603, 49.24375719605987, 131.54846705471542, 66.27533813566708, 58.00492724965547, 51.076408468386425, 99.955605458909, 12.396402254059282, 42.13988353627989, 46.43326273071129, 43.73131916851289, 115.82866592889755, 94.44069679014018, 76.10687331148074, 82.8232208278608, 64.342221792548, 103.8375104425935, 47.190676954668085, 49.29453450671916, 59.72447918882262, 81.58540090003665, 55.38644508236738, 56.61898978079963, 118.08688627165543, 60.463788380794625, 81.49244282829909, 47.726686297057036, 57.22861375481003, 50.49745001533832, 143.348593966447, 97.33205369194135, 81.42942925884498, 61.843047881240025, 127.89902557073074, 47.426319065150345, 128.1325571182827, 48.025797568793394, 197.82238504376974, 11.721854181666465, 5.217621636754181, 5.964731897259467, 163.90856894071396, 59.51452527559491, 73.85089519538586, 44.850346402516465, 51.93444372782192, 124.85908785463617, 52.0397692634748, 33.3780922368806, 78.47479748301527, 75.39716343506795, 49.30721011173214, 88.93201748614703, 80.18562977329418, 48.51947302815968, 46.24346246653622, 55.31254368872509, 71.6926059354124, 97.94139065152446, 66.46834065353232, 35.76242282216497, 38.173287108483876, 123.23122513346283, 103.73797686768073, 91.70887694721297, 51.874192407512226, 65.74838858509932, 55.10752332854938, 58.16961178614899, 44.47712898220014, 93.87893926211169, 46.49007054936428, 67.62969380738797, 38.78129917794589, 38.712034595722535, 38.87231735633039, 69.50747331887115, 131.31898882617935, 152.6408956434924, 163.2421974364305, 50.00906062939488, 58.82648101131156, 77.20512625701954, 48.685372162146734, 6.428511195698019, 83.82980729984648, 64.31754144868556, 115.12613717143059, 46.44543587574337, 107.82028407579031, 55.92593421654203, 23.269738399639827, 54.32230474616173, 86.82082219971846, 120.81617604966678, 56.536472030160546, 7.743470727864152, 49.145081701275934, 90.79578052955134, 59.00628774195508, 109.21768945861682, 63.787054513547055, 76.89090887653623, 61.0027834196072, 72.72322443284199, 70.73468315166433, 129.52255335416413, 41.583405891619236, 175.9842460697283, 61.55230940649245, 6.904124580697437, 172.493604038512, 74.1679289130222, 51.35326386452526, 85.97106870583914, 80.57128231241313, 204.51959320454196, 122.88146804717032, 148.72488072572372, 43.33081635135752, 62.431858285336524, 58.76386718151956, 8.521166608774127, 83.61789102454168, 190.9014719475978, 41.88823949407376, 41.03648081499066, 23.951082395534197, 64.9371196042597, 102.32652597541392, 73.660021944169, 50.78028356782685, 129.41290690455304, 53.88528511832251, 49.85887220893611, 72.64769471839408, 56.84622136281893, 62.34687888671744, 66.49626005367143, 62.9046726193134, 114.6290678199142, 64.31445228829514, 68.44311264989396, 46.72979954413199, 105.49823927334198, 144.79654266682954, 84.26998950388487, 7.832450097009383, 28.479828024852402, 80.02481764250066, 75.01562888069684, 129.47331945561095, 50.28159779537165, 8.12099094222702, 55.19450804287009, 161.9764737239908, 51.289199176602324, 72.50370646733288, 89.94192831644565, 130.84965455739703, 51.76511833221933, 50.86894593622153, 58.71490772336535, 46.51461251208806, 86.24624260445773, 170.04022503741345, 64.54887201944429, 38.99610538059727, 38.851316156602046, 70.56189344381659, 62.30975239457135, 60.590405175548504, 88.92829243493426, 89.60597467636845, 60.83380698639083, 57.71098031056974, 49.46877260513046, 74.82984002278255, 48.62178538518155, 225.40959376098462, 7.3392243159576225, 66.25215234640459, 46.006462604773, 4.820664234820738, 47.61045870285482, 84.90526825559695, 90.27512831727039, 49.469775537142766, 152.63107258807284, 29.51123927552387, 78.90745093288453, 5.904120372828192, 120.87839896016419, 75.82721324657183, 59.3370156051245, 60.43454444022133, 98.74330647224754, 113.72473551004039, 32.12400340757845, 62.29586619058515, 86.45858960639382, 59.96514682598374, 5.870540891063064, 51.70529074561775, 45.78819743783818, 109.72588643291485, 56.02848897131136, 53.9266318745306, 53.165509387583036, 60.20775151596131, 71.47829171907112, 7.175474330902403, 102.58290313685885, 96.12895450592507, 61.66702642403156, 47.625175167179286, 39.74763029996381, 120.23613785153009, 6.2908645688704015, 66.02065074822556, 82.79777610374869, 384.20261982621344, 60.912325007266396, 116.49184726772901, 45.291812753797366, 92.83422701378443, 89.5725147174019, 56.47793334113686, 81.05920107456552, 60.170678675936664, 44.70476793335284, 7.320807380224901, 199.06560273770359, 51.56223001139137, 120.4626883302056, 55.49793693467967, 50.857838907716406, 96.51532644587978, 116.94300858728123, 61.782969357949725, 9.81906760270409, 63.42881982669784, 41.43040792851002, 88.57882087392356, 73.17169586166035, 175.77193421564075, 52.1111575103445, 78.89639759719076, 67.41313967477475, 42.623359103432534, 54.753428660039724, 47.335221015038876, 45.30075216021207, 47.50674140506703, 7.614475247142003, 53.66580885085225, 88.19464311710621, 15.445275179398275, 58.72717774820617, 79.58112247543242, 63.889582811020155, 136.76089122606447, 153.6005394884596, 44.61976268496081, 179.07375584649196, 7.047565907851149, 130.104373057798, 118.66366954831553, 65.25761591579331, 5.882316372607879, 83.24021946510669, 73.70935117922974, 56.34724952080873, 49.58414576850661, 37.98804600881493, 51.355836355581694, 56.46378832870581, 66.84243462268512, 117.18032157002405, 8.648372770160938, 78.14397673567152, 89.22972099305649, 81.68217597444138, 73.87976286423286, 47.598794119086875, 9.323339037783956, 224.4950685750886, 53.504569763052, 61.4147642831717, 48.826232681602356, 57.65457819461456, 115.98352050031399, 148.14729123154007, 145.68806309443028, 117.51410753537385, 42.06423563577702, 82.24892499846231, 63.15783665572995, 58.93477043060618, 69.30214420960104, 52.43670764749947, 12.110198680972275, 51.11537418483183, 100.23918012650223, 55.16535843931812, 561.0109571696887, 58.127035520985544, 6.908153901890331, 9.072133057400956, 136.85162383263082, 44.57085865699339, 78.40793954143604, 97.09984795170472, 54.398554494082944, 63.48041553363936, 58.190559555098474, 66.45157415120313, 65.27812825075543, 83.79304250735727, 70.82182892425638, 81.92297848683063, 41.39738511266172, 113.71131928497618, 74.2985208122062, 39.92339501725498, 152.7077298253563, 83.02270722240802, 99.78688972897113, 65.10381056353879, 5.796978119694909, 39.817231464985575, 100.538040150826, 62.13496588044188, 56.34374563503983, 82.09336082142498, 66.18093261916937, 49.563575857823366, 86.81541530489562, 39.53722498773808, 127.48317336796389, 46.12133451223203, 57.16722444994811, 183.1701081832981, 40.23834535181615, 43.58142558912027, 47.05204303595812, 70.71717780655608, 77.72958734915218, 5.673148569336339, 91.83370872594722, 113.92920731568458, 10.133120914748236, 88.09868931341244, 63.862162904193134, 40.40835849708586, 113.02558255017634, 106.92268864667193, 90.42615348906044, 54.30356361690185, 106.22165632490241, 47.66743940924759, 101.27873612830325, 5.935782898428051, 96.46526914699265, 62.120824591241984, 107.32173361548179, 77.68026648138603, 67.62246689029449, 140.43565914213605, 42.5121917077332, 94.0378477037523, 105.22482840794206, 52.563706465439736, 193.35972708732461, 51.53252509202364, 43.05827428670331, 46.36016702950025, 90.56142479794495, 56.50277513174473, 70.86947596173488, 76.10224376308483, 43.13093710124897, 95.77643295349517, 71.35696011317495, 12.712812692467686, 47.92966234341778, 82.38149097598851, 133.1423771139004, 54.66963454908808, 70.1532098681905, 64.44008295173438, 56.5660421164266, 113.8285709835474, 74.19514000274467, 49.59570472325412, 92.91614757188927, 121.89722050432047, 54.728209921158005, 47.305001684085475, 68.8085525655267, 120.33851325420393, 76.91363234539789, 73.40821880661036, 47.396852344666456, 108.36077427106163, 73.68923387033114, 106.14449350822618, 81.54335551341462, 70.31938224670151, 58.803023935202226, 76.4264529245811, 65.3322538486428, 102.74312531453887, 82.7818147628525, 41.88483951632012, 52.02129645390934, 39.136331930535604, 87.58861790738092, 241.53743032658014, 104.0107661453121, 53.99867959202893, 59.18894179848156, 111.822655700736, 107.27576707298952, 40.11902560014746, 109.15470145444257, 236.47939006247418, 31.716192153924048, 98.4106933267744, 11.281630176945868, 139.70745957100283, 41.1173395552721, 13.802654696494585, 52.62649021796972, 61.62315004569592, 47.266190636936486, 56.96268094705057, 62.26325551642578, 79.88203738500289, 136.0590069598223, 61.97401746498972, 53.81047692043741, 128.30468146574873, 55.439247485955576, 79.69768769396345, 92.07428656720882, 58.02710596384888, 42.0671717556803, 56.46152834562566, 73.5393219710717, 38.18542240900255, 33.16831315015013, 63.938802900242905, 51.4601207392176, 73.10261461700203, 58.054202020961064, 58.84773931076223, 59.435256118791536, 54.920381889655, 7.278196139938598, 51.952953876848305, 75.26987724895349, 84.0515124188558, 53.784896595282554, 86.93606276730677, 18.65534463189007, 77.73272036403075, 12.525571989269446, 40.79328758790398, 70.49399375465121, 81.41435057146, 126.15969302510725, 61.7833934856785, 106.76159044573531, 27.554803109593184, 164.79409621873435, 51.81202820701773, 78.11439116332014, 104.68159417517433, 59.30552667783056, 79.36493745818731, 190.99877607985846, 58.731178658937935, 9.163717396534286, 73.40368902068718, 75.75462871405949, 67.8952686547854, 91.56175474693602, 38.63986365463857, 56.998070410376855, 60.70780042439048, 97.57543727148864, 113.96506552043795, 39.0872485450984, 76.34705733719566, 44.301666876565335, 71.35003847810465, 16.31419016970561, 114.1889687404366, 213.10164606220863, 69.48660540959206, 75.23076220824477, 44.363904815077014, 6.730570222868479, 73.25350800016572, 58.8674282571513, 40.63698893778971, 69.8156809137943, 102.54943325244608, 94.96913460641721, 94.48469236722313, 51.64244935439394, 189.12353045112172, 52.39317453832961, 34.413228612895665, 111.24165465836683, 49.50069176570959, 53.00071656871003, 55.54760069462058, 61.364758534347565, 61.544800753144806, 118.430157064406, 85.28684902123548, 57.188904272903365, 88.1573928618147, 68.39631920034282, 7.202178741471178, 56.06942374118284, 44.98195497613427, 36.16523916010935, 52.738500355134434, 101.75809631806837, 104.59605486314925, 49.47582362180202, 84.74086543352841, 73.7912985476167, 72.03437229240248, 59.23875433266101, 53.012405476687, 66.51062439928849, 67.84305740983878, 98.21209270277268, 67.69480134375246, 108.96629549527634, 85.80846102884445, 94.95854444203997, 194.3159844965083, 186.96195479141804, 54.58895776225684, 59.67597022660837, 216.0385248283692, 145.4986365105906, 63.99317996182356, 50.46411428312201, 89.3993464320784, 73.90288265773111, 141.10019304732927, 63.8909664040065, 46.499037773815814, 61.340931179448205, 52.348120244160384, 15</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>114.5703678131104</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>70.6198842424816</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>[108.6068115234375, 264.6373596191406, 69.32459259033203, 126.57628631591797, 132.0705108642578, 38.94092559814453, 99.71328735351562, 111.27193450927734, 56.55049514770508, 56.696563720703125, 180.89158630371094, 28.295408248901367, 224.11093139648438, 130.0493621826172, 87.89945983886719, 77.35881042480469, 117.35907745361328, 65.85430908203125, 78.04331970214844, 162.3276824951172, 88.30278778076172, 210.5742645263672, 155.2653350830078, 133.19747924804688, 8.667086601257324, 15.833881378173828, 127.92560577392578, 112.91738891601562, 93.48584747314453, 205.794921875, 113.50288391113281, 303.3412780761719, 83.7910385131836, 129.1955108642578, 126.75804901123047, 8.039782524108887, 53.826995849609375, 84.97117614746094, 90.39070129394531, 59.727073669433594, 250.5835723876953, 88.93842315673828, 314.9388732910156, 49.45927810668945, 46.25710678100586, 127.77964782714844, 54.94021224975586, 151.74012756347656, 307.373046875, 52.720924377441406, 64.7410659790039, 61.0701904296875, 64.38531494140625, 77.9032974243164, 67.28387451171875, 183.72756958007812, 81.19929504394531, 63.225669860839844, 287.4279479980469, 60.17253112792969, 85.62043762207031, 55.248558044433594, 147.58840942382812, 261.9767761230469, 73.41456604003906, 79.44871520996094, 53.42506408691406, 103.59230041503906, 69.2796401977539, 69.46863555908203, 54.90668487548828, 79.44036865234375, 111.39195251464844, 109.54590606689453, 165.46873474121094, 90.08563232421875, 181.379150390625, 73.4162368774414, 162.7654571533203, 127.72393798828125, 189.4305877685547, 74.01566314697266, 135.16981506347656, 96.91646575927734, 71.83689880371094, 240.59515380859375, 189.6961212158203, 184.6401824951172, 48.5579833984375, 38.78030776977539, 124.10890197753906, 91.1418685913086, 246.85169982910156, 61.136627197265625, 50.83909225463867, 66.56172180175781, 72.48876190185547, 84.29359436035156, 68.54208374023438, 288.2903137207031]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01954</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:34:18</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>85.13390095438548</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>65.52634177875433</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>108.4817629179331</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>4606</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>[0.7430754746654005, 0.9516071264234239, 0.47101765608309115, 0.8268527642712138, 0.774658642582967, 0.7091973475797235, 0.6486850622590895, 1.0517904370072042, 1.3881213407761508, 0.9914861481385788, 1.0150029222851085, 0.8159133213273768, 0.4380251397634803, 1.1323555679002562, 0.9876666201128738, 0.8197618406013574, 1.1320753790611495, 0.9275545835340478, 1.0757920421767238, 1.6875814270386005, 0.4012822549530599, 1.942045440990668, 1.7572469822193373, 1.130678642742254, 1.1568536575090367, 0.55682107818823, 1.5192471905759997, 0.7995028815767729, 0.13274337000082717, 0.7189912137933937, 0.920069542002991, 0.5954041878540638, 1.213510767963638, 1.7992984133557715, 1.132722061044552, 0.6978226951381339, 1.761396903580976, 0.8999498538084396, 1.308525763779003, 1.5825888675321764, 1.3209219647727486, 3.359437635992775, 1.973332677254547, 0.6648189971644618, 0.6295640491207432, 0.7282968709112676, 2.035513752495797, 1.5726268700128658, 1.2875687284423016, 0.9015329923997226, 1.2715462992495192, 2.288177788014611, 1.4439567750082924, 1.3478011655958915, 1.1700590454696633, 2.3443685243518306, 1.1804454030965197, 1.5863988231084787, 2.525583694019558, 0.5356183685586686, 1.4642885285990963, 1.073582950474666, 2.393293690257867, 1.6606149370804142, 1.2963902435962738, 1.9226618325049405, 1.8186439820533704, 1.4574387089985503, 1.8525267887052748, 1.8185645505061276, 1.778443568323987, 2.285856235268735, 0.7620794190421781, 1.0133120204741966, 1.0005325117984907, 2.124193744834477, 1.2355787730716394, 1.9603628353886968, 1.0068302205829809, 1.409877608947123, 4.906282073593813, 2.533434521558838, 2.696655557209281, 2.07027695697729, 2.617814297125741, 3.392045298370719, 4.154731151692997, 1.858972319118433, 4.307208513555791, 1.9753449170870685, 4.908254326626589, 5.079194027148657, 0.37721737345305467, 3.554175249085856, 1.6885635714587242, 1.1719757838936102, 0.8669686836082962, 6.541826234981618, 2.471311994835735, 2.739070979485303, 2.56917954667364, 1.3918059116681059, 3.7152478002183607, 2.7836394826254325, 1.9854438691480507, 2.2761848304769443, 2.3366372218294478, 1.9351071837502067, 4.142512895294245, 1.9718516002106308, 2.9995211989872304, 2.718742460512585, 2.1825323856642616, 2.363165221788567, 1.5770065439901948, 2.388515443577054, 0.9561570325618524, 2.3983286751417063, 2.288418514599508, 11.776462642657165, 2.607609844359797, 3.9403009474234634, 3.8469272302289554, 4.275397760793676, 5.106150416812355, 3.889730176415886, 4.986277886827339, 1.8388795303522125, 0.849113674270729, 6.106925181192417, 5.800095842403906, 8.573323744879346, 3.338380893580166, 1.9633322289586352, 7.161297067099867, 2.1326494986384206, 4.311858302211964, 4.18626604508575, 3.2505680012471605, 3.9484830478342317, 5.946337499000536, 7.251619037517923, 5.082167029107762, 7.456005851295896, 5.085228891051909, 3.9882717171545967, 5.370906090424827, 4.976506662414275, 5.640883358068876, 4.202919043352265, 0.9660554776804495, 4.011971950192469, 6.805789246771024, 4.841431457509921, 3.553886221830371, 5.934914232191057, 4.410255316189265, 5.707076478102026, 6.405663910935966, 7.404580536634155, 4.617004272647135, 4.729215470357944, 15.09510029740369, 1.5715071383095798, 4.950416919156829, 11.208878077754285, 17.782260426094965, 23.913729986007123, 5.916262220005946, 11.547655878589511, 7.566208436972218, 0.5140027512495132, 6.603099044145342, 25.114490036157306, 13.126248231181918, 3.32017483610181, 7.301431384626415, 9.62021877443864, 12.912228358350871, 3.7572152727467767, 4.892279059665825, 8.742758917254115, 8.864213408857708, 5.952159016887555, 7.905892884295723, 10.704502025189939, 14.77801920646186, 13.337293824900188, 4.197250824151464, 13.040724683724996, 5.587201686236426, 10.658761561741503, 4.506988551362735, 12.116991357011159, 5.4385078339104265, 11.750137005692412, 9.886094029010417, 2.797890846096096, 13.257255348628203, 15.434632603177889, 31.301649313823084, 21.031348941387478, 19.50241233785641, 18.143360457287876, 9.841678849934233, 18.666625238737787, 11.416964355747144, 34.77726560232245, 17.07719811726002, 4.1273917511378535, 21.60215096536698, 24.36719981123805, 4.3929558231112145, 13.159067004148612, 1.7693479370227112, 7.455134819707652, 16.4803291472972, 8.106148142727829, 13.941957858149426, 7.188088084604996, 15.035160585908837, 12.584750924373493, 15.767887098344453, 10.77044961841191, 15.975463670765658, 13.39159162943851, 10.040449798205596, 18.61799327657394, 7.151557150826483, 26.82500297109701, 8.991873535215847, 15.995684834314972, 14.118181918794743, 12.37071018604221, 11.073554088882434, 21.06297341103957, 13.3212896664807, 27.739892667856754, 17.20758097003332, 4.465374787328531, 22.629864505635673, 31.279585411419628, 17.870678790594543, 51.03281824207483, 30.673100021788645, 18.704751857940412, 25.88008354465698, 10.320723139666722, 23.41626426403821, 23.81812021598304, 20.70189084793962, 20.46819083912074, 43.85231521891965, 5.398734667864117, 24.66806862253457, 34.247089352782346, 31.391940733684333, 20.06291448436824, 14.060611920357621, 32.49161148638269, 17.31653155186244, 22.648069427404184, 25.76662657101343, 13.84530735849341, 12.54501910713889, 24.321347034913824, 36.18059900867895, 25.69139988544801, 36.37735400369422, 19.577242157395226, 20.15431860124181, 4.5294491881998145, 66.12589647354825, 37.05680306477752, 27.88832948713578, 41.86266783093668, 27.666024437740468, 25.01309211933078, 16.486822432747605, 33.95295724309378, 44.07986560190188, 36.280987854750336, 37.167534300636014, 34.827212655296606, 50.48595629140986, 48.58322975802086, 17.525889620794196, 1.3257826437898799, 25.906730481847504, 51.69134576005174, 44.70761398815176, 25.342962781306635, 48.58520853628577, 33.58942367153492, 37.18526033346362, 33.98197674889909, 25.30966729450835, 24.99167169380426, 17.158621724573987, 20.99627562297529, 18.35995060761353, 19.084410974676718, 46.15883368276774, 49.972036532197265, 16.562957008825464, 57.071210301236455, 32.337893647130734, 22.880572942228397, 25.065776940979724, 41.68338021971485, 60.47294698614457, 35.51318315106989, 26.34403676543362, 29.804305403034007, 28.14392627044833, 32.21297465318708, 20.91105562142683, 74.15156575764904, 38.14013936739589, 40.47449216788359, 25.863777341115494, 35.15130491751479, 25.597975338420202, 52.49759802786953, 22.317133413571252, 44.993791449575035, 2.031631280117488, 51.76097119947288, 20.898822985175645, 48.81639595746645, 39.0697140254427, 22.25195053156039, 35.400272362724166, 38.41084515494928, 22.48395547690861, 64.42117245148164, 24.64845906737878, 38.14602075744043, 28.97548571003616, 35.596930526846336, 46.03136237135081, 36.75981405016684, 42.88605442143313, 100.30528192680603, 54.31687388733297, 28.59595982599104, 26.37542498660379, 63.263768474045015, 39.70698661962173, 22.439533772065836, 16.96373093972651, 38.20412636165979, 62.91366019785493, 51.29702436567408, 74.62777606519712, 39.361918247107255, 5.660370789716531, 72.20866800969986, 59.64204602711093, 30.005747785859263, 37.12101121194254, 49.749453768878304, 21.280604299485525, 44.803841969612066, 35.85411382618718, 31.061907422402417, 4.980225790788877, 48.08538323168655, 27.76246878643443, 39.60126112039394, 45.130758795568205, 40.205721918697996, 41.62973425675602, 58.70044120776015, 51.153518252781424, 64.22383565849469, 38.361193051192906, 40.15987312413889, 26.679159367900166, 21.736516322518955, 30.330657336636484, 37.052673551748136, 59.370937741511945, 83.39163590718704, 58.11348179964664, 38.5838605592819, 45.53200794555994, 59.883571221232486, 47.96745915750463, 43.02141310576284, 96.86651395051622, 105.39948775959091, 30.640021917593195, 59.13318903284967, 46.43246221455976, 78.45156021610056, 47.39872595768726, 64.29898928971222, 74.34485047144939, 34.084187308710206, 38.42456747045572, 94.19801784541636, 56.96790594312489, 60.59711430203326, 31.380303670859924, 160.23135613957837, 50.023024926836705, 40.78168320676567, 4.639430656246602, 44.917438601867616, 56.80579098135818, 36.71950726473542, 77.1395440038791, 70.1882880294061, 10.056202532639558, 75.57526102972759, 31.283043760476637, 64.02989531362576, 12.97526885185214, 54.61169889027975, 43.915658020367786, 68.97081479761411, 40.13819392049695, 8.85798396417812, 46.34190873024533, 117.87319082277547, 66.11342011332201, 139.56723885420033, 94.16264570829368, 90.42554913178196, 53.25849149717229, 34.37338050563535, 6.000242561485791, 37.96438247634979, 49.27809139707852, 63.81256102632719, 84.32811089363159, 46.363100536844016, 57.62967509991524, 36.08380900160237, 178.40249304308165, 146.20431979502092, 101.0400173010282, 37.45857956998651, 35.068869429836944, 102.92436629819649, 41.225495727271884, 43.48712766050423, 78.27064685461708, 74.41542935330872, 130.49616419086018, 48.40441549634967, 96.37729506668086, 47.15825911867496, 43.43952385942413, 38.40978832770013, 8.728241638138226, 38.88341643010539, 7.346659478303014, 42.21709489231106, 36.40771537582899, 26.07891585544949, 46.916588883539674, 46.56189864852234, 32.31980926645424, 20.514908365460187, 65.63758763515837, 104.24120036090173, 90.81147314116176, 6.539619901538163, 97.43187839034725, 60.16395767935119, 35.580754249198776, 61.398744629780055, 35.798045534309864, 78.45909111552055, 82.62653501212986, 37.789819986137374, 47.02179620717648, 8.51298212862278, 55.40551329583538, 61.768394624960635, 64.72207043022759, 54.436683747226965, 104.08976746459169, 34.50567682264381, 61.29183650258999, 79.52738562875696, 8.53944387475681, 104.91443587259268, 39.03246485175447, 7.08273651787089, 37.60926736712432, 37.73203105623934, 37.36442954763615, 48.28709520311699, 77.37100633507607, 39.670249243335526, 34.951537901445946, 139.85762065165503, 73.35138389954716, 115.57995344427152, 48.02408558008701, 110.24959535465773, 6.685131656263097, 77.64032928674273, 53.93832305273668, 35.58210842304813, 48.4399488120103, 108.79438835914563, 51.9357655785837, 38.5659332713445, 57.44672621422384, 52.97529625905956, 76.25305277567311, 28.45973523762749, 61.253623240593, 36.13411725289958, 73.10682500186218, 65.14132584516504, 45.57591196337417, 28.5446462010657, 98.78915991651701, 151.31821362026932, 41.654885398828235, 74.19732616329654, 87.21252633066753, 71.2663023943255, 32.47376905905552, 50.638944731156094, 82.33447368728571, 47.439133495693625, 43.187705914347895, 64.45283411032102, 29.183566218615518, 63.44370149123032, 31.33076774711937, 52.76596290701715, 57.2509055555088, 61.997778574995216, 26.080093518935588, 36.60183955870805, 66.42529624387288, 56.41362334220638, 35.49512578438432, 62.492968979845045, 99.51070160876742, 36.47220394404286, 106.17322547946227, 41.922070444091204, 73.0326389016485, 104.84261155006837, 59.88071857592007, 32.54749011883325, 91.041451821892, 44.142463334986694, 33.80605859430692, 53.132120769183125, 50.13853702713732, 32.89047871350658, 65.67734110595835, 35.35273999406683, 97.38709022547985, 194.61469839820447, 46.04507859486678, 86.55114971598596, 48.265065673840624, 77.97897610332696, 40.81512701892442, 50.58186746326103, 54.881910189429604, 41.02490068737602, 44.09991262235779, 81.09103792673116, 52.048284814847804, 41.9181444663499, 9.09786112261639, 53.616287165755665, 81.28813552122112, 158.47989841982002, 81.69104923982627, 94.65299537513033, 40.5656443697015, 61.83932355223557, 50.341247844256785, 6.392951309236307, 145.50622218248816, 34.80537532434381, 63.99672110613553, 86.13466081357625, 68.984715059151, 9.847804298873395, 85.09927874848673, 83.48750802927782, 4.3698114923786635, 102.07152004010925, 50.93255796016027, 78.50792078391709, 7.086147926545102, 55.183418905321034, 40.42453586836624, 77.63435080329599, 59.29679454679922, 112.34472213336208, 65.35048366719259, 46.14602201797251, 76.30049274069356, 56.55215251932044, 50.70467664410138, 39.80945809336516, 71.3538175386989, 67.27693243520363, 82.94703231909432, 38.27088072093486, 83.52665957662909, 82.6656317485853, 128.45575427799758, 39.405325381672675, 33.435236548677764, 47.86650415852333, 4.924568658965381, 54.40897216647606, 71.90165439486339, 37.89329910726344, 70.27659082518964, 44.33151161947488, 51.74178536873088, 35.69982669356389, 92.80061263096113, 41.38016089329654, 58.17975907783789, 68.17877490447853, 42.14639668081742, 87.83135142677928, 65.75250704952074, 136.74141597130102, 67.44427942279698, 52.60384574371393, 91.91520582623173, 134.75567278101127, 7.087908898122953, 56.251637684943645, 54.70301062020871, 33.384118233832446, 5.291154277820578, 51.84744462497908, 47.88734021875598, 68.4045588600017, 45.23867031762343, 47.34444374371623, 99.68684835351353, 41.703443079348745, 6.790113142161861, 42.15256487495367, 134.64411802949377, 58.083851064987854, 50.05134640375782, 40.67611652878609, 43.77946246328429, 61.93119909026521, 69.54518946256096, 61.185333656304, 97.51666955883353, 55.573054759860725, 6.488214141174404, 59.425229499509385, 38.69631329812943, 179.1958278376241, 76.58302669030623, 55.845360928818835, 68.85177085644702, 60.73339176327268, 211.66035782793074, 54.1629213522294, 49.741311940866034, 56.30510219886949, 56.459764020140305, 49.588858623042455, 114.69671836557279, 55.94815495045215, 255.3285677122259, 109.98794548164592, 92.0331188060071, 6.383410422058301, 105.29289931040063, 65.52099801609594, 62.84159992086636, 77.55215714535338, 46.1826032194914, 99.43421580698651, 46.540467605791726, 53.24640199494679, 73.43580929701604, 36.88079713541203, 74.23181188718476, 11.73651070118089, 73.84790243754414, 60.94467580180048, 5.334708343418195, 101.50203214206184, 74.1576860767021, 61.14437064984541, 77.59228743467156, 63.064122284871054, 63.166207168405755, 90.55574878580842, 78.0681914013716, 48.77204666311201, 91.10584502280781, 48.361940309536685, 95.8848739563639, 57.07037104264474, 60.123057182910884, 122.87096335058227, 47.804805147411045, 46.971652107277365, 147.7534848784582, 44.84510749567689, 108.28187569603794, 40.50748896235796, 95.45055547393024, 4.532395941078563, 49.40026086386911, 73.39238789890132, 50.18805535045539, 88.59647693649373, 95.8069915320493, 73.62143469555289, 47.14456785318755, 95.52336643233585, 65.33337752126663, 57.10384348304376, 55.592921324550865, 4.719184752893318, 53.481924042723655, 79.62261892099832, 68.77669793670525, 47.16186580005167, 39.37841367252719, 134.80801619203493, 121.06430724104004, 74.17332378025814, 45.34150603449863, 72.44661126447458, 40.28928338454787, 58.72096535977705, 101.44734463879234, 84.94074845182286, 102.7151992511783, 341.363794456509, 47.32266749677891, 68.24972446018866, 54.44667362683916, 129.06503986543328, 74.32690449613206, 109.36646240875493, 76.6264401089489, 81.68068209224754, 52.4562439271518, 104.77252830083273, 50.038613812505105, 134.22962064650198, 51.725471416914445, 33.99012586543849, 98.71820805021306, 46.87640666110488, 72.5058606287396, 41.99040537072758, 71.22111002590069, 94.84390304282846, 115.22098372665342, 133.80228603164974, 54.99170636063493, 64.08519319517514, 74.9333032760452, 67.43831826092553, 110.13795904048357, 116.37889372809376, 46.94137561471165, 54.852670939913494, 36.44725194969447, 56.16424070733202, 102.3778093783781, 95.17760895095093, 51.10904908900827, 47.22572946393316, 44.35744585498387, 55.62077473729272, 81.59429061679161, 64.89191759147899, 50.53190994631244, 45.70848344819375, 47.242964096318666, 53.25308367486118, 53.493866248733454, 50.82133305092705, 54.52002064830322, 45.44723940943221, 39.78834949797089, 45.64406815780937, 41.245044952471176, 63.665772389559386, 68.11525272358449, 53.69508956951835, 8.390622642305692, 46.00894816993943, 110.65658945140545, 44.97973755763524, 117.19076192344485, 47.970334708387554, 54.38503424226951, 58.05889157783156, 63.404041282167114, 55.54956781110259, 74.74047330065866, 151.22097299941007, 39.70108059905178, 60.83508343224249, 44.19232470231216, 103.22768614008945, 211.6284670883873, 63.91295418321604, 98.71238813085132, 12.244458427956735, 96.61424451420962, 39.38446166525076, 103.04047677145611, 8.234545579353165, 40.64266205411775, 48.208732263231006, 120.01788680323156, 46.65742936349205, 44.91147561574942, 61.750441641011726, 72.80644656895355, 9.761553979679146, 48.761889155910914, 44.626877029111256, 36.159389049135285, 47.848476673379196, 137.16925403347943, 38.50959506957257, 50.5347943777596, 124.45783419032645, 65.16978192138951, 62.54557051488089, 62.86605201937376, 56.39876306378638, 69.02280279211827, 37.72456275171557, 5.180016035792261, 41.60237227978496, 44.07570813794187, 116.44233929714093, 44.89616356162287, 80.13924727174198, 39.04537835115414, 148.63545723326237, 148.27692838444057, 90.26695763359359, 95.42114685078707, 6.244615744547013, 57.03304459487548, 77.94581567644829, 53.8124391114644, 52.920517370182466, 165.30986905061877, 92.41766888578306, 80.42731158181336, 99.98907677905032, 59.74340078711163, 37.500279264057895, 8.169478398845525, 107.64810546012919, 74.92618891308166, 94.09425893687256, 115.41281535701334, 62.47853584595595, 16.1682391496453, 79.88816370122542, 56.56314108913749, 51.02061841873122, 62.26722388918526, 117.97129858983777, 56.096059666233174, 134.94790553564567, 52.183041269432955, 70.70617125065556, 71.72532005036967, 69.04085265736046, 108.79889155291326, 50.70174335337692, 34.957991954569565, 72.23571364225458, 116.90349125706805, 75.58774173842335, 5.641869808603883, 107.14555906105588, 50.081332666580494, 39.735455599452955, 45.874226913812265, 82.14506251185695, 240.3828984481366, 60.14697186509161, 78.3213742063618, 91.06155374935344, 60.38865319987099, 67.8478595645176, 50.10057078292248, 57.81390118875101, 43.469006359257165, 114.04778059673778, 69.00446124050373, 56.768508944592, 76.21564518559465, 49.916720918754734, 40.66162649482016, 61.1896923345016, 53.691787733650315, 64.8244970649751, 98.8762558796364, 78.16308339682116, 68.18719648742436, 69.98605128366538, 55.97498906678412, 43.74256217779109, 51.81912008809622, 53.799855427354004, 93.79569413500629, 96.57398524089288, 100.94922298103718, 42.17074864053927, 104.53074926017187, 292.3174726604967, 89.5419288383722, 36.22826409175142, 45.18365034803517, 60.42910830343739, 44.830164861724406, 46.8893847258983, 63.92759551664025, 98.86339061683758, 85.9317359116303, 124.98601953789834, 42.635962946966316, 67.65547768316027, 52.4631592265655, 144.5667215373639, 51.79083710163587, 112.71823723968527, 82.29632620245056, 43.20252314250781, 7.033790430918764, 150.86456620600788, 10.497688994515851, 129.99313313367003, 44.69394159163977, 50.665210649905106, 61.78384823800027, 63.704622311113496, 70.30979496219189, 6.334181999366464, 74.52955471276441, 54.47274461033372, 40.35533562525497, 67.78486595471776, 170.97631422110385, 45.84899207605473, 45.34242888555908, 80.98941293602981, 49.59772933473961, 50.63609271339685, 52.85091824655129, 38.75629738845395, 41.43084182609584, 51.63187483438901, 66.00082022940913, 58.50195405226803, 48.99988319162312, 59.037549633196235, 57.11094011265616, 65.76705350589266, 52.38727944292171, 56.513273954725186, 47.8758559205858, 43.82078715679211, 131.46598150191994, 48.51427984450133, 10.933032239845211, 153.99544169287716, 66.96335498949405, 89.81515451003104, 56.5613366497317, 81.80203751460031, 62.39975193110215, 47.90185407405338, 99.1206689448293, 130.5027551163164, 72.32930186301174, 63.405898522077266, 56.32563127169843, 39.712752385243256, 94.63946497862791, 107.88117503453894, 4.303809325341904, 40.21452949825527, 116.62799613293332, 65.04899543705653, 152.7469371403321, 101.46473962320968, 82.87206787467855, 41.507392636467095, 45.60925211685653, 89.15681453683914, 69.57574253473999, 114.09676255396049, 88.79560780168245, 39.267565171319085, 46.78611952938101, 127.47018345714825, 39.690138123253334, 42.04793236651825, 56.37039992076067, 50.22607097090121, 65.97965333859838, 60.81488415003473, 7.955248249365607, 68.7238776208113, 42.1134954535158, 91.05573257394155, 68.64865320296128, 67.88910076781576, 88.74229931949786, 52.12900703873796, 41.92991062171162, 61.58513964160367, 40.07225155893067, 101.51995012746647, 52.13521493310728, 41.39217959145813, 45.20693621298297, 60.843500151943545, 108.90033717217288, 80.29811829923695, 41.026453144825744, 82.13238751440198, 168.49505979271134, 38.35371805052404, 33.70604618278676, 44.99313797097163, 113.22119023247586, 138.80908705413677, 86.56076641129117, 40.87958552875943, 8.345567160448763, 37.0986514250683, 57.85767145153713, 42.56773946214999, 47.35831412475848, 90.79589876260492, 70.2714036084462, 47.42623368929489, 65.48255183609852, 8.562261678011323, 42.658109637236564, 38.65019778179774, 109.05605523037114, 81.67810305348587, 40.731146739306986, 136.08974259404684, 16.905961330882512, 78.2326430749701, 108.77442824148959, 40.04254851947619, 129.72786572367983, 141.52688683269125, 54.37063731597738, 104.56524215712093, 75.31835984575808, 56.59192933845098, 92.01138706337892, 78.55657042727846, 60.70493593651376, 47.167237696271656, 71.72656935984627, 120.25332554204704, 13.352791746854717, 49.39347557933587, 67.77421460733703, 60.61008479561856, 56.39526927340809, 8.415968613815437, 183.61549336094234, 54.632926628176484, 29.199031769261232, 74.77335477248499, 59.73660568606594, 43.96038074504864, 78.60653430447135, 99.83799328581472, 46.12687688502657, 111.85048454670613, 87.01915560722736, 83.871413604316, 59.67909207796473, 121.68597259350081, 137.34200422499515, 84.76923752569775, 52.8232002749052, 50.912655468887436, 33.32589315947028, 88.82061044957116, 209.12893047031073, 49.74187281307251, 60.57249077209105, 76.90814954529858, 68.2756800087326, 100.41993928589642, 69.6840060478939, 110.24356416411146, 49.14683012755893, 9.518350118005083, 65.02516213933076, 81.22623239031866, 42.81330836405431, 51.96434381340433, 60.64725722344636, 54.28421015598945, 137.61274189632658, 88.46183536396208, 112.08298334972476, 48.77594429247814, 69.61293977579261, 54.330893250221976, 65.5820638282723, 64.81841242063877, 115.00114260748876, 55.3932388841304, 51.06137507261755, 39.31318872615676, 49.13458338311278, 36.19642138757603, 49.24375719605987, 131.54846705471542, 66.27533813566708, 58.00492724965547, 51.076408468386425, 99.955605458909, 12.396402254059282, 42.13988353627989, 46.43326273071129, 43.73131916851289, 115.82866592889755, 94.44069679014018, 76.10687331148074, 82.8232208278608, 64.342221792548, 103.8375104425935, 47.190676954668085, 49.29453450671916, 59.72447918882262, 81.58540090003665, 55.38644508236738, 56.61898978079963, 118.08688627165543, 60.463788380794625, 81.49244282829909, 47.726686297057036, 57.22861375481003, 50.49745001533832, 143.348593966447, 97.33205369194135, 81.42942925884498, 61.843047881240025, 127.89902557073074, 47.426319065150345, 128.1325571182827, 48.025797568793394, 197.82238504376974, 11.721854181666465, 5.217621636754181, 5.964731897259467, 163.90856894071396, 59.51452527559491, 73.85089519538586, 44.850346402516465, 51.93444372782192, 124.85908785463617, 52.0397692634748, 33.3780922368806, 78.47479748301527, 75.39716343506795, 49.30721011173214, 88.93201748614703, 80.18562977329418, 48.51947302815968, 46.24346246653622, 55.31254368872509, 71.6926059354124, 97.94139065152446, 66.46834065353232, 35.76242282216497, 38.173287108483876, 123.23122513346283, 103.73797686768073, 91.70887694721297, 51.874192407512226, 65.74838858509932, 55.10752332854938, 58.16961178614899, 44.47712898220014, 93.87893926211169, 46.49007054936428, 67.62969380738797, 38.78129917794589, 38.712034595722535, 38.87231735633039, 69.50747331887115, 131.31898882617935, 152.6408956434924, 163.2421974364305, 50.00906062939488, 58.82648101131156, 77.20512625701954, 48.685372162146734, 6.428511195698019, 83.82980729984648, 64.31754144868556, 115.12613717143059, 46.44543587574337, 107.82028407579031, 55.92593421654203, 23.269738399639827, 54.32230474616173, 86.82082219971846, 120.81617604966678, 56.536472030160546, 7.743470727864152, 49.145081701275934, 90.79578052955134, 59.00628774195508, 109.21768945861682, 63.787054513547055, 76.89090887653623, 61.0027834196072, 72.72322443284199, 70.73468315166433, 129.52255335416413, 41.583405891619236, 175.9842460697283, 61.55230940649245, 6.904124580697437, 172.493604038512, 74.1679289130222, 51.35326386452526, 85.97106870583914, 80.57128231241313, 204.51959320454196, 122.88146804717032, 148.72488072572372, 43.33081635135752, 62.431858285336524, 58.76386718151956, 8.521166608774127, 83.61789102454168, 190.9014719475978, 41.88823949407376, 41.03648081499066, 23.951082395534197, 64.9371196042597, 102.32652597541392, 73.660021944169, 50.78028356782685, 129.41290690455304, 53.88528511832251, 49.85887220893611, 72.64769471839408, 56.84622136281893, 62.34687888671744, 66.49626005367143, 62.9046726193134, 114.6290678199142, 64.31445228829514, 68.44311264989396, 46.72979954413199, 105.49823927334198, 144.79654266682954, 84.26998950388487, 7.832450097009383, 28.479828024852402, 80.02481764250066, 75.01562888069684, 129.47331945561095, 50.28159779537165, 8.12099094222702, 55.19450804287009, 161.9764737239908, 51.289199176602324, 72.50370646733288, 89.94192831644565, 130.84965455739703, 51.76511833221933, 50.86894593622153, 58.71490772336535, 46.51461251208806, 86.24624260445773, 170.04022503741345, 64.54887201944429, 38.99610538059727, 38.851316156602046, 70.56189344381659, 62.30975239457135, 60.590405175548504, 88.92829243493426, 89.60597467636845, 60.83380698639083, 57.71098031056974, 49.46877260513046, 74.82984002278255, 48.62178538518155, 225.40959376098462, 7.3392243159576225, 66.25215234640459, 46.006462604773, 4.820664234820738, 47.61045870285482, 84.90526825559695, 90.27512831727039, 49.469775537142766, 152.63107258807284, 29.51123927552387, 78.90745093288453, 5.904120372828192, 120.87839896016419, 75.82721324657183, 59.3370156051245, 60.43454444022133, 98.74330647224754, 113.72473551004039, 32.12400340757845, 62.29586619058515, 86.45858960639382, 59.96514682598374, 5.870540891063064, 51.70529074561775, 45.78819743783818, 109.72588643291485, 56.02848897131136, 53.9266318745306, 53.165509387583036, 60.20775151596131, 71.47829171907112, 7.175474330902403, 102.58290313685885, 96.12895450592507, 61.66702642403156, 47.625175167179286, 39.74763029996381, 120.23613785153009, 6.2908645688704015, 66.02065074822556, 82.79777610374869, 384.20261982621344, 60.912325007266396, 116.49184726772901, 45.291812753797366, 92.83422701378443, 89.5725147174019, 56.47793334113686, 81.05920107456552, 60.170678675936664, 44.70476793335284, 7.320807380224901, 199.06560273770359, 51.56223001139137, 120.4626883302056, 55.49793693467967, 50.857838907716406, 96.51532644587978, 116.94300858728123, 61.782969357949725, 9.81906760270409, 63.42881982669784, 41.43040792851002, 88.57882087392356, 73.17169586166035, 175.77193421564075, 52.1111575103445, 78.89639759719076, 67.41313967477475, 42.623359103432534, 54.753428660039724, 47.335221015038876, 45.30075216021207, 47.50674140506703, 7.614475247142003, 53.66580885085225, 88.19464311710621, 15.445275179398275, 58.72717774820617, 79.58112247543242, 63.889582811020155, 136.76089122606447, 153.6005394884596, 44.61976268496081, 179.07375584649196, 7.047565907851149, 130.104373057798, 118.66366954831553, 65.25761591579331, 5.882316372607879, 83.24021946510669, 73.70935117922974, 56.34724952080873, 49.58414576850661, 37.98804600881493, 51.355836355581694, 56.46378832870581, 66.84243462268512, 117.18032157002405, 8.648372770160938, 78.14397673567152, 89.22972099305649, 81.68217597444138, 73.87976286423286, 47.598794119086875, 9.323339037783956, 224.4950685750886, 53.504569763052, 61.4147642831717, 48.826232681602356, 57.65457819461456, 115.98352050031399, 148.14729123154007, 145.68806309443028, 117.51410753537385, 42.06423563577702, 82.24892499846231, 63.15783665572995, 58.93477043060618, 69.30214420960104, 52.43670764749947, 12.110198680972275, 51.11537418483183, 100.23918012650223, 55.16535843931812, 561.0109571696887, 58.127035520985544, 6.908153901890331, 9.072133057400956, 136.85162383263082, 44.57085865699339, 78.40793954143604, 97.09984795170472, 54.398554494082944, 63.48041553363936, 58.190559555098474, 66.45157415120313, 65.27812825075543, 83.79304250735727, 70.82182892425638, 81.92297848683063, 41.39738511266172, 113.71131928497618, 74.2985208122062, 39.92339501725498, 152.7077298253563, 83.02270722240802, 99.78688972897113, 65.10381056353879, 5.796978119694909, 39.817231464985575, 100.538040150826, 62.13496588044188, 56.34374563503983, 82.09336082142498, 66.18093261916937, 49.563575857823366, 86.81541530489562, 39.53722498773808, 127.48317336796389, 46.12133451223203, 57.16722444994811, 183.1701081832981, 40.23834535181615, 43.58142558912027, 47.05204303595812, 70.71717780655608, 77.72958734915218, 5.673148569336339, 91.83370872594722, 113.92920731568458, 10.133120914748236, 88.09868931341244, 63.862162904193134, 40.40835849708586, 113.02558255017634, 106.92268864667193, 90.42615348906044, 54.30356361690185, 106.22165632490241, 47.66743940924759, 101.27873612830325, 5.935782898428051, 96.46526914699265, 62.120824591241984, 107.32173361548179, 77.68026648138603, 67.62246689029449, 140.43565914213605, 42.5121917077332, 94.0378477037523, 105.22482840794206, 52.563706465439736, 193.35972708732461, 51.53252509202364, 43.05827428670331, 46.36016702950025, 90.56142479794495, 56.50277513174473, 70.86947596173488, 76.10224376308483, 43.13093710124897, 95.77643295349517, 71.35696011317495, 12.712812692467686, 47.92966234341778, 82.38149097598851, 133.1423771139004, 54.66963454908808, 70.1532098681905, 64.44008295173438, 56.5660421164266, 113.8285709835474, 74.19514000274467, 49.59570472325412, 92.91614757188927, 121.89722050432047, 54.728209921158005, 47.305001684085475, 68.8085525655267, 120.33851325420393, 76.91363234539789, 73.40821880661036, 47.396852344666456, 108.36077427106163, 73.68923387033114, 106.14449350822618, 81.54335551341462, 70.31938224670151, 58.803023935202226, 76.4264529245811, 65.3322538486428, 102.74312531453887, 82.7818147628525, 41.88483951632012, 52.02129645390934, 39.136331930535604, 87.58861790738092, 241.53743032658014, 104.0107661453121, 53.99867959202893, 59.18894179848156, 111.822655700736, 107.27576707298952, 40.11902560014746, 109.15470145444257, 236.47939006247418, 31.716192153924048, 98.4106933267744, 11.281630176945868, 139.70745957100283, 41.1173395552721, 13.802654696494585, 52.62649021796972, 61.62315004569592, 47.266190636936486, 56.96268094705057, 62.26325551642578, 79.88203738500289, 136.0590069598223, 61.97401746498972, 53.81047692043741, 128.30468146574873, 55.439247485955576, 79.69768769396345, 92.07428656720882, 58.02710596384888, 42.0671717556803, 56.46152834562566, 73.5393219710717, 38.18542240900255, 33.16831315015013, 63.938802900242905, 51.4601207392176, 73.10261461700203, 58.054202020961064, 58.84773931076223, 59.435256118791536, 54.920381889655, 7.278196139938598, 51.952953876848305, 75.26987724895349, 84.0515124188558, 53.784896595282554, 86.93606276730677, 18.65534463189007, 77.73272036403075, 12.525571989269446, 40.79328758790398, 70.49399375465121, 81.41435057146, 126.15969302510725, 61.7833934856785, 106.76159044573531, 27.554803109593184, 164.79409621873435, 51.81202820701773, 78.11439116332014, 104.68159417517433, 59.30552667783056, 79.36493745818731, 190.99877607985846, 58.731178658937935, 9.163717396534286, 73.40368902068718, 75.75462871405949, 67.8952686547854, 91.56175474693602, 38.63986365463857, 56.998070410376855, 60.70780042439048, 97.57543727148864, 113.96506552043795, 39.0872485450984, 76.34705733719566, 44.301666876565335, 71.35003847810465, 16.31419016970561, 114.1889687404366, 213.10164606220863, 69.48660540959206, 75.23076220824477, 44.363904815077014, 6.730570222868479, 73.25350800016572, 58.8674282571513, 40.63698893778971, 69.8156809137943, 102.54943325244608, 94.96913460641721, 94.48469236722313, 51.64244935439394, 189.12353045112172, 52.39317453832961, 34.413228612895665, 111.24165465836683, 49.50069176570959, 53.00071656871003, 55.54760069462058, 61.364758534347565, 61.544800753144806, 118.430157064406, 85.28684902123548, 57.188904272903365, 88.1573928618147, 68.39631920034282, 7.202178741471178, 56.06942374118284, 44.98195497613427, 36.16523916010935, 52.738500355134434, 101.75809631806837, 104.59605486314925, 49.47582362180202, 84.74086543352841, 73.7912985476167, 72.03437229240248, 59.23875433266101, 53.012405476687, 66.51062439928849, 67.84305740983878, 98.21209270277268, 67.69480134375246, 108.96629549527634, 85.80846102884445, 94.95854444203997, 194.3159844965083, 186.96195479141804, 54.58895776225684, 59.67597022660837, 216.0385248283692, 145.4986365105906, 63.99317996182356, 50.46411428312201, 89.3993464320784, 73.90288265773111, 141.10019304732927, 63.8909664040065, 46.499037773815814, 61.340931179448205, 52.348120244160384, 15</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>114.5703678131104</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>70.6198842424816</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>[108.6068115234375, 264.6373596191406, 69.32459259033203, 126.57628631591797, 132.0705108642578, 38.94092559814453, 99.71328735351562, 111.27193450927734, 56.55049514770508, 56.696563720703125, 180.89158630371094, 28.295408248901367, 224.11093139648438, 130.0493621826172, 87.89945983886719, 77.35881042480469, 117.35907745361328, 65.85430908203125, 78.04331970214844, 162.3276824951172, 88.30278778076172, 210.5742645263672, 155.2653350830078, 133.19747924804688, 8.667086601257324, 15.833881378173828, 127.92560577392578, 112.91738891601562, 93.48584747314453, 205.794921875, 113.50288391113281, 303.3412780761719, 83.7910385131836, 129.1955108642578, 126.75804901123047, 8.039782524108887, 53.826995849609375, 84.97117614746094, 90.39070129394531, 59.727073669433594, 250.5835723876953, 88.93842315673828, 314.9388732910156, 49.45927810668945, 46.25710678100586, 127.77964782714844, 54.94021224975586, 151.74012756347656, 307.373046875, 52.720924377441406, 64.7410659790039, 61.0701904296875, 64.38531494140625, 77.9032974243164, 67.28387451171875, 183.72756958007812, 81.19929504394531, 63.225669860839844, 287.4279479980469, 60.17253112792969, 85.62043762207031, 55.248558044433594, 147.58840942382812, 261.9767761230469, 73.41456604003906, 79.44871520996094, 53.42506408691406, 103.59230041503906, 69.2796401977539, 69.46863555908203, 54.90668487548828, 79.44036865234375, 111.39195251464844, 109.54590606689453, 165.46873474121094, 90.08563232421875, 181.379150390625, 73.4162368774414, 162.7654571533203, 127.72393798828125, 189.4305877685547, 74.01566314697266, 135.16981506347656, 96.91646575927734, 71.83689880371094, 240.59515380859375, 189.6961212158203, 184.6401824951172, 48.5579833984375, 38.78030776977539, 124.10890197753906, 91.1418685913086, 246.85169982910156, 61.136627197265625, 50.83909225463867, 66.56172180175781, 72.48876190185547, 84.29359436035156, 68.54208374023438, 288.2903137207031]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst02334</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 03:08:37</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>88.2121636610336</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>70.69438050211001</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>104.0531028738026</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>4802</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>[1.3307360286777823, 0.7316750700243062, 0.43243334088499524, 1.0184556735313746, 0.8306176887481849, 0.8720109597673333, 2.3115835407612337, 0.8511964410292991, 0.8759701627183736, 1.3189691209391268, 1.250284426618825, 0.8515716998416543, 0.19662553325651902, 0.976848477027281, 1.4367810143146633, 0.8488228398847576, 0.16702939288881283, 0.9058797193548253, 1.053191569402821, 1.3894358219703469, 0.9880447516564423, 0.7603382848695098, 1.4463537757630782, 2.669818559875987, 0.9716265465913989, 0.8628911887771685, 1.0193511361462828, 1.4419528107982553, 0.069849966711897, 0.6107652117642255, 0.6662207498947986, 1.0799487904130107, 0.7238005015017328, 1.1584847167277887, 1.5592168196133147, 1.3094548058062472, 1.730017959849686, 1.5600755608258325, 0.9732960158409997, 1.2580506574797508, 0.8713618949874342, 0.17015689254303817, 1.2760469433878077, 2.969107570739972, 1.4639374557501088, 1.1639420091595514, 1.4941790758276114, 1.127437305921625, 1.7461782522774167, 1.5938696160975474, 1.3815962441821965, 2.0612325594645418, 2.660246127673932, 0.7508205048077411, 1.4053573219168594, 2.026325763863169, 1.9314268341251761, 1.6530771563816031, 1.6214629644812593, 1.346889215765892, 1.0579157124968168, 1.299876868745128, 2.166014700033527, 1.896379116841178, 0.9705949774473704, 2.63222426511089, 2.5991442012581962, 1.273535628172792, 2.457532021278095, 1.6848205855766463, 0.4880842245977347, 2.583167547692669, 1.510367470020014, 1.3552385804986655, 1.667132932657096, 1.2054945237697658, 1.48500401995704, 1.5836050780651854, 2.2292437057299037, 3.7804401634367455, 2.310486230513221, 2.609960664825776, 1.8295616067427711, 4.531958383069713, 5.035146895135457, 1.6262034811858148, 1.8306183159805391, 1.6921670529936297, 0.26754468384961905, 1.2967089008345354, 3.693064662267623, 2.2431218893086626, 3.862281595332745, 1.4862377493636743, 3.2037931551940177, 3.062719104814307, 0.4633959483025119, 1.4589659185403334, 4.1345122989865715, 0.641129008944681, 2.106532914662979, 4.63341861891451, 2.2991304112547, 2.5125043078605844, 2.254523537786874, 5.849878853735235, 0.6898509117198861, 3.3291688321529223, 4.350814735722914, 4.512660103758117, 2.336390003990791, 2.529575020212933, 3.8805639917845025, 5.2032573782295515, 1.2221860227490384, 5.250766891951755, 1.65653264274507, 1.8669233361525137, 3.184497686570182, 4.281392351503236, 3.9746785884682336, 2.1066572538916843, 2.6942153849330346, 9.300016556018136, 3.8373681812340363, 5.8759708337743755, 4.599460462465125, 3.724530824294859, 2.4553502912913165, 4.013732041169395, 4.687546641196366, 4.3735277503177645, 6.477842068829489, 4.41222716408029, 6.999899708989648, 5.030990979432585, 4.653137198226555, 4.350983250831641, 3.132720589583863, 3.832269893710962, 0.6719658667147854, 2.8574402348395918, 9.5703079276784, 4.624327910975926, 3.852727858566043, 5.025994086485636, 1.6377009517152445, 3.0824626771991834, 5.836319866499825, 5.142666617078253, 3.0130901845174347, 2.804405824334329, 3.131633632249586, 4.967379559915429, 2.487773295579096, 2.4493106506323974, 4.241141994844355, 8.42487836951041, 3.0110807957603964, 4.797044564020044, 6.881474730784246, 5.902942789030658, 4.785837108363922, 19.18590891447693, 7.022536332538576, 7.202783804435971, 12.907656343307261, 7.66001513478226, 4.853570294081107, 4.59133532607347, 4.826563384775777, 7.673263138994233, 10.515728777936012, 8.250654902119061, 8.018572198877347, 4.80549392896923, 7.2051284877372, 7.9096374718570095, 2.735373369370283, 13.931051398065648, 0.39275938272030503, 7.286617882854834, 4.131495377974606, 16.63770028385772, 6.841143736731026, 3.729495125026228, 7.215261947361915, 13.655431279334463, 5.321470895302933, 6.897323916910344, 0.6068050135677818, 9.909237598051362, 8.2824630132377, 10.378284389234329, 6.725902178875925, 10.134603644468895, 5.327739702982353, 13.04361302328511, 10.713059424373268, 21.828375140517107, 9.84929302812061, 10.89147235085677, 15.968519372343165, 19.07040586310103, 0.570977545635863, 0.6760624245829402, 8.711881222063008, 9.346215012097895, 14.905107966293537, 23.80289680502158, 19.783335897299565, 23.481490870003395, 10.545689944301703, 7.1431658646732235, 3.028475059533066, 14.389776963769826, 17.21088732208807, 17.435517833709934, 29.351992692054665, 18.55782863192433, 4.124637020314068, 6.912502001844936, 9.118412206878764, 12.15781887984266, 13.698178829666007, 16.414698674538652, 29.934242828868094, 8.002596987516295, 7.5466390525201135, 1.6666705126303891, 12.46267017827219, 0.5581568563460442, 13.510409121727978, 17.208799078803825, 10.744897332303498, 10.790810255184443, 1.4489322710763464, 45.93479356976977, 19.337980193155822, 17.248283984219842, 30.07190222546545, 27.523672885126754, 18.022998450858797, 26.70838082812006, 35.664925532530965, 15.94559661304506, 8.655415233350785, 16.765828048130047, 14.437760957430243, 18.352127980917164, 24.10661889814284, 21.832649052936688, 5.309439845780167, 16.67002055065364, 23.362235202743584, 16.501540176073878, 24.159903364773957, 32.66137836728444, 17.60373459741227, 14.914584126599912, 11.401661311430866, 3.5194307977505335, 19.500348161636705, 29.394710281328663, 21.56480529027094, 38.64682132768282, 19.63138327596095, 28.11567739053609, 28.971244938081522, 14.177625757493752, 26.407595321825983, 16.615643009962966, 16.414019490772354, 7.680119731272053, 18.974769036348814, 26.22443479948294, 38.668303443531734, 37.7473850679582, 27.1039243770144, 41.27857876158575, 30.650056590304686, 25.03366311745718, 50.726925570281225, 52.74109261502441, 22.728082195558354, 21.535255363565266, 31.94835337531632, 10.571587871731026, 2.9158252287309523, 32.68058982398092, 20.68494518481187, 20.664500206308773, 3.1337053302034015, 16.304378801742168, 41.10383504499179, 14.172822012712453, 19.650007170158542, 16.351678129539525, 24.387960689408377, 25.905322868418565, 38.08641312162888, 27.660547765083972, 25.12255629330329, 8.608066645746133, 31.502399784363554, 3.820243988765576, 31.034322261639776, 32.39628159398352, 23.849665016864584, 19.786393685108308, 13.705042853941164, 4.322574089490125, 8.290398625011582, 43.463498400460324, 27.971527860795053, 58.70970686612089, 26.493168843470396, 50.56179504084198, 28.443293305623293, 25.739840476032594, 23.767407026562623, 28.159075535230194, 23.306570422619046, 23.597392207126966, 21.548022720823543, 26.494234699485183, 34.8749303912714, 5.260588419468802, 22.8138746142455, 31.500746022024174, 46.02659591835109, 34.873130474974666, 24.104594605725044, 38.505654418833565, 15.88376895946348, 51.793336233716786, 24.217636064552504, 18.491444469818887, 25.11546935418526, 39.51980556585544, 50.96247130239199, 29.258668029795075, 41.99334536702764, 22.37229350710982, 57.350723686067646, 49.168697442315576, 30.620185765516165, 31.670014955644817, 54.61249657979156, 45.63763072350134, 48.871158965271796, 47.03960093358004, 51.579693454598626, 35.53663078482233, 56.440888172623865, 53.84268095219887, 51.79823768724462, 36.963796242946145, 53.06551182330419, 38.134098450525414, 47.91017333528837, 6.089367934581785, 35.86641522143967, 40.95807866577535, 2.7066760993860584, 66.13584127029715, 54.08427289122012, 56.565915624968376, 61.94883692111169, 53.405767836364184, 68.56581149791421, 6.964884121301384, 2.1540039058111287, 2.3901101795999606, 28.00305764153274, 28.48524894766699, 53.64657880587982, 49.23275727577874, 23.629969099141846, 26.247075055276387, 55.07379023185345, 35.14004999947408, 59.30076082680933, 19.582360261958886, 42.1284673747313, 73.81912142917085, 41.634440316333524, 76.02243508430428, 51.799535012210825, 36.56533905811139, 129.84898747825486, 33.04394210184529, 64.82372418578247, 39.19748431032281, 3.354287041506587, 51.82902007641064, 40.073094877926614, 58.07885621657471, 7.867924828434659, 59.767952012279366, 27.16499277536331, 39.65467334255472, 79.42050943671245, 7.525822792361685, 63.800772965864645, 45.35393149138274, 60.697882451755994, 50.834420533270624, 91.20171908421717, 54.04156286163159, 22.124946591691202, 34.01965152521678, 42.99459790198724, 30.059107839092146, 29.33214868096571, 81.40863314916045, 10.018178516562019, 5.075784473410272, 35.28630815502967, 52.11114949961495, 31.193685289952914, 28.199869484222283, 47.76109776180827, 27.22749408868803, 39.39658391125501, 86.26387677568353, 33.06031960057883, 53.26105179294101, 47.28463488140099, 48.315937315351206, 68.608085962188, 37.939919491864764, 51.27960425769604, 45.13038071508314, 22.086385328363733, 52.18371930681975, 27.65061666445079, 63.38313649418507, 53.07857493917784, 38.77218833521568, 51.15253890522618, 4.225490054154869, 25.143966231083088, 88.27207814530927, 57.271962794969156, 53.21479591934208, 39.70925866494923, 38.495457386528045, 86.63811305827333, 57.880439954075264, 41.603676915153294, 40.43656417337775, 25.751491846549012, 44.496453825824105, 75.97364895037244, 40.99070286255085, 28.90677788677706, 40.46186462757459, 31.651591004447802, 56.886210963219916, 55.50945419948568, 63.34927658215432, 29.85783341328558, 42.92490851452383, 41.709243112308876, 73.8701225831491, 66.88640228604832, 67.23368639390546, 35.08553047827833, 96.3844153590982, 26.43775806920536, 32.54851964320772, 63.75202859382942, 42.29235600543911, 119.28609644932556, 133.78548912787124, 32.32247950264847, 28.615302434872635, 44.23288045077292, 54.11886400765253, 43.792869201425496, 56.28043057695303, 49.313273235888836, 63.019665841473746, 64.40896476360712, 57.87899585575206, 75.89793945578562, 91.95715071236823, 40.73654390298296, 39.76028736735457, 34.80151465789554, 22.979917953440626, 100.71257127403427, 75.67916914353657, 62.72483093623645, 82.56119406145194, 38.3077312798933, 85.93702362734973, 8.005798035633452, 45.9792664758794, 75.46453357819041, 134.1474929901825, 59.548120752577304, 36.82312394549021, 34.78682625054038, 43.555330755068304, 58.093111268725906, 37.79180423318603, 47.895447847632525, 39.63782187430856, 47.74396150327787, 74.93913217410554, 73.00049152086909, 64.55827791565034, 76.66652875984991, 48.764772435288606, 45.95297324384632, 40.45474854294258, 36.66907907231009, 87.96744487090241, 77.62849744303311, 42.129293747861574, 47.322529237456656, 100.6382082040701, 45.18432200333547, 131.52203925815346, 91.14239317281367, 113.98404863486014, 7.830934190417861, 52.21507412084996, 49.63374759691475, 35.74892414964621, 117.63557870774146, 41.674434429463176, 42.63651540709462, 53.95155144511507, 24.57419357438652, 46.80057296740977, 45.01398900611657, 69.124951581978, 46.23958486661393, 55.24537012500969, 45.38463149327326, 31.422468794501196, 86.80888335377249, 56.5341269038464, 45.323086497149184, 8.589243185513682, 43.039003266832346, 66.52097534394466, 38.039239123526066, 47.37124277555786, 107.25102957706497, 98.76389334812649, 8.990513849316011, 100.87116497356186, 68.77991416314029, 74.3259474977641, 76.02910359612862, 42.96928815289678, 49.34399407068357, 47.62571706364177, 178.23216100940763, 69.66428755498936, 36.873880406967125, 46.84052641325732, 71.98367199876982, 57.504667074673044, 98.8192456471682, 55.679885727248646, 52.059457286593734, 29.311241983469138, 49.578501876300614, 43.64529748128164, 40.47674212328997, 51.33803887938489, 56.35524334708828, 135.2617257258111, 83.95626860921246, 46.26951024414869, 101.2912991475527, 10.281150481672544, 106.63779836342741, 75.22931981005183, 101.80984343114311, 39.424944923816135, 155.19013344313322, 59.90064888668915, 4.916045169671053, 77.37686915921165, 72.20722969665493, 100.54755695065897, 44.37179653450758, 74.85506302451373, 41.429176023935575, 109.35282870619243, 42.099656725826485, 68.69922942572312, 62.785173117253876, 76.63403495852269, 62.630251214470704, 66.09624133248433, 115.89726479099892, 54.82105749838799, 65.84927139272008, 47.432789329710765, 71.62355600028053, 73.030589623896, 47.20378110522817, 47.91266761782051, 46.29906926025711, 76.29309340726999, 7.4962288191533535, 79.01283435446315, 73.05916257074901, 130.28305357380515, 47.413679261723686, 66.78281819206173, 51.56019723886244, 126.1396271699352, 38.97095105699142, 51.49281848220286, 85.94896067854887, 69.44673622393682, 64.72526211618491, 48.94221498786334, 38.89404434091635, 90.24456267566558, 48.354536303928704, 113.21764427820075, 79.70824678930269, 177.04276018751915, 100.17902464554356, 106.99914824204244, 51.83006400026452, 52.383837579739186, 48.258892688869366, 90.06403467484158, 43.891479398069556, 87.40962875777888, 78.39254871435959, 66.73654895816063, 128.84364337296057, 12.730795748138368, 81.85946051547447, 82.32378454004201, 52.05610793556789, 99.38874156930692, 50.119000223846264, 43.07167600870211, 144.23613256018106, 58.69233547301135, 80.08057630293312, 30.70018549543697, 42.329180318187504, 68.38014691837671, 63.14107212785424, 46.80695653125042, 103.54492218859362, 64.20505233905764, 49.50613579885323, 80.06890392300697, 54.7631148849819, 53.59467738729823, 47.875156811276135, 66.27625785313451, 62.292475661193784, 125.30301065729661, 38.858519336614194, 67.61223746925728, 56.26130906253813, 52.38141819735774, 94.7705991186334, 36.08248001548406, 125.69342050075366, 175.17608474861268, 4.654722592157494, 51.266511353404184, 51.54108233534085, 34.75601084118173, 108.03597395308543, 70.99565409493366, 47.53174839197151, 69.04890610324806, 44.383997334316284, 57.21284758461228, 134.3809550065529, 129.4177152754204, 81.71757105989026, 58.98177400868787, 63.96324897624391, 64.76050137960242, 91.64367231804331, 147.12968814349887, 81.78778088690699, 56.04545584182486, 30.714114313678877, 62.190357956268976, 103.17017981853002, 79.71290596163124, 85.70278186729382, 86.65743954860098, 117.3601122573583, 58.19931856094444, 141.2669472853507, 37.26084326079622, 85.16232368955738, 69.63301700954962, 54.662181900171845, 75.80142583009288, 65.63112462884094, 7.144050447990717, 57.11863772140898, 49.490074923443544, 49.64635353843581, 68.53084493814862, 56.60341973763959, 111.17167009328509, 49.38973127101571, 53.182101985621706, 53.67178010278906, 5.658205703144828, 46.50978525311678, 66.52469243184888, 73.48272522505046, 33.356534777290584, 76.44661694921598, 75.31198281533736, 81.57454357960681, 51.74725266445659, 66.59813188233707, 40.230795097635266, 66.63580854267896, 66.31983879554976, 75.5697688078968, 79.36791281169572, 51.057088121358426, 50.24490108811203, 53.72128345971203, 76.1797061418084, 135.86804971098124, 73.41836442192852, 92.89109490667147, 58.03464205691034, 122.15955971818025, 59.923433202980554, 84.57091945467995, 63.524573445428246, 135.71644192619468, 103.11374006209367, 66.56618331914683, 84.86311732373319, 61.294330552145766, 47.231441333584016, 48.2240255848356, 196.8892834759756, 123.9091162270173, 42.27248361713703, 37.23365172575312, 71.92539402979759, 81.39029352704345, 71.86928183072152, 80.03549671391691, 56.919428779772666, 70.35283328953604, 56.64463992552856, 83.46816140370319, 36.670685948523584, 53.065055504850136, 184.55824776669087, 74.24238238376103, 116.91508262131123, 41.343895719426534, 50.71352910215558, 79.6194911986287, 51.43330792586719, 60.65836392651609, 60.64252567533391, 151.35029333089236, 63.158518228491246, 55.84242745993467, 63.65711207281307, 123.25724981226891, 75.79849207693587, 133.44836863968015, 41.76806375676781, 71.62024007168004, 43.439670754585606, 50.26569222848351, 45.8446404461875, 68.77480954890383, 46.49001396806361, 121.69118483521942, 91.44760832555615, 62.43249875619645, 82.63406313868167, 58.60844429575661, 129.2257068509989, 54.295984395365636, 46.64984619965664, 154.08874791775904, 44.25116089574397, 94.30353205706268, 166.03877231878445, 123.87360306467508, 42.594319028683, 131.58844107879233, 45.7610036131184, 102.70229740627605, 50.516514710010256, 61.07985877895124, 5.20957126127509, 62.69821821325132, 104.38688421318622, 15.87189876323087, 130.18717356161477, 69.77473264198582, 74.25190998386392, 78.18559018747682, 46.42950000262713, 69.15979278318198, 196.91459484355286, 95.60399139265448, 84.3641081580071, 68.23887208214384, 77.24745304212162, 104.31331813167071, 49.075614927981476, 52.470996659487035, 91.18739599332109, 62.83210319091364, 136.97261011794726, 75.76983011337508, 99.58123106220921, 59.82824064055147, 55.24169333013009, 68.96176295542999, 54.5803692024647, 62.26305324607175, 69.18951098766155, 90.68759021288618, 55.845799365064074, 61.679793607331035, 44.19443158131637, 44.42441490157022, 58.602087472836764, 70.7346655327084, 83.31854017512022, 42.57797673139929, 9.00213998392358, 55.702575196355795, 54.37869428156453, 12.857377236801758, 16.572472236391807, 50.87023677784335, 58.08054757911747, 104.86058866359531, 6.653446013301789, 63.89219956479629, 38.032518112995575, 61.63268300005054, 49.17375578581074, 43.14284342305389, 53.28987791889029, 51.991143808139945, 52.609563652379094, 123.78529119204524, 82.96265687793503, 76.72347809387489, 84.51263810796716, 114.46721757938386, 40.386529586174476, 128.3701682141796, 43.015601845849154, 87.02051099785497, 48.52830517278191, 69.87625759399828, 126.74858324209357, 6.415863985282482, 157.28978793663083, 118.96936296398863, 64.1146667042797, 64.7133416569059, 175.33300463841647, 49.82031644829903, 44.56154248024009, 11.439085989865646, 110.69280731292896, 56.180821812489505, 56.24573299740506, 65.51708446583838, 43.136923765265585, 51.00577037066256, 101.9295036445867, 7.977455552728592, 44.42290923744476, 86.31194021105138, 87.54819685083842, 55.427015943078395, 52.01122248367663, 55.84122889646054, 18.28685375120388, 53.79192858662054, 89.87791063011449, 41.429067982618854, 42.45930396550392, 111.10472228581456, 33.77810606556752, 69.25767358062141, 93.53208508035155, 51.93925717142277, 37.07263829233114, 50.95768534572541, 38.865296815158985, 49.302305852915616, 60.67538103255352, 49.37000796487904, 39.73854863163332, 50.16055475772091, 82.72534521676934, 98.28647437140775, 129.56020209147158, 57.056242318808884, 39.79542032735574, 56.54184390277811, 185.23761525293983, 49.483974787138955, 52.37824012587021, 80.59856875588218, 51.5368557407551, 46.26775289872164, 107.09559817434148, 59.56439041392996, 58.429140995523376, 187.1720039726225, 59.120477471009046, 5.078917205726709, 78.05713793590819, 78.40046090121677, 51.55084106051872, 133.61412546924544, 101.79540260062612, 107.15204868650392, 65.21999917049314, 48.69329301509215, 5.632966301440356, 11.641862817048203, 56.36102713971964, 124.48927108824957, 93.7532251598533, 109.58685374699374, 72.61979663583496, 50.62606996297809, 119.52992072888453, 52.48805960709104, 57.46545753273607, 84.1469504823595, 72.98312252976835, 4.890478103814458, 67.40397665519473, 59.51976257382287, 63.08044253762633, 54.313198071721395, 101.25955016700158, 5.965881287774756, 45.85877128630186, 100.53055067301568, 46.96845876617058, 82.70741438230489, 64.99337243205541, 119.92543068286936, 98.91208840221609, 113.21995682459266, 53.157661548917424, 67.54455288390467, 54.57227626736839, 53.04111486827835, 110.88751199976471, 55.635451685709796, 52.36489169919186, 49.76867429715769, 89.10006010810807, 82.08594551728187, 69.7352142982024, 91.06333955707056, 5.839940857384058, 91.87272182367563, 139.5011286415495, 55.48560370128029, 67.48651389361203, 2.705542303797278, 67.21609513533124, 90.61372545563397, 33.90599394729186, 4.2295369733977575, 52.53154725356688, 76.16532804552747, 45.51954673063533, 54.182667936248144, 48.37004815776794, 40.95033454675876, 68.18787064278102, 78.11024177095621, 47.816883300459736, 42.57205987320551, 54.911652306744735, 72.53458730554914, 70.10888636820218, 137.9118486972404, 75.87654796472435, 66.3000437502214, 69.55035034936053, 51.83415099761065, 50.01415974427971, 41.27167900617125, 91.75485682828882, 146.92522381209807, 56.14616455804252, 109.83856902377497, 74.28655447865172, 58.85367927323416, 82.48311270749669, 98.78957401222777, 54.37371123288683, 99.88676652230387, 126.15411616095078, 67.62841466224927, 53.91832916641735, 110.78406129358564, 61.61656079304018, 159.7045424346127, 99.21648805617225, 153.86775002516848, 82.67527841868248, 10.070038785114853, 210.88013480138184, 47.96057263424902, 100.89376736595926, 65.70115612470535, 83.8376784387611, 52.12380945349207, 76.3052299859632, 94.74684106636187, 52.61949706643401, 57.4749763737119, 57.06519298562854, 64.21587771965916, 47.53613094685697, 114.78203395802049, 139.89238373569083, 6.387749028544444, 62.697420313314616, 86.46367067103985, 53.62341612322651, 5.744813039394612, 138.08586434259175, 44.65967398273037, 198.30067588459187, 77.47239991192527, 89.43110233872332, 183.0323547704517, 61.47312126870804, 66.15731908030615, 69.20681987028804, 67.83439841336916, 11.441765259026889, 257.0710251035338, 140.4681998717608, 184.82735043522828, 193.92662599658541, 50.507168837259606, 82.2911969331876, 61.810880699950296, 32.859870918153504, 62.92550918084075, 30.173653116736833, 193.46125498218845, 51.289660884545945, 138.20525090978165, 73.54062269013045, 79.02135167758915, 99.2702431662168, 62.44529344308098, 54.14797207979674, 106.3558354841856, 200.81072504742295, 57.53247618261659, 48.305518191477525, 83.57381535438236, 8.307698714382045, 96.86392809253223, 43.39066157865638, 84.53772814405322, 59.00849214031635, 114.25212687604305, 62.43665196027284, 60.193626827208135, 315.194482692556, 56.8889008869879, 53.03912823546632, 47.92272854763352, 75.0625729589379, 73.41602604613405, 58.66395378041421, 9.70165806329122, 47.86204874583888, 44.678860126895515, 56.861128994793496, 136.73925314095086, 50.95198968211774, 71.52939077206929, 80.19076570871215, 10.473139488728863, 62.57461175658899, 209.61671336422756, 56.128007492087875, 68.94778777717535, 45.244487657489785, 58.3865281627285, 11.063554421823518, 55.97094750712567, 88.80121830895733, 46.05810253429422, 71.94373206291604, 77.06172079096442, 111.76756720437297, 40.8705323813961, 85.59903273369748, 70.47523756531801, 93.42951332100694, 68.45810294952118, 62.26079007928801, 111.74782477837779, 121.67195417371869, 91.54490609778702, 53.995650449885254, 78.11383101379273, 18.322985331965917, 55.34848697735097, 135.73313773173263, 90.94284184457915, 79.51555780879941, 69.35059371719758, 56.71578522461798, 230.41562479489804, 70.13098782124017, 50.76511437908028, 54.580247933881544, 58.52603706634559, 69.48830604606744, 63.72563205452962, 224.71240785207922, 89.42926523831773, 61.70926409043107, 59.832611114254306, 109.0285264747337, 44.60070668209965, 173.3242720058865, 44.207949472704435, 148.26499429204165, 104.76635768079858, 49.69275479448566, 37.192581529240876, 58.241225910301594, 168.35229241149514, 89.51369791913739, 52.99482445599818, 39.25653562557272, 74.78318068583954, 126.99035802678159, 125.0040993011321, 106.41296389492047, 73.08332885431706, 83.82583420768331, 118.68679399573662, 102.24260544313982, 64.92237262095249, 76.58270824756205, 43.96420124491884, 49.03363863044414, 51.207717399803606, 75.7845601729576, 51.711708146120216, 58.21866992058754, 92.46992725839814, 49.14884603330188, 31.479398640218744, 70.65229179893407, 54.36970783426968, 66.75088090537228, 52.72130122240171, 9.33044871252088, 74.93244027103621, 270.38839443817386, 68.3603627950762, 54.84024422412204, 51.351181407896995, 44.9480469313116, 50.807935301624966, 74.30487441666128, 54.0507185077086, 125.59750253055358, 130.5168927787889, 6.4719543913366975, 153.85835989419016, 65.97440461521231, 76.6136548843595, 34.655117721643414, 75.24650738298376, 57.017000093055245, 43.912010792545345, 78.85391945349335, 85.41567795770555, 73.02853992626338, 51.44240787994376, 56.086707637047034, 52.60411834132156, 65.32743548876921, 52.95978204602365, 74.15269260323922, 56.784999184724754, 50.82582079616693, 9.976929015434216, 148.26260045003178, 75.6719957226835, 128.8869606657227, 189.89796929446447, 130.53046506557777, 97.22678954028643, 117.99666761268853, 54.35749879203515, 195.1486584158782, 93.61391006040292, 70.5108097488288, 62.40271921434969, 82.77870086593987, 75.0820881187755, 132.84628098018234, 78.09717467413923, 64.14716082491266, 7.334621495655779, 82.83329655980255, 82.72855447912123, 48.24906345268004, 68.8797314137592, 70.90228255264151, 37.29168408778181, 119.41351660165739, 73.57042205496113, 42.87452643081992, 109.29848440378015, 146.43262040230158, 66.42801492031317, 149.96264939291183, 127.67635768289954, 156.46023398201234, 82.37439300073841, 147.41394396539476, 7.556082057678923, 60.75070041794793, 58.65778381579829, 74.28588987960362, 98.01652456723232, 62.02877993756914, 9.049312835292529, 92.353892203127, 123.56981353263042, 111.08461314970651, 43.25993705745818, 86.55809137320492, 50.28677255938186, 61.38802265183824, 66.14453595445842, 73.73382940529692, 75.88060137539752, 45.95377759886986, 89.74437585701475, 90.75361513151243, 81.41018914690892, 80.61992214060727, 67.9256532444962, 179.38978739060542, 72.67425591376721, 253.53835135391046, 168.69575682517177, 57.698055451781116, 76.30170990194742, 48.70761272100958, 52.90720971977002, 147.22468490019128, 180.09196538971082, 45.479726790740905, 91.33410917965882, 10.89856785095373, 77.6197985611808, 75.79386018524886, 62.57591236534777, 49.13413287906949, 83.51012174354457, 142.82873346229283, 11.06544861706741, 82.17883313335342, 79.73562903909944, 55.17466993457949, 61.20351699063827, 71.31969626158332, 219.43462726836512, 73.6489128861659, 44.760104020463224, 142.20175643709695, 83.68956649724986, 10.636313738306182, 48.81073825637362, 106.89676907813681, 149.56294154918024, 75.1607592702086, 164.86272639779352, 57.67907057861497, 55.37832864033532, 64.23541915179169, 92.01164612191836, 216.39050537236244, 72.4861833770427, 155.6153745832823, 343.48808727338866, 9.932249627805184, 65.67628290073367, 65.54007169854566, 68.44349395741982, 121.53690993090514, 50.9848437341162, 36.58671113547033, 14.00693010489785, 59.162089083087885, 98.78912507721522, 21.86240869764949, 45.96783900566857, 68.91054331039037, 52.604764410903734, 101.19867618985637, 38.470876637181725, 156.78522528186068, 72.50532588616198, 131.86874872433745, 59.97348116876948, 42.09693180882272, 79.66943633563315, 54.44109845394525, 123.50395016427423, 57.02354650566139, 45.73117634453997, 58.14110205153443, 35.3253357880876, 70.4818264091983, 119.3720557258765, 114.34521724976724, 88.85153894785991, 76.13286106388557, 50.04730616458828, 51.43286747462839, 77.84794864953454, 36.76259150783592, 67.63671103903118, 7.184259503720576, 73.96722682870748, 50.77026956142646, 52.70284595483175, 65.81699331434284, 67.09872795171489, 113.26126830209483, 77.85007676980538, 67.80721807068088, 146.50615432573497, 62.499450870803756, 48.601210484620616, 132.26473277633187, 36.562698048149066, 50.28568591789971, 66.38689127021213, 72.94749021530848, 107.22338472972861, 47.82250235400054, 53.79454838321496, 56.034703368892124, 58.64278402115005, 132.45982551701826, 78.16426780397987, 58.49691173296472, 50.79351977192079, 44.852221623616465, 38.10558696495363, 86.81004399396723, 103.06930687312789, 100.51584584363444, 72.93965308699586, 47.029864343500805, 87.22046675660918, 107.41070015584057, 61.1724899491088, 44.05756009486308, 60.80226325427663, 175.08762929704736, 44.57292138988164, 55.629390149088394, 75.1580973941446, 62.23613063927368, 142.14221442092088, 148.10164991002554, 59.387927493047535, 87.03168257718167, 50.10514859301469, 62.16022139588792, 50.52585118047119, 138.10796215481517, 53.124309095806716, 134.9563345377955, 42.29936324035564, 104.42273909814429, 90.42017324967128, 6.900363215614115, 47.09494003565658, 64.15254614602202, 171.84843343189075, 159.6822702999537, 49.1312696061238, 16.591167268810903, 98.87501258113754, 39.467522318196096, 41.65233258742249, 81.78669563868131, 37.00536866029402, 64.53439051464227, 7.750633991082928, 68.04252415791909, 54.242810948477604, 66.57103811661898, 49.36032395201977, 83.1828281119561, 76.14591267887246, 69.18629363556228, 135.66526400182536, 66.18354278936717, 69.1406528339002, 103.63313392942139, 99.1711940776353, 72.32670917379575, 77.83728770546399, 188.0496465184731, 111.97369025091638, 53.43944981320434, 122.14124135332985, 86.57218829575098, 100.35229334087316, 61.511756104990965, 73.05112226034096, 56.28374484867633, 8.051149966677372, 55.27407329776266, 60.12057297051318, 68.30936882806931, 54.59720503624102, 115.38055538958886, 50.021779584186696, 59.50450327950656, 56.219395592685245, 134.730090326683, 34.97441579085067, 154.98621783600112, 5.636652231613689, 138.108311152336, 208.2981176451514, 84.47163940033865, 87.49514617221682, 80.40939205971746, 40.74997068649132, 60.218742352398905, 96.07683034252717, 72.26357078804256, 53.3036378355605, 84.147195023083, 60.79835472592156, 121.37421766952855, 45.45911931666443, 22.408673808682146, 52.37694888476434, 90.36840007400271, 41.29515883660846, 65.5765477308096, 54.0849564723696, 88.96743959604318, 11.450517123978154, 49.811453091921166, 65.93488412756709, 63.0847454797584, 69.36710953403674, 60.43996791656512, 79.2374234589947, 6.481169062563408, 65.19601153762291, 11.823696909393904, 212.51960867959392, 67.4965791930168, 164.05352338406868, 218.72206859810086, 111.44066997332433, 40.71681805701172, 88.3565087947895, 51.06546327378949, 166.3591702598455, 69.20282604457027, 62.94506428493201, 56.203173164418814, 89.05606925457282, 87.07276511140775, 61.166382001521534, 12.429226461154844, 161.39361311139427, 21.416051529329934, 56.89011625192939, 131.00389797819184, 58.3233994590952, 54.91110206561417, 88.00040416028385, 62.13351488195473, 58.71174154898011, 56.85259547661975, 55.07113290224644, 63.62882477089773, 62.53846241387123, 79.46150253153567, 7.763815670453603, 116.97862593777316, 61.244447857079926, 63.274720114128456, 39.29763074181344, 128.99002242194902, 195.62767771225523, 58.94878789295443, 63.72380694456323, 114.56915758603924, 68.08376629398246, 76.25524463880488, 61.10118422248652, 66.65058548002072, 60.549796527665514, 55.79436749240096, 80.32083863381003, 65.94484864321467, 52.60639846614065, 52.89915217571819, 92.21932732659177, 75.29981344907385, 190.47660412692343, 48.166185549038225, 76.9444132104601, 54.04570775646508, 5.737570900595488, 134.81444882440536, 59.58540059580896, 68.14756709202825, 124.19182024828432, 81.37826424956249, 8.256012463175349, 58.08094560001048, 64.63996368305621, 58.84355440494801, 50.844530456804016, 52.34650097949688, 59.20355958942793, 86.39291898425112, 76.62606797095088, 105.51999457439513, 70.00941820230514, 100.84264171512767, 11.040995454211604, 49.963020269836115, 101.68601085731726, 65.52975381659303, 66.97727051539833, 10.205238339086796, 50.357483037619716, 88.85511431883968, 52.747097148046585, 41.60296543206061, 35.53340081874673, 61.05011263458907, 70.06742389619613, 91.69200461795954, 107.85730740290667, 64.25312698501475, 108.80596697499112, 53.02780297466415, 102.09296020549924, 82.66230457411578, 47.9134820582951, 61.6732002694969, 83.19704135572493, 83.77110963341791, 80.79070114656515, 101.13912829655187, 54.295310915537684, 98.3427939332909, 149.47069997359975, 50.08452200921701, 65.0371376390537, 90.7210374436372, 7.459421247293797, 54.19042939408892, 171.84449858435593, 75.2785006201548, 173.53194948251664, 176.85432535493365, 54.977960465339876, 115.41548917694554, 91.50518262854509, 89.7763482008918, 192.102510787005, 102.38798657662313, 101.42718010172933, 89.01500193692647, 102.77822301633499, 70.65487954977142, 37.65359151982898, 11.196073636462927, 70.59146775414835, 101.65680181043922, 329.025192777616, 93.13377825967335, 174.68124183416026, 94.9049289914608, 57.26151925422006, 102.90562665449248, 142.96464261662683, 114.74969700199462, 68.77111507922017, 81.72796819172193, 62.08343414740279, 68.29481508643981, 92.35420858316621, 70.85665070206922, 127.69675496615407, 58.63034653200661, 48.57344794361623, 80.7969702181098, 163.19885638049365, 125.33630537726171, 60.43266991049768, 59.585377395325665, 84.8377349638571, 88.01555866935334, 78.18203573937836, 80.70768698672451, 79.10565194440744, 46.35672060627964, 52.026464055495424, 75.9098635676157, 84.83415408426079, 45.732292295371714, 61.352509284925134, 5.59350804525226, 205.83886301399363, 92.18840424122334, 11.91324398969094, 372.581577869248, 52.14416705613956, 41.86140420928308, 71.42515284572656, 59.355739575695324, 128.64482725109096, 111.32909898845953, 141.36514114965937, 38.36951887181919, 35.295098283947745, 347.86552348103356, 129.3396617940662, 106.75602453478147, 170.16150393813754, 151.30194728130772, 20.33770244540384, 78.15647857426902, 59.42092027876061, 68.9614417837204, 6.819973217979373, 60.18874426482017, 41.67626382147197, 74.10417096754648, 47.74226324430292, 96.8038975011053, 83.41767968173254, 36.8744434511129, 57.37013793156611, 124.63727523484523, 201.660227286687, 59.03847447929734, 41.701710835478075, 105.7286337650499, 8.028119236485498, 48.45500202605524, 46.242</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>118.7441567134857</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>95.42599578171513</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>[87.55733489990234, 117.5550308227539, 136.6644287109375, 74.28791809082031, 318.12469482421875, 46.196685791015625, 131.4047393798828, 55.85951232910156, 20.313547134399414, 137.64471435546875, 66.30593872070312, 224.3693389892578, 127.88220977783203, 335.1879577636719, 84.29026794433594, 93.61988830566406, 48.28975296020508, 49.38071823120117, 172.2406005859375, 107.2049331665039, 164.33445739746094, 96.82820129394531, 103.06687927246094, 47.50446701049805, 61.86640930175781, 72.92346954345703, 45.947120666503906, 189.37484741210938, 80.42926788330078, 48.469947814941406, 58.88112258911133, 10.763513565063477, 85.81538391113281, 168.4691925048828, 41.5605583190918, 58.513824462890625, 74.5248794555664, 46.21141052246094, 477.1987609863281, 60.74861526489258, 97.2738037109375, 67.18521118164062, 39.81300735473633, 109.00031280517578, 72.94335174560547, 59.80903244018555, 153.4866485595703, 76.41046142578125, 66.68016052246094, 119.09868621826172, 70.84064483642578, 38.38438034057617, 85.84701538085938, 161.4570770263672, 65.34859466552734, 37.39012908935547, 50.00249099731445, 12.64061450958252, 93.44999694824219, 130.5547332763672, 145.69967651367188, 109.36820983886719, 88.5381088256836, 87.10613250732422, 115.82258605957031, 78.82489013671875, 149.53147888183594, 89.40764617919922, 323.8999938964844, 102.91506958007812, 50.36025619506836, 195.76361083984375, 81.66316986083984, 64.90062713623047, 143.50656127929688, 332.9368896484375, 180.3920440673828, 25.930421829223633, 71.02539825439453, 183.92498779296875, 171.95013427734375, 192.60806274414062, 52.57180404663086, 392.47576904296875, 209.46255493164062, 231.82615661621094, 53.44449996948242, 47.543006896972656, 490.4530944824219, 187.98880004882812, 46.161556243896484, 172.3901824951172, 126.80047607421875, 75.89229583740234, 422.9801025390625, 48.77598571777344, 148.1776885986328, 36.04082489013672, 98.04698944091797, 11.879032135009766]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst02335</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 03:15:05</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>88.2121636610336</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>70.69438050211001</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>104.0531028738026</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>4802</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>[1.3307360286777823, 0.7316750700243062, 0.43243334088499524, 1.0184556735313746, 0.8306176887481849, 0.8720109597673333, 2.3115835407612337, 0.8511964410292991, 0.8759701627183736, 1.3189691209391268, 1.250284426618825, 0.8515716998416543, 0.19662553325651902, 0.976848477027281, 1.4367810143146633, 0.8488228398847576, 0.16702939288881283, 0.9058797193548253, 1.053191569402821, 1.3894358219703469, 0.9880447516564423, 0.7603382848695098, 1.4463537757630782, 2.669818559875987, 0.9716265465913989, 0.8628911887771685, 1.0193511361462828, 1.4419528107982553, 0.069849966711897, 0.6107652117642255, 0.6662207498947986, 1.0799487904130107, 0.7238005015017328, 1.1584847167277887, 1.5592168196133147, 1.3094548058062472, 1.730017959849686, 1.5600755608258325, 0.9732960158409997, 1.2580506574797508, 0.8713618949874342, 0.17015689254303817, 1.2760469433878077, 2.969107570739972, 1.4639374557501088, 1.1639420091595514, 1.4941790758276114, 1.127437305921625, 1.7461782522774167, 1.5938696160975474, 1.3815962441821965, 2.0612325594645418, 2.660246127673932, 0.7508205048077411, 1.4053573219168594, 2.026325763863169, 1.9314268341251761, 1.6530771563816031, 1.6214629644812593, 1.346889215765892, 1.0579157124968168, 1.299876868745128, 2.166014700033527, 1.896379116841178, 0.9705949774473704, 2.63222426511089, 2.5991442012581962, 1.273535628172792, 2.457532021278095, 1.6848205855766463, 0.4880842245977347, 2.583167547692669, 1.510367470020014, 1.3552385804986655, 1.667132932657096, 1.2054945237697658, 1.48500401995704, 1.5836050780651854, 2.2292437057299037, 3.7804401634367455, 2.310486230513221, 2.609960664825776, 1.8295616067427711, 4.531958383069713, 5.035146895135457, 1.6262034811858148, 1.8306183159805391, 1.6921670529936297, 0.26754468384961905, 1.2967089008345354, 3.693064662267623, 2.2431218893086626, 3.862281595332745, 1.4862377493636743, 3.2037931551940177, 3.062719104814307, 0.4633959483025119, 1.4589659185403334, 4.1345122989865715, 0.641129008944681, 2.106532914662979, 4.63341861891451, 2.2991304112547, 2.5125043078605844, 2.254523537786874, 5.849878853735235, 0.6898509117198861, 3.3291688321529223, 4.350814735722914, 4.512660103758117, 2.336390003990791, 2.529575020212933, 3.8805639917845025, 5.2032573782295515, 1.2221860227490384, 5.250766891951755, 1.65653264274507, 1.8669233361525137, 3.184497686570182, 4.281392351503236, 3.9746785884682336, 2.1066572538916843, 2.6942153849330346, 9.300016556018136, 3.8373681812340363, 5.8759708337743755, 4.599460462465125, 3.724530824294859, 2.4553502912913165, 4.013732041169395, 4.687546641196366, 4.3735277503177645, 6.477842068829489, 4.41222716408029, 6.999899708989648, 5.030990979432585, 4.653137198226555, 4.350983250831641, 3.132720589583863, 3.832269893710962, 0.6719658667147854, 2.8574402348395918, 9.5703079276784, 4.624327910975926, 3.852727858566043, 5.025994086485636, 1.6377009517152445, 3.0824626771991834, 5.836319866499825, 5.142666617078253, 3.0130901845174347, 2.804405824334329, 3.131633632249586, 4.967379559915429, 2.487773295579096, 2.4493106506323974, 4.241141994844355, 8.42487836951041, 3.0110807957603964, 4.797044564020044, 6.881474730784246, 5.902942789030658, 4.785837108363922, 19.18590891447693, 7.022536332538576, 7.202783804435971, 12.907656343307261, 7.66001513478226, 4.853570294081107, 4.59133532607347, 4.826563384775777, 7.673263138994233, 10.515728777936012, 8.250654902119061, 8.018572198877347, 4.80549392896923, 7.2051284877372, 7.9096374718570095, 2.735373369370283, 13.931051398065648, 0.39275938272030503, 7.286617882854834, 4.131495377974606, 16.63770028385772, 6.841143736731026, 3.729495125026228, 7.215261947361915, 13.655431279334463, 5.321470895302933, 6.897323916910344, 0.6068050135677818, 9.909237598051362, 8.2824630132377, 10.378284389234329, 6.725902178875925, 10.134603644468895, 5.327739702982353, 13.04361302328511, 10.713059424373268, 21.828375140517107, 9.84929302812061, 10.89147235085677, 15.968519372343165, 19.07040586310103, 0.570977545635863, 0.6760624245829402, 8.711881222063008, 9.346215012097895, 14.905107966293537, 23.80289680502158, 19.783335897299565, 23.481490870003395, 10.545689944301703, 7.1431658646732235, 3.028475059533066, 14.389776963769826, 17.21088732208807, 17.435517833709934, 29.351992692054665, 18.55782863192433, 4.124637020314068, 6.912502001844936, 9.118412206878764, 12.15781887984266, 13.698178829666007, 16.414698674538652, 29.934242828868094, 8.002596987516295, 7.5466390525201135, 1.6666705126303891, 12.46267017827219, 0.5581568563460442, 13.510409121727978, 17.208799078803825, 10.744897332303498, 10.790810255184443, 1.4489322710763464, 45.93479356976977, 19.337980193155822, 17.248283984219842, 30.07190222546545, 27.523672885126754, 18.022998450858797, 26.70838082812006, 35.664925532530965, 15.94559661304506, 8.655415233350785, 16.765828048130047, 14.437760957430243, 18.352127980917164, 24.10661889814284, 21.832649052936688, 5.309439845780167, 16.67002055065364, 23.362235202743584, 16.501540176073878, 24.159903364773957, 32.66137836728444, 17.60373459741227, 14.914584126599912, 11.401661311430866, 3.5194307977505335, 19.500348161636705, 29.394710281328663, 21.56480529027094, 38.64682132768282, 19.63138327596095, 28.11567739053609, 28.971244938081522, 14.177625757493752, 26.407595321825983, 16.615643009962966, 16.414019490772354, 7.680119731272053, 18.974769036348814, 26.22443479948294, 38.668303443531734, 37.7473850679582, 27.1039243770144, 41.27857876158575, 30.650056590304686, 25.03366311745718, 50.726925570281225, 52.74109261502441, 22.728082195558354, 21.535255363565266, 31.94835337531632, 10.571587871731026, 2.9158252287309523, 32.68058982398092, 20.68494518481187, 20.664500206308773, 3.1337053302034015, 16.304378801742168, 41.10383504499179, 14.172822012712453, 19.650007170158542, 16.351678129539525, 24.387960689408377, 25.905322868418565, 38.08641312162888, 27.660547765083972, 25.12255629330329, 8.608066645746133, 31.502399784363554, 3.820243988765576, 31.034322261639776, 32.39628159398352, 23.849665016864584, 19.786393685108308, 13.705042853941164, 4.322574089490125, 8.290398625011582, 43.463498400460324, 27.971527860795053, 58.70970686612089, 26.493168843470396, 50.56179504084198, 28.443293305623293, 25.739840476032594, 23.767407026562623, 28.159075535230194, 23.306570422619046, 23.597392207126966, 21.548022720823543, 26.494234699485183, 34.8749303912714, 5.260588419468802, 22.8138746142455, 31.500746022024174, 46.02659591835109, 34.873130474974666, 24.104594605725044, 38.505654418833565, 15.88376895946348, 51.793336233716786, 24.217636064552504, 18.491444469818887, 25.11546935418526, 39.51980556585544, 50.96247130239199, 29.258668029795075, 41.99334536702764, 22.37229350710982, 57.350723686067646, 49.168697442315576, 30.620185765516165, 31.670014955644817, 54.61249657979156, 45.63763072350134, 48.871158965271796, 47.03960093358004, 51.579693454598626, 35.53663078482233, 56.440888172623865, 53.84268095219887, 51.79823768724462, 36.963796242946145, 53.06551182330419, 38.134098450525414, 47.91017333528837, 6.089367934581785, 35.86641522143967, 40.95807866577535, 2.7066760993860584, 66.13584127029715, 54.08427289122012, 56.565915624968376, 61.94883692111169, 53.405767836364184, 68.56581149791421, 6.964884121301384, 2.1540039058111287, 2.3901101795999606, 28.00305764153274, 28.48524894766699, 53.64657880587982, 49.23275727577874, 23.629969099141846, 26.247075055276387, 55.07379023185345, 35.14004999947408, 59.30076082680933, 19.582360261958886, 42.1284673747313, 73.81912142917085, 41.634440316333524, 76.02243508430428, 51.799535012210825, 36.56533905811139, 129.84898747825486, 33.04394210184529, 64.82372418578247, 39.19748431032281, 3.354287041506587, 51.82902007641064, 40.073094877926614, 58.07885621657471, 7.867924828434659, 59.767952012279366, 27.16499277536331, 39.65467334255472, 79.42050943671245, 7.525822792361685, 63.800772965864645, 45.35393149138274, 60.697882451755994, 50.834420533270624, 91.20171908421717, 54.04156286163159, 22.124946591691202, 34.01965152521678, 42.99459790198724, 30.059107839092146, 29.33214868096571, 81.40863314916045, 10.018178516562019, 5.075784473410272, 35.28630815502967, 52.11114949961495, 31.193685289952914, 28.199869484222283, 47.76109776180827, 27.22749408868803, 39.39658391125501, 86.26387677568353, 33.06031960057883, 53.26105179294101, 47.28463488140099, 48.315937315351206, 68.608085962188, 37.939919491864764, 51.27960425769604, 45.13038071508314, 22.086385328363733, 52.18371930681975, 27.65061666445079, 63.38313649418507, 53.07857493917784, 38.77218833521568, 51.15253890522618, 4.225490054154869, 25.143966231083088, 88.27207814530927, 57.271962794969156, 53.21479591934208, 39.70925866494923, 38.495457386528045, 86.63811305827333, 57.880439954075264, 41.603676915153294, 40.43656417337775, 25.751491846549012, 44.496453825824105, 75.97364895037244, 40.99070286255085, 28.90677788677706, 40.46186462757459, 31.651591004447802, 56.886210963219916, 55.50945419948568, 63.34927658215432, 29.85783341328558, 42.92490851452383, 41.709243112308876, 73.8701225831491, 66.88640228604832, 67.23368639390546, 35.08553047827833, 96.3844153590982, 26.43775806920536, 32.54851964320772, 63.75202859382942, 42.29235600543911, 119.28609644932556, 133.78548912787124, 32.32247950264847, 28.615302434872635, 44.23288045077292, 54.11886400765253, 43.792869201425496, 56.28043057695303, 49.313273235888836, 63.019665841473746, 64.40896476360712, 57.87899585575206, 75.89793945578562, 91.95715071236823, 40.73654390298296, 39.76028736735457, 34.80151465789554, 22.979917953440626, 100.71257127403427, 75.67916914353657, 62.72483093623645, 82.56119406145194, 38.3077312798933, 85.93702362734973, 8.005798035633452, 45.9792664758794, 75.46453357819041, 134.1474929901825, 59.548120752577304, 36.82312394549021, 34.78682625054038, 43.555330755068304, 58.093111268725906, 37.79180423318603, 47.895447847632525, 39.63782187430856, 47.74396150327787, 74.93913217410554, 73.00049152086909, 64.55827791565034, 76.66652875984991, 48.764772435288606, 45.95297324384632, 40.45474854294258, 36.66907907231009, 87.96744487090241, 77.62849744303311, 42.129293747861574, 47.322529237456656, 100.6382082040701, 45.18432200333547, 131.52203925815346, 91.14239317281367, 113.98404863486014, 7.830934190417861, 52.21507412084996, 49.63374759691475, 35.74892414964621, 117.63557870774146, 41.674434429463176, 42.63651540709462, 53.95155144511507, 24.57419357438652, 46.80057296740977, 45.01398900611657, 69.124951581978, 46.23958486661393, 55.24537012500969, 45.38463149327326, 31.422468794501196, 86.80888335377249, 56.5341269038464, 45.323086497149184, 8.589243185513682, 43.039003266832346, 66.52097534394466, 38.039239123526066, 47.37124277555786, 107.25102957706497, 98.76389334812649, 8.990513849316011, 100.87116497356186, 68.77991416314029, 74.3259474977641, 76.02910359612862, 42.96928815289678, 49.34399407068357, 47.62571706364177, 178.23216100940763, 69.66428755498936, 36.873880406967125, 46.84052641325732, 71.98367199876982, 57.504667074673044, 98.8192456471682, 55.679885727248646, 52.059457286593734, 29.311241983469138, 49.578501876300614, 43.64529748128164, 40.47674212328997, 51.33803887938489, 56.35524334708828, 135.2617257258111, 83.95626860921246, 46.26951024414869, 101.2912991475527, 10.281150481672544, 106.63779836342741, 75.22931981005183, 101.80984343114311, 39.424944923816135, 155.19013344313322, 59.90064888668915, 4.916045169671053, 77.37686915921165, 72.20722969665493, 100.54755695065897, 44.37179653450758, 74.85506302451373, 41.429176023935575, 109.35282870619243, 42.099656725826485, 68.69922942572312, 62.785173117253876, 76.63403495852269, 62.630251214470704, 66.09624133248433, 115.89726479099892, 54.82105749838799, 65.84927139272008, 47.432789329710765, 71.62355600028053, 73.030589623896, 47.20378110522817, 47.91266761782051, 46.29906926025711, 76.29309340726999, 7.4962288191533535, 79.01283435446315, 73.05916257074901, 130.28305357380515, 47.413679261723686, 66.78281819206173, 51.56019723886244, 126.1396271699352, 38.97095105699142, 51.49281848220286, 85.94896067854887, 69.44673622393682, 64.72526211618491, 48.94221498786334, 38.89404434091635, 90.24456267566558, 48.354536303928704, 113.21764427820075, 79.70824678930269, 177.04276018751915, 100.17902464554356, 106.99914824204244, 51.83006400026452, 52.383837579739186, 48.258892688869366, 90.06403467484158, 43.891479398069556, 87.40962875777888, 78.39254871435959, 66.73654895816063, 128.84364337296057, 12.730795748138368, 81.85946051547447, 82.32378454004201, 52.05610793556789, 99.38874156930692, 50.119000223846264, 43.07167600870211, 144.23613256018106, 58.69233547301135, 80.08057630293312, 30.70018549543697, 42.329180318187504, 68.38014691837671, 63.14107212785424, 46.80695653125042, 103.54492218859362, 64.20505233905764, 49.50613579885323, 80.06890392300697, 54.7631148849819, 53.59467738729823, 47.875156811276135, 66.27625785313451, 62.292475661193784, 125.30301065729661, 38.858519336614194, 67.61223746925728, 56.26130906253813, 52.38141819735774, 94.7705991186334, 36.08248001548406, 125.69342050075366, 175.17608474861268, 4.654722592157494, 51.266511353404184, 51.54108233534085, 34.75601084118173, 108.03597395308543, 70.99565409493366, 47.53174839197151, 69.04890610324806, 44.383997334316284, 57.21284758461228, 134.3809550065529, 129.4177152754204, 81.71757105989026, 58.98177400868787, 63.96324897624391, 64.76050137960242, 91.64367231804331, 147.12968814349887, 81.78778088690699, 56.04545584182486, 30.714114313678877, 62.190357956268976, 103.17017981853002, 79.71290596163124, 85.70278186729382, 86.65743954860098, 117.3601122573583, 58.19931856094444, 141.2669472853507, 37.26084326079622, 85.16232368955738, 69.63301700954962, 54.662181900171845, 75.80142583009288, 65.63112462884094, 7.144050447990717, 57.11863772140898, 49.490074923443544, 49.64635353843581, 68.53084493814862, 56.60341973763959, 111.17167009328509, 49.38973127101571, 53.182101985621706, 53.67178010278906, 5.658205703144828, 46.50978525311678, 66.52469243184888, 73.48272522505046, 33.356534777290584, 76.44661694921598, 75.31198281533736, 81.57454357960681, 51.74725266445659, 66.59813188233707, 40.230795097635266, 66.63580854267896, 66.31983879554976, 75.5697688078968, 79.36791281169572, 51.057088121358426, 50.24490108811203, 53.72128345971203, 76.1797061418084, 135.86804971098124, 73.41836442192852, 92.89109490667147, 58.03464205691034, 122.15955971818025, 59.923433202980554, 84.57091945467995, 63.524573445428246, 135.71644192619468, 103.11374006209367, 66.56618331914683, 84.86311732373319, 61.294330552145766, 47.231441333584016, 48.2240255848356, 196.8892834759756, 123.9091162270173, 42.27248361713703, 37.23365172575312, 71.92539402979759, 81.39029352704345, 71.86928183072152, 80.03549671391691, 56.919428779772666, 70.35283328953604, 56.64463992552856, 83.46816140370319, 36.670685948523584, 53.065055504850136, 184.55824776669087, 74.24238238376103, 116.91508262131123, 41.343895719426534, 50.71352910215558, 79.6194911986287, 51.43330792586719, 60.65836392651609, 60.64252567533391, 151.35029333089236, 63.158518228491246, 55.84242745993467, 63.65711207281307, 123.25724981226891, 75.79849207693587, 133.44836863968015, 41.76806375676781, 71.62024007168004, 43.439670754585606, 50.26569222848351, 45.8446404461875, 68.77480954890383, 46.49001396806361, 121.69118483521942, 91.44760832555615, 62.43249875619645, 82.63406313868167, 58.60844429575661, 129.2257068509989, 54.295984395365636, 46.64984619965664, 154.08874791775904, 44.25116089574397, 94.30353205706268, 166.03877231878445, 123.87360306467508, 42.594319028683, 131.58844107879233, 45.7610036131184, 102.70229740627605, 50.516514710010256, 61.07985877895124, 5.20957126127509, 62.69821821325132, 104.38688421318622, 15.87189876323087, 130.18717356161477, 69.77473264198582, 74.25190998386392, 78.18559018747682, 46.42950000262713, 69.15979278318198, 196.91459484355286, 95.60399139265448, 84.3641081580071, 68.23887208214384, 77.24745304212162, 104.31331813167071, 49.075614927981476, 52.470996659487035, 91.18739599332109, 62.83210319091364, 136.97261011794726, 75.76983011337508, 99.58123106220921, 59.82824064055147, 55.24169333013009, 68.96176295542999, 54.5803692024647, 62.26305324607175, 69.18951098766155, 90.68759021288618, 55.845799365064074, 61.679793607331035, 44.19443158131637, 44.42441490157022, 58.602087472836764, 70.7346655327084, 83.31854017512022, 42.57797673139929, 9.00213998392358, 55.702575196355795, 54.37869428156453, 12.857377236801758, 16.572472236391807, 50.87023677784335, 58.08054757911747, 104.86058866359531, 6.653446013301789, 63.89219956479629, 38.032518112995575, 61.63268300005054, 49.17375578581074, 43.14284342305389, 53.28987791889029, 51.991143808139945, 52.609563652379094, 123.78529119204524, 82.96265687793503, 76.72347809387489, 84.51263810796716, 114.46721757938386, 40.386529586174476, 128.3701682141796, 43.015601845849154, 87.02051099785497, 48.52830517278191, 69.87625759399828, 126.74858324209357, 6.415863985282482, 157.28978793663083, 118.96936296398863, 64.1146667042797, 64.7133416569059, 175.33300463841647, 49.82031644829903, 44.56154248024009, 11.439085989865646, 110.69280731292896, 56.180821812489505, 56.24573299740506, 65.51708446583838, 43.136923765265585, 51.00577037066256, 101.9295036445867, 7.977455552728592, 44.42290923744476, 86.31194021105138, 87.54819685083842, 55.427015943078395, 52.01122248367663, 55.84122889646054, 18.28685375120388, 53.79192858662054, 89.87791063011449, 41.429067982618854, 42.45930396550392, 111.10472228581456, 33.77810606556752, 69.25767358062141, 93.53208508035155, 51.93925717142277, 37.07263829233114, 50.95768534572541, 38.865296815158985, 49.302305852915616, 60.67538103255352, 49.37000796487904, 39.73854863163332, 50.16055475772091, 82.72534521676934, 98.28647437140775, 129.56020209147158, 57.056242318808884, 39.79542032735574, 56.54184390277811, 185.23761525293983, 49.483974787138955, 52.37824012587021, 80.59856875588218, 51.5368557407551, 46.26775289872164, 107.09559817434148, 59.56439041392996, 58.429140995523376, 187.1720039726225, 59.120477471009046, 5.078917205726709, 78.05713793590819, 78.40046090121677, 51.55084106051872, 133.61412546924544, 101.79540260062612, 107.15204868650392, 65.21999917049314, 48.69329301509215, 5.632966301440356, 11.641862817048203, 56.36102713971964, 124.48927108824957, 93.7532251598533, 109.58685374699374, 72.61979663583496, 50.62606996297809, 119.52992072888453, 52.48805960709104, 57.46545753273607, 84.1469504823595, 72.98312252976835, 4.890478103814458, 67.40397665519473, 59.51976257382287, 63.08044253762633, 54.313198071721395, 101.25955016700158, 5.965881287774756, 45.85877128630186, 100.53055067301568, 46.96845876617058, 82.70741438230489, 64.99337243205541, 119.92543068286936, 98.91208840221609, 113.21995682459266, 53.157661548917424, 67.54455288390467, 54.57227626736839, 53.04111486827835, 110.88751199976471, 55.635451685709796, 52.36489169919186, 49.76867429715769, 89.10006010810807, 82.08594551728187, 69.7352142982024, 91.06333955707056, 5.839940857384058, 91.87272182367563, 139.5011286415495, 55.48560370128029, 67.48651389361203, 2.705542303797278, 67.21609513533124, 90.61372545563397, 33.90599394729186, 4.2295369733977575, 52.53154725356688, 76.16532804552747, 45.51954673063533, 54.182667936248144, 48.37004815776794, 40.95033454675876, 68.18787064278102, 78.11024177095621, 47.816883300459736, 42.57205987320551, 54.911652306744735, 72.53458730554914, 70.10888636820218, 137.9118486972404, 75.87654796472435, 66.3000437502214, 69.55035034936053, 51.83415099761065, 50.01415974427971, 41.27167900617125, 91.75485682828882, 146.92522381209807, 56.14616455804252, 109.83856902377497, 74.28655447865172, 58.85367927323416, 82.48311270749669, 98.78957401222777, 54.37371123288683, 99.88676652230387, 126.15411616095078, 67.62841466224927, 53.91832916641735, 110.78406129358564, 61.61656079304018, 159.7045424346127, 99.21648805617225, 153.86775002516848, 82.67527841868248, 10.070038785114853, 210.88013480138184, 47.96057263424902, 100.89376736595926, 65.70115612470535, 83.8376784387611, 52.12380945349207, 76.3052299859632, 94.74684106636187, 52.61949706643401, 57.4749763737119, 57.06519298562854, 64.21587771965916, 47.53613094685697, 114.78203395802049, 139.89238373569083, 6.387749028544444, 62.697420313314616, 86.46367067103985, 53.62341612322651, 5.744813039394612, 138.08586434259175, 44.65967398273037, 198.30067588459187, 77.47239991192527, 89.43110233872332, 183.0323547704517, 61.47312126870804, 66.15731908030615, 69.20681987028804, 67.83439841336916, 11.441765259026889, 257.0710251035338, 140.4681998717608, 184.82735043522828, 193.92662599658541, 50.507168837259606, 82.2911969331876, 61.810880699950296, 32.859870918153504, 62.92550918084075, 30.173653116736833, 193.46125498218845, 51.289660884545945, 138.20525090978165, 73.54062269013045, 79.02135167758915, 99.2702431662168, 62.44529344308098, 54.14797207979674, 106.3558354841856, 200.81072504742295, 57.53247618261659, 48.305518191477525, 83.57381535438236, 8.307698714382045, 96.86392809253223, 43.39066157865638, 84.53772814405322, 59.00849214031635, 114.25212687604305, 62.43665196027284, 60.193626827208135, 315.194482692556, 56.8889008869879, 53.03912823546632, 47.92272854763352, 75.0625729589379, 73.41602604613405, 58.66395378041421, 9.70165806329122, 47.86204874583888, 44.678860126895515, 56.861128994793496, 136.73925314095086, 50.95198968211774, 71.52939077206929, 80.19076570871215, 10.473139488728863, 62.57461175658899, 209.61671336422756, 56.128007492087875, 68.94778777717535, 45.244487657489785, 58.3865281627285, 11.063554421823518, 55.97094750712567, 88.80121830895733, 46.05810253429422, 71.94373206291604, 77.06172079096442, 111.76756720437297, 40.8705323813961, 85.59903273369748, 70.47523756531801, 93.42951332100694, 68.45810294952118, 62.26079007928801, 111.74782477837779, 121.67195417371869, 91.54490609778702, 53.995650449885254, 78.11383101379273, 18.322985331965917, 55.34848697735097, 135.73313773173263, 90.94284184457915, 79.51555780879941, 69.35059371719758, 56.71578522461798, 230.41562479489804, 70.13098782124017, 50.76511437908028, 54.580247933881544, 58.52603706634559, 69.48830604606744, 63.72563205452962, 224.71240785207922, 89.42926523831773, 61.70926409043107, 59.832611114254306, 109.0285264747337, 44.60070668209965, 173.3242720058865, 44.207949472704435, 148.26499429204165, 104.76635768079858, 49.69275479448566, 37.192581529240876, 58.241225910301594, 168.35229241149514, 89.51369791913739, 52.99482445599818, 39.25653562557272, 74.78318068583954, 126.99035802678159, 125.0040993011321, 106.41296389492047, 73.08332885431706, 83.82583420768331, 118.68679399573662, 102.24260544313982, 64.92237262095249, 76.58270824756205, 43.96420124491884, 49.03363863044414, 51.207717399803606, 75.7845601729576, 51.711708146120216, 58.21866992058754, 92.46992725839814, 49.14884603330188, 31.479398640218744, 70.65229179893407, 54.36970783426968, 66.75088090537228, 52.72130122240171, 9.33044871252088, 74.93244027103621, 270.38839443817386, 68.3603627950762, 54.84024422412204, 51.351181407896995, 44.9480469313116, 50.807935301624966, 74.30487441666128, 54.0507185077086, 125.59750253055358, 130.5168927787889, 6.4719543913366975, 153.85835989419016, 65.97440461521231, 76.6136548843595, 34.655117721643414, 75.24650738298376, 57.017000093055245, 43.912010792545345, 78.85391945349335, 85.41567795770555, 73.02853992626338, 51.44240787994376, 56.086707637047034, 52.60411834132156, 65.32743548876921, 52.95978204602365, 74.15269260323922, 56.784999184724754, 50.82582079616693, 9.976929015434216, 148.26260045003178, 75.6719957226835, 128.8869606657227, 189.89796929446447, 130.53046506557777, 97.22678954028643, 117.99666761268853, 54.35749879203515, 195.1486584158782, 93.61391006040292, 70.5108097488288, 62.40271921434969, 82.77870086593987, 75.0820881187755, 132.84628098018234, 78.09717467413923, 64.14716082491266, 7.334621495655779, 82.83329655980255, 82.72855447912123, 48.24906345268004, 68.8797314137592, 70.90228255264151, 37.29168408778181, 119.41351660165739, 73.57042205496113, 42.87452643081992, 109.29848440378015, 146.43262040230158, 66.42801492031317, 149.96264939291183, 127.67635768289954, 156.46023398201234, 82.37439300073841, 147.41394396539476, 7.556082057678923, 60.75070041794793, 58.65778381579829, 74.28588987960362, 98.01652456723232, 62.02877993756914, 9.049312835292529, 92.353892203127, 123.56981353263042, 111.08461314970651, 43.25993705745818, 86.55809137320492, 50.28677255938186, 61.38802265183824, 66.14453595445842, 73.73382940529692, 75.88060137539752, 45.95377759886986, 89.74437585701475, 90.75361513151243, 81.41018914690892, 80.61992214060727, 67.9256532444962, 179.38978739060542, 72.67425591376721, 253.53835135391046, 168.69575682517177, 57.698055451781116, 76.30170990194742, 48.70761272100958, 52.90720971977002, 147.22468490019128, 180.09196538971082, 45.479726790740905, 91.33410917965882, 10.89856785095373, 77.6197985611808, 75.79386018524886, 62.57591236534777, 49.13413287906949, 83.51012174354457, 142.82873346229283, 11.06544861706741, 82.17883313335342, 79.73562903909944, 55.17466993457949, 61.20351699063827, 71.31969626158332, 219.43462726836512, 73.6489128861659, 44.760104020463224, 142.20175643709695, 83.68956649724986, 10.636313738306182, 48.81073825637362, 106.89676907813681, 149.56294154918024, 75.1607592702086, 164.86272639779352, 57.67907057861497, 55.37832864033532, 64.23541915179169, 92.01164612191836, 216.39050537236244, 72.4861833770427, 155.6153745832823, 343.48808727338866, 9.932249627805184, 65.67628290073367, 65.54007169854566, 68.44349395741982, 121.53690993090514, 50.9848437341162, 36.58671113547033, 14.00693010489785, 59.162089083087885, 98.78912507721522, 21.86240869764949, 45.96783900566857, 68.91054331039037, 52.604764410903734, 101.19867618985637, 38.470876637181725, 156.78522528186068, 72.50532588616198, 131.86874872433745, 59.97348116876948, 42.09693180882272, 79.66943633563315, 54.44109845394525, 123.50395016427423, 57.02354650566139, 45.73117634453997, 58.14110205153443, 35.3253357880876, 70.4818264091983, 119.3720557258765, 114.34521724976724, 88.85153894785991, 76.13286106388557, 50.04730616458828, 51.43286747462839, 77.84794864953454, 36.76259150783592, 67.63671103903118, 7.184259503720576, 73.96722682870748, 50.77026956142646, 52.70284595483175, 65.81699331434284, 67.09872795171489, 113.26126830209483, 77.85007676980538, 67.80721807068088, 146.50615432573497, 62.499450870803756, 48.601210484620616, 132.26473277633187, 36.562698048149066, 50.28568591789971, 66.38689127021213, 72.94749021530848, 107.22338472972861, 47.82250235400054, 53.79454838321496, 56.034703368892124, 58.64278402115005, 132.45982551701826, 78.16426780397987, 58.49691173296472, 50.79351977192079, 44.852221623616465, 38.10558696495363, 86.81004399396723, 103.06930687312789, 100.51584584363444, 72.93965308699586, 47.029864343500805, 87.22046675660918, 107.41070015584057, 61.1724899491088, 44.05756009486308, 60.80226325427663, 175.08762929704736, 44.57292138988164, 55.629390149088394, 75.1580973941446, 62.23613063927368, 142.14221442092088, 148.10164991002554, 59.387927493047535, 87.03168257718167, 50.10514859301469, 62.16022139588792, 50.52585118047119, 138.10796215481517, 53.124309095806716, 134.9563345377955, 42.29936324035564, 104.42273909814429, 90.42017324967128, 6.900363215614115, 47.09494003565658, 64.15254614602202, 171.84843343189075, 159.6822702999537, 49.1312696061238, 16.591167268810903, 98.87501258113754, 39.467522318196096, 41.65233258742249, 81.78669563868131, 37.00536866029402, 64.53439051464227, 7.750633991082928, 68.04252415791909, 54.242810948477604, 66.57103811661898, 49.36032395201977, 83.1828281119561, 76.14591267887246, 69.18629363556228, 135.66526400182536, 66.18354278936717, 69.1406528339002, 103.63313392942139, 99.1711940776353, 72.32670917379575, 77.83728770546399, 188.0496465184731, 111.97369025091638, 53.43944981320434, 122.14124135332985, 86.57218829575098, 100.35229334087316, 61.511756104990965, 73.05112226034096, 56.28374484867633, 8.051149966677372, 55.27407329776266, 60.12057297051318, 68.30936882806931, 54.59720503624102, 115.38055538958886, 50.021779584186696, 59.50450327950656, 56.219395592685245, 134.730090326683, 34.97441579085067, 154.98621783600112, 5.636652231613689, 138.108311152336, 208.2981176451514, 84.47163940033865, 87.49514617221682, 80.40939205971746, 40.74997068649132, 60.218742352398905, 96.07683034252717, 72.26357078804256, 53.3036378355605, 84.147195023083, 60.79835472592156, 121.37421766952855, 45.45911931666443, 22.408673808682146, 52.37694888476434, 90.36840007400271, 41.29515883660846, 65.5765477308096, 54.0849564723696, 88.96743959604318, 11.450517123978154, 49.811453091921166, 65.93488412756709, 63.0847454797584, 69.36710953403674, 60.43996791656512, 79.2374234589947, 6.481169062563408, 65.19601153762291, 11.823696909393904, 212.51960867959392, 67.4965791930168, 164.05352338406868, 218.72206859810086, 111.44066997332433, 40.71681805701172, 88.3565087947895, 51.06546327378949, 166.3591702598455, 69.20282604457027, 62.94506428493201, 56.203173164418814, 89.05606925457282, 87.07276511140775, 61.166382001521534, 12.429226461154844, 161.39361311139427, 21.416051529329934, 56.89011625192939, 131.00389797819184, 58.3233994590952, 54.91110206561417, 88.00040416028385, 62.13351488195473, 58.71174154898011, 56.85259547661975, 55.07113290224644, 63.62882477089773, 62.53846241387123, 79.46150253153567, 7.763815670453603, 116.97862593777316, 61.244447857079926, 63.274720114128456, 39.29763074181344, 128.99002242194902, 195.62767771225523, 58.94878789295443, 63.72380694456323, 114.56915758603924, 68.08376629398246, 76.25524463880488, 61.10118422248652, 66.65058548002072, 60.549796527665514, 55.79436749240096, 80.32083863381003, 65.94484864321467, 52.60639846614065, 52.89915217571819, 92.21932732659177, 75.29981344907385, 190.47660412692343, 48.166185549038225, 76.9444132104601, 54.04570775646508, 5.737570900595488, 134.81444882440536, 59.58540059580896, 68.14756709202825, 124.19182024828432, 81.37826424956249, 8.256012463175349, 58.08094560001048, 64.63996368305621, 58.84355440494801, 50.844530456804016, 52.34650097949688, 59.20355958942793, 86.39291898425112, 76.62606797095088, 105.51999457439513, 70.00941820230514, 100.84264171512767, 11.040995454211604, 49.963020269836115, 101.68601085731726, 65.52975381659303, 66.97727051539833, 10.205238339086796, 50.357483037619716, 88.85511431883968, 52.747097148046585, 41.60296543206061, 35.53340081874673, 61.05011263458907, 70.06742389619613, 91.69200461795954, 107.85730740290667, 64.25312698501475, 108.80596697499112, 53.02780297466415, 102.09296020549924, 82.66230457411578, 47.9134820582951, 61.6732002694969, 83.19704135572493, 83.77110963341791, 80.79070114656515, 101.13912829655187, 54.295310915537684, 98.3427939332909, 149.47069997359975, 50.08452200921701, 65.0371376390537, 90.7210374436372, 7.459421247293797, 54.19042939408892, 171.84449858435593, 75.2785006201548, 173.53194948251664, 176.85432535493365, 54.977960465339876, 115.41548917694554, 91.50518262854509, 89.7763482008918, 192.102510787005, 102.38798657662313, 101.42718010172933, 89.01500193692647, 102.77822301633499, 70.65487954977142, 37.65359151982898, 11.196073636462927, 70.59146775414835, 101.65680181043922, 329.025192777616, 93.13377825967335, 174.68124183416026, 94.9049289914608, 57.26151925422006, 102.90562665449248, 142.96464261662683, 114.74969700199462, 68.77111507922017, 81.72796819172193, 62.08343414740279, 68.29481508643981, 92.35420858316621, 70.85665070206922, 127.69675496615407, 58.63034653200661, 48.57344794361623, 80.7969702181098, 163.19885638049365, 125.33630537726171, 60.43266991049768, 59.585377395325665, 84.8377349638571, 88.01555866935334, 78.18203573937836, 80.70768698672451, 79.10565194440744, 46.35672060627964, 52.026464055495424, 75.9098635676157, 84.83415408426079, 45.732292295371714, 61.352509284925134, 5.59350804525226, 205.83886301399363, 92.18840424122334, 11.91324398969094, 372.581577869248, 52.14416705613956, 41.86140420928308, 71.42515284572656, 59.355739575695324, 128.64482725109096, 111.32909898845953, 141.36514114965937, 38.36951887181919, 35.295098283947745, 347.86552348103356, 129.3396617940662, 106.75602453478147, 170.16150393813754, 151.30194728130772, 20.33770244540384, 78.15647857426902, 59.42092027876061, 68.9614417837204, 6.819973217979373, 60.18874426482017, 41.67626382147197, 74.10417096754648, 47.74226324430292, 96.8038975011053, 83.41767968173254, 36.8744434511129, 57.37013793156611, 124.63727523484523, 201.660227286687, 59.03847447929734, 41.701710835478075, 105.7286337650499, 8.028119236485498, 48.45500202605524, 46.242</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>118.7441567134857</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>95.42599578171513</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>[87.55733489990234, 117.5550308227539, 136.6644287109375, 74.28791809082031, 318.12469482421875, 46.196685791015625, 131.4047393798828, 55.85951232910156, 20.313547134399414, 137.64471435546875, 66.30593872070312, 224.3693389892578, 127.88220977783203, 335.1879577636719, 84.29026794433594, 93.61988830566406, 48.28975296020508, 49.38071823120117, 172.2406005859375, 107.2049331665039, 164.33445739746094, 96.82820129394531, 103.06687927246094, 47.50446701049805, 61.86640930175781, 72.92346954345703, 45.947120666503906, 189.37484741210938, 80.42926788330078, 48.469947814941406, 58.88112258911133, 10.763513565063477, 85.81538391113281, 168.4691925048828, 41.5605583190918, 58.513824462890625, 74.5248794555664, 46.21141052246094, 477.1987609863281, 60.74861526489258, 97.2738037109375, 67.18521118164062, 39.81300735473633, 109.00031280517578, 72.94335174560547, 59.80903244018555, 153.4866485595703, 76.41046142578125, 66.68016052246094, 119.09868621826172, 70.84064483642578, 38.38438034057617, 85.84701538085938, 161.4570770263672, 65.34859466552734, 37.39012908935547, 50.00249099731445, 12.64061450958252, 93.44999694824219, 130.5547332763672, 145.69967651367188, 109.36820983886719, 88.5381088256836, 87.10613250732422, 115.82258605957031, 78.82489013671875, 149.53147888183594, 89.40764617919922, 323.8999938964844, 102.91506958007812, 50.36025619506836, 195.76361083984375, 81.66316986083984, 64.90062713623047, 143.50656127929688, 332.9368896484375, 180.3920440673828, 25.930421829223633, 71.02539825439453, 183.92498779296875, 171.95013427734375, 192.60806274414062, 52.57180404663086, 392.47576904296875, 209.46255493164062, 231.82615661621094, 53.44449996948242, 47.543006896972656, 490.4530944824219, 187.98880004882812, 46.161556243896484, 172.3901824951172, 126.80047607421875, 75.89229583740234, 422.9801025390625, 48.77598571777344, 148.1776885986328, 36.04082489013672, 98.04698944091797, 11.879032135009766]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst00309</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:45:09</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>87.85169267210608</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>67.04693261148985</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>104.2089676746611</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>4795</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>[0.9307515971243785, 1.541087283969086, 1.9476840864162939, 0.609657316764484, 1.4193136445483463, 0.6567556558924583, 1.4103143703053997, 0.4475560977714044, 0.38553487306247547, 0.9296241955537997, 1.7748852121285565, 1.72214856671768, 1.1192656987972867, 1.249478662305523, 0.7644384381112678, 0.6585971701943899, 0.5233498986442064, 0.5230420235554072, 1.2587815053724853, 1.4919287474789202, 1.2043552647478533, 1.218187234729192, 1.3479398457642668, 0.7115299492629444, 1.3408170841383036, 1.1853127071972862, 0.6690622980483024, 1.2445400055634823, 0.9800427179928052, 2.3373480031077722, 0.8960307444709379, 0.8778507912927983, 0.6924244309748506, 1.3091256814975334, 1.3267115186799643, 0.60095415560067, 1.092732159757896, 0.9180056893744589, 1.4409936115582835, 1.609763630925567, 1.6301345455553198, 1.7505939844756355, 3.3953805615667303, 1.7257133362325956, 1.7955324668880723, 2.0183843906473737, 3.0521207144111893, 2.337306836110346, 1.5785889470379482, 0.22301937783894574, 1.0211510175785656, 1.5853029561930447, 1.178107336219869, 2.6259330679522424, 2.7186393189568423, 1.5085714831447166, 1.9504188816214896, 0.671484753092623, 2.125625252425104, 1.5085986001271914, 2.096826282999945, 0.803189183756675, 2.947783929358203, 2.144432304600102, 1.553837029359036, 1.9244218427596715, 2.0974237678126717, 0.18003826362324427, 2.0516468824286025, 2.8893784633117234, 2.189385532732124, 1.3151454674753817, 3.2818169552312844, 1.2460770796499834, 1.280490672374502, 1.4907258673311625, 1.7650942268268814, 1.0719523632358543, 2.9539525785155387, 0.39875468636318423, 3.988047241344027, 1.323218030455267, 1.1673095630226773, 1.6232462543229906, 1.3158018316741762, 3.971688698917009, 3.0466841092236434, 0.3422285318885405, 2.518245990965293, 3.2487950571000863, 1.3874970919977234, 2.4825059883154763, 2.536621930449387, 2.119330462274465, 2.969757596454085, 1.7769096843330825, 3.638387736499708, 3.9397310206958203, 2.1068951247045984, 2.455488922634394, 2.7550206108051545, 1.6145031159288061, 2.367707115979653, 1.3703405352729265, 2.0905108131381644, 2.981833790284511, 1.016545249424158, 1.9251212294321265, 2.226498690331356, 3.267565467806502, 3.839941792539075, 1.149442000096305, 2.4252317575416513, 2.330678540972556, 3.7386744277340043, 3.9715538924800073, 1.8402926829798332, 2.9352343457905, 3.1970230161322752, 7.58777171322421, 2.202019088407834, 1.9297089853993377, 4.6118473482842095, 0.5115624274566667, 5.43259143825825, 5.77676852325588, 2.7066144608173666, 3.7837069270932844, 2.216309661096726, 3.293040397869488, 3.1257888846006963, 4.6710564299329205, 7.3838423910758575, 3.2362655599582126, 4.602402857761743, 5.292110833469994, 4.650608843943067, 4.559310980301597, 8.603468387832615, 1.9380418206798655, 3.8660446487887654, 4.439449557618157, 3.797050396729444, 5.700766009605458, 2.2484336442105373, 5.751121412542625, 2.221196727771105, 3.5481773300547923, 4.180693914477461, 2.1597223141601014, 3.882390912987609, 0.7546797279219867, 4.406342099762679, 2.7160424734411683, 2.5028872978831767, 5.890906670836395, 3.9630606489103384, 3.258359765184622, 0.8213229944235813, 7.55366588317239, 8.334818253665194, 14.044511611793986, 8.03949134221256, 20.179919395920752, 8.897170780953084, 21.060476840176065, 6.711996365955258, 8.419157769453502, 7.824054008584268, 10.437057047128114, 4.134822301073763, 3.7103416391176647, 5.867303819024335, 6.5379308817560675, 6.369153796383323, 4.507105227891444, 17.719587698745876, 14.024815089123743, 5.493781033503976, 6.316555951565572, 4.0809264189474534, 7.1043686197088185, 6.1160891001117434, 19.311919400084463, 7.529732878795271, 9.816759879340019, 7.733983449821657, 4.4137025639139855, 6.506586688870208, 5.314717953667567, 5.179971560067091, 6.243704848268668, 14.862388272306784, 18.58091605581896, 16.154215876702743, 13.818817565147492, 8.42466422115115, 18.543715052966334, 9.235161400356455, 10.373883384566524, 18.86969944777893, 17.195039733877202, 19.759062357179303, 13.290323165503715, 12.253166886828076, 14.219907491049064, 22.422992612912296, 10.93388608044417, 9.434153377497164, 17.44786842051909, 15.33285425101143, 10.979069638084146, 9.674227347015307, 6.227376826074477, 11.817652798071716, 10.516621770525804, 17.181759030811758, 18.735553078175414, 13.554359604713614, 21.13685793641821, 3.8351305380832748, 16.490544620526297, 3.540468970225927, 25.57510469272413, 19.031243951352117, 23.48957884407211, 16.30330190791164, 16.52915301068577, 21.949762080008288, 22.701009719092067, 12.441561668829351, 10.211261404158817, 10.000025237926778, 7.33200480610435, 1.8951489297455666, 27.59810990829101, 31.79328428421515, 17.548040477211014, 12.032041538956962, 32.63013433909962, 15.366795078753293, 7.170240492933708, 15.487324360695915, 20.30455942097752, 20.924704301800045, 28.11618636201432, 28.66104519186694, 12.266250405781316, 13.371013577831384, 26.19278666356908, 15.683694068489165, 25.54375035029043, 7.3066494358218375, 19.045683067567005, 23.332015583575206, 13.51979573056596, 51.484952955710106, 47.140497431189054, 24.423549296248133, 32.893070413116774, 44.810305314897136, 50.29283685164397, 4.154410485231698, 15.927353076882033, 9.190941706823168, 19.4583074868293, 12.292467040879863, 11.40382774908159, 14.602005905360373, 34.198702585217035, 24.12802170392303, 19.491578495312982, 16.857107086488355, 29.49340095412361, 36.34534734545042, 29.600436862728518, 47.089277734165236, 29.1439722506668, 48.076877036286604, 19.288254087646155, 31.131214956095874, 28.254769452114616, 26.497087340072735, 26.757322838237624, 39.70118264828931, 10.633331606687289, 52.49354753971245, 5.6526650788898465, 13.657259729823043, 28.729693659325118, 31.6722845890086, 29.57805426687395, 22.38551771078051, 20.967210665753253, 50.45089654849414, 20.960308599279884, 40.21293939314967, 23.097725285972867, 17.012893884534236, 26.297648218623443, 42.28374891560404, 36.50407004687371, 30.709033560911276, 27.34464967513695, 15.337290762997627, 36.65356022236748, 4.29736505695648, 22.614347444363016, 42.69311694252934, 29.042706479802888, 69.9584776264087, 3.2836117846567814, 39.80574149005928, 25.426106996902607, 43.535633308208844, 22.704426958672418, 20.975486177678707, 55.743449364795055, 39.799603141424235, 63.39662916490663, 18.40982456478585, 2.647112040874927, 40.45944844030907, 34.18323012586173, 4.578102305364208, 23.149549023444656, 5.162617554994013, 21.109172322302364, 40.98714514545532, 46.24935476585298, 29.488618813171005, 53.858447186520834, 88.10645812529337, 56.53594728057043, 3.394693094716162, 53.761458001301555, 37.09520373413942, 31.258756527941003, 28.91282199254831, 20.768869718680712, 36.83943466581584, 42.8881825938485, 41.78680062057403, 5.249719281929954, 37.543992592093005, 37.193282654485415, 63.751653121994764, 40.435071345145595, 47.08628651467328, 26.492122230791708, 32.6130635765671, 59.09457625995066, 6.248631518885214, 57.36454839882278, 24.01239212323398, 28.24602826193373, 56.055498362396854, 38.493835945714245, 95.9894492329377, 30.16801320770902, 4.079736343305793, 30.069393996398908, 51.98432677850438, 38.34362477811743, 59.33806429324127, 27.65722414159275, 29.948550104853222, 38.57954396683502, 43.50951873660327, 60.31234207964966, 54.74740148005805, 37.47807013568497, 92.55098194724438, 48.20538720752182, 50.73942666245679, 86.1723931700718, 39.939636110679, 85.65440901352173, 32.15302556466991, 37.37479660780086, 65.55349126928984, 52.52574532351515, 35.90977765414096, 66.27639160468432, 44.13116374861013, 58.98802965479609, 67.19019687234207, 42.21732693295019, 75.58532175231855, 47.10457669572965, 74.15448558129293, 52.45036789803169, 41.46575728697655, 51.831536502639146, 51.49538817737444, 41.994563985925055, 44.178212866329915, 34.31799937177905, 45.4361339966889, 25.831435041056967, 32.92451438594728, 13.465930724495202, 81.69677608296041, 32.00040818767724, 49.545256301617286, 79.92447188852401, 29.256287402130006, 91.32271704026753, 44.563684380150015, 42.29914486354282, 52.09308671721831, 45.486025696249456, 52.88301045153307, 42.00705299030741, 49.691489075325194, 30.452842214569017, 65.60542817219302, 64.16718242590899, 47.25955998868055, 33.72957674420601, 75.95489718756824, 36.87257586911305, 33.99753641349442, 70.95414321350113, 61.058926116166234, 208.17803185764822, 37.63402799305486, 45.49465198460686, 39.12560665246367, 80.92438777671882, 113.28050239121224, 44.05248728010823, 76.7343877343577, 54.609196100170905, 25.76185903661254, 62.07962824801873, 82.80471083329854, 46.905567128330915, 35.704704169299134, 60.08701366730725, 45.21471668922558, 19.16767790666129, 53.70813266912269, 53.92453731216785, 35.672385863780484, 44.12695527940346, 54.10496730687892, 35.00039205930718, 56.04361907434365, 49.186668570926415, 45.77355814245593, 54.972385432501234, 59.2843449257045, 65.74714199733381, 101.21443407283455, 42.92572027278656, 6.8145580295622645, 22.243880763546965, 54.64659975176358, 6.479319924223309, 38.366191628550375, 33.94553355968703, 34.355070713829704, 79.81948876249044, 5.387713268333226, 150.17845630379637, 49.36029722250827, 36.29731395179807, 38.68533204606333, 4.895805260463403, 41.387476365505066, 4.394983629274903, 112.10839173193582, 29.415463250596684, 45.08338511731276, 99.64799867641835, 85.17998507086568, 23.080486082017455, 56.8617613748574, 46.91614953248807, 69.07514549704804, 56.31358803631817, 48.82016433543418, 64.96178291544146, 40.54188300526624, 47.394767582351754, 40.21295237521039, 46.95309953018124, 71.32636573223283, 34.02089922006422, 34.25314338962761, 5.826241917852109, 7.522162095332692, 68.70864056582967, 47.89007088545451, 57.267729009113395, 71.37785136189022, 36.4696606164705, 31.842336092307093, 43.96298834659793, 51.36244052091437, 76.10833083084101, 92.22051281545183, 97.38729965660767, 89.84715279039551, 66.33516352665202, 48.50959534681231, 35.481208018323585, 55.749716552608625, 78.96580235509556, 53.171493387905315, 75.07872351940348, 110.69843520092361, 72.04799196109826, 6.935963194233427, 63.3752488347127, 44.553427345012224, 49.987481849082585, 45.4354941057613, 79.27989341884286, 38.17254368543787, 106.14616220257307, 63.884776898949, 57.01919260852199, 52.78408798999247, 67.90230421013315, 161.7615506150018, 69.5653790508275, 46.2403206614873, 40.63220917627753, 11.586894361893611, 48.1000692790619, 37.436050656145504, 105.12324498387048, 75.10964262845137, 57.48052001367533, 58.67292382800493, 47.325404725058256, 61.70024365017493, 58.26667932592419, 64.42465742323228, 55.59080303913675, 32.277673359648986, 101.6953254059244, 60.35174107492678, 46.511422849147806, 46.174985178613085, 27.069725818509657, 43.90020793028596, 9.863258568215652, 43.853006361572476, 79.49080514197459, 45.992945860647964, 42.15684426333002, 48.31482282213751, 57.72530499406586, 36.820040965057736, 41.29493133858508, 77.87535657351053, 39.04368119480903, 5.968219002760266, 128.07903378838435, 51.75981691534076, 64.91233854667993, 42.3990753595697, 109.07106315769735, 57.61202914124909, 38.97083889209128, 37.999197871330686, 59.246114340303656, 122.33000060098726, 35.02648594628369, 53.923368271722026, 44.13781665321015, 72.38650532644708, 68.72208761187765, 39.64716214793105, 33.41575991541969, 51.83572449446606, 100.98995143931114, 67.36570121256194, 6.2575116409273726, 37.6834906466001, 98.20650173671271, 44.69547065943173, 84.19848299111165, 16.97248663559044, 116.32266771752438, 31.905024585863956, 45.380312954206, 71.05796370368124, 100.2520791715387, 86.88513021415194, 81.4472920477187, 48.19491603620605, 55.41926739698672, 43.12728769182303, 82.3221540828839, 46.628306050985515, 48.9525992790986, 72.38026947434201, 33.977054307960955, 45.209461909183084, 43.77225580186174, 80.28327301764196, 70.94526754824783, 97.530322667715, 53.101056919261026, 52.82495617137224, 51.0089105560459, 68.24229307569061, 46.578686423456375, 66.6868450899413, 38.07083220132359, 93.02640170575837, 43.598125034520436, 96.971937414405, 33.33172777228505, 51.61155030011069, 91.28880817702596, 148.82943539673184, 41.44332454772114, 36.24593253551085, 108.87877263629063, 60.24540026176503, 41.8449105536682, 65.73623283516748, 58.21032322124606, 135.99730110719509, 75.69592916716456, 64.47174197248536, 45.3302985273931, 76.22169987340646, 57.36868047982825, 58.74033466835192, 39.0764479859127, 37.729863209630786, 52.66250469980309, 82.71578956891439, 9.412019331131672, 99.64703068112655, 24.67323814208488, 48.38614011911015, 49.29300992591621, 5.78299628982602, 16.418086927532197, 85.86404544068046, 58.61937269055574, 55.43901851812425, 19.9516295159595, 55.45242422664013, 80.40020149443534, 53.6390195695746, 58.57004924592378, 42.99176304474049, 64.79109095973676, 74.19525667996933, 96.27016507557552, 49.18826030105939, 52.178941197975604, 39.12901139505127, 71.30020559807355, 75.94658824876075, 46.28247945888944, 84.64086976302698, 43.94385439417502, 51.68563256468609, 59.81432768493682, 109.30742181041553, 99.1528930306278, 42.30772973487042, 62.65624363599763, 33.860587040780246, 53.24781341357873, 73.48013757168727, 80.09857220651698, 59.9422492030461, 5.083865560318565, 49.523228730026815, 72.44936556288009, 49.69849516391776, 45.57093000842251, 73.81348094098234, 12.171663608711201, 56.202829417560004, 221.70787582651005, 41.811480756666626, 39.16808576846314, 61.247786601166794, 87.82416610736523, 55.785708898850345, 92.76962632730324, 81.0661698171983, 115.73988019950974, 53.18335055607712, 71.29512234775812, 94.3125022977522, 118.48827159899025, 51.36414182620702, 48.00011823083353, 56.28396627080919, 7.106088117292754, 78.33320788564296, 78.63516322259544, 104.14100024782778, 105.77291078152638, 21.870289373795668, 70.57918202515056, 131.39990423514553, 96.2710266276105, 66.60031072074487, 68.14001850235438, 70.92614096546302, 72.43375151280166, 115.84551162725509, 87.74973400957856, 6.366337872954869, 50.34968301383662, 61.03762188367406, 132.07154521937028, 32.287192563662195, 10.886042889935808, 66.98283826166893, 85.70747063319487, 64.60592290270375, 90.83705467645842, 55.0946459190592, 86.97695326155375, 128.1796666586658, 59.77327270893551, 53.58625464754049, 69.68705513956711, 42.18151493268643, 73.23000032184814, 69.00721362848849, 43.24565015364462, 7.655154480908487, 78.7073434434272, 25.867770708121256, 8.468170559002417, 47.325740950445855, 59.1454002581496, 11.133638877706932, 59.399192720197256, 52.60374274352376, 91.2113863497923, 63.89207747395787, 80.20888314365706, 41.95449577844266, 257.71901412581576, 87.3254659820844, 178.37255465754217, 34.66254959959083, 79.63766908680977, 71.88289651581987, 45.68039706103468, 20.98579095402432, 45.79421230876656, 94.66971400726294, 36.952383248289095, 43.78748705675594, 45.661972200713585, 42.95616134574452, 239.7126169457226, 52.97931745168599, 50.21944671413064, 56.934023351380105, 61.726197546865826, 63.376673075808775, 58.15460407387263, 112.15027769780936, 77.64961483222417, 55.70814978520145, 53.25499664414049, 56.48160142410649, 39.35285359239454, 48.54329356195631, 49.2433250416747, 63.523108157196965, 51.16332510728876, 60.90592541532727, 46.58450536033672, 3.9404107778825144, 96.32400867148908, 35.86494442329046, 122.71758403271502, 59.34894663808845, 64.05564778800564, 84.53586573367706, 73.99810479205101, 57.89543857152382, 50.32309732472577, 78.56384416814251, 151.12255597595393, 46.06562477742106, 60.62680392244914, 137.35101252990194, 72.52567955957068, 14.244076908578961, 59.31470286508681, 69.56627709716653, 13.076054098136648, 70.81676067964482, 49.93495731942765, 95.13349092334246, 67.60695101019951, 69.63218668588607, 61.13689946582116, 50.79762495900288, 40.713636413788066, 48.030786863864215, 55.09873351041693, 131.1523558090838, 50.347952526452026, 62.77293811253445, 40.75456510989109, 70.58021541970865, 115.93615003983989, 150.22283663928616, 147.11568189591864, 63.61506844833387, 63.475508986345204, 43.46885710040624, 179.16286642283637, 50.696607544008124, 50.483469053477165, 82.33677060891847, 154.95210341610556, 68.17926347086006, 52.3433662550623, 56.74354634642197, 46.44171474041274, 109.89914435866623, 72.4171870210623, 55.15469246632796, 50.052510799605045, 74.82733091791513, 94.94872031358821, 59.471655335184465, 50.64126755122833, 68.46816050435787, 57.46990313206475, 81.86732246376664, 72.48838151409456, 118.79260494198587, 47.483520834814215, 95.14065471549252, 52.894932810731504, 49.5493333870199, 54.37680081135713, 68.55445618659442, 65.64895932613383, 150.98009484846332, 105.88801092139096, 44.10436783308771, 143.4886246889756, 68.25729051997193, 88.67906762602253, 68.07389435107196, 41.13692595143553, 54.448181690699265, 98.3708730052786, 50.77487867273766, 36.82293974965613, 48.62794242524013, 54.289662952275044, 7.6834622356813735, 162.83211088949187, 98.3403287196838, 136.82315033095898, 43.50902063169769, 150.25130835496307, 53.65233620839475, 109.25410333316952, 64.43596196748088, 64.66509459083485, 134.06889163877128, 63.7602647729683, 87.88801628669451, 68.32890786746081, 20.52777860242785, 89.37636816833422, 91.30159694125395, 129.7482608931077, 48.91948425016739, 52.729658579526124, 136.42945798831687, 108.99020950355212, 51.35447679572036, 197.98071867995984, 67.81113237309746, 56.32781375376578, 108.87201724149666, 66.82884267823358, 96.1782320880676, 39.87806454009903, 142.23997851716373, 82.0117911080741, 75.88426739879617, 64.97667230099155, 8.451338044229464, 212.9694480333827, 43.51595389497825, 38.11183542299472, 350.7356130289314, 156.82771551752145, 133.66758153093548, 48.007149150075435, 51.35570547776458, 47.8053953278296, 49.542113625641015, 102.41201536583857, 111.15635919303048, 51.13382305766047, 42.314030926171434, 59.69336153500524, 50.96073994257569, 50.48829296325624, 10.298354293098216, 42.06148952601728, 116.3600331923193, 68.34889021655243, 132.4986171970966, 5.768183736784667, 25.29853061478769, 68.44768548952801, 82.29068443975058, 46.65665057570957, 75.18948168156105, 118.92416038815409, 183.9532683406451, 12.40043698494211, 56.07713863025346, 41.091285960817395, 95.94671481093505, 150.37933173036058, 214.03340305535943, 115.21900240159258, 117.67365397302743, 79.70648264523376, 71.13022811863351, 8.510831137493298, 99.3644535036189, 157.78109560892437, 189.64567524252175, 124.49685958307855, 42.72828114951954, 93.16112465467873, 76.32695783240372, 76.67215724207358, 54.763931709293225, 8.776102014745785, 231.18369439494356, 82.51876202549971, 134.3472643370094, 62.463359277261674, 43.40744945189109, 90.90896011872056, 56.50355474236, 155.02139554811777, 148.1281786483302, 48.58597772932432, 55.63755843641411, 77.54283611054159, 41.36425047897454, 57.63711181094372, 87.91939990142193, 61.83954746164089, 111.13894660212537, 169.61592476708756, 147.93151152098878, 114.39094942890564, 86.1317640163001, 56.94446952502485, 45.74653366956668, 65.61357674597605, 133.46679201640453, 137.51109877227142, 55.44758662822112, 105.30428546289927, 67.161072790516, 10.553420340568955, 40.80402807279793, 144.30214024547672, 90.45831331207559, 49.02949140310631, 47.740054387958864, 54.57246552309283, 98.07390379046502, 71.78286945749, 68.4354175831276, 72.90713958328107, 128.5910241952681, 104.29691481265095, 60.00680601270495, 77.81011717638525, 122.69516387747886, 46.779081394932355, 66.9716927802088, 56.97140149747794, 55.7243765133959, 48.27700070346729, 47.44580294817451, 134.8745693933035, 110.1687487776884, 74.64405682088842, 77.4128630230268, 160.93319948223407, 58.25190170115954, 50.014226533298164, 62.25394814396174, 40.528890593281936, 15.684759812516118, 226.64414001922444, 72.44517799208452, 66.12330155925892, 13.043341228386646, 37.76527051329676, 49.334320038988366, 49.923694682151904, 101.89963985805309, 84.24571346765555, 57.48551955428843, 68.18535441137102, 49.64849598372275, 152.25546035248817, 98.94553502070013, 95.16946613943453, 84.8431072923053, 70.02524138018605, 96.24667731249555, 122.91481566707847, 8.810417400265065, 42.78424168466413, 153.84362344644782, 35.66432944532083, 63.27235268621577, 10.501343777785687, 5.656969844208229, 97.5444830670971, 57.181540736305465, 84.05932077681072, 83.30276981601533, 81.77438297597914, 96.82736591252194, 61.05673465074399, 151.923650045828, 113.25298045257426, 128.95060175840183, 45.01738175527674, 48.16813115324248, 43.53406919418571, 71.05310061560994, 71.54691841824553, 152.81017233755506, 77.58886130044687, 8.652021646832441, 196.89904834923695, 82.90596725726517, 13.61394942986353, 25.800309538826916, 81.55970058236153, 7.095667237414763, 75.1940342792195, 46.229149174833054, 56.89062451256149, 67.53186811136656, 56.143606240669946, 92.8210195779722, 62.023970572784506, 219.3398131725758, 51.575434745884316, 132.38407816563887, 72.51532075241956, 61.58311205714627, 86.35411791638164, 63.857554819566744, 259.59721403039055, 46.90439290931609, 90.41137138118133, 35.90208832413783, 92.8795327825379, 139.4703472326558, 107.04766331812154, 73.44514200391917, 216.22147194656128, 86.25212161659191, 4.458532249492326, 89.65612243308817, 139.63930513247246, 42.44621972546133, 147.74764596692094, 51.9338122061067, 115.68221163912288, 118.63847523093531, 45.82197918560277, 101.07148721000856, 69.81939608727458, 61.296411700277424, 41.66223425908154, 62.013356980999205, 94.80177771381484, 149.36571870266877, 48.896838970523206, 123.02578546232445, 7.1424255909041, 158.71375330938622, 107.4728001058367, 73.6371685250041, 70.17522485558635, 34.93885195614383, 29.230316429558698, 157.25026407330088, 111.96549189127903, 75.80225982024089, 44.607266151370354, 260.04773352508516, 98.35203675461042, 72.56695687700773, 91.46386009737695, 53.376609404826795, 28.537130212238306, 135.77354370218703, 60.37165811332318, 75.60750439801606, 91.05815421283629, 89.68055602134932, 90.25365796481307, 46.45034434301342, 84.14268192311322, 63.214142800475294, 39.33312892472559, 113.23863106399273, 102.42971953265874, 56.71826135811814, 125.25000090084811, 58.992555804979396, 58.12399063316608, 86.21092050245689, 80.32854820589573, 84.41137171452816, 80.79580327659161, 76.17572994619154, 93.85996608186785, 74.92103251612374, 72.86113112127903, 61.44484392103578, 96.21556694968542, 316.91110144522605, 64.56421757909656, 118.48305155637065, 93.95001892326317, 56.97361827168382, 10.967518408302308, 88.7306564992456, 56.50229543171686, 97.98326522003525, 188.726202862695, 92.37203488096434, 71.29287521694913, 148.941340788156, 91.88143571334446, 38.29567973060706, 67.515701333597, 87.04795148144555, 63.95404789127794, 83.90227117690094, 11.31423686036527, 78.07531544265828, 123.24968344310035, 60.23874693310591, 45.61490270878979, 66.17609026119933, 122.10976235118484, 44.632771210142444, 63.66498756747037, 79.19506569127563, 48.3271971621384, 118.25384327420724, 164.02663054149582, 40.677031002797, 57.87776620042318, 131.0829432418935, 34.59950764847117, 103.36369360198802, 99.43708385157514, 42.42375937617298, 100.18285848705531, 84.86286467938795, 77.33159057726076, 79.76050804597824, 17.9804424357158, 93.1601812839586, 64.70596066487984, 96.72255855187882, 74.32074609487645, 76.21541313362393, 41.94581531252556, 129.78682337656232, 72.30241117763612, 45.85779740494339, 16.337960663698166, 78.37862638439, 78.80315974223603, 109.90316928330853, 6.932805820253797, 112.48427790580155, 74.4228129403346, 121.7383115086244, 56.47879759007379, 57.36385830245153, 66.61891203882398, 41.34254678697371, 65.07484010339887, 54.63044851708228, 60.713820870857845, 88.56759638546902, 123.06600457770534, 13.117635495036318, 116.33371364508622, 78.27825827399809, 53.389163816728065, 258.5640688756818, 91.63184977907257, 119.12493298478783, 62.35972296361223, 108.46109655370506, 49.70854314900215, 48.15961248176457, 151.0064442432747, 65.47455866451396, 84.5734694880066, 56.1915968486481, 34.02361092401438, 119.1137906623929, 5.779339254122993, 124.1266860739981, 67.7305952976356, 68.45935751437153, 9.955878761852883, 6.1088276985125205, 70.78646755718597, 66.58532860110743, 64.64531404204074, 66.71542215386091, 72.37358310905225, 16.71057540487546, 233.91674530050264, 93.01653301652334, 159.29350428317406, 49.23574385898224, 8.60218831617823, 46.3057711994342, 45.68089163989582, 81.74187052514587, 79.64667311701959, 134.3226379305417, 123.14431676229354, 6.276214941416323, 57.990199362705035, 94.77845662221158, 10.503422284421518, 89.51981024381233, 128.4690966845299, 9.69915541746149, 126.1793427608151, 55.15525335003481, 49.434896429121636, 58.88496446904233, 120.05084533512199, 105.68272806728653, 56.5281487960712, 209.32172799016166, 89.15717564628206, 117.59503024437636, 75.62718878674717, 13.13173684299571, 106.21434119819175, 43.52739281945578, 59.01512136222129, 15.843848175187743, 61.42722352549383, 104.72784694283577, 48.866645017204675, 80.08636979338378, 60.0058308774252, 182.32318349096747, 70.7578095828128, 13.822213226100313, 50.69569369406099, 87.63425898569311, 56.6782842359707, 75.67070428124131, 46.58984789958236, 52.377831139143424, 70.00116645419546, 63.82577740465839, 43.74785392807483, 112.24033882940105, 58.66899803546241, 28.3405370495909, 82.2093550788167, 65.11160857839786, 58.352868041409074, 82.15135559574348, 52.274185810927115, 10.019025721457025, 74.0815442196226, 83.62251910554686, 87.07706894231113, 76.90869352887506, 5.379682006855135, 157.75545459663343, 58.41525504188929, 79.64596927912835, 145.83374740212452, 65.23482339110666, 58.60599934344674, 48.669051788201834, 113.70003831786352, 73.04648946964338, 87.3536191602163, 67.5659711270076, 136.42019163864717, 82.56493332604335, 104.67156411716076, 148.4688260278693, 213.27290624451075, 52.078292145990915, 126.52683268160375, 106.87912191831762, 53.151567924863826, 76.72446221157865, 103.9940365296362, 27.363367449010827, 70.60762053487502, 46.01858903375472, 92.08730990427688, 44.76642078803752, 4.626766459374778, 119.97932575892924, 57.45813665703944, 109.96904248407309, 94.26400089696777, 83.82572857458436, 74.32086258522492, 65.25643429502394, 82.78144747613743, 217.14253175266018, 127.85017296610606, 51.177220126804734, 9.871239807566875, 98.38744289178258, 28.23664261175732, 62.72755442602626, 57.23790324733992, 110.22084038006219, 88.35855229986194, 51.50555270399427, 108.57534000532056, 128.46136693756608, 55.69153639726567, 71.77367097120352, 86.40176688608804, 107.7456121704554, 44.223976064872915, 69.35964681302958, 57.453506945211146, 105.58924780109044, 72.47059173452698, 33.05023903364435, 56.08115166291099, 50.31483953682463, 32.18331791292511, 71.03232579182962, 145.3769034609088, 45.199357195295, 89.49349345119467, 58.74678111333528, 118.02850681084905, 79.01326082103499, 80.94953441133103, 120.25962082378895, 100.36451871791787, 167.32540979086875, 109.83407403386421, 47.55297295685772, 92.02477713824362, 35.896877084806384, 56.814255494128616, 284.3708262076002, 65.95766476382404, 68.930241615997, 279.87806365591, 122.93060759904267, 103.7672170142099, 152.41284946296608, 86.58329029807345, 52.39420395845624, 70.26034463410409, 138.7227519245404, 141.93891108633224, 97.68992346568957, 72.09486826664694, 89.29407513270067, 284.8554649878332, 5.856235445373345, 42.18945283180205, 68.0579691452187, 53.39524842689455, 76.22584367539378, 66.38965080880679, 183.47314829817716, 119.33090921099041, 58.334347809670604, 109.29497948426665, 54.76153589603262, 59.84482365680796, 87.30733565374436, 136.94153713924825, 62.52862844717205, 130.26890060214376, 92.36983511378888, 11.532562962435005, 55.67637264617045, 93.01090918905972, 49.87389429451841, 204.87926484571528, 103.00635366522799, 128.46780565846382, 103.93214235055281, 66.84575462087754, 74.84232699706125, 73.01193296424228, 54.622655705899234, 84.7116172441815, 105.1076396354139, 63.47013082841631, 212.11147002356648, 78.37452160659257, 78.84495986097674, 63.61737350073797, 116.47452151606973, 50.70545009281794, 59.9134602685798, 108.10986434561016, 79.760435479117, 140.52511923174777, 67.50097886164166, 92.1465005232143, 83.9560582492435, 31.561076961932464, 72.29193920614787, 64.60194053709213, 56.18416327782659, 73.88641464692529, 138.3182174627557, 79.13850307892754, 43.80357244616292, 51.3365557585343, 79.20826077436472, 110.98865406240587, 94.29761568150886, 69.28237021509608, 75.21113621148217, 70.90796366230637, 66.35676353839015, 137.21026506050487, 46.48834063396366, 116.33912280932083, 89.78865031075424, 67.32711741284045, 44.304873933532214, 47.06833108371223, 149.01028147076113, 52.929547140324374, 56.72680739156594, 70.04972318689838, 49.056610467596045, 72.04856063258549, 51.629654866007805, 74.3314845782468, 168.37680837677337, 168.84509607849873, 56.97385933179258, 5.137637841416195, 51.47255650248787, 87.27141533267958, 109.11289758880297, 54.65842092295586, 104.93408821366346, 60.88897848813581, 59.3440716894426, 21.57922555906572, 93.62042401330174, 117.03059560633714, 116.95048621432116, 69.02172177187502, 58.62223018815314, 52.26889631526667, 116.80584469745502, 72.11802635131892, 80.42942299180005, 60.9498377628937, 131.30174445974794, 115.91435101787671, 108.76636615861453, 68.49313881259172, 111.51559694004887, 69.93662423159165, 138.86579703286367, 77.2462363308696, 55.18606378631796, 24.450178949598577, 97.1392453372729, 61.08420967292976, 56.996470181207016, 85.74894505848334, 101.43847691258698, 65.04852404980147, 35.412793169804594, 155.0701715726338, 46.78896087635038, 263.7723618738318, 94.82735452425058, 57.29870244159659, 61.80286017320809, 68.25739991008783, 54.47611616869927, 34.975580948268494, 6.596985131346891, 63.81286131102445, 64.88859021126954, 66.70867925183782, 64.1907266319235, 59.490086507415455, 43.53540020577189, 43.92889879929436, 313.6301124246846, 99.12476053381457, 8.018902567235228, 72.02127034887783, 64.8600417149363, 208.86991638172682, 91.473365839466, 117.65180860245582, 67.1537629091993, 67.40700000366029, 84.0004352734268, 68.93299896325107, 123.87936000827618, 107.16102961529212, 99.73487438671403, 90.4417285395673, 66.68806822776975, 71.27822899485534, 82.21512688755506, 111.33160724843474, 49.68442088887898, 191.4275239559384, 85.5575687571715, 59.43005813068472, 112.23964361100035, 64.12932453135191, 85.40516833029507, 77.28947029858726, 157.41032207973535, 62.902214209234685, 11.213393700101935, 152.37388901294506, 161.4861542910597, 80.86201301783687, 10.165605071450212, 119.05133263722934, 76.04403350965777, 73.13363492869985, 7.598340616091483, 81.2164127278169, 75.72771724845423, 63.326239614323875, 108.20156818886537, 89.12572206591898, 85.05914650624783, 64.07855337377495, 53.45323882487778, 81.74800285098215, 121.23237867725858, 102.15471245951981, 114.70143820128743, 136.72699937639533, 43.18004858194765, 71.18692366018306, 120.71475217621264, 92.81643032704878, 52.64938707119038, 4.778390662809695, 89.37795844491497, 47.61440256008689, 37.69058523488172, 51.61978458881987, 45.411024199307676, 52.14312630038894, 97.05950800577357, 52.492109404882385, 109.24572354900009, 81.00659738737635, 68.20643593853013, 75.30861503204012, 139.79027920243723, 43.54412677391732, 82.9200764691518, 136.32962289725324, 157.83111689788674, 105.50044103662489, 79.72511413511288, 90.24512596719093, 106.03478309848525, 79.18976314633333, 91.69731210843932, 7.161510396374102, 198.6720525053756, 71.40121371522378, 113.48193554575224, 62.15409351349062, 49.94507360909834, 129.91825698747667, 178.37424781664816, 6.272394315332859, 54.94768528979481, 96.75173991068552, 71.83968969313067, 65.76749838699888, 72.0625032528555, 88.49332210144756, 86.70610771855561, 113.371763438666, 82.64823069788982, 113.51177111861796, 71.17039800391474, 74.03425442042526, 50.86874689349324, 245.29130934666478, 67.29840877443768, 57.127416956184526, 94.35765090373361, 88.75224927552043, 189.3973220081023, 192.6355045635566, 153.56893304873154, 60.23259408359655, 52.63725354933162, 53.59751022031681, 148.02678275864565, 73.32690640650789, 78.91826983356906, 58.66377436808404, 98.62507659359707, 87.31219841669818, 143.45088926528803, 44.75515499748723, 155.86209103688086, 93.43243704144336, 89.82689015461102, 91.36908104091093, 67.63727589194421, 62.40288416806042, 82.69187207303337, 78.5156061615362, 153.07784834079783, 89.88752694396449, 50.41841179684916, 50.97923504271824, 178.46648037174054, 90.23148147467128, 62.616798390173834, 77.49909537499707, 62.04984556935734, 90.88387312709231, 34.26553272199796, 65.28427072932105, 67.63168500981277, 99.57207535381924, 65.53099956709958, 207.43663309241168, 89.91400238828163, 441.7090178769266, 82.82186301293001, 53.20684674648702, 40.67707777226201, 90.17573880679487, 133.55222560051718, 100.94198510351158, 65.44759062524453, 116.28992211677411, 51.52407269882342, 36.45104799795456, 127.30251815922097, 130.25742795838872, 45.45996953070656, 34.722798906421275, 78.63200209857615,</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>117.5315532493591</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>91.26385716178538</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>[115.11665344238281, 103.69825744628906, 127.93094635009766, 79.83558654785156, 83.26913452148438, 181.39236450195312, 141.68099975585938, 173.3926239013672, 39.33804702758789, 92.09040832519531, 68.59166717529297, 189.92835998535156, 35.237430572509766, 70.79370880126953, 118.96125030517578, 204.5042266845703, 103.06398010253906, 151.9327850341797, 71.95588684082031, 399.021728515625, 66.20675659179688, 209.1926727294922, 106.28140258789062, 9.447199821472168, 34.837860107421875, 48.77973556518555, 76.03938293457031, 9.708819389343262, 51.8015022277832, 93.85595703125, 48.49617004394531, 68.54496765136719, 77.3094482421875, 91.0130844116211, 15.693909645080566, 99.15660858154297, 94.0801773071289, 249.12811279296875, 102.61384582519531, 84.12725830078125, 172.531005859375, 82.18936920166016, 557.05029296875, 68.55414581298828, 111.10199737548828, 207.05694580078125, 67.2025146484375, 533.1022338867188, 50.59560775756836, 141.61537170410156, 73.85720825195312, 64.45997619628906, 72.71294403076172, 44.775028228759766, 195.22462463378906, 91.18205261230469, 51.651126861572266, 99.50089263916016, 249.7707977294922, 78.50433349609375, 93.9478530883789, 125.20960235595703, 123.3061752319336, 54.926124572753906, 305.4013366699219, 58.446815490722656, 69.91403198242188, 201.76296997070312, 63.52057647705078, 293.38360595703125, 76.8183822631836, 84.92288208007812, 69.3428955078125, 69.11119842529297, 68.11460876464844, 271.09747314453125, 120.18218994140625, 233.5401611328125, 96.58574676513672, 117.64987182617188, 75.17627716064453, 85.39385223388672, 54.62156677246094, 105.64508819580078, 88.56134033203125, 169.728515625, 65.80217742919922, 164.71185302734375, 11.097228050231934, 153.1634063720703, 35.68181610107422, 50.07884979248047, 195.0278778076172, 106.65154266357422, 102.44050598144531, 47.07980728149414, 122.96456146240234, 134.52674865722656, 89.88441467285156, 97.04400634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst00316</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:49:21</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>87.85169267210608</v>
+      </c>
+      <c r="M36" t="n">
+        <v>67.04693261148985</v>
+      </c>
+      <c r="N36" t="n">
+        <v>104.2089676746611</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4795</v>
+      </c>
+      <c r="P36" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>[0.9307515971243785, 1.541087283969086, 1.9476840864162939, 0.609657316764484, 1.4193136445483463, 0.6567556558924583, 1.4103143703053997, 0.4475560977714044, 0.38553487306247547, 0.9296241955537997, 1.7748852121285565, 1.72214856671768, 1.1192656987972867, 1.249478662305523, 0.7644384381112678, 0.6585971701943899, 0.5233498986442064, 0.5230420235554072, 1.2587815053724853, 1.4919287474789202, 1.2043552647478533, 1.218187234729192, 1.3479398457642668, 0.7115299492629444, 1.3408170841383036, 1.1853127071972862, 0.6690622980483024, 1.2445400055634823, 0.9800427179928052, 2.3373480031077722, 0.8960307444709379, 0.8778507912927983, 0.6924244309748506, 1.3091256814975334, 1.3267115186799643, 0.60095415560067, 1.092732159757896, 0.9180056893744589, 1.4409936115582835, 1.609763630925567, 1.6301345455553198, 1.7505939844756355, 3.3953805615667303, 1.7257133362325956, 1.7955324668880723, 2.0183843906473737, 3.0521207144111893, 2.337306836110346, 1.5785889470379482, 0.22301937783894574, 1.0211510175785656, 1.5853029561930447, 1.178107336219869, 2.6259330679522424, 2.7186393189568423, 1.5085714831447166, 1.9504188816214896, 0.671484753092623, 2.125625252425104, 1.5085986001271914, 2.096826282999945, 0.803189183756675, 2.947783929358203, 2.144432304600102, 1.553837029359036, 1.9244218427596715, 2.0974237678126717, 0.18003826362324427, 2.0516468824286025, 2.8893784633117234, 2.189385532732124, 1.3151454674753817, 3.2818169552312844, 1.2460770796499834, 1.280490672374502, 1.4907258673311625, 1.7650942268268814, 1.0719523632358543, 2.9539525785155387, 0.39875468636318423, 3.988047241344027, 1.323218030455267, 1.1673095630226773, 1.6232462543229906, 1.3158018316741762, 3.971688698917009, 3.0466841092236434, 0.3422285318885405, 2.518245990965293, 3.2487950571000863, 1.3874970919977234, 2.4825059883154763, 2.536621930449387, 2.119330462274465, 2.969757596454085, 1.7769096843330825, 3.638387736499708, 3.9397310206958203, 2.1068951247045984, 2.455488922634394, 2.7550206108051545, 1.6145031159288061, 2.367707115979653, 1.3703405352729265, 2.0905108131381644, 2.981833790284511, 1.016545249424158, 1.9251212294321265, 2.226498690331356, 3.267565467806502, 3.839941792539075, 1.149442000096305, 2.4252317575416513, 2.330678540972556, 3.7386744277340043, 3.9715538924800073, 1.8402926829798332, 2.9352343457905, 3.1970230161322752, 7.58777171322421, 2.202019088407834, 1.9297089853993377, 4.6118473482842095, 0.5115624274566667, 5.43259143825825, 5.77676852325588, 2.7066144608173666, 3.7837069270932844, 2.216309661096726, 3.293040397869488, 3.1257888846006963, 4.6710564299329205, 7.3838423910758575, 3.2362655599582126, 4.602402857761743, 5.292110833469994, 4.650608843943067, 4.559310980301597, 8.603468387832615, 1.9380418206798655, 3.8660446487887654, 4.439449557618157, 3.797050396729444, 5.700766009605458, 2.2484336442105373, 5.751121412542625, 2.221196727771105, 3.5481773300547923, 4.180693914477461, 2.1597223141601014, 3.882390912987609, 0.7546797279219867, 4.406342099762679, 2.7160424734411683, 2.5028872978831767, 5.890906670836395, 3.9630606489103384, 3.258359765184622, 0.8213229944235813, 7.55366588317239, 8.334818253665194, 14.044511611793986, 8.03949134221256, 20.179919395920752, 8.897170780953084, 21.060476840176065, 6.711996365955258, 8.419157769453502, 7.824054008584268, 10.437057047128114, 4.134822301073763, 3.7103416391176647, 5.867303819024335, 6.5379308817560675, 6.369153796383323, 4.507105227891444, 17.719587698745876, 14.024815089123743, 5.493781033503976, 6.316555951565572, 4.0809264189474534, 7.1043686197088185, 6.1160891001117434, 19.311919400084463, 7.529732878795271, 9.816759879340019, 7.733983449821657, 4.4137025639139855, 6.506586688870208, 5.314717953667567, 5.179971560067091, 6.243704848268668, 14.862388272306784, 18.58091605581896, 16.154215876702743, 13.818817565147492, 8.42466422115115, 18.543715052966334, 9.235161400356455, 10.373883384566524, 18.86969944777893, 17.195039733877202, 19.759062357179303, 13.290323165503715, 12.253166886828076, 14.219907491049064, 22.422992612912296, 10.93388608044417, 9.434153377497164, 17.44786842051909, 15.33285425101143, 10.979069638084146, 9.674227347015307, 6.227376826074477, 11.817652798071716, 10.516621770525804, 17.181759030811758, 18.735553078175414, 13.554359604713614, 21.13685793641821, 3.8351305380832748, 16.490544620526297, 3.540468970225927, 25.57510469272413, 19.031243951352117, 23.48957884407211, 16.30330190791164, 16.52915301068577, 21.949762080008288, 22.701009719092067, 12.441561668829351, 10.211261404158817, 10.000025237926778, 7.33200480610435, 1.8951489297455666, 27.59810990829101, 31.79328428421515, 17.548040477211014, 12.032041538956962, 32.63013433909962, 15.366795078753293, 7.170240492933708, 15.487324360695915, 20.30455942097752, 20.924704301800045, 28.11618636201432, 28.66104519186694, 12.266250405781316, 13.371013577831384, 26.19278666356908, 15.683694068489165, 25.54375035029043, 7.3066494358218375, 19.045683067567005, 23.332015583575206, 13.51979573056596, 51.484952955710106, 47.140497431189054, 24.423549296248133, 32.893070413116774, 44.810305314897136, 50.29283685164397, 4.154410485231698, 15.927353076882033, 9.190941706823168, 19.4583074868293, 12.292467040879863, 11.40382774908159, 14.602005905360373, 34.198702585217035, 24.12802170392303, 19.491578495312982, 16.857107086488355, 29.49340095412361, 36.34534734545042, 29.600436862728518, 47.089277734165236, 29.1439722506668, 48.076877036286604, 19.288254087646155, 31.131214956095874, 28.254769452114616, 26.497087340072735, 26.757322838237624, 39.70118264828931, 10.633331606687289, 52.49354753971245, 5.6526650788898465, 13.657259729823043, 28.729693659325118, 31.6722845890086, 29.57805426687395, 22.38551771078051, 20.967210665753253, 50.45089654849414, 20.960308599279884, 40.21293939314967, 23.097725285972867, 17.012893884534236, 26.297648218623443, 42.28374891560404, 36.50407004687371, 30.709033560911276, 27.34464967513695, 15.337290762997627, 36.65356022236748, 4.29736505695648, 22.614347444363016, 42.69311694252934, 29.042706479802888, 69.9584776264087, 3.2836117846567814, 39.80574149005928, 25.426106996902607, 43.535633308208844, 22.704426958672418, 20.975486177678707, 55.743449364795055, 39.799603141424235, 63.39662916490663, 18.40982456478585, 2.647112040874927, 40.45944844030907, 34.18323012586173, 4.578102305364208, 23.149549023444656, 5.162617554994013, 21.109172322302364, 40.98714514545532, 46.24935476585298, 29.488618813171005, 53.858447186520834, 88.10645812529337, 56.53594728057043, 3.394693094716162, 53.761458001301555, 37.09520373413942, 31.258756527941003, 28.91282199254831, 20.768869718680712, 36.83943466581584, 42.8881825938485, 41.78680062057403, 5.249719281929954, 37.543992592093005, 37.193282654485415, 63.751653121994764, 40.435071345145595, 47.08628651467328, 26.492122230791708, 32.6130635765671, 59.09457625995066, 6.248631518885214, 57.36454839882278, 24.01239212323398, 28.24602826193373, 56.055498362396854, 38.493835945714245, 95.9894492329377, 30.16801320770902, 4.079736343305793, 30.069393996398908, 51.98432677850438, 38.34362477811743, 59.33806429324127, 27.65722414159275, 29.948550104853222, 38.57954396683502, 43.50951873660327, 60.31234207964966, 54.74740148005805, 37.47807013568497, 92.55098194724438, 48.20538720752182, 50.73942666245679, 86.1723931700718, 39.939636110679, 85.65440901352173, 32.15302556466991, 37.37479660780086, 65.55349126928984, 52.52574532351515, 35.90977765414096, 66.27639160468432, 44.13116374861013, 58.98802965479609, 67.19019687234207, 42.21732693295019, 75.58532175231855, 47.10457669572965, 74.15448558129293, 52.45036789803169, 41.46575728697655, 51.831536502639146, 51.49538817737444, 41.994563985925055, 44.178212866329915, 34.31799937177905, 45.4361339966889, 25.831435041056967, 32.92451438594728, 13.465930724495202, 81.69677608296041, 32.00040818767724, 49.545256301617286, 79.92447188852401, 29.256287402130006, 91.32271704026753, 44.563684380150015, 42.29914486354282, 52.09308671721831, 45.486025696249456, 52.88301045153307, 42.00705299030741, 49.691489075325194, 30.452842214569017, 65.60542817219302, 64.16718242590899, 47.25955998868055, 33.72957674420601, 75.95489718756824, 36.87257586911305, 33.99753641349442, 70.95414321350113, 61.058926116166234, 208.17803185764822, 37.63402799305486, 45.49465198460686, 39.12560665246367, 80.92438777671882, 113.28050239121224, 44.05248728010823, 76.7343877343577, 54.609196100170905, 25.76185903661254, 62.07962824801873, 82.80471083329854, 46.905567128330915, 35.704704169299134, 60.08701366730725, 45.21471668922558, 19.16767790666129, 53.70813266912269, 53.92453731216785, 35.672385863780484, 44.12695527940346, 54.10496730687892, 35.00039205930718, 56.04361907434365, 49.186668570926415, 45.77355814245593, 54.972385432501234, 59.2843449257045, 65.74714199733381, 101.21443407283455, 42.92572027278656, 6.8145580295622645, 22.243880763546965, 54.64659975176358, 6.479319924223309, 38.366191628550375, 33.94553355968703, 34.355070713829704, 79.81948876249044, 5.387713268333226, 150.17845630379637, 49.36029722250827, 36.29731395179807, 38.68533204606333, 4.895805260463403, 41.387476365505066, 4.394983629274903, 112.10839173193582, 29.415463250596684, 45.08338511731276, 99.64799867641835, 85.17998507086568, 23.080486082017455, 56.8617613748574, 46.91614953248807, 69.07514549704804, 56.31358803631817, 48.82016433543418, 64.96178291544146, 40.54188300526624, 47.394767582351754, 40.21295237521039, 46.95309953018124, 71.32636573223283, 34.02089922006422, 34.25314338962761, 5.826241917852109, 7.522162095332692, 68.70864056582967, 47.89007088545451, 57.267729009113395, 71.37785136189022, 36.4696606164705, 31.842336092307093, 43.96298834659793, 51.36244052091437, 76.10833083084101, 92.22051281545183, 97.38729965660767, 89.84715279039551, 66.33516352665202, 48.50959534681231, 35.481208018323585, 55.749716552608625, 78.96580235509556, 53.171493387905315, 75.07872351940348, 110.69843520092361, 72.04799196109826, 6.935963194233427, 63.3752488347127, 44.553427345012224, 49.987481849082585, 45.4354941057613, 79.27989341884286, 38.17254368543787, 106.14616220257307, 63.884776898949, 57.01919260852199, 52.78408798999247, 67.90230421013315, 161.7615506150018, 69.5653790508275, 46.2403206614873, 40.63220917627753, 11.586894361893611, 48.1000692790619, 37.436050656145504, 105.12324498387048, 75.10964262845137, 57.48052001367533, 58.67292382800493, 47.325404725058256, 61.70024365017493, 58.26667932592419, 64.42465742323228, 55.59080303913675, 32.277673359648986, 101.6953254059244, 60.35174107492678, 46.511422849147806, 46.174985178613085, 27.069725818509657, 43.90020793028596, 9.863258568215652, 43.853006361572476, 79.49080514197459, 45.992945860647964, 42.15684426333002, 48.31482282213751, 57.72530499406586, 36.820040965057736, 41.29493133858508, 77.87535657351053, 39.04368119480903, 5.968219002760266, 128.07903378838435, 51.75981691534076, 64.91233854667993, 42.3990753595697, 109.07106315769735, 57.61202914124909, 38.97083889209128, 37.999197871330686, 59.246114340303656, 122.33000060098726, 35.02648594628369, 53.923368271722026, 44.13781665321015, 72.38650532644708, 68.72208761187765, 39.64716214793105, 33.41575991541969, 51.83572449446606, 100.98995143931114, 67.36570121256194, 6.2575116409273726, 37.6834906466001, 98.20650173671271, 44.69547065943173, 84.19848299111165, 16.97248663559044, 116.32266771752438, 31.905024585863956, 45.380312954206, 71.05796370368124, 100.2520791715387, 86.88513021415194, 81.4472920477187, 48.19491603620605, 55.41926739698672, 43.12728769182303, 82.3221540828839, 46.628306050985515, 48.9525992790986, 72.38026947434201, 33.977054307960955, 45.209461909183084, 43.77225580186174, 80.28327301764196, 70.94526754824783, 97.530322667715, 53.101056919261026, 52.82495617137224, 51.0089105560459, 68.24229307569061, 46.578686423456375, 66.6868450899413, 38.07083220132359, 93.02640170575837, 43.598125034520436, 96.971937414405, 33.33172777228505, 51.61155030011069, 91.28880817702596, 148.82943539673184, 41.44332454772114, 36.24593253551085, 108.87877263629063, 60.24540026176503, 41.8449105536682, 65.73623283516748, 58.21032322124606, 135.99730110719509, 75.69592916716456, 64.47174197248536, 45.3302985273931, 76.22169987340646, 57.36868047982825, 58.74033466835192, 39.0764479859127, 37.729863209630786, 52.66250469980309, 82.71578956891439, 9.412019331131672, 99.64703068112655, 24.67323814208488, 48.38614011911015, 49.29300992591621, 5.78299628982602, 16.418086927532197, 85.86404544068046, 58.61937269055574, 55.43901851812425, 19.9516295159595, 55.45242422664013, 80.40020149443534, 53.6390195695746, 58.57004924592378, 42.99176304474049, 64.79109095973676, 74.19525667996933, 96.27016507557552, 49.18826030105939, 52.178941197975604, 39.12901139505127, 71.30020559807355, 75.94658824876075, 46.28247945888944, 84.64086976302698, 43.94385439417502, 51.68563256468609, 59.81432768493682, 109.30742181041553, 99.1528930306278, 42.30772973487042, 62.65624363599763, 33.860587040780246, 53.24781341357873, 73.48013757168727, 80.09857220651698, 59.9422492030461, 5.083865560318565, 49.523228730026815, 72.44936556288009, 49.69849516391776, 45.57093000842251, 73.81348094098234, 12.171663608711201, 56.202829417560004, 221.70787582651005, 41.811480756666626, 39.16808576846314, 61.247786601166794, 87.82416610736523, 55.785708898850345, 92.76962632730324, 81.0661698171983, 115.73988019950974, 53.18335055607712, 71.29512234775812, 94.3125022977522, 118.48827159899025, 51.36414182620702, 48.00011823083353, 56.28396627080919, 7.106088117292754, 78.33320788564296, 78.63516322259544, 104.14100024782778, 105.77291078152638, 21.870289373795668, 70.57918202515056, 131.39990423514553, 96.2710266276105, 66.60031072074487, 68.14001850235438, 70.92614096546302, 72.43375151280166, 115.84551162725509, 87.74973400957856, 6.366337872954869, 50.34968301383662, 61.03762188367406, 132.07154521937028, 32.287192563662195, 10.886042889935808, 66.98283826166893, 85.70747063319487, 64.60592290270375, 90.83705467645842, 55.0946459190592, 86.97695326155375, 128.1796666586658, 59.77327270893551, 53.58625464754049, 69.68705513956711, 42.18151493268643, 73.23000032184814, 69.00721362848849, 43.24565015364462, 7.655154480908487, 78.7073434434272, 25.867770708121256, 8.468170559002417, 47.325740950445855, 59.1454002581496, 11.133638877706932, 59.399192720197256, 52.60374274352376, 91.2113863497923, 63.89207747395787, 80.20888314365706, 41.95449577844266, 257.71901412581576, 87.3254659820844, 178.37255465754217, 34.66254959959083, 79.63766908680977, 71.88289651581987, 45.68039706103468, 20.98579095402432, 45.79421230876656, 94.66971400726294, 36.952383248289095, 43.78748705675594, 45.661972200713585, 42.95616134574452, 239.7126169457226, 52.97931745168599, 50.21944671413064, 56.934023351380105, 61.726197546865826, 63.376673075808775, 58.15460407387263, 112.15027769780936, 77.64961483222417, 55.70814978520145, 53.25499664414049, 56.48160142410649, 39.35285359239454, 48.54329356195631, 49.2433250416747, 63.523108157196965, 51.16332510728876, 60.90592541532727, 46.58450536033672, 3.9404107778825144, 96.32400867148908, 35.86494442329046, 122.71758403271502, 59.34894663808845, 64.05564778800564, 84.53586573367706, 73.99810479205101, 57.89543857152382, 50.32309732472577, 78.56384416814251, 151.12255597595393, 46.06562477742106, 60.62680392244914, 137.35101252990194, 72.52567955957068, 14.244076908578961, 59.31470286508681, 69.56627709716653, 13.076054098136648, 70.81676067964482, 49.93495731942765, 95.13349092334246, 67.60695101019951, 69.63218668588607, 61.13689946582116, 50.79762495900288, 40.713636413788066, 48.030786863864215, 55.09873351041693, 131.1523558090838, 50.347952526452026, 62.77293811253445, 40.75456510989109, 70.58021541970865, 115.93615003983989, 150.22283663928616, 147.11568189591864, 63.61506844833387, 63.475508986345204, 43.46885710040624, 179.16286642283637, 50.696607544008124, 50.483469053477165, 82.33677060891847, 154.95210341610556, 68.17926347086006, 52.3433662550623, 56.74354634642197, 46.44171474041274, 109.89914435866623, 72.4171870210623, 55.15469246632796, 50.052510799605045, 74.82733091791513, 94.94872031358821, 59.471655335184465, 50.64126755122833, 68.46816050435787, 57.46990313206475, 81.86732246376664, 72.48838151409456, 118.79260494198587, 47.483520834814215, 95.14065471549252, 52.894932810731504, 49.5493333870199, 54.37680081135713, 68.55445618659442, 65.64895932613383, 150.98009484846332, 105.88801092139096, 44.10436783308771, 143.4886246889756, 68.25729051997193, 88.67906762602253, 68.07389435107196, 41.13692595143553, 54.448181690699265, 98.3708730052786, 50.77487867273766, 36.82293974965613, 48.62794242524013, 54.289662952275044, 7.6834622356813735, 162.83211088949187, 98.3403287196838, 136.82315033095898, 43.50902063169769, 150.25130835496307, 53.65233620839475, 109.25410333316952, 64.43596196748088, 64.66509459083485, 134.06889163877128, 63.7602647729683, 87.88801628669451, 68.32890786746081, 20.52777860242785, 89.37636816833422, 91.30159694125395, 129.7482608931077, 48.91948425016739, 52.729658579526124, 136.42945798831687, 108.99020950355212, 51.35447679572036, 197.98071867995984, 67.81113237309746, 56.32781375376578, 108.87201724149666, 66.82884267823358, 96.1782320880676, 39.87806454009903, 142.23997851716373, 82.0117911080741, 75.88426739879617, 64.97667230099155, 8.451338044229464, 212.9694480333827, 43.51595389497825, 38.11183542299472, 350.7356130289314, 156.82771551752145, 133.66758153093548, 48.007149150075435, 51.35570547776458, 47.8053953278296, 49.542113625641015, 102.41201536583857, 111.15635919303048, 51.13382305766047, 42.314030926171434, 59.69336153500524, 50.96073994257569, 50.48829296325624, 10.298354293098216, 42.06148952601728, 116.3600331923193, 68.34889021655243, 132.4986171970966, 5.768183736784667, 25.29853061478769, 68.44768548952801, 82.29068443975058, 46.65665057570957, 75.18948168156105, 118.92416038815409, 183.9532683406451, 12.40043698494211, 56.07713863025346, 41.091285960817395, 95.94671481093505, 150.37933173036058, 214.03340305535943, 115.21900240159258, 117.67365397302743, 79.70648264523376, 71.13022811863351, 8.510831137493298, 99.3644535036189, 157.78109560892437, 189.64567524252175, 124.49685958307855, 42.72828114951954, 93.16112465467873, 76.32695783240372, 76.67215724207358, 54.763931709293225, 8.776102014745785, 231.18369439494356, 82.51876202549971, 134.3472643370094, 62.463359277261674, 43.40744945189109, 90.90896011872056, 56.50355474236, 155.02139554811777, 148.1281786483302, 48.58597772932432, 55.63755843641411, 77.54283611054159, 41.36425047897454, 57.63711181094372, 87.91939990142193, 61.83954746164089, 111.13894660212537, 169.61592476708756, 147.93151152098878, 114.39094942890564, 86.1317640163001, 56.94446952502485, 45.74653366956668, 65.61357674597605, 133.46679201640453, 137.51109877227142, 55.44758662822112, 105.30428546289927, 67.161072790516, 10.553420340568955, 40.80402807279793, 144.30214024547672, 90.45831331207559, 49.02949140310631, 47.740054387958864, 54.57246552309283, 98.07390379046502, 71.78286945749, 68.4354175831276, 72.90713958328107, 128.5910241952681, 104.29691481265095, 60.00680601270495, 77.81011717638525, 122.69516387747886, 46.779081394932355, 66.9716927802088, 56.97140149747794, 55.7243765133959, 48.27700070346729, 47.44580294817451, 134.8745693933035, 110.1687487776884, 74.64405682088842, 77.4128630230268, 160.93319948223407, 58.25190170115954, 50.014226533298164, 62.25394814396174, 40.528890593281936, 15.684759812516118, 226.64414001922444, 72.44517799208452, 66.12330155925892, 13.043341228386646, 37.76527051329676, 49.334320038988366, 49.923694682151904, 101.89963985805309, 84.24571346765555, 57.48551955428843, 68.18535441137102, 49.64849598372275, 152.25546035248817, 98.94553502070013, 95.16946613943453, 84.8431072923053, 70.02524138018605, 96.24667731249555, 122.91481566707847, 8.810417400265065, 42.78424168466413, 153.84362344644782, 35.66432944532083, 63.27235268621577, 10.501343777785687, 5.656969844208229, 97.5444830670971, 57.181540736305465, 84.05932077681072, 83.30276981601533, 81.77438297597914, 96.82736591252194, 61.05673465074399, 151.923650045828, 113.25298045257426, 128.95060175840183, 45.01738175527674, 48.16813115324248, 43.53406919418571, 71.05310061560994, 71.54691841824553, 152.81017233755506, 77.58886130044687, 8.652021646832441, 196.89904834923695, 82.90596725726517, 13.61394942986353, 25.800309538826916, 81.55970058236153, 7.095667237414763, 75.1940342792195, 46.229149174833054, 56.89062451256149, 67.53186811136656, 56.143606240669946, 92.8210195779722, 62.023970572784506, 219.3398131725758, 51.575434745884316, 132.38407816563887, 72.51532075241956, 61.58311205714627, 86.35411791638164, 63.857554819566744, 259.59721403039055, 46.90439290931609, 90.41137138118133, 35.90208832413783, 92.8795327825379, 139.4703472326558, 107.04766331812154, 73.44514200391917, 216.22147194656128, 86.25212161659191, 4.458532249492326, 89.65612243308817, 139.63930513247246, 42.44621972546133, 147.74764596692094, 51.9338122061067, 115.68221163912288, 118.63847523093531, 45.82197918560277, 101.07148721000856, 69.81939608727458, 61.296411700277424, 41.66223425908154, 62.013356980999205, 94.80177771381484, 149.36571870266877, 48.896838970523206, 123.02578546232445, 7.1424255909041, 158.71375330938622, 107.4728001058367, 73.6371685250041, 70.17522485558635, 34.93885195614383, 29.230316429558698, 157.25026407330088, 111.96549189127903, 75.80225982024089, 44.607266151370354, 260.04773352508516, 98.35203675461042, 72.56695687700773, 91.46386009737695, 53.376609404826795, 28.537130212238306, 135.77354370218703, 60.37165811332318, 75.60750439801606, 91.05815421283629, 89.68055602134932, 90.25365796481307, 46.45034434301342, 84.14268192311322, 63.214142800475294, 39.33312892472559, 113.23863106399273, 102.42971953265874, 56.71826135811814, 125.25000090084811, 58.992555804979396, 58.12399063316608, 86.21092050245689, 80.32854820589573, 84.41137171452816, 80.79580327659161, 76.17572994619154, 93.85996608186785, 74.92103251612374, 72.86113112127903, 61.44484392103578, 96.21556694968542, 316.91110144522605, 64.56421757909656, 118.48305155637065, 93.95001892326317, 56.97361827168382, 10.967518408302308, 88.7306564992456, 56.50229543171686, 97.98326522003525, 188.726202862695, 92.37203488096434, 71.29287521694913, 148.941340788156, 91.88143571334446, 38.29567973060706, 67.515701333597, 87.04795148144555, 63.95404789127794, 83.90227117690094, 11.31423686036527, 78.07531544265828, 123.24968344310035, 60.23874693310591, 45.61490270878979, 66.17609026119933, 122.10976235118484, 44.632771210142444, 63.66498756747037, 79.19506569127563, 48.3271971621384, 118.25384327420724, 164.02663054149582, 40.677031002797, 57.87776620042318, 131.0829432418935, 34.59950764847117, 103.36369360198802, 99.43708385157514, 42.42375937617298, 100.18285848705531, 84.86286467938795, 77.33159057726076, 79.76050804597824, 17.9804424357158, 93.1601812839586, 64.70596066487984, 96.72255855187882, 74.32074609487645, 76.21541313362393, 41.94581531252556, 129.78682337656232, 72.30241117763612, 45.85779740494339, 16.337960663698166, 78.37862638439, 78.80315974223603, 109.90316928330853, 6.932805820253797, 112.48427790580155, 74.4228129403346, 121.7383115086244, 56.47879759007379, 57.36385830245153, 66.61891203882398, 41.34254678697371, 65.07484010339887, 54.63044851708228, 60.713820870857845, 88.56759638546902, 123.06600457770534, 13.117635495036318, 116.33371364508622, 78.27825827399809, 53.389163816728065, 258.5640688756818, 91.63184977907257, 119.12493298478783, 62.35972296361223, 108.46109655370506, 49.70854314900215, 48.15961248176457, 151.0064442432747, 65.47455866451396, 84.5734694880066, 56.1915968486481, 34.02361092401438, 119.1137906623929, 5.779339254122993, 124.1266860739981, 67.7305952976356, 68.45935751437153, 9.955878761852883, 6.1088276985125205, 70.78646755718597, 66.58532860110743, 64.64531404204074, 66.71542215386091, 72.37358310905225, 16.71057540487546, 233.91674530050264, 93.01653301652334, 159.29350428317406, 49.23574385898224, 8.60218831617823, 46.3057711994342, 45.68089163989582, 81.74187052514587, 79.64667311701959, 134.3226379305417, 123.14431676229354, 6.276214941416323, 57.990199362705035, 94.77845662221158, 10.503422284421518, 89.51981024381233, 128.4690966845299, 9.69915541746149, 126.1793427608151, 55.15525335003481, 49.434896429121636, 58.88496446904233, 120.05084533512199, 105.68272806728653, 56.5281487960712, 209.32172799016166, 89.15717564628206, 117.59503024437636, 75.62718878674717, 13.13173684299571, 106.21434119819175, 43.52739281945578, 59.01512136222129, 15.843848175187743, 61.42722352549383, 104.72784694283577, 48.866645017204675, 80.08636979338378, 60.0058308774252, 182.32318349096747, 70.7578095828128, 13.822213226100313, 50.69569369406099, 87.63425898569311, 56.6782842359707, 75.67070428124131, 46.58984789958236, 52.377831139143424, 70.00116645419546, 63.82577740465839, 43.74785392807483, 112.24033882940105, 58.66899803546241, 28.3405370495909, 82.2093550788167, 65.11160857839786, 58.352868041409074, 82.15135559574348, 52.274185810927115, 10.019025721457025, 74.0815442196226, 83.62251910554686, 87.07706894231113, 76.90869352887506, 5.379682006855135, 157.75545459663343, 58.41525504188929, 79.64596927912835, 145.83374740212452, 65.23482339110666, 58.60599934344674, 48.669051788201834, 113.70003831786352, 73.04648946964338, 87.3536191602163, 67.5659711270076, 136.42019163864717, 82.56493332604335, 104.67156411716076, 148.4688260278693, 213.27290624451075, 52.078292145990915, 126.52683268160375, 106.87912191831762, 53.151567924863826, 76.72446221157865, 103.9940365296362, 27.363367449010827, 70.60762053487502, 46.01858903375472, 92.08730990427688, 44.76642078803752, 4.626766459374778, 119.97932575892924, 57.45813665703944, 109.96904248407309, 94.26400089696777, 83.82572857458436, 74.32086258522492, 65.25643429502394, 82.78144747613743, 217.14253175266018, 127.85017296610606, 51.177220126804734, 9.871239807566875, 98.38744289178258, 28.23664261175732, 62.72755442602626, 57.23790324733992, 110.22084038006219, 88.35855229986194, 51.50555270399427, 108.57534000532056, 128.46136693756608, 55.69153639726567, 71.77367097120352, 86.40176688608804, 107.7456121704554, 44.223976064872915, 69.35964681302958, 57.453506945211146, 105.58924780109044, 72.47059173452698, 33.05023903364435, 56.08115166291099, 50.31483953682463, 32.18331791292511, 71.03232579182962, 145.3769034609088, 45.199357195295, 89.49349345119467, 58.74678111333528, 118.02850681084905, 79.01326082103499, 80.94953441133103, 120.25962082378895, 100.36451871791787, 167.32540979086875, 109.83407403386421, 47.55297295685772, 92.02477713824362, 35.896877084806384, 56.814255494128616, 284.3708262076002, 65.95766476382404, 68.930241615997, 279.87806365591, 122.93060759904267, 103.7672170142099, 152.41284946296608, 86.58329029807345, 52.39420395845624, 70.26034463410409, 138.7227519245404, 141.93891108633224, 97.68992346568957, 72.09486826664694, 89.29407513270067, 284.8554649878332, 5.856235445373345, 42.18945283180205, 68.0579691452187, 53.39524842689455, 76.22584367539378, 66.38965080880679, 183.47314829817716, 119.33090921099041, 58.334347809670604, 109.29497948426665, 54.76153589603262, 59.84482365680796, 87.30733565374436, 136.94153713924825, 62.52862844717205, 130.26890060214376, 92.36983511378888, 11.532562962435005, 55.67637264617045, 93.01090918905972, 49.87389429451841, 204.87926484571528, 103.00635366522799, 128.46780565846382, 103.93214235055281, 66.84575462087754, 74.84232699706125, 73.01193296424228, 54.622655705899234, 84.7116172441815, 105.1076396354139, 63.47013082841631, 212.11147002356648, 78.37452160659257, 78.84495986097674, 63.61737350073797, 116.47452151606973, 50.70545009281794, 59.9134602685798, 108.10986434561016, 79.760435479117, 140.52511923174777, 67.50097886164166, 92.1465005232143, 83.9560582492435, 31.561076961932464, 72.29193920614787, 64.60194053709213, 56.18416327782659, 73.88641464692529, 138.3182174627557, 79.13850307892754, 43.80357244616292, 51.3365557585343, 79.20826077436472, 110.98865406240587, 94.29761568150886, 69.28237021509608, 75.21113621148217, 70.90796366230637, 66.35676353839015, 137.21026506050487, 46.48834063396366, 116.33912280932083, 89.78865031075424, 67.32711741284045, 44.304873933532214, 47.06833108371223, 149.01028147076113, 52.929547140324374, 56.72680739156594, 70.04972318689838, 49.056610467596045, 72.04856063258549, 51.629654866007805, 74.3314845782468, 168.37680837677337, 168.84509607849873, 56.97385933179258, 5.137637841416195, 51.47255650248787, 87.27141533267958, 109.11289758880297, 54.65842092295586, 104.93408821366346, 60.88897848813581, 59.3440716894426, 21.57922555906572, 93.62042401330174, 117.03059560633714, 116.95048621432116, 69.02172177187502, 58.62223018815314, 52.26889631526667, 116.80584469745502, 72.11802635131892, 80.42942299180005, 60.9498377628937, 131.30174445974794, 115.91435101787671, 108.76636615861453, 68.49313881259172, 111.51559694004887, 69.93662423159165, 138.86579703286367, 77.2462363308696, 55.18606378631796, 24.450178949598577, 97.1392453372729, 61.08420967292976, 56.996470181207016, 85.74894505848334, 101.43847691258698, 65.04852404980147, 35.412793169804594, 155.0701715726338, 46.78896087635038, 263.7723618738318, 94.82735452425058, 57.29870244159659, 61.80286017320809, 68.25739991008783, 54.47611616869927, 34.975580948268494, 6.596985131346891, 63.81286131102445, 64.88859021126954, 66.70867925183782, 64.1907266319235, 59.490086507415455, 43.53540020577189, 43.92889879929436, 313.6301124246846, 99.12476053381457, 8.018902567235228, 72.02127034887783, 64.8600417149363, 208.86991638172682, 91.473365839466, 117.65180860245582, 67.1537629091993, 67.40700000366029, 84.0004352734268, 68.93299896325107, 123.87936000827618, 107.16102961529212, 99.73487438671403, 90.4417285395673, 66.68806822776975, 71.27822899485534, 82.21512688755506, 111.33160724843474, 49.68442088887898, 191.4275239559384, 85.5575687571715, 59.43005813068472, 112.23964361100035, 64.12932453135191, 85.40516833029507, 77.28947029858726, 157.41032207973535, 62.902214209234685, 11.213393700101935, 152.37388901294506, 161.4861542910597, 80.86201301783687, 10.165605071450212, 119.05133263722934, 76.04403350965777, 73.13363492869985, 7.598340616091483, 81.2164127278169, 75.72771724845423, 63.326239614323875, 108.20156818886537, 89.12572206591898, 85.05914650624783, 64.07855337377495, 53.45323882487778, 81.74800285098215, 121.23237867725858, 102.15471245951981, 114.70143820128743, 136.72699937639533, 43.18004858194765, 71.18692366018306, 120.71475217621264, 92.81643032704878, 52.64938707119038, 4.778390662809695, 89.37795844491497, 47.61440256008689, 37.69058523488172, 51.61978458881987, 45.411024199307676, 52.14312630038894, 97.05950800577357, 52.492109404882385, 109.24572354900009, 81.00659738737635, 68.20643593853013, 75.30861503204012, 139.79027920243723, 43.54412677391732, 82.9200764691518, 136.32962289725324, 157.83111689788674, 105.50044103662489, 79.72511413511288, 90.24512596719093, 106.03478309848525, 79.18976314633333, 91.69731210843932, 7.161510396374102, 198.6720525053756, 71.40121371522378, 113.48193554575224, 62.15409351349062, 49.94507360909834, 129.91825698747667, 178.37424781664816, 6.272394315332859, 54.94768528979481, 96.75173991068552, 71.83968969313067, 65.76749838699888, 72.0625032528555, 88.49332210144756, 86.70610771855561, 113.371763438666, 82.64823069788982, 113.51177111861796, 71.17039800391474, 74.03425442042526, 50.86874689349324, 245.29130934666478, 67.29840877443768, 57.127416956184526, 94.35765090373361, 88.75224927552043, 189.3973220081023, 192.6355045635566, 153.56893304873154, 60.23259408359655, 52.63725354933162, 53.59751022031681, 148.02678275864565, 73.32690640650789, 78.91826983356906, 58.66377436808404, 98.62507659359707, 87.31219841669818, 143.45088926528803, 44.75515499748723, 155.86209103688086, 93.43243704144336, 89.82689015461102, 91.36908104091093, 67.63727589194421, 62.40288416806042, 82.69187207303337, 78.5156061615362, 153.07784834079783, 89.88752694396449, 50.41841179684916, 50.97923504271824, 178.46648037174054, 90.23148147467128, 62.616798390173834, 77.49909537499707, 62.04984556935734, 90.88387312709231, 34.26553272199796, 65.28427072932105, 67.63168500981277, 99.57207535381924, 65.53099956709958, 207.43663309241168, 89.91400238828163, 441.7090178769266, 82.82186301293001, 53.20684674648702, 40.67707777226201, 90.17573880679487, 133.55222560051718, 100.94198510351158, 65.44759062524453, 116.28992211677411, 51.52407269882342, 36.45104799795456, 127.30251815922097, 130.25742795838872, 45.45996953070656, 34.722798906421275, 78.63200209857615,</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>117.5315532493591</v>
+      </c>
+      <c r="S36" t="n">
+        <v>91.26385716178538</v>
+      </c>
+      <c r="T36" t="n">
+        <v>100</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>[115.11665344238281, 103.69825744628906, 127.93094635009766, 79.83558654785156, 83.26913452148438, 181.39236450195312, 141.68099975585938, 173.3926239013672, 39.33804702758789, 92.09040832519531, 68.59166717529297, 189.92835998535156, 35.237430572509766, 70.79370880126953, 118.96125030517578, 204.5042266845703, 103.06398010253906, 151.9327850341797, 71.95588684082031, 399.021728515625, 66.20675659179688, 209.1926727294922, 106.28140258789062, 9.447199821472168, 34.837860107421875, 48.77973556518555, 76.03938293457031, 9.708819389343262, 51.8015022277832, 93.85595703125, 48.49617004394531, 68.54496765136719, 77.3094482421875, 91.0130844116211, 15.693909645080566, 99.15660858154297, 94.0801773071289, 249.12811279296875, 102.61384582519531, 84.12725830078125, 172.531005859375, 82.18936920166016, 557.05029296875, 68.55414581298828, 111.10199737548828, 207.05694580078125, 67.2025146484375, 533.1022338867188, 50.59560775756836, 141.61537170410156, 73.85720825195312, 64.45997619628906, 72.71294403076172, 44.775028228759766, 195.22462463378906, 91.18205261230469, 51.651126861572266, 99.50089263916016, 249.7707977294922, 78.50433349609375, 93.9478530883789, 125.20960235595703, 123.3061752319336, 54.926124572753906, 305.4013366699219, 58.446815490722656, 69.91403198242188, 201.76296997070312, 63.52057647705078, 293.38360595703125, 76.8183822631836, 84.92288208007812, 69.3428955078125, 69.11119842529297, 68.11460876464844, 271.09747314453125, 120.18218994140625, 233.5401611328125, 96.58574676513672, 117.64987182617188, 75.17627716064453, 85.39385223388672, 54.62156677246094, 105.64508819580078, 88.56134033203125, 169.728515625, 65.80217742919922, 164.71185302734375, 11.097228050231934, 153.1634063720703, 35.68181610107422, 50.07884979248047, 195.0278778076172, 106.65154266357422, 102.44050598144531, 47.07980728149414, 122.96456146240234, 134.52674865722656, 89.88441467285156, 97.04400634765625]</t>
         </is>
       </c>
     </row>

--- a/Work/policy/runs_results.xlsx
+++ b/Work/policy/runs_results.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="2">
@@ -2993,77 +2993,1577 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>p-1.0srandomst00316</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>2026-03-31 06:49:21</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="E36" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ppo</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>100</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="E36" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L36" s="3" t="n">
         <v>87.85169267210608</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="3" t="n">
         <v>67.04693261148985</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="3" t="n">
         <v>104.2089676746611</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" s="3" t="n">
         <v>4795</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>[0.9307515971243785, 1.541087283969086, 1.9476840864162939, 0.609657316764484, 1.4193136445483463, 0.6567556558924583, 1.4103143703053997, 0.4475560977714044, 0.38553487306247547, 0.9296241955537997, 1.7748852121285565, 1.72214856671768, 1.1192656987972867, 1.249478662305523, 0.7644384381112678, 0.6585971701943899, 0.5233498986442064, 0.5230420235554072, 1.2587815053724853, 1.4919287474789202, 1.2043552647478533, 1.218187234729192, 1.3479398457642668, 0.7115299492629444, 1.3408170841383036, 1.1853127071972862, 0.6690622980483024, 1.2445400055634823, 0.9800427179928052, 2.3373480031077722, 0.8960307444709379, 0.8778507912927983, 0.6924244309748506, 1.3091256814975334, 1.3267115186799643, 0.60095415560067, 1.092732159757896, 0.9180056893744589, 1.4409936115582835, 1.609763630925567, 1.6301345455553198, 1.7505939844756355, 3.3953805615667303, 1.7257133362325956, 1.7955324668880723, 2.0183843906473737, 3.0521207144111893, 2.337306836110346, 1.5785889470379482, 0.22301937783894574, 1.0211510175785656, 1.5853029561930447, 1.178107336219869, 2.6259330679522424, 2.7186393189568423, 1.5085714831447166, 1.9504188816214896, 0.671484753092623, 2.125625252425104, 1.5085986001271914, 2.096826282999945, 0.803189183756675, 2.947783929358203, 2.144432304600102, 1.553837029359036, 1.9244218427596715, 2.0974237678126717, 0.18003826362324427, 2.0516468824286025, 2.8893784633117234, 2.189385532732124, 1.3151454674753817, 3.2818169552312844, 1.2460770796499834, 1.280490672374502, 1.4907258673311625, 1.7650942268268814, 1.0719523632358543, 2.9539525785155387, 0.39875468636318423, 3.988047241344027, 1.323218030455267, 1.1673095630226773, 1.6232462543229906, 1.3158018316741762, 3.971688698917009, 3.0466841092236434, 0.3422285318885405, 2.518245990965293, 3.2487950571000863, 1.3874970919977234, 2.4825059883154763, 2.536621930449387, 2.119330462274465, 2.969757596454085, 1.7769096843330825, 3.638387736499708, 3.9397310206958203, 2.1068951247045984, 2.455488922634394, 2.7550206108051545, 1.6145031159288061, 2.367707115979653, 1.3703405352729265, 2.0905108131381644, 2.981833790284511, 1.016545249424158, 1.9251212294321265, 2.226498690331356, 3.267565467806502, 3.839941792539075, 1.149442000096305, 2.4252317575416513, 2.330678540972556, 3.7386744277340043, 3.9715538924800073, 1.8402926829798332, 2.9352343457905, 3.1970230161322752, 7.58777171322421, 2.202019088407834, 1.9297089853993377, 4.6118473482842095, 0.5115624274566667, 5.43259143825825, 5.77676852325588, 2.7066144608173666, 3.7837069270932844, 2.216309661096726, 3.293040397869488, 3.1257888846006963, 4.6710564299329205, 7.3838423910758575, 3.2362655599582126, 4.602402857761743, 5.292110833469994, 4.650608843943067, 4.559310980301597, 8.603468387832615, 1.9380418206798655, 3.8660446487887654, 4.439449557618157, 3.797050396729444, 5.700766009605458, 2.2484336442105373, 5.751121412542625, 2.221196727771105, 3.5481773300547923, 4.180693914477461, 2.1597223141601014, 3.882390912987609, 0.7546797279219867, 4.406342099762679, 2.7160424734411683, 2.5028872978831767, 5.890906670836395, 3.9630606489103384, 3.258359765184622, 0.8213229944235813, 7.55366588317239, 8.334818253665194, 14.044511611793986, 8.03949134221256, 20.179919395920752, 8.897170780953084, 21.060476840176065, 6.711996365955258, 8.419157769453502, 7.824054008584268, 10.437057047128114, 4.134822301073763, 3.7103416391176647, 5.867303819024335, 6.5379308817560675, 6.369153796383323, 4.507105227891444, 17.719587698745876, 14.024815089123743, 5.493781033503976, 6.316555951565572, 4.0809264189474534, 7.1043686197088185, 6.1160891001117434, 19.311919400084463, 7.529732878795271, 9.816759879340019, 7.733983449821657, 4.4137025639139855, 6.506586688870208, 5.314717953667567, 5.179971560067091, 6.243704848268668, 14.862388272306784, 18.58091605581896, 16.154215876702743, 13.818817565147492, 8.42466422115115, 18.543715052966334, 9.235161400356455, 10.373883384566524, 18.86969944777893, 17.195039733877202, 19.759062357179303, 13.290323165503715, 12.253166886828076, 14.219907491049064, 22.422992612912296, 10.93388608044417, 9.434153377497164, 17.44786842051909, 15.33285425101143, 10.979069638084146, 9.674227347015307, 6.227376826074477, 11.817652798071716, 10.516621770525804, 17.181759030811758, 18.735553078175414, 13.554359604713614, 21.13685793641821, 3.8351305380832748, 16.490544620526297, 3.540468970225927, 25.57510469272413, 19.031243951352117, 23.48957884407211, 16.30330190791164, 16.52915301068577, 21.949762080008288, 22.701009719092067, 12.441561668829351, 10.211261404158817, 10.000025237926778, 7.33200480610435, 1.8951489297455666, 27.59810990829101, 31.79328428421515, 17.548040477211014, 12.032041538956962, 32.63013433909962, 15.366795078753293, 7.170240492933708, 15.487324360695915, 20.30455942097752, 20.924704301800045, 28.11618636201432, 28.66104519186694, 12.266250405781316, 13.371013577831384, 26.19278666356908, 15.683694068489165, 25.54375035029043, 7.3066494358218375, 19.045683067567005, 23.332015583575206, 13.51979573056596, 51.484952955710106, 47.140497431189054, 24.423549296248133, 32.893070413116774, 44.810305314897136, 50.29283685164397, 4.154410485231698, 15.927353076882033, 9.190941706823168, 19.4583074868293, 12.292467040879863, 11.40382774908159, 14.602005905360373, 34.198702585217035, 24.12802170392303, 19.491578495312982, 16.857107086488355, 29.49340095412361, 36.34534734545042, 29.600436862728518, 47.089277734165236, 29.1439722506668, 48.076877036286604, 19.288254087646155, 31.131214956095874, 28.254769452114616, 26.497087340072735, 26.757322838237624, 39.70118264828931, 10.633331606687289, 52.49354753971245, 5.6526650788898465, 13.657259729823043, 28.729693659325118, 31.6722845890086, 29.57805426687395, 22.38551771078051, 20.967210665753253, 50.45089654849414, 20.960308599279884, 40.21293939314967, 23.097725285972867, 17.012893884534236, 26.297648218623443, 42.28374891560404, 36.50407004687371, 30.709033560911276, 27.34464967513695, 15.337290762997627, 36.65356022236748, 4.29736505695648, 22.614347444363016, 42.69311694252934, 29.042706479802888, 69.9584776264087, 3.2836117846567814, 39.80574149005928, 25.426106996902607, 43.535633308208844, 22.704426958672418, 20.975486177678707, 55.743449364795055, 39.799603141424235, 63.39662916490663, 18.40982456478585, 2.647112040874927, 40.45944844030907, 34.18323012586173, 4.578102305364208, 23.149549023444656, 5.162617554994013, 21.109172322302364, 40.98714514545532, 46.24935476585298, 29.488618813171005, 53.858447186520834, 88.10645812529337, 56.53594728057043, 3.394693094716162, 53.761458001301555, 37.09520373413942, 31.258756527941003, 28.91282199254831, 20.768869718680712, 36.83943466581584, 42.8881825938485, 41.78680062057403, 5.249719281929954, 37.543992592093005, 37.193282654485415, 63.751653121994764, 40.435071345145595, 47.08628651467328, 26.492122230791708, 32.6130635765671, 59.09457625995066, 6.248631518885214, 57.36454839882278, 24.01239212323398, 28.24602826193373, 56.055498362396854, 38.493835945714245, 95.9894492329377, 30.16801320770902, 4.079736343305793, 30.069393996398908, 51.98432677850438, 38.34362477811743, 59.33806429324127, 27.65722414159275, 29.948550104853222, 38.57954396683502, 43.50951873660327, 60.31234207964966, 54.74740148005805, 37.47807013568497, 92.55098194724438, 48.20538720752182, 50.73942666245679, 86.1723931700718, 39.939636110679, 85.65440901352173, 32.15302556466991, 37.37479660780086, 65.55349126928984, 52.52574532351515, 35.90977765414096, 66.27639160468432, 44.13116374861013, 58.98802965479609, 67.19019687234207, 42.21732693295019, 75.58532175231855, 47.10457669572965, 74.15448558129293, 52.45036789803169, 41.46575728697655, 51.831536502639146, 51.49538817737444, 41.994563985925055, 44.178212866329915, 34.31799937177905, 45.4361339966889, 25.831435041056967, 32.92451438594728, 13.465930724495202, 81.69677608296041, 32.00040818767724, 49.545256301617286, 79.92447188852401, 29.256287402130006, 91.32271704026753, 44.563684380150015, 42.29914486354282, 52.09308671721831, 45.486025696249456, 52.88301045153307, 42.00705299030741, 49.691489075325194, 30.452842214569017, 65.60542817219302, 64.16718242590899, 47.25955998868055, 33.72957674420601, 75.95489718756824, 36.87257586911305, 33.99753641349442, 70.95414321350113, 61.058926116166234, 208.17803185764822, 37.63402799305486, 45.49465198460686, 39.12560665246367, 80.92438777671882, 113.28050239121224, 44.05248728010823, 76.7343877343577, 54.609196100170905, 25.76185903661254, 62.07962824801873, 82.80471083329854, 46.905567128330915, 35.704704169299134, 60.08701366730725, 45.21471668922558, 19.16767790666129, 53.70813266912269, 53.92453731216785, 35.672385863780484, 44.12695527940346, 54.10496730687892, 35.00039205930718, 56.04361907434365, 49.186668570926415, 45.77355814245593, 54.972385432501234, 59.2843449257045, 65.74714199733381, 101.21443407283455, 42.92572027278656, 6.8145580295622645, 22.243880763546965, 54.64659975176358, 6.479319924223309, 38.366191628550375, 33.94553355968703, 34.355070713829704, 79.81948876249044, 5.387713268333226, 150.17845630379637, 49.36029722250827, 36.29731395179807, 38.68533204606333, 4.895805260463403, 41.387476365505066, 4.394983629274903, 112.10839173193582, 29.415463250596684, 45.08338511731276, 99.64799867641835, 85.17998507086568, 23.080486082017455, 56.8617613748574, 46.91614953248807, 69.07514549704804, 56.31358803631817, 48.82016433543418, 64.96178291544146, 40.54188300526624, 47.394767582351754, 40.21295237521039, 46.95309953018124, 71.32636573223283, 34.02089922006422, 34.25314338962761, 5.826241917852109, 7.522162095332692, 68.70864056582967, 47.89007088545451, 57.267729009113395, 71.37785136189022, 36.4696606164705, 31.842336092307093, 43.96298834659793, 51.36244052091437, 76.10833083084101, 92.22051281545183, 97.38729965660767, 89.84715279039551, 66.33516352665202, 48.50959534681231, 35.481208018323585, 55.749716552608625, 78.96580235509556, 53.171493387905315, 75.07872351940348, 110.69843520092361, 72.04799196109826, 6.935963194233427, 63.3752488347127, 44.553427345012224, 49.987481849082585, 45.4354941057613, 79.27989341884286, 38.17254368543787, 106.14616220257307, 63.884776898949, 57.01919260852199, 52.78408798999247, 67.90230421013315, 161.7615506150018, 69.5653790508275, 46.2403206614873, 40.63220917627753, 11.586894361893611, 48.1000692790619, 37.436050656145504, 105.12324498387048, 75.10964262845137, 57.48052001367533, 58.67292382800493, 47.325404725058256, 61.70024365017493, 58.26667932592419, 64.42465742323228, 55.59080303913675, 32.277673359648986, 101.6953254059244, 60.35174107492678, 46.511422849147806, 46.174985178613085, 27.069725818509657, 43.90020793028596, 9.863258568215652, 43.853006361572476, 79.49080514197459, 45.992945860647964, 42.15684426333002, 48.31482282213751, 57.72530499406586, 36.820040965057736, 41.29493133858508, 77.87535657351053, 39.04368119480903, 5.968219002760266, 128.07903378838435, 51.75981691534076, 64.91233854667993, 42.3990753595697, 109.07106315769735, 57.61202914124909, 38.97083889209128, 37.999197871330686, 59.246114340303656, 122.33000060098726, 35.02648594628369, 53.923368271722026, 44.13781665321015, 72.38650532644708, 68.72208761187765, 39.64716214793105, 33.41575991541969, 51.83572449446606, 100.98995143931114, 67.36570121256194, 6.2575116409273726, 37.6834906466001, 98.20650173671271, 44.69547065943173, 84.19848299111165, 16.97248663559044, 116.32266771752438, 31.905024585863956, 45.380312954206, 71.05796370368124, 100.2520791715387, 86.88513021415194, 81.4472920477187, 48.19491603620605, 55.41926739698672, 43.12728769182303, 82.3221540828839, 46.628306050985515, 48.9525992790986, 72.38026947434201, 33.977054307960955, 45.209461909183084, 43.77225580186174, 80.28327301764196, 70.94526754824783, 97.530322667715, 53.101056919261026, 52.82495617137224, 51.0089105560459, 68.24229307569061, 46.578686423456375, 66.6868450899413, 38.07083220132359, 93.02640170575837, 43.598125034520436, 96.971937414405, 33.33172777228505, 51.61155030011069, 91.28880817702596, 148.82943539673184, 41.44332454772114, 36.24593253551085, 108.87877263629063, 60.24540026176503, 41.8449105536682, 65.73623283516748, 58.21032322124606, 135.99730110719509, 75.69592916716456, 64.47174197248536, 45.3302985273931, 76.22169987340646, 57.36868047982825, 58.74033466835192, 39.0764479859127, 37.729863209630786, 52.66250469980309, 82.71578956891439, 9.412019331131672, 99.64703068112655, 24.67323814208488, 48.38614011911015, 49.29300992591621, 5.78299628982602, 16.418086927532197, 85.86404544068046, 58.61937269055574, 55.43901851812425, 19.9516295159595, 55.45242422664013, 80.40020149443534, 53.6390195695746, 58.57004924592378, 42.99176304474049, 64.79109095973676, 74.19525667996933, 96.27016507557552, 49.18826030105939, 52.178941197975604, 39.12901139505127, 71.30020559807355, 75.94658824876075, 46.28247945888944, 84.64086976302698, 43.94385439417502, 51.68563256468609, 59.81432768493682, 109.30742181041553, 99.1528930306278, 42.30772973487042, 62.65624363599763, 33.860587040780246, 53.24781341357873, 73.48013757168727, 80.09857220651698, 59.9422492030461, 5.083865560318565, 49.523228730026815, 72.44936556288009, 49.69849516391776, 45.57093000842251, 73.81348094098234, 12.171663608711201, 56.202829417560004, 221.70787582651005, 41.811480756666626, 39.16808576846314, 61.247786601166794, 87.82416610736523, 55.785708898850345, 92.76962632730324, 81.0661698171983, 115.73988019950974, 53.18335055607712, 71.29512234775812, 94.3125022977522, 118.48827159899025, 51.36414182620702, 48.00011823083353, 56.28396627080919, 7.106088117292754, 78.33320788564296, 78.63516322259544, 104.14100024782778, 105.77291078152638, 21.870289373795668, 70.57918202515056, 131.39990423514553, 96.2710266276105, 66.60031072074487, 68.14001850235438, 70.92614096546302, 72.43375151280166, 115.84551162725509, 87.74973400957856, 6.366337872954869, 50.34968301383662, 61.03762188367406, 132.07154521937028, 32.287192563662195, 10.886042889935808, 66.98283826166893, 85.70747063319487, 64.60592290270375, 90.83705467645842, 55.0946459190592, 86.97695326155375, 128.1796666586658, 59.77327270893551, 53.58625464754049, 69.68705513956711, 42.18151493268643, 73.23000032184814, 69.00721362848849, 43.24565015364462, 7.655154480908487, 78.7073434434272, 25.867770708121256, 8.468170559002417, 47.325740950445855, 59.1454002581496, 11.133638877706932, 59.399192720197256, 52.60374274352376, 91.2113863497923, 63.89207747395787, 80.20888314365706, 41.95449577844266, 257.71901412581576, 87.3254659820844, 178.37255465754217, 34.66254959959083, 79.63766908680977, 71.88289651581987, 45.68039706103468, 20.98579095402432, 45.79421230876656, 94.66971400726294, 36.952383248289095, 43.78748705675594, 45.661972200713585, 42.95616134574452, 239.7126169457226, 52.97931745168599, 50.21944671413064, 56.934023351380105, 61.726197546865826, 63.376673075808775, 58.15460407387263, 112.15027769780936, 77.64961483222417, 55.70814978520145, 53.25499664414049, 56.48160142410649, 39.35285359239454, 48.54329356195631, 49.2433250416747, 63.523108157196965, 51.16332510728876, 60.90592541532727, 46.58450536033672, 3.9404107778825144, 96.32400867148908, 35.86494442329046, 122.71758403271502, 59.34894663808845, 64.05564778800564, 84.53586573367706, 73.99810479205101, 57.89543857152382, 50.32309732472577, 78.56384416814251, 151.12255597595393, 46.06562477742106, 60.62680392244914, 137.35101252990194, 72.52567955957068, 14.244076908578961, 59.31470286508681, 69.56627709716653, 13.076054098136648, 70.81676067964482, 49.93495731942765, 95.13349092334246, 67.60695101019951, 69.63218668588607, 61.13689946582116, 50.79762495900288, 40.713636413788066, 48.030786863864215, 55.09873351041693, 131.1523558090838, 50.347952526452026, 62.77293811253445, 40.75456510989109, 70.58021541970865, 115.93615003983989, 150.22283663928616, 147.11568189591864, 63.61506844833387, 63.475508986345204, 43.46885710040624, 179.16286642283637, 50.696607544008124, 50.483469053477165, 82.33677060891847, 154.95210341610556, 68.17926347086006, 52.3433662550623, 56.74354634642197, 46.44171474041274, 109.89914435866623, 72.4171870210623, 55.15469246632796, 50.052510799605045, 74.82733091791513, 94.94872031358821, 59.471655335184465, 50.64126755122833, 68.46816050435787, 57.46990313206475, 81.86732246376664, 72.48838151409456, 118.79260494198587, 47.483520834814215, 95.14065471549252, 52.894932810731504, 49.5493333870199, 54.37680081135713, 68.55445618659442, 65.64895932613383, 150.98009484846332, 105.88801092139096, 44.10436783308771, 143.4886246889756, 68.25729051997193, 88.67906762602253, 68.07389435107196, 41.13692595143553, 54.448181690699265, 98.3708730052786, 50.77487867273766, 36.82293974965613, 48.62794242524013, 54.289662952275044, 7.6834622356813735, 162.83211088949187, 98.3403287196838, 136.82315033095898, 43.50902063169769, 150.25130835496307, 53.65233620839475, 109.25410333316952, 64.43596196748088, 64.66509459083485, 134.06889163877128, 63.7602647729683, 87.88801628669451, 68.32890786746081, 20.52777860242785, 89.37636816833422, 91.30159694125395, 129.7482608931077, 48.91948425016739, 52.729658579526124, 136.42945798831687, 108.99020950355212, 51.35447679572036, 197.98071867995984, 67.81113237309746, 56.32781375376578, 108.87201724149666, 66.82884267823358, 96.1782320880676, 39.87806454009903, 142.23997851716373, 82.0117911080741, 75.88426739879617, 64.97667230099155, 8.451338044229464, 212.9694480333827, 43.51595389497825, 38.11183542299472, 350.7356130289314, 156.82771551752145, 133.66758153093548, 48.007149150075435, 51.35570547776458, 47.8053953278296, 49.542113625641015, 102.41201536583857, 111.15635919303048, 51.13382305766047, 42.314030926171434, 59.69336153500524, 50.96073994257569, 50.48829296325624, 10.298354293098216, 42.06148952601728, 116.3600331923193, 68.34889021655243, 132.4986171970966, 5.768183736784667, 25.29853061478769, 68.44768548952801, 82.29068443975058, 46.65665057570957, 75.18948168156105, 118.92416038815409, 183.9532683406451, 12.40043698494211, 56.07713863025346, 41.091285960817395, 95.94671481093505, 150.37933173036058, 214.03340305535943, 115.21900240159258, 117.67365397302743, 79.70648264523376, 71.13022811863351, 8.510831137493298, 99.3644535036189, 157.78109560892437, 189.64567524252175, 124.49685958307855, 42.72828114951954, 93.16112465467873, 76.32695783240372, 76.67215724207358, 54.763931709293225, 8.776102014745785, 231.18369439494356, 82.51876202549971, 134.3472643370094, 62.463359277261674, 43.40744945189109, 90.90896011872056, 56.50355474236, 155.02139554811777, 148.1281786483302, 48.58597772932432, 55.63755843641411, 77.54283611054159, 41.36425047897454, 57.63711181094372, 87.91939990142193, 61.83954746164089, 111.13894660212537, 169.61592476708756, 147.93151152098878, 114.39094942890564, 86.1317640163001, 56.94446952502485, 45.74653366956668, 65.61357674597605, 133.46679201640453, 137.51109877227142, 55.44758662822112, 105.30428546289927, 67.161072790516, 10.553420340568955, 40.80402807279793, 144.30214024547672, 90.45831331207559, 49.02949140310631, 47.740054387958864, 54.57246552309283, 98.07390379046502, 71.78286945749, 68.4354175831276, 72.90713958328107, 128.5910241952681, 104.29691481265095, 60.00680601270495, 77.81011717638525, 122.69516387747886, 46.779081394932355, 66.9716927802088, 56.97140149747794, 55.7243765133959, 48.27700070346729, 47.44580294817451, 134.8745693933035, 110.1687487776884, 74.64405682088842, 77.4128630230268, 160.93319948223407, 58.25190170115954, 50.014226533298164, 62.25394814396174, 40.528890593281936, 15.684759812516118, 226.64414001922444, 72.44517799208452, 66.12330155925892, 13.043341228386646, 37.76527051329676, 49.334320038988366, 49.923694682151904, 101.89963985805309, 84.24571346765555, 57.48551955428843, 68.18535441137102, 49.64849598372275, 152.25546035248817, 98.94553502070013, 95.16946613943453, 84.8431072923053, 70.02524138018605, 96.24667731249555, 122.91481566707847, 8.810417400265065, 42.78424168466413, 153.84362344644782, 35.66432944532083, 63.27235268621577, 10.501343777785687, 5.656969844208229, 97.5444830670971, 57.181540736305465, 84.05932077681072, 83.30276981601533, 81.77438297597914, 96.82736591252194, 61.05673465074399, 151.923650045828, 113.25298045257426, 128.95060175840183, 45.01738175527674, 48.16813115324248, 43.53406919418571, 71.05310061560994, 71.54691841824553, 152.81017233755506, 77.58886130044687, 8.652021646832441, 196.89904834923695, 82.90596725726517, 13.61394942986353, 25.800309538826916, 81.55970058236153, 7.095667237414763, 75.1940342792195, 46.229149174833054, 56.89062451256149, 67.53186811136656, 56.143606240669946, 92.8210195779722, 62.023970572784506, 219.3398131725758, 51.575434745884316, 132.38407816563887, 72.51532075241956, 61.58311205714627, 86.35411791638164, 63.857554819566744, 259.59721403039055, 46.90439290931609, 90.41137138118133, 35.90208832413783, 92.8795327825379, 139.4703472326558, 107.04766331812154, 73.44514200391917, 216.22147194656128, 86.25212161659191, 4.458532249492326, 89.65612243308817, 139.63930513247246, 42.44621972546133, 147.74764596692094, 51.9338122061067, 115.68221163912288, 118.63847523093531, 45.82197918560277, 101.07148721000856, 69.81939608727458, 61.296411700277424, 41.66223425908154, 62.013356980999205, 94.80177771381484, 149.36571870266877, 48.896838970523206, 123.02578546232445, 7.1424255909041, 158.71375330938622, 107.4728001058367, 73.6371685250041, 70.17522485558635, 34.93885195614383, 29.230316429558698, 157.25026407330088, 111.96549189127903, 75.80225982024089, 44.607266151370354, 260.04773352508516, 98.35203675461042, 72.56695687700773, 91.46386009737695, 53.376609404826795, 28.537130212238306, 135.77354370218703, 60.37165811332318, 75.60750439801606, 91.05815421283629, 89.68055602134932, 90.25365796481307, 46.45034434301342, 84.14268192311322, 63.214142800475294, 39.33312892472559, 113.23863106399273, 102.42971953265874, 56.71826135811814, 125.25000090084811, 58.992555804979396, 58.12399063316608, 86.21092050245689, 80.32854820589573, 84.41137171452816, 80.79580327659161, 76.17572994619154, 93.85996608186785, 74.92103251612374, 72.86113112127903, 61.44484392103578, 96.21556694968542, 316.91110144522605, 64.56421757909656, 118.48305155637065, 93.95001892326317, 56.97361827168382, 10.967518408302308, 88.7306564992456, 56.50229543171686, 97.98326522003525, 188.726202862695, 92.37203488096434, 71.29287521694913, 148.941340788156, 91.88143571334446, 38.29567973060706, 67.515701333597, 87.04795148144555, 63.95404789127794, 83.90227117690094, 11.31423686036527, 78.07531544265828, 123.24968344310035, 60.23874693310591, 45.61490270878979, 66.17609026119933, 122.10976235118484, 44.632771210142444, 63.66498756747037, 79.19506569127563, 48.3271971621384, 118.25384327420724, 164.02663054149582, 40.677031002797, 57.87776620042318, 131.0829432418935, 34.59950764847117, 103.36369360198802, 99.43708385157514, 42.42375937617298, 100.18285848705531, 84.86286467938795, 77.33159057726076, 79.76050804597824, 17.9804424357158, 93.1601812839586, 64.70596066487984, 96.72255855187882, 74.32074609487645, 76.21541313362393, 41.94581531252556, 129.78682337656232, 72.30241117763612, 45.85779740494339, 16.337960663698166, 78.37862638439, 78.80315974223603, 109.90316928330853, 6.932805820253797, 112.48427790580155, 74.4228129403346, 121.7383115086244, 56.47879759007379, 57.36385830245153, 66.61891203882398, 41.34254678697371, 65.07484010339887, 54.63044851708228, 60.713820870857845, 88.56759638546902, 123.06600457770534, 13.117635495036318, 116.33371364508622, 78.27825827399809, 53.389163816728065, 258.5640688756818, 91.63184977907257, 119.12493298478783, 62.35972296361223, 108.46109655370506, 49.70854314900215, 48.15961248176457, 151.0064442432747, 65.47455866451396, 84.5734694880066, 56.1915968486481, 34.02361092401438, 119.1137906623929, 5.779339254122993, 124.1266860739981, 67.7305952976356, 68.45935751437153, 9.955878761852883, 6.1088276985125205, 70.78646755718597, 66.58532860110743, 64.64531404204074, 66.71542215386091, 72.37358310905225, 16.71057540487546, 233.91674530050264, 93.01653301652334, 159.29350428317406, 49.23574385898224, 8.60218831617823, 46.3057711994342, 45.68089163989582, 81.74187052514587, 79.64667311701959, 134.3226379305417, 123.14431676229354, 6.276214941416323, 57.990199362705035, 94.77845662221158, 10.503422284421518, 89.51981024381233, 128.4690966845299, 9.69915541746149, 126.1793427608151, 55.15525335003481, 49.434896429121636, 58.88496446904233, 120.05084533512199, 105.68272806728653, 56.5281487960712, 209.32172799016166, 89.15717564628206, 117.59503024437636, 75.62718878674717, 13.13173684299571, 106.21434119819175, 43.52739281945578, 59.01512136222129, 15.843848175187743, 61.42722352549383, 104.72784694283577, 48.866645017204675, 80.08636979338378, 60.0058308774252, 182.32318349096747, 70.7578095828128, 13.822213226100313, 50.69569369406099, 87.63425898569311, 56.6782842359707, 75.67070428124131, 46.58984789958236, 52.377831139143424, 70.00116645419546, 63.82577740465839, 43.74785392807483, 112.24033882940105, 58.66899803546241, 28.3405370495909, 82.2093550788167, 65.11160857839786, 58.352868041409074, 82.15135559574348, 52.274185810927115, 10.019025721457025, 74.0815442196226, 83.62251910554686, 87.07706894231113, 76.90869352887506, 5.379682006855135, 157.75545459663343, 58.41525504188929, 79.64596927912835, 145.83374740212452, 65.23482339110666, 58.60599934344674, 48.669051788201834, 113.70003831786352, 73.04648946964338, 87.3536191602163, 67.5659711270076, 136.42019163864717, 82.56493332604335, 104.67156411716076, 148.4688260278693, 213.27290624451075, 52.078292145990915, 126.52683268160375, 106.87912191831762, 53.151567924863826, 76.72446221157865, 103.9940365296362, 27.363367449010827, 70.60762053487502, 46.01858903375472, 92.08730990427688, 44.76642078803752, 4.626766459374778, 119.97932575892924, 57.45813665703944, 109.96904248407309, 94.26400089696777, 83.82572857458436, 74.32086258522492, 65.25643429502394, 82.78144747613743, 217.14253175266018, 127.85017296610606, 51.177220126804734, 9.871239807566875, 98.38744289178258, 28.23664261175732, 62.72755442602626, 57.23790324733992, 110.22084038006219, 88.35855229986194, 51.50555270399427, 108.57534000532056, 128.46136693756608, 55.69153639726567, 71.77367097120352, 86.40176688608804, 107.7456121704554, 44.223976064872915, 69.35964681302958, 57.453506945211146, 105.58924780109044, 72.47059173452698, 33.05023903364435, 56.08115166291099, 50.31483953682463, 32.18331791292511, 71.03232579182962, 145.3769034609088, 45.199357195295, 89.49349345119467, 58.74678111333528, 118.02850681084905, 79.01326082103499, 80.94953441133103, 120.25962082378895, 100.36451871791787, 167.32540979086875, 109.83407403386421, 47.55297295685772, 92.02477713824362, 35.896877084806384, 56.814255494128616, 284.3708262076002, 65.95766476382404, 68.930241615997, 279.87806365591, 122.93060759904267, 103.7672170142099, 152.41284946296608, 86.58329029807345, 52.39420395845624, 70.26034463410409, 138.7227519245404, 141.93891108633224, 97.68992346568957, 72.09486826664694, 89.29407513270067, 284.8554649878332, 5.856235445373345, 42.18945283180205, 68.0579691452187, 53.39524842689455, 76.22584367539378, 66.38965080880679, 183.47314829817716, 119.33090921099041, 58.334347809670604, 109.29497948426665, 54.76153589603262, 59.84482365680796, 87.30733565374436, 136.94153713924825, 62.52862844717205, 130.26890060214376, 92.36983511378888, 11.532562962435005, 55.67637264617045, 93.01090918905972, 49.87389429451841, 204.87926484571528, 103.00635366522799, 128.46780565846382, 103.93214235055281, 66.84575462087754, 74.84232699706125, 73.01193296424228, 54.622655705899234, 84.7116172441815, 105.1076396354139, 63.47013082841631, 212.11147002356648, 78.37452160659257, 78.84495986097674, 63.61737350073797, 116.47452151606973, 50.70545009281794, 59.9134602685798, 108.10986434561016, 79.760435479117, 140.52511923174777, 67.50097886164166, 92.1465005232143, 83.9560582492435, 31.561076961932464, 72.29193920614787, 64.60194053709213, 56.18416327782659, 73.88641464692529, 138.3182174627557, 79.13850307892754, 43.80357244616292, 51.3365557585343, 79.20826077436472, 110.98865406240587, 94.29761568150886, 69.28237021509608, 75.21113621148217, 70.90796366230637, 66.35676353839015, 137.21026506050487, 46.48834063396366, 116.33912280932083, 89.78865031075424, 67.32711741284045, 44.304873933532214, 47.06833108371223, 149.01028147076113, 52.929547140324374, 56.72680739156594, 70.04972318689838, 49.056610467596045, 72.04856063258549, 51.629654866007805, 74.3314845782468, 168.37680837677337, 168.84509607849873, 56.97385933179258, 5.137637841416195, 51.47255650248787, 87.27141533267958, 109.11289758880297, 54.65842092295586, 104.93408821366346, 60.88897848813581, 59.3440716894426, 21.57922555906572, 93.62042401330174, 117.03059560633714, 116.95048621432116, 69.02172177187502, 58.62223018815314, 52.26889631526667, 116.80584469745502, 72.11802635131892, 80.42942299180005, 60.9498377628937, 131.30174445974794, 115.91435101787671, 108.76636615861453, 68.49313881259172, 111.51559694004887, 69.93662423159165, 138.86579703286367, 77.2462363308696, 55.18606378631796, 24.450178949598577, 97.1392453372729, 61.08420967292976, 56.996470181207016, 85.74894505848334, 101.43847691258698, 65.04852404980147, 35.412793169804594, 155.0701715726338, 46.78896087635038, 263.7723618738318, 94.82735452425058, 57.29870244159659, 61.80286017320809, 68.25739991008783, 54.47611616869927, 34.975580948268494, 6.596985131346891, 63.81286131102445, 64.88859021126954, 66.70867925183782, 64.1907266319235, 59.490086507415455, 43.53540020577189, 43.92889879929436, 313.6301124246846, 99.12476053381457, 8.018902567235228, 72.02127034887783, 64.8600417149363, 208.86991638172682, 91.473365839466, 117.65180860245582, 67.1537629091993, 67.40700000366029, 84.0004352734268, 68.93299896325107, 123.87936000827618, 107.16102961529212, 99.73487438671403, 90.4417285395673, 66.68806822776975, 71.27822899485534, 82.21512688755506, 111.33160724843474, 49.68442088887898, 191.4275239559384, 85.5575687571715, 59.43005813068472, 112.23964361100035, 64.12932453135191, 85.40516833029507, 77.28947029858726, 157.41032207973535, 62.902214209234685, 11.213393700101935, 152.37388901294506, 161.4861542910597, 80.86201301783687, 10.165605071450212, 119.05133263722934, 76.04403350965777, 73.13363492869985, 7.598340616091483, 81.2164127278169, 75.72771724845423, 63.326239614323875, 108.20156818886537, 89.12572206591898, 85.05914650624783, 64.07855337377495, 53.45323882487778, 81.74800285098215, 121.23237867725858, 102.15471245951981, 114.70143820128743, 136.72699937639533, 43.18004858194765, 71.18692366018306, 120.71475217621264, 92.81643032704878, 52.64938707119038, 4.778390662809695, 89.37795844491497, 47.61440256008689, 37.69058523488172, 51.61978458881987, 45.411024199307676, 52.14312630038894, 97.05950800577357, 52.492109404882385, 109.24572354900009, 81.00659738737635, 68.20643593853013, 75.30861503204012, 139.79027920243723, 43.54412677391732, 82.9200764691518, 136.32962289725324, 157.83111689788674, 105.50044103662489, 79.72511413511288, 90.24512596719093, 106.03478309848525, 79.18976314633333, 91.69731210843932, 7.161510396374102, 198.6720525053756, 71.40121371522378, 113.48193554575224, 62.15409351349062, 49.94507360909834, 129.91825698747667, 178.37424781664816, 6.272394315332859, 54.94768528979481, 96.75173991068552, 71.83968969313067, 65.76749838699888, 72.0625032528555, 88.49332210144756, 86.70610771855561, 113.371763438666, 82.64823069788982, 113.51177111861796, 71.17039800391474, 74.03425442042526, 50.86874689349324, 245.29130934666478, 67.29840877443768, 57.127416956184526, 94.35765090373361, 88.75224927552043, 189.3973220081023, 192.6355045635566, 153.56893304873154, 60.23259408359655, 52.63725354933162, 53.59751022031681, 148.02678275864565, 73.32690640650789, 78.91826983356906, 58.66377436808404, 98.62507659359707, 87.31219841669818, 143.45088926528803, 44.75515499748723, 155.86209103688086, 93.43243704144336, 89.82689015461102, 91.36908104091093, 67.63727589194421, 62.40288416806042, 82.69187207303337, 78.5156061615362, 153.07784834079783, 89.88752694396449, 50.41841179684916, 50.97923504271824, 178.46648037174054, 90.23148147467128, 62.616798390173834, 77.49909537499707, 62.04984556935734, 90.88387312709231, 34.26553272199796, 65.28427072932105, 67.63168500981277, 99.57207535381924, 65.53099956709958, 207.43663309241168, 89.91400238828163, 441.7090178769266, 82.82186301293001, 53.20684674648702, 40.67707777226201, 90.17573880679487, 133.55222560051718, 100.94198510351158, 65.44759062524453, 116.28992211677411, 51.52407269882342, 36.45104799795456, 127.30251815922097, 130.25742795838872, 45.45996953070656, 34.722798906421275, 78.63200209857615,</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R36" s="3" t="n">
         <v>117.5315532493591</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S36" s="3" t="n">
         <v>91.26385716178538</v>
       </c>
-      <c r="T36" t="n">
-        <v>100</v>
-      </c>
-      <c r="U36" t="inlineStr">
+      <c r="T36" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t>[115.11665344238281, 103.69825744628906, 127.93094635009766, 79.83558654785156, 83.26913452148438, 181.39236450195312, 141.68099975585938, 173.3926239013672, 39.33804702758789, 92.09040832519531, 68.59166717529297, 189.92835998535156, 35.237430572509766, 70.79370880126953, 118.96125030517578, 204.5042266845703, 103.06398010253906, 151.9327850341797, 71.95588684082031, 399.021728515625, 66.20675659179688, 209.1926727294922, 106.28140258789062, 9.447199821472168, 34.837860107421875, 48.77973556518555, 76.03938293457031, 9.708819389343262, 51.8015022277832, 93.85595703125, 48.49617004394531, 68.54496765136719, 77.3094482421875, 91.0130844116211, 15.693909645080566, 99.15660858154297, 94.0801773071289, 249.12811279296875, 102.61384582519531, 84.12725830078125, 172.531005859375, 82.18936920166016, 557.05029296875, 68.55414581298828, 111.10199737548828, 207.05694580078125, 67.2025146484375, 533.1022338867188, 50.59560775756836, 141.61537170410156, 73.85720825195312, 64.45997619628906, 72.71294403076172, 44.775028228759766, 195.22462463378906, 91.18205261230469, 51.651126861572266, 99.50089263916016, 249.7707977294922, 78.50433349609375, 93.9478530883789, 125.20960235595703, 123.3061752319336, 54.926124572753906, 305.4013366699219, 58.446815490722656, 69.91403198242188, 201.76296997070312, 63.52057647705078, 293.38360595703125, 76.8183822631836, 84.92288208007812, 69.3428955078125, 69.11119842529297, 68.11460876464844, 271.09747314453125, 120.18218994140625, 233.5401611328125, 96.58574676513672, 117.64987182617188, 75.17627716064453, 85.39385223388672, 54.62156677246094, 105.64508819580078, 88.56134033203125, 169.728515625, 65.80217742919922, 164.71185302734375, 11.097228050231934, 153.1634063720703, 35.68181610107422, 50.07884979248047, 195.0278778076172, 106.65154266357422, 102.44050598144531, 47.07980728149414, 122.96456146240234, 134.52674865722656, 89.88441467285156, 97.04400634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01115</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:55:19</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>97.69690071267874</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>77.61283017591184</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>102.5888272745944</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>4869</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>[0.558066729445612, 0.7994379335218993, 0.06802045552166183, 0.17813697325213657, 1.1264753393544038, 1.2349174830765708, 1.1019455039021289, 0.07420440711538126, 0.8346650636097225, 0.9253462731611694, 0.6663050318157611, 1.46893178635991, 1.1571648095779101, 1.6979991540131876, 0.9939017800382514, 1.080595859858686, 0.8394168104109997, 1.1787975031535574, 0.6025989452706735, 2.144890783456577, 0.3117480063796581, 0.9121907602696944, 1.900550220720695, 1.1894082486543958, 1.0194488017227763, 0.9027781895275878, 1.070952880557335, 0.29328816127362556, 1.3991872883721341, 1.2424056899661584, 1.8544468398325618, 1.3830275453112932, 0.40328742167623155, 0.8985646968141142, 0.9879935508613203, 1.279063850515951, 0.6025555371738215, 0.6036386535222321, 0.675569445782289, 1.524503608079877, 0.549625465677461, 0.2477754535063281, 2.103497762432204, 1.6284236358746456, 2.622122618591506, 2.3303084961307814, 0.6253963587317449, 1.7054738880488036, 1.4369106773298603, 2.185969115081909, 0.9579751774203281, 0.9018239225842003, 1.211536887801694, 1.9777762058649215, 1.1678127869099886, 1.4496310514791164, 2.035009622929204, 0.30752435147546753, 1.2964617532497789, 0.9226787657916908, 1.2452270365085958, 1.5327435410745156, 2.4681001767586035, 1.5363896591299764, 1.3629917786438552, 2.0444141585192024, 1.6357663966579397, 1.5507199931098803, 1.8209455150338512, 2.3882188448719117, 2.2277693703182964, 1.9149467891863992, 3.0148155354841233, 1.4814991134604094, 0.591084066258915, 0.9146205144668993, 1.7839245194943445, 0.8189331853668818, 4.446441108592966, 1.1500306817677568, 0.9548659418747445, 0.8647784588624955, 3.8145821358432004, 1.9383163200424436, 2.9608942838616494, 2.014091882121908, 2.840411735936266, 2.85824074144144, 2.5696168736957232, 2.219167906229617, 3.0228705748258604, 1.619379974727837, 2.37226527746706, 3.6694352713727985, 2.0972511885061977, 1.4012676589739201, 1.2445356471409608, 1.9500823270817993, 2.975595866615342, 2.929495353156418, 3.547398367018842, 1.247235927872108, 2.4109688734845167, 4.026305071824146, 3.1245687059267233, 2.195379026604864, 1.9683920683476057, 1.9460849896741843, 2.3430454466803754, 6.385810669422848, 2.121547808892817, 2.7221414717615544, 2.0703935805986595, 3.238408125918168, 1.017374954410485, 2.606834981774558, 4.1389302088092474, 2.2642642078525195, 2.695747961406118, 2.579767705720577, 5.26489435404114, 3.6969969657012594, 4.197285373585278, 3.8968700601843707, 7.711015131798059, 2.9413523917402125, 6.368814077458602, 4.579631111843764, 3.7248285059885466, 4.359849206688266, 3.6595854884148915, 3.3074204968458196, 1.921020707739873, 3.1922069538229327, 4.1197048302529415, 5.532012866249199, 4.308377086491917, 3.7967670806697154, 2.737808818455748, 1.8948752460164413, 3.2011861575691483, 2.275054963736508, 4.580869672813715, 4.820252580056478, 5.563590835115285, 2.01148449475267, 3.476643113047508, 4.29532069378508, 5.045718549053032, 5.490123342822144, 3.2045698041889823, 3.6129566977615513, 6.507082632399822, 6.947941047395651, 3.4559918806131567, 4.59977533140963, 5.7170573468242845, 6.559776074700711, 3.7327705594184106, 8.988850626328807, 10.344387902659482, 10.24303734465944, 9.784536975830575, 6.479059606702982, 10.437629918652501, 2.391293055055643, 11.875153737305448, 3.1515682561724447, 7.221664355747354, 5.386989937192383, 11.768507586314632, 11.49684029246923, 21.786454667503186, 7.586549099845354, 8.922180018410673, 9.084629108902945, 5.778622988750544, 8.28979119763263, 5.3425831831572035, 1.8623319081461087, 6.14864894433468, 7.741808739732231, 10.523646486115064, 8.869389385726599, 2.8302055678002547, 7.186266184600932, 9.77890264365289, 3.486819003415772, 6.476551379815197, 7.532630259741792, 4.209971595168356, 4.975907472897535, 8.403755227647741, 13.360688466149446, 2.6425760376190652, 11.346891770392714, 12.867323054830164, 10.246467737134974, 4.8959872972876, 4.255421041072833, 0.7748467312262002, 31.128301978801964, 16.774200501206746, 11.92052327633776, 17.7416606971621, 4.682756939763023, 6.965089700644928, 11.34724294692984, 7.55273430057577, 16.506977842781456, 11.024571286230367, 8.65195678906485, 9.108955479644246, 13.18821912279868, 31.17316121321553, 21.313041252704647, 18.553128759049397, 10.367925300513926, 12.464548932787482, 20.27533602467025, 20.317354997196635, 28.146403972169004, 12.935569221631962, 13.217032524665246, 14.79621890303865, 32.88911366704784, 20.328231894878034, 12.13122887486639, 32.704214587784016, 9.045707441282593, 15.786928562841942, 19.71216851484683, 15.885044860917443, 18.80954598289164, 16.30198766308952, 12.019976431933213, 17.60603398230878, 30.142603140230783, 16.191520687038, 21.904027503644546, 20.908170426316396, 19.418834290939078, 24.122460779231965, 19.667155295506713, 14.797932465287138, 16.35872106841424, 17.37045832565061, 24.180685436255057, 15.210055894734085, 17.696493573457943, 20.479100802028597, 19.462331882939765, 38.85701306648499, 4.53101972906828, 36.740859736883074, 30.37262394061417, 13.135560945437586, 33.033076386564595, 24.509364204587204, 42.57866449401108, 22.920278529461086, 19.177942026973096, 29.96826492170462, 43.53154828342681, 29.414780161514074, 23.430995093466905, 27.393503662775235, 35.74781640602673, 49.714392682496864, 22.139517940331974, 24.30438758129395, 39.02308179759036, 29.79204191528467, 20.816547879351774, 51.81206806792001, 29.336327202609123, 24.851132030307742, 55.455230624371026, 35.73570358540583, 38.129841509384484, 33.66672385911671, 20.845943456343946, 13.588732279069506, 15.995095047874546, 45.13775466994509, 22.495388849749443, 17.64827773685604, 28.620745287748658, 27.407641736397345, 54.480526397524315, 27.97515660017409, 20.212044022253536, 25.957081616601528, 4.382360723884378, 34.29122582724722, 18.930614232691163, 16.72865895449924, 36.47473405068208, 28.171410661070077, 50.09610506214192, 9.124301844583972, 36.55069881989029, 35.210219029792654, 29.696610005400526, 21.568586185882836, 29.767296876273594, 6.4809869463936804, 66.80254173091288, 39.285585052463226, 24.830259706872887, 51.32176983300019, 40.188202475919844, 12.871113114106652, 42.06629767638855, 41.9548395437651, 17.66034003458142, 50.27502721605812, 5.258722767060873, 27.17916679019869, 6.486142791850585, 25.979308987599214, 21.53505371494925, 26.983637419111872, 46.71553657317613, 29.31366122543005, 15.61020043951426, 45.71997404499055, 48.130671862794095, 18.721262082765318, 58.13042518531389, 51.72404083903515, 33.328663959776904, 29.694295743320694, 22.325302234749365, 29.088291464693658, 4.945678669879966, 56.16340152617496, 14.07881327240919, 52.70432009864028, 59.83228627000399, 28.960654233472752, 3.7355017219056856, 17.2166136052022, 50.88221184412743, 27.03793662821196, 13.693456367772447, 37.56850687331737, 39.82801873777454, 30.081686382784266, 6.603267894518381, 36.828817045899385, 58.04458302212993, 24.20751850511995, 31.507499621178543, 63.82590672673321, 37.04718704277117, 38.46654035903053, 60.61314499692312, 34.39550659673579, 34.570081999006284, 26.85513651002847, 35.351524652983876, 28.177379683355003, 39.21189012700588, 7.444966693795719, 25.42158631264552, 84.7205486734156, 39.09173650842636, 55.66534104725287, 41.47953385957002, 48.461915499686434, 40.851975756157465, 5.228200482088637, 71.2298476524106, 6.942955698963128, 23.717825500266954, 38.50126840313529, 36.2788780580225, 56.64472336744657, 60.03972464073021, 48.15029166242266, 53.198056384513514, 21.084704989196236, 50.96359142363331, 28.31130164471866, 22.155468089346858, 46.53355068682445, 67.56127389017648, 65.65737467578664, 24.556273739152143, 43.04505392121527, 49.74328035670739, 55.95301315383957, 6.704946567615163, 106.67622919281608, 50.91316582330756, 61.1660968615326, 21.3315466507081, 59.46829507865426, 37.7561006200378, 39.011593256514104, 62.06121697453502, 37.69077174133401, 19.216229376715624, 65.17429078931178, 66.67453700216197, 47.305211728823004, 62.863726265968886, 40.12687455712472, 46.67539954882448, 38.0529906490574, 61.44153932028728, 50.13371422727645, 89.41864854367385, 45.559230579334006, 37.425799754353974, 52.77341357966337, 76.14909212933797, 63.27495325616961, 51.194907844134754, 101.96895926392904, 32.44320174442714, 40.79255586530635, 52.1073083685846, 34.77813434274783, 34.72079015385133, 50.16700814787741, 59.72938773012524, 30.73145558502991, 77.1748664105205, 40.99822723949461, 30.39132245291555, 72.2276937751253, 44.977647336087834, 33.557805014631676, 59.67499153117467, 30.90868122744845, 45.8466327399704, 89.73244198002003, 40.67549399280536, 34.64446927692469, 34.63620663405982, 72.9709916669584, 48.676373361398376, 43.37379391954743, 39.84159983223305, 51.452631814389356, 70.7752086931234, 29.781646166156847, 84.46954281108675, 25.271600705310036, 43.22614024888323, 27.503143764691426, 106.10835263945283, 96.4564066571885, 66.40875540002428, 69.89248435904446, 25.47433594590038, 64.84854323763017, 41.735832691980505, 79.8929229412682, 51.81285487806834, 90.411387889193, 58.257350367601184, 48.29430099095794, 54.98747264263685, 66.25046791847463, 46.180228670950214, 47.10534157504065, 4.0038889139491145, 7.864831873616876, 55.121667796091714, 32.33965599667388, 85.88955844230384, 67.11325098815432, 55.96456479544907, 45.14308207743384, 46.83977002370679, 44.883150105776025, 88.93764057505045, 50.47918786466731, 51.38148133539871, 43.33716249838987, 7.988249189414741, 68.1470135952995, 55.247792449864846, 64.63733400843995, 51.61862574815968, 100.86127666148491, 39.88751359568414, 157.63914519198462, 60.77781999692897, 8.83131152721311, 36.29378223065801, 114.39063974826911, 42.17452076161099, 47.431111821276666, 120.31209182897788, 77.73997361258441, 78.95068621531335, 52.09988645920549, 25.102589215599984, 87.0853083210728, 71.88313266199374, 4.110851755505416, 135.47879359469505, 48.933008280389345, 58.38956276632793, 106.8905516862925, 36.11660034414456, 44.7081469445542, 56.42585649546238, 37.045208144034675, 17.23429033437724, 55.29081270520756, 55.98741503355921, 89.29248243219065, 61.2434673423326, 54.181498877320344, 33.98921267584461, 43.99936634590776, 44.03367172320229, 50.34637944169046, 42.217270459007025, 40.17086219268789, 50.66454279593343, 57.96359132174008, 36.53328212046605, 59.528636680698106, 74.65470367924931, 126.24807517250555, 48.787230089575985, 127.37351638738157, 40.977452944669395, 41.10994961098804, 42.64819743805262, 116.3316325236984, 49.963963460377535, 51.06801261565145, 45.56393250502119, 76.27090516934383, 41.38173867791815, 40.63758988896234, 120.4665101862569, 70.4631375323217, 44.85355020452777, 49.608204255327784, 71.55418947429064, 9.321573723665901, 231.5321809766089, 68.46925395070194, 45.41754497350611, 96.97681183166111, 39.031265820656465, 58.957028116460144, 33.248978795601786, 70.0068937234949, 38.958589398378216, 44.21803698351015, 53.44733643549215, 42.13741217857905, 92.75870781554188, 79.75342427742834, 48.17406169796066, 57.68318327968339, 83.16897040085011, 61.88449516643518, 65.54198218260353, 50.490790420753406, 66.56516574370237, 134.30609361341072, 74.12628748202175, 46.0234685838508, 107.56535481875366, 69.87787865795809, 45.24258952480987, 75.52949050865212, 54.94704433179404, 79.6322837136769, 52.197934321804986, 66.62532491387816, 54.48356192918672, 46.67436566371967, 54.17228637811974, 68.53870231482601, 75.2922328509159, 85.23118883349794, 53.42176141711476, 68.35888211058666, 43.79763149131075, 156.73638144626074, 49.35313913243069, 109.99134967080207, 50.85841711775357, 63.12070842466552, 58.03963831253417, 55.50091619605895, 61.20201262629873, 53.19385607790771, 40.78772812523957, 46.350042128889214, 5.798523190871558, 5.391572317791553, 62.97096767629262, 69.02979843444167, 91.03375260597404, 42.02585364539635, 87.6908286335518, 156.8191613195581, 53.23134765058412, 58.819492979177866, 54.624392807930896, 78.86414235876593, 120.46760682851682, 80.64239409759992, 163.73468249149659, 71.73919844799799, 44.177538398744424, 124.57571474012092, 50.02786819479361, 95.91692257727719, 64.37304998446857, 55.05595617809413, 52.54541547603443, 93.10123609654553, 35.09724597898956, 65.2933983266355, 86.54065152533313, 35.91916017592468, 74.41646263838686, 13.421912920574924, 40.658067383832176, 70.16561976702245, 48.67288328987135, 51.26598354079042, 62.66744882705509, 82.92936227739276, 144.30218848002113, 87.81320260496086, 68.63395929478763, 58.40439778796246, 70.96010785482089, 72.78930872388005, 60.12700912885322, 75.59755919647466, 160.63069608422057, 52.4090351560051, 93.51306147929793, 106.80781585979875, 50.82349800682863, 51.27334068809613, 73.95688001553793, 17.65891912935673, 138.11958911652005, 103.94623278265803, 47.37081575620578, 135.17136660460682, 53.89171584786661, 243.53540219690976, 96.24944320057544, 64.64636993314302, 94.47771310772055, 58.61613288635122, 61.459852946876666, 50.370751648984715, 67.80853476860965, 51.967241500203095, 41.6053093703064, 52.71595643349896, 17.644181974435885, 44.969159945135374, 42.00815583888307, 61.84686385552692, 31.968596232183167, 45.99154250506735, 91.81342760575521, 140.09273120224984, 58.12165862465326, 51.658424184603035, 98.18731787318546, 68.31153181008627, 69.2512659025179, 116.13725764176962, 129.6252924649315, 225.9205731389829, 4.772104423964513, 157.11665267570984, 62.154741894430735, 7.340857430807504, 44.48484531462949, 199.5447774182496, 67.0987107979165, 176.00317417820872, 36.08022737406329, 6.658276404429032, 44.27527958005053, 58.0740649153883, 255.4718052266162, 77.16487567307166, 49.51478389780533, 77.13592309641525, 49.64096758326498, 130.16266961885032, 66.1124477525393, 59.27782817275481, 67.59618344793559, 14.76297527756331, 35.46803498710202, 5.5087941603337525, 69.88476727898453, 40.883621446454185, 77.21565955577776, 118.6016168748994, 79.58805177583304, 57.471847708758325, 86.67404745018638, 46.51147386259832, 49.284239903224346, 51.67759850213717, 36.236074565824836, 59.24546961905343, 65.01943154162475, 52.998197945321856, 58.81718777216344, 173.0581269826658, 85.61770542186815, 133.31692350035001, 38.41203159022726, 35.77951156212086, 105.08454245591581, 60.98018074824825, 43.81834794855679, 212.63790381653567, 33.22828416158307, 82.9489342246855, 47.83337384287733, 12.733703537235291, 103.46733052339638, 49.76178975841543, 42.10410335736538, 49.89474448587536, 69.86752259487966, 57.55791544631415, 54.41736640390704, 73.08488507363192, 5.373245611526136, 109.33369462667741, 74.46023924985748, 148.5213483325293, 47.49319727960568, 56.275185487646716, 45.39148494511976, 72.38593853864761, 195.5294659933238, 57.04027237591622, 47.415757313543416, 64.95382547306933, 85.84503777786571, 102.19922768795743, 99.60278187079071, 93.41585996061048, 52.51922668704905, 131.0620952462125, 130.05518926425995, 65.43241333605525, 92.33755476504071, 65.48985520732217, 72.08424959986142, 96.37300168967877, 57.22438286751968, 42.285920926540776, 130.548041523471, 113.17194774683043, 66.76784393123836, 69.28037108377188, 61.3331816683902, 66.43373344665166, 103.53911166006651, 87.06825920767467, 63.15362058435954, 8.60303869002911, 84.16296812861734, 41.07686647150951, 32.716748497478825, 42.87206089781355, 63.95790882039607, 85.23725474071696, 84.32275462450569, 87.62033418709326, 99.96488169161319, 172.7987573341094, 92.95107063027986, 79.50979384047612, 62.621588254667145, 41.13072939515972, 51.85529472146338, 674.161602542651, 45.39871542306756, 47.940235543337764, 6.188197722247584, 82.54797527318118, 133.3957726694741, 36.99316008282266, 140.80213080586176, 69.5198726248054, 77.71518925438008, 50.401897306346406, 70.7493446583283, 92.85604233146078, 128.2993868360222, 37.39004311044423, 63.75452500257062, 89.88097300413774, 54.35496738134495, 63.562094819536355, 86.87624035898276, 73.65880476917845, 104.03205723395985, 165.04444089639486, 95.32529255334246, 73.99766762541609, 58.64546372226685, 127.13061139482612, 65.18168771496798, 41.83219242165978, 91.61847523936609, 64.67457808236288, 84.12238137073724, 299.7817756263833, 83.24358013348609, 185.9192377784889, 57.01083046509964, 98.30047238356012, 118.67332433264978, 132.20027603648433, 87.05449448186481, 52.7279459086941, 66.29692447587512, 71.25927476288378, 55.3949439647829, 51.88584319075145, 54.63208485471453, 56.93951085390723, 63.262755127032115, 134.9448114329705, 212.3415637282745, 57.27660039743871, 4.2367103350312165, 101.38161262296889, 47.97694726161514, 139.0672644481942, 41.60359730557104, 91.62120026829517, 78.86102366807111, 91.2041987985624, 74.15909359027442, 34.43735450429426, 69.4570716622246, 38.04432443015264, 53.699257119938565, 12.436780072809992, 225.60232571061562, 80.55407203030254, 87.0727302090309, 83.13970385554977, 49.940116797378764, 42.62164869670183, 72.63046651453217, 39.361466347275574, 151.01949016867235, 32.4153168693649, 100.40298365323717, 38.46231935126873, 71.06437163555994, 155.67018341116363, 79.80536006671792, 64.9268636455825, 40.30307174596759, 63.92539294992196, 96.08790325195046, 77.83256553858514, 44.9038204795609, 50.25554866487839, 69.92435251739762, 98.29534738037624, 81.24080069755199, 52.50802288860049, 45.200915206148885, 88.51098953377489, 95.40214164885964, 84.49618959255753, 148.78360549557942, 83.9410722934044, 56.538045567958875, 74.46526002124999, 40.44905999351162, 59.15452171306325, 73.59890857397119, 194.99830528183676, 89.06765933180408, 50.13434940188169, 105.44475970499785, 14.958717603952635, 102.91674981699371, 75.8535433899337, 40.88365953723174, 42.42032700207074, 63.865584610628396, 78.73526971513735, 50.254592461876655, 99.40585165754446, 117.9562712360591, 59.8018161183211, 69.46429699376553, 77.15283672460916, 60.49238712379895, 103.92790799780691, 200.07865351356136, 104.96753747054238, 47.5315558229895, 44.01358189786741, 49.37747834067651, 63.564893023638, 122.24138439495476, 63.51121385357636, 66.08956186155434, 39.010761399308684, 51.137539405930255, 169.80077661218522, 37.74716926011759, 103.84032025736575, 84.80797214856754, 129.3683218679776, 150.70301930769566, 89.81437654291928, 58.66043542229659, 107.51291425124748, 3.383105593880454, 60.13110272846981, 77.67635356405069, 46.57147750389669, 42.405137836711624, 88.40993589726585, 185.30358414275545, 52.13107943076185, 100.68631044234733, 57.93699343241363, 75.69918483947538, 46.65440988339267, 33.918817937243304, 99.85857387915448, 131.03445243973528, 79.41074080778455, 72.35188863956155, 74.78676166391702, 125.74503459147594, 38.53341190241767, 53.683313685808066, 92.94962268592744, 67.08548443752865, 87.81260569238086, 42.225807148733914, 122.94022762771935, 58.381064168719746, 100.71172791520144, 10.852855002447832, 32.96834933624734, 67.8562342482798, 154.0045951639159, 72.23682983605067, 80.32409221293261, 77.96129627241041, 201.4649886950151, 67.96725223466804, 60.49992322968238, 92.15085193437963, 66.62888165625463, 53.77565956433568, 8.773478782172932, 103.13365087491732, 137.77457631833684, 57.74608302329242, 59.73613947312426, 61.41667817014783, 80.46781476238563, 49.13268426148657, 45.28126086385945, 5.804218123479041, 100.71527988315205, 17.482646667005213, 126.52277438143646, 18.653197973616955, 64.82317117431155, 117.49555283219853, 90.11367350216946, 144.21673088055744, 125.94031892277295, 81.73578750208799, 87.16833944601171, 13.11034665423941, 52.098362032368286, 72.49977381959725, 69.14264502575504, 7.385735755742553, 79.40101236683928, 88.35086938403309, 54.914477528072375, 74.86216250542421, 47.938018260752436, 187.8651332283971, 349.1481851256575, 45.71947185734667, 94.94142696370051, 50.103030078974136, 70.54802626396143, 56.27643129392246, 147.269977597112, 222.15822785232947, 16.147299798831853, 175.66872376709264, 95.3612018424433, 85.14355645931751, 101.2452201554326, 134.51203578392568, 86.5775929450381, 8.942458034211002, 45.760900675357156, 61.344110041148625, 61.745569985914685, 68.97381582280325, 133.99242620366635, 46.92209173420321, 185.7312872343257, 88.27660700146866, 48.314545048851045, 52.3637869176165, 99.6803313983323, 58.912631730452574, 51.38050033922132, 15.19092172561102, 68.82412884522813, 7.394861197761541, 381.03750867128844, 70.32846143318976, 93.14402250114208, 47.564628028135104, 77.04643042169621, 153.15698765190768, 45.51650725250899, 35.48805957903895, 55.38989986153302, 83.07828490069913, 66.8615145602136, 43.16833740050101, 60.467552482540626, 8.420814548060104, 112.388586865816, 44.29390381801736, 68.10813774637178, 51.32839386811838, 116.87081344667244, 88.24969367458439, 87.35186145743593, 70.33678232232886, 45.622129574223244, 45.680743767208625, 98.24253397827763, 71.39355397615118, 77.68350175094682, 77.85652251338598, 72.63625351429847, 114.8579251500394, 57.66117366751231, 158.6398456791033, 111.93811847468336, 68.05738334217847, 61.67367227389729, 15.444643625291876, 70.53218063338358, 10.894826228925972, 60.04157011360064, 47.144147315958776, 54.15366842558708, 179.28095483001377, 144.8990903793503, 49.4420202105308, 61.191851923632726, 113.5380487504343, 94.77462269620129, 174.71903199032485, 48.7984481327816, 34.753097306567284, 56.53054214333774, 75.94897234852793, 46.94974180633027, 68.60735596246582, 76.70022672595229, 83.40055328467858, 40.57057539376637, 119.47886406642439, 68.34185619746331, 62.7206251569827, 83.74973837057543, 133.17242803754814, 45.714172098152076, 10.17924916350955, 75.79827143802507, 208.48841468319327, 48.77543271573993, 65.27396568373634, 75.46563663604391, 181.81984088893765, 114.89724403268204, 195.45094963323243, 116.04059224972653, 54.34725032175127, 105.09661623125906, 54.25389248104327, 572.2633758493986, 63.44249504203408, 35.00975700568979, 103.16753174420477, 97.56983014372082, 61.08490484223289, 178.81685589083506, 87.47565931489315, 68.57768268703822, 132.1004705638435, 183.82630513631366, 71.71929681954266, 114.06299128319091, 133.99841265555932, 30.33576904767439, 57.40284095870907, 64.51224121548523, 67.35323507684743, 168.1498128167159, 41.772095727779465, 66.82641378797732, 176.38721193840823, 42.98752138349688, 140.48029000510968, 95.31967088508317, 62.84992851363832, 37.214486590519634, 74.98954850815184, 87.89897413234151, 74.58208476519731, 65.97058630734067, 75.59335122310836, 101.39299372053648, 208.66444017239112, 72.32492444788753, 14.672634027329478, 62.36587430869535, 100.1743451211153, 63.438512882673486, 42.699532004778455, 69.47956133259025, 280.119299762627, 61.69491395101093, 89.4800343283593, 71.16280815112658, 111.27672604684858, 106.44684045624417, 66.43237992980809, 50.26575658240759, 79.52035222051566, 52.79554844990684, 109.70126500362508, 29.920677998576974, 128.44848501580304, 90.44641354104472, 84.65003824593065, 48.48273674912492, 57.00881223294444, 84.3003548616195, 127.07190964798485, 92.95594024652574, 54.380101420279615, 92.56281901942184, 72.35569618833938, 105.11646782364228, 55.25640447496345, 102.6418529421359, 143.75382879085714, 222.1103749523098, 53.90500148941997, 74.64753914916443, 54.079449467968956, 133.1427916712776, 98.90495670561617, 344.8492073745495, 121.6323148978699, 145.12885416218475, 87.94377734782819, 67.66815754715745, 476.93330491105365, 129.0812774601257, 72.90090191715244, 65.96401239532214, 96.74796009419268, 82.30138102576498, 66.59210278181334, 45.5206225539753, 111.05116289541542, 74.64383103382409, 69.04560655030778, 75.49789303078978, 79.03861787425178, 80.18520884217718, 77.68025091785451, 56.860134554299236, 53.37035170974274, 77.0637085167058, 80.48475663702033, 338.214232985648, 34.1460713877816, 50.49566500597883, 64.86200555292746, 161.44895106157875, 60.50768909925708, 87.89615842170632, 85.17242869024776, 57.953195544450864, 53.116856112175725, 89.27065071719598, 92.67787799279662, 49.91451178821006, 559.060279103749, 130.34609293036792, 12.549090603100828, 115.58845935171249, 83.94235456525828, 49.30365148104147, 58.61146854113207, 109.26557343782952, 52.01163739352171, 53.449736272140825, 82.36335484909075, 133.771622332804, 49.96350511545271, 79.13017336226805, 69.73117057891008, 9.182497975979722, 41.44305595204315, 51.17157171248212, 69.64478742537653, 71.363864852415, 110.29548936270987, 53.69488269080172, 6.8729195852454925, 163.51418657257346, 270.04789066107224, 60.902321794297386, 89.15657818858888, 191.72313715805114, 75.41107182089551, 72.50317521169276, 75.17622389751594, 52.757806540601166, 99.81796264849609, 97.94917931765676, 89.17262483261698, 105.52630443814697, 128.27139155546175, 77.96380981642147, 79.16060049839831, 106.61089065739961, 159.38211467720956, 57.403055304681565, 307.7606561660429, 35.59439390442155, 6.986443324056832, 103.1315584145495, 95.93224144097417, 162.2066321087326, 43.166429746802706, 47.914807352172645, 89.73024342715019, 50.157879287697796, 93.1652261840643, 70.32144127733793, 89.73070625252195, 62.870462981990684, 77.42495031669355, 145.11070446601525, 75.49945373116142, 66.03812406756802, 112.37413735727664, 217.1087264869377, 193.86617276190557, 7.396627382313782, 269.88788723866645, 48.7178146919219, 63.83474989437503, 52.79958270658554, 82.7889933687117, 57.70740778924964, 115.71480787479484, 74.76962635247794, 67.18879871295785, 68.369483131372, 118.12308230268454, 328.8181452225054, 76.33042624765658, 229.2134571463009, 68.79897541012994, 53.105362968872484, 8.83640486331162, 42.44583732093898, 66.03182827960985, 56.4648625584976, 24.384180038952792, 50.1292907869396, 71.99810423257523, 91.35214929709727, 35.750247372127355, 73.10611469946795, 42.14418089032657, 84.21284073804823, 50.82207834352923, 122.65418186435893, 13.420274550977716, 41.327822216094816, 46.909531322271185, 68.51257280177471, 146.71353914975492, 212.45219950711885, 63.40946561914109, 72.3215147402623, 72.83530372021188, 113.83459356230938, 198.21700372253386, 46.77132612216238, 52.09816817604783, 110.60046837796487, 107.12775212743671, 64.11007948203975, 122.6006035094313, 65.103767202777, 368.95111902874055, 94.71628493626665, 6.311279854809407, 97.8427076383717, 61.69670638564164, 30.651645486241744, 121.55221654295292, 119.43585064764399, 80.98310080804148, 9.346272354527606, 54.857572611239334, 124.50137465435576, 159.89348777411018, 84.48391630991959, 100.22118290722975, 77.98982333106065, 141.5821906546722, 131.48970436861217, 63.24970130400352, 131.9776144389, 279.74517618782505, 63.71078606362625, 41.39289396895699, 91.90930907266116, 97.26324533804197, 60.65420430744409, 71.37320284794684, 188.33262411575552, 40.25782478534234, 68.99380818242403, 101.87490915681396, 79.7674583580181, 108.47463873146759, 101.80085025026678, 77.67499632177292, 187.8863690947702, 87.3215369099201, 109.18088080610468, 100.39294159926781, 50.92346006916638, 86.79159581445471, 138.65047488583934, 71.74557947577985, 94.57043172634947, 70.4953297954596, 38.678737478787184, 56.399502866009485, 78.27479356446956, 72.50940192407852, 170.70062193865164, 53.70550469634569, 58.80450314024041, 75.37905091941306, 50.09088008103941, 116.39967694419737, 62.8170359124578, 51.68203403201291, 142.22914650955545, 325.82647988006255, 63.37842514394297, 44.569584494748305, 161.68876956671113, 58.75307396710728, 53.15412833639328, 134.74073283055583, 49.7755934668447, 106.03335191834526, 87.35646312314573, 229.8456045289334, 74.38231505404461, 140.40936769261944, 55.20390913265235, 141.45885370026357, 65.0997557356688, 244.59722430109, 172.2481431003985, 56.943436648887186, 172.5659591038266, 80.28707979453134, 68.51824146072724, 62.54918394792205, 48.100531402799135, 99.9328343047892, 103.16539954432898, 82.57350486527811, 67.57267800080825, 47.634490672412156, 9.687516511603015, 55.721984101027, 99.54123386159556, 111.89969772044533, 73.69826537226504, 49.34525545804108, 269.0805022439311, 236.34113071434382, 50.43903529011241, 213.82478808671027, 95.27124516271586, 41.05395187437376, 75.4446561466092, 77.70980123106689, 84.70314621422895, 248.87005491217974, 40.90201856046585, 58.49483873497532, 41.44847439309437, 207.5442281065979, 57.38575755480474, 84.87795054619282, 84.66436171453863, 78.63062289298284, 144.89358486783343, 150.77855276205784, 103.65021019803974, 63.794339798089545, 125.66464081469037, 48.479324923336485, 44.49100816012569, 84.40889382500835, 42.27377688538368, 65.49023506426832, 46.519115718465294, 317.1906829617353, 62.938454649949406, 83.16489332389783, 56.393403898609314, 75.82928660878811, 64.44047632041655, 7.980784865909431, 205.32396303468005, 75.04670298960806, 46.47683754727376, 130.9563973089282, 64.69514818678891, 79.1398129659478, 61.24518634118516, 35.19244026397618, 126.5462532457155, 10.881438586629136, 73.72434407361924, 130.58904177366148, 104.74594814330321, 79.37395773025925, 67.06728473259693, 94.57024163697974, 95.55957947510274, 66.78786129337381, 66.8628590887866, 87.25764887367761, 53.28516481107552, 65.91434340292822, 162.22448988382257, 92.32507862493756, 41.73218509283419, 31.23225905353589, 53.158240048260346, 74.39973028231682, 71.87598475274032, 181.33117443122697, 178.25815460575606, 87.12174277965387, 84.31975191894894, 85.74069597135778, 14.411091337160833, 56.477397526790924, 76.71479785938398, 196.39780803167926, 13.55795846288508, 38.34111245200709, 588.153171628031, 127.07724142360132, 77.44747225222748, 127.85333555037985, 130.69040390170593, 107.97786099350228, 141.8481540099807, 159.41065509698524, 65.61002139409833, 81.0812200288396, 63.679150512096456, 63.98698142930762, 193.00721030366614, 74.16792975751278, 142.739046980134, 57.3394978839764, 59.859827496658866, 213.17964869771632, 74.85692407692018, 64.93424387072187, 211.8315921806078, 83.26642715874821, 108.61499012513386, 77.79510743683167, 71.63058615132294, 70.70077222177032, 306.38902754537213, 96.29213787530823, 133.9601824683165, 92.24765176521376, 89.58699436186419, 46.92091459123994, 43.570069404486325, 15.069194086088427, 84.2396745789577, 246.4789186211573, 223.9143015896348, 143.66701591500356, 87.09091171167972, 143.1392718684562, 185.60430032494187, 102.05534858187669, 202.19969294049795, 83.05608399262563, 47.6346979206927, 53.77168336716886, 58.78887629529031, 60.42008322833242, 109.54667280523172, 56.328585760594244, 92.45222809046669, 77.62652097042944, 54.35456281710754, 7.647697314431109, 192.43048423575095, 6.2803188648857295, 117.00677390087466, 305.0463282692659, 157.84996016606453, 152.41578150994974, 87.42284939396589, 44.766499365853576, 152.31846023161506, 105.18170247792581, 70.1709754916191, 67.0426111262801, 168.71034676129204, 118.15665579228185, 49.82697906264572, 57.957796594205405, 61.643501483299985, 24.963979047365278, 101.18961808763632, 57.185647969487285, 99.11251071416076, 65.14608229664991, 61.85355503301585, 93.77191699571773, 63.22349077908301, 98.79595329883, 115.0922714975577, 62.090777772112965, 44.43101120593457, 110.2904145413542, 103.56677245658204, 67.67115351656989, 90.63231254511166, 164.30450894632534, 67.70394766299101, 265.80962224333194, 90.17387092186561, 114.36710435058635, 67.8049774049702, 82.63760763156246, 38.41524027546497, 104.7048040962501, 6.680319078477089, 55.667262728632714, 148.59667488451373, 136.081726696526, 51.48715625618282, 42.75482773960092, 81.9187507327264, 55.20268249260392, 82.53228036608738, 57.878546059790004, 64.53720048195831, 147.42275596846116, 98.74777235811655, 69.07842840888362, 81.23956527707358, 105.28570241550693, 65.42023448656356, 55.208440352692925, 58.17358523488692, 66.26840031465763, 51.07679731666151, 130.31835280301482, 67.3297246696581, 181.35394446822013, 61.48471726308747, 56.40139890150226, 56.81453776705671, 106.69701241770723, 94.1316270850144, 93.5789066907373, 82.61708650063328, 71.51681999002963, 96.90211226356233, 46.18524420986255, 48.20261100772395, 159.7653558042697, 94.94572169162208, 93.55110693576032, 84.75081675306461, 192.55349101986823, 111.9948003502808, 70.26693802614312, 95.39547900820689, 67.13950912732417, 77.1948798335482, 9.879188386268472, 38.12345066218536, 165.95131967636488, 84.88282619147272, 66.59711025502193, 111.06404739390044, 70.35665211125986, 143.06009558918333, 50.8808955793191, 62.57330427194987, 89.84592780223191, 80.20759874025586, 184.69250211544662, 123.8796681150777, 65.19135630651606, 74.73427494273542, 43.56020490157975, 44.26045351607787, 9.02703321333981, 59.79491371198815, 76.06354558907577, 65.47555081380432, 185.394606771902, 90.44720484819516, 93.08237886510483, 227.27165254548055, 128.32694053134148, 34.84884957329958, 77.26081144983146, 110.36420414050016, 64.73840259923712, 49.00853756956792, 183.526818695767, 73.54181962112513, 154.49413833869224, 91.38625408127334, 216.21210330267363, 73.03494478105239, 69.90165438390734, 79.54335606072345, 122.72531009145949, 84.23272262668576, 58.43791808778516, 121.16358725201027, 110.46839730302985, 109.4165818773737, 106.77827100373015, 49.040415848466345, 107.45072820970286, 42.517366143</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>101.6725306367874</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>76.49684983955655</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>[89.57271575927734, 127.35409545898438, 53.08642578125, 143.78158569335938, 136.1829376220703, 124.48292541503906, 16.183958053588867, 189.74024963378906, 135.24855041503906, 164.6922607421875, 168.29217529296875, 56.56387710571289, 103.1157455444336, 10.092584609985352, 7.377274990081787, 60.26551818847656, 154.55184936523438, 20.162391662597656, 85.6982421875, 63.47487258911133, 133.996826171875, 43.083709716796875, 55.430015563964844, 154.45101928710938, 134.19866943359375, 61.6701774597168, 60.15404510498047, 65.222412109375, 57.754539489746094, 64.31378173828125, 132.30967712402344, 90.02155303955078, 124.91407012939453, 131.34010314941406, 25.74718475341797, 63.115264892578125, 72.00808715820312, 48.606380462646484, 71.33130645751953, 100.05445098876953, 67.88998413085938, 99.0432357788086, 90.83209228515625, 89.46875762939453, 77.9318618774414, 61.69033432006836, 48.10249328613281, 103.57774353027344, 122.6577377319336, 153.08004760742188, 183.369384765625, 50.64175796508789, 46.65321350097656, 100.84781646728516, 32.13307571411133, 123.44715881347656, 50.665870666503906, 166.3253173828125, 551.8272705078125, 72.15077209472656, 111.04740142822266, 73.17279815673828, 101.68346405029297, 143.7013397216797, 98.8299560546875, 19.217355728149414, 208.33193969726562, 22.936002731323242, 56.79825210571289, 200.9282684326172, 89.68534851074219, 164.6666717529297, 51.37776184082031, 40.359291076660156, 112.79776763916016, 11.727409362792969, 306.03765869140625, 10.34626293182373, 70.8929214477539, 87.49436950683594, 343.4601745605469, 69.65744018554688, 110.02510070800781, 89.87894439697266, 111.6904525756836, 300.6639099121094, 71.24738311767578, 73.43270111083984, 122.03216552734375, 35.33858108520508, 185.51931762695312, 52.146080017089844, 92.18982696533203, 45.81890869140625, 92.21585083007812, 91.13720703125, 56.878448486328125, 235.48187255859375, 53.70138168334961, 60.72563934326172]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011112</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:24</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>90.91248101685777</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>72.7067348926073</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>102.2404338039697</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>4887</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.885867790918811, 0.7813886207315305, 0.6604608531376656, 0.9909747956141346, 1.304132993468668, 1.2268378300712814, 0.4592193118741292, 1.1991546498038534, 0.6074209678839164, 0.47341342516853446, 0.9133808330355492, 0.6740745707335662, 1.7704900727000308, 2.1412352602939317, 1.4481389222549428, 1.7255805133167887, 1.2590380581255172, 1.4292546412873066, 1.241618146071886, 2.282943626026312, 0.9768752613824513, 0.38309490460645185, 1.5853552159118565, 0.9180291537048838, 0.7369000508819065, 1.0767731688400461, 0.6788183497080192, 0.8284281168854323, 1.3409171515683538, 1.3323504228347727, 1.2176858075086456, 1.1755294216457342, 0.5281283614655377, 0.7485529059529655, 2.302073456164561, 0.9359968031943504, 1.2070213934790361, 0.8202396966405546, 0.3265085563270601, 1.327581392646706, 0.7923591853482477, 1.8149352548258293, 1.1880833623055909, 0.8154377181302586, 1.2492141042069274, 2.0017223214351496, 1.5201892544170084, 1.4698011529386739, 2.1164504731237423, 1.6395365188637114, 1.6019691193152223, 1.2156306929570724, 1.975184328704708, 1.5960377653385875, 1.738484752070153, 1.4884161464093841, 1.4764292734390414, 1.6118714642926155, 1.6118490904123473, 2.2787986708909593, 1.997673636432237, 1.5288196123022195, 0.8523194346402005, 1.9114214223156967, 1.835190067132173, 0.643610320978356, 2.088562909777497, 1.3660541955465229, 1.277652387064438, 1.9538107289103102, 1.2433544734050295, 5.814280832371341, 1.274801607620082, 1.3665788799417622, 1.0240511831679586, 1.1867482938720364, 2.6461237166452323, 2.2667654770557424, 2.0912445463107243, 1.6430875726236922, 2.074853829719356, 2.3579852563969146, 2.00844550655796, 3.5203678741387336, 1.183943576107192, 3.247974130446157, 2.603869287273189, 4.34185026725789, 2.2952873323267817, 2.795832418806219, 2.0682538612245263, 4.166308903329296, 4.108700969199681, 3.55302457842758, 3.12809251445492, 4.336020492871513, 3.7930934920243033, 4.663911757926579, 2.9436057527888444, 3.064302054172256, 1.8123457927818363, 2.5031649075647526, 5.497198203926484, 3.4413528210712734, 4.18793280285417, 4.311806105746972, 1.9981234413363564, 2.6540677852247687, 4.829941581672334, 2.29091885495992, 3.6089882213389246, 4.482105857380585, 2.3956851339980054, 5.6191297881344395, 3.0789244622277456, 3.546372565016253, 7.186821217429305, 4.967169867682717, 6.536706107380563, 7.063688920523514, 4.085754142953639, 7.79518419239187, 3.76437707574741, 2.843169408474341, 6.52893766362321, 7.755425152811117, 6.692847899329482, 7.018137060157498, 4.463302105287651, 3.4383380349121255, 10.658366896280741, 3.1855214635554345, 7.579719412154549, 2.2522987334724167, 2.037748384874693, 5.148636192889327, 6.132465523445036, 10.1974886054885, 3.369128389707572, 3.1210680426660224, 5.2437067017239665, 4.256660374572787, 3.4293012240279253, 9.284453630446308, 3.2755959985292336, 6.49647005345254, 2.2431010416418866, 4.879543008837509, 4.277456306703828, 6.4857984357384195, 3.1748753136856465, 5.382375994206452, 5.710440829058135, 4.055120162500276, 4.02643343110743, 10.170448231164869, 15.604305221179219, 6.639029663498468, 4.556314224474471, 8.805848324653738, 9.003213682946107, 14.945491051887965, 13.001385835431062, 5.572004510286582, 8.324963978613694, 5.773638265257179, 13.17428101028239, 11.745552733924608, 4.048560295610283, 8.198222796245288, 12.005781149732016, 13.80039849164831, 8.684999472491583, 10.33996501380882, 6.3108814637257575, 10.995262259702924, 9.250272185732534, 6.3048711393555905, 10.423281423671238, 5.64743297524077, 10.361508456943865, 12.782138434564311, 4.275569288936858, 6.56087373120523, 11.847024274023825, 9.975511018894128, 16.052784529833698, 9.794055828182938, 12.496480212820723, 13.820993821902674, 6.3125905594338825, 18.05938948063751, 11.91420863552181, 17.22309280427457, 16.28668934938626, 18.049721916379, 11.229928941295451, 9.276542619472762, 19.55401843316926, 16.212898702416858, 22.298847816165985, 15.317323804084612, 20.360317740886284, 5.997569882764959, 24.195505305978372, 34.93509386099433, 9.873948478275532, 18.972023853178165, 20.752844209202138, 17.853226866207407, 17.786245086553112, 25.989919653077273, 3.350984185117196, 14.956552885111774, 10.74225712121422, 16.698383873772382, 20.116129748625557, 27.59538404252054, 15.47054479772217, 18.855353916075515, 25.04357106090682, 22.222332580936342, 3.219003302389434, 12.014507468930807, 18.566120600009103, 13.777962825698625, 29.181962775053265, 8.394785078710438, 20.857983385581967, 24.772888726798712, 27.080901386168737, 16.488677293018082, 25.306178993508812, 30.291802322650142, 33.95148508411217, 23.561506103743717, 15.72142533395147, 26.77523158395426, 13.23640988948668, 33.02608449582514, 35.06552237871042, 25.618690016068207, 13.93222889513648, 20.567744264969058, 27.47522355623853, 15.276444524877968, 25.80187718249314, 24.02225124668621, 31.954445646342165, 7.772885545806847, 19.72902879862869, 36.964978790228315, 14.638179034837787, 15.01329677058258, 42.7418462736355, 15.346880028165161, 17.373795027688157, 13.914913192847417, 32.95611637806026, 15.21815059013917, 13.958567499069877, 17.346102444016548, 52.113030390757515, 20.47248587400905, 30.620324501627696, 23.9644982863359, 26.894800784095736, 30.837924742563413, 29.252586384018915, 36.79814985471768, 3.898536487593935, 56.78540812798954, 28.52825787222087, 20.361643144529097, 47.96263920314068, 29.058720123686626, 39.655913558120574, 43.57597574422352, 17.250970077825237, 41.97848778300936, 39.69794972834842, 35.64472741714298, 31.55613829917351, 25.275563348754165, 44.59670564868703, 22.003101997446084, 54.735815722514936, 38.207577013612855, 20.943754307132085, 23.775494359164068, 23.107916120705497, 5.048737109098298, 26.064235166949814, 16.99375371091007, 24.425579569937536, 25.398840647572065, 43.12314745328817, 35.18425566488853, 20.50468841093268, 25.771780953913336, 28.617243672045152, 25.95322521781365, 19.92932304737255, 29.30214100448642, 27.051776934035598, 23.130478619766578, 25.806493439989268, 25.57628624601574, 57.711622160210865, 25.322221652680046, 20.069198381331383, 31.52972007487363, 40.80063129985566, 19.611092677111678, 8.913887729124932, 20.599592352702324, 55.81080958321619, 7.700535909897609, 43.34532412441964, 22.65107696376456, 67.4130293919655, 36.86448307934303, 32.73716100247621, 79.53359867927277, 16.3893504596948, 32.38763975774532, 34.89282222938348, 24.42047314742317, 46.27747259519483, 23.30503755341859, 37.21914055168175, 2.522353028402027, 25.03547649548313, 21.38689303720315, 31.60708078097885, 25.35797824072052, 29.644067117238272, 50.91571557767546, 50.52526273241956, 75.1573254917934, 31.195632335393462, 21.54135398543111, 51.35768245826728, 41.63883602167096, 2.5517401588811133, 22.108310948140176, 45.38171580455112, 35.25513373489371, 24.364749809346442, 64.63573642401632, 27.261706476494165, 59.00077773581852, 63.16026438989796, 3.9329023724697767, 31.911893552962233, 48.4867987316402, 4.335743567878159, 54.30662088307963, 38.548256816857254, 39.79240548032875, 41.75037017966463, 59.78560636836299, 65.4366292644589, 32.80455398827734, 34.22198420426487, 41.84855801540573, 31.20483589203693, 59.9610086748908, 37.50437977991276, 31.126266592076796, 40.38193853021001, 3.3417761360565414, 26.18530113664532, 5.292492543578944, 23.057731889704005, 47.0237176912067, 87.11552931787995, 85.71642826752462, 78.13103333192655, 38.68179415319054, 24.086995991870648, 40.77155005416282, 31.625477767521655, 27.414874422281045, 31.254595274646142, 38.88531037838067, 21.81073758938662, 28.031888994715967, 42.33020435124248, 39.74471880003687, 24.169468989498995, 23.549709159231984, 34.770054037847196, 30.986006473276003, 41.54037957806281, 25.614594181018997, 89.65234427641286, 24.654073053559618, 29.643767420977806, 68.96591906169505, 29.76159753600582, 53.519933540412445, 60.2084318139164, 29.38108803962091, 29.909927733365265, 28.170866071164035, 34.06746716034952, 19.14694448751402, 28.095349945254473, 70.16756488057182, 24.163275816474883, 31.588102713658014, 60.62749580247378, 25.86612926035297, 36.31766761465575, 35.63513412217372, 35.99910556765723, 47.986530692098974, 34.091358701191865, 56.328382094963054, 50.726895184957016, 33.144026362410315, 33.944492328326696, 57.59520714520912, 80.25817605152116, 65.21866057074445, 58.43175096590744, 12.057865821292724, 39.365489966470776, 26.624606023674037, 35.91454818599985, 140.51403676057012, 81.47955900919602, 36.207161741864425, 67.09160703522137, 33.92362748090098, 28.432892462307052, 51.08745897916731, 29.029063807274895, 28.013910199654404, 49.48282981508565, 53.74213689315926, 46.37780001586315, 64.59854221069865, 51.27277872857764, 69.32168844598009, 38.045517913823915, 5.091113689935699, 57.462322532890106, 27.291260452358177, 45.198241722016284, 36.57207602106258, 34.71904399292224, 32.05541961761302, 65.60514884372684, 58.667897695921226, 12.849237780778624, 43.600559085946884, 45.576283134177594, 45.8546108087837, 26.943391080015285, 30.224227650063277, 41.80519813123815, 33.69691009285811, 73.2438306547277, 108.67293181031579, 30.900483719380727, 27.531714284548062, 4.751694904443727, 61.905537396973145, 61.29989354403857, 34.59021278179096, 38.73890547332704, 42.33196106881732, 32.36015171104129, 38.48491186923649, 54.338449748922145, 48.399515118609095, 63.66475131560482, 57.27744775012013, 87.02066156831057, 52.183219803770626, 46.164514579062974, 40.40787206985545, 41.345112053307155, 33.53363481542998, 33.66475309205017, 75.13388735706796, 92.23398958848665, 44.76298576605386, 46.43907828239156, 53.91371950156364, 33.6944877638986, 49.99724495645354, 43.10122014384389, 111.46754580944109, 32.91898112758362, 21.473128717770493, 31.457896316063096, 66.0525864290327, 132.7181306230125, 55.4823432115781, 63.97219504073966, 71.09111103061069, 37.801905294556626, 44.34731508485246, 59.22763770018278, 14.440182118065236, 109.06811117870862, 31.75329691045177, 55.14538785801002, 95.72755869585768, 68.16308806964543, 33.68425442958885, 35.839705515402514, 65.23040015301557, 79.98465851730008, 47.33194232160062, 32.945225972145245, 35.585422722376094, 75.82307045017596, 52.400947786925585, 34.67901210042096, 47.68134356850057, 59.99045208720191, 52.72016566336989, 58.75703677568319, 61.60274384363364, 95.87718335329117, 54.57682548508715, 159.76014854071926, 110.39093670207666, 50.09009405519299, 80.70883737920838, 66.83713840375306, 45.041270858024575, 59.781820218097316, 88.7226825400138, 82.87691128060811, 87.71117346989531, 43.15362657910367, 113.3857345090082, 54.569925368744805, 115.23416050609951, 64.94487538862163, 36.54616778187498, 42.38894093808565, 66.80687531431255, 100.87341703824437, 36.567979278740296, 36.466240858714364, 41.16450982566992, 63.782813217702135, 29.66146169272069, 93.83922968055835, 35.581811570815226, 69.00272043029474, 34.905700741718825, 36.57086542239231, 68.90838087522569, 56.23705389186891, 39.768104025739206, 96.66875736222741, 90.04323325775184, 78.87273575014719, 44.27573902078518, 34.528721079875204, 53.73604317456735, 39.10516681059527, 5.560691056102742, 48.84375941653742, 39.24494473898932, 48.190378967184564, 124.68284963104654, 47.738211676683434, 58.82016722754993, 79.49724484182732, 33.66734512095888, 50.760744773181706, 44.844231376205315, 79.22063187024226, 42.77797482519295, 66.1581538097552, 40.59966949809947, 53.501127800362156, 55.1312561728061, 41.25407671250968, 41.351168320555885, 51.50755311748886, 48.36070970984119, 33.55999056601751, 6.71961869527892, 40.716280738757746, 56.62116078246306, 121.42471038472397, 52.496306459670585, 39.4694324219888, 40.60889332471765, 44.35989891444751, 64.06365924383877, 42.3574249724323, 97.70958883337072, 66.07926486614801, 43.302947705440616, 50.50652338564199, 76.4301188770189, 121.95893643794477, 40.54470771297697, 89.01003104610338, 65.31550126748272, 50.569241829014345, 61.49352447293114, 108.78890227546343, 45.70934407485589, 56.45621664273532, 68.35877082136525, 79.52817565838951, 51.45304138217796, 47.15887556797549, 84.43625387934367, 54.45851890245405, 41.29879495507914, 48.5594932756713, 10.904173707217751, 42.30562204286508, 85.74950491969227, 146.60950759459703, 84.25054286259453, 40.64259691316158, 46.91179132919312, 56.00778960182459, 81.81554328567712, 41.37887080897134, 43.07291199933536, 62.09933759147853, 59.74811902712577, 62.51077496002048, 101.86977513509709, 42.686260660054685, 40.582452714075465, 98.50974490503368, 63.139554881824324, 83.50067457084887, 86.0635537083848, 13.074582859790128, 44.475402308350155, 46.60173077725931, 56.081284009551474, 49.15145398793656, 55.80763730297564, 51.491445597277604, 66.7524232588847, 50.305413198628855, 4.115770803705359, 59.58061204806938, 36.27649247814952, 101.78077836277107, 43.09648100969313, 94.45538569725112, 68.41107944153806, 80.29602615984236, 117.97179261176787, 55.58524183139319, 136.8494998283706, 297.2584166299406, 70.88187651457466, 71.45276756069408, 46.78987786239563, 115.8684642233069, 57.15535919355495, 112.74499226317599, 38.83785785935464, 174.4378334224253, 52.301923345087154, 98.82612908355007, 200.18550375949147, 64.56910656838504, 52.022034551534716, 60.252597176423535, 15.870108613895141, 50.57280113121062, 59.798245425210624, 83.90768898999377, 59.438215038273675, 46.3807855217528, 57.03278525216684, 94.01765769935666, 44.903334543168995, 119.45436532972886, 34.10349379815341, 55.255772652564744, 112.53623983090544, 119.02302113654547, 33.06272248506923, 54.067062554160856, 60.94666361230031, 102.82402223921679, 44.17117794516728, 74.0987237000215, 63.52680890159872, 49.88844338470125, 59.96470598892631, 51.264397623203024, 17.034136707003793, 34.78338095309932, 70.57062625403765, 48.957220606425594, 4.591765047567297, 38.32873762003294, 47.208254060723625, 68.32712854408722, 63.86968383369031, 63.214842232477935, 31.42384550925226, 52.954337650546314, 109.59435223852628, 94.4137673229538, 68.09419742610652, 2.9039669186698145, 63.09873247421342, 106.77487570079013, 47.88077981065399, 104.38320305674293, 55.2341989101292, 55.88186973008005, 64.94173232159808, 60.55832370564218, 54.0850886941052, 100.08915385226294, 58.913017641682714, 52.7479280816405, 44.158968415106, 46.02294273841379, 40.73181666643615, 58.56753637480489, 43.906572753063585, 50.750270424682384, 149.93114017472672, 2.65246496615307, 67.88405168721822, 73.29257976954946, 107.5902809845778, 46.85542845158447, 39.02334485147674, 67.78223130115349, 56.7472693156567, 108.59141652446372, 53.34060127875851, 108.54459289796951, 53.53926316343852, 56.257220975286636, 82.14306977193976, 61.026178490193416, 34.92302200142632, 58.344319640303375, 53.52444079696905, 136.92638172107002, 96.03788620355769, 63.484835831217254, 100.28465237686102, 56.169017892839136, 62.135569664887576, 83.0750300609339, 100.45134634110902, 58.72406211248122, 69.22619213064088, 30.393762971820912, 67.07168952676163, 119.62298432071967, 67.77891387996321, 6.37145726176352, 175.98446751544205, 17.02655008206707, 69.35739803439355, 63.392396723185115, 79.56432438437717, 80.30574250890476, 54.977132636995044, 64.1682847095785, 49.19666652061618, 49.42092444297909, 68.94258295729438, 87.67903111031623, 80.11890853481069, 70.01968599542877, 68.27518652100056, 39.27763374587249, 8.090696630217128, 139.8519032065984, 76.01531009938465, 37.349003683674766, 54.400871222681864, 68.6222270034721, 39.2508728472466, 80.89714788119926, 141.40416042681574, 66.16954659322968, 38.52231216760138, 46.87638910018304, 90.73841948457451, 9.814468687176443, 68.28184766004134, 61.386500372025395, 40.15826118604618, 127.06269953294245, 91.07173683474079, 30.44227257282174, 69.90171820762055, 74.35083253096944, 13.530168659757445, 42.937308174373634, 45.71204647423926, 66.59956286328662, 48.97159107654643, 16.89110919818572, 56.394626350900815, 129.89227668068162, 60.31181741350852, 57.86940246602297, 52.839281455269074, 60.82802660159301, 97.39335971017452, 66.79952906818244, 61.06252013503866, 42.675809210802015, 48.468618330243125, 49.30077170580472, 98.8614144902057, 52.19932660734641, 50.64767000951192, 67.31219499241104, 38.78713388172107, 37.55506079467847, 12.951931980131107, 40.15238961090029, 77.75457159217258, 68.36068729762445, 48.95078022046378, 33.82851385105981, 71.12724340335052, 109.58408642219767, 73.95240787293226, 68.32391031451046, 10.076578900559213, 53.17827432790448, 95.46009765095599, 139.8135303792642, 111.13646490377025, 55.791641244133906, 57.31921445360847, 62.35587803471132, 7.084994079438339, 55.238462370697604, 56.146597138821804, 37.69199842655984, 84.15607895640188, 100.04948042499393, 102.043077340514, 48.74885354309218, 161.9959523089058, 73.09801811779697, 52.27180738261641, 60.97174076556163, 47.767810919979674, 47.182482009550085, 16.228469679386134, 41.36544599065806, 98.99702639739982, 60.13386770726668, 64.90102265801576, 58.906475021430495, 70.04890133901725, 120.2253161848934, 92.00407096183422, 72.96847463119428, 12.732930565216567, 54.64069458189642, 4.561611725851334, 73.38421107042892, 94.73492189657144, 40.32995693424245, 140.71976076119205, 93.03481441623734, 130.71866655377212, 96.18135828199458, 63.07499341041733, 109.18081268341757, 36.13872841451222, 52.77785771320491, 56.76155112159917, 40.60061832665527, 76.15785838814666, 9.90111179393605, 49.04867784045247, 74.8940371049648, 51.94096522015194, 53.0725970168714, 88.88156535043137, 80.85067954350197, 154.29070470951822, 78.60327478792031, 70.71130580895833, 5.794404565339759, 9.356016259947452, 173.3157451531335, 152.61887930707712, 43.6343826354008, 61.9630117834919, 12.571933654843287, 58.22920645771359, 47.33567972293127, 64.85049688268403, 128.66578123581158, 50.061587615567134, 80.93999428675521, 89.16369104656528, 44.511456540312956, 52.348678024283075, 42.69605781093394, 96.36333438671983, 114.77546637690203, 57.86721937379971, 52.850680684786724, 12.521855770075971, 3.7095365524420356, 44.80201673804069, 133.58054485634796, 63.157347125811754, 62.10573122962285, 46.61214376048447, 35.96203690968669, 151.22241793743893, 109.81209767768068, 39.515586272706756, 42.34648242993687, 51.26336749480968, 53.8219260939392, 64.56805569369709, 92.54989436610245, 56.42002346805237, 116.20101967172012, 73.98311608399074, 52.46504891871532, 37.71414094552307, 74.03867723018195, 47.89697611889419, 5.378634444307324, 73.25533537784807, 99.87326558192134, 95.91072870755677, 94.8518100156205, 64.52497400136264, 160.51887494843243, 42.89246106158474, 63.36019538639637, 149.49555097083913, 67.37329525189229, 48.191894735669806, 47.79390425298317, 79.1823860044659, 69.40798002876535, 107.4801873132126, 61.773434916827256, 15.336547774935678, 41.55602530977613, 62.83956125292336, 145.93009618344402, 52.65159251329461, 49.86239407485358, 48.058950619959724, 84.86157422129725, 9.343058804096248, 99.93586458589854, 49.4891327674067, 175.9589515170631, 99.26564402323531, 59.81837891157952, 165.50983521394235, 48.21591950098902, 89.84193639960992, 54.68897661682421, 65.98674093481831, 121.96098047046213, 61.746434254945854, 59.49637464534296, 41.76066671296942, 43.27502653143998, 72.83517977636052, 52.38478231994698, 66.07164584594786, 81.32801632186805, 60.566812630503485, 81.61038115320635, 45.854659282580144, 44.111444086903504, 176.54557763121335, 68.06566598647333, 215.16168151432726, 58.91010257110639, 51.78878041016968, 43.78881068124497, 115.99053381996845, 46.95378646984038, 106.39608531305268, 94.52259109281502, 98.94756518780939, 111.13857521629551, 41.958772779383054, 64.60562088656616, 57.10389221619931, 67.60891828367626, 51.69995386343162, 61.239268698048974, 42.507242617691276, 75.23539347157312, 88.3348781624762, 42.2553715009745, 46.48076316476681, 189.69957918578962, 52.521611535008134, 44.87249092762719, 61.10804464415224, 64.6398445786468, 146.20412799759384, 94.26484800085115, 60.95410095044123, 48.22445537920489, 65.79950431815573, 69.17057227169313, 194.98038808527525, 68.43815080216689, 57.46422558170057, 90.02501312554176, 52.903583280205304, 72.72982637158975, 18.390042798445748, 63.19594404283998, 63.3016147187233, 37.1988076467256, 71.48210179480807, 68.16414986849162, 60.99244077533769, 50.42984727727398, 86.76483584291415, 111.67275230112902, 36.776019010115654, 83.14430806539153, 57.916521364819474, 87.5627121797261, 45.49833575591054, 104.22486712504896, 44.946405874562004, 48.80691794211402, 37.253325871352835, 61.58298426692494, 62.301568971944036, 37.28993708631113, 63.07698737746492, 58.4045521662935, 63.04077610416869, 48.587797839148095, 29.70126997505423, 14.08622810664481, 192.1700785302613, 62.15578108159257, 51.29727620896341, 5.522722438118922, 48.02374376018838, 74.34498782660447, 43.97217354895944, 46.432128167165374, 43.59271007341599, 162.60138868397826, 57.66383676346819, 55.70848181826695, 119.43869808786795, 106.08740217299223, 49.499027273901106, 50.92621379042856, 56.85967089973075, 95.79541031381176, 41.32990028905175, 43.512007445117355, 66.66731821191803, 41.59056219498857, 48.032434104104375, 61.400889544171065, 58.39797188090239, 113.51844676800039, 19.20913858225277, 52.31953536530193, 63.83257158437888, 45.85840630076231, 79.7020527664958, 47.64887755254307, 35.90636727794189, 117.16457629101754, 59.324789112491096, 106.27205529969287, 89.23789976693287, 41.51587380705737, 81.69606508539107, 47.994726254120515, 48.224217316566246, 44.136029378327926, 96.96930933389527, 70.48503012735686, 97.75861772323884, 66.08482800678996, 69.7905224976098, 235.96856152216034, 53.525646355497834, 194.3088782777385, 45.516029200706235, 132.4281544987612, 100.5856320559207, 65.99286812589857, 146.17815349295918, 73.13825496611251, 35.396626758878135, 54.392166247551685, 101.75860535333712, 56.62539500802513, 80.98528432980264, 104.61323765453199, 107.72059074714927, 99.60043943361926, 15.163650321565445, 51.93663614732543, 60.0575927957326, 49.093881526436384, 81.94590738378602, 110.30585974212465, 86.10595343574481, 82.44405589219275, 105.43057728059054, 102.95093847434131, 80.19963511710242, 93.13315172804612, 47.93670774072522, 68.34954997177091, 52.84682598592547, 201.1416682728124, 128.04640144239093, 95.52880871011807, 124.77203912390985, 189.6076723450659, 124.74256425898724, 208.71007603403362, 5.31436451876952, 68.88498714751952, 59.27177565651549, 87.115244789076, 61.01345541729514, 171.9541381754355, 122.93487872395676, 80.69242712233456, 75.30502858802885, 114.36984760167775, 53.76830620481326, 83.7291242447938, 65.53291989806516, 74.95425098574661, 118.0855990011624, 70.0316595543416, 16.428855373664017, 53.32781903036576, 86.75792869917808, 54.39647712962446, 119.90856988684699, 131.02584563363294, 37.791473490894745, 147.03708709555468, 46.19147742617303, 83.69431724742913, 66.99949700033467, 43.86383094464207, 36.801090245827844, 62.395402742578185, 84.03044621116352, 54.633536264471196, 49.566994020419195, 69.67988597392214, 70.01250148751515, 112.31542800802454, 106.51657778634828, 153.02674663916244, 63.973292789583525, 150.65549405955352, 18.898139589991402, 50.22111483760384, 63.04072540344373, 45.98945025748352, 160.97734421299543, 7.094387163673252, 92.48533057168093, 102.34321855523582, 75.82285295351899, 49.033929796226296, 71.18769512883689, 43.621355332301164, 56.45251288042515, 58.72847386707773, 79.00372270611729, 74.76712653962566, 143.66595321443253, 257.9047870924495, 6.491206560226397, 69.88850754275524, 94.70385720225359, 111.49145202301916, 80.76237310814838, 65.48826039475362, 61.21478706273318, 39.45989330021619, 44.50755862585645, 57.14849313940175, 77.76621418498068, 312.49254914248, 69.7779319072345, 184.3674797514962, 124.02283889651288, 114.38250934389792, 116.9857133586651, 114.54005244922365, 41.95004046136418, 62.14693272250746, 119.66349998654636, 51.65906837316087, 6.740100277586186, 124.76512624858982, 56.9557868679521, 135.47351213742883, 68.80543640872143, 98.46645985855646, 60.59265153047845, 55.79012017602071, 40.45935270053849, 52.9846543215479, 113.14550647953604, 72.96089383025588, 44.263136475515225, 74.92750878980762, 58.11479622811067, 50.024390132168804, 86.6490423123728, 54.17486318743784, 78.59719475224607, 49.73143962987837, 52.96484470245746, 57.378897993663166, 7.291777728024144, 80.48792438674855, 52.19407769784186, 84.98807656905817, 81.49020990588518, 71.89973567200158, 103.32146934895466, 206.44285632328865, 45.55955776251072, 67.397431295833, 63.84277020828036, 12.17514090889688, 48.333188406464885, 70.52522491412077, 62.26236081002829, 70.38509445103867, 178.17734589401007, 65.85395179443506, 63.172287310061584, 102.26141355055763, 57.829959248196246, 47.73911376083706, 53.04903772804253, 99.03596924065397, 93.70903646986876, 61.29984539855493, 71.97338422831757, 204.8403197614669, 72.69048749127614, 117.2165654780212, 78.33189869763179, 131.17986799705858, 136.07076794434087, 150.16103583128563, 67.10525592052997, 199.61445415999208, 42.14577296831871, 100.86119959753813, 83.13695652485153, 130.85735580801068, 65.65356470280362, 151.71659554069544, 64.70603200375379, 88.45570469995756, 57.53974589854823, 104.70271890606071, 87.58350473976247, 31.607166348288327, 50.081479024570925, 206.56418794401816, 62.14609522165444, 77.82470543235137, 56.61449494756489, 60.11548607249307, 108.21301725055798, 61.965684501703194, 2.910767872048062, 96.12842496193778, 76.03872900953259, 81.2037956150328, 63.53230603823303, 153.8679847671371, 66.40478229064632, 137.42292387393533, 71.53193966827988, 88.02305163947192, 131.63695622179185, 46.34667516603552, 91.53750899486452, 66.40389202435148, 200.9217528210184, 78.45849902706398, 67.7157239647702, 41.69325810579575, 52.892342179145444, 56.928890486846335, 109.79273179157234, 88.8214157077907, 40.58177267700738, 36.70469654407653, 54.77300566808132, 54.99354740125013, 52.58096730586301, 86.9388287618728, 54.017014033403285, 47.79275899863319, 62.210606567204216, 65.5192814430775, 41.98195910880995, 58.0303190275802, 54.13937312174535, 81.84847384334054, 75.52007990044778, 58.3725094859874, 95.94315475413543, 85.70656327418166, 67.00389526996929, 87.71609503243012, 56.270927192101766, 52.9826260012653, 10.772008938498454, 60.29358887191956, 74.73078901884243, 52.9525318636148, 95.357098401115, 144.2174430309326, 69.91024709671379, 64.78739202743579, 133.81472863066196, 420.291579611468, 49.713963002325094, 77.53775652158669, 53.20445986849613, 77.32055826604847, 102.28861038924313, 118.23160694219357, 119.9101285867087, 58.30726320784154, 47.4927403082729, 35.567528303144414, 59.01345942064365, 58.01939256405899, 88.06262906263133, 100.92700453653687, 52.636475767053604, 104.47813761176167, 49.21161364768229, 84.42108440473237, 173.89174765878857, 69.89025396608545, 85.66572788181462, 62.32423899717734, 101.76829429029621, 74.42955779359413, 69.20495847809451, 73.5083603451435, 157.9286011635614, 56.57277586847724, 58.00102488681695, 39.190333229547264, 69.05431013532225, 154.98152680908737, 70.53684838706346, 73.59867178493771, 78.29917570726163, 200.2656324718323, 105.9586474276989, 75.66208366511331, 60.12006556317004, 53.89680354189147, 77.14870719991622, 95.2162297629091, 48.218020270199254, 60.21370659071109, 53.043209366075835, 155.57166516503816, 45.20575146726379, 78.75559535895387, 92.57814371077566, 47.48689962055905, 77.81624170619719, 85.84796445945355, 76.61025994022853, 69.91368109336663, 105.01658251274138, 73.47904323154116, 44.368064397515205, 50.50475522947602, 45.30999261327834, 90.56399337482601, 96.15691534182473, 50.18558789884292, 203.44122198413018, 259.8921502346693, 221.50844519733687, 76.6752800824452, 41.11616218665533, 50.58910574009711, 172.95067495876197, 44.074186890967844, 73.14513672007475, 81.05627521858123, 9.433156272280922, 92.82836419458266, 82.10967066895758, 56.78359590482708, 98.42235311712184, 67.97115245779403, 82.8510667858032, 40.496976915919085, 76.65836309956411, 133.48581636829502, 68.57025121278544, 72.01270170426466, 73.57205636242425, 55.545608873557484, 6.490963259909974, 39.34284877065715, 99.224858486132, 276.5966084961057, 43.3999296781889, 12.750493870075964, 16.081253748541908, 78.87468318146544, 107.80862522833468, 104.18239166801166, 44.5222068245646, 82.71765186025262, 206.224465120122, 173.94555965989858, 70.35972325814731, 79.29310519256173, 68.08402236530554, 117.51706802054159, 86.89098979684249, 63.824148636942795, 56.289286751983475, 97.96826389357315, 80.00793382720141, 70.95584340659308, 7.121201749269727, 62.414187702520636, 190.72943057100818, 80.44433321768057, 47.981779819429725, 143.12674134335165, 68.38782808241035, 117.92109174888263, 156.67269570339005, 48.51815178440069, 165.12274776288578, 104.07127552102267, 204.1824914226006, 64.2681184944653, 72.70317012935112, 79.57985541289185, 62.72122190080543, 49.3297219854085, 70.84370758486499, 51.27836075957537, 68.86411403438679, 62.18718910948226, 60.45700848177342, 82.19244092340847, 39.04400514681344, 47.92870957834251, 14.035688106374785, 116.14861956253453, 62.699309336630186, 82.92569993513636, 148.31918372530157, 237.11643333694346, 89.15029525083617, 124.57750766439605, 45.429298820096605, 139.59696816609738, 56.90284699608387, 79.8757277150639, 142.28256490736715, 76.09130273484662, 40.98268403713259, 67.00088435818134, 132.09383486380625, 6.01703437141542, 71.45289621376645, 93.9890094929473, 255.40052172888886, 72.97293413191606, 140.83597931461463, 72.69678424534861, 33.77675536425864, 182.60856236207152, 83.12032308986485, 127.58283265685141, 77.01991125906522, 70.22199559483293, 104.1584907413981, 8.204237813267628, 209.41199923487238, 11.866014179108497, 59.60204444246344, 177.77432329017498, 5.770957354297879, 6.767166558969512, 77.1431339177993, 83.10392400270577, 95.00259575102136, 88.26592286697823, 54.95442113483939, 61.1466333327458, 69.82425027034954, 63.31560371627886, 157.16015696886828, 95.02333016671994, 114.85478609324116, 93.57721175788167, 96.96926292988891, 46.09823752519345, 61.3182172647925, 107.48774510254464, 57.813586468119176, 80.40648462411545, 129.217532519633, 72.23006143888148, 12.903341134692571, 86.2886535194651, 72.06970159046692, 56.986929126805634, 51.898716779321326, 81.18349099906186, 47.71418993382764, 161.09418309272013, 191.06982155177326, 220.97928026484868, 77.95758788578618, 88.93636564055984, 47.637545558330835, 47.21167433113424, 81.76098660851068, 166.00760015105038, 8.473688194462012, 82.0675814710876, 74.18488039099496, 90.33063773136897, 58.57778700250403, 250.5131458979756, 59.122859729181386, 8.92556357034988, 219.26031282102414, 48.93252235151389, 69.58502867017128, 52.08819234547795, 71.88784570295452, 54.356848855204696, 69.4668427202073, 188.2229212343788, 161.87674465773017, 6.741645531528148, 107.37962643418895, 60.73697054196125, 7.179414622278869, 61.93599077881975, 82.93876222032533, 70.10092666655059, 127.81713634420046, 46.293506127917546, 84.22285687666187, 159.15445452361823, 68.0114644078311, 103.26714996975774, 40.741356044015056, 111.12621346279528, 101.23696424566438, 84.25917157922673, 61.37983175534637, 49.938653631650816, 11.526418820468223, 145.73573937715153, 70.19310591537173, 110.93132311583553, 63.31873049297023, 48.64263468802792, 68.58143660298487, 56.99549216617627, 38.402230722199036, 69.76249130022337, 98.28182940922045, 158.6093552505045, 63.92969308164135, 69.54004945936761, 67.30635654906972, 98.77378573281152, 60.271309257610355, 166.18615648283836, 61.92635023556969, 92.35675362449365, 68.63179816965705, 73.53323875264178, 121.95087092734285, 208.71205448625662, 51.29356726143129, 57.490092244348475, 58.09873006325424, 79.09855266957311, 189.4653519112117, 296.9950099182991, 90.68385037967073, 79.85459490955786, 69.16940300578462, 127.71023134481317, 41.638519787757325, 62.02226120258405, 109.44135510950449, 67.21775997518579, 127.57440689186701, 50.31375212564152, 96.92700874273226, 75.26003014359938, 90.17805767262487, 184.0527580795455, 98.11733129187297, 69.0920007312376, 82.5841914418405, 152.02236914132126, 66.18431503009938, 63.72016617846594, 42.5330809336092, 79.30904490439744, 62.32918508959745, 128.87961861062547, 52.89267263140433, 58.87967088538488, 114.19431574391386, 123.71377653196024, 60.836441004707304, 88.63444165131014, 77.3467376292948, 68.13119587971708, 62.13323838003668, 126.32638067241437, 157.98580123042655, 186.58587651396553, 189.3467410784886, 7.3153103117199825, 150.62660564105963, 59.712840998248964, 48.357917324848415, 62.57440483268178, 66.90616873554832, 73.44789106240033, 48.21040304084486, 117.1101451417445, 85.25665491765278, 38.44298137182521, 64.73812006363633, 109.97783534678976, 139.14443939958718, 130.21847892189336, 90.65601886111685, 96.46059944066495, 102.9711988853254, 129.47158502744034, 46.97549276544768, 112.29022105895586, 55.8560182095297, 89.36765241357553, 135.460344</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>116.7532060527802</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>80.27308581483524</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>[140.60032653808594, 157.72544860839844, 10.72118854522705, 62.86947250366211, 277.2611083984375, 146.67381286621094, 63.31480407714844, 13.029439926147461, 151.5391845703125, 216.7476043701172, 81.69488525390625, 69.5611572265625, 65.74591064453125, 92.8314208984375, 87.15933227539062, 197.20547485351562, 118.52790069580078, 343.1767272949219, 53.5223388671875, 23.24957847595215, 90.52674102783203, 70.99396514892578, 60.76948165893555, 61.30970764160156, 70.76118469238281, 41.85939407348633, 68.60692596435547, 151.49876403808594, 208.2129364013672, 144.4435577392578, 85.86971282958984, 135.1082305908203, 51.40895462036133, 277.0621643066406, 115.50450134277344, 100.394287109375, 74.41860961914062, 78.1587142944336, 61.56439971923828, 79.82330322265625, 164.518310546875, 158.97377014160156, 45.09062576293945, 66.5380630493164, 18.27484130859375, 54.485721588134766, 127.57748413085938, 85.95061492919922, 86.82808685302734, 160.23362731933594, 74.0547103881836, 173.7333526611328, 41.389888763427734, 346.8572692871094, 80.99012756347656, 133.5198211669922, 55.360050201416016, 90.86895751953125, 179.22799682617188, 91.59136962890625, 186.61587524414062, 261.1429443359375, 9.026141166687012, 54.627113342285156, 212.6452178955078, 213.81251525878906, 71.20989227294922, 123.3603286743164, 11.398931503295898, 51.06068801879883, 226.4202117919922, 164.36338806152344, 61.753910064697266, 170.83096313476562, 59.92792510986328, 41.56831359863281, 43.5516471862793, 147.1851348876953, 10.486481666564941, 133.76449584960938, 79.70829010009766, 88.87542724609375, 118.613525390625, 93.5879898071289, 61.17301559448242, 58.158512115478516, 73.43897247314453, 75.98473358154297, 99.94901275634766, 386.4532775878906, 332.3446044921875, 321.935791015625, 220.97402954101562, 72.33314514160156, 124.78690338134766, 137.58692932128906, 48.53984832763672, 63.63276290893555, 124.65239715576172, 200.3219757080078]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01115</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:01:11</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>92.08489446510939</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>76.83153280779486</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>99.96039207841568</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>4999</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>[0.8769308046504629, 0.8011264649045112, 1.0397675265229656, 0.6921087159347381, 1.1879087140858136, 1.370542536850724, 1.1467446345530485, 0.3101272008032878, 1.677466696456907, 0.10968628275483673, 0.9739010137751829, 0.09134106012846353, 0.8738299798298741, 0.5791869550466108, 1.6631660359728209, 1.687047905785643, 1.4143520046857145, 2.453902457950901, 1.162286198703704, 1.8301598262763996, 2.2871241272206766, 2.383629646350758, 0.38326341737085773, 0.8065916720012456, 1.1502051566957152, 0.3902932823212479, 0.8181783921990464, 1.0168992680820794, 0.6126925980238034, 0.866796133315289, 1.1671784421346127, 1.429448898424296, 1.0371042599417104, 0.7706399286448635, 1.4353685291368015, 1.0092744268480849, 2.383923134277688, 1.3960381406156668, 1.7707493650856978, 0.5135670005957425, 1.6537541102970204, 0.9125980016425912, 1.7378585747918138, 1.464022927906812, 0.2099145581936257, 0.8695553407243071, 2.0565863202183836, 2.1365567814921724, 2.9589193009266412, 1.8634880492918302, 1.5986372577754466, 1.3128611770742944, 2.42098492613957, 1.83677922059439, 1.877694580786745, 2.1511000908966778, 2.25423919449781, 0.8741750549342305, 1.372107059660986, 1.217919491868586, 2.2538366250645656, 0.39159556515185023, 1.6986038691124017, 2.048175746913967, 1.3632789837605974, 1.967574340514835, 1.550380874145835, 1.0544014076429726, 1.8799628312601697, 1.2665415604100014, 1.2599089908296845, 1.2500666934185438, 1.6938076668783904, 3.359980234885317, 3.692934934316, 1.1235018347186292, 0.31808944477619605, 0.8127957309707153, 0.605883319276753, 1.2459912058299738, 3.054819700227895, 1.8061144232045865, 2.7881600242508138, 2.047698435305375, 2.5238624166732673, 2.211664315301465, 3.5288665822178027, 1.73515225324838, 3.4888596343795206, 4.65594977505233, 4.8123229038231425, 2.3690215715360954, 1.549978042958345, 2.930826111194118, 3.0967379163558535, 4.810440824965912, 2.830100973045164, 3.479537919056316, 3.6450962217068286, 3.763129222365414, 5.695815855980006, 2.7280921188014147, 2.7984642941890647, 2.4269542235353456, 0.8256642458504101, 5.537983315768468, 1.334061577714891, 4.657827477712033, 3.6566625733462033, 3.0610863551612453, 3.5097543195661243, 2.1065552581329667, 6.6630334131601, 2.749770613565707, 2.4009215495027108, 5.802499686294344, 4.059364769114884, 3.3879983590053584, 1.528887282855438, 1.6769161861560198, 5.921924797203543, 4.1577160785796865, 7.93428835336614, 12.177738873538074, 4.411838478990764, 8.312319289864735, 3.8655446288893858, 4.7466309917143334, 5.984463668362692, 5.858091206834883, 7.661577286463199, 3.475073446647793, 6.843572292105119, 3.302487169748469, 3.917649300994667, 10.291290553071445, 3.8683336574882143, 0.3509695286400801, 6.419029520367692, 2.019142357667037, 2.9493289736094694, 4.703764117245227, 5.106722362206075, 0.7265195019576574, 9.198251234137336, 6.359987410148027, 3.6103591435009776, 3.654229083211146, 7.720883954209196, 3.650535970669442, 2.9452438161061036, 4.86182541098061, 3.5431652152397817, 7.567439290023942, 4.829087876051966, 6.249143345632968, 7.984426811562893, 1.5081693122197226, 6.354768979154244, 7.60956591468226, 3.462621787551585, 3.5078211862836244, 5.823369432023357, 16.870329959948535, 6.333426306500684, 4.055581993143147, 8.439500364883568, 7.804246707354614, 14.308237930269609, 9.5142632831055, 11.24094590797773, 7.44787774888716, 6.775832580604362, 11.857798457618257, 11.436954767934552, 8.29789903876788, 10.09334184041613, 7.488731454364448, 10.671985698909323, 22.01752240064178, 9.246433952356817, 8.86914595108223, 12.09377236668477, 10.50898307932752, 6.618731189367893, 7.366689949238405, 10.462844100541211, 7.50510428600624, 7.5784637661279985, 9.57033106537716, 7.819205942984615, 7.1300148425217005, 3.7289791871918476, 2.138904406083811, 7.7250733203917035, 6.35979488999298, 9.700706809101858, 11.669418466298369, 9.846697458855694, 17.41987995398308, 17.782745880472497, 16.656283270379593, 10.127222183156361, 20.991112699560805, 10.740280274326436, 10.891869810069764, 22.67347034630413, 8.3507556957312, 24.170953581519857, 8.513968713496693, 13.53344424892108, 21.926167610571007, 38.367111846821885, 9.090709964245539, 6.350237526763104, 15.556739186972585, 28.462632003208384, 7.456770761591448, 15.157142079238364, 14.358957682235694, 10.908874822535324, 13.463099514660062, 23.520448919811418, 14.783678079516445, 27.17042893058838, 20.965126687283888, 11.461611632088232, 29.245313804744633, 9.701609972517758, 16.152472298374924, 8.471105901493477, 16.596708380328977, 13.42038236990996, 14.58475600608884, 17.267380401275577, 10.865742289732193, 10.538837874902773, 24.487315067064863, 23.319616955856084, 10.231543680350434, 22.495931008162124, 21.128844906322875, 19.660188224581873, 34.17513619530154, 14.639868801036881, 31.665736554017712, 17.32934631436291, 21.917276944261115, 14.936843995486768, 54.316835668586094, 11.07388028697524, 6.847972993279075, 35.01905951645273, 8.259598525208252, 15.021523189535992, 32.92557402867176, 23.484975102708724, 22.077675895763186, 19.388770497600355, 14.325029130040047, 24.468466543503784, 40.964156505022366, 28.472756590208, 11.420685639548717, 22.76833616251522, 9.467592957657741, 41.09335153889767, 22.357620600180617, 13.180381481746675, 26.21071988010667, 38.44124077556986, 23.903469914964507, 30.785845620521, 13.132143052318645, 26.712600013905263, 27.39799094205671, 38.499037449224076, 16.01401892779652, 44.977596733083814, 21.72697900302343, 28.305918707417366, 41.87827063438929, 13.824603131836856, 21.821213700855242, 36.1121331779784, 48.408520919746444, 40.76417708964839, 32.6188786367459, 16.09979693244824, 36.64643361183056, 24.49518057164397, 31.787687588114842, 35.15250706679117, 21.932550557338626, 21.188938401905315, 28.451831962561723, 13.964327417288873, 20.956888646179877, 21.520501705686193, 5.33121052866688, 43.37811701436515, 24.427006601603985, 17.480890343227202, 1.9719409396087006, 2.5919304926860676, 33.03521427109687, 20.45390125380923, 3.0548729460246933, 17.207442510340755, 24.576604246189962, 27.680888226262514, 19.974111157775177, 27.79908918509632, 3.3636555958882894, 28.938602441961024, 26.295860254999724, 36.232400065283834, 35.60513466379766, 42.30763858090685, 28.976815257877156, 27.725502205716985, 7.0703164232409215, 23.0715885865725, 51.45491056148781, 45.65341754336696, 22.700239172235236, 37.10893422780629, 56.20759529907237, 37.26405838150994, 42.945056677511396, 32.30761307869497, 46.2908778300959, 25.91587523278549, 19.69874035957433, 29.537774432443523, 32.703558051723185, 34.79843583597234, 28.664254639793835, 23.92568767838975, 40.699849416602135, 49.330130036223764, 19.50106196641234, 23.94246007592643, 47.497986474346106, 3.608313419602759, 42.21891519753306, 66.6695958871585, 81.73837785089435, 20.63120986586413, 25.242692135559, 48.06926199949894, 25.154344873916177, 41.013260834186, 39.33147755291991, 19.84625696692216, 42.27725748191894, 39.85217533693265, 45.90381423725243, 22.20838002333125, 28.169097960643015, 30.255449260231256, 34.850006825155674, 19.487197438493336, 82.50811057894042, 25.767871747095562, 52.516708926752976, 34.953148354794614, 33.100309104753805, 2.893408651527709, 32.54513562849806, 24.643366436831258, 69.97878559951549, 55.96178890248223, 21.767043043424618, 32.671291012682595, 21.23789167751597, 27.410386459090272, 22.849458526198035, 19.370008231090406, 45.52933062031017, 3.795638238623929, 22.127480183241744, 43.674223575962166, 6.731943317086607, 2.984831842832778, 30.739401109637036, 48.019650840493796, 41.96080074446599, 25.569785020519813, 50.505224826185376, 32.58971236222794, 47.989229166125256, 60.78139536056017, 3.113626214187236, 59.02632552291185, 39.53546812100988, 30.39127629014303, 44.492185546222544, 44.37413736360308, 29.189446712858324, 61.29157456558497, 55.55860423456832, 30.86281598086997, 27.96223613108752, 67.64844707883611, 40.0174048129129, 26.283179356332703, 53.71575414395987, 41.86933846020718, 38.63458527929697, 43.23866756937698, 55.28621938157879, 52.19404062907878, 64.16577221949927, 50.91449015870225, 43.12819700456516, 53.6060412038098, 48.333650294980316, 37.65431343696327, 4.15998290672483, 67.06703768256503, 31.9101185200765, 31.056272216870948, 50.07057162832313, 46.198070549722345, 26.04408943139468, 37.93484534266103, 63.67665254688458, 41.217570697848394, 29.727445560000287, 3.7096499867338224, 41.40120205039323, 55.17251554133222, 37.04662511500779, 28.97363205615769, 51.32574802665509, 38.03826180944362, 32.21942411886641, 26.50059161103113, 39.390685194571624, 109.37843306290361, 45.36473910286049, 53.70250452497062, 91.13657979093631, 87.29669383328988, 78.91696088037276, 49.36141271032931, 100.63883586536714, 40.61688253354596, 42.66361000381627, 29.26080649372812, 44.84413412727685, 76.15203314789257, 55.60583186132969, 67.14800393435145, 43.18396841279219, 50.65811065999997, 34.58665374561191, 42.80868016400701, 48.65445954456463, 98.88842229060315, 142.26381947877704, 43.748205751512664, 51.38303393541804, 79.49247096614454, 42.38773597614196, 34.75274540793794, 66.63492824111496, 54.01741128851816, 73.6506050974012, 38.69713194267466, 48.487889807090596, 41.77672003089274, 86.1316538336786, 35.01100027791489, 23.126617209186506, 39.575784957513456, 64.07791806627232, 59.56530868484861, 39.24821895458968, 58.21496258775633, 38.41210071396688, 45.02800144571929, 186.40589568709248, 44.53730343796967, 45.688468016663194, 37.2334187275697, 92.64714116424854, 32.82688085217307, 83.70299335944497, 42.323328077811965, 18.308034950689233, 10.863137910986143, 140.84718810690558, 54.176755161146524, 8.407892961175559, 114.42983789161504, 49.34111252216823, 99.26616541775284, 156.2076227806133, 54.19073926264694, 59.686006837145825, 55.513945161298494, 86.90855364792051, 53.77350429814379, 65.33677269867256, 58.82818397686094, 72.25544859568168, 13.183558602259346, 40.18159942711241, 44.09063900876398, 69.13825901116496, 160.454509246905, 41.63002924507388, 43.645432922235216, 43.089043550922604, 87.92647091746775, 112.20150023555055, 59.3157478390296, 131.66797030852055, 43.12552555227226, 35.37067747871906, 9.500289625248758, 69.0519989605539, 63.25214109032936, 81.43486689606843, 34.11633431519746, 47.43464349594866, 53.626072401571044, 58.79435165808085, 42.40669785491069, 52.329017903065534, 46.836716008906784, 39.04185581302174, 41.89298869482393, 5.985715390013099, 50.78995510779995, 47.343223767933694, 40.50952749876031, 42.578261229702626, 56.57201607309936, 40.86157028996928, 37.224097703375506, 56.56699462225333, 61.06099396782746, 53.90095333845145, 75.41182934937598, 79.70160995804235, 59.00426399988555, 77.63201717980114, 53.245483265651444, 55.05599687972515, 60.6679904831944, 53.086319081747654, 72.59676382628638, 44.17963453358481, 57.16114629866749, 83.06481033025779, 73.71440173796849, 102.92702387360261, 36.399197115255646, 51.36128023453773, 49.557004115306036, 102.93855642023017, 43.47733486969869, 128.98223760905344, 59.35342302346749, 66.15905847768893, 57.856521643795936, 44.54700440228056, 123.1678176773121, 40.063269127821606, 40.15291889108757, 69.45250512817613, 42.81429473732168, 32.73488819819725, 127.84445142481792, 57.515852679477284, 40.74228641880444, 50.41385988447506, 39.83438615068788, 75.71422371114201, 72.70637863160357, 52.89129665718995, 172.13758533334888, 76.90652438726424, 45.93056338442833, 43.11011925827417, 90.07544673010449, 39.58038594809496, 62.84143525785427, 42.490088435091174, 46.019468897716266, 61.67968912333054, 43.77930972484078, 82.19825481064386, 84.66473366468675, 101.88385388936757, 47.4610524547347, 74.52623793577796, 69.84173112002358, 39.163593925043784, 48.49139664466626, 160.8770195690912, 66.97046702144026, 33.67671720906509, 45.00842626650983, 60.15684765547003, 91.49958808421127, 36.52562039169868, 114.80535343832011, 41.83069667340839, 34.98947951558936, 89.03790769424981, 56.198947823665335, 62.91943639117498, 54.232896344777316, 44.64098657671057, 164.46258427148723, 39.289427168873814, 65.1004534527166, 125.04807607009437, 46.49644950394637, 98.11660462580903, 7.642982083641278, 151.70071754167853, 40.07346057693944, 45.97855969118058, 103.14212577052109, 62.67563323629367, 36.46059950599875, 70.06521860080292, 78.3230130451655, 101.87758260718341, 100.52330833221899, 47.758082046902125, 53.62549447240257, 53.876247217412946, 60.9394401012716, 46.788898502773876, 57.3714053607895, 52.24884399046905, 43.65088082506518, 54.00728957263903, 59.23418677796266, 60.74718028066209, 139.6565647216496, 48.102669233421494, 36.944151791444085, 92.0807733920474, 178.80864876175474, 96.2784808023839, 46.820227378485725, 49.76570840614826, 51.52671975325561, 53.90820239878037, 11.156906807217634, 82.3472498000722, 78.16404534785067, 68.81646375041589, 48.37007341826208, 45.09977756951177, 73.63825797745105, 58.04766758170389, 5.379028589452991, 7.283202255278005, 56.621002567246975, 45.910330076622685, 80.94026639343733, 46.839565868320754, 73.26150646456719, 10.988224992663419, 55.22830752304737, 86.9966113677106, 75.9570878208631, 82.19803793716224, 107.86777850831234, 5.709824305339544, 90.65694018046568, 135.33767322595992, 40.437825558295785, 62.919418773893824, 83.02242377827814, 74.40255559632088, 44.87189658822982, 85.93690995195219, 107.88091925320687, 143.1127961013695, 39.65996316884692, 51.44130453110045, 31.29007472709278, 5.210935695908706, 115.36061258877356, 49.85719635254735, 76.37824592352966, 46.932958792513546, 44.20661348271965, 90.49631198323009, 127.28921513693555, 75.5961219471727, 58.619237636764, 42.947906384878046, 4.497376263678527, 116.24779448418302, 94.50173802005449, 80.19834466064525, 65.17396208350543, 113.51458925563387, 37.9381259710599, 47.736073117382034, 46.133695999331636, 40.75186958417568, 132.58392461037658, 109.87589892339238, 68.43335348288606, 101.15434834750225, 59.74161807536133, 41.37352752816048, 50.1598786703727, 5.2956755581642, 77.58098528363027, 67.5626695787534, 35.566531245406736, 76.51784838032094, 37.27636734946912, 51.13586939967696, 128.84692331248607, 99.5753056788879, 88.59677160716454, 60.13967740298746, 37.77936424116223, 46.8745474956856, 43.095425552758996, 45.208729609890504, 71.43320254677606, 172.99850900133305, 48.21521593073485, 163.75689626371454, 51.409206002129615, 61.19632300935425, 122.93998812866377, 42.52486719884167, 84.02118056751874, 10.524183944503218, 46.13707862507433, 7.163924599530511, 142.35599170827845, 55.8712124883518, 124.21617711284205, 75.01523944262931, 56.67454150968598, 46.83130259263562, 53.729442170347525, 42.2708948731368, 25.68858545832742, 96.14246862958028, 15.945549877623616, 5.610969461421016, 91.61159635961731, 87.53178796517399, 81.55857749470354, 40.54268329833342, 8.842347882846262, 74.88343913533501, 85.25800874098877, 53.33246210673838, 79.81703184010091, 53.23036936997829, 44.045634364705755, 93.31739304639338, 82.02638315300764, 53.594931100523084, 51.79213741671038, 7.637707344214119, 106.39531766452181, 83.08017887796764, 90.18084510915678, 83.66616511343355, 54.9752410655857, 86.45151491375555, 29.180984959255163, 70.85664878185801, 78.66978957057886, 38.84488882433372, 56.834220947296444, 57.94014100962795, 55.293325780019586, 66.46029005954355, 41.903933089371925, 94.923768940299, 40.861689468843636, 74.41947565140221, 62.13113610019039, 52.338622116620726, 5.77669667223901, 68.2671039598232, 115.16736697996528, 69.8111513734204, 57.91008012507676, 36.795623352790116, 41.74684368681789, 56.61242466291824, 38.780661851681046, 157.85035602258642, 71.33057165487283, 66.4738458510341, 58.70985665009524, 50.02605107362102, 60.29560442247322, 108.57517710507659, 58.920903371524744, 50.80664286631937, 55.519902450207944, 57.85876105599907, 62.74457861585665, 8.58059466873151, 73.8105609448998, 127.07212191273065, 72.40362931930734, 40.18706314542031, 81.89198777182379, 116.2333196811168, 39.74037133986967, 54.87331500388426, 4.780190527803096, 84.399875295747, 54.92818692247079, 90.65972791133368, 61.87886982811603, 6.356367973646948, 59.82945218420982, 72.24434067560462, 120.0086688284414, 74.45142206238357, 63.60776857870814, 70.92989540761988, 58.378121540007804, 62.57549724029445, 30.375710494772342, 93.0261502004551, 63.23722931281163, 35.41518006519432, 53.355084664973845, 99.64114705341304, 55.74101598304318, 59.094492072694095, 134.7781672821871, 9.120144533249178, 48.781732574951185, 42.04204856261687, 56.297315506410655, 123.53252024997283, 156.88871508988439, 36.292446814396634, 56.04115697376192, 96.15111446203323, 43.13218819411316, 46.03897889105598, 56.94391763329214, 87.07808878671513, 110.83550931089849, 47.744408428003865, 62.55935163839778, 47.21424244985207, 56.41004826422436, 71.05767442365375, 12.843344766721907, 62.978380741278905, 55.55450902848551, 65.06155726631052, 38.837041243767594, 104.50999650648197, 44.508941285106914, 49.394314931491174, 68.2023512259306, 105.88226298820462, 149.89205161313288, 137.4849303615919, 45.43434724742513, 45.78615724733231, 50.08102856128959, 57.69045135072751, 47.32465185231635, 51.37045526540513, 120.05788349698624, 61.31349966023943, 171.50445919701562, 102.04127848362194, 76.72959052514264, 39.07865927841827, 81.58578043888956, 55.86967004742873, 162.0508304653645, 131.3422412273584, 32.264805844150786, 134.92715106860928, 77.20561946596837, 66.40597457495359, 96.69704093704922, 79.5204351140398, 20.859850316076404, 141.73276255533298, 5.3723689716432785, 56.00201289068263, 37.67525346436289, 51.220313064396734, 96.750875514895, 34.738556327115994, 8.198169688898748, 86.91348218336645, 117.44333319078474, 33.607159275887824, 50.85525470731511, 55.46212958971809, 87.58572269856778, 57.813182584515545, 133.8495446250735, 5.091728584171059, 53.86411616100379, 54.11508771140416, 5.362942020780202, 104.83915881585072, 131.23480227775215, 58.98037717448358, 7.917194683751921, 47.27373759030897, 53.410598903410914, 87.27894892237853, 84.42898312307376, 125.56951567150804, 57.444383731326795, 99.91459725795468, 50.85305025274363, 48.39561725472313, 52.5414739308318, 45.299706229648145, 130.74528637790152, 155.05755871369067, 40.45161668001414, 41.408880736612176, 47.23538869502791, 61.26556262793193, 72.98188930964542, 63.45829002330004, 49.20771250317581, 46.43372869648367, 36.4898665686463, 141.67044918488466, 56.53216520015366, 71.24644247460316, 62.49864729877505, 62.08781054589274, 46.859786015396516, 55.68749861922608, 92.4173897111926, 59.14533240897162, 94.71751880028394, 9.221946471304719, 59.65888655312942, 101.82727551263527, 33.90080938338588, 57.47568203569976, 85.7545717036435, 60.90297389500441, 66.69608275526546, 197.08232667731005, 70.21497762212371, 63.33054719743827, 96.24669595231956, 114.41322274778125, 41.38241203188272, 54.05359201005, 111.09653767124185, 53.82940010797016, 78.70356780612353, 39.40806516039195, 46.87989313110441, 65.49482618842634, 81.92890659251579, 117.65860952032628, 133.84151087894554, 147.6100774668454, 65.66985753592904, 71.0648529331936, 42.557787628051386, 57.32866255009316, 59.21755410860304, 42.39339671148626, 84.94200389060963, 40.80075518189583, 84.30326332366933, 48.114282825258826, 78.73814835939133, 7.394953909328541, 52.499956743608955, 80.26792129641413, 105.13781088820124, 42.79551040238589, 52.9819228153046, 6.258377985871508, 84.41472381029601, 121.19793498113528, 94.29005693972816, 78.65111766435382, 42.858302708150866, 59.34342917751509, 97.0585107069197, 93.23064286065915, 75.81105732639391, 63.266879499142156, 57.20199010293682, 71.6903836600043, 136.5705497303385, 73.894926515367, 47.58732225287974, 65.59253100465926, 62.471746651377785, 67.67006168892212, 96.9048295647721, 43.74250267997372, 37.74582055852386, 58.098047370886476, 53.204929916766474, 68.4475853841013, 149.31801516327664, 66.2010573191045, 51.8359372189804, 45.54289479352051, 81.24287078471998, 46.126536333524015, 107.02211722935452, 60.20039288004478, 68.57954715194266, 61.11483397844484, 105.77671084203642, 37.40270407088095, 92.21707386668463, 113.36800236831803, 39.475824710485, 48.246173487651205, 97.09047780757496, 69.09885929625914, 120.65653247464529, 106.05825932641264, 80.26885521687322, 97.20341363023526, 75.76565313314514, 149.09163516818333, 40.031327203513726, 45.62548149950444, 51.08404461888565, 91.74577011022816, 188.40139063952168, 38.68024405463486, 49.8941777480854, 143.57266049638443, 6.83396367037487, 70.4399700826213, 22.74290912846725, 46.229649399739614, 70.29771769918634, 66.2145158759811, 57.029897357247215, 166.45696036203012, 22.471154536568875, 104.31746232677118, 80.97731245480477, 84.99264015475224, 45.8612022814798, 47.63483790489315, 44.63290486949591, 124.12219294707837, 182.74319679099978, 118.15574958226505, 95.04805714453114, 64.90597572443443, 43.60249643980792, 67.2562006825645, 65.20690587749536, 40.883575120593456, 60.54020420370739, 80.20843920035354, 71.45395831805565, 39.14052305600289, 39.89791229729795, 49.81709556658632, 66.31467150614014, 87.08909035700685, 14.235494233086362, 67.66432846440556, 64.24889487663148, 38.21339439080216, 68.08535754386394, 44.29752291362839, 55.07253358975607, 45.02908997016806, 200.77356277704666, 68.64778192032769, 81.6568904887624, 95.34953712669953, 95.89498636624796, 70.71229873520566, 39.78936070315285, 141.44421112321064, 65.84164573813122, 38.63545402722502, 58.9775098170622, 76.6413314924964, 44.003054888579356, 46.1823171322474, 56.58829269939544, 81.34916234985081, 90.16349908880042, 145.4386412121098, 67.12711639719384, 74.74616636966762, 48.32971891429004, 107.374267717469, 51.38234934240345, 224.0143053924552, 69.89776574413247, 72.8074853540622, 153.05677535359618, 96.07391903658684, 46.24992886878018, 73.39191229513911, 32.76427011147123, 87.73640811609911, 84.97602022261864, 88.69197193505455, 210.5958438157215, 49.907199326318505, 125.22891402964748, 74.16862538491148, 118.95627246972352, 84.0629989878589, 47.06639148102354, 166.4068260823372, 78.54831868007311, 82.92462487952976, 185.56681894852818, 90.44691255615462, 45.58138930574956, 55.47028236547342, 99.03454241605647, 148.61172104940977, 40.895720954691356, 64.94313164327912, 271.4447808393013, 107.97974764731663, 56.33089212793698, 67.78746311364063, 59.9471517401646, 160.40122587775534, 67.42523412042539, 59.79419649979569, 72.86485791070616, 88.6602839045331, 122.72997922901907, 47.13910968956069, 40.08394422303202, 74.52343338080837, 72.6552317674469, 219.47323846167723, 79.78917350306173, 79.27021227035996, 77.41119112266571, 38.163750661681085, 84.02620730093606, 13.560066351571127, 48.27547068069415, 118.34467521509696, 58.21472248852931, 58.27414045759634, 89.2183904328654, 75.16476488901372, 58.65610891466643, 82.40162799442591, 53.21505215162737, 82.75260787573457, 205.9773397538921, 66.13135261352507, 67.48786384255243, 97.87252982240548, 64.62992639781726, 101.08388546763551, 40.25264221423513, 10.758716181453467, 135.21708242849363, 8.76957524867095, 38.269892941188836, 56.21350888409274, 136.00011068478992, 59.054713894974725, 99.75072945044208, 193.5190908369115, 94.8482814454643, 111.51839955490001, 128.98308771274426, 63.288087294505246, 108.77836269780369, 45.961025784848886, 82.138799164535, 98.72137548093848, 47.621252615923076, 41.04720746310401, 70.77814992503895, 75.6565776054507, 55.62549250517877, 47.79591923791427, 64.41769326401163, 260.67551672407944, 179.5857394438159, 7.150706500845015, 138.66789603278283, 246.06779142489663, 65.57519724517887, 64.27021340459656, 65.14777469006616, 45.641211246193045, 123.60456659389983, 70.932335571507, 68.01534742180651, 94.8863811819328, 84.26155850284488, 52.74846483355397, 77.87630630409487, 49.12472263855332, 60.12770327311248, 56.44967995407284, 73.76199371622144, 63.35998523925721, 50.02420434792379, 62.931588000207476, 178.26395586644696, 75.72827191765333, 91.43846626011309, 172.57731290291022, 82.38906297032189, 173.18701817897548, 69.3758961609557, 57.99112028291577, 11.77069754264272, 50.99358106397914, 48.51995899187752, 59.29104601890866, 268.06361290716876, 55.68865762481603, 134.67675261275645, 64.63612766157314, 81.29416281275243, 93.1734526284168, 103.91046509818783, 107.01672021217226, 7.076599068881663, 99.19583222410866, 45.71296605059363, 169.9707309534595, 52.78473519538106, 98.8509329319984, 82.74407777466587, 69.36060890405908, 87.93798407070192, 77.32807096357077, 163.59538471580674, 42.941999615364324, 49.49161916518265, 54.61916817687127, 55.61158174143247, 170.38476080826467, 59.69423262762952, 96.30080108739548, 18.49015581870584, 51.545496918275084, 18.885526518335407, 77.086146619811, 8.33449295800861, 66.88938036134742, 58.952790847501596, 117.9515071028101, 78.92184172083948, 62.18265926067276, 55.08885367048237, 53.723860798303576, 90.05501629822948, 128.99302486890133, 52.84131112548076, 78.31258084423746, 87.89118457743129, 74.85380674594832, 45.851040719478625, 47.468884461249786, 119.62900686065173, 107.20480903164938, 48.105162430718245, 118.35553354746196, 77.39209436869255, 76.50998122262601, 65.45131586251011, 57.617374916148286, 70.48368290256282, 102.55830513915264, 12.837913933253141, 57.99506692673399, 120.32833838859618, 68.497384165871, 60.37522625869065, 143.2271406055666, 122.59841453091269, 86.96173338131545, 266.53209773468546, 73.73687009479511, 8.212528163992133, 9.206774440173959, 195.9405204095618, 21.131778217990703, 83.10432478559322, 131.1066188732911, 67.50526172863114, 83.51416379444564, 66.39439589267295, 135.50353600032673, 93.56576456333674, 59.33056250961301, 76.13766832891812, 15.864627695262001, 88.65394513226161, 75.00672680924622, 89.97749300526641, 66.97739053910567, 139.2934015892345, 61.2865320888394, 219.86201658309432, 42.89570132001614, 48.25439231705021, 83.38731627006241, 40.84420096015966, 59.45878183420771, 91.83718796581596, 84.58847184732664, 44.29431010598783, 150.46491840525456, 88.025330913024, 88.62399651003172, 82.22070036081908, 96.89435567358434, 57.49554430202047, 87.31812044171473, 61.88110887581332, 48.46515661795415, 105.72766849170661, 106.30089416624628, 55.45006822412377, 42.408001556587394, 56.605323057956475, 58.72560290345706, 9.441114489768307, 152.64539307036634, 7.737132099013379, 20.14659617976237, 175.39942920440967, 55.81307702389008, 63.40767924387426, 74.48021666693988, 81.21328959777999, 82.07597100186952, 12.057080633916234, 169.8475916143839, 81.3429789095939, 53.38702013308222, 235.06831200790745, 74.62961640174746, 65.65121165434064, 9.130213203062269, 52.198662467485185, 47.537183819512244, 186.90359957528793, 110.79649522124174, 61.06246215156533, 54.29730297945727, 76.95603982196286, 50.90522835821969, 101.86362839026783, 127.76182426669303, 97.54759147811279, 66.65985211143179, 14.21075842042783, 55.73882956979306, 58.66371880238056, 51.375630110389025, 108.2780671317362, 89.9496270305238, 69.71627340789843, 18.17687617091834, 113.58721888928577, 72.75754181503545, 115.21984513640606, 69.44260121195282, 10.88209285612173, 64.08136052880111, 10.240338653993279, 127.5483859831348, 87.21787428521147, 52.03808518179578, 83.00603762724575, 50.53449636500257, 82.569906899692, 63.73204919557044, 53.72501459220624, 69.63527816714549, 34.915252778801616, 63.5705574147226, 55.51646750896433, 60.25040508491689, 39.88545683529349, 8.176204104787399, 64.33920283338962, 43.97942573877519, 49.35390604865415, 51.34561208842463, 61.32639884182064, 54.735727772718846, 116.02275135935565, 157.94635782597734, 10.969944520915057, 96.83852819712325, 11.655839779601378, 166.26178644468325, 228.38794345033568, 191.85827361151294, 51.1843958360235, 299.7071432681201, 87.843214419776, 143.29814252950717, 43.886542770599966, 119.55464633208352, 111.2294664076869, 82.42463821115996, 122.11357140700203, 63.380683782264086, 52.15942844222911, 68.79856076326116, 76.96770140247693, 80.12254128673021, 94.89817959009467, 106.06028886572875, 41.36611112270429, 54.961101236836775, 127.83702986710831, 92.2023422336688, 69.72033669771376, 128.62029998589577, 140.43562798165334, 145.603294116932, 10.893725291625106, 73.1977374654968, 60.77239958013562, 239.11105899811534, 126.21411931407152, 47.084111575795596, 155.99303432330572, 71.82830213857872, 77.2405348722129, 69.97824914729371, 53.257201245633766, 8.419132701233892, 247.32328794139468, 81.69409244103255, 134.54253544539569, 88.41132357521386, 72.92419718814895, 94.56377065878513, 282.9763188879357, 58.96825043767087, 110.37057139230495, 115.24820326554207, 158.60402874029413, 165.5794885898939, 64.44030853271876, 64.34986562738321, 89.05027757701909, 257.7141981800816, 89.8015833437852, 96.95782072495851, 55.3356596501573, 258.3960155041845, 68.06356650100165, 53.13881352682488, 153.0478727666543, 59.31367810002138, 34.19319276506988, 89.70214303136426, 53.29815311751227, 133.0319669890126, 70.57815135867561, 9.256355897304449, 66.12026853112273, 82.24616136572358, 175.11777328976447, 136.21849805237198, 10.95461853708641, 57.789479905810744, 58.61956788063746, 99.9777287361195, 108.76926065380705, 20.94777071791046, 38.019930527461014, 6.042752737898616, 134.6476304266135, 78.04807160279337, 57.862568276448144, 34.9108041497996, 81.82654976094035, 74.35685950111908, 44.039698095625944, 55.34990161082187, 138.02256706673305, 158.889729349368, 84.02777711130715, 82.090035043156, 238.0383815110762, 32.979844598503924, 114.09948490676096, 141.58355573728593, 230.74716667358126, 44.83865568120578, 44.398257766330815, 70.76533361922952, 87.60578851781192, 96.78014098573507, 106.90910406911212, 87.73040248527042, 68.24720259431952, 45.6861601300642, 107.54673496388703, 113.8826278679084, 168.24831830864608, 82.75387382681097, 86.86733053709004, 47.56525405122757, 113.64568206538465, 150.31821778712228, 59.63265630125302, 159.7081572380414, 121.60442796799427, 22.297271962492317, 344.80565496566646, 74.91789041515013, 51.59682724720124, 61.88778817131719, 53.7183917623735, 63.64217696335336, 45.11834901091583, 88.29123948584514, 60.238312473334155, 55.437458010919386, 103.41650026173727, 47.13004885689332, 106.02249066099088, 62.24365624487176, 67.87795806060893, 146.4118443915293, 68.7271156612499, 129.9027132610728, 119.10460758445748, 62.22572399793678, 54.13573380368444, 105.26274402271281, 89.29753688314497, 63.71091902477687, 132.7660293330208, 104.66199656018378, 48.95169171537682, 220.66634347386596, 89.53911041518589, 69.65849976685831, 37.97897664287434, 111.24470393020923, 84.06552171371793, 279.7457394922424, 55.847783195612045, 84.06019803542587, 184.48218159264232, 75.9141653160831, 137.2504189672839, 44.484866777791304, 52.44121276874545, 204.00460648806308, 133.60247041716178, 235.59482968563864, 250.5249426221009, 49.71725683671387, 46.75998872527983, 106.38048562802511, 116.06813793947894, 79.32731933531555, 83.49165580772483, 148.65149264962452, 39.80370237948734, 77.33574737546469, 85.73084829801367, 58.81684554874907, 65.18966763334252, 49.226895749168165, 115.53656472885079, 39.64540194701561, 8.1017568928936, 216.42968476260683, 96.4386961803385, 124.08087978193208, 206.26157868112767, 146.69010717305662, 88.75750250494679, 92.83428969928497, 109.26392148434849, 51.168639782121346, 82.18380053842122, 7.040627565849244, 76.49961986712545, 93.29272879110447, 51.48494517223675, 55.16573892364931, 56.023369335584775, 82.7563219074962, 30.736559287884653, 80.03040905720748, 154.63824249150414, 111.23953809685058, 51.51523165888466, 87.02497489018177, 88.96952760641852, 74.96091515267331, 89.9060804812184, 159.6384081293692, 82.67219900043123, 222.86721507829915, 61.53591260177493, 89.26664277673794, 123.55328603237986, 88.24651561911669, 83.31247485909626, 154.0321944917687, 106.50209814826977, 291.8233925054524, 37.89434571734186, 8.304638541773324, 33.4387433242469, 84.7082914870607, 115.71285391556242, 45.99112383053575, 64.80448524486464, 120.13562105048469, 35.67170295066112, 98.66073329845725, 149.04621566110572, 75.15630021926984, 46.18956935657616, 16.97042305799619, 52.60935880152461, 53.62618944416967, 90.07272726307886, 43.82869733183217, 78.10980779427778, 182.64004667767492, 93.53079819783731, 73.15788057147728, 77.6832795212729, 110.26869830431387, 134.91916670314137, 156.23584459864276, 85.86170763121179, 84.16494424008218, 263.0310147201822, 62.174519050639994, 185.8097539064144, 303.5004987289061, 45.027644984636346, 76.30238280690578, 41.40140976976335, 85.63947342086333, 83.2798851024647, 140.00207410818794, 14.186933035734745, 130.53824342611918, 55.44765757420375, 78.61328838773781, 78.17779761688206, 168.30532207564056, 42.927560176225, 54.48864218663334, 88.83569778714342, 91.14145741897316, 96.08690848701164, 60.22536726617521, 105.35507024728318, 90.4785864423483, 87.65254775164179, 85.97088630746104, 86.42273713440711, 71.22547234893013, 6.4240194052134125, 64.65685103145628, 1</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>113.8439700126648</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>85.93263814105489</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>[131.1273193359375, 159.8739013671875, 53.8621940612793, 235.9087677001953, 64.7526626586914, 251.1658172607422, 34.32735824584961, 117.17913055419922, 196.92556762695312, 87.9483413696289, 66.1889419555664, 58.8765983581543, 92.92533874511719, 85.4333724975586, 203.15487670898438, 128.6514434814453, 305.6389465332031, 15.303524017333984, 42.07221603393555, 128.96324157714844, 68.47811126708984, 57.973331451416016, 60.72064208984375, 66.20027923583984, 42.52860641479492, 92.3326416015625, 269.312255859375, 65.00688171386719, 150.49070739746094, 76.4128189086914, 161.64503479003906, 52.43532943725586, 217.71734619140625, 140.57579040527344, 90.18891143798828, 70.75931549072266, 73.18345642089844, 61.698062896728516, 98.36180877685547, 268.28814697265625, 40.58183288574219, 45.912357330322266, 56.809242248535156, 91.04740905761719, 53.956573486328125, 227.75167846679688, 85.51327514648438, 149.87347412109375, 57.82942199707031, 67.59243774414062, 64.07459259033203, 132.88648986816406, 11.014800071716309, 150.6859130859375, 57.50522994995117, 135.78538513183594, 81.98585510253906, 10.816911697387695, 170.21725463867188, 133.05874633789062, 361.9944763183594, 243.71127319335938, 143.30062866210938, 11.030903816223145, 107.97257995605469, 60.81235885620117, 69.55463409423828, 115.27265930175781, 72.24052429199219, 236.35528564453125, 194.07070922851562, 58.281158447265625, 165.8627166748047, 58.16909408569336, 39.30946350097656, 42.78050231933594, 215.6039276123047, 123.48377990722656, 63.22472381591797, 111.35980987548828, 116.09622192382812, 91.84227752685547, 59.94511032104492, 57.224910736083984, 71.99778747558594, 65.28129577636719, 112.41278076171875, 617.7435913085938, 154.9647216796875, 168.9499969482422, 94.31657409667969, 58.899497985839844, 77.41222381591797, 59.789222717285156, 51.258235931396484, 188.31649780273438, 108.47403717041016, 32.06501007080078, 56.33781433105469, 177.1900634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011114</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:01:15</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>94.36378894860748</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>72.02819315872968</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>107.4394493439449</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>4649</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>[0.5593928594473803, 0.8377584320219247, 0.5481224114243675, 1.4799697775225151, 0.6860865068866843, 0.9234697658362786, 0.6904323312362579, 1.0252285570028874, 0.5121248095825045, 1.294534483087024, 0.8022251231829429, 0.8315718313867451, 1.2224949122159092, 1.0677253455632678, 0.7021740327262852, 1.057410068714226, 1.1839253553834765, 0.9954800491303154, 1.7705111566721194, 0.28578275408282305, 1.7530659525431391, 1.4478403397703195, 0.6479654521761964, 0.5669309192022265, 1.7390356688435826, 0.9565302546814497, 0.5854298682613205, 2.3390313777286407, 1.2979110782804628, 1.3709666224008297, 1.6587281411081103, 1.409481988826891, 0.7292151744894043, 1.134102942387842, 1.3418957649983996, 1.1218106395382135, 0.9681294222461475, 0.4103429312237743, 1.9440957151605411, 1.8405107236555884, 1.5608796121159982, 2.761033769364436, 2.8500287224814125, 1.6231945723725432, 1.4818573365654308, 2.3611039195469323, 1.081301972714549, 1.3865870743396727, 1.3095998427646287, 0.9292561738259307, 0.9216063319214094, 1.7933067203086195, 1.4541657089838558, 1.5703008410504011, 0.8828395524164065, 0.988062984086226, 1.1570216384297687, 2.455360822090973, 2.0007930041377886, 1.1301419368512895, 1.3935980199615985, 1.8733923684303704, 1.2771729812426693, 2.045809099625938, 1.0842778517320166, 0.9141578700984659, 2.7606124746669662, 1.7152898407703459, 2.1648390621407874, 2.4470591440475205, 2.3937178364546816, 1.163322899496014, 1.806354057051153, 1.0465602137059966, 3.5777118426791668, 1.8108233969630412, 0.9571572694191622, 1.369411449715064, 2.6974157821974862, 3.341657812098555, 2.2270725172607464, 2.188344584616844, 2.948573632910304, 3.0905365835307617, 2.770036755308953, 2.8862551749262364, 3.2990656293518903, 1.7579948226172186, 2.590436568098488, 3.745727866046198, 2.897775591713577, 0.5528258782340025, 0.8836525929739467, 1.7116304093965151, 2.7343089354507133, 2.112877606091999, 4.093761694596267, 1.909505695751853, 0.4252517739213097, 3.6698102791196776, 3.882148910897328, 3.1718744189118033, 2.0871729661405256, 2.13449807945303, 0.21422254118138853, 2.3763058639553534, 1.8651602063746335, 8.04742915104841, 3.730323521534892, 1.2954767220389078, 2.395710383536897, 2.49818350237743, 2.52384608481351, 2.0639674793165326, 3.947112302574891, 2.1230941628788136, 5.076101645207021, 5.601252940805313, 5.709340660442018, 4.1966983184283055, 3.6267187339384375, 2.4076680037340012, 7.499760245635045, 7.300116551192757, 3.8046570157813235, 7.9488371978998345, 4.884991925274007, 3.9632297261565346, 4.776527709995742, 0.5461690453630073, 2.5539911200766827, 5.7307503263957145, 3.9343536119911597, 7.162215078370556, 3.2179050255696353, 2.5412353474131884, 3.8605868639894427, 3.3113541516264138, 0.9689528752675056, 0.5561707336339422, 3.2344984774269054, 4.857003543885353, 6.3260285797046665, 3.761489651009, 3.3244330539393045, 1.4824921332974483, 5.216702733581211, 5.740817045488021, 6.808842854335159, 5.735268110845921, 3.261142019152429, 4.121472256875344, 11.549945492933537, 3.751963125430804, 5.5612562034286395, 4.21318056559775, 7.346205423933364, 1.3373403401480959, 5.8094258183711105, 1.2641610675350985, 12.03734756207365, 12.345009066308027, 10.607497866495684, 13.918877894724831, 6.607015306947218, 15.487608684403115, 6.301109998537787, 3.0119341468184917, 6.289240817098955, 26.548530547150545, 27.208892220158397, 5.790046059528196, 8.704048400809903, 10.122135419177415, 7.023089973320623, 7.508516789690195, 6.707402927357881, 5.6040920717190374, 7.770274139269779, 4.670171574033665, 9.14307052629335, 18.269833279616915, 8.342222505353362, 9.239660908064398, 9.126566815107779, 10.427502553567795, 6.665013837165076, 6.376499886487167, 12.0425681281614, 6.444123449574358, 7.823871876383411, 9.627160024070193, 10.99676173629789, 14.792651688203607, 10.901287219698183, 15.153862713800345, 33.133904786475426, 15.267101830689136, 9.236896201860585, 22.62181161264411, 4.107911856388177, 5.407633157649413, 17.241512296154458, 6.502999194853635, 21.27169259442148, 16.17324834515278, 12.252073131349404, 13.191800260559406, 16.820828608810007, 24.335604191834754, 19.577765422163775, 14.001318431836758, 9.693384941328969, 13.319802771407028, 17.32149567894997, 22.57608936832911, 18.829922618393063, 23.670045338965192, 11.513548393119187, 17.426526419814824, 13.411322766839445, 14.92503787883495, 28.379576999507783, 20.405227254762842, 7.340199729944062, 18.97529127168911, 14.82559789997305, 15.069199671799815, 15.98393427643322, 31.526793128896877, 25.49610934134142, 22.49760960500622, 16.107961961418987, 19.291785322973826, 17.123896930718164, 24.568377057197477, 40.6647257254576, 14.812833788725015, 10.252208892272781, 33.16982552341275, 22.461071378557598, 9.326738392333796, 30.142440918379943, 26.49101703942359, 12.315822373746165, 15.863507290029656, 36.380262453606456, 40.48453869228853, 51.07696031600444, 24.49143988858068, 12.112958687706715, 30.080900375297492, 14.295632570371046, 15.599292094831066, 58.827415098431054, 30.779217220487084, 20.307060877856934, 12.505067572679042, 22.356096336218776, 19.315220841272446, 28.509249681815405, 26.758902524471218, 14.58606307975019, 36.95962078829831, 32.54980178419886, 30.84819757357263, 28.10936587065456, 37.55116323388504, 35.023342618952846, 24.3909776386685, 36.142639291256735, 17.173922303802943, 34.62923370736157, 19.959298658336404, 33.92637544417685, 24.32033203579248, 30.76592336184562, 34.02628003892929, 26.314602455543177, 29.58170496620814, 17.305096289648098, 33.87302457102107, 45.84778801421854, 50.160558219740366, 55.4426684868966, 36.78686284405768, 33.97814633074456, 27.64373257613634, 32.2451245064228, 24.204725502225056, 22.810077615679152, 20.596090810189096, 18.123380290413287, 46.44708816172754, 43.00381650692864, 20.02676212233301, 60.45630909475917, 37.12764349830556, 17.012610377761717, 19.15155703417394, 47.15252339760139, 40.02320352668123, 55.26619653412348, 12.047039181319798, 36.90058380293845, 19.072662675222745, 47.09994106820789, 21.945970071806546, 29.65658276727272, 50.918224866890526, 31.106857777867116, 70.9793626127233, 72.01219078570344, 22.874938877601316, 19.24521389106425, 26.2323906449761, 47.94823211883113, 32.199671892996975, 33.28153938658529, 42.75910212356937, 33.671628424775655, 59.20174801405003, 36.79458943596506, 25.50241402689403, 3.57917311115218, 4.811060939845515, 17.231410586798255, 47.028092407507565, 26.26551079467007, 43.627983167322526, 29.796160266384742, 36.39424924355309, 48.435686301838516, 22.825059285266036, 34.58872290114102, 13.473062127086878, 34.13316705647834, 13.469809782446614, 40.10719386062958, 60.182174108180796, 56.72964851562656, 45.61472565951744, 27.342844916080537, 42.13074780711737, 27.02045211365149, 35.457963507825724, 12.061671836723896, 55.83797221278704, 30.228076957926955, 58.003937284234595, 57.99169723634299, 54.16401357064338, 27.269391692990595, 61.32916988353125, 52.572805682463986, 43.827192561086264, 40.19024874710936, 68.85946908500058, 62.48487001567787, 55.9643018872769, 22.67982406852031, 96.25823045187894, 47.5075493937562, 5.497704765144128, 48.70165923216506, 31.262050552652003, 35.09953818007401, 30.544861982602534, 54.660697063989396, 70.26947555065935, 79.07725249053867, 42.64657041862207, 46.753244765652745, 9.166800825559754, 30.50259908901214, 56.28078278669252, 58.18355173135923, 57.567935324667275, 74.436830641445, 10.157839433877866, 35.26075502804372, 47.487671078848116, 34.500706241397715, 30.151752784748076, 36.967826496790245, 40.859319130322916, 56.596327383861436, 57.051667647254305, 51.2480357487414, 47.6433221894279, 35.39916272854885, 23.403180057058382, 33.306587711426445, 8.43334696347962, 46.35859071493528, 69.02334892683706, 95.3972324403964, 77.07411175671488, 40.66533365106739, 31.189365448246935, 44.65107050327879, 36.92043939944197, 57.005886960392495, 30.59197853185343, 56.278629660127095, 36.30571737757291, 55.9210168316898, 41.25167522959708, 40.48728551591284, 40.13963858170258, 61.6161926065491, 78.30165633859879, 29.412090054297956, 34.80496274519896, 64.54415859052116, 28.262208953656195, 51.47149354646415, 54.06422689398948, 42.92027159908177, 100.6282127866745, 34.70950116063325, 32.926285751660366, 32.00995453671158, 50.381533767641315, 74.41897836375914, 78.56019806863256, 7.405343117957476, 49.35812992815814, 83.05003859607052, 35.484874257252464, 39.10673324030068, 89.62829066351023, 21.262642327995145, 70.93355586003267, 47.54094005238035, 33.36993837325253, 39.829553614968944, 66.22300130303745, 52.49877796816629, 43.57860773495016, 53.48646114162004, 38.41807192345978, 53.78318882565257, 58.316320669979675, 88.90666647415837, 39.04053509262862, 89.28649772247867, 40.599590009350315, 47.14287730194694, 47.507360272333365, 38.62539366558553, 108.14377075707533, 48.678732986931706, 37.932726646628126, 36.32852175335756, 49.79945425942425, 81.49192352699838, 36.206839894824355, 57.44082525991433, 16.58183754646868, 41.92229867700044, 29.344890920038726, 51.69227179602034, 51.03926372336999, 65.46726513127119, 80.21210041534255, 46.33680415006001, 50.010672412589344, 67.52755932090186, 128.00321221892239, 35.848175337785776, 8.832418106756595, 32.907121377652956, 85.66810709247191, 53.30699049778104, 47.108492148719314, 44.157967454896685, 44.09099826374871, 44.74782426890717, 57.31349984263722, 104.22327624869989, 39.78590357819059, 62.20471154540834, 30.252317860405146, 43.40220235805311, 105.30322791089148, 36.82091057686513, 80.22086998203635, 61.30960600205318, 71.39671143468026, 49.999527007107474, 52.53222677390009, 74.08002378286533, 80.65429396813059, 30.30231427439194, 56.84180548740587, 76.66838584885679, 94.72445495091976, 39.88818151056528, 37.70425053384478, 82.44717037477884, 58.36938702240794, 98.91789028082498, 114.59230332126302, 36.562350457266746, 57.49259734661548, 121.58262825858189, 54.48950070820173, 122.74521232579548, 7.991350892947934, 34.52203817127742, 65.31144359299422, 61.84842068600857, 82.75948888599024, 38.03676589999992, 44.45649691363216, 54.16523814846268, 63.379188790764495, 6.1279987744244595, 72.97989023243474, 51.60698215845345, 86.0371313023945, 71.09911717848682, 47.74379123904311, 63.98042955608753, 40.43750913709425, 55.47889827332827, 89.70118306544478, 67.37818793493929, 69.42814066207289, 144.32080601273645, 62.45756154560318, 67.38023554102936, 43.3629215413971, 42.21553956146228, 44.79241624227164, 6.561833824828019, 67.57424456077763, 68.76521531852262, 46.74121504076399, 143.97077713249936, 39.88291150665472, 39.6847807439083, 93.00722966705267, 40.38929760429531, 72.95816447671963, 67.59707503525894, 44.47578395887114, 46.13732981424607, 62.32771556612925, 84.75259492791372, 71.47435473227728, 36.773207043595114, 39.75452276717378, 61.54295175787368, 54.260064551668336, 89.84800408717258, 50.38833522340227, 122.31513446692914, 124.03286539957179, 82.66033924869808, 64.04643510845906, 56.33688217306104, 46.13927486614306, 66.97892965387285, 39.03480576030911, 66.61249808628743, 61.85888744967701, 57.55535151718401, 102.64034963518822, 47.47291836763194, 39.03945118157787, 61.86884462511207, 76.20226933653365, 129.04847473151153, 51.36079523410359, 66.36434849409748, 122.70168133957243, 198.17382543366196, 102.42407341868201, 50.020939083643896, 88.9994633518913, 87.96849166339797, 77.64323859073455, 58.16614309328062, 148.75904282524561, 40.97923559860616, 37.09084018768772, 54.801456791395225, 60.64282860852707, 94.7428613284849, 46.910755757961, 76.53667722343623, 44.33697210862697, 86.18984029000826, 90.53246305737561, 43.162120156104244, 32.80951356284716, 43.13401757276976, 103.09895828952766, 73.8623998701288, 18.79056075937947, 136.33667940108936, 60.45336927683228, 69.0512460090121, 61.37619299689628, 44.087763741301494, 118.06481517209211, 59.01572062025618, 103.03482625508667, 45.76548279411061, 75.87202739000503, 126.99833111942394, 59.93029790278257, 45.73592077440889, 40.195762147062226, 74.08935456440737, 76.38657215537866, 51.07611266820944, 35.360371061924816, 87.93839466679965, 72.27232015187954, 117.01474588774072, 56.40703000141383, 17.762739017750118, 6.622124567667397, 53.21012876561472, 6.407046225922824, 97.06075040809083, 79.94467800017902, 48.14907020626924, 94.65345884015915, 151.62758414337048, 50.53342209144357, 80.1380109859605, 115.5031530685512, 4.506198002162844, 82.29544532165511, 56.408891821290126, 53.71465023315161, 184.7370282663886, 84.9093639979926, 50.3813675459335, 6.231807594691271, 48.80935285860164, 41.54510264954796, 51.351200513215616, 45.2307940179415, 120.15316858463643, 56.638969172310496, 66.57015010445895, 40.083031730756666, 51.030760950515294, 54.943390501411365, 47.715070134154075, 72.38741230030969, 90.69151815789385, 49.621559197841016, 85.78190528603655, 41.53528575167858, 63.885504494333404, 41.719475978612394, 80.44638307020102, 95.00961751531614, 112.04598213189692, 88.95807974129866, 54.133863167841845, 67.36964201709281, 58.88044247750256, 58.13227426767875, 9.053380462845503, 61.248362641461895, 166.21281617858725, 90.74429762607441, 95.32616522863088, 12.23338220730929, 130.91097750056596, 43.254211864970095, 146.5621756645887, 79.92330133351862, 36.690480048484154, 97.01721540352271, 34.58939687088085, 40.29009147680612, 51.622720548493, 42.151602174642655, 143.3707621425547, 41.951388919562255, 9.104889917296541, 50.38924217694562, 51.148179600294775, 43.174101271852635, 96.87338237964106, 95.00854696518716, 57.64808556548144, 157.05795608287363, 62.741320029229136, 59.750485303268995, 42.59357676177898, 95.85453811078573, 48.29685713732095, 153.5388542391023, 185.42394752848196, 37.67347480875331, 90.06301514711375, 47.0338420367295, 59.89182487169569, 67.14586126685532, 50.30396795194099, 58.001236275706766, 72.24892074093063, 82.35769466687024, 63.267725498593414, 59.94921327598862, 65.45565310424539, 79.79355122040954, 60.17106010407278, 32.89301830572835, 180.70277038326807, 41.4324384132393, 62.11393870058809, 55.90137160342444, 141.347508502293, 44.61311739119551, 58.31759435142977, 50.9002908226074, 64.85058169324144, 60.527913783472655, 65.05062953298493, 60.565248382760636, 101.6382703363844, 81.48924934199401, 160.46622340344328, 43.33881647656738, 51.11744687578972, 59.56132549292093, 64.89879402325097, 55.507515252181825, 45.120844414299725, 64.11922196012408, 56.43142748203569, 47.132309884903265, 126.4492656437078, 59.54141371953357, 99.18847959770557, 66.46001016090683, 43.61246523009384, 168.8745922787889, 62.995241489050244, 39.90797446728028, 101.53831829694751, 51.74024072749158, 70.12694246835788, 134.85511228986687, 42.99225439397958, 124.15751092851325, 99.56844511677144, 60.4156669230332, 56.4205316551407, 58.874373127858966, 56.760352763680544, 69.88212196665663, 51.08355430277363, 76.97398930096746, 105.41235246159911, 56.718951727954256, 31.36418082252326, 49.29464527594878, 48.19066537908368, 95.01240117861961, 71.9739999734885, 58.172911839743, 72.30831248477324, 81.67787079243291, 88.79036824756005, 64.68281539888697, 72.7026726558444, 74.47191333862241, 64.26190106363512, 100.58148995660949, 135.91494502447247, 101.77517848033247, 44.685729284492695, 64.83165438631556, 156.74995835950457, 90.16708996112612, 55.63063463707331, 90.83150631472647, 158.04674121653224, 41.195572055594695, 173.07083887370794, 107.14883279520899, 99.87711430555001, 112.98628961302498, 121.24599433086918, 135.68957777047024, 50.66137224330474, 51.44802381584007, 99.53044256767252, 70.86839785794801, 53.13902792607676, 54.92476416024361, 100.25936766727723, 177.13183898811684, 76.42307849467682, 46.08199997511524, 57.89126930284207, 366.69881911553443, 59.15798007282414, 53.28277750447563, 61.53150594585894, 62.87413394546832, 71.2985283868599, 85.01919848501277, 58.89419319137651, 140.44777699958, 89.01315924243501, 62.198464398448316, 77.85676243863966, 43.06672620652253, 82.77638866131888, 84.91916704381303, 49.90392823339601, 57.52790492072448, 66.69825950265431, 163.68143147648487, 88.44819944004759, 86.29923635793865, 67.62139258722749, 51.49180053176514, 174.4929736721369, 36.97574317313653, 171.83581327115985, 72.8481549977045, 63.42064536721198, 114.29245403135154, 97.89429212612349, 95.78572917844389, 128.87716049594093, 77.54260820105023, 76.78033411636073, 67.06923351540956, 78.56232559753482, 78.98935655763474, 49.92902651360042, 78.99969788225268, 60.366910907001206, 52.27976424059513, 31.672330389245158, 58.57011163890358, 45.251250826992006, 81.15136273433798, 146.92758210658218, 112.59086849940108, 72.41313491324178, 9.483933142357955, 146.03753125727394, 101.01833391593397, 39.91099067228846, 101.97504667300318, 70.84263385566204, 76.89088943727555, 65.15290515005951, 70.55825941351038, 92.45182155743261, 112.03630439184316, 55.08216729948272, 60.534889394675155, 8.586995646930495, 113.59085089365828, 118.93724110156957, 100.7510468751115, 47.70683278933842, 9.875414303370643, 79.810915976953, 66.3112021497828, 86.1920864580287, 123.87851269895533, 20.904585889404544, 52.70350052495059, 58.26070793352122, 96.66414752088657, 56.13455332398173, 49.7107355901724, 157.92168911114135, 167.76900069744005, 199.530505309804, 46.5519733465075, 201.78689202356315, 91.15313031581157, 96.41123608010346, 70.04444659297745, 96.78282198123541, 139.64063205719253, 69.99698880258808, 47.47907526048151, 82.37089114891145, 9.555572181374043, 100.27300393206208, 63.64802868455921, 49.83184174338621, 40.88516196529351, 50.78728122282097, 50.56532785289572, 107.30474784138038, 40.42267583807906, 89.33996479088117, 292.4608787877313, 42.716330697218574, 81.20195602224695, 113.0462922448831, 60.57646976880558, 102.25604980644269, 32.14061867698388, 108.0544747309229, 104.93495078843726, 36.9907192735648, 153.08252121641422, 56.24782781509118, 84.8114844153668, 45.53497301695993, 81.74074728294774, 55.43380145397152, 66.55556169556522, 102.3436745496326, 136.820362363048, 49.94439175117455, 110.03733888285656, 104.0700408397802, 71.84929983157394, 87.90112869967697, 81.52234586595563, 65.80283167576363, 115.30742351303647, 52.615687806403514, 55.55116630029367, 46.53820756276423, 71.1984219170086, 155.446196433902, 62.281278994688805, 70.95774054209626, 105.03524104780277, 56.825365287861594, 48.55316118034426, 51.60420824999666, 113.13735216128973, 72.73505607355119, 58.14825662732255, 368.4385086969834, 67.97190507189202, 87.02232965812254, 69.40990293902507, 147.13849852862103, 142.31148698517427, 95.73364788145399, 76.6139521012603, 81.60928120159986, 109.48034067803135, 65.79862600343111, 11.865112406189894, 74.10945718395182, 116.86727226730146, 139.78766700578245, 95.14082756375765, 90.02441152745274, 203.3488374111099, 117.95427521793621, 182.0121350031511, 86.70083441331823, 45.10378700095693, 69.91307289496262, 125.6698484149401, 43.28061503050544, 56.487730752278516, 70.55200725235858, 83.54887527722573, 52.40110040813648, 327.5746765126653, 81.40199390515127, 131.32624021479066, 91.6506388612867, 130.64336518480346, 72.57398830507837, 57.5403291213786, 157.82900452187693, 79.33228553213017, 52.336898092077725, 84.89876352930585, 40.04292851607245, 54.46423802037187, 58.95557635613278, 25.763568977225727, 25.521473440557582, 78.28673455870371, 84.44174701907684, 69.42717520658148, 119.35550904675094, 62.64342050743244, 232.48557698462017, 87.02698811022557, 61.155808529588846, 98.22771637555584, 58.04768078812448, 103.67114649981268, 70.71105042541183, 55.55891304354257, 183.08730267703598, 252.86642146330544, 73.0140933724986, 49.66651305464309, 67.22204462140505, 42.7967983914051, 135.01392505821656, 64.27372348373947, 143.20642026632603, 117.24633282714788, 81.43777025110563, 75.76865120444262, 78.45928637923878, 118.07156560449327, 71.88709311004723, 97.02573314772823, 94.17879215646545, 31.40184015509972, 106.46307755277537, 69.72292792703288, 55.59249629449204, 97.11052770420915, 193.97456017608746, 69.91145275366006, 91.26026538552749, 207.75962960665507, 95.39673442010421, 58.790278757660964, 94.38642192282026, 69.32366539913879, 74.3360686478227, 67.25957126211182, 64.19704798362979, 76.11768129431465, 280.5626933640958, 57.33829131918043, 112.31222653572075, 60.27201586872511, 51.85406158117737, 402.18864674706356, 67.27948260831599, 55.04512274649531, 102.45971066255622, 104.71327695997766, 140.38163395372584, 31.530896749020876, 91.10897453423944, 48.197145721705716, 69.32089552127381, 46.13688403041679, 52.246978086658395, 194.6575406133101, 61.832027914971086, 40.09121952371316, 137.96501793803375, 90.24727159077774, 108.80758790573334, 111.27400447207073, 49.04959224554648, 151.40700983920996, 14.742657339310199, 94.17150267926301, 5.7803064960036785, 44.11683782666343, 167.2259537996724, 78.31415278999924, 68.66881331213585, 98.91388775849039, 92.32065636132113, 73.45442774168183, 52.225583766604004, 82.87223765002268, 69.83804808328543, 49.22401464181155, 96.73669310718208, 24.771409073520847, 57.35723682870113, 53.91920981325512, 88.20023708203323, 93.5921607670472, 41.02559379686511, 54.151300225679336, 109.61226168374448, 91.22318557866872, 50.173056369926485, 65.96304552441242, 62.86674054892286, 87.6109382745142, 455.36219025683977, 86.77247535270439, 76.59990177952537, 49.293209367184225, 117.11867175229229, 115.96782989288549, 6.713504671579624, 84.44560465926654, 93.4792114094434, 98.59283093490585, 57.4909990358139, 190.81370819945133, 62.745987089222425, 106.86457361490531, 59.505231846489764, 46.081824364399175, 120.53138918402679, 71.75568247317152, 43.93825916403941, 79.29915346395697, 70.62305038162795, 37.565218734792715, 116.79846591679693, 96.85933111121251, 58.48548897033958, 58.8221724532072, 71.93261120736564, 18.712920517904326, 46.19827371160973, 118.98296381115105, 84.14275858637001, 107.18392583194144, 95.85204417913735, 80.78205154728984, 27.88572443928969, 123.03097958899909, 55.46484668919673, 118.72867362005509, 202.41092660206357, 40.48550329819738, 105.86982078726946, 85.0033361795228, 38.19711554374772, 72.48757686964053, 33.340051446075805, 71.20568391329233, 60.057528321139635, 67.99780684275093, 95.4038381548705, 184.36226387439328, 53.416927451576406, 63.569905518804006, 90.56734981915677, 137.26814456727453, 180.21309557704222, 103.22534025293393, 150.8276105853041, 101.93632810319284, 90.4162986008637, 59.340170561081855, 96.46921717862452, 116.06781032327319, 159.6184082805981, 227.7554552344658, 165.3325159762509, 47.00402639702835, 108.06848366211041, 70.19886716687728, 83.30632273009718, 184.38932649658062, 56.11100903532078, 100.5442704500193, 58.221160330325176, 56.81280886095787, 95.77186231176665, 80.89676740879074, 352.92461854860363, 75.82201454346594, 118.17824948352614, 138.20453197646668, 126.94279749307714, 57.793311747890556, 49.91648883706886, 134.23698990311357, 49.50728913491155, 104.8621034714529, 82.45352405691055, 83.92193610491532, 65.40461632209309, 54.03533125886656, 93.07600796074559, 144.04672086221814, 91.8039224655291, 53.8612944377344, 38.004152946481106, 62.76567291061267, 80.17278129189319, 19.00635201492828, 48.525552888439336, 84.53024133596314, 124.075973771031, 145.9471294340891, 176.39767153618106, 95.44818756895926, 51.23853752546033, 118.74280473380877, 46.908168163126085, 46.16805339380002, 48.65265291197301, 68.23273103159283, 118.99713227737348, 46.04362558591708, 94.96002138649393, 93.5438321345025, 119.56842196951452, 70.07762458528181, 84.10873767796447, 79.56199680697648, 48.7649008910046, 51.703491769490896, 64.59565272837767, 72.52598762510517, 117.2053289794875, 170.51539339086773, 117.5153569729229, 61.89797095007537, 163.95442529256582, 95.89427649287165, 71.96101915721948, 217.12861245922687, 119.57856671324129, 104.04180046599367, 56.98449877801743, 103.65850195199901, 60.78815896852609, 68.86277537386303, 86.45606655843561, 139.64637913092884, 108.08318466845223, 138.32160413607733, 78.56712053705462, 69.48272544394904, 63.18993277881667, 138.12436885839665, 87.58453029383348, 219.7616026645542, 141.42933669735552, 95.58764677037308, 83.84590074924898, 73.54773686837093, 63.06646410033026, 100.01303308255623, 52.03421084978132, 94.96608650960138, 47.685322267581185, 106.26059741196445, 61.007926018582936, 80.6292534312543, 57.93102031598496, 71.31032388739372, 177.38023417821793, 107.1022561964184, 61.10621919228142, 54.7386263433254, 52.21469700549059, 105.49701752600292, 130.95651091493633, 76.74481431430473, 100.45608067922726, 97.80871565966726, 46.83123522905903, 61.92860122809463, 99.49542233842658, 83.94675710935266, 13.772515361249422, 53.66513464568569, 96.75447882175138, 85.40627654058588, 70.47335112725835, 52.3680145921935, 62.18747166295668, 34.02661687869216, 71.69842123115343, 88.99120239552252, 73.0307573229645, 93.91441502750483, 61.13771193979099, 60.5037084040388, 38.51629321298127, 284.62870338986846, 118.07775959166742, 54.04545271431558, 54.174661475533725, 97.23947430094698, 72.13166866462431, 55.120764185311266, 157.6263626320068, 68.20566622727465, 61.31821730208905, 92.05043502501195, 54.464991614433615, 71.91855306908154, 65.26220281171193, 12.307020539503599, 12.571840483485772, 112.76393382205055, 68.76098765675214, 75.51755508548621, 59.0984336749396, 56.74966148178304, 41.299281206947214, 50.58491691415881, 48.39895884563043, 79.72823080234211, 47.790842937685966, 61.69986361716486, 129.15639642831658, 64.11348731497264, 99.9491853912856, 61.44848407854897, 83.6599611178953, 108.3079122556091, 119.90532371455105, 101.00457124249826, 56.41779442180179, 30.61872700220769, 77.92930872596963, 81.27900359857982, 131.3060797719452, 93.72781506951742, 39.365461657251345, 109.43007996604732, 70.76299435638535, 63.3739019651939, 67.54731195554248, 36.7898291268823, 56.57713246901688, 83.16293982849803, 84.33223786103619, 56.62308104519554, 46.16726936046406, 66.44978376502105, 48.33870205450455, 51.93884412022757, 56.8762923129826, 60.4534721540344, 52.195813682224895, 53.452772280491274, 56.99742750447689, 34.55764303273155, 56.84395417248834, 62.84332913562872, 62.449025135009805, 39.641923055053006, 23.90013155354718, 16.02109960554886, 87.74104761397142, 72.47301488593499, 55.96729800355253, 36.92237778414553, 38.747520404076035, 66.72797582398334, 65.43880679803794, 62.96383958439558, 69.70993192341105, 65.1685473739963, 44.28917378062133, 114.21833147057092, 89.12591488997832, 67.40957653003933, 56.94139685334107, 57.72353675405397, 62.188615242805824, 40.887961829427596, 31.66753353098534, 43.51996132593446, 7.423873580765719, 203.62695004032625, 43.14211430596085, 220.59295220605034, 9.003422670513777, 65.77691121236495, 41.45110015347793, 78.85616891568432, 87.71251461885187, 146.8356109222713, 56.780039949156404, 78.63712403939358, 173.90544839097416, 38.448919246402845, 92.89538612930288, 80.81238237965412, 57.794950267848456, 230.26639028770083, 60.87805107107025, 80.58753206080527, 65.46422158814583, 70.02314063166946, 92.82231854259884, 73.65020837020447, 124.22596407416495, 9.560328770482787, 55.550729990830604, 46.630825284702965, 105.75495862099199, 127.20153712326953, 57.9182002053646, 14.276478871401286, 143.1003666042021, 61.845481667341964, 76.948831776648, 18.72353957732046, 54.93813495041013, 79.10818488966913, 53.55836216837174, 86.66962513671773, 119.34921341916935, 57.87224178697638, 7.059688589049489, 95.4275022812453, 69.55371977515344, 91.31340765246792, 136.93879664822933, 45.51611376116005, 42.77623797608619, 62.365714620836975, 85.30416219906417, 161.18015129095562, 311.6652037102099, 106.22771080793754, 167.17937850839132, 153.16857811141682, 105.78702606867579, 54.8466320157341, 58.1344539811718, 41.40660083627663, 61.49114867278779, 184.34117553685763, 35.279910448225586, 136.78209240270985, 128.51915231971736, 155.6329488623913, 165.7574579182346, 78.33050298776075, 163.00733253058692, 14.800755763334086, 115.39830117431957, 10.173336319395172, 121.98243806145085, 69.12669377400488, 135.31246410295898, 42.410200007907974, 107.63629119917788, 89.92152631943458, 369.8365446379886, 65.00630350657164, 61.249029275739545, 309.7410195348853, 108.09372887141254, 63.805413058059, 124.53571189360649, 66.47247396035236, 66.12491877759592, 228.4194195432955, 54.69373591057355, 41.40672773855947, 8.773274102341391, 62.14784016642048, 51.9305152901231, 38.18254004078765, 209.335758949238, 148.6232552667487, 68.91320933340802, 68.07272023173287, 86.25034975118187, 57.44089489658283, 231.9441908098746, 86.11332120616223, 87.95135811462771, 181.56437704659243, 33.6801329882624, 74.90896667820297, 84.75754707226484, 60.39538172399728, 246.68923462401196, 69.74625022271776, 83.52277169012702, 170.7610258102209, 157.82406948522674, 51.1070834226612, 146.86548613085048, 43.03147604646068, 63.56622821740877, 222.6919066538071, 33.52829241635202, 91.2908139599831, 62.151444979051504, 51.27504021498129, 79.29748899644338, 39.35441147518448, 64.29747811137636, 59.949487069294584, 93.40256380812777, 203.5241375197051, 252.3240436595405, 105.39054377396265, 62.25131316596658, 144.4992516348759, 75.4585905476309, 91.8203221367103, 95.91550853550332, 71.56543364433539, 93.61292011083803, 42.39470529507341, 42.18881874924038, 158.31651149470812, 124.10335077425151, 39.6454001001834, 106.44207123396416, 75.21055624910619, 122.24073195529616, 42.294600702737725, 125.84776074412154, 79.78863415339312, 228.27238155237632, 73.89891216392863, 37.99654328287387, 48.80186174271046, 50.21863637055817, 50.60270572790162, 55.64267649949308, 71.62337320477198, 87.28918278958876, 59.505709415526546, 87.67868852587729, 90.84125013829312, 49.94017052260493, 192.15581524308726, 80.7496604378225, 57.91468326005293, 75.8775256508067, 80.31477189204283, 136.4132125740944, 142.49271981931386, 87.54864908191375, 47.16883748604455, 97.41999452211763, 174.13994904269225, 69.678129901987, 123.9358469528497, 69.57303480731149, 80.0386263057245, 53.041768736028594, 79.9146531730567, 68.80626132838104, 101.86563900521004, 66.68228732621898, 47.54646239125585, 90.66692388267826, 80.17175163768236, 96.54646835719447, 109.81840573784649, 72.5148875978011, 322.8518665867495, 57.24827861067811, 106.49600291485439, 76.5454297430973, 77.06771736129507, 90.00144051929998, 116.1795294998734, 92.1041306479827, 262.10930020763993, 111.37803924110975, 78.34409605205933, 61.901350487260075, 138.57957418035832, 86.14985716203282, 293.2686628762002, 72.60169781342343, 57.635249846987, 84.5382102450061, 58.608164479183145, 33.40049321340918, 218.2233601218718, 7.54154032121829, 51.82438973493914, 152.86678682614743, 230.11534729484305, 49.491269217195, 114.1641929864196, 71.17362380888699, 88.99162552721059, 134.0113047494284, 94.51076034192415, 71.9431539299232, 92.78398522342108, 53.52023630260304, 91.15965763692179, 239.07368766765578, 70.64042176147362, 102.80330589123946, 248.11833032025964, 683.9574902732521, 60.784810458737525, 57.91902486345799, 65.50523176999532, 78.04248718180264, 112.09577163450523, 102.40339094994044, 183.4911009699615, 124.1176310447023, 66.27511363055288, 95.19397749819909, 89.27243814598499, 54.72594843627179, 33.794429820133594, 208.59703068760632, 94.57840567717335, 77.78890490333151, 116.01397102276945, 52.38749290996086, 92.05633672500123, 53.21972861994728, 70.68856336787645, 88.13147040797632, 72.12401440179364, 176.39543303117918, 122.80105136979934, 62.05175893777832, 68.85610934275554, 44.645479100356745, 45.629245277033974, 60.67218515181418, 105.78278763116138, 56.87633069195826, 158.77387294020994, 101.44256754213113, 92.0488882120947, 116.02112102284866, 54.55162156926199, 143.61597920015055, 88.60236297723112, 210.45073954457166, 71.72879096007749, 18.98593128897209, 85.40265399355998, 78.96722957406557, 109.85011432750487, 117.93304878501088, 295.72528837015517, 49.61473097506113, 72.23820189041834, 67.31735350632324, 83.51626554223053, 110.03062953415318, 94.64102446463704, 59.03496290052117, 182.7083919405495, 52.3310730312383, 10.427998579876935, 74.6927843420208, 115.74249008303075, 52.287984888725404, 56.90655588233202, 229.4800534909506, 94.89130627646192, 116.12903218439564, 137.4811570517561, 97.83788340684008, 121.21485723018252, 313.4624621065872, 219.91423570303414, 145.7168327917993, 69.94457819792629, 58.471949763984334, 146.12540237491953, 77.41927881268208, 167.06499383245435, 162.98612397413783, 166.0733863539182, 52.64854638683019, 114.65970287028047, 85.70597889324436, 52.833031322450424, 62.95465096953872, 129.4488075265072, 92.75771302186563, 45.20981315294658, 241.1954113903319, 13.935888733800354, 67.37217894791432, 49.6118511891277, 43.568636088269365, 196.51817422830806, 60.819472087255456, 97.94881358002368, 40.686108367750634, 58.96845572257367, 7.013423342960407, 217.74170053411422, 172.13260650923357, 39.491115480486265, 122.85611202362833, 246.52630159886266, 49.869035749034</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>105.8147968673706</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>77.70622110320608</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>[81.18409729003906, 117.74308013916016, 62.06460952758789, 104.52652740478516, 81.00951385498047, 106.73838806152344, 96.55529022216797, 124.67752075195312, 45.548065185546875, 138.13861083984375, 94.68701171875, 58.76929473876953, 94.41161346435547, 54.082984924316406, 81.06708526611328, 101.13511657714844, 88.50174713134766, 58.26393127441406, 117.75328063964844, 10.35498332977295, 52.85966491699219, 70.17855834960938, 68.34331512451172, 78.63504028320312, 62.54631042480469, 72.64946746826172, 44.84297561645508, 152.3467254638672, 78.49018096923828, 103.4487533569336, 304.3717041015625, 135.0532989501953, 67.4715576171875, 50.67505645751953, 86.83474731445312, 52.16940689086914, 57.4500846862793, 100.46526336669922, 76.16331481933594, 112.84928894042969, 127.1834487915039, 52.0123291015625, 91.30056762695312, 91.09739685058594, 132.12579345703125, 343.71234130859375, 43.90969467163086, 126.05440521240234, 101.36168670654297, 49.87748718261719, 50.789337158203125, 150.97842407226562, 508.8802795410156, 112.6352767944336, 78.41490173339844, 84.37542724609375, 165.30810546875, 89.09392547607422, 27.934236526489258, 84.73634338378906, 75.12540435791016, 51.16544723510742, 95.71430206298828, 60.57271957397461, 126.26960754394531, 49.51475524902344, 48.46155548095703, 9.700484275817871, 98.76436614990234, 300.8165283203125, 61.6037712097168, 99.17903900146484, 209.0610809326172, 70.36187744140625, 131.9830780029297, 280.14788818359375, 26.293804168701172, 107.19055938720703, 130.4792022705078, 100.99119567871094, 53.13862228393555, 199.45594787597656, 50.86212158203125, 77.05919647216797, 42.129493713378906, 181.0587921142578, 44.070899963378906, 392.0657043457031, 81.3586196899414, 82.40166473388672, 145.37974548339844, 62.9011344909668, 69.61235809326172, 255.9019317626953, 70.66718292236328, 45.64888381958008, 152.12232971191406, 138.37313842773438, 161.97994995117188, 85.05642700195312]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011502</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:47:23</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>94.01675252378377</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>69.98977975138095</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>104.0195670274771</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>4804</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[1.8860247464854427, 1.2384723878957957, 1.1467246041459827, 0.6593223049624943, 0.30531912374800385, 1.415808115659121, 0.12881385575448287, 0.5370863782453157, 0.7483474789888126, 0.9577138975905019, 0.2106133171099146, 0.7943246052514288, 1.2200658023951523, 1.1725052735671848, 0.3186022808906397, 0.7801222467632142, 1.0469668641121102, 1.0810272987066711, 1.4007002260701342, 0.21821251139501271, 1.6940455240219963, 0.6584879578769575, 0.19174889465991646, 0.9272206261034082, 1.4504040892974799, 1.4350260036531677, 2.125204660503789, 1.5529828594067705, 0.59116076373158, 0.6465130404519938, 0.5239234701927145, 1.4255615916463458, 1.1168932082995615, 1.095145959777861, 0.917652321950332, 1.2524486228905856, 1.273667949118176, 0.7274170721492126, 0.6690106471988635, 1.0009743701714966, 0.20317656475124343, 1.033588207981641, 0.8653578786347011, 1.2598192397566683, 1.4061580828293527, 0.8359731093086434, 1.9708638946184245, 2.7168407369295444, 1.9548215723904805, 1.5762117947468968, 1.7596148064750976, 1.1468934721594015, 1.1772027795254214, 3.1303528435744794, 3.910855205038526, 1.0625054053455505, 1.393802106148091, 1.5051471973653534, 1.2416344194365978, 2.1166208816494025, 2.6619337406112624, 1.883808229906498, 1.8066941082928998, 3.9862382541873025, 1.6291954016611552, 3.4079868132808704, 1.2955223074066196, 1.9950034476733827, 1.5938545821292112, 1.307206605078618, 0.31336424600011314, 0.8511553661602858, 1.1505547176310211, 0.493562604278816, 0.9345928178114971, 1.2406097589325387, 1.4817896464663871, 1.490512475487527, 1.3411230989517047, 2.0967594386100377, 0.5954560424263949, 2.456435253065655, 1.359055050568247, 2.5663408395688156, 1.3884955445333875, 1.6091554926989395, 2.6863700591875204, 4.169848686864875, 4.367340819345523, 3.79018709874308, 1.851215982033522, 1.4664946912047727, 2.5643385268943253, 1.4908281346799535, 2.0958670165958786, 3.2195015365283624, 1.648525390021011, 3.1704873540391927, 2.8908393219603417, 2.5812228556899046, 1.036441399846591, 4.659587502149578, 2.9652533105982117, 10.782288312878345, 2.2281829909239694, 2.5188561425175244, 3.2604955618238867, 3.056799781658146, 1.770086271005789, 1.7966011658365957, 5.1567621343179, 2.684702252185633, 1.840061966454035, 1.877694874117818, 3.8832305991666516, 3.426831882475276, 4.573697171270696, 1.9415004463668772, 2.172479973975797, 4.405606661240809, 2.1822505901642386, 2.3618543486747177, 3.4475039220043207, 5.246498523882623, 3.14208003828158, 7.084555506364392, 8.863843944055228, 2.0388278873117356, 5.93346085001137, 2.9707222445303776, 5.84043451153854, 9.044135259948137, 5.327764476634306, 4.282742889171123, 5.769879180143158, 4.70001296477391, 5.318847908049811, 3.487844752886921, 5.113766388666984, 4.562430201144307, 4.256314019485341, 3.8236459439273314, 7.072185933264643, 6.937779114015267, 4.090270748000421, 5.673204618491434, 1.2519899565073311, 11.137171819226232, 7.984350892410726, 3.0932328689806377, 3.0277307604816848, 6.5751051497812325, 4.475668920683742, 2.9416074964207843, 8.58307786861865, 6.938220096125771, 4.177093023261226, 6.14350952673875, 3.5251783400645085, 5.1051396029833835, 3.032740299579609, 3.6979631742146855, 12.921298233083855, 15.937303022444487, 14.233633716704944, 13.535573751197855, 7.336041171002355, 8.6024686495092, 11.521477731228131, 9.181914462486484, 8.61617585462116, 9.765093299378176, 6.235250939378053, 12.089151286847748, 6.555934269039133, 6.459755481495434, 10.19763046509641, 7.919905618256522, 13.104354775505048, 4.715967345528399, 9.467130016779672, 15.665496680649694, 7.92584108451576, 15.398515058891237, 10.840145356525836, 8.458387466389924, 7.997477586190823, 22.78490678712781, 12.323616812139571, 9.58577282474432, 11.09145542805193, 19.964201347233754, 14.132535737463757, 15.200155776174428, 9.422984269025093, 20.274899623411564, 7.2396264766246325, 14.447150301067756, 3.281876830757491, 17.98861845630348, 16.258620778567668, 28.173352701140114, 12.289138306896131, 19.399763089985285, 18.328704485489528, 33.148737740637124, 19.48479539693939, 15.70577106886093, 17.25429006686102, 11.578539640913656, 11.352167797472296, 19.184031618174977, 16.313977494246892, 13.538817082573418, 21.566672024494416, 11.756690269881597, 23.38564783380862, 6.288179134208986, 18.41997186024971, 41.07048930098746, 21.615051577710265, 20.389639763332617, 30.4048122159596, 21.68231629400022, 10.307300737596846, 20.043790353947465, 10.699329138958321, 16.52259564073197, 10.017728509941472, 9.73629988345647, 1.6856080169145253, 15.471332285251005, 27.278093767627546, 17.684083587450942, 23.27286567227867, 17.88110727407387, 22.627805359826834, 22.096554967523733, 31.829192161280503, 43.606257816546055, 18.88539119400532, 44.36893815165401, 48.33384574384583, 16.317263024845676, 30.753641650599878, 16.4252441582945, 19.32582130235492, 14.018937770451615, 17.41110211598665, 19.78279592061301, 25.12617501111525, 24.18933085179746, 9.262869700240833, 3.0585602619712926, 16.60386828664282, 24.497095497172857, 16.989171721186885, 51.24843322947737, 32.027921960639844, 38.98127982435116, 29.66803119990111, 20.74074452298042, 20.14716829502682, 19.197315009413735, 42.43284713193399, 26.936950443957397, 22.613244730611573, 27.451928064648875, 35.72151806030657, 16.285033097915974, 18.710917343755977, 19.192726519690424, 25.15981753144818, 23.815449449212636, 23.975727850763416, 63.778241065895116, 25.20572883588135, 25.12483207200383, 57.69012654191196, 25.667281482411603, 19.885223617295836, 63.385246075662096, 56.42512217596974, 34.68509599181472, 27.802240404008103, 72.45956258430267, 33.30837374589134, 27.308350939443653, 36.73026627715528, 39.295759742079305, 29.7049523038543, 15.635283250663157, 39.25998091271327, 22.59153714016467, 36.282696366639804, 30.5015505598736, 35.53545924796208, 22.862835534041565, 28.747023904581095, 42.18482635785001, 12.460879974785707, 35.888347427777774, 27.73840006522492, 60.85539601402893, 48.115684744521495, 19.44987543391297, 30.21335350490736, 51.58399730888192, 43.42109074177166, 57.72006614275214, 34.71753631848706, 34.16034222518059, 17.88377419499483, 42.86002814320071, 17.221618557083644, 29.441225786151602, 23.80285506507562, 31.384594365281828, 32.759953365733274, 42.081162776482714, 42.311995742762605, 37.632482789964925, 46.0323729502233, 34.69175660115703, 63.568634988386734, 27.962452937681093, 29.264473839278327, 30.461722974307563, 31.407118488840695, 64.60227113120308, 37.48859499306401, 49.372323173966784, 28.62718859304115, 48.68465723339929, 27.371098025377737, 32.27115263546106, 78.80320405230889, 38.06823698986107, 31.57866368972692, 29.239117300518043, 32.94583443347404, 72.32211643144981, 37.404896293959084, 37.852427966570495, 52.0011699859971, 44.70293376011797, 33.491917148722955, 56.68850995098365, 80.01502363790227, 54.33273346069929, 53.45056723050315, 36.793550046487724, 53.52036174863199, 66.05906735804689, 57.21286418685622, 18.68125372880565, 46.46083052292521, 42.55857193356574, 40.90635397030076, 44.97117364766533, 32.950877688527214, 23.225746638475464, 81.3249199480787, 48.81314064675148, 32.1712726083436, 81.00693696171756, 55.00735527003073, 38.05193322195145, 68.89611823751198, 57.555896850182485, 68.83194346299197, 80.00098378287282, 45.56756672994534, 43.8240880801201, 43.308316961393786, 75.97765509915143, 43.44500312983135, 42.0249432465837, 47.21430674016858, 31.28747732359585, 24.7517147365549, 81.69409164557662, 45.431845580558125, 51.070829046079346, 39.80731701154159, 36.76206829400305, 13.638148393820275, 9.88372620695332, 51.14868029918547, 66.14871535582152, 39.75478519148935, 88.31465569978887, 60.803266005375605, 73.68223280000792, 69.65295428446085, 36.59006635926013, 22.819675261488115, 69.87635454700373, 84.2984368160318, 84.99595600104534, 65.28063565246983, 32.385359235066204, 56.347749208914905, 57.23030713182493, 28.416139787451815, 93.4769490301271, 93.45603535453975, 27.58216504466995, 30.176843921087176, 48.344878555768865, 62.57577183082652, 64.45683901808714, 32.24239478453774, 88.01965562175437, 61.999644285032375, 47.664508618989, 38.7618551964938, 41.69357833064747, 31.8885135265978, 52.39579174312522, 44.51165185829103, 37.28826338805689, 44.28264565730576, 157.44869766927104, 46.71774937910308, 11.222820558390422, 33.885111473089296, 32.27048392092117, 55.425574361538374, 39.40384780549453, 53.36675129543889, 74.90731356255246, 83.1196079331627, 57.338653214856464, 74.66857847923932, 45.51240461677409, 80.67587285821261, 42.3739149620847, 9.303945472705372, 82.27289762223536, 83.0030964005632, 41.05678276576727, 98.21660475412783, 71.7431832676336, 57.94867187127915, 57.93618744616974, 56.015015586120136, 6.727215873659233, 40.999165343336074, 51.69306875665906, 55.83725257140844, 34.688231858148015, 51.88852385766773, 51.49885325270499, 46.96005682210101, 38.00988267160922, 4.7358718195670235, 111.66671056504069, 79.94447522804474, 44.044892012949276, 128.74471696319767, 47.41534530074934, 75.24214872302477, 6.849375237579705, 45.74597339527838, 100.93552375079116, 95.81444292645321, 51.77827813919173, 41.506082148194885, 53.83631400322276, 83.69178551112151, 28.697039574670224, 34.95044276894934, 33.750677935795885, 58.101534276004806, 85.1093843009403, 60.168931098017325, 55.13900924308108, 55.4842901853505, 47.24211729070067, 84.1892231446283, 69.66375559726694, 46.423662020110186, 175.27231031226887, 99.98537258960646, 90.30728333827439, 112.0744468265024, 65.99174243280933, 53.243916117235024, 47.3020696075493, 49.866725319332396, 74.63355981639727, 129.42152002077646, 65.2116615504948, 98.3390040546401, 37.35019564222503, 50.33130020615721, 51.50115451372481, 66.36733506509295, 31.199975105012765, 67.14208931819267, 77.83866719872252, 64.9792596691212, 22.423040609942657, 114.55494155734654, 42.2110753278889, 45.332091311530135, 92.6351134685932, 73.44700546148003, 129.8825419243767, 99.29279294729687, 94.99415914964953, 66.69548243119871, 4.722433991216525, 42.02247694706161, 52.36971853393656, 37.986914821979376, 53.14256493025377, 54.31800421413949, 94.05015577622805, 42.813644568357034, 66.0132139848254, 60.68961205850857, 51.53268324304413, 44.620502890226476, 68.74102816128777, 66.0916890824737, 31.832040026866302, 68.21463345500683, 115.78748922308135, 51.140358872828095, 100.110739364542, 42.247287308283624, 108.71505899709382, 66.29906278301085, 62.99428556735149, 160.83872278306174, 58.14744715875166, 43.847776235137566, 298.1151469774337, 40.89934308771981, 44.09446036156386, 8.83911192926488, 58.80210197478514, 103.9470937148961, 83.519930293676, 62.66205974236706, 43.899166817721344, 33.19797616432737, 48.19334884543457, 40.309691101524805, 105.16375400257688, 54.072264213729525, 91.81213683525763, 73.44192468892709, 47.18393735699999, 153.12703424768256, 38.67243741758776, 72.3251238065644, 97.11249663801604, 47.06662313416912, 71.04807312738205, 103.6198033814353, 66.14963318349473, 45.17293072656024, 17.706632021475972, 78.5306865634097, 79.5372527459718, 36.28464155602981, 19.09920639188099, 71.07562800873787, 5.9577221770509885, 108.9626240955815, 50.72907715253002, 51.295078293336026, 101.97185789268694, 39.76364497701003, 50.433570252974484, 51.776899111082166, 40.88086045422895, 54.650410199609155, 74.17522388086799, 106.28063867030268, 46.03682430225962, 72.6650191904494, 57.67963794175071, 55.9773294572205, 69.50187271152295, 81.60876243629353, 44.043047739575144, 48.13685563257341, 76.14136215653686, 46.710442564444435, 96.39688812420363, 87.86919526063313, 110.21315768022707, 84.24239102498073, 31.959916341308343, 64.85420964442986, 103.47789261845162, 119.5143892478055, 61.334647528991745, 148.60663406238328, 5.8773523046688485, 46.29052825410538, 49.36609049460175, 71.93935822933727, 138.57497616091788, 35.96609395706366, 51.36397413736916, 37.1468999598948, 105.80905024969118, 4.806675794491284, 61.30008782949006, 56.187149675206975, 63.32247763949442, 52.783944665962316, 99.29219880381395, 67.11201544680131, 83.32019765032788, 177.77950225148055, 44.46760829546235, 78.540092645715, 72.24205224135765, 52.81786891764361, 128.34344607861087, 85.74812237270872, 68.69057891205371, 42.86096489069844, 45.18462548679371, 100.94617789004073, 55.97134166952592, 99.223093695928, 6.216326948083053, 52.19456032305823, 103.53836163050757, 48.72363199922047, 40.58992235254683, 69.85600800274598, 65.97609217485652, 40.09055580019399, 119.99741923679885, 71.26267095615977, 62.29672200229595, 52.42400408629139, 41.9401432496635, 72.70553950460308, 68.55885008135435, 45.498058901070024, 5.603944465326538, 70.89404014505504, 50.23746450218227, 92.49893407406566, 98.79718932313091, 74.31751499956368, 67.13435126071833, 45.49393381125608, 30.651004458511913, 91.06969777635918, 7.032260057497137, 50.431800645968316, 119.79950357501653, 46.91973625560985, 68.74280730178204, 60.775927547070594, 61.45324693218223, 127.6443168796433, 90.92287424328579, 86.77230377936552, 46.822726203184835, 43.5379671624457, 105.90040404005573, 54.5887750706835, 49.583496648173664, 44.300848954604724, 117.06184544291838, 45.31077631285202, 54.98654200597062, 56.45102925844568, 48.838689724757735, 104.69762250405694, 55.48438275965525, 63.22418231124745, 196.27532894564501, 73.97418325965701, 47.32376403972637, 49.95898956246555, 72.24752273736989, 228.62656720392073, 65.22566609940976, 42.97605628640454, 55.12507621539259, 69.7013316339163, 45.56840414652574, 138.3192830205102, 79.56365336688302, 10.047166835721802, 105.43026193182023, 42.54649826907616, 52.09568898180024, 58.99667059345636, 114.68313100161855, 77.21496842449268, 64.56716098885258, 8.806134014686455, 48.304263237423186, 84.52159893156418, 163.93571231497546, 65.01660398988457, 62.066280873477595, 93.71450550468525, 50.7314723291872, 41.97038001163855, 48.08925722137134, 97.53568029198614, 44.35061643914294, 12.705926719953348, 56.09878999702293, 226.51775299017598, 89.6838822613088, 92.45129509965064, 66.37998492762631, 155.2385261325139, 8.759162311422788, 60.77220936362943, 8.845697168721133, 148.23142279124784, 63.355462170134224, 88.44598592909323, 39.38236212119812, 126.932527955222, 89.92354941267597, 54.8499757447034, 70.39394190467864, 49.67755613515362, 64.23005622789859, 64.71801388813884, 76.77523058964402, 59.381924060346755, 12.114294248124132, 79.28800133679852, 89.34799021895681, 69.77835857977193, 86.53923726251708, 89.66165508776042, 78.76620565482922, 82.06791546566505, 73.42842683015094, 59.241729039959836, 41.01245907011766, 48.042366427136024, 67.32979930371825, 37.769713896938256, 47.52168794455514, 49.6229231900071, 96.23614020746498, 71.76273945600909, 83.06988102892895, 52.511545411936225, 62.17004157715266, 83.2409713781908, 51.75429442488663, 49.96994799692629, 50.42583039253251, 72.8214785124694, 66.17753978135951, 71.5674242531103, 39.628774131437666, 122.96696286732045, 51.47831292238088, 54.14986984371776, 102.2348703092829, 49.529548207773985, 113.08369802493745, 129.03959498392877, 62.553069539984165, 53.82792268848774, 72.9163949199378, 48.383187959344816, 72.42817345568865, 38.978919804618045, 55.64348364323287, 72.51183419500649, 52.78665476079337, 62.2447615799099, 73.37493793826248, 84.74949274071199, 120.88655452914495, 113.44684867257428, 43.351503897567106, 84.3885358219426, 59.6608057804186, 85.01622599083981, 47.39779842686432, 49.48072650962996, 31.89312838138541, 45.56429133173585, 57.582965478798876, 59.37549957548721, 38.755989109891786, 86.798800058056, 83.74753937792829, 43.31627191413103, 57.95433196419613, 51.14129082977142, 61.84971848645344, 94.91311428965369, 76.02035871114273, 54.45900536937829, 81.47999044246777, 56.91199344914622, 42.994277433073066, 98.48348591835146, 87.55130465035194, 56.32135345826474, 91.22167076163421, 109.43912141842432, 60.29148010280049, 40.73280007921559, 85.9360880231765, 49.239834873089755, 79.63164601785815, 51.76803230831778, 117.72872878087294, 114.43876388977495, 51.03360979228711, 172.48888159865402, 57.3122780042185, 45.57388932531395, 71.88408341911075, 116.98839751223665, 72.40960800566764, 76.66003559371296, 129.14727774255613, 209.36304577973357, 79.16795147701065, 68.95010139412022, 70.3690657774426, 113.26076647720781, 46.58909580636362, 151.80434861309067, 91.40696171831573, 98.72449072848099, 92.48197200827335, 41.27765680035739, 130.01870004592976, 80.84450603112182, 30.31607206826347, 51.390771777295996, 239.65092105196132, 46.23674722281677, 78.79817480267812, 56.48409105400332, 52.575493150418254, 68.03679286120243, 95.02343591735162, 67.48077762588474, 52.11578780072198, 67.51560779341818, 39.1800730113906, 9.241358040981062, 86.30083710833627, 143.7098796524515, 63.42426234387585, 66.23419367084664, 253.1145336985267, 105.20337015436556, 62.91260712749276, 160.58845498482594, 152.89607015214224, 44.10931340827845, 98.78379020503613, 167.22583160264733, 110.61908260237743, 89.45707596628954, 65.13331344482573, 79.06660000042362, 57.99426650683609, 164.822008678698, 119.15067786326549, 113.224503957881, 108.54851860022212, 10.772389332562174, 92.74488986478316, 41.63827701083422, 70.82411786764727, 186.35579577500545, 136.30041642566803, 68.7986287310169, 165.94802160261324, 63.939779702788805, 73.71384522350299, 51.351988599048866, 63.12920144470405, 66.06562218509664, 74.85150407614921, 55.35381623894052, 107.18458047433826, 96.72847285331316, 60.28558014569539, 62.77859564982406, 52.289876004553165, 184.35396500568314, 73.24113388054096, 42.6093839582235, 52.452456853640214, 62.793596770663854, 41.009721729929986, 61.67631976011438, 64.95618678077378, 92.09502963281113, 109.94091232193355, 50.00017587885451, 66.53471982336362, 47.65987438702375, 63.80724953491071, 82.999137274156, 59.39044810542784, 80.7698827913381, 56.36575654475476, 52.62398531881376, 2.999874297467739, 58.37827478418408, 153.9134169322866, 55.386309044685895, 67.83275684155078, 68.68592290892626, 50.721491508126654, 57.60886754308001, 40.838032475938924, 55.617548463389596, 50.16401499647992, 67.92567553486319, 59.04964865399137, 59.205184445282455, 122.51452036051165, 83.00097001477064, 54.41002896450725, 56.47928070315898, 68.85737821247851, 50.862347516607414, 19.442348920104116, 67.33310390148158, 68.6248226678568, 43.96868347089153, 71.0813533534378, 59.262628816869615, 70.59663181367483, 50.841537940350165, 132.1734040028435, 67.9370655458575, 56.34957815632369, 69.03336454366054, 111.42164812353099, 323.2220867949438, 86.93270279290081, 124.05836027172188, 110.76818884700295, 63.0630411759363, 176.32892980447255, 62.60228021290772, 51.60022625777421, 161.32307318337013, 57.15052312952967, 93.48210040863482, 66.18559033864852, 37.9478148686763, 52.09539418012806, 16.403449622720128, 74.10554476837375, 71.5506369772977, 110.99154147812175, 66.83588051502947, 60.37128403802447, 3.2858789258254593, 50.674520823387475, 97.78654383952151, 125.87662596559085, 65.84141730361202, 68.70671092641817, 52.80358465372242, 224.61030181710785, 138.4029838978825, 251.47722407006964, 99.47428282307604, 65.4146312375957, 61.56067961460781, 120.16141677472235, 60.2263626190402, 119.83356026710395, 45.06514385436567, 53.394468105249494, 57.88778684041733, 94.1579668440516, 175.658372983369, 52.63838218731391, 102.26212403059523, 59.857086103165294, 67.86878574156468, 255.387100607142, 63.741455194888026, 108.13965448425213, 48.77854662400078, 60.41104950824334, 197.13165275204642, 15.489156921529682, 183.5313271788531, 207.19786127615578, 9.285522259206974, 73.91800338638384, 55.303031730999166, 97.59369489790903, 124.04488429155191, 58.07598503986941, 67.81268558091215, 62.084636038955864, 81.94687751487119, 115.91341798513248, 62.41621043774069, 72.4932890470507, 7.141493176162582, 57.99752843812447, 39.08749227389518, 56.358225161798735, 101.58056644793399, 103.72243935177309, 105.09313649265106, 59.84683809958728, 44.197429526778336, 58.764089421153614, 152.2248539302445, 98.58306347002305, 65.39307047405259, 51.19296164541839, 140.24865085861785, 47.178082323045835, 62.092909509491705, 63.026514178071565, 58.56076109065682, 83.70632015005457, 97.9023472649177, 75.40813382705295, 76.73926752853798, 52.95766812433132, 93.87240603774781, 113.58073220379325, 71.67887259683985, 71.82080215115522, 50.985158446259106, 44.972217541918795, 67.50900191516224, 74.37230789884781, 77.13526130825275, 113.71465143966915, 76.0295646187116, 71.49744689007133, 189.3491464787394, 99.44976905642217, 73.69626104134285, 120.43393718748933, 73.20114203965616, 8.289711381420872, 77.70106930466228, 46.95042543186905, 92.96643339671252, 64.1986304829837, 121.97842902304234, 124.37762511952968, 78.35590740093423, 71.05352997325366, 61.9989997457093, 58.45506025203356, 50.60279445201182, 61.52644576213929, 80.73155074825625, 134.66432129680967, 60.57213429613377, 40.32864573153768, 137.0915661944275, 61.06122904450497, 47.22191458676352, 55.662373784806306, 57.14081560991093, 143.56030632816888, 130.57797696697364, 54.36681906577908, 6.839502090769214, 144.35484288413684, 102.24237219399096, 91.57338331623345, 87.65803261656188, 68.66207048236713, 50.35556323119503, 89.17263904429632, 67.28059763594152, 95.834525357545, 103.9568879345745, 80.77967959246939, 56.4986975204609, 51.31752015213437, 199.78369656018833, 111.15038068333295, 54.4451556196324, 56.05590077124909, 101.60313367207632, 46.86664263319909, 65.0042810182442, 70.39451745769881, 73.0350788129833, 8.417484637429057, 60.13164888055233, 109.68560840590001, 86.09684679709437, 50.8376344876726, 121.42264957709386, 64.40837373185056, 92.72113559344442, 37.85167359985418, 49.5024749403774, 36.8643551686826, 117.2322212170406, 50.29833932110603, 70.56673458850746, 7.957957648990757, 56.606450443571894, 80.94614841052109, 47.094675464896454, 73.27610507445405, 113.52563292941343, 154.31196617266872, 94.44083408509535, 73.96164550181591, 94.09441994381108, 71.99015856775583, 163.23965644468242, 52.17846179714685, 61.41480750401477, 143.26467475013237, 128.5869087733888, 143.5551816158914, 101.28790547093828, 51.31142073638394, 92.1180152254796, 51.6662467925554, 122.844724540467, 74.69992382742359, 104.3068394240062, 68.7063276269722, 48.77400813510534, 77.94395392189617, 75.9163245417035, 73.19551256830322, 52.728616443694825, 63.08009667607094, 166.50472779294753, 71.59712363168967, 136.01958229590662, 66.85446991849315, 3.6275470291028826, 288.5627913283896, 61.21035081262685, 82.76239077224204, 127.7319554750726, 92.1266941408469, 193.93184551382646, 62.13709243885328, 56.92160344051027, 62.207507637236006, 91.68646888762807, 103.73285823871363, 168.36512744788374, 99.61441500351943, 148.12291255825, 49.95833739139436, 76.27972183443853, 40.21572109113089, 85.6533247715627, 99.53995476616565, 62.09516454814256, 93.66624101840802, 107.28944999277878, 47.721618460638496, 41.07151054844816, 64.156928459415, 74.96754060619705, 99.1374632836969, 56.61379206514729, 59.768194094852916, 241.88939438931976, 84.84982886367663, 62.961819910939035, 110.08834297405141, 111.69225902379146, 145.85075931394218, 96.44147803912718, 67.92477098269258, 83.42573128868793, 234.62428949349027, 47.63726677555488, 65.69338008492929, 84.8429564513294, 83.44971899033534, 220.41540701071594, 136.08441752825357, 40.79969887965301, 38.3809156744135, 7.707131273191962, 58.72300050577602, 57.43347836178902, 85.28122942260735, 56.0045934038621, 71.15241756154992, 61.85089002404261, 217.87877576112365, 61.579260591850485, 317.1627878247647, 63.00366577338396, 13.716765400280869, 69.61469432258275, 75.76331084986069, 45.10450253931691, 48.42818950137925, 62.51735039032191, 52.30055272990271, 75.45054903841427, 113.02958580166607, 99.79374214737942, 45.694085311737, 74.53066501928195, 58.209825666080995, 92.46599306100643, 61.23125535893539, 86.50908397274175, 81.64507879863392, 61.702322800401426, 115.43353843246229, 67.3708565420495, 112.53661455671921, 68.49198717745571, 100.43986691978391, 65.69272273848908, 57.88111438598281, 209.48361542036565, 338.82150322169963, 154.80972661939123, 62.72547175869196, 47.97053863509122, 9.81086164720152, 89.77033985305411, 138.5501564744423, 158.779654167827, 22.945148389031118, 52.5381834511795, 85.76577445190816, 337.4265740660445, 61.9443827794581, 208.6324544763961, 73.05255142909009, 42.5387367303175, 84.07572278701097, 6.813521968896147, 123.2992139566647, 83.52060439137993, 143.44474381726485, 211.43418844483242, 136.23922509179036, 128.11857387173, 51.5670025731292, 70.87183749065095, 42.23324179346572, 76.09558739947026, 161.50988933752333, 59.355060585809184, 166.87934985502594, 144.61541117584204, 102.25465501389645, 57.715965240018114, 55.89839970405913, 12.162014155447634, 141.82043621025156, 221.08580774113756, 42.630966549906155, 63.06084147518226, 61.34709791740561, 113.61063450669096, 74.28920999663346, 7.0633552165066735, 69.06361517888634, 13.014952852515275, 119.10466156556211, 71.36432781580068, 50.047019682105685, 73.61097851411822, 156.9264014653713, 124.91127162629843, 8.506922698357357, 90.95093909095311, 63.77931195826134, 115.3173062407759, 79.97287686593982, 79.58593518011331, 68.799848182428, 236.12961827068222, 62.46317145294955, 78.13513450119001, 7.959004260585301, 109.36751025288625, 103.45788317723802, 83.65786343662603, 64.67127021390675, 86.38363798534202, 45.80644941323079, 56.13924058832372, 65.55879853250734, 85.8957294860738, 50.44532557961096, 54.12297060778887, 294.9006889827675, 103.88935543793217, 9.980720458880764, 13.459195949168679, 116.63809639851596, 51.309626063042174, 10.510473289257105, 76.61625412918258, 105.66740710198471, 80.3868214978956, 92.65128768376005, 120.68436550590546, 44.89158986622215, 120.97670963878424, 47.095206351095996, 129.59287626081928, 54.57299163639625, 107.94085155112109, 139.31192732656444, 50.71528054550802, 52.79322587984439, 98.47462551188059, 69.61856232451278, 104.34319567418275, 63.59284960792133, 78.24970316241037, 91.63540877243896, 189.97311727148795, 12.946408557189347, 72.42317063209745, 72.80008208832116, 45.775523404808844, 35.230998888938345, 141.06807672684477, 39.44057486455803, 73.06971495383829, 72.16112323584278, 55.212192363545384, 69.86669869991316, 105.59528391310212, 40.804575234126666, 175.69918208387728, 68.9199741156259, 204.97929151489345, 88.41934906687659, 75.68475137739264, 67.33870922292067, 224.71783942127718, 322.8688830427583, 111.44666473426956, 66.23596249431935, 62.63802376563376, 56.19539980557204, 108.98523902600175, 79.78928855006626, 42.75492464669329, 78.9001368958984, 61.24560338752231, 39.34324439864124, 14.27744729721302, 153.48768021764738, 75.40137282031866, 36.606458688534154, 109.40142967962022, 119.58264320999903, 95.3047284807573, 41.37819472248533, 68.06475762167427, 204.53608395886576, 77.2610398909496, 65.7019010073196, 71.21947177464679, 94.95989749311325, 123.65430750431618, 40.45062460817138, 110.77319419362091, 154.3711609710995, 128.2594943016097, 62.34110022000729, 46.48930321614518, 41.40663410680452, 116.91546350307672, 48.60927321585739, 33.77411429565511, 54.732623479059164, 40.21974333837957, 56.340984727717306, 64.83142230641583, 72.79231671030578, 160.93362593401292, 75.90550813623278, 31.325139564458215, 66.49967415462498, 115.45870885382013, 54.74320488308, 43.294895042891554, 36.696803936162304, 95.8461528080403, 51.45713144577015, 92.72782132905915, 80.7952972034449, 58.474828501676, 38.25939658512045, 61.351688391155804, 112.053681670082, 55.0828169372861, 57.448214098603486, 49.463994658107126, 51.26473864000446, 87.82952413493328, 60.59709650317686, 113.64260178032234, 51.4242808721128, 83.07692145564953, 47.97305243972513, 48.60941558833754, 45.548607695597596, 66.4378322635282, 8.799493902710765, 71.0756493749643, 42.5107948928984, 59.06910406541976, 84.21502666128215, 59.730773534182234, 81.84443194582472, 65.51921065245342, 85.61174648184834, 63.29432640254447, 94.82985770377648, 107.30792145536499, 82.71752227382213, 6.9649994638532124, 80.4930212314626, 54.08445015845559, 102.4946362511642, 114.82572065842679, 109.96635490619617, 119.26904860403059, 82.46994812758155, 93.5619109649946, 127.7472858094935, 154.14772805794902, 125.91139332816601, 48.4879305076236, 91.9018726486178, 115.55293969584838, 64.17368734408383, 36.848296334398846, 113.41786947777271, 118.4952223837399, 42.22291976827024, 101.10049765761866, 82.19118861393187, 63.97756118205631, 93.67188796254885, 71.24429867996068, 46.37841341415454, 58.70691075159916, 54.85152141997693, 88.2750279506251, 57.8846636120804, 56.103580036431275, 6.392581779471033, 61.33031252787103, 70.61436904743039, 119.34667272343096, 6.943943088585515, 287.34966046386825, 248.60880229145977, 155.6794139832008, 84.33505196561204, 101.61238734658627, 7.6912477772560415, 55.54729246079885, 67.60743727016896, 75.64492219682046, 75.51382339378843, 87.74114533484811, 143.02030616420797, 113.907233973919, 56.50079162834564, 85.0630640464085, 72.05161969109606, 86.12195681285564, 66.22633180207971, 61.42810706707387, 60.00369753727098, 132.9567211993684, 51.506424939685076, 57.747284354912495, 104.35660075734904, 5.607021662402689, 7.820753706393714, 53.695175352269665, 151.75033424193444, 90.43412276611555, 176.60295952612492, 94.26438997018087, 85.23653576017414, 85.8319770349403, 63.908690381125595, 127.20336430975988, 53.014808252617684, 76.54557987588821, 23.74932862983613, 87.24129756517074, 40.749921905885174, 157.19229644508536, 46.476373833479144, 169.82983170772548, 143.76497029464957, 6.392954964552205, 106.82636208652893, 86.45066744283668, 40.25050884036887, 70.2005682802919, 64.67826044879078, 59.9557517733446, 169.30982599132116, 49.17802984160519, 55.467905896570414, 43.129826882097284, 75.08619031181566, 64.19822924583288, 112.79272711418936, 78.92579949315122, 106.57029086724583, 95.5636141556636, 31.937919192094935, 64.21740694679559, 81.22449650562342, 112.32690720151183, 205.3262402234133, 82.37228791013654, 43.853661881639425, 118.54468163843754, 184.60379782541153, 92.07228214440805, 101.971945344528, 78.90109967191688, 42.659393936139374, 145.93462572750644, 80.85946133359938, 118.93655148031439, 145.38074121818792, 46.164329988366084, 70.13322900841298, 72.63891247733697, 57.55517726559069, 52.088583253634134, 40.797173290091486, 116.6197361133885, 133.42936666313636, 101.65085417608363, 91.08400923800826, 118.98120214581199, 20.85334098058604, 144.9960597961575, 74.60978920682803, 67.51768940555417, 76.5375799633376, 80.96772374072863, 50.61276981258165, 102.13172271670605, 66.74893925889153, 104.50204141348632, 176.31317646027992, 175.3731740130198, 153.67540223893823, 233.21047060923078, 166.0232310287024, 60.991191984826344, 227.189037483945, 82.03205765651033, 46.10746074731703, 75.867224995567, 69.03835859318711, 67.23340052409756, 61.18069378806303, 67.50693102924276, 86.0523817099576, 62.64820719561859, 171.54727995200292, 115.7489859878029, 127.66615337921397, 91.94908122051349, 100.41338847637489, 141.57625230913445, 66.53371374916217, 91.01114603761609, 127.66051989796739, 294.26398097164605, 72.7548392557412, 114.27016338777379, 81.64542437467213, 62.108304479397724, 129.63913342080969, 54.42549192764726, 49.281192558550906, 86.06232861087996, 70.77076266546496, 52.69213666786494, 63.7493918140447, 68.53404507432809, 70.24982510575012, 12.883185246021275, 77.52022769725191, 109.36970059421503, 104.84991962054886, 109.48656672506047, 63.25138311537335, 404.30510256117793, 84.73309488590951, 276.03189084227836, 88.78465956696166, 119.1375966624534, 20.642339621702774, 64.9532593615987, 53.4219253087621, 49.062448560045596, 83.14976941867698, 20.962268326966598, 197.78063924876986, 92.17705590399459, 60.227369465596965, 96.1929595531245, 85.61448469100891, 36.69364673770166, 152.412253079133, 91.842600629402, 238.2241728795469, 85.89919961030525, 73.7693205782482, 97.49520989647029, 48.060739043847576, 59.88522151257814, 133.51376467289353, 79.21583133993978, 95.04344841566291, 93.3287665039934, 50.49272489962123, 165.4206056005726, 57.294517134942815, 248.72540251977247, 91.74596806235328, 85.05614396688229, 144.6406266506568, 81.01635577923557, 186.04649090110104, 113.29981428377346, 43.08111911243325, 55.34346556828615, 46.63750510803656, 126.93853326144429, 50.273858010977, 123.69644548851636, 158.906254878467, 85.46935979090532, 66.88550739356668, 65.83908779752834, 13.360657194057143, 79.27348831525246, 97.60535290599749, 63.52372114310429, 65.07401871262452, 71.5723701851395, 56.836848986774996, 103.8115593738823, 74.98305588479964, 71.87096134791408, 92.66227321353725, 39.67168096775605, 57.43628221202, 42.42458574572159, 67.76345088734077, 44.57200802330655, 130.69683999360745, 61.70568649389194, 51.07784095549797, 71.08572690463127, 103.51433074492536, 150.98825975672136, 114.24844449741329, 55.97469255167652, 81.20773224514713, </t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>114.9442366027832</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>57.69587786871395</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>[112.65039825439453, 139.72950744628906, 45.85279083251953, 57.60123062133789, 64.40049743652344, 160.24508666992188, 75.19080352783203, 56.42781448364258, 86.53219604492188, 153.976318359375, 61.99897766113281, 161.9163818359375, 76.17862701416016, 159.56259155273438, 76.5015640258789, 17.03871726989746, 22.4252986907959, 93.38123321533203, 55.84034729003906, 107.12273406982422, 126.53547668457031, 81.35485076904297, 77.59783935546875, 217.54515075683594, 205.2202911376953, 137.09022521972656, 73.31936645507812, 163.4719696044922, 68.1495590209961, 125.37905883789062, 95.06809997558594, 57.341651916503906, 198.71017456054688, 132.96331787109375, 113.5986099243164, 125.94705200195312, 66.34196472167969, 107.45039367675781, 53.00371551513672, 58.37891387939453, 303.6768493652344, 169.45265197753906, 141.83509826660156, 43.27381134033203, 140.63589477539062, 234.35435485839844, 215.7981719970703, 256.5746154785156, 183.05308532714844, 82.58489990234375, 60.59686279296875, 67.60822296142578, 93.06295013427734, 72.21308135986328, 108.1822509765625, 70.49755096435547, 88.8287353515625, 116.54325866699219, 70.2492446899414, 138.5977783203125, 72.37334442138672, 106.69058990478516, 147.9879608154297, 55.48236083984375, 107.47718048095703, 312.2193298339844, 189.39822387695312, 113.5896224975586, 151.13682556152344, 153.833740234375, 88.82294464111328, 163.5028839111328, 200.4992218017578, 71.2115249633789, 140.7374725341797, 84.005126953125, 64.89430236816406, 149.0472412109375, 62.11111068725586, 84.85430908203125, 161.68260192871094, 82.23657989501953, 136.33059692382812, 86.05702209472656, 87.96209716796875, 171.54269409179688, 53.8437385559082, 217.26742553710938, 126.14327239990234, 87.18168640136719, 118.71536254882812, 83.3985366821289, 65.74585723876953, 187.99595642089844, 87.71357727050781, 82.39261627197266, 198.8354949951172, 51.47163009643555, 97.33369445800781, 64.03773498535156]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01502</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:47:28</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>92.87847997134118</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>73.9342401989328</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>102.0968532897425</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>4894</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>[1.791905026366888, 1.3010169958952844, 1.0150659413346061, 0.9433648147114375, 1.0985008911394603, 0.8888757802655948, 0.7971336736282806, 1.2326146338525328, 1.7619542232915808, 1.3099188177238998, 0.48923231660157535, 0.6593706449355985, 2.3124665737249352, 1.0235254395812428, 0.7094685862087237, 1.9369961681559702, 0.818134232836132, 0.1167570854957368, 1.656721279034246, 1.5196171521854092, 0.9056908605171352, 0.74923034897314, 0.7942249491040085, 0.6925880935252906, 1.5417286781056552, 0.9353407922771527, 0.5944822349840808, 0.73868651271964, 1.6423732950161432, 1.4922250217544855, 1.0538238224661471, 0.850817721408198, 1.6274402340087666, 0.7202557569062857, 1.3875038147857741, 1.0572730447842864, 0.34067507537688735, 1.767262153962756, 1.235853315962273, 1.673779509280209, 2.6767923088043624, 1.7308399046183693, 1.2026002660490425, 1.9495777879858374, 1.1230980079905328, 2.194625169345459, 0.8535736373376334, 1.5432049013526439, 1.7891005337109362, 3.037811794785571, 2.5390872715370145, 2.218842908018713, 2.206126732014045, 2.58742435942109, 2.3921828495469666, 1.7066015801477927, 1.0522756417850256, 1.0054658029755654, 1.8053724477942261, 1.804670859892601, 1.8822323044983034, 1.3617662698162565, 2.1981627394970396, 1.9218669424340689, 1.2473607016321473, 1.4659899005827064, 1.1666760590511553, 2.290417200367891, 2.5728678130344504, 1.5378812565310707, 0.8978681731036975, 1.271506547513332, 1.6741948684390862, 0.2782461206956111, 2.3454133418520033, 2.4332134312696283, 1.4138974636454038, 1.9455154420808003, 2.320562165717182, 1.7216287602301479, 1.6063632864564854, 2.7102268391051494, 3.004531701405533, 1.554626426001957, 2.280956458856382, 2.630608308392429, 1.6042341226898427, 2.6290510018491138, 2.9877692580686337, 2.302042723268449, 2.1553092346774925, 1.8860526450558133, 4.9640650370067005, 2.5218363151291316, 2.0894406008217916, 3.181309816938488, 3.1110708086581, 2.468477223544514, 2.656676961230786, 2.5796593951226376, 1.4488383329748231, 1.1550711352096417, 3.5293175809889816, 2.4558861955539673, 3.7213564837643447, 0.3021907694569457, 2.339538912550999, 1.5023188486135537, 0.5758921914485103, 2.7547641770567624, 4.435150079660148, 0.581000519842096, 1.8871377876085493, 2.4843147585787255, 1.957266120743147, 2.8435284891701498, 1.8779515509208886, 2.215873736996479, 2.7989398817547153, 1.86863076480136, 6.2610905515814474, 4.142163828162156, 0.7244821104711041, 0.6484526125693522, 4.5020007490678005, 3.958862536628215, 3.5593529223827813, 3.937697330718128, 3.5085067803999213, 1.672410723413894, 6.1668654218337, 4.921921893950546, 8.17221382131015, 3.01650709147298, 3.66540036344841, 4.802521163215286, 5.023663309577043, 6.040723896458913, 9.90371807068252, 4.180027919994757, 7.324714378166915, 3.4552394218984253, 10.439758546375435, 3.1833389645158854, 4.5428828993897294, 5.261112241160853, 5.912097810987724, 2.8544489047912345, 3.477632931566342, 5.496637255247493, 8.852328505365751, 4.5826004387075665, 2.838013422699156, 3.826772182997652, 5.160063317531868, 4.486460597852789, 3.159002315983087, 7.502686569350438, 6.124787743313522, 6.364393722106999, 10.071911109825972, 1.9086435965970352, 13.777968555428613, 23.172773996923713, 3.303011018752318, 14.20744517779001, 10.781206760082268, 5.870682962553566, 7.198077744654327, 14.072850922950677, 0.6833414944852915, 5.1265444109841205, 7.082840945260149, 1.185230302295049, 8.567300974270985, 10.152418055214259, 8.368846279144922, 5.104072454690381, 12.401216016217212, 1.5077381601413844, 3.9464981259807814, 4.1277204375588035, 9.529073981653172, 4.41517460862186, 4.13727806362454, 13.668362111146557, 5.269558488624456, 5.418796835785533, 10.508397326907446, 1.9731556945924367, 9.35747944479535, 11.551702949326687, 1.3612704503569504, 22.70419746301439, 8.003453273382503, 5.85766437107236, 4.078385625179295, 4.674930120617179, 10.225808822522533, 8.275047895625177, 18.33382765198861, 7.619508342981999, 5.85112408757491, 12.376585063856567, 30.293341030241656, 24.448852754722548, 17.519824584042595, 13.602243024127018, 15.929202183822317, 1.7980239466631363, 20.540012970871498, 8.550549905589307, 5.107723322963023, 16.535865776270928, 16.715685789331953, 27.559934615290317, 5.871632142873665, 1.4872119246436246, 11.643945600828793, 16.64881598593775, 22.4591160235992, 14.397316185055251, 24.402618904091156, 18.913136115602057, 16.58496180641556, 19.655474295980415, 14.51586241048827, 8.967390493935003, 16.864030406255004, 10.419670913769611, 13.473005161558621, 13.798447655360102, 15.268505927163853, 20.78234186736726, 16.37581275929988, 14.058273680755143, 16.418230837835445, 23.88462563703701, 24.8872708740144, 16.818091181940453, 26.925547996835466, 10.827927423729841, 12.448642222042443, 19.62565781544332, 20.29621811133168, 22.134867079436592, 19.66709765210296, 27.589428890447067, 8.948227833362466, 18.49685573816845, 42.99531816334173, 19.848390986960737, 25.708660319803077, 22.449019143723593, 10.496494360996108, 9.853781445618006, 22.754187732617602, 25.517440708176927, 8.229945978844293, 25.112013484554158, 54.645786548213415, 7.319992196656946, 19.513143033443036, 17.69795517509939, 19.986454510206435, 22.467558010549336, 20.842058562073312, 34.65098206010161, 30.49428615265586, 8.566258094495614, 14.577438607236687, 25.223853639112267, 21.19876854024204, 41.959559321464056, 41.53623396749895, 27.257807594809375, 18.13991612325218, 29.732038298302523, 24.6305313347685, 21.269343177847812, 50.51139644865968, 18.013624186269777, 32.91053255543198, 17.45542289054734, 22.407188701171574, 22.601723679670876, 16.645624022181902, 1.8913823712459976, 28.108758375597347, 28.91926335801034, 24.024677419509185, 6.702763017996514, 24.21248710286362, 21.081871251371798, 25.15347833342394, 41.84294026890452, 46.30597161965847, 23.55854389165271, 35.01735525432404, 19.995649232564407, 33.88502200057036, 33.88447228598672, 33.4095566418075, 34.96808980267317, 34.47695049587563, 40.22485924212042, 28.73020730678259, 27.842414575939415, 20.876700443023243, 4.8020500586515205, 45.261126221712644, 57.636450986316554, 41.056133726545845, 33.95071827162646, 29.27378923755751, 34.06433123681448, 55.37173408392715, 41.57620596211573, 53.11485956731456, 37.164917549777485, 4.455663937634546, 18.490472088442715, 36.34767337063336, 41.017010058647784, 28.455510968859407, 30.56069078169406, 27.678338358852088, 28.459808572884814, 48.99271271431106, 25.518037998098528, 20.166191934896194, 18.96438386282776, 29.48636630610711, 72.75033569218672, 54.45175528748937, 38.61551845853181, 4.071960623333411, 10.674533120370228, 32.19667448243843, 24.968999910375157, 13.653419332502063, 31.86541629210018, 46.07843141002158, 25.4686364831154, 37.578538593220124, 8.987114222241622, 35.8512375005983, 44.20255117992451, 29.821866350217693, 38.43047090790472, 66.09019307439704, 32.41678513867279, 32.0490704083456, 36.84776161049775, 27.703525979980277, 65.37568967195419, 50.706000919006435, 72.36822622483702, 10.530563683407868, 6.2940573827367166, 19.51301201698688, 16.744953476450995, 19.64565329937916, 36.7304505473473, 67.92277251844642, 27.83750849354939, 71.05947070576163, 60.57284047740022, 45.19259503582297, 65.25282909958435, 51.20309412619243, 28.258376099562017, 60.46449908560553, 5.123643572409799, 17.51157920215477, 31.54386828629317, 38.941174711081146, 45.72485965672568, 40.029465731858615, 68.35025418210053, 55.45505349274063, 44.31381620346688, 49.42497855523662, 41.55594576532728, 52.63306891623221, 60.04294347795202, 39.070283972187966, 45.35480347926433, 55.19058226753481, 8.149513187263057, 47.487790542600465, 41.651557165969734, 19.979223668553644, 59.38669872756424, 47.62673204251652, 57.48905406216047, 22.900106369443424, 33.99589404179026, 32.95113275083658, 54.972822250887084, 20.810558136072284, 59.153408580309396, 40.484885396024445, 75.07438083745203, 31.522911074414132, 38.365940220263035, 35.943105377795675, 57.13704211263793, 44.9208901021943, 40.266084757314665, 99.66782054549766, 34.8022318339232, 43.49426430057174, 38.339963588266976, 94.29437370089978, 34.06844631243059, 44.092284070641895, 34.444662363282475, 44.33486658850188, 37.46672003765845, 52.486364142214896, 58.76569567153347, 121.33635304385186, 6.369210677841172, 58.143687204651336, 37.64919671092013, 38.55419450496247, 29.344266884814754, 60.56374175945956, 54.62679602168081, 54.847752826930176, 37.701823938622766, 47.3524711015876, 3.6798415998229665, 56.61797937009459, 6.79885590969346, 72.85957211344189, 5.200934080492342, 23.89394442242345, 59.0529168570508, 83.90442220575491, 37.86528948786085, 71.02278752034296, 29.840930355727316, 37.75146249744752, 53.79165063936281, 38.75357021700282, 42.257303952903456, 55.637573475471044, 40.30876450502305, 57.89463159348971, 44.779620557758726, 29.880192603104366, 34.82193986994567, 47.67392266560487, 32.44992727942023, 41.17907740152336, 28.429137429317525, 72.01684225826052, 74.03221868600683, 53.20771632464036, 37.46663802211991, 52.56831040455813, 44.67178094391978, 29.657860395901626, 36.698057434826694, 39.91075222837209, 49.34337977752497, 86.59438391974366, 84.9505048696406, 69.52673610183528, 40.260080547898376, 60.909556487883904, 52.21326595082048, 126.57854837149875, 49.94742726102981, 36.94541388870338, 96.79065285249806, 41.88819719967606, 75.4562989957606, 18.990628793196674, 38.38021004788993, 67.65701763717946, 46.25389518187263, 45.067591574733136, 52.79102027671692, 34.71625765208127, 28.91143833017233, 23.605884767181852, 36.68443964763187, 42.84211657896953, 10.677991399607917, 75.29464306420452, 35.89047540462664, 69.73437260459134, 51.90994571809972, 30.067151213651634, 81.56606110483875, 46.25706633435722, 132.64980890423186, 80.04989556703532, 88.43808234172118, 50.83610875765218, 68.87285943254052, 76.03982253072346, 77.28948383170464, 5.906135277627611, 95.38545439546057, 34.764161938476185, 157.98645873443334, 63.59358071634348, 45.96171851373734, 58.462582254751844, 66.23444568018672, 49.79261771531047, 41.58620942872443, 156.53874896333284, 93.56187654854482, 75.0293290262925, 34.92924498437207, 54.205256273173646, 54.54169714030592, 32.14854404234053, 87.03932739027996, 37.06186147951223, 69.12945924840727, 41.24518132347695, 56.604193288221154, 140.3231727669713, 134.9740096004644, 47.523477355869275, 125.09945611729847, 86.90901997510717, 40.83009724888596, 5.28632344502106, 59.49013819440144, 55.54568087189807, 59.329189887981464, 54.80630257777096, 104.07820934065823, 53.768502887116234, 55.968696843953964, 37.57279368340611, 7.828846785094682, 34.887296314174534, 45.8857500542483, 43.45261779433585, 7.453587105252277, 54.573230139801666, 7.444491713012559, 149.0015910091176, 41.51920466318397, 177.44288025421935, 62.99398759657701, 64.49380481824717, 48.96299794841684, 60.50616407431204, 5.613077280791438, 50.37385636698936, 95.37421712588963, 40.63860595446138, 51.50942048170517, 61.3397636991035, 3.985003129139425, 56.39186562485457, 109.64872708976557, 61.2728807707452, 98.04062234121363, 25.611390157193718, 57.83226385300619, 31.75580884229773, 73.52871255416326, 50.59767607070122, 47.22484909442595, 35.265763543832215, 58.42708476558035, 56.41687013100923, 40.73982503117736, 9.073977066989697, 37.590346008334805, 86.61757662867166, 61.39164340019092, 78.52280563332569, 63.569996561255046, 42.137389610541625, 45.84018977892336, 35.195991967323295, 49.60400622875765, 13.911519596400696, 57.56036579320855, 43.8178569987518, 44.84930540511661, 38.888386918910456, 61.83414492465612, 81.2051615228152, 63.88854036915456, 137.90607467114867, 208.17279336426313, 52.81905392626197, 26.185031202544614, 52.50238199131728, 36.019911677346606, 79.53061066064086, 52.717369202610406, 57.791162499451275, 4.715892687345638, 94.03048039257304, 85.80124888083212, 104.14884159253715, 112.87714714121067, 52.53955626439842, 92.52586713363722, 74.0630740647741, 40.72312244281483, 63.84339007740629, 5.487280648564505, 57.93375306365576, 6.527471015396227, 86.3888896136954, 48.97437733175297, 38.16504643373114, 53.32222085029766, 31.599775975721755, 75.39899391560817, 98.88968540697736, 63.7710198271251, 54.659724691189766, 6.66836207937002, 45.99371996544522, 124.26041149202246, 132.94353452085315, 64.92654400295622, 45.266370215028296, 48.863567845634826, 40.66819881322784, 85.7992729559816, 68.79271167739296, 86.22043836205498, 70.41441087218303, 68.91719727791049, 64.50885839361499, 34.64872214062452, 43.12485062366652, 143.97554567543222, 65.87556176398422, 60.122304399194796, 76.0853424815315, 58.0908122975184, 57.59513288717158, 42.55463907108784, 48.81090730858126, 81.2129044966117, 45.385639901359966, 43.56837921918735, 52.026190978423465, 73.11285241082788, 73.4554029062277, 38.30319800800579, 75.14308725254944, 107.3447607268007, 37.03066408980199, 70.22739743848587, 61.3250333472931, 38.813544687021945, 39.17923402866275, 87.73916751955139, 55.480074578015724, 65.1674963202, 122.96388081448939, 46.961402517149, 47.29349029534995, 49.044099465518656, 53.56430128506149, 88.86979744893446, 39.4062757776664, 49.089238076108366, 113.90135833751985, 90.70282287309244, 152.43258244005693, 102.08979572472192, 60.743591781138946, 49.01518143645927, 129.1948165534763, 70.46801892301535, 128.47066428053765, 34.92780218822479, 42.47157703642657, 56.084154617988276, 70.80891858606677, 33.184271855154286, 46.686121752518474, 42.037233640212925, 74.42239517073916, 32.10023574848282, 40.51284788939236, 64.22890171180903, 130.87277947677927, 74.9085759251806, 64.20608078591212, 66.16494860964976, 58.601447630729425, 64.22742395464925, 53.74381883616847, 45.916493842861264, 33.54940282233128, 60.317026664981434, 108.41404041965932, 71.92774784020247, 52.569567698453966, 10.222675813882933, 65.55724630347987, 63.55909018634872, 58.21627563653601, 84.6908172937526, 66.04810303314078, 55.74077199647441, 58.38231102336333, 157.78736493180799, 98.60318352704145, 36.40553619919302, 58.82768561934975, 68.36782227458666, 25.200901033184735, 52.91925500342019, 71.40387780399953, 149.24652919465595, 118.42971552289589, 50.19486775805727, 112.6886226921969, 57.023590700579966, 48.12423476881213, 155.3598300770898, 38.395256434656034, 50.058066990236526, 87.16875587955039, 44.22578078832557, 34.60473078131036, 66.62574585428611, 43.90347268380367, 113.28435489954083, 149.3057597011795, 91.63602000198462, 53.79234797080391, 8.312345991436127, 35.565284619953886, 136.57561910384976, 140.78699474577726, 86.92925406271145, 47.54169859386598, 71.45946811699719, 60.49079810816098, 85.40794610555147, 44.35885546938249, 45.20310921141466, 36.68366536738548, 35.81451460929159, 37.54089478348286, 44.896934749110294, 118.10483523440382, 60.003691622637845, 83.9657986998848, 55.97961383624707, 83.04791997419188, 41.10673445980004, 39.60139656488636, 45.48838635674089, 80.0735919952449, 95.38250432759273, 55.65961601516094, 68.92493036578841, 7.529262582956462, 62.864693064552796, 44.67950982287612, 45.280265595784186, 53.769486977783835, 84.26139801214369, 46.52785507412941, 57.8827483632673, 107.69750928899265, 60.89088957984095, 40.45821361731332, 52.96384067020143, 115.86474387368256, 52.2133538445067, 122.68066705944932, 35.76892185637398, 187.54121424805805, 88.80671571446362, 43.45654249217392, 97.25351250340601, 39.86858028946747, 55.52741947007124, 117.44642771913463, 67.26269589233023, 68.60084475096528, 60.94376218671525, 43.494986731721625, 58.801612824973276, 71.2199952980688, 97.57474513369057, 37.885307152347586, 46.09832712709615, 46.83182079203476, 78.19650785864413, 40.446619437135965, 99.21338986208593, 46.514634381042015, 82.0940154046289, 55.50954270689544, 14.688628687456898, 65.00576131732979, 75.40802235312736, 95.34758266651295, 64.73922904199348, 40.67908393215272, 68.80712814289359, 50.95996739275931, 42.001110099768, 53.443817157563984, 44.82154728300939, 58.122015592936556, 103.7241026257589, 66.51006940772763, 44.03555092074464, 127.07499301196533, 5.812427827535264, 119.59298045817606, 70.25202485468996, 38.324611867255854, 54.58417633434757, 40.368745219475386, 44.6592520624522, 70.35384839944668, 47.857804880869196, 76.10851625282736, 11.152542903186259, 13.425263276648515, 35.56839642105546, 54.581749343512705, 71.5003590177949, 43.06618034414469, 100.08561630366391, 48.069211870518686, 36.267484271052744, 47.76845968177633, 81.12046852091066, 59.062242930440426, 253.03290923589535, 84.12608779384483, 57.936862372335305, 91.48544040215799, 49.934576631011545, 4.446010748693644, 4.758321876967535, 132.9378660535625, 72.18815176605001, 41.02161789881002, 93.59294446593252, 74.34847848896938, 46.158845817336555, 65.71602972663736, 53.80043635711261, 52.79112376812316, 54.375710268930256, 8.171790117226374, 61.94521595303919, 8.222082203018926, 96.17220880490424, 154.13956777640584, 74.42668156290073, 110.28557795238017, 120.91501360239346, 110.41236784160238, 69.10322041431426, 131.5933439045842, 7.023555011500464, 46.68191357929973, 86.52616776894894, 51.95477643139989, 54.10151705617602, 117.03505028569522, 91.70531976447663, 77.49106251942511, 18.49607026910686, 5.950566523474429, 129.39762356413803, 57.54802970783017, 54.187047657763976, 6.064235537825508, 70.56040080059616, 145.30682438690368, 49.21885032937067, 54.534487772469376, 12.037474560461924, 76.31559607905025, 75.14094830891361, 67.37791504489061, 107.24090590638663, 70.48866787276391, 27.006219365326157, 106.63352246981309, 48.58233903101121, 8.00714026770601, 61.62706142373174, 146.98854060332638, 2.8903619296639085, 83.50328903604589, 80.28075891173079, 61.28866149779996, 40.004108408610904, 55.74361745041923, 80.58660475036528, 85.70534361231798, 47.24878068253633, 7.880663969876809, 82.86953322443544, 92.5967955562406, 190.2851202192012, 58.6005231974809, 69.39839065774576, 37.20945786912637, 109.71854273104138, 138.42102875642007, 61.13692927100841, 59.198098423367696, 68.04365982645443, 135.36943945197783, 90.66385825649999, 141.74423512951185, 51.947491557639786, 99.72623809093344, 17.338933791055453, 74.94589195629136, 64.7667651610405, 69.53156662963804, 135.06564721226934, 141.5540622805224, 13.43840195643446, 84.9031676042008, 68.43833324063606, 45.08661870329172, 104.38467075084706, 59.39479379673186, 254.39086881565663, 55.83841134410927, 91.13185452578823, 86.55295930008438, 81.29157844529053, 102.16517848465844, 44.34848790683972, 96.80378310078035, 96.59508951351867, 5.567634473469761, 48.966581710114006, 105.73591357789688, 101.47505933038435, 58.63459021101165, 94.65045892551177, 157.3653102121077, 150.29231819617974, 68.9892134861079, 102.18163291765485, 80.34687144268825, 54.256867736002846, 95.22610068140553, 100.19645291085452, 65.3027205430036, 43.0286643353928, 184.885173408109, 48.16447982334327, 34.21267650131063, 157.9975424813589, 71.30419534128515, 62.55310537544759, 73.66806635946071, 81.52345913088273, 7.032336931860621, 71.43282467436998, 71.83785099294136, 38.86757371887328, 13.56546822430212, 5.309688317404079, 56.34980127908283, 48.968845251940344, 42.73378380768727, 71.2414521800358, 41.984408897593944, 73.35976790191116, 46.211724401149574, 67.64010070955992, 81.16192543662203, 60.51403078199629, 124.79647712756699, 112.53748637065009, 40.29543536090092, 81.07771370246341, 42.85883621053616, 192.48755073664714, 45.48898212916565, 57.14108115439338, 119.5453379875609, 100.7314937634884, 101.78549131465871, 131.76722364151655, 31.03180797723621, 66.48917430210255, 219.65090715284137, 189.72849827296136, 71.73745047078701, 114.77420120603239, 46.33729156004908, 101.40514073346124, 152.1756825101743, 144.51310862755935, 4.095397689156454, 59.85313879115728, 73.50437149756033, 98.8986408149934, 9.67988469075395, 60.59090623381699, 82.01326530670106, 135.66225957935885, 117.3329504076108, 53.17691439422779, 80.7233388987927, 79.31584925667117, 63.59241727824222, 89.20872289357173, 44.84853281725903, 366.89238305653714, 53.8022979896646, 131.68490716873964, 62.46458211148585, 112.22398246242194, 8.73912773427841, 59.08811737385771, 94.13534577156955, 73.75438650567125, 40.06288319915959, 65.47350531961419, 132.19976709040532, 49.9589461547936, 15.274255250654637, 113.1071498361514, 55.06334964410844, 71.41219969093294, 68.1093641318905, 50.85256711305601, 58.52611683400266, 44.89964813041467, 77.9555104464742, 145.42779729887627, 201.53169451447675, 62.2433703472967, 84.29831742865812, 94.73923114378431, 100.06457457253846, 88.3107821313069, 157.07503101886437, 50.05239395382919, 49.26247605320565, 75.18219341209591, 192.40844211350338, 85.07185549352575, 43.84065086728446, 63.38189012830808, 239.2982257827995, 46.24168163088468, 174.0979466480235, 65.90500573621378, 58.02228864603604, 95.25545278875495, 124.21479927985659, 68.3131917462511, 77.08286356851303, 9.208347911241995, 58.66194344240576, 154.33428601228408, 77.30434610968263, 120.72922296027933, 99.5026935098889, 57.93555361169973, 36.696454136059394, 85.82134767549913, 76.34890392952202, 71.4774765343251, 15.313006185361095, 64.5444451285496, 9.671284579982629, 84.02849607390976, 69.52336288311226, 48.74965613057597, 9.806376900510564, 62.008688192596324, 71.74422638085466, 52.03645565671369, 58.79510064829656, 94.6040616244942, 6.432135934003563, 105.28448733550968, 43.77122786330202, 65.98713510455599, 72.77350696880572, 80.37333738329599, 74.92062849523404, 72.86857667051025, 60.21313350072693, 57.11657512680067, 182.72652254618328, 57.96398889322257, 72.67077869276217, 59.549797332282466, 86.88140512110108, 62.80674784387146, 53.73266889351609, 60.57090059590232, 57.303589319852826, 123.4182045751211, 70.89568268480056, 49.820728800108675, 162.6245166578212, 202.76605691914628, 62.316813531137925, 78.09393237888791, 86.5439293575495, 37.271306936979535, 116.73640419379328, 109.16949631957966, 151.16348755973405, 80.48800218771188, 102.27244374165232, 187.86614116566574, 72.65087824559757, 196.6726246099767, 62.31464308183951, 79.28967482201348, 146.53136965729277, 23.262336794642202, 182.49585503027868, 59.368426127558614, 30.76397266820981, 99.22414697091536, 117.34807135447329, 91.37766921209881, 70.25451008460021, 58.627460166040684, 130.6799350598134, 112.63376751322006, 49.23954712186007, 96.99379499247104, 284.53464076080337, 112.19924009147775, 37.7655156327239, 70.85282460414437, 57.1323871317944, 53.391357348839136, 98.48097026608201, 70.02201048989794, 88.43164859428695, 88.21979008232617, 169.9981564684883, 111.62995826315638, 44.20421621534462, 59.408901877712566, 96.4840237352404, 88.44749568198611, 17.102500483034444, 47.6219768409176, 165.23962843170418, 119.53782228495918, 6.351488472776844, 115.32677867823978, 101.34026075611513, 185.17659901671394, 9.23397080872119, 200.1038434532831, 68.29526105139381, 84.33278496977253, 57.41091004597678, 39.863295272327186, 107.0249739624742, 143.69830219989518, 141.8525015064163, 19.56807053749575, 62.99997257404265, 64.78122078752666, 78.65204853227142, 38.56360370826181, 92.41092224244801, 40.927547624237384, 101.89495847686739, 174.40633425442624, 42.860494805369164, 41.70182009591218, 8.971263301523761, 61.88919963403031, 86.9491184612691, 53.845060766140016, 10.632958102351907, 106.05554035082332, 212.03392812077945, 65.61749093795547, 138.15580077663824, 50.369229946582166, 186.90882449786446, 88.8645948234537, 71.28285498148226, 185.05760543729082, 80.7112744830952, 85.64972091889724, 57.8943339988716, 56.68793592444311, 58.390045241537976, 48.60220673252767, 77.48061249939305, 76.96921280837125, 108.25888588923975, 357.97171402501124, 63.33734613273082, 10.902654566096473, 106.77675083743213, 50.44833450356905, 61.381352872900344, 66.59941824358918, 78.50031640307594, 74.40288988244751, 124.88459632427411, 14.086457729198864, 193.43639703626212, 59.09311733307664, 94.15853147260519, 87.7795748034424, 9.262719709421425, 96.03314366467497, 107.5950846985982, 72.8720517390195, 62.97852027899475, 44.97572712183164, 74.80864408523671, 59.4132088946959, 58.22578652730874, 70.74459712533753, 58.62086776708409, 95.9265467756664, 61.72122958885642, 128.0868377796909, 223.50001051095984, 150.84248500044197, 200.36423034081017, 118.87733970575982, 18.351749858357795, 58.73132008787275, 81.98861494639483, 171.7970917991569, 142.46043229910225, 41.38201453097326, 110.08057568967305, 49.882946033673086, 55.03462734506039, 51.33697452907524, 80.13863742219974, 71.5746776540939, 43.247172684124685, 62.465029510414205, 30.731273130423645, 88.63120997126586, 123.27300017010826, 60.704437267249105, 68.82940995352689, 68.86203709121344, 7.484054857845522, 93.30453755152531, 103.65053304395327, 54.917259626097106, 78.07895332758956, 79.25577897651856, 47.48874026464522, 47.150938924875405, 66.40949291419368, 86.36700951513548, 57.00191641922674, 147.4322886329905, 69.51894774992144, 51.42651446740464, 73.03842041986385, 74.66348674088884, 112.56933849783462, 235.50615890834578, 132.55974620218373, 128.45410958344132, 106.10617424022597, 87.99917577772547, 171.49632982628376, 63.18681091141343, 217.42371416985247, 84.00329606882094, 94.648478306557, 125.30086446189974, 45.210752245527345, 53.91581403471846, 58.80790389877452, 97.6124054213655, 117.279727504876, 67.46251445219534, 57.44888075514844, 72.26790441175866, 52.21452490388049, 47.024065333939475, 59.98638549840384, 46.22225801790414, 172.09188109250437, 58.14060160993145, 54.457044407918126, 130.04335448061533, 82.06978073387756, 31.68071168837447, 138.91978834079697, 77.58898698255184, 67.8568578695711, 88.1785024987815, 104.69760275229473, 42.09456754287861, 67.06433872856698, 45.41674391249855, 43.08629965268446, 11.533224894352868, 51.58281386020288, 133.3575366793077, 112.37794326106123, 57.148109268400816, 84.14334415353298, 129.7295580572975, 67.89397566562322, 66.04358620535191, 169.1489351657481, 195.09310238763132, 64.96382898736206, 47.75770506853003, 105.5102166384344, 56.5826016285002, 77.60091474290671, 66.88873075433764, 58.614174030368936, 148.46849925355505, 131.4523230373653, 147.20374466194696, 40.06653201989345, 97.746776168846, 181.9018889898334, 71.87712910557273, 127.8219731557708, 62.69196868636935, 40.54659406742199, 102.76826054245964, 89.01971170013852, 108.04754038259559, 199.7070680756706, 95.47938373787163, 74.33294164913258, 50.46086338979212, 94.09854386094929, 48.74772658218934, 49.49183965887565, 84.02319089087146, 91.57146905885726, 42.729828704040514, 140.65552276232643, 57.087228158155185, 87.61508592096605, 68.72220160582297, 234.05500145915377, 70.87107889750918, 63.29062637305736, 120.24913552762524, 47.21242095214779, 156.53370643659332, 86.60377870750212, 159.3966483891154, 58.0018093596295, 152.47547975879726, 61.096181323855625, 23.94920529087307, 115.0542924908236, 189.56322781540428, 70.33760805674521, 57.19077122219511, 51.502584848503645, 172.90198273843848, 92.96533537385217, 64.86645194136727, 68.34087548567861, 58.73390235702113, 60.26470351535103, 59.64548849575278, 39.10501132356204, 14.783631007819734, 43.26052480302777, 68.6201903384732, 140.56995929334087, 73.82091559794887, 54.82126115920452, 111.52449552259658, 75.16753363094031, 80.13699870584168, 47.73966743258944, 250.29056572150964, 61.19739977021884, 39.541110914625726, 160.91227170194313, 74.99646075085656, 41.201421153503325, 57.859498641195906, 74.17849122194818, 49.693069721603834, 78.78803364383901, 61.189312290843226, 102.87121081496275, 57.58370545995628, 68.09709982788002, 44.78885795119801, 177.22614593674496, 211.51191506623624, 52.6558716751666, 60.22301143450045, 175.4005671857726, 77.21446283450577, 78.33558074738141, 214.6900414653839, 209.11734781646882, 105.49585905868324, 101.398198743197, 44.76977615477372, 37.55989923253924, 89.81698856105844, 68.37976984335536, 50.17583434582687, 321.92510392054817, 78.25779575439225, 9.050038778879838, 68.51919326427986, 261.5367500711804, 45.72071976744781, 7.360418745452854, 45.70089286291591, 210.905068871074, 67.41763413415921, 56.7902870619477, 52.920326656074245, 60.941532679215925, 64.27183246505746, 144.45628583883794, 39.31996585822135, 11.400012028247959, 13.25863680703837, 102.88126236095839, 91.29115155638361, 213.3280575149798, 55.42850532336168, 97.85810528493008, 32.71320699350291, 92.38822691090095, 57.66787358647021, 105.6930932549859, 71.6706202874189, 117.7495201044596, 68.66772120897826, 89.13353874181344, 139.98945430206996, 15.026514050014908, 194.82211011026638, 74.12517081811069, 120.60408652295348, 75.38091392600447, 45.7062629315687, 35.42662787102553, 88.46432979204106, 10.501341563700073, 352.3283653425748, 204.095812215991, 130.45254795915238, 35.63752878811298, 39.883837934771876, 40.64486015112076, 13.553325438350813, 214.81607866795056, 11.174482414352429, 63.749252950335716, 96.37408229268961, 111.55664950326899, 137.92684020206048, 221.21193810603427, 72.69679778065323, 135.36264266293975, 141.01972449174534, 99.49703120340874, 83.35136095694456, 81.69048316186496, 42.32838893516446, 193.69699661132086, 31.243292340386482, 97.04789881056956, 156.28335739755164, 151.69877790778528, 53.80148395202951, 62.88527866355429, 223.2442260986337, 273.0307734446303, 58.52841433462713, 90.23291447133813, 51.671804787198894, 58.92516628353959, 8.456137813330997, 43.53392681915274, 58.94616756907893, 130.8961468888274, 122.74018896873001, 65.16151351390249, 75.70674997462584, 38.985768822771675, 98.31980095252861, 52.804996374695406, 50.29240747671428, 173.3372131438109, 76.1652361259814, 79.5048514493565, 68.93166535781795, 95.49625691575503, 104.0031246963308, 58.90551627894415, 67.8906355165281, 152.39857564404625, 71.6751984762578, 41.8219991071519, 141.09138642898043, 92.75631397950463, 50.69050131019569, 192.81980505538755, 53.60600513156879, 90.70936788874043, 61.29423728170263, 215.27844677831115, 37.53610513502807, 54.251035550502216, 62.09694379799174, 39.171824675718035, 20.02126890937994, 50.64366028959734, 44.79730028859147, 55.97113359058402, 81.32342986451627, 124.28914784169503, 87.61247930072395, 112.0148091101083, 54.38114673657503, 53.127193976893594, 54.11263151904092, 23.57062301560085, 42.15431627263163, 192.68352530834602, 62.07426902595887, 96.60229233860508, 199.43993968351643, 129.79390977163325, 89.69300796261764, 48.803259267671415, 42.050853481887316, 142.77357894869374, 46.777598608699805, 58.47446204170538, 209.17902192054726, 91.69223086056563, 132.9955900020596, 82.24796199345614, 67.68788889222, 16.8332694863998, 95.49120422096134, 80.2657202444745, 163.85411057758995, 61.520067702338395, 114.8526240246929, 10.326242325941829, 75.6680444858211, 73.52669283836691, 168.69548088148284, 187.89362861063475, 58.83331909912433, 143.43228976345776, 62.73089873890606, 85.28198320699288, 189.0961004275783, 120.85486402292956, 79.78291201985922, 62.38328396137613, 7.451825441182232, 84.51757097251406, 233.40828377873117, 74.76200861476808, 98.17194110081608, 102.56824949740948, 124.58306404997488, 60.08106661161749, 67.84731072712736, 71.72815823569535, 80.93692693964668, 66.45729507159056, 80.14153352349658, 72.6335198114026, 44.9134344339926, 81.69358591806902, 114.01732816528215, 49.1239521731901, 45.19246816656911, 6.8132901315696195, 108.48284638331673, 80.15082737591119, 79.66958251389788, 83.96740579648235, 54.3913680442158, 88.99179025756621, 123.23663898696464, 78.95382886478625, 133.27267759237037, 197.79584074432753, 87.52958802904773, 81.4015765845694, 135.75190654385955, 64.3322030313299, 54.40540933284468, 76.13478964422742, 91.36710679042865, 75.46199754021396, 64.03630777207864, 91.21040765401666, 56.055629237060515, 52.0365158535152, 139.7098257269959, 66.45261481930984, 66.82957100075598, 141.01386475916289, 60.373423114767114, 183.14455590228422, 64.78272614990335, 14.506449131644155, 73.08043290429661, 86.70318083353592, 72.62500161880364, 33.70303597778161, 77.58418414361041, 94.52082719424318, 140.94552833996113, 45.97816677987489, 40.136738266930294, 163.13398330445656, 125.10034272847412, 127.21787128094245, 99.11743928281913, 69.373042708943, 43.94717741275196, 68.41604955674025, 117.28881459611104, 25.27555182147373, 63.70444509656064, 66.9912540003081, 80.46376417595236, 155.98982336960358, 64.49503249148297, 79.8975306933646, 143.09516470717722, 54.82441412424907, 45.5519060626322, 86.13643332537664, 165.58367873772474, 97.1748693030914, 12.03549697449105, 71.60327476598357, 78.47893122895381, 63.39772100581489, 78.34828649592058, 113.1087509261375, 66.35981560021342, 72.63019054919793, 36.596886949600325, 48.66264765362546, 97.68848655466182, 113.21915043147276, 129.03412729313928, 51.357121541488624, 51.901760505765466, 227.98078457141213, 104.42480035398262, 37.34541226448467, 77.52714268869205, 59.57667827351905, 9.337684649278643, 86.16155452344059, 221.53899144837152, 98.01792395210393, 72.12255999309951, 143.71401307120175, 66.47064117</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>112.2095406150818</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>68.13062484665633</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>[124.0470962524414, 62.17881393432617, 182.22433471679688, 108.7799301147461, 146.55189514160156, 82.53931427001953, 79.67486572265625, 54.97074508666992, 59.73379135131836, 21.535446166992188, 17.63085174560547, 94.80231475830078, 106.9712142944336, 95.52789306640625, 66.38414001464844, 56.07547378540039, 147.6909637451172, 96.76985931396484, 80.27373504638672, 127.1262435913086, 225.6326904296875, 69.50129699707031, 54.974021911621094, 120.16658782958984, 46.92890930175781, 63.97251510620117, 69.55636596679688, 42.999515533447266, 151.23892211914062, 72.09327697753906, 278.3799743652344, 143.71145629882812, 139.65452575683594, 102.4893798828125, 53.99258041381836, 159.42381286621094, 11.760284423828125, 52.29745864868164, 172.6008758544922, 203.1627960205078, 96.9002456665039, 106.08184051513672, 140.292724609375, 210.3992919921875, 344.2892761230469, 47.768638610839844, 244.9041748046875, 179.1565399169922, 74.48597717285156, 141.63851928710938, 207.7462158203125, 72.93447875976562, 14.993000030517578, 104.1656265258789, 7.667314529418945, 97.15251159667969, 10.034051895141602, 148.97901916503906, 246.16323852539062, 20.872098922729492, 267.87701416015625, 81.27671813964844, 60.178009033203125, 57.43025588989258, 114.2837142944336, 96.63896179199219, 78.44661712646484, 54.89338302612305, 137.9124298095703, 88.775146484375, 86.16093444824219, 106.36314392089844, 59.19734191894531, 235.592041015625, 54.05049133300781, 86.73017883300781, 246.34886169433594, 59.735260009765625, 61.3568000793457, 138.55210876464844, 94.49560546875, 191.5329132080078, 105.0457534790039, 107.06875610351562, 167.26953125, 57.81262969970703, 162.57070922851562, 246.54515075683594, 97.76509094238281, 51.61533737182617, 58.20122146606445, 136.0362091064453, 46.91468811035156, 57.178672790527344, 155.3135528564453, 248.94119262695312, 156.07862854003906, 115.60499572753906, 43.98484420776367, 186.52821350097656]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01456</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:48:15</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>91.84221549681344</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>73.04964044433083</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>106.0012728044124</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>4714</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>[0.236359759124361, 1.63349889671431, 1.289876494933169, 1.0843525487110521, 0.6845618074892307, 1.331738663125778, 0.3833507230049607, 0.6312304530764017, 0.697632705585977, 0.6426903915154207, 0.7106893637664466, 0.5198433668900411, 1.1063977951659496, 1.1007106284751011, 1.1810815424524148, 0.9236816826762472, 0.9924151419732464, 1.2068774492865364, 1.1982089001130503, 1.519706707511459, 0.5629042171588169, 0.6972717391824469, 0.28181243444787374, 0.5947009572130064, 1.3535849805343554, 1.9675704610721627, 2.080084019194682, 1.259560782984445, 0.8620046541154631, 0.8376686453133486, 1.1531099096879682, 1.5247681286570196, 0.8367122107300579, 1.1865951592774409, 0.8862946123921658, 1.5154527122861488, 0.9239152413579884, 0.2878301339005117, 0.7816109020763302, 1.167951793376199, 1.6803719334922669, 1.3900830331075003, 1.1970717878137587, 1.2948064466054645, 1.8960695907720788, 1.8874745779324102, 1.6310806790229526, 1.6513748094354013, 2.3800556107767936, 1.3259388375225079, 3.3550568213713006, 1.4465701541861538, 1.1760091338828254, 0.7634190833786612, 1.8138831984342407, 1.1199923661238262, 1.9008845913857695, 2.916150711619465, 2.376510457952556, 3.93973656373904, 0.9897167593568564, 2.518666657102524, 2.2866344394579947, 2.5233772110260104, 1.8579560097444707, 0.8843560865786099, 0.455526741774328, 1.310605646166755, 1.5892889436265558, 1.4713921219250667, 1.477417225501496, 1.8686285400892453, 1.242331731499117, 1.902526250774081, 2.394701154042023, 1.658096673159479, 2.126637212026183, 1.3520511090387182, 1.8476411409596818, 3.165121233473976, 1.8158077519164664, 2.18110211896731, 1.5866541251953776, 2.4343399301304935, 1.6365687093355488, 1.256862830073726, 1.4278113409494224, 2.8857371359814628, 1.8248240986240145, 3.465642377379473, 2.167293136639459, 2.6795882931767707, 1.830541807940174, 2.7294342966910445, 2.669274147317443, 3.1419492655062267, 4.9248705885048025, 5.108922325111749, 0.6410956005455162, 3.0811865878737295, 1.1938385657961323, 2.901931082296518, 1.7700403721089493, 1.851712711225595, 1.6948866193836098, 2.657980394097068, 2.300020513886023, 1.8188922510273713, 3.467317959844077, 1.5168701550767876, 2.8704434370872245, 2.98415674426905, 2.34186553258945, 2.050077422450151, 1.4820177324439974, 2.226818356263895, 2.051219059719363, 1.8161096301446935, 2.6339888548747616, 4.07703905327711, 1.0097850820655672, 4.327925505190509, 5.49749270133917, 4.0388622490337225, 1.0785613465778645, 4.870853283746703, 2.8110004164692914, 2.575448529626246, 5.480243507237242, 4.543575917095163, 3.528956602050521, 3.595341786882996, 5.063470626255651, 3.746017904135936, 5.957878206702225, 4.134126196966577, 2.0565552571837156, 2.7431565974012115, 2.5425951041732775, 4.48132166941032, 4.6554145796299755, 3.326658356979008, 4.628753507486957, 5.6609567119601625, 8.472556893368164, 4.677926280999277, 2.3968738546394985, 6.4881250971292, 3.654706005500939, 3.183056485543115, 6.31187865843853, 4.1926971833725775, 4.025958604949581, 6.555164600527678, 7.246240973961165, 3.211914625306406, 2.4652183881645535, 12.712006437922435, 11.082626696649717, 9.164909671278023, 15.010518118058108, 7.599019845261059, 10.121854424397457, 4.000529795023066, 5.130077389935059, 8.203614942863432, 9.02565823778184, 4.3662514959803875, 8.17739574223945, 0.78000547587233, 6.06556302238905, 8.53502191052996, 2.7558694385020837, 5.177088722596665, 10.140446538260655, 5.9679183316218385, 1.4277260197048443, 13.777964070757683, 8.22377606669635, 15.186848352699947, 11.483784508296978, 6.2325983215215315, 8.212532562962474, 12.428132863746269, 12.540116564833056, 3.7677615850896715, 6.975377073795541, 1.8160113978970993, 14.83453997898065, 10.436267532793893, 9.928081895155447, 8.116836698426837, 16.873539615359622, 6.037238332254372, 11.603567618022462, 3.7843136685557703, 16.249809577843788, 11.427141844032395, 22.680194532475657, 5.357452222092002, 24.260119915502102, 25.269965471750034, 21.88088718705448, 13.425180491922124, 17.23790268021542, 21.720652286732797, 9.871380718241271, 9.124616758436098, 15.0272360316412, 10.340355846721009, 11.786905637439128, 16.251109903227555, 11.067702115792072, 16.633959574828395, 18.771678762581647, 34.3160594742323, 25.81858435635798, 14.043611710601729, 3.5242611562516624, 22.050055374366195, 3.9584184904055384, 8.021649936052915, 19.209628673218994, 8.812911903362576, 24.870967695216837, 6.905562712652328, 10.286384148507054, 16.62206248293623, 34.317473609348724, 22.341848418949354, 15.088676456694602, 15.82972012521158, 16.588424718002816, 24.949110391906142, 27.428513758336845, 18.175737247230966, 34.612766565372986, 27.741252413266103, 28.676437846367175, 19.487345912425894, 11.005475763666238, 29.251243172219542, 16.0639753595335, 15.598779377507924, 24.38324108985624, 20.262574262144458, 16.32577324991359, 20.110118787368826, 14.339974135541036, 12.818734015473613, 18.047423348673263, 43.96072046258492, 25.902678926138826, 23.93461199895014, 13.65264994923424, 28.630406847113232, 25.16069200212319, 48.896031517159166, 23.81971497633848, 24.206471924715594, 11.659323827576946, 19.714824374460587, 39.5741698441837, 14.746375245180092, 18.568357705919443, 19.852769274588923, 21.989093784559216, 30.544195920403453, 19.609482340879712, 40.013516930149294, 22.071098760520933, 30.61003861487966, 60.77752099200241, 21.629484955622733, 38.28704439921319, 40.753296146232344, 43.83535350985734, 15.718396940949381, 23.354044701409727, 28.74165002934921, 27.800304018752453, 28.064560561654783, 17.862244048018656, 26.98591916477973, 20.342171437303676, 49.78886348836079, 26.29071692557248, 30.783413647083584, 25.38604061155474, 40.526754913213715, 53.05496675740923, 33.877493457881044, 50.96489097333112, 37.75006286681943, 31.56989689872105, 20.895257686842378, 54.66446961397804, 33.146811911689795, 49.531179956543646, 45.941479951515014, 36.892144552297445, 25.86684260872425, 30.78573691391218, 34.666573232285806, 31.718915073057463, 46.318181190884445, 12.820642763034279, 3.773393970336342, 27.332079260972098, 32.533456586883645, 34.32637812758542, 39.26522065667734, 51.19873686879282, 22.708709529592394, 38.92648782499791, 50.616693763181864, 42.00809305429704, 19.495754487589718, 20.225342294229236, 27.374786813090786, 27.26131376960539, 26.606673691290183, 25.168094694076945, 32.86615961262699, 58.77736978164308, 35.31513178753947, 20.24920416375456, 29.146344175559943, 48.166360537414675, 34.33713318741967, 27.13745576292458, 61.24850997113503, 23.741594562312926, 26.399586987598724, 31.24716594853992, 16.229960082697254, 43.22719838804785, 51.639761217953335, 26.99924575796258, 5.495638886593683, 44.08428609995514, 27.296674875370883, 61.765327630652116, 4.2372865221890255, 28.130148205817214, 32.09343091574941, 40.63816841934873, 48.31923587911762, 4.977356296544381, 26.178519229504936, 18.749694290849853, 45.68156573560886, 59.985629992209525, 38.374132394573365, 67.38503565841354, 63.37966562477671, 47.5789946992344, 42.93283316932649, 22.040249590075202, 35.37692257405422, 50.40773463365928, 30.188938639729844, 84.14953237609146, 44.88583791519791, 32.20746117680004, 49.706878865139494, 37.33148832805368, 35.82844412764536, 110.02885464274144, 27.42623600225011, 56.24488620667048, 28.51825881125928, 36.27408728154065, 35.515912127297, 58.04731714687408, 58.64859621735158, 31.609149231843457, 57.10967964396703, 32.05920638705996, 26.108535043076508, 45.18494581482114, 36.60497032050619, 40.076914819323754, 24.74430328263931, 18.978776876943837, 34.11979913202275, 52.23007178078481, 33.27572061679267, 70.09182592487751, 40.721975064746495, 28.019150408099925, 60.08155321579547, 105.13546268089884, 26.446886979516044, 26.828165262967957, 53.208165429079855, 13.059893058368125, 47.28089276784163, 30.631181388484084, 41.49471725533381, 80.3589919558161, 35.443010356411904, 63.3636230049537, 4.095249112635334, 22.82879396749983, 41.762298529143685, 52.50934849272832, 25.852657998456003, 100.87743413772202, 43.734266617735265, 48.04528324978709, 40.834024529328204, 52.581250117841016, 101.90427303023559, 36.99426312975125, 45.458114526584204, 71.76212232375713, 50.26675978343408, 76.14299899432972, 38.88147068711946, 67.88002456868627, 43.02859158425002, 52.22498639866512, 100.40871216916302, 30.627726522715744, 15.346712498482203, 40.384675295599585, 86.46086804945644, 33.611481636836814, 42.27135626840105, 82.57720176916195, 40.33119667341433, 50.43867343334237, 40.919579398707626, 50.25349983319686, 83.54521218647324, 63.919869063360096, 39.46829457948446, 107.94937591065755, 71.18581083054237, 42.87318491811819, 76.9428363883806, 133.16090140320807, 34.560105707349905, 116.25100302097907, 66.07574753423354, 55.59290440252251, 98.50906752606795, 64.35402902754592, 68.25285227276295, 84.84852406155785, 60.37701112531041, 75.41590331153809, 57.73723937749704, 42.85194030013443, 37.53380444504151, 80.47994116875417, 97.80293206441277, 79.17927336655634, 83.16430039275654, 89.23834585673913, 70.51657218892106, 44.48913785165419, 37.76062409906226, 41.49240905120208, 95.33892209060897, 49.41052821021741, 37.30844036387726, 4.990327391988079, 89.45468389690507, 86.37940699716772, 37.93660028410551, 47.32992698896487, 86.79253853300827, 36.21927325041902, 58.49764437588423, 68.25917322444488, 29.052995279839223, 64.4290010152704, 100.71027688612156, 47.877584415735654, 88.87386587372825, 9.880544057357087, 33.02825423859536, 94.88300106364778, 35.965609434534436, 79.77203411202149, 47.65828474198825, 58.02040599200052, 52.38182892770105, 27.127089779995764, 50.76692449416711, 42.62779753706324, 60.1913654477912, 89.53723430525984, 41.86060092154588, 27.1476737710249, 78.67166290464542, 51.3368229576142, 56.384059226952026, 179.63574917006466, 38.97621730219421, 39.87856450270319, 83.89244599775321, 49.26041791928052, 54.462039276520095, 72.6869553793468, 52.417013939596636, 53.73438195865745, 61.08380082470634, 74.05685005521566, 67.6190250259457, 55.76841171255502, 56.76337328299359, 45.14430311448846, 40.90677580446926, 55.525515670535285, 36.54297105224337, 65.55022993766204, 38.78400694589776, 87.32727310708712, 44.7785211295141, 46.59324954646389, 58.62933537709263, 47.220880836196166, 68.90579662749128, 47.86119737594672, 57.2643091297333, 59.97592803970653, 40.7076343105093, 30.21134751746413, 41.44552344016867, 66.12295909816268, 84.49542312969685, 52.5135226337938, 46.27183508002973, 104.08042492192433, 6.409625463329137, 43.73655090840282, 64.86716225740683, 126.56201272054119, 91.03985097946213, 38.60673529511445, 101.98825992344608, 87.63300968132354, 156.560241954311, 57.56890863215113, 73.78497209670532, 54.27545978749593, 17.087252845062935, 75.40140522119646, 106.94592625524938, 61.01733602978996, 40.597668225258786, 67.96776227262896, 57.19300896879208, 52.096069915557294, 42.94981803874543, 63.72962997760782, 39.28468884392899, 176.5142238997568, 4.565054095155829, 37.48307979353126, 44.17820035851251, 126.20172836170985, 48.56263964489843, 70.25424752091891, 69.08036340242481, 60.75905496271901, 71.59744549291305, 37.175168638302544, 75.50966331654908, 49.69180274360869, 35.10846181506025, 47.54671169460477, 40.58591804001007, 202.11565728284216, 37.286528291592084, 58.434914592120315, 42.08132847438943, 45.96541728061859, 56.963714713337396, 53.72497713873999, 93.99731598642356, 65.55914800177806, 62.747323612643775, 81.08856106725041, 44.03059979416229, 56.17328925649889, 53.04515268267449, 49.79261936209356, 221.88489107725792, 45.257671098901284, 48.539814533834594, 68.2245769141465, 98.08730523315047, 73.76177929673612, 79.60507566882197, 59.29092527439423, 69.00670412532736, 53.739550669195694, 55.138095101504824, 70.15421882563585, 73.23318483617365, 35.97116426691504, 72.19001302615966, 7.277692555906523, 169.81737015724408, 48.631187508948216, 104.30093072679311, 256.4203916475962, 73.44409505549667, 129.87141815697913, 47.40716067173896, 96.47426864155953, 54.350889803974866, 38.90335035814026, 54.61075092828857, 104.27693420060652, 43.29650757235034, 47.116808600464886, 50.195386352737124, 126.73859428875132, 59.047567898922125, 79.7887536395784, 62.243079083595404, 8.803260340246736, 68.92690284662487, 101.21398561235641, 67.28156135171072, 89.19310455100114, 41.60724139729567, 43.90239844784988, 67.5122844408957, 59.38619745263856, 69.70969416725939, 55.68508874275735, 64.02191008097648, 131.47180488503116, 64.98886017935563, 75.05060520058319, 62.43026524323586, 41.326918937694124, 88.60927306440757, 78.26282954035345, 34.74794058043268, 12.037181459453198, 56.64615783318256, 50.670517466914234, 63.98351524697051, 73.07893538318258, 42.65576270361307, 52.43668747731037, 65.96977116674967, 60.71922464714788, 54.178396943511125, 55.414596199130045, 14.765546071432194, 14.290394388409323, 104.16661598372403, 71.01209176192972, 38.05570224109452, 49.89731688459369, 116.9348653254425, 56.22426366484891, 50.17269363052887, 114.17344830725125, 74.04124173088849, 63.12480548846861, 64.99328442130152, 152.93407456819602, 61.49624266572478, 59.17562322156593, 119.69276271637975, 32.115501764329366, 41.02932314750554, 74.3629071005067, 44.78575086649068, 68.19783605617735, 47.47066328584819, 69.42750603584084, 6.834542670295435, 49.16387469996625, 52.57075278584991, 115.36596722702201, 83.19113204620905, 58.21265358869263, 120.8003524865296, 79.41709683973237, 70.05887797925172, 96.46219350304936, 70.43726799561482, 203.5198895177661, 52.504376490908655, 84.52134711290766, 108.28421527032064, 45.070252715641324, 83.31648542211602, 53.57109642904082, 51.628947257362995, 39.79527735065238, 44.13753529693419, 74.10071126971583, 83.22050002171025, 129.87180950123562, 48.59796499456283, 120.00548850282227, 48.157786105232624, 78.45066535466422, 60.662123801927635, 79.37368534371251, 44.94702309192861, 168.0490775889224, 48.60377257625799, 88.99026397911295, 120.90337420490704, 84.76783981649179, 57.08285843555545, 4.887398410607065, 73.19582523797318, 99.42012928929833, 58.8375241038576, 114.47027361294037, 7.668184415851613, 146.65801583300987, 8.935545775709542, 50.801183173632296, 107.96837351897697, 67.20403574872098, 6.527221264528329, 133.37883166634188, 9.918063033351853, 46.31838241726392, 65.91112516699052, 35.834866073770044, 41.48390918491793, 90.74669836159019, 58.529230109554334, 90.64154406187988, 47.96885698588875, 50.455453062678615, 105.85693627268046, 49.110150681632064, 181.9105690304677, 78.84236389521409, 76.87427564474896, 142.42725324416767, 122.49861882618215, 147.9299169601675, 63.797474528815606, 67.50288849597798, 54.23114075344537, 124.60006403324772, 33.41120464639622, 66.98602280981315, 58.960382609167304, 62.75804745200571, 82.35549348150927, 56.812281556568585, 37.561220728209626, 111.00857502061154, 75.83543193804675, 39.61829992377705, 39.06820051206464, 52.007620215303284, 56.78192301712205, 49.787302572922364, 47.26877202871428, 39.99874945717452, 70.92360738182043, 82.76932694304652, 53.718851455822936, 58.588712061459795, 123.11339003808953, 116.78159968540136, 66.49305781448761, 73.85684570087028, 69.18208315519458, 65.84074770791025, 82.03621591247834, 74.09424829278697, 44.87330086921555, 76.15802251063789, 76.39207259776107, 64.04167070089326, 106.49787705219654, 58.58351951456523, 157.37793074357796, 68.68548303793436, 53.22826885595214, 162.86568043663, 63.99145208221167, 7.874347005349081, 86.7396998557833, 65.322025671431, 66.62609414767607, 67.89241781970294, 79.18051915968951, 125.29140976030658, 95.10819206269288, 57.25057493756422, 53.826260698461255, 52.86560736143821, 45.778120437550534, 63.73232298991156, 230.7691488995593, 178.87965891439077, 76.53348326999954, 68.33676877904456, 75.34259020201262, 74.37724008817612, 67.0985540930707, 70.4448660533156, 86.79001360241297, 73.62327773815767, 58.20456442593179, 56.41283503131862, 63.66396777179001, 75.54151521605172, 183.030594885122, 149.442908033239, 133.3238496461265, 50.68192529328845, 73.44282116536264, 95.11753411138292, 195.98391949792543, 130.80301602801094, 104.6662328182878, 110.89629063278278, 100.41545158134825, 64.97568152588163, 181.91440600168013, 60.72617720451882, 63.78309148467295, 76.61320906931748, 172.1680550394382, 69.78644386264256, 107.49436508097011, 46.54513628201187, 250.42351532850114, 7.709317685430752, 32.223602993930555, 77.68528396389071, 74.6018326378846, 66.20657141305921, 103.31032492588119, 70.53950046043781, 13.715623590649924, 87.60658852472169, 75.96869951494446, 63.3938564312815, 44.05871685903908, 48.60422677457034, 51.91153597070076, 57.35526887336053, 51.74107119200812, 76.12638874530558, 70.08428426393978, 70.34468900189064, 55.243869973833206, 71.08045306568951, 52.87188334790371, 6.259665876588072, 56.60077902655585, 43.82865381678443, 64.82228188930705, 92.12899886639008, 72.59431150032773, 4.643761300297709, 140.0592859241596, 177.3443365553589, 168.90080059454948, 41.548761742059, 98.30512060711337, 61.006313838257114, 13.378728410723893, 81.51704689474249, 16.842794919877313, 56.116302992852965, 142.6030737703517, 63.76751979689431, 58.53329056059838, 59.67747927515366, 48.65277860453536, 103.47809233005674, 62.61994883915314, 57.08683250521409, 47.38633868331913, 63.55792574754973, 108.98648813843154, 62.89920527775208, 140.55136119680782, 80.5749978434342, 88.89036298026413, 5.540252614773635, 9.924644052508176, 131.19337325468234, 100.43368197037378, 111.17238821033057, 50.147377712271435, 64.09596898410922, 38.89587999093662, 72.38191900397103, 65.99366926810025, 8.576751153989088, 98.64215392813901, 187.75457465793806, 81.53248732773791, 61.75759715915144, 83.20437266248744, 55.67777822242012, 49.70755109354199, 258.77033487282756, 108.94406480729083, 103.0164652205815, 101.88085136836862, 47.06179670897827, 7.152187312214803, 208.67599407507075, 50.53096085117036, 84.83385556830409, 247.98229827909967, 57.30892046759131, 155.29732813832837, 84.90483730458234, 43.24043588159228, 103.42632761909452, 50.79944838090315, 94.42020125069392, 63.14269174392058, 49.65383973231707, 107.2807816159736, 123.3330148544538, 86.59669293331804, 114.05603259336138, 67.73473886204812, 46.19873590267691, 71.67503888276198, 108.1307325111304, 61.48530378028816, 193.83973855742244, 74.06269718039938, 49.878168389926515, 60.361016416628814, 41.67631087514603, 72.6778151496503, 162.52313089243174, 63.17343592175139, 71.4324141760983, 79.16999560414041, 59.81232874505606, 76.33535501120065, 58.154615171240366, 6.531703445879469, 47.7605320902846, 131.08541093797885, 89.52815447025094, 118.31499477942971, 83.80561890238124, 71.68573814715273, 76.14593334356815, 9.48660168788772, 77.75061874830139, 179.0516658532592, 60.77018575773715, 54.51531143389964, 171.37945831221597, 153.25072706664037, 95.89498280690802, 133.06472345734318, 151.28007753450922, 217.31934841199867, 54.175403482121254, 69.31349733355056, 88.95805933790794, 56.49225916336985, 46.280484939174464, 102.31999924171218, 5.993556161900288, 115.75250413281174, 64.08571116143662, 58.748230932830076, 53.765431286467006, 101.93088572884423, 91.93707687398039, 74.08568305774983, 11.461837069777403, 47.748361273073535, 70.59678878596142, 56.53947522279106, 5.821968076096207, 70.59430347539882, 6.332188164100786, 106.04452507272222, 156.9699377615683, 54.538972533412526, 182.4618254609779, 37.16501857370076, 49.52979823783885, 80.51257631828659, 96.28895357204067, 158.77901163825288, 79.14480640118829, 175.4111077193656, 72.55389528380834, 47.06450404128164, 53.06670612956017, 61.394517572849274, 64.91391445862864, 66.24294936057639, 78.85259336611117, 47.40822263522229, 68.49554382786573, 47.346264624056296, 46.65041715613062, 118.31683660130837, 81.3871007442674, 14.43537237584546, 50.54251014251401, 88.75489974337493, 90.30184513255836, 60.90406606560035, 79.43844470398543, 273.1765067263515, 83.28448899477642, 55.94073195914779, 81.13594431055682, 49.6689208553292, 55.025546855276204, 105.75876993636125, 48.85913768979757, 185.85482800190255, 58.753661055387944, 34.903031524909146, 95.71856637507554, 87.64538376612222, 53.74488790031881, 68.92519623522611, 62.18729477353025, 172.30955137213965, 159.8817243179316, 80.01844464695853, 79.22194109924396, 59.374015476605614, 161.60187284015828, 94.51024318439883, 63.93353282165878, 57.27417824907878, 69.93294933034564, 44.71676721135425, 49.66325132804566, 44.1163967076134, 96.77568354177349, 50.63398099047171, 69.74162721285455, 74.71103029054021, 81.79502276667907, 179.471884119915, 63.910526987463825, 98.64371201449661, 181.20876624702066, 76.59063518051639, 108.31928367278167, 111.77586722359133, 65.42792837550274, 46.53248759543725, 49.84547557491208, 68.55379180397672, 211.38575068570168, 162.402326455319, 131.88949801305688, 59.446912574968465, 60.1178951428345, 75.92974739545973, 185.77961549755048, 104.38407337195142, 113.45110777681452, 80.60099533507776, 10.82331568434587, 38.13214192145036, 59.84790664820651, 72.61098959087559, 101.1475910475114, 60.84880994115586, 87.02370261055145, 32.821845636504925, 36.58035578335364, 65.2220374366774, 145.2562302546629, 168.96371024764196, 7.216766841311671, 71.79779550029252, 67.50946844174635, 10.292859168251491, 55.696437842588146, 55.93404589558354, 98.7296249692224, 53.556951623727464, 96.94348738193848, 43.98966175666765, 53.70665390103525, 83.20642833587465, 52.63326585335696, 53.264599679178154, 82.85581518903844, 100.61609504763051, 43.52707549081175, 56.99614028351549, 108.41831523760364, 87.68225585520652, 59.23179782100993, 40.515751480329875, 47.23541192008978, 162.38668906315834, 46.786014375755975, 6.010557513499666, 75.16563270555093, 143.18462613397537, 59.326253741510214, 132.9696308877617, 169.1943307705846, 95.51883697672656, 48.25016800678763, 88.57307782533559, 80.03633331692772, 88.9259831371286, 34.96379571079734, 114.99361984308183, 57.95067001072702, 50.11560335428308, 133.81767805261427, 6.5540547030723735, 161.17285662918206, 85.09954026548546, 59.43176033714125, 64.20898000701473, 65.25608341832486, 105.75241715476038, 42.105687599015, 144.49061236259215, 72.65562341553473, 124.19908890078388, 80.17127847258857, 76.74139166332904, 63.14329105025707, 98.36684878116044, 54.43457477907097, 58.84332058066428, 109.96505937646576, 94.43143762148009, 147.22094264489812, 89.57969824362034, 83.32462108553555, 66.4383335564311, 72.83241014416686, 41.98065980901488, 86.89004250804561, 71.81220456588302, 9.312262123684132, 56.52646839383177, 65.34575581525345, 104.03944679774452, 63.24635903771686, 106.03139859808168, 64.94357525860549, 96.90065941763534, 51.96393676933893, 54.10187565241918, 231.05802264322406, 82.34787102489507, 59.317172793077354, 33.264944153535836, 124.67055321357287, 62.650255184647634, 60.733518538153994, 12.520887743433446, 95.16289960990166, 33.3564751282431, 81.08037563891064, 93.10405768189258, 45.7320485346706, 65.50083303100831, 116.6532584289784, 57.93596545307605, 371.5374938047795, 58.42057060608874, 35.49053706855312, 64.27928111320256, 54.35851848565188, 121.41714335256222, 46.06067224857589, 90.67736454559184, 48.28154045451372, 152.50516013655186, 48.90560821975922, 105.81819334537228, 118.79585530107269, 16.886883658209737, 87.79906610766257, 92.18356906161918, 45.6279481051609, 40.71977518517374, 61.322846598572724, 49.381525584984615, 66.08532508930472, 112.38150572095148, 62.348604774146246, 55.54228912246663, 155.70887429314232, 130.92553340667044, 58.82229200647108, 58.39698257498809, 101.00368882406771, 234.71927743435282, 57.46724773522557, 114.12936104456718, 47.23141859025837, 61.96147737622276, 35.34705418362103, 70.46862239506079, 70.30793875823515, 78.02976629955896, 59.76974609704514, 119.70396777609774, 73.20823946129963, 133.46274918378666, 36.50959079630793, 85.5894680679861, 76.70477832305082, 111.06189909670003, 61.7610878208043, 100.81689941098017, 184.71073165192124, 62.86248887972677, 101.74534523619478, 63.64523454868619, 53.84072703600971, 179.69889175267343, 36.68963790271843, 56.409103783430915, 73.69411096933236, 38.50485611363008, 43.49351257746276, 58.30909968673342, 62.68497260968789, 84.40621571518926, 91.34175506212145, 76.19153829235351, 66.5828929814602, 134.75369791367902, 43.859659341030216, 39.068026025167214, 79.48839526711161, 6.986600889205308, 170.56078684916736, 176.84063673948003, 74.3240087818919, 193.26257155733734, 62.41419620612265, 69.87113055442357, 99.40607600565065, 136.65593944186963, 41.09343548428605, 57.97492605822795, 50.40318460476302, 107.36781804977808, 58.849009824814196, 17.36509006693752, 144.64436014228616, 213.9740730420635, 47.26499959859592, 69.96227812410191, 65.74904263478325, 98.39386793556207, 24.909908118425072, 153.71276385159828, 78.32698207027642, 73.90766766770749, 72.82243576298997, 82.69544797275604, 79.49600213669865, 480.2164725828906, 127.33107536678153, 194.1333242618581, 120.049369235856, 10.307923821055118, 40.110699835973676, 44.88317336293832, 47.68894338380756, 58.41453740266684, 13.31957263392741, 68.62259568239091, 58.07173169855156, 41.818384866175805, 74.53158526438412, 160.81788842537526, 89.1850853823371, 85.49551566166103, 63.37866133730133, 44.85024565958467, 111.4248789788602, 158.21192895886293, 185.43681278060808, 128.93186434271664, 40.52935439873042, 84.72652093219158, 62.16102912406774, 173.83241063976217, 288.78021077785337, 64.30511827780549, 49.37525779755442, 46.433632001746204, 226.90664663357313, 102.11179774083277, 50.24113786841336, 87.9359397487445, 335.02795155111914, 98.53035024559944, 56.62340006025193, 64.95847890562627, 43.054148266309426, 43.93612137827346, 61.90310820680041, 160.8388877702367, 74.0306035346049, 48.0644690147024, 60.5111351796964, 93.35995130670419, 37.34505249776273, 183.1575829233062, 127.72513079293087, 399.23001021406264, 73.96478999337961, 68.30952124633812, 90.09309737648076, 54.62839161035382, 192.11047629755416, 70.47769029650756, 68.7503718164595, 81.99874660039988, 23.36078193285945, 81.2598639929806, 88.13367558796502, 49.24793078327269, 116.20503376130625, 95.48923693288776, 96.90353915850919, 126.96406227341232, 55.93201905161286, 297.6207314051291, 137.39436561990374, 41.93139805209554, 58.944915695807836, 116.94628053485046, 78.18856407254324, 91.47024507579583, 117.91029592015616, 92.99093357419565, 67.5080657590031, 38.18149413374544, 123.66001003251995, 66.07998587618991, 15.053688913791998, 113.9970900295491, 54.158338903285916, 43.637201290914646, 39.64880746811775, 73.17368427118662, 48.97366575497863, 35.37347296390183, 63.31440938966809, 41.58818186383472, 60.44495439737891, 11.779797392922607, 171.75727823291126, 61.79745176125276, 66.87495488902765, 40.462557935019106, 113.28219193778533, 57.261951458963146, 137.70401225100832, 43.06270607768411, 140.14478226907875, 57.47050331467589, 72.21483114629363, 53.08318064392429, 86.05457883669698, 58.44202350521031, 73.60801101199479, 192.46744390961658, 118.46440299649207, 122.63587611996397, 65.095746472635, 145.6527365150416, 84.55616652865686, 63.709821631385516, 41.97810545951931, 52.24958525839925, 45.001987518838845, 60.40045550947132, 133.08923229245207, 60.306724692403066, 137.64437068027766, 81.77387074182934, 97.955108227585, 90.54076438945789, 56.947774579182095, 68.021396098418, 187.1864801691672, 120.5227775055408, 78.4290069747269, 49.70035843781511, 131.60819249655998, 84.1238995750366, 168.4690978187755, 142.83472139274716, 133.37663200606394, 100.29515275998685, 46.38654114247408, 68.42165259303935, 211.26770431992426, 74.0097006493772, 180.211714381378, 73.3962423413828, 63.6550807984612, 61.5959402383086, 87.20160589931778, 42.62924313848583, 147.62546383803254, 67.67379266358861, 73.3739764493283, 71.75467251692982, 11.612555426096895, 90.32929283895812, 85.9671060931575, 58.803680239750875, 54.90702770651708, 62.98432074134555, 53.5325445738054, 75.43619277402344, 103.32384418179377, 99.92404013927114, 140.81476101350464, 59.16103870643365, 101.67910152838046, 129.1463517636677, 55.48481131926431, 72.50431018360335, 12.146805974872862, 75.78482088003442, 129.01264032456862, 72.39887901375192, 79.53790910744733, 56.94302874251708, 56.77854846251244, 254.20025949031074, 62.24822406877635, 91.79377845188105, 46.0695335682028, 89.50537136379046, 84.27058420512955, 56.64338821343767, 105.82715906600947, 48.7984481295866, 113.84750152302598, 215.9258183848584, 56.0435596831288, 200.3597013479937, 107.50606819704792, 46.84932834054321, 127.33826544413769, 136.74775284697122, 97.18929569011368, 53.064388855691305, 105.15502686746454, 105.48305532708059, 38.146694360345045, 146.00472336291338, 110.53768328005232, 72.4839661246833, 15.178576674269841, 64.93528096850136, 68.74806619419196, 58.13536541883797, 71.67344875032016, 187.79397254996866, 180.7347942761136, 53.25429624253673, 62.15295806562504, 99.32039295407544, 71.41816457571616, 52.89754263606654, 129.6690280872576, 491.79380506466214, 128.27076644647545, 69.26688622484305, 43.7039267838163, 84.91282234413843, 91.94561759436148, 59.92160675070156, 91.30967141860519, 67.01396543522178, 6.128035724080609, 65.1176471702908, 83.33550662729834, 16.63032390422738, 110.05179057199294, 47.213543807600104, 54.09712487173697, 21.312264265888526, 60.95707681792409, 76.80078213054864, 100.90614895530906, 129.30954904804543, 95.94290666679363, 69.93493715158885, 33.04392850896288, 54.75675411446936, 68.589901291184, 80.57199372320021, 82.63551121454387, 57.54936933334234, 111.39917358798517, 124.26503971171505, 87.58347575257852, 85.11728551009857, 83.82513978629385, 5.881203949516826, 310.1905618093453, 44.20803431962338, 47.18918018481346, 69.35856070740674, 12.420670945490647, 105.26613304671689, 288.76850715682326, 112.21093838123267, 140.02551404351223, 143.28934807470532, 251.3469055888302, 97.28411456527387, 9.093346333093955, 130.09181433740105, 61.60159682514935, 58.53274764637879, 196.11716066667435, 82.55072654833579, 90.43906480163699, 58.93414896618751, 45.17966946037072, 59.35221595851195, 58.72516241948887, 126.51283818313406, 53.05637250321135, 103.77517858033148, 234.26360645757504, 51.344719942966684, 51.752537001282235, 93.9874357158964, 7.342797297657895, 211.4599911451932, 86.6591145693487, 92.7554902931577, 256.672968441074, 11.21890376722117, 63.957451119798186, 58.530167648047815, 58.6219389517433, 74.24811082737874, 144.4035051427294, 16.344199174176673, 73.61568741485455, 74.99186807057484, 80.78642857623299, 49.897914141087234, 62.41306019921146, 110.86282905374436, 82.52789630190149, 57.94695394947324, 46.14557079291299, 59.998922042450744, 62.68312859056884, 131.19952708293167, 89.00538227833572, 235.09161349881646, 56.93166403215544, 158.56667916631338, 47.3282501094339, 83.7160249870131, 45.57076814854248, 11.518521985882817, 63.15045970009806, 59.43229827669603, 36.07095924441207, 11.120517300564583, 96.5635681453555, 222.37877011250905, 102.72592511999329, 7.406894228362084, 53.61459771013029, 190.74094666445484, 57.42527275229098, 67.56956007904775, 101.05850752813592, 219.91267195571288, 59.57370260069208, 77.00944099688893, 105.984601801722, 58.30945321179102, 152.79285558409333, 111.48466096452343, 63.58776940059172, 43.56078140287215, 66.34525629906469, 68.83880451061351, 161.44069868478616, 47.558178614007964, 8.141974927191935, 105.45761929512818, 85.7194289968523, 77.70912025215064, 84.18235907603831, 150.58897350970184, 163.5772521342994, 82.79881810934907, 45.12764009480782, 56.3624792823024, 45.69982219529061, 122.8121303919161, 52.19878685324625, 168.71503110420747, 72.95287709017853, 144.73041524650998, 84.63866645670173, 70.7503781377833, 61.306043336725274, 70.80584107392507, 49.21123198957553, 104.41498604245793, 62.45105652543071, 61.71795933426746, 81.65722190073483, 60.08026436144395, 58.78279763364005, 102.01409525815986, 35.41170341360787, 73.82674941806307, 54.329113987755726, 17.870126052906848, 11.119361657060958, 55.32002351816807, 52.03913306895445, 60.87885487550565, 68.30580427209334, 114.29889220229391, 62.54572432483531, 68.70315012163307, 7.651897085581373, 112.01439458913414, 46.028706664242655, 36.74074680130218, 141.49505496901753, 66.4464436975129, 95.0645018352395, 236.59560895243942, 63.46251069991004, 151.96244482964906, 69.58552137157328, 89.61437631969694, 150.26708644693406, 74.7684157851057, 61.884071848207086, 430.1191697413328, 153.06616729215799, 10.85045434870375, 103.52953511471966, 51.13170497701392, 56.722383191596606, 99.78547786864682, 13.506861665139144, 56.63827440385498, 58.57090755884667, 101.79278133173376, 129.09344492777961, 144.7729148899933, 46.74387504643921, 68.61711067889877, 47.7182503103472, 15.879730138778157, 60.73316509250233, 77.37328254120533, 252.4385928297147, 80.85900249179919, 34.357126755316436, 302.0873193464422, 41.03929242912287, 65.82925066445534, 64.73580359052693, 88.2691343244334, 117.03499927</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>124.346262512207</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>80.09632936340563</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>[92.22664642333984, 113.93099212646484, 51.42313766479492, 44.791221618652344, 77.41040802001953, 237.3922882080078, 80.91281127929688, 58.65048599243164, 21.405475616455078, 165.6435089111328, 46.34979248046875, 190.78887939453125, 87.29364013671875, 161.82057189941406, 72.14436340332031, 146.9561767578125, 94.15177154541016, 109.29792785644531, 154.41030883789062, 92.1753158569336, 69.13338470458984, 186.09585571289062, 15.11978816986084, 187.94203186035156, 137.3026885986328, 61.14967346191406, 148.70779418945312, 14.574098587036133, 474.5025329589844, 50.66687774658203, 151.68948364257812, 120.82854461669922, 139.23565673828125, 111.62171173095703, 67.74285125732422, 114.12726593017578, 39.756126403808594, 60.31682205200195, 120.34005737304688, 105.91290283203125, 85.30670928955078, 148.65330505371094, 39.81067657470703, 276.6495361328125, 99.61560821533203, 125.0948715209961, 204.85171508789062, 101.55265808105469, 308.97186279296875, 80.28894805908203, 75.34037017822266, 108.34020233154297, 64.96340942382812, 85.14883422851562, 154.55282592773438, 227.4832000732422, 107.46368408203125, 150.8942413330078, 115.55046081542969, 150.84219360351562, 52.433326721191406, 102.21216583251953, 430.2518615722656, 127.98982238769531, 91.47297668457031, 182.6082305908203, 127.16542053222656, 91.64085388183594, 89.01227569580078, 79.13170623779297, 90.78504943847656, 56.57194519042969, 173.65399169921875, 225.23443603515625, 103.2877197265625, 55.670677185058594, 109.99751281738281, 9.23115062713623, 89.7611312866211, 89.69770050048828, 115.36580657958984, 96.2267837524414, 88.3579330444336, 10.508045196533203, 186.5797576904297, 68.90263366699219, 122.3249282836914, 140.85543823242188, 126.09362030029297, 134.64437866210938, 114.65699768066406, 189.34730529785156, 68.00545501708984, 91.25888061523438, 236.93264770507812, 56.483497619628906, 285.0414123535156, 165.047119140625, 188.9481658935547, 383.9183044433594]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011501</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:51:10</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>91.54659861649755</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>68.61777390165103</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>104.054768846314</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>4802</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>[1.3164204643202653, 0.9794291836600157, 0.9318195180772388, 0.8312299160537358, 0.9024398389665046, 1.0786556087302697, 0.8200705295346133, 0.7919952587862449, 1.1576692243423334, 1.574508678865052, 0.8905459298809433, 1.1050802077623425, 0.7438843739248647, 2.4927423764549217, 1.056677372721219, 1.039547042229136, 1.5945839715741663, 0.6743551429735862, 0.9777256890085946, 1.3476840185479477, 1.3458871447410945, 0.8240277070222356, 0.6426349985658624, 0.5945823334367064, 1.481541672935626, 1.0885425496292198, 1.0338527623048823, 1.0185505628275726, 1.279959136911119, 0.9048293069406512, 1.0927944633911544, 0.7476862336559625, 1.7188968849873691, 0.5295513692012419, 1.298226728787548, 1.0688900832853487, 0.984972274355437, 1.8209715361605765, 1.252728678041176, 1.3494473905863504, 2.0996078319494034, 1.9722749559881587, 1.8763398794752228, 1.636517462870248, 1.5346612353833748, 2.343847949646096, 1.594989413801579, 1.577497086338442, 1.1549404147633497, 3.985447471143681, 1.3313608423516936, 3.9522788628531815, 3.2123575333327437, 1.7553575351262096, 2.0489774747650156, 0.9217254052504065, 0.983838762711683, 1.4275652031445458, 1.6389492991909487, 1.1974005590782757, 1.0593512973512003, 0.9295503111371622, 1.2902840728607465, 2.061469748244256, 2.152420942987591, 1.0404507451553755, 1.348538825361522, 2.376181996025297, 1.8449180044548532, 2.8131576337197584, 1.4967017949480277, 2.0392715697150225, 0.8923612502093712, 1.4881662401406557, 2.5435981071898177, 1.295606956301157, 1.246547280537838, 2.160224976144704, 2.5091877853637543, 1.653936590173162, 1.8197122065475406, 1.8475318198651098, 3.505763290017709, 1.238577600986143, 2.1658095397364683, 3.279678044799724, 2.090896776269413, 2.935544820965034, 2.700075516563199, 3.2587271494671795, 1.97084975729554, 4.492975172894983, 2.734066688173515, 2.3040907853821504, 3.284389200669454, 3.901846657278935, 2.615354561954939, 2.3337141784865336, 2.55209687540158, 1.430904958309497, 2.555843995037575, 2.8456338742809386, 3.0697083344722573, 2.120864268948928, 3.876384247211212, 2.329425572683071, 3.4839864764266153, 2.387349964772587, 2.930299703289445, 1.871031282800339, 1.4782480010699897, 2.384014348083971, 1.0972844761697256, 3.138043197723633, 3.585642178511997, 4.528939387458093, 3.2928168639439845, 2.935937453662291, 4.503093093066027, 4.617700803853643, 2.3151579003790737, 3.955945152352248, 3.682071534585443, 5.178120987235933, 2.3728244834688748, 6.779965036571534, 7.073163968697329, 2.7873084899560476, 4.003400648250499, 5.274348727768489, 5.104221296797292, 5.723599062682334, 9.410186089307595, 2.4978534103206838, 5.694077818562406, 7.921747156675137, 12.865762071343719, 4.003866938699747, 5.212889407773718, 6.426996109977047, 3.573703807352614, 4.171038550582913, 7.285393736798058, 2.3922478366598567, 6.597780638225404, 5.662514742464325, 1.3185983083493447, 4.407954052338538, 5.5612583983998665, 3.125726441909445, 2.22242459001074, 7.428475205168593, 6.498533723648298, 8.83934245562639, 7.887418880868108, 6.133125386771445, 24.292405748472476, 7.854212340394777, 9.831610006130315, 12.407267576893432, 7.21465463219873, 3.661373946065338, 6.428785774492796, 5.094671325858714, 6.1168810729992025, 11.836084851299237, 5.158687553880094, 18.229219167199126, 4.375773250061409, 6.045957309222458, 4.79293505994923, 11.282609221616612, 7.18258433958506, 4.6639014600087, 8.401576689667124, 6.5222619598955776, 3.9273095578456423, 15.820286057896928, 5.042536033929748, 6.004147567566681, 10.48672245141713, 7.368929171981311, 8.787627577586816, 9.372073551433873, 7.123864623043317, 23.496912678732937, 4.981810658867362, 3.007300445256276, 4.638705074901835, 6.489995724802389, 10.437457524508176, 9.213674324934559, 14.095881504120428, 11.711831679008531, 7.123782903142422, 12.906449970959933, 34.73687597466508, 15.842706133961808, 19.02190422920612, 23.604212857713435, 17.423413327053893, 9.895650698812522, 16.503131472446803, 9.603495487168672, 12.317561150283257, 23.19476102349021, 17.518702045491143, 31.276998445749314, 11.799578513680794, 2.1906724268900155, 21.093834741806788, 20.326107140472654, 11.34805673341566, 22.457346181995597, 15.746205634398045, 22.35881262857454, 8.659421798943043, 16.520883322984222, 13.622977244652846, 8.379498806117244, 15.95128067029505, 16.129495212277, 20.065365351836803, 18.64885682514964, 16.128433684703204, 2.027735288230848, 20.63121125034361, 19.341298336689636, 20.434372307485965, 15.458651135263485, 25.607523461710244, 24.418712473526554, 26.680152957056276, 12.565050147256944, 22.48073422190181, 17.577535887104915, 4.218012503710204, 19.500986283501614, 18.25448160288804, 9.775786103730168, 11.155276885946387, 32.89058410676289, 1.0179358008631256, 16.873782927813405, 30.123886126572845, 31.62017602479653, 33.65142933468173, 14.651643650802992, 25.21429407428581, 11.221110380641107, 13.60239599153062, 63.780468933423755, 19.08176305398762, 4.498807642072647, 20.548946965305962, 39.82489220606655, 25.038252575369604, 15.719890322629329, 23.667114237451365, 31.725480954757156, 20.671439382462307, 25.499529106409387, 39.920734681949945, 29.970943195582585, 33.90725479987647, 44.43787203981212, 29.945911522971386, 3.4046092179343557, 29.065994796790605, 74.19941422610255, 34.69258664269142, 20.779691002732193, 30.00843382109381, 25.21692113075544, 40.74850635766464, 33.75525459528912, 26.2611556690341, 31.987932123252055, 46.07253214518474, 48.49905477721985, 1.8482606798175025, 30.001830795150727, 30.62060247093043, 19.333607861094464, 23.03546247792406, 33.12384702017713, 25.853855534772688, 25.42350065771363, 40.14985177315416, 20.4282554312504, 24.92611678690796, 33.814923179008055, 22.159003359577255, 25.21946805566539, 39.23927808157681, 42.93343271094487, 35.97302986421715, 20.5363947647212, 49.82740763175689, 3.5789077714242654, 33.8561036253127, 31.926438318748158, 25.441610318440894, 4.06000070031418, 45.44645221983923, 19.087844620012763, 39.81786581840374, 48.696119202067244, 3.893024361718301, 43.32326250206408, 39.564972507013564, 39.42658625071106, 59.38599441429539, 34.59358814757515, 4.028879697860146, 21.103773679870855, 58.8322395545556, 52.89612064308676, 58.373286794290145, 49.82913141066229, 33.54524886615925, 48.3004251067843, 30.712996044594007, 52.92482708718663, 42.892910473676004, 12.87779272786686, 35.15864038635718, 28.705739596840253, 8.818223070594446, 3.982232403343751, 39.08386067290286, 41.77348292593808, 27.63661437772183, 4.810580813076837, 44.387953182446616, 25.712479185930643, 29.37993056256661, 34.568857879276344, 78.97389124718309, 47.38826325065469, 26.6862659695057, 28.8975025283812, 59.454987841363426, 3.813919862999337, 65.66354997754418, 31.446382064096507, 42.72307830897328, 24.993683103856473, 25.232585844588534, 56.3432138968264, 31.247032225051026, 60.71518892713917, 40.39273772774195, 73.86808834089797, 36.201396189863075, 46.20604824379117, 32.21660315370833, 27.861851408352905, 23.352326021972466, 4.576403978910708, 6.095495607413296, 105.91685373560485, 39.99237247393282, 39.03607382256641, 54.30747480055001, 62.466118448816765, 32.5595643450432, 48.82943145331359, 35.71299101564288, 51.00981308103335, 12.192731555183371, 39.18564157027854, 33.36705658802019, 42.868754677283526, 5.792652235608296, 23.494947686204213, 37.11537829934723, 44.619302689761966, 23.298350224743412, 44.092500124213096, 89.74773619841778, 41.89042153784973, 34.44023438733693, 59.34999642275476, 85.76351399429846, 37.30235661697608, 61.93331632365481, 45.67321619065857, 67.54288776903066, 44.717055094593476, 60.38635998027787, 54.898580595611236, 31.858416620642313, 78.54851003003479, 46.78182939988763, 25.341401202913893, 61.64737432859224, 24.78082299494686, 54.66199736916493, 57.680756566790755, 35.32050987178972, 70.7054261596805, 49.14788658779422, 24.02661914528686, 54.86394968508725, 62.13828268095955, 46.84465155422472, 45.92635948503212, 24.68594835405115, 89.00033707676876, 65.74833746144397, 38.359452202773355, 61.94901254799214, 31.07349384985355, 38.27333046356787, 49.307485675621244, 77.78679637844164, 43.77369618585733, 42.1574499122538, 72.23880608467161, 43.43091187458688, 71.74893254622305, 55.50324340530887, 50.56592655986745, 71.38316513109166, 37.698297746156456, 53.6991258087694, 46.53064106928042, 65.06599901854203, 54.35216377930273, 38.19732197818932, 59.45911869962084, 47.89180361562757, 75.93646489485377, 36.454732001821206, 61.69248509352221, 57.4490230419283, 79.64657750833811, 77.31540035910939, 95.0847918120602, 37.338575287874704, 53.49983839515784, 64.66174966395701, 57.00164717871971, 2.3302266914273613, 53.6567867031302, 40.902608053194044, 60.31849820187543, 42.64427982639503, 38.19206688071484, 37.816245326333664, 56.51589085395202, 14.961685857998873, 67.97296336108019, 162.2075173252467, 35.89747750689717, 46.49638252228828, 50.119472894644524, 32.074427562003024, 39.96035757949216, 89.25937535596428, 44.675640620804145, 20.19012282608127, 61.43671780557044, 72.77166903562909, 31.694718193527578, 108.12933984787412, 67.03584223269779, 42.25660933623461, 18.72466067990336, 39.64083743965112, 103.1506754269272, 64.58771509099839, 38.41381993989445, 41.150242772499716, 55.678194716381476, 22.720580968943807, 43.04238540382661, 74.21234079928283, 89.0970731622373, 47.4407875439137, 61.48688206394888, 35.5292897527739, 25.492020879008688, 24.35597524086288, 37.1898681398958, 76.75173981236927, 4.195522149540961, 46.83822165479867, 72.22388909226345, 45.00333678274519, 58.87227869491562, 100.5577305235295, 49.452292804547064, 34.702619181738214, 76.3457419231338, 4.978289203035867, 59.64232963573817, 49.123309456889125, 112.33162015973824, 37.76951978559159, 149.0843619407295, 95.20421185811168, 85.07685794690981, 128.85948713496873, 71.10980077912566, 45.21212409595474, 30.380681104706923, 8.55082161841211, 55.50932689121187, 47.722655776037946, 44.51955022888248, 73.36711610781276, 48.764855806627885, 7.604322660623352, 70.04384239300512, 47.89205340512499, 115.31410573532912, 126.69339377342803, 53.10663948113786, 46.8879918413128, 3.8476996236569154, 106.52222411502323, 77.27726281063438, 36.14753834428603, 83.64625122124417, 81.15468193876048, 50.81878927309549, 8.130203618218472, 46.357506936281055, 81.87317259860197, 76.21161470769331, 8.407244770587532, 146.9487540208742, 85.91551549244325, 74.4161510170723, 160.58086773447505, 84.19562333564413, 46.86470434930021, 66.1751493455722, 67.97445649879808, 40.80108006337799, 61.93990125770503, 115.78234011138684, 69.76817732292628, 101.01477011806185, 60.62853242541744, 90.6260976739882, 81.24142158199253, 95.36104266650678, 65.60912066284935, 40.40316961073685, 68.19392434806933, 43.42716903661538, 91.4401351318373, 86.82429885326357, 64.81963155749764, 56.66278467568987, 66.14479436077775, 32.97924164616302, 72.34998786003763, 43.46398569096245, 78.16272609787171, 7.978919086095981, 47.44149055579326, 68.36779758783, 56.7957311882889, 54.5832873544675, 61.01602146688247, 8.340298225378012, 73.62991048115222, 210.09990750252413, 49.0162176255847, 52.68175553894859, 38.67360517975367, 37.65900189589506, 33.38210404629515, 55.22417730124911, 61.27381032176248, 81.61236605698737, 40.24937708462191, 51.89237004441479, 40.41428010031674, 69.46901749791368, 48.21740013439018, 128.39001907036382, 51.39839171037217, 69.90873772094241, 32.82241731765713, 82.62897324418702, 160.9395681004512, 42.37844781278724, 66.52644106252485, 85.95327990508628, 5.909718511845611, 79.11288194552324, 43.706590173880564, 66.82870091170061, 50.05513310500731, 126.01644986166127, 47.7933266764684, 54.53608451351094, 53.19001499989493, 98.84372338676467, 44.013186076389886, 153.1148689006016, 51.02831810942136, 49.99263812264115, 56.236397020533964, 89.65899235270139, 71.50220706953073, 107.12395848921116, 416.4555330120446, 43.6873633082982, 46.31785424513106, 57.88475875751328, 52.451848795222794, 104.18117796302565, 74.38447288834946, 10.480264426204505, 42.385142423797056, 38.687218306420995, 8.255834282368994, 68.29259269276263, 59.43323199275316, 41.02155150151587, 89.98175992496101, 86.61346918730125, 37.89449248435603, 46.69414088988223, 49.22824733829107, 64.62756118210567, 35.46722059149835, 51.29071879581033, 55.037028656130374, 61.203607671054904, 145.2587593421786, 154.03049250377578, 8.020574301930852, 61.650677729023876, 86.91358588328063, 8.495602804470007, 58.97244751564068, 96.14348671136942, 114.75041747327809, 69.93900421494193, 78.04531378747541, 47.59431918377698, 7.498181387458191, 11.19888143413939, 4.908581101341478, 72.01771450271968, 41.39611393825625, 75.39334450804235, 57.13509725772145, 110.94615470137092, 65.12400404486257, 99.94962791078044, 62.81417820267347, 97.60052454679735, 57.62495569020756, 172.51421947494998, 56.23074487892662, 66.70001681439648, 38.087891865051176, 12.92651385448977, 115.21398183999763, 46.71041330322416, 43.42875946282597, 94.6086870734426, 39.20437701789601, 88.58563290501742, 82.92221478851242, 6.488199029738363, 65.21821864915209, 56.2647338710561, 72.71027031039733, 50.70273613732111, 68.20066059305358, 281.46302607479885, 46.165436858217, 71.19740692573816, 47.11952384995929, 52.675909141413484, 74.44975571723903, 51.96351317441412, 58.377455096671994, 108.982644718739, 66.85584442295519, 69.07526918295468, 48.842285795694856, 46.81308068439747, 53.588640814716655, 52.6423810457975, 56.915906677218764, 90.12717404920159, 48.10808887612053, 52.8608055373307, 63.68065964929888, 97.7799664278929, 65.10228361637999, 15.648190770743925, 64.1851026449654, 67.58943355087595, 50.850066067396995, 47.52484680400231, 122.35371108130308, 47.4886675451359, 89.32772228118002, 64.40911029093931, 95.6496926287663, 111.55413867916594, 61.7489829910844, 78.39437763282409, 77.36939937539495, 50.862474105750344, 61.058141571973124, 55.602190484098, 75.44952038291552, 126.43680232267587, 60.83584393778293, 74.36057084595106, 52.60294672839906, 53.02325310721515, 110.18338357304826, 60.805879160781586, 55.82992458115464, 157.3833643965127, 192.80173173626795, 97.61554772867566, 42.793682810011084, 55.585027533693186, 71.06664433240492, 60.842859363807996, 18.866093257654565, 92.45756064106297, 68.84223374537305, 91.45568744840719, 47.22813557581018, 52.42257788439733, 40.47840334257461, 145.3057937117006, 64.61666758885367, 69.19961363383625, 52.154679042275795, 96.65248095092838, 74.92314987900578, 58.973170845047456, 73.505384576113, 109.24983740379878, 17.923180354349036, 50.66113753167532, 64.54404960047184, 70.43547920414296, 65.788893912553, 97.32104212106712, 66.4168335817889, 71.46293626574935, 87.4608059811329, 97.59410496995818, 85.73243026637934, 39.012923803308546, 93.1301995152562, 152.30351007206625, 81.26351389756671, 86.97997364690148, 82.60927094700202, 133.7164177539353, 65.90779214446069, 59.26611123773613, 89.20459415695332, 117.12637479408377, 79.33833322930086, 56.372751188869316, 68.14581839085491, 71.12470697628478, 47.95088684003948, 108.03470723996097, 61.372125096487075, 43.64754858228629, 85.29562569752355, 99.01744552596172, 136.23051833708817, 121.78748209934984, 68.0934380873567, 91.86671325052843, 128.37639632692424, 48.19557034326064, 9.897657709384955, 63.849652737148304, 7.173287379095402, 50.54047941237655, 106.50100782201461, 50.87934491987091, 56.712186062445745, 33.916526109363794, 50.58399925327173, 73.31295498616386, 33.09316264414246, 71.37407495604313, 73.74228432084632, 51.02485548490427, 50.39153900096425, 47.481683505927855, 45.99518923000563, 52.22492129159819, 50.277065728098705, 33.127936337759415, 50.41567822147459, 7.157470240541854, 54.22304616038881, 46.82570889245523, 68.99633348664094, 57.695327703914934, 180.33947030312322, 50.50975221537274, 58.323359685203734, 58.5780347748394, 41.55261741179269, 64.08658823904264, 44.622236294305026, 52.25171913958616, 73.74569668909112, 67.05216221343578, 41.412184395140144, 49.66417347199583, 60.79828687101784, 42.186077909115355, 174.22814226770228, 82.27453470506775, 117.04051055994975, 77.83261910824878, 50.111499713840885, 82.45369289002178, 44.910497719341876, 60.14036802676389, 72.90030338697221, 48.72025018908171, 51.73541723648714, 76.06474735520976, 54.85931271829395, 128.80625974814672, 64.94735046176382, 50.39990204340268, 88.11363062723736, 36.5431772097411, 61.446173835880366, 37.156882907090214, 52.77759034991733, 44.34138147218415, 50.847922262355915, 82.2645616585507, 66.18365051798813, 70.16605661480125, 152.55214668493352, 96.99874925245278, 55.91218950063101, 139.35617630980033, 61.5854967248073, 95.60090975749355, 5.898593171380279, 80.66746860690088, 38.402767809437194, 4.114109014108835, 82.98790946989382, 95.88397929314432, 190.10814359847777, 96.02162125531741, 52.77505271785324, 128.904065229847, 114.79332053263673, 114.21490918092016, 86.85784873152377, 21.2827551745307, 41.639666776326756, 4.09154533849415, 43.41209640805778, 89.28746601077071, 58.01628463470504, 85.11300559907961, 76.56174304255725, 97.41888564384615, 42.35491086026674, 139.16635453950684, 54.97012069465528, 21.53634002857346, 63.0430522043272, 66.64318479418135, 140.0870284258252, 38.797881869395844, 58.45617850448136, 129.8296065594038, 105.32581308614147, 8.240137665664482, 62.82969001747664, 71.37401163820542, 101.45336164571765, 42.428291093100796, 52.19021366470578, 62.78639460441505, 130.8336799386685, 45.720597929462855, 231.42695739584613, 54.47224068344391, 50.11664875929443, 87.7067761050385, 65.58158629219459, 126.17758255247773, 64.96964606413033, 144.8903674111533, 131.78028917380522, 86.41721961159416, 61.04190669712253, 42.021829121782005, 68.44902489864425, 55.06620346009394, 54.9276689432316, 49.59028677078499, 57.99078962382927, 343.61738100245765, 101.70489275295738, 73.92040764128791, 56.64026203081653, 80.56717960747925, 63.382045148116475, 75.86912274444062, 39.14644492958966, 49.21601875705428, 47.60792746939689, 76.8620043870811, 58.86557413875067, 48.05113753940555, 66.2808603740815, 59.60346222502493, 75.89516574684976, 43.06387820473342, 61.28919829044798, 61.92029932670024, 56.20441034236854, 99.44743923556386, 48.27996495807768, 54.45341306217027, 91.56107479259836, 199.97049492990936, 40.01392550250204, 70.82806376232205, 88.5478098890746, 133.9240198266871, 5.548500781617597, 55.85706600769868, 53.96622393307029, 6.508411201817845, 59.91253651422072, 91.51540830839237, 73.67085481072948, 81.28562808088135, 318.2099601919893, 86.96497977195196, 78.08155441245151, 54.12819124936421, 67.59327030182075, 98.71730547277983, 90.44572408774485, 219.63194100885258, 55.82954386113168, 7.059421457879738, 56.952673970342374, 87.67894146079549, 144.15584523445867, 70.33181169914255, 81.8674203004773, 45.32125354787435, 135.82863609115014, 69.65592561378608, 36.85139761863234, 88.18582266767504, 118.96067575912386, 45.94117447912229, 140.87218128949158, 93.70364265651561, 75.28320405226599, 77.76099299998803, 65.68715376025396, 93.66880891078198, 57.34254912376019, 6.999942647195809, 108.13586622841791, 92.67264426272973, 196.02207234877986, 160.40534261894805, 38.40315073132057, 160.62100753345888, 227.28215231110943, 63.893713435231795, 64.73055267935675, 58.43552216612197, 62.6500883236964, 72.96807300807804, 75.38279032218017, 129.34782147099972, 88.92855785500144, 63.336361521732194, 6.872379736132071, 60.54121923593724, 60.856515789180676, 82.24997002738935, 31.850613428735894, 6.981449883784766, 70.0063323846226, 84.09349358180705, 32.917062367438625, 104.86144220534281, 112.89476145778578, 56.96843633135237, 142.06824871471633, 10.64659532751012, 99.67272869531078, 44.32504598115686, 54.61149286335504, 9.678977831345168, 7.805655554865302, 59.44898493799444, 122.97832455060448, 120.67611453812471, 86.48300091896066, 64.00639483931623, 97.11906971889104, 84.84346691967434, 212.0998173255455, 136.25802128502744, 58.43414503849689, 49.93154614129632, 112.59464288843323, 67.43099756151113, 49.55445347359508, 50.30370682253029, 98.76013170003758, 170.82244445005742, 111.68618269359517, 62.1049382295356, 11.472097196942293, 73.32622542109009, 65.81894676429239, 102.74234936778647, 90.19652869161527, 55.28412618172721, 95.69052512165595, 102.26720247756464, 22.14081153976931, 38.61730241185192, 8.162735898843202, 71.06405628297595, 51.79929166154357, 49.80690954488157, 164.04464616928223, 67.80479975391647, 63.10327451692105, 58.25546773416316, 69.58450981170216, 7.844049333801912, 73.375371323159, 177.33669399010128, 54.46600214428863, 98.79817413718501, 60.18417081236739, 58.17026739047222, 35.094030033189874, 57.629470888583825, 8.943478520514152, 55.312213569187556, 76.01063993016977, 7.757702527047708, 65.51820097133428, 111.54726438848616, 115.76504602939586, 53.65146572248876, 180.36253161082863, 107.96387536290166, 42.04960550453247, 44.03550935418762, 47.015183279074655, 69.35779435882844, 109.16931945990598, 209.5812421324152, 93.88463647834324, 54.595363549807466, 86.18600685596668, 110.02523243346744, 121.58090028580153, 101.16367263381863, 50.474799093755344, 84.19460087261973, 104.28677530796227, 9.183809343779478, 32.11603781935554, 87.82312014863575, 299.887435984169, 37.68505213538594, 70.52246509815214, 114.88601809270779, 191.370506778728, 163.09765858126067, 78.16363102894776, 118.0712396902324, 80.35589197335456, 88.8724792267028, 53.946751365728744, 54.58423726497598, 184.84312928515166, 92.31408151986496, 41.7974262973852, 53.89981113844015, 91.32480186945948, 74.6784353208765, 9.173300455601993, 70.28635825798021, 101.9904174131831, 169.40017850694778, 61.41173385710823, 51.81569042138864, 62.1224374329917, 55.269304813348356, 62.91288455921683, 98.26301213488057, 73.20963586964628, 58.94960149792553, 88.6695589038444, 131.92165125989936, 58.81188069791302, 88.56092419244753, 68.20018830723474, 78.98996323365128, 72.64224760724315, 48.28966839994, 107.1305252234451, 51.374781055724235, 68.8555797469829, 40.16519683515549, 78.25266974184161, 269.10471048449824, 63.76496251427634, 72.17551672306685, 76.6056982558694, 99.63891572174232, 107.4893859478086, 40.377993154769314, 135.6460977576372, 86.09190588604461, 74.98628850441519, 37.51009233045171, 107.10020455937682, 81.6085431090163, 80.23055098426757, 64.37331425415353, 65.93906977065986, 46.94014591969604, 32.324608770439056, 59.749208861390564, 40.48766654211107, 8.878376656380775, 94.29758895724687, 113.06666855374365, 52.41265792097524, 65.69995782649737, 40.8254761221552, 61.830923200007106, 104.4132416459032, 68.93409212458666, 54.90576232971756, 98.02655564296181, 49.628950479797396, 213.6054859327304, 65.07702887907304, 187.1055483056638, 74.15512998746631, 89.30195753139215, 26.986013893851432, 112.1921141350095, 67.20265944773273, 62.72592483080132, 43.73733260513272, 104.06554648653595, 89.44638369492665, 54.87145722301234, 73.85548039310696, 104.67782796255955, 108.81317015519335, 71.05350880560988, 153.9485138070175, 74.7212887284195, 68.38500219391243, 44.04183618630858, 89.23293546436025, 66.48598900791396, 42.59761575086626, 82.06270238623078, 30.16222179863486, 43.10459177467316, 80.32740377591833, 211.88655608172414, 76.3107818272583, 137.6927843096995, 94.14551473425036, 99.54495909109087, 280.0738499778887, 39.864998958613874, 108.73971895783986, 91.74050564831336, 34.97627653258827, 48.19540341975277, 27.230804895121683, 46.92494744878517, 73.75334054956232, 44.782728931841355, 93.82720323705733, 69.06078128335183, 142.12467007613344, 49.33052458426637, 52.415640443273176, 118.79781545634211, 52.735221029697605, 130.9137999928844, 92.61470094874399, 106.3118462300405, 71.37924032621416, 84.44745252189514, 128.40578728638062, 48.61937092728866, 82.89242021629545, 133.257384343282, 59.9373491555339, 127.2105494288273, 109.0179501485716, 46.45613836763145, 87.74173741813554, 64.81132305073847, 42.18338630994403, 72.30343706229289, 74.11908695321955, 67.76823660428056, 117.5591935042889, 54.162328193398615, 136.29714310534698, 71.1657468850156, 69.97272862538176, 87.00599136664961, 131.2236597316564, 62.57224866338315, 152.27658343255123, 59.52230392060002, 22.539882741032024, 172.81274758409776, 84.31354268336152, 129.83998330753047, 45.26991708999688, 81.17959973108378, 46.98482845274637, 218.31180917772807, 101.50005581063121, 84.48148984527313, 50.92093101485705, 68.77195782748576, 31.977563097625485, 155.2121016664798, 74.04374785318875, 57.812725486054546, 60.608767692639546, 67.60869545930758, 72.07761326342582, 75.01383823682643, 88.95338820094925, 57.12496807993711, 94.22190404972145, 86.19804113868307, 100.64560835799351, 169.0610552567305, 78.18283955043721, 82.96181130518065, 51.03328535109597, 45.7570674976981, 46.75375810816268, 40.184823803351485, 50.38543862551622, 28.298833371497558, 13.341318049754788, 109.20196948586063, 112.7668526224796, 80.0679679473622, 78.03011593241429, 82.3690954929482, 49.05916731099788, 90.1616614209002, 140.97300759997168, 58.29436251442647, 49.40342133114591, 48.05789468768667, 46.37293296564593, 89.4753916532292, 72.59644520721885, 62.237834355678274, 57.724058497582476, 41.281524698499275, 68.27408392189584, 11.8332975883383, 50.06893941969862, 134.26325468063933, 76.0454784906085, 160.58367077931533, 86.21653494436332, 227.67306816201062, 90.91518640327433, 87.02489653003836, 87.0525314935142, 141.79155351730745, 61.05960374288023, 177.74982033052424, 88.5793311413397, 254.27369404991373, 124.3943640376492, 77.1924599870228, 57.188184536285114, 78.55441521502206, 233.55669456088415, 60.466347086358056, 78.38022381054685, 65.51362752845797, 74.39922920777938, 46.58340733729142, 55.2841673822276, 33.80303454753943, 115.95702105480571, 37.41328901718626, 74.94827568591708, 74.37873361190172, 42.3370899774523, 91.19331921571778, 29.456683827660036, 133.69768801457647, 87.60737961137632, 74.73113449930923, 157.52143858374436, 53.93496120695771, 35.18112429037643, 98.54803108070158, 96.9946436845056, 95.45391607970531, 131.57312017182517, 52.326288093888266, 174.26437431645488, 116.90595011424318, 72.02461252548176, 109.66535259480854, 36.444677621921926, 83.51803143439783, 358.2412391736568, 145.45268977167052, 47.889492918870616, 173.56221627963362, 185.6795311857838, 58.97082741635394, 85.05621514063333, 92.04518290481198, 73.03609469923298, 113.07810383591385, 91.17652143135814, 62.03472979403115, 62.908562391829264, 69.92432403360979, 237.43979820983054, 110.38999393577525, 118.99744044245499, 162.51847381690217, 92.17692133589792, 245.73018166722576, 266.96402127836245, 55.05983429959742, 52.84248798191985, 48.217285143075266, 197.0900343413569, 42.30313983132546, 118.5104273848225, 218.38840143914697, 12.357647335222596, 74.97021375488181, 78.34472320631177, 109.38637796843776, 135.1170885871823, 140.38559691265235, 188.27186096173713, 127.85491714164522, 154.48172479491686, 212.37942035533624, 75.39392478684965, 118.44560467699233, 62.36431478489989, 75.92942356474025, 58.45638726279041, 81.54165726826885, 81.72481328806992, 157.90908248318271, 75.39210467815242, 125.38264083858944, 11.918997196113025, 58.50697039876943, 127.11401970417032, 95.51793284507878, 81.35831843132591, 86.5577220172175, 66.61383416151547, 65.5557508184727, 69.87862781095741, 39.66354597299109, 54.55447394811941, 55.355851123184806, 38.136883522450184, 114.48456849538343, 93.06484956444766, 42.36242011538043, 116.01253228839857, 51.90301393683003, 201.37362768024605, 45.21442570423454, 75.18329818571401, 193.38889672564073, 43.984284577991765, 52.525736838810516, 166.12142200733336, 43.76186057052184, 110.86955598432775, 66.60632823286231, 7.816116415737468, 47.1331923798762, 117.9200790698343, 113.58802214147757, 10.296411146082725, 62.60357129826017, 115.53520237242309, 44.820882947529775, 74.57397173289424, 84.6041227853729, 101.99778283076921, 182.20272825750274, 230.16695907671033, 81.06787724069909, 110.07166609424623, 51.13360889061152, 123.06896953590719, 145.06510756208826, 10.222055589725963, 68.56340513227913, 105.16589015765027, 65.92364929061482, 52.17081123029963, 128.07157954159302, 182.88326991048373, 51.41497535616014, 93.19331175988906, 65.78122437535755, 123.78574295310293, 52.81153970052917, 56.44905261968097, 136.0174280563098, 57.826696649118695, 51.54734868030938, 7.981877729679367, 64.5240044551786, 89.26516823767493, 116.71353122542557, 52.356645143620746, 72.05511470831085, 127.52295900401278, 93.92689500691306, 53.79682194414588, 45.703822162447054, 85.77915562032749, 111.47978374339195, 121.06027255369617, 137.20595726716698, 122.49594891684262, 41.24579859919078, 81.73017245289019, 83.44410338087185, 186.4437215394829, 50.09675062676801, 57.911268130349505, 46.67468279848668, 55.645321706573775, 105.67235431669319, 104.51385610994267, 52.6122358498515, 72.83942807712126, 57.544033719392104, 63.71413122295763, 61.50288210990791, 61.885795704497575, 39.97516213609982, 40.24759926710174, 402.7683106238561, 62.91034119433269, 169.67568770542323, 82.71844290941657, 72.27419043395793, 31.459284663935193, 34.73856001002744, 39.471257928647546, 100.279450065812, 72.10350881708612, 65.58683082195476, 136.06998943615278, 64.76514853071426, 234.2072368224778, 89.36488124880931, 50.73585774253545, 56.53010892472305, 71.79892235979388, 7.65346306553843, 98.95772921036209, 142.94532669997298, 80.64313484403336, 151.21556611282307, 51.643691979692136, 71.63903047055607, 60.23714782621995, 222.7043983809359, 112.11240827697111, 142.81613995930752, 72.67979940466958, 90.378936582899, 113.9718346793827, 34.85646780022567, 200.11871518121825, 63.189346566313176, 130.75268688135662, 78.28019148417188, 74.10067159617383, 54.02648729207354, 139.52329713165403, 79.25516348666936, 202.53306105479646, 89.68872531137589, 54.13096770865105, 66.3557713118844, 226.48859640248088, 61.67279407534366, 61.319221217816306, 109.7631542204489, 99.8819576438881, 411.8854489124109, 92.8975323347025, 96.07807184368276, 130.15441229142584, 282.0268540713349, 89.44383251661498, 74.22933238751243, 97.33814705138278, 86.1844427133477, 83.0242540491346, 182.48345112147362, 20.989683862764558, 101.25634001694166, 8.730865753853084, 151.49570705058898, 66.77961365199546, 147.6568551901601, 51.72892432281158, 22.69804755489129, 149.2390396297748, 79.52378239307633, 166.96833880474153, 51.27850179406566, 8.374719417786709, 33.63560366039538, 102.81722407400389, 47.83439693711674, 42.141872209221994, 91.92995395466454, 72.4631227431692, 94.49718097517709, 104.8412742435036, 18.37216188888328, 39.363361883577674, 47.45550653009014, 101.86317947859634, 47.336508145686764, 90.148817876337, 133.48650888728352, 89.56972728300222, 126.91262938981487, 59.36913858375499, 304.81238466729104, 102.69466800669039, 43.71819846307228, 63.12102446929718, 62.21427260066849, 74.45031996796546, 108.46428476473315, 70.8168970788206, 95.77123924003399, 75.7294621336157, 69.01943617243067, 105.21229505781972, 41.2354116465444, 23.297225875189024, 187.0272770631159, 77.58065480140353, 75.08875911118449, 138.95478207497948, 81.98058331914305, 124.95350065746612, 43.114938210238975, 40.60525849038523, 78.55107066018397, 68.68291110623817, 118.81585534626187, 100.06808475808684, 93.0361291203859, 89.50218289331009, 147.55051548784743, 83.47819031891893, 452.22737370483736, 84.15206027728146, 68.6135066996625, 121.66814912335725, 35.32679473870936, 66.53782406698691, 122.50130780875368, 125.37625789736246, 107.53123470991805, 65.2237392768725, 126.43462690557408, 55.741825055086764, 49.79057276245914, 44.09144382705709, 74.75215215451323, 61.602657631569556, 218.38034940112993, 71.52463141413546, 125.95876766150357, 70.93838383015758, 27.201411992893426, 678.5366172034385, 93.32452892983237, 95.1093546244312, 125.50744257879826, 88.9023523200917, 47.03067301629952, 195.3862883753749, 64.22885074322423, 64.7330017539658, 69.68082020219063, 82.5448186445162, 72.84734653525943, 41.42202136797943, 95.2149373770914, 111.61238107729129, 97.468283347447, 45.603547397811816, 10.218027326030008, 41.8165098398624, 120.78721390121186, 86.86499005232099, 102.43904143792325, 65.57042927392257, 79.94613797079025, 48.91593891153177, 124.17118144060045, 70.90842241789345, 93.14088460372145, 62.9714844280885, 51.23798147235534, 82.6854053722779, 121.0484305017998, 93.60788475914201, 98.72693401256623, 233.3748784758185, 41.69009871343617, 87.9442318654594, 13.652417482101175, 72.01779849666495, 63.34541585726979, 70.49393861490715, 77.82645793715216, 222.9205758147288, 72.84018099312362, 355.0638610779574, 65.4097146877417, 69.79679375461295, 122.33719091884016, 210.76942839544472, 97.85689941050819, 54.523581633308815, 163.0020182290981, 69.2734649802112, 131.3004107867312, 108.88425920020023, 34.24706360001424, 43.71298094124206, 118.2857852797927, 69.25644101029854, 92.95793901018294, 75.97592218787989, 45.48657771542791, 305.9636542851731, 136.215490507</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>123.2646888542175</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>92.82696276083698</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>[119.7459716796875, 550.57958984375, 100.11125183105469, 44.571327209472656, 96.38285064697266, 96.34695434570312, 116.0601577758789, 193.10226440429688, 159.3987579345703, 90.14790344238281, 65.48029327392578, 55.677730560302734, 97.62215423583984, 100.39469909667969, 76.60774230957031, 121.21463775634766, 205.2163543701172, 69.19094848632812, 71.28457641601562, 172.11737060546875, 69.54694366455078, 68.9164047241211, 42.054603576660156, 165.31036376953125, 52.008399963378906, 144.03372192382812, 187.57199096679688, 130.87791442871094, 82.61013793945312, 63.184410095214844, 147.70254516601562, 77.23198699951172, 156.53521728515625, 196.1290283203125, 90.17293548583984, 100.60679626464844, 120.1192855834961, 209.92413330078125, 305.0318298339844, 40.40169143676758, 197.3170166015625, 344.5767517089844, 131.49789428710938, 78.4430923461914, 56.55945587158203, 62.57561492919922, 105.41632080078125, 82.04328155517578, 55.515106201171875, 638.0266723632812, 44.520347595214844, 103.7519302368164, 26.174219131469727, 100.97150421142578, 104.30682373046875, 91.01121520996094, 94.4740982055664, 164.27711486816406, 111.00361633300781, 132.45040893554688, 80.29530334472656, 187.6809844970703, 56.52410125732422, 106.6343994140625, 44.89934158325195, 73.93220520019531, 201.95880126953125, 57.36726760864258, 59.656333923339844, 131.17771911621094, 92.94969177246094, 147.59701538085938, 98.65255737304688, 120.90033721923828, 304.0099792480469, 140.70535278320312, 229.99351501464844, 84.5657730102539, 50.51163101196289, 52.38445281982422, 100.46302795410156, 46.71390914916992, 55.64280319213867, 153.04156494140625, 217.93783569335938, 120.05693054199219, 116.92823028564453, 45.709129333496094, 158.31520080566406, 52.201560974121094, 181.26199340820312, 123.06437683105469, 339.4664611816406, 78.98678588867188, 71.24595642089844, 62.681297302246094, 70.234375, 67.63606262207031, 96.74662017822266, 69.60163879394531]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01848</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 22:26:19</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>85.13390095438548</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>65.52634177875433</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>108.4817629179331</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>4606</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>[0.7430754746654005, 0.9516071264234239, 0.47101765608309115, 0.8268527642712138, 0.774658642582967, 0.7091973475797235, 0.6486850622590895, 1.0517904370072042, 1.3881213407761508, 0.9914861481385788, 1.0150029222851085, 0.8159133213273768, 0.4380251397634803, 1.1323555679002562, 0.9876666201128738, 0.8197618406013574, 1.1320753790611495, 0.9275545835340478, 1.0757920421767238, 1.6875814270386005, 0.4012822549530599, 1.942045440990668, 1.7572469822193373, 1.130678642742254, 1.1568536575090367, 0.55682107818823, 1.5192471905759997, 0.7995028815767729, 0.13274337000082717, 0.7189912137933937, 0.920069542002991, 0.5954041878540638, 1.213510767963638, 1.7992984133557715, 1.132722061044552, 0.6978226951381339, 1.761396903580976, 0.8999498538084396, 1.308525763779003, 1.5825888675321764, 1.3209219647727486, 3.359437635992775, 1.973332677254547, 0.6648189971644618, 0.6295640491207432, 0.7282968709112676, 2.035513752495797, 1.5726268700128658, 1.2875687284423016, 0.9015329923997226, 1.2715462992495192, 2.288177788014611, 1.4439567750082924, 1.3478011655958915, 1.1700590454696633, 2.3443685243518306, 1.1804454030965197, 1.5863988231084787, 2.525583694019558, 0.5356183685586686, 1.4642885285990963, 1.073582950474666, 2.393293690257867, 1.6606149370804142, 1.2963902435962738, 1.9226618325049405, 1.8186439820533704, 1.4574387089985503, 1.8525267887052748, 1.8185645505061276, 1.778443568323987, 2.285856235268735, 0.7620794190421781, 1.0133120204741966, 1.0005325117984907, 2.124193744834477, 1.2355787730716394, 1.9603628353886968, 1.0068302205829809, 1.409877608947123, 4.906282073593813, 2.533434521558838, 2.696655557209281, 2.07027695697729, 2.617814297125741, 3.392045298370719, 4.154731151692997, 1.858972319118433, 4.307208513555791, 1.9753449170870685, 4.908254326626589, 5.079194027148657, 0.37721737345305467, 3.554175249085856, 1.6885635714587242, 1.1719757838936102, 0.8669686836082962, 6.541826234981618, 2.471311994835735, 2.739070979485303, 2.56917954667364, 1.3918059116681059, 3.7152478002183607, 2.7836394826254325, 1.9854438691480507, 2.2761848304769443, 2.3366372218294478, 1.9351071837502067, 4.142512895294245, 1.9718516002106308, 2.9995211989872304, 2.718742460512585, 2.1825323856642616, 2.363165221788567, 1.5770065439901948, 2.388515443577054, 0.9561570325618524, 2.3983286751417063, 2.288418514599508, 11.776462642657165, 2.607609844359797, 3.9403009474234634, 3.8469272302289554, 4.275397760793676, 5.106150416812355, 3.889730176415886, 4.986277886827339, 1.8388795303522125, 0.849113674270729, 6.106925181192417, 5.800095842403906, 8.573323744879346, 3.338380893580166, 1.9633322289586352, 7.161297067099867, 2.1326494986384206, 4.311858302211964, 4.18626604508575, 3.2505680012471605, 3.9484830478342317, 5.946337499000536, 7.251619037517923, 5.082167029107762, 7.456005851295896, 5.085228891051909, 3.9882717171545967, 5.370906090424827, 4.976506662414275, 5.640883358068876, 4.202919043352265, 0.9660554776804495, 4.011971950192469, 6.805789246771024, 4.841431457509921, 3.553886221830371, 5.934914232191057, 4.410255316189265, 5.707076478102026, 6.405663910935966, 7.404580536634155, 4.617004272647135, 4.729215470357944, 15.09510029740369, 1.5715071383095798, 4.950416919156829, 11.208878077754285, 17.782260426094965, 23.913729986007123, 5.916262220005946, 11.547655878589511, 7.566208436972218, 0.5140027512495132, 6.603099044145342, 25.114490036157306, 13.126248231181918, 3.32017483610181, 7.301431384626415, 9.62021877443864, 12.912228358350871, 3.7572152727467767, 4.892279059665825, 8.742758917254115, 8.864213408857708, 5.952159016887555, 7.905892884295723, 10.704502025189939, 14.77801920646186, 13.337293824900188, 4.197250824151464, 13.040724683724996, 5.587201686236426, 10.658761561741503, 4.506988551362735, 12.116991357011159, 5.4385078339104265, 11.750137005692412, 9.886094029010417, 2.797890846096096, 13.257255348628203, 15.434632603177889, 31.301649313823084, 21.031348941387478, 19.50241233785641, 18.143360457287876, 9.841678849934233, 18.666625238737787, 11.416964355747144, 34.77726560232245, 17.07719811726002, 4.1273917511378535, 21.60215096536698, 24.36719981123805, 4.3929558231112145, 13.159067004148612, 1.7693479370227112, 7.455134819707652, 16.4803291472972, 8.106148142727829, 13.941957858149426, 7.188088084604996, 15.035160585908837, 12.584750924373493, 15.767887098344453, 10.77044961841191, 15.975463670765658, 13.39159162943851, 10.040449798205596, 18.61799327657394, 7.151557150826483, 26.82500297109701, 8.991873535215847, 15.995684834314972, 14.118181918794743, 12.37071018604221, 11.073554088882434, 21.06297341103957, 13.3212896664807, 27.739892667856754, 17.20758097003332, 4.465374787328531, 22.629864505635673, 31.279585411419628, 17.870678790594543, 51.03281824207483, 30.673100021788645, 18.704751857940412, 25.88008354465698, 10.320723139666722, 23.41626426403821, 23.81812021598304, 20.70189084793962, 20.46819083912074, 43.85231521891965, 5.398734667864117, 24.66806862253457, 34.247089352782346, 31.391940733684333, 20.06291448436824, 14.060611920357621, 32.49161148638269, 17.31653155186244, 22.648069427404184, 25.76662657101343, 13.84530735849341, 12.54501910713889, 24.321347034913824, 36.18059900867895, 25.69139988544801, 36.37735400369422, 19.577242157395226, 20.15431860124181, 4.5294491881998145, 66.12589647354825, 37.05680306477752, 27.88832948713578, 41.86266783093668, 27.666024437740468, 25.01309211933078, 16.486822432747605, 33.95295724309378, 44.07986560190188, 36.280987854750336, 37.167534300636014, 34.827212655296606, 50.48595629140986, 48.58322975802086, 17.525889620794196, 1.3257826437898799, 25.906730481847504, 51.69134576005174, 44.70761398815176, 25.342962781306635, 48.58520853628577, 33.58942367153492, 37.18526033346362, 33.98197674889909, 25.30966729450835, 24.99167169380426, 17.158621724573987, 20.99627562297529, 18.35995060761353, 19.084410974676718, 46.15883368276774, 49.972036532197265, 16.562957008825464, 57.071210301236455, 32.337893647130734, 22.880572942228397, 25.065776940979724, 41.68338021971485, 60.47294698614457, 35.51318315106989, 26.34403676543362, 29.804305403034007, 28.14392627044833, 32.21297465318708, 20.91105562142683, 74.15156575764904, 38.14013936739589, 40.47449216788359, 25.863777341115494, 35.15130491751479, 25.597975338420202, 52.49759802786953, 22.317133413571252, 44.993791449575035, 2.031631280117488, 51.76097119947288, 20.898822985175645, 48.81639595746645, 39.0697140254427, 22.25195053156039, 35.400272362724166, 38.41084515494928, 22.48395547690861, 64.42117245148164, 24.64845906737878, 38.14602075744043, 28.97548571003616, 35.596930526846336, 46.03136237135081, 36.75981405016684, 42.88605442143313, 100.30528192680603, 54.31687388733297, 28.59595982599104, 26.37542498660379, 63.263768474045015, 39.70698661962173, 22.439533772065836, 16.96373093972651, 38.20412636165979, 62.91366019785493, 51.29702436567408, 74.62777606519712, 39.361918247107255, 5.660370789716531, 72.20866800969986, 59.64204602711093, 30.005747785859263, 37.12101121194254, 49.749453768878304, 21.280604299485525, 44.803841969612066, 35.85411382618718, 31.061907422402417, 4.980225790788877, 48.08538323168655, 27.76246878643443, 39.60126112039394, 45.130758795568205, 40.205721918697996, 41.62973425675602, 58.70044120776015, 51.153518252781424, 64.22383565849469, 38.361193051192906, 40.15987312413889, 26.679159367900166, 21.736516322518955, 30.330657336636484, 37.052673551748136, 59.370937741511945, 83.39163590718704, 58.11348179964664, 38.5838605592819, 45.53200794555994, 59.883571221232486, 47.96745915750463, 43.02141310576284, 96.86651395051622, 105.39948775959091, 30.640021917593195, 59.13318903284967, 46.43246221455976, 78.45156021610056, 47.39872595768726, 64.29898928971222, 74.34485047144939, 34.084187308710206, 38.42456747045572, 94.19801784541636, 56.96790594312489, 60.59711430203326, 31.380303670859924, 160.23135613957837, 50.023024926836705, 40.78168320676567, 4.639430656246602, 44.917438601867616, 56.80579098135818, 36.71950726473542, 77.1395440038791, 70.1882880294061, 10.056202532639558, 75.57526102972759, 31.283043760476637, 64.02989531362576, 12.97526885185214, 54.61169889027975, 43.915658020367786, 68.97081479761411, 40.13819392049695, 8.85798396417812, 46.34190873024533, 117.87319082277547, 66.11342011332201, 139.56723885420033, 94.16264570829368, 90.42554913178196, 53.25849149717229, 34.37338050563535, 6.000242561485791, 37.96438247634979, 49.27809139707852, 63.81256102632719, 84.32811089363159, 46.363100536844016, 57.62967509991524, 36.08380900160237, 178.40249304308165, 146.20431979502092, 101.0400173010282, 37.45857956998651, 35.068869429836944, 102.92436629819649, 41.225495727271884, 43.48712766050423, 78.27064685461708, 74.41542935330872, 130.49616419086018, 48.40441549634967, 96.37729506668086, 47.15825911867496, 43.43952385942413, 38.40978832770013, 8.728241638138226, 38.88341643010539, 7.346659478303014, 42.21709489231106, 36.40771537582899, 26.07891585544949, 46.916588883539674, 46.56189864852234, 32.31980926645424, 20.514908365460187, 65.63758763515837, 104.24120036090173, 90.81147314116176, 6.539619901538163, 97.43187839034725, 60.16395767935119, 35.580754249198776, 61.398744629780055, 35.798045534309864, 78.45909111552055, 82.62653501212986, 37.789819986137374, 47.02179620717648, 8.51298212862278, 55.40551329583538, 61.768394624960635, 64.72207043022759, 54.436683747226965, 104.08976746459169, 34.50567682264381, 61.29183650258999, 79.52738562875696, 8.53944387475681, 104.91443587259268, 39.03246485175447, 7.08273651787089, 37.60926736712432, 37.73203105623934, 37.36442954763615, 48.28709520311699, 77.37100633507607, 39.670249243335526, 34.951537901445946, 139.85762065165503, 73.35138389954716, 115.57995344427152, 48.02408558008701, 110.24959535465773, 6.685131656263097, 77.64032928674273, 53.93832305273668, 35.58210842304813, 48.4399488120103, 108.79438835914563, 51.9357655785837, 38.5659332713445, 57.44672621422384, 52.97529625905956, 76.25305277567311, 28.45973523762749, 61.253623240593, 36.13411725289958, 73.10682500186218, 65.14132584516504, 45.57591196337417, 28.5446462010657, 98.78915991651701, 151.31821362026932, 41.654885398828235, 74.19732616329654, 87.21252633066753, 71.2663023943255, 32.47376905905552, 50.638944731156094, 82.33447368728571, 47.439133495693625, 43.187705914347895, 64.45283411032102, 29.183566218615518, 63.44370149123032, 31.33076774711937, 52.76596290701715, 57.2509055555088, 61.997778574995216, 26.080093518935588, 36.60183955870805, 66.42529624387288, 56.41362334220638, 35.49512578438432, 62.492968979845045, 99.51070160876742, 36.47220394404286, 106.17322547946227, 41.922070444091204, 73.0326389016485, 104.84261155006837, 59.88071857592007, 32.54749011883325, 91.041451821892, 44.142463334986694, 33.80605859430692, 53.132120769183125, 50.13853702713732, 32.89047871350658, 65.67734110595835, 35.35273999406683, 97.38709022547985, 194.61469839820447, 46.04507859486678, 86.55114971598596, 48.265065673840624, 77.97897610332696, 40.81512701892442, 50.58186746326103, 54.881910189429604, 41.02490068737602, 44.09991262235779, 81.09103792673116, 52.048284814847804, 41.9181444663499, 9.09786112261639, 53.616287165755665, 81.28813552122112, 158.47989841982002, 81.69104923982627, 94.65299537513033, 40.5656443697015, 61.83932355223557, 50.341247844256785, 6.392951309236307, 145.50622218248816, 34.80537532434381, 63.99672110613553, 86.13466081357625, 68.984715059151, 9.847804298873395, 85.09927874848673, 83.48750802927782, 4.3698114923786635, 102.07152004010925, 50.93255796016027, 78.50792078391709, 7.086147926545102, 55.183418905321034, 40.42453586836624, 77.63435080329599, 59.29679454679922, 112.34472213336208, 65.35048366719259, 46.14602201797251, 76.30049274069356, 56.55215251932044, 50.70467664410138, 39.80945809336516, 71.3538175386989, 67.27693243520363, 82.94703231909432, 38.27088072093486, 83.52665957662909, 82.6656317485853, 128.45575427799758, 39.405325381672675, 33.435236548677764, 47.86650415852333, 4.924568658965381, 54.40897216647606, 71.90165439486339, 37.89329910726344, 70.27659082518964, 44.33151161947488, 51.74178536873088, 35.69982669356389, 92.80061263096113, 41.38016089329654, 58.17975907783789, 68.17877490447853, 42.14639668081742, 87.83135142677928, 65.75250704952074, 136.74141597130102, 67.44427942279698, 52.60384574371393, 91.91520582623173, 134.75567278101127, 7.087908898122953, 56.251637684943645, 54.70301062020871, 33.384118233832446, 5.291154277820578, 51.84744462497908, 47.88734021875598, 68.4045588600017, 45.23867031762343, 47.34444374371623, 99.68684835351353, 41.703443079348745, 6.790113142161861, 42.15256487495367, 134.64411802949377, 58.083851064987854, 50.05134640375782, 40.67611652878609, 43.77946246328429, 61.93119909026521, 69.54518946256096, 61.185333656304, 97.51666955883353, 55.573054759860725, 6.488214141174404, 59.425229499509385, 38.69631329812943, 179.1958278376241, 76.58302669030623, 55.845360928818835, 68.85177085644702, 60.73339176327268, 211.66035782793074, 54.1629213522294, 49.741311940866034, 56.30510219886949, 56.459764020140305, 49.588858623042455, 114.69671836557279, 55.94815495045215, 255.3285677122259, 109.98794548164592, 92.0331188060071, 6.383410422058301, 105.29289931040063, 65.52099801609594, 62.84159992086636, 77.55215714535338, 46.1826032194914, 99.43421580698651, 46.540467605791726, 53.24640199494679, 73.43580929701604, 36.88079713541203, 74.23181188718476, 11.73651070118089, 73.84790243754414, 60.94467580180048, 5.334708343418195, 101.50203214206184, 74.1576860767021, 61.14437064984541, 77.59228743467156, 63.064122284871054, 63.166207168405755, 90.55574878580842, 78.0681914013716, 48.77204666311201, 91.10584502280781, 48.361940309536685, 95.8848739563639, 57.07037104264474, 60.123057182910884, 122.87096335058227, 47.804805147411045, 46.971652107277365, 147.7534848784582, 44.84510749567689, 108.28187569603794, 40.50748896235796, 95.45055547393024, 4.532395941078563, 49.40026086386911, 73.39238789890132, 50.18805535045539, 88.59647693649373, 95.8069915320493, 73.62143469555289, 47.14456785318755, 95.52336643233585, 65.33337752126663, 57.10384348304376, 55.592921324550865, 4.719184752893318, 53.481924042723655, 79.62261892099832, 68.77669793670525, 47.16186580005167, 39.37841367252719, 134.80801619203493, 121.06430724104004, 74.17332378025814, 45.34150603449863, 72.44661126447458, 40.28928338454787, 58.72096535977705, 101.44734463879234, 84.94074845182286, 102.7151992511783, 341.363794456509, 47.32266749677891, 68.24972446018866, 54.44667362683916, 129.06503986543328, 74.32690449613206, 109.36646240875493, 76.6264401089489, 81.68068209224754, 52.4562439271518, 104.77252830083273, 50.038613812505105, 134.22962064650198, 51.725471416914445, 33.99012586543849, 98.71820805021306, 46.87640666110488, 72.5058606287396, 41.99040537072758, 71.22111002590069, 94.84390304282846, 115.22098372665342, 133.80228603164974, 54.99170636063493, 64.08519319517514, 74.9333032760452, 67.43831826092553, 110.13795904048357, 116.37889372809376, 46.94137561471165, 54.852670939913494, 36.44725194969447, 56.16424070733202, 102.3778093783781, 95.17760895095093, 51.10904908900827, 47.22572946393316, 44.35744585498387, 55.62077473729272, 81.59429061679161, 64.89191759147899, 50.53190994631244, 45.70848344819375, 47.242964096318666, 53.25308367486118, 53.493866248733454, 50.82133305092705, 54.52002064830322, 45.44723940943221, 39.78834949797089, 45.64406815780937, 41.245044952471176, 63.665772389559386, 68.11525272358449, 53.69508956951835, 8.390622642305692, 46.00894816993943, 110.65658945140545, 44.97973755763524, 117.19076192344485, 47.970334708387554, 54.38503424226951, 58.05889157783156, 63.404041282167114, 55.54956781110259, 74.74047330065866, 151.22097299941007, 39.70108059905178, 60.83508343224249, 44.19232470231216, 103.22768614008945, 211.6284670883873, 63.91295418321604, 98.71238813085132, 12.244458427956735, 96.61424451420962, 39.38446166525076, 103.04047677145611, 8.234545579353165, 40.64266205411775, 48.208732263231006, 120.01788680323156, 46.65742936349205, 44.91147561574942, 61.750441641011726, 72.80644656895355, 9.761553979679146, 48.761889155910914, 44.626877029111256, 36.159389049135285, 47.848476673379196, 137.16925403347943, 38.50959506957257, 50.5347943777596, 124.45783419032645, 65.16978192138951, 62.54557051488089, 62.86605201937376, 56.39876306378638, 69.02280279211827, 37.72456275171557, 5.180016035792261, 41.60237227978496, 44.07570813794187, 116.44233929714093, 44.89616356162287, 80.13924727174198, 39.04537835115414, 148.63545723326237, 148.27692838444057, 90.26695763359359, 95.42114685078707, 6.244615744547013, 57.03304459487548, 77.94581567644829, 53.8124391114644, 52.920517370182466, 165.30986905061877, 92.41766888578306, 80.42731158181336, 99.98907677905032, 59.74340078711163, 37.500279264057895, 8.169478398845525, 107.64810546012919, 74.92618891308166, 94.09425893687256, 115.41281535701334, 62.47853584595595, 16.1682391496453, 79.88816370122542, 56.56314108913749, 51.02061841873122, 62.26722388918526, 117.97129858983777, 56.096059666233174, 134.94790553564567, 52.183041269432955, 70.70617125065556, 71.72532005036967, 69.04085265736046, 108.79889155291326, 50.70174335337692, 34.957991954569565, 72.23571364225458, 116.90349125706805, 75.58774173842335, 5.641869808603883, 107.14555906105588, 50.081332666580494, 39.735455599452955, 45.874226913812265, 82.14506251185695, 240.3828984481366, 60.14697186509161, 78.3213742063618, 91.06155374935344, 60.38865319987099, 67.8478595645176, 50.10057078292248, 57.81390118875101, 43.469006359257165, 114.04778059673778, 69.00446124050373, 56.768508944592, 76.21564518559465, 49.916720918754734, 40.66162649482016, 61.1896923345016, 53.691787733650315, 64.8244970649751, 98.8762558796364, 78.16308339682116, 68.18719648742436, 69.98605128366538, 55.97498906678412, 43.74256217779109, 51.81912008809622, 53.799855427354004, 93.79569413500629, 96.57398524089288, 100.94922298103718, 42.17074864053927, 104.53074926017187, 292.3174726604967, 89.5419288383722, 36.22826409175142, 45.18365034803517, 60.42910830343739, 44.830164861724406, 46.8893847258983, 63.92759551664025, 98.86339061683758, 85.9317359116303, 124.98601953789834, 42.635962946966316, 67.65547768316027, 52.4631592265655, 144.5667215373639, 51.79083710163587, 112.71823723968527, 82.29632620245056, 43.20252314250781, 7.033790430918764, 150.86456620600788, 10.497688994515851, 129.99313313367003, 44.69394159163977, 50.665210649905106, 61.78384823800027, 63.704622311113496, 70.30979496219189, 6.334181999366464, 74.52955471276441, 54.47274461033372, 40.35533562525497, 67.78486595471776, 170.97631422110385, 45.84899207605473, 45.34242888555908, 80.98941293602981, 49.59772933473961, 50.63609271339685, 52.85091824655129, 38.75629738845395, 41.43084182609584, 51.63187483438901, 66.00082022940913, 58.50195405226803, 48.99988319162312, 59.037549633196235, 57.11094011265616, 65.76705350589266, 52.38727944292171, 56.513273954725186, 47.8758559205858, 43.82078715679211, 131.46598150191994, 48.51427984450133, 10.933032239845211, 153.99544169287716, 66.96335498949405, 89.81515451003104, 56.5613366497317, 81.80203751460031, 62.39975193110215, 47.90185407405338, 99.1206689448293, 130.5027551163164, 72.32930186301174, 63.405898522077266, 56.32563127169843, 39.712752385243256, 94.63946497862791, 107.88117503453894, 4.303809325341904, 40.21452949825527, 116.62799613293332, 65.04899543705653, 152.7469371403321, 101.46473962320968, 82.87206787467855, 41.507392636467095, 45.60925211685653, 89.15681453683914, 69.57574253473999, 114.09676255396049, 88.79560780168245, 39.267565171319085, 46.78611952938101, 127.47018345714825, 39.690138123253334, 42.04793236651825, 56.37039992076067, 50.22607097090121, 65.97965333859838, 60.81488415003473, 7.955248249365607, 68.7238776208113, 42.1134954535158, 91.05573257394155, 68.64865320296128, 67.88910076781576, 88.74229931949786, 52.12900703873796, 41.92991062171162, 61.58513964160367, 40.07225155893067, 101.51995012746647, 52.13521493310728, 41.39217959145813, 45.20693621298297, 60.843500151943545, 108.90033717217288, 80.29811829923695, 41.026453144825744, 82.13238751440198, 168.49505979271134, 38.35371805052404, 33.70604618278676, 44.99313797097163, 113.22119023247586, 138.80908705413677, 86.56076641129117, 40.87958552875943, 8.345567160448763, 37.0986514250683, 57.85767145153713, 42.56773946214999, 47.35831412475848, 90.79589876260492, 70.2714036084462, 47.42623368929489, 65.48255183609852, 8.562261678011323, 42.658109637236564, 38.65019778179774, 109.05605523037114, 81.67810305348587, 40.731146739306986, 136.08974259404684, 16.905961330882512, 78.2326430749701, 108.77442824148959, 40.04254851947619, 129.72786572367983, 141.52688683269125, 54.37063731597738, 104.56524215712093, 75.31835984575808, 56.59192933845098, 92.01138706337892, 78.55657042727846, 60.70493593651376, 47.167237696271656, 71.72656935984627, 120.25332554204704, 13.352791746854717, 49.39347557933587, 67.77421460733703, 60.61008479561856, 56.39526927340809, 8.415968613815437, 183.61549336094234, 54.632926628176484, 29.199031769261232, 74.77335477248499, 59.73660568606594, 43.96038074504864, 78.60653430447135, 99.83799328581472, 46.12687688502657, 111.85048454670613, 87.01915560722736, 83.871413604316, 59.67909207796473, 121.68597259350081, 137.34200422499515, 84.76923752569775, 52.8232002749052, 50.912655468887436, 33.32589315947028, 88.82061044957116, 209.12893047031073, 49.74187281307251, 60.57249077209105, 76.90814954529858, 68.2756800087326, 100.41993928589642, 69.6840060478939, 110.24356416411146, 49.14683012755893, 9.518350118005083, 65.02516213933076, 81.22623239031866, 42.81330836405431, 51.96434381340433, 60.64725722344636, 54.28421015598945, 137.61274189632658, 88.46183536396208, 112.08298334972476, 48.77594429247814, 69.61293977579261, 54.330893250221976, 65.5820638282723, 64.81841242063877, 115.00114260748876, 55.3932388841304, 51.06137507261755, 39.31318872615676, 49.13458338311278, 36.19642138757603, 49.24375719605987, 131.54846705471542, 66.27533813566708, 58.00492724965547, 51.076408468386425, 99.955605458909, 12.396402254059282, 42.13988353627989, 46.43326273071129, 43.73131916851289, 115.82866592889755, 94.44069679014018, 76.10687331148074, 82.8232208278608, 64.342221792548, 103.8375104425935, 47.190676954668085, 49.29453450671916, 59.72447918882262, 81.58540090003665, 55.38644508236738, 56.61898978079963, 118.08688627165543, 60.463788380794625, 81.49244282829909, 47.726686297057036, 57.22861375481003, 50.49745001533832, 143.348593966447, 97.33205369194135, 81.42942925884498, 61.843047881240025, 127.89902557073074, 47.426319065150345, 128.1325571182827, 48.025797568793394, 197.82238504376974, 11.721854181666465, 5.217621636754181, 5.964731897259467, 163.90856894071396, 59.51452527559491, 73.85089519538586, 44.850346402516465, 51.93444372782192, 124.85908785463617, 52.0397692634748, 33.3780922368806, 78.47479748301527, 75.39716343506795, 49.30721011173214, 88.93201748614703, 80.18562977329418, 48.51947302815968, 46.24346246653622, 55.31254368872509, 71.6926059354124, 97.94139065152446, 66.46834065353232, 35.76242282216497, 38.173287108483876, 123.23122513346283, 103.73797686768073, 91.70887694721297, 51.874192407512226, 65.74838858509932, 55.10752332854938, 58.16961178614899, 44.47712898220014, 93.87893926211169, 46.49007054936428, 67.62969380738797, 38.78129917794589, 38.712034595722535, 38.87231735633039, 69.50747331887115, 131.31898882617935, 152.6408956434924, 163.2421974364305, 50.00906062939488, 58.82648101131156, 77.20512625701954, 48.685372162146734, 6.428511195698019, 83.82980729984648, 64.31754144868556, 115.12613717143059, 46.44543587574337, 107.82028407579031, 55.92593421654203, 23.269738399639827, 54.32230474616173, 86.82082219971846, 120.81617604966678, 56.536472030160546, 7.743470727864152, 49.145081701275934, 90.79578052955134, 59.00628774195508, 109.21768945861682, 63.787054513547055, 76.89090887653623, 61.0027834196072, 72.72322443284199, 70.73468315166433, 129.52255335416413, 41.583405891619236, 175.9842460697283, 61.55230940649245, 6.904124580697437, 172.493604038512, 74.1679289130222, 51.35326386452526, 85.97106870583914, 80.57128231241313, 204.51959320454196, 122.88146804717032, 148.72488072572372, 43.33081635135752, 62.431858285336524, 58.76386718151956, 8.521166608774127, 83.61789102454168, 190.9014719475978, 41.88823949407376, 41.03648081499066, 23.951082395534197, 64.9371196042597, 102.32652597541392, 73.660021944169, 50.78028356782685, 129.41290690455304, 53.88528511832251, 49.85887220893611, 72.64769471839408, 56.84622136281893, 62.34687888671744, 66.49626005367143, 62.9046726193134, 114.6290678199142, 64.31445228829514, 68.44311264989396, 46.72979954413199, 105.49823927334198, 144.79654266682954, 84.26998950388487, 7.832450097009383, 28.479828024852402, 80.02481764250066, 75.01562888069684, 129.47331945561095, 50.28159779537165, 8.12099094222702, 55.19450804287009, 161.9764737239908, 51.289199176602324, 72.50370646733288, 89.94192831644565, 130.84965455739703, 51.76511833221933, 50.86894593622153, 58.71490772336535, 46.51461251208806, 86.24624260445773, 170.04022503741345, 64.54887201944429, 38.99610538059727, 38.851316156602046, 70.56189344381659, 62.30975239457135, 60.590405175548504, 88.92829243493426, 89.60597467636845, 60.83380698639083, 57.71098031056974, 49.46877260513046, 74.82984002278255, 48.62178538518155, 225.40959376098462, 7.3392243159576225, 66.25215234640459, 46.006462604773, 4.820664234820738, 47.61045870285482, 84.90526825559695, 90.27512831727039, 49.469775537142766, 152.63107258807284, 29.51123927552387, 78.90745093288453, 5.904120372828192, 120.87839896016419, 75.82721324657183, 59.3370156051245, 60.43454444022133, 98.74330647224754, 113.72473551004039, 32.12400340757845, 62.29586619058515, 86.45858960639382, 59.96514682598374, 5.870540891063064, 51.70529074561775, 45.78819743783818, 109.72588643291485, 56.02848897131136, 53.9266318745306, 53.165509387583036, 60.20775151596131, 71.47829171907112, 7.175474330902403, 102.58290313685885, 96.12895450592507, 61.66702642403156, 47.625175167179286, 39.74763029996381, 120.23613785153009, 6.2908645688704015, 66.02065074822556, 82.79777610374869, 384.20261982621344, 60.912325007266396, 116.49184726772901, 45.291812753797366, 92.83422701378443, 89.5725147174019, 56.47793334113686, 81.05920107456552, 60.170678675936664, 44.70476793335284, 7.320807380224901, 199.06560273770359, 51.56223001139137, 120.4626883302056, 55.49793693467967, 50.857838907716406, 96.51532644587978, 116.94300858728123, 61.782969357949725, 9.81906760270409, 63.42881982669784, 41.43040792851002, 88.57882087392356, 73.17169586166035, 175.77193421564075, 52.1111575103445, 78.89639759719076, 67.41313967477475, 42.623359103432534, 54.753428660039724, 47.335221015038876, 45.30075216021207, 47.50674140506703, 7.614475247142003, 53.66580885085225, 88.19464311710621, 15.445275179398275, 58.72717774820617, 79.58112247543242, 63.889582811020155, 136.76089122606447, 153.6005394884596, 44.61976268496081, 179.07375584649196, 7.047565907851149, 130.104373057798, 118.66366954831553, 65.25761591579331, 5.882316372607879, 83.24021946510669, 73.70935117922974, 56.34724952080873, 49.58414576850661, 37.98804600881493, 51.355836355581694, 56.46378832870581, 66.84243462268512, 117.18032157002405, 8.648372770160938, 78.14397673567152, 89.22972099305649, 81.68217597444138, 73.87976286423286, 47.598794119086875, 9.323339037783956, 224.4950685750886, 53.504569763052, 61.4147642831717, 48.826232681602356, 57.65457819461456, 115.98352050031399, 148.14729123154007, 145.68806309443028, 117.51410753537385, 42.06423563577702, 82.24892499846231, 63.15783665572995, 58.93477043060618, 69.30214420960104, 52.43670764749947, 12.110198680972275, 51.11537418483183, 100.23918012650223, 55.16535843931812, 561.0109571696887, 58.127035520985544, 6.908153901890331, 9.072133057400956, 136.85162383263082, 44.57085865699339, 78.40793954143604, 97.09984795170472, 54.398554494082944, 63.48041553363936, 58.190559555098474, 66.45157415120313, 65.27812825075543, 83.79304250735727, 70.82182892425638, 81.92297848683063, 41.39738511266172, 113.71131928497618, 74.2985208122062, 39.92339501725498, 152.7077298253563, 83.02270722240802, 99.78688972897113, 65.10381056353879, 5.796978119694909, 39.817231464985575, 100.538040150826, 62.13496588044188, 56.34374563503983, 82.09336082142498, 66.18093261916937, 49.563575857823366, 86.81541530489562, 39.53722498773808, 127.48317336796389, 46.12133451223203, 57.16722444994811, 183.1701081832981, 40.23834535181615, 43.58142558912027, 47.05204303595812, 70.71717780655608, 77.72958734915218, 5.673148569336339, 91.83370872594722, 113.92920731568458, 10.133120914748236, 88.09868931341244, 63.862162904193134, 40.40835849708586, 113.02558255017634, 106.92268864667193, 90.42615348906044, 54.30356361690185, 106.22165632490241, 47.66743940924759, 101.27873612830325, 5.935782898428051, 96.46526914699265, 62.120824591241984, 107.32173361548179, 77.68026648138603, 67.62246689029449, 140.43565914213605, 42.5121917077332, 94.0378477037523, 105.22482840794206, 52.563706465439736, 193.35972708732461, 51.53252509202364, 43.05827428670331, 46.36016702950025, 90.56142479794495, 56.50277513174473, 70.86947596173488, 76.10224376308483, 43.13093710124897, 95.77643295349517, 71.35696011317495, 12.712812692467686, 47.92966234341778, 82.38149097598851, 133.1423771139004, 54.66963454908808, 70.1532098681905, 64.44008295173438, 56.5660421164266, 113.8285709835474, 74.19514000274467, 49.59570472325412, 92.91614757188927, 121.89722050432047, 54.728209921158005, 47.305001684085475, 68.8085525655267, 120.33851325420393, 76.91363234539789, 73.40821880661036, 47.396852344666456, 108.36077427106163, 73.68923387033114, 106.14449350822618, 81.54335551341462, 70.31938224670151, 58.803023935202226, 76.4264529245811, 65.3322538486428, 102.74312531453887, 82.7818147628525, 41.88483951632012, 52.02129645390934, 39.136331930535604, 87.58861790738092, 241.53743032658014, 104.0107661453121, 53.99867959202893, 59.18894179848156, 111.822655700736, 107.27576707298952, 40.11902560014746, 109.15470145444257, 236.47939006247418, 31.716192153924048, 98.4106933267744, 11.281630176945868, 139.70745957100283, 41.1173395552721, 13.802654696494585, 52.62649021796972, 61.62315004569592, 47.266190636936486, 56.96268094705057, 62.26325551642578, 79.88203738500289, 136.0590069598223, 61.97401746498972, 53.81047692043741, 128.30468146574873, 55.439247485955576, 79.69768769396345, 92.07428656720882, 58.02710596384888, 42.0671717556803, 56.46152834562566, 73.5393219710717, 38.18542240900255, 33.16831315015013, 63.938802900242905, 51.4601207392176, 73.10261461700203, 58.054202020961064, 58.84773931076223, 59.435256118791536, 54.920381889655, 7.278196139938598, 51.952953876848305, 75.26987724895349, 84.0515124188558, 53.784896595282554, 86.93606276730677, 18.65534463189007, 77.73272036403075, 12.525571989269446, 40.79328758790398, 70.49399375465121, 81.41435057146, 126.15969302510725, 61.7833934856785, 106.76159044573531, 27.554803109593184, 164.79409621873435, 51.81202820701773, 78.11439116332014, 104.68159417517433, 59.30552667783056, 79.36493745818731, 190.99877607985846, 58.731178658937935, 9.163717396534286, 73.40368902068718, 75.75462871405949, 67.8952686547854, 91.56175474693602, 38.63986365463857, 56.998070410376855, 60.70780042439048, 97.57543727148864, 113.96506552043795, 39.0872485450984, 76.34705733719566, 44.301666876565335, 71.35003847810465, 16.31419016970561, 114.1889687404366, 213.10164606220863, 69.48660540959206, 75.23076220824477, 44.363904815077014, 6.730570222868479, 73.25350800016572, 58.8674282571513, 40.63698893778971, 69.8156809137943, 102.54943325244608, 94.96913460641721, 94.48469236722313, 51.64244935439394, 189.12353045112172, 52.39317453832961, 34.413228612895665, 111.24165465836683, 49.50069176570959, 53.00071656871003, 55.54760069462058, 61.364758534347565, 61.544800753144806, 118.430157064406, 85.28684902123548, 57.188904272903365, 88.1573928618147, 68.39631920034282, 7.202178741471178, 56.06942374118284, 44.98195497613427, 36.16523916010935, 52.738500355134434, 101.75809631806837, 104.59605486314925, 49.47582362180202, 84.74086543352841, 73.7912985476167, 72.03437229240248, 59.23875433266101, 53.012405476687, 66.51062439928849, 67.84305740983878, 98.21209270277268, 67.69480134375246, 108.96629549527634, 85.80846102884445, 94.95854444203997, 194.3159844965083, 186.96195479141804, 54.58895776225684, 59.67597022660837, 216.0385248283692, 145.4986365105906, 63.99317996182356, 50.46411428312201, 89.3993464320784, 73.90288265773111, 141.10019304732927, 63.8909664040065, 46.499037773815814, 61.340931179448205, 52.348120244160384, 15</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>114.5703678131104</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>70.6198842424816</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>[108.6068115234375, 264.6373596191406, 69.32459259033203, 126.57628631591797, 132.0705108642578, 38.94092559814453, 99.71328735351562, 111.27193450927734, 56.55049514770508, 56.696563720703125, 180.89158630371094, 28.295408248901367, 224.11093139648438, 130.0493621826172, 87.89945983886719, 77.35881042480469, 117.35907745361328, 65.85430908203125, 78.04331970214844, 162.3276824951172, 88.30278778076172, 210.5742645263672, 155.2653350830078, 133.19747924804688, 8.667086601257324, 15.833881378173828, 127.92560577392578, 112.91738891601562, 93.48584747314453, 205.794921875, 113.50288391113281, 303.3412780761719, 83.7910385131836, 129.1955108642578, 126.75804901123047, 8.039782524108887, 53.826995849609375, 84.97117614746094, 90.39070129394531, 59.727073669433594, 250.5835723876953, 88.93842315673828, 314.9388732910156, 49.45927810668945, 46.25710678100586, 127.77964782714844, 54.94021224975586, 151.74012756347656, 307.373046875, 52.720924377441406, 64.7410659790039, 61.0701904296875, 64.38531494140625, 77.9032974243164, 67.28387451171875, 183.72756958007812, 81.19929504394531, 63.225669860839844, 287.4279479980469, 60.17253112792969, 85.62043762207031, 55.248558044433594, 147.58840942382812, 261.9767761230469, 73.41456604003906, 79.44871520996094, 53.42506408691406, 103.59230041503906, 69.2796401977539, 69.46863555908203, 54.90668487548828, 79.44036865234375, 111.39195251464844, 109.54590606689453, 165.46873474121094, 90.08563232421875, 181.379150390625, 73.4162368774414, 162.7654571533203, 127.72393798828125, 189.4305877685547, 74.01566314697266, 135.16981506347656, 96.91646575927734, 71.83689880371094, 240.59515380859375, 189.6961212158203, 184.6401824951172, 48.5579833984375, 38.78030776977539, 124.10890197753906, 91.1418685913086, 246.85169982910156, 61.136627197265625, 50.83909225463867, 66.56172180175781, 72.48876190185547, 84.29359436035156, 68.54208374023438, 288.2903137207031]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011848</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 22:29:30</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>88.90975221052868</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>67.59705042693497</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>106.4898742272437</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>4691</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>[1.2068281541065444, 1.1853325982408638, 0.4909314715229599, 0.8726940065356127, 1.3253621115562093, 1.4828635438670146, 1.1390433446468042, 1.6752407148957515, 1.0978466288883013, 1.0104465866728973, 1.7210364462497105, 1.9745624901273688, 2.198132714545031, 2.0550883446580532, 1.063319819549325, 1.869280543856182, 1.4252948315805787, 0.5775146722690798, 0.5515879367436849, 0.7989139696647262, 0.7545084428326492, 1.254356530985163, 0.6449987720311602, 0.6044761412946329, 1.5057427416687696, 0.6816212312394893, 1.709210730654417, 1.6594907798518395, 1.2198889725770152, 1.7495331471439481, 0.6779031051061591, 1.99102357129054, 1.437491385103216, 1.8790567532425675, 0.927126296263185, 2.069272604693475, 2.076122579091177, 1.8454930228262627, 1.441619067812426, 1.1037978264976542, 1.6087092608274876, 3.1420232444017158, 1.9481532473853649, 2.0540286705922415, 1.3454105578106512, 1.601131546529009, 0.6186665420741517, 1.5218439162894426, 2.670731085941399, 0.8127255677172729, 0.8642594205374039, 1.820268899978585, 1.9572991546065635, 1.4958398473192316, 1.7189667451894322, 0.9777606480920581, 1.6352323327693887, 1.8976360111781607, 1.1871440896305918, 0.655124730029071, 1.4381086039301594, 3.7613375370755895, 1.9646825432719643, 0.37966761173194696, 2.0703958991317006, 2.055989316002866, 1.3748458551025522, 1.9184882206856786, 1.2911946796617613, 1.6457167105442665, 0.6941883115409355, 1.1581206485555315, 3.4630694312035217, 1.0797645981286859, 1.765073293729107, 3.699276091181204, 2.2529104158713142, 3.24691022904457, 4.327617970309831, 3.264502642514409, 4.042295226929689, 2.4756679855487147, 2.1999774508097554, 1.4967374185699378, 2.5765847824682226, 3.201966191882914, 0.9865753614234997, 1.180216881868734, 1.1697183081008613, 1.9933453245486188, 0.8866860815465364, 4.161446891055397, 2.008975269691576, 4.1128331809861285, 3.2215465684380167, 0.9386024428085162, 1.2191307193182852, 2.7214133094300172, 2.4015098389818306, 3.292276480931438, 1.350591791705719, 1.741772664450328, 2.0630884013336015, 1.3913556655154558, 5.852571447722443, 3.456848606821857, 0.38432358379973586, 1.3130310925439574, 1.4893185787865946, 4.682811800570404, 2.9535582196612484, 3.249356901043062, 3.252789339484856, 1.4762400611588473, 8.785047525272633, 2.517143571615291, 9.003470344693218, 5.347838524880125, 6.013263336336945, 5.664900975040478, 3.3072029486920624, 4.0797643812935735, 3.5230088751882853, 7.5590333793118765, 5.651042395903169, 3.195744157040084, 3.754154962239911, 7.8645250612603075, 3.9658499268188687, 4.347158144601728, 0.724463265519367, 3.5135990275010536, 5.387824638595863, 4.4085415115426825, 4.560162489798085, 6.277038472756609, 2.44935603261982, 8.109925046565431, 5.41682620170933, 3.6324010781167986, 3.5883043364386626, 6.849865682970028, 2.580993980605448, 5.476646871241453, 4.872642369578001, 5.571267485280892, 5.697108283521155, 3.9288729363075054, 4.392566069610008, 12.004477886228589, 2.342612577592539, 1.3879730662585172, 5.395213351982907, 9.97331010844363, 17.437609500006158, 7.3214907707590715, 9.391732227447934, 9.009112889107117, 2.0787278852812516, 9.46034084181489, 4.906744696199428, 9.076975299578118, 1.3933799595071577, 5.223459539740141, 7.165711024485095, 3.33698866897777, 5.699258976222857, 15.4721265436844, 8.060335811973824, 4.683140953426957, 5.0699195189517505, 5.9092188063679885, 6.6086800311769895, 7.027891459418051, 3.762083316616191, 14.676867580023849, 9.04988210031498, 4.871663731497736, 9.88390356907079, 6.566053170686409, 7.675058902979193, 6.6302109843779435, 2.0769006976816726, 9.882777089374962, 1.08516863933646, 4.369533754025515, 7.639095851424689, 11.064802687176034, 7.219285993951759, 9.336541678988207, 6.897917205645369, 6.455182488547256, 9.008864129027787, 14.141488776611892, 9.95979052499289, 24.223480387023546, 23.20966733829981, 6.561511113830535, 10.943263954764983, 12.456893964798908, 20.69522397893769, 11.281383515752783, 16.088772711536105, 11.814287504896788, 8.383128718373065, 8.878847560419578, 22.444747544599316, 15.526400527793491, 13.13278342875768, 19.940685738051982, 10.100143207931987, 20.424053982124125, 19.29108537928807, 6.50946189451066, 21.89869822372119, 12.909140789289967, 19.860921256751883, 16.2383350314007, 14.603001318104148, 12.320527039866322, 11.949153002696395, 13.456623573350939, 16.220352926860457, 4.294071448465473, 10.89576225729857, 15.584585795965694, 1.836500366390369, 9.202767810360198, 9.148292089008153, 21.434665578398775, 21.376020892291706, 17.388075084877347, 21.007479897577042, 18.28098878208685, 15.028581175523374, 1.845235170137627, 36.63020394255377, 8.840184617620723, 22.391710643409883, 19.074668690514038, 4.746015990245531, 20.672396015432906, 25.700563768995988, 4.845217492976535, 21.148110139984706, 16.831783174326873, 15.687364442404185, 1.4985586455553268, 12.967198451055925, 21.13971231789531, 16.305502134412034, 36.146730571678184, 3.8454569987286065, 16.263915134108828, 11.45042777655718, 15.195000747225501, 5.479373112301421, 22.10225494691249, 15.18691745457959, 11.576327936156654, 36.64479803913695, 4.215051146902361, 14.659560590723178, 44.92256436616548, 18.80495056939338, 19.455293366504243, 17.845859732325245, 23.94666244299193, 18.90279641173611, 32.24068650175721, 26.878041600808917, 23.95922654306208, 41.966208826540374, 39.2362324395982, 19.584245370348782, 26.545077391578964, 27.52741342458504, 30.883127261351657, 17.87051219278402, 51.47358898972025, 33.21859423095277, 13.635705045087672, 18.39795784954999, 64.34245053989169, 18.25405850999816, 19.709265034671642, 27.23262911415704, 20.99929867965738, 22.392965514136094, 33.98217388842716, 37.281873358487786, 42.26120161898232, 45.88203364470347, 35.502967441397786, 24.70609087574354, 21.509353459352635, 21.400233393615007, 36.7595786789823, 23.112357545227145, 36.95070123177538, 12.009234738648539, 33.04485701335212, 36.249079391512936, 33.237178886970405, 20.604611437007396, 55.90163420519553, 70.14402465786077, 24.85389692961154, 38.410484301929124, 47.455443929992136, 38.95137829191896, 42.58860714281087, 46.52728544014802, 34.668172854154676, 18.72368675785535, 47.30098017879528, 20.029468612165257, 36.49450014671893, 41.999463633329135, 38.833294534177284, 3.838929590493006, 33.221011152891975, 40.61056809147857, 31.233180968969826, 23.486896572987167, 49.800247471400276, 47.9282190105818, 24.160077901845987, 39.59633905300588, 23.222566520210556, 24.690082857863555, 40.606978253573374, 40.23315095242587, 45.363244314860786, 49.698226371564836, 13.460459891717118, 56.441445637436864, 54.88923901048557, 32.05174911923082, 41.60179453828272, 35.77852688699841, 64.56447443893477, 22.417583893830876, 44.845866666629746, 71.13475604903783, 38.195909626791625, 58.60826183803146, 47.80510014994178, 61.95722221017032, 29.725949210709175, 40.04872061721876, 15.454305166344769, 46.70435371653438, 33.27211692436038, 19.951379839882957, 45.79336124190496, 74.7423543395662, 46.49834051876263, 74.60984080505857, 32.82256517124233, 75.08285592871663, 28.586031966429307, 25.329634122742455, 33.080922052593436, 54.547369223041784, 58.98285111691722, 41.72167836427057, 25.362739580445588, 53.916710175216096, 37.41256954758859, 5.675339047443779, 28.641783367923956, 61.0820579242456, 63.99376254374104, 27.356936547899636, 33.509775009773186, 35.245409048495674, 44.259261314242764, 82.00259621382362, 60.984080240635365, 57.69733619704554, 61.46373216680371, 30.479700995726823, 28.31330359531648, 54.634248280735264, 32.699261121432095, 60.014698679322166, 44.980780126949554, 63.91215275583113, 50.36382392139014, 29.28259569055184, 23.382619007543486, 66.27178640028625, 69.37229599758415, 21.25822541159604, 40.0859768609348, 30.91766278261525, 27.392472997623425, 32.72600786978906, 46.65521454931898, 26.769361157954485, 48.00204869063998, 47.91427655595214, 38.57941133287007, 72.79288094925151, 45.06762135415999, 23.80914888898673, 32.59718473494337, 11.984241693625446, 47.40801311642391, 45.54736630658293, 65.55890193529603, 8.77006783527804, 28.914770515588124, 20.90487936188556, 33.8788310847504, 80.39569482176734, 71.69510186709874, 48.28823247326898, 49.023494062455214, 45.10624836105216, 45.38874541947118, 34.707474962191476, 38.224772083969604, 5.9212930859098485, 39.98757924503861, 35.807685513830855, 92.28655727497075, 31.777408577488853, 29.708764775118688, 56.02998060780192, 32.079133844823176, 46.83224522923156, 78.59535509482517, 86.13610373082386, 3.4466394406063445, 32.386636820900804, 42.62898068169717, 40.21620473924271, 53.2060538060836, 35.56456345622056, 48.91054066499697, 34.68922499292102, 95.05460600355214, 56.955619837782784, 34.4020340276089, 42.666051993497135, 115.70969132344776, 34.47514220303335, 123.37831274490082, 4.318969833498769, 82.16128884778784, 52.92690923962485, 74.66061733927846, 87.380983888792, 88.6000230465244, 185.19701312949016, 53.754045020588975, 70.68398600753, 65.53026089375398, 74.24412083058445, 48.48699625258736, 20.550293209101334, 42.46677501785774, 38.75624804517139, 36.19317462039308, 56.58013772810551, 149.250839514097, 61.262983653262374, 60.375718242635, 122.37836935741683, 107.67260310301403, 55.1623263188046, 58.04275951571653, 84.31371240615391, 36.37308083223039, 51.86348260787326, 71.21677440615798, 54.328221578275134, 78.28538191791209, 99.93823861624458, 80.86903921445852, 55.5968423350903, 43.36985548234555, 51.00841152632856, 85.75534809926026, 72.07205258485752, 139.79302900195967, 70.7408368235429, 43.08938383707699, 38.84524614928399, 55.47138094119473, 34.878856767990136, 31.54190465481009, 55.67012937566606, 93.67459052631932, 76.56722406369184, 57.87201099968986, 84.32856164234815, 121.62727699897066, 45.479013777598624, 59.33834737096293, 40.780598226517824, 58.650903471908435, 41.65492001163901, 39.19774721516985, 41.21374324259277, 36.106013617413225, 56.32053155828234, 38.926252577921275, 55.05319029603808, 118.02543738639847, 101.71093281648112, 76.99303365290267, 46.44991464036772, 54.94720124969692, 41.1853090943259, 40.926277103524285, 141.94039680443169, 57.32818785009895, 41.685779341654566, 63.70665142283053, 81.81710499959998, 48.995389930590655, 76.97459891387412, 46.15971778488792, 70.58021445851034, 55.62310029637457, 40.96023671671065, 142.8721943153962, 58.616777276852815, 130.2291004004282, 46.20883151105801, 55.792838747230554, 47.44076576764674, 66.77184179501226, 112.75674225741538, 41.18362796182486, 78.92292809437639, 49.249680373670664, 63.45059015151696, 65.87782459299329, 47.19911520407353, 78.18340270050564, 49.034081602721955, 60.046919398272195, 63.9816439794403, 63.41970158490175, 42.214528843466574, 38.145877017871406, 62.160806916598666, 55.80034593314841, 50.627184103944934, 44.968480529257214, 6.360546219460461, 50.553112470902995, 61.92390222492774, 62.737186496704524, 41.49923584259692, 113.14894697516822, 55.52845395881931, 64.49776534456115, 50.06026161741943, 82.54144166227425, 54.024910916460385, 40.245851515857005, 82.16132457302186, 47.863686149165574, 85.27167894054296, 219.33227498233816, 42.42214662944744, 41.03466150984076, 39.89034714437918, 59.62581222138883, 56.463941157653686, 235.4073661020426, 43.478838809219766, 57.18687245734746, 112.96941537997802, 43.98009280928979, 53.22229952678568, 33.8156782505973, 79.58107349678168, 48.40206927594047, 75.76457899153525, 42.234334282185564, 43.767115489987475, 32.35738784285924, 68.33895684470228, 80.94981843569875, 46.80654126758039, 41.75730143466328, 82.00923220824086, 37.132600488568045, 67.24782395146016, 50.54186665240951, 54.39699160770455, 42.944348647352, 38.549517098608305, 64.09957059972237, 95.33685978342672, 69.8360992295131, 55.57738984969671, 58.536869422082205, 113.81700338024157, 89.90475311889143, 36.87294006324739, 55.55755104664423, 50.00313030586462, 49.900590798014356, 54.4236627580194, 33.30337882074602, 52.10486607458716, 73.71719022535154, 38.74992250508371, 54.63153906847547, 48.20347431513198, 147.53483808460567, 46.236835920479095, 64.56806517157335, 45.5357497284691, 66.17866950896129, 133.65846548108405, 70.15202998887133, 73.40750417559673, 34.96812917474675, 39.78560340134795, 84.97339792755146, 48.651272576997236, 49.12878603176841, 48.72292713947654, 44.08948161086881, 97.13003485793962, 38.38030978183039, 108.54966149039346, 93.24825906846812, 80.34248244811957, 58.949098120049946, 99.8397038754453, 40.17608924983378, 66.42671092216531, 45.79347980874125, 45.583045606594446, 68.90573514739611, 118.92958312940402, 43.317478789176896, 56.66649784005224, 99.34086754392919, 164.33446451349045, 66.97512781589577, 9.895487197890553, 94.65474411572914, 45.46266501971921, 59.90197691042965, 45.08526219237446, 45.69377144191201, 41.512815395516256, 57.882760387221964, 72.38145044648029, 59.83629251323641, 127.88577266491217, 83.23788913807331, 88.42674793639966, 55.749712872629836, 130.16971240151477, 107.95801937887752, 42.16235560163451, 133.95126851157943, 50.26977706753677, 97.5536784478326, 52.02100398478532, 50.520333527684926, 67.72427334578373, 117.65813309625324, 101.3951552343802, 73.68956884453382, 70.40514108661365, 15.108556672715563, 36.54652770970526, 38.66944832216583, 7.805057281533799, 81.34549239543915, 3.1076897457368506, 45.40130509918078, 72.78078018769622, 89.19330348414857, 54.41364064033883, 54.65262172556274, 101.89107992429976, 51.38080984908489, 72.44001296084036, 117.13612540622846, 92.03516743580043, 67.28387338953733, 29.900373367727823, 46.36901101602497, 78.4411321524444, 70.71629944801228, 10.254091977400329, 60.66302240794876, 70.85273891376201, 63.27531361813254, 49.87661454281762, 53.654888376388115, 48.611078999349424, 81.01331453021479, 49.36329805533948, 180.8564965064918, 81.15628534422075, 58.574870130501886, 50.15488666670321, 7.155821308270061, 83.91171861653694, 39.457711476497835, 37.27838113453655, 44.33876131088527, 41.919704940655336, 47.99684681649975, 76.6923241204705, 50.5050936162586, 44.45106973331492, 76.42744658742797, 49.79163233334458, 108.90254184260847, 5.093201419333005, 44.78047763829289, 189.9673062729762, 108.97832854232493, 71.92250241863337, 40.00168672162474, 93.51676384434708, 55.95307566365206, 81.63307271913767, 48.36885547274579, 41.08537004046554, 55.84073906943795, 4.896676877132123, 69.770204484753, 73.2633420044479, 79.41086470218232, 53.435473506034946, 42.19832317654005, 88.31907309015, 45.033923430819826, 126.88848745850542, 33.05615740968808, 75.14627173140097, 42.263516720338416, 38.6947828784751, 50.635953153531, 97.27813950721709, 51.55260006047964, 83.30615071594775, 59.59173298308313, 44.785634735908125, 5.6058424347872915, 60.6885739897756, 124.09765574212345, 54.36996146484348, 68.76962351720951, 107.78469965050685, 58.384980865179365, 72.68568192616384, 165.17019930974496, 115.42630544125043, 38.31793033601775, 44.0051600635791, 86.33639482300295, 40.43295720237241, 50.387676773438734, 63.32085656557709, 37.755621343454315, 35.54979744348953, 154.75340439151375, 58.19662898064304, 65.82208362032976, 42.328546942152755, 79.20690807477199, 68.20791043139793, 51.20533813714747, 49.918386942338664, 60.808034884181566, 68.78222253920961, 102.78474845075122, 52.7732880642142, 50.411472495169015, 45.47126595697135, 43.15809790475619, 87.3634266456259, 41.25669463254055, 59.53694935655857, 62.24941219937551, 143.37737943539145, 68.66334690293925, 50.66214668495124, 131.56255716552394, 21.80308744805213, 49.14482736041437, 41.413570722776385, 81.17631168679594, 52.953342219018715, 140.7176780233673, 35.54420645351795, 57.48305193980236, 5.078157636461223, 75.64277062660872, 39.974657274212966, 52.75511394039966, 62.12516563146902, 61.15999272893911, 51.052081706593555, 61.16131728612323, 59.647637123130494, 95.42953390504232, 54.52902601677175, 76.85910479257245, 110.56366196716975, 47.96884756710068, 53.70172419121311, 111.15166029316812, 84.04686320517293, 65.058920772166, 55.73948394692434, 107.09329538281867, 87.42131271879879, 39.7980226040502, 70.70902515956959, 33.79800063173343, 55.99541537329293, 58.179363313955356, 55.89792484505034, 53.382850049434936, 98.78909664919942, 70.88949669876746, 83.57377903062105, 76.77156774136661, 42.859218058211745, 50.29886798586391, 65.62113423356172, 62.820425571046435, 48.03593554849742, 43.11652323904032, 78.91295395196553, 71.05557874619029, 70.88462386053021, 39.41041731377659, 54.05868399118948, 89.3900768290874, 134.20133152447522, 99.73752560683366, 20.151116115136933, 78.62404842746486, 92.16335735083703, 36.98040254045515, 62.157657013171345, 105.10659312613501, 117.90176091977226, 44.047599271410235, 62.685670565340985, 225.453617263907, 114.51235617151761, 55.05242187322444, 7.794677308420932, 66.85816757096838, 63.514967753758945, 91.7768683450936, 86.28398575461476, 75.7962830024592, 82.30493544743287, 101.18612524098727, 54.248624935875775, 50.977275969244545, 49.300687308744294, 43.6157192268765, 77.2548040761529, 64.34736166277166, 175.85599063950608, 45.90399242675371, 41.52962721394422, 5.782896011843811, 61.94624336004044, 68.6920722644053, 53.884939784898805, 100.26988938378356, 69.28870992631273, 38.624816118466306, 90.99596103787164, 75.77171375080539, 5.563895306016609, 39.41116351985921, 63.648488644635414, 79.14731322174634, 66.55949902073459, 107.0572902448326, 67.02565083527996, 72.76006538109121, 64.4147384332108, 47.00503777126508, 64.76073312159177, 56.13317209365909, 37.20364195337, 146.36421348896457, 197.5769041146312, 50.55050627923817, 6.813580486234921, 46.82739770253615, 44.13053818757106, 90.47254457551999, 47.6947683268244, 53.40471133827644, 49.48344995658111, 57.100160340760006, 71.75049782961898, 9.64723039180663, 44.67402714441532, 65.7287755699666, 53.07085624692578, 74.87518205782558, 61.78768582760425, 186.14455472603808, 53.604334485138565, 78.16482971089157, 5.895872203407116, 41.07101570917369, 5.039887947165202, 129.97920162755935, 40.36344466830971, 97.46569510844296, 53.27099988532873, 49.7839271541317, 47.755795552009346, 44.644876373480606, 33.02734618252885, 36.5573023995811, 39.856951747075776, 44.83998289842638, 40.87449891140047, 51.765914261277025, 87.10867308608486, 168.60530565825633, 44.79241112006561, 35.06636364351339, 96.12539250201479, 62.1773554128065, 102.68418997582123, 89.48097628083217, 52.31452747482139, 116.96699042364325, 91.35628207806917, 109.84824031048517, 64.53208685206029, 75.94820663091426, 60.90994876707024, 18.665483797909094, 64.22309269270532, 45.77308206142238, 47.69119933259364, 67.77896111663034, 58.628222199979184, 57.13475691606025, 51.288805021793586, 99.23993904848042, 34.41230755108306, 108.95835736743827, 72.77880988862691, 59.25224510241765, 62.432799419202155, 118.40373890076934, 71.43270260017223, 257.46096640885287, 64.48982029884571, 62.87267597557977, 44.79838111668244, 227.09472220335894, 68.98525644768885, 61.57427194917278, 62.14575431172519, 54.52497770249994, 3.8548034493104972, 39.23113037015461, 80.75354984485588, 89.7191548507486, 40.78549817910911, 167.7140031371834, 60.898722533522395, 122.29051849964029, 71.9172973379934, 69.82660505279637, 61.595056990753, 263.35019617174777, 46.875981707636974, 79.34600934420156, 38.169484185716406, 39.75348107384194, 46.07897769462891, 42.3679946201639, 79.02532703384566, 53.923861640311884, 92.64234552887288, 61.67302053279596, 121.15884746902923, 76.66317673306827, 56.50490318566292, 19.0972246653951, 21.92448676173094, 16.689424506671955, 118.13514625314862, 76.5512962628389, 177.75565314997948, 53.130123179989326, 50.375469699398565, 115.52163103267976, 5.914782852280087, 100.9786612999783, 60.40352015009785, 96.06497426597147, 116.74061935555781, 75.89538855566737, 49.70373774648047, 80.02830406079279, 65.23931982625736, 140.42201218089966, 48.49295488091588, 209.92459779197398, 90.66592884914148, 91.97939839845718, 55.27261540511113, 138.57754984321798, 59.22634966478858, 56.82598584381774, 166.61555916451115, 75.96047132934197, 52.759648586552956, 89.98962303865913, 89.1827826794055, 54.45976496809844, 59.54630876358728, 89.44511132341987, 72.5281749769698, 56.99874571966367, 66.00261636948386, 56.729558179863574, 71.06779560372198, 51.21932533642089, 23.592096941725206, 68.31563784531357, 54.97678998879748, 61.865555681190564, 94.55196033342385, 41.243966194588765, 69.97014167564711, 62.839397208178084, 158.35802918527804, 34.621326253527435, 41.17344859602862, 121.7224878078058, 72.97896303668423, 42.842751768703245, 59.83940992994734, 50.141089502057405, 129.13929051625647, 129.31249912438037, 49.07263433689164, 55.43382439021855, 56.35366563661162, 60.52719025882218, 157.3480604212081, 56.39282401408094, 83.34842603000925, 106.47021640792843, 296.7616360229779, 45.12430168482675, 78.01273872134811, 74.8888733667732, 28.845083813041196, 60.16985512669689, 84.13873277779099, 61.429733290978874, 44.96802296424198, 59.56961235720573, 60.44838354639171, 75.12207907480138, 68.67490476895823, 59.45846300586869, 103.31536512464152, 152.26332426318456, 47.45142612599852, 33.17252655673104, 56.185119122890924, 58.7675049180581, 128.00778217294067, 59.19047904905573, 61.082696379676825, 76.19656346691694, 86.20865525080282, 95.44820972015744, 107.13751643392582, 52.644255659771794, 321.9394169912961, 47.184064813791096, 85.21386074746366, 73.05377712589132, 66.44800539418712, 130.01361727544634, 86.32242386696187, 57.38815599497019, 63.3668502237904, 48.184517273122, 52.673557594938856, 78.3369543423435, 72.89745884285763, 38.28340657456987, 194.7934259697414, 48.341003728387506, 66.23254992058911, 57.38341532063584, 130.50425305105128, 85.90396092406169, 44.99476526374484, 46.484053735643236, 56.82824892740262, 129.4842070761412, 153.08662742800269, 108.39904589177529, 85.96416520255822, 75.95804094597212, 53.81129735483469, 54.2022761493711, 281.7732245033934, 130.7833633006451, 111.24877800967748, 70.42079685348637, 60.86007905955349, 166.92400676727004, 10.042041437818227, 138.83540972514083, 49.3674344068562, 105.66488450048543, 132.5219313822226, 172.57627259118064, 75.26717310880414, 72.59986807656459, 110.2447833378339, 79.76433588075598, 40.037436351724274, 47.53829607283732, 69.93645160289975, 185.46643239367512, 9.048983653376503, 169.72855947803362, 63.33688319249056, 9.251976318321804, 54.955394214158694, 99.48719505332045, 40.851307608457496, 251.40484331449912, 77.64397323870787, 43.29101380623103, 103.37714378498343, 61.9645511686451, 49.49132094353657, 44.307435550183925, 81.54268005256488, 72.2804452595308, 50.51683962325108, 76.76709675424807, 180.87745597620804, 9.941111819950972, 44.69602713041698, 120.80175803531588, 69.13724337551977, 62.550845880219214, 72.76869463322552, 50.11180860062233, 72.26197490686414, 159.93240358410898, 74.4732432879697, 80.90926442548508, 41.18126411744404, 148.79761101198085, 174.6205225725714, 110.09251781308494, 52.88869293853151, 111.2731391684866, 60.799246807235015, 88.41301229882545, 223.6956725155319, 117.49385552894321, 52.35425133561058, 49.74881732079518, 60.899958321867196, 71.34492221911272, 48.59427077833033, 64.1310789648971, 65.0182717296323, 38.99343632509623, 63.30103130899289, 107.34558287300987, 79.7553475280374, 62.56146900235092, 47.97948234989133, 82.2553515909084, 44.97520640488652, 9.508047116986003, 79.00468592570881, 114.30774936363524, 8.790000627928169, 50.46693940488621, 59.54159806070689, 78.65574489604128, 49.54988358719096, 60.62398742287344, 95.57204321209926, 53.461738684641006, 216.97069201110648, 164.54677797133465, 66.73922978310075, 265.4760190515654, 72.19894378322265, 63.254992084548064, 50.497653018982476, 34.54756486946237, 77.27923653053715, 176.51336972693696, 67.89364403951444, 57.36767714834368, 60.49894046992217, 34.10623996795696, 92.84687765452463, 69.59211752789241, 53.852841018321875, 97.79339768511143, 83.33399377749602, 47.93982821671054, 43.43447524330322, 59.3081909528393, 137.06493727534047, 66.0615516473079, 50.40342479011877, 280.03578353107747, 39.56518197720435, 56.28082678556573, 54.308293226568225, 48.81906851375269, 199.75810096869333, 8.45596323855191, 53.74413740450118, 44.65525092617332, 94.11542507794775, 56.19412764074886, 41.0297109436037, 54.92081976643258, 66.73122837899489, 54.76899931092222, 48.245863022462984, 174.12998858546493, 55.42458433726464, 50.776275648283466, 44.73864838314494, 63.84293557899724, 92.41658007335047, 87.22187362068274, 116.46181875995404, 9.955558044239654, 94.31106710604153, 104.19865354331974, 83.73668043337373, 160.08808040518343, 11.323137765768902, 78.08820876404246, 176.8437783906133, 112.58182059371549, 20.98819669629554, 79.55024041760532, 117.7949082759176, 45.917615127052954, 64.67990483482612, 97.17122082578959, 67.73878320096253, 110.14944835325832, 48.562816588871506, 91.15376843932734, 68.02542911056017, 67.86108618980474, 60.04429782538169, 52.04406695640988, 63.16510823203814, 75.05013881999237, 43.337831492357736, 55.91972629992682, 103.20489880259662, 60.13809358054159, 39.30255674121699, 44.51817625081052, 80.25077646699937, 142.18350589276278, 72.50232867801992, 63.02110041369989, 40.166012969334574, 77.25014973968676, 98.10734856573956, 77.49363924473768, 245.1655555689204, 77.56004564745402, 98.0144519590368, 213.91672551829424, 67.24446301417196, 70.35745626428202, 67.83769046131043, 18.27802605828722, 54.13861442611671, 124.8025722008189, 46.25278720079738, 68.876382038885, 60.51558131641045, 113.66426268828849, 87.56846717161605, 75.63191292766645, 72.53323907062085, 8.422240701877952, 115.9132055298205, 58.60277300933874, 421.5118756524623, 57.204744060540136, 57.67752526367585, 37.21595960986855, 121.08056382600513, 42.05127185843377, 43.68560640696608, 58.815706382421304, 42.94432529562364, 65.47634724000807, 107.86430139840616, 63.49213961787869, 44.32101357164529, 101.47799493731084, 64.68657817461525, 185.29896044359452, 86.49138234939625, 82.65115779254874, 72.19385293523229, 37.39631438000272, 63.528660753250506, 46.26607820752924, 66.90171732641079, 106.1666862851356, 381.329867359934, 68.78744718363416, 106.91968806008865, 42.52540772828846, 36.42255746273289, 75.02642294539044, 81.18265336377836, 78.76040045057312, 44.0297852085738, 53.75580416649828, 125.4755670082668, 423.8952413104007, 72.01114967580696, 55.97324280466003, 122.46647620700453, 86.08836906251797, 99.64387192361325, 78.77179925003605, 95.03903561536357, 65.68710506900949, 181.95726277167867, 63.96851879772962, 68.6610427437969, 58.67600495766298, 72.61199497205678, 41.95897879181234, 116.73041206266647, 62.209854646004814, 65.92716357364014, 121.2120197781838, 109.91303341971653, 114.6596400567553, 71.69948585785022, 147.8319309554412, 71.1145883680191, 73.49170873912269, 131.6566247642024, 151.83783321377922, 63.44106141656914, 75.17387552216624, 8.147485153006137, 57.10091431610576, 85.85984375103826, 56.86667991597378, 56.91342315342895, 144.12008781060624, 56.55670228721616, 50.378955212080115, 67.68271819347518, 45.29569624689991, 121.22518432084307, 49.94425974413645, 70.5553441793638, 62.59924681836583, 138.2467836587606, 102.59698034259569, 92.54381022999789, 99.55097994962239, 59.74837160504786, 61.517166379273775, 90.67485666427757, 116.8091062758165, 135.5603623360904, 401.26115515504983, 165.57503065125584, 82.21377383907483, 218.76014388052315, 54.00222658746078, 13.377371588192558, 103.53932331261728, 40.94510870732162, 70.55068629919626, 50.88553244491091, 118.72473314027528, 34.07707020202472, 69.32747774192146, 74.98957100024906, 80.30970658691476, 46.17289177420935, 90.53351366389153, 76.68086682974483, 64.90265556928266, 62.703189983941876, 63.16887474685239, 75.4466966368, 130.6251878440092, 69.4541685894924, 110.06899067837394, 83.61554146854046, 138.73714632174014, 54.358562750148046, 242.4986478658845, 95.1856726991843, 97.54323161881985, 96.52708037778514, 74.39297314455999, 123.2990985981144, 60.56946409206355, 52.7684755807904, 73.63927347339131, 100.11787381521845, 51.479360668780465, 129.14726476909806, 7.153102835468652, 49.08341330475986, 68.98182291129109, 101.83191195842633, 69.49228010663397, 281.99770570834045, 68.14768626492346, 100.5694826611212, 92.09267464975258, 63.14266557691303, 58.92217210775475, 177.06560474392288, 83.49568411414229, 68.87984210203814, 55.435817948966125, 15.518088814784589, 51.65421334142225, 260.6947688105729, 47.968301785672, 42.55172058293908, 70.50020320287082, 76.2755119174732, 80.79250463824697, 103.91747151094391, 55.423192051431734, 115.83479866451266, 63.56778309067745, 98.47665854142613, 77.65945834736142, 129.41173630888568, 71.00583390710214, 88.61969594687666, 74.32823201256763, 60.265831494331614, 69.82786628862371, 67.91688095723232, 109.35992667801698, 75.83741295215688, 188.80446060837744, 269.6346078093615, 97.88372234685846, 150.4060191453414, 10.305766384708912, 131.3896755612517, 76.09648017279592, 11.251240094790019, 51.403884931719084, 66.33781434191484, 93.92940534723637, 72.71887931335408, 46.43355545137888, 49.02597001273426, 159.6665044959846, 74.54198317188202, 86.32024624949148, 81.2921306378001, 54.19296212689521, 71.95895608407501, 147.9726542687997, 10.754926863770663, 155.22957217420245, 82.66979010982955, 137.24095947033447, 84.50183604197352, 135.34050748637156, 50.26297338602816, 65.25135234466924, 114.54713747250634, 105.80816540761838, 236.48633167196868, 74.90513373604688, 97.14322765752787, 103.64648920340267, 117.39545887040829, 120.13601736248415, 104.79644275618651, 56.321077701472845, 100.6160479590036, 80.99355833538854, 164.0952578243981, 70.72125435392748, 76.43320411291934, 49.65659407203033, 53.1626111175279, 70.65708561617016, 182.06573762839255, 127.28972292359194, 114.13508839708045, 102.43746170703697, 96.39972571179318, 56.16207983712912, 120.58730222018463, 54.675495592801724, 49.33819648744577, 71.22521843708952, 176.6688593611419, 44.52565200495832, 5.910987013493311, 151.19349315871722, 74.42394315773956, 70.45182006175703, 7.555847067524647, 235.38373934328754, 88.18047711486088, 51.942686659216356, 78.62191749933076, 49.726229128247724, 48.079996472682886, 51.67301499632152, 51.702806062473925, 78.43463424718907, 136.097878806047, 41.675983193858855, 51.339977537195125, 333.17534403645976, 111.46444063232245, 278.96375378034463, 62.49830418639221, 54.158796699831385, 82.20327015150752, 102.83465233837308, 85.37297223096691, 119.52994086092536, 60.6659870126082, 86.76109125260759, 47.42978764742487, 92.9550185241464, 90.381701118304, 51.555080168818975, 115.37241191671201, 88.33151772473005, 64.10834813220677, 127.20783625982654, 122.53774086411194, 58.66904832011035, 71.2632738224687, 127.47879104440433, 78.36081099837592, 47.28279287869928, 146.56649221228076, 60.97154213737265, 447.28454919687556, 74.855534170492, 87.21266093285483, 124.26755640007976, 180.3105039910172, 103.63196036963316, 193.25545747830014, 7.070443239933685, 98.74098060385681, 45.67621898822574, 224.00121884580375, 58.30310299690903, 57.36804997014712, 51.82090058535556, 76.71281905290634, 80.97654040855427, 99.6000094458657, 55.1879533782823, 169.79300663629073, 67.65294302313289, 104.00236420704283, 35.71929454885448, 143.73638672774445, 68.51750792630826, 150.3156234022138, 85.06840827738773, 92.659416462506, 148.27261885760723, 38.20469889632671, 39.234226474027736, 268.8080412905749, 7.487849226161664, 113.33613780281978, 241.08153128109262, 55.92448715227216, 66.87395164725405, 317.3207608725678, 47.71193436646623, 129.6666113278113, 60.418087348939856, 69.72960610091518, 68.68708073083897, 66.74806150967686, 130.8391640710897, 72.03798665243494, 132.27254868652878, 57.146241890204294, 65.84341723195081, 130.1608631485479, 64.3966109566124, 13.15248429457302, 45.98755848616602, 80.69804446463188, 63.11289889982411, 100.68603739055021, 125.9832630391959, 80.0155958604566, 62.86134487210449, 56.52690447129751, 164.68325259609762, 94.26895726930934, 75.23342474568841, 135.81933971082094, 108.21624691475922, 105.7023360726548, 63.5844926585189, 53.03084807046774, 85.73277468419401, 53.691288055562346, 57.683151303687595, 165.28256704352054, 75.5342287475723, 95.04348992561643, 97.91824224538047, 36.539993445542386, 83.20199000066654, 58.30076581569106, 103.21493390720978, 97.83174073281194, 58.31231421995192, 93.40978354298883, 10.826396108873958, 50.281695226065146, 62.987934145636345, 89.71577632576172, 227.0255145827368, 99.55828132971551, 101.8063649117683, 98.57934550661209, 91.75646556816422, 144.58431896893433, 188.46967303081897, 51.49853583957797, 68.6154735499344, 122.98223351822043, 64.90223421661216, 99.26271849425605, 46.41138155452589, 80.97721707202665, 71.7726886728065, 95.2326535457781, 57.47000115966368, 142.5642274771084, 56.00518076494354, 111.4023308158406, 45.72757192919265, 105.92841038637435, 283.5810594743192, 76.30997652070262, 76.15590566559248, 124.66630684721305</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>108.6951456642151</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>86.46511858023297</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>[22.784378051757812, 134.75550842285156, 76.34066009521484, 66.18302154541016, 408.66705322265625, 216.40692138671875, 91.69117736816406, 78.81722259521484, 197.8628692626953, 238.0382537841797, 49.44811248779297, 175.296875, 38.80895233154297, 71.75438690185547, 90.09813690185547, 122.07412719726562, 66.36254119873047, 84.16925048828125, 90.52476501464844, 46.226585388183594, 72.89932250976562, 118.97314453125, 49.5177001953125, 60.77975845336914, 65.92559051513672, 37.37456512451172, 67.50119018554688, 114.9252700805664, 251.6896209716797, 64.03562927246094, 86.39884185791016, 167.74615478515625, 69.08946990966797, 218.8631591796875, 65.06248474121094, 258.7588806152344, 255.9554443359375, 67.78237915039062, 90.95384216308594, 94.92000579833984, 55.50990295410156, 109.53028869628906, 8.060083389282227, 162.14328002929688, 21.591581344604492, 64.89940643310547, 50.40807342529297, 46.844932556152344, 90.04918670654297, 44.96212387084961, 184.73851013183594, 15.548937797546387, 63.37661361694336, 75.37187957763672, 93.04854583740234, 229.500732421875, 202.09378051757812, 50.79113006591797, 22.249774932861328, 360.33587646484375, 74.90230560302734, 70.80388641357422, 295.31414794921875, 83.31153106689453, 56.06765365600586, 140.45994567871094, 107.0119857788086, 75.02397918701172, 48.23720169067383, 66.58560180664062, 174.49534606933594, 10.537728309631348, 311.8194885253906, 71.0038833618164, 62.49430847167969, 16.78592300415039, 116.31100463867188, 10.649214744567871, 83.71629333496094, 174.2921905517578, 74.41144561767578, 35.029788970947266, 85.57707214355469, 153.19821166992188, 72.8233413696289, 121.5386962890625, 149.5238800048828, 107.66119384765625, 15.255005836486816, 30.099809646606445, 13.571380615234375, 311.120361328125, 105.70954132080078, 46.73204803466797, 148.96505737304688, 96.24870300292969, 89.99404907226562, 65.97590637207031, 54.5111198425293, 445.2264404296875]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst01849</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 22:30:36</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>93.09717544049118</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>72.94985237023076</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>100.8443681873234</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>4954</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>[1.3398464799972385, 1.2674188073836725, 0.7565608735590182, 0.6174559779558905, 1.3416990950651673, 1.3223298658501663, 0.46075494639519826, 1.7596848019098896, 1.0524096433343186, 0.8807375211808919, 1.285185969095537, 1.2993322740356663, 1.5017480562315, 1.9990262089278816, 1.3752983182004876, 1.8613008367547934, 1.7147444954519508, 1.337350244486854, 0.7826367374432198, 0.9124952087089762, 0.06077813993855967, 0.8716946942600321, 1.007442704969782, 0.7932786624862798, 0.755031400855999, 1.1286328473796872, 0.8126967324368272, 1.0476040881416466, 1.5895150114149224, 1.8309658711834083, 1.0587409160506538, 1.8172952840459229, 0.6614268326260422, 1.581377673500165, 1.2160341910058587, 2.7902227700627864, 0.7382207741165994, 1.6841352720511238, 0.573375469677419, 1.9527313460790614, 1.6453413430058952, 1.7500641816450888, 1.08021557944241, 1.2968396034307128, 2.177129220697055, 1.5984668460115263, 1.8146180432823265, 1.463979887750336, 1.530774906119028, 1.0126121159065666, 1.017627710717236, 2.7076555676059013, 0.8800980942840148, 0.5386361972303041, 1.7282087783470343, 1.9483478476514122, 0.4931971227884123, 1.7592758216357762, 2.019646474575556, 1.6459601462142084, 1.7083281937716357, 1.2614287563887912, 1.133234937347822, 1.5172196109528233, 2.3139985918039, 0.781568654361246, 1.4567023621543878, 1.9368356813412722, 0.7337797195449419, 2.344004481126481, 0.8034978744598174, 1.7726832413372662, 2.082787873728235, 1.05797127749414, 1.886035715348724, 1.7876871703906179, 1.1594623660465837, 2.1629900075038155, 1.397928613289329, 1.405557605295834, 3.1595428532855663, 2.159756081865589, 7.903455648458593, 2.5272461955156835, 1.9497602396311344, 2.5469880984764317, 7.618544502641594, 1.2585635267887845, 2.333225631380647, 2.7628997317339827, 2.27388513849508, 2.934048978184948, 0.1674157328457147, 1.7017931740961203, 0.9735248752248434, 0.833044712195866, 1.424258955015371, 2.855322546045776, 1.0246103428217181, 1.74991559973168, 2.110583605229547, 6.032832938722488, 1.6747565068550736, 2.181536648011112, 2.50189185852266, 0.6353923812007335, 3.5454972228235575, 2.182847171038949, 1.4579917123802655, 0.6703768019725811, 3.689714778270662, 5.291316037978063, 1.6929390815883327, 4.82296647410959, 2.5491746937708992, 4.675739181538581, 2.6243851299013508, 3.676431791081666, 2.7391519898530197, 3.327982565157225, 8.724199157038953, 3.5093639359005144, 6.740233874750034, 9.72536436916315, 4.923748012234601, 2.147030912452774, 6.914954760265829, 3.3350830941565723, 4.0602618423501875, 1.8438077854242605, 10.812135184512186, 6.196989307940858, 3.3952303563544466, 2.7250522564197013, 4.633172747543324, 1.2070465063380569, 4.223726358303785, 3.8381471923487633, 4.168678146751457, 4.0633842309102, 2.5999409966720157, 5.811900217094601, 4.972731999294633, 3.2659808835778925, 4.585261004819562, 13.04522085060351, 2.490872218895312, 5.617869364675208, 3.784641026289399, 3.622729228336543, 6.029923094175974, 4.227129923348121, 4.715601480666102, 8.06914005155134, 7.163552059581825, 7.782758699039163, 3.6907416313624264, 3.69638620309685, 13.044438307103107, 3.259773762076092, 7.442464595157921, 12.181545086562632, 1.9236696609626907, 18.678479113468175, 19.186901838185058, 6.0507383152351695, 6.648525688443681, 13.161431968220692, 11.11572331021923, 4.333112196633478, 9.041315110633008, 6.143786225438356, 7.787109645324721, 1.4885517174859633, 11.329963592638663, 5.373723899483299, 9.412070641594957, 5.346772267564262, 8.133000801778657, 9.233653315314164, 10.412359560916103, 9.632263355085362, 9.821130578540547, 6.754336036045371, 5.026375712575138, 9.6776831587488, 9.249409305059293, 11.867187233357159, 4.417942086734236, 11.321967413251976, 1.2844169850457001, 3.739658460063672, 8.25605247063931, 3.950254025541961, 14.473583605124995, 6.900613373792989, 7.899981749450649, 9.190000804577378, 8.2997559122219, 11.49043940119352, 17.406892179765855, 22.71914440190374, 9.646715140823074, 3.4710426769598404, 23.542669620971225, 2.6158691456050933, 5.072849565311318, 26.438213324278404, 22.274224526284794, 12.565486361891285, 12.520673507862996, 12.799965090181084, 13.117386531502014, 11.983143603742592, 19.154376045836248, 19.028218167651126, 21.916249176419843, 18.874150015157408, 8.48407371586517, 17.639304035878084, 16.405123139761415, 20.106575680945348, 24.58349380293002, 18.34287679009986, 9.055988761833476, 9.304442334577812, 13.42434339363769, 17.059682886425062, 20.574118595176675, 17.572407434393845, 19.89200286272096, 17.73549961613035, 7.251466697155914, 12.117854480304437, 12.076865354112456, 7.0570072959559695, 17.14993789711225, 62.696377813713084, 54.14169234034154, 26.64140367097801, 16.66338941847452, 15.210585337393574, 13.180849164567766, 29.383228989468705, 8.679959106511301, 3.195158052433121, 26.69519262560611, 15.999517220794502, 7.706966723971924, 28.592696371014668, 28.633707664319356, 28.4823737758215, 16.47528717830453, 17.969618053389233, 1.4315953673391233, 15.017059058307813, 12.514913680372285, 20.140235988749122, 21.914254441642935, 24.41471799946397, 58.64122940856422, 17.07705149892823, 32.12924691710387, 27.994123233770125, 20.425151465994283, 14.96820511147554, 25.144461973575353, 26.58022339730428, 33.58593135711088, 22.99601081078673, 28.86236765730946, 27.979825228484724, 19.46581440974686, 28.486378008291464, 27.39840537555933, 34.52591679577491, 29.905016841734156, 31.54935379885402, 38.99632548952157, 56.44667565764319, 14.716785626826313, 40.37454052121893, 28.332048236685655, 24.531437626185703, 20.21905164148999, 36.321921287066104, 56.37937212818353, 23.750252583596296, 38.85774498502387, 28.549595736819576, 28.802039818825975, 42.83857258881202, 21.511112890689862, 18.7884650211625, 4.399197796469585, 28.507042305618846, 24.543231659901444, 40.046805001653084, 31.952418651481082, 87.46473702188015, 42.99196940149367, 37.56550388480217, 36.60848906844622, 48.05172710809452, 27.29434814982021, 18.94414225473707, 55.06938578813122, 54.003022077950746, 28.865521177182636, 32.11294563538688, 48.04667144417571, 51.22788827893702, 27.622825631199362, 4.126340843983624, 52.22605678714285, 27.68266210481693, 20.477236576541014, 35.071549024632, 73.80243338163376, 76.93747420607832, 52.44085471807772, 16.42203549881167, 30.32528632634773, 32.22325573969556, 53.19600758268813, 81.22384564674051, 66.60729576067256, 49.09321351029405, 31.344418706981873, 4.219690859607654, 31.87745447243062, 28.19106211223673, 24.722144479758516, 49.928475501265105, 25.591558455528816, 8.998619549052107, 41.9373658105034, 25.949515335590274, 65.03862616629362, 41.366956462699285, 76.50531758993596, 43.228433476813876, 53.48528526729416, 32.57239091534898, 6.213495829822368, 29.722073794911, 35.37815775261833, 55.46706943035948, 33.26975103900038, 51.812415631732584, 34.57985513221009, 49.15069480815026, 41.10332722070661, 60.974178616709, 45.442222136321874, 31.645390003258093, 39.83727009390101, 38.38276968780075, 33.23561476490211, 52.81168273984389, 49.07957425220332, 40.95999705030533, 56.79725978480137, 45.50570893652897, 35.44978513671893, 26.689427727198556, 111.7491231742999, 68.52130475248661, 41.36314430677271, 39.97421743629111, 46.19462688342118, 68.38799826748424, 35.6935954584662, 36.19609319313065, 29.92362832558079, 73.76714461101498, 38.50671310185332, 3.114020677383116, 76.96790990739298, 53.49473135169283, 32.4352766317664, 49.48422596453511, 40.165484885429535, 28.39411363714342, 33.61949657032359, 6.366863437379069, 42.36428299090379, 47.11367092422817, 32.07259765152857, 59.362547963416695, 28.912935396567775, 67.37181283834492, 71.0951836272297, 35.581314815923, 52.70885226239658, 36.19404957484316, 59.89934697552813, 22.292241695218888, 60.927236349251956, 42.8533171756767, 45.8063376804978, 6.113575290831348, 26.89379154764692, 81.87513204866542, 42.39710437386526, 57.00338410822093, 23.55419480979619, 47.23289844721133, 5.644053469284117, 71.82749370151443, 24.08692676513864, 5.195960903458795, 29.545888806342663, 78.11724698524154, 55.4273900310607, 36.80394204520992, 65.05806465466111, 40.04125138309144, 57.312145957622455, 30.343062216908834, 56.37177374941252, 31.291755991813485, 37.00591115202511, 90.66949205893876, 68.289658433967, 24.939747166503913, 44.3061631022508, 36.834252805142235, 73.56126204109445, 58.52893999916888, 56.42735230743146, 41.23830666017785, 47.386353013325326, 34.86203685116316, 36.03992841964882, 47.391644315356736, 39.798018027443895, 82.93426914539306, 41.239047322439454, 9.562632889818264, 30.216835876009227, 82.80862588903764, 40.79693468310911, 69.05866229095194, 28.954509529134622, 4.83368664194095, 75.31816063721227, 38.140893653031156, 18.21944101968229, 74.26900893352952, 50.48360762457124, 80.69857638819805, 45.70500522522994, 44.4970045309355, 36.46270142404393, 48.572158055122046, 54.673917800069844, 42.88885736593847, 91.94647194913136, 54.59533945296319, 32.130309005854286, 53.16246285756144, 36.28979339619267, 29.302812340658427, 76.2014252696986, 67.80150078287595, 96.50326574373773, 48.03420746170448, 93.53057541111451, 51.720667397326885, 70.40082612900434, 64.45639504321164, 44.713586964658795, 37.1490294546676, 108.84571855640785, 80.05316835747698, 30.33787025002496, 41.06024454428205, 101.69533065619585, 84.65019350472302, 75.28888102895527, 58.8253548072281, 6.820241935845015, 62.653769196260136, 47.34074978645211, 48.567821021841, 69.78392117489217, 48.00943163927958, 41.339636668013036, 25.633015739091174, 63.13009249535366, 36.02896606392238, 76.85515136503716, 48.023625058915606, 54.941842213608645, 39.95724876426515, 7.193502950726287, 41.64080755074241, 60.05599408957572, 13.573545143523894, 89.57967431483291, 45.47023890357498, 63.737444063079494, 42.0094450108036, 44.47791579238248, 48.857479628467445, 40.87012087564509, 81.20229195884866, 36.016789053087, 66.76940234384898, 48.38224815122012, 44.48569501851668, 71.99391800201613, 8.332367057072062, 51.966358313508586, 55.61623498851291, 44.479166337993185, 29.84228413711347, 64.11695132670773, 97.92423599804015, 42.573417836021655, 63.10893121409527, 71.75401283870438, 32.99857898835416, 59.79788538608928, 66.79207429328413, 48.95202084453842, 65.4633328032747, 82.8425023940064, 180.93592156050534, 45.419974328654945, 64.26879242549478, 61.84269765036608, 50.32224023340171, 82.57693165850631, 37.943154233328734, 143.34888040572713, 119.34803087335291, 61.355396686413584, 45.1860786421096, 68.43487855937096, 168.902531438252, 37.94646648477524, 55.55825056277533, 40.95638735140153, 101.90172874389559, 60.86207449176526, 14.31791748118595, 49.029350904136066, 45.94149640371583, 61.50172028140406, 6.567783810634749, 73.51521718579333, 84.51653133708015, 78.58843156419837, 36.274249739482585, 85.5196701314062, 69.20515563259154, 148.1693469622584, 61.11121389173381, 56.46682038341994, 39.16517713699519, 42.6586288285631, 105.77747163870627, 49.82678033342535, 82.88366092974654, 61.51662167217648, 70.52013895249613, 52.629462495214945, 167.13106760591393, 131.22537568091656, 4.860105427892583, 59.8755958055501, 42.79215998528847, 47.87678290068995, 71.67267715311854, 63.83925411734488, 62.18193861441271, 65.47588325169495, 51.237064986584436, 35.466446149104684, 53.48658821447137, 43.23657817937049, 150.23630559787276, 40.7088645295167, 171.17500353490556, 48.080320763367084, 50.76206233261498, 173.28065474768857, 65.79766794665215, 71.11484271407645, 47.88174916710213, 96.21435700690132, 44.126267156505115, 46.68876767661818, 45.591330717079714, 127.05718379803352, 41.028640249287015, 92.32526270494863, 49.5100540898191, 13.546150484253793, 156.368433674357, 105.98828487700284, 46.32575104911344, 51.99481661833461, 62.149795509234025, 133.69474771630405, 10.873759680600827, 50.41283893088597, 3.5615452052594234, 74.24864025306508, 52.163622179005735, 98.7557920261363, 65.0215680717748, 45.78317815473375, 66.13459567941958, 89.75468367446814, 111.5978902653711, 113.65492402607171, 48.02683973251169, 49.29289789921624, 73.17127201359823, 41.62957598286575, 75.37438395769927, 125.95987673299923, 46.80935462215894, 65.93309668380398, 96.68536447185222, 67.97796431812417, 62.48066279386161, 86.71510031237088, 47.45658358323432, 36.51884033423697, 91.88300184616433, 102.76529469736205, 107.90326097064107, 54.57229784149274, 57.97408317904842, 62.3765473012753, 51.38402379842065, 69.47986473675114, 6.094460253924776, 55.68277263290785, 54.94844667419094, 152.893268728212, 88.24244390352449, 47.45094839486935, 72.33137960021432, 11.393067664061675, 40.88260439262258, 39.295616319874185, 81.86384559223215, 117.00120197838844, 66.46965783327391, 50.376263424468455, 56.10613627640094, 128.75688627440982, 50.700528949470154, 144.89938358868363, 90.0330075638255, 131.91726558644214, 39.98538531370996, 71.28060088065288, 95.88894875321971, 65.3094799484411, 43.808308151279434, 290.60373701752764, 94.61936578214859, 48.83581177900675, 38.953774291266555, 53.74362539007801, 44.336994869877586, 104.67589768551488, 47.06814795635716, 40.6821506448225, 141.49921089995883, 40.10284361614668, 39.51577559997396, 42.085193575339666, 74.87293480940326, 47.55661034380419, 69.37930527504008, 46.03641251229544, 97.1889016830793, 33.413887293403235, 34.5659227972873, 65.63826457057908, 49.76744053292299, 83.59051172639987, 77.50162547972876, 45.58867106588432, 182.8599512131469, 117.3639131708392, 59.66815331668362, 35.35389627384692, 44.953538452815756, 56.83509655885468, 72.06270136613507, 64.5838946701493, 72.90419569393275, 35.07443204282004, 57.157896695457886, 72.5062626062747, 124.59466898493753, 49.72186096053459, 85.55299485309405, 51.07031603836957, 105.96307734606141, 60.26363773034235, 45.685651944087034, 91.21369281571371, 88.29498407220555, 146.05578386308724, 44.10785117005689, 102.26127341695485, 110.86113226136032, 78.92093659430229, 58.92496506296504, 25.838215080410002, 119.5278957384468, 100.08187573643526, 50.106012567296794, 78.80363161900925, 45.12244946581283, 62.505506442978024, 51.40588601436444, 101.4709463202296, 97.40307833519655, 51.457605475483206, 44.639629522973365, 87.28907930889109, 35.799507359179565, 74.13556407948805, 70.06695129446463, 49.17816577561195, 121.83691446349482, 97.46963056164552, 122.38110493454545, 79.30486586927411, 89.36291656484696, 67.66626686801895, 59.29478836143924, 16.591330314070976, 49.86961142883356, 59.20112007620418, 46.49080707280683, 31.357630075104254, 121.1411025898682, 121.60415957029782, 35.441887498903505, 83.34379766697167, 57.82659987461662, 88.43017217312084, 52.91419237833295, 52.6098548599157, 63.08501350509401, 36.000299535412594, 109.15090893757889, 36.30791499780122, 133.50604523756942, 81.79311011709818, 45.89337834800775, 172.91109825693803, 244.6481166069961, 67.55178562064286, 43.837731334806506, 43.584852915457255, 24.5632977451176, 38.14702172106636, 10.722347621604944, 157.11571309948914, 234.83635926632928, 52.99274192103652, 18.525349208306217, 46.18296649984636, 66.22545635195792, 45.6327854450004, 64.41953858866448, 64.55461350795514, 54.933751232352286, 63.442166907648954, 98.30269714267445, 12.706614478528316, 73.32839189452184, 50.20422566343997, 40.73295586819617, 58.54194637656232, 54.1787000211688, 57.30264590024792, 52.769655037910944, 60.8184979355103, 74.02892820478165, 41.50450473352612, 76.22395482976738, 55.49641400451622, 55.360597363660624, 198.21930173002502, 134.20247495998922, 135.54025685874626, 75.14885918541525, 61.2099831585898, 45.89789324692999, 51.879021116431524, 12.388632682766435, 51.56076239366654, 63.43727244319843, 10.610820673595438, 55.975579019029006, 40.32137529712567, 54.71364814306644, 46.01000784792297, 108.91164876881922, 58.84223208488667, 69.48276675459054, 35.38654807814383, 85.30143297801055, 6.864638631282217, 47.39414946164256, 76.80645106942544, 46.217170684454125, 67.84109909624433, 144.61640879892374, 59.58247851034179, 65.51221261857502, 5.120964117418571, 126.60618804341665, 58.27165020139086, 83.2466204265995, 105.56556160340614, 93.23319346482415, 48.21861865335336, 94.42121696014426, 49.73985180215903, 47.335388869677956, 84.01072425873541, 43.394756520898895, 160.75828205074697, 42.91948921838245, 177.225400167341, 212.29777505707062, 118.48324275120311, 117.69582685988692, 52.64609005978354, 55.98345696343878, 135.32324590701484, 101.16961713170045, 87.9415020812494, 119.08737406114257, 72.5053833520567, 62.25050750745554, 106.3460374472577, 92.05016433735402, 75.33328778716992, 90.72770288844379, 98.97899027758892, 55.79134605564775, 57.59472054016419, 91.11424974018196, 81.1070449248748, 57.812989017576875, 82.88486211851928, 53.5575758254844, 68.80568388296325, 72.36601454317557, 39.78832469258254, 79.8441895461776, 139.08283352883387, 50.724112414086655, 57.44129728829485, 47.714358686652254, 116.5005693043097, 126.58787440227778, 47.88317941638914, 85.8085165894597, 105.3515151284319, 63.298610866821434, 72.4971453481037, 115.52785069312549, 88.91879697752314, 199.22909459726802, 63.505363115658014, 61.034841696893, 129.29412957347637, 62.00463450625603, 185.90523805726394, 64.64483039517074, 68.9986955035183, 51.79061825531507, 66.13753493851222, 79.93830515740527, 59.38196741552195, 163.3797178659846, 38.496333999817374, 5.726586616010376, 163.8092679519028, 125.77152566758298, 11.956412547429268, 51.00406516973436, 5.734070935652111, 169.1533749555191, 27.527280257181832, 29.897646654066516, 103.16526619452392, 118.99334465057208, 55.761366087116656, 93.7051336569646, 61.92016192628181, 109.86465834527296, 51.71545748680828, 81.6394562704527, 64.13133678220987, 54.23938292674738, 98.38064362895656, 60.51493826444252, 64.73824983905898, 241.37147845447984, 57.28900572314035, 77.30589025642776, 87.33143847519636, 85.79204021257948, 86.31031141289242, 77.71563666741383, 61.2776628843972, 50.99337229089148, 61.60987430202738, 117.5552757890633, 57.50710612640429, 145.01236680105262, 38.28179126899822, 53.61073661424036, 12.298878337137916, 216.60862238919464, 99.452905065751, 88.7449621310052, 67.95030778362357, 71.50297506286552, 79.28667943081406, 58.90909809915029, 58.94554800233677, 68.62806246297913, 142.05460257989492, 58.47924569783646, 55.397811799580566, 151.08202517535224, 84.08904370433095, 81.91991994777668, 26.6843216890549, 63.28601886209037, 76.32881876647097, 159.8501247146898, 73.57354048258351, 48.08342667409275, 81.24932925897076, 50.45644020219238, 50.032736687601115, 118.1479240880759, 114.47706145356642, 47.37457191619762, 152.2255419776786, 115.16189611121618, 81.46818815518023, 60.39749854440474, 47.20828327930225, 68.96922310767418, 93.23705452432162, 48.338747690455605, 43.94993601646571, 61.83631738211067, 127.89408427863317, 9.16124515246928, 55.296322910134336, 64.00717225179238, 50.95175938039535, 58.55723798401689, 13.74593802293489, 102.96615069376409, 6.674103188525382, 63.79133968567939, 74.98702541286627, 183.48794187199653, 38.86109640057221, 61.609117750240344, 83.99862179911567, 64.82159642677048, 49.60727921892375, 147.45646002940117, 57.99535224098243, 59.34798343769951, 44.85647646559387, 61.645246523832384, 7.675833840247447, 65.61116422899704, 54.23617085439387, 55.29963350318549, 43.72318919117145, 153.8761576346989, 76.05597275079526, 62.72794387266259, 69.37317441122552, 83.58295313801969, 60.74657259612722, 179.93731378980488, 52.65405668141911, 62.1696926920515, 73.79741754564269, 95.82003832469438, 60.935561198630005, 90.02733257027637, 69.49108583122307, 75.59646025166333, 65.90418052389391, 221.68920613215138, 50.02105800093489, 112.61073653827775, 50.217623593686284, 83.41240917479853, 108.0613493144872, 53.088699073395425, 94.44952852143187, 105.04800351158404, 92.09109092673252, 125.61689178445566, 72.19326951097673, 133.58714064276697, 100.44215973818054, 45.88372153285073, 20.286417593237218, 51.97784041724517, 194.2463702896311, 65.26002624383374, 82.88909891369687, 60.59591536386113, 167.00218789570377, 71.16120303058462, 89.50927738751662, 85.61520102850417, 51.48499572040288, 83.45751821972742, 93.42381316611613, 92.43847533054222, 67.945695153649, 162.3626092079124, 7.518881736791719, 53.737403660683135, 148.98387334396233, 583.8774177974864, 57.394270107649035, 84.08266821215955, 229.00073393793178, 62.18209067397225, 71.99675525813295, 89.87599015319859, 96.65151107791641, 68.27625101743709, 177.50771185716772, 60.18863065005553, 48.96914614206542, 68.73683295311366, 135.3933009501457, 134.61709142632702, 75.1239312684019, 130.37396474033275, 87.53481600715845, 78.26688265030383, 82.02090727007985, 83.7898080211115, 114.83292525411083, 48.35837838978285, 154.71730771550975, 44.30942487041173, 171.08692473624637, 87.07281336507099, 98.78029362946276, 48.88879282648846, 72.31155422080822, 68.66606406949953, 68.20746815417998, 98.86181373686394, 115.98227607377326, 61.588763335454956, 32.312847873498, 69.1693667414734, 72.70675325046845, 106.1717475524269, 120.48209721467688, 129.18961303173973, 319.46209640700556, 142.20585573249318, 71.58316843537042, 41.40520948018732, 93.00151023722587, 33.39421749042191, 179.8243647276328, 122.58286270446943, 14.901950357841606, 39.444167155816366, 85.92345864134516, 54.24110680552805, 103.57296845361721, 65.01567296376166, 107.22286386976486, 221.6106820065711, 63.23812816658889, 15.292551892022377, 36.44694289662845, 131.60531581816076, 98.06094200025562, 57.898985141457125, 68.05910174086475, 135.10466630914723, 12.963253042570587, 54.318484926103174, 71.37551457966005, 84.28947636221915, 90.74214176522639, 10.584691854065603, 59.14790731648745, 51.76237055039161, 90.99712375462578, 61.372578307338664, 95.3398207493427, 60.54311182658369, 69.89253950235417, 94.92727737520731, 58.20073235735737, 56.233953940776956, 81.03577039971627, 7.856929589687232, 108.09798177363054, 113.01719844816432, 67.90481517355163, 75.73689417833779, 6.366651314754707, 123.76342563953115, 55.48974266290639, 61.34128363825032, 79.49912981717407, 59.71174850969822, 19.19432320324443, 69.07822574603843, 123.87256487668868, 146.16620027402936, 55.604377680560944, 55.68611141488685, 60.52238568903063, 104.36308289508271, 7.749713264665547, 101.03457071577195, 111.48832950352151, 72.5578823558806, 57.13439797868251, 71.51461809784642, 164.66686415155795, 123.09794189054266, 64.33351506574778, 147.48501446325332, 46.56552925630044, 97.25809974926457, 92.37438042651839, 47.58458970197342, 119.97487969681949, 11.436372071093551, 13.772851062628467, 189.0127915248045, 104.17807882960928, 102.7463218373131, 109.8867959161415, 75.97412775330562, 79.70036101875839, 12.776515787377816, 115.67874371017471, 41.019456977079976, 45.118743311888466, 96.98870926082252, 16.889936161211523, 74.96828739375826, 64.90995576538538, 166.72581057841518, 58.244257090275006, 71.57461546167492, 38.10989766328207, 60.85206395491048, 39.278250582717725, 70.59950384903429, 69.99355229991353, 119.54873631723221, 51.24955468166894, 103.83455681672211, 55.45368924461333, 64.03393323672748, 8.127260853925822, 47.73326509487017, 58.174967970323586, 74.8959206013427, 50.02357956248956, 65.56186623334452, 44.660343142356034, 189.9514987266399, 59.09105207508511, 137.76113394700786, 85.60528494151491, 71.2047350076004, 103.55245051261902, 54.63493532473855, 77.88533798443831, 59.96254599489502, 84.19050284748067, 6.993957821481104, 65.50666798743667, 143.3435075333727, 68.41511212310736, 91.47411112207641, 9.227706740665024, 74.2996853986331, 110.71173069300332, 74.29688166486002, 64.54855821326676, 48.8304368561216, 114.61781554956394, 112.36917008026376, 77.24042427253163, 47.68335191889386, 119.52723855226112, 41.35674176880258, 75.93184225528552, 299.37639476620024, 58.82009353448336, 72.37145900820859, 58.176491614242096, 59.25109655058288, 115.6342941912127, 61.26212466518655, 72.65522201615563, 107.97550358728625, 81.03109187828723, 99.60742275404695, 45.812707388295365, 146.18615752752999, 83.85505484465747, 64.69280772818647, 67.47961321523874, 71.05563373370452, 95.90754755073222, 98.4253981118718, 38.70218229316567, 87.47857459190996, 90.10451640253105, 116.94021764351324, 89.3515380446912, 162.76820326297178, 245.0985454205122, 86.77196060298618, 13.903246078401176, 67.60140112917796, 52.75130794724912, 179.13183018891405, 77.38709003116637, 96.8939716038676, 92.7245856629119, 85.01054946551236, 40.85036175265034, 71.40835725523768, 161.40032803151024, 86.25816481993706, 102.97377703787525, 69.36828159056259, 99.28432116584038, 78.26224269017659, 60.49251781103498, 66.34527242468519, 118.83031576215895, 79.15029946381846, 61.81369798005293, 25.632413024405892, 68.47958661246648, 68.08631869540312, 98.3286837440051, 61.254497649037454, 66.56381342793082, 71.0378557670268, 96.79530562929236, 53.947932562253335, 140.20834695299445, 39.09560950640627, 47.48568167356339, 81.536721196846, 53.94109365740115, 42.89734590891801, 13.301071593154939, 52.76470257406132, 84.62434111772961, 85.99806283731425, 175.16533711710386, 60.378719869065996, 130.46204912133115, 51.85091854171656, 159.37112227527425, 45.022871005203946, 197.62280452020138, 83.03927358218324, 86.6186001748637, 84.39044677068468, 95.88878691869047, 15.264135922785961, 45.460107848470244, 90.28444759671197, 198.18058542066146, 65.00718920220012, 106.8401542096619, 80.95298148143854, 86.18454126546449, 40.02911984025557, 97.75969148140977, 7.603593656581526, 112.4437364142216, 72.75695244736538, 174.80244742966477, 77.46994426772868, 82.90156464981777, 83.93291418958476, 83.61884289848376, 10.603087763273473, 129.27473650505584, 90.98134632247911, 59.798803427613855, 133.76687373256348, 86.58657282477114, 101.3542428292796, 145.84755727948811, 213.55232250946446, 73.10397730050964, 77.35410795470965, 55.93760101510427, 150.8418091790931, 68.35356192825317, 78.5887530732325, 141.99707554018136, 87.55250916280642, 12.906951435805915, 15.804695744446144, 64.14014306918455, 105.48821477849438, 50.985571847121456, 53.72311802169311, 41.90899319504381, 66.66739044047574, 51.64627072433921, 45.3206542159363, 70.30093610844543, 9.29831232387242, 60.12747601818284, 90.93863671730486, 51.95428635403673, 147.44245747258833, 90.3515371181105, 91.06573957280716, 84.67443305027341, 40.141010703706, 99.4830573555615, 53.619498749042755, 100.18406550339957, 113.7836761394401, 57.86751330122557, 52.30578802219386, 52.70225881913987, 50.61435487566801, 78.86381175779891, 57.65783296074502, 38.1411375722307, 55.80883294446506, 62.108833536766184, 61.084811486372075, 99.4057882567946, 172.99588098757206, 50.0775629821854, 86.7875021021545, 153.18758381188883, 97.29587179879002, 73.25103309621862, 568.5098653882241, 154.82319390373516, 58.65741193044261, 86.19793216818448, 58.10504373777499, 134.02920060462017, 91.554429970881, 85.77678815882577, 77.16482831533585, 81.75453630121986, 42.56622547700291, 166.88347537942886, 116.27034180602028, 70.14082941208665, 135.25982798173092, 83.88554478740282, 66.41683247721707, 67.83706358192164, 6.76753731707312, 57.84235558927317, 186.25239598520486, 330.6839076519598, 72.20442560789719, 109.44688732882888, 63.302048790098084, 7.311835936388546, 100.07399088295851, 72.08166820054421, 112.92062913856722, 76.7441464304247, 243.1331911727959, 115.9367844555558, 43.523861732253806, 303.55846855433356, 98.20183572237677, 84.39595044434925, 129.60625927102427, 46.339114140318586, 82.7711023177534, 74.9978470370944, 385.62417271244607, 152.55509099299366, 179.01118783278127, 200.40481317667374, 57.29162104386937, 99.02381168341077, 55.543461663887875, 90.68141506495776, 56.04438004782201, 80.34887578280093, 62.16542863858009, 295.1659248779181, 51.91293512274378, 59.39890591689026, 59.83443455073484, 61.53243084755996, 60.91567795932277, 42.34460835275805, 117.21808422331782, 85.81959768132373, 94.20525570199386, 124.34298969248036, 135.27027338251813, 67.43738144092461, 49.71559953292931, 60.153619785511324, 66.73703477647084, 72.63184684271503, 79.61572993455523, 158.02368931172498, 412.026877014359, 80.23923496105375, 160.07846499538837, 333.01782377162885, 57.83719951566947, 98.08102924812495, 87.31701063903893, 43.35056607306686, 49.95570391854915, 94.66691271674796, 28.261595045161275, 94.39480541612507, 38.89305109321897, 157.5210337867373, 59.83850606225638, 52.35611607031439, 104.17318665068878, 152.27521413866774, 65.38574487420264, 59.20727265315742, 155.3052864781388, 80.79845999197178, 6.886156058522771, 217.6741615771063, 67.95163196971829, 109.28899395116036, 64.19397958954019, 69.21801182160634, 59.118444581072744, 43.98490270319179, 189.96071190686396, 47.9576621503762, 85.79015976122659, 89.69457860646718, 26.101523908353407, 209.44588217541713, 47.86459324838999, 50.14990395689262, 127.58564758488474, 78.74963897363453, 79.87884859702226, 128.76163618680903, 35.06031634783338, 85.84374749438003, 45.669333348459816, 43.816627881094874, 47.82294364698926, 47.33878972633842, 48.05772804474256, 50.552721089535616, 68.05079692458129, 70.15388556496428, 51.50185187178433, 58.4856173391319, 29.393219992420548, 101.33557330908124, 107.06568145088713, 111.98328780921211, 137.38942629471924, 103.35597340963353, 84.39481177636806, 47.224567852185324, 149.74975454449972, 54.58820025931697, 74.28078392417844, 39.36582974549559, 42.83267792305962, 47.10703834570353, 152.03515030236707, 266.76776407026796, 74.15988506359552, 35.28751994626282, 105.34667057903344, 144.45844165257736, 78.15449160680379, 134.28246711823837, 84.65399354160921, 437.5955673343518, 58.77528154315737, 40.528044860700476, 110.93016459490784, 126.55399800773405, 75.96591776577378, 86.18360588826822, 90.51901741135777, 74.12695639293948, 146.65896622236778, 181.0418949305479, 5.545708792461011, 86.75777958610036, 67.53615130861299, 59.3229250938802, 19.761671285532646, 49.240680184445104, 227.14123924285934, 339.74137261595024, 38.66977041324479, 50.000341126263706, 72.65214034602185, 95.53105228376657, 46.57080745104055, 47.61196803739543, 54.79570662826405, 64.88539299775492, 85.01870254417085, 107.19207846853861, 180.44592295761765, 51.43305825994707, 118.0539106184651, 44.045415005326326, 61.00619651513816, 81.37955455520043, 44.7657287679452, 125.50552413883891, 64.40814648708327, 98.96730275067067, 388.88218357617154, 68.38836020312105, 69.22175570741271, 132.82142292601876, 72.87011900726864, 69.67134516479015, 169.4433548466268, 55.42957706289217, 111.66063133089031, 57.46473704203908, 48.15818917587113, 200.97556121961725, 112.52602974331106, 78.92115443604717, 68.36635739463797, 72.19121614891843, 91.00815578002737, 43.37649313094047, 94.49099703635801, 234.3024014430613, 135.3432507862896, 101.04572392885585, 192.3178191705058, 85.25848558952126, 124.64508226800426, 156.7795848380033, 12.904776738210472, 84.9761401824201, 68.14752567705145, 180.66859272184627, 86.73256862594324, 68.7667616832929, 128.1443169363162, 58.083129017074896, 97.22392542755446, 134.4411678787813, 92.35630845653755, 60.798201712209156, 69.86959412438328, 62.88137232320236, 43.191444234594066, 169.45828886510597, 35.94797059971161, 52.35471721376851, 130.7525237609554, 44.81606700347383, 35.09693823989627, 71.87702996174252, 70.42701347633165, 81.1867446186514, 64.86698456040854, 135.79242007266944, 122.51198534314577, 55.58096547257237, 49.39485098813628, 120.28317929077426, 85.36300440896773, 189.85582251280073, 123.74493859655729, 84.61614453902813, 143.30728480389297, 75.22909517941139, 88.56453673109208, 92.93266719117473, 82.90221010342731, 223.93744693340565, 55.32915993681616, 6.129539672724275, 207.5429376402285, 18.194390235730545, 110.99889477364897, 65.50011679281742, 108.05502307821686, 165.98714718981114, 46.60414949503859, 160.97246501849583, 13.575089060373204, 68.28432028959558, 149.69292279968025, 128.03798215206544, 111.21107138330913, 96.89795347535691, 95.29829058562771, 19.47442639240345, 134.00082289613368, 48.10738567660392, 80.73247086406838, 112.44763853735873, 118.59999166217189, 86.51987333320051, 73.26821016550703, 109.96055500559056, 52.45354211300094, 75.42795993163473, 149.9993414623805, 200.55848037431412, 9.109052182553901, 88.67957590331561, 81.41924729144925, 84.8785133546143, 17.309432674272333, 58.484350730833604, 9.11396975393093, 40.35798844411598, 58.86233469269831, 63.21788998261082, 291.843244117367, 103.89202046609034, 38.89168785399081, 51.25691953019268, 64.14777081806257, 74.31220960937779, 78.57016340115597, 14.187280764847221, 25.908069830733897, 12.914843460111165, 66.35680131314835, 63.188542090690916, 101.9431706966915, 167.05570980963117, 153.27077582019857, 122.99620923824484, 75.22332700484746, 185.73855028894468, 86.26586001075918, 55.55149597364544, 46.46423686181903, 12.690507504082726, 97.23355327029299, 114.33975678524278, 125.30729357324263, 157.07433508988456, 47.64914214017102, 57.728595902886674, 57.4320789729697, 50.10558356586665, 223.</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>130.2411031532287</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>109.462707711644</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>[80.57661437988281, 66.40135955810547, 81.46405792236328, 65.95821380615234, 494.4472351074219, 210.6371612548828, 154.19175720214844, 90.94774627685547, 130.62026977539062, 260.8936767578125, 51.9511604309082, 143.37738037109375, 57.255313873291016, 66.11503601074219, 59.50394058227539, 77.57554626464844, 8.897515296936035, 95.66986846923828, 337.0225830078125, 59.16468811035156, 112.30620574951172, 352.07574462890625, 56.73434066772461, 76.84813690185547, 43.45842361450195, 73.71526336669922, 150.81106567382812, 258.51531982421875, 67.46320343017578, 90.87039947509766, 197.73944091796875, 62.05543899536133, 249.2222442626953, 65.46492767333984, 259.39971923828125, 199.29559326171875, 81.53764343261719, 163.12339782714844, 49.516239166259766, 170.84552001953125, 91.58011627197266, 57.410247802734375, 85.50292205810547, 100.93450927734375, 115.5739974975586, 50.907108306884766, 86.61585998535156, 46.098663330078125, 191.2461395263672, 102.29402160644531, 111.49188232421875, 60.25535202026367, 77.93080139160156, 11.885536193847656, 84.10840606689453, 640.1781005859375, 325.30572509765625, 80.21766662597656, 70.07152557373047, 348.63507080078125, 80.2850341796875, 55.34033966064453, 143.05990600585938, 114.29959869384766, 106.75020599365234, 49.61083221435547, 67.32205200195312, 177.2145538330078, 336.6325988769531, 54.5661735534668, 50.7043571472168, 55.14138412475586, 231.87152099609375, 18.138648986816406, 65.67369079589844, 181.37789916992188, 92.18943786621094, 36.7310905456543, 91.64994049072266, 160.55062866210938, 65.83291625976562, 160.81874084472656, 79.90998840332031, 130.19993591308594, 63.0474967956543, 127.86215209960938, 369.1365051269531, 109.86080932617188, 232.8220977783203, 90.87687683105469, 137.27183532714844, 83.16999816894531, 54.239288330078125, 516.320068359375, 104.10993957519531, 15.355088233947754, 81.23220825195312, 91.54454040527344, 91.8051986694336, 137.67169189453125]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p011852</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 22:45:04</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>88.88922269517488</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>69.91416583486324</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>106.1051178594181</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>4709</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>[0.7430754746654005, 0.8429539048339204, 0.45011073337225205, 0.7357876661449371, 0.5260147067296467, 0.8559978631617374, 0.5350806028446405, 0.6258678161476883, 1.1237511894258752, 1.1705172055535455, 1.1413959273778327, 0.8572395372887303, 1.162658481259171, 0.5324503424768722, 0.8776140632685685, 1.0800709346527264, 0.867282783653985, 1.1709348097037695, 1.2575208637471607, 1.1180839642785945, 1.3539435489925429, 1.8764741127795987, 1.1647734121636617, 0.9875215847416456, 1.5349774727001098, 0.8238355150737295, 0.7216369888681052, 1.0884113737501322, 0.520342094612604, 0.8728618638401641, 0.9704538365163728, 0.459141824004376, 1.108805676678924, 0.9653628280694393, 1.8408778146899767, 0.4582024834417386, 1.4432841582058706, 1.884951989311475, 1.0363873914317026, 0.8710663321304711, 1.545042277635392, 1.0388026598021451, 3.8930763635151058, 1.2814276303685959, 1.153479239733601, 0.5563930023946171, 2.2949581062969484, 1.640158462085867, 1.3309384418429069, 0.9863458306727367, 1.5414363061669534, 1.7078111903179714, 1.2210908638379774, 1.9221477110694098, 1.3129685407637015, 4.294784287791509, 0.7797313769795949, 1.4764560858059819, 3.2268888436020196, 1.4196105136561947, 2.2545420631503172, 2.132745062211672, 1.25048056440489, 1.3585289905716278, 1.7486405499193438, 0.8433082099237086, 0.33019520185033735, 1.8587194984282833, 1.7094884961086692, 2.326160242276061, 0.9890764288184353, 1.4383212303525137, 1.9603775806684833, 0.22962962833323752, 0.6994423839237986, 1.2354179200808035, 1.6674814537070002, 1.0304296923230678, 1.3210608528067558, 1.8799735132222628, 1.8997570590288881, 3.214913134301599, 4.6707547374310465, 1.8207327149059354, 1.6260461512926625, 1.8177117172518453, 1.7972626764108313, 3.149458844972019, 3.353309987322595, 1.8112920108107753, 2.7012636622237487, 2.840498334091846, 1.0933132948846638, 4.8832567234024005, 2.662882666823331, 2.7227798725380654, 2.941983996364016, 1.938884734770474, 2.063871095502566, 4.664009477236247, 4.892137008147233, 2.955530376445196, 2.8973014595028044, 1.8549166274832718, 3.8037832211667815, 3.234078884423099, 1.4502712644167608, 2.3124142327557813, 1.6448834843485183, 3.4482047033320327, 3.0381764172556665, 1.863051450427636, 1.986227354714138, 2.608341698349837, 2.682858036840817, 3.679095148944809, 2.052330764940179, 2.7728740369589078, 1.633837379061535, 1.4583637732814276, 12.655309237670824, 2.0404930580639, 3.900159904909674, 3.868790092546041, 1.5041235528917989, 6.823787298490057, 3.403723739940117, 5.092630218353478, 4.440225536913377, 4.777716740076702, 3.4374759227342624, 3.412177698232878, 7.975997322717014, 3.711093559741586, 7.31430303500592, 2.567866867055587, 2.418744306095157, 5.3328977045049895, 4.851409735586761, 1.8356723143682743, 3.6219234859788894, 5.3265925573903194, 4.738970636460796, 3.943839114598148, 7.2576202262638185, 3.542980234367442, 5.164686020011408, 7.152618302215456, 1.3660438125983123, 4.9709074268058355, 6.48943096927271, 3.4056072946735423, 3.288268446052045, 4.079108852495393, 8.86092147439823, 2.387939932804473, 5.5465413118318505, 2.8968845942718455, 3.9318777845088024, 6.327391846542455, 7.303561493094162, 3.6090377241007556, 3.1430136277047356, 3.0006770085054395, 7.363451721084978, 12.422219053845273, 5.4188273599311945, 3.1550982595604697, 15.653275507004345, 2.540011101016709, 11.151895351895206, 12.31878130802017, 12.38739321451829, 6.105799442787358, 0.7458036383395189, 7.239490147005932, 17.518443468380056, 11.299982674347143, 5.311654606275599, 4.038604267229816, 5.705656377153056, 10.88483544174533, 8.48047551207796, 4.4474813852625825, 6.391799474667899, 5.884961135505874, 9.501993230536593, 7.235485893820188, 4.780166382677976, 11.438275014773742, 14.332537323188058, 13.556301125615745, 4.293833045570375, 9.318641952923898, 9.559441758952364, 10.140847779228814, 4.56981755770456, 10.481782726755045, 3.8344508002511746, 6.858179560510932, 8.802693067568205, 10.49110200616056, 24.082830529436908, 25.62065761589289, 17.509572835059007, 19.15842000325776, 9.670291235781791, 11.151192565991348, 11.261184085904459, 8.180634904053736, 12.87711400741472, 17.756334718923256, 13.491111291850016, 13.885569525203454, 24.36556572402264, 26.236932930700316, 9.053048565880566, 7.964961154546725, 8.524748835944104, 5.426412156466095, 6.888963979432508, 13.427969814834771, 11.081447335087715, 17.994814775174053, 11.008990530882762, 29.04064991972168, 15.43539164166747, 11.97321850184972, 11.596605752109737, 17.794443960512424, 5.491439924498847, 33.104442396975685, 5.466911944608408, 12.579820651994043, 8.487169506177391, 10.195714808804407, 12.133381664906487, 17.47515434523651, 19.278292707650653, 22.142252706941402, 17.52471121283741, 24.29986801470695, 19.88107606251115, 37.66703537432316, 40.44032970535829, 33.01794288740583, 13.263436076454832, 17.228353594846766, 9.880108209195289, 7.732612777216169, 13.211163460603844, 11.706876557617075, 21.8809749159315, 37.674051717619, 47.33739393815463, 13.70944561077187, 26.0141709959322, 44.82471505282077, 17.485412023877846, 15.98194903843962, 25.871720279539165, 15.646763455245228, 23.476495263405713, 17.90709014625798, 18.693200826077902, 14.785849483513987, 27.126370073483056, 10.58340785692055, 24.18754482698397, 23.427567937207495, 45.211780450060026, 18.15152434643985, 1.8095759015831852, 12.86907977681349, 47.51263743779774, 40.7970563670392, 9.831847437893835, 23.2301586975687, 36.862606814367304, 28.41829290326737, 33.795310466351374, 42.70045942365185, 35.086301426416775, 39.33273118953918, 31.382319604240035, 34.50600836108163, 36.15580992398526, 16.516545010516786, 20.570753151108498, 4.194967769275721, 25.23179781432027, 37.1202062392863, 19.983446427642082, 52.324552180112434, 38.70402360278534, 19.608894160773147, 33.096218582988385, 26.99654616977599, 28.673146155818, 6.197134924200548, 36.425143038398275, 42.08808115605406, 28.615656947335236, 18.692662345623, 30.531827677723154, 42.78399884244822, 2.9422749340357104, 28.56748746811605, 26.15496862953244, 22.11190657048083, 48.19343491490098, 38.57878793310051, 24.907841525418185, 23.514769765137245, 17.60112321123446, 24.92648443243273, 50.07798092305674, 3.077279267178135, 22.524308045677504, 45.660244057064325, 55.08463525762059, 32.55037316854613, 59.100488927829275, 35.91978122132918, 49.507672743456965, 11.14430337880813, 18.293682855265548, 23.18677524171763, 44.82994812683823, 16.40381363969173, 37.744950966785176, 27.12168180167455, 26.963380375101636, 12.916956186621048, 56.088989126069215, 24.56902763506286, 35.156043710034965, 19.782981779543626, 27.474880845147613, 22.429119098047458, 28.95898437975098, 25.81413280126945, 28.673575871358537, 47.47334567994899, 49.896835326292546, 39.57871027269874, 32.20211717974705, 53.26536640081675, 30.823919051839727, 64.61137483417495, 53.121672319391315, 39.804269441592936, 25.407176506322003, 4.168630605306046, 51.116086973151035, 46.40107811821869, 34.339541006011466, 21.384433317480717, 36.60708260426766, 63.31283271161359, 53.79366393788726, 77.2203655442879, 24.95343452016212, 28.724442194692035, 22.026549114665915, 73.26696520423353, 50.59607882507709, 37.69788037425757, 63.29806414852456, 50.059884958931136, 67.29814248131439, 35.27441240035875, 66.02246907548967, 26.933662728646798, 49.50302946282842, 40.06208937479791, 52.84339221595364, 50.472236902095744, 15.837034592203503, 26.639002246209692, 30.18383563263429, 21.317873879156693, 55.331628166792626, 32.33679232184335, 61.1533330110453, 32.229286764518, 40.66498815083046, 71.92223681055684, 52.639509630811204, 66.0735215967178, 27.27565883517865, 41.515612209934055, 56.25070056293198, 55.717715584715265, 63.507570001024085, 36.28263911958298, 42.31839875575888, 38.8159079604229, 45.064576229174364, 45.24526514833036, 23.09664564170223, 34.846156312934085, 32.10007864617194, 14.814858374586182, 72.52552571912071, 33.68800586201436, 87.3219629717716, 93.40656054408262, 30.696100752015894, 31.306860952619516, 65.66337666700775, 67.4990481655246, 48.112099492462065, 67.3469183029162, 63.60064017414925, 110.78046140489842, 65.60791688318362, 87.21567658684994, 66.62326050957425, 32.42951030532209, 71.3204895798258, 47.798929125725124, 54.78753948637205, 98.78837104248234, 37.29688579216764, 3.165896254574986, 95.82162347424209, 49.117689767046706, 33.05363764892325, 52.984241632060225, 88.3533606833292, 47.835731273629754, 42.76560882814091, 43.124997229121455, 102.97798101103807, 73.34269908405466, 35.41773129195242, 41.532611755368386, 31.55028531944651, 91.39248666347198, 39.977293227220514, 55.29667039140305, 38.990658157057474, 50.56498000807084, 28.867919660856476, 96.04953421266133, 129.77374967659551, 104.4586496723903, 38.054423612025, 60.4077100889977, 42.824719534500915, 45.99701497836055, 60.30753433353578, 61.65995508033568, 61.27836948605246, 89.3029769978581, 87.83727340573085, 81.49275853837932, 32.301175150630364, 100.56078728318548, 59.119826566348046, 47.44541983150332, 39.459865522443614, 29.072193625217245, 4.45309575347468, 51.60638489159961, 64.34016665644397, 32.18037023592178, 88.5480248316448, 91.36967494828829, 49.47039169432153, 29.500331893138977, 84.4740257529869, 72.33061207182901, 60.89455336752798, 37.58663613363394, 34.96533165155392, 74.78834163083779, 87.03162289068526, 78.09412083806023, 42.88537331881744, 53.56516976399712, 37.20393086946115, 39.19604077002573, 51.53359042695449, 72.07029976971687, 27.215596226626904, 32.47513411638475, 43.858782708131656, 89.17696754489153, 5.289094558547528, 91.69590471023838, 12.76531458253603, 49.81790105198775, 32.33989350054425, 56.765865091650156, 54.16129064307088, 49.73664436712207, 26.655739384923884, 51.55855091620527, 86.79264129057769, 42.736229270352005, 55.648426401673404, 17.93282080266228, 129.10129149603864, 66.85969380367047, 4.286742601422575, 46.3465010670169, 13.917068459875386, 68.68180040468083, 41.289352788620576, 71.4009802738511, 55.46419032493173, 51.29548826891184, 46.58593681746616, 79.87249425916757, 28.148139973636734, 90.33681586068231, 91.81474699980494, 37.8289700009125, 26.352995644078952, 43.653766983802925, 48.479996792474836, 74.40125043824075, 38.447563094600135, 72.80796079684286, 38.97828427033883, 47.20107694081875, 45.33332713137099, 67.5541357065607, 58.64839719114164, 27.63026241911563, 62.67013234861439, 43.68105618745946, 56.468981120790176, 38.24207072261981, 43.67539476113426, 49.54277061639379, 35.810372420586184, 38.20990883990499, 70.88293105917563, 33.28307025542936, 46.08495172239855, 62.61100621487478, 47.32250683369959, 53.11900581214422, 58.46592158821036, 27.735058735337912, 44.586366214640734, 67.0054343145892, 55.37667941796792, 31.99900823789745, 51.27883105274883, 56.66791231585767, 31.044793773673558, 17.631431887197426, 37.04140199057193, 25.671612894322784, 52.35965539491558, 39.18576245983145, 5.297669278276795, 54.1754683079454, 36.26706893436983, 106.38883348250226, 17.233463490373264, 43.755864334566816, 37.25740624601042, 55.88977932621947, 57.286691265347436, 87.87612987127162, 98.32737021247495, 52.5583238461884, 112.98924835892058, 26.92493008758159, 61.90427029238113, 115.62557322456775, 32.62292482654709, 70.73537104759154, 38.96872307133442, 63.9155007578076, 60.86357669401085, 44.96851916328096, 38.83214082854403, 50.91297121299041, 97.39018357311521, 52.6702063330219, 37.36388409203525, 71.35550348960005, 106.77401904634958, 42.975746603839966, 26.396044446666654, 20.10574762551188, 37.92949869800717, 40.695888867737935, 42.86797495854108, 52.424835730043924, 48.580720963371114, 39.32504808564551, 91.6433245034573, 37.95307463470103, 120.41146880764447, 80.03032341261995, 98.62367967623211, 49.90927808000379, 39.43105511005504, 47.330385365511546, 41.34000799751393, 63.89593563882579, 37.97229054131154, 84.86320470801647, 124.54692798404216, 90.22357722658246, 46.21298546927093, 54.00511311142743, 3.7807642042533205, 15.13974153293239, 38.37241474215964, 135.5173914960846, 51.447812799425584, 94.8790964368657, 42.49589286665431, 111.20619755050245, 40.61383953265893, 80.26077120987898, 96.22870919899262, 47.03878230622097, 41.09878008349803, 54.581623162927, 50.75863440088699, 56.0998668793908, 51.25031377511793, 35.71182239326361, 42.87612103922458, 30.114390109016824, 32.63001165097765, 99.20590513596763, 46.78512939682215, 42.436355514576235, 38.151853984194375, 8.516802581407363, 104.30422085087724, 34.93180237592672, 44.091085022004826, 61.72765218992141, 44.60317297570797, 40.325115242953316, 39.337166368803516, 47.302271197125826, 52.8107219268671, 98.77465112861564, 4.82954800892199, 19.022208073033003, 50.76466296866964, 36.114275853281825, 80.65956598362001, 35.93725667033156, 70.66864161910084, 41.665842225989756, 62.751014678175935, 49.151273139305395, 59.88582833338766, 68.43384116897684, 6.866715934890598, 6.778710574080831, 62.06351656178806, 42.916501299465295, 98.6614499796989, 113.67461899148398, 63.238502687604196, 55.08661693715875, 8.550585305327475, 74.97303796765249, 67.68360246777338, 47.14437833975129, 77.57671003222934, 103.26654495284572, 61.12108796525916, 43.193263307866594, 130.33725027072003, 92.89713490247503, 107.23700783125771, 57.82936189643749, 7.771954255386175, 61.016812173231244, 78.09565251473562, 42.04609349410612, 51.990510782136546, 91.15748668638068, 78.86044834667351, 49.22222182987655, 70.47729206994651, 65.73444597558974, 83.69319386987348, 50.467718831221596, 76.35251157077914, 44.432108631553106, 7.818835645640384, 49.08218223068757, 40.50905910547252, 52.958961671667474, 96.19052986470659, 44.01044451692584, 76.89778937992823, 57.34312881130848, 74.08730940338435, 4.887565183290328, 54.75287756419077, 35.333762501961395, 38.14466837934309, 46.04785557663772, 114.66917684293145, 69.30095281470138, 53.696929388588785, 431.5434925114224, 52.81720142609521, 72.03725293512309, 53.29938491560185, 55.767867935036634, 72.27027574324731, 39.10129263057363, 83.57354227184531, 76.03107087729377, 52.34996456066587, 111.36957571495753, 50.63614291663258, 60.25724538244104, 97.8444836865846, 89.53508163307417, 46.884605008620525, 61.884644776470054, 75.364325768528, 106.02147078354949, 124.29209813631927, 46.68581741482942, 58.46734371033218, 5.1808081935427, 53.72228654180313, 52.85173902573985, 29.303243433631923, 78.88895815254062, 69.64540515865423, 36.99027635036594, 59.47473512131794, 58.56412283116723, 61.42332027720132, 61.1883040287293, 67.35280864942071, 70.56660549406651, 101.10369736373593, 44.71426476000975, 41.441888050971734, 39.39060422408955, 64.54965929801193, 36.47847319441659, 97.50598220546644, 40.51678680874206, 87.47090810843886, 100.91333219054577, 63.142440746511994, 39.26723855517156, 92.59849274478721, 56.70275334053867, 296.6075951753499, 75.03163835775739, 54.46304343326654, 55.44823469382776, 56.98409698069879, 46.412677932114306, 67.8225112512931, 71.61321241075126, 55.947060757633395, 74.78240397928592, 49.885180601342405, 155.04860102341547, 100.3069927443218, 51.60048005696037, 54.8487243843143, 129.0845380819613, 84.73020852782321, 67.91711821515166, 7.745191164614528, 61.28689728233031, 48.358906548286285, 110.0107100508903, 94.1620382188711, 64.00987281572802, 158.3073212868488, 80.98794875948519, 88.8540095174007, 59.2987337937941, 44.03993103213097, 7.22547486964957, 38.48038230486299, 44.199900603576204, 99.85359412574414, 54.32127256187089, 65.95387790645513, 5.589133860055151, 52.32032857126554, 129.0288051344141, 56.76312494474839, 62.745296384963794, 67.26907578437968, 56.383936825564675, 73.81765550118234, 68.32241418596263, 36.081518526966555, 57.60137272428603, 34.500939949789384, 79.28092004412741, 49.26065117510784, 6.389192326250638, 53.84827450552399, 38.914513483694115, 57.99852671921772, 55.005128987053176, 72.56872864852511, 166.5385884299665, 46.576417026743485, 30.364851156525816, 47.359760846830206, 38.60468721182482, 42.185677609402354, 70.06740722721088, 95.10357912333323, 36.63044108649656, 110.23017825466323, 45.57666828515441, 60.96564315681116, 66.93468235434909, 105.14540595432787, 52.35767116698544, 56.13827253298701, 47.75717468261693, 63.65629969525237, 41.32954065258147, 155.73046875925832, 5.0204944782484775, 78.97755023727466, 103.97104945671725, 47.75431790571507, 38.003258532387775, 75.84305526206981, 88.05609239530185, 29.300656317408098, 54.37123828170194, 57.21575755235421, 49.351945795007204, 62.119117133372, 104.31961279308308, 191.44004866548494, 35.38767742754019, 8.062004794072731, 37.611409036252, 52.90557236546859, 57.89119931932634, 36.80154109692211, 42.37096698079917, 69.89460053099187, 77.13603733361015, 47.67875736581758, 53.66225786310966, 45.08638646623529, 44.83091085590141, 135.67511704974333, 54.699392261792376, 55.78761882172496, 58.92108385913716, 52.62039812990146, 49.365076071833016, 79.7019004394685, 82.13669675606788, 33.825425559079555, 71.92459195933941, 72.5255528764224, 106.06881439101281, 55.268970535460554, 79.26716231922312, 59.41430094178201, 63.5458839321557, 24.806890881566947, 66.71763564916529, 82.14000418239681, 6.591246283053749, 89.38941939710426, 46.55164161859746, 90.1329465458551, 58.55507121752506, 95.72855919153008, 175.3285607927861, 130.21779641030395, 217.3503941437906, 114.0733961886302, 80.7865785634012, 82.3870876473997, 62.77231139317923, 65.19032957346013, 8.891332510393282, 53.208364586148825, 61.1831726831839, 19.99027764473769, 56.82548787154109, 59.49608993515736, 84.29469630276932, 103.68918467200277, 39.489997955510795, 128.43554838467995, 73.29050948535269, 44.90655094785271, 88.13419632793267, 71.07274762112111, 39.337985290349245, 89.56821621498771, 97.30244570770849, 111.96039647769574, 65.88152036681566, 141.30025719011016, 86.08458140356288, 59.76057819523194, 80.54559458249243, 68.89208762029634, 68.40358129269782, 83.29775025447759, 57.03720391879179, 50.51340772579341, 90.14629014713623, 62.27485754895555, 68.12233770689039, 101.51197409730794, 47.965768425664464, 63.031169399942534, 70.68059448921646, 131.74659865698197, 50.21566031402452, 104.53599237464749, 161.81956370832165, 126.5406938021607, 47.63619857461775, 47.736027550993974, 60.77072522168878, 56.106133372979784, 185.18744247368295, 87.59583169417563, 4.938276623898963, 95.41167216274106, 72.55981201350085, 105.12353933127325, 69.11103502640758, 53.568630386747515, 53.245874624367865, 147.10835144622393, 161.72729714285586, 71.67494712185777, 51.52156145340942, 98.84379311647193, 56.010293353888024, 129.93028209050837, 149.80826641391852, 79.5541172611235, 131.49796829267663, 68.36862461714237, 124.94049723391926, 55.74633665869, 49.38644045319792, 46.135729401376615, 61.8926613077176, 60.55605095863986, 83.92438591750366, 73.12566448533605, 51.270745782116734, 183.30712804018236, 32.14655343110294, 170.7931837470124, 121.44794947201193, 61.920378400880864, 225.1363654691449, 61.85293646978955, 115.87292054426685, 54.11886001277042, 68.48754178860354, 43.1534596724404, 62.29332056929876, 135.30561796134134, 61.906034166229624, 166.82212843547248, 142.54853850132343, 116.5400704282241, 37.14747642717771, 122.89102047537351, 97.3691133715273, 59.02518730896409, 145.30899194377537, 40.38476945224907, 140.80574906972498, 72.253249132419, 68.7154788358603, 65.60023193887778, 48.515716686627, 71.44723696691236, 69.06775690882155, 84.86316486669494, 61.21175009076964, 53.820847339193286, 104.88663230455757, 38.67235423928122, 197.78449034177362, 120.4668838445851, 90.31928342436534, 89.07708626894411, 42.94153282447426, 63.626431865401415, 46.712952031710984, 74.28683444619153, 73.43501107318802, 89.9216600199689, 80.69101370041905, 66.96590181487281, 109.55841616126484, 55.54443423668623, 52.92413325921502, 39.29388646629756, 42.13883187838179, 88.22711794093634, 116.70018915195115, 42.59355498925561, 168.7804787545721, 72.09295339346878, 91.4157145980948, 67.49022601120852, 81.62391992020116, 67.71805103217248, 41.38080934837378, 37.86775524799612, 206.3941376550672, 72.2411229582766, 58.72540255264802, 12.674020506205405, 100.6179581151004, 84.8867611582316, 60.379616544202406, 61.64665187153851, 58.220404147204135, 58.74319050399235, 95.29084929070616, 33.05623981824818, 101.85714460024933, 52.63607790632762, 57.77930662472241, 106.75141358077272, 97.94672707169502, 61.08408278143486, 69.98909355868174, 90.9518840854064, 38.61951910207932, 75.16661651744424, 82.75334642456167, 46.7301412307762, 81.29690725988894, 63.43703249090877, 73.66913493114424, 111.92142577492523, 54.43663971986751, 45.56630542804506, 60.62734171460955, 62.42642850047074, 69.9347480808001, 55.75395182675902, 137.7709131121599, 51.81295649442585, 91.53902795484395, 100.55954398071056, 88.07438191015135, 146.23260724234737, 113.20787522178819, 303.67401131128287, 83.97371044070061, 110.84180840756511, 65.13484929697681, 59.23633754190264, 202.1895204401034, 102.62455627208419, 84.76515678861595, 68.34014042212924, 73.4876058082751, 56.82072474907734, 83.28993430174617, 63.13550540783861, 52.50981188069542, 14.943882045566852, 57.554911127480565, 44.97054214190233, 87.1671437405573, 105.77903227345912, 9.777123414596495, 203.50992907224617, 44.5405894387019, 120.14979468167682, 106.7981203926857, 64.01282414737447, 100.18291490308975, 74.39290245310671, 53.96845287569511, 51.778411952687094, 93.06653633345903, 57.17782504631972, 100.81891724057613, 50.47738959441157, 38.30167441427177, 44.28908449043761, 122.99516144173468, 74.36689292924544, 53.33824267840744, 66.9018116376793, 71.14906821376553, 63.612813201568216, 31.753268670378482, 138.68642470136413, 130.56949689742257, 88.37534377459471, 62.46210321531774, 81.03269181404659, 51.00680652243415, 67.3552586141678, 74.22490272931415, 67.29460676958216, 170.38431061237014, 47.35949346648406, 169.8576781707451, 67.84196815249837, 105.88777018738969, 59.25847362558025, 86.01428392277575, 62.75324149434321, 73.01401636413543, 9.278954270444222, 135.84149136923156, 81.80740623458924, 89.84562582312473, 52.87042602184087, 62.584963452223406, 49.70301885820642, 157.2525378578954, 79.74820302499299, 81.91257688827962, 77.7354132357573, 76.8563921494783, 40.47902237916319, 68.28412911765832, 76.48539593127687, 91.87574820317644, 105.54558813307865, 49.74270124740702, 166.27505330227058, 163.92388940827993, 67.36525690124631, 59.79139596833688, 166.5620821117276, 86.84591471874892, 61.702440345099795, 19.186319603185495, 80.30843125679503, 79.03573153934775, 102.55289797938603, 88.76739267030081, 147.88507542536263, 52.854120027335185, 54.35031137510892, 51.52388019089968, 100.86609209494766, 49.20303689024624, 109.78737143961114, 101.71576077300575, 86.27397801799228, 73.387917610386, 26.710281679980024, 46.283008917660915, 73.09147505071904, 66.03683733477384, 71.71677627552843, 154.58304131126462, 106.67908858674515, 75.18365876654474, 77.60973952451887, 77.0848653925762, 110.86696590751286, 51.507345559660216, 61.17093754213342, 231.9758702057871, 109.5706693082697, 70.43384383176101, 52.50793040752902, 52.80493525949632, 98.2135968115702, 66.54915697719254, 54.02980988352867, 55.364144842733445, 58.80271625406797, 96.2224578858755, 91.97044522517719, 111.41082937406635, 181.47271991983953, 54.74967954583326, 45.666107753058505, 83.99825346537571, 59.38005235825784, 246.27547395569906, 47.87382050025302, 7.851785240736027, 35.344635143071784, 31.556003969937564, 134.58633516395045, 54.354472675466646, 114.56074827091207, 69.63368865810668, 99.71393144065452, 7.762217157996281, 47.59185124706784, 42.046222521200086, 131.99450705447543, 113.97592293817009, 53.75692326300829, 148.68160281395419, 63.83201498696707, 40.021225679310525, 48.27043744883269, 98.50380384731919, 65.91441230722992, 65.03928646276795, 80.58733076306838, 42.99995684046395, 74.70356816888065, 63.64048012077562, 99.61058026310768, 106.23199295945174, 58.15150327124822, 46.189616174256756, 92.92444236645348, 50.65995036590467, 172.62875396064462, 20.328630775761173, 65.83507142889778, 114.3644000006625, 114.79016068666436, 35.29911634690146, 43.872668763741515, 72.08804900776254, 110.18182739815802, 69.64230248321273, 226.94351688365987, 83.17082527014793, 10.491049218415682, 12.729150256715117, 59.33508757998874, 73.03332273754516, 65.81670132345668, 84.7183989800833, 58.02628926608967, 145.5625803705018, 61.63451189402904, 146.90993497853577, 50.68786027525683, 34.50353237826119, 58.942792700632985, 110.16243185802635, 6.815699967844399, 78.12726685429698, 244.30764395582355, 92.49804289909507, 47.211020282203926, 103.89326140003135, 62.285179666578195, 185.7137833052511, 89.23449605223172, 115.64316683586797, 70.19781281130304, 92.99250146047846, 77.68285153251823, 88.3208014434497, 48.032680104700624, 108.44785776478271, 61.66949201466981, 60.922596271802966, 82.87136821071684, 132.44605824488434, 91.72198003650036, 73.94769280733956, 43.281253747091256, 98.2935350593821, 9.421404836555377, 115.00293327510813, 117.45053541204973, 37.503952424437905, 135.09033843327356, 43.4228080238213, 8.486348423031448, 50.48891303737398, 69.929529965782, 77.2624400987995, 39.89124748545142, 78.31820979180037, 85.11502592444305, 60.670982523325, 44.20249269255483, 66.61725517695508, 139.6753578195998, 81.67458055750977, 62.37927407205922, 98.32300698590542, 40.09054587751911, 46.625866616947775, 51.025332424224686, 112.6997613900126, 61.321178351001706, 69.96977473922284, 116.5694388845572, 68.37938397032298, 104.33873513330691, 68.90250247543989, 60.461365302677095, 74.69632395013433, 145.16013290871308, 67.49020253144974, 104.96779571711431, 118.08988606143497, 141.15399782195342, 92.2679711414976, 170.6527648435169, 99.43249308684499, 65.97496144066106, 164.77908060766515, 51.675853718624225, 8.46250526249754, 93.59087226657003, 112.16214260118483, 101.35528958885203, 51.51416579707541, 94.8665473467864, 106.51410654679124, 56.12096669654257, 44.733773133086146, 102.66206749044201, 155.8098796985664, 51.03121503799713, 43.87103046454777, 177.13541130394447, 144.57816819808983, 7.29675206343726, 100.59185910669314, 124.0047374159944, 42.012551139946886, 75.70798427577354, 129.2683469450325, 44.47136089590681, 146.15361617370374, 170.58669937099688, 79.87652782813683, 38.79088356104971, 88.54612215297323, 159.73834152489778, 89.15334162901286, 54.82353592454453, 158.1003239899552, 28.187808234860324, 76.03979833465652, 168.48363847726728, 134.74185030920066, 125.36249034582228, 80.57499884704143, 58.5974966021359, 66.01732226699022, 33.858080037643475, 80.23554382143276, 129.17070852439156, 63.19397581437278, 68.42015970293997, 55.12179232129496, 62.27784576308597, 88.00778854821615, 59.057102162822666, 48.07267906426588, 50.281678333987784, 40.06556399659841, 67.05537143879157, 85.14849308035959, 102.36320255493276, 92.60168540309168, 109.56589104246956, 105.64994548604626, 65.12539371170404, 101.90943112835102, 41.2569882950961, 119.22871290053442, 61.15381732974488, 208.11110462347756, 143.13983740360845, 64.97992768014612, 49.764170775704066, 75.855878369285, 111.05663893405354, 65.07267080808353, 59.34299419898102, 51.16775058828258, 66.30049907765886, 158.4249980458964, 107.66413082849304, 148.41731233830518, 55.645453993434664, 38.011463611267494, 11.52320955000481, 30.99954921903554, 624.3262380760134, 31.853335347396115, 120.39358828710228, 137.9546562324699, 172.4290491138581, 112.23356797330788, 39.83036892832015, 56.646294001753574, 135.86378944373885, 38.48541153896562, 89.77722686717499, 45.337675118457135, 98.95289515917467, 166.87429599285946, 101.3887751917527, 54.8007645560088, 51.380604804022724, 59.13709241047396, 80.99385970506441, 41.25817140263627, 6.611537515250003, 79.23018251636846, 212.79558779062023, 80.96952777799117, 73.39453305202682, 98.97348093086413, 212.6716890547899, 86.32568577190158, 111.16454967045317, 111.50921196106376, 78.97549492374606, 178.18801999861137, 55.46351075695667, 63.665918316189995, 61.07705668277115, 127.31239059519275, 68.0657573246924, 51.145111670783436, 55.14702315176241, 104.31589546019487, 67.81770011570926, 53.581471739596715, 94.20901155817016, 235.8933345108891, 95.87982806015447, 54.76786658498017, 87.69860751418824, 513.0675148730012, 132.08800691673804, 68.32527471895857, 57.13023494716519, 83.89558085603979, 62.21908030451341, 136.00187463727937, 60.186022946588764, 52.27882597365692, 121.39843499640158, 80.81923675469281, 52.98958040589849, 87.56702401873285, 92.477387686033, 59.04689993870385, 218.42640962056697, 63.93439022569666, 468.56149069412044, 99.20497602828463, 62.961789485517684, 48.89356760775277, 129.07874394251942, 104.76726427748957, 180.43066543039737, 73.90423054153634, 52.79835754549281, 110.61039578690887, 56.17628219636266, 57.81593420394269, 86.30713931989654, 166.09823190768077, 89.59573432669966, 53.39680550605944, 131.00646831800236, 75.63894992977045, 46.54202420719372, 423.23668618065807, 127.22416250332385, 69.21404135769949, 48.60564544121381, 43.145934383843134, 152.468968798827, 69.83297066342179, 112.97567453650551, 122.64276055457265, 56.935018946753736, 59.82783976868263, 57.70922917843048, 59.01169672938535, 137.4151179517375, 47.33632475411276, 58.37855636345309, 80.99732642649919, 154.5711798137404, 119.5233831503898, 77.34356272811404, 178.95979443809767, 47.95470761405898, 60.63568199586664, 128.22664555815612, 7.039570984078563, 103.93856343113926, 61.93671543120618, 108.36380792265558, 85.9809007234173, 78.11891591222266, 106.99763378125303, 43.35554801775701, 47.404798702108195, 50.4960264989509, 109.69372229778033, 118.61888006981658, 141.39023449731314, 179.00919350560739, 102.98270261895341, 108.31145334632585, 61.86577659116485, 156.85852111167569, 47.496882175421085, 55.53294198732126, 45.660351323989374, 43.35712283793236, 255.18038848166725, 54.6655638398691, 79.50319553989412, 107.86138446013824, 146.68340330734125, 106.31532621528216, 76.89359714203997, 87.79450108854265, 97.24047060768741, 96.79192609816357, 59.67647942222416, 93.00277399194222, 63.15116768782022, 106.69974814104798, 78.2556323925597, 62.24788444470516, 73.65097322170567, 49.274452393763305, 100.42937993003909, 160.7031009117356, 48.73420525902535, 75.2915630683141, 73.36245859217135, 55.57910442659696, 166.5347358846123, 6.145525513698858, 59.33009166932294, 123.18182537032337, 49.41762459563309, 76.72633220334959, 103.8938696684478, 92.08216038599939, 54.351405946093934, 95.47871300323798, 54.35298228451214, 13.349030863390684, 66.69288601662655, 154.97667085075798, 57.332168958353904, 62.890447896810926, 47.60005888281139, 93.93370581199632, 182.35963819815197, 130.41120986690402, 140.92890444819804, 60.24676169645877, 93.3845234389851, 120.61686434848329, 79.43126257092374, 93.95577204800941, 140.8037880594286, 63.71026627386837, 43.330379952009565, 67.29396126280464, 105.16712885913856, 50.86852167971458, 35.477455296614686, 127.17115465413539, 107.21180465705154, 48.2966834189839, 66.88616348158357, 77.10902519949583, 81.42716055097124, 133.53588108860308, 100.81038335758872, 148.9863649256062, 5.242761560474308, 37.58354467814856, 53.04122797847155, 130.00605231486625, 81.30958491492353, 99.79145902937636, 33.22751739642196, 84.79707733434398, 12.489454024627099, 96.6356128894135, 45.576620484149586, 138.61557984284863, 63.87620560119324, 42.60876726826047, 8.090334699908842, 146.03509895165118, 74.83943172310794, 107.86748655162373, 96.41719383277945, 89.37006451138662, 72.41600634915257, 327.7067821608814, 5.713533200680677, 39.90407865157462, 66.73110277254074, 66.27329531512336, 100.90419914805823, 59.39093677730596, 52.411364014113026, 92.26184361258446, 115.25179872148381, 73.9048863451948, 102.13250826355339, 77.73153225157228, 83.99061783848478, 136.9796514577386, 68.50600476041772, 124.0823028593924, 113.5686457140425, 70.16203749263462, 144.69130992244143, 38.85184639269121, 99.38132094008874, 72.25146340614378, 63.457581149149064, 74.59880425577988, 100.39581420426731, 168.7492093256681, 73.26064236021382, 54.84950398786521, 60.44108709212421, 65.49411436854129, 146.00522763182974, 78.42914706233506, 128.49638931496347, 50.52444418581285, 58.31553659906684, 145.556007007324, 134.1002558510567, 53.85698467609524, 59.93109002944491, 74.44474004537994, 45.670674892694294, 55.076498927665156, 61.4628602394692, 56.785134369329214, 65.81537063160751, 53.16798661311112, 103.28061167634176, 102.51994159376177, 98.11902224643816, 110.59265681796182, 57.24763943630933, 158.21712547938887, 52.83162466819109, 63.87663602532852, 62.30762454629739, 287.4198591674875, 81.19757826827097, 83.15805040597417, 111.84424625101636, 64.97240519815824, 41.243178295609226, 91.17277254564375, 87.875015267709, 53.72381878737569, 71.3188972962884, 77.38990523493392, 79.59634592768036, 102.73069835052529, 59.93173772081423, 81.18149479004681, 181.8178844018854, 44.622787135730675, 74.35</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>117.398115606308</v>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>77.57533555107825</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>[132.60726928710938, 177.53530883789062, 62.73810958862305, 192.7012176513672, 347.95751953125, 107.25402069091797, 66.06195831298828, 56.47565841674805, 55.656314849853516, 55.10020446777344, 73.3519287109375, 94.70220184326172, 298.0073547363281, 13.494720458984375, 103.66983795166016, 74.32172393798828, 61.16044616699219, 159.2171630859375, 112.33750915527344, 86.51134490966797, 65.09469604492188, 49.03791427612305, 101.7927474975586, 73.04530334472656, 54.40673828125, 68.6087875366211, 257.7593688964844, 101.51750183105469, 108.8827133178711, 199.8745880126953, 166.2242889404297, 117.15812683105469, 108.49653625488281, 449.47552490234375, 172.49923706054688, 152.84217834472656, 8.644379615783691, 200.34181213378906, 90.66146087646484, 115.58428192138672, 61.113189697265625, 217.3282470703125, 47.79256057739258, 97.88401794433594, 70.79193878173828, 228.25282287597656, 47.0992546081543, 21.304288864135742, 97.5264892578125, 95.22174072265625, 159.72076416015625, 303.47796630859375, 45.11713790893555, 59.632965087890625, 48.42362594604492, 86.3714828491211, 109.54113006591797, 68.06111907958984, 222.38197326660156, 95.7950439453125, 65.33130645751953, 149.57528686523438, 68.30615997314453, 82.70047760009766, 77.13939666748047, 53.86267852783203, 197.7880859375, 101.45763397216797, 286.0135498046875, 75.33302307128906, 48.334251403808594, 138.84210205078125, 63.07204055786133, 68.4803466796875, 57.479644775390625, 100.92115020751953, 83.99578094482422, 99.84783935546875, 113.2650146484375, 46.65465545654297, 131.8516845703125, 308.5207214355469, 212.24693298339844, 73.01914978027344, 160.8163299560547, 90.08904266357422, 88.68103790283203, 175.34132385253906, 108.34219360351562, 77.2236328125, 206.59597778320312, 66.06932830810547, 86.25226593017578, 269.9859313964844, 46.155967712402344, 38.6164436340332, 86.4067153930664, 145.26327514648438, 132.05665588378906, 82.22876739501953]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst02227</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 02:13:30</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>88.2121636610336</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>70.69438050211001</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>104.0531028738026</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>4802</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>[1.3307360286777823, 0.7316750700243062, 0.43243334088499524, 1.0184556735313746, 0.8306176887481849, 0.8720109597673333, 2.3115835407612337, 0.8511964410292991, 0.8759701627183736, 1.3189691209391268, 1.250284426618825, 0.8515716998416543, 0.19662553325651902, 0.976848477027281, 1.4367810143146633, 0.8488228398847576, 0.16702939288881283, 0.9058797193548253, 1.053191569402821, 1.3894358219703469, 0.9880447516564423, 0.7603382848695098, 1.4463537757630782, 2.669818559875987, 0.9716265465913989, 0.8628911887771685, 1.0193511361462828, 1.4419528107982553, 0.069849966711897, 0.6107652117642255, 0.6662207498947986, 1.0799487904130107, 0.7238005015017328, 1.1584847167277887, 1.5592168196133147, 1.3094548058062472, 1.730017959849686, 1.5600755608258325, 0.9732960158409997, 1.2580506574797508, 0.8713618949874342, 0.17015689254303817, 1.2760469433878077, 2.969107570739972, 1.4639374557501088, 1.1639420091595514, 1.4941790758276114, 1.127437305921625, 1.7461782522774167, 1.5938696160975474, 1.3815962441821965, 2.0612325594645418, 2.660246127673932, 0.7508205048077411, 1.4053573219168594, 2.026325763863169, 1.9314268341251761, 1.6530771563816031, 1.6214629644812593, 1.346889215765892, 1.0579157124968168, 1.299876868745128, 2.166014700033527, 1.896379116841178, 0.9705949774473704, 2.63222426511089, 2.5991442012581962, 1.273535628172792, 2.457532021278095, 1.6848205855766463, 0.4880842245977347, 2.583167547692669, 1.510367470020014, 1.3552385804986655, 1.667132932657096, 1.2054945237697658, 1.48500401995704, 1.5836050780651854, 2.2292437057299037, 3.7804401634367455, 2.310486230513221, 2.609960664825776, 1.8295616067427711, 4.531958383069713, 5.035146895135457, 1.6262034811858148, 1.8306183159805391, 1.6921670529936297, 0.26754468384961905, 1.2967089008345354, 3.693064662267623, 2.2431218893086626, 3.862281595332745, 1.4862377493636743, 3.2037931551940177, 3.062719104814307, 0.4633959483025119, 1.4589659185403334, 4.1345122989865715, 0.641129008944681, 2.106532914662979, 4.63341861891451, 2.2991304112547, 2.5125043078605844, 2.254523537786874, 5.849878853735235, 0.6898509117198861, 3.3291688321529223, 4.350814735722914, 4.512660103758117, 2.336390003990791, 2.529575020212933, 3.8805639917845025, 5.2032573782295515, 1.2221860227490384, 5.250766891951755, 1.65653264274507, 1.8669233361525137, 3.184497686570182, 4.281392351503236, 3.9746785884682336, 2.1066572538916843, 2.6942153849330346, 9.300016556018136, 3.8373681812340363, 5.8759708337743755, 4.599460462465125, 3.724530824294859, 2.4553502912913165, 4.013732041169395, 4.687546641196366, 4.3735277503177645, 6.477842068829489, 4.41222716408029, 6.999899708989648, 5.030990979432585, 4.653137198226555, 4.350983250831641, 3.132720589583863, 3.832269893710962, 0.6719658667147854, 2.8574402348395918, 9.5703079276784, 4.624327910975926, 3.852727858566043, 5.025994086485636, 1.6377009517152445, 3.0824626771991834, 5.836319866499825, 5.142666617078253, 3.0130901845174347, 2.804405824334329, 3.131633632249586, 4.967379559915429, 2.487773295579096, 2.4493106506323974, 4.241141994844355, 8.42487836951041, 3.0110807957603964, 4.797044564020044, 6.881474730784246, 5.902942789030658, 4.785837108363922, 19.18590891447693, 7.022536332538576, 7.202783804435971, 12.907656343307261, 7.66001513478226, 4.853570294081107, 4.59133532607347, 4.826563384775777, 7.673263138994233, 10.515728777936012, 8.250654902119061, 8.018572198877347, 4.80549392896923, 7.2051284877372, 7.9096374718570095, 2.735373369370283, 13.931051398065648, 0.39275938272030503, 7.286617882854834, 4.131495377974606, 16.63770028385772, 6.841143736731026, 3.729495125026228, 7.215261947361915, 13.655431279334463, 5.321470895302933, 6.897323916910344, 0.6068050135677818, 9.909237598051362, 8.2824630132377, 10.378284389234329, 6.725902178875925, 10.134603644468895, 5.327739702982353, 13.04361302328511, 10.713059424373268, 21.828375140517107, 9.84929302812061, 10.89147235085677, 15.968519372343165, 19.07040586310103, 0.570977545635863, 0.6760624245829402, 8.711881222063008, 9.346215012097895, 14.905107966293537, 23.80289680502158, 19.783335897299565, 23.481490870003395, 10.545689944301703, 7.1431658646732235, 3.028475059533066, 14.389776963769826, 17.21088732208807, 17.435517833709934, 29.351992692054665, 18.55782863192433, 4.124637020314068, 6.912502001844936, 9.118412206878764, 12.15781887984266, 13.698178829666007, 16.414698674538652, 29.934242828868094, 8.002596987516295, 7.5466390525201135, 1.6666705126303891, 12.46267017827219, 0.5581568563460442, 13.510409121727978, 17.208799078803825, 10.744897332303498, 10.790810255184443, 1.4489322710763464, 45.93479356976977, 19.337980193155822, 17.248283984219842, 30.07190222546545, 27.523672885126754, 18.022998450858797, 26.70838082812006, 35.664925532530965, 15.94559661304506, 8.655415233350785, 16.765828048130047, 14.437760957430243, 18.352127980917164, 24.10661889814284, 21.832649052936688, 5.309439845780167, 16.67002055065364, 23.362235202743584, 16.501540176073878, 24.159903364773957, 32.66137836728444, 17.60373459741227, 14.914584126599912, 11.401661311430866, 3.5194307977505335, 19.500348161636705, 29.394710281328663, 21.56480529027094, 38.64682132768282, 19.63138327596095, 28.11567739053609, 28.971244938081522, 14.177625757493752, 26.407595321825983, 16.615643009962966, 16.414019490772354, 7.680119731272053, 18.974769036348814, 26.22443479948294, 38.668303443531734, 37.7473850679582, 27.1039243770144, 41.27857876158575, 30.650056590304686, 25.03366311745718, 50.726925570281225, 52.74109261502441, 22.728082195558354, 21.535255363565266, 31.94835337531632, 10.571587871731026, 2.9158252287309523, 32.68058982398092, 20.68494518481187, 20.664500206308773, 3.1337053302034015, 16.304378801742168, 41.10383504499179, 14.172822012712453, 19.650007170158542, 16.351678129539525, 24.387960689408377, 25.905322868418565, 38.08641312162888, 27.660547765083972, 25.12255629330329, 8.608066645746133, 31.502399784363554, 3.820243988765576, 31.034322261639776, 32.39628159398352, 23.849665016864584, 19.786393685108308, 13.705042853941164, 4.322574089490125, 8.290398625011582, 43.463498400460324, 27.971527860795053, 58.70970686612089, 26.493168843470396, 50.56179504084198, 28.443293305623293, 25.739840476032594, 23.767407026562623, 28.159075535230194, 23.306570422619046, 23.597392207126966, 21.548022720823543, 26.494234699485183, 34.8749303912714, 5.260588419468802, 22.8138746142455, 31.500746022024174, 46.02659591835109, 34.873130474974666, 24.104594605725044, 38.505654418833565, 15.88376895946348, 51.793336233716786, 24.217636064552504, 18.491444469818887, 25.11546935418526, 39.51980556585544, 50.96247130239199, 29.258668029795075, 41.99334536702764, 22.37229350710982, 57.350723686067646, 49.168697442315576, 30.620185765516165, 31.670014955644817, 54.61249657979156, 45.63763072350134, 48.871158965271796, 47.03960093358004, 51.579693454598626, 35.53663078482233, 56.440888172623865, 53.84268095219887, 51.79823768724462, 36.963796242946145, 53.06551182330419, 38.134098450525414, 47.91017333528837, 6.089367934581785, 35.86641522143967, 40.95807866577535, 2.7066760993860584, 66.13584127029715, 54.08427289122012, 56.565915624968376, 61.94883692111169, 53.405767836364184, 68.56581149791421, 6.964884121301384, 2.1540039058111287, 2.3901101795999606, 28.00305764153274, 28.48524894766699, 53.64657880587982, 49.23275727577874, 23.629969099141846, 26.247075055276387, 55.07379023185345, 35.14004999947408, 59.30076082680933, 19.582360261958886, 42.1284673747313, 73.81912142917085, 41.634440316333524, 76.02243508430428, 51.799535012210825, 36.56533905811139, 129.84898747825486, 33.04394210184529, 64.82372418578247, 39.19748431032281, 3.354287041506587, 51.82902007641064, 40.073094877926614, 58.07885621657471, 7.867924828434659, 59.767952012279366, 27.16499277536331, 39.65467334255472, 79.42050943671245, 7.525822792361685, 63.800772965864645, 45.35393149138274, 60.697882451755994, 50.834420533270624, 91.20171908421717, 54.04156286163159, 22.124946591691202, 34.01965152521678, 42.99459790198724, 30.059107839092146, 29.33214868096571, 81.40863314916045, 10.018178516562019, 5.075784473410272, 35.28630815502967, 52.11114949961495, 31.193685289952914, 28.199869484222283, 47.76109776180827, 27.22749408868803, 39.39658391125501, 86.26387677568353, 33.06031960057883, 53.26105179294101, 47.28463488140099, 48.315937315351206, 68.608085962188, 37.939919491864764, 51.27960425769604, 45.13038071508314, 22.086385328363733, 52.18371930681975, 27.65061666445079, 63.38313649418507, 53.07857493917784, 38.77218833521568, 51.15253890522618, 4.225490054154869, 25.143966231083088, 88.27207814530927, 57.271962794969156, 53.21479591934208, 39.70925866494923, 38.495457386528045, 86.63811305827333, 57.880439954075264, 41.603676915153294, 40.43656417337775, 25.751491846549012, 44.496453825824105, 75.97364895037244, 40.99070286255085, 28.90677788677706, 40.46186462757459, 31.651591004447802, 56.886210963219916, 55.50945419948568, 63.34927658215432, 29.85783341328558, 42.92490851452383, 41.709243112308876, 73.8701225831491, 66.88640228604832, 67.23368639390546, 35.08553047827833, 96.3844153590982, 26.43775806920536, 32.54851964320772, 63.75202859382942, 42.29235600543911, 119.28609644932556, 133.78548912787124, 32.32247950264847, 28.615302434872635, 44.23288045077292, 54.11886400765253, 43.792869201425496, 56.28043057695303, 49.313273235888836, 63.019665841473746, 64.40896476360712, 57.87899585575206, 75.89793945578562, 91.95715071236823, 40.73654390298296, 39.76028736735457, 34.80151465789554, 22.979917953440626, 100.71257127403427, 75.67916914353657, 62.72483093623645, 82.56119406145194, 38.3077312798933, 85.93702362734973, 8.005798035633452, 45.9792664758794, 75.46453357819041, 134.1474929901825, 59.548120752577304, 36.82312394549021, 34.78682625054038, 43.555330755068304, 58.093111268725906, 37.79180423318603, 47.895447847632525, 39.63782187430856, 47.74396150327787, 74.93913217410554, 73.00049152086909, 64.55827791565034, 76.66652875984991, 48.764772435288606, 45.95297324384632, 40.45474854294258, 36.66907907231009, 87.96744487090241, 77.62849744303311, 42.129293747861574, 47.322529237456656, 100.6382082040701, 45.18432200333547, 131.52203925815346, 91.14239317281367, 113.98404863486014, 7.830934190417861, 52.21507412084996, 49.63374759691475, 35.74892414964621, 117.63557870774146, 41.674434429463176, 42.63651540709462, 53.95155144511507, 24.57419357438652, 46.80057296740977, 45.01398900611657, 69.124951581978, 46.23958486661393, 55.24537012500969, 45.38463149327326, 31.422468794501196, 86.80888335377249, 56.5341269038464, 45.323086497149184, 8.589243185513682, 43.039003266832346, 66.52097534394466, 38.039239123526066, 47.37124277555786, 107.25102957706497, 98.76389334812649, 8.990513849316011, 100.87116497356186, 68.77991416314029, 74.3259474977641, 76.02910359612862, 42.96928815289678, 49.34399407068357, 47.62571706364177, 178.23216100940763, 69.66428755498936, 36.873880406967125, 46.84052641325732, 71.98367199876982, 57.504667074673044, 98.8192456471682, 55.679885727248646, 52.059457286593734, 29.311241983469138, 49.578501876300614, 43.64529748128164, 40.47674212328997, 51.33803887938489, 56.35524334708828, 135.2617257258111, 83.95626860921246, 46.26951024414869, 101.2912991475527, 10.281150481672544, 106.63779836342741, 75.22931981005183, 101.80984343114311, 39.424944923816135, 155.19013344313322, 59.90064888668915, 4.916045169671053, 77.37686915921165, 72.20722969665493, 100.54755695065897, 44.37179653450758, 74.85506302451373, 41.429176023935575, 109.35282870619243, 42.099656725826485, 68.69922942572312, 62.785173117253876, 76.63403495852269, 62.630251214470704, 66.09624133248433, 115.89726479099892, 54.82105749838799, 65.84927139272008, 47.432789329710765, 71.62355600028053, 73.030589623896, 47.20378110522817, 47.91266761782051, 46.29906926025711, 76.29309340726999, 7.4962288191533535, 79.01283435446315, 73.05916257074901, 130.28305357380515, 47.413679261723686, 66.78281819206173, 51.56019723886244, 126.1396271699352, 38.97095105699142, 51.49281848220286, 85.94896067854887, 69.44673622393682, 64.72526211618491, 48.94221498786334, 38.89404434091635, 90.24456267566558, 48.354536303928704, 113.21764427820075, 79.70824678930269, 177.04276018751915, 100.17902464554356, 106.99914824204244, 51.83006400026452, 52.383837579739186, 48.258892688869366, 90.06403467484158, 43.891479398069556, 87.40962875777888, 78.39254871435959, 66.73654895816063, 128.84364337296057, 12.730795748138368, 81.85946051547447, 82.32378454004201, 52.05610793556789, 99.38874156930692, 50.119000223846264, 43.07167600870211, 144.23613256018106, 58.69233547301135, 80.08057630293312, 30.70018549543697, 42.329180318187504, 68.38014691837671, 63.14107212785424, 46.80695653125042, 103.54492218859362, 64.20505233905764, 49.50613579885323, 80.06890392300697, 54.7631148849819, 53.59467738729823, 47.875156811276135, 66.27625785313451, 62.292475661193784, 125.30301065729661, 38.858519336614194, 67.61223746925728, 56.26130906253813, 52.38141819735774, 94.7705991186334, 36.08248001548406, 125.69342050075366, 175.17608474861268, 4.654722592157494, 51.266511353404184, 51.54108233534085, 34.75601084118173, 108.03597395308543, 70.99565409493366, 47.53174839197151, 69.04890610324806, 44.383997334316284, 57.21284758461228, 134.3809550065529, 129.4177152754204, 81.71757105989026, 58.98177400868787, 63.96324897624391, 64.76050137960242, 91.64367231804331, 147.12968814349887, 81.78778088690699, 56.04545584182486, 30.714114313678877, 62.190357956268976, 103.17017981853002, 79.71290596163124, 85.70278186729382, 86.65743954860098, 117.3601122573583, 58.19931856094444, 141.2669472853507, 37.26084326079622, 85.16232368955738, 69.63301700954962, 54.662181900171845, 75.80142583009288, 65.63112462884094, 7.144050447990717, 57.11863772140898, 49.490074923443544, 49.64635353843581, 68.53084493814862, 56.60341973763959, 111.17167009328509, 49.38973127101571, 53.182101985621706, 53.67178010278906, 5.658205703144828, 46.50978525311678, 66.52469243184888, 73.48272522505046, 33.356534777290584, 76.44661694921598, 75.31198281533736, 81.57454357960681, 51.74725266445659, 66.59813188233707, 40.230795097635266, 66.63580854267896, 66.31983879554976, 75.5697688078968, 79.36791281169572, 51.057088121358426, 50.24490108811203, 53.72128345971203, 76.1797061418084, 135.86804971098124, 73.41836442192852, 92.89109490667147, 58.03464205691034, 122.15955971818025, 59.923433202980554, 84.57091945467995, 63.524573445428246, 135.71644192619468, 103.11374006209367, 66.56618331914683, 84.86311732373319, 61.294330552145766, 47.231441333584016, 48.2240255848356, 196.8892834759756, 123.9091162270173, 42.27248361713703, 37.23365172575312, 71.92539402979759, 81.39029352704345, 71.86928183072152, 80.03549671391691, 56.919428779772666, 70.35283328953604, 56.64463992552856, 83.46816140370319, 36.670685948523584, 53.065055504850136, 184.55824776669087, 74.24238238376103, 116.91508262131123, 41.343895719426534, 50.71352910215558, 79.6194911986287, 51.43330792586719, 60.65836392651609, 60.64252567533391, 151.35029333089236, 63.158518228491246, 55.84242745993467, 63.65711207281307, 123.25724981226891, 75.79849207693587, 133.44836863968015, 41.76806375676781, 71.62024007168004, 43.439670754585606, 50.26569222848351, 45.8446404461875, 68.77480954890383, 46.49001396806361, 121.69118483521942, 91.44760832555615, 62.43249875619645, 82.63406313868167, 58.60844429575661, 129.2257068509989, 54.295984395365636, 46.64984619965664, 154.08874791775904, 44.25116089574397, 94.30353205706268, 166.03877231878445, 123.87360306467508, 42.594319028683, 131.58844107879233, 45.7610036131184, 102.70229740627605, 50.516514710010256, 61.07985877895124, 5.20957126127509, 62.69821821325132, 104.38688421318622, 15.87189876323087, 130.18717356161477, 69.77473264198582, 74.25190998386392, 78.18559018747682, 46.42950000262713, 69.15979278318198, 196.91459484355286, 95.60399139265448, 84.3641081580071, 68.23887208214384, 77.24745304212162, 104.31331813167071, 49.075614927981476, 52.470996659487035, 91.18739599332109, 62.83210319091364, 136.97261011794726, 75.76983011337508, 99.58123106220921, 59.82824064055147, 55.24169333013009, 68.96176295542999, 54.5803692024647, 62.26305324607175, 69.18951098766155, 90.68759021288618, 55.845799365064074, 61.679793607331035, 44.19443158131637, 44.42441490157022, 58.602087472836764, 70.7346655327084, 83.31854017512022, 42.57797673139929, 9.00213998392358, 55.702575196355795, 54.37869428156453, 12.857377236801758, 16.572472236391807, 50.87023677784335, 58.08054757911747, 104.86058866359531, 6.653446013301789, 63.89219956479629, 38.032518112995575, 61.63268300005054, 49.17375578581074, 43.14284342305389, 53.28987791889029, 51.991143808139945, 52.609563652379094, 123.78529119204524, 82.96265687793503, 76.72347809387489, 84.51263810796716, 114.46721757938386, 40.386529586174476, 128.3701682141796, 43.015601845849154, 87.02051099785497, 48.52830517278191, 69.87625759399828, 126.74858324209357, 6.415863985282482, 157.28978793663083, 118.96936296398863, 64.1146667042797, 64.7133416569059, 175.33300463841647, 49.82031644829903, 44.56154248024009, 11.439085989865646, 110.69280731292896, 56.180821812489505, 56.24573299740506, 65.51708446583838, 43.136923765265585, 51.00577037066256, 101.9295036445867, 7.977455552728592, 44.42290923744476, 86.31194021105138, 87.54819685083842, 55.427015943078395, 52.01122248367663, 55.84122889646054, 18.28685375120388, 53.79192858662054, 89.87791063011449, 41.429067982618854, 42.45930396550392, 111.10472228581456, 33.77810606556752, 69.25767358062141, 93.53208508035155, 51.93925717142277, 37.07263829233114, 50.95768534572541, 38.865296815158985, 49.302305852915616, 60.67538103255352, 49.37000796487904, 39.73854863163332, 50.16055475772091, 82.72534521676934, 98.28647437140775, 129.56020209147158, 57.056242318808884, 39.79542032735574, 56.54184390277811, 185.23761525293983, 49.483974787138955, 52.37824012587021, 80.59856875588218, 51.5368557407551, 46.26775289872164, 107.09559817434148, 59.56439041392996, 58.429140995523376, 187.1720039726225, 59.120477471009046, 5.078917205726709, 78.05713793590819, 78.40046090121677, 51.55084106051872, 133.61412546924544, 101.79540260062612, 107.15204868650392, 65.21999917049314, 48.69329301509215, 5.632966301440356, 11.641862817048203, 56.36102713971964, 124.48927108824957, 93.7532251598533, 109.58685374699374, 72.61979663583496, 50.62606996297809, 119.52992072888453, 52.48805960709104, 57.46545753273607, 84.1469504823595, 72.98312252976835, 4.890478103814458, 67.40397665519473, 59.51976257382287, 63.08044253762633, 54.313198071721395, 101.25955016700158, 5.965881287774756, 45.85877128630186, 100.53055067301568, 46.96845876617058, 82.70741438230489, 64.99337243205541, 119.92543068286936, 98.91208840221609, 113.21995682459266, 53.157661548917424, 67.54455288390467, 54.57227626736839, 53.04111486827835, 110.88751199976471, 55.635451685709796, 52.36489169919186, 49.76867429715769, 89.10006010810807, 82.08594551728187, 69.7352142982024, 91.06333955707056, 5.839940857384058, 91.87272182367563, 139.5011286415495, 55.48560370128029, 67.48651389361203, 2.705542303797278, 67.21609513533124, 90.61372545563397, 33.90599394729186, 4.2295369733977575, 52.53154725356688, 76.16532804552747, 45.51954673063533, 54.182667936248144, 48.37004815776794, 40.95033454675876, 68.18787064278102, 78.11024177095621, 47.816883300459736, 42.57205987320551, 54.911652306744735, 72.53458730554914, 70.10888636820218, 137.9118486972404, 75.87654796472435, 66.3000437502214, 69.55035034936053, 51.83415099761065, 50.01415974427971, 41.27167900617125, 91.75485682828882, 146.92522381209807, 56.14616455804252, 109.83856902377497, 74.28655447865172, 58.85367927323416, 82.48311270749669, 98.78957401222777, 54.37371123288683, 99.88676652230387, 126.15411616095078, 67.62841466224927, 53.91832916641735, 110.78406129358564, 61.61656079304018, 159.7045424346127, 99.21648805617225, 153.86775002516848, 82.67527841868248, 10.070038785114853, 210.88013480138184, 47.96057263424902, 100.89376736595926, 65.70115612470535, 83.8376784387611, 52.12380945349207, 76.3052299859632, 94.74684106636187, 52.61949706643401, 57.4749763737119, 57.06519298562854, 64.21587771965916, 47.53613094685697, 114.78203395802049, 139.89238373569083, 6.387749028544444, 62.697420313314616, 86.46367067103985, 53.62341612322651, 5.744813039394612, 138.08586434259175, 44.65967398273037, 198.30067588459187, 77.47239991192527, 89.43110233872332, 183.0323547704517, 61.47312126870804, 66.15731908030615, 69.20681987028804, 67.83439841336916, 11.441765259026889, 257.0710251035338, 140.4681998717608, 184.82735043522828, 193.92662599658541, 50.507168837259606, 82.2911969331876, 61.810880699950296, 32.859870918153504, 62.92550918084075, 30.173653116736833, 193.46125498218845, 51.289660884545945, 138.20525090978165, 73.54062269013045, 79.02135167758915, 99.2702431662168, 62.44529344308098, 54.14797207979674, 106.3558354841856, 200.81072504742295, 57.53247618261659, 48.305518191477525, 83.57381535438236, 8.307698714382045, 96.86392809253223, 43.39066157865638, 84.53772814405322, 59.00849214031635, 114.25212687604305, 62.43665196027284, 60.193626827208135, 315.194482692556, 56.8889008869879, 53.03912823546632, 47.92272854763352, 75.0625729589379, 73.41602604613405, 58.66395378041421, 9.70165806329122, 47.86204874583888, 44.678860126895515, 56.861128994793496, 136.73925314095086, 50.95198968211774, 71.52939077206929, 80.19076570871215, 10.473139488728863, 62.57461175658899, 209.61671336422756, 56.128007492087875, 68.94778777717535, 45.244487657489785, 58.3865281627285, 11.063554421823518, 55.97094750712567, 88.80121830895733, 46.05810253429422, 71.94373206291604, 77.06172079096442, 111.76756720437297, 40.8705323813961, 85.59903273369748, 70.47523756531801, 93.42951332100694, 68.45810294952118, 62.26079007928801, 111.74782477837779, 121.67195417371869, 91.54490609778702, 53.995650449885254, 78.11383101379273, 18.322985331965917, 55.34848697735097, 135.73313773173263, 90.94284184457915, 79.51555780879941, 69.35059371719758, 56.71578522461798, 230.41562479489804, 70.13098782124017, 50.76511437908028, 54.580247933881544, 58.52603706634559, 69.48830604606744, 63.72563205452962, 224.71240785207922, 89.42926523831773, 61.70926409043107, 59.832611114254306, 109.0285264747337, 44.60070668209965, 173.3242720058865, 44.207949472704435, 148.26499429204165, 104.76635768079858, 49.69275479448566, 37.192581529240876, 58.241225910301594, 168.35229241149514, 89.51369791913739, 52.99482445599818, 39.25653562557272, 74.78318068583954, 126.99035802678159, 125.0040993011321, 106.41296389492047, 73.08332885431706, 83.82583420768331, 118.68679399573662, 102.24260544313982, 64.92237262095249, 76.58270824756205, 43.96420124491884, 49.03363863044414, 51.207717399803606, 75.7845601729576, 51.711708146120216, 58.21866992058754, 92.46992725839814, 49.14884603330188, 31.479398640218744, 70.65229179893407, 54.36970783426968, 66.75088090537228, 52.72130122240171, 9.33044871252088, 74.93244027103621, 270.38839443817386, 68.3603627950762, 54.84024422412204, 51.351181407896995, 44.9480469313116, 50.807935301624966, 74.30487441666128, 54.0507185077086, 125.59750253055358, 130.5168927787889, 6.4719543913366975, 153.85835989419016, 65.97440461521231, 76.6136548843595, 34.655117721643414, 75.24650738298376, 57.017000093055245, 43.912010792545345, 78.85391945349335, 85.41567795770555, 73.02853992626338, 51.44240787994376, 56.086707637047034, 52.60411834132156, 65.32743548876921, 52.95978204602365, 74.15269260323922, 56.784999184724754, 50.82582079616693, 9.976929015434216, 148.26260045003178, 75.6719957226835, 128.8869606657227, 189.89796929446447, 130.53046506557777, 97.22678954028643, 117.99666761268853, 54.35749879203515, 195.1486584158782, 93.61391006040292, 70.5108097488288, 62.40271921434969, 82.77870086593987, 75.0820881187755, 132.84628098018234, 78.09717467413923, 64.14716082491266, 7.334621495655779, 82.83329655980255, 82.72855447912123, 48.24906345268004, 68.8797314137592, 70.90228255264151, 37.29168408778181, 119.41351660165739, 73.57042205496113, 42.87452643081992, 109.29848440378015, 146.43262040230158, 66.42801492031317, 149.96264939291183, 127.67635768289954, 156.46023398201234, 82.37439300073841, 147.41394396539476, 7.556082057678923, 60.75070041794793, 58.65778381579829, 74.28588987960362, 98.01652456723232, 62.02877993756914, 9.049312835292529, 92.353892203127, 123.56981353263042, 111.08461314970651, 43.25993705745818, 86.55809137320492, 50.28677255938186, 61.38802265183824, 66.14453595445842, 73.73382940529692, 75.88060137539752, 45.95377759886986, 89.74437585701475, 90.75361513151243, 81.41018914690892, 80.61992214060727, 67.9256532444962, 179.38978739060542, 72.67425591376721, 253.53835135391046, 168.69575682517177, 57.698055451781116, 76.30170990194742, 48.70761272100958, 52.90720971977002, 147.22468490019128, 180.09196538971082, 45.479726790740905, 91.33410917965882, 10.89856785095373, 77.6197985611808, 75.79386018524886, 62.57591236534777, 49.13413287906949, 83.51012174354457, 142.82873346229283, 11.06544861706741, 82.17883313335342, 79.73562903909944, 55.17466993457949, 61.20351699063827, 71.31969626158332, 219.43462726836512, 73.6489128861659, 44.760104020463224, 142.20175643709695, 83.68956649724986, 10.636313738306182, 48.81073825637362, 106.89676907813681, 149.56294154918024, 75.1607592702086, 164.86272639779352, 57.67907057861497, 55.37832864033532, 64.23541915179169, 92.01164612191836, 216.39050537236244, 72.4861833770427, 155.6153745832823, 343.48808727338866, 9.932249627805184, 65.67628290073367, 65.54007169854566, 68.44349395741982, 121.53690993090514, 50.9848437341162, 36.58671113547033, 14.00693010489785, 59.162089083087885, 98.78912507721522, 21.86240869764949, 45.96783900566857, 68.91054331039037, 52.604764410903734, 101.19867618985637, 38.470876637181725, 156.78522528186068, 72.50532588616198, 131.86874872433745, 59.97348116876948, 42.09693180882272, 79.66943633563315, 54.44109845394525, 123.50395016427423, 57.02354650566139, 45.73117634453997, 58.14110205153443, 35.3253357880876, 70.4818264091983, 119.3720557258765, 114.34521724976724, 88.85153894785991, 76.13286106388557, 50.04730616458828, 51.43286747462839, 77.84794864953454, 36.76259150783592, 67.63671103903118, 7.184259503720576, 73.96722682870748, 50.77026956142646, 52.70284595483175, 65.81699331434284, 67.09872795171489, 113.26126830209483, 77.85007676980538, 67.80721807068088, 146.50615432573497, 62.499450870803756, 48.601210484620616, 132.26473277633187, 36.562698048149066, 50.28568591789971, 66.38689127021213, 72.94749021530848, 107.22338472972861, 47.82250235400054, 53.79454838321496, 56.034703368892124, 58.64278402115005, 132.45982551701826, 78.16426780397987, 58.49691173296472, 50.79351977192079, 44.852221623616465, 38.10558696495363, 86.81004399396723, 103.06930687312789, 100.51584584363444, 72.93965308699586, 47.029864343500805, 87.22046675660918, 107.41070015584057, 61.1724899491088, 44.05756009486308, 60.80226325427663, 175.08762929704736, 44.57292138988164, 55.629390149088394, 75.1580973941446, 62.23613063927368, 142.14221442092088, 148.10164991002554, 59.387927493047535, 87.03168257718167, 50.10514859301469, 62.16022139588792, 50.52585118047119, 138.10796215481517, 53.124309095806716, 134.9563345377955, 42.29936324035564, 104.42273909814429, 90.42017324967128, 6.900363215614115, 47.09494003565658, 64.15254614602202, 171.84843343189075, 159.6822702999537, 49.1312696061238, 16.591167268810903, 98.87501258113754, 39.467522318196096, 41.65233258742249, 81.78669563868131, 37.00536866029402, 64.53439051464227, 7.750633991082928, 68.04252415791909, 54.242810948477604, 66.57103811661898, 49.36032395201977, 83.1828281119561, 76.14591267887246, 69.18629363556228, 135.66526400182536, 66.18354278936717, 69.1406528339002, 103.63313392942139, 99.1711940776353, 72.32670917379575, 77.83728770546399, 188.0496465184731, 111.97369025091638, 53.43944981320434, 122.14124135332985, 86.57218829575098, 100.35229334087316, 61.511756104990965, 73.05112226034096, 56.28374484867633, 8.051149966677372, 55.27407329776266, 60.12057297051318, 68.30936882806931, 54.59720503624102, 115.38055538958886, 50.021779584186696, 59.50450327950656, 56.219395592685245, 134.730090326683, 34.97441579085067, 154.98621783600112, 5.636652231613689, 138.108311152336, 208.2981176451514, 84.47163940033865, 87.49514617221682, 80.40939205971746, 40.74997068649132, 60.218742352398905, 96.07683034252717, 72.26357078804256, 53.3036378355605, 84.147195023083, 60.79835472592156, 121.37421766952855, 45.45911931666443, 22.408673808682146, 52.37694888476434, 90.36840007400271, 41.29515883660846, 65.5765477308096, 54.0849564723696, 88.96743959604318, 11.450517123978154, 49.811453091921166, 65.93488412756709, 63.0847454797584, 69.36710953403674, 60.43996791656512, 79.2374234589947, 6.481169062563408, 65.19601153762291, 11.823696909393904, 212.51960867959392, 67.4965791930168, 164.05352338406868, 218.72206859810086, 111.44066997332433, 40.71681805701172, 88.3565087947895, 51.06546327378949, 166.3591702598455, 69.20282604457027, 62.94506428493201, 56.203173164418814, 89.05606925457282, 87.07276511140775, 61.166382001521534, 12.429226461154844, 161.39361311139427, 21.416051529329934, 56.89011625192939, 131.00389797819184, 58.3233994590952, 54.91110206561417, 88.00040416028385, 62.13351488195473, 58.71174154898011, 56.85259547661975, 55.07113290224644, 63.62882477089773, 62.53846241387123, 79.46150253153567, 7.763815670453603, 116.97862593777316, 61.244447857079926, 63.274720114128456, 39.29763074181344, 128.99002242194902, 195.62767771225523, 58.94878789295443, 63.72380694456323, 114.56915758603924, 68.08376629398246, 76.25524463880488, 61.10118422248652, 66.65058548002072, 60.549796527665514, 55.79436749240096, 80.32083863381003, 65.94484864321467, 52.60639846614065, 52.89915217571819, 92.21932732659177, 75.29981344907385, 190.47660412692343, 48.166185549038225, 76.9444132104601, 54.04570775646508, 5.737570900595488, 134.81444882440536, 59.58540059580896, 68.14756709202825, 124.19182024828432, 81.37826424956249, 8.256012463175349, 58.08094560001048, 64.63996368305621, 58.84355440494801, 50.844530456804016, 52.34650097949688, 59.20355958942793, 86.39291898425112, 76.62606797095088, 105.51999457439513, 70.00941820230514, 100.84264171512767, 11.040995454211604, 49.963020269836115, 101.68601085731726, 65.52975381659303, 66.97727051539833, 10.205238339086796, 50.357483037619716, 88.85511431883968, 52.747097148046585, 41.60296543206061, 35.53340081874673, 61.05011263458907, 70.06742389619613, 91.69200461795954, 107.85730740290667, 64.25312698501475, 108.80596697499112, 53.02780297466415, 102.09296020549924, 82.66230457411578, 47.9134820582951, 61.6732002694969, 83.19704135572493, 83.77110963341791, 80.79070114656515, 101.13912829655187, 54.295310915537684, 98.3427939332909, 149.47069997359975, 50.08452200921701, 65.0371376390537, 90.7210374436372, 7.459421247293797, 54.19042939408892, 171.84449858435593, 75.2785006201548, 173.53194948251664, 176.85432535493365, 54.977960465339876, 115.41548917694554, 91.50518262854509, 89.7763482008918, 192.102510787005, 102.38798657662313, 101.42718010172933, 89.01500193692647, 102.77822301633499, 70.65487954977142, 37.65359151982898, 11.196073636462927, 70.59146775414835, 101.65680181043922, 329.025192777616, 93.13377825967335, 174.68124183416026, 94.9049289914608, 57.26151925422006, 102.90562665449248, 142.96464261662683, 114.74969700199462, 68.77111507922017, 81.72796819172193, 62.08343414740279, 68.29481508643981, 92.35420858316621, 70.85665070206922, 127.69675496615407, 58.63034653200661, 48.57344794361623, 80.7969702181098, 163.19885638049365, 125.33630537726171, 60.43266991049768, 59.585377395325665, 84.8377349638571, 88.01555866935334, 78.18203573937836, 80.70768698672451, 79.10565194440744, 46.35672060627964, 52.026464055495424, 75.9098635676157, 84.83415408426079, 45.732292295371714, 61.352509284925134, 5.59350804525226, 205.83886301399363, 92.18840424122334, 11.91324398969094, 372.581577869248, 52.14416705613956, 41.86140420928308, 71.42515284572656, 59.355739575695324, 128.64482725109096, 111.32909898845953, 141.36514114965937, 38.36951887181919, 35.295098283947745, 347.86552348103356, 129.3396617940662, 106.75602453478147, 170.16150393813754, 151.30194728130772, 20.33770244540384, 78.15647857426902, 59.42092027876061, 68.9614417837204, 6.819973217979373, 60.18874426482017, 41.67626382147197, 74.10417096754648, 47.74226324430292, 96.8038975011053, 83.41767968173254, 36.8744434511129, 57.37013793156611, 124.63727523484523, 201.660227286687, 59.03847447929734, 41.701710835478075, 105.7286337650499, 8.028119236485498, 48.45500202605524, 46.242</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>118.7441567134857</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>95.42599578171513</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>[87.55733489990234, 117.5550308227539, 136.6644287109375, 74.28791809082031, 318.12469482421875, 46.196685791015625, 131.4047393798828, 55.85951232910156, 20.313547134399414, 137.64471435546875, 66.30593872070312, 224.3693389892578, 127.88220977783203, 335.1879577636719, 84.29026794433594, 93.61988830566406, 48.28975296020508, 49.38071823120117, 172.2406005859375, 107.2049331665039, 164.33445739746094, 96.82820129394531, 103.06687927246094, 47.50446701049805, 61.86640930175781, 72.92346954345703, 45.947120666503906, 189.37484741210938, 80.42926788330078, 48.469947814941406, 58.88112258911133, 10.763513565063477, 85.81538391113281, 168.4691925048828, 41.5605583190918, 58.513824462890625, 74.5248794555664, 46.21141052246094, 477.1987609863281, 60.74861526489258, 97.2738037109375, 67.18521118164062, 39.81300735473633, 109.00031280517578, 72.94335174560547, 59.80903244018555, 153.4866485595703, 76.41046142578125, 66.68016052246094, 119.09868621826172, 70.84064483642578, 38.38438034057617, 85.84701538085938, 161.4570770263672, 65.34859466552734, 37.39012908935547, 50.00249099731445, 12.64061450958252, 93.44999694824219, 130.5547332763672, 145.69967651367188, 109.36820983886719, 88.5381088256836, 87.10613250732422, 115.82258605957031, 78.82489013671875, 149.53147888183594, 89.40764617919922, 323.8999938964844, 102.91506958007812, 50.36025619506836, 195.76361083984375, 81.66316986083984, 64.90062713623047, 143.50656127929688, 332.9368896484375, 180.3920440673828, 25.930421829223633, 71.02539825439453, 183.92498779296875, 171.95013427734375, 192.60806274414062, 52.57180404663086, 392.47576904296875, 209.46255493164062, 231.82615661621094, 53.44449996948242, 47.543006896972656, 490.4530944824219, 187.98880004882812, 46.161556243896484, 172.3901824951172, 126.80047607421875, 75.89229583740234, 422.9801025390625, 48.77598571777344, 148.1776885986328, 36.04082489013672, 98.04698944091797, 11.879032135009766]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p012230</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 02:17:16</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>88.1879103685301</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>67.48278192466034</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>106.8470915312233</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>4676</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>[0.5824826319661797, 1.2910540853144228, 0.8301655179295909, 1.189459349504575, 0.8895716280574484, 0.7094651094367855, 0.7446886998746453, 1.2736893909193707, 0.9058775486936134, 0.3536588164342943, 1.0064343238636682, 0.6846397815270813, 0.7300266807434092, 1.0960912633584268, 0.9117971661673797, 2.000687475960221, 0.5405550646916034, 1.7331035675248598, 1.2724995462471689, 1.5578733147299895, 1.4575360914504372, 1.155396682899442, 0.6614011646166759, 0.7187374133501699, 0.7214378654040017, 1.1257773575489234, 1.482323508454813, 0.5997382475665433, 1.9226830211820156, 0.8495269196556736, 0.42412772445661273, 0.8883577479383762, 0.6122641451329683, 1.3299270189616292, 0.36943455439110356, 1.5952291047220755, 1.8760494557470788, 0.5809172684342598, 0.7377505335092461, 1.1329128509669877, 0.7285268596562039, 0.16279739682568467, 2.9110850923230305, 2.9161654949228475, 0.6434331910952754, 1.229076698674415, 2.1581458910548976, 2.338776911787121, 1.5799545715070182, 1.2891473128038748, 1.8728200256625955, 0.8140801484577793, 1.394135614818678, 1.0160985392122865, 2.0831538201967716, 1.1495132282056382, 1.5238351515570663, 1.2132970952024527, 1.8529208180997079, 2.307456348909943, 2.741248610134696, 1.548101007132462, 2.011634672662176, 3.285686121125058, 1.8546686053941701, 0.8343215439163223, 1.5046746951862473, 3.022991166851607, 0.40500738379366885, 1.914751864717911, 1.4486384523058125, 1.4941425592035376, 2.058385021909718, 2.405270482696386, 2.0568635768580767, 2.415923664241827, 2.0735172027993483, 1.8572113234494336, 2.2995196416782817, 2.274605539117845, 2.4018918469471946, 3.164010767598873, 3.7871818748525543, 4.415154002644354, 4.7340819765755775, 2.5887870457914377, 1.1152420177761575, 1.9881445029823557, 1.0710809703685222, 1.9305217187715673, 1.9530651032693105, 1.884114443020425, 3.181819186429101, 2.5160878292222386, 0.5804746527804207, 2.615405395325642, 3.609432831404961, 1.7707003458592945, 2.982301993773329, 2.0092512289701876, 4.724488628096371, 2.6358561385174495, 4.758955153825544, 1.415442458962015, 0.5037405956603166, 2.613958495684467, 1.5363903927236233, 2.3505293604485744, 7.827397435451953, 4.535324604329593, 1.7854448197135104, 1.6932299557405497, 2.372982389818354, 4.697859892965941, 3.263354839028484, 2.628154193851763, 1.7801904505661943, 2.468358576888684, 1.7065218899342258, 2.3444497580070864, 2.721403258029842, 0.8396570122762427, 2.586801799561848, 7.155208702473038, 6.591040284766445, 4.146847514422165, 0.6858789928347345, 4.807194775840319, 6.700653680477512, 5.026495245943754, 4.878908546765075, 3.995435910120876, 2.256770643772934, 3.5937644240842843, 2.1914701957317506, 5.102102097616185, 9.97446924701455, 2.761180302791972, 4.003520894609571, 6.068900890527246, 1.6087456247599874, 5.956131647198993, 4.619028766292212, 5.558939403769581, 6.879284088882667, 0.7060787651507511, 3.8881534491362015, 3.181344656148866, 5.02492991518878, 3.575192673985112, 3.9315725561627293, 4.727963417203029, 3.0902434328080757, 1.3557082346349802, 7.9621373560001825, 1.8320435973500035, 3.6263028379940754, 5.951800122906733, 2.975960750678282, 4.5753470312952045, 7.330865444432701, 5.572793849642375, 5.0578766575002625, 15.572094067982478, 7.073145810550663, 20.909916901754734, 0.6585188579654848, 5.361664378613171, 4.66009035643603, 4.827498782491639, 5.0701849451375995, 7.172534743282213, 14.560705029449359, 3.1995900555486068, 2.9198441028179634, 7.043649477387056, 4.94373304755255, 3.7292143119017176, 7.499868466010656, 4.81644849897614, 13.992974788472385, 4.120399846576846, 6.20252294978983, 4.557267041436703, 4.3432389058549346, 6.88017538785635, 5.172484051330651, 8.207187829409731, 1.548800700674436, 9.33196519622004, 6.608225971753225, 15.831424235364276, 7.969303426556877, 13.35730101277642, 5.479313582327069, 6.596438100903866, 1.3412472792779444, 1.2102537460649148, 11.028211538621058, 15.078535963839334, 4.822083531989382, 7.855074605922732, 8.902922478272027, 10.736424684333738, 14.06613882193489, 17.757156078518843, 22.614883217094437, 7.495889876761758, 11.462455293074715, 1.2593756801186442, 30.475158746767722, 9.021595717890028, 15.358131060042478, 9.691047190655102, 9.084397300834919, 17.689630407236965, 5.533843283802376, 21.44316559549079, 20.081873380657264, 12.82797725069675, 29.399167650536217, 7.538200701466083, 7.42478140531598, 22.057071531695033, 19.84768363098154, 7.462703413862121, 10.501660961650506, 16.61662229426829, 12.29892878809549, 15.58061825353873, 4.283470425581363, 25.55661741293098, 1.1293421806038584, 2.724782243916051, 21.093887262391267, 26.913362039905447, 14.076281362491732, 10.276484426761511, 30.139330193630773, 9.644485208009234, 20.346891965134898, 45.81565065244354, 26.371418709532986, 16.074466250552106, 23.206993730447433, 20.128810202868628, 24.052313747261618, 13.542206448766922, 15.519879090930786, 21.193650856116268, 7.515923819974369, 3.764332087132725, 12.19868508574789, 1.2594883722724073, 1.508606179043201, 28.56790361486791, 18.28758734335722, 2.287407592871136, 13.9617429874412, 11.005861655805392, 18.812222544690403, 16.160893994384, 16.040765745815225, 36.43970756455572, 21.596051180869765, 14.03184850699466, 23.35249127530982, 30.43926633684523, 22.642799903671527, 9.214466741117201, 21.952344317941257, 11.907809473604148, 14.2760021079633, 27.07942447370488, 26.282705605251635, 17.562869464623315, 36.93289278393081, 22.997541407947697, 25.336828068884476, 7.42674896414438, 24.792369402711262, 34.671317432639, 1.109645431286436, 32.230321108916065, 53.88326292135332, 28.7982695607894, 30.20163767561053, 16.758043943456236, 27.41147672354231, 31.773010850520002, 20.405005699442704, 24.069332514107987, 33.549111173403034, 16.46988558060161, 24.601788650882234, 4.265730098672934, 31.46846866423654, 14.948065399826726, 33.824024431831795, 21.602291145862196, 27.049563929680197, 26.459833752681266, 2.5096006533365065, 16.063088252651724, 17.01123965065476, 19.858385987360187, 18.41747927868687, 28.352514306377515, 3.6905972124065527, 42.84083728925469, 23.361974314354278, 24.424707437382416, 29.695593804317095, 26.965582536632386, 26.64109862036627, 35.16075599591532, 4.707059260027138, 22.349853179377675, 30.808645545765568, 25.215595245212718, 16.438842625709462, 51.0774399500983, 50.42222538911392, 46.648022858886755, 55.16437578569614, 35.54998304437249, 23.016795390096583, 32.308310337295495, 43.4682923934942, 6.5928975834545955, 49.19203554777901, 55.64635365317722, 37.802722798179175, 54.163393610607706, 42.6715870135509, 60.754814946316, 50.546056602572776, 38.881660239902736, 54.54776124607992, 6.27289662422449, 70.59435542487371, 34.89979964089025, 49.65482202188586, 35.38309123213222, 26.32744199823655, 24.33908825802471, 44.86466507592082, 13.025873912258085, 30.00232928061986, 24.652704751585613, 24.791527859835465, 32.10560508521575, 33.18849516581311, 24.58660276432281, 23.624705513731723, 47.935191220443734, 46.42063243999128, 5.883392660222782, 57.29084016879429, 44.157184892252786, 54.558346632312066, 55.60414908278471, 45.77129118374277, 60.67259799719287, 57.63277140800569, 64.87888676939029, 36.89391311587988, 27.21183554552271, 42.73323207466098, 45.405969546093225, 5.870401242368923, 74.28964662220234, 20.126060995999456, 42.50311280723144, 63.04101440565299, 33.419981855219376, 19.35716794410505, 40.117385333714736, 61.45397859281621, 68.13297849446016, 55.80242321503032, 45.56370081866791, 61.368047341935615, 49.85001354333235, 29.738509554686, 31.20318504974241, 9.266388657678178, 40.06369072825259, 34.46811277243917, 35.85154931116937, 51.150795855170166, 57.750181625305956, 71.99228661479931, 75.49945736795048, 58.441978186568456, 24.79039799445086, 58.711562259553226, 64.37309739078651, 47.77563311494608, 46.37565661238043, 37.51770124235573, 31.456324138399136, 65.3857978238525, 57.4394460068874, 55.57040772909129, 56.351790839175315, 23.63222134366182, 61.78439734835963, 27.649646731146387, 40.027149910752804, 69.60840457679114, 52.91986553490866, 35.82103163836368, 56.808680415950725, 50.70731628593934, 41.14680104566381, 52.759280342961, 30.05127260633267, 73.18581609288164, 38.41575677690101, 32.509871868306526, 65.33333420336675, 58.31403707291641, 36.09454569256737, 31.4047677466854, 62.94106153382407, 43.31960246347429, 66.89137234065463, 53.812457627398885, 77.59150389658161, 48.45763236298109, 42.88577472494953, 5.263980609276458, 49.70109905503813, 61.427320044215655, 40.90516317671997, 27.279761055789525, 54.95057597637694, 80.8612416356713, 75.38066377970472, 38.42402110785341, 42.45052140386403, 46.99262834522616, 35.304186683142014, 30.390058301678838, 45.58584057318074, 25.793510128244684, 65.44542274486786, 4.421001938385279, 61.76339204480514, 64.77082069298602, 26.752949635781356, 48.84802708502539, 33.50856369123602, 67.48105661045625, 86.4068268520087, 78.2285714290054, 79.29355835403636, 46.50685716160366, 38.69331434255898, 45.15854662604655, 79.91466911549054, 27.92626137244004, 40.97883776192399, 42.93202747048099, 53.92081748924108, 88.58455451247505, 37.528653615481865, 7.151790700326039, 45.58617904250919, 79.56413711577501, 32.28645017342674, 45.55171478884408, 32.61756310221225, 5.007421929271219, 32.28250677826962, 36.35948895905126, 46.46141671820483, 31.18794089546258, 89.16089325494505, 43.05742154754347, 13.838345037348336, 42.84801482452208, 29.61869492000756, 36.53049768738326, 134.15695884903215, 64.60520774634692, 38.83918468240557, 85.6724268478794, 36.054829734531054, 83.94283792153372, 12.938560631506236, 49.41179332347258, 46.50335516509137, 7.142905800289201, 31.54075859884188, 10.970557172952425, 37.19324385148381, 76.01544786649985, 54.164237188482815, 31.62437633102112, 46.25650166087494, 88.57496105532682, 24.38745681847015, 25.26339075834703, 72.27623947753989, 72.81950065598174, 44.84302465271676, 70.57333531345819, 118.15583937801372, 57.85420150117553, 27.16950712215404, 116.13241739905891, 55.22437379908085, 74.84863381957533, 43.728166056822964, 37.234496585866076, 42.10949656815309, 61.54882553041177, 41.31600102046468, 7.383972225953853, 51.45371592393454, 58.28577843255303, 42.77117738293887, 34.00497390995276, 66.17243932825507, 96.54308940373966, 93.97763808167811, 52.7209393144409, 10.358763179048015, 81.63209665239025, 81.94106667483834, 52.6183223255531, 3.3663347476392387, 101.78827372920124, 41.92411787500802, 42.0047990779434, 107.88845234469375, 86.70161087099494, 36.468789141489, 88.4913711280805, 31.657053567680766, 85.63663282034676, 37.715475969868635, 31.78324034988832, 58.92128434969577, 105.69206914805787, 44.06148379420617, 49.01302078059175, 140.23178945145935, 44.7335955905262, 74.22516044871091, 79.31351100591937, 111.90741019873111, 35.451796425765885, 33.41400424960164, 4.518257503224295, 43.34315044262096, 64.13827334094898, 38.64638795429612, 29.32979371557493, 47.04006807733614, 101.24407187401589, 69.45059895773588, 48.992422042124424, 100.51646104438787, 71.39235660869628, 42.349726827222824, 105.71854522313288, 65.58682295939872, 36.005797307461044, 49.19686642627073, 58.643460857582745, 34.20389025331123, 48.33084640746038, 64.92090371397326, 38.917489384781824, 44.38066428304198, 51.315057094319776, 109.42841170562232, 65.71464575878004, 91.5929210513802, 66.54015708647191, 49.89951615359862, 43.21889152958292, 78.6248717818038, 100.33692965872838, 35.03971887318985, 48.93802881990368, 58.79742115832233, 50.23139925206481, 84.95262157277709, 97.9514519421595, 97.98720797541755, 46.893896354272755, 32.19132967467622, 103.5783137162313, 57.11272528416215, 63.83308016928682, 37.79901378677731, 33.350359822651996, 55.20947987579267, 108.05534127655245, 56.68816696175466, 71.51284152715294, 128.07392155987276, 62.693308488760465, 54.067095293854244, 66.71525742529465, 6.195946639626642, 50.463799331940685, 177.83647719647837, 72.18390379131807, 87.16199947477043, 54.530784922216945, 32.50120030333937, 47.73720003695807, 32.24382622266276, 77.34141247427577, 48.186945797576215, 40.477862511282595, 119.89716873299393, 45.16255192575774, 70.1545457815193, 53.75135171570458, 62.60490430039034, 43.69649284123631, 92.78336114776326, 66.58434001353353, 39.84737499856939, 52.888185956095896, 67.56805726269793, 86.37541662292544, 138.13681830132901, 68.79397280129078, 39.06237422972056, 136.57962573242523, 54.47754239725985, 124.7775753666008, 46.828333071200376, 57.886761149989, 41.811230464735694, 70.98234287462802, 64.81921985462334, 84.80759131815427, 51.31144704229648, 26.998335726907932, 40.55319721294639, 96.59081954591299, 47.05865407591495, 59.2275559305289, 57.42799942611378, 37.987525932871414, 77.46616994611746, 31.453859894421043, 58.55489430224417, 107.7185468289353, 164.0130329639352, 41.48947817601385, 91.72158248126016, 31.863188925876337, 34.09559957556827, 42.10456077021931, 31.446024413762245, 49.741477107078566, 44.00044945245323, 67.55932958903541, 8.0695152112119, 78.41820843186525, 29.50520608758153, 73.64817558905844, 60.0492567976214, 117.3475061769847, 59.43285366755822, 47.11065090178327, 111.58572027418812, 94.52202291652863, 47.01103357435303, 91.51218997506442, 44.97346257664202, 60.631577683762906, 30.74169415648564, 109.92958835207486, 75.0663096090438, 51.91293760543944, 60.65806867821313, 51.9943925141823, 65.67383909483672, 38.367293765336626, 56.54258784592155, 96.038388384982, 52.42913817395011, 51.13696445358965, 49.96483548539166, 62.24266860776321, 31.322035754037742, 169.08360154688555, 36.95225707078529, 101.2546383739607, 31.25697822448805, 75.42111957888227, 91.50401217102267, 84.83213059814457, 74.42158557314366, 7.893294071066721, 37.032261556196445, 49.78463266487419, 82.33845796573921, 6.013261182026162, 58.643101708573695, 63.19833714284555, 70.78517989568863, 127.02718390069346, 64.34777196224677, 36.921144448179426, 86.03575093569074, 144.01335072263362, 37.33949998328083, 80.65429333261477, 49.05527016564691, 55.10704827893552, 40.22935538248922, 56.834550617280165, 51.22119703130277, 75.40102464425568, 102.6173646809615, 82.79069724929926, 102.95985790962897, 98.7155081558617, 7.72164655443705, 53.704555167589106, 87.90996638955754, 76.80600219985098, 60.896177841137686, 92.87693753426659, 39.29438231147031, 56.57751743827613, 46.99086629861753, 85.06629434380856, 4.9401233565082, 87.9606528809043, 94.63486957143306, 52.76699619678224, 123.0498430586906, 70.07220631953057, 49.09471547061391, 195.27091942297523, 135.2532570968082, 72.41750486625276, 44.85044282760303, 4.284341105252253, 61.414075671047115, 40.82478849011344, 37.12805202427787, 74.12709663545851, 40.094761022669196, 54.45270708469509, 14.860876848548848, 54.31242495515012, 76.8546596866378, 143.77751124564384, 6.857657647661911, 44.28034666177818, 95.78394026442962, 71.60435517002391, 85.38375707064633, 106.10415952937971, 63.632631802818906, 68.11750797005905, 80.0829891446721, 74.68290939791709, 95.57771691766392, 148.74962735940898, 45.78161049300391, 156.28285410705246, 49.94138673881793, 35.01287484598259, 109.54863633738813, 119.53295820721576, 59.6913271008563, 70.44131833507753, 55.05068839716072, 49.71702614162565, 44.02860533030642, 45.35762089665607, 43.30091037321409, 106.0237315213302, 76.3010735800696, 40.03568571489585, 5.2935676188492495, 98.97265052973162, 103.62203229443782, 47.25652498200022, 67.23504295358113, 39.812973320039184, 53.205623995438536, 6.676696135307315, 41.83621947312469, 126.71586609464883, 81.76832173883373, 94.39915427669895, 57.804058253872775, 10.443018546442902, 89.05184294122266, 8.563624004028915, 84.83086214077134, 66.01112826534363, 43.63284445749344, 46.84646706274135, 59.18279628886642, 52.991379959032734, 89.14318056033954, 95.0220340268123, 275.702017567068, 54.357538119028604, 67.6390345916879, 72.46948592987889, 78.26568069987563, 89.61347743310395, 64.81976258893725, 130.51256206328335, 91.24092274844675, 41.79745933100642, 51.67798061326211, 53.1411897303696, 43.80332802556601, 69.99215120865932, 50.10918233050237, 55.53623657967062, 64.6022466278823, 69.82784842880658, 95.26069757303378, 102.71315370103275, 48.59313368155335, 115.0559065527984, 56.97060839164524, 8.77210714841341, 43.84031262397868, 78.8175968667597, 47.60802403207477, 60.59861393109469, 7.389367073598143, 90.62478722081389, 53.095651024554854, 139.7208052474409, 59.94011409733858, 43.09145554182725, 70.5901414484585, 63.09415596092275, 11.694264417032056, 9.502672219323554, 58.93218815419294, 57.982285301789034, 66.87568139070893, 49.549598367394054, 6.875941919608468, 52.81409999214641, 44.149378426335, 48.76759808064176, 56.0732222711262, 47.57016236052803, 66.50227956261963, 83.89628994548526, 39.063170226892126, 85.09077028427826, 47.413406965789484, 100.29929073560402, 43.24741263499643, 85.84077093500906, 121.54352513253755, 89.49749380965034, 75.03416945024317, 104.46575009664647, 47.15044864897726, 52.58541058692822, 125.79551947290996, 68.598054857134, 9.566002400342764, 54.581772268901815, 73.07152973474115, 456.93278264889767, 78.2720510762867, 57.803045718270916, 76.4991523949948, 53.58878159504964, 73.84993216771441, 55.155311137801675, 176.32123893110264, 41.59999880084596, 131.5390766421495, 72.4603248989312, 113.05731952388223, 94.59112853123345, 56.5333743407638, 82.31991168317988, 61.636843122031976, 49.974086751679515, 60.98619718475306, 72.47668221865351, 94.42843079173755, 60.291579047728106, 105.69538421847126, 50.49876288933947, 6.623436738869639, 93.7329169658926, 59.88043327322949, 46.03086527006566, 62.01510200353253, 76.33676258410546, 61.80284097336506, 57.88241466484029, 60.709072391898566, 69.83624069958036, 47.46781104200137, 45.45451443344245, 83.32626919592488, 69.27774012918943, 86.75401363166812, 59.97354311845461, 39.94256325256452, 61.01939450089304, 72.02666851510094, 11.635598456676671, 5.7163630456495715, 61.66133575142493, 85.23474036052524, 97.33817705196911, 72.56506370256265, 54.46461100912802, 99.37732185571235, 18.675188524904105, 55.32753868988982, 76.39744718614045, 74.6536658517218, 36.67855483637264, 191.58562245528753, 86.8654381451804, 10.633749915889648, 144.82687330752356, 107.43537166847938, 64.04103798421428, 54.86686533957872, 57.060482071384726, 77.50235962883178, 95.05429836097524, 64.7435420406729, 57.796175932573824, 57.71629138443611, 96.16863370372656, 72.01183582176292, 86.80350497746738, 83.52956752980072, 76.36007660483239, 123.3587868056754, 98.89349077384531, 59.99264487801927, 60.57312139757624, 47.158937875822005, 48.46103725795729, 70.78992210457801, 152.32433211651826, 131.50085628324473, 67.14673240272124, 77.70121056313484, 61.79407085898275, 49.466211185589884, 79.29524284847021, 54.672842076576, 15.66647403764418, 92.54194914249241, 73.00982820615647, 55.18513360563596, 39.43016342679134, 43.74481761370836, 68.41032302201857, 45.28730600342958, 54.74047841918494, 4.480215496541369, 55.24913290919335, 82.13903111932163, 41.059574513259435, 83.06268059613903, 89.02125316347747, 73.13253853268955, 111.09719902455974, 82.74669149631976, 48.39363596000991, 61.402033505222164, 122.27200190000117, 7.042094667727615, 5.856460661574725, 6.605087916891187, 69.05289672384663, 75.24418334845292, 42.57779236507555, 71.73246501783127, 112.45881359409516, 83.18053792399489, 238.90689543315028, 90.68054987579835, 99.16530801321974, 74.31495480034204, 64.01902988947057, 73.76062988333045, 76.36924742806907, 79.93493689981291, 98.95103492853622, 68.28109980594932, 30.311052313827254, 68.03911818907153, 61.43224523988708, 68.70697652782053, 61.19393084653986, 58.798180708215476, 106.80593054022243, 75.09164201736222, 46.62434681775883, 72.38668218278477, 150.07354170232608, 79.4260047551561, 70.47819286341526, 47.888032105601766, 114.91084023905294, 115.39679490262833, 55.70751697037455, 51.09341920244549, 76.80611221057309, 51.997778868842175, 52.33260182712566, 92.49516406225165, 43.246390284687216, 50.950288064484006, 57.25408924679131, 62.90264668379494, 83.82810492079027, 55.17086194060186, 85.95349302416165, 60.649443134244464, 117.96552257741922, 74.94805329495702, 35.27673229428562, 78.09929428151183, 51.136375790197526, 197.28159048092596, 13.527763001366864, 52.21280353173199, 56.53317158526588, 201.49113499583305, 103.12367747674946, 5.890189702529866, 40.59223388040359, 72.09945344306561, 161.19442945901088, 132.5512057158993, 364.01164321313496, 74.47218704075206, 61.19376722403328, 71.96806548498063, 56.36613418586649, 70.67931123736878, 81.07181751284384, 219.01667271434184, 79.17656540575945, 72.93882244126965, 38.793231852200066, 56.80297247031662, 42.16838970564968, 87.09685438419399, 8.139770074789048, 52.724614888890734, 55.6192057264468, 119.17914212280786, 78.71950092416579, 137.60498887708547, 56.781361559623264, 50.00616853858754, 101.52364253673903, 114.33049171276724, 54.00282364754426, 78.39698901132199, 186.78685015731762, 81.30181996420752, 7.6185117156996, 250.6500193002404, 57.92145994695158, 59.612603742283454, 60.653737431421646, 41.54218551302553, 49.62117737091852, 110.32085594700206, 255.111469389898, 61.456788183385925, 77.24699539259605, 84.83893406824863, 47.61272276737679, 45.0025278113394, 63.220724729807785, 60.85814737454933, 69.15550261355418, 52.55228757992985, 69.55870645559703, 95.43727464286208, 72.21652142834554, 60.53391863999984, 73.33965894851202, 99.64516508218578, 50.66418182621878, 66.11006220281017, 78.20619800841067, 39.9442536676477, 69.10187987000783, 49.174694781724796, 160.8528749266629, 44.245450521615375, 90.04666794625334, 64.60708905141406, 118.61251302651205, 53.28500111183314, 47.98755593332571, 217.51321945399405, 101.67665861819167, 37.194207238153666, 48.3179207904936, 50.39534242300877, 74.78089063301628, 65.57607146486532, 62.62426408173435, 86.58760363043058, 196.55021383099086, 110.4739730026263, 84.42401145936613, 97.28514518095817, 86.44996888504987, 72.83172729540036, 96.24043301122497, 95.09320895749026, 9.611212491915731, 223.1605737518254, 48.13335384878621, 50.53235421706708, 43.55943482408164, 105.91162278057607, 42.003354205351386, 63.870662828399134, 62.11079628888046, 68.47263011312899, 65.6788356745208, 10.571420333295725, 65.42142288068598, 93.30703521122642, 8.188720721865076, 60.89336974498923, 113.22302560445733, 59.46303546002248, 57.67801550102644, 88.24924277065065, 55.70282151430471, 51.73843522268916, 241.17305252245154, 41.10227605012187, 88.74362613417581, 58.104064582995335, 84.87375719071825, 44.35025613538887, 79.66022940406081, 45.72669675015843, 104.78471160953403, 108.15029532010468, 84.38201768110734, 44.89900848312543, 40.06312156544013, 112.14026642613676, 65.44456996566672, 71.71544603728911, 71.64911812346307, 60.969534109935005, 55.35601559289522, 75.0919649738423, 63.37838277447323, 37.925111148924564, 115.95278861027353, 106.36810543201013, 212.03281085788726, 76.98835157620991, 59.427005557564875, 100.8195710419494, 166.70701143858696, 64.39337267319047, 74.07662014860988, 237.46970857763228, 166.804463346191, 59.08436787142914, 9.548886268458983, 58.7743879511211, 90.89028446023025, 74.87193061275339, 41.528110755697554, 38.785194338345015, 74.81591352381733, 90.01790496128498, 74.84629842369279, 81.70296212194103, 46.65299568943637, 89.57938695069743, 207.0897063612318, 48.791849098056886, 6.031000365896265, 70.782886073627, 74.45021910886666, 95.940942958091, 69.87258042405169, 42.82844503685659, 54.45865811060291, 78.85973793056421, 139.09440335875286, 42.30232640929282, 157.42436518925254, 50.701168143282814, 76.92781384080051, 72.70196527276036, 10.253698710629669, 63.578642507417996, 55.54530959782308, 52.31500778701037, 45.200364396655154, 86.0447911846584, 67.13536893045578, 82.04971135418076, 129.19241401080137, 42.61219333753263, 157.48196664566711, 98.73828164257533, 108.30011776108117, 47.924168333498535, 60.02558068370552, 68.6213247008882, 75.30060025565625, 64.1742438998394, 101.68406599367981, 102.30636196527016, 52.699769914912395, 69.58562046875211, 52.00105734794374, 137.0093301332841, 71.45624657875756, 67.55289935073831, 52.35426584566501, 42.386651985784994, 59.55600462891859, 45.53044925467051, 63.47946145294038, 5.424225062930551, 56.738240099108914, 50.18909820666474, 55.60852754831963, 47.45134892055566, 68.10469661564142, 92.13717250195829, 49.80496957411812, 91.58050659149568, 67.76817044224494, 139.72258995483665, 104.90221047321717, 61.21875790317882, 53.25149975846526, 74.6541083247124, 101.55800191659802, 78.17408214325965, 41.773677681017304, 138.68038592483887, 91.16750476365023, 58.647842430712096, 53.38830449795408, 78.93330007010154, 64.25595148118387, 64.98161636006785, 53.08380182957577, 58.329269219491145, 121.36825703501165, 83.94071512647055, 63.96701359330529, 42.493730444124935, 137.37504820606907, 51.277459299497366, 134.48134967944415, 49.815703972082225, 86.96992936740979, 165.47439178377158, 81.61152865360656, 93.35489460648581, 86.06896060473693, 64.7460311081429, 74.85849169482903, 65.38535710254295, 98.8483213187852, 46.575470795929014, 57.36148416343888, 38.024400128325425, 134.59767592352614, 61.07909879205084, 82.86706149088849, 61.291030906412544, 112.20324782337804, 65.56737141003556, 58.30898679005637, 48.30720856773717, 82.61965414092437, 77.95632821503747, 43.96088768058978, 93.81186384887309, 216.03398139387548, 153.6932096973979, 87.70673919996968, 70.76947232936712, 70.52054304074859, 59.670542525067255, 54.83318898809073, 63.32554092082786, 199.74364477540212, 69.13347072225358, 80.36714368089095, 112.75527936397566, 48.54780293415893, 49.94003899067475, 154.090927908238, 72.9840274594309, 67.99966780472552, 35.693846303294684, 52.44855944530819, 38.22662179910199, 6.156234094984451, 54.23189255653477, 95.8653505296387, 71.16030761332541, 96.54184959910391, 72.06155140578049, 37.40780004524337, 132.024889761149, 47.065787561865335, 53.45271107112766, 101.92480102930286, 150.83851778406338, 98.95118613342963, 59.5904828800653, 57.417024314402205, 37.966185389812864, 123.77731217156787, 101.80295056115246, 74.5269409701794, 201.37101230757776, 111.29968138667405, 145.44606931274515, 58.56629793843824, 145.49548808798588, 36.00989741665228, 65.9332435007094, 55.340646015167145, 60.4002863854842, 155.25602990385906, 153.0116802742797, 76.84485280589688, 78.0355663445824, 111.4432629265979, 82.78261653336347, 36.33278157971679, 179.53457369138386, 37.54419738188956, 60.70375136862484, 280.2759449426251, 83.51739479886376, 102.6464573244074, 74.03379649553987, 48.09720640836204, 53.75288695093271, 74.88855481162993, 63.477817099964625, 213.5451832979631, 54.72599470996392, 8.765968404409376, 109.62827641640536, 79.13669297728147, 147.22294677878105, 78.72781652093107, 64.0967978802105, 91.98826654046303, 81.64407459505767, 158.231494950121, 43.52771528547373, 98.66065430585685, 75.69752776120606, 131.3443117768861, 160.31576966384588, 54.003821538392316, 214.68210964823348, 60.507869854240994, 43.92623961027071, 196.38060441921942, 8.439057110098375, 149.15488500785077, 55.37734243964935, 58.296661658539286, 83.72543990998999, 142.838095825529, 70.29019018808054, 66.34910395494842, 130.3191923047725, 42.94741514399084, 46.433640498503244, 62.287605600414054, 75.78214994893766, 44.112312998956625, 77.28829234742962, 333.3073212771256, 77.59970010304825, 60.2450121125164, 239.05720748713296, 58.4537599455693, 85.8697813694511, 174.57622206646255, 65.70838899399025, 179.93019983215046, 103.67043526066058, 64.07107134921803, 38.994057460886516, 51.59223367457487, 114.74024197244147, 64.56120741506403, 83.17930645322662, 140.90628513323227, 97.1286386196617, 110.25788569426066, 201.07913408388845, 184.23882725034775, 150.28673295694378, 162.9753507384476, 72.72535110990935, 79.06253953534952, 89.96324592150182, 72.94019130406843, 56.820194708179, 84.4542719752715, 92.88131537635378, 33.27530621911945, 60.9205167219516, 142.36733507934534, 57.339043354531185, 137.43658132538013, 54.77705618680577, 96.00599586492858, 71.13979796376705, 34.96076889571736, 104.99485794113633, 82.69676228194993, 51.60490148495427, 163.4869094407565, 75.19374855367205, 63.648578491972394, 88.09587364945331, 59.59275283652976, 40.70714076651478, 129.9343581337784, 86.78915126155732, 67.99309925279418, 175.24523040775313, 120.3126525146249, 93.18458731620525, 193.84198736770398, 93.65780954519128, 78.35741030307487, 86.62359627111965, 232.85392454441606, 65.33555005197624, 44.79902594347665, 51.3996647817179, 45.49771191071069, 110.16834866677982, 259.4150466781953, 42.09420174520237, 58.289582113783, 150.65782093297594, 42.418187040376544, 60.1766324505439, 118.25803635555904, 77.36121230043173, 40.21872392104936, 64.06990918243936, 108.93297342777475, 58.17757652898006, 56.150138159081635, 6.954881220677695, 84.74301202247389, 69.17827368152082, 69.55646179492767, 93.68621068351275, 46.66590919148955, 54.13002685136146, 51.928325255063555, 61.02404319700025, 155.94419255936504, 84.04957882239081, 47.289899315383046, 123.47904375823072, 34.019701675265516, 66.78436497898166, 64.6287445580936, 87.13587122224205, 69.20623756434483, 56.417592143807994, 74.63769946981365, 47.293655929969354, 128.8743515584407, 65.41968794926231, 77.77264027454213, 145.2130106865235, 89.19977614230274, 69.21017164922496, 88.59077044941279, 383.40680482177595, 78.57234357541019, 88.51377475278946, 52.07024020923331, 88.05414885155184, 49.75478676803434, 201.33763717725324, 102.38394426366727, 43.95577444179712, 76.34238166119991, 57.97436102084209, 77.3710412485672, 75.4644988348653, 106.62784921360293, 57.62143804693868, 113.57145020755716, 92.42677725954702, 36.277154259320426, 48.212180264280676, 53.33029872962579, 39.490536467325406, 128.59746964021323, 50.022935825924705, 158.48370595141284, 126.5544050762789, 51.93653202723814, 225.68771342969268, 96.56016923237692, 73.73520314045042, 134.27824905045938, 68.31325982037109, 61.2904732412901, 86.77605603186487, 69.88121677110556, 221.33049521210344, 230.77732959314827, 79.0166744482902, 48.11456582800949, 48.59932773423592, 6.864003212140394, 70.80743000093078, 42.92442729876433, 88.04567941143692, 51.9743378031858, 166.9209436894508, 60.67874534478657, 47.306557967397495, 47.131695492360855, 53.07245524946877, 60.629660302643195, 289.05214213014875, 153.4909928343128, 65.10752758514326, 173.43465659216034, 55.39745593381849, 153.7939206407794, 46.893767783976216, 84.47095616903043, 46.10076861870801, 92.46758841925052, 75.49239282075924, 65.35889624113645, 138.88258332295004, 93.36532001511068, 112.36311342809438, 89.22178106757165, 49.26169804884526, 108.54422054785879, 162.60473229665013, 115.7807794310278, 89.79431425365898, 188.74060235500247, 99.40782294433322, 148.14765918931568, 61.621312601346965, 40.47011626766377, 64.37102653274269, 62.01642405920369, 68.25943291247991, 46.13768104818091, 67.18104873566753, 74.70424751535042, 115.95433824799973, 115.0595437517467, 49.53757541534122, 100.03765321692616, 62.07981551168849, 116.96698025506481, 48.33725992423004, 77.36578772480122, 75.67716083942643, 71.91072619752045, 67.50847268120049, 143.15711571727883, 99.78498619508224, 111.19972566940143, 145.4367725864558, 142.0178547587345, 66.39310002942327, 124.8252443943722, 129.68347264109948, 115.53200852325283, 88.51236263391755, 58.72286546602864, 60.3593801106419, 41.70184456647884, 36.58333495573331, 95.73264984407582, 40.64938980809806, 64.12730489610533, 84.11502358933487, 67.34445486364363, 41.82181841571032, 91.64082734079692, 85.1430095176965, 78.40028677734257, 78.18547986096068, 59.78308490553029, 99.19977898053651, 114.73018693289924, 56.54735314240364, 85.51766528729252, 104.16506536249715, 85.76861357078819, 81.91796285683793, 13.372994992244493, 76.91713509665396, 131.02015835536446, 67.75592993150097, 60.29495268263208, 79.15274596577048, 91.68129151747989, 76.93121839862962, 15.85184916579455, 149.08780215797503, 414.4241567110363, 14.261518783077848, 93.2909370679561, 84.35820390081012, 281.7377413498385, 124.10056127324333, 62.42428309005279, 111.47812553734879, 99.00099007837898, 96.48166603970664, 62.564498679860876, 57.616215263016485, 263.22215662410065, 58.4871845682809, 100.54981340775333, 61.49344804451063, 107.89456022600484, 61.093847636000625, 72.45306338498007, 158.0665660157879, 10.526929644060171, 48.69411825170668, 15.876211432575849, 148.63980494486663, 139.57605170847918, 129.21924020245535, 59.69448202245149, 94.47518826975647, 47.138328955921885, 72.44289287510966, 52.74325788370783, 71.81141426302139, 128.48909222435546, 122.01877099193628, 142.20125911799815, 80.17128003602248, 53.153266635589965, 60.73383359895118, 58.768095257175986, 39.22891471169232, 172.71209004418105, 51.83736600935353, 75.37350573860357, 32.616139195677185, 99.87625116656982, 128.2174941979004, 66.79239588997875, 89.88928746964339, 45.468651835884714, 166.868283416884</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>97.47759042739868</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>67.35742263232234</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>[71.76653289794922, 54.784324645996094, 170.13519287109375, 135.81692504882812, 128.611083984375, 89.13208770751953, 63.35234451293945, 60.0774040222168, 67.24198913574219, 55.54387283325195, 319.4086608886719, 9.641866683959961, 304.22821044921875, 182.53262329101562, 37.558895111083984, 132.98330688476562, 58.78725814819336, 85.7218017578125, 55.06354522705078, 43.696800231933594, 89.03330993652344, 79.8365707397461, 133.62940979003906, 71.50836181640625, 86.19014739990234, 93.41805267333984, 85.1709213256836, 52.610328674316406, 207.72654724121094, 71.6561279296875, 65.24837493896484, 109.10997009277344, 36.8970947265625, 113.78019714355469, 172.911376953125, 48.276161193847656, 92.02294921875, 88.02140808105469, 87.68223571777344, 83.78050994873047, 80.0263900756836, 10.153348922729492, 55.68266677856445, 120.83492279052734, 79.46015167236328, 101.6205062866211, 51.341514587402344, 51.43997573852539, 182.8594207763672, 47.23062515258789, 46.04576873779297, 83.67200469970703, 150.31838989257812, 51.01408004760742, 50.13660430908203, 255.3134307861328, 103.57859802246094, 126.95130157470703, 115.12928009033203, 61.74502182006836, 72.13687896728516, 296.4764404296875, 57.07136154174805, 74.30287170410156, 68.78710174560547, 65.7829360961914, 50.81063461303711, 72.13301086425781, 50.6624641418457, 52.33049011230469, 110.8659896850586, 77.78694152832031, 101.89916229248047, 49.903236389160156, 50.207908630371094, 186.60182189941406, 80.85478973388672, 106.23700714111328, 176.50877380371094, 236.35049438476562, 157.480712890625, 61.97358703613281, 62.636592864990234, 58.96166229248047, 48.22441482543945, 117.18608856201172, 77.12599182128906, 14.278627395629883, 101.86540222167969, 277.6531066894531, 364.5780944824219, 55.971778869628906, 54.05609893798828, 42.69363784790039, 44.8507080078125, 63.33218002319336, 41.19408416748047, 61.29081726074219, 86.18559265136719, 99.36076354980469]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst02231</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 02:18:54</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>91.27932019411946</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>71.18196941598916</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>101.5223486387647</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>4922</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>[0.12508418948817782, 0.7053178114488233, 1.2177177425631784, 0.8671379282758359, 0.9121626438105433, 0.9509215363793891, 0.7824903370215579, 0.5556252090962316, 0.7834174520417234, 1.3264897514429914, 0.7643438548378237, 0.14873413833340296, 0.9982083726990055, 0.8999256014414094, 0.89100196196149, 1.2142141763489023, 1.164284840647903, 1.754577715623667, 1.085457415262313, 1.0657412410810676, 1.1719980786747888, 0.32964924371324017, 1.7908000888263769, 1.0241676185565924, 0.8410183902348508, 0.7601882107107842, 0.7959108432992849, 0.533527535866004, 0.562225585053489, 1.1694853045702334, 1.3563438474649423, 2.0717034432945405, 1.0700754176400273, 0.4698808010679959, 0.811908853966789, 0.4975426950617443, 1.1489834763223528, 0.561124352927483, 0.841787357364489, 2.4397496737129765, 1.1471245219899464, 0.5249976452111552, 0.9521899850310073, 0.8935882766919915, 1.4328558453818148, 1.5823693723654502, 3.648414688475669, 1.2051065501871177, 2.1079968435137686, 0.3045583356555142, 2.390275089910985, 2.06034705617901, 1.038961948993463, 1.7277483419236837, 0.8617471064535571, 1.877387596469197, 1.907795211944763, 0.8512736403358263, 1.408075737058393, 1.4850776093916633, 1.3048811096333013, 2.353614248773037, 3.1218180160372393, 1.593474607671911, 2.6051299683416644, 2.666757220166806, 1.3493390664613014, 0.8487474652546351, 1.4966753298572346, 0.7546403666086762, 2.9226563866645865, 1.0334934483251181, 1.8667612262979094, 1.2433163407686103, 2.4453885221124683, 2.6124013300701874, 0.19361541656882433, 1.719026453295227, 1.9831989387548106, 2.4064231976974018, 1.8701927973847565, 1.8310293275549567, 0.7554867801082216, 2.3501102919012324, 3.870706184784873, 2.4284163490548525, 0.6658024517973566, 2.6781182416765463, 1.093113518023941, 5.571943126798235, 4.152909522536556, 1.701878731856668, 2.082631181901825, 0.8098746207523031, 2.3315414462815434, 1.7032977402372915, 2.3819067046409437, 2.2111696836499055, 1.7772663604283756, 0.4680562894311666, 3.975274313879167, 2.0565551564988036, 1.7452421040914952, 2.8775833079851405, 5.062683430886008, 3.8527109252008858, 4.0664059087680515, 1.43044759535954, 3.058856644228296, 1.8489910141524326, 7.807215572310006, 0.7305440883139771, 4.283742526742444, 2.311685268365222, 3.934323294765588, 3.486611211340311, 3.561695476614952, 2.783114207661719, 2.5365109985676897, 1.536254113944646, 4.012673289870628, 1.9385391839514334, 2.179436826407649, 2.5824337756606432, 3.7952942241281358, 7.176494933084112, 3.554781279819526, 3.6610787651235266, 4.329669497514563, 6.6894075520796825, 2.0001487373141105, 5.527853603983522, 5.249810452199885, 4.386138570607681, 1.7162025313709177, 4.558810672710212, 0.8974282056248163, 5.391870000188685, 3.3057138470949754, 4.76427274577465, 2.5781329415929486, 1.0139186741402708, 7.608645398986256, 1.3491898768772204, 5.368313826660265, 3.8521605936308374, 2.9802100506010247, 3.4568423019047487, 7.378136576528807, 4.022782840913129, 4.24285270861039, 4.858940864197123, 4.423639232878609, 6.231493205670606, 5.302496551268988, 5.0377240184626055, 4.644119394252475, 1.6669721650455311, 6.320637294025774, 4.5263030696954285, 3.881034612726828, 8.61285843834301, 7.286447205344168, 5.730544567101674, 23.665522832353624, 2.8793022232247147, 11.433825516372668, 12.196783565794231, 3.7865743963242076, 5.831116837781172, 0.8429180148168014, 5.594702843994249, 5.418360525131051, 16.89255369248462, 5.2598654093515105, 4.079549907551198, 9.35232728962307, 4.247377965571536, 6.567134560932403, 8.38299807639462, 11.062408267373497, 5.659793401556998, 5.69334113509646, 6.967813173762914, 3.6480765733390124, 5.519047789211014, 6.673296449580555, 3.5883126910239436, 7.6127386044041705, 7.961365980734987, 4.151715063001201, 23.31462922318381, 9.316952955406954, 16.419470977967457, 9.818395436165842, 6.661987970193399, 8.500524082571932, 11.235735095487762, 8.023634060164351, 5.510761989722857, 11.214968879272838, 12.472408752223828, 17.704284119706834, 37.044397969584416, 16.184454745905175, 11.884275298223548, 15.358653473164171, 30.248302432502147, 17.398778055243035, 18.086264659839273, 11.045925657694594, 22.09994458079428, 6.746301198608404, 23.528394565492917, 15.687622191117688, 12.283932888491611, 21.478903467778032, 13.990855783004564, 6.994527670874777, 27.924466735814878, 27.993842707038414, 8.109465241534242, 9.118101341068657, 15.994118567684652, 21.731242770624412, 13.556336243725053, 19.80985560073309, 24.67285581602408, 17.98415834735763, 14.720936138797883, 18.696386727519354, 18.192345561202078, 6.233651253285382, 34.06877577639556, 17.39448546373503, 18.489414690917553, 59.02063053907941, 36.93295992833582, 27.23262080965872, 29.655231239300125, 16.848146398134325, 43.40089232163744, 7.616709556468026, 30.67453126602804, 17.480702010048052, 22.783227081774456, 16.03428088107977, 29.139284940334306, 15.676533689974171, 22.238220841378517, 25.100768353284472, 31.384020520562586, 31.366929367154743, 24.733130874975267, 25.798319689634674, 29.892114530852627, 37.84219699174098, 28.2186344076651, 26.45537808522716, 11.278608287572803, 45.90263349866656, 17.02936397286891, 3.1774824321979733, 23.627630438605337, 20.005378517831506, 26.42709772554742, 21.228360119909212, 39.41034524301371, 38.68662223688607, 17.572364882020903, 20.721416211616432, 28.21293694541221, 53.632685757321475, 27.725078850651354, 44.965564115907924, 60.11896301596217, 5.389117948974732, 42.81057760637721, 54.74561943114026, 20.026573418182874, 30.93271232246023, 38.69972478486631, 26.31416085381523, 67.0091102220883, 69.39948026978294, 5.614871630177465, 29.073663231856568, 43.11938003419195, 49.058372088154414, 47.97549976190452, 21.835200183222675, 17.389995719488404, 30.673901302257693, 23.18409231427639, 30.151693034346565, 21.937737522360873, 34.25770060145556, 21.979380532070895, 57.131336628288565, 41.82471613569327, 50.68838812057255, 20.79318967054002, 34.4362406008092, 14.208158105809076, 15.295001200860623, 38.26288814256002, 32.534231119482904, 32.92652862730156, 40.041682483092956, 55.582130785135064, 23.325829824711114, 25.096729890374196, 17.319951430076966, 42.90027063921894, 36.916499382053615, 3.115196362096887, 48.51741949432173, 31.744422859439034, 32.06186947184071, 30.996343136831324, 25.72770020848986, 31.732572494381877, 29.284876926125577, 66.68559021931537, 62.951379963515365, 42.27991528815803, 51.963923821642624, 36.633705157206315, 32.69320006262244, 50.559352730901615, 25.589401550888546, 7.932137847603885, 43.76268924909904, 20.664046770043818, 16.82471985388939, 35.76115583935322, 33.1529670945398, 56.39297212826497, 58.78035337468355, 76.83503680207714, 25.858868518562907, 19.078505923407615, 33.16830548337283, 37.48401549922226, 44.91177859162642, 29.755936008190076, 36.14967581585156, 11.894321432016966, 64.0574721354477, 23.03353563630774, 45.8433962931528, 40.96380400155438, 31.867678929420325, 89.26350640097431, 34.84144928572766, 48.17873352428682, 47.08047035786257, 25.750904876407844, 9.803077331850746, 60.00333609134371, 25.193460798545505, 50.404476245863705, 36.81558852396044, 23.80543957343236, 31.773072334267102, 36.6789631620291, 4.669295102518731, 60.07591064843888, 44.614267157204814, 29.750263931009645, 43.26096276833188, 45.448191589427694, 20.140749210471206, 5.2000403951105065, 40.9684528068112, 4.295486246088097, 3.8380567180315484, 46.236112898284325, 55.0306640449736, 53.69668917096068, 27.25406438730318, 58.66412787278719, 48.72823615059238, 47.174257453328785, 29.811992422017173, 82.76231630804766, 10.966446759247319, 83.73678122482329, 53.45050151568952, 75.08663350324805, 60.66666293768303, 51.93207357238418, 53.808770875442285, 84.64341830928035, 61.077920805899026, 31.479687757848236, 30.453437310095186, 67.56452507979041, 33.29080951542706, 53.35754503174801, 81.61776698156314, 36.10614749255669, 105.76052545445685, 75.04580725589695, 67.3321314232646, 50.41483660962229, 27.480416673603262, 45.47085716819916, 44.88334475969489, 39.289352080787154, 65.0753438482879, 48.531965183493966, 68.56336917524514, 86.82984641495297, 8.814225610798513, 13.297241964617955, 36.352377234697684, 46.74358053531418, 35.62215785965056, 47.416378721591016, 68.16828126951391, 55.350382289459965, 104.09844139469533, 90.48054121837936, 81.65456145354285, 62.358776488619746, 58.26040492041394, 81.24832262448564, 35.32463456485549, 30.363281716440877, 48.851777594541055, 78.3082622217341, 57.527890905391025, 44.21997275862295, 81.88141605977718, 41.632086155620314, 47.07183990056168, 3.53781868898656, 58.66587380523207, 8.097380443185406, 73.34204333897272, 88.83205759005777, 35.85815073524755, 82.25952491604016, 61.11172392427893, 50.980874284794346, 75.32712448861184, 104.0383491910545, 53.43121619711845, 23.353353037659875, 79.80251632596774, 57.534395166530096, 145.40565853051783, 56.13549839025598, 63.21013770358763, 43.503087190839224, 2.8466747700152264, 114.67892097320617, 38.10520406750031, 84.67528832617992, 29.909440990490523, 65.2041310037106, 68.12686678276603, 58.6419051306559, 45.07618585665352, 69.15774598979017, 46.59854996394605, 54.32892929927824, 131.94413066308348, 60.819114272733366, 53.68913894867842, 68.21080438220275, 29.343192687924066, 33.38763343461667, 29.13236576345292, 75.48769265692023, 40.301188852975535, 45.606726001788246, 4.42643492444366, 44.775675556483364, 36.79232269358369, 55.39084186991275, 11.385304731146716, 39.07834720017325, 53.89506496583106, 54.67298342302858, 83.14642130860955, 35.81175172344811, 103.82911181455508, 72.85233309857291, 57.58356361136963, 80.03454848277521, 53.464984823582306, 34.92330386949299, 47.60560439705456, 34.456766578170516, 49.17613844125603, 30.871834816348123, 71.19342714619144, 45.79753714101841, 100.53912372247973, 70.6276617033848, 8.427839344327221, 43.54201954196285, 50.26651922132432, 119.02405855603084, 42.08899633134487, 69.87701259873266, 40.473578281749816, 39.38188674710923, 43.42861782479298, 61.30646580498653, 151.50973712453646, 72.89737573725385, 64.82943031988268, 64.99614452059471, 33.796281468613834, 5.89339357988007, 142.03518383639877, 95.84636442111874, 74.06159598563569, 62.665025160279285, 40.33530186848504, 89.67479022804376, 53.13985078351284, 65.66161995647103, 39.231595191374154, 41.16018167400112, 45.72150441547477, 40.424981114836775, 50.63467705524517, 116.82417295186171, 132.70637968290185, 38.57037521702652, 5.028388815322247, 53.58020813701246, 98.9376423570856, 115.37448060443964, 98.6139612977144, 7.67152215645755, 28.99271170499484, 118.67860380726302, 31.962734833030343, 49.405112908409556, 61.345241987711084, 35.29709677062913, 54.25100167174572, 116.73854502966115, 78.58592753515724, 48.95353802193302, 62.42270418959676, 43.588074684011275, 46.212906666660146, 6.399750329414763, 86.49092575052822, 57.66731844054213, 37.97341063879861, 40.27203512135773, 55.76405980947628, 60.13045341903652, 73.93609917471618, 63.13279521954163, 160.16544265535583, 41.784700332401066, 48.152000653244436, 94.78843571537507, 50.36815107634078, 34.813348543280725, 54.20116970942907, 71.29621257080582, 65.38397311841555, 47.72812581017073, 49.80232790165205, 64.9870042339821, 89.43891623720606, 101.46431243611794, 89.88681110087296, 54.72260086673604, 55.31983875954573, 5.1576450119584685, 44.46651088032892, 30.027576362674804, 82.81454508573178, 68.92628696908608, 36.999584816641665, 95.25544065614984, 49.85446832883818, 55.227748850322186, 97.63053128174494, 73.2709060269807, 70.66447130118793, 43.22447191733054, 67.12071419290375, 107.00909891374985, 46.4392752088169, 44.96561722860463, 38.73428385540769, 71.31019776438131, 53.765829712485875, 100.34936986635529, 54.19234585344026, 48.26946276604958, 43.61583962833023, 67.77202295350658, 62.359058570564564, 39.27082719719412, 44.792675530676284, 17.82107882251243, 97.14460560999237, 138.41782508375832, 49.76272173234729, 87.37178452875462, 44.15217729489036, 63.585562293966156, 53.01300885689638, 39.409077813996376, 69.76534450279368, 9.732962851424714, 31.972928850685992, 42.16811967869305, 71.1411738576624, 37.66136605194367, 61.198497308440665, 67.24448325185143, 197.01883955727803, 30.60125030598705, 50.399986427767466, 91.81955837744675, 46.551705909719104, 7.548289964698028, 57.938909247887146, 55.731238357205, 43.082081558430275, 80.50841417216198, 119.67871092471762, 38.1101295997821, 61.530213311150405, 116.34102196965725, 20.88477388678309, 84.97375068023445, 6.953560657473985, 48.36623673983288, 61.183149859024404, 119.41221801456702, 45.743099848450484, 54.20325473030837, 96.30302930929388, 170.7872352973922, 70.12581356457467, 39.38038927451055, 126.54264665687242, 13.163434637779202, 37.026112003719, 50.79780346304027, 5.811070007152105, 42.396859802192346, 54.29833096435225, 59.302653927112054, 58.885254706245426, 60.62095920786686, 121.94126183369318, 151.11159018727326, 5.652189216741954, 61.042947848584795, 193.21047930330363, 135.48863677911646, 46.96323891522821, 53.89264477440707, 64.21140945913709, 98.07066840861559, 135.2092601886692, 54.09205490999235, 56.73459706498071, 212.40607048241085, 54.980914825126234, 61.204513225190766, 48.83433705828543, 84.70276539423259, 37.647683415267316, 54.64414334722707, 129.6400468723965, 35.11120366672894, 39.735305119597626, 30.249667422834833, 44.5342894382966, 33.59109062737065, 104.17412154145394, 53.191143610853096, 61.26735662885953, 93.83050118554507, 65.33136337901503, 72.85882292650666, 38.909184430376584, 69.74328424759173, 92.71120332555388, 47.4598842653618, 89.95546053234838, 45.83541866167018, 56.49085141071268, 55.251333412144106, 45.58676232355765, 54.710656192372795, 97.77794977163867, 47.088609768535974, 98.05786558617481, 67.87953879103296, 151.16358864541994, 57.60984662908349, 50.19779607483859, 69.0357711822289, 44.67954017085399, 178.41441765085963, 7.257199266178403, 42.14178639590031, 67.50807342312102, 43.234833011026296, 27.67816056629631, 49.07664024831888, 73.74433867155656, 51.929010276026716, 59.067160361406096, 154.54932856056354, 46.2567245809247, 68.48133179000092, 59.42598310708725, 60.01726597833637, 73.8962112483801, 64.26906346979364, 56.97987697042787, 48.2051158362625, 78.80881264048537, 57.44953745230913, 58.380194299458765, 49.853945367472626, 32.625703371725564, 39.46728592256623, 56.48975115434508, 31.265355436605674, 62.14627750283163, 115.97070483662206, 63.652987161503795, 99.2839865725235, 57.83228539064262, 52.14472088207454, 67.94621890232112, 71.741420602559, 88.04375478224743, 75.87430828484239, 37.73594514951973, 56.616228623625666, 67.92770778925892, 62.07781286874946, 131.3013790522402, 48.46174310760172, 58.586515018231076, 58.06563248608906, 73.49499665187952, 103.31404053491222, 66.59327045206376, 174.70398333021595, 68.66862102205678, 39.2217055583879, 331.64629229373793, 14.229478097846311, 17.925527214917746, 81.1547221189914, 62.58886611677333, 189.43931622751757, 81.36614319529352, 109.13726707230958, 49.582199112507936, 67.80078343657655, 207.00915519288807, 160.93264760854785, 36.59372806122511, 50.34444052432565, 30.320579287144486, 82.14419330630132, 77.80963473720296, 57.117971272881334, 63.57670280027031, 145.59291319892645, 77.73045981162011, 57.16310118277194, 98.65731698059668, 58.64762542242402, 42.140075380075686, 76.30222061008432, 86.85513081938835, 67.11309501727384, 111.25228305512667, 103.70658590317672, 49.156488884384004, 99.88043717705371, 40.48314268924899, 97.7872410545568, 42.83708506411087, 171.63228967991145, 57.97680997689191, 59.22800389502363, 104.31927134961491, 136.50543776563404, 101.41754265351948, 52.66154802152847, 73.23586832895555, 75.95481203563416, 58.78992215985105, 69.5332505862911, 61.52679302669844, 53.06911616219035, 130.7791013013943, 93.60385785453698, 76.73783968550573, 65.43614122911562, 117.31391801427728, 46.69074087316136, 73.34480095068781, 91.72056770879844, 50.32692524822981, 105.58453514965996, 141.07271744901487, 70.37441859438232, 106.55929391503301, 52.648734968037594, 179.34343579997216, 87.86248498249012, 55.31213054179665, 41.18944155825518, 89.49017193581737, 74.63376421199935, 104.91957266328728, 65.6517554525905, 133.9549292056752, 47.610960683758115, 64.95744485775636, 90.92727898378313, 131.74322124276728, 43.772944326423705, 99.42134461834026, 172.15780192550196, 86.01579720062983, 70.98788082057327, 179.04502919469638, 207.92966105832718, 58.823827120050666, 46.215720265211914, 108.2730187327386, 7.9509148334090405, 96.76106134982255, 67.76423676769008, 74.61344397424656, 53.32109928634824, 59.2662938368319, 69.30041344076456, 57.66332290777707, 72.61265758281232, 12.49219237402327, 46.779780110160445, 58.21104872668885, 81.97075308220522, 12.497460761997203, 10.786622851811243, 136.68658906110085, 73.93267120417819, 46.517646865368455, 42.73575591126047, 136.3390780559109, 55.04872611877719, 74.03428758849664, 166.0656964322852, 42.732845436703805, 58.710648367643174, 86.88223812804071, 67.8556390440435, 37.39710057398057, 58.69290362196071, 149.8809781955363, 18.919754863236328, 142.57859090628597, 68.28634173998698, 63.53000013913859, 45.77454427158884, 202.11852790514362, 58.44200777969893, 80.71265933603529, 99.9278120950192, 60.90361423071007, 47.09167808053024, 169.6391195398502, 77.45417937225245, 122.66499628514016, 74.39711569195559, 376.7937694735036, 53.733477168838654, 62.33282250849318, 77.67399790526309, 77.88437329479403, 66.04116739907289, 57.703270194383705, 72.13424862141625, 75.5759126176642, 73.2527066025903, 51.949745106409246, 109.30325995559488, 32.92107121532836, 10.174916548255668, 127.88461944711364, 38.74235248893697, 68.63261408485923, 126.69397717459101, 119.39820092373044, 38.48891046935892, 56.62070148344433, 9.814834152403735, 93.50337495083399, 56.77409786171797, 121.01029619780435, 58.420685425540356, 63.28759373303958, 53.93475314639747, 158.39806420587988, 61.30529854094473, 77.91980606558333, 8.8768542946812, 53.70424834291873, 119.65221403696152, 137.94056958409806, 64.28119938105232, 85.49395771995054, 114.3057600560232, 82.04383731097619, 40.279006247024704, 68.42803436823885, 116.98593281873404, 67.15655156506418, 89.12267217546116, 72.95784179920565, 72.8568111072417, 71.92015829756924, 58.21094768246324, 81.59112328572651, 70.8947402203801, 103.63122270862846, 68.96292684430422, 62.364623729516246, 104.99080036247136, 74.6229923418348, 126.64987052182767, 19.05633598756244, 51.19608465121171, 76.1032949887042, 65.79400504180306, 117.96914246124804, 75.44853379000588, 53.039784629705395, 56.83936241861468, 86.45929488112314, 75.44531744237693, 18.40303209306255, 54.635620382882955, 209.47960895011028, 59.407070183629116, 39.89083208803906, 9.469728445487284, 56.142613511928246, 9.85038656640967, 54.610650452197106, 95.41022179705129, 109.94183907680836, 60.52209431431128, 56.20920023614122, 18.75411660646202, 222.2081190088318, 67.43468710599359, 43.964579299273616, 36.54200309902348, 65.57453931362554, 13.031262778921741, 90.85947030334688, 70.5416915329675, 66.59340448106529, 106.81873827883682, 44.98403667487595, 42.00795541819011, 73.72829561831803, 70.07340305961763, 124.88660941844331, 112.74886977608622, 172.67263854118232, 83.72390456952719, 121.96814290936342, 71.2984362084497, 78.08759549710096, 47.7889983206023, 44.871468319469244, 105.43638212469699, 118.80321283655692, 210.48798322605344, 7.956904557714572, 76.73943697414437, 65.13402291692489, 81.54162882991423, 74.2504830749332, 83.03193573792598, 175.86803780907098, 5.671604271647027, 122.12411935586461, 121.7763164508033, 100.56773801677231, 39.25626586274488, 98.3973063291206, 57.43583824428745, 87.03449558703463, 82.03566846451962, 50.330168876774295, 151.0738936120255, 118.24492146029715, 182.132517250464, 85.43443518305442, 110.63150506178023, 63.476665399256326, 44.264952700880265, 19.684730963825427, 14.437068777231476, 123.71954190900574, 106.84414238953603, 70.05996052786585, 39.27522067637501, 93.37081745969357, 74.04281742246314, 80.22125053706336, 72.66349725465531, 15.327277393498338, 61.71332421932342, 167.45428270633928, 106.53363540409555, 117.73140060319284, 44.392512924852674, 78.05561247787237, 32.190368566873595, 131.36703790453956, 85.26392174776747, 33.974870976121764, 75.82280927854833, 53.09249929674136, 52.04580897156206, 130.64825604124664, 61.943193104961445, 66.54241797217628, 231.6026105460238, 118.75734210489352, 57.30863031723701, 35.54350334623469, 59.24297969769174, 170.46416228836162, 103.26607237703527, 63.27781339542302, 99.78922080532247, 96.01723712938792, 56.99319233211919, 51.73489294356475, 64.65769948686027, 125.02111550835644, 75.42816309484596, 76.85188329177235, 143.06193349724532, 140.30529619357844, 71.51395741621464, 53.023182249795184, 35.2896027293932, 132.52842746851553, 71.19408022759197, 72.57425810271788, 34.100073555303794, 153.048203878343, 71.94715190035456, 72.73631949989922, 205.97150059489883, 82.27326778359458, 99.17085083293622, 133.21401347972017, 110.52252155530225, 95.19646235570094, 192.18330185221035, 86.08247440523726, 50.13831515223448, 61.37573992431169, 68.88813564055191, 34.33393226542364, 47.89104853647316, 77.31226551569047, 77.27207496144949, 77.17290640387252, 116.6297340300922, 149.46299820683396, 7.856346617585941, 57.72963896720305, 40.87231331666902, 25.617064201736074, 141.51799546475604, 55.68963345607427, 53.29886368023687, 60.35314251068414, 123.42394574914225, 7.761109100792962, 61.642326577394634, 48.34803043332911, 113.86286545555397, 117.17271368141536, 154.39861604518273, 55.08736995619121, 102.9820113803895, 58.09559658338285, 9.960685397624806, 74.45292758222176, 50.71373538908467, 147.9595017175545, 61.2272939378166, 78.38234204889116, 77.65120494980009, 55.19765108376895, 42.3340665361717, 101.45803860140458, 71.43046244585803, 167.37561324541625, 51.966793682272204, 51.50507758707525, 170.2610928966631, 180.2842039612661, 69.51833421249117, 51.992567534501354, 49.509800896608745, 229.46633066969628, 45.33675031670908, 70.51259937541674, 65.75121472146631, 153.5914374373678, 65.81529974827667, 53.31178831019699, 108.59233260314437, 88.58009580405133, 98.42543951121928, 99.56927945941665, 68.45072814004179, 118.20589581712609, 108.07758978199726, 96.80630675385605, 41.83801451009239, 55.512118862962524, 99.4705089680628, 86.82940205902744, 104.36319895417721, 51.27641041857604, 81.10584823831341, 56.16979905959076, 65.36046531476875, 68.60363213423862, 120.41132165775709, 87.87965329686728, 115.29802860955702, 65.51637136604829, 45.26492472731043, 132.82565735285453, 96.65976357529202, 65.6914218133502, 57.293481970277135, 78.03758741892626, 147.05323663882214, 42.19354943164549, 61.25316675455369, 37.27382158437416, 132.16165375752914, 76.56804535743392, 47.76754901859029, 92.48262523989145, 48.62638081592305, 114.7464826232361, 376.89837586864024, 50.920432847814595, 36.74544640791315, 20.57520078649779, 59.74349010927961, 262.0017754461733, 127.19391070448138, 49.4836833410363, 265.6365092170571, 66.59358511316678, 16.5011579730005, 47.648126962973386, 88.3458323053706, 69.53547983168082, 91.13061338658694, 141.21431241995947, 61.50484806092292, 53.53938368351158, 8.269896300489096, 91.84558750120021, 87.92656638484785, 109.67722861112973, 50.96979780722989, 85.27992646432534, 186.3344367526233, 74.74961075413931, 7.96970692476252, 37.23970625036393, 43.64482335247961, 65.61683943831359, 122.72800667738089, 296.863159599409, 112.31537621023071, 64.62611843284319, 116.86230569252935, 77.68629634521794, 116.97056691369822, 53.16131269716903, 90.05089242307109, 86.54932405857588, 92.18929792730333, 43.45141594329528, 138.33928839204873, 111.074951151878, 201.46100802983796, 151.02459923728057, 70.65360903360434, 228.3569814219359, 71.97463136469048, 51.32087985195884, 107.5251546519481, 34.59214737507798, 70.29900769576447, 115.55926718966508, 145.9461939128878, 71.92797473049609, 61.87460525511539, 101.09375872488006, 7.0631930251638995, 58.121829344663574, 61.95729247156829, 58.64409572096857, 49.87960406109314, 38.56525547322913, 110.02055790455167, 69.94006985919908, 98.73930326729052, 77.6877643811771, 69.71817907986302, 78.7344558570388, 64.8467821515325, 56.49801428646388, 34.21607502330571, 56.729595008841656, 60.39332766515881, 46.42914257203429, 45.060933917551, 268.4234480554202, 50.30001187472175, 35.62140911537931, 68.12764907834065, 57.11442115958779, 71.18339595387961, 156.6138411546414, 61.35130886142636, 73.08767624283165, 125.20130307009832, 54.35565904932706, 89.09654375461221, 8.933667554164076, 131.7738202384146, 88.42557525435822, 154.4734669774518, 44.1574894984046, 109.53082060010298, 105.91549987827429, 41.202210908362126, 143.8124723455959, 125.93298028534927, 6.461241598187044, 200.7842844796448, 79.59841683046125, 64.40883974877374, 47.92618794511546, 118.18218106122065, 176.6259823239191, 75.92101660061674, 28.499123782157227, 90.98692693442511, 95.46068614891341, 96.11554856691754, 57.86960561272621, 51.47406191552496, 60.15956977480788, 71.16075989563197, 154.37608594400018, 50.19864736801503, 51.689914615748464, 140.48355528718966, 134.13311388158638, 61.712072785428866, 64.09798267019148, 58.02827095467399, 72.06238252727388, 49.40810804849388, 99.09588779063597, 64.59961177410013, 98.79350686860737, 54.66694808047491, 90.82073580288379, 55.53523524363038, 65.14821823787344, 94.1872388641708, 81.7665752215927, 92.54215668034809, 62.90560408998819, 41.19137833867869, 88.64058241086745, 99.47388050444737, 52.64068474365668, 52.708594029373614, 155.54274726958718, 40.02799977032328, 68.97205324650402, 98.84942577986932, 47.69676371263145, 75.21003345365656, 13.957353293411488, 71.22193616000513, 64.2451795156285, 94.7747496044311, 133.76968965587707, 90.77575490010835, 449.2652059032779, 52.16110257367734, 149.12539997232312, 66.69784941991196, 127.42928183902215, 73.82646680917303, 365.0945485521545, 408.78515121257266, 75.74571025874903, 8.973368295928326, 106.36665287706076, 144.14433060782918, 53.30446795250374, 150.03554489765426, 192.57743302073098, 52.89536652867956, 39.22568866052049, 77.0489467290196, 45.3839522531313, 12.655261881947068, 66.99034040035512, 69.37132630281164, 101.53327566750528, 141.16175691322863, 56.3920797106814, 11.082702471510164, 94.05290740083284, 62.04171842756398, 53.24756813108222, 49.19746175616089, 210.5195225047462, 79.14866519774822, 114.6766148183741, 54.18054468339857, 60.052126155442785, 40.85399681922518, 121.8249657321325, 142.27302960091683, 82.5225526646837, 124.94632873416136, 96.42769170233552, 74.64410915912147, 9.703027119639959, 251.44351680241215, 130.35752654363858, 42.64007096338031, 8.476058889886536, 60.74457491871682, 45.13569879873409, 85.55389537834043, 8.338162790674213, 126.7996811121483, 166.53149101666347, 70.03250268881318, 75.74495425045875, 81.97132438692586, 114.06936845643082, 52.62567241466513, 193.82111777600917, 69.06203873827741, 58.722471704261956, 131.3076731500164, 144.0019228502478, 78.55641765908646, 124.6813301420383, 210.99797609846655, 97.80037273913861, 59.633003534984546, 67.8074710053494, 96.27062184229185, 7.382773496229213, 68.47150284955612, 65.49236280002948, 68.4706315825213, 99.55240242391572, 137.20269045381096, 77.09627522153046, 131.6698563524045, 107.85204214936718, 150.5476033623543, 85.57256465585381, 46.66448374023918, 102.079173545233, 93.47823245918997, 143.18160499904448, 157.57563350061184, 99.94697288553539, 7.668467101354688, 254.5733044974292, 90.86810772762604, 170.53018695355578, 81.01284493208067, 165.82188851920074, 83.36609609669071, 90.76780670010972, 13.024744210502199, 46.97318973327281, 98.83008714692596, 55.953936895296884, 70.6985496892132, 147.05653798837736, 48.68304069036623, 49.246680826495144, 74.57379500263603, 83.72161005814476, 52.505026503053614, 223.60353091964797, 108.67908475529174, 60.02916101213447, 83.76326323025414, 85.17935297245222, 185.53317408916996, 60.357035307186194, 98.25278797697194, 115.16997954704424, 95.69594510245425, 169.41532510145655, 54.92992217448786, 104.91655091969383, 82.83551989614114, 49.55677460684152, 47.692888641491955, 125.57524807846467, 63.54624217854589, 95.06231758855465, 92.56736681368895, 127.56501349901501, 59.27310874857447, 79.72925712121281, 32.68576490167906, 140.42425051819492, 87.92759019505712, 53.16639715544236, 106.13394595528324, 85.74014713075337, 48.75912736807733, 66.31991619552079, 121.23974544648038, 98.93627329734625, 81.52414403339976, 48.508372969388404, 93.11614999044893, 80.77208092874292, 35.24336023191901, 67.52359913859696, 50.58301925792454, 95.66446591183964, 15.30388818313937, 46.66462307263506, 57.90141670441449, 65.31453199238027, 87.6176663799801, 116.03317847846935, 45.3074084511981, 58.31418062676677, 47.18580279129402, 136.31102058062007, 40.231685620250694, 133.4972096622663, 107.80490234384587, 98.42789401666784, 97.23933578608113, 66.32103052300064, 44.04657687990498, 51.85397522799067, 75.45626779391479, 76.36721683755245, 80.5512375390174, 251.5673868465368, 70.19388031438157, 120.07707338499985, 66.76439329941483, 95.3444508688004, 104.99513732679998, 11.325496445150183, 78.81497090696486, 65.07156110831953, 144.924007773476, 65.70975262522467, 49.89009294785041, 67.96729147357924, 57.25201803325128, 118.08144856919145, 45.662704221323466, 80.6339841229859, 116.97119457433327, 55.782435475015916, 63.36145351664944, 58.05454325803738, 89.06857853361657, 101.3801979862537, 137.38094616194059, 5.692930353244214, 87.73665883415387, 47.27245332279317, 166.7339653905907, 99.23183457034999, 46.43783270677854, 82.69684607449042, 197.38279445651372, 67.8651946470039, 62.5889722359142, 157.39338864630503, 36.091037597133855, 197.66939976476786, 8.293063124350795, 154.06173166878784, 31.367335773097466, 78.5272794845223, 60.308680787451124, 183.22670564929922, 48.93618345737099, 146.33050162216978, 45.46851161097283, 64.48219872718978, 128.37789667197933, 61.49744044521653, 120.59219322906166, 52.896492889746064, 57.7018019355433, 134.560751935242, 123.1466326000308, 131.9444679280813, 71.9674127269419, 51.03109077655891, 68.76636390096311, 93.45304654020407, 47.50352659261175, 61.587897592528826, 83.23009486484291, 86.39548507960845, 55.69896513876089, 39.38563543903497, 78.63685777552507, 79.65656340949502, 58.40376583594265, 72.10006779263547, 57.08222334357723, 39.25089697047665, 93.02249198423556, 119.33934717757779, 179.65381520918928, 119.88544513379222, 124.35923728277221, 173.02233908493758, 60.94060599006558, 45.735001042217974, 48.26995311654646, 77.52998212947497, 87.13601758588882, 62.75306611998292, 134.74143222990753, 61.42106708527362, 121.17070617905942, 66.0408150044451, 50.81800405369098, 43.951149778980806, 122.32712489175097, 45.5049454289785, 45.707085662236594, 130.78189397309427, 110.03780605843463, 62.93067909035883, 69.68840702691173, 132.9980778349472, 72.65625982572445, 95.36276442351765, 143.61576943204517, 84.31972758899786, 141.4330689979158, 50.942353814636476, 11.576859927706463, 37.80621172249779, 84.66442154604349, 41.578142652903935, 95.15300140116797, 51.01616354986348, 133.50050982592668, 124.86112376187987, 44.36550345528288, 43.95823197543287, 66.57276098861922, 58.587553307248534, 86.17230406432812, 466.3331643916487, 123.5598786812575, 202.74025640656217, 52.071367592360325, 105.41910242774922, 63.20033213370068, 74.16511987963919, 52.15782883024609, 72.01368899385912, 241.46507909234052, 46.6116220802432, 277.42472568353634, 62.74505067230573, 117.88525478227528, 98.03414530011361, 63.33542644521296, 88.52596484456514, 87.55306623520444, 66.26890458020294, 255.2874111132632, 198.15267345998444, 85.77655950636769, 66.83267741498328, 122.45061852108094, 84.21539831481037, 38.449914554816964, 119.50521147768326, 71.8707479183777, 56.52161381728225, 18.678142649129658, 65.67345025670903, 78.12527398099733, 152.23448048388008, 96.07680232944111, 54.53725008964943, 116.26739879163978, 120.4601158083249, 78.838236082737, 50.63295349268381, 101.11493375839723, 218.22247162440345, 58.91183267342847, 40.2276343903004, 9.420274870884198, 29.358568908542466, 107.7943053328473, 337.24277973506554, 64.05527949724441, 11.447003444721512, 62.459617458853295, 46.38958555111433, 310.4557329333561, 88.69522822167978, 135.50215064953318, 95.39395193507701, 325.4141064296438, 32.96509166334499, 16.716845670732265, 56.52669083022482, 79.65902128671952, 151.35087842820872, 56.49791954647611, 39.66800089406047, 64.33982689217261, 75.49940724834434, 45.38235736673367, 61.55748922742103, 149.92291399676628, 124.21117281812097, 40.119279992803, 48.22094658427761, 171.99175335136255, 79.7259988884627, 64.04532580442584, 63.14047007082867, 167.55899013299629, 78.56975020325902, 141.7426711535983, 426.05567303280003, 11.384432815033506, 193.18638923074815, 87.96047998168581, 83.62747060457095, 131.64600</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>104.0701243495941</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>70.93427639958439</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>[73.91341400146484, 58.18598556518555, 189.7703094482422, 136.6929168701172, 140.4950408935547, 89.2871322631836, 66.55918884277344, 62.18060302734375, 71.21086120605469, 57.26403045654297, 318.7348937988281, 109.49641418457031, 141.39027404785156, 188.1422119140625, 37.210227966308594, 88.22859191894531, 17.240032196044922, 59.40653991699219, 80.1970443725586, 54.61075973510742, 44.91865921020508, 11.488704681396484, 151.5408477783203, 188.18020629882812, 81.63990783691406, 5.360494613647461, 94.56343078613281, 129.78472900390625, 48.35218811035156, 68.1646957397461, 371.2705078125, 86.07270050048828, 183.58555603027344, 46.276634216308594, 57.288814544677734, 9.517123222351074, 226.83763122558594, 200.90615844726562, 66.37211608886719, 90.9352798461914, 138.46055603027344, 57.166133880615234, 84.926025390625, 10.545328140258789, 82.269287109375, 85.8125228881836, 90.91392517089844, 56.02445983886719, 54.25728225708008, 206.53123474121094, 133.92185974121094, 83.14997100830078, 218.5347137451172, 55.806461334228516, 47.702430725097656, 195.22653198242188, 282.1585998535156, 61.1931037902832, 100.99679565429688, 55.545806884765625, 88.20682525634766, 178.83897399902344, 311.2918395996094, 77.79188537597656, 167.90875244140625, 15.25217056274414, 84.5138168334961, 53.849342346191406, 44.171630859375, 126.9679946899414, 114.26644897460938, 105.6366958618164, 53.16702651977539, 53.8981819152832, 112.20121765136719, 127.28749084472656, 119.40847778320312, 143.88482666015625, 119.8443832397461, 145.13519287109375, 54.88466262817383, 85.726806640625, 66.69573211669922, 81.56118774414062, 50.61410903930664, 117.73196411132812, 77.39236450195312, 160.64016723632812, 299.544677734375, 226.56069946289062, 70.62322235107422, 56.524147033691406, 45.53813552856445, 43.68550109863281, 46.695133209228516, 65.29119873046875, 40.52764892578125, 66.8017349243164, 94.09073638916016, 107.94354248046875]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p012246</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 02:29:52</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>91.79169056279164</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>66.90209010254421</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>108.1278943951526</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>4621</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>[1.337542689910066, 1.046626380433721, 0.3376593373561578, 0.9589191027460144, 0.8491413741919295, 1.1124592155563366, 2.2179003732614175, 0.38871174485590587, 1.5518192886244768, 2.0290708201241663, 0.7754918761038669, 0.8542858605450605, 1.2673138175769998, 1.5443926594713746, 0.6918801756821721, 1.3393887489129845, 1.489531771939942, 1.6263918196003393, 0.6736891817930234, 0.976667404705274, 1.8408195592384697, 1.7113187505874723, 0.5166713795745098, 0.8869455112303002, 1.7486525157680082, 0.7002395219078603, 1.509220739608816, 0.5892304148458591, 0.8682599325331514, 2.003912607670938, 1.7106392001826816, 1.5842524257683968, 0.9720363256979765, 0.7341879219975423, 1.0238183653874282, 0.7240230187376122, 0.9955945834016954, 1.6023608903468476, 3.042655293882396, 1.5223038205816803, 1.5234325438194347, 1.11569721421153, 1.0162114958667303, 1.502115329578827, 2.3602723066492324, 2.4377450745062297, 3.5155382202976213, 1.292673297439642, 1.2480925107038974, 2.654021168135474, 0.8754420066700644, 1.3645096148856215, 0.8802551889310687, 1.4628881202225363, 1.306741701857771, 0.9712115780378535, 1.6894678259662883, 1.811945691274945, 2.371693962833419, 2.4787611555850106, 1.3679563293948356, 1.8403752499460913, 2.0783065751911303, 1.9286419102877197, 2.025350525381279, 2.3662444143532704, 1.5154632144405245, 1.3902687529342996, 1.5677171179829166, 1.263839918163934, 1.1741421350662793, 1.1012964475404496, 1.8506766575252014, 1.7448829513066535, 3.6373019289755573, 1.901558456512137, 2.6573981927559074, 5.273588294098891, 2.923601668208578, 3.73130744966868, 1.2632757889240396, 2.227685673729464, 1.6500842412212664, 1.2637681051658198, 3.2029668492887167, 2.9918279665660426, 3.642018773961126, 3.2986085468670256, 2.168472133799678, 1.6406539495685917, 2.107970111531337, 2.820146636480979, 2.868529626777716, 3.8544624553026487, 1.880260536912809, 2.2109199159746007, 3.283875304762757, 6.040376689624308, 3.083785882749818, 3.5281299270052235, 2.2276771943815694, 3.3616512848479125, 2.067071011441428, 2.289084928977115, 1.795201912691381, 4.617321492637816, 3.436645454217966, 0.772920996814075, 5.181895134136262, 2.392029688567078, 1.6875789107959605, 2.65497382355659, 3.5794040408265126, 5.824261584924532, 3.0475096942824527, 3.0044337274575588, 7.862113277888365, 3.0880751390355483, 4.689995714589481, 4.308872214046485, 4.765941026940185, 2.7586809248886364, 3.4333246515564335, 4.215975896317512, 3.441845572720497, 7.423136573053351, 4.334546957844346, 5.503957290136968, 5.685496310749244, 5.643579290995403, 2.752227681406285, 2.8260708959964527, 5.322836075575533, 3.277131827989902, 3.0925402648249087, 8.414080675626185, 3.6069105116600624, 5.274085868921168, 5.02161398967128, 1.3806944645324322, 3.337741680992698, 5.552192662450918, 7.665921719099607, 3.477585915977632, 2.3956121885877137, 4.06001393123745, 3.0660338541801857, 2.785395710203093, 4.1840004000701105, 2.282330712555043, 5.516669944777183, 7.214306072014951, 5.003631910475479, 5.914607865141414, 6.742051230506576, 11.010387648816932, 7.720946312901632, 7.960402997518391, 11.349821447570406, 11.084437640466868, 5.702306371820933, 4.648317209243773, 7.659802166620603, 4.708404508875953, 10.389039601690369, 11.69956146924748, 10.977054178729071, 7.525421067060196, 6.316579217586433, 8.01680652822504, 11.662363599169577, 7.248715264120916, 4.284817862777246, 13.737809777353608, 7.400663290365767, 3.2188276496314807, 6.341431078752231, 8.681706326976215, 8.429137042321845, 4.788324735852247, 10.184552801268202, 9.292194630370549, 6.763303692367376, 11.64810732177889, 8.461784244746388, 7.4854635097302396, 15.095656717193519, 6.502227058816073, 19.337838514815623, 12.944759656519706, 17.654592293459086, 14.481549618198882, 25.001354599145646, 2.0372725413811064, 0.6433357118898528, 9.4463676773058, 9.416477109260066, 19.425437382573225, 17.224891708830512, 19.864996711378225, 31.469625987570545, 10.003071457844065, 5.069656719191516, 13.653895080448004, 17.95279079195214, 22.663082899767204, 29.523790054079463, 20.004724433306233, 4.906742143844572, 8.35985087639791, 15.451638286533441, 16.031286695960116, 30.45819313706847, 32.02798842250768, 10.81322818574244, 12.312068642079302, 12.340660655731114, 13.439051152267625, 11.184697734595174, 10.136976363621526, 22.355849721491392, 22.606984169851565, 35.933990357019006, 25.448954676661767, 31.237366147915065, 25.860590800826504, 13.931530490729383, 14.679282421068567, 16.807190126781162, 16.904190579596037, 5.938170130833025, 14.537443021551567, 6.100005175768481, 16.52519121199241, 16.879938644228893, 17.800749230206545, 14.890129732005159, 36.580106499417596, 9.527775795135467, 27.82546832457521, 16.157381203129663, 28.016687332081624, 18.990373765508572, 33.37747897973894, 3.9339675581417435, 18.668108205203897, 12.172889192249329, 3.3064044193898185, 18.02894055313385, 17.82612105125312, 37.49989448439458, 28.465065001697653, 25.981376645817363, 30.414902585028816, 23.282760264293895, 18.68098995000246, 20.350205231497846, 18.554184957895092, 26.097005982999292, 19.80480073810436, 22.90355963463786, 31.214067536699638, 38.10381381952862, 27.79367706708786, 22.350932451228122, 28.08095990330726, 36.961275444018824, 52.14345931589306, 44.435052745232575, 31.05762163596032, 39.81162367964201, 29.242160702702453, 34.77940993508192, 32.03645832294485, 44.880221203121664, 47.47948984600554, 33.737418828330775, 15.105817268889302, 39.09949697491897, 26.5622539099909, 15.460670311665691, 27.627399462274223, 43.23502647142659, 45.84480183826313, 28.860960125135925, 42.33724882716786, 30.580058989520374, 22.389479369897536, 24.238463676449967, 37.3300488533793, 21.39046853654979, 24.734936897630394, 36.08952437263411, 41.65347932014139, 23.52619659545169, 74.89009486538292, 22.49215972873323, 36.59436421451651, 26.073569618471566, 26.128010386715925, 40.40251563947712, 25.19702493990995, 54.05316120121057, 44.300788846975315, 25.47500893484883, 47.05855069465467, 84.66769695955522, 33.73770267332554, 13.175421994052398, 56.75361613684786, 44.791465506871134, 61.36775894476267, 83.2459045756954, 47.5898863376554, 22.60570233876297, 27.064134746156586, 63.875877337450795, 20.07714119423768, 29.542281202384395, 33.614485326828515, 37.769445071222215, 26.787005757773475, 37.21565932894207, 27.934172178131487, 29.22178228684888, 2.0751047477922664, 29.526035673948392, 26.883026550475513, 44.14301767731639, 33.01417104290632, 41.64303852497619, 43.8595224298806, 74.4530390492749, 11.127143062008779, 28.519188652215128, 25.521844837747164, 30.508168161404758, 31.398115959648017, 6.911715885180866, 34.22849759031588, 43.181508509205024, 56.436588693911695, 47.8638915251941, 25.02464793176774, 34.62025194880572, 52.79024018816091, 24.309916353669035, 25.669261422625066, 40.81070177262842, 50.82374368520575, 49.101143178224206, 23.979108084048303, 34.8084396994558, 59.08239364149227, 42.14859816783506, 107.77373779510883, 93.61631161926232, 22.246956308289388, 39.74089679449532, 67.9301783131882, 6.018565338014501, 4.227731076819647, 63.286549972903344, 39.05056787303829, 27.720058273293336, 45.17593040055418, 29.7334769630882, 41.6418300183195, 34.18894562360814, 109.28380248632541, 131.95530835198375, 40.23701857564979, 88.73820844359355, 27.47767129296826, 51.95570631852334, 54.49735464787313, 60.195026709347424, 5.326197818153321, 69.5767569592985, 95.81562472614218, 36.46379725186094, 46.349326574864754, 80.27813636765768, 86.06216277528048, 49.21084612219148, 45.41911221303484, 35.34600228571289, 88.15948414351563, 55.65612664397696, 37.770848011795, 59.09916488999758, 60.434574236267636, 68.97262986970173, 41.97465256966744, 67.72988363633175, 80.13162195976533, 68.02642599903261, 34.86600098688959, 27.18047289687131, 91.12743628632232, 51.10995871382738, 32.24630924969706, 34.9303956227236, 33.81074396048691, 67.51167373204157, 55.268949989315715, 71.3291788462162, 43.30682577186568, 72.47913094684172, 57.2261619578533, 55.24446947349048, 67.33678861462485, 53.38107710319231, 56.1600423797008, 32.426878041261446, 43.917948859585245, 40.51501321913324, 33.29034332820136, 47.90265295542494, 37.990506381588744, 75.83916940925292, 121.63215768224741, 52.243890064970785, 33.12759409211635, 66.97831455862463, 36.563182801908134, 46.052935488960415, 47.52166129830149, 40.88013581914411, 63.76580333146094, 176.1919220991584, 72.1704125860895, 31.53983180827673, 60.059066770294024, 66.62656716085642, 68.43092635744054, 65.60199566642638, 29.96289327355501, 47.50456615914595, 71.27522159701036, 75.36717338574158, 87.17231901364588, 44.128509865460245, 66.14495130472183, 160.63145422606172, 50.73169937378038, 47.59794916501063, 55.61282717375251, 74.21060649618597, 53.36745302637591, 35.40625573566719, 45.33327976921068, 95.14621927745216, 52.787628691532994, 42.18204140930021, 40.268559684392045, 72.51705165693174, 37.62895464175633, 45.328101244839694, 43.36345160945231, 111.64427479707956, 88.12623222044182, 40.771781258184404, 69.27046496845925, 48.92427962173413, 59.58673025517194, 79.68151812635332, 39.96658086541624, 43.3599582637009, 75.1834742536644, 80.26736795242358, 36.193479063358254, 37.626752199746214, 48.1476955499306, 112.82978880646155, 57.59771857600751, 76.90502063660483, 42.01725354791363, 45.81796000166618, 53.30816397472649, 58.55423900908216, 126.44882457644441, 39.235332107093264, 92.68399041395773, 41.67898426800813, 81.06697674118307, 61.22728960658374, 48.269992142266965, 93.98757397871562, 72.27937442970622, 44.61027591814251, 84.6396882920093, 32.7215310510083, 78.50838060916526, 55.18951241587362, 32.50360519951716, 32.82680309844028, 36.26138008526024, 40.29556514335309, 102.59812976652023, 32.14323686956024, 38.076745324145634, 59.836102176143186, 58.347088794270064, 37.20332623153712, 93.19800126844872, 51.355321939904975, 36.53612752494101, 66.54858964446099, 114.11789776399172, 65.77371832249973, 34.28138388798023, 97.11512827830578, 68.20751849643258, 7.422730017613394, 41.473754097199276, 123.45714330887826, 56.55602165346106, 53.833964778095975, 43.33137734837796, 30.054211186419945, 35.71723651177029, 69.53166086206971, 110.16522975410871, 80.38039884469207, 68.1266276766221, 56.98959617303147, 65.26106981622164, 50.39307944358708, 42.75951758524224, 72.83765892829724, 117.64831968619175, 27.334940341592215, 63.605639254255166, 34.767423127919805, 42.57732696300727, 60.87204439076142, 46.02166354455352, 50.532970235683834, 54.37041699829503, 50.32555831170402, 116.14256167005381, 103.18358213171702, 78.20774134468627, 75.87579549688228, 44.17132668439172, 48.82858648151848, 102.99749448110227, 51.561706382204996, 102.09583310033047, 45.83232287091819, 90.23358219696907, 190.12420632933782, 108.81597681270222, 63.440779144038686, 112.99380419301139, 43.79123127959885, 57.17820499197508, 76.62627053083271, 127.71808248192158, 50.70140570391886, 84.12324876512868, 52.61714703449814, 64.37969058931664, 60.78676174202366, 70.1445213932972, 127.43541138451803, 97.68648192003938, 48.91285847408384, 45.18360210323499, 70.69659474074552, 128.98810227239406, 83.48887295616922, 48.478179283397566, 70.97567773784603, 45.53738155999329, 40.65122985520618, 66.70301818692806, 110.54731992392696, 53.80486338641202, 64.58641245724502, 50.597116053721805, 9.303251129525286, 46.29384252279383, 53.15285309589463, 35.45686179463765, 43.457207102697275, 73.70183436843134, 44.54662661669924, 43.917286176719, 53.06401543306296, 50.13026153334873, 44.83776537508412, 80.70867191205853, 40.48156261094878, 40.51136671841389, 69.47312252346836, 68.61627632933379, 72.41926344979089, 58.42481768071739, 163.57091482253392, 60.95988718830268, 38.30430083995594, 52.86511077229297, 49.358386660887255, 50.27238794785054, 120.78044090808302, 108.58907467765023, 99.82243649284146, 59.62663807613734, 81.39952915536477, 40.34281123896335, 49.166647534105365, 66.76053638333406, 42.2861744160117, 69.69598443775283, 63.54258033184227, 82.56818461407558, 201.1934762685023, 59.22299927167472, 97.03196364537139, 44.42678371887398, 65.51805279660802, 43.6916516165665, 7.876239327874344, 51.00832957973886, 40.48888595087546, 58.6207508655024, 48.85353985773897, 30.37036561426981, 65.76779014836639, 69.94188169212495, 62.10838583016699, 142.64278055068874, 126.50434429997325, 51.74834901207164, 159.0239956879525, 43.063117734657936, 61.06741112044409, 41.96986571267413, 46.92414635513906, 54.199738001614506, 40.62458645650322, 107.75295039270334, 55.146415537890505, 42.71956643683575, 57.82045367467328, 61.40072596574204, 78.07961013047722, 8.002073287825855, 79.73566944314021, 50.135750961464794, 158.80384877955004, 65.03939829446293, 52.21023942264613, 9.891564766121117, 60.76418889136166, 125.28742126053587, 87.53535857473257, 47.81065931857046, 69.76076594191005, 142.76677685994386, 6.4429943869394215, 61.558244290641056, 93.94101509735032, 78.61185245269182, 76.2495890092159, 89.76745495357527, 58.371173512372174, 100.69852864313718, 57.572222674047126, 156.93237347022728, 60.57814109507198, 68.01671186840669, 86.92298689761186, 49.999924284582505, 3.6194857678152914, 62.4567783836184, 99.12892619668548, 55.79688620343368, 65.57389207409595, 61.43189792937166, 53.708326773745306, 82.47419282103041, 63.510405585859566, 121.6967859450771, 80.7303938365853, 44.24490203716206, 45.74303679033562, 6.954349218960806, 127.54392845745558, 74.73896598722457, 103.6809457527177, 134.25929618517432, 74.7005847031207, 89.06837790394309, 67.44397801167352, 54.9161303436148, 65.3331099253395, 36.93728008724174, 157.49172350477974, 3.320324638262779, 19.887851905886897, 107.0909247235043, 86.1286129846891, 54.13274541963039, 8.124816084118752, 59.377641351493445, 144.6292321798034, 92.79078733945943, 59.770098662490696, 45.66379178648152, 64.83387048833423, 88.37261094002339, 124.89638265265437, 48.829428101713894, 77.12265521531097, 14.72488296021485, 61.88136202906474, 80.2104649784251, 176.4906540422545, 42.52375953579724, 37.161647376056344, 146.53574169067946, 35.43559920361024, 63.88475754778976, 153.18307902092172, 76.4610047714662, 70.75341757240989, 50.68552258426121, 94.06547815574373, 80.4329669902859, 51.1881258864475, 54.329003056324574, 96.69236097578059, 38.488853390602046, 54.773034681078556, 56.118457661388945, 71.84061385794674, 74.510864365018, 139.60363021689102, 47.795184092389015, 122.29341528659135, 140.68143458891842, 67.60845346262673, 72.21447557160755, 101.26670190443937, 101.65890211545536, 60.85349461843634, 49.96797075780765, 61.58433768408157, 161.51829626682505, 59.98435844548743, 106.21143730440825, 72.44530914565792, 83.31655831271054, 49.04977535146117, 81.70081926714282, 92.63357668911823, 85.62662660927282, 92.35601037109002, 79.68006986784447, 55.84282123434061, 37.341934613517815, 151.381665878903, 90.78058533009226, 68.95601739738211, 60.1111514649557, 42.94810913655749, 67.6102028410984, 48.60675691704262, 69.17498391348612, 44.52448508009105, 285.2149299288467, 83.77165914567678, 134.2690309363386, 67.10252593532988, 104.09816788621121, 97.87430549733548, 48.37138841875472, 69.94290291816304, 37.672320429285946, 61.31596639594565, 41.893369514485975, 88.79232784122645, 50.93712264218287, 64.01314211366909, 68.69227219650213, 66.28867061123887, 43.696617424234354, 376.387302694095, 106.44918109817233, 101.5733488122294, 77.0659867791602, 117.05217398812428, 5.788540073770596, 79.64444370344003, 124.96795844426487, 86.09939454051542, 50.029908969565646, 89.1801360979268, 72.85267679506977, 54.420409950080646, 95.71565807087323, 39.680485314285626, 43.28405986300088, 101.09072260969288, 5.977944845581255, 54.82804240378524, 59.10003995438779, 109.4142849392882, 92.41617666437821, 82.21884024641435, 63.330494750873164, 70.33034697729485, 79.68250819375952, 126.00397170601497, 53.038966063842196, 113.13937736455875, 147.91221663746268, 76.08695686178643, 70.66108746472909, 5.09321129331872, 68.22611282639586, 193.3580291971667, 46.81393361455202, 112.61213243617367, 68.74819783815296, 64.40244972131113, 68.86893580088389, 78.43493707469268, 82.80628952108732, 54.82047903597143, 40.84191846690602, 156.2316375772388, 48.35459218909187, 42.929944937885715, 92.32535900265401, 45.25566666834311, 50.28024603046112, 49.625648593695125, 187.25250326886402, 66.89466836699268, 41.81908728836107, 78.12244297391362, 89.10093229521092, 44.10072181033253, 37.7807211144458, 35.91916015779666, 51.65974260418654, 40.05177850882264, 136.73494670003646, 4.890560089809923, 6.268480233925934, 57.00211103813361, 55.05091442748413, 55.82031809948723, 71.94087820594041, 31.103832480463893, 48.5254073676988, 49.586105883748175, 40.102539640166036, 49.535484898911356, 43.20798435758219, 181.49991929293182, 72.95386795696545, 45.77402286359801, 104.90214333562712, 105.97373556998312, 35.10862149479263, 38.41247805700514, 59.03516859106053, 74.381218064906, 40.86780836550861, 47.26188078407678, 53.13794908359036, 130.56777999275477, 70.3095834635431, 180.3729812638307, 203.44344856006248, 31.031973992046183, 59.87940837701321, 54.22795989010851, 65.67345812104823, 89.96222658874389, 63.11893760548477, 40.2160363554882, 78.17502985140692, 58.44477897930175, 45.838811992260865, 55.47580115513551, 86.29643613190449, 51.627667791682896, 9.115278203284827, 50.705603648879524, 112.64896907080352, 59.05765462024867, 54.41405286041726, 103.75609796433663, 60.30628701057123, 45.14524992609337, 66.50273636671093, 63.14389926496504, 4.2464539022153, 65.62375838346351, 71.843854047535, 51.237488492900454, 71.14370585217759, 137.51071311558815, 122.32663021405854, 60.60238283421918, 44.98048031928556, 51.436300262501305, 75.61843398696001, 88.26207204855169, 50.0819147451039, 85.92141235645809, 10.678421913327355, 66.77130511685772, 97.72302847418068, 81.22866768657872, 66.42395294963107, 74.15256728409257, 84.9203763197804, 106.64670060452721, 393.5277018322807, 53.28123627087166, 35.01169544102557, 185.24726967576046, 81.11449891570548, 66.38740102683255, 78.87283046844298, 195.41731653476836, 121.56293654252151, 43.049817513453235, 67.10427219531886, 103.94726214928292, 110.8873085507072, 61.01932405048255, 84.7129337269364, 42.54501059516029, 148.81424775016762, 55.492528681463796, 50.45191215286569, 70.28976720871435, 42.3787738499349, 96.41731591378311, 128.52061249139535, 124.39678919435795, 34.14271690383748, 65.43046091553087, 90.37170107443062, 51.31077387831112, 5.649563109815661, 77.33963976065935, 46.0861887711595, 51.655603312319585, 9.246189980078345, 53.0698164892276, 228.77990431443212, 76.9770838961971, 96.04809303883081, 137.55167312274574, 133.85890667827846, 144.61941630047866, 6.60111526903193, 65.0991359801277, 65.74477025326755, 65.37347802719843, 60.951127603169965, 77.65690990571242, 36.24236785033191, 48.925775866401324, 11.152690482899217, 63.852764301388945, 99.16527482191256, 32.09925407849248, 63.06783266893791, 54.2825582705962, 62.75817537212954, 56.56683428349694, 126.92154969714979, 94.94712235644323, 45.19821466307805, 112.8993091946631, 69.48587589381997, 99.63945474255368, 111.24062313362465, 70.90774713737602, 40.54355652249235, 4.50739119339119, 68.72612889781355, 48.3874734999174, 66.29574663482482, 52.29877515207508, 35.59062782252149, 131.63933921461836, 82.84098732034062, 55.65837863282525, 57.80975468641315, 145.7124374328694, 53.108577718592834, 71.66398346336966, 63.24017397120852, 47.01890811974835, 47.046764518024325, 67.33888008960093, 39.8681534401235, 132.7019586926233, 158.2653845133978, 100.69807888353671, 59.21811250745808, 5.815769335240075, 96.17763252583585, 50.55145234591933, 51.170235172446326, 70.3149490891315, 193.87702743318877, 75.37980573201166, 142.64338399701472, 65.23203707856537, 66.54249887345591, 39.23095873350574, 97.59278984048987, 64.2819756594391, 53.88252487821464, 85.25888686137692, 52.50614419804715, 57.07281268340195, 100.4131173033568, 88.68351364069242, 67.85235762546156, 47.965378992207086, 154.23166977842175, 37.46367985689859, 125.2196219069618, 47.30851037360253, 50.156559036648765, 49.21776216889888, 61.207546008633074, 92.13896415419501, 76.72732005544628, 117.90560872894207, 142.26864139973446, 61.99196403581691, 73.1335940011696, 133.00973865255995, 135.66444462161536, 89.20370555559825, 53.8960380687581, 77.75898595779904, 203.89474450421008, 77.70927426242854, 69.0337265674513, 54.984508845786905, 67.75414652091698, 48.46134841364566, 56.836898653639736, 77.41985645264481, 61.076002362118054, 66.40463377728219, 93.77267277096377, 34.81203478136081, 87.2658033898553, 64.86753881529206, 48.59871486783192, 51.82535677808252, 72.14510302360547, 76.58777934542267, 55.82508901535084, 76.51045875269028, 59.33678660829709, 79.44712941170889, 44.52592970037601, 54.220371027521715, 104.74360857942892, 40.71758248481523, 58.60731764948439, 90.64655090993024, 57.67923288360914, 56.03143188164165, 137.30310868879099, 69.99537679135157, 174.42699461416785, 82.96490678822711, 91.34576734991397, 64.10741969511251, 68.87758872859733, 3.345261256996341, 179.907737424992, 65.85048224218502, 82.2509363231007, 81.67296197069429, 57.31974415447784, 96.14594698559922, 135.0134253196056, 99.43450873112177, 67.4036316356477, 124.34657365657226, 70.03457868906402, 59.20273512633417, 79.36453432251665, 58.234325845668295, 75.23834697588057, 114.90413842789825, 51.72152475127542, 99.7707285145498, 52.036029055645145, 182.70883601255787, 67.47202265316022, 72.42896651639774, 69.49956542058214, 154.90947487559643, 65.88952174290563, 59.76735184097223, 48.999532828422886, 70.9199777314077, 193.90512636311712, 49.49807145100024, 54.75690298688888, 84.57953080309781, 95.50403921127872, 73.74663105961505, 81.61530325228104, 65.13034821887699, 51.357597567888256, 5.011754827500826, 174.0331649939612, 56.98184359652424, 124.03898864785285, 59.78395428248872, 103.89880615833881, 61.86153425742005, 152.23216624149106, 59.3025638484084, 60.92035098901224, 128.62925190887026, 67.65593410513678, 48.577928258786486, 136.24231281334417, 48.81208584066054, 60.618264096519546, 114.85893178891658, 55.45732929193626, 58.4254343226403, 75.63392550521687, 67.0723313372797, 87.55126020618098, 60.257003405216075, 147.0447744492174, 54.372826684351615, 12.695568058951915, 86.73257581940847, 102.42893776775854, 149.50435117272008, 62.450845579381834, 67.13324650817546, 174.13079702204251, 76.25574318420433, 4.64497913876826, 79.97352359787611, 108.75675635458583, 108.7892731966568, 94.87181930425574, 75.50353072555332, 44.35393131863475, 46.703399472439564, 99.93750833609683, 4.9560550932538305, 66.96243668417303, 51.73453791308551, 45.730214167761446, 94.75863178488115, 51.32515677480819, 54.131103359952455, 63.06422815641509, 53.20700963561722, 8.887285024562074, 67.55762002861252, 45.64411492320304, 153.5007862894795, 117.24906027533719, 11.06918858893216, 46.99002511790822, 37.00469158355942, 57.02804907889364, 55.42635751908203, 5.149294806979333, 59.01039445166686, 95.28841705294238, 45.090048496844034, 43.97931627521479, 90.69688483922977, 88.47596130043948, 86.0857792781278, 114.76515494738338, 74.50362404745987, 81.55509914702486, 41.613203981908846, 172.49351477210476, 40.99360424336031, 50.94704726030134, 233.82356786425527, 76.06724908218027, 53.00492184691745, 69.14355305967264, 49.74976569958764, 102.49448095372979, 78.01581853902489, 67.83295832234732, 53.19728485283083, 59.861985577339894, 61.08436006963717, 146.22106121907248, 75.16220271831115, 82.00349024372835, 65.50502725914954, 92.04414201430762, 48.171905464776245, 44.08680827058484, 83.16083841786012, 159.90706464679405, 49.000782965823014, 117.08564506372869, 115.06205609694369, 8.170788754768765, 79.37444100014358, 40.60768932304577, 45.67297271330514, 34.601068079315084, 54.42832320954175, 86.32429310033682, 74.24266558343541, 34.448643888181806, 64.17963109205152, 131.32319821465222, 130.40231523353384, 64.31447801718501, 61.90160296303644, 66.39812637945796, 42.209080664202155, 61.79066340737067, 65.58022987819221, 62.63820769054213, 62.28169540869996, 56.58776287218034, 119.64385802576726, 92.73619083957853, 147.78547594612618, 145.7987100266107, 302.6161862870121, 64.39619675799703, 117.29647385754608, 84.01715312951409, 80.65495723024272, 105.00005822281021, 124.4646996518964, 40.85561539732085, 125.19457401591013, 78.00920017041813, 88.23816586509625, 60.291040476512, 98.7102736249709, 65.81042736886411, 62.13974962612688, 129.1704436176162, 124.96430800766481, 86.48290573606427, 141.8737618807027, 122.97003106095872, 53.297740387825, 62.41783002139563, 149.04568057191653, 80.38643945166497, 104.66273352629223, 17.60468964802627, 194.5597557011, 77.4329922543632, 89.21435285186226, 59.01608288742332, 65.7254587959649, 65.89718111084682, 101.31820019553948, 134.09575260446564, 71.84302633538167, 58.660626531222256, 56.0092792027768, 63.627648602128815, 77.92995424974467, 63.08963023619431, 54.253954616414134, 100.86049755030156, 67.33898464540405, 88.34741185277771, 63.93365560965259, 421.7697608938592, 57.08446643738953, 92.27596407407579, 59.89589198626927, 64.09920278233383, 76.53266060966253, 62.715748204653785, 49.64766987081457, 40.742685626885205, 54.70704630640673, 69.14780384080592, 60.16546609517339, 89.83339971314409, 103.43826006731823, 111.6723170868746, 62.834093172368114, 76.27254873832774, 42.770651655812124, 118.39225181621255, 65.75403652188075, 64.50924982775234, 182.04344532612325, 83.19147386922758, 96.42132987316813, 5.34829508370878, 76.41746244092013, 150.2853858719639, 66.88318777679358, 77.00716301031098, 47.64827972980377, 51.96209045906337, 215.4913473756313, 123.35043763372433, 125.71919262480218, 58.06832511162587, 81.44471256935984, 58.251332400805666, 95.28549583126933, 67.59106777541054, 87.53256776467508, 48.6405526598399, 66.79054489891517, 57.2868863836932, 78.30546094235245, 64.4742865632186, 113.36491701677828, 38.435368009538394, 106.05359777445013, 38.698997729359746, 215.00796052240125, 130.6327398361152, 90.9945829146069, 42.3079697020704, 50.11538083985591, 43.44658099673528, 54.99930640731337, 79.03700934843505, 95.3425672433275, 100.20020556364122, 47.16689894856125, 58.18921538131129, 86.88203386854954, 62.221561839680994, 133.53419937550976, 66.37252823105949, 67.03824208785453, 59.84478062324471, 5.110840100822133, 116.47158906202603, 112.44249877051345, 67.09399975415893, 81.56174882955503, 146.2395251275245, 43.92939297726725, 64.75332015152135, 81.81735147430278, 64.86229531692501, 112.37382249069563, 144.20452486567945, 124.55434437848236, 71.25570457624238, 73.88393778682669, 68.15973693532236, 100.46494651587649, 69.9370028635141, 7.676925463047456, 60.27244801981419, 66.3017892942477, 45.692397285666964, 62.39521580097098, 101.52790530971136, 108.4206013323575, 47.30868110606353, 105.72088985980892, 63.39109966093222, 43.51985284094208, 46.82490176164665, 79.27657540218293, 70.67316675197817, 119.79541093057054, 82.76898028305081, 81.40741130066105, 164.8195361483246, 67.18140289769204, 61.01479139868579, 106.3278669444957, 45.9602111484638, 55.55400087317266, 159.01721252274064, 34.036803801157625, 94.00570760957613, 79.81359187407827, 52.795723881561415, 80.59613729937297, 196.37715398509508, 92.95431508641599, 57.69414389820593, 86.8614234475992, 102.09007424114144, 67.70073020941106, 114.7127629498697, 142.0405679653425, 138.48493076054766, 56.717339082730334, 37.81082533247639, 46.859326487064166, 92.46114148849696, 57.87793398055032, 54.22487244891232, 68.40966818709725, 67.88969741105261, 57.48411811334175, 72.8223784991321, 104.5503831999453, 190.82291345634428, 50.92123943965672, 59.20715288623437, 8.838093184972669, 126.51817737630918, 130.6644782199053, 64.60531608785041, 285.83353917795574, 76.47297029241815, 115.00517467991483, 62.39256157066704, 63.35445046848342, 80.27648492498659, 64.69135452883572, 176.02714327891525, 65.1950823344154, 58.35716743986763, 18.365357383530675, 58.20456796152924, 160.11311461877173, 62.067099663457455, 44.449575021041554, 10.945962644343838, 140.57540244277007, 91.76728957878045, 201.44014919336277, 120.62447598187465, 57.14041395606027, 70.43511590960819, 59.10223697775718, 84.01198955489203, 124.92447998935693, 84.61608754534765, 92.02942150288126, 46.413475059272606, 157.73883744021626, 97.87105011412552, 64.04595875610292, 107.98153258923476, 61.901329582330426, 57.551217121680345, 160.02844639296933, 98.67749112025135, 52.87626847601529, 87.7651771723226, 11.79993477769866, 81.5814971812523, 39.82404274116304, 108.81395343119381, 56.722405747698595, 139.2249429418424, 100.74386277485422, 80.84760384998283, 65.9676776425847, 318.6753277915304, 207.50309116973582, 50.35894572990791, 51.836492381418104, 74.3484247036523, 61.51454422957621, 93.14726578960739, 98.06614813815169, 249.7809405194368, 104.83392854213838, 60.04944732470142, 55.72756815469457, 106.26022053944727, 101.03953660871194, 43.89410322994261, 64.58798888837183, 78.13911542526725, 53.144226315149744, 119.51058468978651, 19.809693939938725, 49.28542383220379, 54.12312949725932, 45.977703251835884, 69.46615403332103, 54.83280945901528, 55.16707460208964, 111.03187986790947, 72.87468018525021, 64.79210740727233, 82.59065938490416, 50.93518772781231, 166.10081355273098, 114.048716004773, 57.153205828123355, 55.43647267517801, 55.632203258712785, 95.71556944470134, 81.01911218385705, 57.592087546731115, 77.33951016850756, 57.68690649618872, 58.182621801133735, 428.78575277483515, 58.12162298126638, 119.77548511329516, 63.84737871093975, 21.41148536547889, 73.95265755880332, 84.99736259800721, 64.4987372346212, 52.5329641851633, 159.01936769078648, 127.52379093011496, 62.82830250068585, 62.4057499059361, 78.26171918702522, 67.33137894235254, 78.28269644565604, 89.49669576758208, 101.49897191337921, 69.56327299350448, 59.70074882559865, 95.73305606472955, 62.67154374799424, 57.08346402457809, 190.18442494234387, 53.03628982911191, 66.14941735331536, 54.247962010817034, 84.93035730584297, 69.97760667239578, 115.12268153893713, 50.48997989857993, 70.07078950300937, 11.461184758724286, 123.71269798682741, 39.112658222783125, 41.85051452237043, 78.92386823016915, 91.30831055345888, 100.13626861671605, 64.51844032964, 85.78354036684144, 65.09265800996448, 62.4142054888792, 167.38080883160504, 61.48334025557767, 44.78825221268514, 68.48619819384636, 65.30671151989593, 70.50891357498905, 11.93743216933139, 62.68558000519219, 117.51516958758565, 175.23580996059528, 128.76563756090235, 20.644396472542685, 70.38298694501754, 89.7303910458599, 160.20310316210643, 66.6308615554799, 113.91979283532942, 175.85617550669798, 153.1802272444743, 81.83452881016693, 74.22169427131277, 79.53902973122074, 55.818864048763835, 63.888078341312415, 54.318096109794816, 68.75964190702241, 134.81652324895754, 86.37942090251632, 72.55827769870551, 321.61047417943627, 238.08846064911322, 118.96538807188392, 79.36134261765844, 64.75323746152159, 86.74217002495011, 106.84109916498083, 298.71779181927184, 80.76557671795486, 90.96633644551572, 44.25309654311588, 94.6328849629521, 99.5511957128112, 148.62674372878442, 54.122537317460676, 96.50408804790483, 68.5177275917231, 61.423581514232914, 124.19122640134825, 97.53980943497156, 127.54371545696044, 157.79584342810494, 89.88933648870021, 147.8142469957409, 13.193402591774873, 66.72858232152862, 61.11832543234466, 61.09172603155124, 191.4949754440443, 184.04466994032927, 64.55471953187232, 218.6980999845315, 72.83623549479601, 75.0137783315003, 55.917996463768496, 42.814047386662224, 106.13665009894271, 58.8258837736369, 78.29878421184388, 100.84317053021333, 161.0022851829713, 182.91161461463153, 112.46386076988735, 65.21051892480207, 73.05780210294924, 90.87578257138748, 101.74341027476272, 21.005515500691107, 171.95311615840484, 34.999437894509974, 35.83241197495834, 71.24204710841732, 69.37048942692749, 22.179599364818554, 165.81325686292496, 50.94519471515643, 262.7928701829738, 26.08334604007221, 73.37916819918098, 95.4353485064168, 66.79634197200119, 75.00195267543408, 60.87540522777835, 63.21600261602651, 80.18431548695928, 49.78174498049161, 86.38826013257926, 47.83643293673504, 41.543386044038165, 96.05298956913919, 81.15293610232115, 117.40489713650226, 84.81676183106798, 126.66079512538192, 108.4074445530251, 91.34856227238089, 47.072362278403794, 42.448445804432595, 54.97303362377438, 95.7448748038901, 11.22065379461902, 95.07016888311585, 71.36317497376459, 60.88624180956347, 189.56896950381088, 49.98054012396038, 64.2019312886841, 78.17458977098497, 94.79805892116592, 40.00012557380532, 53.93023583721238, 180.83746939406092, 14.132778195501698, 104.45923020293989, 47.60304267532337, 49.04848700681943, 134.56546323821433, 92.4341104597978, 112.77908824793835, 74.55244263763092, 68.77572279484637, 80.5564161001921, 66.44649155339326, 126.58352930762587, 63.54454</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>133.5587022781372</v>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>104.9407483050235</v>
+      </c>
+      <c r="T52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>[93.60713195800781, 306.6662902832031, 117.11548614501953, 334.03717041015625, 58.29177474975586, 134.85992431640625, 61.894927978515625, 246.47885131835938, 60.06867599487305, 171.1448516845703, 305.00653076171875, 125.98622131347656, 75.46343231201172, 62.699195861816406, 110.79598999023438, 59.242313385009766, 167.4165496826172, 102.3429183959961, 101.6876449584961, 158.29263305664062, 108.35276794433594, 55.15205001831055, 75.88681030273438, 88.95027160644531, 74.19091033935547, 77.25517272949219, 111.66972351074219, 48.04563903808594, 462.73638916015625, 10.808467864990234, 130.02572631835938, 66.4122543334961, 77.640869140625, 57.26392364501953, 306.40020751953125, 98.09002685546875, 98.25284576416016, 89.3698959350586, 45.1678581237793, 111.6008529663086, 12.534730911254883, 58.74909591674805, 89.84380340576172, 178.40432739257812, 100.0984115600586, 175.0521697998047, 75.38628387451172, 79.7729721069336, 73.08482360839844, 58.634490966796875, 101.37752532958984, 60.73042678833008, 185.29714965820312, 245.34068298339844, 111.07121276855469, 140.95755004882812, 80.1775894165039, 90.87195587158203, 174.5841522216797, 224.38755798339844, 55.73104476928711, 507.6900939941406, 72.56190490722656, 8.404740333557129, 51.10372543334961, 146.89773559570312, 78.6078109741211, 55.226741790771484, 149.10739135742188, 269.34637451171875, 315.3792419433594, 81.89315795898438, 146.43331909179688, 221.35061645507812, 176.78565979003906, 83.16874694824219, 383.03472900390625, 223.47206115722656, 229.09832763671875, 76.16056060791016, 58.8487548828125, 74.45074462890625, 100.78097534179688, 181.4640350341797, 59.03806686401367, 252.2882080078125, 105.30601501464844, 84.23223114013672, 651.0170288085938, 127.87748718261719, 42.45246505737305, 7.461400032043457, 92.53364562988281, 127.86873626708984, 112.69293975830078, 169.3063201904297, 92.68072509765625, 123.07301330566406, 101.37115478515625, 96.94420623779297]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst00214</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 06:01:41</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>87.85169267210608</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>67.04693261148985</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>104.2089676746611</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>4795</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>[0.9307515971243785, 1.541087283969086, 1.9476840864162939, 0.609657316764484, 1.4193136445483463, 0.6567556558924583, 1.4103143703053997, 0.4475560977714044, 0.38553487306247547, 0.9296241955537997, 1.7748852121285565, 1.72214856671768, 1.1192656987972867, 1.249478662305523, 0.7644384381112678, 0.6585971701943899, 0.5233498986442064, 0.5230420235554072, 1.2587815053724853, 1.4919287474789202, 1.2043552647478533, 1.218187234729192, 1.3479398457642668, 0.7115299492629444, 1.3408170841383036, 1.1853127071972862, 0.6690622980483024, 1.2445400055634823, 0.9800427179928052, 2.3373480031077722, 0.8960307444709379, 0.8778507912927983, 0.6924244309748506, 1.3091256814975334, 1.3267115186799643, 0.60095415560067, 1.092732159757896, 0.9180056893744589, 1.4409936115582835, 1.609763630925567, 1.6301345455553198, 1.7505939844756355, 3.3953805615667303, 1.7257133362325956, 1.7955324668880723, 2.0183843906473737, 3.0521207144111893, 2.337306836110346, 1.5785889470379482, 0.22301937783894574, 1.0211510175785656, 1.5853029561930447, 1.178107336219869, 2.6259330679522424, 2.7186393189568423, 1.5085714831447166, 1.9504188816214896, 0.671484753092623, 2.125625252425104, 1.5085986001271914, 2.096826282999945, 0.803189183756675, 2.947783929358203, 2.144432304600102, 1.553837029359036, 1.9244218427596715, 2.0974237678126717, 0.18003826362324427, 2.0516468824286025, 2.8893784633117234, 2.189385532732124, 1.3151454674753817, 3.2818169552312844, 1.2460770796499834, 1.280490672374502, 1.4907258673311625, 1.7650942268268814, 1.0719523632358543, 2.9539525785155387, 0.39875468636318423, 3.988047241344027, 1.323218030455267, 1.1673095630226773, 1.6232462543229906, 1.3158018316741762, 3.971688698917009, 3.0466841092236434, 0.3422285318885405, 2.518245990965293, 3.2487950571000863, 1.3874970919977234, 2.4825059883154763, 2.536621930449387, 2.119330462274465, 2.969757596454085, 1.7769096843330825, 3.638387736499708, 3.9397310206958203, 2.1068951247045984, 2.455488922634394, 2.7550206108051545, 1.6145031159288061, 2.367707115979653, 1.3703405352729265, 2.0905108131381644, 2.981833790284511, 1.016545249424158, 1.9251212294321265, 2.226498690331356, 3.267565467806502, 3.839941792539075, 1.149442000096305, 2.4252317575416513, 2.330678540972556, 3.7386744277340043, 3.9715538924800073, 1.8402926829798332, 2.9352343457905, 3.1970230161322752, 7.58777171322421, 2.202019088407834, 1.9297089853993377, 4.6118473482842095, 0.5115624274566667, 5.43259143825825, 5.77676852325588, 2.7066144608173666, 3.7837069270932844, 2.216309661096726, 3.293040397869488, 3.1257888846006963, 4.6710564299329205, 7.3838423910758575, 3.2362655599582126, 4.602402857761743, 5.292110833469994, 4.650608843943067, 4.559310980301597, 8.603468387832615, 1.9380418206798655, 3.8660446487887654, 4.439449557618157, 3.797050396729444, 5.700766009605458, 2.2484336442105373, 5.751121412542625, 2.221196727771105, 3.5481773300547923, 4.180693914477461, 2.1597223141601014, 3.882390912987609, 0.7546797279219867, 4.406342099762679, 2.7160424734411683, 2.5028872978831767, 5.890906670836395, 3.9630606489103384, 3.258359765184622, 0.8213229944235813, 7.55366588317239, 8.334818253665194, 14.044511611793986, 8.03949134221256, 20.179919395920752, 8.897170780953084, 21.060476840176065, 6.711996365955258, 8.419157769453502, 7.824054008584268, 10.437057047128114, 4.134822301073763, 3.7103416391176647, 5.867303819024335, 6.5379308817560675, 6.369153796383323, 4.507105227891444, 17.719587698745876, 14.024815089123743, 5.493781033503976, 6.316555951565572, 4.0809264189474534, 7.1043686197088185, 6.1160891001117434, 19.311919400084463, 7.529732878795271, 9.816759879340019, 7.733983449821657, 4.4137025639139855, 6.506586688870208, 5.314717953667567, 5.179971560067091, 6.243704848268668, 14.862388272306784, 18.58091605581896, 16.154215876702743, 13.818817565147492, 8.42466422115115, 18.543715052966334, 9.235161400356455, 10.373883384566524, 18.86969944777893, 17.195039733877202, 19.759062357179303, 13.290323165503715, 12.253166886828076, 14.219907491049064, 22.422992612912296, 10.93388608044417, 9.434153377497164, 17.44786842051909, 15.33285425101143, 10.979069638084146, 9.674227347015307, 6.227376826074477, 11.817652798071716, 10.516621770525804, 17.181759030811758, 18.735553078175414, 13.554359604713614, 21.13685793641821, 3.8351305380832748, 16.490544620526297, 3.540468970225927, 25.57510469272413, 19.031243951352117, 23.48957884407211, 16.30330190791164, 16.52915301068577, 21.949762080008288, 22.701009719092067, 12.441561668829351, 10.211261404158817, 10.000025237926778, 7.33200480610435, 1.8951489297455666, 27.59810990829101, 31.79328428421515, 17.548040477211014, 12.032041538956962, 32.63013433909962, 15.366795078753293, 7.170240492933708, 15.487324360695915, 20.30455942097752, 20.924704301800045, 28.11618636201432, 28.66104519186694, 12.266250405781316, 13.371013577831384, 26.19278666356908, 15.683694068489165, 25.54375035029043, 7.3066494358218375, 19.045683067567005, 23.332015583575206, 13.51979573056596, 51.484952955710106, 47.140497431189054, 24.423549296248133, 32.893070413116774, 44.810305314897136, 50.29283685164397, 4.154410485231698, 15.927353076882033, 9.190941706823168, 19.4583074868293, 12.292467040879863, 11.40382774908159, 14.602005905360373, 34.198702585217035, 24.12802170392303, 19.491578495312982, 16.857107086488355, 29.49340095412361, 36.34534734545042, 29.600436862728518, 47.089277734165236, 29.1439722506668, 48.076877036286604, 19.288254087646155, 31.131214956095874, 28.254769452114616, 26.497087340072735, 26.757322838237624, 39.70118264828931, 10.633331606687289, 52.49354753971245, 5.6526650788898465, 13.657259729823043, 28.729693659325118, 31.6722845890086, 29.57805426687395, 22.38551771078051, 20.967210665753253, 50.45089654849414, 20.960308599279884, 40.21293939314967, 23.097725285972867, 17.012893884534236, 26.297648218623443, 42.28374891560404, 36.50407004687371, 30.709033560911276, 27.34464967513695, 15.337290762997627, 36.65356022236748, 4.29736505695648, 22.614347444363016, 42.69311694252934, 29.042706479802888, 69.9584776264087, 3.2836117846567814, 39.80574149005928, 25.426106996902607, 43.535633308208844, 22.704426958672418, 20.975486177678707, 55.743449364795055, 39.799603141424235, 63.39662916490663, 18.40982456478585, 2.647112040874927, 40.45944844030907, 34.18323012586173, 4.578102305364208, 23.149549023444656, 5.162617554994013, 21.109172322302364, 40.98714514545532, 46.24935476585298, 29.488618813171005, 53.858447186520834, 88.10645812529337, 56.53594728057043, 3.394693094716162, 53.761458001301555, 37.09520373413942, 31.258756527941003, 28.91282199254831, 20.768869718680712, 36.83943466581584, 42.8881825938485, 41.78680062057403, 5.249719281929954, 37.543992592093005, 37.193282654485415, 63.751653121994764, 40.435071345145595, 47.08628651467328, 26.492122230791708, 32.6130635765671, 59.09457625995066, 6.248631518885214, 57.36454839882278, 24.01239212323398, 28.24602826193373, 56.055498362396854, 38.493835945714245, 95.9894492329377, 30.16801320770902, 4.079736343305793, 30.069393996398908, 51.98432677850438, 38.34362477811743, 59.33806429324127, 27.65722414159275, 29.948550104853222, 38.57954396683502, 43.50951873660327, 60.31234207964966, 54.74740148005805, 37.47807013568497, 92.55098194724438, 48.20538720752182, 50.73942666245679, 86.1723931700718, 39.939636110679, 85.65440901352173, 32.15302556466991, 37.37479660780086, 65.55349126928984, 52.52574532351515, 35.90977765414096, 66.27639160468432, 44.13116374861013, 58.98802965479609, 67.19019687234207, 42.21732693295019, 75.58532175231855, 47.10457669572965, 74.15448558129293, 52.45036789803169, 41.46575728697655, 51.831536502639146, 51.49538817737444, 41.994563985925055, 44.178212866329915, 34.31799937177905, 45.4361339966889, 25.831435041056967, 32.92451438594728, 13.465930724495202, 81.69677608296041, 32.00040818767724, 49.545256301617286, 79.92447188852401, 29.256287402130006, 91.32271704026753, 44.563684380150015, 42.29914486354282, 52.09308671721831, 45.486025696249456, 52.88301045153307, 42.00705299030741, 49.691489075325194, 30.452842214569017, 65.60542817219302, 64.16718242590899, 47.25955998868055, 33.72957674420601, 75.95489718756824, 36.87257586911305, 33.99753641349442, 70.95414321350113, 61.058926116166234, 208.17803185764822, 37.63402799305486, 45.49465198460686, 39.12560665246367, 80.92438777671882, 113.28050239121224, 44.05248728010823, 76.7343877343577, 54.609196100170905, 25.76185903661254, 62.07962824801873, 82.80471083329854, 46.905567128330915, 35.704704169299134, 60.08701366730725, 45.21471668922558, 19.16767790666129, 53.70813266912269, 53.92453731216785, 35.672385863780484, 44.12695527940346, 54.10496730687892, 35.00039205930718, 56.04361907434365, 49.186668570926415, 45.77355814245593, 54.972385432501234, 59.2843449257045, 65.74714199733381, 101.21443407283455, 42.92572027278656, 6.8145580295622645, 22.243880763546965, 54.64659975176358, 6.479319924223309, 38.366191628550375, 33.94553355968703, 34.355070713829704, 79.81948876249044, 5.387713268333226, 150.17845630379637, 49.36029722250827, 36.29731395179807, 38.68533204606333, 4.895805260463403, 41.387476365505066, 4.394983629274903, 112.10839173193582, 29.415463250596684, 45.08338511731276, 99.64799867641835, 85.17998507086568, 23.080486082017455, 56.8617613748574, 46.91614953248807, 69.07514549704804, 56.31358803631817, 48.82016433543418, 64.96178291544146, 40.54188300526624, 47.394767582351754, 40.21295237521039, 46.95309953018124, 71.32636573223283, 34.02089922006422, 34.25314338962761, 5.826241917852109, 7.522162095332692, 68.70864056582967, 47.89007088545451, 57.267729009113395, 71.37785136189022, 36.4696606164705, 31.842336092307093, 43.96298834659793, 51.36244052091437, 76.10833083084101, 92.22051281545183, 97.38729965660767, 89.84715279039551, 66.33516352665202, 48.50959534681231, 35.481208018323585, 55.749716552608625, 78.96580235509556, 53.171493387905315, 75.07872351940348, 110.69843520092361, 72.04799196109826, 6.935963194233427, 63.3752488347127, 44.553427345012224, 49.987481849082585, 45.4354941057613, 79.27989341884286, 38.17254368543787, 106.14616220257307, 63.884776898949, 57.01919260852199, 52.78408798999247, 67.90230421013315, 161.7615506150018, 69.5653790508275, 46.2403206614873, 40.63220917627753, 11.586894361893611, 48.1000692790619, 37.436050656145504, 105.12324498387048, 75.10964262845137, 57.48052001367533, 58.67292382800493, 47.325404725058256, 61.70024365017493, 58.26667932592419, 64.42465742323228, 55.59080303913675, 32.277673359648986, 101.6953254059244, 60.35174107492678, 46.511422849147806, 46.174985178613085, 27.069725818509657, 43.90020793028596, 9.863258568215652, 43.853006361572476, 79.49080514197459, 45.992945860647964, 42.15684426333002, 48.31482282213751, 57.72530499406586, 36.820040965057736, 41.29493133858508, 77.87535657351053, 39.04368119480903, 5.968219002760266, 128.07903378838435, 51.75981691534076, 64.91233854667993, 42.3990753595697, 109.07106315769735, 57.61202914124909, 38.97083889209128, 37.999197871330686, 59.246114340303656, 122.33000060098726, 35.02648594628369, 53.923368271722026, 44.13781665321015, 72.38650532644708, 68.72208761187765, 39.64716214793105, 33.41575991541969, 51.83572449446606, 100.98995143931114, 67.36570121256194, 6.2575116409273726, 37.6834906466001, 98.20650173671271, 44.69547065943173, 84.19848299111165, 16.97248663559044, 116.32266771752438, 31.905024585863956, 45.380312954206, 71.05796370368124, 100.2520791715387, 86.88513021415194, 81.4472920477187, 48.19491603620605, 55.41926739698672, 43.12728769182303, 82.3221540828839, 46.628306050985515, 48.9525992790986, 72.38026947434201, 33.977054307960955, 45.209461909183084, 43.77225580186174, 80.28327301764196, 70.94526754824783, 97.530322667715, 53.101056919261026, 52.82495617137224, 51.0089105560459, 68.24229307569061, 46.578686423456375, 66.6868450899413, 38.07083220132359, 93.02640170575837, 43.598125034520436, 96.971937414405, 33.33172777228505, 51.61155030011069, 91.28880817702596, 148.82943539673184, 41.44332454772114, 36.24593253551085, 108.87877263629063, 60.24540026176503, 41.8449105536682, 65.73623283516748, 58.21032322124606, 135.99730110719509, 75.69592916716456, 64.47174197248536, 45.3302985273931, 76.22169987340646, 57.36868047982825, 58.74033466835192, 39.0764479859127, 37.729863209630786, 52.66250469980309, 82.71578956891439, 9.412019331131672, 99.64703068112655, 24.67323814208488, 48.38614011911015, 49.29300992591621, 5.78299628982602, 16.418086927532197, 85.86404544068046, 58.61937269055574, 55.43901851812425, 19.9516295159595, 55.45242422664013, 80.40020149443534, 53.6390195695746, 58.57004924592378, 42.99176304474049, 64.79109095973676, 74.19525667996933, 96.27016507557552, 49.18826030105939, 52.178941197975604, 39.12901139505127, 71.30020559807355, 75.94658824876075, 46.28247945888944, 84.64086976302698, 43.94385439417502, 51.68563256468609, 59.81432768493682, 109.30742181041553, 99.1528930306278, 42.30772973487042, 62.65624363599763, 33.860587040780246, 53.24781341357873, 73.48013757168727, 80.09857220651698, 59.9422492030461, 5.083865560318565, 49.523228730026815, 72.44936556288009, 49.69849516391776, 45.57093000842251, 73.81348094098234, 12.171663608711201, 56.202829417560004, 221.70787582651005, 41.811480756666626, 39.16808576846314, 61.247786601166794, 87.82416610736523, 55.785708898850345, 92.76962632730324, 81.0661698171983, 115.73988019950974, 53.18335055607712, 71.29512234775812, 94.3125022977522, 118.48827159899025, 51.36414182620702, 48.00011823083353, 56.28396627080919, 7.106088117292754, 78.33320788564296, 78.63516322259544, 104.14100024782778, 105.77291078152638, 21.870289373795668, 70.57918202515056, 131.39990423514553, 96.2710266276105, 66.60031072074487, 68.14001850235438, 70.92614096546302, 72.43375151280166, 115.84551162725509, 87.74973400957856, 6.366337872954869, 50.34968301383662, 61.03762188367406, 132.07154521937028, 32.287192563662195, 10.886042889935808, 66.98283826166893, 85.70747063319487, 64.60592290270375, 90.83705467645842, 55.0946459190592, 86.97695326155375, 128.1796666586658, 59.77327270893551, 53.58625464754049, 69.68705513956711, 42.18151493268643, 73.23000032184814, 69.00721362848849, 43.24565015364462, 7.655154480908487, 78.7073434434272, 25.867770708121256, 8.468170559002417, 47.325740950445855, 59.1454002581496, 11.133638877706932, 59.399192720197256, 52.60374274352376, 91.2113863497923, 63.89207747395787, 80.20888314365706, 41.95449577844266, 257.71901412581576, 87.3254659820844, 178.37255465754217, 34.66254959959083, 79.63766908680977, 71.88289651581987, 45.68039706103468, 20.98579095402432, 45.79421230876656, 94.66971400726294, 36.952383248289095, 43.78748705675594, 45.661972200713585, 42.95616134574452, 239.7126169457226, 52.97931745168599, 50.21944671413064, 56.934023351380105, 61.726197546865826, 63.376673075808775, 58.15460407387263, 112.15027769780936, 77.64961483222417, 55.70814978520145, 53.25499664414049, 56.48160142410649, 39.35285359239454, 48.54329356195631, 49.2433250416747, 63.523108157196965, 51.16332510728876, 60.90592541532727, 46.58450536033672, 3.9404107778825144, 96.32400867148908, 35.86494442329046, 122.71758403271502, 59.34894663808845, 64.05564778800564, 84.53586573367706, 73.99810479205101, 57.89543857152382, 50.32309732472577, 78.56384416814251, 151.12255597595393, 46.06562477742106, 60.62680392244914, 137.35101252990194, 72.52567955957068, 14.244076908578961, 59.31470286508681, 69.56627709716653, 13.076054098136648, 70.81676067964482, 49.93495731942765, 95.13349092334246, 67.60695101019951, 69.63218668588607, 61.13689946582116, 50.79762495900288, 40.713636413788066, 48.030786863864215, 55.09873351041693, 131.1523558090838, 50.347952526452026, 62.77293811253445, 40.75456510989109, 70.58021541970865, 115.93615003983989, 150.22283663928616, 147.11568189591864, 63.61506844833387, 63.475508986345204, 43.46885710040624, 179.16286642283637, 50.696607544008124, 50.483469053477165, 82.33677060891847, 154.95210341610556, 68.17926347086006, 52.3433662550623, 56.74354634642197, 46.44171474041274, 109.89914435866623, 72.4171870210623, 55.15469246632796, 50.052510799605045, 74.82733091791513, 94.94872031358821, 59.471655335184465, 50.64126755122833, 68.46816050435787, 57.46990313206475, 81.86732246376664, 72.48838151409456, 118.79260494198587, 47.483520834814215, 95.14065471549252, 52.894932810731504, 49.5493333870199, 54.37680081135713, 68.55445618659442, 65.64895932613383, 150.98009484846332, 105.88801092139096, 44.10436783308771, 143.4886246889756, 68.25729051997193, 88.67906762602253, 68.07389435107196, 41.13692595143553, 54.448181690699265, 98.3708730052786, 50.77487867273766, 36.82293974965613, 48.62794242524013, 54.289662952275044, 7.6834622356813735, 162.83211088949187, 98.3403287196838, 136.82315033095898, 43.50902063169769, 150.25130835496307, 53.65233620839475, 109.25410333316952, 64.43596196748088, 64.66509459083485, 134.06889163877128, 63.7602647729683, 87.88801628669451, 68.32890786746081, 20.52777860242785, 89.37636816833422, 91.30159694125395, 129.7482608931077, 48.91948425016739, 52.729658579526124, 136.42945798831687, 108.99020950355212, 51.35447679572036, 197.98071867995984, 67.81113237309746, 56.32781375376578, 108.87201724149666, 66.82884267823358, 96.1782320880676, 39.87806454009903, 142.23997851716373, 82.0117911080741, 75.88426739879617, 64.97667230099155, 8.451338044229464, 212.9694480333827, 43.51595389497825, 38.11183542299472, 350.7356130289314, 156.82771551752145, 133.66758153093548, 48.007149150075435, 51.35570547776458, 47.8053953278296, 49.542113625641015, 102.41201536583857, 111.15635919303048, 51.13382305766047, 42.314030926171434, 59.69336153500524, 50.96073994257569, 50.48829296325624, 10.298354293098216, 42.06148952601728, 116.3600331923193, 68.34889021655243, 132.4986171970966, 5.768183736784667, 25.29853061478769, 68.44768548952801, 82.29068443975058, 46.65665057570957, 75.18948168156105, 118.92416038815409, 183.9532683406451, 12.40043698494211, 56.07713863025346, 41.091285960817395, 95.94671481093505, 150.37933173036058, 214.03340305535943, 115.21900240159258, 117.67365397302743, 79.70648264523376, 71.13022811863351, 8.510831137493298, 99.3644535036189, 157.78109560892437, 189.64567524252175, 124.49685958307855, 42.72828114951954, 93.16112465467873, 76.32695783240372, 76.67215724207358, 54.763931709293225, 8.776102014745785, 231.18369439494356, 82.51876202549971, 134.3472643370094, 62.463359277261674, 43.40744945189109, 90.90896011872056, 56.50355474236, 155.02139554811777, 148.1281786483302, 48.58597772932432, 55.63755843641411, 77.54283611054159, 41.36425047897454, 57.63711181094372, 87.91939990142193, 61.83954746164089, 111.13894660212537, 169.61592476708756, 147.93151152098878, 114.39094942890564, 86.1317640163001, 56.94446952502485, 45.74653366956668, 65.61357674597605, 133.46679201640453, 137.51109877227142, 55.44758662822112, 105.30428546289927, 67.161072790516, 10.553420340568955, 40.80402807279793, 144.30214024547672, 90.45831331207559, 49.02949140310631, 47.740054387958864, 54.57246552309283, 98.07390379046502, 71.78286945749, 68.4354175831276, 72.90713958328107, 128.5910241952681, 104.29691481265095, 60.00680601270495, 77.81011717638525, 122.69516387747886, 46.779081394932355, 66.9716927802088, 56.97140149747794, 55.7243765133959, 48.27700070346729, 47.44580294817451, 134.8745693933035, 110.1687487776884, 74.64405682088842, 77.4128630230268, 160.93319948223407, 58.25190170115954, 50.014226533298164, 62.25394814396174, 40.528890593281936, 15.684759812516118, 226.64414001922444, 72.44517799208452, 66.12330155925892, 13.043341228386646, 37.76527051329676, 49.334320038988366, 49.923694682151904, 101.89963985805309, 84.24571346765555, 57.48551955428843, 68.18535441137102, 49.64849598372275, 152.25546035248817, 98.94553502070013, 95.16946613943453, 84.8431072923053, 70.02524138018605, 96.24667731249555, 122.91481566707847, 8.810417400265065, 42.78424168466413, 153.84362344644782, 35.66432944532083, 63.27235268621577, 10.501343777785687, 5.656969844208229, 97.5444830670971, 57.181540736305465, 84.05932077681072, 83.30276981601533, 81.77438297597914, 96.82736591252194, 61.05673465074399, 151.923650045828, 113.25298045257426, 128.95060175840183, 45.01738175527674, 48.16813115324248, 43.53406919418571, 71.05310061560994, 71.54691841824553, 152.81017233755506, 77.58886130044687, 8.652021646832441, 196.89904834923695, 82.90596725726517, 13.61394942986353, 25.800309538826916, 81.55970058236153, 7.095667237414763, 75.1940342792195, 46.229149174833054, 56.89062451256149, 67.53186811136656, 56.143606240669946, 92.8210195779722, 62.023970572784506, 219.3398131725758, 51.575434745884316, 132.38407816563887, 72.51532075241956, 61.58311205714627, 86.35411791638164, 63.857554819566744, 259.59721403039055, 46.90439290931609, 90.41137138118133, 35.90208832413783, 92.8795327825379, 139.4703472326558, 107.04766331812154, 73.44514200391917, 216.22147194656128, 86.25212161659191, 4.458532249492326, 89.65612243308817, 139.63930513247246, 42.44621972546133, 147.74764596692094, 51.9338122061067, 115.68221163912288, 118.63847523093531, 45.82197918560277, 101.07148721000856, 69.81939608727458, 61.296411700277424, 41.66223425908154, 62.013356980999205, 94.80177771381484, 149.36571870266877, 48.896838970523206, 123.02578546232445, 7.1424255909041, 158.71375330938622, 107.4728001058367, 73.6371685250041, 70.17522485558635, 34.93885195614383, 29.230316429558698, 157.25026407330088, 111.96549189127903, 75.80225982024089, 44.607266151370354, 260.04773352508516, 98.35203675461042, 72.56695687700773, 91.46386009737695, 53.376609404826795, 28.537130212238306, 135.77354370218703, 60.37165811332318, 75.60750439801606, 91.05815421283629, 89.68055602134932, 90.25365796481307, 46.45034434301342, 84.14268192311322, 63.214142800475294, 39.33312892472559, 113.23863106399273, 102.42971953265874, 56.71826135811814, 125.25000090084811, 58.992555804979396, 58.12399063316608, 86.21092050245689, 80.32854820589573, 84.41137171452816, 80.79580327659161, 76.17572994619154, 93.85996608186785, 74.92103251612374, 72.86113112127903, 61.44484392103578, 96.21556694968542, 316.91110144522605, 64.56421757909656, 118.48305155637065, 93.95001892326317, 56.97361827168382, 10.967518408302308, 88.7306564992456, 56.50229543171686, 97.98326522003525, 188.726202862695, 92.37203488096434, 71.29287521694913, 148.941340788156, 91.88143571334446, 38.29567973060706, 67.515701333597, 87.04795148144555, 63.95404789127794, 83.90227117690094, 11.31423686036527, 78.07531544265828, 123.24968344310035, 60.23874693310591, 45.61490270878979, 66.17609026119933, 122.10976235118484, 44.632771210142444, 63.66498756747037, 79.19506569127563, 48.3271971621384, 118.25384327420724, 164.02663054149582, 40.677031002797, 57.87776620042318, 131.0829432418935, 34.59950764847117, 103.36369360198802, 99.43708385157514, 42.42375937617298, 100.18285848705531, 84.86286467938795, 77.33159057726076, 79.76050804597824, 17.9804424357158, 93.1601812839586, 64.70596066487984, 96.72255855187882, 74.32074609487645, 76.21541313362393, 41.94581531252556, 129.78682337656232, 72.30241117763612, 45.85779740494339, 16.337960663698166, 78.37862638439, 78.80315974223603, 109.90316928330853, 6.932805820253797, 112.48427790580155, 74.4228129403346, 121.7383115086244, 56.47879759007379, 57.36385830245153, 66.61891203882398, 41.34254678697371, 65.07484010339887, 54.63044851708228, 60.713820870857845, 88.56759638546902, 123.06600457770534, 13.117635495036318, 116.33371364508622, 78.27825827399809, 53.389163816728065, 258.5640688756818, 91.63184977907257, 119.12493298478783, 62.35972296361223, 108.46109655370506, 49.70854314900215, 48.15961248176457, 151.0064442432747, 65.47455866451396, 84.5734694880066, 56.1915968486481, 34.02361092401438, 119.1137906623929, 5.779339254122993, 124.1266860739981, 67.7305952976356, 68.45935751437153, 9.955878761852883, 6.1088276985125205, 70.78646755718597, 66.58532860110743, 64.64531404204074, 66.71542215386091, 72.37358310905225, 16.71057540487546, 233.91674530050264, 93.01653301652334, 159.29350428317406, 49.23574385898224, 8.60218831617823, 46.3057711994342, 45.68089163989582, 81.74187052514587, 79.64667311701959, 134.3226379305417, 123.14431676229354, 6.276214941416323, 57.990199362705035, 94.77845662221158, 10.503422284421518, 89.51981024381233, 128.4690966845299, 9.69915541746149, 126.1793427608151, 55.15525335003481, 49.434896429121636, 58.88496446904233, 120.05084533512199, 105.68272806728653, 56.5281487960712, 209.32172799016166, 89.15717564628206, 117.59503024437636, 75.62718878674717, 13.13173684299571, 106.21434119819175, 43.52739281945578, 59.01512136222129, 15.843848175187743, 61.42722352549383, 104.72784694283577, 48.866645017204675, 80.08636979338378, 60.0058308774252, 182.32318349096747, 70.7578095828128, 13.822213226100313, 50.69569369406099, 87.63425898569311, 56.6782842359707, 75.67070428124131, 46.58984789958236, 52.377831139143424, 70.00116645419546, 63.82577740465839, 43.74785392807483, 112.24033882940105, 58.66899803546241, 28.3405370495909, 82.2093550788167, 65.11160857839786, 58.352868041409074, 82.15135559574348, 52.274185810927115, 10.019025721457025, 74.0815442196226, 83.62251910554686, 87.07706894231113, 76.90869352887506, 5.379682006855135, 157.75545459663343, 58.41525504188929, 79.64596927912835, 145.83374740212452, 65.23482339110666, 58.60599934344674, 48.669051788201834, 113.70003831786352, 73.04648946964338, 87.3536191602163, 67.5659711270076, 136.42019163864717, 82.56493332604335, 104.67156411716076, 148.4688260278693, 213.27290624451075, 52.078292145990915, 126.52683268160375, 106.87912191831762, 53.151567924863826, 76.72446221157865, 103.9940365296362, 27.363367449010827, 70.60762053487502, 46.01858903375472, 92.08730990427688, 44.76642078803752, 4.626766459374778, 119.97932575892924, 57.45813665703944, 109.96904248407309, 94.26400089696777, 83.82572857458436, 74.32086258522492, 65.25643429502394, 82.78144747613743, 217.14253175266018, 127.85017296610606, 51.177220126804734, 9.871239807566875, 98.38744289178258, 28.23664261175732, 62.72755442602626, 57.23790324733992, 110.22084038006219, 88.35855229986194, 51.50555270399427, 108.57534000532056, 128.46136693756608, 55.69153639726567, 71.77367097120352, 86.40176688608804, 107.7456121704554, 44.223976064872915, 69.35964681302958, 57.453506945211146, 105.58924780109044, 72.47059173452698, 33.05023903364435, 56.08115166291099, 50.31483953682463, 32.18331791292511, 71.03232579182962, 145.3769034609088, 45.199357195295, 89.49349345119467, 58.74678111333528, 118.02850681084905, 79.01326082103499, 80.94953441133103, 120.25962082378895, 100.36451871791787, 167.32540979086875, 109.83407403386421, 47.55297295685772, 92.02477713824362, 35.896877084806384, 56.814255494128616, 284.3708262076002, 65.95766476382404, 68.930241615997, 279.87806365591, 122.93060759904267, 103.7672170142099, 152.41284946296608, 86.58329029807345, 52.39420395845624, 70.26034463410409, 138.7227519245404, 141.93891108633224, 97.68992346568957, 72.09486826664694, 89.29407513270067, 284.8554649878332, 5.856235445373345, 42.18945283180205, 68.0579691452187, 53.39524842689455, 76.22584367539378, 66.38965080880679, 183.47314829817716, 119.33090921099041, 58.334347809670604, 109.29497948426665, 54.76153589603262, 59.84482365680796, 87.30733565374436, 136.94153713924825, 62.52862844717205, 130.26890060214376, 92.36983511378888, 11.532562962435005, 55.67637264617045, 93.01090918905972, 49.87389429451841, 204.87926484571528, 103.00635366522799, 128.46780565846382, 103.93214235055281, 66.84575462087754, 74.84232699706125, 73.01193296424228, 54.622655705899234, 84.7116172441815, 105.1076396354139, 63.47013082841631, 212.11147002356648, 78.37452160659257, 78.84495986097674, 63.61737350073797, 116.47452151606973, 50.70545009281794, 59.9134602685798, 108.10986434561016, 79.760435479117, 140.52511923174777, 67.50097886164166, 92.1465005232143, 83.9560582492435, 31.561076961932464, 72.29193920614787, 64.60194053709213, 56.18416327782659, 73.88641464692529, 138.3182174627557, 79.13850307892754, 43.80357244616292, 51.3365557585343, 79.20826077436472, 110.98865406240587, 94.29761568150886, 69.28237021509608, 75.21113621148217, 70.90796366230637, 66.35676353839015, 137.21026506050487, 46.48834063396366, 116.33912280932083, 89.78865031075424, 67.32711741284045, 44.304873933532214, 47.06833108371223, 149.01028147076113, 52.929547140324374, 56.72680739156594, 70.04972318689838, 49.056610467596045, 72.04856063258549, 51.629654866007805, 74.3314845782468, 168.37680837677337, 168.84509607849873, 56.97385933179258, 5.137637841416195, 51.47255650248787, 87.27141533267958, 109.11289758880297, 54.65842092295586, 104.93408821366346, 60.88897848813581, 59.3440716894426, 21.57922555906572, 93.62042401330174, 117.03059560633714, 116.95048621432116, 69.02172177187502, 58.62223018815314, 52.26889631526667, 116.80584469745502, 72.11802635131892, 80.42942299180005, 60.9498377628937, 131.30174445974794, 115.91435101787671, 108.76636615861453, 68.49313881259172, 111.51559694004887, 69.93662423159165, 138.86579703286367, 77.2462363308696, 55.18606378631796, 24.450178949598577, 97.1392453372729, 61.08420967292976, 56.996470181207016, 85.74894505848334, 101.43847691258698, 65.04852404980147, 35.412793169804594, 155.0701715726338, 46.78896087635038, 263.7723618738318, 94.82735452425058, 57.29870244159659, 61.80286017320809, 68.25739991008783, 54.47611616869927, 34.975580948268494, 6.596985131346891, 63.81286131102445, 64.88859021126954, 66.70867925183782, 64.1907266319235, 59.490086507415455, 43.53540020577189, 43.92889879929436, 313.6301124246846, 99.12476053381457, 8.018902567235228, 72.02127034887783, 64.8600417149363, 208.86991638172682, 91.473365839466, 117.65180860245582, 67.1537629091993, 67.40700000366029, 84.0004352734268, 68.93299896325107, 123.87936000827618, 107.16102961529212, 99.73487438671403, 90.4417285395673, 66.68806822776975, 71.27822899485534, 82.21512688755506, 111.33160724843474, 49.68442088887898, 191.4275239559384, 85.5575687571715, 59.43005813068472, 112.23964361100035, 64.12932453135191, 85.40516833029507, 77.28947029858726, 157.41032207973535, 62.902214209234685, 11.213393700101935, 152.37388901294506, 161.4861542910597, 80.86201301783687, 10.165605071450212, 119.05133263722934, 76.04403350965777, 73.13363492869985, 7.598340616091483, 81.2164127278169, 75.72771724845423, 63.326239614323875, 108.20156818886537, 89.12572206591898, 85.05914650624783, 64.07855337377495, 53.45323882487778, 81.74800285098215, 121.23237867725858, 102.15471245951981, 114.70143820128743, 136.72699937639533, 43.18004858194765, 71.18692366018306, 120.71475217621264, 92.81643032704878, 52.64938707119038, 4.778390662809695, 89.37795844491497, 47.61440256008689, 37.69058523488172, 51.61978458881987, 45.411024199307676, 52.14312630038894, 97.05950800577357, 52.492109404882385, 109.24572354900009, 81.00659738737635, 68.20643593853013, 75.30861503204012, 139.79027920243723, 43.54412677391732, 82.9200764691518, 136.32962289725324, 157.83111689788674, 105.50044103662489, 79.72511413511288, 90.24512596719093, 106.03478309848525, 79.18976314633333, 91.69731210843932, 7.161510396374102, 198.6720525053756, 71.40121371522378, 113.48193554575224, 62.15409351349062, 49.94507360909834, 129.91825698747667, 178.37424781664816, 6.272394315332859, 54.94768528979481, 96.75173991068552, 71.83968969313067, 65.76749838699888, 72.0625032528555, 88.49332210144756, 86.70610771855561, 113.371763438666, 82.64823069788982, 113.51177111861796, 71.17039800391474, 74.03425442042526, 50.86874689349324, 245.29130934666478, 67.29840877443768, 57.127416956184526, 94.35765090373361, 88.75224927552043, 189.3973220081023, 192.6355045635566, 153.56893304873154, 60.23259408359655, 52.63725354933162, 53.59751022031681, 148.02678275864565, 73.32690640650789, 78.91826983356906, 58.66377436808404, 98.62507659359707, 87.31219841669818, 143.45088926528803, 44.75515499748723, 155.86209103688086, 93.43243704144336, 89.82689015461102, 91.36908104091093, 67.63727589194421, 62.40288416806042, 82.69187207303337, 78.5156061615362, 153.07784834079783, 89.88752694396449, 50.41841179684916, 50.97923504271824, 178.46648037174054, 90.23148147467128, 62.616798390173834, 77.49909537499707, 62.04984556935734, 90.88387312709231, 34.26553272199796, 65.28427072932105, 67.63168500981277, 99.57207535381924, 65.53099956709958, 207.43663309241168, 89.91400238828163, 441.7090178769266, 82.82186301293001, 53.20684674648702, 40.67707777226201, 90.17573880679487, 133.55222560051718, 100.94198510351158, 65.44759062524453, 116.28992211677411, 51.52407269882342, 36.45104799795456, 127.30251815922097, 130.25742795838872, 45.45996953070656, 34.722798906421275, 78.63200209857615,</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>117.5315532493591</v>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>91.26385716178538</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>[115.11665344238281, 103.69825744628906, 127.93094635009766, 79.83558654785156, 83.26913452148438, 181.39236450195312, 141.68099975585938, 173.3926239013672, 39.33804702758789, 92.09040832519531, 68.59166717529297, 189.92835998535156, 35.237430572509766, 70.79370880126953, 118.96125030517578, 204.5042266845703, 103.06398010253906, 151.9327850341797, 71.95588684082031, 399.021728515625, 66.20675659179688, 209.1926727294922, 106.28140258789062, 9.447199821472168, 34.837860107421875, 48.77973556518555, 76.03938293457031, 9.708819389343262, 51.8015022277832, 93.85595703125, 48.49617004394531, 68.54496765136719, 77.3094482421875, 91.0130844116211, 15.693909645080566, 99.15660858154297, 94.0801773071289, 249.12811279296875, 102.61384582519531, 84.12725830078125, 172.531005859375, 82.18936920166016, 557.05029296875, 68.55414581298828, 111.10199737548828, 207.05694580078125, 67.2025146484375, 533.1022338867188, 50.59560775756836, 141.61537170410156, 73.85720825195312, 64.45997619628906, 72.71294403076172, 44.775028228759766, 195.22462463378906, 91.18205261230469, 51.651126861572266, 99.50089263916016, 249.7707977294922, 78.50433349609375, 93.9478530883789, 125.20960235595703, 123.3061752319336, 54.926124572753906, 305.4013366699219, 58.446815490722656, 69.91403198242188, 201.76296997070312, 63.52057647705078, 293.38360595703125, 76.8183822631836, 84.92288208007812, 69.3428955078125, 69.11119842529297, 68.11460876464844, 271.09747314453125, 120.18218994140625, 233.5401611328125, 96.58574676513672, 117.64987182617188, 75.17627716064453, 85.39385223388672, 54.62156677246094, 105.64508819580078, 88.56134033203125, 169.728515625, 65.80217742919922, 164.71185302734375, 11.097228050231934, 153.1634063720703, 35.68181610107422, 50.07884979248047, 195.0278778076172, 106.65154266357422, 102.44050598144531, 47.07980728149414, 122.96456146240234, 134.52674865722656, 89.88441467285156, 97.04400634765625]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p010218</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 06:02:36</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>93.79909506747273</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>69.58435314972995</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>105.5458386142797</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>4734</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>[1.537656728169014, 0.6342948649030338, 1.2917959353736208, 1.4690367648665725, 1.246370458762846, 1.237866557744991, 1.159367434081241, 0.913802591186223, 1.4273166479810924, 1.215796050811081, 0.5514515674561622, 1.0230479829445085, 1.2284738982879104, 0.949623065944538, 0.6821921211453718, 1.4144950067209152, 0.5700124719273034, 2.075315138744419, 1.18885793067861, 1.5560948691422105, 1.2357298231620328, 0.9899255859554538, 0.635679164029482, 0.839258189498454, 0.861914957037948, 1.1253976360133306, 1.7991106618607857, 1.2923129965163713, 1.026804220996151, 0.24097126008841718, 0.10396220714586189, 1.2482844655270418, 1.0266469230004232, 0.6033565109807565, 0.6055761088426157, 0.10182938667894716, 1.5461467153592086, 1.564277845664127, 0.7910551775976987, 1.5787050143670789, 1.6586050858070118, 1.3334376887717359, 1.8293822997692246, 1.5460607437765552, 1.3016053766457647, 0.9963964135661506, 2.5187940362203487, 2.332793417177917, 2.4407889749264235, 2.4591182712244204, 2.38291747289488, 2.126043684729541, 3.75204491127411, 3.2554669421337943, 1.7286555667773493, 1.292944911094161, 1.1351988984500536, 0.6102566988388336, 2.5877731441820844, 1.2002438881339326, 2.1791942851007753, 2.137913571292398, 1.9821674990621154, 1.0469669127631753, 2.2050056577525163, 0.6740870077620237, 1.5660672035577745, 1.2177401867480773, 2.2673887594877304, 1.6450969913247595, 2.642347655030962, 1.3169532053167512, 1.3764269336433268, 1.7674080824842673, 0.3048439551320732, 1.910966732589845, 0.6271360285094569, 2.294923805120651, 1.1520687477444804, 2.1133022117923614, 0.7705165732871327, 1.1023842279124882, 1.822631039537348, 4.376809855191742, 2.331177845921098, 0.9792371704292826, 4.166807313784078, 0.7350536642983675, 2.4311966500988573, 3.4793971025779125, 3.666250651140722, 2.6295109464855915, 4.409598808000927, 4.598351073397559, 2.9480166448031566, 2.0184422187535, 1.3155644356780598, 5.527917707952682, 5.688027598775967, 4.444218497799965, 0.7153385995688794, 3.142652789837294, 2.7659424213121495, 3.0038279702680613, 0.9451735497771475, 2.9061367552812687, 3.201063639924734, 2.591802817684104, 3.518870934436757, 2.698643061180501, 6.1831691272366, 2.37368887753665, 2.9293986710951994, 3.5349474179852454, 2.25138743156476, 2.7079399438144622, 1.4394316931801823, 2.378621712147124, 6.167985493953477, 5.271756945381167, 9.905242235876486, 4.6124733471501855, 1.0299018906555257, 0.8605987562702406, 3.5789301513031715, 4.507998800581142, 6.756798576742189, 6.419113593150159, 5.034035928120288, 5.601211189501264, 2.913245110256445, 0.8122909451112724, 5.9180886542542295, 4.2133912327056375, 2.8717486051989076, 3.5555449780090074, 4.782073255655547, 7.4734779513890235, 5.6297894109483355, 3.2658314465049494, 3.4294734123775994, 5.186372432742246, 3.9547693973841467, 2.7761114288195023, 4.5455490306743345, 7.111252261360888, 3.4439669652957168, 6.563207654364971, 5.663562315439157, 1.8015298935325137, 3.545948208815908, 5.4213546994594894, 1.9740933834989085, 9.324593838965473, 2.6038403122825504, 4.0573436368294, 6.90875366642955, 6.720396502035566, 12.096804943778302, 7.169998714922947, 8.686411387205705, 15.824312791631668, 7.497414974558999, 4.2999992690784525, 12.534697879325481, 4.70345816061162, 9.73327596840524, 4.4718525270323894, 9.852396455707137, 8.162279457456846, 16.096827121063104, 6.119231286423089, 11.851388386260272, 8.349537407414465, 4.97804163139547, 4.833765946062977, 8.228828139969778, 9.546159957271275, 10.287753055878385, 6.022663761634734, 3.471219941400229, 5.365408081367532, 8.578704945490134, 11.432170744761649, 12.733741533135092, 4.46380049857011, 7.9632001687062415, 3.063529714732997, 13.5965415102686, 9.206291853193902, 9.247958484807555, 7.5501999318310835, 9.400227291362425, 12.044119981481586, 7.400453742350708, 12.56833542830597, 13.409468832753376, 27.66560923000422, 12.749435324672481, 2.824320739863644, 9.22408739234484, 5.62129474854886, 10.645483643629968, 7.531888687590237, 21.04093206687686, 12.367377627121677, 10.940798116080005, 14.729747469433656, 16.02994273406302, 22.885427369565015, 3.6105163211100963, 26.375541370864795, 12.645417954538795, 11.79808324720635, 12.93181744353636, 20.55542116621593, 5.859105706066052, 9.261923017786703, 4.958075424017003, 13.8279991872427, 16.610255414095636, 19.739742769934836, 22.813264429433254, 19.653542976198462, 3.0018052732635048, 19.92327975732542, 28.86099008807635, 16.986215738327804, 16.63003694854641, 16.97509576580352, 9.850431891400211, 17.713235665927048, 14.546744440122872, 19.026608409773168, 41.2588476833714, 19.574728554246576, 23.274586054693287, 49.309959154454724, 22.708446177543124, 22.842543302910506, 20.885264747417583, 46.62525530019241, 23.514476495517368, 26.380208796501627, 17.606066292032924, 14.422369907240943, 17.988719291024296, 36.76983283092696, 17.42126852319699, 10.139122569332432, 23.975907210248934, 22.655053213554783, 21.632758850646866, 14.404625387890928, 17.07134596883401, 59.49626293773215, 8.742822901131978, 21.346572008295176, 14.473458270629223, 31.29914280801518, 6.870551818474838, 19.02247391396708, 29.89296921978438, 37.701516174569434, 32.317500640513316, 25.439162338655294, 46.34820430537645, 25.964172091057538, 54.69176913542998, 49.16026164666784, 48.36715189440416, 45.00784452273981, 18.528282604098912, 39.752245646029046, 24.83943461320395, 53.463942377337936, 43.09022222372018, 22.670220227792342, 40.29621933827446, 35.734274221752244, 38.49904392754293, 22.057255856883, 40.01927552750573, 31.84658165171973, 43.49450349961899, 18.05552319817727, 25.69975062423814, 27.00087758828316, 39.61454206085193, 24.22885001492429, 61.81985066271008, 36.768517699709555, 72.19069359111526, 43.30840114001915, 49.92605820672826, 44.95666878086079, 13.940621069499251, 27.294437339555, 35.28803678305437, 52.776173259951356, 63.139227429954666, 30.045781121016525, 58.84526612674438, 40.555298310143144, 48.67712869312972, 23.203677818123392, 71.01260524070192, 9.861608001742066, 28.866730306070266, 30.421122146499442, 51.91179345393589, 61.39556934385319, 43.635369076824354, 26.263022551608586, 21.69156613836882, 38.86909989546772, 30.79829059032437, 49.648115061212934, 52.20714721107416, 56.27398589048822, 69.93936119884125, 11.26726640662542, 30.148041279217473, 51.21294963490143, 30.903414954531726, 72.75692501249495, 39.84181243368395, 26.550715757858505, 23.503578686838882, 19.36131892768251, 19.24041710295965, 28.386347459026826, 41.69501159474705, 29.349477764228805, 29.127792221984034, 67.89537984782359, 73.7073954004003, 38.33917663089828, 20.873193243506382, 73.55042211348028, 51.6462807324327, 46.853594802280824, 45.19267829474475, 22.39073365921453, 39.61308577042878, 38.50339526378033, 35.64816140921683, 22.03081251342347, 30.194054244599783, 78.27292070101721, 2.9820534984670237, 27.77641648304993, 46.028035305560316, 86.72925914143109, 40.3018203833328, 99.38840633643406, 43.14616342655219, 49.06670693718409, 22.240978076735903, 98.49945139020576, 29.035705424547995, 30.851578650218716, 58.45603444465322, 34.17147034648903, 47.50130657641945, 33.38840973021362, 24.423970754186787, 37.12688131014603, 50.41195832599933, 30.407466375679295, 43.090209051382686, 20.95548287908537, 4.891385980041284, 35.99950222075398, 60.1012251749968, 40.933569495830156, 37.46290945812556, 60.54617392477091, 78.01442974892099, 36.20601719395971, 89.42136009338591, 25.35395306680375, 50.59557492058304, 55.15216999269819, 35.64085215669155, 23.59945899401237, 55.87542566638951, 60.2139405440271, 30.77465701420306, 62.76834517132494, 33.87817061542279, 65.86101449883567, 47.6636247583488, 44.81034732602584, 43.879312232384194, 44.517053533001516, 38.61723520963253, 33.21350205865521, 43.986342876337766, 49.36240680642171, 30.16156426636104, 41.00478126225647, 66.83797655195845, 53.66959909458683, 47.55132848663547, 105.68042138520138, 40.402643509207266, 57.8999287028974, 47.445863952954994, 25.477889362081186, 37.0158816401934, 49.747212014274155, 123.2386921170697, 76.91148179440364, 48.068086166621974, 60.18551644139985, 2.9685424633419233, 46.75688003954134, 71.71144606643094, 54.62179551455839, 35.10287308302862, 62.31062619174838, 57.170813629846855, 41.106796368547776, 11.065606889702865, 51.72891323441296, 72.98918547804064, 98.46017067313657, 122.0041559101055, 42.89425807059589, 41.812314208670685, 2.697654881909333, 31.310129065140767, 45.82788590830492, 52.40764834624029, 55.05153428088815, 79.80552743046616, 37.33278769398826, 55.226533955619225, 36.31119286575722, 89.02610101187784, 42.100632111467675, 47.65432106193297, 52.46884670654269, 98.93190949614777, 46.238598693328434, 47.57763201315106, 88.38200138769044, 106.51244627008467, 47.16193850576522, 69.37361319937588, 51.52468571174342, 41.83499911239563, 81.29988014842546, 3.8955765711252863, 8.90457330462175, 42.837948187160904, 63.85652080471936, 105.23646517156412, 134.17843131736976, 104.86674933561886, 53.04002605207414, 59.852343508630604, 35.594159324396166, 80.28019313314245, 59.47034559921921, 48.29661860673481, 59.53980381837586, 221.50044713512634, 68.43709598433458, 46.79971512373117, 95.90387975782693, 40.56410851943313, 62.9714912137008, 71.61869575501834, 87.04542239293595, 61.841549028452675, 41.00093704175659, 57.40986645281348, 41.28418974229297, 20.841766111096284, 130.65779666471616, 51.45765825076591, 75.58670405013376, 77.60205036988403, 181.73039537029757, 50.775519524893504, 72.45119111628442, 77.86620756201118, 45.78478626129453, 86.22337275690465, 5.472746196835947, 38.44316836187791, 6.302238676772353, 58.75438222795893, 66.93549787766963, 62.28190748754885, 48.12228869490389, 153.00754235935457, 124.81881392406852, 6.921280152686914, 74.58388903933233, 8.342711313405998, 111.67629776746392, 13.248223841476483, 62.49868588825131, 51.78884831562513, 7.1471067039545595, 49.426291639934355, 46.76745212922636, 50.89319371180997, 101.34038652046948, 63.51515094252014, 5.361824141975204, 40.75444128777338, 52.59976169741823, 103.19476018347952, 82.1190078580385, 85.05145191986138, 51.665862273824835, 12.046168887360803, 36.408124028338335, 55.990943130110615, 9.780919192002758, 59.59432624384756, 50.14296724101814, 114.73730444470343, 103.82692373237785, 30.544256497587416, 4.408115843468931, 60.994543789145276, 8.578806220983749, 41.50278996043085, 54.23217181686258, 103.89728314986621, 45.81524282675478, 42.29372104025854, 74.00033198770943, 102.7199441366577, 42.81520868854198, 41.43883843141301, 49.552149991294215, 5.573530934344339, 45.51866557558206, 48.080868252696376, 83.23703318628952, 39.06110877894157, 80.9084667008192, 133.75409611935166, 38.09643709522484, 30.708665981228787, 44.55072458469606, 80.29454334176438, 36.67482302936144, 112.0118995644506, 8.18947171415813, 59.48038922054506, 77.94992198519877, 75.07566512931123, 61.36161557640662, 42.73947999778053, 115.7519057704344, 46.349508611575786, 74.80023902035303, 48.44852659675483, 41.27050306103753, 48.70692275255324, 61.316435563131684, 50.43600869993701, 214.7182749750311, 80.20102748311034, 106.54959971531525, 96.34372786126744, 88.95212640470824, 73.69398361747797, 54.75950563148663, 38.08850049285564, 259.63458302705186, 49.556707306359876, 61.03816106314154, 42.742224194101446, 44.99455341670383, 90.69892112252106, 50.84821327689697, 101.94354417567766, 59.799967330787666, 96.03516568046356, 96.88566387997757, 38.93611675390251, 93.36441212121771, 80.40348831661903, 40.49192809751573, 45.84252911111206, 45.501040457900075, 91.3350045947469, 61.60444092429427, 93.01013730038797, 90.82797481894147, 114.2972508343578, 84.37350299648833, 143.12020470781425, 61.604142373841896, 41.88894271254358, 108.0529070126732, 113.50091816566851, 65.17338813356474, 85.60708627329726, 68.27685052705392, 78.53212028441048, 62.23233559284863, 37.55249391470261, 66.92622543002265, 68.98237651111657, 110.16684316706043, 102.26029918298792, 73.04507013157546, 52.712132458273764, 86.73190701162933, 57.514389326516486, 124.21801280466266, 92.25083842000765, 48.5135277458514, 55.29464273144727, 62.27066881736421, 4.919551542217106, 4.400464900309862, 52.4079935837409, 118.53043186812384, 58.06977314980018, 125.0283100710909, 66.03873075010898, 53.52819235743427, 44.98221710974107, 101.69643316904397, 57.12341571800606, 58.73180554617934, 74.92835158293906, 61.41787388976809, 49.2030898191026, 67.43384073980438, 142.4323395249435, 51.291868349346835, 68.30703154887651, 70.54387763875049, 79.90986158575915, 74.91716538892493, 54.38913296146592, 59.120048646395716, 104.88439286789509, 47.0834103590751, 44.316250388580684, 86.98938560967903, 36.44052764366611, 39.01602682378831, 42.49083596379804, 5.315547942212871, 67.17091251348036, 47.309969070230565, 79.87425198333078, 47.77624261000472, 52.59338390984798, 54.680559284854674, 39.871525790212786, 93.42685278638366, 234.82900310709124, 4.431605823570401, 98.61356951542412, 50.9224758397258, 86.54003776255573, 135.11310152282832, 55.2086648345945, 53.477499559042215, 149.96200865432715, 90.96528676415832, 104.9740974102877, 85.50636891291231, 61.70793547711585, 61.86064049795029, 220.17290399719616, 173.2032843155009, 64.5996091389365, 51.142817052297836, 97.85705408200222, 107.28973803838156, 72.2821877624522, 51.20129799480068, 80.76866693154271, 100.81100067324665, 80.70169989345465, 77.88012306550746, 45.30990919749954, 50.85986149308592, 123.69505216823154, 101.57561878734765, 58.07072198479017, 38.05045000191766, 80.9759446310869, 55.33389249845668, 96.74959563107473, 52.59691803791685, 85.58896486114398, 33.215763308572605, 89.8612927419264, 39.75639429165279, 43.79411259506376, 6.603769085051202, 9.856815765586314, 64.74467540716967, 76.15295710261579, 15.537493048049333, 42.538788642618954, 78.36405175501797, 132.0954839217221, 88.30096426955969, 36.88098053408278, 107.9268624194419, 76.1627993866807, 69.18415547067234, 140.6542491917977, 62.952328840647525, 33.326928184063135, 59.1127881516528, 59.783084436656374, 91.7377005555615, 44.23646696661457, 43.90463265872899, 68.35296000209995, 70.41702476910739, 47.44904766898811, 15.120797737725523, 9.287428650437475, 57.30940897021004, 67.90636398902478, 75.64772999725446, 64.1769871428384, 9.536847381368949, 43.39749256513749, 40.043281496620565, 121.864019315433, 33.3592186484054, 52.84484242649043, 94.18297867110284, 59.81077874569565, 122.58184885498508, 52.97554149537908, 8.467047033284702, 62.02658486745586, 85.01642018115788, 64.3909997395803, 9.339026068646646, 67.42323903970205, 51.57978853744324, 58.71603263438931, 11.327432111715336, 67.01767698302574, 118.62361835342615, 171.46722192360153, 47.95220352596128, 65.76059746442789, 93.45001578387983, 58.5658341722402, 14.165984619258762, 51.86950917531013, 66.01082864519535, 48.72813125242665, 62.234453968367575, 60.38950147211334, 32.568868012599886, 70.74300724224884, 88.03928754652561, 83.48037800679884, 114.2409930271311, 76.69882537211635, 8.97937640787088, 59.42385254758115, 60.20978116224826, 51.45480751865691, 98.28208520726228, 55.35373434342575, 61.03510089760751, 112.23138837378195, 59.21829853191143, 71.61097177057265, 28.979690023037776, 8.147431586779911, 63.03239557621235, 152.42882058323136, 79.44673128282791, 58.28246910814351, 83.47170262404593, 56.171887287076935, 70.40122818601115, 95.96992873066954, 72.4791657440356, 55.35480463657079, 64.15985954319478, 57.077240799080286, 66.2237314143379, 76.41135421945998, 57.4027925350563, 170.86402795673274, 44.91353757015703, 76.82412705808359, 56.06950047699136, 53.094604604949886, 132.2736229162745, 78.98737644543354, 89.50263616640244, 65.28541965137988, 86.04505798288548, 43.25477866422694, 65.18635316573796, 59.18174666904255, 91.7354974782131, 74.11888002318567, 85.37202729888182, 66.78259734523023, 52.41346292289069, 87.22127766468155, 46.09911833337651, 85.72388062724025, 47.17244403483012, 212.62122372075515, 124.43310752778956, 104.12314821222975, 142.33980906897776, 103.89338524448497, 136.2205343416812, 50.76914459330684, 95.9964583719071, 54.39341101709623, 57.25209869301955, 53.43091762016737, 53.688322620541705, 130.7019294745796, 96.76088197163392, 100.70455036415727, 122.62720743807235, 54.609879569529625, 84.68281589778513, 7.006027128429845, 108.98960566426379, 85.44954617259083, 181.20668400116108, 65.21900090545172, 111.48885640632005, 97.25928001394477, 73.26132256175576, 98.78490312493778, 37.48875337556291, 51.460792000067705, 67.41023542250964, 122.30335459647041, 189.4911746088128, 91.07572215559784, 110.87711715095023, 184.3189743780886, 158.44777224011713, 46.894749930260936, 66.90440013051021, 55.85780553970155, 64.43433053096399, 66.64639268001642, 89.09110572787445, 11.174288568489665, 52.99418379767022, 100.26474670085494, 75.71882132323903, 8.881637420291808, 54.77413936147133, 127.0741020495914, 51.1066033865671, 98.11852472861601, 70.03124071243872, 163.4172550568618, 57.92244061687173, 116.61970378403657, 267.228606435963, 61.4953032993438, 6.6616830328444845, 86.82030316871976, 128.56069274489212, 65.67777271028372, 58.92406152182364, 53.59648566858641, 79.90231143375976, 92.92086207711048, 65.29419001876258, 107.96472242920693, 57.38802136959188, 45.60216342825045, 82.02390986518017, 9.095277214453628, 10.459832999868242, 93.54391236354832, 81.44242307968163, 45.82727681292688, 48.25332180570274, 59.88198977233704, 64.56730728865617, 43.8470433865187, 93.33309987083524, 55.95568687841658, 57.69502691701774, 50.131171595695285, 73.9595594608143, 59.43209047634741, 88.20652521209374, 36.478362843891034, 11.719342955823222, 66.233185520153, 87.74431846561922, 109.78661301797071, 42.92318059309659, 76.62663411414215, 53.931148391447735, 66.00368423562354, 156.3477286002269, 68.9489067117721, 59.65897781694407, 119.15738597112286, 87.35997324833235, 65.56955177887997, 54.30428757511578, 75.30283777781116, 60.705090995859464, 49.68892729806538, 42.61013272990433, 66.81806731030306, 74.65410159508369, 58.65337520868704, 71.83390332207934, 88.9165751826006, 76.68926330582802, 58.548850698570014, 170.96920754905184, 36.20321838988284, 168.43610850648054, 123.39130781061685, 128.9737230022424, 120.36716685629905, 47.1752873957895, 97.07112782179627, 63.857692498684685, 80.07673939403585, 44.53840115320586, 102.3285043022162, 71.33869777297176, 80.82427225270297, 98.68298056273784, 70.87798551750308, 128.53315191687682, 133.0964187960628, 65.25182202212146, 93.78972463469346, 38.93764585243122, 48.64029846569279, 77.62062183974342, 96.02931462763217, 58.99943721410497, 50.399196014809604, 276.1642362194218, 12.374893512243574, 113.82674988354866, 91.77630196939218, 197.12263433001146, 81.91568943827349, 38.409651127519275, 201.46834020121378, 117.84404097472623, 58.89111184975665, 56.77118655665391, 35.25418779132686, 100.6590903310712, 117.54745836587023, 68.08846758280202, 72.27379291885461, 18.98259777850156, 64.91286553280857, 63.258389735441526, 92.2799561242542, 59.84979706313814, 279.6941962650799, 319.07071761922, 83.96730638058106, 115.79530473598541, 181.33760854976308, 64.72592041174885, 133.37529771282937, 65.75284599320324, 39.07967217924623, 96.03800207365826, 71.30294133516504, 80.205776998475, 142.7269822804925, 117.1548196865082, 65.11035805770115, 45.36814564054279, 155.6470380656185, 52.45053115619388, 36.506569644785735, 94.0538314972614, 109.6997949370697, 118.05544063967052, 80.03871348116436, 210.54057691971175, 74.2751265356287, 58.33954594575891, 9.77657802106171, 73.89045662688693, 221.46086724740638, 160.74414438965982, 85.43901827212407, 101.33550238271022, 79.94980359255442, 46.21617644379833, 135.32620349437732, 57.28238541826352, 35.776093668711326, 209.4440030657878, 74.05587658541023, 102.17035220953946, 109.08004742649523, 218.9147599089413, 119.81287537296696, 46.049308152436076, 47.93465430718015, 102.75648663801034, 98.31287662340775, 65.85071347408027, 55.57432150106297, 88.25071501398051, 57.41829499781057, 72.48694257337142, 8.254337607942276, 90.00677722732681, 131.39392603466823, 172.54107874469398, 15.563181249723298, 116.19095951106002, 84.813113910169, 73.81913026102548, 92.03592995648643, 83.21343339076115, 73.69461107490184, 128.2414725965463, 141.04903828443912, 52.71389688045419, 53.1351170065611, 88.13301757331509, 9.984686112083354, 6.82573574422401, 131.70725406213398, 85.43406896491052, 10.013041205353794, 79.1407120844162, 50.52437856702237, 110.28974607944167, 9.791657082081691, 108.51843682491634, 5.276880682518033, 76.82092614966109, 31.371689213749086, 58.579779967519734, 108.69550594680372, 73.65431554660003, 65.98332785612607, 47.66794988596721, 45.94465297804578, 296.52882474321535, 125.13208634050173, 91.83713384791778, 113.88273937886835, 150.5452459818553, 16.988091163319925, 141.2314286819991, 83.78915116266221, 67.20799834825085, 112.08309491711861, 68.44183155743194, 84.04732107672513, 60.41410284810438, 54.14380257128842, 95.23942225878098, 11.024844519811346, 44.692729937390894, 84.9332807767305, 61.42588414394124, 55.59797877887753, 67.24473210289761, 195.10859614204801, 61.69655776849065, 52.53998124923103, 148.1260499938021, 175.6496042028985, 130.69244082018568, 70.8090809992056, 153.76962904345564, 71.4602659910485, 52.678380237575816, 165.4102864874131, 77.45988971836718, 90.12388581483292, 56.79377502376618, 95.35372854338081, 81.09706370359947, 116.76979613745347, 5.837565087888154, 425.03430643431227, 50.81315897661989, 153.2116033654903, 84.83420372920384, 60.91657506332173, 77.77038287724992, 161.51999877542727, 68.68390402893934, 73.87193787333932, 104.9564916957235, 77.2279679157898, 88.94077424640803, 103.83621848844403, 55.08515541224539, 78.48865757942343, 75.90047075770201, 81.63292922371724, 94.37840288689485, 64.75848786042765, 83.10730942889262, 60.66911813268557, 176.43564030635855, 118.30279171069118, 37.95482008605582, 74.84377803389182, 12.8278895136713, 37.98754059631215, 95.04322863774581, 66.64917867611582, 156.6390707855556, 46.09448347158475, 185.24711028471123, 48.06056442103337, 157.6533379824532, 86.18011164683489, 196.03127793336648, 144.2765218992435, 118.1978972273629, 104.99481379479019, 58.602175781067174, 197.79714475789763, 144.1610513285496, 61.051235299679995, 57.59412326535455, 285.48952154396477, 147.40936677534756, 79.73411033558642, 65.7485836891971, 104.99040805592404, 51.69593124927571, 80.76325397972965, 66.9651482585594, 54.20384188794829, 62.793682862115354, 74.60051609432948, 122.61671989921733, 75.97493446251318, 52.35446009678691, 92.95299735777387, 88.78955074342551, 86.07823427357293, 101.73396710235838, 82.46302040514946, 166.2431936855508, 75.25899753241455, 103.78184672482779, 256.9603962520216, 308.63321224607466, 98.66996140125869, 125.7632741663513, 174.07598873080383, 136.2179327929136, 68.48088852096235, 12.259013653614401, 163.81393108493575, 127.67702560009715, 68.56469568935864, 112.59503229696985, 189.82473166599615, 46.83561717510217, 103.11488605709349, 102.16615497744128, 243.2771191499964, 93.88577201696108, 152.33447502961346, 80.34242569832912, 359.8314194758402, 145.55276207850392, 53.11745857056018, 73.07376315017063, 45.403748509704684, 92.68989986854979, 134.5059162682157, 124.56392273897612, 99.34094240826269, 82.43889499643308, 68.59015523149735, 201.39928083788533, 75.25972659765611, 60.63944487716519, 55.9261121968399, 128.0576050712505, 309.68991441939966, 49.625998898179546, 93.00487444322783, 99.79714987453954, 70.12510458976352, 59.86820930584738, 77.704649954137, 128.55612074199732, 78.02268028282798, 53.66214604539821, 77.35743981139076, 96.0592636150768, 82.31978692278287, 141.53734182666253, 56.818365437461935, 56.486013883180355, 68.75449195407474, 188.94283370298746, 8.117324201609224, 80.44592485932387, 137.32264053896438, 65.56061582439915, 40.10834013335237, 89.09847318429594, 79.21265251323227, 47.21529780611288, 98.31609188857021, 41.644019978352716, 80.19366311827505, 180.87028568882843, 72.49670182276375, 81.38053581681615, 230.8663268531316, 132.83672879070284, 67.95996649677568, 133.540865498024, 89.05870216645347, 58.685425987628506, 75.83343884904549, 102.75332583939289, 138.73890542071035, 41.55663129778583, 46.02042216919048, 73.50149917060081, 139.4777771961385, 267.83875453580737, 54.752944789473034, 51.60114828398412, 105.25801383012411, 61.8002006795261, 135.14268646300545, 47.86928166328871, 256.02182594990154, 185.06564073283857, 309.45973867066664, 118.87569816748703, 64.74624025500026, 48.96300349619967, 89.71921629557444, 78.9714980018295, 72.19889906979417, 53.57629202564754, 32.074860726070916, 80.96331232284757, 113.91007344718837, 51.024190037600675, 37.2130189207006, 66.26421296623178, 115.21312921326195, 79.91737599521711, 60.00355469497461, 93.37677109047644, 37.58292289493625, 60.814366839737666, 133.72454903823444, 51.142249491887696, 113.78027028412748, 386.58367677893705, 119.57346142042476, 63.68771684634916, 62.00821427918942, 41.59139268756951, 46.28986724541734, 56.787532978250894, 60.920173703523005, 76.29817242145576, 210.6627030477722, 107.98282149400336, 74.12491620282974, 88.96532964728262, 140.84641698350788, 92.56605497354325, 238.15166789084762, 146.43343548780007, 89.7348868425488, 194.92849819096526, 38.51554078954665, 254.9588644968703, 76.7302208200201, 132.66478289064565, 106.29214967469558, 118.00593731351574, 400.1462501774682, 103.06368127962058, 61.85585919701462, 58.722347816694054, 142.71131701356958, 78.33498555344634, 52.54253271620165, 59.93364433274242, 79.83164973165691, 115.0159264860752, 44.2620426703643, 84.39583297067935, 81.71930881739817, 61.281505656526896, 93.41416019214256, 90.40280970322173, 70.90189784154622, 83.52970888280669, 122.02925767710359, 70.42273641831481, 103.34786938960221, 68.6347989060955, 80.00567452986081, 66.52484431225317, 70.34673463924088, 124.55123818654745, 48.931190387473244, 67.21205003854534, 40.46402034017244, 74.10379602130926, 54.6845889405584, 52.80574121873874, 58.35599489674632, 177.9705490492004, 11.083397445471414, 93.06506254827096, 95.93512074470341, 178.61629839439675, 66.36595139677438, 59.47383045084349, 98.45696606000409, 8.879089861279452, 63.67038391493716, 160.58636612179254, 148.15066047549035, 87.20587669665774, 58.53822515940271, 95.22071442154025, 54.04310295642376, 10.99818115895385, 163.76491182751008, 41.17310147705815, 67.09881318721303, 116.8005229386117, 40.87927368013164, 37.84472075407296, 62.06837035448026, 81.11256869087798, 130.88574147188504, 65.90262657882688, 91.69376186900621, 115.48128157130614, 50.79822543816195, 116.98086951684917, 77.87645202286129, 47.599882916357544, 42.25930599577385, 81.83025007212896, 82.92768520171333, 117.12925826543419, 91.63428069967455, 93.59801948859668, 33.450390311494445, 186.0098898506057, 93.53597676300329, 57.42168626963799, 184.70456692496762, 78.41055543216986, 70.34382561086139, 8.324122811421876, 104.68112395731875, 214.1843162953024, 144.08380516760053, 59.17761833737388, 63.87689735584543, 123.88745984782756, 62.85341639653998, 51.790537911794104, 44.02357357174573, 59.84738865408369, 130.84592156596176, 98.6730460565393, 70.08525780601302, 135.6986682057687, 38.08535547216193, 72.31541472775933, 82.2154734662194, 145.9131165117409, 76.28017808748609, 122.618530427283, 73.91804768495402, 70.00408578385901, 73.56250618236706, 105.06830043777374, 5.376812923602947, 56.755580303298395, 62.84330384990377, 131.9310403315676, 42.55891896501159, 99.6054752522796, 46.681547119483156, 76.52463811025426, 60.54778530811919, 66.2541433835537, 41.65464105415921, 65.92473223309509, 100.8610465282242, 78.88413287307677, 106.38940186113878, 33.35668028484528, 44.09922526818518, 13.441599235806628, 83.41712239893462, 81.50383852664557, 47.50485862569942, 77.13405620455086, 78.84723772781301, 106.78220606579242, 171.0410782728331, 204.70066352429683, 7.4989868050330095, 76.09168085069757, 10.7954856504883, 109.31299324569424, 67.74654147348896, 88.82982753879296, 145.0903577472539, 86.59335693099966, 89.15700595664777, 58.27706055098917, 63.83311862898697, 95.0072684523255, 61.8727443834017, 146.74643424525243, 49.5076515872087, 115.96765157600643, 328.2885923863785, 58.99223101197308, 46.788311535901165, 307.52291929897484, 205.59122279252935, 82.20921489777534, 104.11827674715464, 109.17977088460401, 218.90920900377446, 99.4863765938566, 78.89856693793392, 64.80741995045187, 80.2862359050077, 52.995584074665, 50.98696253319925, 79.71462353913869, 53.5586881219837, 58.992703625385765, 7.484787686858514, 20.870706944198595, 60.71782891073146, 62.927710567438595, 221.88570679214362, 129.67751871380113, 56.252470055322945, 478.2772777539601, 172.43491222961813, 59.506605006268806, 131.68408493081336, 87.32861619669042, 93.1800693027981, 142.55689067636663, 131.53956848044496, 233.05212815260586, 70.90443711316009, 36.73206604954884, 91.64801936924668, 57.40872906939089, 82.4730909511935, 84.95379097429223, 85.39371375319448, 120.20032727422554, 204.11198309971607, 72.77638296594004, 67.82798117471508, 113.9888917555972, 47.93943748534238, 128.33203203800142, 65.75175109966905, 84.18536954019179, 81.0149582441452, 45.897845012820824, 108.100912082693, 70.0323612565166, 62.486334277316644, 42.184139593546625, 125.58664860327565, 92.66572480091422, 86.55247965484968, 74.32127784031273, 144.52247630190487, 83.69290588908905, 208.9934237160522, 91.14017183714034, 51.23921639751304, 243.8796967073189, 70.38975159500163, 69.02309421412149, 68.29122344113586, 211.2566295972545, 52.39213436948768, 217.74998972511176, 96.26939602467458, 92.90388325305899, 71.35965637813229, 5.686253613657188, 103.81771339583341, 186.0134226941843, 74.47644504784165, 66.06396091806695, 97.14450532652975, 10.770354098150989, 106.76174684646071, 159.10377784051755, 267.69900513558537, 153.04635890897066, 59.864569232823555, 173.79641908232563, 104.73877417282047, 110.04015618328248, 60.9790120652878, 75.94763796420081, 208.5945308944684, 6.7905661283827214, 89.88865637015373, 200.5379655661833, 103.94869533740547, 144.39451385996003, 74.96525933519993, 80.56141439679293, 43.77356979398447, 40.36490830354194, 54.98045591476835, 52.61270891303397, 81.39470878688644, 112.2157171755569, 103.26216379831843, 246.59786373987603, 87.75559623282598, 58.435178323150446, 44.778958820315545, 54.236296199439956, 55.610285222936156, 57.65340897477469, 167.37633874349888, 47.37899482879176, 9.827153565164672, 57.697909089566735, 73.47864584726699, 37.974104533349895, 47.18794834346007, 57.608930349733654, 71.73577265504115, 41.296537735837546, 116.91638725967795, 57.43199089900384, 131.81545648467025, 96.20050997412677, 70.26901890245057, 57.87791118161376, 48.98290679825771, 35.970691241844115, 76.49551441205486, 56.60113330706598, 159.5372659118583, 146.66158817024186, 220.67371662787664, 167.56069047766997, 117.27670582461742, 190.55626382064992, 13.444700095951397, 112.5467897559485, 338.3321931537577, 96.44196547645194, 92.87986732985432, 54.97031793135249, 228.99967926475384, 161.79492773608374, 65.590678390969, 163.12616732604667, 92.27696661770723, 88.91034014557164, 53.92284832315725, 54.57284379552272, 204.58361041674198, 55.41866276390359, 150.71560680596298, 176.53649094759814, 205.25438016784827, 42.06968309241189, 395.21451253514846, 76.68420360542314, 52.03912662607624, 79.62693508842334, 85.65022325201865, 105.61873952839872, 84.03559178781295, 93.33032037811664, 103.82806814650569, 167.58534342703777, 74.1255125320394, 98.1814947880232, 86.74660507761087, 124.23277379508868, 54.564607251531974, 229.18613430766953, 75.29688725924868, 69.67076487631348, 97.15294856572226, 184.65870013992674, 104.36740093962433, 58.18466530624724, 73.52026086343608, 56.84577798507591, 79.91487792157434, 50.275145612821156, 60.48731605576152, 48.362750184108066, 63.613611887002975, 8.69023195266275, 131.09855807937902, 59.87328440151877, 88.24627038981076, 103.09806115914756, 271.3356251982902, 61.68500110224085, 58.608350939465815, 132.1813203847789, 58.85065152720973, 58.41654537373948, 4.78803246677046, 83.7126343568098, 37.090103782938144, 71.50950897361696, 46.17151293764975, 57.9100362782256, 105.96225717326588, 49.68804485119718, 151.8324789862498, 79.94158350107884, 185.72934341034357, 261.8706710055874, 80.10184105779962, 130.56388811918322, 69.8770765516245, 89.77818364677012, 138.97770636998254, 86.34448107350431, 74.2503386930211, 100.244474887363, 74.26715497774235, 33.016330624853154, 46.86789347873489, 103.7376881516678, 227.59123302216742, 105.87352823421146, 67.18515243307046, 121.9869868806111, 88.54116096768229, 114.80278137333445, 100.67745643179222, 109.57469330516004, 62.539218070345584, 111.026325462865, 59.13140962631208, 98.23873533972034, 84.50969274621299, 73.90805954439402, 48.570173121113775, 112.63056431867928, 84.23285278721752, 62.90479808263401, 12.26658838</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>113.3806245613098</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>84.12651354570554</v>
+      </c>
+      <c r="T54" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>[158.66773986816406, 312.781982421875, 64.12783813476562, 174.95956420898438, 116.6187744140625, 76.07901763916016, 59.93323516845703, 70.45211029052734, 131.24012756347656, 68.41405487060547, 135.1426239013672, 146.4602508544922, 162.42860412597656, 77.05133819580078, 147.22796630859375, 202.6587371826172, 105.23481750488281, 82.94203186035156, 52.18545150756836, 98.64949035644531, 121.06271362304688, 7.908565521240234, 45.04560852050781, 18.991891860961914, 106.071533203125, 136.24429321289062, 72.10282897949219, 11.637694358825684, 67.77471923828125, 54.1978874206543, 64.95913696289062, 146.69003295898438, 190.77842712402344, 92.37128448486328, 89.92142486572266, 164.57359313964844, 87.01532745361328, 74.58368682861328, 109.53185272216797, 201.2906036376953, 68.01487731933594, 104.79743194580078, 54.53514099121094, 172.57467651367188, 69.48756408691406, 81.21202850341797, 214.5047149658203, 139.01626586914062, 5.880265235900879, 372.564453125, 180.40255737304688, 180.648681640625, 133.22677612304688, 630.5521240234375, 22.24556541442871, 63.60114288330078, 119.97848510742188, 116.61551666259766, 60.642425537109375, 80.35247039794922, 116.53262329101562, 46.132835388183594, 67.92855072021484, 55.78940200805664, 35.27333450317383, 103.95252990722656, 143.1050567626953, 74.82504272460938, 49.69777297973633, 64.3341293334961, 69.30261993408203, 203.37310791015625, 104.23883056640625, 75.0916519165039, 56.198570251464844, 65.87447357177734, 47.453487396240234, 103.1316146850586, 63.59376525878906, 126.4709701538086, 170.32447814941406, 43.56665802001953, 50.40807342529297, 141.36752319335938, 174.22808837890625, 58.38633346557617, 144.0415496826172, 73.32440185546875, 228.31373596191406, 232.01107788085938, 132.72113037109375, 131.00057983398438, 80.895263671875, 341.0661315917969, 175.91879272460938, 22.99176597595215, 41.1661262512207, 82.19794464111328, 69.85868835449219, 95.1117172241211]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>p-1.0srandomst00219</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 06:05:21</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>89.39412441958426</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>70.39194298529272</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>104.2031282586027</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>4795</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>[1.537656728169014, 0.4631391234610408, 0.691680844928828, 1.5430227035940356, 1.6961684280164842, 1.1504575439433382, 1.3484806370318574, 1.3177674211525614, 1.1342728262289847, 1.5978715305118947, 0.2692289297916618, 0.42879146479049823, 1.0052770337238102, 1.645320164174578, 0.5073359628489414, 1.1417463567863506, 1.1876262689735435, 1.2842150193221145, 1.2871720223741456, 1.327336675184992, 1.4619573800867918, 0.7333507521299241, 0.621944911187787, 0.6535463419341727, 0.42869303607863457, 0.7137079931675628, 1.2847228199294047, 1.1345974196319177, 2.7146571930950083, 1.3097708511375925, 1.1379153569241465, 0.9366512226719003, 1.0398931404640894, 0.07963453802773537, 0.6076965544268228, 1.1239342326699524, 0.5240253571552357, 1.5828200710568971, 0.919209700063636, 0.4159058901903153, 1.743201916353758, 0.5911902655725076, 1.3029668104368646, 1.6154135792654407, 1.7108209306453943, 1.5258992273498257, 0.23859564336060277, 0.9062513548240155, 2.534170868590587, 2.6281423840281324, 2.6685238285318107, 3.3110109154841267, 1.2196466170114222, 1.5207734871576042, 2.2978279438252063, 3.01450555743487, 1.7634295895487297, 1.6743816737428823, 0.8294042437561778, 1.7113709647578392, 2.9957746093561717, 0.4179620906380957, 1.0177734907960614, 2.1147658447612816, 1.849058490135401, 2.732393804375198, 2.6648417044706125, 1.0684918089205433, 2.0922001933598247, 2.3929371185179185, 1.9705608684753064, 2.3010533145562793, 0.5750338211319914, 1.311472049887716, 2.874716334724537, 1.612840947244496, 0.21257746668323368, 1.6475585237119685, 2.4635583896875977, 0.7647878511588457, 2.5645242099109287, 2.3931578810586633, 2.3752882662667174, 3.3254415017260572, 1.8551737978136744, 2.2688454269828853, 3.5675234918976133, 3.522961897407936, 3.1997889777312656, 4.686289261217279, 2.69831151894847, 6.364213036437121, 1.322243795817337, 2.5408475543219193, 1.2642911902634284, 1.9598680182024384, 3.0604890183613027, 4.3818177998506815, 3.912269171784267, 2.263535522733725, 1.4020308866433324, 3.450011225984379, 1.558408225500495, 2.741794301819124, 2.5538535157477678, 1.6476490519813565, 5.307664369647193, 2.102784197171925, 5.532783135917403, 4.928299808453153, 3.4489258221898287, 2.367154017278858, 1.6617486655682998, 2.2587583870079735, 2.4258385405337064, 2.7716137294376786, 1.4516822165820396, 1.832539827848704, 1.7023632999438396, 5.185902800563891, 3.704813168061588, 10.178792980839857, 2.8716067428565815, 5.268637596715633, 1.0582925111945212, 3.830398275637325, 3.4223108677248555, 6.305593755268683, 2.6190870683848013, 8.71860987852652, 3.452951545353159, 1.9913438743028027, 4.832906291739549, 4.320556745595929, 3.2216323942541227, 6.297610705119137, 3.572288413547648, 5.8417252118227525, 4.525421397040889, 3.6552948913788796, 4.613826879156874, 3.781061832249025, 3.4555090051203736, 6.638296331042819, 4.691380059083993, 3.867398257022182, 5.253215398570866, 4.388313720663546, 3.232999409232448, 4.276827635852474, 8.433142189811342, 6.905267450555189, 4.188858546204848, 2.08864885611331, 2.928237786024415, 5.022489017488738, 4.6443783198572355, 9.727233697439267, 5.2143326450214005, 4.367218660953006, 16.377323957066714, 5.314478833905315, 4.878183362895122, 3.468979161082324, 13.593470024645972, 3.7231135260557524, 5.923627436985743, 7.769122455820652, 7.4789399595915445, 13.633289953964551, 5.179967205867266, 18.490782180073545, 3.490543694968798, 4.24552493022757, 6.946924397977597, 7.253883748587765, 6.851790761195761, 11.394769202375352, 3.26634219846887, 4.211990003971859, 5.042336009896695, 11.770828939397605, 4.67842015757567, 14.749097973573955, 6.5873916392885965, 2.3387757624169856, 3.0672158848128195, 7.92934164313487, 8.975010447049861, 7.723846921896081, 11.984774072143326, 7.229743192952743, 7.505705343739316, 8.495590359748316, 13.33538335180276, 16.27706285964738, 9.36107227811259, 7.923184207252728, 5.517495932611694, 5.522119301202602, 4.735140782400862, 11.138559102707335, 8.44470440254027, 14.339870553212192, 17.772410042955613, 13.716922911944234, 14.039411571793833, 14.820203696935923, 26.5606291058854, 12.891991367934272, 3.150756763301436, 8.619232275842934, 0.6748897178589773, 19.451187707636045, 14.595918562724234, 16.843305653808354, 8.771191757875686, 5.855359332890023, 10.417192170306599, 10.809916518836108, 3.0416324285443173, 0.5810744638070495, 27.240706430438795, 7.115611099432373, 14.447619793737879, 16.82035845856587, 16.632955193108423, 14.454243239044843, 17.04170248744842, 12.962709215118887, 12.011219898207997, 13.517099565988838, 7.218876814952314, 7.206149656753047, 9.015254757267758, 51.35587531183881, 21.719037696152448, 5.119844664660654, 22.384828501168503, 19.37500103568422, 15.921780942183325, 10.610102588551383, 25.163503352726583, 31.517738981248215, 3.189738484683722, 3.680999395021097, 28.643547086548974, 22.36072251943827, 29.570509524665365, 3.494968654100507, 19.680813044239, 24.102126712451884, 16.598483042291324, 10.831110385713364, 15.83934542058903, 17.527628344600004, 4.459814178000224, 17.13460939412759, 15.824401543946262, 19.93211027564317, 34.29861952326877, 11.078660698843041, 34.385907953808406, 39.98553091246671, 8.850842596223316, 16.51240429140303, 25.83048578495727, 23.418147238173507, 29.753357095891953, 19.528317213506206, 25.472235070717204, 28.868857480891293, 29.830185931031735, 20.76242635397137, 40.23508295934616, 36.813703891649865, 37.233183549645, 23.82374985388114, 16.341701411947483, 23.889464018489022, 15.271633648683979, 31.06250435929314, 32.44688561235913, 2.805870127831281, 23.957544476773045, 23.23604732526883, 24.848551797390186, 22.50262773792915, 24.57644282715705, 19.996875026196584, 35.8321991481738, 30.40255251021981, 23.349646650864006, 39.29097592446377, 13.879075729633506, 65.11470141043048, 19.28397081024558, 23.26734474940933, 54.060912672854336, 42.401572431965405, 20.308559098679222, 11.823427102955446, 28.412402458863443, 42.46493442046244, 28.619961534241057, 20.182525281924313, 23.70096512095504, 3.093721661264935, 26.313123252864717, 42.42362512831903, 42.94438216917362, 35.62591699559704, 20.70517808306834, 45.32870514819374, 34.13532805915993, 16.159671542460295, 4.019799574997102, 47.893134260267416, 22.96967353256075, 52.37135493986441, 26.132975978747755, 45.687392878080836, 58.13041705304883, 33.74318237840515, 16.50058193217688, 10.18485452869357, 35.491910922617016, 35.37776714448712, 56.66466332689135, 38.54319033556839, 13.222736564892678, 39.9454856649377, 21.788045574248073, 29.858523906471518, 31.92101302381106, 25.155075615682776, 53.984587703003655, 48.23960477064376, 30.804488906894754, 47.25378832187591, 16.93129511099712, 29.998485847602783, 26.592567159599795, 45.593510508638964, 25.05913379969928, 74.00412406098387, 70.31901986828227, 20.986065436141363, 30.9164521862114, 34.16889827920863, 41.819129330378075, 33.34364045390032, 26.616312102558094, 42.90555826067797, 74.92821640191876, 28.687066850281138, 25.124641086882036, 16.34014812104813, 42.64175832970491, 36.52075666540054, 60.47204673780515, 65.47956741067941, 94.94523980192146, 34.72952173859371, 31.493957516657705, 48.86007072167208, 38.991082324106024, 30.020984064713208, 26.970283937145066, 31.547251346710475, 55.29093250788033, 30.77851738823253, 67.05747725032622, 44.79499746883573, 28.45594910219053, 49.30155788686189, 29.422734835257955, 48.91660081639699, 75.68110228598155, 81.30758616864368, 48.82391567227434, 76.76885207804987, 31.713368663504923, 46.744666622102976, 64.35860546153918, 56.97828520913177, 49.73732338864559, 43.79169658382923, 43.08707555900338, 87.59523876612057, 30.179858821794152, 66.22207977949327, 35.7700422590721, 94.41413510454586, 55.703323437923466, 33.42805862688525, 6.635272411217145, 82.21740006108605, 68.3281294194843, 24.314909645052605, 38.755100294791596, 38.00134599648326, 49.67144823169187, 23.17305943448073, 37.73348409180502, 29.449221756279734, 4.938233544072685, 38.27478746857649, 91.53818418708568, 59.838702796379216, 33.41626597263941, 8.282848754926107, 98.5048544944054, 46.17565448479385, 52.75649991244793, 61.00244098507501, 58.508500377875514, 46.54842555509706, 60.655166343375214, 30.464401397733724, 38.519403686389914, 74.00164308518478, 100.68464785060819, 41.67569918907228, 95.45906324789782, 36.954900896199476, 35.96790162486732, 63.55137530887402, 5.063552730550413, 38.755054544208186, 33.82708078139307, 8.955581235951296, 60.3609656585957, 57.64954742107583, 42.28681960150022, 95.12704766340973, 37.47289051639137, 55.055129175307215, 52.30967967984617, 48.3577690522204, 44.23588501809691, 78.80300338703881, 45.258573492165276, 83.33499049164946, 14.98449754126545, 38.05616316671413, 66.91998993284209, 64.70215201225922, 42.86665700392277, 32.336216646758636, 55.21390118950787, 35.85295526723882, 66.14503406923407, 36.28597846857431, 34.125064300889235, 37.91949416179975, 85.38255415869352, 6.605187529720898, 68.31268187138603, 32.428511899127244, 45.866431787768654, 39.48400881644037, 42.06782793745918, 70.25934921115261, 57.963955179222005, 32.434349518131675, 36.797206818841325, 30.47296203970773, 72.13564669205665, 41.725362145940466, 50.9122810150943, 48.788538317892574, 46.60665022194235, 66.35015674121462, 39.14064031492067, 67.75875497662668, 33.170477412601464, 61.84121949125202, 38.831596787932966, 42.806922433676434, 39.163256751687896, 56.442780793808225, 52.15115538289113, 65.23464479699193, 69.34602955174691, 65.59947946573871, 38.9347366165929, 77.97740079626256, 32.77916273371149, 43.96036669627734, 14.167581366735021, 28.292862341158646, 64.15942951463101, 36.36323792856359, 86.16776831862602, 104.61924522222915, 47.62946164891851, 56.854269390816064, 74.51039491310256, 44.79245412486132, 83.37382742037845, 40.44884555200235, 54.09992884375125, 5.300611151595956, 71.8385151396706, 64.01546266144081, 41.097893248711095, 46.59199583799228, 110.06706691806352, 38.05386045843028, 71.38263094106485, 81.47488660373348, 113.12924837302565, 136.09039321319358, 112.17146776952785, 56.72337644086519, 41.45251132541538, 77.22190795360184, 42.05723942442435, 52.25889481133591, 36.013495709901434, 75.57965799783821, 41.6089496984579, 52.2603997564338, 87.8290025384302, 78.22559645839486, 83.02414736759755, 88.0272957503306, 45.96428438188745, 65.49584458101081, 71.22659830548261, 59.32034472849415, 54.81072077714868, 61.63139290990241, 72.11136398366978, 33.88964588627526, 47.23764847869065, 51.85459569734292, 66.51862472312503, 42.22587238616585, 64.64781655100464, 38.9106089616698, 59.710095216391586, 46.46502883516719, 50.18192901312455, 64.72963838024985, 58.32224457835319, 44.38183235027864, 77.67138231634334, 52.46676944400257, 49.957611080744456, 52.36880548559991, 42.585444919292385, 103.13708125093763, 134.1344768699523, 44.47965084806096, 86.90283886359681, 82.06775284565583, 81.2325308008366, 30.430039144600386, 78.23684876695208, 49.0939765347064, 140.20613868539155, 71.3121409298965, 47.77497145354156, 78.6026236645982, 93.91673171124758, 55.34318475184429, 48.72277725761069, 3.4482958784312046, 60.048584469094095, 41.99891382658523, 69.02803671657368, 53.98304022687236, 71.4198369391781, 36.28665737359605, 53.940011136908616, 58.22748155318696, 122.42973563036396, 72.9650247285341, 101.30986300048036, 113.0968053164379, 71.79903248943911, 67.50082141820819, 55.92797267179049, 60.12767899589116, 40.513719543382216, 47.45042816099445, 125.59543328695028, 90.78581086263635, 64.35878861366447, 39.65336278039982, 45.32716784892904, 53.353699507969274, 81.90548795772023, 43.28417086410208, 57.60414062951912, 7.48142306597275, 32.67082174259852, 32.81255014672258, 163.08917581780304, 59.86749387145961, 66.22759544234421, 73.5970728993376, 55.474589614564415, 112.01423163178272, 66.94292550042076, 72.04249101385982, 26.513573377950955, 94.04441270066324, 67.1453416077514, 9.24115683173248, 58.29245365028547, 120.23254603224778, 56.58881415156156, 100.12095708861186, 70.70613776181501, 56.665958715274826, 34.59483813578356, 194.6108261477077, 48.39717124748112, 49.82347672675598, 43.407434951179674, 142.67338725612103, 59.01765083506498, 121.65604716016799, 67.71174019049887, 52.38592693198024, 131.74396283844823, 37.08675106873022, 37.38485261453208, 109.29033738673272, 81.64233849652696, 75.6918574155828, 60.00142102245236, 193.25006058985613, 50.536162423563496, 57.87991336185843, 77.93924373625418, 65.5682488432649, 54.924189054319534, 52.05873942614464, 63.602547732338124, 133.50715224037148, 85.78750291505534, 10.753976219015179, 108.74487693313863, 89.35430311063584, 44.01386810066762, 76.26042173731946, 52.49357708243062, 38.90452722230663, 94.13607801360335, 58.66136215984361, 86.16924481388502, 40.827235723669, 35.10987881532917, 5.653823127907516, 96.84111434502312, 46.733260330004605, 48.94989032531941, 51.89039144350795, 42.46016728541113, 36.53603055806164, 75.39246548818909, 43.68553645903522, 56.71142151786337, 119.26549413270293, 18.928500275091, 46.10435680061623, 108.56576490008439, 147.7082269491341, 43.79892766142917, 38.090241819267476, 53.118243344616786, 140.21507539141984, 97.97364926764114, 57.20248883548788, 71.07927190371807, 66.99289961427017, 64.99061038384589, 47.3521798670624, 45.88897030741475, 17.158112343097933, 93.09301454360943, 82.01013577845487, 100.73176163160842, 46.9724027242059, 305.44618023469144, 63.371557957809806, 124.58740200329261, 105.90336648292724, 44.84400512325892, 7.64669650738412, 48.69285126320418, 72.32889658285033, 42.74537456292571, 47.08596207591402, 73.28857715655012, 49.95314157287672, 7.8543645861121485, 48.22797154574642, 117.09889417068358, 71.78420688472826, 47.32369065650451, 79.55809347543308, 55.35511082819999, 56.69442733668728, 41.95255242192437, 135.4553218072198, 27.11996606149243, 55.95842502830425, 12.415328310434822, 45.28183230108539, 80.67815365895581, 62.03865260845363, 42.13023316527073, 136.96004281130269, 34.306015764161366, 54.49981668391627, 35.34428940284797, 98.92781146901133, 71.17521717960784, 67.2001882055784, 130.6517753729152, 45.21282367274962, 33.456200534087316, 61.05003612687384, 58.44409226928136, 98.47121414819982, 39.1626930391345, 5.231283530562192, 67.11713211565237, 52.47069057340392, 113.80004047307672, 65.85608356766195, 96.99514345392652, 6.353787631390147, 14.103384943395692, 89.270668685775, 68.90880098110533, 54.27247087149035, 119.43864877188881, 32.453070933965314, 66.90392359339332, 87.99379434910264, 156.20715025099238, 61.882110387057075, 54.03824928276524, 56.53639902407168, 70.96396602199852, 99.38646880023299, 54.14532531103357, 44.608452578046325, 172.29043032642429, 67.77801956473834, 38.94779173269701, 61.41560925874614, 37.46223983194999, 50.61398107323759, 58.12363370585036, 63.721873383244926, 55.8285252638901, 15.670185288846005, 44.10621320947619, 57.156866443332476, 49.9733495917036, 64.32224546050962, 59.42478484630288, 50.149217947729774, 53.35560238875413, 37.21784956437672, 71.01044516307127, 56.546063406938615, 6.935601747825675, 73.27622292397676, 147.19406756242086, 73.55708584650709, 100.55782447687729, 87.2814110844419, 54.89374721118184, 123.54356876183463, 75.54161248276525, 37.563069117182174, 57.76010783369633, 38.421881844072786, 41.99448935572517, 107.28547421888011, 60.3969860673059, 80.68620978292985, 58.35370571043911, 45.695106429884895, 85.13409013834716, 55.00256208132626, 108.56906364767491, 51.5366428962714, 94.64226441796505, 97.3949592753161, 73.65317974526016, 75.07431999965841, 50.02259241853514, 132.6908749360994, 57.26445883107847, 43.24704071716097, 43.33654381640471, 46.80142519604893, 37.329839973066434, 54.28021235141107, 119.02375145075293, 7.788776861904385, 69.14088487409795, 62.18796683380929, 52.67577022750632, 157.5202146130362, 44.1700327627862, 56.91846185514408, 98.47669764987721, 67.68755333949635, 71.4100098558995, 6.637260187848109, 84.01605278722425, 50.41452930295768, 41.2736269925903, 59.61944186220952, 84.321426049112, 134.2758781866136, 103.19444746646238, 66.93455923278435, 93.20873556397548, 59.53427975155147, 18.038009741094637, 49.79847123709545, 71.82756302367478, 48.053371197697004, 6.461664858747446, 43.72553209561198, 100.14013245084298, 167.55318458806022, 6.577460841710066, 77.57838762170515, 73.4807065804683, 93.07344945450713, 119.66575600553738, 81.55034115354785, 90.73925882511924, 135.64386594777966, 41.704964612840584, 5.699175321146129, 58.401195759032035, 48.34643299891411, 64.19746247850453, 97.83231274370931, 73.47680926596539, 65.4454893936942, 50.114826679483045, 161.32430120748464, 50.61713479060184, 117.04130820199653, 118.48101500661197, 60.54089622920256, 66.28894823294551, 42.93978916596792, 56.90716014389871, 57.040050198201406, 55.40094360317117, 60.23200809915211, 68.61018467051008, 53.02671366767635, 53.98995852343646, 99.4959889876205, 71.75263075670993, 131.37799605913494, 70.99900063864573, 112.0689809808552, 180.17970286262207, 60.388245894898446, 54.74913977581362, 113.5212713565447, 130.90371009285846, 91.78653107811927, 50.845311451718864, 72.65091993769309, 61.2864135513704, 72.5521240198944, 5.338123056757249, 97.18336254924742, 58.215737255858066, 109.03113193379743, 197.53605607963826, 47.29271617456499, 137.4759892523169, 88.9144938925408, 71.69407411659898, 65.02613292913848, 53.01982234971809, 60.55912943636452, 59.08001870208362, 40.47553566853113, 84.35856668421472, 58.841203019625176, 154.16696324052413, 68.88064887747035, 38.99416576407208, 48.60952211714648, 49.35091563297924, 69.47161637937074, 56.965214529901196, 48.00509961656439, 223.41903370678523, 90.58728058890307, 52.18531978258136, 61.727256016627955, 10.121816518269197, 47.014380951768274, 50.221043368303654, 57.40868446328822, 47.01327160793883, 102.00249622194542, 44.29919825580102, 70.76119612325965, 67.44925636951906, 46.59794016070336, 39.370706979331274, 36.43974274982989, 72.50760155834804, 46.7600017773946, 59.92662609716877, 57.19673099578067, 97.75248562922418, 43.574978379960235, 62.74687790259147, 6.148564713628613, 43.322735093506616, 38.20305742962545, 78.90278023301711, 45.625333417395105, 173.01657381774723, 70.4139642600077, 70.76989792659754, 50.13113317692724, 48.71534038433224, 56.089170624793425, 69.46654457490202, 167.11067608503726, 45.41896771992331, 37.8265123596164, 79.6219405325144, 51.197424157739796, 45.673396089237045, 160.75122727425807, 103.80108106013421, 67.2154627662921, 39.814730100772906, 68.73130657445327, 42.30878972145297, 58.50612814874265, 186.4631490173298, 92.4526571791281, 122.73053552632368, 50.96432551318904, 76.9249873948364, 67.20065550406555, 56.71191980468361, 44.95870087810408, 117.63560907811211, 49.30226402854721, 34.84483772823398, 46.76230814769599, 42.83871076948734, 93.88347635505275, 61.13905233195652, 134.9730002232044, 75.1977801106447, 68.02578542243616, 38.340328492114836, 76.50347437309182, 6.7530824250110495, 79.2027771142281, 109.45904527248373, 63.396561215578075, 92.66115678258242, 73.34867070024902, 85.98016275749846, 79.67434314074364, 67.32239650765733, 37.40705037464603, 65.93429635674062, 61.29892306811671, 41.5026487127724, 83.37231016041494, 42.74935786599464, 69.1696218504991, 65.11150165388686, 176.27200514236543, 48.434448794172965, 37.24842282708956, 146.834038492149, 45.061052332637225, 39.5291219676629, 41.89218843721196, 7.824601692492899, 51.992072767324686, 63.16118916315665, 69.90923453359645, 148.29140960919426, 68.57863743003638, 51.374297458608375, 65.40342733156575, 10.156926531199801, 89.03913249245167, 120.37513118981188, 76.89368196315745, 100.88288940562099, 56.9689077840555, 35.58355823896256, 62.006544152408146, 7.1356349137997, 58.06551770273438, 66.96545985263413, 95.09749788797643, 93.42059613987925, 78.39419130385288, 159.01359165956737, 63.4454490524088, 16.159810519367504, 50.83263004729965, 73.61760055873273, 42.69097748913243, 58.30607162922112, 82.70159591649696, 7.387980671688939, 69.98666261340503, 59.47735352627706, 66.19566212252981, 66.86853725168582, 101.58061910962871, 53.34728463012292, 102.25286670466983, 6.561247609846066, 14.770673329070805, 61.115976397387804, 45.72472869523151, 45.94223311628417, 60.331496950115756, 12.963778354616071, 74.61245345040686, 55.67529406389873, 73.21369287496752, 95.39449380085698, 57.814073636806626, 98.49204221981273, 40.667596359710956, 64.642702736805, 99.28426936436423, 62.48348868173537, 64.43290436559549, 59.51139159222667, 62.30402534355104, 50.945307907118135, 80.78214933163365, 71.09379619692034, 50.22583065187335, 61.10408560471973, 68.384073271565, 73.94973707458722, 82.63140546580357, 37.76898952145004, 59.58784186602704, 51.72504030226297, 51.47260178473136, 148.3324015807873, 78.74925465467012, 91.77832044996991, 136.35921596063488, 4.092151737148332, 9.171073192775498, 132.0000159023564, 90.67842628200998, 63.00468778692709, 144.43326608976966, 47.696194672841244, 255.72672712026738, 48.787316666209755, 54.53753415563474, 56.63165972237352, 6.298700194371234, 79.01379483478098, 45.5928373516173, 52.96119186606803, 52.82578597691307, 93.4670093412822, 38.73901234963358, 56.10964077206831, 50.7960449621004, 115.25366935971462, 71.07062171636889, 149.61017286147148, 111.27705701687947, 92.94122312211877, 88.64858035078096, 96.23712306395647, 52.94273974837301, 71.46029543224128, 97.85903725084971, 45.516875488218844, 137.45742785975196, 68.44922560824297, 146.01785983871952, 98.23960545258491, 52.69986706259817, 67.96466006236304, 69.03076663873536, 49.34894711182366, 41.672902245491656, 64.27363324569606, 6.79799095134316, 55.918358657770966, 64.37740870109546, 5.615443020671253, 46.61959719037523, 66.79323772085186, 77.91670698343464, 72.80062692009662, 90.89765335653327, 5.838093347073533, 65.17842522941223, 91.54657125327476, 67.05053435057897, 108.88315352144495, 72.08223627541521, 58.463447985497965, 84.00980209129827, 68.42242657020648, 57.33325626837335, 57.79061906516136, 8.674364936364226, 74.7672149901456, 65.33145348708472, 68.59558559901197, 161.95641830719907, 96.57826344352071, 34.59016932590119, 71.66018153725706, 48.70707016573641, 95.2618302464352, 60.501913725859914, 67.93129444887053, 104.04740848405916, 81.76422624830734, 56.39262330597112, 192.0452787353368, 62.971497755150146, 100.49521300956222, 52.316356165674485, 51.99526501167965, 59.90451969404824, 73.91769940671237, 64.72377184184046, 94.79816143103582, 126.20008227287713, 61.558643432002704, 49.92156585115315, 74.0518860528071, 63.69835423718864, 61.592636638628925, 73.34565217760782, 68.45784675904076, 76.7018575478984, 148.58770968422021, 62.88734272040568, 107.16718002795031, 50.760505032929835, 158.76002238973342, 63.94624518969342, 185.69870146864355, 95.10797570342709, 89.05834347795232, 37.7366986627, 85.86695708412563, 92.21144436354624, 90.31097669083684, 69.70651598481149, 86.95837756186316, 86.76680368302195, 5.490315854871829, 76.43752091995634, 149.31426752041068, 47.31744303346322, 57.277536015421646, 73.87226295882601, 84.37345844938902, 62.4157044324558, 120.25801337825088, 70.49684073364602, 149.79043724419262, 94.87943884003624, 87.1598193472491, 123.2630666788774, 118.44322917595332, 57.89972076220127, 81.03587539579709, 113.60986875056342, 50.60443167607968, 109.17706936281813, 50.3672567617006, 42.58269526251277, 81.25123839647844, 115.06763282263843, 230.42834093196768, 56.6775482211974, 111.39490125959297, 141.85698629062819, 73.73827801443859, 56.194347485806055, 243.85520245344992, 129.70012085452476, 57.70032601118277, 41.74336446280066, 58.303743268981485, 73.80407814377955, 51.629540785695866, 73.30842699339098, 68.39059692787627, 82.71545320091654, 101.07853777577472, 49.06388060966684, 47.37003754337907, 60.88093200290914, 61.44532825659249, 52.91264828845438, 61.65313232724062, 60.76711376872314, 128.5890704747002, 6.308288742573415, 55.405942230269346, 285.53240365924046, 195.08978543003195, 380.0024785081559, 72.66900717204416, 47.791577886165804, 48.50354662465292, 41.85219776840153, 175.93229697866275, 65.69466220869671, 70.0980085741565, 119.19089611657651, 64.55733276247426, 58.86169372656987, 80.86781244452212, 51.30322884158983, 39.53186820355422, 43.64447754032522, 110.23156708159573, 81.81346549927294, 54.69894450802351, 36.23224420530238, 49.65642581161608, 188.5946382277632, 147.22554558644325, 129.90851215596436, 111.15936735526537, 125.37229585901645, 167.83534794307343, 49.968166184908725, 83.4492066628815, 13.889524536547246, 124.27019920729076, 57.201217269944415, 75.59305079037894, 9.12563245413265, 76.19243963897495, 60.24325345004847, 48.835485145844196, 59.22675154537582, 50.2950533607301, 46.02849249124453, 54.01763429768611, 50.634912771049024, 72.87470250975619, 93.2812985685655, 51.535077502131294, 36.23990786786834, 67.6648951907015, 80.50474315342069, 59.76866313531274, 63.897095195349635, 121.01638547687097, 38.94060088113143, 101.81980305865223, 44.93350829647382, 46.45994518374799, 97.93336498793339, 117.04116321458149, 43.92045115074161, 72.03452512668791, 58.03670959672409, 55.7128666964698, 6.98646709355509, 70.58536786482827, 52.176379017672275, 61.08137008708244, 75.32836363583631, 145.1001342310793, 93.73095222926996, 72.28842147828932, 97.97770880749314, 83.38552622480557, 88.16533100801024, 146.14563862374706, 7.619150014074966, 264.4893273360524, 75.66364345641988, 9.302627041109242, 42.97703025652149, 62.409330981277016, 84.94810196810323, 68.98179479109477, 268.7927946792391, 141.3776859551906, 268.12120652134814, 96.50869019726817, 75.88511296163207, 47.31421950326613, 120.06967727199266, 74.44374885271519, 95.63624051950434, 63.9169528769464, 64.83578640013357, 42.40935654425965, 85.09791513482246, 137.24742869962643, 43.884223247816095, 74.03583687379785, 7.003751160587275, 126.60767578610948, 72.06767052800781, 137.39217584198613, 61.86435857141846, 86.17331828013744, 72.25403488462543, 148.80018040792032, 65.27189835303487, 106.59739438531531, 54.20207808873285, 70.9435261977347, 36.29498497828408, 56.15278856707407, 58.09705633439272, 66.46405442166292, 49.003105406696406, 84.26560125827513, 123.23983075611974, 64.93022771603773, 88.35699797437523, 46.492725054942, 54.14688468616739, 51.069300837912394, 77.81417733398334, 69.20755352016592, 144.9542834294037, 69.84246356605242, 49.23901973583998, 66.46436244341193, 128.02113517797883, 48.515878650533296, 88.50562768573614, 61.692067009411616, 65.53508179532265, 103.4655539436449, 45.30249785256325, 37.8760098958942, 59.95905103691868, 65.131691348992, 119.26135287549366, 64.65492018923591, 74.91440831213647, 173.20782126694698, 102.81628487589047, 25.628056899959248, 54.12639901052157, 58.37452975144187, 71.89798645699823, 62.04782097523409, 77.87766688518641, 79.3077617867869, 97.08278857257164, 33.15586011847807, 15.75700501680728, 81.95511620925781, 11.02099611590281, 67.04781912960591, 209.2763320527725, 78.88550479041098, 65.27387653170037, 105.16130668464562, 172.40855445743858, 132.11511817819567, 76.61838532966553, 78.32927646304887, 61.979942491044284, 82.490613807828, 86.89769410105731, 73.80919081052029, 134.09731956813494, 72.98890340975984, 97.18346992673527, 57.41356818402534, 42.853336440609546, 54.01448232112106, 65.8704295335478, 82.3393989034969, 47.31273891485523, 41.854156639239385, 59.73667632956975, 58.70910512439286, 7.258474399942425, 66.73522753834817, 7.71955046212587, 55.52739619147403, 126.28540103368702, 53.34429067162315, 139.67783778269433, 44.317668763533725, 136.55019796740186, 14.507150504746274, 64.23098469525063, 81.74579098432216, 45.0500950569472, 33.24450253100497, 63.82022396267914, 54.079025016251045, 65.64892055849396, 78.407613552483, 35.19036972268231, 39.020428977087334, 59.53588980473564, 53.14964519516745, 55.07296580080451, 40.725258509856076, 47.234773035988255, 93.29819632626463, 219.68589370453017, 43.81271202524582, 113.38752044960391, 32.780309449533924, 90.77234006017542, 82.73138452423619, 65.2437432344864, 73.28969781265413, 83.18898436201373, 97.00485060297322, 61.29241076977894, 59.85228496355319, 63.18304463921395, 77.81307822574774, 54.82491199189069, 106.11197366243736, 38.87726025619842, 106.16457888965668, 163.08388667958423, 63.02697995671921, 57.811985237404954, 81.36412924467906, 168.68843724765208, 279.93496052811275, 112.87128713501333, 140.02108950004722, 86.63404618305772, 136.45813076212468, 51.46260929054057, 101.19689082182504, 71.48316243607978, 45.69379821470429, 46.08308203296672, 61.02743177974987, 53.12075271228737, 78.00525834063833, 65.32871523181393, 81.51804230019141, 96.0402358456662, 91.08462927451376, 72.05188630011057, 55.19089962173007, 79.89307390849223, 83.7985991870692, 54.039670610322595, 84.8822677069816, 61.72735386214755, 29.786953200217518, 168.12374492955644, 115.38991334907054, 92.00257449791077, 253.29342020909556, 144.08937318773337, 81.18527270727053, 102.14340720971214, 77.81921992336125, 221.58675578336712, 80.8074895773751, 217.53334695493953, 117.14165171235851, 42.399091010347476, 74.93715083485576, 98.37452219274205, 42.836734053039244, 61.341008878261974, 58.31936314341254, 108.33783211907898, 62.91153833579847, 44.54878994508437, 90.29102697048624, 93.46814754235315, 67.81278586432876, 92.55436171363581, 42.98335914177121, 51.49010465557152, 92.16110443574149, 43.171736191287394, 59.465528405294435, 68.16569257614977, 133.77509286801896, 172.4654815366574, 36.88328558104962, 149.51581737282513, 136.79793855721778, 82.423211145599, 59.59686598287247, 103.33224359991786, 55.395127977225386, 127.03462781039019, 65.55972319491605, 67.80891059488773, 148.9127695557809, 64.422423498213, 60.60223519912421, 13.682079443882913, 139.80399678968948, 99.3026528898566, 91.37526409589606, 103.31368321055656, 141.019511788724, 60.24926038980701, 149.29445134334188, 136.63115648621414, 54.868667604485196, 128.69468634418985, 111.2917818487726, 83.9436728688062, 92.83789112544368, 57.537501635222355, 9.206042064480119, 73.28626575196888, 74.19104609249251, 158.16373912430745, 61.73946628749083, 106.54963471531808, 57.015630853502316, 142.09846218275524, 52.42115084624306, 48.85271568917833, 45.449216626185894, 62.08645347558374, 138.99191615747165, 72.82104519083316, 94.92527094563204, 41.50246112775399, 113.33485344762201, 127.21817749426238, 78.0796730928057, 55.86069726673047, 44.50674658773788, 56.83031719235296, 149.67537181325773, 43.54345487581831, 46.550223135396934, 56.732090050916646, 56.649072531325295, 47.43384277335076, 37.70173209138282, 67.73137310691193, 92.94871430572455, 190.97462796218946, 61.76275482796388, 81.98868307053088, 5.2384217305131955, 131.63720968668918, 47.171815558790044, 58.78082480254102, 44.31102761938681, 40.531829067357926, 136.32008992883337, 77.40169218441035, 79.47724071688648, 88.83470659583556, 104.94228073523372, 155.19565718163366, 88.36554831476073, 58.664222631922705, 108.06534031603748, 77.53598642436782, 48.7160569723396, 81.15847200652972, 60.975337115249914, 187.39594366122105, 72.8260861871574, 62.86501471037149, 145.8972032363174, 230.10645913911733, 65.6925798251248, 55.12589273611851, 75.82231732653221, 87.94021941098384, 50.180454995568994, 23.647620617866732, 121.14774838544692, 162.17443077756488, 302.5611422579019, 158.8479063300643, 61.265691350197876, 48.24166663932106, 120.51669950033333, 88.10762049492568, 63.143640240831935, 70.12690186805249, 68.53348632467245, 61.87386150378443, 133.04595748172372, 63.771738521295205, 14.187628909776608, 53.93697735541476, 80.50721120244799, 87.86672259304173, 229.29466102876628, 56.82253489404945, 57.87236041497363, 89.53556497286064, 63.161391079050624, 144.68691332700942, 64.9616324546238, 59.21960040604072, 81.8370749146954, 250.079909623832, 106.61325329272721, 8.948332401376021, 131.52483337796477, 51.11597342714573, 192.7142966528879, 52.76079863458859, 52.35516662235492, 51.90621943316358, 135.62727645354713, 82.68473511440155, 74.10574795539395, 71.89654327120208, 123.53757262191452, 142.69058770719755, 104.08916512337647, 113.770640259652, 47.68430173557941, 8.590236747432154, 131.22145958771927, 46.252243624958446, 40.84806085707764, 73.20983639206524, 67.95862833631301, 88.2724966450299, 40.354689109638905, 62.67886542497512, 97.9744863858815, 61.41738073070318, 79.45222767003702, 169.80510592692997, 159.76906373947457, 115.62774122979941, 63.258000558735766, 70.73223592239606, 147.82123533602953, 94.36513518787378, 56.30239787160678, 55.94530531034397, 76.60334972106395, 32.44819169778046, 43.85883531588, 201.63951779645856, 109.09913611693379, 114.3417836194962, 95.56568360378105, 38.781077366398634, 91.3631079184364, 82.90734705650041, 91.9144519351368, 87.39549161594198, 59.83466064561344, 90.77584990950243, 56.32528872457551, 86.07763280062528, 85.19493508216587, 77.54511670896335, 38.32453420893928, 67.74706287311155, 70.348200870339, 77.897367443241</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>117.7682032680512</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>88.01802792983355</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>[156.72183227539062, 309.19775390625, 63.43281936645508, 149.7366485595703, 119.25753021240234, 84.31403350830078, 58.86494445800781, 62.37976837158203, 147.61314392089844, 22.043323516845703, 71.78632354736328, 58.1161994934082, 120.7547836303711, 11.290372848510742, 92.47906494140625, 93.79483795166016, 192.94717407226562, 242.3980255126953, 52.099212646484375, 77.90487670898438, 53.329593658447266, 117.2183837890625, 106.65774536132812, 50.663448333740234, 278.8909606933594, 151.56756591796875, 142.565673828125, 104.76952362060547, 67.30170440673828, 74.61656951904297, 59.96711730957031, 338.85797119140625, 107.98468017578125, 70.11933135986328, 74.24215698242188, 61.27457046508789, 59.867122650146484, 80.87525939941406, 56.24273681640625, 98.3623275756836, 47.91291046142578, 107.60343170166016, 52.627166748046875, 170.6168670654297, 68.83269500732422, 82.33941650390625, 211.00711059570312, 137.46530151367188, 429.42474365234375, 203.7994842529297, 499.2330627441406, 385.9274597167969, 14.531742095947266, 88.76226043701172, 64.41699981689453, 118.47665405273438, 10.885371208190918, 75.88716888427734, 157.40451049804688, 87.97368621826172, 117.5890121459961, 73.27548217773438, 52.54865646362305, 33.197784423828125, 16.908113479614258, 106.68124389648438, 272.1741638183594, 50.488311767578125, 59.00096893310547, 66.99125671386719, 191.6256103515625, 105.53124237060547, 74.45954895019531, 55.55434799194336, 63.51416015625, 47.6992073059082, 104.73175048828125, 63.66995620727539, 127.69207000732422, 168.47561645507812, 42.9727783203125, 49.99723815917969, 139.8504180908203, 170.12786865234375, 57.70359420776367, 144.9232635498047, 72.85795593261719, 228.4178466796875, 224.2495574951172, 133.40171813964844, 130.61439514160156, 80.4258041381836, 336.7170104980469, 174.4380340576172, 89.3201904296875, 70.35353088378906, 96.49297332763672, 101.68607330322266, 114.55757141113281, 108.26884460449219]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>p0.5srandomst0p010230</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-04-04 06:14:33</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>100</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L56" t="n">
+        <v>84.13482557341565</v>
+      </c>
+      <c r="M56" t="n">
+        <v>60.64578292850809</v>
+      </c>
+      <c r="N56" t="n">
+        <v>108.3456201214224</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4612</v>
+      </c>
+      <c r="P56" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>[0.8887089685177488, 1.712225472645772, 1.9042459995872083, 0.5580048086616287, 1.3030470707213684, 1.0023846375984764, 0.3884482898432192, 0.9866477581663341, 0.4440388557033221, 0.37992265713830287, 1.1334478273243294, 1.424265855721227, 0.8671015725920974, 0.6280641742032147, 0.8844584399508091, 0.5647851117569135, 0.9947568788689259, 0.4535687915144612, 0.6537179135451869, 0.2974611546271942, 0.5104095746621956, 1.2527079470141929, 2.241966398700211, 0.6919658689608159, 1.7732839644020344, 1.2177886065103076, 0.6480204131731068, 1.8999008087420743, 0.8019236454871834, 1.2370839172917278, 0.976062477949543, 0.7790388677379393, 1.7527867703507165, 0.9401750420662629, 1.0212125709120414, 0.5326104257849563, 1.686466419016164, 0.5959832707734757, 0.6063592819819427, 1.0889144473965748, 1.659179408443752, 1.0328375211239469, 1.2243564168492815, 1.5788691700675368, 1.8406294854852097, 2.9761563556351507, 1.5977811101615451, 1.9616978928747988, 2.009924307799277, 4.513250718067399, 1.3183582615606169, 1.7385873738958093, 1.0424822582703273, 1.7655242455000053, 1.2923306556544272, 1.6762808211827263, 3.4705805661686906, 0.9207428474221231, 1.2834475343100509, 1.6511833885201457, 1.7564492547833515, 2.6422873326683187, 1.1399558401465946, 2.8536824778252026, 2.086821584232492, 2.211705735235304, 2.1819748520748954, 1.684602957288307, 2.741883688828091, 2.6447404863542365, 2.2461251491161836, 2.018782798517402, 2.464079196103907, 1.5863166583675314, 1.7543022323938335, 1.1493925099870703, 1.4128292788619987, 2.791818548627871, 1.748568275861171, 3.0621791329624823, 1.984169283562311, 1.7049750054137343, 1.9747567380111386, 4.64609085911598, 2.479141207928678, 2.2396834420702785, 2.6147077918806563, 2.006606940505993, 2.6710700125289897, 1.288051805099176, 2.196091486729384, 2.6221943078922494, 1.9668834518605895, 2.297359609460382, 4.209966352000175, 3.831072962496946, 2.0732035395184716, 3.0125213730030826, 2.761156377553286, 3.8671841415067973, 1.8139330450937265, 1.3241686285375842, 3.1055675147895143, 1.6460172059466087, 1.976345325623754, 3.331710347466923, 2.8782637852911366, 3.2011593550470185, 1.4153121980355927, 2.6764657123468565, 1.6542263624215305, 3.5048874646273482, 2.6762041813669373, 3.4201427046356283, 2.7127374573339442, 3.0385358298017793, 5.098792800522228, 5.769496677850722, 1.8950236065720243, 5.073062572169857, 4.529860219018123, 5.32433313805565, 2.407131803203464, 3.9094224845087053, 2.414361198286116, 3.7667547066266556, 2.495580729024547, 3.406464012699505, 8.07094870618879, 3.8593066483584084, 3.3696249176017843, 5.26314294954754, 1.7974919809088117, 14.648055204521011, 7.115543055483097, 3.233849368335289, 2.1705459166080554, 2.766630003527251, 3.7058084356451295, 5.021236028047337, 2.5154758540630895, 0.7908661398870743, 4.734866593874382, 3.0353056885893634, 3.6805299644135117, 1.757400939703125, 1.92404952198473, 3.3205327285140616, 5.372873532430028, 4.546538733517711, 2.932093739016275, 5.057811830843822, 2.340382245879197, 3.5767926706161637, 4.308625314154804, 1.9528365395770328, 8.392399263082751, 5.865270121926468, 16.67587052677299, 13.533800313564702, 7.249479595675118, 16.99824205391536, 2.6160234477800945, 12.223765047968246, 1.7241060353553639, 9.811273548955063, 12.230758543396085, 4.616929994851838, 4.982029561009453, 3.9800804067193885, 9.149545011122196, 6.697570850624993, 8.489616158298695, 17.876309395303927, 10.926549882057957, 3.6888232953535103, 6.519603514457053, 5.825878182087193, 4.035547199902397, 9.29331342842939, 5.66528833761525, 3.593648109782876, 10.674106410177213, 6.340209856687467, 3.225525251174467, 4.963418339265314, 6.187013593855035, 8.115825708949245, 12.385611561164696, 3.944215837698885, 26.24343093634278, 14.822857620054487, 0.8713025645354406, 7.7566801527352665, 18.788187067965602, 5.509348195787599, 8.09123328372199, 7.791965255245548, 21.345173079149504, 19.57456327797773, 1.4147732751828266, 11.859280730034092, 10.696448205460154, 9.973068135100496, 17.434200326672663, 4.941535625193868, 13.862308161337282, 16.812289233463197, 25.1350682136862, 14.521538381251718, 10.05889362137205, 7.760846309697314, 10.043600692992127, 10.053006247368364, 10.609515662357122, 13.991737601603823, 17.241809561833715, 17.500524745528836, 22.36463148804343, 16.822943124994804, 28.30373807163844, 23.568378164919565, 19.259216054284316, 22.9118291349566, 20.722336738724145, 14.122752555078856, 5.465075520811643, 31.654096144667374, 10.516765528387472, 25.315026549121164, 10.681593227291588, 8.816212737670146, 34.091440587021864, 14.25051346784954, 13.22204221029307, 3.6698724200644413, 13.263561943211561, 20.176248053170795, 17.7902469111846, 25.365094910155523, 22.34142789861294, 12.34155603209597, 10.642691364349535, 8.973843981836154, 25.519582212490963, 10.576123054666072, 3.0430116303239814, 26.081110210714726, 1.972248335001023, 31.53095617660606, 17.971974072840588, 35.168995202341286, 28.671045280410766, 14.08945593690217, 23.19452126999494, 7.014084521115692, 16.828288493477434, 34.14224449784001, 18.866301485769764, 13.315590487195681, 1.7292562840459131, 29.43429267930902, 9.59025556957668, 25.659846630101367, 28.384397775946297, 10.868228774543873, 23.07911859203101, 8.857609907977238, 29.146578024560114, 31.404567465699863, 18.379645630796606, 13.0805666966965, 25.132528348104803, 23.451250444272045, 12.334445868600817, 43.88858545619872, 17.477222564996573, 48.327797876600606, 24.098105691516608, 15.801477009626533, 32.512829420782154, 18.155442475012126, 22.163519142799128, 19.439790668540997, 24.721250534870435, 35.354894252944256, 19.855370396081604, 29.904585060630065, 15.978140706864975, 22.821920076839074, 29.144737312205223, 15.655365191071946, 26.69835131387461, 23.237386451805364, 10.797364433538409, 31.887550164569586, 6.479742281647486, 26.394770603869596, 33.215433162079506, 17.974707642450806, 36.775758264759325, 38.212622167324064, 46.531836932963174, 41.997508928308505, 64.1787422169227, 38.48949683935999, 34.59951421397093, 23.6787940186647, 2.6250911732150706, 40.788067362763705, 26.628819163451826, 84.8746081307158, 26.919933450615037, 67.31001009326492, 18.809104464536503, 29.056431307561553, 22.45896503566018, 20.877182849540617, 18.520811441493297, 24.534228960133923, 29.241809722468847, 24.447648608342657, 25.885948353290875, 36.35596442892324, 44.10299432013161, 3.2560059643531623, 31.99709114497215, 34.826912371294675, 44.14403354226578, 50.97171055755981, 26.40914795509347, 32.406034047450305, 32.84754520117083, 3.77399782946677, 22.362406668186903, 3.831390320553308, 86.79262987291071, 19.761760130917963, 36.49311046651712, 46.21594511192208, 13.27830653015261, 59.34936200099434, 62.80637877300573, 25.247066281887207, 56.16360699252498, 49.94241897784501, 9.678340571801039, 34.60880675506916, 25.451289696031303, 48.18480777884153, 49.30420958084721, 51.40355011804683, 59.34441793363768, 29.96606985592455, 41.52002465872067, 67.40207758129735, 46.69553899414056, 60.880367862631594, 21.98775846292552, 29.38552631108299, 32.05678705029762, 46.20930932236945, 34.466326739032176, 79.45205519084814, 64.08376725214228, 54.99177489137162, 41.431227840518794, 24.253102732826864, 22.3721588340406, 43.7983901986984, 39.027885237975475, 7.144388705232764, 33.896598302269105, 33.55154974474901, 73.85851498908207, 49.06713036397746, 57.87849777751066, 17.84322974369946, 59.4411741702046, 43.197401576051085, 7.25357768538847, 7.252722671387152, 81.99587094494015, 43.57712449781483, 43.66172792920521, 43.831822055008956, 51.70266386918994, 51.72990896363609, 34.31533367994624, 7.990126960955725, 43.35187288944054, 38.66880315772372, 19.826215449730757, 38.221843118474666, 51.96729985253195, 43.12530459363515, 30.552942038673713, 53.836945855225345, 85.1171336446072, 20.270588178212222, 34.06805929310595, 59.52589763527516, 28.746067024094124, 66.61812168324603, 43.34396416851378, 40.47257497122024, 24.793217955608387, 39.55440233948394, 39.73163209719389, 68.52762889451922, 35.732527059532735, 35.709752952757405, 43.99304935879458, 43.24838200314481, 45.244104148743546, 40.869905762137186, 62.42548808372114, 51.908258643508, 44.118335887552675, 43.77051436679684, 62.08146222966476, 47.32104861172965, 37.70854208831732, 53.19307599540974, 30.601011277211164, 45.90669125580153, 39.5091864857827, 83.10415481066187, 100.52677044698375, 26.49555304786025, 50.62554001409608, 40.45885621265647, 33.511602189495406, 46.06775609467562, 72.0827497223349, 104.6406357276736, 65.11511272222324, 4.584141501884143, 53.05271078715996, 45.30202389106285, 54.20488873591991, 38.00654918542655, 38.827658885257044, 68.64073762735593, 45.755447693617924, 102.70168555903209, 7.021552666457668, 48.90486566279585, 77.22841907115017, 46.332513007026094, 44.6237339917996, 52.52238312077793, 39.014795532014496, 33.18266468454177, 51.842133103181446, 30.830098431757335, 51.508436679708176, 58.71940995278818, 45.50497288178434, 48.70690328119047, 76.67991161464923, 37.70924982688256, 43.824655801243324, 38.369615836397415, 43.97159744365416, 34.31852639504848, 32.17813310330609, 48.08222714016049, 82.95112841173002, 43.60177380701165, 41.58124870978047, 112.41067752740251, 22.83352021251616, 33.24384916072669, 40.807474312444974, 59.838656902220364, 69.53467461414982, 50.567873969015, 38.104813381416506, 27.572460609329895, 33.3249603637756, 32.86212310836141, 47.69871456831165, 138.83386995067832, 55.42624846627559, 52.072684254604745, 79.02832731559985, 7.305148871805976, 36.6976059057047, 32.1210599324309, 83.29737993042487, 38.082693124286784, 34.69700406108914, 88.8756123455617, 51.081545257156776, 57.66737511300893, 76.114399117976, 34.9460148815557, 27.83996733172616, 56.46597773090904, 84.31645909827175, 26.7514107106657, 58.330108508725075, 137.00098908612847, 4.760729805521677, 95.26462889899054, 62.01527092989234, 42.27144317760841, 83.70177503320501, 39.27335878413663, 50.72804664387351, 87.59802160424327, 102.58760690413891, 64.8040203219586, 45.638859658869364, 35.68712510553472, 46.1526326413628, 42.7140779305245, 42.656624174929355, 38.719569009883344, 118.34093812283635, 57.98357441981647, 32.304672925905955, 38.74955350161331, 111.78973192676845, 84.38699281542188, 72.43140071353082, 62.57845630239641, 56.29419263821576, 45.86385426016898, 62.069527187855115, 37.90403723066706, 51.55721807646017, 66.6445945515142, 80.98246462361944, 34.99203832791488, 37.72183574584413, 58.98824723833712, 39.90212115600404, 73.34927304520467, 38.70575591904467, 3.548760824217505, 38.813420999667656, 20.858476057434434, 71.03430944525982, 50.4348882246382, 43.64554894452859, 67.39291987673285, 66.45960610252898, 72.49759997309124, 25.943918434239926, 42.58021525752917, 38.3014148100721, 53.79888601113553, 99.51832262440742, 56.52149143305707, 66.19137728687089, 82.1346822658412, 47.50721380717321, 92.25944355932741, 33.85159273755295, 56.686451606103454, 42.196835300566214, 68.41923073482316, 132.94493649923666, 50.702410904972155, 44.062134300239634, 47.37824899741116, 57.42307281194324, 36.821571990756546, 88.45518091840697, 46.46227007777652, 132.7755994065055, 28.621231349858267, 238.34898566930232, 43.92727143310851, 27.997845380754555, 57.459025843998425, 50.92371174608637, 65.99033705614121, 70.44189722910421, 88.63432408556535, 9.616616726460933, 87.93543198317467, 37.76044645666855, 101.44987024478195, 58.29353781196732, 64.59723576645654, 60.28179391955307, 32.99765433692537, 38.047276478135814, 43.52707971530303, 72.45267875443695, 31.6156011981017, 53.34720492444149, 90.18482133477764, 34.23598837513797, 51.19348364688994, 70.02638533384172, 50.585709680437084, 131.79780501390437, 90.24052041241771, 136.91333462516428, 56.721047784014644, 54.2303030705596, 41.74410105424103, 74.23639133615926, 83.65783435400256, 50.165106770999444, 40.123248184181065, 50.90509225513024, 46.3964868425827, 46.569039449481544, 77.15326968296463, 196.7867042236132, 139.46461732201143, 81.13282098052419, 39.06956979240709, 103.36867415574524, 47.50392338882948, 69.84150131035409, 101.05371704440135, 57.888791461046424, 47.20335558783233, 96.64672584861853, 44.976887759056794, 58.057174612215796, 59.9863638898859, 45.13140836621309, 12.622564007942872, 46.34090508733095, 47.92350030266242, 10.558786128720417, 72.97163131874161, 56.676413448998346, 217.28992887521588, 96.23243901539297, 38.582694601444445, 124.84552526159194, 56.207396932944945, 52.69294660460942, 99.95662710219476, 60.336769321953135, 52.53157176364334, 155.298078333903, 90.85006492828505, 36.248917543219235, 50.61933021553778, 47.51198612104027, 48.4720920692254, 53.58252212123689, 48.621029702441305, 45.131387698992455, 45.174224610969205, 77.1900637611584, 79.46377108427771, 58.20720174526986, 50.91569190798426, 169.74039846231219, 51.706052805401846, 52.22271363714883, 45.60870334847906, 47.98717139202123, 14.409423575230251, 59.04951032212936, 50.324107258063364, 67.57296041530604, 69.62781177981084, 82.75352376290782, 112.4461275646527, 55.80498664368203, 51.508589393066565, 66.24637620614037, 56.89231767882717, 53.41824865223853, 176.5712367043482, 57.804071957114296, 78.81055172002513, 144.3324298861058, 47.53009392923205, 36.38396760155702, 46.73943634291367, 63.26813158020861, 109.54154457580425, 87.65870057043986, 70.06230373867318, 74.7200371162448, 70.5597138221116, 120.80613604549868, 68.6226157991827, 39.26658930141194, 81.49199887125957, 66.74988470122157, 125.1239296627308, 107.79457244390291, 39.36686933119677, 43.892032847721865, 99.02730837192178, 54.709120696451045, 65.54539963850299, 45.715776862839554, 80.79309073492126, 66.9531144576852, 56.43134344851399, 108.29804076655668, 51.194358875179866, 109.96415895453192, 13.788940212142865, 64.7634976104482, 44.46079433587535, 45.2371992462639, 52.0702043350904, 90.68862388960179, 39.31555876881965, 141.49460890001214, 93.00733188697336, 52.61237630088471, 52.34082626203474, 61.703368595274554, 117.1538859741898, 119.73631518960947, 167.72041893558153, 39.4849022098719, 65.5534406854431, 83.17901696358636, 61.10278837442334, 104.53233583787066, 70.39195264649366, 45.994418093495035, 97.05544995099409, 48.59227362349289, 13.162225051305796, 82.29821728019661, 60.92920802317213, 88.52460343295883, 97.87295251341482, 60.057592600650594, 62.17054886992021, 96.22657586572929, 40.96645142017313, 80.69541804729167, 55.81378023279333, 20.996133318272992, 60.92776002940662, 39.09215931517099, 56.05541473252577, 48.806580238988275, 51.53395662256053, 82.80630572226555, 71.64694422309297, 46.893142546900656, 10.375914950563311, 43.0976713960905, 60.236048024802514, 67.34468898831297, 72.00596037174179, 43.53383800155532, 53.065361228211394, 171.11199147081751, 45.73809809461049, 46.36543054333735, 59.4351341241743, 97.27436875156337, 57.19354974746135, 55.45822965673569, 67.98066275679098, 153.23937462630292, 62.64784773584174, 74.5812344529155, 67.95679005129729, 61.557574090481666, 39.47192004958602, 178.66434476616965, 68.03041208949703, 43.66227385789698, 69.51183219025661, 42.21775337136035, 101.90221335028467, 48.19443103105172, 48.43230674887109, 46.72588391248215, 11.543257788073417, 46.80635469353427, 32.70347930294541, 49.56048154965827, 40.12351460398011, 14.224163444318316, 59.753779801695146, 58.027849490468604, 56.55772794306697, 37.6965528047249, 58.12231816740636, 99.38738794994063, 78.28911638429953, 127.80614156063254, 80.82035169587873, 86.48069969393359, 23.042984488046006, 120.69888393513253, 82.80955827570907, 35.313456293804094, 49.726238097174885, 52.73348110079853, 66.00690131919691, 9.912285734138024, 48.52406317893619, 40.7610704289889, 116.82661597026535, 109.45529552415228, 38.536615509094, 67.74934790766338, 49.06851413438267, 42.61658347592212, 68.80116966713945, 53.402048544275154, 52.534044381960186, 62.834813392594015, 10.36424878166743, 62.89788872184975, 92.41986889603099, 72.0546886974777, 53.19785888257127, 67.43082932002808, 5.328350060833591, 43.6925415682291, 151.46213230821877, 114.664129312131, 14.072673834586341, 76.2318474711704, 74.08193590262938, 40.300406263052444, 58.8177152911809, 51.20767569634738, 53.400012161610235, 132.85281884015623, 56.023382861443444, 45.11353055848411, 9.984263362000679, 171.70143807833193, 71.50433268987172, 71.35798713204206, 48.63617614366252, 53.49882713636286, 48.13267013956243, 54.72268199017617, 54.314430723791226, 97.26814222684386, 167.3471088616285, 53.94321967125368, 46.67158116213399, 8.299079099626391, 50.45372919603592, 54.68229011164935, 82.03386561324506, 158.13573387799013, 134.36038174374121, 94.93480818009992, 61.5491571481375, 79.34991066503954, 53.357346716554645, 139.00933909397205, 63.51382466203502, 131.35379724015488, 138.26080663001673, 53.86434412429845, 158.76581931216506, 75.99808846542427, 126.81034088227925, 123.22950224363028, 68.76293288143167, 262.0813829758751, 44.569298888436684, 68.8788383462911, 88.47730461274708, 62.20448702003681, 71.22530328779993, 72.77304396373319, 5.510704399228976, 81.42634205957435, 44.30797588972194, 38.66695452163209, 5.649579502143722, 138.83039756608497, 73.98703643548511, 95.17715371420461, 70.31137036805947, 102.18331540216818, 74.43960169452639, 100.26412737157781, 101.0933844974834, 83.91530426062906, 60.62747170125295, 65.89514384593755, 81.25532640806502, 109.16365531124164, 46.072326509901046, 36.62669292335144, 49.72863050914623, 51.150106420203706, 115.87836352150988, 77.15041733203967, 77.45630534434723, 56.61088371358333, 119.63001507384696, 69.02479597217791, 100.53883841125631, 71.0540299540751, 70.33259478013848, 40.87450807914039, 35.588842436052985, 184.1579616234172, 43.36044007641704, 57.963345717839196, 81.60730416228407, 193.62021394191427, 86.89574912690085, 47.39634675586547, 59.222828170874465, 81.9628834258791, 60.33320385207296, 65.63396908675364, 10.633910857774378, 66.95867629238046, 73.36745770183512, 40.7353895721239, 55.34558828174014, 70.52439552975629, 51.38709769725738, 60.57907510920989, 42.830012777067644, 76.32157537402058, 70.81824199750912, 54.83933540556516, 106.13976330275679, 66.23549403664354, 43.01203279462836, 64.38129281557498, 57.22562318158401, 86.76678567288438, 84.2654079518967, 43.941296589668866, 77.79283861473925, 88.00028552048494, 184.6775574020316, 68.10408208304626, 94.61491967856058, 74.31546932540905, 121.72254214040976, 114.47662023017982, 78.07576817823397, 179.49211613125217, 53.80702330434315, 88.24527646296984, 75.53403561011358, 67.25543098362215, 8.943183435716033, 50.727659612094016, 133.37650662326683, 54.904683723648766, 48.63676906497277, 88.02492499118927, 89.30602118248498, 8.392563016387756, 47.69650538399387, 86.37034720888596, 63.449092515184816, 57.925656280866306, 70.45095643625072, 64.15512479856675, 40.559924014610225, 44.983971223917536, 74.59413644558038, 61.5185155997663, 54.47162624169898, 43.89756038877283, 75.04349234653571, 54.01306655015833, 105.32111240349047, 50.10322211148362, 55.2024970541723, 58.46745934838089, 63.43069839993366, 71.48983370849254, 89.19637706812352, 60.93666357178454, 105.92233646057835, 6.953007975892873, 97.804093511876, 47.313098075300516, 42.56397667887682, 53.5121055167081, 131.4745271114379, 65.09212863308369, 11.61121745179167, 58.77297628583139, 62.33013878976661, 43.03829667516636, 36.30334922503967, 63.640182450352995, 71.26828953503606, 64.11345393263223, 80.88082949679357, 51.71259907098031, 83.44040929651152, 52.12102819063755, 147.4380356509542, 52.62679984600366, 152.00629754350496, 164.62740422577582, 53.22941561044456, 59.820901825602405, 108.99784818042917, 36.10411595758472, 71.40104028023781, 66.43352665036211, 132.31863446391125, 140.20851299844736, 52.78729633650634, 7.533573630046856, 62.13982913323741, 73.276640452532, 40.97695748096037, 68.56584615435793, 98.51705222454099, 114.13597942697493, 9.760196216844427, 55.352729947074714, 57.783085200677185, 67.36657238825707, 87.65280868845755, 9.05859469249432, 65.07111290475446, 72.3418251837813, 78.47234403691233, 61.308110711964986, 65.42128064651887, 64.85369874305708, 153.7640940299229, 107.65640685861584, 5.368158544217574, 54.800971824946096, 86.90814083049875, 35.73759951847718, 37.636638835623394, 74.76400555994893, 104.25490878181348, 40.92500894965638, 190.5192844903526, 67.08328345144282, 6.0677920207109, 65.61819948088045, 141.438532452098, 116.58356668568115, 70.81982640942675, 86.89123178503012, 36.26697880131296, 52.264785416500885, 174.4240402059672, 10.483025374169287, 54.59455328066912, 54.785474976323236, 75.40605700795636, 49.11608202028295, 4.4106084030228185, 50.58341289012401, 65.39968536587459, 81.10904679615487, 81.0821002903309, 86.56653802742865, 4.115883296636163, 75.91545209315944, 241.74453972989303, 41.13247293001133, 56.02112728673534, 48.05384495583302, 69.65973707895616, 48.02505508152368, 119.1325305231535, 102.4778155740211, 103.05205365537923, 64.88380029624386, 50.80510461531294, 42.88355021709965, 61.470977020084725, 122.74315788723298, 54.86770199104113, 50.84114455552768, 33.96062064986782, 48.395368245963006, 4.283582547692108, 166.4225718510937, 73.34933878623288, 40.858000969177986, 81.77484636802814, 60.56946558147946, 7.176178398021136, 84.94271970619624, 78.88789162229983, 4.706427186462356, 89.09813093531636, 72.51867556115465, 56.23709085508429, 55.26667886612936, 38.78554344865483, 66.809977114151, 111.62511375350952, 35.799805777453855, 120.48865689560043, 47.549655475035436, 7.494786448902967, 93.00017119835036, 61.27855987891383, 58.1246395689163, 67.69606039678935, 43.329321998054404, 70.19611387704516, 45.69973562492667, 236.3928896795644, 46.08711748766359, 55.4323637126079, 125.70327043915974, 178.96819849353216, 68.6634039968901, 101.60510285270382, 10.695068794323738, 82.74244989654188, 75.32828733364612, 52.52196885359215, 119.8529336891564, 95.10703037276218, 58.56473161268, 49.72343568042289, 84.99392003097826, 122.60844496241755, 55.10205904620841, 392.8598123111764, 49.90721137854303, 8.45631218306583, 49.851956005588015, 49.69136287485437, 108.85248535570922, 77.89607788812673, 53.81688509707613, 93.00619600890205, 73.85142206423176, 62.36990927179324, 41.362241678258336, 76.48290540306189, 53.56318010311284, 37.772221181735084, 58.97029067275863, 74.96174777722527, 115.48103879168455, 42.97068338974291, 134.37494819283916, 78.61156227107604, 95.99754353891441, 38.812867121355815, 72.34266503897067, 86.51147601507634, 51.23921060324104, 76.76800011381032, 49.05932909643334, 101.8627082714484, 56.920008314547566, 73.46180700256683, 104.20677174387764, 98.5138916654795, 49.40964826440717, 73.50914591418024, 200.58597642468072, 89.00306387191394, 76.52050895391046, 57.79115629664022, 55.68572045534194, 239.67652641062242, 46.507498184353025, 110.50218536032153, 96.15059564077929, 49.74498026580406, 62.29283353570816, 54.22346549476095, 55.84473400588336, 47.06986093339287, 123.3583410709414, 91.41084768152936, 4.9905948608100195, 54.01288635223917, 46.825858887229096, 75.52472328300117, 57.213115281894076, 98.69212451666012, 60.681723694399125, 86.62149235319274, 64.6895691788856, 42.223570755873524, 113.96572001387639, 36.818678024887795, 50.66767129937317, 61.784144102650444, 91.64447771956696, 166.08167285494753, 59.95354675385812, 88.8736357547602, 45.63069700411885, 156.68733878009377, 42.09806989960326, 86.43411726888401, 51.60877989268699, 37.72102448242862, 47.39958394827547, 105.93187089169199, 57.485820693021466, 139.38669687211183, 64.36600964348256, 139.85402064840582, 53.73374705794362, 43.979307360399446, 67.9445318793456, 75.81663415048962, 6.477940237090464, 136.61112935246607, 144.4484744943298, 44.11528542797369, 50.76733022833727, 88.69828613346883, 64.57293230346792, 5.294024558169323, 79.0273351975366, 210.00710098655424, 52.0992495921553, 45.83741663817397, 62.54371403061016, 82.01986973469131, 100.22694200948415, 43.88714749758585, 79.09818191633103, 87.94660812782521, 49.56248742742737, 79.41440096810379, 82.61976879790915, 55.02007077968821, 49.21342269082203, 69.7458238629503, 54.21947341126793, 186.9606190287596, 46.235569501169756, 76.3801480075906, 80.597290530286, 82.17225781041162, 66.07758216275562, 37.29655308461, 54.82468852835984, 51.618057513108226, 11.18240702700659, 80.84084981107561, 39.02443229769619, 59.37754916477753, 107.64211519633847, 49.817393787901956, 58.49460954368823, 67.88238714965146, 46.93258947279999, 97.14722886809837, 69.79832839475674, 56.405659534974795, 75.87466768008792, 55.90528449972499, 52.218523807589754, 62.557147812911886, 92.08849425358666, 7.480500680402535, 64.13439853857989, 87.95614080467568, 135.41861192237926, 82.48942273243793, 60.7488418889298, 62.01624716392449, 60.7658820155287, 47.6324202642397, 107.08001165798309, 75.34958733422519, 68.03685168454003, 52.10008299693521, 162.34988665619764, 222.89095731093863, 56.60369389134535, 55.778913660401, 54.023990156109456, 74.90638360302736, 198.30246470643178, 77.09100439569288, 96.81928805813615, 63.135943563870754, 8.899977888795032, 66.98440499741392, 81.0595935132939, 137.50428415512758, 42.388067024804116, 97.3979887571189, 48.872530326034166, 99.05946267817382, 135.6498037862238, 63.02105850074694, 145.83176305047596, 86.4465938782821, 204.4434615837188, 91.51258394758935, 87.4091594432661, 66.69367319236247, 35.02539005157709, 10.91375722968961, 160.13036969391112, 77.7021546659581, 56.22155142860149, 232.21164788652624, 50.16708944171709, 70.62119999632891, 56.76645709155568, 66.49026848628776, 66.8941776788849, 89.62860128457768, 77.91304697554902, 253.76147293359168, 129.9956597864669, 19.071247139437794, 90.80321548372785, 32.33667443357453, 120.69152212647586, 53.4010641505496, 102.69861571250046, 196.81843020725364, 53.17519630973277, 114.26766939191701, 119.40042658165737, 83.55664643279705, 67.85409588077482, 10.340519608030723, 60.41640296812306, 59.238416119880405, 97.9969309348846, 55.70313883126553, 61.67037887938985, 38.50984034958462, 109.55720587655362, 101.09000774316829, 91.63400614026165, 177.84999555614266, 50.57542908267233, 11.831877405819446, 80.79003172687693, 58.60283783020579, 72.95530932401816, 51.76360928060449, 52.334901044362155, 80.43639041581106, 52.098321568007904, 64.42563932497376, 151.76227523262486, 55.43697708248133, 61.20308492260095, 28.087618021154164, 21.727382340657982, 109.29169705890598, 52.42542300764047, 52.42510549397237, 38.678737086369374, 81.95736422668202, 249.31020491837182, 65.95799488083243, 170.76991100730493, 103.61934082185027, 67.70290844803112, 69.85737088537027, 82.9287450831601, 57.056278683966234, 93.75083000459308, 54.441768890910666, 141.916911337182, 68.72101551799122, 49.56439774027633, 64.99907273010507, 55.870912237348776, 98.75665530823025, 58.24834130493659, 12.525481182558284, 54.382794684137025, 90.07727869332344, 67.51165701606789, 104.03724517746168, 53.6451008900408, 63.537652922167545, 57.754180124683764, 103.52613954623338, 103.11569116112061, 57.604022386341775, 68.85077785094597, 118.96241524629053, 80.7264573534448, 83.67963672053385, 114.82011292214096, 110.56489385224423, 129.20293640201845, 14.353895584650068, 59.92859910002737, 127.96509348039585, 61.47891620083969, 114.55591306337558, 70.57868920573108, 104.61382631501748, 56.96932428347318, 54.960457035232416, 75.63306228029089, 217.17554670886412, 46.584471141377406, 81.11189797418572, 46.93544505836479, 183.99598287638239, 93.31697063094839, 69.82438181292362, 110.3394998275943, 130.34472999079387, 89.83638032828232, 55.972557721530016, 54.94624821769081, 181.20926582738392, 57.53865081652353, 45.88766439968928, 12.310142476769434, 64.92307286823774, 26.66424081411822, 58.03237782436778, 59.144336395060385, 140.8354334616216, 48.16387781112998, 76.75304006336793, 75.0032660293663, 111.81558185356124, 66.2296272337867, 141.31435418960092, 97.76991691960461, 68.55297509340915, 65.10095486372535, 111.99517222560065, 132.39063722676522, 59.13045999025403, 56.91289474954233, 51.25684317706616, 51.48579198531454, 204.54173029087488, 68.10715821515385, 80.0553328502837, 63.447703304830355, 173.81402067622133, 57.88854551864448, 63.29411463494907, 92.98938939244138, 16.845091137415316, 95.79410355251095, 44.802460773080114, 72.84010678647958, 79.43898785100838, 57.043863097731766, 63.80508361509534, 66.17968901864067, 47.1426286073357, 41.72772074430934, 187.8039778033721, 57.11639783411555, 28.071450928703246, 9.577961447516321, 190.46653970717313, 59.47659493354791, 115.16059080376651, 48.33812734280414, 58.39381863438972, 8.781149142380295, 247.127287818012, 42.57354370077624, 61.478405000257936, 64.98301418987255, 142.6605772544876, 51.63350700444049, 74.21274938383114, 8.793315937414148, 57.68475834552679, 112.74756838254444, 93.08092914598153, 10.596829754650999, 45.000099232365955, 61.30747814639495, 53.27989179087411, 39.149643371579096, 51.10450349960194, 40.15894831444544, 50.635974054439856, 40.73817145838093, 147.58324328788308, 119.48026818345514, 136.29927675183208, 97.00877586939214, 85.49214830775908, 87.68203874523785, 105.8318654620911, 51.43254262034667, 257.5432999476919, 140.53370317050963, 93.63839998632307, 122.80694470300251, 85.30066619071441, 57.92260664984667, 69.80639742277818, 48.21162149032162, 109.35500218375434, 11.786904945284375, 70.28277356469485, 54.465730538408216, 79.21524679515987, 6.459390096022294, 65.95233518986755, 80.92218645001081, 56.50837124278097, 91.48718922355627, 70.58135639055706, 265.7219075176302, 128.57424138089084, 91.56454992894108, 60.253949811605736, 5.328268912065525, 108.94086763690201, 54.817241870780556, 58.18743170813878, 43.64732557682871, 135.83122319005872, 85.38268183040837, 67.15727415536495, 49.492678379476516, 200.84063048037626, 82.71131089203203, 140.24501128020944, 214.21171662785196, 151.7636486374656, 61.31995395113028, 40.81446681004847, 61.00512750921866, 97.29858099108623, 7.7435392870671915, 62.91309595605582, 56.61380494919728, 95.37035224423832, 44.07966322046615, 39.79559762000984, 51.55595591254373, 115.70179328756736, 26.270463290081466, 70.02254856504378, 48.363176834606456, 83.21729693573424, 79.12184666966827, 58.72102833152302, 59.619608665753624, 91.51560446957406, 58.15010338187861, 123.40307915753307, 80.17289695119942, 84.5496006035815, 68.9496964596954, 58.088622678252854, 174.05225395028026, 128.94692535021923, 47.060913212550076, 69.59690278565274, 50.04033989392471, 81.72744864461197, 63.11188143929784, 67.90504659268169, 132.5266092183081, 46.88826113539379, 64.05842543495845, 82.26180161659859, 73.4546399520216, 67.25411740623741, 37.5665606760813, 91.71395896355422, 69.4837288943816, 52.270052606396845, 65.2507871415101, 77.12477284814305, 67.33658382056892, 187.0240669773952, 64.10917091964961, 71.69183770666562, 65.71563860090627, 94.57008986639087, 35.93112562720872, 199.70675149039158, 5.1232034739261945, 100.679062841855, 88.93529869499893, 75.07666079164488, 135.2677213677407, 240.38787676505754, 221.19791599259995, 86.94969650636232, 66.67158089739694, 113.75397230260758, 88.25635110051653, 101.13005751206711, 67.56633362747331, 71.51328467609756, 82.6751456200513, 134.77179848600485, 71.58475851803739, 117.07546744625257, 36.843374353762314, 94.89416942827351, 82.04900147129904, 73.5885597741083, 55.004443898751354, 131.2479499018124, 100.44405672345455, 79.14124359394876, 116.024630876287, 56.84052723091203, 45.66989464043534, 120.53526017641673, 45.34686416595384, 62.72425474981112, 107.34489625481999, 85.57064456469264, 67.98352190396908, 92.30873800523575, 57.336392952512234, 78.46849242028665, 102.89433906510135, 115.70744327666557, 113.42405245866257, 155.10243041411428, 129.55399946808464, 61.35140592495943, 47.450500305825024, 46.57118053824667, 78.67739845498774, 9.234262578779258, 15.179172850349776, 41.58918791670225, 7.539500606085145, 128.29851330500605, 120.64737899361272, 48.905201414828625, 36.510962141308, 127.29014474653115, 84.8484674212219, 37.82625641075411, 47.26664399374979, 55.708328767463016, 52.70304798796808, 100.36893819879148, 66.94830510262065, 85.70497739523405, 89.85407183303589, 81.342669316438, 49.06000323424421, 95.05936924325471, 7.253721708859535, 60.46278027203516, 70.47442206015192, 61.78528443938956, 196.40006668118872, 71.81308724972587, 96.85499755150349, 73.17491036993239, 56.3895590443987, 73.0332569545063, 135.62913873646517, 106.95663709387361, 132.4536396103402, 50.3733277138087, 54.393220605856925, 121.99101085766033, 108.2579564580014, 104.35994963792129, 79.07888416868131, 82.01292758819119, 77.2373225252642, 67.8324705117757, 62.46029325789678, 226.04447581169, 62.75024130782986, 100.47532636249923, 180.10058936510572, 63.500945923445, 56.42448816625763, 37.185422640929275, 9.462951920674499, 124.35573852750494, 80.87819031579826, 38.22908847341013, 39.054768118889065, 60.45154529735426,</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>116.6561097002029</v>
+      </c>
+      <c r="S56" t="n">
+        <v>91.42631236766378</v>
+      </c>
+      <c r="T56" t="n">
+        <v>100</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>[143.48963928222656, 326.1622619628906, 69.28093719482422, 92.43937683105469, 143.802001953125, 118.70943450927734, 185.10617065429688, 40.069801330566406, 82.00274658203125, 114.99384307861328, 86.00995635986328, 36.8582649230957, 65.27339935302734, 103.33013916015625, 10.834807395935059, 130.8031463623047, 89.24749755859375, 291.50189208984375, 100.2730712890625, 325.65728759765625, 176.21511840820312, 130.5067596435547, 90.04840087890625, 44.581268310546875, 164.7112579345703, 47.827125549316406, 82.00736999511719, 51.93645477294922, 59.57971954345703, 83.8161849975586, 82.53952026367188, 70.61274719238281, 52.45607376098633, 178.52223205566406, 103.54358673095703, 94.51954650878906, 72.3996810913086, 154.10768127441406, 77.8081283569336, 331.55389404296875, 65.15716552734375, 299.51129150390625, 14.877571105957031, 139.9371337890625, 54.557743072509766, 62.05116653442383, 11.47998046875, 80.88436126708984, 59.23856735229492, 339.4112243652344, 10.88602352142334, 72.44685363769531, 108.35030364990234, 72.33270263671875, 60.58228302001953, 88.6363296508789, 72.11585235595703, 81.46212768554688, 178.194091796875, 89.84587860107422, 86.3440933227539, 94.31182098388672, 119.1676025390625, 68.55699920654297, 90.58576965332031, 64.05364990234375, 281.7703552246094, 125.21050262451172, 62.515907287597656, 6.454470157623291, 195.3822021484375, 79.83858489990234, 83.45240783691406, 76.71018981933594, 389.5791015625, 72.66000366210938, 129.28221130371094, 512.9075317382812, 153.90965270996094, 67.89747619628906, 79.28311920166016, 49.56065368652344, 83.87783813476562, 99.24405670166016, 233.8200225830078, 271.23736572265625, 62.70868682861328, 45.7745361328125, 44.08491516113281, 45.093536376953125, 119.03602600097656, 86.1363754272461, 134.13424682617188, 8.734367370605469, 63.46535110473633, 56.75837707519531, 359.3381652832031, 89.79326629638672, 183.5789337158203, 122.26351928710938]</t>
         </is>
       </c>
     </row>
